--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -876,7 +876,7 @@
     <t xml:space="preserve">Seleccion, cupos por formato, costo comprometido por creador (congelado)</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4 escribio la primera fila de campaign_creators y la protegio; falta el compromiso economico</t>
+    <t xml:space="preserve">docs/fase-7/7.5. DEC-103 a DEC-105. BR-CAMPAIGN-005 nombraba un dato que no existia. Cupos por mercado siguen siendo objetivo, no tope</t>
   </si>
   <si>
     <t xml:space="preserve">7.6</t>
@@ -885,7 +885,7 @@
     <t xml:space="preserve">Invitaciones: envio, expiracion, aceptacion, rechazo con motivo, preguntas</t>
   </si>
   <si>
-    <t xml:space="preserve">Tabla invitations lista. El envio depende de 4.9</t>
+    <t xml:space="preserve">BLOQUEADA por F4.9 (correo). El monto ya se fija y se congela (7.5); lo que falta es enviar</t>
   </si>
   <si>
     <t xml:space="preserve">7.7</t>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(Actividades!$H$2:$H$164,Actividades!$I$2:$I$164)/SUM(Actividades!$I$2:$I$164),0)</f>
-        <v>0.216049382716049</v>
+        <v>0.222222222222222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">IFERROR(SUMPRODUCT($B$22:$B$25,$C$22:$C$25)/SUM($C$22:$C$25),0)</f>
-        <v>0.167426166208648</v>
+        <v>0.171391797404947</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2435,11 +2435,11 @@
       </c>
       <c r="B13" s="8" t="n">
         <f aca="false">COUNTIF(Actividades!$G$2:$G$164,$A13)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">IFERROR($B13/COUNTA(Actividades!$A$2:$A$164),0)</f>
-        <v>0.165644171779141</v>
+        <v>0.171779141104294</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2461,11 +2461,11 @@
       </c>
       <c r="B15" s="8" t="n">
         <f aca="false">COUNTIF(Actividades!$G$2:$G$164,$A15)</f>
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C15" s="9" t="n">
         <f aca="false">IFERROR($B15/COUNTA(Actividades!$A$2:$A$164),0)</f>
-        <v>0.717791411042945</v>
+        <v>0.705521472392638</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2474,11 +2474,11 @@
       </c>
       <c r="B16" s="8" t="n">
         <f aca="false">COUNTIF(Actividades!$G$2:$G$164,$A16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">IFERROR($B16/COUNTA(Actividades!$A$2:$A$164),0)</f>
-        <v>0.0122699386503067</v>
+        <v>0.0184049079754601</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="B23" s="9" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Actividades!$B$2:$B$164=$A23)*Actividades!$H$2:$H$164*Actividades!$I$2:$I$164)/SUMPRODUCT((Actividades!$B$2:$B$164=$A23)*Actividades!$I$2:$I$164),0)</f>
-        <v>0.176470588235294</v>
+        <v>0.191176470588235</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>12</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E23" s="8" t="n">
         <f aca="false">SUMPRODUCT((Actividades!$B$2:$B$164=$A23)*(Actividades!$G$2:$G$164="Terminado"))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C36" s="9" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Actividades!$C$2:$C$164=$A36)*Actividades!$H$2:$H$164*Actividades!$I$2:$I$164)/SUMPRODUCT((Actividades!$C$2:$C$164=$A36)*Actividades!$I$2:$I$164),0)</f>
-        <v>0.392857142857143</v>
+        <v>0.464285714285714</v>
       </c>
       <c r="D36" s="8" t="n">
         <f aca="false">COUNTIF(Actividades!$C$2:$C$164,$A36)</f>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="E36" s="8" t="n">
         <f aca="false">SUMPRODUCT((Actividades!$C$2:$C$164=$A36)*(Actividades!$G$2:$G$164="Terminado"))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5495,7 +5495,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="21" t="n">
         <v>65</v>
       </c>
@@ -5515,11 +5515,11 @@
         <v>282</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H66" s="25" t="n">
         <f aca="false">IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G66,Config!$A$3:$A$8,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="26" t="n">
         <f aca="false">IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G66,Config!$A$3:$A$8,0)),0)</f>
@@ -5549,7 +5549,7 @@
         <v>285</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H67" s="25" t="n">
         <f aca="false">IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G67,Config!$A$3:$A$8,0)),0)</f>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -621,7 +621,7 @@
     <t xml:space="preserve">Colas, scheduler, workers, Horizon</t>
   </si>
   <si>
-    <t xml:space="preserve">Las tablas jobs existen (esqueleto de Laravel); no hay ni un job propio</t>
+    <t xml:space="preserve">F4.9 estreno la cola: EnviarCorreo es el primer job propio, con QUEUE_CONNECTION=database. Faltan scheduler, supervisor y panel</t>
   </si>
   <si>
     <t xml:space="preserve">4.9</t>
@@ -630,7 +630,7 @@
     <t xml:space="preserve">Email: plantillas en BD con idioma/version/variables + Email Log + reintentos</t>
   </si>
   <si>
-    <t xml:space="preserve">Bloquea 4.1 (recuperacion), 5.9 (enlace de contrasena) y T-10</t>
+    <t xml:space="preserve">docs/fase-4/4.12-CORREO.md. DEC-106 a DEC-108. Adelantada porque bloqueaba 7.6, 5.9, 4.1 y T-10. Falta la cuenta de SMTP (Q-20)</t>
   </si>
   <si>
     <t xml:space="preserve">4.10</t>
@@ -885,7 +885,7 @@
     <t xml:space="preserve">Invitaciones: envio, expiracion, aceptacion, rechazo con motivo, preguntas</t>
   </si>
   <si>
-    <t xml:space="preserve">BLOQUEADA por F4.9 (correo). El monto ya se fija y se congela (7.5); lo que falta es enviar</t>
+    <t xml:space="preserve">Desbloqueada: F4.9 cerrada. El monto ya se fija y se congela (7.5)</t>
   </si>
   <si>
     <t xml:space="preserve">7.7</t>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(Actividades!$H$2:$H$164,Actividades!$I$2:$I$164)/SUM(Actividades!$I$2:$I$164),0)</f>
-        <v>0.222222222222222</v>
+        <v>0.231481481481481</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">IFERROR(SUMPRODUCT($B$22:$B$25,$C$22:$C$25)/SUM($C$22:$C$25),0)</f>
-        <v>0.171391797404947</v>
+        <v>0.178931714613699</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2435,11 +2435,11 @@
       </c>
       <c r="B13" s="8" t="n">
         <f aca="false">COUNTIF(Actividades!$G$2:$G$164,$A13)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">IFERROR($B13/COUNTA(Actividades!$A$2:$A$164),0)</f>
-        <v>0.171779141104294</v>
+        <v>0.177914110429448</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2448,11 +2448,11 @@
       </c>
       <c r="B14" s="8" t="n">
         <f aca="false">COUNTIF(Actividades!$G$2:$G$164,$A14)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">IFERROR($B14/COUNTA(Actividades!$A$2:$A$164),0)</f>
-        <v>0.098159509202454</v>
+        <v>0.104294478527607</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2461,11 +2461,11 @@
       </c>
       <c r="B15" s="8" t="n">
         <f aca="false">COUNTIF(Actividades!$G$2:$G$164,$A15)</f>
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C15" s="9" t="n">
         <f aca="false">IFERROR($B15/COUNTA(Actividades!$A$2:$A$164),0)</f>
-        <v>0.705521472392638</v>
+        <v>0.699386503067485</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2474,11 +2474,11 @@
       </c>
       <c r="B16" s="8" t="n">
         <f aca="false">COUNTIF(Actividades!$G$2:$G$164,$A16)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">IFERROR($B16/COUNTA(Actividades!$A$2:$A$164),0)</f>
-        <v>0.0184049079754601</v>
+        <v>0.0122699386503067</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Actividades!$B$2:$B$164=$A22)*Actividades!$H$2:$H$164*Actividades!$I$2:$I$164)/SUMPRODUCT((Actividades!$B$2:$B$164=$A22)*Actividades!$I$2:$I$164),0)</f>
-        <v>0.578947368421053</v>
+        <v>0.618421052631579</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>8.5</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="E22" s="8" t="n">
         <f aca="false">SUMPRODUCT((Actividades!$B$2:$B$164=$A22)*(Actividades!$G$2:$G$164="Terminado"))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C33" s="9" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Actividades!$C$2:$C$164=$A33)*Actividades!$H$2:$H$164*Actividades!$I$2:$I$164)/SUMPRODUCT((Actividades!$C$2:$C$164=$A33)*Actividades!$I$2:$I$164),0)</f>
-        <v>0.40625</v>
+        <v>0.5</v>
       </c>
       <c r="D33" s="8" t="n">
         <f aca="false">COUNTIF(Actividades!$C$2:$C$164,$A33)</f>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="E33" s="8" t="n">
         <f aca="false">SUMPRODUCT((Actividades!$C$2:$C$164=$A33)*(Actividades!$G$2:$G$164="Terminado"))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4453,7 +4453,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="n">
         <v>34</v>
       </c>
@@ -4473,11 +4473,11 @@
         <v>197</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" s="25" t="n">
         <f aca="false">IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G35,Config!$A$3:$A$8,0)),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I35" s="26" t="n">
         <f aca="false">IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G35,Config!$A$3:$A$8,0)),0)</f>
@@ -4507,11 +4507,11 @@
         <v>200</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H36" s="25" t="n">
         <f aca="false">IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G36,Config!$A$3:$A$8,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="26" t="n">
         <f aca="false">IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G36,Config!$A$3:$A$8,0)),0)</f>
@@ -5549,7 +5549,7 @@
         <v>285</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H67" s="25" t="n">
         <f aca="false">IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G67,Config!$A$3:$A$8,0)),0)</f>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -4992,7 +4992,7 @@
       </c>
       <c r="G67" s="23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="H67" s="24">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="J67" s="22" t="inlineStr">
         <is>
-          <t>SIGUIENTE ITERACION PROPUESTA. Ya no tiene nada delante: 7.4 deja la lista corta, 7.5 el monto y F4.9 el correo. Decision pendiente: que pasa con el cupo cuando una invitacion caduca</t>
+          <t>docs/fase-7/7.6-INVITACIONES.md. DEC-119 a DEC-123. Enlace de un solo uso, plazo por campana, rechazo con motivo y reinvitacion con constancia. Las PREGUNTAS quedan fuera: T-38</t>
         </is>
       </c>
     </row>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -3009,7 +3009,7 @@
       </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>docs/fase-5/5.9-ENLACE-DE-CONTRASENA.md. DEC-113 a DEC-118. Recuperacion por enlace de 1 h, misma respuesta exista o no el correo, URL sin el token dentro. Falta la verificacion de correo</t>
+          <t>docs/fase-5/5.9 y docs/fase-7/7.6b. DEC-113 a DEC-118 y DEC-126. Recuperacion por enlace, misma respuesta exista o no el correo, URL sin token. Desde 7.6b tampoco se teclea la del equipo (BR-SEC-004 cerrada). Falta la verificacion de correo</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="J68" s="22" t="inlineStr">
         <is>
-          <t>La pantalla mas usada del sistema, segun el roadmap</t>
+          <t>SIGUIENTE ITERACION PROPUESTA. La pantalla mas usada del sistema, segun el roadmap. Ya no tiene nada delante</t>
         </is>
       </c>
     </row>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -5040,7 +5040,7 @@
       </c>
       <c r="G68" s="23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="H68" s="24">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="J68" s="22" t="inlineStr">
         <is>
-          <t>SIGUIENTE ITERACION PROPUESTA. La pantalla mas usada del sistema, segun el roadmap. Ya no tiene nada delante</t>
+          <t>docs/fase-7/7.7-SEGUIMIENTO.md. DEC-127 y DEC-128. Embudo, cupo por mercado (cubierto = aceptado, no invitado), dinero con el margen detras de su permiso, y cuatro alertas</t>
         </is>
       </c>
     </row>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -691,7 +691,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -755,7 +754,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -870,7 +868,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -993,7 +990,6 @@
         <v/>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -1460,7 +1456,6 @@
         <v/>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
@@ -5360,7 +5355,7 @@
       </c>
       <c r="G75" s="23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="H75" s="24">
@@ -5373,7 +5368,7 @@
       </c>
       <c r="J75" s="22" t="inlineStr">
         <is>
-          <t>Tablas deliverables y deliverable_versions disenadas en 2.12</t>
+          <t>docs/fase-8/8.1-ENTREGABLES.md. DEC-129 a DEC-132. Se generan solos al aceptar, del brief EFECTIVO del mercado (N-03). Enlace https obligatorio + imagen opcional. Si faltan los hashtags del brief no se envia y se dice cuales. Portal del creador (/mis-entregas) con creator.portal, primer permiso de ambito EXTERNAL. 32 pruebas.</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5403,7 @@
       </c>
       <c r="G76" s="23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="H76" s="24">
@@ -5421,7 +5416,7 @@
       </c>
       <c r="J76" s="22" t="inlineStr">
         <is>
-          <t>Disenado en 2.12</t>
+          <t>docs/fase-8/8.2-VERSION-VIGENTE.md. DEC-137 y DEC-138. El append-only es de 8.1 (uq_dv_number con la fila bloqueada); 8.2 anade el puntero a la version APROBADA con clave ajena COMPUESTA --garantiza que la version es de ESE entregable-- y la reapertura con motivo de lista cerrada y firma, que no deshace nada. Ademas tg_dv_entregable_abierto: el veto de «no se entrega sobre algo cerrado» vivia en el servicio desde 8.1 y la base no lo conocia (T-47).</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5451,7 @@
       </c>
       <c r="G77" s="23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="H77" s="24">
@@ -5467,7 +5462,11 @@
         <f>IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G77,Config!$A$3:$A$8,0)),0)</f>
         <v/>
       </c>
-      <c r="J77" s="22" t="inlineStr"/>
+      <c r="J77" s="22" t="inlineStr">
+        <is>
+          <t>docs/fase-8/8.3-REVISION.md. DEC-133 a DEC-136. Bandeja GLOBAL ordenada por lo que lleva mas esperando. Solo las rondas del CLIENTE cuentan y son POR ENTREGABLE (el contador estaba en campaign_creators). Pasarse bloquea y exige decidir si se cobra o se absorbe, firmado. Tres permisos: content.review, content.approve y content.extra_round. tg_cvw_inmutable cierra el append-only que 2.12 afirmaba sin impedir nada. 30 pruebas.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="20" t="n">
@@ -5500,7 +5499,7 @@
       </c>
       <c r="G78" s="23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="H78" s="24">
@@ -5513,7 +5512,7 @@
       </c>
       <c r="J78" s="22" t="inlineStr">
         <is>
-          <t>included_revision_rounds ya se guarda en la campana</t>
+          <t>included_revision_rounds se cuenta y se impone desde 8.3, por entregable y solo con las rondas del cliente. Queda el limite duro: hoy se puede pasar tantas veces como haga falta mientras se decida y se firme cada una.</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5591,7 @@
       </c>
       <c r="G80" s="23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="H80" s="24">
@@ -5603,7 +5602,11 @@
         <f>IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G80,Config!$A$3:$A$8,0)),0)</f>
         <v/>
       </c>
-      <c r="J80" s="22" t="inlineStr"/>
+      <c r="J80" s="22" t="inlineStr">
+        <is>
+          <t>docs/fase-8/8.6-PUBLICACION.md. DEC-139 a DEC-141. El creador pega el enlace desde su portal y el equipo puede hacerlo por el; solo se publica lo APROBADO y esa version (snapshot con clave ajena compuesta). La red se deduce del enlace con platforms.url_pattern y tiene que ser la del brief. La huella normaliza la URL para que uq_pub_fingerprint sirva de algo. 31 pruebas. La PROGRAMACION queda fuera: hoy se registra lo ya publicado.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="20" t="n">

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G81" s="23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="H81" s="24">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="J81" s="22" t="inlineStr">
         <is>
-          <t>Tabla publication_evidence disenada</t>
+          <t>docs/fase-8/8.7-EVIDENCIA.md. DEC-142 a DEC-144. La evidencia es una CAPTURA y no una comprobacion HTTP: Instagram y TikTok responden igual a un post vivo que a un bloqueo, y de verified cuelga el pago. Permiso propio content.verify. Si el post no esta, el entregable vuelve al CREADOR y se le avisa. permanence_until se calcula al verificar. T-50: una rechazada bloqueaba su propio enlace (columna puerta viva_gate, la decimoquinta). 21 pruebas.</t>
         </is>
       </c>
     </row>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="1623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="1635">
   <si>
     <t xml:space="preserve">LATAM Social - avance del alcance completo</t>
   </si>
@@ -1314,10 +1314,10 @@
     <t xml:space="preserve">9.19b</t>
   </si>
   <si>
-    <t xml:space="preserve">El aviso por correo de la reaceptacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q-46 empieza por «les llega un correo». Se aparto por §2: sin el correo 9.19 ya funciona --el creador se entera al entrar y los tres escalones se aplican-- y el equipo lo ve en el panel de configuracion. La bandeja interna es 8.9.</t>
+    <t xml:space="preserve">El aviso por correo de la reaceptacion, y la frontera Core/Creator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31. Al publicar una version DE FONDO sale un correo a cada creador activo, y el texto dice que pasa despues. Core levanta un evento y Creator escucha, asi que un SMTP caido no tumba la publicacion (DEC-220). Cada envio en su propio try (DEC-222). Y corrige T-74, que era mio: Terminos leia creators desde Core, la frontera rota que deptrac no ve. Hay una prueba que lee el codigo fuente porque no hay herramienta que lo cace. DEC-220 a DEC-222. 20 pruebas. Sin migracion. docs/fase-9/9.19b-EL-AVISO-POR-CORREO.md</t>
   </si>
   <si>
     <t xml:space="preserve">9.14b</t>
@@ -2427,6 +2427,15 @@
     <t xml:space="preserve">Cobertura::abiertaEnPais() mira solo las coberturas abiertas; el disparador de no-solape mira todas. Se da de baja una sociedad --DEC-081 cierra sus coberturas con la fecha de la baja-- y al declarar la del sucesor ESE MISMO DIA la pantalla cree que el pais esta libre, no cierra nada, y el INSERT sale como un 45000 crudo. La prueba que ya existia no lo vio porque usa el dia SIGUIENTE al cierre, que es el caso que funciona. Arreglado con queTapaLaFecha() y un veto con palabras y con la fecha en la que si se puede. Se comprobo que la prueba de regresion falla sin el arreglo.</t>
   </si>
   <si>
+    <t xml:space="preserve">T-74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESUELTA (2026-08-31, iteracion 9.19b) el dia siguiente a abrirse. Core dejo de ser Core, y lo hice yo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En 9.19, Core\Services\Terminos leia creators.activated_at y recorria creators entera. deptrac dice Core: [Framework, Shared], y una consulta a la tabla de otro modulo es una frontera rota que deptrac NO VE: no hay clase importada, solo un nombre de tabla dentro de un DB::table(). Es exactamente la trampa contra la que avisa la cabecera del Vigilante, escrita en 9.15, y cai en ella cuatro iteraciones despues. No la vio ninguna de las seis puertas porque no hay herramienta que la vea, asi que el arreglo trae una prueba que LEE EL CODIGO FUENTE. De paso, el recuento hacia una consulta por creador; ahora es una.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Preguntas de negocio (Q-XX). Una pregunta abierta es trabajo que NO se puede hacer hasta que alguien decida. Las respondidas conservan la pregunta original detrás de la respuesta. Fuente: docs/05-DECISION-LOG.md.</t>
   </si>
   <si>
@@ -2937,10 +2946,37 @@
     <t xml:space="preserve">Detalle y por qué</t>
   </si>
   <si>
+    <t xml:space="preserve">DEC-220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decidida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core levanta un evento; Creator escucha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEC-221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEC-222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un correo que falla no deja sin avisar a los demas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DEC-216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decidida</t>
   </si>
   <si>
     <t xml:space="preserve">Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
@@ -5822,7 +5858,7 @@
       </c>
       <c r="B6" s="6" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(Actividades!$H$2:$H$174,Actividades!$I$2:$I$174)/SUM(Actividades!$I$2:$I$174),0)</f>
-        <v>0.401162790697674</v>
+        <v>0.406976744186047</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5831,7 +5867,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">IFERROR(SUMPRODUCT($B$22:$B$25,$C$22:$C$25)/SUM($C$22:$C$25),0)</f>
-        <v>0.276375377011965</v>
+        <v>0.279704548880463</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5874,11 +5910,11 @@
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNTIF(Actividades!$G$2:$G$174,$A13)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">IFERROR($B13/COUNTA(Actividades!$A$2:$A$174),0)</f>
-        <v>0.358381502890173</v>
+        <v>0.364161849710983</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5900,11 +5936,11 @@
       </c>
       <c r="B15" s="1" t="n">
         <f aca="false">COUNTIF(Actividades!$G$2:$G$174,$A15)</f>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" s="9" t="n">
         <f aca="false">IFERROR($B15/COUNTA(Actividades!$A$2:$A$174),0)</f>
-        <v>0.554913294797688</v>
+        <v>0.549132947976879</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5994,7 +6030,7 @@
       </c>
       <c r="B23" s="9" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Actividades!$B$2:$B$174=$A23)*Actividades!$H$2:$H$174*Actividades!$I$2:$I$174)/SUMPRODUCT((Actividades!$B$2:$B$174=$A23)*Actividades!$I$2:$I$174),0)</f>
-        <v>0.54320987654321</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>12</v>
@@ -6005,7 +6041,7 @@
       </c>
       <c r="E23" s="1" t="n">
         <f aca="false">SUMPRODUCT((Actividades!$B$2:$B$174=$A23)*(Actividades!$G$2:$G$174="Terminado"))</f>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6259,7 +6295,7 @@
       </c>
       <c r="C38" s="9" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Actividades!$C$2:$C$174=$A38)*Actividades!$H$2:$H$174*Actividades!$I$2:$I$174)/SUMPRODUCT((Actividades!$C$2:$C$174=$A38)*Actividades!$I$2:$I$174),0)</f>
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="D38" s="1" t="n">
         <f aca="false">COUNTIF(Actividades!$C$2:$C$174,$A38)</f>
@@ -6267,7 +6303,7 @@
       </c>
       <c r="E38" s="1" t="n">
         <f aca="false">SUMPRODUCT((Actividades!$C$2:$C$174=$A38)*(Actividades!$G$2:$G$174="Terminado"))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6545,7 +6581,7 @@
       </c>
       <c r="B62" s="1" t="n">
         <f aca="false">COUNTIF(Decisiones!$B$3:$B$201,"Propuesta")</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>199</v>
@@ -10580,11 +10616,11 @@
         <v>427</v>
       </c>
       <c r="G110" s="26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H110" s="27" t="n">
         <f aca="false">IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G110,Config!$A$3:$A$8,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" s="28" t="n">
         <f aca="false">IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G110,Config!$A$3:$A$8,0)),0)</f>
@@ -12731,7 +12767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="23" t="n">
         <v>173</v>
       </c>
@@ -12806,7 +12842,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -14198,7 +14234,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="33" t="s">
         <v>795</v>
       </c>
@@ -14217,6 +14253,27 @@
       </c>
       <c r="G67" s="16" t="s">
         <v>797</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="33" t="s">
+        <v>798</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>634</v>
+      </c>
+      <c r="C68" s="34"/>
+      <c r="D68" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="F68" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -14270,7 +14327,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -14290,7 +14347,7 @@
         <v>576</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E2" s="32" t="s">
         <v>578</v>
@@ -14304,623 +14361,623 @@
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B3" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C3" s="34"/>
       <c r="D3" s="16" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B4" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C4" s="34"/>
       <c r="D4" s="16" t="s">
+        <v>809</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>810</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>806</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>807</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>803</v>
-      </c>
       <c r="G4" s="16" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="B5" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C5" s="34"/>
       <c r="D5" s="16" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B6" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="16" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="16" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="16" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B9" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C9" s="34"/>
       <c r="D9" s="16" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>318</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C10" s="34"/>
       <c r="D10" s="16" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>324</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C11" s="34"/>
       <c r="D11" s="16" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>321</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C12" s="34"/>
       <c r="D12" s="16" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C13" s="34"/>
       <c r="D13" s="16" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="F13" s="16" t="s">
         <v>757</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C14" s="34"/>
       <c r="D14" s="16" t="s">
+        <v>846</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>843</v>
       </c>
-      <c r="E14" s="16" t="s">
-        <v>840</v>
-      </c>
       <c r="F14" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C15" s="34"/>
       <c r="D15" s="16" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>757</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C16" s="34"/>
       <c r="D16" s="16" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>757</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B17" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C17" s="34"/>
       <c r="D17" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C19" s="34"/>
       <c r="D19" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F19" s="16" t="s">
         <v>757</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C20" s="34"/>
       <c r="D20" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C21" s="34"/>
       <c r="D21" s="16" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="33" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C22" s="34"/>
       <c r="D22" s="16" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C23" s="34"/>
       <c r="D23" s="16" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="33" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C24" s="34"/>
       <c r="D24" s="16" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="B25" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C25" s="34"/>
       <c r="D25" s="16" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E25" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B26" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C26" s="34"/>
       <c r="D26" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="33" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C27" s="34"/>
       <c r="D27" s="16" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="33" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B28" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C28" s="34"/>
       <c r="D28" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="33" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B29" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C29" s="34"/>
       <c r="D29" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F29" s="16" t="s">
         <v>757</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="33" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B30" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C30" s="34"/>
       <c r="D30" s="16" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="33" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C31" s="34"/>
       <c r="D31" s="16" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="33" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B32" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C32" s="34"/>
       <c r="D32" s="16" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>636</v>
@@ -14929,593 +14986,593 @@
         <v>757</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="33" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B33" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C33" s="34"/>
       <c r="D33" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="33" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C34" s="34"/>
       <c r="D34" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="33" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B35" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C35" s="34"/>
       <c r="D35" s="16" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="E35" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="33" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B36" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C36" s="34"/>
       <c r="D36" s="16" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="33" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B37" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C37" s="34"/>
       <c r="D37" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F37" s="16" t="s">
         <v>757</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B38" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C38" s="34"/>
       <c r="D38" s="16" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E38" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G38" s="16"/>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="33" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C39" s="34"/>
       <c r="D39" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="33" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C40" s="34"/>
       <c r="D40" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="33" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B41" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C41" s="34"/>
       <c r="D41" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="33" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B42" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C42" s="34"/>
       <c r="D42" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="33" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="B43" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="16" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="33" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="B44" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C44" s="34"/>
       <c r="D44" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="33" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B45" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C45" s="34"/>
       <c r="D45" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="33" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B46" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C46" s="34"/>
       <c r="D46" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="33" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B47" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C47" s="34"/>
       <c r="D47" s="16" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E47" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="33" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B48" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C48" s="34"/>
       <c r="D48" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="33" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B49" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C49" s="34"/>
       <c r="D49" s="16" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="E49" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="33" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B50" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C50" s="34"/>
       <c r="D50" s="16" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="33" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="B51" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C51" s="34"/>
       <c r="D51" s="16" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="E51" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="33" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B52" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C52" s="34"/>
       <c r="D52" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="33" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B53" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C53" s="34"/>
       <c r="D53" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F53" s="16" t="s">
         <v>757</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="33" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B54" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C54" s="34"/>
       <c r="D54" s="16" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="E54" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="33" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B55" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C55" s="34"/>
       <c r="D55" s="16" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E55" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="33" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B56" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C56" s="34"/>
       <c r="D56" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F56" s="16" t="s">
         <v>757</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="33" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B57" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C57" s="34"/>
       <c r="D57" s="16" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="E57" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="33" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="B58" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C58" s="34"/>
       <c r="D58" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="33" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B59" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C59" s="34"/>
       <c r="D59" s="16" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E59" s="16" t="s">
         <v>636</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="33" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="B60" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C60" s="34"/>
       <c r="D60" s="16" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="F60" s="16" t="s">
         <v>757</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
     </row>
   </sheetData>
@@ -15555,7 +15612,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F222"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -15568,7 +15625,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -15587,2773 +15644,2779 @@
         <v>576</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C3" s="34"/>
       <c r="D3" s="16" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="B4" s="34" t="s">
         <v>972</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>969</v>
       </c>
       <c r="C4" s="34"/>
       <c r="D4" s="16" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C5" s="34"/>
       <c r="D5" s="16" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="16" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>422</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="16" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="16" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C9" s="34"/>
       <c r="D9" s="16" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C10" s="34"/>
       <c r="D10" s="16" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>419</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C11" s="34"/>
       <c r="D11" s="16" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C12" s="34"/>
       <c r="D12" s="16" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C13" s="34"/>
       <c r="D13" s="16" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C14" s="34"/>
       <c r="D14" s="16" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C15" s="34"/>
       <c r="D15" s="16" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C16" s="34"/>
       <c r="D16" s="16" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C17" s="34"/>
       <c r="D17" s="16" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>408</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="16" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C19" s="34"/>
       <c r="D19" s="16" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C20" s="34"/>
       <c r="D20" s="16" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C21" s="34"/>
       <c r="D21" s="16" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>404</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="33" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C22" s="34"/>
       <c r="D22" s="16" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>404</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C23" s="34"/>
       <c r="D23" s="16" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>404</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="33" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C24" s="34"/>
       <c r="D24" s="16" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C25" s="34"/>
       <c r="D25" s="16" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C26" s="34"/>
       <c r="D26" s="16" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>524</v>
+        <v>404</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="33" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C27" s="34"/>
       <c r="D27" s="16" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="33" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C28" s="34"/>
       <c r="D28" s="16" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="33" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C29" s="34"/>
       <c r="D29" s="16" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>401</v>
+        <v>524</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="33" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C30" s="34"/>
       <c r="D30" s="16" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>401</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="33" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C31" s="34"/>
       <c r="D31" s="16" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>401</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="33" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>969</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>583</v>
-      </c>
+        <v>972</v>
+      </c>
+      <c r="C32" s="34"/>
       <c r="D32" s="16" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>401</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="33" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C33" s="34"/>
       <c r="D33" s="16" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="33" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C34" s="34"/>
       <c r="D34" s="16" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="33" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>969</v>
-      </c>
-      <c r="C35" s="34"/>
+        <v>972</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>583</v>
+      </c>
       <c r="D35" s="16" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="33" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C36" s="34"/>
       <c r="D36" s="16" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>398</v>
+        <v>429</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="33" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C37" s="34"/>
       <c r="D37" s="16" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>383</v>
+        <v>429</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C38" s="34"/>
       <c r="D38" s="16" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="33" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C39" s="34"/>
       <c r="D39" s="16" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="33" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C40" s="34"/>
       <c r="D40" s="16" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="33" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="B41" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C41" s="34"/>
       <c r="D41" s="16" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="33" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C42" s="34"/>
       <c r="D42" s="16" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="33" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="16" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="33" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C44" s="34"/>
       <c r="D44" s="16" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="33" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C45" s="34"/>
       <c r="D45" s="16" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="33" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C46" s="34"/>
       <c r="D46" s="16" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="33" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C47" s="34"/>
       <c r="D47" s="16" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="33" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C48" s="34"/>
       <c r="D48" s="16" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="E48" s="16" t="s">
         <v>371</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="33" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="B49" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C49" s="34"/>
       <c r="D49" s="16" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="33" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C50" s="34"/>
       <c r="D50" s="16" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="33" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="B51" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C51" s="34"/>
       <c r="D51" s="16" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="33" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="B52" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C52" s="34"/>
       <c r="D52" s="16" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="33" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C53" s="34"/>
       <c r="D53" s="16" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="33" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C54" s="34"/>
       <c r="D54" s="16" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="33" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="B55" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C55" s="34"/>
       <c r="D55" s="16" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="33" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C56" s="34"/>
       <c r="D56" s="16" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="E56" s="16" t="s">
         <v>362</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="33" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="B57" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C57" s="34"/>
       <c r="D57" s="16" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="33" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C58" s="34"/>
       <c r="D58" s="16" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="33" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="B59" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C59" s="34"/>
       <c r="D59" s="16" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="33" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="B60" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C60" s="34"/>
       <c r="D60" s="16" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="E60" s="16" t="s">
         <v>359</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="33" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="B61" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C61" s="34"/>
       <c r="D61" s="16" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="33" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="B62" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C62" s="34"/>
       <c r="D62" s="16" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="33" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="B63" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C63" s="34"/>
       <c r="D63" s="16" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="33" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="B64" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C64" s="34"/>
       <c r="D64" s="16" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="E64" s="16" t="s">
         <v>356</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="33" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="B65" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C65" s="34"/>
       <c r="D65" s="16" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="33" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="B66" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C66" s="34"/>
       <c r="D66" s="16" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="33" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B67" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C67" s="34"/>
       <c r="D67" s="16" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="33" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="B68" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C68" s="34"/>
       <c r="D68" s="16" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="33" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="B69" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C69" s="34"/>
       <c r="D69" s="16" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="33" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="B70" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C70" s="34"/>
       <c r="D70" s="16" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="33" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C71" s="34"/>
       <c r="D71" s="16" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="33" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="B72" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C72" s="34"/>
       <c r="D72" s="16" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="33" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="B73" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C73" s="34"/>
       <c r="D73" s="16" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="33" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C74" s="34"/>
       <c r="D74" s="16" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="33" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C75" s="34"/>
       <c r="D75" s="16" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="33" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="B76" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C76" s="34"/>
       <c r="D76" s="16" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="E76" s="16" t="s">
         <v>339</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="33" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="B77" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C77" s="34"/>
       <c r="D77" s="16" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="E77" s="16" t="s">
         <v>339</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="33" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="B78" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C78" s="34"/>
       <c r="D78" s="16" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="33" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C79" s="34"/>
       <c r="D79" s="16" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="33" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C80" s="34"/>
       <c r="D80" s="16" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="33" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C81" s="34"/>
       <c r="D81" s="16" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="33" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="B82" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C82" s="34"/>
       <c r="D82" s="16" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="33" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="B83" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C83" s="34"/>
       <c r="D83" s="16" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="33" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="B84" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C84" s="34"/>
       <c r="D84" s="16" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="33" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="B85" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C85" s="34"/>
       <c r="D85" s="16" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="33" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B86" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C86" s="34"/>
       <c r="D86" s="16" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="33" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B87" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C87" s="34"/>
       <c r="D87" s="16" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="33" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="B88" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C88" s="34"/>
       <c r="D88" s="16" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="33" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="B89" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C89" s="34"/>
       <c r="D89" s="16" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="E89" s="16" t="s">
         <v>324</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="33" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="B90" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C90" s="34"/>
       <c r="D90" s="16" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F90" s="16" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="33" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="B91" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C91" s="34"/>
       <c r="D91" s="16" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="33" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="B92" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C92" s="34"/>
       <c r="D92" s="16" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F92" s="16" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="33" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="B93" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C93" s="34"/>
       <c r="D93" s="16" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="E93" s="16" t="s">
         <v>318</v>
       </c>
       <c r="F93" s="16" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="33" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="B94" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C94" s="34"/>
       <c r="D94" s="16" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="F94" s="16" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="33" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B95" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C95" s="34"/>
       <c r="D95" s="16" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="33" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B96" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C96" s="34"/>
       <c r="D96" s="16" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="E96" s="16" t="s">
-        <v>1250</v>
+        <v>318</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="33" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="B97" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C97" s="34"/>
       <c r="D97" s="16" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>1250</v>
+        <v>302</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="33" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="B98" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C98" s="34"/>
       <c r="D98" s="16" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>1250</v>
+        <v>302</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="33" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="B99" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C99" s="34"/>
       <c r="D99" s="16" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>299</v>
+        <v>1262</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="33" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="B100" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C100" s="34"/>
       <c r="D100" s="16" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E100" s="16" t="s">
         <v>1262</v>
       </c>
-      <c r="E100" s="16" t="s">
-        <v>299</v>
-      </c>
       <c r="F100" s="16" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="33" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="B101" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C101" s="34"/>
       <c r="D101" s="16" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>299</v>
+        <v>1262</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="33" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="B102" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C102" s="34"/>
       <c r="D102" s="16" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="E102" s="16" t="s">
         <v>299</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="33" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B103" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C103" s="34"/>
       <c r="D103" s="16" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="E103" s="16" t="s">
         <v>299</v>
       </c>
       <c r="F103" s="16" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="33" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B104" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C104" s="34"/>
       <c r="D104" s="16" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>1275</v>
+        <v>299</v>
       </c>
       <c r="F104" s="16" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="33" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="B105" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C105" s="34"/>
       <c r="D105" s="16" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="E105" s="16" t="s">
-        <v>1275</v>
+        <v>299</v>
       </c>
       <c r="F105" s="16" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="33" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="B106" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C106" s="34"/>
       <c r="D106" s="16" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>1275</v>
+        <v>299</v>
       </c>
       <c r="F106" s="16" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="33" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="B107" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C107" s="34"/>
       <c r="D107" s="16" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>180</v>
+        <v>1287</v>
       </c>
       <c r="F107" s="16" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="33" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="B108" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C108" s="34"/>
       <c r="D108" s="16" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E108" s="16" t="s">
         <v>1287</v>
       </c>
-      <c r="E108" s="16" t="s">
-        <v>1275</v>
-      </c>
       <c r="F108" s="16" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="33" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B109" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C109" s="34"/>
       <c r="D109" s="16" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="E109" s="16" t="s">
-        <v>1275</v>
+        <v>1287</v>
       </c>
       <c r="F109" s="16" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="33" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="B110" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C110" s="34"/>
       <c r="D110" s="16" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="E110" s="16" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="F110" s="16" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="33" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="B111" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C111" s="34"/>
       <c r="D111" s="16" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="E111" s="16" t="s">
-        <v>225</v>
+        <v>1287</v>
       </c>
       <c r="F111" s="16" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="33" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="B112" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C112" s="34"/>
       <c r="D112" s="16" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="E112" s="16" t="s">
-        <v>225</v>
+        <v>1287</v>
       </c>
       <c r="F112" s="16" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="33" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="B113" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C113" s="34"/>
       <c r="D113" s="16" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="E113" s="16" t="s">
         <v>225</v>
       </c>
       <c r="F113" s="16" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="33" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="B114" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C114" s="34"/>
       <c r="D114" s="16" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="33" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="B115" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C115" s="34"/>
       <c r="D115" s="16" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="E115" s="16" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F115" s="16" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="33" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="B116" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C116" s="34"/>
       <c r="D116" s="16" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="E116" s="16" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F116" s="16" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="33" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="B117" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C117" s="34"/>
       <c r="D117" s="16" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="E117" s="16" t="s">
-        <v>296</v>
+        <v>213</v>
       </c>
       <c r="F117" s="16" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="33" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="B118" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C118" s="34"/>
       <c r="D118" s="16" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="E118" s="16" t="s">
-        <v>296</v>
+        <v>213</v>
       </c>
       <c r="F118" s="16" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="33" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="B119" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C119" s="34"/>
       <c r="D119" s="16" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="E119" s="16" t="s">
-        <v>296</v>
+        <v>213</v>
       </c>
       <c r="F119" s="16" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="33" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="B120" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C120" s="34"/>
       <c r="D120" s="16" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="E120" s="16" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F120" s="16" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="33" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="B121" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C121" s="34"/>
       <c r="D121" s="16" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="E121" s="16" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F121" s="16" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="33" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="B122" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C122" s="34"/>
       <c r="D122" s="16" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="E122" s="16" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F122" s="16" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="33" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="B123" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C123" s="34"/>
       <c r="D123" s="16" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="E123" s="16" t="s">
         <v>293</v>
       </c>
       <c r="F123" s="16" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="33" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="B124" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C124" s="34"/>
       <c r="D124" s="16" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="E124" s="16" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F124" s="16" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="33" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="B125" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C125" s="34"/>
       <c r="D125" s="16" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="E125" s="16" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F125" s="16" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="33" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="B126" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C126" s="34"/>
       <c r="D126" s="16" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="E126" s="16" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F126" s="16" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="33" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="B127" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C127" s="34"/>
       <c r="D127" s="16" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="E127" s="16" t="s">
         <v>290</v>
       </c>
       <c r="F127" s="16" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="33" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="B128" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C128" s="34"/>
       <c r="D128" s="16" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="E128" s="16" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F128" s="16" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="33" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="B129" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C129" s="34"/>
       <c r="D129" s="16" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="E129" s="16" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F129" s="16" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="33" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="B130" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C130" s="34"/>
       <c r="D130" s="16" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="E130" s="16" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F130" s="16" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="33" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="B131" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C131" s="34"/>
       <c r="D131" s="16" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="E131" s="16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F131" s="16" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="33" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="B132" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C132" s="34"/>
       <c r="D132" s="16" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F132" s="16" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="33" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B133" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C133" s="34"/>
       <c r="D133" s="16" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="E133" s="16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F133" s="16" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="33" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="B134" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C134" s="34"/>
       <c r="D134" s="16" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>207</v>
+        <v>284</v>
       </c>
       <c r="F134" s="16" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="33" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="B135" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C135" s="34"/>
       <c r="D135" s="16" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>201</v>
+        <v>284</v>
       </c>
       <c r="F135" s="16" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="33" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="B136" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C136" s="34"/>
       <c r="D136" s="16" t="s">
-        <v>1371</v>
-      </c>
-      <c r="E136" s="16"/>
-      <c r="F136" s="16"/>
+        <v>1374</v>
+      </c>
+      <c r="E136" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="F136" s="16" t="s">
+        <v>1375</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="33" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="B137" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C137" s="34"/>
       <c r="D137" s="16" t="s">
-        <v>1373</v>
-      </c>
-      <c r="E137" s="16"/>
-      <c r="F137" s="16"/>
+        <v>1377</v>
+      </c>
+      <c r="E137" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="F137" s="16" t="s">
+        <v>1378</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="33" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
       <c r="B138" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C138" s="34"/>
       <c r="D138" s="16" t="s">
-        <v>1375</v>
-      </c>
-      <c r="E138" s="16"/>
-      <c r="F138" s="16"/>
+        <v>1380</v>
+      </c>
+      <c r="E138" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="F138" s="16" t="s">
+        <v>1381</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="33" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="B139" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C139" s="34"/>
       <c r="D139" s="16" t="s">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="E139" s="16"/>
       <c r="F139" s="16"/>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="33" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B140" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C140" s="34"/>
       <c r="D140" s="16" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="E140" s="16"/>
       <c r="F140" s="16"/>
     </row>
     <row r="141" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="33" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="B141" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C141" s="34"/>
       <c r="D141" s="16" t="s">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="E141" s="16"/>
       <c r="F141" s="16"/>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="33" t="s">
-        <v>1382</v>
+        <v>1388</v>
       </c>
       <c r="B142" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C142" s="34"/>
       <c r="D142" s="16" t="s">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="E142" s="16"/>
       <c r="F142" s="16"/>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="33" t="s">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="B143" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C143" s="34"/>
       <c r="D143" s="16" t="s">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="E143" s="16"/>
       <c r="F143" s="16"/>
     </row>
     <row r="144" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="33" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="B144" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C144" s="34"/>
       <c r="D144" s="16" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="E144" s="16"/>
       <c r="F144" s="16"/>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="33" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B145" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C145" s="34"/>
       <c r="D145" s="16" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="E145" s="16"/>
       <c r="F145" s="16"/>
     </row>
     <row r="146" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="33" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="B146" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C146" s="34"/>
       <c r="D146" s="16" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="E146" s="16"/>
       <c r="F146" s="16"/>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="33" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B147" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C147" s="34"/>
       <c r="D147" s="16" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="E147" s="16"/>
       <c r="F147" s="16"/>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="33" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="B148" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C148" s="34"/>
       <c r="D148" s="16" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="E148" s="16"/>
       <c r="F148" s="16"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="33" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="B149" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C149" s="34"/>
       <c r="D149" s="16" t="s">
-        <v>1397</v>
-      </c>
-      <c r="E149" s="16" t="s">
-        <v>1398</v>
-      </c>
+        <v>1403</v>
+      </c>
+      <c r="E149" s="16"/>
       <c r="F149" s="16"/>
     </row>
     <row r="150" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="33" t="s">
-        <v>1399</v>
+        <v>1404</v>
       </c>
       <c r="B150" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C150" s="34"/>
       <c r="D150" s="16" t="s">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="E150" s="16"/>
       <c r="F150" s="16"/>
     </row>
     <row r="151" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="33" t="s">
-        <v>1401</v>
+        <v>1406</v>
       </c>
       <c r="B151" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C151" s="34"/>
       <c r="D151" s="16" t="s">
-        <v>1402</v>
+        <v>1407</v>
       </c>
       <c r="E151" s="16"/>
       <c r="F151" s="16"/>
     </row>
     <row r="152" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="33" t="s">
-        <v>1403</v>
+        <v>1408</v>
       </c>
       <c r="B152" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C152" s="34"/>
       <c r="D152" s="16" t="s">
-        <v>1404</v>
-      </c>
-      <c r="E152" s="16"/>
+        <v>1409</v>
+      </c>
+      <c r="E152" s="16" t="s">
+        <v>1410</v>
+      </c>
       <c r="F152" s="16"/>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="33" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="B153" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C153" s="34"/>
       <c r="D153" s="16" t="s">
-        <v>1406</v>
-      </c>
-      <c r="E153" s="16" t="s">
-        <v>1398</v>
-      </c>
+        <v>1412</v>
+      </c>
+      <c r="E153" s="16"/>
       <c r="F153" s="16"/>
     </row>
     <row r="154" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="33" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="B154" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C154" s="34"/>
       <c r="D154" s="16" t="s">
-        <v>1408</v>
-      </c>
-      <c r="E154" s="16" t="s">
-        <v>1398</v>
-      </c>
+        <v>1414</v>
+      </c>
+      <c r="E154" s="16"/>
       <c r="F154" s="16"/>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="33" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="B155" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C155" s="34"/>
       <c r="D155" s="16" t="s">
-        <v>1410</v>
-      </c>
-      <c r="E155" s="16" t="s">
-        <v>1411</v>
-      </c>
+        <v>1416</v>
+      </c>
+      <c r="E155" s="16"/>
       <c r="F155" s="16"/>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="33" t="s">
-        <v>1412</v>
+        <v>1417</v>
       </c>
       <c r="B156" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C156" s="34"/>
       <c r="D156" s="16" t="s">
-        <v>1413</v>
+        <v>1418</v>
       </c>
       <c r="E156" s="16" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F156" s="16"/>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="33" t="s">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="B157" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C157" s="34"/>
       <c r="D157" s="16" t="s">
-        <v>1415</v>
+        <v>1420</v>
       </c>
       <c r="E157" s="16" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F157" s="16"/>
     </row>
     <row r="158" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="33" t="s">
-        <v>1416</v>
+        <v>1421</v>
       </c>
       <c r="B158" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C158" s="34"/>
       <c r="D158" s="16" t="s">
-        <v>1417</v>
+        <v>1422</v>
       </c>
       <c r="E158" s="16" t="s">
-        <v>1411</v>
+        <v>1423</v>
       </c>
       <c r="F158" s="16"/>
     </row>
     <row r="159" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="33" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="B159" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C159" s="34"/>
       <c r="D159" s="16" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="E159" s="16" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="F159" s="16"/>
     </row>
     <row r="160" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="33" t="s">
-        <v>1421</v>
+        <v>1426</v>
       </c>
       <c r="B160" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C160" s="34"/>
       <c r="D160" s="16" t="s">
-        <v>1422</v>
+        <v>1427</v>
       </c>
       <c r="E160" s="16" t="s">
         <v>1423</v>
@@ -18362,377 +18425,371 @@
     </row>
     <row r="161" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="33" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="B161" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C161" s="34"/>
       <c r="D161" s="16" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="E161" s="16" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="F161" s="16"/>
     </row>
     <row r="162" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="33" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="B162" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C162" s="34"/>
       <c r="D162" s="16" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="E162" s="16" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="F162" s="16"/>
     </row>
     <row r="163" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="33" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="B163" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C163" s="34"/>
       <c r="D163" s="16" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="E163" s="16" t="s">
-        <v>1426</v>
+        <v>1435</v>
       </c>
       <c r="F163" s="16"/>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="33" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="B164" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C164" s="34"/>
       <c r="D164" s="16" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="E164" s="16" t="s">
-        <v>1426</v>
+        <v>1438</v>
       </c>
       <c r="F164" s="16"/>
     </row>
     <row r="165" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="33" t="s">
-        <v>1434</v>
+        <v>1439</v>
       </c>
       <c r="B165" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C165" s="34"/>
       <c r="D165" s="16" t="s">
-        <v>1435</v>
+        <v>1440</v>
       </c>
       <c r="E165" s="16" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="F165" s="16"/>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="33" t="s">
-        <v>1437</v>
+        <v>1442</v>
       </c>
       <c r="B166" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C166" s="34"/>
       <c r="D166" s="16" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E166" s="16" t="s">
         <v>1438</v>
-      </c>
-      <c r="E166" s="16" t="s">
-        <v>1439</v>
       </c>
       <c r="F166" s="16"/>
     </row>
     <row r="167" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="33" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="B167" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C167" s="34"/>
       <c r="D167" s="16" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="E167" s="16" t="s">
-        <v>1442</v>
-      </c>
-      <c r="F167" s="16" t="s">
-        <v>1443</v>
-      </c>
+        <v>1438</v>
+      </c>
+      <c r="F167" s="16"/>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="33" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B168" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C168" s="34"/>
       <c r="D168" s="16" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="E168" s="16" t="s">
-        <v>1442</v>
-      </c>
-      <c r="F168" s="16" t="s">
-        <v>1446</v>
-      </c>
+        <v>1448</v>
+      </c>
+      <c r="F168" s="16"/>
     </row>
     <row r="169" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="33" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="B169" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C169" s="34"/>
       <c r="D169" s="16" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="E169" s="16" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="F169" s="16"/>
     </row>
     <row r="170" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="33" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="B170" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C170" s="34"/>
       <c r="D170" s="16" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="E170" s="16" t="s">
-        <v>1452</v>
-      </c>
-      <c r="F170" s="16"/>
+        <v>1454</v>
+      </c>
+      <c r="F170" s="16" t="s">
+        <v>1455</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="33" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="B171" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C171" s="34"/>
       <c r="D171" s="16" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E171" s="16" t="s">
         <v>1454</v>
       </c>
-      <c r="E171" s="16" t="s">
-        <v>1455</v>
-      </c>
       <c r="F171" s="16" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="33" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="B172" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C172" s="34"/>
       <c r="D172" s="16" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="E172" s="16" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="F172" s="16"/>
     </row>
     <row r="173" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="33" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="B173" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C173" s="34"/>
       <c r="D173" s="16" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E173" s="16" t="s">
-        <v>1452</v>
-      </c>
-      <c r="F173" s="16" t="s">
-        <v>1462</v>
-      </c>
+        <v>1464</v>
+      </c>
+      <c r="F173" s="16"/>
     </row>
     <row r="174" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="33" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="B174" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C174" s="34"/>
       <c r="D174" s="16" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="E174" s="16" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="F174" s="16" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="33" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="B175" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C175" s="34"/>
       <c r="D175" s="16" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="E175" s="16" t="s">
-        <v>1459</v>
-      </c>
-      <c r="F175" s="16" t="s">
-        <v>1469</v>
-      </c>
+        <v>1471</v>
+      </c>
+      <c r="F175" s="16"/>
     </row>
     <row r="176" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="33" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="B176" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C176" s="34"/>
       <c r="D176" s="16" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="E176" s="16" t="s">
-        <v>1472</v>
+        <v>1464</v>
       </c>
       <c r="F176" s="16" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="33" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B177" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C177" s="34"/>
       <c r="D177" s="16" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="E177" s="16" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="F177" s="16" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="33" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B178" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C178" s="34"/>
       <c r="D178" s="16" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="E178" s="16" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="F178" s="16" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="33" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B179" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C179" s="34"/>
       <c r="D179" s="16" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="E179" s="16" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="F179" s="16" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="33" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B180" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C180" s="34"/>
       <c r="D180" s="16" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="E180" s="16" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="F180" s="16" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="33" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B181" s="34" t="s">
-        <v>1490</v>
+        <v>972</v>
       </c>
       <c r="C181" s="34"/>
       <c r="D181" s="16" t="s">
         <v>1491</v>
       </c>
       <c r="E181" s="16" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F181" s="16" t="s">
         <v>1492</v>
-      </c>
-      <c r="F181" s="16" t="s">
-        <v>1493</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="33" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>1490</v>
+        <v>972</v>
       </c>
       <c r="C182" s="34"/>
       <c r="D182" s="16" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E182" s="16" t="s">
         <v>1495</v>
-      </c>
-      <c r="E182" s="16" t="s">
-        <v>1492</v>
       </c>
       <c r="F182" s="16" t="s">
         <v>1496</v>
@@ -18743,719 +18800,773 @@
         <v>1497</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>1490</v>
+        <v>972</v>
       </c>
       <c r="C183" s="34"/>
       <c r="D183" s="16" t="s">
         <v>1498</v>
       </c>
       <c r="E183" s="16" t="s">
-        <v>1492</v>
+        <v>1499</v>
       </c>
       <c r="F183" s="16" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="33" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B184" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C184" s="34"/>
       <c r="D184" s="16" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="E184" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F184" s="16" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="33" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="B185" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C185" s="34"/>
       <c r="D185" s="16" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E185" s="16" t="s">
         <v>1504</v>
       </c>
-      <c r="E185" s="16" t="s">
-        <v>1492</v>
-      </c>
       <c r="F185" s="16" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="33" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C186" s="34"/>
       <c r="D186" s="16" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="E186" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F186" s="16" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="33" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="B187" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C187" s="34"/>
       <c r="D187" s="16" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
       <c r="E187" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F187" s="16" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="33" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="B188" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C188" s="34"/>
       <c r="D188" s="16" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="E188" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F188" s="16" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="33" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
       <c r="B189" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C189" s="34"/>
       <c r="D189" s="16" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="E189" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F189" s="16" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="33" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
       <c r="B190" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C190" s="34"/>
       <c r="D190" s="16" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
       <c r="E190" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F190" s="16" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="33" t="s">
-        <v>486</v>
+        <v>1524</v>
       </c>
       <c r="B191" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C191" s="34"/>
       <c r="D191" s="16" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="E191" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F191" s="16" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="33" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="B192" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C192" s="34"/>
       <c r="D192" s="16" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="E192" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F192" s="16" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="33" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="B193" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C193" s="34"/>
       <c r="D193" s="16" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="E193" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F193" s="16" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="33" t="s">
-        <v>1529</v>
+        <v>486</v>
       </c>
       <c r="B194" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C194" s="34"/>
       <c r="D194" s="16" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="E194" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F194" s="16" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="33" t="s">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="B195" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C195" s="34"/>
       <c r="D195" s="16" t="s">
-        <v>1533</v>
+        <v>1536</v>
       </c>
       <c r="E195" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F195" s="16" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="33" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="B196" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C196" s="34"/>
       <c r="D196" s="16" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="E196" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F196" s="16" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="33" t="s">
-        <v>1538</v>
+        <v>1541</v>
       </c>
       <c r="B197" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C197" s="34"/>
       <c r="D197" s="16" t="s">
-        <v>1539</v>
+        <v>1542</v>
       </c>
       <c r="E197" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F197" s="16" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="33" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="B198" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C198" s="34"/>
       <c r="D198" s="16" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="E198" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F198" s="16" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="33" t="s">
-        <v>1544</v>
+        <v>1547</v>
       </c>
       <c r="B199" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C199" s="34"/>
       <c r="D199" s="16" t="s">
-        <v>1545</v>
+        <v>1548</v>
       </c>
       <c r="E199" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F199" s="16" t="s">
-        <v>1546</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="33" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="B200" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C200" s="34"/>
       <c r="D200" s="16" t="s">
-        <v>1548</v>
+        <v>1551</v>
       </c>
       <c r="E200" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F200" s="16" t="s">
-        <v>1549</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="33" t="s">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="B201" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C201" s="34"/>
       <c r="D201" s="16" t="s">
-        <v>1551</v>
+        <v>1554</v>
       </c>
       <c r="E201" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F201" s="16" t="s">
-        <v>1552</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="33" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="B202" s="34" t="s">
-        <v>969</v>
+        <v>1502</v>
       </c>
       <c r="C202" s="34"/>
       <c r="D202" s="16" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="E202" s="16" t="s">
-        <v>1555</v>
+        <v>1504</v>
       </c>
       <c r="F202" s="16" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="33" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="B203" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C203" s="34"/>
       <c r="D203" s="16" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="E203" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F203" s="16" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="33" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B204" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C204" s="34"/>
       <c r="D204" s="16" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="E204" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F204" s="16" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="33" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B205" s="34" t="s">
-        <v>1490</v>
+        <v>972</v>
       </c>
       <c r="C205" s="34"/>
       <c r="D205" s="16" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="E205" s="16" t="s">
-        <v>1492</v>
+        <v>1567</v>
       </c>
       <c r="F205" s="16" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="33" t="s">
-        <v>1566</v>
+        <v>1569</v>
       </c>
       <c r="B206" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C206" s="34"/>
       <c r="D206" s="16" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
       <c r="E206" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F206" s="16" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="33" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="B207" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C207" s="34"/>
       <c r="D207" s="16" t="s">
-        <v>1570</v>
+        <v>1573</v>
       </c>
       <c r="E207" s="16" t="s">
-        <v>1571</v>
+        <v>1504</v>
       </c>
       <c r="F207" s="16" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="33" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B208" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C208" s="34"/>
       <c r="D208" s="16" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="E208" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F208" s="16" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="33" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B209" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C209" s="34"/>
       <c r="D209" s="16" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="E209" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F209" s="16" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="33" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B210" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C210" s="34"/>
       <c r="D210" s="16" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="E210" s="16" t="s">
-        <v>1492</v>
+        <v>1583</v>
       </c>
       <c r="F210" s="16" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="33" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="B211" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C211" s="34"/>
       <c r="D211" s="16" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="E211" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F211" s="16" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="33" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="B212" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C212" s="34"/>
       <c r="D212" s="16" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
       <c r="E212" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F212" s="16" t="s">
-        <v>1587</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="33" t="s">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="B213" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C213" s="34"/>
       <c r="D213" s="16" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
       <c r="E213" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F213" s="16" t="s">
-        <v>1590</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="33" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="B214" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C214" s="34"/>
       <c r="D214" s="16" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="E214" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F214" s="16" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="33" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="B215" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C215" s="34"/>
       <c r="D215" s="16" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
       <c r="E215" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F215" s="16" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="33" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
       <c r="B216" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C216" s="34"/>
       <c r="D216" s="16" t="s">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="E216" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F216" s="16" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="33" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="B217" s="34" t="s">
-        <v>969</v>
+        <v>1502</v>
       </c>
       <c r="C217" s="34"/>
       <c r="D217" s="16" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="E217" s="16" t="s">
-        <v>1602</v>
+        <v>1504</v>
       </c>
       <c r="F217" s="16" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="33" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="B218" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C218" s="34"/>
       <c r="D218" s="16" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="E218" s="16" t="s">
-        <v>1606</v>
+        <v>1504</v>
       </c>
       <c r="F218" s="16" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="33" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B219" s="34" t="s">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="C219" s="34"/>
       <c r="D219" s="16" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="E219" s="16" t="s">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="F219" s="16" t="s">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="33" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B220" s="34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C220" s="34"/>
       <c r="D220" s="16" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="E220" s="16" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="F220" s="16" t="s">
-        <v>1614</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="33" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B221" s="34" t="s">
-        <v>969</v>
+        <v>1502</v>
       </c>
       <c r="C221" s="34"/>
       <c r="D221" s="16" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="E221" s="16" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="F221" s="16" t="s">
-        <v>1618</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="33" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B222" s="34" t="s">
-        <v>969</v>
+        <v>1502</v>
       </c>
       <c r="C222" s="34"/>
       <c r="D222" s="16" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="E222" s="16" t="s">
-        <v>1621</v>
+        <v>1504</v>
       </c>
       <c r="F222" s="16" t="s">
         <v>1622</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="33" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B223" s="34" t="s">
+        <v>972</v>
+      </c>
+      <c r="C223" s="34"/>
+      <c r="D223" s="16" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E223" s="16" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F223" s="16" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="33" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B224" s="34" t="s">
+        <v>972</v>
+      </c>
+      <c r="C224" s="34"/>
+      <c r="D224" s="16" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E224" s="16" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F224" s="16" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="33" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B225" s="34" t="s">
+        <v>972</v>
+      </c>
+      <c r="C225" s="34"/>
+      <c r="D225" s="16" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E225" s="16" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F225" s="16" t="s">
+        <v>1634</v>
       </c>
     </row>
   </sheetData>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -10552,7 +10552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="35" min="1" max="1"/>
@@ -12853,6 +12853,39 @@
       <c r="G70" s="69" t="inlineStr">
         <is>
           <t>verificar-migraciones.py acuso a document_series de crear la columna document_type de mas: la migracion de 9.12 suelta la tabla y la vuelve a crear con otra forma, pero el doble de Schema no soltaba nada, asi que el grabador recogia la union de las dos formas. Mismo archivo, mismo motivo y misma familia que T-75. La leccion: cada doble vacio del grabador es un falso positivo esperando, y un verificador que da rojo por algo que esta bien acaba ignorado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="67" t="inlineStr">
+        <is>
+          <t>T-77</t>
+        </is>
+      </c>
+      <c r="B71" s="68" t="inlineStr">
+        <is>
+          <t>Resuelta</t>
+        </is>
+      </c>
+      <c r="C71" s="68" t="n"/>
+      <c r="D71" s="69" t="inlineStr">
+        <is>
+          <t>RESUELTA (2026-08-31, hotfix de 9.12). El sembrador reescribia lo que una persona ya habia configurado, y ademas reventaba.</t>
+        </is>
+      </c>
+      <c r="E71" s="69" t="inlineStr">
+        <is>
+          <t>9.12 (hotfix)</t>
+        </is>
+      </c>
+      <c r="F71" s="69" t="inlineStr">
+        <is>
+          <t>Equipo de desarrollo</t>
+        </is>
+      </c>
+      <c r="G71" s="69" t="inlineStr">
+        <is>
+          <t>Reportada desde la instalacion: db:seed se paro con un 45000 porque updateOrInsert movia el valid_from de la fila ABIERTA de fx_official_sources encima de un periodo cerrado a mano (T-73 desde el otro lado). Lo que el error tapaba era peor: el sembrador murio en la linea 71 de 700, asi que los proveedores de 9.17d y los tipos de comprobante de 9.12 no llegaron a entrar. Y de fondo: cada db:seed --lo que el runbook manda tras cada migracion-- devolvia a fabrica el nombre, lema, colores y tipografia de la marca y la direccion de la sociedad, REGENERABA sus uuid y reactivaba fuentes y proveedores apagados a proposito. Regla nueva: lo que una persona puede cambiar se siembra si falta y no se toca si esta (sembrarSiFalta); donde hay vigencia, el periodo empieza el dia siguiente al ultimo cierre. 5 pruebas verificadas en rojo sin el arreglo.</t>
         </is>
       </c>
     </row>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -2241,7 +2241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J177"/>
+  <dimension ref="A1:J178"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="35" min="1" max="1"/>
@@ -10510,6 +10510,56 @@
       <c r="I177" s="35">
         <f>IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G177,Config!$A$3:$A$8,0)),0)</f>
         <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="57" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B178" s="35" t="inlineStr">
+        <is>
+          <t>Ola 2 - Escalar comercialmente</t>
+        </is>
+      </c>
+      <c r="C178" s="35" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="D178" s="35" t="inlineStr">
+        <is>
+          <t>Finanzas y facturacion</t>
+        </is>
+      </c>
+      <c r="E178" s="35" t="inlineStr">
+        <is>
+          <t>9.20</t>
+        </is>
+      </c>
+      <c r="F178" s="35" t="inlineStr">
+        <is>
+          <t>Cada cosa en su sitio: menu por grupos y la configuracion con una sola puerta</t>
+        </is>
+      </c>
+      <c r="G178" s="35" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="H178" s="35">
+        <f>IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G178,Config!$A$3:$A$8,0)),0)</f>
+        <v/>
+      </c>
+      <c r="I178" s="35">
+        <f>IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G178,Config!$A$3:$A$8,0)),0)</f>
+        <v/>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2026-08-31. FUERA DEL ALCANCE ORIGINAL, reportado al revisar el sitio. Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario sin saber donde estaba. Menu en tres grupos y una sola puerta (DEC-233); la portada por bloques con orden fijo (DEC-234); los catalogos pasan a ser un area con portada y aviso (DEC-235). Miga de pan en cada pantalla. Sin migracion y sin mover ninguna ruta. 984 pruebas. docs/fase-9/9.20-CADA-COSA-EN-SU-SITIO.md</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -14921,7 +14971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F238"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="35" min="1" max="1"/>
@@ -14974,7 +15024,7 @@
     <row r="3" ht="79.5" customHeight="1" s="36">
       <c r="A3" s="67" t="inlineStr">
         <is>
-          <t>DEC-228</t>
+          <t>DEC-233</t>
         </is>
       </c>
       <c r="B3" s="68" t="inlineStr">
@@ -14985,24 +15035,24 @@
       <c r="C3" s="68" t="n"/>
       <c r="D3" s="69" t="inlineStr">
         <is>
-          <t>Los tipos de comprobante son un catalogo por pais, no un enum en el codigo</t>
+          <t>La configuracion tiene UNA sola puerta, y el menu lateral solo lleva trabajo</t>
         </is>
       </c>
       <c r="E3" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F3" s="69" t="inlineStr">
         <is>
-          <t>ck_ds_type decia IN ('invoice','boleta','credit_note','debit_note','other') desde la Fase 2: la boleta es peruana, el CFDI mexicano no estaba y anadir uno exigia desplegar. Cada tipo declara su codigo oficial de SUNAT, la forma de su serie, como se le pide a una persona y cuantos digitos tiene el correlativo. No contradice a DEC-026: el codigo SE RAMIFICA por proposito de integracion, mientras que el tipo de comprobante NO se ramifica, VIAJA al emisor electronico.</t>
+          <t>Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario en una pantalla que se veia igual que Campanas y con el menu marcando otra entrada. El menu queda en tres grupos --Operacion, Finanzas, Registros-- mas Ajustes: Configuracion, y un grupo del que no se puede ver nada desaparece entero.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="57" customHeight="1" s="36">
       <c r="A4" s="67" t="inlineStr">
         <is>
-          <t>DEC-229</t>
+          <t>DEC-234</t>
         </is>
       </c>
       <c r="B4" s="68" t="inlineStr">
@@ -15013,24 +15063,24 @@
       <c r="C4" s="68" t="n"/>
       <c r="D4" s="69" t="inlineStr">
         <is>
-          <t>El numero se reserva bajo bloqueo de la fila de la serie, no con MAX()+1</t>
+          <t>El orden de los grupos es una decision y vive en el registro, no en la plantilla</t>
         </is>
       </c>
       <c r="E4" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F4" s="69" t="inlineStr">
         <is>
-          <t>MAX()+1 es correcto exactamente hasta la primera vez que dos personas emiten a la vez, y eso no es raro: es un cierre de mes. El bloqueo pone en fila a la segunda peticion antes de que lea el contador. Y aun asi existe uq_dn_number: el bloqueo es la primera linea y la unica es la ultima. Medido con dos clientes de verdad (patron de 4.11), con su contraejemplo: sin FOR UPDATE, B no espera.</t>
+          <t>revision() ordena por URGENCIA, que es lo correcto para una lista de avisos y lo peor para una navegacion: «Fiscal y facturacion» saldria arriba o abajo segun que falte hoy, y un sitio que cambia de forma segun el dia no se aprende. Por lo mismo, que rutas son configuracion sale de Preparacion::rutas() y no de la plantilla.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="79.5" customHeight="1" s="36">
       <c r="A5" s="67" t="inlineStr">
         <is>
-          <t>DEC-230</t>
+          <t>DEC-235</t>
         </is>
       </c>
       <c r="B5" s="68" t="inlineStr">
@@ -15041,24 +15091,24 @@
       <c r="C5" s="68" t="n"/>
       <c r="D5" s="69" t="inlineStr">
         <is>
-          <t>Cada numero que sale queda escrito, y el hueco se explica en vez de taparse</t>
+          <t>Los catalogos son configuracion, con portada propia</t>
         </is>
       </c>
       <c r="E5" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F5" s="69" t="inlineStr">
         <is>
-          <t>Reservar y no emitir deja un numero sin documento, y eso NO se arregla reutilizandolo: reutilizarlo ES el duplicado. document_numbers guarda cada numero con su estado; reserved es el unico del que se sale, used dice a que documento fue y voided dice por que, con un motivo de al menos diez caracteres. Un hueco explicado es defendible ante un requerimiento; uno mudo, no.</t>
+          <t>Los seis colgaban del menu bajo un titulo que no era un sitio: era una etiqueta. Ahora son un area con portada --cuantas filas y cuantas activas-- y su aviso: una lista sin ninguna fila activa sale en rojo, porque un catalogo vacio no da error, deja un desplegable vacio. La pantalla de cada catalogo no se mueve.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34.5" customHeight="1" s="36">
       <c r="A6" s="67" t="inlineStr">
         <is>
-          <t>DEC-231</t>
+          <t>DEC-228</t>
         </is>
       </c>
       <c r="B6" s="68" t="inlineStr">
@@ -15069,7 +15119,7 @@
       <c r="C6" s="68" t="n"/>
       <c r="D6" s="69" t="inlineStr">
         <is>
-          <t>Una sola serie por defecto por (sociedad, tipo, entorno), y la forma la impone el pais</t>
+          <t>Los tipos de comprobante son un catalogo por pais, no un enum en el codigo</t>
         </is>
       </c>
       <c r="E6" s="69" t="inlineStr">
@@ -15079,14 +15129,14 @@
       </c>
       <c r="F6" s="69" t="inlineStr">
         <is>
-          <t>uq_ds_default es la columna puerta 32: con dos series por defecto, «emitir una factura» no tendria respuesta hasta que alguien eligiera. El empate se rechaza al CONFIGURAR y no al emitir. Y tg_ds_forma_ins/upd exige que la serie tenga la forma que declara su tipo y que el tipo sea del pais de la sociedad: una sociedad peruana no emite comprobantes colombianos.</t>
+          <t>ck_ds_type decia IN ('invoice','boleta','credit_note','debit_note','other') desde la Fase 2: la boleta es peruana, el CFDI mexicano no estaba y anadir uno exigia desplegar. Cada tipo declara su codigo oficial de SUNAT, la forma de su serie, como se le pide a una persona y cuantos digitos tiene el correlativo. No contradice a DEC-026: el codigo SE RAMIFICA por proposito de integracion, mientras que el tipo de comprobante NO se ramifica, VIAJA al emisor electronico.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="36">
       <c r="A7" s="67" t="inlineStr">
         <is>
-          <t>DEC-232</t>
+          <t>DEC-229</t>
         </is>
       </c>
       <c r="B7" s="68" t="inlineStr">
@@ -15097,7 +15147,7 @@
       <c r="C7" s="68" t="n"/>
       <c r="D7" s="69" t="inlineStr">
         <is>
-          <t>Las series NO se siembran: unica configuracion sin valor de partida</t>
+          <t>El numero se reserva bajo bloqueo de la fila de la serie, no con MAX()+1</t>
         </is>
       </c>
       <c r="E7" s="69" t="inlineStr">
@@ -15107,14 +15157,14 @@
       </c>
       <c r="F7" s="69" t="inlineStr">
         <is>
-          <t>Excepcion razonada a DEC-190: una serie se registra ante la administracion tributaria y una inventada produciria comprobantes invalidos ante SUNAT --un valor de fabrica aqui no es comodidad, es un error fiscal--. No bloquea nada, que es lo que DEC-190 exige de verdad: sale en rojo en el panel con las palabras que explican por que no hay ninguna. Lo que si se siembra son los TIPOS, que son la regla del pais.</t>
+          <t>MAX()+1 es correcto exactamente hasta la primera vez que dos personas emiten a la vez, y eso no es raro: es un cierre de mes. El bloqueo pone en fila a la segunda peticion antes de que lea el contador. Y aun asi existe uq_dn_number: el bloqueo es la primera linea y la unica es la ultima. Medido con dos clientes de verdad (patron de 4.11), con su contraejemplo: sin FOR UPDATE, B no espera.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34.5" customHeight="1" s="36">
       <c r="A8" s="67" t="inlineStr">
         <is>
-          <t>DEC-223</t>
+          <t>DEC-230</t>
         </is>
       </c>
       <c r="B8" s="68" t="inlineStr">
@@ -15125,24 +15175,24 @@
       <c r="C8" s="68" t="n"/>
       <c r="D8" s="69" t="inlineStr">
         <is>
-          <t>Las credenciales de las APIs viven en tres tablas propias, no en .env ni en legal_entities</t>
+          <t>Cada numero que sale queda escrito, y el hueco se explica en vez de taparse</t>
         </is>
       </c>
       <c r="E8" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F8" s="69" t="inlineStr">
         <is>
-          <t>DEC-033 y docs/12 ya lo habian decidido y aqui se construye. Una sociedad es QUIEN factura; una conexion es CON QUE se conecta uno a un proveedor, y cambia mucho mas a menudo que una razon social. En .env seria peor: cambiar de entorno de pruebas a produccion exigiria entrar por SSH, que es DEC-190 roto por la puerta de atras.</t>
+          <t>Reservar y no emitir deja un numero sin documento, y eso NO se arregla reutilizandolo: reutilizarlo ES el duplicado. document_numbers guarda cada numero con su estado; reserved es el unico del que se sale, used dice a que documento fue y voided dice por que, con un motivo de al menos diez caracteres. Un hueco explicado es defendible ante un requerimiento; uno mudo, no.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1" s="36">
       <c r="A9" s="67" t="inlineStr">
         <is>
-          <t>DEC-224</t>
+          <t>DEC-231</t>
         </is>
       </c>
       <c r="B9" s="68" t="inlineStr">
@@ -15153,24 +15203,24 @@
       <c r="C9" s="68" t="n"/>
       <c r="D9" s="69" t="inlineStr">
         <is>
-          <t>Tres tablas de las cinco de docs/12: las asignaciones no se construyen todavia</t>
+          <t>Una sola serie por defecto por (sociedad, tipo, entorno), y la forma la impone el pais</t>
         </is>
       </c>
       <c r="E9" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F9" s="69" t="inlineStr">
         <is>
-          <t>El eje (marca, sociedad, pais) con vigencia resuelve un problema que hoy no existe: una conexion sirve a una sociedad o a la plataforma entera, y eso cabe en un legal_entity_id nullable donde NULL significa «de la plataforma». Construir la tabla de tres ejes antes de tener el segundo caso es construir contra un supuesto. Queda escrito en la cabecera de la migracion para que no se tome por un olvido.</t>
+          <t>uq_ds_default es la columna puerta 32: con dos series por defecto, «emitir una factura» no tendria respuesta hasta que alguien eligiera. El empate se rechaza al CONFIGURAR y no al emitir. Y tg_ds_forma_ins/upd exige que la serie tenga la forma que declara su tipo y que el tipo sea del pais de la sociedad: una sociedad peruana no emite comprobantes colombianos.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="57" customHeight="1" s="36">
       <c r="A10" s="67" t="inlineStr">
         <is>
-          <t>DEC-225</t>
+          <t>DEC-232</t>
         </is>
       </c>
       <c r="B10" s="68" t="inlineStr">
@@ -15181,24 +15231,24 @@
       <c r="C10" s="68" t="n"/>
       <c r="D10" s="69" t="inlineStr">
         <is>
-          <t>Rotar una credencial crea la version siguiente y cierra la anterior; no la pisa</t>
+          <t>Las series NO se siembran: unica configuracion sin valor de partida</t>
         </is>
       </c>
       <c r="E10" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F10" s="69" t="inlineStr">
         <is>
-          <t>Se guardan el cifrado y los cuatro ultimos caracteres, nada mas. Pisar el valor deja sin respuesta «cual era la de antes» y «cuando cambio». Las dos escrituras van en la misma transaccion y en ese orden, porque uq_icred_vigente solo admite una viva por (conexion, clase). tg_icred_inmutable impide reescribir una credencial: lo unico que cambia en una fila existente es revocarla.</t>
+          <t>Excepcion razonada a DEC-190: una serie se registra ante la administracion tributaria y una inventada produciria comprobantes invalidos ante SUNAT --un valor de fabrica aqui no es comodidad, es un error fiscal--. No bloquea nada, que es lo que DEC-190 exige de verdad: sale en rojo en el panel con las palabras que explican por que no hay ninguna. Lo que si se siembra son los TIPOS, que son la regla del pais.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="68.25" customHeight="1" s="36">
       <c r="A11" s="67" t="inlineStr">
         <is>
-          <t>DEC-226</t>
+          <t>DEC-223</t>
         </is>
       </c>
       <c r="B11" s="68" t="inlineStr">
@@ -15209,7 +15259,7 @@
       <c r="C11" s="68" t="n"/>
       <c r="D11" s="69" t="inlineStr">
         <is>
-          <t>La bitacora anota QUE cambio, no que valor</t>
+          <t>Las credenciales de las APIs viven en tres tablas propias, no en .env ni en legal_entities</t>
         </is>
       </c>
       <c r="E11" s="69" t="inlineStr">
@@ -15219,14 +15269,14 @@
       </c>
       <c r="F11" s="69" t="inlineStr">
         <is>
-          <t>Ni el secreto ni los cuatro ultimos entran en audit_log (BR-SEC-001). Un registro de auditoria que guarda el secreto es un segundo sitio donde esta el secreto, y ademas uno que por diseno no se puede borrar. Por eso el servicio parte la lectura en dos: estado() es lo que ve una persona y secreto() lo llama el cliente de la API.</t>
+          <t>DEC-033 y docs/12 ya lo habian decidido y aqui se construye. Una sociedad es QUIEN factura; una conexion es CON QUE se conecta uno a un proveedor, y cambia mucho mas a menudo que una razon social. En .env seria peor: cambiar de entorno de pruebas a produccion exigiria entrar por SSH, que es DEC-190 roto por la puerta de atras.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="68.25" customHeight="1" s="36">
       <c r="A12" s="67" t="inlineStr">
         <is>
-          <t>DEC-227</t>
+          <t>DEC-224</t>
         </is>
       </c>
       <c r="B12" s="68" t="inlineStr">
@@ -15237,7 +15287,7 @@
       <c r="C12" s="68" t="n"/>
       <c r="D12" s="69" t="inlineStr">
         <is>
-          <t>Una conexion ACTIVA exige https; un borrador no</t>
+          <t>Tres tablas de las cinco de docs/12: las asignaciones no se construyen todavia</t>
         </is>
       </c>
       <c r="E12" s="69" t="inlineStr">
@@ -15247,14 +15297,14 @@
       </c>
       <c r="F12" s="69" t="inlineStr">
         <is>
-          <t>ck_iconn_url es la unica regla de la iteracion que no es de forma sino de fondo: una URL http a un servicio de facturacion manda las claves secundarias por la red en claro. Se puede escribir mientras la conexion es un borrador y no se puede activar. La regla vive en la base y no en el formulario, porque el formulario no es el unico que escribe.</t>
+          <t>El eje (marca, sociedad, pais) con vigencia resuelve un problema que hoy no existe: una conexion sirve a una sociedad o a la plataforma entera, y eso cabe en un legal_entity_id nullable donde NULL significa «de la plataforma». Construir la tabla de tres ejes antes de tener el segundo caso es construir contra un supuesto. Queda escrito en la cabecera de la migracion para que no se tome por un olvido.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="68.25" customHeight="1" s="36">
       <c r="A13" s="67" t="inlineStr">
         <is>
-          <t>DEC-220</t>
+          <t>DEC-225</t>
         </is>
       </c>
       <c r="B13" s="68" t="inlineStr">
@@ -15265,24 +15315,24 @@
       <c r="C13" s="68" t="n"/>
       <c r="D13" s="69" t="inlineStr">
         <is>
-          <t>Core levanta un evento; Creator escucha</t>
+          <t>Rotar una credencial crea la version siguiente y cierra la anterior; no la pisa</t>
         </is>
       </c>
       <c r="E13" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F13" s="69" t="inlineStr">
         <is>
-          <t>Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
+          <t>Se guardan el cifrado y los cuatro ultimos caracteres, nada mas. Pisar el valor deja sin respuesta «cual era la de antes» y «cuando cambio». Las dos escrituras van en la misma transaccion y en ese orden, porque uq_icred_vigente solo admite una viva por (conexion, clase). tg_icred_inmutable impide reescribir una credencial: lo unico que cambia en una fila existente es revocarla.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45.75" customHeight="1" s="36">
       <c r="A14" s="67" t="inlineStr">
         <is>
-          <t>DEC-221</t>
+          <t>DEC-226</t>
         </is>
       </c>
       <c r="B14" s="68" t="inlineStr">
@@ -15293,24 +15343,24 @@
       <c r="C14" s="68" t="n"/>
       <c r="D14" s="69" t="inlineStr">
         <is>
-          <t>El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
+          <t>La bitacora anota QUE cambio, no que valor</t>
         </is>
       </c>
       <c r="E14" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F14" s="69" t="inlineStr">
         <is>
-          <t>Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
+          <t>Ni el secreto ni los cuatro ultimos entran en audit_log (BR-SEC-001). Un registro de auditoria que guarda el secreto es un segundo sitio donde esta el secreto, y ademas uno que por diseno no se puede borrar. Por eso el servicio parte la lectura en dos: estado() es lo que ve una persona y secreto() lo llama el cliente de la API.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1" s="36">
       <c r="A15" s="67" t="inlineStr">
         <is>
-          <t>DEC-222</t>
+          <t>DEC-227</t>
         </is>
       </c>
       <c r="B15" s="68" t="inlineStr">
@@ -15321,24 +15371,24 @@
       <c r="C15" s="68" t="n"/>
       <c r="D15" s="69" t="inlineStr">
         <is>
-          <t>Un correo que falla no deja sin avisar a los demas</t>
+          <t>Una conexion ACTIVA exige https; un borrador no</t>
         </is>
       </c>
       <c r="E15" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F15" s="69" t="inlineStr">
         <is>
-          <t>Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
+          <t>ck_iconn_url es la unica regla de la iteracion que no es de forma sino de fondo: una URL http a un servicio de facturacion manda las claves secundarias por la red en claro. Se puede escribir mientras la conexion es un borrador y no se puede activar. La regla vive en la base y no en el formulario, porque el formulario no es el unico que escribe.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="57" customHeight="1" s="36">
       <c r="A16" s="67" t="inlineStr">
         <is>
-          <t>DEC-216</t>
+          <t>DEC-220</t>
         </is>
       </c>
       <c r="B16" s="68" t="inlineStr">
@@ -15349,24 +15399,24 @@
       <c r="C16" s="68" t="n"/>
       <c r="D16" s="69" t="inlineStr">
         <is>
-          <t>Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
+          <t>Core levanta un evento; Creator escucha</t>
         </is>
       </c>
       <c r="E16" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F16" s="69" t="inlineStr">
         <is>
-          <t>El plazo es parte de lo que se le comunico a la gente: «tienes 15 dias» dicho en enero no puede convertirse en «tenias 10» porque en marzo alguien cambio un ajuste global. Cada version lleva los suyos, se eligen al publicarla y despues son inmutables. Lo configurable es el valor por defecto, que es lo que el formulario trae puesto. readonly_days = 0 significa «sin periodo de solo lectura»; un numero muy grande, lo contrario.</t>
+          <t>Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="57" customHeight="1" s="36">
       <c r="A17" s="67" t="inlineStr">
         <is>
-          <t>DEC-217</t>
+          <t>DEC-221</t>
         </is>
       </c>
       <c r="B17" s="68" t="inlineStr">
@@ -15377,24 +15427,24 @@
       <c r="C17" s="68" t="n"/>
       <c r="D17" s="69" t="inlineStr">
         <is>
-          <t>El reloj no empieza al publicar: empieza cuando le toca a el</t>
+          <t>El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
         </is>
       </c>
       <c r="E17" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F17" s="69" t="inlineStr">
         <is>
-          <t>Un creador activado ayer no puede aparecer bloqueado por una version de hace tres meses. Su plazo cuenta desde el dia en que se activo, o desde la fecha de la version si es posterior. Sin esto, el primer creador que se diera de alta despues de un cambio de fondo entraria directamente al muro sin haber tenido un solo dia.</t>
+          <t>Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="68.25" customHeight="1" s="36">
       <c r="A18" s="67" t="inlineStr">
         <is>
-          <t>DEC-218</t>
+          <t>DEC-222</t>
         </is>
       </c>
       <c r="B18" s="68" t="inlineStr">
@@ -15405,24 +15455,24 @@
       <c r="C18" s="68" t="n"/>
       <c r="D18" s="69" t="inlineStr">
         <is>
-          <t>La pantalla del muro no lleva permiso, y eso es la decision</t>
+          <t>Un correo que falla no deja sin avisar a los demas</t>
         </is>
       </c>
       <c r="E18" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F18" s="69" t="inlineStr">
         <is>
-          <t>/mis-terminos es la unica salida de un creador bloqueado: un permiso dejaria sin salida justo a quien la necesita. La autorizacion es tener ficha de creador atada a la sesion. El trinquete de rutas exentas subio de 4 a 6 a mano y con motivo escrito, que es todo el sentido de ese trinquete. Lleva throttle:10,1.</t>
+          <t>Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45.75" customHeight="1" s="36">
       <c r="A19" s="67" t="inlineStr">
         <is>
-          <t>DEC-219</t>
+          <t>DEC-216</t>
         </is>
       </c>
       <c r="B19" s="68" t="inlineStr">
@@ -15433,7 +15483,7 @@
       <c r="C19" s="68" t="n"/>
       <c r="D19" s="69" t="inlineStr">
         <is>
-          <t>Una franja fija, no un popup</t>
+          <t>Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
         </is>
       </c>
       <c r="E19" s="69" t="inlineStr">
@@ -15443,14 +15493,14 @@
       </c>
       <c r="F19" s="69" t="inlineStr">
         <is>
-          <t>El negocio pidio «popup como recordatorio al loguearse». Un popup se cierra sin leerlo y no vuelve hasta la siguiente sesion; la franja sigue ahi mientras siga sin aceptarse. El equipo interno no la ve nunca.</t>
+          <t>El plazo es parte de lo que se le comunico a la gente: «tienes 15 dias» dicho en enero no puede convertirse en «tenias 10» porque en marzo alguien cambio un ajuste global. Cada version lleva los suyos, se eligen al publicarla y despues son inmutables. Lo configurable es el valor por defecto, que es lo que el formulario trae puesto. readonly_days = 0 significa «sin periodo de solo lectura»; un numero muy grande, lo contrario.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="57" customHeight="1" s="36">
       <c r="A20" s="67" t="inlineStr">
         <is>
-          <t>DEC-212</t>
+          <t>DEC-217</t>
         </is>
       </c>
       <c r="B20" s="68" t="inlineStr">
@@ -15461,24 +15511,24 @@
       <c r="C20" s="68" t="n"/>
       <c r="D20" s="69" t="inlineStr">
         <is>
-          <t>Una politica de precios con vigencia, no dos constantes</t>
+          <t>El reloj no empieza al publicar: empieza cuando le toca a el</t>
         </is>
       </c>
       <c r="E20" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F20" s="69" t="inlineStr">
         <is>
-          <t>pricing_policies guarda la retencion (Q-13), el umbral de rentabilidad y sobre que se calcula. Los tres cambian: el 29,5 % por decreto y el 20 % con datos reales. Tiene historia --una sola vigente-- y una cerrada no se reescribe ni se borra: es la que explica como se pacto un compromiso de hace tres meses.</t>
+          <t>Un creador activado ayer no puede aparecer bloqueado por una version de hace tres meses. Su plazo cuenta desde el dia en que se activo, o desde la fecha de la version si es posterior. Sin esto, el primer creador que se diera de alta despues de un cambio de fondo entraria directamente al muro sin haber tenido un solo dia.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34.5" customHeight="1" s="36">
       <c r="A21" s="67" t="inlineStr">
         <is>
-          <t>DEC-213</t>
+          <t>DEC-218</t>
         </is>
       </c>
       <c r="B21" s="68" t="inlineStr">
@@ -15489,24 +15539,24 @@
       <c r="C21" s="68" t="n"/>
       <c r="D21" s="69" t="inlineStr">
         <is>
-          <t>margin_basis es configuracion, no una pregunta</t>
+          <t>La pantalla del muro no lleva permiso, y eso es la decision</t>
         </is>
       </c>
       <c r="E21" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F21" s="69" t="inlineStr">
         <is>
-          <t>Con 100 de neto y 29,5 % el costo es 141,84; el ejemplo del negocio dio 170,21, que es 141,84 x 1,20 (recargo sobre el COSTO). Un 20 % de margen sobre el INGRESO habria dado 177,31. Lo iba a preguntar dos veces; DEC-190 dice que estas cosas se configuran, y preguntarlo habria sido quemar la respuesta en el codigo con la firma del negocio encima. Es una columna con dos valores, sembrada en cost, con la pantalla ensenando las dos cifras y una prueba de cada una.</t>
+          <t>/mis-terminos es la unica salida de un creador bloqueado: un permiso dejaria sin salida justo a quien la necesita. La autorizacion es tener ficha de creador atada a la sesion. El trinquete de rutas exentas subio de 4 a 6 a mano y con motivo escrito, que es todo el sentido de ese trinquete. Lleva throttle:10,1.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="68.25" customHeight="1" s="36">
       <c r="A22" s="67" t="inlineStr">
         <is>
-          <t>DEC-214</t>
+          <t>DEC-219</t>
         </is>
       </c>
       <c r="B22" s="68" t="inlineStr">
@@ -15517,24 +15567,24 @@
       <c r="C22" s="68" t="n"/>
       <c r="D22" s="69" t="inlineStr">
         <is>
-          <t>Se pacta el costo o el neto, y el ingreso minimo se dice, no se impone</t>
+          <t>Una franja fija, no un popup</t>
         </is>
       </c>
       <c r="E22" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F22" s="69" t="inlineStr">
         <is>
-          <t>agreed_amount sigue siendo el costo: de esa columna cuelgan devengos, pagos y la rentabilidad de 9.10. Se anaden la base, el neto y la tasa. Con net se teclean 100 y se escriben 141,8440, y el motor rehace la resta: un neto que no cuadra con su bruto se descubriria en la conversacion con el creador que cobro de menos. El mensaje dice el ingreso minimo y no bloquea: se puede aceptar menos margen, pero sabiendolo y antes de invitar. Los tres numeros se congelan en la participacion.</t>
+          <t>El negocio pidio «popup como recordatorio al loguearse». Un popup se cierra sin leerlo y no vuelve hasta la siguiente sesion; la franja sigue ahi mientras siga sin aceptarse. El equipo interno no la ve nunca.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="57" customHeight="1" s="36">
       <c r="A23" s="67" t="inlineStr">
         <is>
-          <t>DEC-215</t>
+          <t>DEC-212</t>
         </is>
       </c>
       <c r="B23" s="68" t="inlineStr">
@@ -15545,7 +15595,7 @@
       <c r="C23" s="68" t="n"/>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>La cuenta la hace el motor, no PHP</t>
+          <t>Una politica de precios con vigencia, no dos constantes</t>
         </is>
       </c>
       <c r="E23" s="69" t="inlineStr">
@@ -15555,14 +15605,14 @@
       </c>
       <c r="F23" s="69" t="inlineStr">
         <is>
-          <t>neto / (1 - tasa/100) con float da 141.84397163120568 y de ahi a un DECIMAL(18,4) hay un redondeo que puede caer del lado que el CHECK no admite. El contenedor no tiene bcmath, asi que la aritmetica exacta se hace en el motor con CAST a DECIMAL(28,12). Misma tecnica que 9.1 y 9.3.</t>
+          <t>pricing_policies guarda la retencion (Q-13), el umbral de rentabilidad y sobre que se calcula. Los tres cambian: el 29,5 % por decreto y el 20 % con datos reales. Tiene historia --una sola vigente-- y una cerrada no se reescribe ni se borra: es la que explica como se pacto un compromiso de hace tres meses.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34.5" customHeight="1" s="36">
       <c r="A24" s="67" t="inlineStr">
         <is>
-          <t>DEC-209</t>
+          <t>DEC-213</t>
         </is>
       </c>
       <c r="B24" s="68" t="inlineStr">
@@ -15573,24 +15623,24 @@
       <c r="C24" s="68" t="n"/>
       <c r="D24" s="69" t="inlineStr">
         <is>
-          <t>La forma del codigo de localidad la declara el pais, no el codigo</t>
+          <t>margin_basis es configuracion, no una pregunta</t>
         </is>
       </c>
       <c r="E24" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F24" s="69" t="inlineStr">
         <is>
-          <t>El comprobante peruano lleva el ubigeo del INEI (seis digitos) y el colombiano el codigo DANE (cinco). Una columna ubigeo CHAR(6) habria sido la regla de un pais escrita en el codigo de los seis y rechazaria un codigo colombiano correcto. countries declara como se llama, que forma tiene y si ese pais lo exige; el formulario pide «Ubigeo» a una peruana y «Codigo DANE» a una colombiana sin una linea de codigo por pais. La imponen dos disparadores cruzados que leen el patron de countries.</t>
+          <t>Con 100 de neto y 29,5 % el costo es 141,84; el ejemplo del negocio dio 170,21, que es 141,84 x 1,20 (recargo sobre el COSTO). Un 20 % de margen sobre el INGRESO habria dado 177,31. Lo iba a preguntar dos veces; DEC-190 dice que estas cosas se configuran, y preguntarlo habria sido quemar la respuesta en el codigo con la firma del negocio encima. Es una columna con dos valores, sembrada en cost, con la pantalla ensenando las dos cifras y una prueba de cada una.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45.75" customHeight="1" s="36">
       <c r="A25" s="67" t="inlineStr">
         <is>
-          <t>DEC-210</t>
+          <t>DEC-214</t>
         </is>
       </c>
       <c r="B25" s="68" t="inlineStr">
@@ -15601,24 +15651,24 @@
       <c r="C25" s="68" t="n"/>
       <c r="D25" s="69" t="inlineStr">
         <is>
-          <t>El codigo de establecimiento nace en «0000» y no admite nulo</t>
+          <t>Se pacta el costo o el neto, y el ingreso minimo se dice, no se impone</t>
         </is>
       </c>
       <c r="E25" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F25" s="69" t="inlineStr">
         <is>
-          <t>Un comprobante SIEMPRE lleva uno; dejarlo nulo obligaria a decidirlo al emitir, que es tarde. «0000» es el domicilio fiscal en SUNAT. El formulario lo puede dejar en blanco --al crear y al editar-- y entonces vale 0000: sin esa normalizacion, vaciar el campo metia una cadena vacia que ck_le_establecimiento rechaza con un 45000 sin explicar nada.</t>
+          <t>agreed_amount sigue siendo el costo: de esa columna cuelgan devengos, pagos y la rentabilidad de 9.10. Se anaden la base, el neto y la tasa. Con net se teclean 100 y se escriben 141,8440, y el motor rehace la resta: un neto que no cuadra con su bruto se descubriria en la conversacion con el creador que cobro de menos. El mensaje dice el ingreso minimo y no bloquea: se puede aceptar menos margen, pero sabiendolo y antes de invitar. Los tres numeros se congelan en la participacion.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="57" customHeight="1" s="36">
       <c r="A26" s="67" t="inlineStr">
         <is>
-          <t>DEC-211</t>
+          <t>DEC-215</t>
         </is>
       </c>
       <c r="B26" s="68" t="inlineStr">
@@ -15629,24 +15679,24 @@
       <c r="C26" s="68" t="n"/>
       <c r="D26" s="69" t="inlineStr">
         <is>
-          <t>Que falte el ubigeo no bloquea: es un aviso rojo</t>
+          <t>La cuenta la hace el motor, no PHP</t>
         </is>
       </c>
       <c r="E26" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F26" s="69" t="inlineStr">
         <is>
-          <t>requires_tax_location no impide guardar una sociedad a medias; hace que el panel de 9.17b lo enseñe en rojo con el nombre que ese pais le da. Y sale a la luz algo que no decia nadie: el sembrador escribe address_line1 = «Por completar» porque la columna es NOT NULL, la sociedad parecia completa, y ese texto habria salido impreso en un comprobante.</t>
+          <t>neto / (1 - tasa/100) con float da 141.84397163120568 y de ahi a un DECIMAL(18,4) hay un redondeo que puede caer del lado que el CHECK no admite. El contenedor no tiene bcmath, asi que la aritmetica exacta se hace en el motor con CAST a DECIMAL(28,12). Misma tecnica que 9.1 y 9.3.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="68.25" customHeight="1" s="36">
       <c r="A27" s="67" t="inlineStr">
         <is>
-          <t>DEC-205</t>
+          <t>DEC-209</t>
         </is>
       </c>
       <c r="B27" s="68" t="inlineStr">
@@ -15657,24 +15707,24 @@
       <c r="C27" s="68" t="n"/>
       <c r="D27" s="69" t="inlineStr">
         <is>
-          <t>Un registro de preparacion, y cada modulo declara lo suyo</t>
+          <t>La forma del codigo de localidad la declara el pais, no el codigo</t>
         </is>
       </c>
       <c r="E27" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F27" s="69" t="inlineStr">
         <is>
-          <t>9.16 y 9.17 dejaron cada una su lista de avisos y cada una solo se ve entrando en su pantalla. Preparacion las junta, y cada modulo declara las comprobaciones de su area en su ServiceProvider: un revisor central pondria a Shared a saber de cinco modulos sin que deptrac lo vea, porque son consultas a tablas y no clases importadas. Hay una prueba que se rompe cuando alguien construye una pantalla de configuracion nueva y no la enchufa.</t>
+          <t>El comprobante peruano lleva el ubigeo del INEI (seis digitos) y el colombiano el codigo DANE (cinco). Una columna ubigeo CHAR(6) habria sido la regla de un pais escrita en el codigo de los seis y rechazaria un codigo colombiano correcto. countries declara como se llama, que forma tiene y si ese pais lo exige; el formulario pide «Ubigeo» a una peruana y «Codigo DANE» a una colombiana sin una linea de codigo por pais. La imponen dos disparadores cruzados que leen el patron de countries.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="57" customHeight="1" s="36">
       <c r="A28" s="67" t="inlineStr">
         <is>
-          <t>DEC-206</t>
+          <t>DEC-210</t>
         </is>
       </c>
       <c r="B28" s="68" t="inlineStr">
@@ -15685,24 +15735,24 @@
       <c r="C28" s="68" t="n"/>
       <c r="D28" s="69" t="inlineStr">
         <is>
-          <t>Si no puedes arreglarlo, no lo ves</t>
+          <t>El codigo de establecimiento nace en «0000» y no admite nulo</t>
         </is>
       </c>
       <c r="E28" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F28" s="69" t="inlineStr">
         <is>
-          <t>Cada area declara el permiso con el que SE ARREGLA, no el que hace falta para abrir el panel, y la revision filtra por el. BR-SEC-001 sigue en pie aunque la pantalla reuna en un sitio lo que estaba repartido en cinco, y ningun aviso lleva a un 403. Por eso config.view se le puede dar a finanzas sin miedo: ve el area de tipos de cambio y nada mas.</t>
+          <t>Un comprobante SIEMPRE lleva uno; dejarlo nulo obligaria a decidirlo al emitir, que es tarde. «0000» es el domicilio fiscal en SUNAT. El formulario lo puede dejar en blanco --al crear y al editar-- y entonces vale 0000: sin esa normalizacion, vaciar el campo metia una cadena vacia que ck_le_establecimiento rechaza con un 45000 sin explicar nada.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="68.25" customHeight="1" s="36">
       <c r="A29" s="67" t="inlineStr">
         <is>
-          <t>DEC-207</t>
+          <t>DEC-211</t>
         </is>
       </c>
       <c r="B29" s="68" t="inlineStr">
@@ -15713,24 +15763,24 @@
       <c r="C29" s="68" t="n"/>
       <c r="D29" s="69" t="inlineStr">
         <is>
-          <t>Una comprobacion que revienta no tumba el panel</t>
+          <t>Que falte el ubigeo no bloquea: es un aviso rojo</t>
         </is>
       </c>
       <c r="E29" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F29" s="69" t="inlineStr">
         <is>
-          <t>Un revisor que lanza una excepcion se convierte en un aviso ambar que lo dice, y las demas areas se siguen viendo. Un panel de «que me falta» que responde 500 porque a un area le pasa algo deja de contestar justo el dia en que hay algo que contestar.</t>
+          <t>requires_tax_location no impide guardar una sociedad a medias; hace que el panel de 9.17b lo enseñe en rojo con el nombre que ese pais le da. Y sale a la luz algo que no decia nadie: el sembrador escribe address_line1 = «Por completar» porque la columna es NOT NULL, la sociedad parecia completa, y ese texto habria salido impreso en un comprobante.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45.75" customHeight="1" s="36">
       <c r="A30" s="67" t="inlineStr">
         <is>
-          <t>DEC-208</t>
+          <t>DEC-205</t>
         </is>
       </c>
       <c r="B30" s="68" t="inlineStr">
@@ -15741,7 +15791,7 @@
       <c r="C30" s="68" t="n"/>
       <c r="D30" s="69" t="inlineStr">
         <is>
-          <t>El correo en log es ROJO, y va el primero del panel</t>
+          <t>Un registro de preparacion, y cada modulo declara lo suyo</t>
         </is>
       </c>
       <c r="E30" s="69" t="inlineStr">
@@ -15751,14 +15801,14 @@
       </c>
       <c r="F30" s="69" t="inlineStr">
         <is>
-          <t>mail.default vale log mientras nadie ponga una cuenta SMTP (Q-20), y con ese valor el correo no sale de la maquina: se escribe en storage/logs. La aplicacion no falla, la bitacora dice enviado y el creador no recibe su enlace de alta. Es el modo de fallo mas caro del sistema porque no se nota desde dentro, y hasta hoy no lo decia ninguna pantalla.</t>
+          <t>9.16 y 9.17 dejaron cada una su lista de avisos y cada una solo se ve entrando en su pantalla. Preparacion las junta, y cada modulo declara las comprobaciones de su area en su ServiceProvider: un revisor central pondria a Shared a saber de cinco modulos sin que deptrac lo vea, porque son consultas a tablas y no clases importadas. Hay una prueba que se rompe cuando alguien construye una pantalla de configuracion nueva y no la enchufa.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="79.5" customHeight="1" s="36">
       <c r="A31" s="67" t="inlineStr">
         <is>
-          <t>DEC-199</t>
+          <t>DEC-206</t>
         </is>
       </c>
       <c r="B31" s="68" t="inlineStr">
@@ -15769,24 +15819,24 @@
       <c r="C31" s="68" t="n"/>
       <c r="D31" s="69" t="inlineStr">
         <is>
-          <t>La marca es una fila, y hay UNA sola por defecto</t>
+          <t>Si no puedes arreglarlo, no lo ves</t>
         </is>
       </c>
       <c r="E31" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F31" s="69" t="inlineStr">
         <is>
-          <t>«LATAM Social» estaba escrito en tres plantillas --title, barra lateral y pantalla de acceso--, el favicon era un archivo del repositorio y el pie legal con la razon social y el RUC estaba a mano al pie del formulario de entrada. platform_brands guardaba todo eso desde 2.10 y nadie la leyo nunca. default_gate es la 28.a columna puerta y uq_pb_default la hace unica: dos marcas por defecto es media aplicacion ensenando un nombre y la otra mitad otro sin que nada falle.</t>
+          <t>Cada area declara el permiso con el que SE ARREGLA, no el que hace falta para abrir el panel, y la revision filtra por el. BR-SEC-001 sigue en pie aunque la pantalla reuna en un sitio lo que estaba repartido en cinco, y ningun aviso lleva a un 403. Por eso config.view se le puede dar a finanzas sin miedo: ve el area de tipos de cambio y nada mas.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="68.25" customHeight="1" s="36">
       <c r="A32" s="67" t="inlineStr">
         <is>
-          <t>DEC-200</t>
+          <t>DEC-207</t>
         </is>
       </c>
       <c r="B32" s="68" t="inlineStr">
@@ -15797,24 +15847,24 @@
       <c r="C32" s="68" t="n"/>
       <c r="D32" s="69" t="inlineStr">
         <is>
-          <t>Una configuracion que falta NO bloquea: valor de partida y aviso con prioridad</t>
+          <t>Una comprobacion que revienta no tumba el panel</t>
         </is>
       </c>
       <c r="E32" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F32" s="69" t="inlineStr">
         <is>
-          <t>DEC-190 llevado al codigo. Sin tabla, sin fila o con un campo vacio se cae al valor de partida y aparece un badge: rojo lo que un tercero va a ver mal (sin logotipo, sin correo de soporte), ambar lo que conviene (sin favicon, sin pie legal, sin web), verde cuando no falta nada. El sistema arranca con dos rojos y funciona perfectamente con los dos puestos.</t>
+          <t>Un revisor que lanza una excepcion se convierte en un aviso ambar que lo dice, y las demas areas se siguen viendo. Un panel de «que me falta» que responde 500 porque a un area le pasa algo deja de contestar justo el dia en que hay algo que contestar.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45.75" customHeight="1" s="36">
       <c r="A33" s="67" t="inlineStr">
         <is>
-          <t>DEC-201</t>
+          <t>DEC-208</t>
         </is>
       </c>
       <c r="B33" s="68" t="inlineStr">
@@ -15825,24 +15875,24 @@
       <c r="C33" s="68" t="n"/>
       <c r="D33" s="69" t="inlineStr">
         <is>
-          <t>El logotipo se sirve por una puerta publica propia, sin identificador</t>
+          <t>El correo en log es ROJO, y va el primero del panel</t>
         </is>
       </c>
       <c r="E33" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F33" s="69" t="inlineStr">
         <is>
-          <t>La pantalla de acceso la ve quien no ha entrado, asi que el permiso file.view de 9.15 dejaria la marca fuera de la unica pantalla que ve todo el mundo. Lo que hace seguras a /marca/logo y /marca/favicon no es un permiso: es que NO aceptan identificador. Estan en RUTAS-ABIERTAS con su motivo y MuroTest las conoce.</t>
+          <t>mail.default vale log mientras nadie ponga una cuenta SMTP (Q-20), y con ese valor el correo no sale de la maquina: se escribe en storage/logs. La aplicacion no falla, la bitacora dice enviado y el creador no recibe su enlace de alta. Es el modo de fallo mas caro del sistema porque no se nota desde dentro, y hasta hoy no lo decia ninguna pantalla.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45.75" customHeight="1" s="36">
       <c r="A34" s="67" t="inlineStr">
         <is>
-          <t>DEC-202</t>
+          <t>DEC-199</t>
         </is>
       </c>
       <c r="B34" s="68" t="inlineStr">
@@ -15853,7 +15903,7 @@
       <c r="C34" s="68" t="n"/>
       <c r="D34" s="69" t="inlineStr">
         <is>
-          <t>El codigo de la marca no se cambia; el nombre visible si</t>
+          <t>La marca es una fila, y hay UNA sola por defecto</t>
         </is>
       </c>
       <c r="E34" s="69" t="inlineStr">
@@ -15863,14 +15913,14 @@
       </c>
       <c r="F34" s="69" t="inlineStr">
         <is>
-          <t>tg_pb_code lo impide en el motor. El code es la llave con la que el sembrador encuentra la marca: si cambia, el siguiente db:seed crea otra, el sistema amanece con dos y las pantallas siguen ensenando la vieja mientras alguien edita la nueva.</t>
+          <t>«LATAM Social» estaba escrito en tres plantillas --title, barra lateral y pantalla de acceso--, el favicon era un archivo del repositorio y el pie legal con la razon social y el RUC estaba a mano al pie del formulario de entrada. platform_brands guardaba todo eso desde 2.10 y nadie la leyo nunca. default_gate es la 28.a columna puerta y uq_pb_default la hace unica: dos marcas por defecto es media aplicacion ensenando un nombre y la otra mitad otro sin que nada falle.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="68.25" customHeight="1" s="36">
       <c r="A35" s="67" t="inlineStr">
         <is>
-          <t>DEC-203</t>
+          <t>DEC-200</t>
         </is>
       </c>
       <c r="B35" s="68" t="inlineStr">
@@ -15881,7 +15931,7 @@
       <c r="C35" s="68" t="n"/>
       <c r="D35" s="69" t="inlineStr">
         <is>
-          <t>Los colores y la tipografia se desinfectan ademas del CHECK</t>
+          <t>Una configuracion que falta NO bloquea: valor de partida y aviso con prioridad</t>
         </is>
       </c>
       <c r="E35" s="69" t="inlineStr">
@@ -15891,14 +15941,14 @@
       </c>
       <c r="F35" s="69" t="inlineStr">
         <is>
-          <t>El color acaba dentro de una regla CSS y la tipografia dentro de una URL y de una regla CSS, en todas las pantallas a la vez. Un nombre con comillas y llaves cierra la regla y escribe estilo ajeno en toda la aplicacion. Si el valor entra por una via que no pasa por el CHECK --carga masiva, restauracion de copia--, la segunda cerradura es lo unico que queda.</t>
+          <t>DEC-190 llevado al codigo. Sin tabla, sin fila o con un campo vacio se cae al valor de partida y aparece un badge: rojo lo que un tercero va a ver mal (sin logotipo, sin correo de soporte), ambar lo que conviene (sin favicon, sin pie legal, sin web), verde cuando no falta nada. El sistema arranca con dos rojos y funciona perfectamente con los dos puestos.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="57" customHeight="1" s="36">
       <c r="A36" s="67" t="inlineStr">
         <is>
-          <t>DEC-204</t>
+          <t>DEC-201</t>
         </is>
       </c>
       <c r="B36" s="68" t="inlineStr">
@@ -15909,7 +15959,7 @@
       <c r="C36" s="68" t="n"/>
       <c r="D36" s="69" t="inlineStr">
         <is>
-          <t>brand.manage es un permiso propio, y no legal_entity.manage</t>
+          <t>El logotipo se sirve por una puerta publica propia, sin identificador</t>
         </is>
       </c>
       <c r="E36" s="69" t="inlineStr">
@@ -15919,14 +15969,14 @@
       </c>
       <c r="F36" s="69" t="inlineStr">
         <is>
-          <t>Quien da de alta sociedades del grupo no tiene por que poder cambiar lo que ve todo el mundo en todas las pantallas, incluida la de acceso. Hoy los dos los tiene solo admin; el dia que legal_entity.manage se le de a alguien de operaciones, esa persona no podra cambiar la marca. Hay una prueba que lo fija.</t>
+          <t>La pantalla de acceso la ve quien no ha entrado, asi que el permiso file.view de 9.15 dejaria la marca fuera de la unica pantalla que ve todo el mundo. Lo que hace seguras a /marca/logo y /marca/favicon no es un permiso: es que NO aceptan identificador. Estan en RUTAS-ABIERTAS con su motivo y MuroTest las conoce.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="68.25" customHeight="1" s="36">
       <c r="A37" s="67" t="inlineStr">
         <is>
-          <t>DEC-198</t>
+          <t>DEC-202</t>
         </is>
       </c>
       <c r="B37" s="68" t="inlineStr">
@@ -15937,24 +15987,24 @@
       <c r="C37" s="68" t="n"/>
       <c r="D37" s="69" t="inlineStr">
         <is>
-          <t>El permiso se mira en CADA peticion: no hay URL firmada de archivo.</t>
+          <t>El codigo de la marca no se cambia; el nombre visible si</t>
         </is>
       </c>
       <c r="E37" s="69" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F37" s="69" t="inlineStr">
         <is>
-          <t>Una URL firmada sigue funcionando cuando se reenvia y cuando a esa persona ya se le quito el acceso, y lo que sale por aqui son documentos de identidad y comprobantes bancarios. Con ruta propia, quitar un permiso surte efecto en la siguiente peticion y no queda ningun enlace circulando. El archivo se busca por uuid y no por id --un id correlativo invita a probar el siguiente-- y la respuesta lleva no-store (una identidad en la cache de un equipo compartido sobrevive al cierre de sesion), nosniff y una CSP que impide que un HTML o un SVG subido como «evidencia» se ejecute. El creador ve lo suyo, incluida su identidad: es informacion suya y le permite comprobar que archivamos el correcto. Rastro en bitacora solo para los sensibles --identidad, terminos y comprobante bancario--: anotar cada captura convertiria la bitacora en ruido, y una bitacora que nadie lee no protege nada</t>
+          <t>tg_pb_code lo impide en el motor. El code es la llave con la que el sembrador encuentra la marca: si cambia, el siguiente db:seed crea otra, el sistema amanece con dos y las pantallas siguen ensenando la vieja mientras alguien edita la nueva.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="45.75" customHeight="1" s="36">
       <c r="A38" s="67" t="inlineStr">
         <is>
-          <t>DEC-197</t>
+          <t>DEC-203</t>
         </is>
       </c>
       <c r="B38" s="68" t="inlineStr">
@@ -15965,24 +16015,24 @@
       <c r="C38" s="68" t="n"/>
       <c r="D38" s="69" t="inlineStr">
         <is>
-          <t>Cada modulo declara quien puede ver SUS archivos; no hay un switch central.</t>
+          <t>Los colores y la tipografia se desinfectan ademas del CHECK</t>
         </is>
       </c>
       <c r="E38" s="69" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>La regla de cada archivo depende de la tabla que lo apunta --identidad de creators, captura de publication_evidence, comprobante de payouts-- y un decisor central que las consultara todas pondria a Shared o a Core a saber de payouts. deptrac no lo veria: son consultas a tablas y no clases importadas, o sea una frontera rota en silencio, que es la peor clase. Cada modulo registra su regla en su ServiceProvider, igual que registra sus escuchas. Y se niega por omision: un proposito sin regla no se abre ni para el administrador, asi que un archivo nuevo cuyo autor olvido declarar quien puede verlo se queda cerrado y no abierto a todos</t>
+          <t>El color acaba dentro de una regla CSS y la tipografia dentro de una URL y de una regla CSS, en todas las pantallas a la vez. Un nombre con comillas y llaves cierra la regla y escribe estilo ajeno en toda la aplicacion. Si el valor entra por una via que no pasa por el CHECK --carga masiva, restauracion de copia--, la segunda cerradura es lo unico que queda.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="90.75" customHeight="1" s="36">
       <c r="A39" s="67" t="inlineStr">
         <is>
-          <t>DEC-196</t>
+          <t>DEC-204</t>
         </is>
       </c>
       <c r="B39" s="68" t="inlineStr">
@@ -15993,24 +16043,24 @@
       <c r="C39" s="68" t="n"/>
       <c r="D39" s="69" t="inlineStr">
         <is>
-          <t>La Academia del creador se construye, y cada modulo se configura desde el admin.</t>
+          <t>brand.manage es un permiso propio, y no legal_entity.manage</t>
         </is>
       </c>
       <c r="E39" s="69" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>Es G-08 del addendum de gamificacion y la de mas retorno de las once: modulos cortos --leer un brief sin gastar rondas, iluminacion y audio con un movil, como se rotula el contenido comercial, que derechos esta cediendo, como subir su evidencia-- con evaluacion al final e insignia de creador certificado. Ataca tres dolores ya medidos: cada ronda evitada es tiempo del equipo de revision, cada evidencia subida sola es el proceso mas manual que se deja de perseguir, y «creadores certificados» es un argumento de venta ante la marca. El software es la parte barata: modulos, orden, formato, evaluacion, intentos, XP e insignia salen del admin (DEC-190), y al completar uno se levanta TrainingModuleCompleted, previsto en el modelo desde la Fase 2. Lo caro es el CONTENIDO --guiones, video, mantenerlo cuando cambie una norma o una red-- y eso no lo hace el sistema. Se puede arrancar con modulos de solo texto, que cuestan casi nada y ya bajan rondas. Cierra Q-27</t>
+          <t>Quien da de alta sociedades del grupo no tiene por que poder cambiar lo que ve todo el mundo en todas las pantallas, incluida la de acceso. Hoy los dos los tiene solo admin; el dia que legal_entity.manage se le de a alguien de operaciones, esa persona no podra cambiar la marca. Hay una prueba que lo fija.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="45.75" customHeight="1" s="36">
       <c r="A40" s="67" t="inlineStr">
         <is>
-          <t>DEC-195</t>
+          <t>DEC-198</t>
         </is>
       </c>
       <c r="B40" s="68" t="inlineStr">
@@ -16021,24 +16071,24 @@
       <c r="C40" s="68" t="n"/>
       <c r="D40" s="69" t="inlineStr">
         <is>
-          <t>El lado del tipo de cambio se configura POR TIPO DE TRANSACCION.</t>
+          <t>El permiso se mira en CADA peticion: no hay URL firmada de archivo.</t>
         </is>
       </c>
       <c r="E40" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>No se fija uno en el codigo: lo que se le paga a un creador, lo que se le cobra a un cliente y un gasto operativo no tienen por que convertirse con el mismo lado, y esa eleccion es contable. El admin declara, para cada tipo de transaccion, que lado se aplica (compra, venta o media) y con que fuente. Cierra Q-63, que era la que impedia dar un porcentaje de margen cuando hay dos monedas (DEC-185)</t>
+          <t>Una URL firmada sigue funcionando cuando se reenvia y cuando a esa persona ya se le quito el acceso, y lo que sale por aqui son documentos de identidad y comprobantes bancarios. Con ruta propia, quitar un permiso surte efecto en la siguiente peticion y no queda ningun enlace circulando. El archivo se busca por uuid y no por id --un id correlativo invita a probar el siguiente-- y la respuesta lleva no-store (una identidad en la cache de un equipo compartido sobrevive al cierre de sesion), nosniff y una CSP que impide que un HTML o un SVG subido como «evidencia» se ejecute. El creador ve lo suyo, incluida su identidad: es informacion suya y le permite comprobar que archivamos el correcto. Rastro en bitacora solo para los sensibles --identidad, terminos y comprobante bancario--: anotar cada captura convertiria la bitacora en ruido, y una bitacora que nadie lee no protege nada</t>
         </is>
       </c>
     </row>
     <row r="41" ht="57" customHeight="1" s="36">
       <c r="A41" s="67" t="inlineStr">
         <is>
-          <t>DEC-194</t>
+          <t>DEC-197</t>
         </is>
       </c>
       <c r="B41" s="68" t="inlineStr">
@@ -16049,24 +16099,24 @@
       <c r="C41" s="68" t="n"/>
       <c r="D41" s="69" t="inlineStr">
         <is>
-          <t>La gamificacion premia con reconocimiento y con un catalogo de premios canjeables por XP.</t>
+          <t>Cada modulo declara quien puede ver SUS archivos; no hay un switch central.</t>
         </is>
       </c>
       <c r="E41" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>Nada de dinero. Los premios --viajes, objetos-- viven en una tabla configurable desde el admin con su coste en XP y su disponibilidad, y el creador los canjea. El hito que consolida un referido es la primera campana completada (Q-25). Cierra Q-23, Q-24 y Q-26</t>
+          <t>La regla de cada archivo depende de la tabla que lo apunta --identidad de creators, captura de publication_evidence, comprobante de payouts-- y un decisor central que las consultara todas pondria a Shared o a Core a saber de payouts. deptrac no lo veria: son consultas a tablas y no clases importadas, o sea una frontera rota en silencio, que es la peor clase. Cada modulo registra su regla en su ServiceProvider, igual que registra sus escuchas. Y se niega por omision: un proposito sin regla no se abre ni para el administrador, asi que un archivo nuevo cuyo autor olvido declarar quien puede verlo se queda cerrado y no abierto a todos</t>
         </is>
       </c>
     </row>
     <row r="42" ht="45.75" customHeight="1" s="36">
       <c r="A42" s="67" t="inlineStr">
         <is>
-          <t>DEC-193</t>
+          <t>DEC-196</t>
         </is>
       </c>
       <c r="B42" s="68" t="inlineStr">
@@ -16077,24 +16127,24 @@
       <c r="C42" s="68" t="n"/>
       <c r="D42" s="69" t="inlineStr">
         <is>
-          <t>Publicar terminos nuevos no expulsa a nadie de golpe: hay plazo, aviso y aterrizaje suave.</t>
+          <t>La Academia del creador se construye, y cada modulo se configura desde el admin.</t>
         </is>
       </c>
       <c r="E42" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>Correo con enlace de aceptacion, 15 dias de plazo, aviso en la bandeja interna de la plataforma y recordatorio al entrar. Cumplido el plazo sin aceptar, la sesion cae en una pantalla que exige aceptar para continuar; si no acepta, solo lectura durante 30 dias. Los dos plazos son configurables (DEC-190). Es la respuesta a Q-46, y encaja con el «cambio menor» de 9.16: una errata no dispara nada de esto</t>
+          <t>Es G-08 del addendum de gamificacion y la de mas retorno de las once: modulos cortos --leer un brief sin gastar rondas, iluminacion y audio con un movil, como se rotula el contenido comercial, que derechos esta cediendo, como subir su evidencia-- con evaluacion al final e insignia de creador certificado. Ataca tres dolores ya medidos: cada ronda evitada es tiempo del equipo de revision, cada evidencia subida sola es el proceso mas manual que se deja de perseguir, y «creadores certificados» es un argumento de venta ante la marca. El software es la parte barata: modulos, orden, formato, evaluacion, intentos, XP e insignia salen del admin (DEC-190), y al completar uno se levanta TrainingModuleCompleted, previsto en el modelo desde la Fase 2. Lo caro es el CONTENIDO --guiones, video, mantenerlo cuando cambie una norma o una red-- y eso no lo hace el sistema. Se puede arrancar con modulos de solo texto, que cuestan casi nada y ya bajan rondas. Cierra Q-27</t>
         </is>
       </c>
     </row>
     <row r="43" ht="68.25" customHeight="1" s="36">
       <c r="A43" s="67" t="inlineStr">
         <is>
-          <t>DEC-192</t>
+          <t>DEC-195</t>
         </is>
       </c>
       <c r="B43" s="68" t="inlineStr">
@@ -16105,7 +16155,7 @@
       <c r="C43" s="68" t="n"/>
       <c r="D43" s="69" t="inlineStr">
         <is>
-          <t>Facturacion electronica DIRECTA con SUNAT, no por proveedor.</t>
+          <t>El lado del tipo de cambio se configura POR TIPO DE TRANSACCION.</t>
         </is>
       </c>
       <c r="E43" s="69" t="inlineStr">
@@ -16115,14 +16165,14 @@
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>Configurable entero desde el admin: URL, certificado, usuario y clave secundarios, y correlativos independientes de factura, boleta y notas de credito de cada una. Con monitor de documentos timbrados: estado de cada uno, reintento manual, reintento automatico por job con frecuencia y numero de reintentos configurables, descarga de CDR, XML y PDF --el PDF con plantilla configurable-- y envio al cliente por correo con cuerpo configurable y variables arrastrables. Cierra Q-03 y de paso Q-21, que preguntaba por el contrato con un proveedor que ya no hay</t>
+          <t>No se fija uno en el codigo: lo que se le paga a un creador, lo que se le cobra a un cliente y un gasto operativo no tienen por que convertirse con el mismo lado, y esa eleccion es contable. El admin declara, para cada tipo de transaccion, que lado se aplica (compra, venta o media) y con que fuente. Cierra Q-63, que era la que impedia dar un porcentaje de margen cuando hay dos monedas (DEC-185)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="79.5" customHeight="1" s="36">
       <c r="A44" s="67" t="inlineStr">
         <is>
-          <t>DEC-191</t>
+          <t>DEC-194</t>
         </is>
       </c>
       <c r="B44" s="68" t="inlineStr">
@@ -16133,7 +16183,7 @@
       <c r="C44" s="68" t="n"/>
       <c r="D44" s="69" t="inlineStr">
         <is>
-          <t>La retencion se calcula HACIA ATRAS desde el neto pactado, y se compara con un umbral de rentabilidad.</t>
+          <t>La gamificacion premia con reconocimiento y con un catalogo de premios canjeables por XP.</t>
         </is>
       </c>
       <c r="E44" s="69" t="inlineStr">
@@ -16143,14 +16193,14 @@
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>Con el creador se pacta lo que VA A RECIBIR --«te pago 100»--; el sistema calcula el bruto que hay que provisionar con la tasa configurada (29,5% por defecto, Q-13/Q-40): bruto = neto / (1 - tasa), o sea 141,84 para 100 netos, de los que 41,84 son retencion. Tres campos y no uno: neto pactado, tasa aplicada (por defecto la del admin, editable en el trato) e importe bruto. Encima va un umbral de rentabilidad minima configurable: con el bruto como costo, la pantalla dice cual es el ingreso mas bajo que hace aceptable esa participacion, y avisa antes de cerrar el trato --no despues--. La tasa, el umbral y la base sobre la que se mide el umbral (sobre costo o sobre ingreso: no dan el mismo numero) salen del admin</t>
+          <t>Nada de dinero. Los premios --viajes, objetos-- viven en una tabla configurable desde el admin con su coste en XP y su disponibilidad, y el creador los canjea. El hito que consolida un referido es la primera campana completada (Q-25). Cierra Q-23, Q-24 y Q-26</t>
         </is>
       </c>
     </row>
     <row r="45" ht="124.5" customHeight="1" s="36">
       <c r="A45" s="67" t="inlineStr">
         <is>
-          <t>DEC-190</t>
+          <t>DEC-193</t>
         </is>
       </c>
       <c r="B45" s="68" t="inlineStr">
@@ -16158,14 +16208,10 @@
           <t>Decidida</t>
         </is>
       </c>
-      <c r="C45" s="68" t="inlineStr">
-        <is>
-          <t>Critica</t>
-        </is>
-      </c>
+      <c r="C45" s="68" t="n"/>
       <c r="D45" s="69" t="inlineStr">
         <is>
-          <t>PRINCIPIO RECTOR: la plataforma es WHITE LABEL y todo se configura desde el admin.</t>
+          <t>Publicar terminos nuevos no expulsa a nadie de golpe: hay plazo, aviso y aterrizaje suave.</t>
         </is>
       </c>
       <c r="E45" s="69" t="inlineStr">
@@ -16175,14 +16221,14 @@
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>Nada de reglas de negocio quemadas en el codigo: ni la razon social, ni el RUC, ni el representante legal, ni la direccion, ni el ubigeo, ni las tasas, ni los plazos, ni los correlativos, ni las credenciales de ninguna API. Lo que el codigo aporta es la REGLA; el VALOR sale de la configuracion. Y una configuracion sin valor no bloquea: se siembra con un valor de partida y se avisa con su prioridad --rojo si es delicado y sigue de fabrica, ambar si conviene revisarlo--. Esto corrige el criterio con el que se habian tomado varias decisiones anteriores --3.5 dejaba el sistema sin arrancar hasta que alguien corriera un comando, y varias preguntas de negocio se plantearon como «elige una y la quemo» cuando la respuesta correcta era «las dos, y que se elija en el admin»--. Toda decision anterior que fije un valor en el codigo queda sujeta a revision bajo este principio (T-69)</t>
+          <t>Correo con enlace de aceptacion, 15 dias de plazo, aviso en la bandeja interna de la plataforma y recordatorio al entrar. Cumplido el plazo sin aceptar, la sesion cae en una pantalla que exige aceptar para continuar; si no acepta, solo lectura durante 30 dias. Los dos plazos son configurables (DEC-190). Es la respuesta a Q-46, y encaja con el «cambio menor» de 9.16: una errata no dispara nada de esto</t>
         </is>
       </c>
     </row>
     <row r="46" ht="90.75" customHeight="1" s="36">
       <c r="A46" s="67" t="inlineStr">
         <is>
-          <t>DEC-189</t>
+          <t>DEC-192</t>
         </is>
       </c>
       <c r="B46" s="68" t="inlineStr">
@@ -16193,24 +16239,24 @@
       <c r="C46" s="68" t="n"/>
       <c r="D46" s="69" t="inlineStr">
         <is>
-          <t>Las 23 rutas sin permiso se escriben, con su motivo, en RUTAS-ABIERTAS.</t>
+          <t>Facturacion electronica DIRECTA con SUNAT, no por proveedor.</t>
         </is>
       </c>
       <c r="E46" s="69" t="inlineStr">
         <is>
-          <t>9.14b</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>Hasta hoy nada distinguia «es publica a proposito» --entrar, recuperar la contrasena, los enlaces firmados de 7.6 y 8.5-- de «se le olvido el middleware a alguien». verificar-muro.py comprueba que tres sitios digan lo mismo: la lista, routes/web.php y la constante de MuroTest; no se pueden fundir porque una la lee Python sin Laravel y otra PHPUnit, y tres copias es como se pierde una (SUITES, 3.12). Al CI: una ruta nueva sin permiso que no este escrita lo pone en rojo. De paso se cerraron dos puertas que no eran nuestras: storage.local y storage.local.upload, que registra el framework con serve =&gt; true sobre el disco privado. No eran una fuga --exigen URL firmada-- pero la aplicacion no genera ninguna, asi que no servian para nada; y ninguna lectura del codigo las habria encontrado, porque no estan en ningun archivo de rutas</t>
+          <t>Configurable entero desde el admin: URL, certificado, usuario y clave secundarios, y correlativos independientes de factura, boleta y notas de credito de cada una. Con monitor de documentos timbrados: estado de cada uno, reintento manual, reintento automatico por job con frecuencia y numero de reintentos configurables, descarga de CDR, XML y PDF --el PDF con plantilla configurable-- y envio al cliente por correo con cuerpo configurable y variables arrastrables. Cierra Q-03 y de paso Q-21, que preguntaba por el contrato con un proveedor que ya no hay</t>
         </is>
       </c>
     </row>
     <row r="47" ht="68.25" customHeight="1" s="36">
       <c r="A47" s="67" t="inlineStr">
         <is>
-          <t>DEC-188</t>
+          <t>DEC-191</t>
         </is>
       </c>
       <c r="B47" s="68" t="inlineStr">
@@ -16221,24 +16267,24 @@
       <c r="C47" s="68" t="n"/>
       <c r="D47" s="69" t="inlineStr">
         <is>
-          <t>El muro se prueba recorriendo TODAS las rutas, no las que uno recuerda.</t>
+          <t>La retencion se calcula HACIA ATRAS desde el neto pactado, y se compara con un umbral de rentabilidad.</t>
         </is>
       </c>
       <c r="E47" s="69" t="inlineStr">
         <is>
-          <t>9.14b</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>MuroTest pide las 145 rutas con nombre como creador, como usuario de cliente y como autenticado sin rol, y exige que ninguna se abra --371 aserciones, y el muro aguanta--. Una pantalla nueva entra sola en la prueba. Las afirmaciones dirigidas que ya habia (DEC-172, DEC-179, DEC-181) comprueban lo que alguien se acordo de mirar; el fallo que de verdad paso --5.9, la portada enseñando los totales internos a cualquier autenticado-- no lo habria cazado ninguna. Lo permitido se escribe en positivo: una lista de lo permitido crece solo cuando alguien la toca a proposito. Se admite un 404 porque SubstituteBindings corre antes del middleware --con un id inventado la ruta contesta antes de llegar al permiso-- y para que no sea el escondite de la prueba se exige que mas de 80 rutas contesten 403 de verdad</t>
+          <t>Con el creador se pacta lo que VA A RECIBIR --«te pago 100»--; el sistema calcula el bruto que hay que provisionar con la tasa configurada (29,5% por defecto, Q-13/Q-40): bruto = neto / (1 - tasa), o sea 141,84 para 100 netos, de los que 41,84 son retencion. Tres campos y no uno: neto pactado, tasa aplicada (por defecto la del admin, editable en el trato) e importe bruto. Encima va un umbral de rentabilidad minima configurable: con el bruto como costo, la pantalla dice cual es el ingreso mas bajo que hace aceptable esa participacion, y avisa antes de cerrar el trato --no despues--. La tasa, el umbral y la base sobre la que se mide el umbral (sobre costo o sobre ingreso: no dan el mismo numero) salen del admin</t>
         </is>
       </c>
     </row>
     <row r="48" ht="45.75" customHeight="1" s="36">
       <c r="A48" s="67" t="inlineStr">
         <is>
-          <t>DEC-187</t>
+          <t>DEC-190</t>
         </is>
       </c>
       <c r="B48" s="68" t="inlineStr">
@@ -16246,27 +16292,31 @@
           <t>Decidida</t>
         </is>
       </c>
-      <c r="C48" s="68" t="n"/>
+      <c r="C48" s="68" t="inlineStr">
+        <is>
+          <t>Critica</t>
+        </is>
+      </c>
       <c r="D48" s="69" t="inlineStr">
         <is>
-          <t>Una suite de QA se construye SU caso y no reusa el de nadie.</t>
+          <t>PRINCIPIO RECTOR: la plataforma es WHITE LABEL y todo se configura desde el admin.</t>
         </is>
       </c>
       <c r="E48" s="69" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>La primera version de 9.14 reusaba lo que dejaban las suites anteriores, como hace 9.6, y se puso amarilla dos veces por motivos opuestos: corriendo sola porque no habia asientos, y corriendo la bateria entera porque para cuando llega el unico devengo pagable ya esta liquidado por 9.6 y las dos participaciones de la semilla estan ocupadas. Ahora crea su campana, su participacion y su devengo. Una suite de QA que depende del orden mide el orden, no la regla</t>
+          <t>Nada de reglas de negocio quemadas en el codigo: ni la razon social, ni el RUC, ni el representante legal, ni la direccion, ni el ubigeo, ni las tasas, ni los plazos, ni los correlativos, ni las credenciales de ninguna API. Lo que el codigo aporta es la REGLA; el VALOR sale de la configuracion. Y una configuracion sin valor no bloquea: se siembra con un valor de partida y se avisa con su prioridad --rojo si es delicado y sigue de fabrica, ambar si conviene revisarlo--. Esto corrige el criterio con el que se habian tomado varias decisiones anteriores --3.5 dejaba el sistema sin arrancar hasta que alguien corriera un comando, y varias preguntas de negocio se plantearon como «elige una y la quemo» cuando la respuesta correcta era «las dos, y que se elija en el admin»--. Toda decision anterior que fije un valor en el codigo queda sujeta a revision bajo este principio (T-69)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="57" customHeight="1" s="36">
       <c r="A49" s="67" t="inlineStr">
         <is>
-          <t>DEC-186</t>
+          <t>DEC-189</t>
         </is>
       </c>
       <c r="B49" s="68" t="inlineStr">
@@ -16277,24 +16327,24 @@
       <c r="C49" s="68" t="n"/>
       <c r="D49" s="69" t="inlineStr">
         <is>
-          <t>Nace verificar-cobertura-sql.py: que regla de la base no ha contestado NUNCA a nadie.</t>
+          <t>Las 23 rutas sin permiso se escriben, con su motivo, en RUTAS-ABIERTAS.</t>
         </is>
       </c>
       <c r="E49" s="69" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.14b</t>
         </is>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>Los verificadores que ya habia comprueban que la regla EXISTA y que sea la misma en los dos motores; ninguno comprobaba lo unico que importa el dia que falle: que alguien se lo haya preguntado. Medido: de las 317 reglas del esquema, 167 no aparecian en ninguna suite ni en ninguna prueba --el 53%--. No significa que esten mal: significa que nadie lo sabe. Una regla que nunca se ha probado no es una regla, es una intencion escrita en DDL. Va a correr-todo.sh y al CI con trinquete (MUDAS-BASE), asi que una regla nueva sin asercion pone el CI en rojo. La pregunta salio de 9.10a, donde campaign_costs llevaba dos semanas con cinco restricciones verdes en todos los verificadores y CERO filas</t>
+          <t>Hasta hoy nada distinguia «es publica a proposito» --entrar, recuperar la contrasena, los enlaces firmados de 7.6 y 8.5-- de «se le olvido el middleware a alguien». verificar-muro.py comprueba que tres sitios digan lo mismo: la lista, routes/web.php y la constante de MuroTest; no se pueden fundir porque una la lee Python sin Laravel y otra PHPUnit, y tres copias es como se pierde una (SUITES, 3.12). Al CI: una ruta nueva sin permiso que no este escrita lo pone en rojo. De paso se cerraron dos puertas que no eran nuestras: storage.local y storage.local.upload, que registra el framework con serve =&gt; true sobre el disco privado. No eran una fuga --exigen URL firmada-- pero la aplicacion no genera ninguna, asi que no servian para nada; y ninguna lectura del codigo las habria encontrado, porque no estan en ningun archivo de rutas</t>
         </is>
       </c>
     </row>
     <row r="50" ht="79.5" customHeight="1" s="36">
       <c r="A50" s="67" t="inlineStr">
         <is>
-          <t>DEC-185</t>
+          <t>DEC-188</t>
         </is>
       </c>
       <c r="B50" s="68" t="inlineStr">
@@ -16305,24 +16355,24 @@
       <c r="C50" s="68" t="n"/>
       <c r="D50" s="69" t="inlineStr">
         <is>
-          <t>El porcentaje de margen solo se da cuando todo esta en una moneda, y si no, se dice por que.</t>
+          <t>El muro se prueba recorriendo TODAS las rutas, no las que uno recuerda.</t>
         </is>
       </c>
       <c r="E50" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14b</t>
         </is>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>Convertir exige elegir compra, venta o media (Q-63) y cada eleccion da un margen distinto para los mismos hechos; el dia que se elija cambian ademas todos los margenes historicos a la vez. Cuando falta, la pantalla escribe el motivo con palabras --«esta campana tiene importes en PEN y USD…»-- y no deja un hueco: quien mira una pantalla donde falta un numero necesita saber si falta porque no lo hay o porque no se puede calcular, y son dos conversaciones distintas. Tampoco hay total por sociedad: el ingreso de hoy es el DECLARADO y no el facturado (9.9), y sumar precios declarados por sociedad se parece a un estado de resultados sin serlo</t>
+          <t>MuroTest pide las 145 rutas con nombre como creador, como usuario de cliente y como autenticado sin rol, y exige que ninguna se abra --371 aserciones, y el muro aguanta--. Una pantalla nueva entra sola en la prueba. Las afirmaciones dirigidas que ya habia (DEC-172, DEC-179, DEC-181) comprueban lo que alguien se acordo de mirar; el fallo que de verdad paso --5.9, la portada enseñando los totales internos a cualquier autenticado-- no lo habria cazado ninguna. Lo permitido se escribe en positivo: una lista de lo permitido crece solo cuando alguien la toca a proposito. Se admite un 404 porque SubstituteBindings corre antes del middleware --con un id inventado la ruta contesta antes de llegar al permiso-- y para que no sea el escondite de la prueba se exige que mas de 80 rutas contesten 403 de verdad</t>
         </is>
       </c>
     </row>
     <row r="51" ht="113.25" customHeight="1" s="36">
       <c r="A51" s="67" t="inlineStr">
         <is>
-          <t>DEC-184</t>
+          <t>DEC-187</t>
         </is>
       </c>
       <c r="B51" s="68" t="inlineStr">
@@ -16333,24 +16383,24 @@
       <c r="C51" s="68" t="n"/>
       <c r="D51" s="69" t="inlineStr">
         <is>
-          <t>Los canjes salen en la lista, marcados, y fuera de todo total.</t>
+          <t>Una suite de QA se construye SU caso y no reusa el de nadie.</t>
         </is>
       </c>
       <c r="E51" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>Su ingreso es cero POR DECISION (7.2), asi que su margen es siempre negativo: el producto y el envio se gastaron igual. Promediarlos hace que la cartera entera parezca peor por un motivo que fue deliberado. Pero se enseñan con su costo, porque un canje tambien cuesta dinero y ese era justo el numero que nadie tenia. Queda fuera del total una segunda clase de campana: la que tiene gastos en OTRA moneda, cuyo margen en la moneda del grupo esta incompleto --y sumar un numero incompleto lo vuelve invisible--. Y la cabecera dice cuantas quedaron fuera y por que: un total que excluye filas sin contarlas engaña por omision</t>
+          <t>La primera version de 9.14 reusaba lo que dejaban las suites anteriores, como hace 9.6, y se puso amarilla dos veces por motivos opuestos: corriendo sola porque no habia asientos, y corriendo la bateria entera porque para cuando llega el unico devengo pagable ya esta liquidado por 9.6 y las dos participaciones de la semilla estan ocupadas. Ahora crea su campana, su participacion y su devengo. Una suite de QA que depende del orden mide el orden, no la regla</t>
         </is>
       </c>
     </row>
     <row r="52" ht="102" customHeight="1" s="36">
       <c r="A52" s="67" t="inlineStr">
         <is>
-          <t>DEC-183</t>
+          <t>DEC-186</t>
         </is>
       </c>
       <c r="B52" s="68" t="inlineStr">
@@ -16361,24 +16411,24 @@
       <c r="C52" s="68" t="n"/>
       <c r="D52" s="69" t="inlineStr">
         <is>
-          <t>Compromiso::margen() se BORRA, no se arregla.</t>
+          <t>Nace verificar-cobertura-sql.py: que regla de la base no ha contestado NUNCA a nadie.</t>
         </is>
       </c>
       <c r="E52" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>Vivia en Campaign desde 7.7 y devolvia revenue_amount menos lo comprometido con creadores: no restaba producto, envios ni produccion, y desde 9.10a esos gastos ya se anotan, asi que el numero habria ido empeorando con cada gasto cargado sin que la pantalla se enterara. No se arregla donde estaba porque campaign_costs es de Finance y deptrac no deja que Campaign la conozca --misma frontera que el devengo de 9.4--. Y se borra en vez de dejarse por si acaso: un metodo que calcula un numero incompleto y se llama margen() es una trampa para quien lo encuentre dentro de seis meses. De paso, SeguimientoController deja de pasar un importe y pasa un booleano mas un enlace: ningun numero interno cruza ya hasta la plantilla, que es BR-SEC-001 un paso mas alla</t>
+          <t>Los verificadores que ya habia comprueban que la regla EXISTA y que sea la misma en los dos motores; ninguno comprobaba lo unico que importa el dia que falle: que alguien se lo haya preguntado. Medido: de las 317 reglas del esquema, 167 no aparecian en ninguna suite ni en ninguna prueba --el 53%--. No significa que esten mal: significa que nadie lo sabe. Una regla que nunca se ha probado no es una regla, es una intencion escrita en DDL. Va a correr-todo.sh y al CI con trinquete (MUDAS-BASE), asi que una regla nueva sin asercion pone el CI en rojo. La pregunta salio de 9.10a, donde campaign_costs llevaba dos semanas con cinco restricciones verdes en todos los verificadores y CERO filas</t>
         </is>
       </c>
     </row>
     <row r="53" ht="79.5" customHeight="1" s="36">
       <c r="A53" s="67" t="inlineStr">
         <is>
-          <t>DEC-182</t>
+          <t>DEC-185</t>
         </is>
       </c>
       <c r="B53" s="68" t="inlineStr">
@@ -16389,24 +16439,24 @@
       <c r="C53" s="68" t="n"/>
       <c r="D53" s="69" t="inlineStr">
         <is>
-          <t>El costo del creador entra al DEVENGARSE, no al pagarse.</t>
+          <t>El porcentaje de margen solo se da cuando todo esta en una moneda, y si no, se dice por que.</t>
         </is>
       </c>
       <c r="E53" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>La deuda existe desde que acepta (9.4) y su importe esta congelado desde 7.5; esperar al pago haria que una campana terminada en marzo pareciera rentabilisima hasta el lote de abril. Sale del libro mayor y no de campaign_creators, porque el libro es quien sabe que devengos siguen vivos: uno anulado ya no se debe. Y no es Compromiso::comprometido(), que cuenta tambien a los shortlisted: alli es correcto --su trabajo es proteger el presupuesto ANTES de invitar-- y aqui contaria dinero de gente que todavia puede decir que no</t>
+          <t>Convertir exige elegir compra, venta o media (Q-63) y cada eleccion da un margen distinto para los mismos hechos; el dia que se elija cambian ademas todos los margenes historicos a la vez. Cuando falta, la pantalla escribe el motivo con palabras --«esta campana tiene importes en PEN y USD…»-- y no deja un hueco: quien mira una pantalla donde falta un numero necesita saber si falta porque no lo hay o porque no se puede calcular, y son dos conversaciones distintas. Tampoco hay total por sociedad: el ingreso de hoy es el DECLARADO y no el facturado (9.9), y sumar precios declarados por sociedad se parece a un estado de resultados sin serlo</t>
         </is>
       </c>
     </row>
     <row r="54" ht="45.75" customHeight="1" s="36">
       <c r="A54" s="67" t="inlineStr">
         <is>
-          <t>DEC-181</t>
+          <t>DEC-184</t>
         </is>
       </c>
       <c r="B54" s="68" t="inlineStr">
@@ -16417,24 +16467,24 @@
       <c r="C54" s="68" t="n"/>
       <c r="D54" s="69" t="inlineStr">
         <is>
-          <t>Cargar gastos no es ver el margen: campaign_manager pierde campaign.view_margin.</t>
+          <t>Los canjes salen en la lista, marcados, y fuera de todo total.</t>
         </is>
       </c>
       <c r="E54" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F54" s="69" t="inlineStr">
         <is>
-          <t>Quien lleva una campana anota lo que se gasta y ve cuanto lleva gastado; el margen --lo que se gana-- es una cifra de direccion, y el camino por el que un numero interno acaba en un correo a un cliente empieza siempre por alguien que podia verlo sin necesitarlo (BR-SEC-001, 🔴). No nace un permiso nuevo para el margen: campaign.view_margin ya existe y hace eso, y un segundo permiso para el mismo secreto es la forma clasica de que un dia se conceda el que nadie mira. Lo que nace es finance.cost.manage, que es la capacidad que de verdad no existia. Y la revocacion va en la MIGRACION y no en el seeder (T-64)</t>
+          <t>Su ingreso es cero POR DECISION (7.2), asi que su margen es siempre negativo: el producto y el envio se gastaron igual. Promediarlos hace que la cartera entera parezca peor por un motivo que fue deliberado. Pero se enseñan con su costo, porque un canje tambien cuesta dinero y ese era justo el numero que nadie tenia. Queda fuera del total una segunda clase de campana: la que tiene gastos en OTRA moneda, cuyo margen en la moneda del grupo esta incompleto --y sumar un numero incompleto lo vuelve invisible--. Y la cabecera dice cuantas quedaron fuera y por que: un total que excluye filas sin contarlas engaña por omision</t>
         </is>
       </c>
     </row>
     <row r="55" ht="79.5" customHeight="1" s="36">
       <c r="A55" s="67" t="inlineStr">
         <is>
-          <t>DEC-180</t>
+          <t>DEC-183</t>
         </is>
       </c>
       <c r="B55" s="68" t="inlineStr">
@@ -16445,24 +16495,24 @@
       <c r="C55" s="68" t="n"/>
       <c r="D55" s="69" t="inlineStr">
         <is>
-          <t>El gasto de una campana se agrupa por moneda: no se suma.</t>
+          <t>Compromiso::margen() se BORRA, no se arregla.</t>
         </is>
       </c>
       <c r="E55" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F55" s="69" t="inlineStr">
         <is>
-          <t>Un envio se paga en dolares y la campana se cobra en soles; sumarlos exige un tipo de cambio, y cual --compra, venta o media-- es una decision contable que sigue abierta (Q-63) y que da tres margenes distintos para los mismos hechos. Es la misma decision que el saldo del creador en 9.8, por el mismo motivo. Un numero que parece exacto y depende de una eleccion que nadie ha hecho es peor que dos numeros separados</t>
+          <t>Vivia en Campaign desde 7.7 y devolvia revenue_amount menos lo comprometido con creadores: no restaba producto, envios ni produccion, y desde 9.10a esos gastos ya se anotan, asi que el numero habria ido empeorando con cada gasto cargado sin que la pantalla se enterara. No se arregla donde estaba porque campaign_costs es de Finance y deptrac no deja que Campaign la conozca --misma frontera que el devengo de 9.4--. Y se borra en vez de dejarse por si acaso: un metodo que calcula un numero incompleto y se llama margen() es una trampa para quien lo encuentre dentro de seis meses. De paso, SeguimientoController deja de pasar un importe y pasa un booleano mas un enlace: ningun numero interno cruza ya hasta la plantilla, que es BR-SEC-001 un paso mas alla</t>
         </is>
       </c>
     </row>
     <row r="56" ht="79.5" customHeight="1" s="36">
       <c r="A56" s="67" t="inlineStr">
         <is>
-          <t>DEC-179</t>
+          <t>DEC-182</t>
         </is>
       </c>
       <c r="B56" s="68" t="inlineStr">
@@ -16473,24 +16523,24 @@
       <c r="C56" s="68" t="n"/>
       <c r="D56" s="69" t="inlineStr">
         <is>
-          <t>Al creador se le avisa al CONFIRMAR y al DEVOLVER, no al enviar.</t>
+          <t>El costo del creador entra al DEVENGARSE, no al pagarse.</t>
         </is>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F56" s="69" t="inlineStr">
         <is>
-          <t>Avisar al enviar es avisar de una intencion: si el banco lo rechaza, el creador ya cree que cobro, y el segundo correo desmiente al primero --dos correos que se contradicen cuestan mas confianza que un correo que llega un dia mas tarde--. Ninguno de los dos lleva numero de cuenta ni referencia bancaria: un correo se lee en pantallas ajenas y se reenvia, y para saber que le pagaron no hace falta ver su cuenta; es la misma decision que los avisos de 4.13. Y lo que faltaba en payouts no eran los estados --estan desde la Fase 2-- sino el GRAFO: sin tg_payout_estado, un pago saltaba de pending a confirmed sin haber salido nunca, y uno devuelto volvia a sent con un UPDATE, borrando que el banco lo habia rechazado. Mismo agujero que ledger_entries tenia antes de 9.3</t>
+          <t>La deuda existe desde que acepta (9.4) y su importe esta congelado desde 7.5; esperar al pago haria que una campana terminada en marzo pareciera rentabilisima hasta el lote de abril. Sale del libro mayor y no de campaign_creators, porque el libro es quien sabe que devengos siguen vivos: uno anulado ya no se debe. Y no es Compromiso::comprometido(), que cuenta tambien a los shortlisted: alli es correcto --su trabajo es proteger el presupuesto ANTES de invitar-- y aqui contaria dinero de gente que todavia puede decir que no</t>
         </is>
       </c>
     </row>
     <row r="57" ht="68.25" customHeight="1" s="36">
       <c r="A57" s="67" t="inlineStr">
         <is>
-          <t>DEC-178</t>
+          <t>DEC-181</t>
         </is>
       </c>
       <c r="B57" s="68" t="inlineStr">
@@ -16501,24 +16551,24 @@
       <c r="C57" s="68" t="n"/>
       <c r="D57" s="69" t="inlineStr">
         <is>
-          <t>Un pago devuelto por el banco NO deshace el devengo.</t>
+          <t>Cargar gastos no es ver el margen: campaign_manager pierde campaign.view_margin.</t>
         </is>
       </c>
       <c r="E57" s="69" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F57" s="69" t="inlineStr">
         <is>
-          <t>El devengo se queda en paid porque se pago: lo que fallo fue la transferencia, no el trabajo --y paid es terminal desde DEC-169--. La correccion es un asiento de payment_reversal que apunta al asiento de pago original (BR-FIN-002), positivo, asi que devuelve el saldo; los dos hechos quedan escritos --se pago, y volvio-- en vez de que el segundo borre al primero. Nace accrued porque ck_ledger_estado_inicial no admite nacer pagable --a pagable se LLEGA-- y se mueve a payable en la misma operacion: el creador ya cumplio, y su dinero no tiene que esperar a que alguien se acuerde de revisarlo. Si el pago no tuviera asiento en el libro mayor, devolver() falla en voz alta en vez de dejar el saldo diciendo que cobro algo que no tiene</t>
+          <t>Quien lleva una campana anota lo que se gasta y ve cuanto lleva gastado; el margen --lo que se gana-- es una cifra de direccion, y el camino por el que un numero interno acaba en un correo a un cliente empieza siempre por alguien que podia verlo sin necesitarlo (BR-SEC-001, 🔴). No nace un permiso nuevo para el margen: campaign.view_margin ya existe y hace eso, y un segundo permiso para el mismo secreto es la forma clasica de que un dia se conceda el que nadie mira. Lo que nace es finance.cost.manage, que es la capacidad que de verdad no existia. Y la revocacion va en la MIGRACION y no en el seeder (T-64)</t>
         </is>
       </c>
     </row>
     <row r="58" ht="34.5" customHeight="1" s="36">
       <c r="A58" s="67" t="inlineStr">
         <is>
-          <t>DEC-177</t>
+          <t>DEC-180</t>
         </is>
       </c>
       <c r="B58" s="68" t="inlineStr">
@@ -16529,24 +16579,24 @@
       <c r="C58" s="68" t="n"/>
       <c r="D58" s="69" t="inlineStr">
         <is>
-          <t>El CSV del lote NO es el archivo del banco.</t>
+          <t>El gasto de una campana se agrupa por moneda: no se suma.</t>
         </is>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F58" s="69" t="inlineStr">
         <is>
-          <t>El formato de una transferencia masiva es especifico de cada entidad y sale de su manual; inventarselo produce un archivo que el banco rechaza sin decir por que, y el sintoma aparece el dia del pago. Lo que hay es un CSV legible por una persona, para teclear o comprobar, y la pantalla lo dice con esas palabras para que nadie lo suba creyendo que es lo otro. El archivo real se construye cuando haya banco y especificacion</t>
+          <t>Un envio se paga en dolares y la campana se cobra en soles; sumarlos exige un tipo de cambio, y cual --compra, venta o media-- es una decision contable que sigue abierta (Q-63) y que da tres margenes distintos para los mismos hechos. Es la misma decision que el saldo del creador en 9.8, por el mismo motivo. Un numero que parece exacto y depende de una eleccion que nadie ha hecho es peor que dos numeros separados</t>
         </is>
       </c>
     </row>
     <row r="59" ht="79.5" customHeight="1" s="36">
       <c r="A59" s="67" t="inlineStr">
         <is>
-          <t>DEC-176</t>
+          <t>DEC-179</t>
         </is>
       </c>
       <c r="B59" s="68" t="inlineStr">
@@ -16557,24 +16607,24 @@
       <c r="C59" s="68" t="n"/>
       <c r="D59" s="69" t="inlineStr">
         <is>
-          <t>Sacar un pago de un lote firmado NO obliga a firmarlo otra vez.</t>
+          <t>Al creador se le avisa al CONFIRMAR y al DEVOLVER, no al enviar.</t>
         </is>
       </c>
       <c r="E59" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="F59" s="69" t="inlineStr">
         <is>
-          <t>Cuando un devengo se retiene entre la firma y la ejecucion --un post que se cae-- ese pago sale y el resto se paga igual. El importe total baja, nunca sube, y eso no puede sorprender a quien ya firmo; devolver el lote entero a borrador castigaria a diez creadores por el problema de uno. La liquidacion se anula, no se borra: es evidencia de que estuvo dentro y de que alguien lo saco, y anularla exige quien y por que (tg_pe_inmutable). Al anularse, el devengo vuelve a la cola. Un lote ya ejecutado no se toca: el dinero salio, y eso se corrige con una devolucion</t>
+          <t>Avisar al enviar es avisar de una intencion: si el banco lo rechaza, el creador ya cree que cobro, y el segundo correo desmiente al primero --dos correos que se contradicen cuestan mas confianza que un correo que llega un dia mas tarde--. Ninguno de los dos lleva numero de cuenta ni referencia bancaria: un correo se lee en pantallas ajenas y se reenvia, y para saber que le pagaron no hace falta ver su cuenta; es la misma decision que los avisos de 4.13. Y lo que faltaba en payouts no eran los estados --estan desde la Fase 2-- sino el GRAFO: sin tg_payout_estado, un pago saltaba de pending a confirmed sin haber salido nunca, y uno devuelto volvia a sent con un UPDATE, borrando que el banco lo habia rechazado. Mismo agujero que ledger_entries tenia antes de 9.3</t>
         </is>
       </c>
     </row>
     <row r="60" ht="102" customHeight="1" s="36">
       <c r="A60" s="67" t="inlineStr">
         <is>
-          <t>DEC-175</t>
+          <t>DEC-178</t>
         </is>
       </c>
       <c r="B60" s="68" t="inlineStr">
@@ -16585,24 +16635,24 @@
       <c r="C60" s="68" t="n"/>
       <c r="D60" s="69" t="inlineStr">
         <is>
-          <t>Dos firmas SIEMPRE, sin umbral.</t>
+          <t>Un pago devuelto por el banco NO deshace el devengo.</t>
         </is>
       </c>
       <c r="E60" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="F60" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-005 habla de un umbral configurable y se decide no tenerlo: el equipo es pequeno y los lotes son pocos y agrupados, asi que la segunda firma cuesta un clic al mes. Un umbral hay que elegirlo, mantenerlo y explicarlo --y el dia que alguien quiera saltarse la firma, parte el lote en dos--. Que el aprobador sea otro no lo comprueba la pantalla: lo impide ck_pbatch_segregation en la base desde la Fase 2; la pantalla solo lo dice ANTES de que nadie pulse. Y el importe del pago no se teclea: sale de sumar lo que liquida, asi que no puede discrepar de lo que el lote dice que paga --Lotes::descuadre() lo comprueba antes de firmar, porque una SUMA sobre otra tabla no cabe en un CHECK--</t>
+          <t>El devengo se queda en paid porque se pago: lo que fallo fue la transferencia, no el trabajo --y paid es terminal desde DEC-169--. La correccion es un asiento de payment_reversal que apunta al asiento de pago original (BR-FIN-002), positivo, asi que devuelve el saldo; los dos hechos quedan escritos --se pago, y volvio-- en vez de que el segundo borre al primero. Nace accrued porque ck_ledger_estado_inicial no admite nacer pagable --a pagable se LLEGA-- y se mueve a payable en la misma operacion: el creador ya cumplio, y su dinero no tiene que esperar a que alguien se acuerde de revisarlo. Si el pago no tuviera asiento en el libro mayor, devolver() falla en voz alta en vez de dejar el saldo diciendo que cobro algo que no tiene</t>
         </is>
       </c>
     </row>
     <row r="61" ht="90.75" customHeight="1" s="36">
       <c r="A61" s="67" t="inlineStr">
         <is>
-          <t>DEC-174</t>
+          <t>DEC-177</t>
         </is>
       </c>
       <c r="B61" s="68" t="inlineStr">
@@ -16613,7 +16663,7 @@
       <c r="C61" s="68" t="n"/>
       <c r="D61" s="69" t="inlineStr">
         <is>
-          <t>Nace payout_earnings: que devengos paga cada pago.</t>
+          <t>El CSV del lote NO es el archivo del banco.</t>
         </is>
       </c>
       <c r="E61" s="69" t="inlineStr">
@@ -16623,14 +16673,14 @@
       </c>
       <c r="F61" s="69" t="inlineStr">
         <is>
-          <t>ledger_entries.payout_id ataba UN asiento de pago a su payout (BR-FIN-013), pero el detalle --que devengos liquida-- no existia. Sin el, «.de que campanas es este dinero?» no tiene respuesta, y sin respuesta no hay nada que comparar con la sociedad del lote, que es lo que DEC-157 mando cerrar aqui. Con el detalle, BR-LE-009 se vuelve una consulta de tres saltos que cabe en tg_pe_sociedad. Se comprueba al enganchar el devengo al pago y no al aprobar el lote: aprobar es una firma sobre algo que ya tiene que estar bien, y una regla que solo mira al final deja existir el estado malo mientras tanto --que es como alguien lo ve, lo exporta, o lo cree--. Vigesimoseptima columna puerta: uq_pe_viva, un devengo en una sola liquidacion VIVA</t>
+          <t>El formato de una transferencia masiva es especifico de cada entidad y sale de su manual; inventarselo produce un archivo que el banco rechaza sin decir por que, y el sintoma aparece el dia del pago. Lo que hay es un CSV legible por una persona, para teclear o comprobar, y la pantalla lo dice con esas palabras para que nadie lo suba creyendo que es lo otro. El archivo real se construye cuando haya banco y especificacion</t>
         </is>
       </c>
     </row>
     <row r="62" ht="57" customHeight="1" s="36">
       <c r="A62" s="67" t="inlineStr">
         <is>
-          <t>DEC-173</t>
+          <t>DEC-176</t>
         </is>
       </c>
       <c r="B62" s="68" t="inlineStr">
@@ -16641,24 +16691,24 @@
       <c r="C62" s="68" t="n"/>
       <c r="D62" s="69" t="inlineStr">
         <is>
-          <t>La fecha de cobro se ensena SOLO cuando el asiento ya es pagable.</t>
+          <t>Sacar un pago de un lote firmado NO obliga a firmarlo otra vez.</t>
         </is>
       </c>
       <c r="E62" s="69" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F62" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-012 dice que el plazo son 30 dias desde la verificacion y que es visible desde que acepta: lo visible desde que acepta es el plazo, y una FECHA es otra cosa que se lee muy distinto. Mientras el asiento esta devengado se ensena que falta --las cinco condiciones de BR-FIN-003, con sus palabras--, que es accionable: un creador puede hacer algo con «no tienes ningun medio de pago verificado» y no puede hacer nada con una fecha que depende de trabajo que aun no ha hecho. Y si esa fecha se corriera, la culpa pareceria nuestra. La cuenta arranca en la ultima verificacion de sus publicaciones, y si no hay ninguna --un formato que no exige post-- en la fecha en que se completo la participacion</t>
+          <t>Cuando un devengo se retiene entre la firma y la ejecucion --un post que se cae-- ese pago sale y el resto se paga igual. El importe total baja, nunca sube, y eso no puede sorprender a quien ya firmo; devolver el lote entero a borrador castigaria a diez creadores por el problema de uno. La liquidacion se anula, no se borra: es evidencia de que estuvo dentro y de que alguien lo saco, y anularla exige quien y por que (tg_pe_inmutable). Al anularse, el devengo vuelve a la cola. Un lote ya ejecutado no se toca: el dinero salio, y eso se corrige con una devolucion</t>
         </is>
       </c>
     </row>
     <row r="63" ht="90.75" customHeight="1" s="36">
       <c r="A63" s="67" t="inlineStr">
         <is>
-          <t>DEC-172</t>
+          <t>DEC-175</t>
         </is>
       </c>
       <c r="B63" s="68" t="inlineStr">
@@ -16669,24 +16719,24 @@
       <c r="C63" s="68" t="n"/>
       <c r="D63" s="69" t="inlineStr">
         <is>
-          <t>El motivo interno de una retencion NO se le ensena al creador.</t>
+          <t>Dos firmas SIEMPRE, sin umbral.</t>
         </is>
       </c>
       <c r="E63" s="69" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F63" s="69" t="inlineStr">
         <is>
-          <t>Lo escribe el equipo para el expediente y puede nombrar personas o sospechas todavia sin confirmar; un texto redactado deprisa --«parece que lo borro a proposito»-- leido sin contexto es una acusacion de la que no se vuelve. El creador ve «En revision -- te escribimos» y, desde 8.8, recibe un correo donde se le explica de verdad. Las palabras del portal tampoco son las del back-office: on_hold es «en revision» y no «retenido», porque la palabra interna describe lo que hace el sistema y la del portal tiene que describir lo que le pasa a el. La frontera vive en Ledger::misIngresos(), que enumera columnas --el mismo sitio que Aprobaciones::pieza() en 8.5--: devolver la fila entera y confiar en que la plantilla no imprima de mas es confiar en la plantilla de manana. Tampoco cruzan los asientos anulados: no le afectan y no sabe leerlos</t>
+          <t>BR-FIN-005 habla de un umbral configurable y se decide no tenerlo: el equipo es pequeno y los lotes son pocos y agrupados, asi que la segunda firma cuesta un clic al mes. Un umbral hay que elegirlo, mantenerlo y explicarlo --y el dia que alguien quiera saltarse la firma, parte el lote en dos--. Que el aprobador sea otro no lo comprueba la pantalla: lo impide ck_pbatch_segregation en la base desde la Fase 2; la pantalla solo lo dice ANTES de que nadie pulse. Y el importe del pago no se teclea: sale de sumar lo que liquida, asi que no puede discrepar de lo que el lote dice que paga --Lotes::descuadre() lo comprueba antes de firmar, porque una SUMA sobre otra tabla no cabe en un CHECK--</t>
         </is>
       </c>
     </row>
     <row r="64" ht="102" customHeight="1" s="36">
       <c r="A64" s="67" t="inlineStr">
         <is>
-          <t>DEC-171</t>
+          <t>DEC-174</t>
         </is>
       </c>
       <c r="B64" s="68" t="inlineStr">
@@ -16697,24 +16747,24 @@
       <c r="C64" s="68" t="n"/>
       <c r="D64" s="69" t="inlineStr">
         <is>
-          <t>El barrido rescata las aceptaciones sin devengo, y avisa de que hubo que rescatarlas.</t>
+          <t>Nace payout_earnings: que devengos paga cada pago.</t>
         </is>
       </c>
       <c r="E64" s="69" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F64" s="69" t="inlineStr">
         <is>
-          <t>Un listener puede fallar, y si falla el creador queda aceptado y su dinero invisible; ademas las participaciones aceptadas antes de 9.4 nunca pasaron por el. ledger:revisar las anota antes de revisar --para que un devengo recuperado hoy pueda pasar a pagable hoy y no manana-- y lo dice en amarillo: que la lista no salga en cero es la noticia, no el arreglo. Es la misma red que 8.1 dejo para los entregables. Las gratuitas quedan fuera de esa lista a proposito: si no, el barrido intentaria lo imposible todos los dias y avisaria todos los dias de algo que esta bien</t>
+          <t>ledger_entries.payout_id ataba UN asiento de pago a su payout (BR-FIN-013), pero el detalle --que devengos liquida-- no existia. Sin el, «.de que campanas es este dinero?» no tiene respuesta, y sin respuesta no hay nada que comparar con la sociedad del lote, que es lo que DEC-157 mando cerrar aqui. Con el detalle, BR-LE-009 se vuelve una consulta de tres saltos que cabe en tg_pe_sociedad. Se comprueba al enganchar el devengo al pago y no al aprobar el lote: aprobar es una firma sobre algo que ya tiene que estar bien, y una regla que solo mira al final deja existir el estado malo mientras tanto --que es como alguien lo ve, lo exporta, o lo cree--. Vigesimoseptima columna puerta: uq_pe_viva, un devengo en una sola liquidacion VIVA</t>
         </is>
       </c>
     </row>
     <row r="65" ht="90.75" customHeight="1" s="36">
       <c r="A65" s="67" t="inlineStr">
         <is>
-          <t>DEC-170</t>
+          <t>DEC-173</t>
         </is>
       </c>
       <c r="B65" s="68" t="inlineStr">
@@ -16725,24 +16775,24 @@
       <c r="C65" s="68" t="n"/>
       <c r="D65" s="69" t="inlineStr">
         <is>
-          <t>Se devenga al ACEPTAR, no al terminar, y por evento.</t>
+          <t>La fecha de cobro se ensena SOLO cuando el asiento ya es pagable.</t>
         </is>
       </c>
       <c r="E65" s="69" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="F65" s="69" t="inlineStr">
         <is>
-          <t>Al aceptar es cuando existe la deuda: 7.5 congela el agreed_amount en ese instante y BR-CREATOR-008 impide cambiarlo despues sin una enmienda firmada por las dos partes. Que todavia no se le pueda pagar es otra cosa y vive en el estado --accrued significa exactamente «se le debe y aun no se le puede pagar»--. Devengar al terminar habria dejado el trabajo hecho y el compromiso invisible hasta el final, que es como una campana se cierra sin que nadie sepa cuanto costo mientras corria. Va por evento y no por llamada directa por lo mismo que 8.1: deptrac no deja que Campaign conozca a Finance, y esta bien que no lo haga --si anotar el asiento falla, la aceptacion sigue siendo cierta, y el creador ya pulso «acepto»--. Y dos finales NO son fallos: que ya hubiera devengo --uq_ledger_devengo funcionando-- y que la colaboracion sea un canje. Si los tres se escribieran igual, el log diria que algo fallo cada vez que alguien acepta un canje, y a la tercera nadie lo lee</t>
+          <t>BR-FIN-012 dice que el plazo son 30 dias desde la verificacion y que es visible desde que acepta: lo visible desde que acepta es el plazo, y una FECHA es otra cosa que se lee muy distinto. Mientras el asiento esta devengado se ensena que falta --las cinco condiciones de BR-FIN-003, con sus palabras--, que es accionable: un creador puede hacer algo con «no tienes ningun medio de pago verificado» y no puede hacer nada con una fecha que depende de trabajo que aun no ha hecho. Y si esa fecha se corriera, la culpa pareceria nuestra. La cuenta arranca en la ultima verificacion de sus publicaciones, y si no hay ninguna --un formato que no exige post-- en la fecha en que se completo la participacion</t>
         </is>
       </c>
     </row>
     <row r="66" ht="68.25" customHeight="1" s="36">
       <c r="A66" s="67" t="inlineStr">
         <is>
-          <t>DEC-169</t>
+          <t>DEC-172</t>
         </is>
       </c>
       <c r="B66" s="68" t="inlineStr">
@@ -16753,24 +16803,24 @@
       <c r="C66" s="68" t="n"/>
       <c r="D66" s="69" t="inlineStr">
         <is>
-          <t>El estado de un asiento tiene un grafo, y moverlo exige decir por que.</t>
+          <t>El motivo interno de una retencion NO se le ensena al creador.</t>
         </is>
       </c>
       <c r="E66" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="F66" s="69" t="inlineStr">
         <is>
-          <t>tg_ledger_no_update es columna por columna y deja pasar status a proposito --sin eso la tabla no serviria-- pero de ahi no salia QUE transicion es valida: un paid podia volver a accrued, o sea dinero ya pagado reapareciendo como deuda. Es tg_del_rondas de 8.4 otra vez. paid y void son terminales: un pago que se deshace se corrige con un asiento de payment_reversal, no cambiando este estado. Y toda transicion exige status_reason: sin ella, «.por que este creador no cobro?» se contesta mirando la fecha y adivinando. A la bitacora solo va lo que decide una persona --las automaticas son miles y taparian justo lo que se busca ahi--; el rastro completo vive en status_transitions. Ademas nace uq_ledger_devengo, vigesimosexta columna puerta: un devengo por participacion, que BR-FIN-015 daba por hecho sin decirlo</t>
+          <t>Lo escribe el equipo para el expediente y puede nombrar personas o sospechas todavia sin confirmar; un texto redactado deprisa --«parece que lo borro a proposito»-- leido sin contexto es una acusacion de la que no se vuelve. El creador ve «En revision -- te escribimos» y, desde 8.8, recibe un correo donde se le explica de verdad. Las palabras del portal tampoco son las del back-office: on_hold es «en revision» y no «retenido», porque la palabra interna describe lo que hace el sistema y la del portal tiene que describir lo que le pasa a el. La frontera vive en Ledger::misIngresos(), que enumera columnas --el mismo sitio que Aprobaciones::pieza() en 8.5--: devolver la fila entera y confiar en que la plantilla no imprima de mas es confiar en la plantilla de manana. Tampoco cruzan los asientos anulados: no le afectan y no sabe leerlos</t>
         </is>
       </c>
     </row>
     <row r="67" ht="68.25" customHeight="1" s="36">
       <c r="A67" s="67" t="inlineStr">
         <is>
-          <t>DEC-168</t>
+          <t>DEC-171</t>
         </is>
       </c>
       <c r="B67" s="68" t="inlineStr">
@@ -16781,24 +16831,24 @@
       <c r="C67" s="68" t="n"/>
       <c r="D67" s="69" t="inlineStr">
         <is>
-          <t>El asiento va en la moneda PACTADA; se convierte al pagar.</t>
+          <t>El barrido rescata las aceptaciones sin devengo, y avisa de que hubo que rescatarlas.</t>
         </is>
       </c>
       <c r="E67" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F67" s="69" t="inlineStr">
         <is>
-          <t>Se escribe con el agreed_amount y la moneda congelados al aceptar en 7.5: se le debe lo que se le prometio, en la moneda en que se le prometio. La conversion ocurre al armar el pago, con la tasa de ESE dia, y se congela en el asiento de pago (BR-FIN-009). Convertir al devengar habria dejado el saldo del creador en una sola moneda --mas facil de leer-- fijando el tipo de cambio meses antes de pagar: si el dolar sube, el creador cobra menos de lo pactado o nosotros pagamos mas, sin que nadie lo haya decidido</t>
+          <t>Un listener puede fallar, y si falla el creador queda aceptado y su dinero invisible; ademas las participaciones aceptadas antes de 9.4 nunca pasaron por el. ledger:revisar las anota antes de revisar --para que un devengo recuperado hoy pueda pasar a pagable hoy y no manana-- y lo dice en amarillo: que la lista no salga en cero es la noticia, no el arreglo. Es la misma red que 8.1 dejo para los entregables. Las gratuitas quedan fuera de esa lista a proposito: si no, el barrido intentaria lo imposible todos los dias y avisaria todos los dias de algo que esta bien</t>
         </is>
       </c>
     </row>
     <row r="68" ht="79.5" customHeight="1" s="36">
       <c r="A68" s="67" t="inlineStr">
         <is>
-          <t>DEC-167</t>
+          <t>DEC-170</t>
         </is>
       </c>
       <c r="B68" s="68" t="inlineStr">
@@ -16809,24 +16859,24 @@
       <c r="C68" s="68" t="n"/>
       <c r="D68" s="69" t="inlineStr">
         <is>
-          <t>Un post caido RETIENE el asiento; no lo anula.</t>
+          <t>Se devenga al ACEPTAR, no al terminar, y por evento.</t>
         </is>
       </c>
       <c r="E68" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F68" s="69" t="inlineStr">
         <is>
-          <t>8.8 ya lo decidio para el contenido --«el sistema no descuenta nada; la decision de que se le paga la toma una persona con el expediente montado»-- y aqui es lo mismo aplicado al dinero: on_hold saca el asiento de la cola de pago y espera. Reversible: si el creador repone el post, vuelve a payable. Anularlo con una reversion habria sido contablemente mas limpio y habria decidido por su cuenta que no se le paga, que es justo lo que DEC-145 prohibe. Y un asiento retenido no cuenta como saldo: meterlo seria prometerle al creador algo que todavia no esta decidido</t>
+          <t>Al aceptar es cuando existe la deuda: 7.5 congela el agreed_amount en ese instante y BR-CREATOR-008 impide cambiarlo despues sin una enmienda firmada por las dos partes. Que todavia no se le pueda pagar es otra cosa y vive en el estado --accrued significa exactamente «se le debe y aun no se le puede pagar»--. Devengar al terminar habria dejado el trabajo hecho y el compromiso invisible hasta el final, que es como una campana se cierra sin que nadie sepa cuanto costo mientras corria. Va por evento y no por llamada directa por lo mismo que 8.1: deptrac no deja que Campaign conozca a Finance, y esta bien que no lo haga --si anotar el asiento falla, la aceptacion sigue siendo cierta, y el creador ya pulso «acepto»--. Y dos finales NO son fallos: que ya hubiera devengo --uq_ledger_devengo funcionando-- y que la colaboracion sea un canje. Si los tres se escribieran igual, el log diria que algo fallo cada vez que alguien acepta un canje, y a la tercera nadie lo lee</t>
         </is>
       </c>
     </row>
     <row r="69" ht="57" customHeight="1" s="36">
       <c r="A69" s="67" t="inlineStr">
         <is>
-          <t>DEC-166</t>
+          <t>DEC-169</t>
         </is>
       </c>
       <c r="B69" s="68" t="inlineStr">
@@ -16837,7 +16887,7 @@
       <c r="C69" s="68" t="n"/>
       <c r="D69" s="69" t="inlineStr">
         <is>
-          <t>Pasar un devengo a pagable lo hace el SISTEMA, no una persona.</t>
+          <t>El estado de un asiento tiene un grafo, y moverlo exige decir por que.</t>
         </is>
       </c>
       <c r="E69" s="69" t="inlineStr">
@@ -16847,14 +16897,14 @@
       </c>
       <c r="F69" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-003 pide cinco cosas --participacion completada, contenido aprobado, publicacion verificada si aplica, documento tributario valido y medio de pago verificado-- y las cinco ya las firmo alguien una por una: quien verifico la publicacion, quien aprobo el perfil fiscal, quien verifico la cuenta. Una sexta firma que solo dice «si, se cumplen las cinco» es un boton que alguien acaba pulsando sin mirar, y una cola que retrasa pagos por acumulacion y no por duda. Ledger::requisitos() devuelve las cinco con su veredicto y no la primera que falla, porque quien mira por que un creador no cobra necesita la lista entera. El «si aplica» de la publicacion se implementa contando: si ningun entregable tiene publicacion el requisito se da por cumplido --un formato que no exige post no puede bloquear un pago para siempre--</t>
+          <t>tg_ledger_no_update es columna por columna y deja pasar status a proposito --sin eso la tabla no serviria-- pero de ahi no salia QUE transicion es valida: un paid podia volver a accrued, o sea dinero ya pagado reapareciendo como deuda. Es tg_del_rondas de 8.4 otra vez. paid y void son terminales: un pago que se deshace se corrige con un asiento de payment_reversal, no cambiando este estado. Y toda transicion exige status_reason: sin ella, «.por que este creador no cobro?» se contesta mirando la fecha y adivinando. A la bitacora solo va lo que decide una persona --las automaticas son miles y taparian justo lo que se busca ahi--; el rastro completo vive en status_transitions. Ademas nace uq_ledger_devengo, vigesimosexta columna puerta: un devengo por participacion, que BR-FIN-015 daba por hecho sin decirlo</t>
         </is>
       </c>
     </row>
     <row r="70" ht="57" customHeight="1" s="36">
       <c r="A70" s="67" t="inlineStr">
         <is>
-          <t>DEC-165</t>
+          <t>DEC-168</t>
         </is>
       </c>
       <c r="B70" s="68" t="inlineStr">
@@ -16865,24 +16915,24 @@
       <c r="C70" s="68" t="n"/>
       <c r="D70" s="69" t="inlineStr">
         <is>
-          <t>Decolecta trae USD → PEN y nada mas, y el sistema lo dice en vez de disimularlo.</t>
+          <t>El asiento va en la moneda PACTADA; se convierte al pagar.</t>
         </is>
       </c>
       <c r="E70" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F70" s="69" t="inlineStr">
         <is>
-          <t>Publica el tipo de cambio de SUNAT, y SUNAT solo publica el dolar. Por eso Decolecta no acepta un par como parametro --sabe traer lo unico que su fuente publica, y decirlo es mas honesto que aceptar COP y fallar raro--; el catalogo declara USD → PEN = sunat y ningun otro par, porque declarar una fuente que no publica es peor que no tener ninguna; la pantalla tiene carga manual con fuente manual y no disfrazada de sunat, que es lo que permite distinguir despues que se trajo y que se tecleo; y lo dice en la propia pantalla, para que «no llega la tasa del peso mexicano» no se diagnostique como un cron roto. Que fuente se usa para los demas pares queda como Q-64</t>
+          <t>Se escribe con el agreed_amount y la moneda congelados al aceptar en 7.5: se le debe lo que se le prometio, en la moneda en que se le prometio. La conversion ocurre al armar el pago, con la tasa de ESE dia, y se congela en el asiento de pago (BR-FIN-009). Convertir al devengar habria dejado el saldo del creador en una sola moneda --mas facil de leer-- fijando el tipo de cambio meses antes de pagar: si el dolar sube, el creador cobra menos de lo pactado o nosotros pagamos mas, sin que nadie lo haya decidido</t>
         </is>
       </c>
     </row>
     <row r="71" ht="45.75" customHeight="1" s="36">
       <c r="A71" s="67" t="inlineStr">
         <is>
-          <t>DEC-164</t>
+          <t>DEC-167</t>
         </is>
       </c>
       <c r="B71" s="68" t="inlineStr">
@@ -16893,24 +16943,24 @@
       <c r="C71" s="68" t="n"/>
       <c r="D71" s="69" t="inlineStr">
         <is>
-          <t>El cron deja rastro de cada intento, y pide TRES dias.</t>
+          <t>Un post caido RETIENE el asiento; no lo anula.</t>
         </is>
       </c>
       <c r="E71" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F71" s="69" t="inlineStr">
         <is>
-          <t>fx_fetch_runs. Cambio::DIAS_ATRAS detecta que las tasas dejaron de llegar cuando alguien va a convertir, o sea el dia de la liquidacion; esto lo ensena antes, y la pantalla lo resume arriba solo si hay algo que mirar --una pantalla que siempre tiene un aviso es una pantalla cuyos avisos nadie lee--. ck_ffr_nuevas obliga a que una corrida fallida diga cero, porque el registro que contesta «.sigue vivo el cron?» no puede afirmar que una corrida con error trajo tres tasas. Tres dias y no uno: si no corrio viernes ni sabado, pedir solo el domingo deja dos huecos que nadie rellena a mano, y repetir un dia no cuesta una fila --uq_fx_rate-- sino una peticion. Y termina en 0 aunque un dia falle: un cron que da error a diario hace ruido donde nadie mira; solo falla si NINGUN dia se pudo traer</t>
+          <t>8.8 ya lo decidio para el contenido --«el sistema no descuenta nada; la decision de que se le paga la toma una persona con el expediente montado»-- y aqui es lo mismo aplicado al dinero: on_hold saca el asiento de la cola de pago y espera. Reversible: si el creador repone el post, vuelve a payable. Anularlo con una reversion habria sido contablemente mas limpio y habria decidido por su cuenta que no se le paga, que es justo lo que DEC-145 prohibe. Y un asiento retenido no cuenta como saldo: meterlo seria prometerle al creador algo que todavia no esta decidido</t>
         </is>
       </c>
     </row>
     <row r="72" ht="79.5" customHeight="1" s="36">
       <c r="A72" s="67" t="inlineStr">
         <is>
-          <t>DEC-163</t>
+          <t>DEC-166</t>
         </is>
       </c>
       <c r="B72" s="68" t="inlineStr">
@@ -16921,24 +16971,24 @@
       <c r="C72" s="68" t="n"/>
       <c r="D72" s="69" t="inlineStr">
         <is>
-          <t>Cada final de la traida tiene su nombre, y traer() no lanza.</t>
+          <t>Pasar un devengo a pagable lo hace el SISTEMA, no una persona.</t>
         </is>
       </c>
       <c r="E72" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F72" s="69" t="inlineStr">
         <is>
-          <t>ok, sin_credencial, error_http, error_red, respuesta_rara. En un catch generico los cinco se ven iguales y exigen cinco arreglos distintos: «no hay clave» se arregla configurandola, «401» rotandola, «200 con un cuerpo raro» mirando la API. Un 404 --dia sin publicar-- ni siquiera se pinta como averia: quien lee la salida del cron todos los dias deja de leerla si le grita por lo normal. Y una respuesta que no se entiende no anota nada: una tasa inventada entraria en una tabla que tg_fx_inmutable no deja corregir</t>
+          <t>BR-FIN-003 pide cinco cosas --participacion completada, contenido aprobado, publicacion verificada si aplica, documento tributario valido y medio de pago verificado-- y las cinco ya las firmo alguien una por una: quien verifico la publicacion, quien aprobo el perfil fiscal, quien verifico la cuenta. Una sexta firma que solo dice «si, se cumplen las cinco» es un boton que alguien acaba pulsando sin mirar, y una cola que retrasa pagos por acumulacion y no por duda. Ledger::requisitos() devuelve las cinco con su veredicto y no la primera que falla, porque quien mira por que un creador no cobra necesita la lista entera. El «si aplica» de la publicacion se implementa contando: si ningun entregable tiene publicacion el requisito se da por cumplido --un formato que no exige post no puede bloquear un pago para siempre--</t>
         </is>
       </c>
     </row>
     <row r="73" ht="68.25" customHeight="1" s="36">
       <c r="A73" s="67" t="inlineStr">
         <is>
-          <t>DEC-162</t>
+          <t>DEC-165</t>
         </is>
       </c>
       <c r="B73" s="68" t="inlineStr">
@@ -16949,7 +16999,7 @@
       <c r="C73" s="68" t="n"/>
       <c r="D73" s="69" t="inlineStr">
         <is>
-          <t>La credencial se configura desde la pantalla, pero el ENTORNO manda y en la base va CIFRADA.</t>
+          <t>Decolecta trae USD → PEN y nada mas, y el sistema lo dice en vez de disimularlo.</t>
         </is>
       </c>
       <c r="E73" s="69" t="inlineStr">
@@ -16959,14 +17009,14 @@
       </c>
       <c r="F73" s="69" t="inlineStr">
         <is>
-          <t>La peticion era «la configurare en la pantalla del admin». Se hace, con dos condiciones que salen de la regla de seguridad del propio proyecto --«no almacenar secretos en texto plano en BD cuando exista alternativa segura»--: si hay DECOLECTA_API_KEY en el entorno se usa esa y la de la base ni se mira --no viaja por el navegador, no esta en ninguna tabla, no sale en un volcado--; y si no la hay, se guarda con Crypt, la misma maquina que cifra las cuentas bancarias desde 3.8. La clave no se reensena jamas, ni al que la escribio un minuto antes: la pantalla dice «termina en 8f2a» y de donde sale. La bitacora anota que cambio y los cuatro ultimos, nunca el valor. Y tg_fxs_credencial_firmada exige quien la puso, cuando y la pista, las tres o ninguna: media firma es peor que ninguna porque parece que «quien la puso» tiene respuesta. El permiso va aparte: la pantalla es fx.manage --la tiene finanzas-- y la credencial es integration.manage --solo admin--, porque una clave de un tercero es un permiso de gasto y no la necesita quien anota una tasa un lunes</t>
+          <t>Publica el tipo de cambio de SUNAT, y SUNAT solo publica el dolar. Por eso Decolecta no acepta un par como parametro --sabe traer lo unico que su fuente publica, y decirlo es mas honesto que aceptar COP y fallar raro--; el catalogo declara USD → PEN = sunat y ningun otro par, porque declarar una fuente que no publica es peor que no tener ninguna; la pantalla tiene carga manual con fuente manual y no disfrazada de sunat, que es lo que permite distinguir despues que se trajo y que se tecleo; y lo dice en la propia pantalla, para que «no llega la tasa del peso mexicano» no se diagnostique como un cron roto. Que fuente se usa para los demas pares queda como Q-64</t>
         </is>
       </c>
     </row>
     <row r="74" ht="68.25" customHeight="1" s="36">
       <c r="A74" s="67" t="inlineStr">
         <is>
-          <t>DEC-161</t>
+          <t>DEC-164</t>
         </is>
       </c>
       <c r="B74" s="68" t="inlineStr">
@@ -16977,24 +17027,24 @@
       <c r="C74" s="68" t="n"/>
       <c r="D74" s="69" t="inlineStr">
         <is>
-          <t>porque() admite alternancia, y eso es lo que faltaba para bajar el trinquete de las 297.</t>
+          <t>El cron deja rastro de cada intento, y pide TRES dias.</t>
         </is>
       </c>
       <c r="E74" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F74" s="69" t="inlineStr">
         <is>
-          <t>Los dos motores contestan cosas distintas a la MISMA regla cuando la creo Restriccion: MariaDB dice «CONSTRAINT ck_fos_dates failed» y Percona dice el mensaje. El nombre sale en uno y el mensaje en el otro, y no coinciden en ningun texto, asi que toda regla de Restriccion tenia que quedarse en un probar ... RECHAZO a secas. Con grep -qE, porque ... 'ck_fos_dates|antes de empezar' afirma el motivo en los dos motores. DEC-154 puso el trinquete y conto 297; esto es la herramienta para bajarlo</t>
+          <t>fx_fetch_runs. Cambio::DIAS_ATRAS detecta que las tasas dejaron de llegar cuando alguien va a convertir, o sea el dia de la liquidacion; esto lo ensena antes, y la pantalla lo resume arriba solo si hay algo que mirar --una pantalla que siempre tiene un aviso es una pantalla cuyos avisos nadie lee--. ck_ffr_nuevas obliga a que una corrida fallida diga cero, porque el registro que contesta «.sigue vivo el cron?» no puede afirmar que una corrida con error trajo tres tasas. Tres dias y no uno: si no corrio viernes ni sabado, pedir solo el domingo deja dos huecos que nadie rellena a mano, y repetir un dia no cuesta una fila --uq_fx_rate-- sino una peticion. Y termina en 0 aunque un dia falle: un cron que da error a diario hace ruido donde nadie mira; solo falla si NINGUN dia se pudo traer</t>
         </is>
       </c>
     </row>
     <row r="75" ht="57" customHeight="1" s="36">
       <c r="A75" s="67" t="inlineStr">
         <is>
-          <t>DEC-160</t>
+          <t>DEC-163</t>
         </is>
       </c>
       <c r="B75" s="68" t="inlineStr">
@@ -17005,24 +17055,24 @@
       <c r="C75" s="68" t="n"/>
       <c r="D75" s="69" t="inlineStr">
         <is>
-          <t>Un dia sin tasa usa la ultima anterior, y lo que se guarda es la fecha de ESA tasa.</t>
+          <t>Cada final de la traida tiene su nombre, y traer() no lanza.</t>
         </is>
       </c>
       <c r="E75" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F75" s="69" t="inlineStr">
         <is>
-          <t>Sabados, domingos y feriados no tienen tipo publicado. Se convierte con la del viernes y el asiento dice «tasa del viernes», no «tasa del domingo»: guardar la fecha de la operacion habria sido mas comodo de leer y habria hecho que el historico afirmara que ese domingo hubo una tasa que nunca existio (BR-FIN-009). Es un supuesto fiscal y esta marcado como tal (§56): que la practica peruana sea el ultimo tipo publicado lo confirma el contador. Y hay un corte de 10 dias, porque «la ultima anterior» tapa una averia: si lo ultimo es de hace tres semanas no fue un feriado, es que el cron dejo de traerlas, y sin ese corte una tabla congelada se ve igual que una sana hasta el dia de la liquidacion</t>
+          <t>ok, sin_credencial, error_http, error_red, respuesta_rara. En un catch generico los cinco se ven iguales y exigen cinco arreglos distintos: «no hay clave» se arregla configurandola, «401» rotandola, «200 con un cuerpo raro» mirando la API. Un 404 --dia sin publicar-- ni siquiera se pinta como averia: quien lee la salida del cron todos los dias deja de leerla si le grita por lo normal. Y una respuesta que no se entiende no anota nada: una tasa inventada entraria en una tabla que tg_fx_inmutable no deja corregir</t>
         </is>
       </c>
     </row>
     <row r="76" ht="45.75" customHeight="1" s="36">
       <c r="A76" s="67" t="inlineStr">
         <is>
-          <t>DEC-159</t>
+          <t>DEC-162</t>
         </is>
       </c>
       <c r="B76" s="68" t="inlineStr">
@@ -17033,24 +17083,24 @@
       <c r="C76" s="68" t="n"/>
       <c r="D76" s="69" t="inlineStr">
         <is>
-          <t>Compra y venta son dos filas, y cual aplica NO tiene valor por defecto.</t>
+          <t>La credencial se configura desde la pantalla, pero el ENTORNO manda y en la base va CIFRADA.</t>
         </is>
       </c>
       <c r="E76" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F76" s="69" t="inlineStr">
         <is>
-          <t>SUNAT publica las dos el mismo dia y no son intercambiables. Con una sola columna rate solo cabe una, y elegir cual guardar habria sido tomar por mi cuenta una decision contable en el sitio donde menos se ve. side entra en la clave, asi que las dos caben sin pisarse. Y Cambio::tasa() exige el lado como parametro sin defecto: un defecto aqui es exactamente la forma en que una decision fiscal se toma sola. Queda Q-63 para el contador, y por eso el buscador de creadores sigue sin convertir aunque la maquina ya exista</t>
+          <t>La peticion era «la configurare en la pantalla del admin». Se hace, con dos condiciones que salen de la regla de seguridad del propio proyecto --«no almacenar secretos en texto plano en BD cuando exista alternativa segura»--: si hay DECOLECTA_API_KEY en el entorno se usa esa y la de la base ni se mira --no viaja por el navegador, no esta en ninguna tabla, no sale en un volcado--; y si no la hay, se guarda con Crypt, la misma maquina que cifra las cuentas bancarias desde 3.8. La clave no se reensena jamas, ni al que la escribio un minuto antes: la pantalla dice «termina en 8f2a» y de donde sale. La bitacora anota que cambio y los cuatro ultimos, nunca el valor. Y tg_fxs_credencial_firmada exige quien la puso, cuando y la pista, las tres o ninguna: media firma es peor que ninguna porque parece que «quien la puso» tiene respuesta. El permiso va aparte: la pantalla es fx.manage --la tiene finanzas-- y la credencial es integration.manage --solo admin--, porque una clave de un tercero es un permiso de gasto y no la necesita quien anota una tasa un lunes</t>
         </is>
       </c>
     </row>
     <row r="77" ht="68.25" customHeight="1" s="36">
       <c r="A77" s="67" t="inlineStr">
         <is>
-          <t>DEC-158</t>
+          <t>DEC-161</t>
         </is>
       </c>
       <c r="B77" s="68" t="inlineStr">
@@ -17061,7 +17111,7 @@
       <c r="C77" s="68" t="n"/>
       <c r="D77" s="69" t="inlineStr">
         <is>
-          <t>Que fuente publica el tipo de cambio se DECLARA, con periodos, y no se elige al convertir.</t>
+          <t>porque() admite alternancia, y eso es lo que faltaba para bajar el trinquete de las 297.</t>
         </is>
       </c>
       <c r="E77" s="69" t="inlineStr">
@@ -17071,14 +17121,14 @@
       </c>
       <c r="F77" s="69" t="inlineStr">
         <is>
-          <t>uq_exchange_rates incluia source a proposito --dos fuentes pueden discrepar el mismo dia y BR-FIN-009 exige poder decir de cual salio la que se aplico-- pero de ahi no salia CUAL SE APLICA. Es el estado EMPATE de CoberturaFacturacion, el que una vez produjo una factura emitida por la sociedad equivocada, y la respuesta es la misma que entonces: uq_fos_current garantiza una sola fuente VIGENTE por par, y fos_sin_solape una sola POR FECHA --que es la mitad que se olvida, porque convertir un importe de marzo resuelve por par Y por fecha--. Con periodos y no con una columna porque el historico tiene que seguir explicandose con quien mandaba entonces: si fuera una columna, cambiar de proveedor reescribiria como se convirtio todo lo anterior</t>
+          <t>Los dos motores contestan cosas distintas a la MISMA regla cuando la creo Restriccion: MariaDB dice «CONSTRAINT ck_fos_dates failed» y Percona dice el mensaje. El nombre sale en uno y el mensaje en el otro, y no coinciden en ningun texto, asi que toda regla de Restriccion tenia que quedarse en un probar ... RECHAZO a secas. Con grep -qE, porque ... 'ck_fos_dates|antes de empezar' afirma el motivo en los dos motores. DEC-154 puso el trinquete y conto 297; esto es la herramienta para bajarlo</t>
         </is>
       </c>
     </row>
     <row r="78" ht="57" customHeight="1" s="36">
       <c r="A78" s="67" t="inlineStr">
         <is>
-          <t>DEC-157</t>
+          <t>DEC-160</t>
         </is>
       </c>
       <c r="B78" s="68" t="inlineStr">
@@ -17089,24 +17139,24 @@
       <c r="C78" s="68" t="n"/>
       <c r="D78" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-009 se comprueba cuando se escribe el primer pago, no en la iteracion 9.11.</t>
+          <t>Un dia sin tasa usa la ultima anterior, y lo que se guarda es la fecha de ESA tasa.</t>
         </is>
       </c>
       <c r="E78" s="69" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F78" s="69" t="inlineStr">
         <is>
-          <t>El roadmap tenia la validacion de «la sociedad que factura y la que liquida son la misma» como iteracion 11 de 14 de la fase de finanzas. Una regla 🔴 que llega la penultima llega despues de que diez iteraciones se hayan construido dandola por buena, y es exactamente la forma de fallo de 8.4: el techo de rondas existia entero en PHP desde 8.3 y nada lo respaldaba en la base. Aqui es peor, porque lo que se cuela no es una ronda: es dinero saliendo de la sociedad equivocada, que es una operacion intercompania no documentada. Pasa a ser requisito de la iteracion que estrene payout_batches, y en la base: un lote nombra su sociedad y sus asientos nombran sus campanas, asi que la comprobacion es cross-table y le toca a un disparador, no a un CHECK. Y con esto DEC-020 deja de ser PROPUESTA: preguntaba si permitir que la entidad que factura y la que liquida divergieran, y recomendaba modelar la separacion y bloquearla en el MVP. DEC-156 lo contesta y ademas le quita el «en el MVP»</t>
+          <t>Sabados, domingos y feriados no tienen tipo publicado. Se convierte con la del viernes y el asiento dice «tasa del viernes», no «tasa del domingo»: guardar la fecha de la operacion habria sido mas comodo de leer y habria hecho que el historico afirmara que ese domingo hubo una tasa que nunca existio (BR-FIN-009). Es un supuesto fiscal y esta marcado como tal (§56): que la practica peruana sea el ultimo tipo publicado lo confirma el contador. Y hay un corte de 10 dias, porque «la ultima anterior» tapa una averia: si lo ultimo es de hace tres semanas no fue un feriado, es que el cron dejo de traerlas, y sin ese corte una tabla congelada se ve igual que una sana hasta el dia de la liquidacion</t>
         </is>
       </c>
     </row>
     <row r="79" ht="57" customHeight="1" s="36">
       <c r="A79" s="67" t="inlineStr">
         <is>
-          <t>DEC-156</t>
+          <t>DEC-159</t>
         </is>
       </c>
       <c r="B79" s="68" t="inlineStr">
@@ -17117,24 +17167,24 @@
       <c r="C79" s="68" t="n"/>
       <c r="D79" s="69" t="inlineStr">
         <is>
-          <t>La campana decide quien paga a cada creador, y el pais del creador no entra en esa decision.</t>
+          <t>Compra y venta son dos filas, y cual aplica NO tiene valor por defecto.</t>
         </is>
       </c>
       <c r="E79" s="69" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F79" s="69" t="inlineStr">
         <is>
-          <t>Un creador colombiano en una campana de CTS Peru cobra de CTS Peru. La sociedad sale del pais del CLIENTE, se guarda en la campana y el pago la hereda de ahi, congelada al confirmar igual que agreed_amount; lo implementa F9. [Corregido el 2026-08-27, T-59: la version original de esta entrada decia que «payouts no tiene ninguna columna de sociedad» y eso es falso. payout_batches.legal_entity_id existe desde la migracion de finanzas y el pago la hereda de su lote. Lo que NO existe es la garantia de que sea la correcta: nada ata el lote a las campanas cuyos asientos liquida, asi que hoy un lote de CTS Colombia podria pagar el trabajo de una campana de CTS Peru y ninguna restriccion lo notaria.] Esto no inventa la regla: BR-LE-009 ya la decia, con «en el MVP» delante y en naranja. Se le quita el «en el MVP» y sube a 🔴, porque no es una simplificacion temporal sino como funciona el grupo. La alternativa --que pagara la sociedad del pais del creador-- parte una campana en dos contabilidades, obliga a que el margen de una campana se calcule entre sociedades y exige cobertura en el pais de cada creador antes de poder invitarlo: hoy Espana no tiene sociedad y con esa alternativa un creador espanol seria ininvitable. Y cambia el eje de Q-40: la retencion depende de quien paga Y de donde esta el creador, no solo de lo segundo, asi que la tabla del contador pasa a ser «CTS Peru pagando a un creador de cada pais» y CTS Colombia tiene la suya, para un contador colombiano</t>
+          <t>SUNAT publica las dos el mismo dia y no son intercambiables. Con una sola columna rate solo cabe una, y elegir cual guardar habria sido tomar por mi cuenta una decision contable en el sitio donde menos se ve. side entra en la clave, asi que las dos caben sin pisarse. Y Cambio::tasa() exige el lado como parametro sin defecto: un defecto aqui es exactamente la forma en que una decision fiscal se toma sola. Queda Q-63 para el contador, y por eso el buscador de creadores sigue sin convertir aunque la maquina ya exista</t>
         </is>
       </c>
     </row>
     <row r="80" ht="68.25" customHeight="1" s="36">
       <c r="A80" s="67" t="inlineStr">
         <is>
-          <t>DEC-155</t>
+          <t>DEC-158</t>
         </is>
       </c>
       <c r="B80" s="68" t="inlineStr">
@@ -17145,24 +17195,24 @@
       <c r="C80" s="68" t="n"/>
       <c r="D80" s="69" t="inlineStr">
         <is>
-          <t>La sociedad que factura NO se elige: se resuelve, y la pantalla enseña por que.</t>
+          <t>Que fuente publica el tipo de cambio se DECLARA, con periodos, y no se elige al convertir.</t>
         </is>
       </c>
       <c r="E80" s="69" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F80" s="69" t="inlineStr">
         <is>
-          <t>El planteamiento era poner un desplegable «CTS Peru / CTS Colombia» en la campana. No se hace, y el motivo esta en el esquema: uq_lec_country mas tg_lec_sin_solape_ins/upd garantizan que en cualquier fecha hay como mucho una sociedad cubriendo un pais, asi que el desplegable tendria siempre una opcion --y una opcion que se puede cambiar es una que alguien puede cambiar mal--. Ya existia campaigns.billing_legal_entity_id, resuelto a starts_on por Campanas::quienFactura() y congelado al confirmar por tg_camp_entidad_congelada. Lo que faltaba no era el campo: era decirlo. La ficha ahora dice quien factura Y su motivo --«CTS Peru factura a Peru desde el 2025-01-01 (sociedad local)»--, porque una sociedad a secas no se puede comprobar y con su motivo y su fecha quien la lee sabe si es la que esperaba y puede discutirla antes de que salga una factura. El formulario de alta no adelanta una respuesta: el pais del cliente y la fecha todavia no existen, y resolver «con la cobertura de hoy» para ensenarlo es justo el «deducirlo de la configuracion vigente» que prohibe BR-LE-001</t>
+          <t>uq_exchange_rates incluia source a proposito --dos fuentes pueden discrepar el mismo dia y BR-FIN-009 exige poder decir de cual salio la que se aplico-- pero de ahi no salia CUAL SE APLICA. Es el estado EMPATE de CoberturaFacturacion, el que una vez produjo una factura emitida por la sociedad equivocada, y la respuesta es la misma que entonces: uq_fos_current garantiza una sola fuente VIGENTE por par, y fos_sin_solape una sola POR FECHA --que es la mitad que se olvida, porque convertir un importe de marzo resuelve por par Y por fecha--. Con periodos y no con una columna porque el historico tiene que seguir explicandose con quien mandaba entonces: si fuera una columna, cambiar de proveedor reescribiria como se convirtio todo lo anterior</t>
         </is>
       </c>
     </row>
     <row r="81" ht="68.25" customHeight="1" s="36">
       <c r="A81" s="67" t="inlineStr">
         <is>
-          <t>DEC-154</t>
+          <t>DEC-157</t>
         </is>
       </c>
       <c r="B81" s="68" t="inlineStr">
@@ -17173,24 +17223,24 @@
       <c r="C81" s="68" t="n"/>
       <c r="D81" s="69" t="inlineStr">
         <is>
-          <t>Los ayudantes de las suites viven en UN archivo, y nace la SEPTIMA puerta.</t>
+          <t>BR-LE-009 se comprueba cuando se escribe el primer pago, no en la iteracion 9.11.</t>
         </is>
       </c>
       <c r="E81" s="69" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="F81" s="69" t="inlineStr">
         <is>
-          <t>tools/pruebas/comun.sh y tools/verificar-suites.py. La puerta comprueba que toda suite listada existe, que ninguna define sus propios probar/valor/porque, que todas cargan comun.sh, y lleva un trinquete: cuantas aserciones negativas afirman POR QUE se rechaza y cuantas solo que algo fallo. Hoy son 89 con motivo y 297 sin el, y ese segundo numero solo puede bajar (tools/pruebas/MOTIVOS-BASE). No se convierten las 297 en esta iteracion --son veintidos suites de cuatro fases-- pero desde hoy no pueden ser 298, y ademas cada probar ... RECHAZO enseña en gris que restriccion respondio, para que el desajuste se vea al leer la salida. Es la leccion de T-48, T-50, T-51 y T-54: las cuatro fueron aserciones verdes por el motivo equivocado y las cuatro eran un probar ... RECHAZO a secas</t>
+          <t>El roadmap tenia la validacion de «la sociedad que factura y la que liquida son la misma» como iteracion 11 de 14 de la fase de finanzas. Una regla 🔴 que llega la penultima llega despues de que diez iteraciones se hayan construido dandola por buena, y es exactamente la forma de fallo de 8.4: el techo de rondas existia entero en PHP desde 8.3 y nada lo respaldaba en la base. Aqui es peor, porque lo que se cuela no es una ronda: es dinero saliendo de la sociedad equivocada, que es una operacion intercompania no documentada. Pasa a ser requisito de la iteracion que estrene payout_batches, y en la base: un lote nombra su sociedad y sus asientos nombran sus campanas, asi que la comprobacion es cross-table y le toca a un disparador, no a un CHECK. Y con esto DEC-020 deja de ser PROPUESTA: preguntaba si permitir que la entidad que factura y la que liquida divergieran, y recomendaba modelar la separacion y bloquearla en el MVP. DEC-156 lo contesta y ademas le quita el «en el MVP»</t>
         </is>
       </c>
     </row>
     <row r="82" ht="45.75" customHeight="1" s="36">
       <c r="A82" s="67" t="inlineStr">
         <is>
-          <t>DEC-153</t>
+          <t>DEC-156</t>
         </is>
       </c>
       <c r="B82" s="68" t="inlineStr">
@@ -17201,24 +17251,24 @@
       <c r="C82" s="68" t="n"/>
       <c r="D82" s="69" t="inlineStr">
         <is>
-          <t>Una peticion de cambios sin rondas queda PENDIENTE de autorizar.</t>
+          <t>La campana decide quien paga a cada creador, y el pais del creador no entra en esa decision.</t>
         </is>
       </c>
       <c r="E82" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="F82" s="69" t="inlineStr">
         <is>
-          <t>Se registra y no se convierte en ronda hasta que alguien del equipo decida si se le cobra o la absorbemos; al cliente se le confirma que su peticion llego --que es verdad-- sin prometerle que sera gratis. Cae solo del modelo de DEC-151: como la respuesta no crea la revision, no hay ronda que consumir hasta que una persona emite el veredicto. Aprobaciones::pendientes() es la lista de lo que espera esa decision. La pantalla de gracias NO dice «lo corregimos»: decirlo seria prometer por su cuenta algo que todavia no esta decidido</t>
+          <t>Un creador colombiano en una campana de CTS Peru cobra de CTS Peru. La sociedad sale del pais del CLIENTE, se guarda en la campana y el pago la hereda de ahi, congelada al confirmar igual que agreed_amount; lo implementa F9. [Corregido el 2026-08-27, T-59: la version original de esta entrada decia que «payouts no tiene ninguna columna de sociedad» y eso es falso. payout_batches.legal_entity_id existe desde la migracion de finanzas y el pago la hereda de su lote. Lo que NO existe es la garantia de que sea la correcta: nada ata el lote a las campanas cuyos asientos liquida, asi que hoy un lote de CTS Colombia podria pagar el trabajo de una campana de CTS Peru y ninguna restriccion lo notaria.] Esto no inventa la regla: BR-LE-009 ya la decia, con «en el MVP» delante y en naranja. Se le quita el «en el MVP» y sube a 🔴, porque no es una simplificacion temporal sino como funciona el grupo. La alternativa --que pagara la sociedad del pais del creador-- parte una campana en dos contabilidades, obliga a que el margen de una campana se calcule entre sociedades y exige cobertura en el pais de cada creador antes de poder invitarlo: hoy Espana no tiene sociedad y con esa alternativa un creador espanol seria ininvitable. Y cambia el eje de Q-40: la retencion depende de quien paga Y de donde esta el creador, no solo de lo segundo, asi que la tabla del contador pasa a ser «CTS Peru pagando a un creador de cada pais» y CTS Colombia tiene la suya, para un contador colombiano</t>
         </is>
       </c>
     </row>
     <row r="83" ht="68.25" customHeight="1" s="36">
       <c r="A83" s="67" t="inlineStr">
         <is>
-          <t>DEC-152</t>
+          <t>DEC-155</t>
         </is>
       </c>
       <c r="B83" s="68" t="inlineStr">
@@ -17229,24 +17279,24 @@
       <c r="C83" s="68" t="n"/>
       <c r="D83" s="69" t="inlineStr">
         <is>
-          <t>El silencio del cliente no hace nada, y por eso 8.5 no estrena comando.</t>
+          <t>La sociedad que factura NO se elige: se resuelve, y la pantalla enseña por que.</t>
         </is>
       </c>
       <c r="E83" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="F83" s="69" t="inlineStr">
         <is>
-          <t>El enlace caduca, la pieza se queda donde estaba y sale en la bandeja. Nadie aprueba ni rechaza en nombre de nadie. «Silencio = aprobado» habria desbloqueado la campana sin perseguir a nadie y necesita estar escrito en el contrato: dar por buena una pieza que nadie miro es una firma que el sistema pone por el cliente, y de ahi cuelgan la publicacion y el pago. Y de ahi sale que no haga falta un comando de caducidad, al reves que en 7.6: alli una invitacion sin contestar dejaba dinero comprometido y una plaza de cupo ocupada --habia un estado del mundo que corregir-- y aqui expires_at &lt; NOW() basta. Un comando que no arregla nada es una linea de cron mas que mantener y una cosa mas que puede fallar en silencio</t>
+          <t>El planteamiento era poner un desplegable «CTS Peru / CTS Colombia» en la campana. No se hace, y el motivo esta en el esquema: uq_lec_country mas tg_lec_sin_solape_ins/upd garantizan que en cualquier fecha hay como mucho una sociedad cubriendo un pais, asi que el desplegable tendria siempre una opcion --y una opcion que se puede cambiar es una que alguien puede cambiar mal--. Ya existia campaigns.billing_legal_entity_id, resuelto a starts_on por Campanas::quienFactura() y congelado al confirmar por tg_camp_entidad_congelada. Lo que faltaba no era el campo: era decirlo. La ficha ahora dice quien factura Y su motivo --«CTS Peru factura a Peru desde el 2025-01-01 (sociedad local)»--, porque una sociedad a secas no se puede comprobar y con su motivo y su fecha quien la lee sabe si es la que esperaba y puede discutirla antes de que salga una factura. El formulario de alta no adelanta una respuesta: el pais del cliente y la fecha todavia no existen, y resolver «con la cobertura de hoy» para ensenarlo es justo el «deducirlo de la configuracion vigente» que prohibe BR-LE-001</t>
         </is>
       </c>
     </row>
     <row r="84" ht="57" customHeight="1" s="36">
       <c r="A84" s="67" t="inlineStr">
         <is>
-          <t>DEC-151</t>
+          <t>DEC-154</t>
         </is>
       </c>
       <c r="B84" s="68" t="inlineStr">
@@ -17257,24 +17307,24 @@
       <c r="C84" s="68" t="n"/>
       <c r="D84" s="69" t="inlineStr">
         <is>
-          <t>La respuesta del cliente se REGISTRA; el equipo cierra.</t>
+          <t>Los ayudantes de las suites viven en UN archivo, y nace la SEPTIMA puerta.</t>
         </is>
       </c>
       <c r="E84" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="F84" s="69" t="inlineStr">
         <is>
-          <t>El cliente dice «me vale» o «cambiad esto» desde un enlace firmado, y eso queda escrito con su hora y su IP --pero no mueve el entregable--. La alternativa era que su OK aprobara la pieza directamente, y se descarto por dos razones. (a) Habria obligado a partir approved en dos estados: hoy significa «listo para publicar» y 8.6 publica desde ahi, asi que sin un «aprobado interno, esperando al cliente» el mismo estado significaria dos cosas --el fallo de T-50--. (b) Y la que decide: la correccion del cliente gasta ronda, y desde 8.4 una ronda de mas exige firma y decision de facturacion. El cliente no puede firmar un cargo contra si mismo. Si su respuesta moviera la pieza sola, o se le cobraria sin que nadie lo autorizara, o habria que dejarle una puerta por la que las rondas no se cuentan. La pantalla se lo dice con esas palabras: quien pulsa «me vale» y no ve nada moverse tiene derecho a saber que pasa despues</t>
+          <t>tools/pruebas/comun.sh y tools/verificar-suites.py. La puerta comprueba que toda suite listada existe, que ninguna define sus propios probar/valor/porque, que todas cargan comun.sh, y lleva un trinquete: cuantas aserciones negativas afirman POR QUE se rechaza y cuantas solo que algo fallo. Hoy son 89 con motivo y 297 sin el, y ese segundo numero solo puede bajar (tools/pruebas/MOTIVOS-BASE). No se convierten las 297 en esta iteracion --son veintidos suites de cuatro fases-- pero desde hoy no pueden ser 298, y ademas cada probar ... RECHAZO enseña en gris que restriccion respondio, para que el desajuste se vea al leer la salida. Es la leccion de T-48, T-50, T-51 y T-54: las cuatro fueron aserciones verdes por el motivo equivocado y las cuatro eran un probar ... RECHAZO a secas</t>
         </is>
       </c>
     </row>
     <row r="85" ht="57" customHeight="1" s="36">
       <c r="A85" s="67" t="inlineStr">
         <is>
-          <t>DEC-150</t>
+          <t>DEC-153</t>
         </is>
       </c>
       <c r="B85" s="68" t="inlineStr">
@@ -17285,24 +17335,24 @@
       <c r="C85" s="68" t="n"/>
       <c r="D85" s="69" t="inlineStr">
         <is>
-          <t>El techo de rondas pasa a la base, y los disparadores siguen siendo GUARDAS.</t>
+          <t>Una peticion de cambios sin rondas queda PENDIENTE de autorizar.</t>
         </is>
       </c>
       <c r="E85" s="69" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F85" s="69" t="inlineStr">
         <is>
-          <t>8.3 construyo el limite entero --rondas(), vetoParaRevisar(), content.extra_round, over_included, la cola con «quedan/incluidas»-- y lo dejo TODO en PHP. Tres reglas se estaban aplicando sin que nada las respaldara en el esquema: (a) ck_cvw_round no decia DE QUIEN era la correccion, asi que una revision nuestra podia gastarle una ronda al cliente --DEC-133 vivia solo en consumeRonda()--; (b) nada obligaba a over_included a decir la verdad, y esa columna es la que cargosPendientes() cuenta para facturar, o sea que una fila que miente ahi es una correccion que se trabaja y no se cobra; (c) el contador podia bajar, y bajarlo devuelve rondas ya gastadas sin la firma de nadie. tg_cvw_techo mira las DOS direcciones --agotadas sin declarar, y declarada sin estarlo-- y es cross-table, asi que un CHECK no puede verlo; lee el contador ANTES de que emitir() lo suba, que es el mismo valor con el que el servicio calculo su $exceso. Y no se hizo lo tentador: que el contador lo subiera un AFTER INSERT habria hecho imposible la desincronizacion, pero ninguno de los 504 disparadores de este esquema modifica una fila y un disparador que HACE cosas convierte el esquema en algo que actua a espaldas de quien lee el codigo. Habia fecha para esto: 8.5 escribe revisiones del cliente desde un enlace firmado, sin pasar por emitir()</t>
+          <t>Se registra y no se convierte en ronda hasta que alguien del equipo decida si se le cobra o la absorbemos; al cliente se le confirma que su peticion llego --que es verdad-- sin prometerle que sera gratis. Cae solo del modelo de DEC-151: como la respuesta no crea la revision, no hay ronda que consumir hasta que una persona emite el veredicto. Aprobaciones::pendientes() es la lista de lo que espera esa decision. La pantalla de gracias NO dice «lo corregimos»: decirlo seria prometer por su cuenta algo que todavia no esta decidido</t>
         </is>
       </c>
     </row>
     <row r="86" ht="57" customHeight="1" s="36">
       <c r="A86" s="67" t="inlineStr">
         <is>
-          <t>DEC-149</t>
+          <t>DEC-152</t>
         </is>
       </c>
       <c r="B86" s="68" t="inlineStr">
@@ -17313,24 +17363,24 @@
       <c r="C86" s="68" t="n"/>
       <c r="D86" s="69" t="inlineStr">
         <is>
-          <t>Se trabaja en main hasta que haya produccion.</t>
+          <t>El silencio del cliente no hace nada, y por eso 8.5 no estrena comando.</t>
         </is>
       </c>
       <c r="E86" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F86" s="69" t="inlineStr">
         <is>
-          <t>La pregunta fue suya y era la correcta: *«no entiendo el sentido de tener varias ramas si al final haremos merge»*. Medido en el repositorio: main (4.9) -- 5.9 -- 7.6 -- 7.6b -- 7.7 -- 8.1 -- 8.1-8.7 -- 8.8 es una linea recta; nunca hubo dos cosas a la vez. Las tres ramas no eran tres caminos sino tres nombres sobre el mismo camino, y dos apuntaban a puntos ya superados --feat/5.9-4.1-enlace-contrasena es el PADRE de la rama de 7.6, comprobado, no supuesto--. De las cinco cosas para las que sirve una rama, hoy no aplica ninguna: un solo desarrollador, ninguna revision externa, nada desplegado, y el CI que podria opinar antes ya lo hace php tools/diagnostico.php en la maquina. Y el coste si se pagaba: la rama que existia para proteger main lo dejo nueve iteraciones obsoleto, o sea mintiendo a quien clonara. Eso es la ceremonia sin ninguno de los beneficios. Lo que sustituye a la rama no es la confianza, son las seis puertas: no se commitea en rojo. Se revierte el dia que haya produccion, y entonces una rama por iteracion fusionada el mismo dia; lo que no se repite nunca es la rama larga que acumula iteraciones, que no es una rama sino un main con otro nombre. De paso, develop sale del on: push del CI: esa rama no ha existido jamas, y CONTRIBUTING.md la nombraba desde el principio</t>
+          <t>El enlace caduca, la pieza se queda donde estaba y sale en la bandeja. Nadie aprueba ni rechaza en nombre de nadie. «Silencio = aprobado» habria desbloqueado la campana sin perseguir a nadie y necesita estar escrito en el contrato: dar por buena una pieza que nadie miro es una firma que el sistema pone por el cliente, y de ahi cuelgan la publicacion y el pago. Y de ahi sale que no haga falta un comando de caducidad, al reves que en 7.6: alli una invitacion sin contestar dejaba dinero comprometido y una plaza de cupo ocupada --habia un estado del mundo que corregir-- y aqui expires_at &lt; NOW() basta. Un comando que no arregla nada es una linea de cron mas que mantener y una cosa mas que puede fallar en silencio</t>
         </is>
       </c>
     </row>
     <row r="87" ht="68.25" customHeight="1" s="36">
       <c r="A87" s="67" t="inlineStr">
         <is>
-          <t>DEC-148</t>
+          <t>DEC-151</t>
         </is>
       </c>
       <c r="B87" s="68" t="inlineStr">
@@ -17341,24 +17391,24 @@
       <c r="C87" s="68" t="n"/>
       <c r="D87" s="69" t="inlineStr">
         <is>
-          <t>El entregable caido tiene estado propio, y expired pasa a llamarse fulfilled.</t>
+          <t>La respuesta del cliente se REGISTRA; el equipo cierra.</t>
         </is>
       </c>
       <c r="E87" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F87" s="69" t="inlineStr">
         <is>
-          <t>Devolver el entregable a published bastaba para que no cobre, y estaba mal: published significa «esperando a que alguien lo mire» y el dia que F9 construya esa cola meteria incumplimientos dentro --un estado que significa dos cosas es el fallo de T-50--. ck_del_status gana removed, y los dos disparadores que definen «entregable cerrado» lo tratan como cerrado; sin eso se le podria subir una version nueva encima o emitir un veredicto sobre el, y el incumplimiento se disolveria solo. Aparte: ck_pub_status tenia expired desde 2.12 con CERO filas y con un nombre que se lee al reves de lo que significa --la ventana cumplida es lo BUENO, es lo que habilita el pago-- asi que se renombra ahora, que no cuesta nada; con mil filas habria costado una migracion de datos y una discusion. De paso, permanence_checks entra en la lista de 3.12: el criterio de T-16 la incluia desde el primer dia --la fila es evidencia y de ella depende dinero-- y nadie la habia mirado</t>
+          <t>El cliente dice «me vale» o «cambiad esto» desde un enlace firmado, y eso queda escrito con su hora y su IP --pero no mueve el entregable--. La alternativa era que su OK aprobara la pieza directamente, y se descarto por dos razones. (a) Habria obligado a partir approved en dos estados: hoy significa «listo para publicar» y 8.6 publica desde ahi, asi que sin un «aprobado interno, esperando al cliente» el mismo estado significaria dos cosas --el fallo de T-50--. (b) Y la que decide: la correccion del cliente gasta ronda, y desde 8.4 una ronda de mas exige firma y decision de facturacion. El cliente no puede firmar un cargo contra si mismo. Si su respuesta moviera la pieza sola, o se le cobraria sin que nadie lo autorizara, o habria que dejarle una puerta por la que las rondas no se cuentan. La pantalla se lo dice con esas palabras: quien pulsa «me vale» y no ve nada moverse tiene derecho a saber que pasa despues</t>
         </is>
       </c>
     </row>
     <row r="88" ht="34.5" customHeight="1" s="36">
       <c r="A88" s="67" t="inlineStr">
         <is>
-          <t>DEC-147</t>
+          <t>DEC-150</t>
         </is>
       </c>
       <c r="B88" s="68" t="inlineStr">
@@ -17369,24 +17419,24 @@
       <c r="C88" s="68" t="n"/>
       <c r="D88" s="69" t="inlineStr">
         <is>
-          <t>Se avisa al creador y al equipo; al cliente no.</t>
+          <t>El techo de rondas pasa a la base, y los disparadores siguen siendo GUARDAS.</t>
         </is>
       </c>
       <c r="E88" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="F88" s="69" t="inlineStr">
         <is>
-          <t>El creador tiene algo que hacer --reponer el post, decir que la cuenta se puso privada, o decir que lo bajo-- y el equipo lo ve en su bandeja sin que nadie le mande nada. El cliente no se entera hasta que hay algo confirmado: avisarle de un falso positivo cuesta mas que el propio incidente. El correo no dice «incumpliste», dice «no lo encontramos», y dice expresamente que el pago esta en pausa: enterarse de eso cuando no llega el dinero es peor que enterarse ahora</t>
+          <t>8.3 construyo el limite entero --rondas(), vetoParaRevisar(), content.extra_round, over_included, la cola con «quedan/incluidas»-- y lo dejo TODO en PHP. Tres reglas se estaban aplicando sin que nada las respaldara en el esquema: (a) ck_cvw_round no decia DE QUIEN era la correccion, asi que una revision nuestra podia gastarle una ronda al cliente --DEC-133 vivia solo en consumeRonda()--; (b) nada obligaba a over_included a decir la verdad, y esa columna es la que cargosPendientes() cuenta para facturar, o sea que una fila que miente ahi es una correccion que se trabaja y no se cobra; (c) el contador podia bajar, y bajarlo devuelve rondas ya gastadas sin la firma de nadie. tg_cvw_techo mira las DOS direcciones --agotadas sin declarar, y declarada sin estarlo-- y es cross-table, asi que un CHECK no puede verlo; lee el contador ANTES de que emitir() lo suba, que es el mismo valor con el que el servicio calculo su $exceso. Y no se hizo lo tentador: que el contador lo subiera un AFTER INSERT habria hecho imposible la desincronizacion, pero ninguno de los 504 disparadores de este esquema modifica una fila y un disparador que HACE cosas convierte el esquema en algo que actua a espaldas de quien lee el codigo. Habia fecha para esto: 8.5 escribe revisiones del cliente desde un enlace firmado, sin pasar por emitir()</t>
         </is>
       </c>
     </row>
     <row r="89" ht="57" customHeight="1" s="36">
       <c r="A89" s="67" t="inlineStr">
         <is>
-          <t>DEC-146</t>
+          <t>DEC-149</t>
         </is>
       </c>
       <c r="B89" s="68" t="inlineStr">
@@ -17397,7 +17447,7 @@
       <c r="C89" s="68" t="n"/>
       <c r="D89" s="69" t="inlineStr">
         <is>
-          <t>La sonda marca; una persona confirma.</t>
+          <t>Se trabaja en main hasta que haya produccion.</t>
         </is>
       </c>
       <c r="E89" s="69" t="inlineStr">
@@ -17407,14 +17457,14 @@
       </c>
       <c r="F89" s="69" t="inlineStr">
         <is>
-          <t>Es DEC-142 otra vez y por lo mismo --Instagram y TikTok responden igual ante un post borrado, un perfil en privado y un bloqueo geografico-- pero aqui duele mas: en 8.7 un falso negativo retrasa una verificacion, aqui acusa a un creador de incumplir un contrato. Asi que Permanencia::anotar() archiva la comprobacion y no toca publications, y lo que mueve una publicacion a removed es una persona con tg_pub_permanencia exigiendole DOS cosas: una comprobacion con is_live = 0 y una captura tomada DESPUES de haber verificado el post. La segunda condicion es la que costo pensar: la captura vieja probo que el post existia, y reutilizarla como prueba de que ya no esta seria archivar lo contrario de lo que ensena. El comando permanencia:vigilar no sale a Internet: cierra ventanas cumplidas --comparar una fecha con el calendario si lo puede hacer solo, y es lo que habilita el pago-- y cuenta las desatendidas. La comprobacion automatica buena son las APIs oficiales, que son F12</t>
+          <t>La pregunta fue suya y era la correcta: *«no entiendo el sentido de tener varias ramas si al final haremos merge»*. Medido en el repositorio: main (4.9) -- 5.9 -- 7.6 -- 7.6b -- 7.7 -- 8.1 -- 8.1-8.7 -- 8.8 es una linea recta; nunca hubo dos cosas a la vez. Las tres ramas no eran tres caminos sino tres nombres sobre el mismo camino, y dos apuntaban a puntos ya superados --feat/5.9-4.1-enlace-contrasena es el PADRE de la rama de 7.6, comprobado, no supuesto--. De las cinco cosas para las que sirve una rama, hoy no aplica ninguna: un solo desarrollador, ninguna revision externa, nada desplegado, y el CI que podria opinar antes ya lo hace php tools/diagnostico.php en la maquina. Y el coste si se pagaba: la rama que existia para proteger main lo dejo nueve iteraciones obsoleto, o sea mintiendo a quien clonara. Eso es la ceremonia sin ninguno de los beneficios. Lo que sustituye a la rama no es la confianza, son las seis puertas: no se commitea en rojo. Se revierte el dia que haya produccion, y entonces una rama por iteracion fusionada el mismo dia; lo que no se repite nunca es la rama larga que acumula iteraciones, que no es una rama sino un main con otro nombre. De paso, develop sale del on: push del CI: esa rama no ha existido jamas, y CONTRIBUTING.md la nombraba desde el principio</t>
         </is>
       </c>
     </row>
     <row r="90" ht="45.75" customHeight="1" s="36">
       <c r="A90" s="67" t="inlineStr">
         <is>
-          <t>DEC-145</t>
+          <t>DEC-148</t>
         </is>
       </c>
       <c r="B90" s="68" t="inlineStr">
@@ -17425,7 +17475,7 @@
       <c r="C90" s="68" t="n"/>
       <c r="D90" s="69" t="inlineStr">
         <is>
-          <t>Retirar el post antes de tiempo BLOQUEA el pago, y el sistema no descuenta nada.</t>
+          <t>El entregable caido tiene estado propio, y expired pasa a llamarse fulfilled.</t>
         </is>
       </c>
       <c r="E90" s="69" t="inlineStr">
@@ -17435,14 +17485,14 @@
       </c>
       <c r="F90" s="69" t="inlineStr">
         <is>
-          <t>BR-CONTENT-006 decia que el sistema alerta y no decia nada del dinero, que es donde deja de ser tecnico. Las otras dos opciones se descartaron: el descuento proporcional automatico exige que el contrato lo diga por escrito Y que la deteccion sea fiable --y lo segundo hoy no se cumple, ver DEC-146--; solo alertar deja al cliente sin palanca, porque el post se retira, se cobra igual y la unica consecuencia es un correo. Lo que hace: la publicacion pasa a removed con motivo, firma y fecha; el entregable pasa a removed --sale de verified, que es de donde F9 va a pagar--; y ahi se para. La decision de que se le paga la toma una persona con el expediente montado delante. test_firmar_la_caida_para_el_pago_y_no_descuenta_nada afirma las DOS mitades: que el entregable sale de verificado y que el importe acordado sigue intacto. La segunda es la que impide que alguien «mejore» esto manana metiendo una regla de tres</t>
+          <t>Devolver el entregable a published bastaba para que no cobre, y estaba mal: published significa «esperando a que alguien lo mire» y el dia que F9 construya esa cola meteria incumplimientos dentro --un estado que significa dos cosas es el fallo de T-50--. ck_del_status gana removed, y los dos disparadores que definen «entregable cerrado» lo tratan como cerrado; sin eso se le podria subir una version nueva encima o emitir un veredicto sobre el, y el incumplimiento se disolveria solo. Aparte: ck_pub_status tenia expired desde 2.12 con CERO filas y con un nombre que se lee al reves de lo que significa --la ventana cumplida es lo BUENO, es lo que habilita el pago-- asi que se renombra ahora, que no cuesta nada; con mil filas habria costado una migracion de datos y una discusion. De paso, permanence_checks entra en la lista de 3.12: el criterio de T-16 la incluia desde el primer dia --la fila es evidencia y de ella depende dinero-- y nadie la habia mirado</t>
         </is>
       </c>
     </row>
     <row r="91" ht="45.75" customHeight="1" s="36">
       <c r="A91" s="67" t="inlineStr">
         <is>
-          <t>DEC-144</t>
+          <t>DEC-147</t>
         </is>
       </c>
       <c r="B91" s="68" t="inlineStr">
@@ -17453,24 +17503,24 @@
       <c r="C91" s="68" t="n"/>
       <c r="D91" s="69" t="inlineStr">
         <is>
-          <t>Si el post no esta, el entregable vuelve al CREADOR, no a revision.</t>
+          <t>Se avisa al creador y al equipo; al cliente no.</t>
         </is>
       </c>
       <c r="E91" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F91" s="69" t="inlineStr">
         <is>
-          <t>La publicacion queda rejected con su motivo y el entregable vuelve a approved. El contenido no tenia nada malo --ya se aprobo--: lo que falla es que no esta publicado, asi que lo que hay que rehacer es el ENLACE y no la pieza. Reabrir el entregable entero seria mas duro de lo necesario y dejarlo rechazado sin mas deja una campana con una pieza que nadie va a mover. Motivo de lista cerrada, como en 7.6 y 8.2, para poder contestar «.por que se caen las publicaciones?» con un numero. Y se le avisa por correo con el motivo dentro; el correo dice «no lo encontramos» y no «no publicaste», que es la diferencia que importa cuando la cuenta era privada o el enlace se copio mal. Verificar NO manda correo: no le pide nada, su parte termino</t>
+          <t>El creador tiene algo que hacer --reponer el post, decir que la cuenta se puso privada, o decir que lo bajo-- y el equipo lo ve en su bandeja sin que nadie le mande nada. El cliente no se entera hasta que hay algo confirmado: avisarle de un falso positivo cuesta mas que el propio incidente. El correo no dice «incumpliste», dice «no lo encontramos», y dice expresamente que el pago esta en pausa: enterarse de eso cuando no llega el dinero es peor que enterarse ahora</t>
         </is>
       </c>
     </row>
     <row r="92" ht="34.5" customHeight="1" s="36">
       <c r="A92" s="67" t="inlineStr">
         <is>
-          <t>DEC-143</t>
+          <t>DEC-146</t>
         </is>
       </c>
       <c r="B92" s="68" t="inlineStr">
@@ -17481,24 +17531,24 @@
       <c r="C92" s="68" t="n"/>
       <c r="D92" s="69" t="inlineStr">
         <is>
-          <t>Verificar tiene su propio permiso, content.verify.</t>
+          <t>La sonda marca; una persona confirma.</t>
         </is>
       </c>
       <c r="E92" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F92" s="69" t="inlineStr">
         <is>
-          <t>Mismo criterio que separo revisar de aprobar en 8.3: de verified cuelga el pago, asi que es una firma con dinero detras. Lo tienen campaign_manager y content_reviewer; finanzas NO, porque paga contra lo verificado y darle el permiso convertiria una comprobacion en una autoaprobacion. Se comprueba en el POST y no solo escondiendo el boton: los dos veredictos llegan por el mismo formulario</t>
+          <t>Es DEC-142 otra vez y por lo mismo --Instagram y TikTok responden igual ante un post borrado, un perfil en privado y un bloqueo geografico-- pero aqui duele mas: en 8.7 un falso negativo retrasa una verificacion, aqui acusa a un creador de incumplir un contrato. Asi que Permanencia::anotar() archiva la comprobacion y no toca publications, y lo que mueve una publicacion a removed es una persona con tg_pub_permanencia exigiendole DOS cosas: una comprobacion con is_live = 0 y una captura tomada DESPUES de haber verificado el post. La segunda condicion es la que costo pensar: la captura vieja probo que el post existia, y reutilizarla como prueba de que ya no esta seria archivar lo contrario de lo que ensena. El comando permanencia:vigilar no sale a Internet: cierra ventanas cumplidas --comparar una fecha con el calendario si lo puede hacer solo, y es lo que habilita el pago-- y cuenta las desatendidas. La comprobacion automatica buena son las APIs oficiales, que son F12</t>
         </is>
       </c>
     </row>
     <row r="93" ht="45.75" customHeight="1" s="36">
       <c r="A93" s="67" t="inlineStr">
         <is>
-          <t>DEC-142</t>
+          <t>DEC-145</t>
         </is>
       </c>
       <c r="B93" s="68" t="inlineStr">
@@ -17509,24 +17559,24 @@
       <c r="C93" s="68" t="n"/>
       <c r="D93" s="69" t="inlineStr">
         <is>
-          <t>La evidencia de que un post existe es una CAPTURA, no una comprobacion HTTP.</t>
+          <t>Retirar el post antes de tiempo BLOQUEA el pago, y el sistema no descuenta nada.</t>
         </is>
       </c>
       <c r="E93" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F93" s="69" t="inlineStr">
         <is>
-          <t>Tomada con la limitacion delante: Instagram y TikTok devuelven 200 con un muro de login, 403 a todo lo que no sea un navegador, y 200 otra vez cuando el post no existe. Un http_status no distingue «el post existe» de «nos bloquearon», y BR-CONTENT-004 es 🔴 --de verified cuelga el pago--. Asi que lo que se archiva es un screenshot con file_id y tg_pub_verificada_con_evidencia lo impone en la base; la sonda HTTP se guarda como dato complementario y NO decide. Lo que si automatizaria esto son las APIs oficiales --Instagram Graph, TikTok--, que exigen app revisada por Meta y tokens del creador: semanas, y son F12; elegirlas ahora dejaria 8.7, 8.8 y el pago bloqueados hasta entonces. El dia que existan cambia la forma de capturar, no el modelo: publication_evidence ya admite api_snapshot. §56 del prompt maestro pide exactamente esto: no disenar sobre algo extremadamente fragil</t>
+          <t>BR-CONTENT-006 decia que el sistema alerta y no decia nada del dinero, que es donde deja de ser tecnico. Las otras dos opciones se descartaron: el descuento proporcional automatico exige que el contrato lo diga por escrito Y que la deteccion sea fiable --y lo segundo hoy no se cumple, ver DEC-146--; solo alertar deja al cliente sin palanca, porque el post se retira, se cobra igual y la unica consecuencia es un correo. Lo que hace: la publicacion pasa a removed con motivo, firma y fecha; el entregable pasa a removed --sale de verified, que es de donde F9 va a pagar--; y ahi se para. La decision de que se le paga la toma una persona con el expediente montado delante. test_firmar_la_caida_para_el_pago_y_no_descuenta_nada afirma las DOS mitades: que el entregable sale de verificado y que el importe acordado sigue intacto. La segunda es la que impide que alguien «mejore» esto manana metiendo una regla de tres</t>
         </is>
       </c>
     </row>
     <row r="94" ht="45.75" customHeight="1" s="36">
       <c r="A94" s="67" t="inlineStr">
         <is>
-          <t>DEC-141</t>
+          <t>DEC-144</t>
         </is>
       </c>
       <c r="B94" s="68" t="inlineStr">
@@ -17537,24 +17587,24 @@
       <c r="C94" s="68" t="n"/>
       <c r="D94" s="69" t="inlineStr">
         <is>
-          <t>La red se DEDUCE del enlace, y tiene que ser la del brief.</t>
+          <t>Si el post no esta, el entregable vuelve al CREADOR, no a revision.</t>
         </is>
       </c>
       <c r="E94" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F94" s="69" t="inlineStr">
         <is>
-          <t>El brief compro un reel de Instagram; un TikTok no es eso, por bueno que sea. La red no se pregunta --un desplegable en el formulario solo sirve para que alguien elija mal, y el enlace ya lo dice--: sale de platforms.url_pattern, que es una expresion regular y vive en el catalogo desde 2.6 sin que la usara nadie. Si el enlace no es de ninguna red conocida, tampoco entra. Y la huella: uq_pub_fingerprint existe desde la Fase 2 para que dos creadores no reclamen el mismo post, y con la URL cruda no impediria nada --?utm_source=ig basta para esquivarla--. Se normaliza antes de firmar: esquema y host a minusculas, www. fuera, barra final fuera, fragmento fuera, parametros de MEDICION fuera y el resto ordenados. Lo que identifica el post no se toca: la ruta conserva mayusculas --/p/AbC y /p/abc son dos posts-- y la lista de parametros a quitar es explicita, porque youtube.com/watch?v= lleva el identificador en la query y borrar la query entera fundiria todos los videos del canal en una huella. Esa es la mitad que hace dano: rechazar un post legitimo diciendo que ya esta reclamado. La URL se guarda TAL CUAL: la huella es para comparar, no para sustituir</t>
+          <t>La publicacion queda rejected con su motivo y el entregable vuelve a approved. El contenido no tenia nada malo --ya se aprobo--: lo que falla es que no esta publicado, asi que lo que hay que rehacer es el ENLACE y no la pieza. Reabrir el entregable entero seria mas duro de lo necesario y dejarlo rechazado sin mas deja una campana con una pieza que nadie va a mover. Motivo de lista cerrada, como en 7.6 y 8.2, para poder contestar «.por que se caen las publicaciones?» con un numero. Y se le avisa por correo con el motivo dentro; el correo dice «no lo encontramos» y no «no publicaste», que es la diferencia que importa cuando la cuenta era privada o el enlace se copio mal. Verificar NO manda correo: no le pide nada, su parte termino</t>
         </is>
       </c>
     </row>
     <row r="95" ht="57" customHeight="1" s="36">
       <c r="A95" s="67" t="inlineStr">
         <is>
-          <t>DEC-140</t>
+          <t>DEC-143</t>
         </is>
       </c>
       <c r="B95" s="68" t="inlineStr">
@@ -17565,24 +17615,24 @@
       <c r="C95" s="68" t="n"/>
       <c r="D95" s="69" t="inlineStr">
         <is>
-          <t>Solo se publica lo aprobado, y ESA version.</t>
+          <t>Verificar tiene su propio permiso, content.verify.</t>
         </is>
       </c>
       <c r="E95" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F95" s="69" t="inlineStr">
         <is>
-          <t>BR-CONTENT-002 dice que nada llega al cliente sin aprobacion interna, y registrar la publicacion de algo no aprobado es darlo por bueno a posteriori con la firma de nadie. No basta con «el entregable esta aprobado»: se guarda QUE version se publico y tiene que ser la aprobada (tg_pub_version_aprobada), porque de esta fila cuelga el pago --8.7 la verifica y 8.8 cuenta su permanencia--. publications.deliverable_version_id es un SNAPSHOT, igual que amount_snapshot en 7.6: registra lo que se publico ENTONCES y sobrevive a que el entregable se reabra y se apruebe otra version despues, asi que se guarda aunque el puntero de 8.2 diga cual es la aprobada de hoy. Su clave ajena es COMPUESTA, como la de 8.2. Detalle que la suite dice en voz alta: al INSERTAR gana el disparador --la version de otro entregable nunca puede ser la aprobada de este-- y donde la clave se ve sola es en un UPDATE, porque el disparador es BEFORE INSERT y no los mira; ahi esta su asercion, y no en un caso inventado que nunca pasa</t>
+          <t>Mismo criterio que separo revisar de aprobar en 8.3: de verified cuelga el pago, asi que es una firma con dinero detras. Lo tienen campaign_manager y content_reviewer; finanzas NO, porque paga contra lo verificado y darle el permiso convertiria una comprobacion en una autoaprobacion. Se comprueba en el POST y no solo escondiendo el boton: los dos veredictos llegan por el mismo formulario</t>
         </is>
       </c>
     </row>
     <row r="96" ht="57" customHeight="1" s="36">
       <c r="A96" s="67" t="inlineStr">
         <is>
-          <t>DEC-139</t>
+          <t>DEC-142</t>
         </is>
       </c>
       <c r="B96" s="68" t="inlineStr">
@@ -17593,24 +17643,24 @@
       <c r="C96" s="68" t="n"/>
       <c r="D96" s="69" t="inlineStr">
         <is>
-          <t>El post lo reporta el CREADOR, y el equipo tambien puede.</t>
+          <t>La evidencia de que un post existe es una CAPTURA, no una comprobacion HTTP.</t>
         </is>
       </c>
       <c r="E96" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F96" s="69" t="inlineStr">
         <is>
-          <t>El creador es quien lo sabe primero y quien tiene el enlace en la mano: lo pega en su portal en cuanto publica. Y el equipo puede hacerlo por el, porque el caso real existe --el enlace llega por WhatsApp y el creador no entra--. Las alternativas eran peores por el mismo motivo en direcciones opuestas: solo el equipo convierte cada publicacion en una tarea nuestra --con 150 creadores, 150 tareas que perseguir-- y solo el creador deja sin camino el caso de «me lo mando por WhatsApp». Las dos puertas pasan por el MISMO servicio y el MISMO veto; solo cambia quien firma reported_by_user_id. Una segunda puerta con sus propias reglas es una segunda puerta con sus propios agujeros</t>
+          <t>Tomada con la limitacion delante: Instagram y TikTok devuelven 200 con un muro de login, 403 a todo lo que no sea un navegador, y 200 otra vez cuando el post no existe. Un http_status no distingue «el post existe» de «nos bloquearon», y BR-CONTENT-004 es 🔴 --de verified cuelga el pago--. Asi que lo que se archiva es un screenshot con file_id y tg_pub_verificada_con_evidencia lo impone en la base; la sonda HTTP se guarda como dato complementario y NO decide. Lo que si automatizaria esto son las APIs oficiales --Instagram Graph, TikTok--, que exigen app revisada por Meta y tokens del creador: semanas, y son F12; elegirlas ahora dejaria 8.7, 8.8 y el pago bloqueados hasta entonces. El dia que existan cambia la forma de capturar, no el modelo: publication_evidence ya admite api_snapshot. §56 del prompt maestro pide exactamente esto: no disenar sobre algo extremadamente fragil</t>
         </is>
       </c>
     </row>
     <row r="97" ht="57" customHeight="1" s="36">
       <c r="A97" s="67" t="inlineStr">
         <is>
-          <t>DEC-138</t>
+          <t>DEC-141</t>
         </is>
       </c>
       <c r="B97" s="68" t="inlineStr">
@@ -17621,24 +17671,24 @@
       <c r="C97" s="68" t="n"/>
       <c r="D97" s="69" t="inlineStr">
         <is>
-          <t>Un entregable aprobado se puede REABRIR, con motivo de lista cerrada y firma.</t>
+          <t>La red se DEDUCE del enlace, y tiene que ser la del brief.</t>
         </is>
       </c>
       <c r="E97" s="69" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F97" s="69" t="inlineStr">
         <is>
-          <t>Con 8.3 era un callejon sin salida --ni mas veredictos ni mas versiones-- y el cliente cambia de opinion y a veces se aprueba por error: el unico camino cuando eso pasara, y va a pasar, era que alguien tocara la base a mano. Reabrir no deshace nada: es otra fila en content_reviews con outcome='reopened', su motivo y su firma, y la aprobacion anterior se queda en el historial. Misma forma que la anulacion de un perfil fiscal en 3.11, y por la misma razon: el registro tiene que contestar «.que paso?» y no solo «.como esta ahora?». El motivo es de lista cerrada para poder contestar «.por que se reabren las piezas?» con un numero --si el 70% es «se aprobo por error», el problema es la pantalla de revision y no el cliente-- y «otro» exige explicacion, porque «otro» sin explicar es la casilla que se marca para poder seguir. El permiso lo tienen los DOS roles que revisan: «se aprobo por error» lo descubre normalmente quien aprobo, y obligarle a pedirselo a otro convierte un clic en un correo --y en la practica, en que nadie lo arregle--. Reabrir no gasta ronda: la gasta pedir un cambio, y aqui todavia no se ha pedido ninguno</t>
+          <t>El brief compro un reel de Instagram; un TikTok no es eso, por bueno que sea. La red no se pregunta --un desplegable en el formulario solo sirve para que alguien elija mal, y el enlace ya lo dice--: sale de platforms.url_pattern, que es una expresion regular y vive en el catalogo desde 2.6 sin que la usara nadie. Si el enlace no es de ninguna red conocida, tampoco entra. Y la huella: uq_pub_fingerprint existe desde la Fase 2 para que dos creadores no reclamen el mismo post, y con la URL cruda no impediria nada --?utm_source=ig basta para esquivarla--. Se normaliza antes de firmar: esquema y host a minusculas, www. fuera, barra final fuera, fragmento fuera, parametros de MEDICION fuera y el resto ordenados. Lo que identifica el post no se toca: la ruta conserva mayusculas --/p/AbC y /p/abc son dos posts-- y la lista de parametros a quitar es explicita, porque youtube.com/watch?v= lleva el identificador en la query y borrar la query entera fundiria todos los videos del canal en una huella. Esa es la mitad que hace dano: rechazar un post legitimo diciendo que ya esta reclamado. La URL se guarda TAL CUAL: la huella es para comparar, no para sustituir</t>
         </is>
       </c>
     </row>
     <row r="98" ht="34.5" customHeight="1" s="36">
       <c r="A98" s="67" t="inlineStr">
         <is>
-          <t>DEC-137</t>
+          <t>DEC-140</t>
         </is>
       </c>
       <c r="B98" s="68" t="inlineStr">
@@ -17649,24 +17699,24 @@
       <c r="C98" s="68" t="n"/>
       <c r="D98" s="69" t="inlineStr">
         <is>
-          <t>El puntero apunta a la version APROBADA, y su clave ajena es COMPUESTA.</t>
+          <t>Solo se publica lo aprobado, y ESA version.</t>
         </is>
       </c>
       <c r="E98" s="69" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F98" s="69" t="inlineStr">
         <is>
-          <t>«La ultima» sale de un MAX(version_number) y guardarla seria una copia que se puede desviar --el proyecto acaba de quitar una columna por eso mismo, el contador de rondas de 8.3--. La aprobada no es derivable sin recorrer content_reviews, y es el dato del que cuelgan 8.6 --se publica lo aprobado-- y 8.7 --se archiva evidencia de eso--; sin ella las dos tendrian que adivinar cual. Y ahi esta casi todo el valor: FOREIGN KEY (approved_version_id, id) REFERENCES deliverable_versions(id, deliverable_id). Una clave simple garantizaria que la version EXISTE; esta garantiza que es DE ESTE ENTREGABLE --sin la segunda columna, un UPDATE mal escrito deja el entregable de Ana apuntando a la version aprobada del de Luis y la fila sigue siendo valida--. Mismo patron que fk_ccr_market_campaign (7.3). Ademas impide borrar la version apuntada mientras siga aprobada, y ck_del_approved_version exige que aprobado y puntero vayan juntos o no vayan: un dato que a veces esta es igual de util que no tenerlo. La columna espero dos iteraciones a proposito: antes de 8.3 no habia nadie que la escribiera, y habria sido el sexto caso de una columna que existe y no tiene una sola fila</t>
+          <t>BR-CONTENT-002 dice que nada llega al cliente sin aprobacion interna, y registrar la publicacion de algo no aprobado es darlo por bueno a posteriori con la firma de nadie. No basta con «el entregable esta aprobado»: se guarda QUE version se publico y tiene que ser la aprobada (tg_pub_version_aprobada), porque de esta fila cuelga el pago --8.7 la verifica y 8.8 cuenta su permanencia--. publications.deliverable_version_id es un SNAPSHOT, igual que amount_snapshot en 7.6: registra lo que se publico ENTONCES y sobrevive a que el entregable se reabra y se apruebe otra version despues, asi que se guarda aunque el puntero de 8.2 diga cual es la aprobada de hoy. Su clave ajena es COMPUESTA, como la de 8.2. Detalle que la suite dice en voz alta: al INSERTAR gana el disparador --la version de otro entregable nunca puede ser la aprobada de este-- y donde la clave se ve sola es en un UPDATE, porque el disparador es BEFORE INSERT y no los mira; ahi esta su asercion, y no en un caso inventado que nunca pasa</t>
         </is>
       </c>
     </row>
     <row r="99" ht="57" customHeight="1" s="36">
       <c r="A99" s="67" t="inlineStr">
         <is>
-          <t>DEC-136</t>
+          <t>DEC-139</t>
         </is>
       </c>
       <c r="B99" s="68" t="inlineStr">
@@ -17677,24 +17727,24 @@
       <c r="C99" s="68" t="n"/>
       <c r="D99" s="69" t="inlineStr">
         <is>
-          <t>Tres permisos y no uno: revisar, aprobar y autorizar una ronda de mas.</t>
+          <t>El post lo reporta el CREADOR, y el equipo tambien puede.</t>
         </is>
       </c>
       <c r="E99" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F99" s="69" t="inlineStr">
         <is>
-          <t>content.review abre la cola y pide cambios; content.approve da el visto bueno --lo que deja el contenido listo para el cliente y, con F9, lo que dispara el pago--; content.extra_round autoriza el cargo. Mismo criterio que separo capturar de aprobar en el perfil fiscal (DEC-062). content_reviewer tiene los dos primeros y no el tercero: esa decision es de dinero --o se le cobra al cliente o se come el margen-- y quien revisa contenido no tiene por que cargar con ella; la tiene campaign_manager, que responde del margen y es quien va a tener que explicarsela al cliente. Los tres se comprueban en el POST y no solo en la ruta: los tres botones llegan por el mismo formulario, y esconder un boton no es una regla de autorizacion. Y la cola es una BANDEJA GLOBAL, no una por campana: revisar es trabajo por lotes, y una cola por campana obliga a recorrer campanas para descubrir si hay algo esperando --lo que se descubre recorriendo se descubre tarde--. Ordenada por lo que lleva mas esperando y no por lo que vence antes, que es como una cola deja a alguien esperando para siempre</t>
+          <t>El creador es quien lo sabe primero y quien tiene el enlace en la mano: lo pega en su portal en cuanto publica. Y el equipo puede hacerlo por el, porque el caso real existe --el enlace llega por WhatsApp y el creador no entra--. Las alternativas eran peores por el mismo motivo en direcciones opuestas: solo el equipo convierte cada publicacion en una tarea nuestra --con 150 creadores, 150 tareas que perseguir-- y solo el creador deja sin camino el caso de «me lo mando por WhatsApp». Las dos puertas pasan por el MISMO servicio y el MISMO veto; solo cambia quien firma reported_by_user_id. Una segunda puerta con sus propias reglas es una segunda puerta con sus propios agujeros</t>
         </is>
       </c>
     </row>
     <row r="100" ht="34.5" customHeight="1" s="36">
       <c r="A100" s="67" t="inlineStr">
         <is>
-          <t>DEC-135</t>
+          <t>DEC-138</t>
         </is>
       </c>
       <c r="B100" s="68" t="inlineStr">
@@ -17705,24 +17755,24 @@
       <c r="C100" s="68" t="n"/>
       <c r="D100" s="69" t="inlineStr">
         <is>
-          <t>Pasarse de las rondas incluidas se BLOQUEA y exige decidir y firmar; y el cargo NO va a campaign_costs.</t>
+          <t>Un entregable aprobado se puede REABRIR, con motivo de lista cerrada y firma.</t>
         </is>
       </c>
       <c r="E100" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="F100" s="69" t="inlineStr">
         <is>
-          <t>No un aviso: un aviso que se puede saltar acaba en un cargo que se descubre al facturar, que es tarde para discutirlo con el cliente. Cuando la ronda que se va a pedir es la tercera de dos incluidas hay que decir si se cobra o se absorbe, y quien lo dice queda en authorized_by_user_id (ck_cvw_over, en la base y no solo en la pantalla). campaign_costs seria el sitio equivocado y era tentador: es lo que gastamos NOSOTROS y resta del margen (BR-FIN-011), mientras que una ronda de mas facturada al cliente es INGRESO --meterla ahi bajaria el margen de una campana que acaba de ganar dinero--. Aqui queda la decision y la pantalla de entregables la ensena como pendiente de facturar; donde acaba la linea cuando exista F9 es Q-57, y se decide con invoice_lines delante</t>
+          <t>Con 8.3 era un callejon sin salida --ni mas veredictos ni mas versiones-- y el cliente cambia de opinion y a veces se aprueba por error: el unico camino cuando eso pasara, y va a pasar, era que alguien tocara la base a mano. Reabrir no deshace nada: es otra fila en content_reviews con outcome='reopened', su motivo y su firma, y la aprobacion anterior se queda en el historial. Misma forma que la anulacion de un perfil fiscal en 3.11, y por la misma razon: el registro tiene que contestar «.que paso?» y no solo «.como esta ahora?». El motivo es de lista cerrada para poder contestar «.por que se reabren las piezas?» con un numero --si el 70% es «se aprobo por error», el problema es la pantalla de revision y no el cliente-- y «otro» exige explicacion, porque «otro» sin explicar es la casilla que se marca para poder seguir. El permiso lo tienen los DOS roles que revisan: «se aprobo por error» lo descubre normalmente quien aprobo, y obligarle a pedirselo a otro convierte un clic en un correo --y en la practica, en que nadie lo arregle--. Reabrir no gasta ronda: la gasta pedir un cambio, y aqui todavia no se ha pedido ninguno</t>
         </is>
       </c>
     </row>
     <row r="101" ht="34.5" customHeight="1" s="36">
       <c r="A101" s="67" t="inlineStr">
         <is>
-          <t>DEC-134</t>
+          <t>DEC-137</t>
         </is>
       </c>
       <c r="B101" s="68" t="inlineStr">
@@ -17733,24 +17783,24 @@
       <c r="C101" s="68" t="n"/>
       <c r="D101" s="69" t="inlineStr">
         <is>
-          <t>Hasta 8.5, quien lleva la cuenta marca de parte de quien viene la correccion.</t>
+          <t>El puntero apunta a la version APROBADA, y su clave ajena es COMPUESTA.</t>
         </is>
       </c>
       <c r="E101" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="F101" s="69" t="inlineStr">
         <is>
-          <t>El portal del cliente es 8.5. Sin esto, en 8.3 nada consumiria ronda y el veto de «rondas agotadas» naceria muerto: el QUINTO caso de una regla escrita sobre una tabla vacia en un proyecto que ya lleva cuatro (campaign_creators en 7.4, domain_events en 4.13, invitations en 7.6, deliverables en 8.1). La salida no es inventarse el portal: es reconocer como trabaja una agencia HOY --el ejecutivo traslada el comentario del cliente y marca que es suyo--. En 8.5 el enlace firmado escribe la misma fila sin intermediario y Revisiones no se entera. Quien traslada queda anotado igual en reviewer_user_id: quien la escribio responde de ella. Y ck_cvw_firma exige usuario solo en las NUESTRAS, porque la del cliente en 8.5 no tendra cuenta detras</t>
+          <t>«La ultima» sale de un MAX(version_number) y guardarla seria una copia que se puede desviar --el proyecto acaba de quitar una columna por eso mismo, el contador de rondas de 8.3--. La aprobada no es derivable sin recorrer content_reviews, y es el dato del que cuelgan 8.6 --se publica lo aprobado-- y 8.7 --se archiva evidencia de eso--; sin ella las dos tendrian que adivinar cual. Y ahi esta casi todo el valor: FOREIGN KEY (approved_version_id, id) REFERENCES deliverable_versions(id, deliverable_id). Una clave simple garantizaria que la version EXISTE; esta garantiza que es DE ESTE ENTREGABLE --sin la segunda columna, un UPDATE mal escrito deja el entregable de Ana apuntando a la version aprobada del de Luis y la fila sigue siendo valida--. Mismo patron que fk_ccr_market_campaign (7.3). Ademas impide borrar la version apuntada mientras siga aprobada, y ck_del_approved_version exige que aprobado y puntero vayan juntos o no vayan: un dato que a veces esta es igual de util que no tenerlo. La columna espero dos iteraciones a proposito: antes de 8.3 no habia nadie que la escribiera, y habria sido el sexto caso de una columna que existe y no tiene una sola fila</t>
         </is>
       </c>
     </row>
     <row r="102" ht="57" customHeight="1" s="36">
       <c r="A102" s="67" t="inlineStr">
         <is>
-          <t>DEC-133</t>
+          <t>DEC-136</t>
         </is>
       </c>
       <c r="B102" s="68" t="inlineStr">
@@ -17761,7 +17811,7 @@
       <c r="C102" s="68" t="n"/>
       <c r="D102" s="69" t="inlineStr">
         <is>
-          <t>Solo las rondas del CLIENTE cuentan contra el precio, y son POR ENTREGABLE.</t>
+          <t>Tres permisos y no uno: revisar, aprobar y autorizar una ronda de mas.</t>
         </is>
       </c>
       <c r="E102" s="69" t="inlineStr">
@@ -17771,14 +17821,14 @@
       </c>
       <c r="F102" s="69" t="inlineStr">
         <is>
-          <t>Dos cosas en una porque las dos las decidio la misma conversacion. (1) Que nuestro equipo le pida al creador rehacer el encuadre antes de ensenarselo a nadie es control de calidad NUESTRO; cobrarselo al cliente seria cobrarle nuestro propio error. reviewer_side distinguia platform de client desde la Fase 2 y lo que faltaba era que alguien lo usara. (2) revision_rounds_used vivia en campaign_creators --dos rondas POR CREADOR--, asi que con un creador que entrega dos reels y tres stories, dos correcciones sobre el primer reel dejaban las otras cuatro piezas sin ninguna ronda, y el cliente habia pagado dos por cada una. Baja a deliverables, que es donde se aplica la regla. Y la columna vieja se va, no se queda como suma: una suma almacenada que nadie recalcula se desvia en silencio, y la suma por creador --la que alimenta el Creator Score-- sale de content_reviews con un SUM() que nunca miente. Tenia cero filas: quitarla hoy es gratis y dentro de tres meses no</t>
+          <t>content.review abre la cola y pide cambios; content.approve da el visto bueno --lo que deja el contenido listo para el cliente y, con F9, lo que dispara el pago--; content.extra_round autoriza el cargo. Mismo criterio que separo capturar de aprobar en el perfil fiscal (DEC-062). content_reviewer tiene los dos primeros y no el tercero: esa decision es de dinero --o se le cobra al cliente o se come el margen-- y quien revisa contenido no tiene por que cargar con ella; la tiene campaign_manager, que responde del margen y es quien va a tener que explicarsela al cliente. Los tres se comprueban en el POST y no solo en la ruta: los tres botones llegan por el mismo formulario, y esconder un boton no es una regla de autorizacion. Y la cola es una BANDEJA GLOBAL, no una por campana: revisar es trabajo por lotes, y una cola por campana obliga a recorrer campanas para descubrir si hay algo esperando --lo que se descubre recorriendo se descubre tarde--. Ordenada por lo que lleva mas esperando y no por lo que vence antes, que es como una cola deja a alguien esperando para siempre</t>
         </is>
       </c>
     </row>
     <row r="103" ht="68.25" customHeight="1" s="36">
       <c r="A103" s="67" t="inlineStr">
         <is>
-          <t>DEC-132</t>
+          <t>DEC-135</t>
         </is>
       </c>
       <c r="B103" s="68" t="inlineStr">
@@ -17789,24 +17839,24 @@
       <c r="C103" s="68" t="n"/>
       <c r="D103" s="69" t="inlineStr">
         <is>
-          <t>Si al caption le faltan las etiquetas del brief, NO SE ENVIA, y se le dice cuales.</t>
+          <t>Pasarse de las rondas incluidas se BLOQUEA y exige decidir y firmar; y el cargo NO va a campaign_costs.</t>
         </is>
       </c>
       <c r="E103" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F103" s="69" t="inlineStr">
         <is>
-          <t>Comprobacion objetiva y barata que ahorra una ronda de correccion entera: el creador lo arregla en diez segundos en vez de enterarse tres dias despues. Avisar y dejar pasar acaba siempre en un aviso que nadie lee; dejarlo para la revision traslada a una persona la clase de tarea que una maquina hace mejor. Sin distinguir mayusculas --#ACMEVerano y #acmeverano son el mismo hashtag para las plataformas, y rechazar por la caja seria rechazar por algo que da igual-- y devolviendo todos los motivos a la vez, porque quien entrega desde el movil prefiere una lista de tres cosas que arreglar a tres intentos</t>
+          <t>No un aviso: un aviso que se puede saltar acaba en un cargo que se descubre al facturar, que es tarde para discutirlo con el cliente. Cuando la ronda que se va a pedir es la tercera de dos incluidas hay que decir si se cobra o se absorbe, y quien lo dice queda en authorized_by_user_id (ck_cvw_over, en la base y no solo en la pantalla). campaign_costs seria el sitio equivocado y era tentador: es lo que gastamos NOSOTROS y resta del margen (BR-FIN-011), mientras que una ronda de mas facturada al cliente es INGRESO --meterla ahi bajaria el margen de una campana que acaba de ganar dinero--. Aqui queda la decision y la pantalla de entregables la ensena como pendiente de facturar; donde acaba la linea cuando exista F9 es Q-57, y se decide con invoice_lines delante</t>
         </is>
       </c>
     </row>
     <row r="104" ht="34.5" customHeight="1" s="36">
       <c r="A104" s="67" t="inlineStr">
         <is>
-          <t>DEC-131</t>
+          <t>DEC-134</t>
         </is>
       </c>
       <c r="B104" s="68" t="inlineStr">
@@ -17817,24 +17867,24 @@
       <c r="C104" s="68" t="n"/>
       <c r="D104" s="69" t="inlineStr">
         <is>
-          <t>Se entrega un ENLACE externo, y opcionalmente una imagen.</t>
+          <t>Hasta 8.5, quien lleva la cuenta marca de parte de quien viene la correccion.</t>
         </is>
       </c>
       <c r="E104" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F104" s="69" t="inlineStr">
         <is>
-          <t>El contenido de verdad --un reel de 80 MB-- no sube aqui y no deberia: el creador ya lo tiene en Drive o en la propia plataforma, y almacenarlo otra vez es coste y responsabilidad sin contrapartida. Se guarda el enlace, obligatoriamente https://, mas una imagen de referencia opcional por Almacen (10 MB). El https:// se comprueba en tres sitios a proposito: EntregarRequest da el mensaje junto al campo, vetoParaEntregar() lo da junto a los demas motivos, y ck_dv_url_https impide la fila venga de donde venga. Sin el tercero, un comando o un import mete javascript:alert(1) en una columna que una vista pinta dentro de un href; sin el segundo, el creador ve un 3819</t>
+          <t>El portal del cliente es 8.5. Sin esto, en 8.3 nada consumiria ronda y el veto de «rondas agotadas» naceria muerto: el QUINTO caso de una regla escrita sobre una tabla vacia en un proyecto que ya lleva cuatro (campaign_creators en 7.4, domain_events en 4.13, invitations en 7.6, deliverables en 8.1). La salida no es inventarse el portal: es reconocer como trabaja una agencia HOY --el ejecutivo traslada el comentario del cliente y marca que es suyo--. En 8.5 el enlace firmado escribe la misma fila sin intermediario y Revisiones no se entera. Quien traslada queda anotado igual en reviewer_user_id: quien la escribio responde de ella. Y ck_cvw_firma exige usuario solo en las NUESTRAS, porque la del cliente en 8.5 no tendra cuenta detras</t>
         </is>
       </c>
     </row>
     <row r="105" ht="57" customHeight="1" s="36">
       <c r="A105" s="67" t="inlineStr">
         <is>
-          <t>DEC-130</t>
+          <t>DEC-133</t>
         </is>
       </c>
       <c r="B105" s="68" t="inlineStr">
@@ -17845,24 +17895,24 @@
       <c r="C105" s="68" t="n"/>
       <c r="D105" s="69" t="inlineStr">
         <is>
-          <t>El brief que se usa es el EFECTIVO, no el general.</t>
+          <t>Solo las rondas del CLIENTE cuentan contra el precio, y son POR ENTREGABLE.</t>
         </is>
       </c>
       <c r="E105" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F105" s="69" t="inlineStr">
         <is>
-          <t>Mercados::briefEfectivo(), que ya resolvia N-03: si el mercado del creador tiene brief propio, ese REEMPLAZA al general. Un creador peruano en una campana con brief especifico para Peru recibe el de Peru, y las etiquetas tambien --que es justo por lo que 7.2 dejo los hashtags fuera hasta que existieran los mercados--. Un entregable generado del brief general cuando hay uno de mercado le pide al creador lo que la campana NO quiere de el, y el error solo se ve al revisar</t>
+          <t>Dos cosas en una porque las dos las decidio la misma conversacion. (1) Que nuestro equipo le pida al creador rehacer el encuadre antes de ensenarselo a nadie es control de calidad NUESTRO; cobrarselo al cliente seria cobrarle nuestro propio error. reviewer_side distinguia platform de client desde la Fase 2 y lo que faltaba era que alguien lo usara. (2) revision_rounds_used vivia en campaign_creators --dos rondas POR CREADOR--, asi que con un creador que entrega dos reels y tres stories, dos correcciones sobre el primer reel dejaban las otras cuatro piezas sin ninguna ronda, y el cliente habia pagado dos por cada una. Baja a deliverables, que es donde se aplica la regla. Y la columna vieja se va, no se queda como suma: una suma almacenada que nadie recalcula se desvia en silencio, y la suma por creador --la que alimenta el Creator Score-- sale de content_reviews con un SUM() que nunca miente. Tenia cero filas: quitarla hoy es gratis y dentro de tres meses no</t>
         </is>
       </c>
     </row>
     <row r="106" ht="34.5" customHeight="1" s="36">
       <c r="A106" s="67" t="inlineStr">
         <is>
-          <t>DEC-129</t>
+          <t>DEC-132</t>
         </is>
       </c>
       <c r="B106" s="68" t="inlineStr">
@@ -17873,7 +17923,7 @@
       <c r="C106" s="68" t="n"/>
       <c r="D106" s="69" t="inlineStr">
         <is>
-          <t>Los entregables se generan SOLOS al aceptar, y la generacion es idempotente.</t>
+          <t>Si al caption le faltan las etiquetas del brief, NO SE ENVIA, y se le dice cuales.</t>
         </is>
       </c>
       <c r="E106" s="69" t="inlineStr">
@@ -17883,14 +17933,14 @@
       </c>
       <c r="F106" s="69" t="inlineStr">
         <is>
-          <t>El brief ya lo dice todo --cuantos, de que formato, con cuantos dias de plazo--, asi que pedirle a alguien que lo teclee otra vez por cada creador es pedirle que copie un dato que el sistema ya tiene. Lo que decide no es el ahorro sino el MODO DE FALLO: si se teclea a mano, el dia que se olvide ese creador no tiene nada que entregar y nadie se entera hasta que la campana termina sin su contenido; si se generan solos, el fallo es que sobra un entregable y se ve en la lista. Va por evento (campaign_creator.accepted --&gt; GenerarEntregables) y no dentro de aceptar(), porque Campaign no puede conocer Content: la misma frontera que se cobro el panel de 7.7. Idempotente porque aceptar dos veces no puede pasar --el enlace es de un solo uso-- pero una reanudacion de la cola o un reintento manual si, y duplicar el trabajo de un creador es la clase de error que se descubre tarde y mal</t>
+          <t>Comprobacion objetiva y barata que ahorra una ronda de correccion entera: el creador lo arregla en diez segundos en vez de enterarse tres dias despues. Avisar y dejar pasar acaba siempre en un aviso que nadie lee; dejarlo para la revision traslada a una persona la clase de tarea que una maquina hace mejor. Sin distinguir mayusculas --#ACMEVerano y #acmeverano son el mismo hashtag para las plataformas, y rechazar por la caja seria rechazar por algo que da igual-- y devolviendo todos los motivos a la vez, porque quien entrega desde el movil prefiere una lista de tres cosas que arreglar a tres intentos</t>
         </is>
       </c>
     </row>
     <row r="107" ht="45.75" customHeight="1" s="36">
       <c r="A107" s="67" t="inlineStr">
         <is>
-          <t>DEC-128</t>
+          <t>DEC-131</t>
         </is>
       </c>
       <c r="B107" s="68" t="inlineStr">
@@ -17901,24 +17951,24 @@
       <c r="C107" s="68" t="n"/>
       <c r="D107" s="69" t="inlineStr">
         <is>
-          <t>En el seguimiento, el dinero SI y el margen solo con su permiso.</t>
+          <t>Se entrega un ENLACE externo, y opcionalmente una imagen.</t>
         </is>
       </c>
       <c r="E107" s="69" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F107" s="69" t="inlineStr">
         <is>
-          <t>Presupuesto, comprometido y disponible los ve quien puede ver la campana: sin esos tres numeros no se decide a quien invitar, y ponerlos detras de un permiso que entonces necesitaria todo el mundo seria un permiso que no protege nada. El margen sigue detras de campaign.view_margin (BR-FIN-007) y no se calcula y luego se esconde: no se calcula --un dato que llega a la vista es un dato que un @if mal puesto puede ensenar, y BR-SEC-001 es 🔴--. La diferencia no es sutil: lo comprometido es lo que se le paga a los creadores; el margen es lo que gana la empresa. Y el disponible se ensena NEGATIVO cuando lo es: redondearlo a cero esconderia justo el caso que hay que ver, una campana que se paso porque finanzas lo autorizo</t>
+          <t>El contenido de verdad --un reel de 80 MB-- no sube aqui y no deberia: el creador ya lo tiene en Drive o en la propia plataforma, y almacenarlo otra vez es coste y responsabilidad sin contrapartida. Se guarda el enlace, obligatoriamente https://, mas una imagen de referencia opcional por Almacen (10 MB). El https:// se comprueba en tres sitios a proposito: EntregarRequest da el mensaje junto al campo, vetoParaEntregar() lo da junto a los demas motivos, y ck_dv_url_https impide la fila venga de donde venga. Sin el tercero, un comando o un import mete javascript:alert(1) en una columna que una vista pinta dentro de un href; sin el segundo, el creador ve un 3819</t>
         </is>
       </c>
     </row>
     <row r="108" ht="57" customHeight="1" s="36">
       <c r="A108" s="67" t="inlineStr">
         <is>
-          <t>DEC-127</t>
+          <t>DEC-130</t>
         </is>
       </c>
       <c r="B108" s="68" t="inlineStr">
@@ -17929,24 +17979,24 @@
       <c r="C108" s="68" t="n"/>
       <c r="D108" s="69" t="inlineStr">
         <is>
-          <t>Cuatro alertas en el panel de seguimiento, y su orden NO es por gravedad.</t>
+          <t>El brief que se usa es el EFECTIVO, no el general.</t>
         </is>
       </c>
       <c r="E108" s="69" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F108" s="69" t="inlineStr">
         <is>
-          <t>Campana sin confirmar con el arranque a menos de 14 dias, preguntas de creadores sin atender, invitaciones que caducan en menos de 12 h, y cupo de mercado sin cubrir. La de «sin confirmar» va PRIMERA porque bloquea a las demas: sin confirmar no se puede invitar a nadie, asi que un cupo corto ahi no se arregla reclutando. Y las preguntas van antes que las invitaciones urgentes porque un creador que pregunto y no recibe respuesta MIENTRAS su plazo corre es la combinacion exacta que convierte un si en un silencio. Cada alerta dice que pasa y que hacer: una que solo dice que hay un problema obliga a buscarlo, y entonces deja de leerse. Y «cubierto» es ACEPTADO, no invitado: una invitacion sin contestar es una plaza esperando, y contarla como cubierta es como se llega al dia de arranque con la mitad del equipo y los numeros en verde</t>
+          <t>Mercados::briefEfectivo(), que ya resolvia N-03: si el mercado del creador tiene brief propio, ese REEMPLAZA al general. Un creador peruano en una campana con brief especifico para Peru recibe el de Peru, y las etiquetas tambien --que es justo por lo que 7.2 dejo los hashtags fuera hasta que existieran los mercados--. Un entregable generado del brief general cuando hay uno de mercado le pide al creador lo que la campana NO quiere de el, y el error solo se ve al revisar</t>
         </is>
       </c>
     </row>
     <row r="109" ht="45.75" customHeight="1" s="36">
       <c r="A109" s="67" t="inlineStr">
         <is>
-          <t>DEC-126</t>
+          <t>DEC-129</t>
         </is>
       </c>
       <c r="B109" s="68" t="inlineStr">
@@ -17957,24 +18007,24 @@
       <c r="C109" s="68" t="n"/>
       <c r="D109" s="69" t="inlineStr">
         <is>
-          <t>usuarios:crear deja de teclear la contrasena; el alta interna usa el mismo enlace de 72 h que la del creador.</t>
+          <t>Los entregables se generan SOLOS al aceptar, y la generacion es idempotente.</t>
         </is>
       </c>
       <c r="E109" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F109" s="69" t="inlineStr">
         <is>
-          <t>Cierra BR-SEC-004 (🔴) del todo. must_change_password era el parche: obligaba a cambiarla DESPUES y dejaba una ventana --de minutos o de meses-- en la que dos personas conocian la credencial, y justo en las cuentas donde la base exige dos personas distintas para el dinero. Ahora no hay ventana: la contrasena no existe hasta que la escribe su dueno. usuarios:contrasena --enlace hace lo mismo para reponer y no toca la contrasena actual --si el correo no llega, la persona no se queda peor de como estaba--. Teclearla a mano sigue existiendo a proposito, como cristal de emergencia para cuando el correo no sale (Q-20), y el comando avisa cada vez de que ese es el camino excepcional</t>
+          <t>El brief ya lo dice todo --cuantos, de que formato, con cuantos dias de plazo--, asi que pedirle a alguien que lo teclee otra vez por cada creador es pedirle que copie un dato que el sistema ya tiene. Lo que decide no es el ahorro sino el MODO DE FALLO: si se teclea a mano, el dia que se olvide ese creador no tiene nada que entregar y nadie se entera hasta que la campana termina sin su contenido; si se generan solos, el fallo es que sobra un entregable y se ve en la lista. Va por evento (campaign_creator.accepted --&gt; GenerarEntregables) y no dentro de aceptar(), porque Campaign no puede conocer Content: la misma frontera que se cobro el panel de 7.7. Idempotente porque aceptar dos veces no puede pasar --el enlace es de un solo uso-- pero una reanudacion de la cola o un reintento manual si, y duplicar el trabajo de un creador es la clase de error que se descubre tarde y mal</t>
         </is>
       </c>
     </row>
     <row r="110" ht="34.5" customHeight="1" s="36">
       <c r="A110" s="67" t="inlineStr">
         <is>
-          <t>DEC-125</t>
+          <t>DEC-128</t>
         </is>
       </c>
       <c r="B110" s="68" t="inlineStr">
@@ -17985,24 +18035,24 @@
       <c r="C110" s="68" t="n"/>
       <c r="D110" s="69" t="inlineStr">
         <is>
-          <t>Cuando un creador contesta, se avisa a QUIEN LE INVITO y a nadie mas.</t>
+          <t>En el seguimiento, el dinero SI y el margen solo con su permiso.</t>
         </is>
       </c>
       <c r="E110" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="F110" s="69" t="inlineStr">
         <is>
-          <t>Es quien espera la respuesta y quien va a hacer algo con ella. Avisar a todo el equipo son cuarenta correos por campana a cada uno, y un buzon asi se filtra a una carpeta y deja de leerse --la forma cara de no avisar a nadie--. El precio, dicho: una invitacion mandada por alguien que luego se va de la empresa queda MUDA. A una cuenta desactivada no se le escribe: no avisa a nadie y puede acabar en un buzon reasignado. El hecho no se pierde, queda en domain_events y se ve en la lista</t>
+          <t>Presupuesto, comprometido y disponible los ve quien puede ver la campana: sin esos tres numeros no se decide a quien invitar, y ponerlos detras de un permiso que entonces necesitaria todo el mundo seria un permiso que no protege nada. El margen sigue detras de campaign.view_margin (BR-FIN-007) y no se calcula y luego se esconde: no se calcula --un dato que llega a la vista es un dato que un @if mal puesto puede ensenar, y BR-SEC-001 es 🔴--. La diferencia no es sutil: lo comprometido es lo que se le paga a los creadores; el margen es lo que gana la empresa. Y el disponible se ensena NEGATIVO cuando lo es: redondearlo a cero esconderia justo el caso que hay que ver, una campana que se paso porque finanzas lo autorizo</t>
         </is>
       </c>
     </row>
     <row r="111" ht="57" customHeight="1" s="36">
       <c r="A111" s="67" t="inlineStr">
         <is>
-          <t>DEC-124</t>
+          <t>DEC-127</t>
         </is>
       </c>
       <c r="B111" s="68" t="inlineStr">
@@ -18013,24 +18063,24 @@
       <c r="C111" s="68" t="n"/>
       <c r="D111" s="69" t="inlineStr">
         <is>
-          <t>Preguntar NO mueve el plazo de la invitacion.</t>
+          <t>Cuatro alertas en el panel de seguimiento, y su orden NO es por gravedad.</t>
         </is>
       </c>
       <c r="E111" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="F111" s="69" t="inlineStr">
         <is>
-          <t>La alternativa --congelarla hasta que alguien conteste-- deja el importe comprometido para siempre si nadie contesta, que es justo el agujero que invitaciones:caducar existe para tapar. La pantalla se lo dice al creador con todas las letras: callarlo dejaria a alguien esperando tranquilo mientras su invitacion caduca, que es peor que no dejarle preguntar. Quien invito ve la pregunta en la lista de candidatos y decide; si hace falta mas tiempo, anula y manda otra. Y no hay respuesta dentro de la aplicacion: el equipo contesta por correo, que es donde el creador ya esta. Un hilo de ida y vuelta es un modulo de mensajeria --notificaciones, no leidos, permisos-- y habria multiplicado por tres la iteracion para resolver lo que un boton de «Responder» ya resuelve. Lo que si hay es un DUENO: «me hago cargo» marca quien atiende y el segundo clic no pisa al primero</t>
+          <t>Campana sin confirmar con el arranque a menos de 14 dias, preguntas de creadores sin atender, invitaciones que caducan en menos de 12 h, y cupo de mercado sin cubrir. La de «sin confirmar» va PRIMERA porque bloquea a las demas: sin confirmar no se puede invitar a nadie, asi que un cupo corto ahi no se arregla reclutando. Y las preguntas van antes que las invitaciones urgentes porque un creador que pregunto y no recibe respuesta MIENTRAS su plazo corre es la combinacion exacta que convierte un si en un silencio. Cada alerta dice que pasa y que hacer: una que solo dice que hay un problema obliga a buscarlo, y entonces deja de leerse. Y «cubierto» es ACEPTADO, no invitado: una invitacion sin contestar es una plaza esperando, y contarla como cubierta es como se llega al dia de arranque con la mitad del equipo y los numeros en verde</t>
         </is>
       </c>
     </row>
     <row r="112" ht="45.75" customHeight="1" s="36">
       <c r="A112" s="67" t="inlineStr">
         <is>
-          <t>DEC-123</t>
+          <t>DEC-126</t>
         </is>
       </c>
       <c r="B112" s="68" t="inlineStr">
@@ -18041,24 +18091,24 @@
       <c r="C112" s="68" t="n"/>
       <c r="D112" s="69" t="inlineStr">
         <is>
-          <t>Pedir un correo se hace desde Shared, no desde el modulo que lo necesita.</t>
+          <t>usuarios:crear deja de teclear la contrasena; el alta interna usa el mismo enlace de 72 h que la del creador.</t>
         </is>
       </c>
       <c r="E112" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F112" s="69" t="inlineStr">
         <is>
-          <t>deptrac.yaml dice Communication: [Framework, Shared, Core, Identity]. En 5.9 el evento del enlace vivio una iteracion dentro de Identity y funciono de milagro: Identity esta en esa lista. Campaign no, y 7.6 necesita mandar un correo igual. Sube a App\Shared\Eventos\CorreoPedido con un solo oyente en Communication: cualquier modulo puede pedir un correo, ninguno conoce a Communication y Communication no conoce a ninguno. No es EventoOcurrido y no puede serlo --ese persiste su payload en domain_events y aqui el payload lleva el token en claro--; el HECHO si se registra, por separado y sin el token</t>
+          <t>Cierra BR-SEC-004 (🔴) del todo. must_change_password era el parche: obligaba a cambiarla DESPUES y dejaba una ventana --de minutos o de meses-- en la que dos personas conocian la credencial, y justo en las cuentas donde la base exige dos personas distintas para el dinero. Ahora no hay ventana: la contrasena no existe hasta que la escribe su dueno. usuarios:contrasena --enlace hace lo mismo para reponer y no toca la contrasena actual --si el correo no llega, la persona no se queda peor de como estaba--. Teclearla a mano sigue existiendo a proposito, como cristal de emergencia para cuando el correo no sale (Q-20), y el comando avisa cada vez de que ese es el camino excepcional</t>
         </is>
       </c>
     </row>
     <row r="113" ht="68.25" customHeight="1" s="36">
       <c r="A113" s="67" t="inlineStr">
         <is>
-          <t>DEC-122</t>
+          <t>DEC-125</t>
         </is>
       </c>
       <c r="B113" s="68" t="inlineStr">
@@ -18069,24 +18119,24 @@
       <c r="C113" s="68" t="n"/>
       <c r="D113" s="69" t="inlineStr">
         <is>
-          <t>La invitacion COPIA el importe con el que salio, y el importe no se mueve mientras este viva.</t>
+          <t>Cuando un creador contesta, se avisa a QUIEN LE INVITO y a nadie mas.</t>
         </is>
       </c>
       <c r="E113" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F113" s="69" t="inlineStr">
         <is>
-          <t>BR-CREATOR-008 congela el precio al ACEPTAR (tg_ccr_compromiso, 7.5) y entre el envio y la respuesta agreed_amount se podia mover: al creador le llegaba «te pagamos 1.500», alguien lo bajaba a 900, y aceptaba 900 sin haberlo visto nunca. No hace falta mala fe; basta con dos personas sobre la misma campana. Se cierra por los dos lados: amount_snapshot --misma decision que payment_term_days_snapshot y billing_legal_entity_id-- y tg_ccr_monto_con_invitacion, que obliga a anular la invitacion antes de renegociar. Y como en 5.9, responder y anular son dos columnas: responded_at tiene que contestar «.llego a contestar?» sin ambiguedad. Decimocuarta columna puerta del esquema</t>
+          <t>Es quien espera la respuesta y quien va a hacer algo con ella. Avisar a todo el equipo son cuarenta correos por campana a cada uno, y un buzon asi se filtra a una carpeta y deja de leerse --la forma cara de no avisar a nadie--. El precio, dicho: una invitacion mandada por alguien que luego se va de la empresa queda MUDA. A una cuenta desactivada no se le escribe: no avisa a nadie y puede acabar en un buzon reasignado. El hecho no se pierde, queda en domain_events y se ve en la lista</t>
         </is>
       </c>
     </row>
     <row r="114" ht="57" customHeight="1" s="36">
       <c r="A114" s="67" t="inlineStr">
         <is>
-          <t>DEC-121</t>
+          <t>DEC-124</t>
         </is>
       </c>
       <c r="B114" s="68" t="inlineStr">
@@ -18097,24 +18147,24 @@
       <c r="C114" s="68" t="n"/>
       <c r="D114" s="69" t="inlineStr">
         <is>
-          <t>Rechazar no cierra la campana para ese creador, y quedan las DOS rondas.</t>
+          <t>Preguntar NO mueve el plazo de la invitacion.</t>
         </is>
       </c>
       <c r="E114" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F114" s="69" t="inlineStr">
         <is>
-          <t>Pasa de verdad: rechaza por el importe, finanzas sube el presupuesto, se vuelve a preguntar. Prohibirlo obligaria a renegociar fuera del sistema. La constancia vive en invitations --una fila por ronda, con su motivo y con lo que se ofrecio entonces--, que es justo para lo que la Fase 2 diseno la tabla («cuantas veces hubo que insistir alimenta el Creator Score»). Lo que si se limpia al reinvitar es campaign_creators.declined_at: esa columna dice cuando se rechazo la ronda ACTUAL, y dejarla puesta haria que un accepted conviviera con una fecha de rechazo. El motivo es de lista cerrada para poder contestar «.por que nos dicen que no?» --si el 70% es el importe, el problema es el presupuesto y no el reclutamiento-- y no decide quien se puede reinvitar</t>
+          <t>La alternativa --congelarla hasta que alguien conteste-- deja el importe comprometido para siempre si nadie contesta, que es justo el agujero que invitaciones:caducar existe para tapar. La pantalla se lo dice al creador con todas las letras: callarlo dejaria a alguien esperando tranquilo mientras su invitacion caduca, que es peor que no dejarle preguntar. Quien invito ve la pregunta en la lista de candidatos y decide; si hace falta mas tiempo, anula y manda otra. Y no hay respuesta dentro de la aplicacion: el equipo contesta por correo, que es donde el creador ya esta. Un hilo de ida y vuelta es un modulo de mensajeria --notificaciones, no leidos, permisos-- y habria multiplicado por tres la iteracion para resolver lo que un boton de «Responder» ya resuelve. Lo que si hay es un DUENO: «me hago cargo» marca quien atiende y el segundo clic no pisa al primero</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="36">
       <c r="A115" s="67" t="inlineStr">
         <is>
-          <t>DEC-120</t>
+          <t>DEC-123</t>
         </is>
       </c>
       <c r="B115" s="68" t="inlineStr">
@@ -18125,7 +18175,7 @@
       <c r="C115" s="68" t="n"/>
       <c r="D115" s="69" t="inlineStr">
         <is>
-          <t>El plazo para contestar vive en la CAMPANA, no en cada invitacion.</t>
+          <t>Pedir un correo se hace desde Shared, no desde el modulo que lo necesita.</t>
         </is>
       </c>
       <c r="E115" s="69" t="inlineStr">
@@ -18135,14 +18185,14 @@
       </c>
       <c r="F115" s="69" t="inlineStr">
         <is>
-          <t>campaigns.invitation_hours, 72 por omision, entre 1 hora y 30 dias (ck_camp_invitation_hours). Un solo numero que explicar y un solo sitio donde cambiarlo; por invitacion seria un dato que hay que decidir cuarenta veces y que nadie mira dos. Y caducar necesita un comando aunque la caducidad se deduzca: expires_at contra el reloj ya impide contestar, pero la participacion seguiria en invited para siempre, su importe seguiria contando contra el presupuesto (BR-CAMPAIGN-005 bloqueando a otros por dinero que nadie se va a gastar) y el cupo del mercado no se liberaria. invitaciones:caducar cada diez minutos: el plazo minimo es una hora, asi que diez minutos deja el retraso maximo en un 17% del plazo mas corto posible</t>
+          <t>deptrac.yaml dice Communication: [Framework, Shared, Core, Identity]. En 5.9 el evento del enlace vivio una iteracion dentro de Identity y funciono de milagro: Identity esta en esa lista. Campaign no, y 7.6 necesita mandar un correo igual. Sube a App\Shared\Eventos\CorreoPedido con un solo oyente en Communication: cualquier modulo puede pedir un correo, ninguno conoce a Communication y Communication no conoce a ninguno. No es EventoOcurrido y no puede serlo --ese persiste su payload en domain_events y aqui el payload lleva el token en claro--; el HECHO si se registra, por separado y sin el token</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="36">
       <c r="A116" s="67" t="inlineStr">
         <is>
-          <t>DEC-119</t>
+          <t>DEC-122</t>
         </is>
       </c>
       <c r="B116" s="68" t="inlineStr">
@@ -18153,7 +18203,7 @@
       <c r="C116" s="68" t="n"/>
       <c r="D116" s="69" t="inlineStr">
         <is>
-          <t>El creador contesta la invitacion EL MISMO, por enlace.</t>
+          <t>La invitacion COPIA el importe con el que salio, y el importe no se mueve mientras este viva.</t>
         </is>
       </c>
       <c r="E116" s="69" t="inlineStr">
@@ -18163,14 +18213,14 @@
       </c>
       <c r="F116" s="69" t="inlineStr">
         <is>
-          <t>Su portal (F6) sigue bloqueado por T-09, asi que no hay pantalla donde entre a decidir. La alternativa era que un operador tecleara «dijo que si por WhatsApp», y eso convierte una ACEPTACION --de la que sale lo que se le paga a una persona-- en la palabra de un tercero. Con enlace hay una IP, una hora y un token que solo el tenia. Y no habia que construir nada: es la pieza de 5.9, ya probada. invitations.channel admite otros canales desde la Fase 2; el dia que exista el de WhatsApp, la fila ya sabe distinguirlo</t>
+          <t>BR-CREATOR-008 congela el precio al ACEPTAR (tg_ccr_compromiso, 7.5) y entre el envio y la respuesta agreed_amount se podia mover: al creador le llegaba «te pagamos 1.500», alguien lo bajaba a 900, y aceptaba 900 sin haberlo visto nunca. No hace falta mala fe; basta con dos personas sobre la misma campana. Se cierra por los dos lados: amount_snapshot --misma decision que payment_term_days_snapshot y billing_legal_entity_id-- y tg_ccr_monto_con_invitacion, que obliga a anular la invitacion antes de renegociar. Y como en 5.9, responder y anular son dos columnas: responded_at tiene que contestar «.llego a contestar?» sin ambiguedad. Decimocuarta columna puerta del esquema</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="36">
       <c r="A117" s="67" t="inlineStr">
         <is>
-          <t>DEC-118</t>
+          <t>DEC-121</t>
         </is>
       </c>
       <c r="B117" s="68" t="inlineStr">
@@ -18181,24 +18231,24 @@
       <c r="C117" s="68" t="n"/>
       <c r="D117" s="69" t="inlineStr">
         <is>
-          <t>La portada se bifurca por TIPO DE USUARIO, y SESSION_DRIVER=database pasa a ser requisito de seguridad.</t>
+          <t>Rechazar no cierra la campana para ese creador, y quedan las DOS rondas.</t>
         </is>
       </c>
       <c r="E117" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F117" s="69" t="inlineStr">
         <is>
-          <t>Dos consecuencias de la misma causa: 5.9 crea la primera cuenta que no es del equipo. (a) /panel ensenaba a cualquier autenticado los totales de creadores, clientes y campanas mas el inventario del esquema; nadie lo habia pensado porque hasta hoy todos los usuarios eran internos. Se bifurca por user_type y no por permiso --un creador no tiene ninguno, y comprobar permisos que dicen «no» a todo deja una pantalla vacia en vez de una que explica donde esta--. (b) Poner una contrasena nueva borra las filas de sessions de ese usuario y rota remember_token; con SESSION_DRIVER=file lo primero es imposible --no hay forma de saber que archivo es de quien-- y una contrasena nueva convivira con la sesion abierta de quien entro con la vieja, que es no haber hecho nada</t>
+          <t>Pasa de verdad: rechaza por el importe, finanzas sube el presupuesto, se vuelve a preguntar. Prohibirlo obligaria a renegociar fuera del sistema. La constancia vive en invitations --una fila por ronda, con su motivo y con lo que se ofrecio entonces--, que es justo para lo que la Fase 2 diseno la tabla («cuantas veces hubo que insistir alimenta el Creator Score»). Lo que si se limpia al reinvitar es campaign_creators.declined_at: esa columna dice cuando se rechazo la ronda ACTUAL, y dejarla puesta haria que un accepted conviviera con una fecha de rechazo. El motivo es de lista cerrada para poder contestar «.por que nos dicen que no?» --si el 70% es el importe, el problema es el presupuesto y no el reclutamiento-- y no decide quien se puede reinvitar</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="36">
       <c r="A118" s="67" t="inlineStr">
         <is>
-          <t>DEC-117</t>
+          <t>DEC-120</t>
         </is>
       </c>
       <c r="B118" s="68" t="inlineStr">
@@ -18209,24 +18259,24 @@
       <c r="C118" s="68" t="n"/>
       <c r="D118" s="69" t="inlineStr">
         <is>
-          <t>El token no se queda en la barra de direcciones.</t>
+          <t>El plazo para contestar vive en la CAMPANA, no en cada invitacion.</t>
         </is>
       </c>
       <c r="E118" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F118" s="69" t="inlineStr">
         <is>
-          <t>El enlace del correo lo lleva --no hay otra forma--, pero esa ruta solo lo guarda en la sesion y redirige a una URL sin el. Una URL con un token dentro viaja en la cabecera Referer a cualquier recurso externo de la pagina --y estas pantallas cargan tipografias de un dominio de terceros--, se queda en el registro de accesos del servidor y en el historial, y se copia entera cuando alguien la pega en un chat preguntando que es. Al guardarlo la sesion se vacia y renueva (invalidate(), no regenerate(): el segundo cambia el identificador y conserva el contenido, y aqui el contenido es lo que sobra)</t>
+          <t>campaigns.invitation_hours, 72 por omision, entre 1 hora y 30 dias (ck_camp_invitation_hours). Un solo numero que explicar y un solo sitio donde cambiarlo; por invitacion seria un dato que hay que decidir cuarenta veces y que nadie mira dos. Y caducar necesita un comando aunque la caducidad se deduzca: expires_at contra el reloj ya impide contestar, pero la participacion seguiria en invited para siempre, su importe seguiria contando contra el presupuesto (BR-CAMPAIGN-005 bloqueando a otros por dinero que nadie se va a gastar) y el cupo del mercado no se liberaria. invitaciones:caducar cada diez minutos: el plazo minimo es una hora, asi que diez minutos deja el retraso maximo en un 17% del plazo mas corto posible</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="36">
       <c r="A119" s="67" t="inlineStr">
         <is>
-          <t>DEC-116</t>
+          <t>DEC-119</t>
         </is>
       </c>
       <c r="B119" s="68" t="inlineStr">
@@ -18237,24 +18287,24 @@
       <c r="C119" s="68" t="n"/>
       <c r="D119" s="69" t="inlineStr">
         <is>
-          <t>Un enlace nuevo invalida el anterior, y usar uno mata todos los demas.</t>
+          <t>El creador contesta la invitacion EL MISMO, por enlace.</t>
         </is>
       </c>
       <c r="E119" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F119" s="69" t="inlineStr">
         <is>
-          <t>Quien pide otro suele hacerlo porque sospecha del primero; dejarlo vivo seria dejar abierta justo la puerta que queria cerrar. Lo garantiza la BASE con la decimotercera columna puerta (uq_pl_vigente), no el servicio. Y revocar no es marcar usado: son dos columnas a proposito, porque el dia que alguien pregunte «.llego a usar el enlace?» la respuesta tiene que salir de una columna que solo se escribe cuando lo uso. La primera version de la tabla las mezclaba --una columna menos-- y ademas chocaba con ck_pl_used, que exige la IP de quien lo usa: a un enlace que sustituyes no le puedes poner una IP. Caducar no se escribe: se deduce de expires_at</t>
+          <t>Su portal (F6) sigue bloqueado por T-09, asi que no hay pantalla donde entre a decidir. La alternativa era que un operador tecleara «dijo que si por WhatsApp», y eso convierte una ACEPTACION --de la que sale lo que se le paga a una persona-- en la palabra de un tercero. Con enlace hay una IP, una hora y un token que solo el tenia. Y no habia que construir nada: es la pieza de 5.9, ya probada. invitations.channel admite otros canales desde la Fase 2; el dia que exista el de WhatsApp, la fila ya sabe distinguirlo</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="36">
       <c r="A120" s="67" t="inlineStr">
         <is>
-          <t>DEC-115</t>
+          <t>DEC-118</t>
         </is>
       </c>
       <c r="B120" s="68" t="inlineStr">
@@ -18265,24 +18315,24 @@
       <c r="C120" s="68" t="n"/>
       <c r="D120" s="69" t="inlineStr">
         <is>
-          <t>Pedir recuperacion contesta lo mismo exista o no el correo.</t>
+          <t>La portada se bifurca por TIPO DE USUARIO, y SESSION_DRIVER=database pasa a ser requisito de seguridad.</t>
         </is>
       </c>
       <c r="E120" s="69" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F120" s="69" t="inlineStr">
         <is>
-          <t>«Si esa direccion tiene una cuenta activa, le acaba de salir un enlace», a los dos, y sin enviar nada en el segundo caso. Distinguirlos convierte la pantalla en un buscador de cuentas dadas de alta: con una lista de direcciones se sabe en un rato cuales son clientes nuestros, y eso vale dinero para quien hace phishing dirigido. El precio es real: quien se equivoca de correo no se entera, y se compensa diciendolo en la propia pantalla en vez de callarlo. La prueba lo afirma byte a byte quitando el testigo anti-CSRF: comparar solo la clave de sesion dejaria pasar una version que escribiera «no tenemos ese correo» dentro de la vista</t>
+          <t>Dos consecuencias de la misma causa: 5.9 crea la primera cuenta que no es del equipo. (a) /panel ensenaba a cualquier autenticado los totales de creadores, clientes y campanas mas el inventario del esquema; nadie lo habia pensado porque hasta hoy todos los usuarios eran internos. Se bifurca por user_type y no por permiso --un creador no tiene ninguno, y comprobar permisos que dicen «no» a todo deja una pantalla vacia en vez de una que explica donde esta--. (b) Poner una contrasena nueva borra las filas de sessions de ese usuario y rota remember_token; con SESSION_DRIVER=file lo primero es imposible --no hay forma de saber que archivo es de quien-- y una contrasena nueva convivira con la sesion abierta de quien entro con la vieja, que es no haber hecho nada</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="36">
       <c r="A121" s="67" t="inlineStr">
         <is>
-          <t>DEC-114</t>
+          <t>DEC-117</t>
         </is>
       </c>
       <c r="B121" s="68" t="inlineStr">
@@ -18293,7 +18343,7 @@
       <c r="C121" s="68" t="n"/>
       <c r="D121" s="69" t="inlineStr">
         <is>
-          <t>De un token de contrasena se guarda la HUELLA, nunca el token.</t>
+          <t>El token no se queda en la barra de direcciones.</t>
         </is>
       </c>
       <c r="E121" s="69" t="inlineStr">
@@ -18303,14 +18353,14 @@
       </c>
       <c r="F121" s="69" t="inlineStr">
         <is>
-          <t>bin2hex(random_bytes(32)) --no Str::random(), no uniqid(), no el uuid de la fila-- y en password_links solo entra su sha256. Misma decision que email_log (la huella del cuerpo, no el cuerpo) y que los medios de pago (la mascara, no el numero), y aqui es la mas importante de las tres: quien lea esta tabla no puede entrar en ninguna cuenta. Corolario que obligo a romper el patron de DEC-112: el aviso a Communication no puede ir por Eventos::ocurrio(), porque ese bus PERSISTE el payload y el payload lleva el enlace dentro. Va por un evento propio de Identity, que Communication ya tiene permitido conocer. El HECHO --«se emitio un enlace de tipo X para el usuario Y»-- si se guarda en domain_events, y sin el token</t>
+          <t>El enlace del correo lo lleva --no hay otra forma--, pero esa ruta solo lo guarda en la sesion y redirige a una URL sin el. Una URL con un token dentro viaja en la cabecera Referer a cualquier recurso externo de la pagina --y estas pantallas cargan tipografias de un dominio de terceros--, se queda en el registro de accesos del servidor y en el historial, y se copia entera cuando alguien la pega en un chat preguntando que es. Al guardarlo la sesion se vacia y renueva (invalidate(), no regenerate(): el segundo cambia el identificador y conserva el contenido, y aqui el contenido es lo que sobra)</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="36">
       <c r="A122" s="67" t="inlineStr">
         <is>
-          <t>DEC-113</t>
+          <t>DEC-116</t>
         </is>
       </c>
       <c r="B122" s="68" t="inlineStr">
@@ -18321,7 +18371,7 @@
       <c r="C122" s="68" t="n"/>
       <c r="D122" s="69" t="inlineStr">
         <is>
-          <t>El enlace de alta dura 72 h; el de recuperacion, 1 h.</t>
+          <t>Un enlace nuevo invalida el anterior, y usar uno mata todos los demas.</t>
         </is>
       </c>
       <c r="E122" s="69" t="inlineStr">
@@ -18331,14 +18381,14 @@
       </c>
       <c r="F122" s="69" t="inlineStr">
         <is>
-          <t>Son la misma pieza con dos relojes: el de alta llega SIN AVISAR y puede caer un viernes por la noche; el de recuperacion lo pide alguien que esta delante de la pantalla ahora. Un solo plazo obligaria a elegir entre dejar la ventana larga del alta valiendo para recuperar, o darle una hora a quien no sabia que iba a recibir nada. La caducidad se guarda en la fila, no es una constante global: un enlace sabe cuando muere</t>
+          <t>Quien pide otro suele hacerlo porque sospecha del primero; dejarlo vivo seria dejar abierta justo la puerta que queria cerrar. Lo garantiza la BASE con la decimotercera columna puerta (uq_pl_vigente), no el servicio. Y revocar no es marcar usado: son dos columnas a proposito, porque el dia que alguien pregunte «.llego a usar el enlace?» la respuesta tiene que salir de una columna que solo se escribe cuando lo uso. La primera version de la tabla las mezclaba --una columna menos-- y ademas chocaba con ck_pl_used, que exige la IP de quien lo usa: a un enlace que sustituyes no le puedes poner una IP. Caducar no se escribe: se deduce de expires_at</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="36">
       <c r="A123" s="67" t="inlineStr">
         <is>
-          <t>DEC-112</t>
+          <t>DEC-115</t>
         </is>
       </c>
       <c r="B123" s="68" t="inlineStr">
@@ -18349,24 +18399,24 @@
       <c r="C123" s="68" t="n"/>
       <c r="D123" s="69" t="inlineStr">
         <is>
-          <t>Los modulos se comunican por EVENTOS, no llamandose.</t>
+          <t>Pedir recuperacion contesta lo mismo exista o no el correo.</t>
         </is>
       </c>
       <c r="E123" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="F123" s="69" t="inlineStr">
         <is>
-          <t>deptrac.yaml no deja que Creator conozca Communication ni al reves, y no es burocracia: si Creator importara Communication, un SMTP caido podria tumbar la captura de un dato fiscal. App\Shared\Eventos estrena domain_events --disenada en 2.4 y sin una sola fila hasta hoy-- y reparte asi: Creator levanta un nombre y un array, Communication recibe un nombre y un array, y ninguno importa al otro. El hecho se GUARDA antes de despachar, para que conste aunque el oyente reviente. Y no es la bitacora: Bitacora responde «quien toco que y que cambio» y es evidencia; esto responde «que paso, para que otros reaccionen» y dispara trabajo</t>
+          <t>«Si esa direccion tiene una cuenta activa, le acaba de salir un enlace», a los dos, y sin enviar nada en el segundo caso. Distinguirlos convierte la pantalla en un buscador de cuentas dadas de alta: con una lista de direcciones se sabe en un rato cuales son clientes nuestros, y eso vale dinero para quien hace phishing dirigido. El precio es real: quien se equivoca de correo no se entera, y se compensa diciendolo en la propia pantalla en vez de callarlo. La prueba lo afirma byte a byte quitando el testigo anti-CSRF: comparar solo la clave de sesion dejaria pasar una version que escribiera «no tenemos ese correo» dentro de la vista</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="36">
       <c r="A124" s="67" t="inlineStr">
         <is>
-          <t>DEC-111</t>
+          <t>DEC-114</t>
         </is>
       </c>
       <c r="B124" s="68" t="inlineStr">
@@ -18377,24 +18427,24 @@
       <c r="C124" s="68" t="n"/>
       <c r="D124" s="69" t="inlineStr">
         <is>
-          <t>Si el aviso no se puede enviar, el cambio sigue adelante.</t>
+          <t>De un token de contrasena se guarda la HUELLA, nunca el token.</t>
         </is>
       </c>
       <c r="E124" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F124" s="69" t="inlineStr">
         <is>
-          <t>Bloquear la captura de un dato fiscal porque un SMTP se cayo convierte un problema de infraestructura en un creador al que no se le puede corregir un dato. Pero el fallo NO se traga: si el correo se encolo aparece en /correos como failed con su motivo, y si ni siquiera se pudo encolar --no hay plantilla, que es un fallo de configuracion-- se registra con report() y queda la fila de domain_events diciendo que el hecho ocurrio sin que saliera aviso</t>
+          <t>bin2hex(random_bytes(32)) --no Str::random(), no uniqid(), no el uuid de la fila-- y en password_links solo entra su sha256. Misma decision que email_log (la huella del cuerpo, no el cuerpo) y que los medios de pago (la mascara, no el numero), y aqui es la mas importante de las tres: quien lea esta tabla no puede entrar en ninguna cuenta. Corolario que obligo a romper el patron de DEC-112: el aviso a Communication no puede ir por Eventos::ocurrio(), porque ese bus PERSISTE el payload y el payload lleva el enlace dentro. Va por un evento propio de Identity, que Communication ya tiene permitido conocer. El HECHO --«se emitio un enlace de tipo X para el usuario Y»-- si se guarda en domain_events, y sin el token</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="36">
       <c r="A125" s="67" t="inlineStr">
         <is>
-          <t>DEC-110</t>
+          <t>DEC-113</t>
         </is>
       </c>
       <c r="B125" s="68" t="inlineStr">
@@ -18405,24 +18455,24 @@
       <c r="C125" s="68" t="n"/>
       <c r="D125" s="69" t="inlineStr">
         <is>
-          <t>El correo de aviso NO lleva el dato dentro.</t>
+          <t>El enlace de alta dura 72 h; el de recuperacion, 1 h.</t>
         </is>
       </c>
       <c r="E125" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F125" s="69" t="inlineStr">
         <is>
-          <t>«Alguien registro un cambio en sus datos de pago; si no ha sido usted, respondanos.» Sin numero, sin banco, sin regimen, sin RUC. Un correo se lee en pantallas ajenas, se reenvia y se queda en buzones que no controlamos --y el escenario del que nos defendemos es precisamente que alguien tenga acceso a ese buzon--. Para decir «yo no fui» no hace falta ver el numero. Misma regla que ya gobierna la bitacora (la mascara, nunca el numero) y email_log (la huella, nunca el cuerpo)</t>
+          <t>Son la misma pieza con dos relojes: el de alta llega SIN AVISAR y puede caer un viernes por la noche; el de recuperacion lo pide alguien que esta delante de la pantalla ahora. Un solo plazo obligaria a elegir entre dejar la ventana larga del alta valiendo para recuperar, o darle una hora a quien no sabia que iba a recibir nada. La caducidad se guarda en la fila, no es una constante global: un enlace sabe cuando muere</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="36">
       <c r="A126" s="67" t="inlineStr">
         <is>
-          <t>DEC-109</t>
+          <t>DEC-112</t>
         </is>
       </c>
       <c r="B126" s="68" t="inlineStr">
@@ -18433,7 +18483,7 @@
       <c r="C126" s="68" t="n"/>
       <c r="D126" s="69" t="inlineStr">
         <is>
-          <t>El aviso de cambio sensible sale al CAPTURAR, no al aprobar.</t>
+          <t>Los modulos se comunican por EVENTOS, no llamandose.</t>
         </is>
       </c>
       <c r="E126" s="69" t="inlineStr">
@@ -18443,14 +18493,14 @@
       </c>
       <c r="F126" s="69" t="inlineStr">
         <is>
-          <t>Es lo unico que le da al creador margen para decir «yo no fui» mientras el cambio todavia se puede parar. Avisar despues de aprobarlo es contarle un hecho consumado: si alguien suplanto su cuenta bancaria, el dinero ya va camino de otro sitio. Hay prueba dedicada: el aviso sale con el perfil todavia en pending</t>
+          <t>deptrac.yaml no deja que Creator conozca Communication ni al reves, y no es burocracia: si Creator importara Communication, un SMTP caido podria tumbar la captura de un dato fiscal. App\Shared\Eventos estrena domain_events --disenada en 2.4 y sin una sola fila hasta hoy-- y reparte asi: Creator levanta un nombre y un array, Communication recibe un nombre y un array, y ninguno importa al otro. El hecho se GUARDA antes de despachar, para que conste aunque el oyente reviente. Y no es la bitacora: Bitacora responde «quien toco que y que cambio» y es evidencia; esto responde «que paso, para que otros reaccionen» y dispara trabajo</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="36">
       <c r="A127" s="67" t="inlineStr">
         <is>
-          <t>DEC-108</t>
+          <t>DEC-111</t>
         </is>
       </c>
       <c r="B127" s="68" t="inlineStr">
@@ -18461,24 +18511,24 @@
       <c r="C127" s="68" t="n"/>
       <c r="D127" s="69" t="inlineStr">
         <is>
-          <t>Tres intentos espaciados (1, 5 y 15 minutos) y luego failed VISIBLE.</t>
+          <t>Si el aviso no se puede enviar, el cambio sigue adelante.</t>
         </is>
       </c>
       <c r="E127" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F127" s="69" t="inlineStr">
         <is>
-          <t>Cubre la caida pasajera del proveedor sin insistir eternamente sobre una direccion que no existe, que es la causa mas comun. ck_el_failed exige en la BASE que un fallido lleve cuando fallo Y por que: un failed sin motivo obliga a mirar el log del servidor, que es exactamente lo que esta tabla existe para evitar. Y la pantalla abre FILTRADA POR FALLIDOS, porque el modo de fallo que importa --«al creador no le llego su enlace»-- lo descubre operaciones, no un desarrollador leyendo storage/logs</t>
+          <t>Bloquear la captura de un dato fiscal porque un SMTP se cayo convierte un problema de infraestructura en un creador al que no se le puede corregir un dato. Pero el fallo NO se traga: si el correo se encolo aparece en /correos como failed con su motivo, y si ni siquiera se pudo encolar --no hay plantilla, que es un fallo de configuracion-- se registra con report() y queda la fila de domain_events diciendo que el hecho ocurrio sin que saliera aviso</t>
         </is>
       </c>
     </row>
     <row r="128" ht="23.25" customHeight="1" s="36">
       <c r="A128" s="67" t="inlineStr">
         <is>
-          <t>DEC-107</t>
+          <t>DEC-110</t>
         </is>
       </c>
       <c r="B128" s="68" t="inlineStr">
@@ -18489,24 +18539,24 @@
       <c r="C128" s="68" t="n"/>
       <c r="D128" s="69" t="inlineStr">
         <is>
-          <t>Sin plantilla en el idioma del destinatario se cae al de por defecto, y se ANOTA.</t>
+          <t>El correo de aviso NO lleva el dato dentro.</t>
         </is>
       </c>
       <c r="E128" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F128" s="69" t="inlineStr">
         <is>
-          <t>Un aviso que no llega es peor que uno en el idioma equivocado. Lo que hace que no sea una chapuza es la segunda mitad: email_log guarda locale_requested junto a template_locale, asi que «que plantillas faltan por traducir» es una consulta sobre envios reales, y sale en la pantalla como lo unico que pide una accion. Sin eso la caida seria silenciosa y nadie se enteraria nunca de que el portugues no existe. pt-BR cae antes a pt que a es: es una caida mucho mas pequena y son dos lineas</t>
+          <t>«Alguien registro un cambio en sus datos de pago; si no ha sido usted, respondanos.» Sin numero, sin banco, sin regimen, sin RUC. Un correo se lee en pantallas ajenas, se reenvia y se queda en buzones que no controlamos --y el escenario del que nos defendemos es precisamente que alguien tenga acceso a ese buzon--. Para decir «yo no fui» no hace falta ver el numero. Misma regla que ya gobierna la bitacora (la mascara, nunca el numero) y email_log (la huella, nunca el cuerpo)</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="36">
       <c r="A129" s="67" t="inlineStr">
         <is>
-          <t>DEC-106</t>
+          <t>DEC-109</t>
         </is>
       </c>
       <c r="B129" s="68" t="inlineStr">
@@ -18517,24 +18567,24 @@
       <c r="C129" s="68" t="n"/>
       <c r="D129" s="69" t="inlineStr">
         <is>
-          <t>Del correo enviado se guarda la HUELLA del cuerpo, no el cuerpo.</t>
+          <t>El aviso de cambio sensible sale al CAPTURAR, no al aprobar.</t>
         </is>
       </c>
       <c r="E129" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F129" s="69" t="inlineStr">
         <is>
-          <t>email_log guarda plantilla, version, idioma, asunto y body_sha256. El cuerpo lleva el nombre de la persona, a veces importes y a veces datos fiscales: guardarlo convierte esa tabla en una SEGUNDA COPIA de la ficha del creador, que hay que proteger, anonimizar y borrar igual que la primera. Y no se pierde nada, porque la version de la plantilla es inmutable --publicar la siguiente cierra la anterior, no la edita-- y la huella demuestra que el cuerpo enviado era exactamente el que sale de renderizarla. «Me llegaron condiciones distintas» se contesta con la version y la huella. Es la regla del proyecto sobre logs, aplicada con cabeza</t>
+          <t>Es lo unico que le da al creador margen para decir «yo no fui» mientras el cambio todavia se puede parar. Avisar despues de aprobarlo es contarle un hecho consumado: si alguien suplanto su cuenta bancaria, el dinero ya va camino de otro sitio. Hay prueba dedicada: el aviso sale con el perfil todavia en pending</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="36">
       <c r="A130" s="67" t="inlineStr">
         <is>
-          <t>DEC-105</t>
+          <t>DEC-108</t>
         </is>
       </c>
       <c r="B130" s="68" t="inlineStr">
@@ -18545,24 +18595,24 @@
       <c r="C130" s="68" t="n"/>
       <c r="D130" s="69" t="inlineStr">
         <is>
-          <t>Pasarse del presupuesto de creadores se BLOQUEA, y finanzas lo autoriza dejando el motivo.</t>
+          <t>Tres intentos espaciados (1, 5 y 15 minutos) y luego failed VISIBLE.</t>
         </is>
       </c>
       <c r="E130" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F130" s="69" t="inlineStr">
         <is>
-          <t>La regla dice «sin aprobacion explicita de un rol autorizado, que queda auditada», asi que la autorizacion es un dato de la fila: quien, cuando y por que. ck_camp_budget_override exige las tres o ninguna --una firma sin explicacion no responde «por que esta campana se paso» dentro de un ano, misma forma que ck_inv_responded--. Lo firma finanzas y no quien monto la campana (DEC-091, DEC-044), y el motivo exige al menos diez caracteres porque «porque» no es una explicacion. Lo que cuenta como comprometido son las participaciones VIVAS: un creador que rechazo no consume presupuesto, y contarlo dejaria campanas bloqueadas por dinero que nadie se va a gastar</t>
+          <t>Cubre la caida pasajera del proveedor sin insistir eternamente sobre una direccion que no existe, que es la causa mas comun. ck_el_failed exige en la BASE que un fallido lleve cuando fallo Y por que: un failed sin motivo obliga a mirar el log del servidor, que es exactamente lo que esta tabla existe para evitar. Y la pantalla abre FILTRADA POR FALLIDOS, porque el modo de fallo que importa --«al creador no le llego su enlace»-- lo descubre operaciones, no un desarrollador leyendo storage/logs</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="36">
       <c r="A131" s="67" t="inlineStr">
         <is>
-          <t>DEC-104</t>
+          <t>DEC-107</t>
         </is>
       </c>
       <c r="B131" s="68" t="inlineStr">
@@ -18573,24 +18623,24 @@
       <c r="C131" s="68" t="n"/>
       <c r="D131" s="69" t="inlineStr">
         <is>
-          <t>El monto acordado se fija al INVITAR y se congela al ACEPTAR.</t>
+          <t>Sin plantilla en el idioma del destinatario se cae al de por defecto, y se ANOTA.</t>
         </is>
       </c>
       <c r="E131" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F131" s="69" t="inlineStr">
         <is>
-          <t>BR-CREATOR-008: la tarifa declarada es referencia, el precio vinculante es el monto congelado en la participacion. Se fija al invitar porque el creador no puede aceptar un numero que no ha visto --tg_ccr_compromiso impide pasar a invited con cero-- y se congela al aceptar porque a partir de ahi es un acuerdo entre dos partes. Congelarlo ya en la invitacion obligaria a cancelar y rehacerla por un dedazo, llenando el historico de invitaciones canceladas que no se cancelaron por negocio: mismo argumento que DEC-090. Excepcion coherente con 7.2: en una campana declarada gratuita si se invita con cero</t>
+          <t>Un aviso que no llega es peor que uno en el idioma equivocado. Lo que hace que no sea una chapuza es la segunda mitad: email_log guarda locale_requested junto a template_locale, asi que «que plantillas faltan por traducir» es una consulta sobre envios reales, y sale en la pantalla como lo unico que pide una accion. Sin eso la caida seria silenciosa y nadie se enteraria nunca de que el portugues no existe. pt-BR cae antes a pt que a es: es una caida mucho mas pequena y son dos lineas</t>
         </is>
       </c>
     </row>
     <row r="132" ht="23.25" customHeight="1" s="36">
       <c r="A132" s="67" t="inlineStr">
         <is>
-          <t>DEC-103</t>
+          <t>DEC-106</t>
         </is>
       </c>
       <c r="B132" s="68" t="inlineStr">
@@ -18601,24 +18651,24 @@
       <c r="C132" s="68" t="n"/>
       <c r="D132" s="69" t="inlineStr">
         <is>
-          <t>«2 reels» en el brief es lo que entrega CADA creador, no el total de la campana.</t>
+          <t>Del correo enviado se guarda la HUELLA del cuerpo, no el cuerpo.</t>
         </is>
       </c>
       <c r="E132" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F132" s="69" t="inlineStr">
         <is>
-          <t>El brief es lo que se le dice a UNA persona; cuantos creadores hay lo dice target_creators de cada mercado (7.3). La alternativa --repartir un total entre los seleccionados-- obliga a decidir quien entrega que y a recalcular cada vez que alguien entra o sale, y un creador no sabria que acepta hasta que la lista este cerrada. Ademas confirma lo ya construido: el coste estimado de 7.4 ya multiplicaba tarifa por cantidad</t>
+          <t>email_log guarda plantilla, version, idioma, asunto y body_sha256. El cuerpo lleva el nombre de la persona, a veces importes y a veces datos fiscales: guardarlo convierte esa tabla en una SEGUNDA COPIA de la ficha del creador, que hay que proteger, anonimizar y borrar igual que la primera. Y no se pierde nada, porque la version de la plantilla es inmutable --publicar la siguiente cierra la anterior, no la edita-- y la huella demuestra que el cuerpo enviado era exactamente el que sale de renderizarla. «Me llegaron condiciones distintas» se contesta con la version y la huella. Es la regla del proyecto sobre logs, aplicada con cabeza</t>
         </is>
       </c>
     </row>
     <row r="133" ht="23.25" customHeight="1" s="36">
       <c r="A133" s="67" t="inlineStr">
         <is>
-          <t>DEC-102</t>
+          <t>DEC-105</t>
         </is>
       </c>
       <c r="B133" s="68" t="inlineStr">
@@ -18629,24 +18679,24 @@
       <c r="C133" s="68" t="n"/>
       <c r="D133" s="69" t="inlineStr">
         <is>
-          <t>Nadie entra en una campana cerrada, y una participacion que ya estaba solo se puede cancelar.</t>
+          <t>Pasarse del presupuesto de creadores se BLOQUEA, y finanzas lo autoriza dejando el motivo.</t>
         </is>
       </c>
       <c r="E133" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F133" s="69" t="inlineStr">
         <is>
-          <t>campaign_creators existia desde la Fase 2 y hasta 7.4 nadie habia escrito una fila; en cuanto se escribe la primera aparece el hueco. Una participacion en una campana terminada devenga en el ledger (9.3) contra un periodo ya liquidado, sale en el reporte «reproducible» del cliente (10.4) y cuenta en el Creator Score (14.3) por un trabajo que nunca existio. Disparadores y no CHECK porque la condicion esta en otra tabla. El de UPDATE hace falta aparte porque cerrar la campana y mover al creador son operaciones distintas; se deja pasar cancelled porque cerrar una campana con candidatos dentro tiene que poder dejarlos resueltos, y la alternativa seria borrar la fila --lo que 3.12 prohibe--</t>
+          <t>La regla dice «sin aprobacion explicita de un rol autorizado, que queda auditada», asi que la autorizacion es un dato de la fila: quien, cuando y por que. ck_camp_budget_override exige las tres o ninguna --una firma sin explicacion no responde «por que esta campana se paso» dentro de un ano, misma forma que ck_inv_responded--. Lo firma finanzas y no quien monto la campana (DEC-091, DEC-044), y el motivo exige al menos diez caracteres porque «porque» no es una explicacion. Lo que cuenta como comprometido son las participaciones VIVAS: un creador que rechazo no consume presupuesto, y contarlo dejaria campanas bloqueadas por dinero que nadie se va a gastar</t>
         </is>
       </c>
     </row>
     <row r="134" ht="23.25" customHeight="1" s="36">
       <c r="A134" s="67" t="inlineStr">
         <is>
-          <t>DEC-101</t>
+          <t>DEC-104</t>
         </is>
       </c>
       <c r="B134" s="68" t="inlineStr">
@@ -18657,24 +18707,24 @@
       <c r="C134" s="68" t="n"/>
       <c r="D134" s="69" t="inlineStr">
         <is>
-          <t>En la lista corta se entra a un mercado CONCRETO, derivado del pais del creador.</t>
+          <t>El monto acordado se fija al INVITAR y se congela al ACEPTAR.</t>
         </is>
       </c>
       <c r="E134" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F134" s="69" t="inlineStr">
         <is>
-          <t>No se pide: es el unico que puede ser, y pedirlo seria pedirle al operador que repita un dato que el sistema ya sabe. De ahi sale el cupo por mercado (target_creators, 7.3) y el reparto de entregables por pais en 7.5. agreed_amount nace en CERO a proposito: el compromiso economico se congela al aceptar (BR-CREATOR-008), no al meter a alguien en una lista, y un candidato con importe es un acuerdo que nadie ha firmado</t>
+          <t>BR-CREATOR-008: la tarifa declarada es referencia, el precio vinculante es el monto congelado en la participacion. Se fija al invitar porque el creador no puede aceptar un numero que no ha visto --tg_ccr_compromiso impide pasar a invited con cero-- y se congela al aceptar porque a partir de ahi es un acuerdo entre dos partes. Congelarlo ya en la invitacion obligaria a cancelar y rehacerla por un dedazo, llenando el historico de invitaciones canceladas que no se cancelaron por negocio: mismo argumento que DEC-090. Excepcion coherente con 7.2: en una campana declarada gratuita si se invita con cero</t>
         </is>
       </c>
     </row>
     <row r="135" ht="23.25" customHeight="1" s="36">
       <c r="A135" s="67" t="inlineStr">
         <is>
-          <t>DEC-100</t>
+          <t>DEC-103</t>
         </is>
       </c>
       <c r="B135" s="68" t="inlineStr">
@@ -18685,24 +18735,24 @@
       <c r="C135" s="68" t="n"/>
       <c r="D135" s="69" t="inlineStr">
         <is>
-          <t>Una categoria que el creador declaro que NO trabaja lo excluye del buscador.</t>
+          <t>«2 reels» en el brief es lo que entrega CADA creador, no el total de la campana.</t>
         </is>
       </c>
       <c r="E135" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F135" s="69" t="inlineStr">
         <is>
-          <t>Es media BR-CAMPAIGN-007 --roja, y hasta 7.4 sin nada detras-- y es la mitad que ya se puede comprobar con lo que hay en el modelo: creator_restrictions contra client_brand_categories. El creador ya dijo que no; invitarlo es hacerle perder el tiempo a los dos. Se sigue viendo con el interruptor de descartados, para poder auditar por que falta alguien. Competidores y exclusividades vigentes llegan en 7.11</t>
+          <t>El brief es lo que se le dice a UNA persona; cuantos creadores hay lo dice target_creators de cada mercado (7.3). La alternativa --repartir un total entre los seleccionados-- obliga a decidir quien entrega que y a recalcular cada vez que alguien entra o sale, y un creador no sabria que acepta hasta que la lista este cerrada. Ademas confirma lo ya construido: el coste estimado de 7.4 ya multiplicaba tarifa por cantidad</t>
         </is>
       </c>
     </row>
     <row r="136" ht="23.25" customHeight="1" s="36">
       <c r="A136" s="67" t="inlineStr">
         <is>
-          <t>DEC-099</t>
+          <t>DEC-102</t>
         </is>
       </c>
       <c r="B136" s="68" t="inlineStr">
@@ -18713,7 +18763,7 @@
       <c r="C136" s="68" t="n"/>
       <c r="D136" s="69" t="inlineStr">
         <is>
-          <t>El buscador ensena a todos los activos; el veto real salta al anadir.</t>
+          <t>Nadie entra en una campana cerrada, y una participacion que ya estaba solo se puede cancelar.</t>
         </is>
       </c>
       <c r="E136" s="69" t="inlineStr">
@@ -18723,14 +18773,14 @@
       </c>
       <c r="F136" s="69" t="inlineStr">
         <is>
-          <t>Un creador activado en junio al que en agosto se le retiro el medio de pago sigue con status = 'active': sale en la busqueda, con lo que le falta a la vista, y NO entra en la lista corta. Dos motivos: revalidar los seis requisitos de BR-CREATOR-006 por candidato y por busqueda es caro --en el veto se hace una vez, sobre uno-- y un creador que desaparece sin explicacion parece un fallo del sistema, mientras que uno que sale con «le falta el medio de pago» es una tarea. El veto usa CompletitudOperativa, la MISMA clase que decide la activacion y no una copia: si manana se anade un septimo requisito, lo hereda sin que nadie se acuerde de venir aqui</t>
+          <t>campaign_creators existia desde la Fase 2 y hasta 7.4 nadie habia escrito una fila; en cuanto se escribe la primera aparece el hueco. Una participacion en una campana terminada devenga en el ledger (9.3) contra un periodo ya liquidado, sale en el reporte «reproducible» del cliente (10.4) y cuenta en el Creator Score (14.3) por un trabajo que nunca existio. Disparadores y no CHECK porque la condicion esta en otra tabla. El de UPDATE hace falta aparte porque cerrar la campana y mover al creador son operaciones distintas; se deja pasar cancelled porque cerrar una campana con candidatos dentro tiene que poder dejarlos resueltos, y la alternativa seria borrar la fila --lo que 3.12 prohibe--</t>
         </is>
       </c>
     </row>
     <row r="137" ht="23.25" customHeight="1" s="36">
       <c r="A137" s="67" t="inlineStr">
         <is>
-          <t>DEC-098</t>
+          <t>DEC-101</t>
         </is>
       </c>
       <c r="B137" s="68" t="inlineStr">
@@ -18741,24 +18791,24 @@
       <c r="C137" s="68" t="n"/>
       <c r="D137" s="69" t="inlineStr">
         <is>
-          <t>Que el mercado sea DE la campana lo garantiza el esquema, con foraneas COMPUESTAS.</t>
+          <t>En la lista corta se entra a un mercado CONCRETO, derivado del pais del creador.</t>
         </is>
       </c>
       <c r="E137" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F137" s="69" t="inlineStr">
         <is>
-          <t>campaign_requirements.campaign_market_id y campaign_creators.campaign_market_id apuntaban a campaign_markets(id), y una foranea asi solo comprueba que el mercado exista: nada impedia un requisito de la campana A colgado del mercado de la campana B, ni un creador aceptado atribuido al pais de otra campana. Se anade uq_cm_id_campaign (id, campaign_id) --redundante como clave, necesaria como destino-- y las dos foraneas pasan a (campaign_market_id, campaign_id). Se prefiere a un disparador porque la comprueba el motor en las dos direcciones --tambien impide mover un mercado de campana-- y porque Percona 5.7 si tiene foraneas compuestas. Y el NULL con significado de N-03 sobrevive sin un caso especial: en MySQL una foranea compuesta con un componente NULL no se comprueba</t>
+          <t>No se pide: es el unico que puede ser, y pedirlo seria pedirle al operador que repita un dato que el sistema ya sabe. De ahi sale el cupo por mercado (target_creators, 7.3) y el reparto de entregables por pais en 7.5. agreed_amount nace en CERO a proposito: el compromiso economico se congela al aceptar (BR-CREATOR-008), no al meter a alguien en una lista, y un candidato con importe es un acuerdo que nadie ha firmado</t>
         </is>
       </c>
     </row>
     <row r="138" ht="34.5" customHeight="1" s="36">
       <c r="A138" s="67" t="inlineStr">
         <is>
-          <t>DEC-097</t>
+          <t>DEC-100</t>
         </is>
       </c>
       <c r="B138" s="68" t="inlineStr">
@@ -18769,24 +18819,24 @@
       <c r="C138" s="68" t="n"/>
       <c r="D138" s="69" t="inlineStr">
         <is>
-          <t>El pais de un mercado no necesita cobertura de facturacion.</t>
+          <t>Una categoria que el creador declaro que NO trabaja lo excluye del buscador.</t>
         </is>
       </c>
       <c r="E138" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F138" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-003 resuelve quien factura por el pais del CLIENTE: un cliente peruano puede pagar una campana que corre en Colombia sin que el grupo tenga sociedad alli, y exigir cobertura en el mercado bloquearia hoy toda campana fuera de Peru. Lo que si puede hacer falta es como se le paga a un creador colombiano, y eso es Q-40, que sigue abierta y desde 7.3 tiene caso de uso</t>
+          <t>Es media BR-CAMPAIGN-007 --roja, y hasta 7.4 sin nada detras-- y es la mitad que ya se puede comprobar con lo que hay en el modelo: creator_restrictions contra client_brand_categories. El creador ya dijo que no; invitarlo es hacerle perder el tiempo a los dos. Se sigue viendo con el interruptor de descartados, para poder auditar por que falta alguien. Competidores y exclusividades vigentes llegan en 7.11</t>
         </is>
       </c>
     </row>
     <row r="139" ht="23.25" customHeight="1" s="36">
       <c r="A139" s="67" t="inlineStr">
         <is>
-          <t>DEC-096</t>
+          <t>DEC-099</t>
         </is>
       </c>
       <c r="B139" s="68" t="inlineStr">
@@ -18797,24 +18847,24 @@
       <c r="C139" s="68" t="n"/>
       <c r="D139" s="69" t="inlineStr">
         <is>
-          <t>De una campana confirmada se ANADE un mercado, no se quita.</t>
+          <t>El buscador ensena a todos los activos; el veto real salta al anadir.</t>
         </is>
       </c>
       <c r="E139" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F139" s="69" t="inlineStr">
         <is>
-          <t>Ampliar a un pais nuevo es una decision comercial normal y no rompe nada de lo prometido; quitar puede dejar fuera a creadores ya invitados o aceptados, y eso exige una enmienda aceptada por las dos partes (BR-CAMPAIGN-003). Lo impide tg_cm_no_quitar_confirmada, un BEFORE DELETE que mira el estado de la CAMPANA y no una columna propia: el congelado de un mercado no es un hecho del mercado. Y hace falta el disparador precisamente porque la regla es asimetrica: una simetrica --«confirmada, no se toca»-- se explica de memoria; una asimetrica se olvida en la mitad de los sitios</t>
+          <t>Un creador activado en junio al que en agosto se le retiro el medio de pago sigue con status = 'active': sale en la busqueda, con lo que le falta a la vista, y NO entra en la lista corta. Dos motivos: revalidar los seis requisitos de BR-CREATOR-006 por candidato y por busqueda es caro --en el veto se hace una vez, sobre uno-- y un creador que desaparece sin explicacion parece un fallo del sistema, mientras que uno que sale con «le falta el medio de pago» es una tarea. El veto usa CompletitudOperativa, la MISMA clase que decide la activacion y no una copia: si manana se anade un septimo requisito, lo hereda sin que nadie se acuerde de venir aqui</t>
         </is>
       </c>
     </row>
     <row r="140" ht="23.25" customHeight="1" s="36">
       <c r="A140" s="67" t="inlineStr">
         <is>
-          <t>DEC-095</t>
+          <t>DEC-098</t>
         </is>
       </c>
       <c r="B140" s="68" t="inlineStr">
@@ -18825,7 +18875,7 @@
       <c r="C140" s="68" t="n"/>
       <c r="D140" s="69" t="inlineStr">
         <is>
-          <t>Una campana necesita al menos un mercado para salir de borrador.</t>
+          <t>Que el mercado sea DE la campana lo garantiza el esquema, con foraneas COMPUESTAS.</t>
         </is>
       </c>
       <c r="E140" s="69" t="inlineStr">
@@ -18835,14 +18885,14 @@
       </c>
       <c r="F140" s="69" t="inlineStr">
         <is>
-          <t>Tercer motivo de BR-CAMPAIGN-004, junto al brief y al ingreso declarado. Una campana que no dice donde se ejecuta es una campana que nadie puede empezar: de ahi sale a quien se puede invitar (7.4). Cliente y marca los garantiza el esquema; el mercado no puede --un CHECK no cuenta filas de otra tabla-- asi que vive en Campanas::loQueFaltaParaSalirDeBorrador(), con los otros dos y diciendolos todos de una vez</t>
+          <t>campaign_requirements.campaign_market_id y campaign_creators.campaign_market_id apuntaban a campaign_markets(id), y una foranea asi solo comprueba que el mercado exista: nada impedia un requisito de la campana A colgado del mercado de la campana B, ni un creador aceptado atribuido al pais de otra campana. Se anade uq_cm_id_campaign (id, campaign_id) --redundante como clave, necesaria como destino-- y las dos foraneas pasan a (campaign_market_id, campaign_id). Se prefiere a un disparador porque la comprueba el motor en las dos direcciones --tambien impide mover un mercado de campana-- y porque Percona 5.7 si tiene foraneas compuestas. Y el NULL con significado de N-03 sobrevive sin un caso especial: en MySQL una foranea compuesta con un componente NULL no se comprueba</t>
         </is>
       </c>
     </row>
     <row r="141" ht="34.5" customHeight="1" s="36">
       <c r="A141" s="67" t="inlineStr">
         <is>
-          <t>DEC-094</t>
+          <t>DEC-097</t>
         </is>
       </c>
       <c r="B141" s="68" t="inlineStr">
@@ -18853,24 +18903,24 @@
       <c r="C141" s="68" t="n"/>
       <c r="D141" s="69" t="inlineStr">
         <is>
-          <t>La regla se recorta a los estados NO iniciales, como sus dos hermanas.</t>
+          <t>El pais de un mercado no necesita cobertura de facturacion.</t>
         </is>
       </c>
       <c r="E141" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F141" s="69" t="inlineStr">
         <is>
-          <t>La primera version de ck_camp_revenue_declarado no lo hacia y habria rechazado toda campana recien creada: revenue_amount e is_gratis nacen los dos a cero, asi que el formulario vacio violaba la regla antes de que nadie pudiera teclear el precio. Es la misma forma que ck_camp_confirmed y ck_camp_billing_entity: *o estas todavia escribiendo la campana, o el dato existe*. Un borrador tiene derecho a estar a medias; lo que no puede es salir de ahi asi</t>
+          <t>BR-LE-003 resuelve quien factura por el pais del CLIENTE: un cliente peruano puede pagar una campana que corre en Colombia sin que el grupo tenga sociedad alli, y exigir cobertura en el mercado bloquearia hoy toda campana fuera de Peru. Lo que si puede hacer falta es como se le paga a un creador colombiano, y eso es Q-40, que sigue abierta y desde 7.3 tiene caso de uso</t>
         </is>
       </c>
     </row>
     <row r="142" ht="23.25" customHeight="1" s="36">
       <c r="A142" s="67" t="inlineStr">
         <is>
-          <t>DEC-093</t>
+          <t>DEC-096</t>
         </is>
       </c>
       <c r="B142" s="68" t="inlineStr">
@@ -18881,24 +18931,24 @@
       <c r="C142" s="68" t="n"/>
       <c r="D142" s="69" t="inlineStr">
         <is>
-          <t>Ingreso cero es valido, pero hay que declararlo.</t>
+          <t>De una campana confirmada se ANADE un mercado, no se quita.</t>
         </is>
       </c>
       <c r="E142" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F142" s="69" t="inlineStr">
         <is>
-          <t>revenue_amount = 0 respondia a dos preguntas distintas con el mismo numero --«esta campana se regala» (canje, cortesia, prueba) y «nadie le ha puesto precio»--, y ante un margen descuadrado la diferencia entre las dos es la diferencia entre «salio como se planeo» y «se nos escapo». Columna is_gratis y ck_camp_revenue_declarado. Va en la BASE y no en la pantalla porque la pregunta que hay que poder responder dentro de un ano es «¿esta campana de cero se regalo o se nos olvido cobrarla?», y esa respuesta tiene que sobrevivir a una importacion y a la proxima pantalla que alguien escriba. Mismo valor por omision que parecia una respuesta que DEC-048 y DEC-068</t>
+          <t>Ampliar a un pais nuevo es una decision comercial normal y no rompe nada de lo prometido; quitar puede dejar fuera a creadores ya invitados o aceptados, y eso exige una enmienda aceptada por las dos partes (BR-CAMPAIGN-003). Lo impide tg_cm_no_quitar_confirmada, un BEFORE DELETE que mira el estado de la CAMPANA y no una columna propia: el congelado de un mercado no es un hecho del mercado. Y hace falta el disparador precisamente porque la regla es asimetrica: una simetrica --«confirmada, no se toca»-- se explica de memoria; una asimetrica se olvida en la mitad de los sitios</t>
         </is>
       </c>
     </row>
     <row r="143" ht="23.25" customHeight="1" s="36">
       <c r="A143" s="67" t="inlineStr">
         <is>
-          <t>DEC-092</t>
+          <t>DEC-095</t>
         </is>
       </c>
       <c r="B143" s="68" t="inlineStr">
@@ -18909,24 +18959,24 @@
       <c r="C143" s="68" t="n"/>
       <c r="D143" s="69" t="inlineStr">
         <is>
-          <t>«Brief definido» son los REQUISITOS, no el texto del briefing.</t>
+          <t>Una campana necesita al menos un mercado para salir de borrador.</t>
         </is>
       </c>
       <c r="E143" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F143" s="69" t="inlineStr">
         <is>
-          <t>BR-CAMPAIGN-004 exige «brief definido» para aprobar y no dice que es. Se decide: al menos una fila en campaign_requirements --un formato, una cantidad, un plazo--. El campo briefing sigue siendo texto libre opcional porque no se puede comprobar de verdad: un espacio en blanco cumpliria cualquier NOT NULL, asi que exigirlo anadiria friccion sin anadir garantia. Los formatos si se comprueban, y son lo que convierte «hay una campana» en «hay algo que entregar»: es lo minimo que un creador necesita para decidir si acepta</t>
+          <t>Tercer motivo de BR-CAMPAIGN-004, junto al brief y al ingreso declarado. Una campana que no dice donde se ejecuta es una campana que nadie puede empezar: de ahi sale a quien se puede invitar (7.4). Cliente y marca los garantiza el esquema; el mercado no puede --un CHECK no cuenta filas de otra tabla-- asi que vive en Campanas::loQueFaltaParaSalirDeBorrador(), con los otros dos y diciendolos todos de una vez</t>
         </is>
       </c>
     </row>
     <row r="144" ht="23.25" customHeight="1" s="36">
       <c r="A144" s="67" t="inlineStr">
         <is>
-          <t>DEC-091</t>
+          <t>DEC-094</t>
         </is>
       </c>
       <c r="B144" s="68" t="inlineStr">
@@ -18937,24 +18987,24 @@
       <c r="C144" s="68" t="n"/>
       <c r="D144" s="69" t="inlineStr">
         <is>
-          <t>Aprobar una campana es de finanzas, no de quien la monta.</t>
+          <t>La regla se recorta a los estados NO iniciales, como sus dos hermanas.</t>
         </is>
       </c>
       <c r="E144" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F144" s="69" t="inlineStr">
         <is>
-          <t>Aprobar fija el ingreso comprometido y congela la sociedad emisora: es una decision de dinero, y la misma separacion que DEC-044 impone en la base para perfiles fiscales y medios de pago. Permiso nuevo campaign.approve, y vive en el GRAFO de transiciones, no en la ruta: una ruta con permiso fijo obligaria a partir la accion en dos y a acordarse de las dos al anadir un estado</t>
+          <t>La primera version de ck_camp_revenue_declarado no lo hacia y habria rechazado toda campana recien creada: revenue_amount e is_gratis nacen los dos a cero, asi que el formulario vacio violaba la regla antes de que nadie pudiera teclear el precio. Es la misma forma que ck_camp_confirmed y ck_camp_billing_entity: *o estas todavia escribiendo la campana, o el dato existe*. Un borrador tiene derecho a estar a medias; lo que no puede es salir de ahi asi</t>
         </is>
       </c>
     </row>
     <row r="145" ht="23.25" customHeight="1" s="36">
       <c r="A145" s="67" t="inlineStr">
         <is>
-          <t>DEC-090</t>
+          <t>DEC-093</t>
         </is>
       </c>
       <c r="B145" s="68" t="inlineStr">
@@ -18965,24 +19015,24 @@
       <c r="C145" s="68" t="n"/>
       <c r="D145" s="69" t="inlineStr">
         <is>
-          <t>Se congela al confirmar, no al salir de borrador.</t>
+          <t>Ingreso cero es valido, pero hay que declararlo.</t>
         </is>
       </c>
       <c r="E145" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F145" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-002 dice «inmutable una vez emitido» y para una campana «emitido» es ambiguo. Mientras es draft o pending_approval se corrige un dedazo; con confirmed_at puesto, no se toca. Lo impone tg_camp_entidad_congelada y no el controlador: de este dato depende que una factura de dentro de dos anos siga sabiendo quien la emitio, asi que tiene que sobrevivir a un UPDATE de mantenimiento. La alternativa --congelar al salir de borrador-- llenaria el historico de campanas cancelled que no se cancelaron por negocio, y un estado que miente sobre por que existe es peor que un campo editable un rato mas</t>
+          <t>revenue_amount = 0 respondia a dos preguntas distintas con el mismo numero --«esta campana se regala» (canje, cortesia, prueba) y «nadie le ha puesto precio»--, y ante un margen descuadrado la diferencia entre las dos es la diferencia entre «salio como se planeo» y «se nos escapo». Columna is_gratis y ck_camp_revenue_declarado. Va en la BASE y no en la pantalla porque la pregunta que hay que poder responder dentro de un ano es «¿esta campana de cero se regalo o se nos olvido cobrarla?», y esa respuesta tiene que sobrevivir a una importacion y a la proxima pantalla que alguien escriba. Mismo valor por omision que parecia una respuesta que DEC-048 y DEC-068</t>
         </is>
       </c>
     </row>
     <row r="146" ht="23.25" customHeight="1" s="36">
       <c r="A146" s="67" t="inlineStr">
         <is>
-          <t>DEC-089</t>
+          <t>DEC-092</t>
         </is>
       </c>
       <c r="B146" s="68" t="inlineStr">
@@ -18993,24 +19043,24 @@
       <c r="C146" s="68" t="n"/>
       <c r="D146" s="69" t="inlineStr">
         <is>
-          <t>La sociedad que factura una campana se resuelve a starts_on.</t>
+          <t>«Brief definido» son los REQUISITOS, no el texto del briefing.</t>
         </is>
       </c>
       <c r="E146" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F146" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-003 dice «en la fecha de la operacion»; para una campana esa fecha es cuando empieza a prestarse el servicio, que es lo que un contador defiende ante SUNAT. Consecuencia: una campana creada en diciembre para arrancar en febrero usa la cobertura de FEBRERO, asi que si la cobertura cambia el 1 de enero la campana nace ya con la sociedad correcta en vez de con una que habria que corregir --y corregirla es justo lo que DEC-090 impide--</t>
+          <t>BR-CAMPAIGN-004 exige «brief definido» para aprobar y no dice que es. Se decide: al menos una fila en campaign_requirements --un formato, una cantidad, un plazo--. El campo briefing sigue siendo texto libre opcional porque no se puede comprobar de verdad: un espacio en blanco cumpliria cualquier NOT NULL, asi que exigirlo anadiria friccion sin anadir garantia. Los formatos si se comprueban, y son lo que convierte «hay una campana» en «hay algo que entregar»: es lo minimo que un creador necesita para decidir si acepta</t>
         </is>
       </c>
     </row>
     <row r="147" ht="23.25" customHeight="1" s="36">
       <c r="A147" s="67" t="inlineStr">
         <is>
-          <t>DEC-088</t>
+          <t>DEC-091</t>
         </is>
       </c>
       <c r="B147" s="68" t="inlineStr">
@@ -19021,24 +19071,24 @@
       <c r="C147" s="68" t="n"/>
       <c r="D147" s="69" t="inlineStr">
         <is>
-          <t>La aritmetica de vigencias vive en Vigencia, y una puerta lo comprueba.</t>
+          <t>Aprobar una campana es de finanzas, no de quien la monta.</t>
         </is>
       </c>
       <c r="E147" s="69" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="F147" s="69" t="inlineStr">
         <is>
-          <t>El error de un dia --cerrar un periodo el mismo dia en que empieza el siguiente, siendo valid_to inclusivo-- ha aparecido NUEVE veces. Vigencia (4.5) le dio un sitio; tools/verificar-vigencias.php impide que vuelva a salir de el. Dos reglas: ninguna aritmetica de dias fuera de Vigencia, y ninguna comparacion de una columna de vigencia contra algo sin normalizar. Escrita en PHP con token_get_all() y no en Python con expresiones regulares, porque los comentarios de este proyecto nombran el defecto y las migraciones llevan SQL con &gt;= dentro: una regex se acusaria a si misma. Al estrenarla quedaban tres sitios sueltos, los tres escritos DESPUES de Vigencia, y uno era un fallo real ----desde=2026-2-1 contra effective_from como cadenas, dejando dos textos legales vigentes el mismo dia--. Ver docs/fase-4/4.7-PUERTA-VIGENCIAS.md</t>
+          <t>Aprobar fija el ingreso comprometido y congela la sociedad emisora: es una decision de dinero, y la misma separacion que DEC-044 impone en la base para perfiles fiscales y medios de pago. Permiso nuevo campaign.approve, y vive en el GRAFO de transiciones, no en la ruta: una ruta con permiso fijo obligaria a partir la accion en dos y a acordarse de las dos al anadir un estado</t>
         </is>
       </c>
     </row>
     <row r="148" ht="23.25" customHeight="1" s="36">
       <c r="A148" s="67" t="inlineStr">
         <is>
-          <t>DEC-087</t>
+          <t>DEC-090</t>
         </is>
       </c>
       <c r="B148" s="68" t="inlineStr">
@@ -19049,24 +19099,24 @@
       <c r="C148" s="68" t="n"/>
       <c r="D148" s="69" t="inlineStr">
         <is>
-          <t>Un 1062 se absorbe o se cuenta segun quien eligio el valor, y hay que NOMBRAR el indice para absorberlo.</t>
+          <t>Se congela al confirmar, no al salir de borrador.</t>
         </is>
       </c>
       <c r="E148" s="69" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="F148" s="69" t="inlineStr">
         <is>
-          <t>Si el valor lo calculo el sistema —el slug de una marca— el choque se recalcula y se reintenta en silencio. Si lo escribio la persona —un RUC, el nombre de una marca— tiene que llegar arriba con palabras. App\Shared\Database\Choque obliga a elegir: reintentar() exige el nombre del indice y vuelve a lanzar cualquier otro a la primera, porque un catch (QueryException) a secas absorberia el RUC repetido igual que el slug. Tres intentos como tope: un bucle sin tope convierte un indice mal entendido en una peticion eterna. El nombre se lee cortando por el ultimo punto —MySQL 8 antepone la tabla y Percona 5.7 no—, comprobado contra los dos motores</t>
+          <t>BR-LE-002 dice «inmutable una vez emitido» y para una campana «emitido» es ambiguo. Mientras es draft o pending_approval se corrige un dedazo; con confirmed_at puesto, no se toca. Lo impone tg_camp_entidad_congelada y no el controlador: de este dato depende que una factura de dentro de dos anos siga sabiendo quien la emitio, asi que tiene que sobrevivir a un UPDATE de mantenimiento. La alternativa --congelar al salir de borrador-- llenaria el historico de campanas cancelled que no se cancelaron por negocio, y un estado que miente sobre por que existe es peor que un campo editable un rato mas</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="36">
       <c r="A149" s="67" t="inlineStr">
         <is>
-          <t>DEC-086</t>
+          <t>DEC-089</t>
         </is>
       </c>
       <c r="B149" s="68" t="inlineStr">
@@ -19077,16 +19127,24 @@
       <c r="C149" s="68" t="n"/>
       <c r="D149" s="69" t="inlineStr">
         <is>
-          <t>La contraseña temporal deja de ser válida en el primer acceso</t>
-        </is>
-      </c>
-      <c r="E149" s="69" t="n"/>
-      <c r="F149" s="69" t="n"/>
+          <t>La sociedad que factura una campana se resuelve a starts_on.</t>
+        </is>
+      </c>
+      <c r="E149" s="69" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="F149" s="69" t="inlineStr">
+        <is>
+          <t>BR-LE-003 dice «en la fecha de la operacion»; para una campana esa fecha es cuando empieza a prestarse el servicio, que es lo que un contador defiende ante SUNAT. Consecuencia: una campana creada en diciembre para arrancar en febrero usa la cobertura de FEBRERO, asi que si la cobertura cambia el 1 de enero la campana nace ya con la sociedad correcta en vez de con una que habria que corregir --y corregirla es justo lo que DEC-090 impide--</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="68.25" customHeight="1" s="36">
       <c r="A150" s="67" t="inlineStr">
         <is>
-          <t>DEC-085</t>
+          <t>DEC-088</t>
         </is>
       </c>
       <c r="B150" s="68" t="inlineStr">
@@ -19097,16 +19155,24 @@
       <c r="C150" s="68" t="n"/>
       <c r="D150" s="69" t="inlineStr">
         <is>
-          <t>La bitácora la protegen dos usuarios de base de datos, no el esquema</t>
-        </is>
-      </c>
-      <c r="E150" s="69" t="n"/>
-      <c r="F150" s="69" t="n"/>
+          <t>La aritmetica de vigencias vive en Vigencia, y una puerta lo comprueba.</t>
+        </is>
+      </c>
+      <c r="E150" s="69" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="F150" s="69" t="inlineStr">
+        <is>
+          <t>El error de un dia --cerrar un periodo el mismo dia en que empieza el siguiente, siendo valid_to inclusivo-- ha aparecido NUEVE veces. Vigencia (4.5) le dio un sitio; tools/verificar-vigencias.php impide que vuelva a salir de el. Dos reglas: ninguna aritmetica de dias fuera de Vigencia, y ninguna comparacion de una columna de vigencia contra algo sin normalizar. Escrita en PHP con token_get_all() y no en Python con expresiones regulares, porque los comentarios de este proyecto nombran el defecto y las migraciones llevan SQL con &gt;= dentro: una regex se acusaria a si misma. Al estrenarla quedaban tres sitios sueltos, los tres escritos DESPUES de Vigencia, y uno era un fallo real ----desde=2026-2-1 contra effective_from como cadenas, dejando dos textos legales vigentes el mismo dia--. Ver docs/fase-4/4.7-PUERTA-VIGENCIAS.md</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="23.25" customHeight="1" s="36">
       <c r="A151" s="67" t="inlineStr">
         <is>
-          <t>DEC-084</t>
+          <t>DEC-087</t>
         </is>
       </c>
       <c r="B151" s="68" t="inlineStr">
@@ -19117,16 +19183,24 @@
       <c r="C151" s="68" t="n"/>
       <c r="D151" s="69" t="inlineStr">
         <is>
-          <t>«Perfil fiscal vigente» exige que ya haya empezado</t>
-        </is>
-      </c>
-      <c r="E151" s="69" t="n"/>
-      <c r="F151" s="69" t="n"/>
+          <t>Un 1062 se absorbe o se cuenta segun quien eligio el valor, y hay que NOMBRAR el indice para absorberlo.</t>
+        </is>
+      </c>
+      <c r="E151" s="69" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="F151" s="69" t="inlineStr">
+        <is>
+          <t>Si el valor lo calculo el sistema —el slug de una marca— el choque se recalcula y se reintenta en silencio. Si lo escribio la persona —un RUC, el nombre de una marca— tiene que llegar arriba con palabras. App\Shared\Database\Choque obliga a elegir: reintentar() exige el nombre del indice y vuelve a lanzar cualquier otro a la primera, porque un catch (QueryException) a secas absorberia el RUC repetido igual que el slug. Tres intentos como tope: un bucle sin tope convierte un indice mal entendido en una peticion eterna. El nombre se lee cortando por el ultimo punto —MySQL 8 antepone la tabla y Percona 5.7 no—, comprobado contra los dos motores</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="34.5" customHeight="1" s="36">
       <c r="A152" s="67" t="inlineStr">
         <is>
-          <t>DEC-083</t>
+          <t>DEC-086</t>
         </is>
       </c>
       <c r="B152" s="68" t="inlineStr">
@@ -19137,7 +19211,7 @@
       <c r="C152" s="68" t="n"/>
       <c r="D152" s="69" t="inlineStr">
         <is>
-          <t>«Cuenta compartida» se calcula al leer, no se guarda</t>
+          <t>La contraseña temporal deja de ser válida en el primer acceso</t>
         </is>
       </c>
       <c r="E152" s="69" t="n"/>
@@ -19146,7 +19220,7 @@
     <row r="153" ht="23.25" customHeight="1" s="36">
       <c r="A153" s="67" t="inlineStr">
         <is>
-          <t>DEC-082</t>
+          <t>DEC-085</t>
         </is>
       </c>
       <c r="B153" s="68" t="inlineStr">
@@ -19157,7 +19231,7 @@
       <c r="C153" s="68" t="n"/>
       <c r="D153" s="69" t="inlineStr">
         <is>
-          <t>Las sociedades del grupo las gestiona sólo admin</t>
+          <t>La bitácora la protegen dos usuarios de base de datos, no el esquema</t>
         </is>
       </c>
       <c r="E153" s="69" t="n"/>
@@ -19166,7 +19240,7 @@
     <row r="154" ht="23.25" customHeight="1" s="36">
       <c r="A154" s="67" t="inlineStr">
         <is>
-          <t>DEC-081</t>
+          <t>DEC-084</t>
         </is>
       </c>
       <c r="B154" s="68" t="inlineStr">
@@ -19177,7 +19251,7 @@
       <c r="C154" s="68" t="n"/>
       <c r="D154" s="69" t="inlineStr">
         <is>
-          <t>Dar de baja una sociedad cierra sus coberturas abiertas</t>
+          <t>«Perfil fiscal vigente» exige que ya haya empezado</t>
         </is>
       </c>
       <c r="E154" s="69" t="n"/>
@@ -19186,7 +19260,7 @@
     <row r="155" ht="23.25" customHeight="1" s="36">
       <c r="A155" s="67" t="inlineStr">
         <is>
-          <t>DEC-080</t>
+          <t>DEC-083</t>
         </is>
       </c>
       <c r="B155" s="68" t="inlineStr">
@@ -19197,7 +19271,7 @@
       <c r="C155" s="68" t="n"/>
       <c r="D155" s="69" t="inlineStr">
         <is>
-          <t>Un gate que comprueba que los nombres entre capas existen</t>
+          <t>«Cuenta compartida» se calcula al leer, no se guarda</t>
         </is>
       </c>
       <c r="E155" s="69" t="n"/>
@@ -19206,7 +19280,7 @@
     <row r="156" ht="23.25" customHeight="1" s="36">
       <c r="A156" s="67" t="inlineStr">
         <is>
-          <t>DEC-079</t>
+          <t>DEC-082</t>
         </is>
       </c>
       <c r="B156" s="68" t="inlineStr">
@@ -19217,7 +19291,7 @@
       <c r="C156" s="68" t="n"/>
       <c r="D156" s="69" t="inlineStr">
         <is>
-          <t>La identidad fiscal del cliente tiene permiso propio, en dos roles</t>
+          <t>Las sociedades del grupo las gestiona sólo admin</t>
         </is>
       </c>
       <c r="E156" s="69" t="n"/>
@@ -19226,7 +19300,7 @@
     <row r="157" ht="23.25" customHeight="1" s="36">
       <c r="A157" s="67" t="inlineStr">
         <is>
-          <t>DEC-078</t>
+          <t>DEC-081</t>
         </is>
       </c>
       <c r="B157" s="68" t="inlineStr">
@@ -19237,7 +19311,7 @@
       <c r="C157" s="68" t="n"/>
       <c r="D157" s="69" t="inlineStr">
         <is>
-          <t>El histórico fiscal del cliente está congelado</t>
+          <t>Dar de baja una sociedad cierra sus coberturas abiertas</t>
         </is>
       </c>
       <c r="E157" s="69" t="n"/>
@@ -19246,7 +19320,7 @@
     <row r="158" ht="57" customHeight="1" s="36">
       <c r="A158" s="67" t="inlineStr">
         <is>
-          <t>DEC-077</t>
+          <t>DEC-080</t>
         </is>
       </c>
       <c r="B158" s="68" t="inlineStr">
@@ -19257,7 +19331,7 @@
       <c r="C158" s="68" t="n"/>
       <c r="D158" s="69" t="inlineStr">
         <is>
-          <t>Un contacto no cambia de cliente</t>
+          <t>Un gate que comprueba que los nombres entre capas existen</t>
         </is>
       </c>
       <c r="E158" s="69" t="n"/>
@@ -19266,7 +19340,7 @@
     <row r="159" ht="23.25" customHeight="1" s="36">
       <c r="A159" s="67" t="inlineStr">
         <is>
-          <t>DEC-076</t>
+          <t>DEC-079</t>
         </is>
       </c>
       <c r="B159" s="68" t="inlineStr">
@@ -19277,7 +19351,7 @@
       <c r="C159" s="68" t="n"/>
       <c r="D159" s="69" t="inlineStr">
         <is>
-          <t>La lista de suites de restricción vive en un solo archivo</t>
+          <t>La identidad fiscal del cliente tiene permiso propio, en dos roles</t>
         </is>
       </c>
       <c r="E159" s="69" t="n"/>
@@ -19286,7 +19360,7 @@
     <row r="160" ht="34.5" customHeight="1" s="36">
       <c r="A160" s="67" t="inlineStr">
         <is>
-          <t>DEC-075</t>
+          <t>DEC-078</t>
         </is>
       </c>
       <c r="B160" s="68" t="inlineStr">
@@ -19297,7 +19371,7 @@
       <c r="C160" s="68" t="n"/>
       <c r="D160" s="69" t="inlineStr">
         <is>
-          <t>El relevo del contacto principal se hace, no se rechaza</t>
+          <t>El histórico fiscal del cliente está congelado</t>
         </is>
       </c>
       <c r="E160" s="69" t="n"/>
@@ -19306,7 +19380,7 @@
     <row r="161" ht="34.5" customHeight="1" s="36">
       <c r="A161" s="67" t="inlineStr">
         <is>
-          <t>DEC-074</t>
+          <t>DEC-077</t>
         </is>
       </c>
       <c r="B161" s="68" t="inlineStr">
@@ -19317,7 +19391,7 @@
       <c r="C161" s="68" t="n"/>
       <c r="D161" s="69" t="inlineStr">
         <is>
-          <t>Al dar de alta un cliente se crea su primera marca</t>
+          <t>Un contacto no cambia de cliente</t>
         </is>
       </c>
       <c r="E161" s="69" t="n"/>
@@ -19326,7 +19400,7 @@
     <row r="162" ht="45.75" customHeight="1" s="36">
       <c r="A162" s="67" t="inlineStr">
         <is>
-          <t>DEC-073</t>
+          <t>DEC-076</t>
         </is>
       </c>
       <c r="B162" s="68" t="inlineStr">
@@ -19337,20 +19411,16 @@
       <c r="C162" s="68" t="n"/>
       <c r="D162" s="69" t="inlineStr">
         <is>
-          <t>Un prospecto se apunta en cualquier país; activarlo exige cobertura</t>
-        </is>
-      </c>
-      <c r="E162" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>La lista de suites de restricción vive en un solo archivo</t>
+        </is>
+      </c>
+      <c r="E162" s="69" t="n"/>
       <c r="F162" s="69" t="n"/>
     </row>
     <row r="163" ht="34.5" customHeight="1" s="36">
       <c r="A163" s="67" t="inlineStr">
         <is>
-          <t>DEC-072</t>
+          <t>DEC-075</t>
         </is>
       </c>
       <c r="B163" s="68" t="inlineStr">
@@ -19361,7 +19431,7 @@
       <c r="C163" s="68" t="n"/>
       <c r="D163" s="69" t="inlineStr">
         <is>
-          <t>creator_addresses queda fuera de la regla de periodos</t>
+          <t>El relevo del contacto principal se hace, no se rechaza</t>
         </is>
       </c>
       <c r="E163" s="69" t="n"/>
@@ -19370,7 +19440,7 @@
     <row r="164" ht="23.25" customHeight="1" s="36">
       <c r="A164" s="67" t="inlineStr">
         <is>
-          <t>DEC-071</t>
+          <t>DEC-074</t>
         </is>
       </c>
       <c r="B164" s="68" t="inlineStr">
@@ -19381,7 +19451,7 @@
       <c r="C164" s="68" t="n"/>
       <c r="D164" s="69" t="inlineStr">
         <is>
-          <t>Un perfil fiscal nuevo no puede empezar antes que el vigente</t>
+          <t>Al dar de alta un cliente se crea su primera marca</t>
         </is>
       </c>
       <c r="E164" s="69" t="n"/>
@@ -19390,7 +19460,7 @@
     <row r="165" ht="23.25" customHeight="1" s="36">
       <c r="A165" s="67" t="inlineStr">
         <is>
-          <t>DEC-070</t>
+          <t>DEC-073</t>
         </is>
       </c>
       <c r="B165" s="68" t="inlineStr">
@@ -19401,16 +19471,20 @@
       <c r="C165" s="68" t="n"/>
       <c r="D165" s="69" t="inlineStr">
         <is>
-          <t>Un bloqueo de agenda se registra aunque pise una campaña aceptada</t>
-        </is>
-      </c>
-      <c r="E165" s="69" t="n"/>
+          <t>Un prospecto se apunta en cualquier país; activarlo exige cobertura</t>
+        </is>
+      </c>
+      <c r="E165" s="69" t="inlineStr">
+        <is>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
+        </is>
+      </c>
       <c r="F165" s="69" t="n"/>
     </row>
     <row r="166" ht="23.25" customHeight="1" s="36">
       <c r="A166" s="67" t="inlineStr">
         <is>
-          <t>DEC-069</t>
+          <t>DEC-072</t>
         </is>
       </c>
       <c r="B166" s="68" t="inlineStr">
@@ -19421,20 +19495,16 @@
       <c r="C166" s="68" t="n"/>
       <c r="D166" s="69" t="inlineStr">
         <is>
-          <t>Las tarifas tienen permiso propio: creator.rate.manage</t>
-        </is>
-      </c>
-      <c r="E166" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>creator_addresses queda fuera de la regla de periodos</t>
+        </is>
+      </c>
+      <c r="E166" s="69" t="n"/>
       <c r="F166" s="69" t="n"/>
     </row>
     <row r="167" ht="34.5" customHeight="1" s="36">
       <c r="A167" s="67" t="inlineStr">
         <is>
-          <t>DEC-068</t>
+          <t>DEC-071</t>
         </is>
       </c>
       <c r="B167" s="68" t="inlineStr">
@@ -19445,20 +19515,16 @@
       <c r="C167" s="68" t="n"/>
       <c r="D167" s="69" t="inlineStr">
         <is>
-          <t>Cero es un precio válido, pero hay que declararlo</t>
-        </is>
-      </c>
-      <c r="E167" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>Un perfil fiscal nuevo no puede empezar antes que el vigente</t>
+        </is>
+      </c>
+      <c r="E167" s="69" t="n"/>
       <c r="F167" s="69" t="n"/>
     </row>
     <row r="168" ht="23.25" customHeight="1" s="36">
       <c r="A168" s="67" t="inlineStr">
         <is>
-          <t>DEC-067</t>
+          <t>DEC-070</t>
         </is>
       </c>
       <c r="B168" s="68" t="inlineStr">
@@ -19469,20 +19535,16 @@
       <c r="C168" s="68" t="n"/>
       <c r="D168" s="69" t="inlineStr">
         <is>
-          <t>Los dos permisos de medios de pago van al rol finance</t>
-        </is>
-      </c>
-      <c r="E168" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
-        </is>
-      </c>
+          <t>Un bloqueo de agenda se registra aunque pise una campaña aceptada</t>
+        </is>
+      </c>
+      <c r="E168" s="69" t="n"/>
       <c r="F168" s="69" t="n"/>
     </row>
     <row r="169" ht="45.75" customHeight="1" s="36">
       <c r="A169" s="67" t="inlineStr">
         <is>
-          <t>DEC-066</t>
+          <t>DEC-069</t>
         </is>
       </c>
       <c r="B169" s="68" t="inlineStr">
@@ -19493,12 +19555,12 @@
       <c r="C169" s="68" t="n"/>
       <c r="D169" s="69" t="inlineStr">
         <is>
-          <t>La cuenta de un medio de pago es inmutable: se sustituye, no se edita</t>
+          <t>Las tarifas tienen permiso propio: creator.rate.manage</t>
         </is>
       </c>
       <c r="E169" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
         </is>
       </c>
       <c r="F169" s="69" t="n"/>
@@ -19506,7 +19568,7 @@
     <row r="170" ht="45.75" customHeight="1" s="36">
       <c r="A170" s="67" t="inlineStr">
         <is>
-          <t>DEC-065</t>
+          <t>DEC-068</t>
         </is>
       </c>
       <c r="B170" s="68" t="inlineStr">
@@ -19517,12 +19579,12 @@
       <c r="C170" s="68" t="n"/>
       <c r="D170" s="69" t="inlineStr">
         <is>
-          <t>La misma cuenta en dos creadores se marca, no se rechaza</t>
+          <t>Cero es un precio válido, pero hay que declararlo</t>
         </is>
       </c>
       <c r="E170" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
         </is>
       </c>
       <c r="F170" s="69" t="n"/>
@@ -19530,7 +19592,7 @@
     <row r="171" ht="23.25" customHeight="1" s="36">
       <c r="A171" s="67" t="inlineStr">
         <is>
-          <t>DEC-064</t>
+          <t>DEC-067</t>
         </is>
       </c>
       <c r="B171" s="68" t="inlineStr">
@@ -19541,7 +19603,7 @@
       <c r="C171" s="68" t="n"/>
       <c r="D171" s="69" t="inlineStr">
         <is>
-          <t>El enfriamiento de un medio de pago son 24 horas, y es configuración</t>
+          <t>Los dos permisos de medios de pago van al rol finance</t>
         </is>
       </c>
       <c r="E171" s="69" t="inlineStr">
@@ -19554,7 +19616,7 @@
     <row r="172" ht="34.5" customHeight="1" s="36">
       <c r="A172" s="67" t="inlineStr">
         <is>
-          <t>DEC-063</t>
+          <t>DEC-066</t>
         </is>
       </c>
       <c r="B172" s="68" t="inlineStr">
@@ -19565,12 +19627,12 @@
       <c r="C172" s="68" t="n"/>
       <c r="D172" s="69" t="inlineStr">
         <is>
-          <t>Los umbrales de coherencia son juicio, no verdad; y no rechazan nada</t>
+          <t>La cuenta de un medio de pago es inmutable: se sustituye, no se edita</t>
         </is>
       </c>
       <c r="E172" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.7) — umbrales revisables</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F172" s="69" t="n"/>
@@ -19578,7 +19640,7 @@
     <row r="173" ht="34.5" customHeight="1" s="36">
       <c r="A173" s="67" t="inlineStr">
         <is>
-          <t>DEC-062</t>
+          <t>DEC-065</t>
         </is>
       </c>
       <c r="B173" s="68" t="inlineStr">
@@ -19589,12 +19651,12 @@
       <c r="C173" s="68" t="n"/>
       <c r="D173" s="69" t="inlineStr">
         <is>
-          <t>Los dos permisos fiscales van al mismo rol; la separación la impone la base</t>
+          <t>La misma cuenta en dos creadores se marca, no se rechaza</t>
         </is>
       </c>
       <c r="E173" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.6)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F173" s="69" t="n"/>
@@ -19602,7 +19664,7 @@
     <row r="174" ht="45.75" customHeight="1" s="36">
       <c r="A174" s="67" t="inlineStr">
         <is>
-          <t>DEC-061</t>
+          <t>DEC-064</t>
         </is>
       </c>
       <c r="B174" s="68" t="inlineStr">
@@ -19613,12 +19675,12 @@
       <c r="C174" s="68" t="n"/>
       <c r="D174" s="69" t="inlineStr">
         <is>
-          <t>Las pruebas usan una base local y desechable, nunca la de desarrollo</t>
+          <t>El enfriamiento de un medio de pago son 24 horas, y es configuración</t>
         </is>
       </c>
       <c r="E174" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F174" s="69" t="n"/>
@@ -19626,7 +19688,7 @@
     <row r="175" ht="34.5" customHeight="1" s="36">
       <c r="A175" s="67" t="inlineStr">
         <is>
-          <t>DEC-060</t>
+          <t>DEC-063</t>
         </is>
       </c>
       <c r="B175" s="68" t="inlineStr">
@@ -19637,12 +19699,12 @@
       <c r="C175" s="68" t="n"/>
       <c r="D175" s="69" t="inlineStr">
         <is>
-          <t>Verificar y activar son permisos distintos, pero hoy el mismo rol</t>
+          <t>Los umbrales de coherencia son juicio, no verdad; y no rechazan nada</t>
         </is>
       </c>
       <c r="E175" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-23, iteración 3.5) — decisión de negocio revisable</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.7) — umbrales revisables</t>
         </is>
       </c>
       <c r="F175" s="69" t="n"/>
@@ -19650,7 +19712,7 @@
     <row r="176" ht="45.75" customHeight="1" s="36">
       <c r="A176" s="67" t="inlineStr">
         <is>
-          <t>DEC-059</t>
+          <t>DEC-062</t>
         </is>
       </c>
       <c r="B176" s="68" t="inlineStr">
@@ -19661,12 +19723,12 @@
       <c r="C176" s="68" t="n"/>
       <c r="D176" s="69" t="inlineStr">
         <is>
-          <t>Se acepta una versión de los términos, no una página</t>
+          <t>Los dos permisos fiscales van al mismo rol; la separación la impone la base</t>
         </is>
       </c>
       <c r="E176" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.6)</t>
         </is>
       </c>
       <c r="F176" s="69" t="n"/>
@@ -19674,7 +19736,7 @@
     <row r="177" ht="34.5" customHeight="1" s="36">
       <c r="A177" s="67" t="inlineStr">
         <is>
-          <t>DEC-058</t>
+          <t>DEC-061</t>
         </is>
       </c>
       <c r="B177" s="68" t="inlineStr">
@@ -19685,7 +19747,7 @@
       <c r="C177" s="68" t="n"/>
       <c r="D177" s="69" t="inlineStr">
         <is>
-          <t>La identidad verificada es evidencia, no una casilla</t>
+          <t>Las pruebas usan una base local y desechable, nunca la de desarrollo</t>
         </is>
       </c>
       <c r="E177" s="69" t="inlineStr">
@@ -19698,7 +19760,7 @@
     <row r="178" ht="34.5" customHeight="1" s="36">
       <c r="A178" s="67" t="inlineStr">
         <is>
-          <t>DEC-057</t>
+          <t>DEC-060</t>
         </is>
       </c>
       <c r="B178" s="68" t="inlineStr">
@@ -19709,12 +19771,12 @@
       <c r="C178" s="68" t="n"/>
       <c r="D178" s="69" t="inlineStr">
         <is>
-          <t>Aprobar una solicitud no activa al creador</t>
+          <t>Verificar y activar son permisos distintos, pero hoy el mismo rol</t>
         </is>
       </c>
       <c r="E178" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.4)</t>
+          <t>ADOPTADA (2026-08-23, iteración 3.5) — decisión de negocio revisable</t>
         </is>
       </c>
       <c r="F178" s="69" t="n"/>
@@ -19722,7 +19784,7 @@
     <row r="179" ht="23.25" customHeight="1" s="36">
       <c r="A179" s="67" t="inlineStr">
         <is>
-          <t>DEC-056</t>
+          <t>DEC-059</t>
         </is>
       </c>
       <c r="B179" s="68" t="inlineStr">
@@ -19733,12 +19795,12 @@
       <c r="C179" s="68" t="n"/>
       <c r="D179" s="69" t="inlineStr">
         <is>
-          <t>La bitácora se ordena por id, no por fecha, y redacta lo sensible</t>
+          <t>Se acepta una versión de los términos, no una página</t>
         </is>
       </c>
       <c r="E179" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.3)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
         </is>
       </c>
       <c r="F179" s="69" t="n"/>
@@ -19746,7 +19808,7 @@
     <row r="180" ht="34.5" customHeight="1" s="36">
       <c r="A180" s="67" t="inlineStr">
         <is>
-          <t>DEC-055</t>
+          <t>DEC-058</t>
         </is>
       </c>
       <c r="B180" s="68" t="inlineStr">
@@ -19757,24 +19819,20 @@
       <c r="C180" s="68" t="n"/>
       <c r="D180" s="69" t="inlineStr">
         <is>
-          <t>La primera pantalla de escritura no toca la identidad</t>
+          <t>La identidad verificada es evidencia, no una casilla</t>
         </is>
       </c>
       <c r="E180" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
-        </is>
-      </c>
-      <c r="F180" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Primera pantalla del proyecto que escribe: edición de creador.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+        </is>
+      </c>
+      <c r="F180" s="69" t="n"/>
     </row>
     <row r="181" ht="90.75" customHeight="1" s="36">
       <c r="A181" s="67" t="inlineStr">
         <is>
-          <t>DEC-054</t>
+          <t>DEC-057</t>
         </is>
       </c>
       <c r="B181" s="68" t="inlineStr">
@@ -19785,24 +19843,20 @@
       <c r="C181" s="68" t="n"/>
       <c r="D181" s="69" t="inlineStr">
         <is>
-          <t>La bitácora es inmutable en la base, no por convención</t>
+          <t>Aprobar una solicitud no activa al creador</t>
         </is>
       </c>
       <c r="E181" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
-        </is>
-      </c>
-      <c r="F181" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — audit_logs existía desde 2.4 y nadie escribía en ella. Al ir a llenarla apareció el segundo problema: la tabla admitía UPDATE y DELETE como cualquier otra.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.4)</t>
+        </is>
+      </c>
+      <c r="F181" s="69" t="n"/>
     </row>
     <row r="182" ht="34.5" customHeight="1" s="36">
       <c r="A182" s="67" t="inlineStr">
         <is>
-          <t>DEC-053</t>
+          <t>DEC-056</t>
         </is>
       </c>
       <c r="B182" s="68" t="inlineStr">
@@ -19813,12 +19867,12 @@
       <c r="C182" s="68" t="n"/>
       <c r="D182" s="69" t="inlineStr">
         <is>
-          <t>Autorización por permiso, sin atajo para el administrador</t>
+          <t>La bitácora se ordena por id, no por fecha, y redacta lo sensible</t>
         </is>
       </c>
       <c r="E182" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.1)</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.3)</t>
         </is>
       </c>
       <c r="F182" s="69" t="n"/>
@@ -19826,7 +19880,7 @@
     <row r="183" ht="23.25" customHeight="1" s="36">
       <c r="A183" s="67" t="inlineStr">
         <is>
-          <t>DEC-052</t>
+          <t>DEC-055</t>
         </is>
       </c>
       <c r="B183" s="68" t="inlineStr">
@@ -19837,20 +19891,24 @@
       <c r="C183" s="68" t="n"/>
       <c r="D183" s="69" t="inlineStr">
         <is>
-          <t>MySQL no admite subconsultas sobre la tabla que se está modificando</t>
+          <t>La primera pantalla de escritura no toca la identidad</t>
         </is>
       </c>
       <c r="E183" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22)</t>
-        </is>
-      </c>
-      <c r="F183" s="69" t="n"/>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
+        </is>
+      </c>
+      <c r="F183" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — Primera pantalla del proyecto que escribe: edición de creador.</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="34.5" customHeight="1" s="36">
       <c r="A184" s="67" t="inlineStr">
         <is>
-          <t>DEC-051</t>
+          <t>DEC-054</t>
         </is>
       </c>
       <c r="B184" s="68" t="inlineStr">
@@ -19861,24 +19919,24 @@
       <c r="C184" s="68" t="n"/>
       <c r="D184" s="69" t="inlineStr">
         <is>
-          <t>El CI corre la suite contra los dos motores, no contra uno</t>
+          <t>La bitácora es inmutable en la base, no por convención</t>
         </is>
       </c>
       <c r="E184" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22). Recordatorio: tools/github-workflow-ci.yml sigue pendiente de mover a .github/workflows/ci.yml a mano — es ruta protegida</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
         </is>
       </c>
       <c r="F184" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — El CI validaba formato, análisis estático, fronteras entre módulos, migraciones y pruebas. Nada de eso comprueba que las restricciones se apliquen en el motor de producción, que no aplica CHECK.</t>
+          <t xml:space="preserve"> — audit_logs existía desde 2.4 y nadie escribía en ella. Al ir a llenarla apareció el segundo problema: la tabla admitía UPDATE y DELETE como cualquier otra.</t>
         </is>
       </c>
     </row>
     <row r="185" ht="34.5" customHeight="1" s="36">
       <c r="A185" s="67" t="inlineStr">
         <is>
-          <t>DEC-050</t>
+          <t>DEC-053</t>
         </is>
       </c>
       <c r="B185" s="68" t="inlineStr">
@@ -19889,12 +19947,12 @@
       <c r="C185" s="68" t="n"/>
       <c r="D185" s="69" t="inlineStr">
         <is>
-          <t>Las migraciones se contrastan contra el esquema de referencia, no se confía en que coincidan</t>
+          <t>Autorización por permiso, sin atajo para el administrador</t>
         </is>
       </c>
       <c r="E185" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22)</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.1)</t>
         </is>
       </c>
       <c r="F185" s="69" t="n"/>
@@ -19902,7 +19960,7 @@
     <row r="186" ht="34.5" customHeight="1" s="36">
       <c r="A186" s="67" t="inlineStr">
         <is>
-          <t>DEC-049</t>
+          <t>DEC-052</t>
         </is>
       </c>
       <c r="B186" s="68" t="inlineStr">
@@ -19913,7 +19971,7 @@
       <c r="C186" s="68" t="n"/>
       <c r="D186" s="69" t="inlineStr">
         <is>
-          <t>Sin datos fiscales no hay alta, pero acompañamos a formalizarse</t>
+          <t>MySQL no admite subconsultas sobre la tabla que se está modificando</t>
         </is>
       </c>
       <c r="E186" s="69" t="inlineStr">
@@ -19921,16 +19979,12 @@
           <t>ADOPTADA (2026-08-22)</t>
         </is>
       </c>
-      <c r="F186" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Respuesta a Q-45. La propuesta inicial era pagar a un familiar del creador con declaración jurada de parentesco. El análisis de docs/fase-2/2.14-PAGO-A-TERCEROS.md identificó tres problemas: el comprobante deja de coincidir con el pago (riesgo de gasto reparable para la empresa que paga), señales de alerta de prevención de lavado, y contradicción con BR-FIN-003, que ya está implementada.</t>
-        </is>
-      </c>
+      <c r="F186" s="69" t="n"/>
     </row>
     <row r="187" ht="34.5" customHeight="1" s="36">
       <c r="A187" s="67" t="inlineStr">
         <is>
-          <t>DEC-048</t>
+          <t>DEC-051</t>
         </is>
       </c>
       <c r="B187" s="68" t="inlineStr">
@@ -19941,24 +19995,24 @@
       <c r="C187" s="68" t="n"/>
       <c r="D187" s="69" t="inlineStr">
         <is>
-          <t>La retención tiene tres estados, no dos</t>
+          <t>El CI corre la suite contra los dos motores, no contra uno</t>
         </is>
       </c>
       <c r="E187" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.15)</t>
+          <t>ADOPTADA (2026-08-22). Recordatorio: tools/github-workflow-ci.yml sigue pendiente de mover a .github/workflows/ci.yml a mano — es ruta protegida</t>
         </is>
       </c>
       <c r="F187" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Sobre Q-40 se decidió «que el modelo lo deje configurable». Al implementarlo apareció que el riesgo que yo había señalado —*«alguien pone un número a ojo y nadie se entera»*— ya estaba dentro del modelo, y era peor.</t>
+          <t xml:space="preserve"> — El CI validaba formato, análisis estático, fronteras entre módulos, migraciones y pruebas. Nada de eso comprueba que las restricciones se apliquen en el motor de producción, que no aplica CHECK.</t>
         </is>
       </c>
     </row>
     <row r="188" ht="34.5" customHeight="1" s="36">
       <c r="A188" s="67" t="inlineStr">
         <is>
-          <t>DEC-047</t>
+          <t>DEC-050</t>
         </is>
       </c>
       <c r="B188" s="68" t="inlineStr">
@@ -19969,7 +20023,7 @@
       <c r="C188" s="68" t="n"/>
       <c r="D188" s="69" t="inlineStr">
         <is>
-          <t>Se factura a todos los países desde Perú</t>
+          <t>Las migraciones se contrastan contra el esquema de referencia, no se confía en que coincidan</t>
         </is>
       </c>
       <c r="E188" s="69" t="inlineStr">
@@ -19977,16 +20031,12 @@
           <t>ADOPTADA e implementada (2026-08-22)</t>
         </is>
       </c>
-      <c r="F188" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Respuesta a Q-42. En lugar de constituir sociedad en cada país, se emiten todos los comprobantes desde la sociedad peruana. Los países se resuelven uno a uno más adelante.</t>
-        </is>
-      </c>
+      <c r="F188" s="69" t="n"/>
     </row>
     <row r="189" ht="34.5" customHeight="1" s="36">
       <c r="A189" s="67" t="inlineStr">
         <is>
-          <t>DEC-046</t>
+          <t>DEC-049</t>
         </is>
       </c>
       <c r="B189" s="68" t="inlineStr">
@@ -19997,24 +20047,24 @@
       <c r="C189" s="68" t="n"/>
       <c r="D189" s="69" t="inlineStr">
         <is>
-          <t>La base impone lo que ve en una fila; el resto lo impone el repositorio</t>
+          <t>Sin datos fiscales no hay alta, pero acompañamos a formalizarse</t>
         </is>
       </c>
       <c r="E189" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA (2026-08-22)</t>
         </is>
       </c>
       <c r="F189" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Cinco invariantes de finanzas son de varias filas o varias tablas (suma de líneas = subtotal, cobros ≤ total facturado, moneda de asiento = moneda de su payout, signo de una reversión, saldo no negativo). Ningún CHECK puede expresarlas.</t>
+          <t xml:space="preserve"> — Respuesta a Q-45. La propuesta inicial era pagar a un familiar del creador con declaración jurada de parentesco. El análisis de docs/fase-2/2.14-PAGO-A-TERCEROS.md identificó tres problemas: el comprobante deja de coincidir con el pago (riesgo de gasto reparable para la empresa que paga), señales de alerta de prevención de lavado, y contradicción con BR-FIN-003, que ya está implementada.</t>
         </is>
       </c>
     </row>
     <row r="190" ht="23.25" customHeight="1" s="36">
       <c r="A190" s="67" t="inlineStr">
         <is>
-          <t>DEC-045</t>
+          <t>DEC-048</t>
         </is>
       </c>
       <c r="B190" s="68" t="inlineStr">
@@ -20025,24 +20075,24 @@
       <c r="C190" s="68" t="n"/>
       <c r="D190" s="69" t="inlineStr">
         <is>
-          <t>La inmutabilidad financiera se impone con disparadores, no con convención</t>
+          <t>La retención tiene tres estados, no dos</t>
         </is>
       </c>
       <c r="E190" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.15)</t>
         </is>
       </c>
       <c r="F190" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — BR-FIN-008 («ningún registro financiero se elimina físicamente») y BR-FIN-002 («una corrección es un asiento de reversión») eran hasta ahora reglas de la capa de aplicación.</t>
+          <t xml:space="preserve"> — Sobre Q-40 se decidió «que el modelo lo deje configurable». Al implementarlo apareció que el riesgo que yo había señalado —*«alguien pone un número a ojo y nadie se entera»*— ya estaba dentro del modelo, y era peor.</t>
         </is>
       </c>
     </row>
     <row r="191" ht="23.25" customHeight="1" s="36">
       <c r="A191" s="67" t="inlineStr">
         <is>
-          <t>DEC-044</t>
+          <t>DEC-047</t>
         </is>
       </c>
       <c r="B191" s="68" t="inlineStr">
@@ -20053,24 +20103,24 @@
       <c r="C191" s="68" t="n"/>
       <c r="D191" s="69" t="inlineStr">
         <is>
-          <t>Todo pago pertenece a un lote (no existen pagos sueltos)</t>
+          <t>Se factura a todos los países desde Perú</t>
         </is>
       </c>
       <c r="E191" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA e implementada (2026-08-22)</t>
         </is>
       </c>
       <c r="F191" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — La primera versión de payouts permitía payout_batch_id NULL, pensando en el pago puntual fuera de la corrida quincenal.</t>
+          <t xml:space="preserve"> — Respuesta a Q-42. En lugar de constituir sociedad en cada país, se emiten todos los comprobantes desde la sociedad peruana. Los países se resuelven uno a uno más adelante.</t>
         </is>
       </c>
     </row>
     <row r="192" ht="45.75" customHeight="1" s="36">
       <c r="A192" s="67" t="inlineStr">
         <is>
-          <t>DEC-043</t>
+          <t>DEC-046</t>
         </is>
       </c>
       <c r="B192" s="68" t="inlineStr">
@@ -20081,24 +20131,24 @@
       <c r="C192" s="68" t="n"/>
       <c r="D192" s="69" t="inlineStr">
         <is>
-          <t>Dónde vive la base de datos de desarrollo</t>
+          <t>La base impone lo que ve en una fila; el resto lo impone el repositorio</t>
         </is>
       </c>
       <c r="E192" s="69" t="inlineStr">
         <is>
-          <t>ACORDADA en su intención; el motor concreto depende de DEC-042</t>
+          <t>ADOPTADA (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F192" s="69" t="inlineStr">
         <is>
-          <t>C. Es lo que hace un equipo profesional y no cuesta más que A: el motor local se instala una vez. El bucle interno —migrar, probar, deshacer, repetir— tiene que ser rápido o se deja de ejecutar, y unas pruebas que tardan minutos son unas pruebas que nadie corre. La base remota es el ensayo general, no el banco de trabajo. — Se propone usar el mismo servidor que producción, con dos bases separadas: una de desarrollo y otra de producción. No es trabajar contra los datos reales; es usar el mismo motor. Ya hay otras aplicaciones Laravel funcionando en ese servidor sin incidencias.</t>
+          <t xml:space="preserve"> — Cinco invariantes de finanzas son de varias filas o varias tablas (suma de líneas = subtotal, cobros ≤ total facturado, moneda de asiento = moneda de su payout, signo de una reversión, saldo no negativo). Ningún CHECK puede expresarlas.</t>
         </is>
       </c>
     </row>
     <row r="193" ht="34.5" customHeight="1" s="36">
       <c r="A193" s="67" t="inlineStr">
         <is>
-          <t>DEC-042</t>
+          <t>DEC-045</t>
         </is>
       </c>
       <c r="B193" s="68" t="inlineStr">
@@ -20109,108 +20159,108 @@
       <c r="C193" s="68" t="n"/>
       <c r="D193" s="69" t="inlineStr">
         <is>
-          <t>🔴 El servidor es MySQL 5.7 y no aplica los CHECK *(confirmado empíricamente)*</t>
+          <t>La inmutabilidad financiera se impone con disparadores, no con convención</t>
         </is>
       </c>
       <c r="E193" s="69" t="inlineStr">
         <is>
-          <t>🔴 CONFIRMADA — pendiente de elegir entre B y C</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F193" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — El servidor de la aplicación es Percona Server 5.7.44-48 sobre cPanel. La base de desarrollo (..._dev) y la de producción viven en él. docs/03 asumía MySQL 8.</t>
+          <t xml:space="preserve"> — BR-FIN-008 («ningún registro financiero se elimina físicamente») y BR-FIN-002 («una corrección es un asiento de reversión») eran hasta ahora reglas de la capa de aplicación.</t>
         </is>
       </c>
     </row>
     <row r="194" ht="34.5" customHeight="1" s="36">
       <c r="A194" s="67" t="inlineStr">
         <is>
-          <t>DEC-041</t>
+          <t>DEC-044</t>
         </is>
       </c>
       <c r="B194" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C194" s="68" t="n"/>
       <c r="D194" s="69" t="inlineStr">
         <is>
-          <t>Gamificación y Creator Score no se fusionan</t>
+          <t>Todo pago pertenece a un lote (no existen pagos sueltos)</t>
         </is>
       </c>
       <c r="E194" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F194" s="69" t="inlineStr">
         <is>
-          <t>B. El Score es interno, puede bajar y sirve para decidir a quién invitar; el XP es externo, nunca baja y sirve para motivar. Un creador que incumplió una vez debe bajar en el score y conservar el XP que ganó antes. — Ambos calculan un número sobre un creador a partir de los mismos eventos. La tentación de unirlos es enorme.</t>
+          <t xml:space="preserve"> — La primera versión de payouts permitía payout_batch_id NULL, pensando en el pago puntual fuera de la corrida quincenal.</t>
         </is>
       </c>
     </row>
     <row r="195" ht="23.25" customHeight="1" s="36">
       <c r="A195" s="67" t="inlineStr">
         <is>
-          <t>DEC-040</t>
+          <t>DEC-043</t>
         </is>
       </c>
       <c r="B195" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C195" s="68" t="n"/>
       <c r="D195" s="69" t="inlineStr">
         <is>
-          <t>Referidos con consolidación diferida</t>
+          <t>Dónde vive la base de datos de desarrollo</t>
         </is>
       </c>
       <c r="E195" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>ACORDADA en su intención; el motor concreto depende de DEC-042</t>
         </is>
       </c>
       <c r="F195" s="69" t="inlineStr">
         <is>
-          <t>B, más topes por periodo y verificación de que referente y referido no comparten documento, teléfono ni medio de pago. El vínculo se conserva siempre aunque el XP no se consolide: es dato de negocio. — Un programa de referidos con recompensa es, sin excepción, un imán de fraude: autorreferidos, cuentas falsas, granjas.</t>
+          <t>C. Es lo que hace un equipo profesional y no cuesta más que A: el motor local se instala una vez. El bucle interno —migrar, probar, deshacer, repetir— tiene que ser rápido o se deja de ejecutar, y unas pruebas que tardan minutos son unas pruebas que nadie corre. La base remota es el ensayo general, no el banco de trabajo. — Se propone usar el mismo servidor que producción, con dos bases separadas: una de desarrollo y otra de producción. No es trabajar contra los datos reales; es usar el mismo motor. Ya hay otras aplicaciones Laravel funcionando en ese servidor sin incidencias.</t>
         </is>
       </c>
     </row>
     <row r="196" ht="57" customHeight="1" s="36">
       <c r="A196" s="67" t="inlineStr">
         <is>
-          <t>DEC-039</t>
+          <t>DEC-042</t>
         </is>
       </c>
       <c r="B196" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C196" s="68" t="n"/>
       <c r="D196" s="69" t="inlineStr">
         <is>
-          <t>Los retos internos llevan siempre recompensa tangible 🔴</t>
+          <t>🔴 El servidor es MySQL 5.7 y no aplica los CHECK *(confirmado empíricamente)*</t>
         </is>
       </c>
       <c r="E196" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>🔴 CONFIRMADA — pendiente de elegir entre B y C</t>
         </is>
       </c>
       <c r="F196" s="69" t="inlineStr">
         <is>
-          <t>B, sin excepción. El XP es el envoltorio y el reconocimiento; nunca el pago. Es la salvaguarda que la propia especificación anticipó en §16. — "Minicampañas de XP por hacer vídeos para la plataforma". Leído desde el otro lado, puede sonar a *"produce contenido de marketing para mi empresa y te pago con puntos"* — a creadores que ya producen por dinero para tus clientes. En una red pequeña, ese daño reputacional se propaga en un grupo de WhatsApp.</t>
+          <t xml:space="preserve"> — El servidor de la aplicación es Percona Server 5.7.44-48 sobre cPanel. La base de desarrollo (..._dev) y la de producción viven en él. docs/03 asumía MySQL 8.</t>
         </is>
       </c>
     </row>
     <row r="197" ht="23.25" customHeight="1" s="36">
       <c r="A197" s="67" t="inlineStr">
         <is>
-          <t>DEC-038</t>
+          <t>DEC-041</t>
         </is>
       </c>
       <c r="B197" s="68" t="inlineStr">
@@ -20221,7 +20271,7 @@
       <c r="C197" s="68" t="n"/>
       <c r="D197" s="69" t="inlineStr">
         <is>
-          <t>Ranking por cohortes, sin tabla global</t>
+          <t>Gamificación y Creator Score no se fusionan</t>
         </is>
       </c>
       <c r="E197" s="69" t="inlineStr">
@@ -20231,14 +20281,14 @@
       </c>
       <c r="F197" s="69" t="inlineStr">
         <is>
-          <t>C. Los puntos de liga se reinician por temporada; el XP nunca. Sin ranking público por ingresos, jamás. Un ranking global solo tiene sentido en una vista interna, y ahí es un reporte, no gamificación. — Una clasificación global con 1.000 creadores significa que 990 abren la app y ven que están perdiendo. Y con el tiempo se estanca: quien lleva más tiempo acumula más.</t>
+          <t>B. El Score es interno, puede bajar y sirve para decidir a quién invitar; el XP es externo, nunca baja y sirve para motivar. Un creador que incumplió una vez debe bajar en el score y conservar el XP que ganó antes. — Ambos calculan un número sobre un creador a partir de los mismos eventos. La tentación de unirlos es enorme.</t>
         </is>
       </c>
     </row>
     <row r="198" ht="23.25" customHeight="1" s="36">
       <c r="A198" s="67" t="inlineStr">
         <is>
-          <t>DEC-037</t>
+          <t>DEC-040</t>
         </is>
       </c>
       <c r="B198" s="68" t="inlineStr">
@@ -20249,7 +20299,7 @@
       <c r="C198" s="68" t="n"/>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>Los niveles se calculan, no se almacenan</t>
+          <t>Referidos con consolidación diferida</t>
         </is>
       </c>
       <c r="E198" s="69" t="inlineStr">
@@ -20259,14 +20309,14 @@
       </c>
       <c r="F198" s="69" t="inlineStr">
         <is>
-          <t>B. Permite ajustar umbrales sin quitarle puntos a nadie, que es justamente lo que DEC-035 prohíbe. — Las curvas de nivel se recalibran; el XP ya otorgado no debe verse afectado.</t>
+          <t>B, más topes por periodo y verificación de que referente y referido no comparten documento, teléfono ni medio de pago. El vínculo se conserva siempre aunque el XP no se consolide: es dato de negocio. — Un programa de referidos con recompensa es, sin excepción, un imán de fraude: autorreferidos, cuentas falsas, granjas.</t>
         </is>
       </c>
     </row>
     <row r="199" ht="23.25" customHeight="1" s="36">
       <c r="A199" s="67" t="inlineStr">
         <is>
-          <t>DEC-036</t>
+          <t>DEC-039</t>
         </is>
       </c>
       <c r="B199" s="68" t="inlineStr">
@@ -20277,7 +20327,7 @@
       <c r="C199" s="68" t="n"/>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>Se premia comportamiento verificado, no resultados</t>
+          <t>Los retos internos llevan siempre recompensa tangible 🔴</t>
         </is>
       </c>
       <c r="E199" s="69" t="inlineStr">
@@ -20287,14 +20337,14 @@
       </c>
       <c r="F199" s="69" t="inlineStr">
         <is>
-          <t>C. A premia al algoritmo de Instagram, no al creador. B produce sobrecompromiso —creadores que aceptan lo que no pueden cumplir— y, en el caso de seguidores, desmotiva al micro-creador y premia el vector de fraude de R-04. Detalle en docs/13 §3. — ¿Sobre qué se otorga XP?</t>
+          <t>B, sin excepción. El XP es el envoltorio y el reconocimiento; nunca el pago. Es la salvaguarda que la propia especificación anticipó en §16. — "Minicampañas de XP por hacer vídeos para la plataforma". Leído desde el otro lado, puede sonar a *"produce contenido de marketing para mi empresa y te pago con puntos"* — a creadores que ya producen por dinero para tus clientes. En una red pequeña, ese daño reputacional se propaga en un grupo de WhatsApp.</t>
         </is>
       </c>
     </row>
     <row r="200" ht="45.75" customHeight="1" s="36">
       <c r="A200" s="67" t="inlineStr">
         <is>
-          <t>DEC-035</t>
+          <t>DEC-038</t>
         </is>
       </c>
       <c r="B200" s="68" t="inlineStr">
@@ -20305,7 +20355,7 @@
       <c r="C200" s="68" t="n"/>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>El XP es append-only y nunca decrece</t>
+          <t>Ranking por cohortes, sin tabla global</t>
         </is>
       </c>
       <c r="E200" s="69" t="inlineStr">
@@ -20315,14 +20365,14 @@
       </c>
       <c r="F200" s="69" t="inlineStr">
         <is>
-          <t>B. Quitar puntos se percibe como robo y destruye la confianza de golpe. Además sería castigar dos veces con el mecanismo equivocado. Mismo patrón que el ledger financiero: se corrige con asientos nuevos, no editando. — ¿Se puede restar XP por un incumplimiento?</t>
+          <t>C. Los puntos de liga se reinician por temporada; el XP nunca. Sin ranking público por ingresos, jamás. Un ranking global solo tiene sentido en una vista interna, y ahí es un reporte, no gamificación. — Una clasificación global con 1.000 creadores significa que 990 abren la app y ven que están perdiendo. Y con el tiempo se estanca: quien lleva más tiempo acumula más.</t>
         </is>
       </c>
     </row>
     <row r="201" ht="34.5" customHeight="1" s="36">
       <c r="A201" s="67" t="inlineStr">
         <is>
-          <t>DEC-034</t>
+          <t>DEC-037</t>
         </is>
       </c>
       <c r="B201" s="68" t="inlineStr">
@@ -20333,7 +20383,7 @@
       <c r="C201" s="68" t="n"/>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>Gamificación como dominio propio (D13)</t>
+          <t>Los niveles se calculan, no se almacenan</t>
         </is>
       </c>
       <c r="E201" s="69" t="inlineStr">
@@ -20343,14 +20393,14 @@
       </c>
       <c r="F201" s="69" t="inlineStr">
         <is>
-          <t>C. Igual que D12: si el motor se cae, la operación sigue igual. Y como se alimenta de eventos, el XP es recalculable: cambiar la tabla de puntos permite reprocesar el histórico. Si el XP se escribiera a mano en el momento, eso sería imposible. — XP, niveles, insignias, ligas, retos y referidos para el creador.</t>
+          <t>B. Permite ajustar umbrales sin quitarle puntos a nadie, que es justamente lo que DEC-035 prohíbe. — Las curvas de nivel se recalibran; el XP ya otorgado no debe verse afectado.</t>
         </is>
       </c>
     </row>
     <row r="202" ht="57" customHeight="1" s="36">
       <c r="A202" s="67" t="inlineStr">
         <is>
-          <t>DEC-033</t>
+          <t>DEC-036</t>
         </is>
       </c>
       <c r="B202" s="68" t="inlineStr">
@@ -20361,7 +20411,7 @@
       <c r="C202" s="68" t="n"/>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>Registrar la conexión emisora en cada documento</t>
+          <t>Se premia comportamiento verificado, no resultados</t>
         </is>
       </c>
       <c r="E202" s="69" t="inlineStr">
@@ -20371,14 +20421,14 @@
       </c>
       <c r="F202" s="69" t="inlineStr">
         <is>
-          <t>B, aplicado a comprobantes electrónicos, cobros por pasarela, pagos a creadores ejecutados por proveedor y correos enviados. — Paralelo exacto de DEC-019. Si dentro de un año hay que consultar ante el proveedor el estado del comprobante F001-00347, hay que saber por cuál se emitió.</t>
+          <t>C. A premia al algoritmo de Instagram, no al creador. B produce sobrecompromiso —creadores que aceptan lo que no pueden cumplir— y, en el caso de seguidores, desmotiva al micro-creador y premia el vector de fraude de R-04. Detalle en docs/13 §3. — ¿Sobre qué se otorga XP?</t>
         </is>
       </c>
     </row>
     <row r="203" ht="23.25" customHeight="1" s="36">
       <c r="A203" s="67" t="inlineStr">
         <is>
-          <t>DEC-032</t>
+          <t>DEC-035</t>
         </is>
       </c>
       <c r="B203" s="68" t="inlineStr">
@@ -20389,7 +20439,7 @@
       <c r="C203" s="68" t="n"/>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>Compartibilidad declarada por propósito</t>
+          <t>El XP es append-only y nunca decrece</t>
         </is>
       </c>
       <c r="E203" s="69" t="inlineStr">
@@ -20399,14 +20449,14 @@
       </c>
       <c r="F203" s="69" t="inlineStr">
         <is>
-          <t>B. Las credenciales de facturación pertenecen al contribuyente: una sociedad no puede emitir con el certificado de otra. Una validación se cumple; una recomendación en un manual, no. Reformula BR-LE-008 sin contradecirla: lo prohibido era la herencia implícita; compartir por asignación explícita es otra cosa, y aun así sigue vedado para lo fiscal. — El addendum permite que una conexión sirva a varias entidades legales. Correcto para almacenamiento o correo; peligroso para facturación.</t>
+          <t>B. Quitar puntos se percibe como robo y destruye la confianza de golpe. Además sería castigar dos veces con el mecanismo equivocado. Mismo patrón que el ledger financiero: se corrige con asientos nuevos, no editando. — ¿Se puede restar XP por un incumplimiento?</t>
         </is>
       </c>
     </row>
     <row r="204" ht="23.25" customHeight="1" s="36">
       <c r="A204" s="67" t="inlineStr">
         <is>
-          <t>DEC-031</t>
+          <t>DEC-034</t>
         </is>
       </c>
       <c r="B204" s="68" t="inlineStr">
@@ -20417,7 +20467,7 @@
       <c r="C204" s="68" t="n"/>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>Una URL de webhook por conexión</t>
+          <t>Gamificación como dominio propio (D13)</t>
         </is>
       </c>
       <c r="E204" s="69" t="inlineStr">
@@ -20427,14 +20477,14 @@
       </c>
       <c r="F204" s="69" t="inlineStr">
         <is>
-          <t>B. El enrutado por URL hace la verificación de firma determinista y de un solo intento. Se acusa de inmediato (2xx) y se procesa en cola: un proveedor que no recibe respuesta en segundos reintenta y multiplica los eventos. — Con varias conexiones del mismo proveedor conviviendo, el payload entrante a menudo no identifica la sociedad, y probar firmas contra todos los secretos es lento e inseguro. El addendum enumera qué registrar de un webhook pero no resuelve de quién es.</t>
+          <t>C. Igual que D12: si el motor se cae, la operación sigue igual. Y como se alimenta de eventos, el XP es recalculable: cambiar la tabla de puntos permite reprocesar el histórico. Si el XP se escribiera a mano en el momento, eso sería imposible. — XP, niveles, insignias, ligas, retos y referidos para el creador.</t>
         </is>
       </c>
     </row>
     <row r="205" ht="23.25" customHeight="1" s="36">
       <c r="A205" s="67" t="inlineStr">
         <is>
-          <t>DEC-030</t>
+          <t>DEC-033</t>
         </is>
       </c>
       <c r="B205" s="68" t="inlineStr">
@@ -20445,7 +20495,7 @@
       <c r="C205" s="68" t="n"/>
       <c r="D205" s="69" t="inlineStr">
         <is>
-          <t>Cifrado sobre para las credenciales</t>
+          <t>Registrar la conexión emisora en cada documento</t>
         </is>
       </c>
       <c r="E205" s="69" t="inlineStr">
@@ -20455,14 +20505,14 @@
       </c>
       <c r="F205" s="69" t="inlineStr">
         <is>
-          <t>B, con versionado en la rotación (no sobrescribir), escritura sin lectura desde la interfaz, y un filtro de redacción a nivel del logger — no "acordarse de no loguear". — El addendum señala que las credenciales pueden requerir almacenamiento distinto, sin concretar.</t>
+          <t>B, aplicado a comprobantes electrónicos, cobros por pasarela, pagos a creadores ejecutados por proveedor y correos enviados. — Paralelo exacto de DEC-019. Si dentro de un año hay que consultar ante el proveedor el estado del comprobante F001-00347, hay que saber por cuál se emitió.</t>
         </is>
       </c>
     </row>
     <row r="206" ht="45.75" customHeight="1" s="36">
       <c r="A206" s="67" t="inlineStr">
         <is>
-          <t>DEC-029</t>
+          <t>DEC-032</t>
         </is>
       </c>
       <c r="B206" s="68" t="inlineStr">
@@ -20473,7 +20523,7 @@
       <c r="C206" s="68" t="n"/>
       <c r="D206" s="69" t="inlineStr">
         <is>
-          <t>Aislamiento de ambiente como barrera, no como filtro</t>
+          <t>Compartibilidad declarada por propósito</t>
         </is>
       </c>
       <c r="E206" s="69" t="inlineStr">
@@ -20483,14 +20533,14 @@
       </c>
       <c r="F206" s="69" t="inlineStr">
         <is>
-          <t>B. La defensa no puede depender de que alguien haya configurado bien. — El fallo más caro posible de este diseño: una conexión de producción resolviéndose fuera de producción. Consecuencias reales: emitir comprobantes fiscales de verdad desde QA, cobrar tarjetas en una demo, o enviar correos reales a 150 creadores desde staging.</t>
+          <t>B. Las credenciales de facturación pertenecen al contribuyente: una sociedad no puede emitir con el certificado de otra. Una validación se cumple; una recomendación en un manual, no. Reformula BR-LE-008 sin contradecirla: lo prohibido era la herencia implícita; compartir por asignación explícita es otra cosa, y aun así sigue vedado para lo fiscal. — El addendum permite que una conexión sirva a varias entidades legales. Correcto para almacenamiento o correo; peligroso para facturación.</t>
         </is>
       </c>
     </row>
     <row r="207" ht="34.5" customHeight="1" s="36">
       <c r="A207" s="67" t="inlineStr">
         <is>
-          <t>DEC-028</t>
+          <t>DEC-031</t>
         </is>
       </c>
       <c r="B207" s="68" t="inlineStr">
@@ -20501,7 +20551,7 @@
       <c r="C207" s="68" t="n"/>
       <c r="D207" s="69" t="inlineStr">
         <is>
-          <t>Matriz de propósitos obligatorios por país</t>
+          <t>Una URL de webhook por conexión</t>
         </is>
       </c>
       <c r="E207" s="69" t="inlineStr">
@@ -20511,14 +20561,14 @@
       </c>
       <c r="F207" s="69" t="inlineStr">
         <is>
-          <t>B, más un panel de cobertura en verde/rojo y una comprobación programada que avisa antes de que una credencial expirada rompa una operación. — Descubrir que no hay conexión de facturación para Ecuador al pulsar "emitir", con el cliente esperando, es un problema de diseño, no de configuración.</t>
+          <t>B. El enrutado por URL hace la verificación de firma determinista y de un solo intento. Se acusa de inmediato (2xx) y se procesa en cola: un proveedor que no recibe respuesta en segundos reintenta y multiplica los eventos. — Con varias conexiones del mismo proveedor conviviendo, el payload entrante a menudo no identifica la sociedad, y probar firmas contra todos los secretos es lento e inseguro. El addendum enumera qué registrar de un webhook pero no resuelve de quién es.</t>
         </is>
       </c>
     </row>
     <row r="208" ht="23.25" customHeight="1" s="36">
       <c r="A208" s="67" t="inlineStr">
         <is>
-          <t>DEC-027</t>
+          <t>DEC-030</t>
         </is>
       </c>
       <c r="B208" s="68" t="inlineStr">
@@ -20529,7 +20579,7 @@
       <c r="C208" s="68" t="n"/>
       <c r="D208" s="69" t="inlineStr">
         <is>
-          <t>Resolución por especificidad, con empates rechazados al guardar</t>
+          <t>Cifrado sobre para las credenciales</t>
         </is>
       </c>
       <c r="E208" s="69" t="inlineStr">
@@ -20539,14 +20589,14 @@
       </c>
       <c r="F208" s="69" t="inlineStr">
         <is>
-          <t>B, y sobre todo: los empates no se resuelven en ejecución, se prohíben al guardar. Si dos asignaciones activas puntúan igual para la misma combinación, la interfaz rechaza el guardado y explica el conflicto. Así el resolver es siempre determinista y nadie descubre un empate emitiendo una factura. — El addendum propone una escalera de cuatro peldaños. Funciona, pero no contempla el eje de marca ni dice qué hacer ante un empate.</t>
+          <t>B, con versionado en la rotación (no sobrescribir), escritura sin lectura desde la interfaz, y un filtro de redacción a nivel del logger — no "acordarse de no loguear". — El addendum señala que las credenciales pueden requerir almacenamiento distinto, sin concretar.</t>
         </is>
       </c>
     </row>
     <row r="209" ht="23.25" customHeight="1" s="36">
       <c r="A209" s="67" t="inlineStr">
         <is>
-          <t>DEC-026</t>
+          <t>DEC-029</t>
         </is>
       </c>
       <c r="B209" s="68" t="inlineStr">
@@ -20557,7 +20607,7 @@
       <c r="C209" s="68" t="n"/>
       <c r="D209" s="69" t="inlineStr">
         <is>
-          <t>purpose es un enum cerrado en código, no un catálogo editable</t>
+          <t>Aislamiento de ambiente como barrera, no como filtro</t>
         </is>
       </c>
       <c r="E209" s="69" t="inlineStr">
@@ -20567,14 +20617,14 @@
       </c>
       <c r="F209" s="69" t="inlineStr">
         <is>
-          <t>B. El código se ramifica por propósito: invoicing implica una interfaz con emit()/getStatus(); email_transactional implica otra distinta. Un propósito creado desde el panel produciría una conexión perfectamente configurada que ningún código sabe ejecutar. Los catálogos editables son para datos de negocio; los propósitos son contratos de código. — El addendum lista los propósitos como si fueran datos administrables.</t>
+          <t>B. La defensa no puede depender de que alguien haya configurado bien. — El fallo más caro posible de este diseño: una conexión de producción resolviéndose fuera de producción. Consecuencias reales: emitir comprobantes fiscales de verdad desde QA, cobrar tarjetas en una demo, o enviar correos reales a 150 creadores desde staging.</t>
         </is>
       </c>
     </row>
     <row r="210" ht="45.75" customHeight="1" s="36">
       <c r="A210" s="67" t="inlineStr">
         <is>
-          <t>DEC-025</t>
+          <t>DEC-028</t>
         </is>
       </c>
       <c r="B210" s="68" t="inlineStr">
@@ -20585,7 +20635,7 @@
       <c r="C210" s="68" t="n"/>
       <c r="D210" s="69" t="inlineStr">
         <is>
-          <t>Proveedor / Conexión / Asignación como tres entidades</t>
+          <t>Matriz de propósitos obligatorios por país</t>
         </is>
       </c>
       <c r="E210" s="69" t="inlineStr">
@@ -20595,14 +20645,14 @@
       </c>
       <c r="F210" s="69" t="inlineStr">
         <is>
-          <t>B, tal como propone el addendum. integration_providers es catálogo respaldado por código (un proveedor solo existe si hay adaptador); integration_connections es la configuración viva; integration_assignments es el alcance, con NULL significando "cualquiera" y con vigencia (valid_from/valid_to) igual que la cobertura de facturación. — Un proveedor puede tener varias conexiones (producción, sandbox, por sociedad) y cada conexión puede aplicar a varios ámbitos.</t>
+          <t>B, más un panel de cobertura en verde/rojo y una comprobación programada que avisa antes de que una credencial expirada rompa una operación. — Descubrir que no hay conexión de facturación para Ecuador al pulsar "emitir", con el cliente esperando, es un problema de diseño, no de configuración.</t>
         </is>
       </c>
     </row>
     <row r="211" ht="34.5" customHeight="1" s="36">
       <c r="A211" s="67" t="inlineStr">
         <is>
-          <t>DEC-024</t>
+          <t>DEC-027</t>
         </is>
       </c>
       <c r="B211" s="68" t="inlineStr">
@@ -20613,7 +20663,7 @@
       <c r="C211" s="68" t="n"/>
       <c r="D211" s="69" t="inlineStr">
         <is>
-          <t>Las integraciones son un subsistema propio, no Settings</t>
+          <t>Resolución por especificidad, con empates rechazados al guardar</t>
         </is>
       </c>
       <c r="E211" s="69" t="inlineStr">
@@ -20623,14 +20673,14 @@
       </c>
       <c r="F211" s="69" t="inlineStr">
         <is>
-          <t>B. Un ajuste resuelve un valor; una integración resuelve una conexión viva que tiene estado, ciclo de vida y que falla. Además necesita dos ejes más (purpose, environment). Lo que sí se unifica son los nombres de los niveles, para que nadie confunda "global" con "plataforma". — DEC-018 ya definió una configuración jerárquica. La tentación es meter las integraciones dentro.</t>
+          <t>B, y sobre todo: los empates no se resuelven en ejecución, se prohíben al guardar. Si dos asignaciones activas puntúan igual para la misma combinación, la interfaz rechaza el guardado y explica el conflicto. Así el resolver es siempre determinista y nadie descubre un empate emitiendo una factura. — El addendum propone una escalera de cuatro peldaños. Funciona, pero no contempla el eje de marca ni dice qué hacer ante un empate.</t>
         </is>
       </c>
     </row>
     <row r="212" ht="23.25" customHeight="1" s="36">
       <c r="A212" s="67" t="inlineStr">
         <is>
-          <t>DEC-023</t>
+          <t>DEC-026</t>
         </is>
       </c>
       <c r="B212" s="68" t="inlineStr">
@@ -20641,7 +20691,7 @@
       <c r="C212" s="68" t="n"/>
       <c r="D212" s="69" t="inlineStr">
         <is>
-          <t>Identidad dual en comunicaciones</t>
+          <t>purpose es un enum cerrado en código, no un catálogo editable</t>
         </is>
       </c>
       <c r="E212" s="69" t="inlineStr">
@@ -20651,14 +20701,14 @@
       </c>
       <c r="F212" s="69" t="inlineStr">
         <is>
-          <t>C. El creador y la marca cliente se relacionan con LATAM Social; las facturas, contratos y comunicaciones de cobranza deben identificar a la sociedad que responde legalmente. Implica remitente configurable por entidad para los correos de facturación. — ¿Los correos salen de "LATAM Social" o de "Soluciones Tecnológicas a Medida S.A.C."?</t>
+          <t>B. El código se ramifica por propósito: invoicing implica una interfaz con emit()/getStatus(); email_transactional implica otra distinta. Un propósito creado desde el panel produciría una conexión perfectamente configurada que ningún código sabe ejecutar. Los catálogos editables son para datos de negocio; los propósitos son contratos de código. — El addendum lista los propósitos como si fueran datos administrables.</t>
         </is>
       </c>
     </row>
     <row r="213" ht="45.75" customHeight="1" s="36">
       <c r="A213" s="67" t="inlineStr">
         <is>
-          <t>DEC-022</t>
+          <t>DEC-025</t>
         </is>
       </c>
       <c r="B213" s="68" t="inlineStr">
@@ -20669,7 +20719,7 @@
       <c r="C213" s="68" t="n"/>
       <c r="D213" s="69" t="inlineStr">
         <is>
-          <t>Monedas: no derivar del país de la entidad</t>
+          <t>Proveedor / Conexión / Asignación como tres entidades</t>
         </is>
       </c>
       <c r="E213" s="69" t="inlineStr">
@@ -20679,14 +20729,14 @@
       </c>
       <c r="F213" s="69" t="inlineStr">
         <is>
-          <t>B. Coherente con BR-FIN-004 y BR-FIN-009, que ya exigían no asumir una sola moneda. — §11 del addendum. CTS Perú puede facturar en PEN a un cliente peruano y en USD a uno ecuatoriano.</t>
+          <t>B, tal como propone el addendum. integration_providers es catálogo respaldado por código (un proveedor solo existe si hay adaptador); integration_connections es la configuración viva; integration_assignments es el alcance, con NULL significando "cualquiera" y con vigencia (valid_from/valid_to) igual que la cobertura de facturación. — Un proveedor puede tener varias conexiones (producción, sandbox, por sociedad) y cada conexión puede aplicar a varios ámbitos.</t>
         </is>
       </c>
     </row>
     <row r="214" ht="34.5" customHeight="1" s="36">
       <c r="A214" s="67" t="inlineStr">
         <is>
-          <t>DEC-021</t>
+          <t>DEC-024</t>
         </is>
       </c>
       <c r="B214" s="68" t="inlineStr">
@@ -20697,7 +20747,7 @@
       <c r="C214" s="68" t="n"/>
       <c r="D214" s="69" t="inlineStr">
         <is>
-          <t>Series y numeración correlativa por entidad legal</t>
+          <t>Las integraciones son un subsistema propio, no Settings</t>
         </is>
       </c>
       <c r="E214" s="69" t="inlineStr">
@@ -20707,42 +20757,42 @@
       </c>
       <c r="F214" s="69" t="inlineStr">
         <is>
-          <t>C. A no permite series por entidad y deja huecos ante transacciones revertidas. B bloquea una fila que se lee constantemente. C aísla el punto de contención. — En Perú la numeración por serie debe ser correlativa y sin huecos. Con varias sociedades hay varios contadores independientes, y bajo concurrencia dos facturas simultáneas pueden tomar el mismo número o saltarse uno.</t>
+          <t>B. Un ajuste resuelve un valor; una integración resuelve una conexión viva que tiene estado, ciclo de vida y que falla. Además necesita dos ejes más (purpose, environment). Lo que sí se unifica son los nombres de los niveles, para que nadie confunda "global" con "plataforma". — DEC-018 ya definió una configuración jerárquica. La tentación es meter las integraciones dentro.</t>
         </is>
       </c>
     </row>
     <row r="215" ht="23.25" customHeight="1" s="36">
       <c r="A215" s="67" t="inlineStr">
         <is>
-          <t>DEC-020</t>
+          <t>DEC-023</t>
         </is>
       </c>
       <c r="B215" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C215" s="68" t="n"/>
       <c r="D215" s="69" t="inlineStr">
         <is>
-          <t>Entidad que factura vs. entidad que liquida al creador</t>
+          <t>Identidad dual en comunicaciones</t>
         </is>
       </c>
       <c r="E215" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ DECIDIDA (2026-08-27) por DEC-156: opción C, y sin el «en el MVP». La sociedad de la campaña paga a todos sus creadores, sea cual sea el país de cada uno (BR-LE-009, ahora 🔴). Dónde se comprueba lo </t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F215" s="69" t="inlineStr">
         <is>
-          <t>C. A cierra la puerta; B la deja abierta para que alguien la cruce sin darse cuenta un martes por la tarde y genere una contingencia fiscal. C conserva la flexibilidad del modelo y exige una decisión consciente, respaldada por asesoría fiscal, para habilitarla. — §12 del addendum pide separar ambos conceptos. Pero si divergen, aparece una operación intercompañía entre dos sociedades del grupo, con precios de transferencia, documentación ante la autoridad tributaria, consolidación contable y posible retención en la fuente.</t>
+          <t>C. El creador y la marca cliente se relacionan con LATAM Social; las facturas, contratos y comunicaciones de cobranza deben identificar a la sociedad que responde legalmente. Implica remitente configurable por entidad para los correos de facturación. — ¿Los correos salen de "LATAM Social" o de "Soluciones Tecnológicas a Medida S.A.C."?</t>
         </is>
       </c>
     </row>
     <row r="216" ht="23.25" customHeight="1" s="36">
       <c r="A216" s="67" t="inlineStr">
         <is>
-          <t>DEC-019</t>
+          <t>DEC-022</t>
         </is>
       </c>
       <c r="B216" s="68" t="inlineStr">
@@ -20753,7 +20803,7 @@
       <c r="C216" s="68" t="n"/>
       <c r="D216" s="69" t="inlineStr">
         <is>
-          <t>Entidad legal explícita e inmutable en cada documento</t>
+          <t>Monedas: no derivar del país de la entidad</t>
         </is>
       </c>
       <c r="E216" s="69" t="inlineStr">
@@ -20763,14 +20813,14 @@
       </c>
       <c r="F216" s="69" t="inlineStr">
         <is>
-          <t>C. A es un error silencioso: no da error, no rompe nada, y falsifica retroactivamente todos los documentos históricos. La clave foránea sola tampoco basta: si la sociedad cambia de domicilio, la factura antigua debe seguir mostrando el domicilio antiguo. — §14 del addendum. Si mañana Ecuador pasa a facturarse desde otra sociedad, las facturas de ayer deben seguir diciendo lo que decían ayer.</t>
+          <t>B. Coherente con BR-FIN-004 y BR-FIN-009, que ya exigían no asumir una sola moneda. — §11 del addendum. CTS Perú puede facturar en PEN a un cliente peruano y en USD a uno ecuatoriano.</t>
         </is>
       </c>
     </row>
     <row r="217" ht="45.75" customHeight="1" s="36">
       <c r="A217" s="67" t="inlineStr">
         <is>
-          <t>DEC-018</t>
+          <t>DEC-021</t>
         </is>
       </c>
       <c r="B217" s="68" t="inlineStr">
@@ -20781,7 +20831,7 @@
       <c r="C217" s="68" t="n"/>
       <c r="D217" s="69" t="inlineStr">
         <is>
-          <t>Configuración jerárquica en cascada</t>
+          <t>Series y numeración correlativa por entidad legal</t>
         </is>
       </c>
       <c r="E217" s="69" t="inlineStr">
@@ -20791,42 +20841,42 @@
       </c>
       <c r="F217" s="69" t="inlineStr">
         <is>
-          <t>B, con dos condiciones no negociables: la interfaz debe mostrar siempre de dónde viene el valor efectivo, y los secretos se cifran por entidad y nunca se heredan. — La configuración deja de ser global: hay ajustes de plataforma, de marca, de entidad legal y de (entidad × país).</t>
+          <t>C. A no permite series por entidad y deja huecos ante transacciones revertidas. B bloquea una fila que se lee constantemente. C aísla el punto de contención. — En Perú la numeración por serie debe ser correlativa y sin huecos. Con varias sociedades hay varios contadores independientes, y bajo concurrencia dos facturas simultáneas pueden tomar el mismo número o saltarse uno.</t>
         </is>
       </c>
     </row>
     <row r="218" ht="34.5" customHeight="1" s="36">
       <c r="A218" s="67" t="inlineStr">
         <is>
-          <t>DEC-017</t>
+          <t>DEC-020</t>
         </is>
       </c>
       <c r="B218" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C218" s="68" t="n"/>
       <c r="D218" s="69" t="inlineStr">
         <is>
-          <t>Cobertura de facturación como relación N:M con vigencia</t>
+          <t>Entidad que factura vs. entidad que liquida al creador</t>
         </is>
       </c>
       <c r="E218" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t xml:space="preserve">✅ DECIDIDA (2026-08-27) por DEC-156: opción C, y sin el «en el MVP». La sociedad de la campaña paga a todos sus creadores, sea cual sea el país de cada uno (BR-LE-009, ahora 🔴). Dónde se comprueba lo </t>
         </is>
       </c>
       <c r="F218" s="69" t="inlineStr">
         <is>
-          <t>C. A es directamente incorrecta. B pierde la información de *cuándo* dejó de aplicar una cobertura, y eso hace imposible auditar por qué una factura de 2027 salió de una sociedad y una de 2029 de otra. La vigencia es lo que permite la evolución del §15 del addendum sin destruir historia. — Una sociedad puede facturar clientes de varios países, y un país puede ser atendido por más de una sociedad.</t>
+          <t>C. A cierra la puerta; B la deja abierta para que alguien la cruce sin darse cuenta un martes por la tarde y genere una contingencia fiscal. C conserva la flexibilidad del modelo y exige una decisión consciente, respaldada por asesoría fiscal, para habilitarla. — §12 del addendum pide separar ambos conceptos. Pero si divergen, aparece una operación intercompañía entre dos sociedades del grupo, con precios de transferencia, documentación ante la autoridad tributaria, consolidación contable y posible retención en la fuente.</t>
         </is>
       </c>
     </row>
     <row r="219" ht="23.25" customHeight="1" s="36">
       <c r="A219" s="67" t="inlineStr">
         <is>
-          <t>DEC-016</t>
+          <t>DEC-019</t>
         </is>
       </c>
       <c r="B219" s="68" t="inlineStr">
@@ -20837,7 +20887,7 @@
       <c r="C219" s="68" t="n"/>
       <c r="D219" s="69" t="inlineStr">
         <is>
-          <t>Desambiguación de los conceptos organizacionales</t>
+          <t>Entidad legal explícita e inmutable en cada documento</t>
         </is>
       </c>
       <c r="E219" s="69" t="inlineStr">
@@ -20847,14 +20897,14 @@
       </c>
       <c r="F219" s="69" t="inlineStr">
         <is>
-          <t>B. A garantiza que en seis meses nadie sepa si brand_id apunta a LATAM Social o a Shampoo ABC. Es la fuente número uno de errores de datos en sistemas multi-entidad. — El addendum introduce "marca de plataforma" (LATAM Social) y "entidad legal" (la sociedad). El modelo anterior ya usaba Brand para la marca del cliente. Cuatro conceptos organizacionales con nombres que se pisan.</t>
+          <t>C. A es un error silencioso: no da error, no rompe nada, y falsifica retroactivamente todos los documentos históricos. La clave foránea sola tampoco basta: si la sociedad cambia de domicilio, la factura antigua debe seguir mostrando el domicilio antiguo. — §14 del addendum. Si mañana Ecuador pasa a facturarse desde otra sociedad, las facturas de ayer deben seguir diciendo lo que decían ayer.</t>
         </is>
       </c>
     </row>
     <row r="220" ht="23.25" customHeight="1" s="36">
       <c r="A220" s="67" t="inlineStr">
         <is>
-          <t>DEC-015</t>
+          <t>DEC-018</t>
         </is>
       </c>
       <c r="B220" s="68" t="inlineStr">
@@ -20865,24 +20915,24 @@
       <c r="C220" s="68" t="n"/>
       <c r="D220" s="69" t="inlineStr">
         <is>
-          <t>Retención y minimización de datos personales</t>
+          <t>Configuración jerárquica en cascada</t>
         </is>
       </c>
       <c r="E220" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA — requiere validación legal</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F220" s="69" t="inlineStr">
         <is>
-          <t>B. Además: la dirección de envío se purga N meses después de la campaña; las copias de documentos de identidad, si se recogen, se cifran y tienen la retención más corta legalmente posible. Menos datos = menos riesgo. — Se recopilan documento de identidad, fecha de nacimiento, dirección, datos bancarios y dirección de envío de cientos de personas.</t>
+          <t>B, con dos condiciones no negociables: la interfaz debe mostrar siempre de dónde viene el valor efectivo, y los secretos se cifran por entidad y nunca se heredan. — La configuración deja de ser global: hay ajustes de plataforma, de marca, de entidad legal y de (entidad × país).</t>
         </is>
       </c>
     </row>
     <row r="221" ht="45.75" customHeight="1" s="36">
       <c r="A221" s="67" t="inlineStr">
         <is>
-          <t>DEC-014</t>
+          <t>DEC-017</t>
         </is>
       </c>
       <c r="B221" s="68" t="inlineStr">
@@ -20893,7 +20943,7 @@
       <c r="C221" s="68" t="n"/>
       <c r="D221" s="69" t="inlineStr">
         <is>
-          <t>Modelo de derechos de uso del contenido</t>
+          <t>Cobertura de facturación como relación N:M con vigencia</t>
         </is>
       </c>
       <c r="E221" s="69" t="inlineStr">
@@ -20903,14 +20953,14 @@
       </c>
       <c r="F221" s="69" t="inlineStr">
         <is>
-          <t>B. Además, alertas de vencimiento: usar contenido después de que expiró la licencia es una infracción con consecuencias legales para el cliente y reputacionales para el operador. — Lo que la marca realmente compra es una licencia. Modelarlo como un booleano "cede derechos: sí/no" es insuficiente y genera disputas.</t>
+          <t>C. A es directamente incorrecta. B pierde la información de *cuándo* dejó de aplicar una cobertura, y eso hace imposible auditar por qué una factura de 2027 salió de una sociedad y una de 2029 de otra. La vigencia es lo que permite la evolución del §15 del addendum sin destruir historia. — Una sociedad puede facturar clientes de varios países, y un país puede ser atendido por más de una sociedad.</t>
         </is>
       </c>
     </row>
     <row r="222" ht="34.5" customHeight="1" s="36">
       <c r="A222" s="67" t="inlineStr">
         <is>
-          <t>DEC-013</t>
+          <t>DEC-016</t>
         </is>
       </c>
       <c r="B222" s="68" t="inlineStr">
@@ -20921,7 +20971,7 @@
       <c r="C222" s="68" t="n"/>
       <c r="D222" s="69" t="inlineStr">
         <is>
-          <t>Alcance del portal de la marca en el MVP</t>
+          <t>Desambiguación de los conceptos organizacionales</t>
         </is>
       </c>
       <c r="E222" s="69" t="inlineStr">
@@ -20931,14 +20981,14 @@
       </c>
       <c r="F222" s="69" t="inlineStr">
         <is>
-          <t>B. Entrega el 90% del valor percibido con el 15% del esfuerzo, y es el camino natural hacia A en F13. Requiere cuidado en seguridad: enlaces de un solo destinatario, con expiración, revocables y auditados. — Con 3 marcas, construir un portal con cuentas, roles, facturación y documentos es esfuerzo desproporcionado.</t>
+          <t>B. A garantiza que en seis meses nadie sepa si brand_id apunta a LATAM Social o a Shampoo ABC. Es la fuente número uno de errores de datos en sistemas multi-entidad. — El addendum introduce "marca de plataforma" (LATAM Social) y "entidad legal" (la sociedad). El modelo anterior ya usaba Brand para la marca del cliente. Cuatro conceptos organizacionales con nombres que se pisan.</t>
         </is>
       </c>
     </row>
     <row r="223" ht="23.85" customHeight="1" s="36">
       <c r="A223" s="67" t="inlineStr">
         <is>
-          <t>DEC-012</t>
+          <t>DEC-015</t>
         </is>
       </c>
       <c r="B223" s="68" t="inlineStr">
@@ -20949,24 +20999,24 @@
       <c r="C223" s="68" t="n"/>
       <c r="D223" s="69" t="inlineStr">
         <is>
-          <t>Longitud del formulario de lead B2B</t>
+          <t>Retención y minimización de datos personales</t>
         </is>
       </c>
       <c r="E223" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>PROPUESTA — requiere validación legal</t>
         </is>
       </c>
       <c r="F223" s="69" t="inlineStr">
         <is>
-          <t>B: empresa, nombre, email corporativo, teléfono/WhatsApp, país, objetivo, mensaje. El resto (presupuesto, cantidad de creadores, países objetivo, industria) se captura en la conversación comercial y se guarda en el CRM. UTM, landing y origen se capturan ocultos, siempre. — La spec lista 16 campos. Cada campo adicional reduce la conversión.</t>
+          <t>B. Además: la dirección de envío se purga N meses después de la campaña; las copias de documentos de identidad, si se recogen, se cifran y tienen la retención más corta legalmente posible. Menos datos = menos riesgo. — Se recopilan documento de identidad, fecha de nacimiento, dirección, datos bancarios y dirección de envío de cientos de personas.</t>
         </is>
       </c>
     </row>
     <row r="224" ht="46.25" customHeight="1" s="36">
       <c r="A224" s="67" t="inlineStr">
         <is>
-          <t>DEC-011</t>
+          <t>DEC-014</t>
         </is>
       </c>
       <c r="B224" s="68" t="inlineStr">
@@ -20977,7 +21027,7 @@
       <c r="C224" s="68" t="n"/>
       <c r="D224" s="69" t="inlineStr">
         <is>
-          <t>¿La plataforma publica en las redes del creador?</t>
+          <t>Modelo de derechos de uso del contenido</t>
         </is>
       </c>
       <c r="E224" s="69" t="inlineStr">
@@ -20987,14 +21037,14 @@
       </c>
       <c r="F224" s="69" t="inlineStr">
         <is>
-          <t>B. A añade riesgo de cuenta, complejidad enorme y las APIs cambian sin aviso. La verificación posterior aporta casi todo el valor con una fracción del costo. — Publicar automáticamente requiere permisos amplios, es frágil y las plataformas lo restringen.</t>
+          <t>B. Además, alertas de vencimiento: usar contenido después de que expiró la licencia es una infracción con consecuencias legales para el cliente y reputacionales para el operador. — Lo que la marca realmente compra es una licencia. Modelarlo como un booleano "cede derechos: sí/no" es insuficiente y genera disputas.</t>
         </is>
       </c>
     </row>
     <row r="225" ht="35.05" customHeight="1" s="36">
       <c r="A225" s="67" t="inlineStr">
         <is>
-          <t>DEC-010</t>
+          <t>DEC-013</t>
         </is>
       </c>
       <c r="B225" s="68" t="inlineStr">
@@ -21005,7 +21055,7 @@
       <c r="C225" s="68" t="n"/>
       <c r="D225" s="69" t="inlineStr">
         <is>
-          <t>Estado de campaña vs. estado de participación</t>
+          <t>Alcance del portal de la marca en el MVP</t>
         </is>
       </c>
       <c r="E225" s="69" t="inlineStr">
@@ -21015,14 +21065,14 @@
       </c>
       <c r="F225" s="69" t="inlineStr">
         <is>
-          <t>B, obligatoriamente. A es el error de diseño más frecuente y más caro en plataformas de este tipo: obliga a hacks inmediatos y hace imposible el reporte de avance. — Una campaña live puede tener creadores aún en revisión.</t>
+          <t>B. Entrega el 90% del valor percibido con el 15% del esfuerzo, y es el camino natural hacia A en F13. Requiere cuidado en seguridad: enlaces de un solo destinatario, con expiración, revocables y auditados. — Con 3 marcas, construir un portal con cuentas, roles, facturación y documentos es esfuerzo desproporcionado.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67" t="inlineStr">
         <is>
-          <t>DEC-009</t>
+          <t>DEC-012</t>
         </is>
       </c>
       <c r="B226" s="68" t="inlineStr">
@@ -21033,7 +21083,7 @@
       <c r="C226" s="68" t="n"/>
       <c r="D226" s="69" t="inlineStr">
         <is>
-          <t>Origen de los datos de audiencia</t>
+          <t>Longitud del formulario de lead B2B</t>
         </is>
       </c>
       <c r="E226" s="69" t="inlineStr">
@@ -21043,14 +21093,14 @@
       </c>
       <c r="F226" s="69" t="inlineStr">
         <is>
-          <t>A en el MVP (manual + evidencia + chequeos de coherencia), B en F12–F14, C evaluado por costo cuando el volumen lo justifique: comprar datos verificados suele ser más barato que construir y mantener integraciones con 6 plataformas. — Los datos autodeclarados son el principal vector de fraude. Las APIs oficiales exigen que el creador conecte su cuenta (Instagram/Facebook requieren cuenta Business/Creator y autorización explícita; TikTok y YouTube tienen sus propios programas).</t>
+          <t>B: empresa, nombre, email corporativo, teléfono/WhatsApp, país, objetivo, mensaje. El resto (presupuesto, cantidad de creadores, países objetivo, industria) se captura en la conversación comercial y se guarda en el CRM. UTM, landing y origen se capturan ocultos, siempre. — La spec lista 16 campos. Cada campo adicional reduce la conversión.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67" t="inlineStr">
         <is>
-          <t>DEC-008</t>
+          <t>DEC-011</t>
         </is>
       </c>
       <c r="B227" s="68" t="inlineStr">
@@ -21061,7 +21111,7 @@
       <c r="C227" s="68" t="n"/>
       <c r="D227" s="69" t="inlineStr">
         <is>
-          <t>Almacenamiento de archivos</t>
+          <t>¿La plataforma publica en las redes del creador?</t>
         </is>
       </c>
       <c r="E227" s="69" t="inlineStr">
@@ -21071,14 +21121,14 @@
       </c>
       <c r="F227" s="69" t="inlineStr">
         <is>
-          <t>B, sin excepción. A rompe el despliegue en más de un servidor, complica los backups, no escala y migrar después implica reescribir rutas de miles de archivos. Cloudflare R2 o Backblaze B2 tienen costo de egreso muy bajo, relevante porque los clientes descargarán contenido. — Campañas UGC generan video pesado (0,5–3 GB por campaña).</t>
+          <t>B. A añade riesgo de cuenta, complejidad enorme y las APIs cambian sin aviso. La verificación posterior aporta casi todo el valor con una fracción del costo. — Publicar automáticamente requiere permisos amplios, es frágil y las plataformas lo restringen.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67" t="inlineStr">
         <is>
-          <t>DEC-007</t>
+          <t>DEC-010</t>
         </is>
       </c>
       <c r="B228" s="68" t="inlineStr">
@@ -21089,7 +21139,7 @@
       <c r="C228" s="68" t="n"/>
       <c r="D228" s="69" t="inlineStr">
         <is>
-          <t>Pasarela de pago (Culqi) en el MVP</t>
+          <t>Estado de campaña vs. estado de participación</t>
         </is>
       </c>
       <c r="E228" s="69" t="inlineStr">
@@ -21099,14 +21149,14 @@
       </c>
       <c r="F228" s="69" t="inlineStr">
         <is>
-          <t>B. Se construye la abstracción (PaymentGatewayInterface) pero no la integración. Si aparece un segmento de ticket bajo (p. ej. paquetes autoservicio para pymes), se activa. — La spec pide integrar Culqi. Pero en B2B LATAM, campañas de miles de soles se pagan por transferencia contra factura, no con tarjeta. Una campaña de S/ 30.000 no se cobra con tarjeta (comisión ~3,5% = S/ 1.050 regalados).</t>
+          <t>B, obligatoriamente. A es el error de diseño más frecuente y más caro en plataformas de este tipo: obliga a hacks inmediatos y hace imposible el reporte de avance. — Una campaña live puede tener creadores aún en revisión.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67" t="inlineStr">
         <is>
-          <t>DEC-006</t>
+          <t>DEC-009</t>
         </is>
       </c>
       <c r="B229" s="68" t="inlineStr">
@@ -21117,7 +21167,7 @@
       <c r="C229" s="68" t="n"/>
       <c r="D229" s="69" t="inlineStr">
         <is>
-          <t>Separación Aplicación vs. Creador</t>
+          <t>Origen de los datos de audiencia</t>
         </is>
       </c>
       <c r="E229" s="69" t="inlineStr">
@@ -21127,42 +21177,42 @@
       </c>
       <c r="F229" s="69" t="inlineStr">
         <is>
-          <t>B. Permite reaplicaciones, conserva el histórico de rechazos y evita que un rechazo contamine la entidad permanente. — La spec mezcla el ciclo de vida de la solicitud con el del creador.</t>
+          <t>A en el MVP (manual + evidencia + chequeos de coherencia), B en F12–F14, C evaluado por costo cuando el volumen lo justifique: comprar datos verificados suele ser más barato que construir y mantener integraciones con 6 plataformas. — Los datos autodeclarados son el principal vector de fraude. Las APIs oficiales exigen que el creador conecte su cuenta (Instagram/Facebook requieren cuenta Business/Creator y autorización explícita; TikTok y YouTube tienen sus propios programas).</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67" t="inlineStr">
         <is>
-          <t>DEC-005</t>
+          <t>DEC-008</t>
         </is>
       </c>
       <c r="B230" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C230" s="68" t="n"/>
       <c r="D230" s="69" t="inlineStr">
         <is>
-          <t>Régimen legal y tributario del pago al creador ✅ RESUELTA (parcial)</t>
+          <t>Almacenamiento de archivos</t>
         </is>
       </c>
       <c r="E230" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA para creadores peruanos · 🔴 Q-33 abierta para extranjeros (bloquea F9 solo en ese caso)</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F230" s="69" t="inlineStr">
         <is>
-          <t>C, con la vía simplificada definida por un contador. Y en cualquier caso: el sistema debe modelar tax_regime por creador y por país, con requisitos documentales configurables por régimen, y bloquear el pago si falta el documento requerido. — En Perú, pagar a una persona natural por un servicio exige normalmente comprobante (recibo por honorarios electrónico) y puede implicar retención de renta de 4.ª categoría, con umbrales y suspensión de retención. Muchos micro-creadores no tienen RUC ni emiten comprobantes. Sin resolver esto, no se puede pagar legalmente a escala.</t>
+          <t>B, sin excepción. A rompe el despliegue en más de un servidor, complica los backups, no escala y migrar después implica reescribir rutas de miles de archivos. Cloudflare R2 o Backblaze B2 tienen costo de egreso muy bajo, relevante porque los clientes descargarán contenido. — Campañas UGC generan video pesado (0,5–3 GB por campaña).</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67" t="inlineStr">
         <is>
-          <t>DEC-004</t>
+          <t>DEC-007</t>
         </is>
       </c>
       <c r="B231" s="68" t="inlineStr">
@@ -21173,24 +21223,24 @@
       <c r="C231" s="68" t="n"/>
       <c r="D231" s="69" t="inlineStr">
         <is>
-          <t>Modelo económico: principal vs. comisión</t>
+          <t>Pasarela de pago (Culqi) en el MVP</t>
         </is>
       </c>
       <c r="E231" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA — confirmar con el contador</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F231" s="69" t="inlineStr">
         <is>
-          <t>A, coherente con §53 de la especificación (Revenue − Creator Cost = Margen). Determina el modelo fiscal, contable y financiero completo. — ¿El operador vende la campaña y compra el contenido (reventa), o cobra una comisión sobre una transacción entre marca y creador?</t>
+          <t>B. Se construye la abstracción (PaymentGatewayInterface) pero no la integración. Si aparece un segmento de ticket bajo (p. ej. paquetes autoservicio para pymes), se activa. — La spec pide integrar Culqi. Pero en B2B LATAM, campañas de miles de soles se pagan por transferencia contra factura, no con tarjeta. Una campaña de S/ 30.000 no se cobra con tarjeta (comisión ~3,5% = S/ 1.050 regalados).</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67" t="inlineStr">
         <is>
-          <t>DEC-003</t>
+          <t>DEC-006</t>
         </is>
       </c>
       <c r="B232" s="68" t="inlineStr">
@@ -21201,7 +21251,7 @@
       <c r="C232" s="68" t="n"/>
       <c r="D232" s="69" t="inlineStr">
         <is>
-          <t>Estrategia de frontend</t>
+          <t>Separación Aplicación vs. Creador</t>
         </is>
       </c>
       <c r="E232" s="69" t="inlineStr">
@@ -21211,14 +21261,14 @@
       </c>
       <c r="F232" s="69" t="inlineStr">
         <is>
-          <t>A. B duplica el trabajo y, sobre todo, duplica la autorización —el punto donde este sistema más se puede romper—. El portal del creador se entrega como PWA instalable con A. — Cuatro portales con necesidades distintas. Equipo pequeño.</t>
+          <t>B. Permite reaplicaciones, conserva el histórico de rechazos y evita que un rechazo contamine la entidad permanente. — La spec mezcla el ciclo de vida de la solicitud con el del creador.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67" t="inlineStr">
         <is>
-          <t>DEC-002</t>
+          <t>DEC-005</t>
         </is>
       </c>
       <c r="B233" s="68" t="inlineStr">
@@ -21229,71 +21279,155 @@
       <c r="C233" s="68" t="n"/>
       <c r="D233" s="69" t="inlineStr">
         <is>
-          <t>Multitenancy ✅ RESUELTA</t>
+          <t>Régimen legal y tributario del pago al creador ✅ RESUELTA (parcial)</t>
         </is>
       </c>
       <c r="E233" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA (decisión del negocio, 2026-08-21)</t>
+          <t>✅ APROBADA para creadores peruanos · 🔴 Q-33 abierta para extranjeros (bloquea F9 solo en ese caso)</t>
         </is>
       </c>
       <c r="F233" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hoy hay un solo operador. La spec contempla agencias y white-label a futuro (§78).</t>
+          <t>C, con la vía simplificada definida por un contador. Y en cualquier caso: el sistema debe modelar tax_regime por creador y por país, con requisitos documentales configurables por régimen, y bloquear el pago si falta el documento requerido. — En Perú, pagar a una persona natural por un servicio exige normalmente comprobante (recibo por honorarios electrónico) y puede implicar retención de renta de 4.ª categoría, con umbrales y suspensión de retención. Muchos micro-creadores no tienen RUC ni emiten comprobantes. Sin resolver esto, no se puede pagar legalmente a escala.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67" t="inlineStr">
         <is>
-          <t>DEC-001</t>
+          <t>DEC-004</t>
         </is>
       </c>
       <c r="B234" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C234" s="68" t="n"/>
       <c r="D234" s="69" t="inlineStr">
         <is>
-          <t>Framework PHP</t>
+          <t>Modelo económico: principal vs. comisión</t>
         </is>
       </c>
       <c r="E234" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA (2026-08-22). Proyecto creado: ver tools/bootstrap-laravel.ps1 y CONTRIBUTING.md</t>
+          <t>PROPUESTA — confirmar con el contador</t>
         </is>
       </c>
       <c r="F234" s="69" t="inlineStr">
         <is>
-          <t>A — Laravel 12. C queda descartada: construir a mano autenticación, colas, migraciones y abstracción de storage añadiría 3–5 meses de trabajo indiferenciado y una superficie de seguridad propia que nadie audita. B es defendible si el equipo ya domina Symfony. — La spec exige PHP 8.3 y "MVC o equivalente bien estructurado", y a la vez pide migraciones, seeders, colas, scheduler, cache, logs, SMTP, webhooks, RBAC, i18n y tests. Todo eso ya existe, probado en producción, en los frameworks maduros.</t>
+          <t>A, coherente con §53 de la especificación (Revenue − Creator Cost = Margen). Determina el modelo fiscal, contable y financiero completo. — ¿El operador vende la campaña y compra el contenido (reventa), o cobra una comisión sobre una transacción entre marca y creador?</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67" t="inlineStr">
         <is>
-          <t>DEC-000</t>
+          <t>DEC-003</t>
         </is>
       </c>
       <c r="B235" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C235" s="68" t="n"/>
       <c r="D235" s="69" t="inlineStr">
         <is>
+          <t>Estrategia de frontend</t>
+        </is>
+      </c>
+      <c r="E235" s="69" t="inlineStr">
+        <is>
+          <t>PROPUESTA</t>
+        </is>
+      </c>
+      <c r="F235" s="69" t="inlineStr">
+        <is>
+          <t>A. B duplica el trabajo y, sobre todo, duplica la autorización —el punto donde este sistema más se puede romper—. El portal del creador se entrega como PWA instalable con A. — Cuatro portales con necesidades distintas. Equipo pequeño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="67" t="inlineStr">
+        <is>
+          <t>DEC-002</t>
+        </is>
+      </c>
+      <c r="B236" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C236" s="68" t="n"/>
+      <c r="D236" s="69" t="inlineStr">
+        <is>
+          <t>Multitenancy ✅ RESUELTA</t>
+        </is>
+      </c>
+      <c r="E236" s="69" t="inlineStr">
+        <is>
+          <t>✅ APROBADA (decisión del negocio, 2026-08-21)</t>
+        </is>
+      </c>
+      <c r="F236" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — Hoy hay un solo operador. La spec contempla agencias y white-label a futuro (§78).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="67" t="inlineStr">
+        <is>
+          <t>DEC-001</t>
+        </is>
+      </c>
+      <c r="B237" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C237" s="68" t="n"/>
+      <c r="D237" s="69" t="inlineStr">
+        <is>
+          <t>Framework PHP</t>
+        </is>
+      </c>
+      <c r="E237" s="69" t="inlineStr">
+        <is>
+          <t>✅ APROBADA (2026-08-22). Proyecto creado: ver tools/bootstrap-laravel.ps1 y CONTRIBUTING.md</t>
+        </is>
+      </c>
+      <c r="F237" s="69" t="inlineStr">
+        <is>
+          <t>A — Laravel 12. C queda descartada: construir a mano autenticación, colas, migraciones y abstracción de storage añadiría 3–5 meses de trabajo indiferenciado y una superficie de seguridad propia que nadie audita. B es defendible si el equipo ya domina Symfony. — La spec exige PHP 8.3 y "MVC o equivalente bien estructurado", y a la vez pide migraciones, seeders, colas, scheduler, cache, logs, SMTP, webhooks, RBAC, i18n y tests. Todo eso ya existe, probado en producción, en los frameworks maduros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="67" t="inlineStr">
+        <is>
+          <t>DEC-000</t>
+        </is>
+      </c>
+      <c r="B238" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C238" s="68" t="n"/>
+      <c r="D238" s="69" t="inlineStr">
+        <is>
           <t>Nombre del producto y dominio ✅ RESUELTA</t>
         </is>
       </c>
-      <c r="E235" s="69" t="inlineStr">
+      <c r="E238" s="69" t="inlineStr">
         <is>
           <t>✅ APROBADA (addendum 2026-08-21)</t>
         </is>
       </c>
-      <c r="F235" s="69" t="inlineStr">
+      <c r="F238" s="69" t="inlineStr">
         <is>
           <t>El addendum del 2026-08-21 lo define: la marca de plataforma es LATAM Social. El identificador técnico del proyecto pasa a latam-social. El nombre de trabajo provisional "CTS Creators" queda descartado. — El repositorio se llama ManageCampaingInfluencer (con error ortográfico). El nombre afecta marca, dominio, correos y branding.</t>
         </is>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -2241,7 +2241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J178"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="35" min="1" max="1"/>
@@ -10556,9 +10556,59 @@
         <f>IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G178,Config!$A$3:$A$8,0)),0)</f>
         <v/>
       </c>
-      <c r="J178" t="inlineStr">
+      <c r="J178" s="35" t="inlineStr">
         <is>
           <t>2026-08-31. FUERA DEL ALCANCE ORIGINAL, reportado al revisar el sitio. Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario sin saber donde estaba. Menu en tres grupos y una sola puerta (DEC-233); la portada por bloques con orden fijo (DEC-234); los catalogos pasan a ser un area con portada y aviso (DEC-235). Miga de pan en cada pantalla. Sin migracion y sin mover ninguna ruta. 984 pruebas. docs/fase-9/9.20-CADA-COSA-EN-SU-SITIO.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="57" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B179" s="35" t="inlineStr">
+        <is>
+          <t>Ola 2 - Escalar comercialmente</t>
+        </is>
+      </c>
+      <c r="C179" s="35" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="D179" s="35" t="inlineStr">
+        <is>
+          <t>Finanzas y facturacion</t>
+        </is>
+      </c>
+      <c r="E179" s="35" t="inlineStr">
+        <is>
+          <t>9.21a</t>
+        </is>
+      </c>
+      <c r="F179" s="35" t="inlineStr">
+        <is>
+          <t>La trastienda se muda a /backoffice para dejar libre la calle</t>
+        </is>
+      </c>
+      <c r="G179" s="35" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="H179" s="35">
+        <f>IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G179,Config!$A$3:$A$8,0)),0)</f>
+        <v/>
+      </c>
+      <c r="I179" s="35">
+        <f>IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G179,Config!$A$3:$A$8,0)),0)</f>
+        <v/>
+      </c>
+      <c r="J179" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-31. FUERA DEL ALCANCE ORIGINAL. Lo vio el negocio antes de escribir una linea de la landing: /creadores era la lista del admin y tiene que ser la puerta publica de los creadores. 149 rutas se mudan con UNA linea --docs/08 prohibe URLs a mano en las vistas, y esa regla es lo que lo hace gratis (DEC-236)--; 21 se quedan fuera con su motivo, incluidas /contrasena/nueva y /marca/logo, que comparten primer segmento con algo que si se movio (DEC-237). Una prueba recorre todas las rutas con nombre. Las 390 URLs a mano de las pruebas quedan como T-78. 984 pruebas. docs/fase-9/9.21a-LA-TRASTIENDA-SE-MUDA.md</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="35" min="1" max="1"/>
@@ -12936,6 +12986,43 @@
       <c r="G71" s="69" t="inlineStr">
         <is>
           <t>Reportada desde la instalacion: db:seed se paro con un 45000 porque updateOrInsert movia el valid_from de la fila ABIERTA de fx_official_sources encima de un periodo cerrado a mano (T-73 desde el otro lado). Lo que el error tapaba era peor: el sembrador murio en la linea 71 de 700, asi que los proveedores de 9.17d y los tipos de comprobante de 9.12 no llegaron a entrar. Y de fondo: cada db:seed --lo que el runbook manda tras cada migracion-- devolvia a fabrica el nombre, lema, colores y tipografia de la marca y la direccion de la sociedad, REGENERABA sus uuid y reactivaba fuentes y proveedores apagados a proposito. Regla nueva: lo que una persona puede cambiar se siembra si falta y no se toca si esta (sembrarSiFalta); donde hay vigencia, el periodo empieza el dia siguiente al ultimo cierre. 5 pruebas verificadas en rojo sin el arreglo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="67" t="inlineStr">
+        <is>
+          <t>T-78</t>
+        </is>
+      </c>
+      <c r="B72" s="68" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="C72" s="68" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D72" s="69" t="inlineStr">
+        <is>
+          <t>Convertir a route() las 390 direcciones escritas a mano en las pruebas.</t>
+        </is>
+      </c>
+      <c r="E72" s="69" t="inlineStr">
+        <is>
+          <t>Al tocar cada archivo</t>
+        </is>
+      </c>
+      <c r="F72" s="69" t="inlineStr">
+        <is>
+          <t>Equipo de desarrollo</t>
+        </is>
+      </c>
+      <c r="G72" s="69" t="inlineStr">
+        <is>
+          <t>La mudanza a /backoffice fue gratis en la aplicacion --ni una URL a mano-- y costo 390 sustituciones en tests/, porque una prueba que escribe /clientes FIJA la URL. Se corrigieron con un guion que sale de la lista real de rutas movidas, y la primera pasada dejo dos fuera (/bitacora?tipo=..., con cadena de consulta) que cazo la suite. Mientras sigan siendo cadenas, la proxima mudanza costara lo mismo.</t>
         </is>
       </c>
     </row>
@@ -14971,7 +15058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F238"/>
+  <dimension ref="A1:F240"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="35" min="1" max="1"/>
@@ -15024,7 +15111,7 @@
     <row r="3" ht="79.5" customHeight="1" s="36">
       <c r="A3" s="67" t="inlineStr">
         <is>
-          <t>DEC-233</t>
+          <t>DEC-236</t>
         </is>
       </c>
       <c r="B3" s="68" t="inlineStr">
@@ -15035,24 +15122,24 @@
       <c r="C3" s="68" t="n"/>
       <c r="D3" s="69" t="inlineStr">
         <is>
-          <t>La configuracion tiene UNA sola puerta, y el menu lateral solo lleva trabajo</t>
+          <t>Todo lo que exige sesion vive bajo /backoffice</t>
         </is>
       </c>
       <c r="E3" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21a</t>
         </is>
       </c>
       <c r="F3" s="69" t="inlineStr">
         <is>
-          <t>Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario en una pantalla que se veia igual que Campanas y con el menu marcando otra entrada. El menu queda en tres grupos --Operacion, Finanzas, Registros-- mas Ajustes: Configuracion, y un grupo del que no se puede ver nada desaparece entero.</t>
+          <t>Lo vio el negocio antes de escribir una linea de la landing: /creadores tiene que ser la puerta PUBLICA de los creadores, y descubrirlo despues de publicar habria roto enlaces ya compartidos. Dentro entra todo lo que pide sesion sea de quien sea; lo que cada uno ve lo siguen decidiendo sus permisos. Costo una linea porque docs/08 prohibe escribir URLs a mano en las vistas: comprobado, cero resultados en app/, resources/ y config/.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="57" customHeight="1" s="36">
       <c r="A4" s="67" t="inlineStr">
         <is>
-          <t>DEC-234</t>
+          <t>DEC-237</t>
         </is>
       </c>
       <c r="B4" s="68" t="inlineStr">
@@ -15063,24 +15150,24 @@
       <c r="C4" s="68" t="n"/>
       <c r="D4" s="69" t="inlineStr">
         <is>
-          <t>El orden de los grupos es una decision y vive en el registro, no en la plantilla</t>
+          <t>Veintiuna rutas se quedan fuera, y cada una con su motivo escrito</t>
         </is>
       </c>
       <c r="E4" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21a</t>
         </is>
       </c>
       <c r="F4" s="69" t="inlineStr">
         <is>
-          <t>revision() ordena por URGENCIA, que es lo correcto para una lista de avisos y lo peor para una navegacion: «Fiscal y facturacion» saldria arriba o abajo segun que falte hoy, y un sitio que cambia de forma segun el dia no se aprende. Por lo mismo, que rutas son configuracion sale de Preparacion::rutas() y no de la plantilla.</t>
+          <t>El acceso y la recuperacion son la puerta; la invitacion y la aprobacion llegan por enlace con token a alguien que no tiene cuenta; el logotipo y el favicon los pinta la pantalla de acceso. Dos comparten primer segmento con algo que si se mudo: /contrasena frente a /contrasena/nueva, y /marca frente a /marca/logo. La lista vive en una prueba que recorre todas las rutas con nombre.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="79.5" customHeight="1" s="36">
       <c r="A5" s="67" t="inlineStr">
         <is>
-          <t>DEC-235</t>
+          <t>DEC-233</t>
         </is>
       </c>
       <c r="B5" s="68" t="inlineStr">
@@ -15091,7 +15178,7 @@
       <c r="C5" s="68" t="n"/>
       <c r="D5" s="69" t="inlineStr">
         <is>
-          <t>Los catalogos son configuracion, con portada propia</t>
+          <t>La configuracion tiene UNA sola puerta, y el menu lateral solo lleva trabajo</t>
         </is>
       </c>
       <c r="E5" s="69" t="inlineStr">
@@ -15101,14 +15188,14 @@
       </c>
       <c r="F5" s="69" t="inlineStr">
         <is>
-          <t>Los seis colgaban del menu bajo un titulo que no era un sitio: era una etiqueta. Ahora son un area con portada --cuantas filas y cuantas activas-- y su aviso: una lista sin ninguna fila activa sale en rojo, porque un catalogo vacio no da error, deja un desplegable vacio. La pantalla de cada catalogo no se mueve.</t>
+          <t>Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario en una pantalla que se veia igual que Campanas y con el menu marcando otra entrada. El menu queda en tres grupos --Operacion, Finanzas, Registros-- mas Ajustes: Configuracion, y un grupo del que no se puede ver nada desaparece entero.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34.5" customHeight="1" s="36">
       <c r="A6" s="67" t="inlineStr">
         <is>
-          <t>DEC-228</t>
+          <t>DEC-234</t>
         </is>
       </c>
       <c r="B6" s="68" t="inlineStr">
@@ -15119,24 +15206,24 @@
       <c r="C6" s="68" t="n"/>
       <c r="D6" s="69" t="inlineStr">
         <is>
-          <t>Los tipos de comprobante son un catalogo por pais, no un enum en el codigo</t>
+          <t>El orden de los grupos es una decision y vive en el registro, no en la plantilla</t>
         </is>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F6" s="69" t="inlineStr">
         <is>
-          <t>ck_ds_type decia IN ('invoice','boleta','credit_note','debit_note','other') desde la Fase 2: la boleta es peruana, el CFDI mexicano no estaba y anadir uno exigia desplegar. Cada tipo declara su codigo oficial de SUNAT, la forma de su serie, como se le pide a una persona y cuantos digitos tiene el correlativo. No contradice a DEC-026: el codigo SE RAMIFICA por proposito de integracion, mientras que el tipo de comprobante NO se ramifica, VIAJA al emisor electronico.</t>
+          <t>revision() ordena por URGENCIA, que es lo correcto para una lista de avisos y lo peor para una navegacion: «Fiscal y facturacion» saldria arriba o abajo segun que falte hoy, y un sitio que cambia de forma segun el dia no se aprende. Por lo mismo, que rutas son configuracion sale de Preparacion::rutas() y no de la plantilla.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="36">
       <c r="A7" s="67" t="inlineStr">
         <is>
-          <t>DEC-229</t>
+          <t>DEC-235</t>
         </is>
       </c>
       <c r="B7" s="68" t="inlineStr">
@@ -15147,24 +15234,24 @@
       <c r="C7" s="68" t="n"/>
       <c r="D7" s="69" t="inlineStr">
         <is>
-          <t>El numero se reserva bajo bloqueo de la fila de la serie, no con MAX()+1</t>
+          <t>Los catalogos son configuracion, con portada propia</t>
         </is>
       </c>
       <c r="E7" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F7" s="69" t="inlineStr">
         <is>
-          <t>MAX()+1 es correcto exactamente hasta la primera vez que dos personas emiten a la vez, y eso no es raro: es un cierre de mes. El bloqueo pone en fila a la segunda peticion antes de que lea el contador. Y aun asi existe uq_dn_number: el bloqueo es la primera linea y la unica es la ultima. Medido con dos clientes de verdad (patron de 4.11), con su contraejemplo: sin FOR UPDATE, B no espera.</t>
+          <t>Los seis colgaban del menu bajo un titulo que no era un sitio: era una etiqueta. Ahora son un area con portada --cuantas filas y cuantas activas-- y su aviso: una lista sin ninguna fila activa sale en rojo, porque un catalogo vacio no da error, deja un desplegable vacio. La pantalla de cada catalogo no se mueve.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34.5" customHeight="1" s="36">
       <c r="A8" s="67" t="inlineStr">
         <is>
-          <t>DEC-230</t>
+          <t>DEC-228</t>
         </is>
       </c>
       <c r="B8" s="68" t="inlineStr">
@@ -15175,7 +15262,7 @@
       <c r="C8" s="68" t="n"/>
       <c r="D8" s="69" t="inlineStr">
         <is>
-          <t>Cada numero que sale queda escrito, y el hueco se explica en vez de taparse</t>
+          <t>Los tipos de comprobante son un catalogo por pais, no un enum en el codigo</t>
         </is>
       </c>
       <c r="E8" s="69" t="inlineStr">
@@ -15185,14 +15272,14 @@
       </c>
       <c r="F8" s="69" t="inlineStr">
         <is>
-          <t>Reservar y no emitir deja un numero sin documento, y eso NO se arregla reutilizandolo: reutilizarlo ES el duplicado. document_numbers guarda cada numero con su estado; reserved es el unico del que se sale, used dice a que documento fue y voided dice por que, con un motivo de al menos diez caracteres. Un hueco explicado es defendible ante un requerimiento; uno mudo, no.</t>
+          <t>ck_ds_type decia IN ('invoice','boleta','credit_note','debit_note','other') desde la Fase 2: la boleta es peruana, el CFDI mexicano no estaba y anadir uno exigia desplegar. Cada tipo declara su codigo oficial de SUNAT, la forma de su serie, como se le pide a una persona y cuantos digitos tiene el correlativo. No contradice a DEC-026: el codigo SE RAMIFICA por proposito de integracion, mientras que el tipo de comprobante NO se ramifica, VIAJA al emisor electronico.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1" s="36">
       <c r="A9" s="67" t="inlineStr">
         <is>
-          <t>DEC-231</t>
+          <t>DEC-229</t>
         </is>
       </c>
       <c r="B9" s="68" t="inlineStr">
@@ -15203,7 +15290,7 @@
       <c r="C9" s="68" t="n"/>
       <c r="D9" s="69" t="inlineStr">
         <is>
-          <t>Una sola serie por defecto por (sociedad, tipo, entorno), y la forma la impone el pais</t>
+          <t>El numero se reserva bajo bloqueo de la fila de la serie, no con MAX()+1</t>
         </is>
       </c>
       <c r="E9" s="69" t="inlineStr">
@@ -15213,14 +15300,14 @@
       </c>
       <c r="F9" s="69" t="inlineStr">
         <is>
-          <t>uq_ds_default es la columna puerta 32: con dos series por defecto, «emitir una factura» no tendria respuesta hasta que alguien eligiera. El empate se rechaza al CONFIGURAR y no al emitir. Y tg_ds_forma_ins/upd exige que la serie tenga la forma que declara su tipo y que el tipo sea del pais de la sociedad: una sociedad peruana no emite comprobantes colombianos.</t>
+          <t>MAX()+1 es correcto exactamente hasta la primera vez que dos personas emiten a la vez, y eso no es raro: es un cierre de mes. El bloqueo pone en fila a la segunda peticion antes de que lea el contador. Y aun asi existe uq_dn_number: el bloqueo es la primera linea y la unica es la ultima. Medido con dos clientes de verdad (patron de 4.11), con su contraejemplo: sin FOR UPDATE, B no espera.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="57" customHeight="1" s="36">
       <c r="A10" s="67" t="inlineStr">
         <is>
-          <t>DEC-232</t>
+          <t>DEC-230</t>
         </is>
       </c>
       <c r="B10" s="68" t="inlineStr">
@@ -15231,7 +15318,7 @@
       <c r="C10" s="68" t="n"/>
       <c r="D10" s="69" t="inlineStr">
         <is>
-          <t>Las series NO se siembran: unica configuracion sin valor de partida</t>
+          <t>Cada numero que sale queda escrito, y el hueco se explica en vez de taparse</t>
         </is>
       </c>
       <c r="E10" s="69" t="inlineStr">
@@ -15241,14 +15328,14 @@
       </c>
       <c r="F10" s="69" t="inlineStr">
         <is>
-          <t>Excepcion razonada a DEC-190: una serie se registra ante la administracion tributaria y una inventada produciria comprobantes invalidos ante SUNAT --un valor de fabrica aqui no es comodidad, es un error fiscal--. No bloquea nada, que es lo que DEC-190 exige de verdad: sale en rojo en el panel con las palabras que explican por que no hay ninguna. Lo que si se siembra son los TIPOS, que son la regla del pais.</t>
+          <t>Reservar y no emitir deja un numero sin documento, y eso NO se arregla reutilizandolo: reutilizarlo ES el duplicado. document_numbers guarda cada numero con su estado; reserved es el unico del que se sale, used dice a que documento fue y voided dice por que, con un motivo de al menos diez caracteres. Un hueco explicado es defendible ante un requerimiento; uno mudo, no.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="68.25" customHeight="1" s="36">
       <c r="A11" s="67" t="inlineStr">
         <is>
-          <t>DEC-223</t>
+          <t>DEC-231</t>
         </is>
       </c>
       <c r="B11" s="68" t="inlineStr">
@@ -15259,24 +15346,24 @@
       <c r="C11" s="68" t="n"/>
       <c r="D11" s="69" t="inlineStr">
         <is>
-          <t>Las credenciales de las APIs viven en tres tablas propias, no en .env ni en legal_entities</t>
+          <t>Una sola serie por defecto por (sociedad, tipo, entorno), y la forma la impone el pais</t>
         </is>
       </c>
       <c r="E11" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F11" s="69" t="inlineStr">
         <is>
-          <t>DEC-033 y docs/12 ya lo habian decidido y aqui se construye. Una sociedad es QUIEN factura; una conexion es CON QUE se conecta uno a un proveedor, y cambia mucho mas a menudo que una razon social. En .env seria peor: cambiar de entorno de pruebas a produccion exigiria entrar por SSH, que es DEC-190 roto por la puerta de atras.</t>
+          <t>uq_ds_default es la columna puerta 32: con dos series por defecto, «emitir una factura» no tendria respuesta hasta que alguien eligiera. El empate se rechaza al CONFIGURAR y no al emitir. Y tg_ds_forma_ins/upd exige que la serie tenga la forma que declara su tipo y que el tipo sea del pais de la sociedad: una sociedad peruana no emite comprobantes colombianos.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="68.25" customHeight="1" s="36">
       <c r="A12" s="67" t="inlineStr">
         <is>
-          <t>DEC-224</t>
+          <t>DEC-232</t>
         </is>
       </c>
       <c r="B12" s="68" t="inlineStr">
@@ -15287,24 +15374,24 @@
       <c r="C12" s="68" t="n"/>
       <c r="D12" s="69" t="inlineStr">
         <is>
-          <t>Tres tablas de las cinco de docs/12: las asignaciones no se construyen todavia</t>
+          <t>Las series NO se siembran: unica configuracion sin valor de partida</t>
         </is>
       </c>
       <c r="E12" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F12" s="69" t="inlineStr">
         <is>
-          <t>El eje (marca, sociedad, pais) con vigencia resuelve un problema que hoy no existe: una conexion sirve a una sociedad o a la plataforma entera, y eso cabe en un legal_entity_id nullable donde NULL significa «de la plataforma». Construir la tabla de tres ejes antes de tener el segundo caso es construir contra un supuesto. Queda escrito en la cabecera de la migracion para que no se tome por un olvido.</t>
+          <t>Excepcion razonada a DEC-190: una serie se registra ante la administracion tributaria y una inventada produciria comprobantes invalidos ante SUNAT --un valor de fabrica aqui no es comodidad, es un error fiscal--. No bloquea nada, que es lo que DEC-190 exige de verdad: sale en rojo en el panel con las palabras que explican por que no hay ninguna. Lo que si se siembra son los TIPOS, que son la regla del pais.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="68.25" customHeight="1" s="36">
       <c r="A13" s="67" t="inlineStr">
         <is>
-          <t>DEC-225</t>
+          <t>DEC-223</t>
         </is>
       </c>
       <c r="B13" s="68" t="inlineStr">
@@ -15315,7 +15402,7 @@
       <c r="C13" s="68" t="n"/>
       <c r="D13" s="69" t="inlineStr">
         <is>
-          <t>Rotar una credencial crea la version siguiente y cierra la anterior; no la pisa</t>
+          <t>Las credenciales de las APIs viven en tres tablas propias, no en .env ni en legal_entities</t>
         </is>
       </c>
       <c r="E13" s="69" t="inlineStr">
@@ -15325,14 +15412,14 @@
       </c>
       <c r="F13" s="69" t="inlineStr">
         <is>
-          <t>Se guardan el cifrado y los cuatro ultimos caracteres, nada mas. Pisar el valor deja sin respuesta «cual era la de antes» y «cuando cambio». Las dos escrituras van en la misma transaccion y en ese orden, porque uq_icred_vigente solo admite una viva por (conexion, clase). tg_icred_inmutable impide reescribir una credencial: lo unico que cambia en una fila existente es revocarla.</t>
+          <t>DEC-033 y docs/12 ya lo habian decidido y aqui se construye. Una sociedad es QUIEN factura; una conexion es CON QUE se conecta uno a un proveedor, y cambia mucho mas a menudo que una razon social. En .env seria peor: cambiar de entorno de pruebas a produccion exigiria entrar por SSH, que es DEC-190 roto por la puerta de atras.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45.75" customHeight="1" s="36">
       <c r="A14" s="67" t="inlineStr">
         <is>
-          <t>DEC-226</t>
+          <t>DEC-224</t>
         </is>
       </c>
       <c r="B14" s="68" t="inlineStr">
@@ -15343,7 +15430,7 @@
       <c r="C14" s="68" t="n"/>
       <c r="D14" s="69" t="inlineStr">
         <is>
-          <t>La bitacora anota QUE cambio, no que valor</t>
+          <t>Tres tablas de las cinco de docs/12: las asignaciones no se construyen todavia</t>
         </is>
       </c>
       <c r="E14" s="69" t="inlineStr">
@@ -15353,14 +15440,14 @@
       </c>
       <c r="F14" s="69" t="inlineStr">
         <is>
-          <t>Ni el secreto ni los cuatro ultimos entran en audit_log (BR-SEC-001). Un registro de auditoria que guarda el secreto es un segundo sitio donde esta el secreto, y ademas uno que por diseno no se puede borrar. Por eso el servicio parte la lectura en dos: estado() es lo que ve una persona y secreto() lo llama el cliente de la API.</t>
+          <t>El eje (marca, sociedad, pais) con vigencia resuelve un problema que hoy no existe: una conexion sirve a una sociedad o a la plataforma entera, y eso cabe en un legal_entity_id nullable donde NULL significa «de la plataforma». Construir la tabla de tres ejes antes de tener el segundo caso es construir contra un supuesto. Queda escrito en la cabecera de la migracion para que no se tome por un olvido.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1" s="36">
       <c r="A15" s="67" t="inlineStr">
         <is>
-          <t>DEC-227</t>
+          <t>DEC-225</t>
         </is>
       </c>
       <c r="B15" s="68" t="inlineStr">
@@ -15371,7 +15458,7 @@
       <c r="C15" s="68" t="n"/>
       <c r="D15" s="69" t="inlineStr">
         <is>
-          <t>Una conexion ACTIVA exige https; un borrador no</t>
+          <t>Rotar una credencial crea la version siguiente y cierra la anterior; no la pisa</t>
         </is>
       </c>
       <c r="E15" s="69" t="inlineStr">
@@ -15381,14 +15468,14 @@
       </c>
       <c r="F15" s="69" t="inlineStr">
         <is>
-          <t>ck_iconn_url es la unica regla de la iteracion que no es de forma sino de fondo: una URL http a un servicio de facturacion manda las claves secundarias por la red en claro. Se puede escribir mientras la conexion es un borrador y no se puede activar. La regla vive en la base y no en el formulario, porque el formulario no es el unico que escribe.</t>
+          <t>Se guardan el cifrado y los cuatro ultimos caracteres, nada mas. Pisar el valor deja sin respuesta «cual era la de antes» y «cuando cambio». Las dos escrituras van en la misma transaccion y en ese orden, porque uq_icred_vigente solo admite una viva por (conexion, clase). tg_icred_inmutable impide reescribir una credencial: lo unico que cambia en una fila existente es revocarla.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="57" customHeight="1" s="36">
       <c r="A16" s="67" t="inlineStr">
         <is>
-          <t>DEC-220</t>
+          <t>DEC-226</t>
         </is>
       </c>
       <c r="B16" s="68" t="inlineStr">
@@ -15399,24 +15486,24 @@
       <c r="C16" s="68" t="n"/>
       <c r="D16" s="69" t="inlineStr">
         <is>
-          <t>Core levanta un evento; Creator escucha</t>
+          <t>La bitacora anota QUE cambio, no que valor</t>
         </is>
       </c>
       <c r="E16" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F16" s="69" t="inlineStr">
         <is>
-          <t>Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
+          <t>Ni el secreto ni los cuatro ultimos entran en audit_log (BR-SEC-001). Un registro de auditoria que guarda el secreto es un segundo sitio donde esta el secreto, y ademas uno que por diseno no se puede borrar. Por eso el servicio parte la lectura en dos: estado() es lo que ve una persona y secreto() lo llama el cliente de la API.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="57" customHeight="1" s="36">
       <c r="A17" s="67" t="inlineStr">
         <is>
-          <t>DEC-221</t>
+          <t>DEC-227</t>
         </is>
       </c>
       <c r="B17" s="68" t="inlineStr">
@@ -15427,24 +15514,24 @@
       <c r="C17" s="68" t="n"/>
       <c r="D17" s="69" t="inlineStr">
         <is>
-          <t>El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
+          <t>Una conexion ACTIVA exige https; un borrador no</t>
         </is>
       </c>
       <c r="E17" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F17" s="69" t="inlineStr">
         <is>
-          <t>Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
+          <t>ck_iconn_url es la unica regla de la iteracion que no es de forma sino de fondo: una URL http a un servicio de facturacion manda las claves secundarias por la red en claro. Se puede escribir mientras la conexion es un borrador y no se puede activar. La regla vive en la base y no en el formulario, porque el formulario no es el unico que escribe.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="68.25" customHeight="1" s="36">
       <c r="A18" s="67" t="inlineStr">
         <is>
-          <t>DEC-222</t>
+          <t>DEC-220</t>
         </is>
       </c>
       <c r="B18" s="68" t="inlineStr">
@@ -15455,7 +15542,7 @@
       <c r="C18" s="68" t="n"/>
       <c r="D18" s="69" t="inlineStr">
         <is>
-          <t>Un correo que falla no deja sin avisar a los demas</t>
+          <t>Core levanta un evento; Creator escucha</t>
         </is>
       </c>
       <c r="E18" s="69" t="inlineStr">
@@ -15465,14 +15552,14 @@
       </c>
       <c r="F18" s="69" t="inlineStr">
         <is>
-          <t>Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
+          <t>Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45.75" customHeight="1" s="36">
       <c r="A19" s="67" t="inlineStr">
         <is>
-          <t>DEC-216</t>
+          <t>DEC-221</t>
         </is>
       </c>
       <c r="B19" s="68" t="inlineStr">
@@ -15483,24 +15570,24 @@
       <c r="C19" s="68" t="n"/>
       <c r="D19" s="69" t="inlineStr">
         <is>
-          <t>Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
+          <t>El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
         </is>
       </c>
       <c r="E19" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F19" s="69" t="inlineStr">
         <is>
-          <t>El plazo es parte de lo que se le comunico a la gente: «tienes 15 dias» dicho en enero no puede convertirse en «tenias 10» porque en marzo alguien cambio un ajuste global. Cada version lleva los suyos, se eligen al publicarla y despues son inmutables. Lo configurable es el valor por defecto, que es lo que el formulario trae puesto. readonly_days = 0 significa «sin periodo de solo lectura»; un numero muy grande, lo contrario.</t>
+          <t>Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="57" customHeight="1" s="36">
       <c r="A20" s="67" t="inlineStr">
         <is>
-          <t>DEC-217</t>
+          <t>DEC-222</t>
         </is>
       </c>
       <c r="B20" s="68" t="inlineStr">
@@ -15511,24 +15598,24 @@
       <c r="C20" s="68" t="n"/>
       <c r="D20" s="69" t="inlineStr">
         <is>
-          <t>El reloj no empieza al publicar: empieza cuando le toca a el</t>
+          <t>Un correo que falla no deja sin avisar a los demas</t>
         </is>
       </c>
       <c r="E20" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F20" s="69" t="inlineStr">
         <is>
-          <t>Un creador activado ayer no puede aparecer bloqueado por una version de hace tres meses. Su plazo cuenta desde el dia en que se activo, o desde la fecha de la version si es posterior. Sin esto, el primer creador que se diera de alta despues de un cambio de fondo entraria directamente al muro sin haber tenido un solo dia.</t>
+          <t>Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34.5" customHeight="1" s="36">
       <c r="A21" s="67" t="inlineStr">
         <is>
-          <t>DEC-218</t>
+          <t>DEC-216</t>
         </is>
       </c>
       <c r="B21" s="68" t="inlineStr">
@@ -15539,7 +15626,7 @@
       <c r="C21" s="68" t="n"/>
       <c r="D21" s="69" t="inlineStr">
         <is>
-          <t>La pantalla del muro no lleva permiso, y eso es la decision</t>
+          <t>Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
         </is>
       </c>
       <c r="E21" s="69" t="inlineStr">
@@ -15549,14 +15636,14 @@
       </c>
       <c r="F21" s="69" t="inlineStr">
         <is>
-          <t>/mis-terminos es la unica salida de un creador bloqueado: un permiso dejaria sin salida justo a quien la necesita. La autorizacion es tener ficha de creador atada a la sesion. El trinquete de rutas exentas subio de 4 a 6 a mano y con motivo escrito, que es todo el sentido de ese trinquete. Lleva throttle:10,1.</t>
+          <t>El plazo es parte de lo que se le comunico a la gente: «tienes 15 dias» dicho en enero no puede convertirse en «tenias 10» porque en marzo alguien cambio un ajuste global. Cada version lleva los suyos, se eligen al publicarla y despues son inmutables. Lo configurable es el valor por defecto, que es lo que el formulario trae puesto. readonly_days = 0 significa «sin periodo de solo lectura»; un numero muy grande, lo contrario.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="68.25" customHeight="1" s="36">
       <c r="A22" s="67" t="inlineStr">
         <is>
-          <t>DEC-219</t>
+          <t>DEC-217</t>
         </is>
       </c>
       <c r="B22" s="68" t="inlineStr">
@@ -15567,7 +15654,7 @@
       <c r="C22" s="68" t="n"/>
       <c r="D22" s="69" t="inlineStr">
         <is>
-          <t>Una franja fija, no un popup</t>
+          <t>El reloj no empieza al publicar: empieza cuando le toca a el</t>
         </is>
       </c>
       <c r="E22" s="69" t="inlineStr">
@@ -15577,14 +15664,14 @@
       </c>
       <c r="F22" s="69" t="inlineStr">
         <is>
-          <t>El negocio pidio «popup como recordatorio al loguearse». Un popup se cierra sin leerlo y no vuelve hasta la siguiente sesion; la franja sigue ahi mientras siga sin aceptarse. El equipo interno no la ve nunca.</t>
+          <t>Un creador activado ayer no puede aparecer bloqueado por una version de hace tres meses. Su plazo cuenta desde el dia en que se activo, o desde la fecha de la version si es posterior. Sin esto, el primer creador que se diera de alta despues de un cambio de fondo entraria directamente al muro sin haber tenido un solo dia.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="57" customHeight="1" s="36">
       <c r="A23" s="67" t="inlineStr">
         <is>
-          <t>DEC-212</t>
+          <t>DEC-218</t>
         </is>
       </c>
       <c r="B23" s="68" t="inlineStr">
@@ -15595,24 +15682,24 @@
       <c r="C23" s="68" t="n"/>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>Una politica de precios con vigencia, no dos constantes</t>
+          <t>La pantalla del muro no lleva permiso, y eso es la decision</t>
         </is>
       </c>
       <c r="E23" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F23" s="69" t="inlineStr">
         <is>
-          <t>pricing_policies guarda la retencion (Q-13), el umbral de rentabilidad y sobre que se calcula. Los tres cambian: el 29,5 % por decreto y el 20 % con datos reales. Tiene historia --una sola vigente-- y una cerrada no se reescribe ni se borra: es la que explica como se pacto un compromiso de hace tres meses.</t>
+          <t>/mis-terminos es la unica salida de un creador bloqueado: un permiso dejaria sin salida justo a quien la necesita. La autorizacion es tener ficha de creador atada a la sesion. El trinquete de rutas exentas subio de 4 a 6 a mano y con motivo escrito, que es todo el sentido de ese trinquete. Lleva throttle:10,1.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34.5" customHeight="1" s="36">
       <c r="A24" s="67" t="inlineStr">
         <is>
-          <t>DEC-213</t>
+          <t>DEC-219</t>
         </is>
       </c>
       <c r="B24" s="68" t="inlineStr">
@@ -15623,24 +15710,24 @@
       <c r="C24" s="68" t="n"/>
       <c r="D24" s="69" t="inlineStr">
         <is>
-          <t>margin_basis es configuracion, no una pregunta</t>
+          <t>Una franja fija, no un popup</t>
         </is>
       </c>
       <c r="E24" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F24" s="69" t="inlineStr">
         <is>
-          <t>Con 100 de neto y 29,5 % el costo es 141,84; el ejemplo del negocio dio 170,21, que es 141,84 x 1,20 (recargo sobre el COSTO). Un 20 % de margen sobre el INGRESO habria dado 177,31. Lo iba a preguntar dos veces; DEC-190 dice que estas cosas se configuran, y preguntarlo habria sido quemar la respuesta en el codigo con la firma del negocio encima. Es una columna con dos valores, sembrada en cost, con la pantalla ensenando las dos cifras y una prueba de cada una.</t>
+          <t>El negocio pidio «popup como recordatorio al loguearse». Un popup se cierra sin leerlo y no vuelve hasta la siguiente sesion; la franja sigue ahi mientras siga sin aceptarse. El equipo interno no la ve nunca.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45.75" customHeight="1" s="36">
       <c r="A25" s="67" t="inlineStr">
         <is>
-          <t>DEC-214</t>
+          <t>DEC-212</t>
         </is>
       </c>
       <c r="B25" s="68" t="inlineStr">
@@ -15651,7 +15738,7 @@
       <c r="C25" s="68" t="n"/>
       <c r="D25" s="69" t="inlineStr">
         <is>
-          <t>Se pacta el costo o el neto, y el ingreso minimo se dice, no se impone</t>
+          <t>Una politica de precios con vigencia, no dos constantes</t>
         </is>
       </c>
       <c r="E25" s="69" t="inlineStr">
@@ -15661,14 +15748,14 @@
       </c>
       <c r="F25" s="69" t="inlineStr">
         <is>
-          <t>agreed_amount sigue siendo el costo: de esa columna cuelgan devengos, pagos y la rentabilidad de 9.10. Se anaden la base, el neto y la tasa. Con net se teclean 100 y se escriben 141,8440, y el motor rehace la resta: un neto que no cuadra con su bruto se descubriria en la conversacion con el creador que cobro de menos. El mensaje dice el ingreso minimo y no bloquea: se puede aceptar menos margen, pero sabiendolo y antes de invitar. Los tres numeros se congelan en la participacion.</t>
+          <t>pricing_policies guarda la retencion (Q-13), el umbral de rentabilidad y sobre que se calcula. Los tres cambian: el 29,5 % por decreto y el 20 % con datos reales. Tiene historia --una sola vigente-- y una cerrada no se reescribe ni se borra: es la que explica como se pacto un compromiso de hace tres meses.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="57" customHeight="1" s="36">
       <c r="A26" s="67" t="inlineStr">
         <is>
-          <t>DEC-215</t>
+          <t>DEC-213</t>
         </is>
       </c>
       <c r="B26" s="68" t="inlineStr">
@@ -15679,7 +15766,7 @@
       <c r="C26" s="68" t="n"/>
       <c r="D26" s="69" t="inlineStr">
         <is>
-          <t>La cuenta la hace el motor, no PHP</t>
+          <t>margin_basis es configuracion, no una pregunta</t>
         </is>
       </c>
       <c r="E26" s="69" t="inlineStr">
@@ -15689,14 +15776,14 @@
       </c>
       <c r="F26" s="69" t="inlineStr">
         <is>
-          <t>neto / (1 - tasa/100) con float da 141.84397163120568 y de ahi a un DECIMAL(18,4) hay un redondeo que puede caer del lado que el CHECK no admite. El contenedor no tiene bcmath, asi que la aritmetica exacta se hace en el motor con CAST a DECIMAL(28,12). Misma tecnica que 9.1 y 9.3.</t>
+          <t>Con 100 de neto y 29,5 % el costo es 141,84; el ejemplo del negocio dio 170,21, que es 141,84 x 1,20 (recargo sobre el COSTO). Un 20 % de margen sobre el INGRESO habria dado 177,31. Lo iba a preguntar dos veces; DEC-190 dice que estas cosas se configuran, y preguntarlo habria sido quemar la respuesta en el codigo con la firma del negocio encima. Es una columna con dos valores, sembrada en cost, con la pantalla ensenando las dos cifras y una prueba de cada una.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="68.25" customHeight="1" s="36">
       <c r="A27" s="67" t="inlineStr">
         <is>
-          <t>DEC-209</t>
+          <t>DEC-214</t>
         </is>
       </c>
       <c r="B27" s="68" t="inlineStr">
@@ -15707,24 +15794,24 @@
       <c r="C27" s="68" t="n"/>
       <c r="D27" s="69" t="inlineStr">
         <is>
-          <t>La forma del codigo de localidad la declara el pais, no el codigo</t>
+          <t>Se pacta el costo o el neto, y el ingreso minimo se dice, no se impone</t>
         </is>
       </c>
       <c r="E27" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F27" s="69" t="inlineStr">
         <is>
-          <t>El comprobante peruano lleva el ubigeo del INEI (seis digitos) y el colombiano el codigo DANE (cinco). Una columna ubigeo CHAR(6) habria sido la regla de un pais escrita en el codigo de los seis y rechazaria un codigo colombiano correcto. countries declara como se llama, que forma tiene y si ese pais lo exige; el formulario pide «Ubigeo» a una peruana y «Codigo DANE» a una colombiana sin una linea de codigo por pais. La imponen dos disparadores cruzados que leen el patron de countries.</t>
+          <t>agreed_amount sigue siendo el costo: de esa columna cuelgan devengos, pagos y la rentabilidad de 9.10. Se anaden la base, el neto y la tasa. Con net se teclean 100 y se escriben 141,8440, y el motor rehace la resta: un neto que no cuadra con su bruto se descubriria en la conversacion con el creador que cobro de menos. El mensaje dice el ingreso minimo y no bloquea: se puede aceptar menos margen, pero sabiendolo y antes de invitar. Los tres numeros se congelan en la participacion.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="57" customHeight="1" s="36">
       <c r="A28" s="67" t="inlineStr">
         <is>
-          <t>DEC-210</t>
+          <t>DEC-215</t>
         </is>
       </c>
       <c r="B28" s="68" t="inlineStr">
@@ -15735,24 +15822,24 @@
       <c r="C28" s="68" t="n"/>
       <c r="D28" s="69" t="inlineStr">
         <is>
-          <t>El codigo de establecimiento nace en «0000» y no admite nulo</t>
+          <t>La cuenta la hace el motor, no PHP</t>
         </is>
       </c>
       <c r="E28" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F28" s="69" t="inlineStr">
         <is>
-          <t>Un comprobante SIEMPRE lleva uno; dejarlo nulo obligaria a decidirlo al emitir, que es tarde. «0000» es el domicilio fiscal en SUNAT. El formulario lo puede dejar en blanco --al crear y al editar-- y entonces vale 0000: sin esa normalizacion, vaciar el campo metia una cadena vacia que ck_le_establecimiento rechaza con un 45000 sin explicar nada.</t>
+          <t>neto / (1 - tasa/100) con float da 141.84397163120568 y de ahi a un DECIMAL(18,4) hay un redondeo que puede caer del lado que el CHECK no admite. El contenedor no tiene bcmath, asi que la aritmetica exacta se hace en el motor con CAST a DECIMAL(28,12). Misma tecnica que 9.1 y 9.3.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="68.25" customHeight="1" s="36">
       <c r="A29" s="67" t="inlineStr">
         <is>
-          <t>DEC-211</t>
+          <t>DEC-209</t>
         </is>
       </c>
       <c r="B29" s="68" t="inlineStr">
@@ -15763,7 +15850,7 @@
       <c r="C29" s="68" t="n"/>
       <c r="D29" s="69" t="inlineStr">
         <is>
-          <t>Que falte el ubigeo no bloquea: es un aviso rojo</t>
+          <t>La forma del codigo de localidad la declara el pais, no el codigo</t>
         </is>
       </c>
       <c r="E29" s="69" t="inlineStr">
@@ -15773,14 +15860,14 @@
       </c>
       <c r="F29" s="69" t="inlineStr">
         <is>
-          <t>requires_tax_location no impide guardar una sociedad a medias; hace que el panel de 9.17b lo enseñe en rojo con el nombre que ese pais le da. Y sale a la luz algo que no decia nadie: el sembrador escribe address_line1 = «Por completar» porque la columna es NOT NULL, la sociedad parecia completa, y ese texto habria salido impreso en un comprobante.</t>
+          <t>El comprobante peruano lleva el ubigeo del INEI (seis digitos) y el colombiano el codigo DANE (cinco). Una columna ubigeo CHAR(6) habria sido la regla de un pais escrita en el codigo de los seis y rechazaria un codigo colombiano correcto. countries declara como se llama, que forma tiene y si ese pais lo exige; el formulario pide «Ubigeo» a una peruana y «Codigo DANE» a una colombiana sin una linea de codigo por pais. La imponen dos disparadores cruzados que leen el patron de countries.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45.75" customHeight="1" s="36">
       <c r="A30" s="67" t="inlineStr">
         <is>
-          <t>DEC-205</t>
+          <t>DEC-210</t>
         </is>
       </c>
       <c r="B30" s="68" t="inlineStr">
@@ -15791,24 +15878,24 @@
       <c r="C30" s="68" t="n"/>
       <c r="D30" s="69" t="inlineStr">
         <is>
-          <t>Un registro de preparacion, y cada modulo declara lo suyo</t>
+          <t>El codigo de establecimiento nace en «0000» y no admite nulo</t>
         </is>
       </c>
       <c r="E30" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F30" s="69" t="inlineStr">
         <is>
-          <t>9.16 y 9.17 dejaron cada una su lista de avisos y cada una solo se ve entrando en su pantalla. Preparacion las junta, y cada modulo declara las comprobaciones de su area en su ServiceProvider: un revisor central pondria a Shared a saber de cinco modulos sin que deptrac lo vea, porque son consultas a tablas y no clases importadas. Hay una prueba que se rompe cuando alguien construye una pantalla de configuracion nueva y no la enchufa.</t>
+          <t>Un comprobante SIEMPRE lleva uno; dejarlo nulo obligaria a decidirlo al emitir, que es tarde. «0000» es el domicilio fiscal en SUNAT. El formulario lo puede dejar en blanco --al crear y al editar-- y entonces vale 0000: sin esa normalizacion, vaciar el campo metia una cadena vacia que ck_le_establecimiento rechaza con un 45000 sin explicar nada.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="79.5" customHeight="1" s="36">
       <c r="A31" s="67" t="inlineStr">
         <is>
-          <t>DEC-206</t>
+          <t>DEC-211</t>
         </is>
       </c>
       <c r="B31" s="68" t="inlineStr">
@@ -15819,24 +15906,24 @@
       <c r="C31" s="68" t="n"/>
       <c r="D31" s="69" t="inlineStr">
         <is>
-          <t>Si no puedes arreglarlo, no lo ves</t>
+          <t>Que falte el ubigeo no bloquea: es un aviso rojo</t>
         </is>
       </c>
       <c r="E31" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F31" s="69" t="inlineStr">
         <is>
-          <t>Cada area declara el permiso con el que SE ARREGLA, no el que hace falta para abrir el panel, y la revision filtra por el. BR-SEC-001 sigue en pie aunque la pantalla reuna en un sitio lo que estaba repartido en cinco, y ningun aviso lleva a un 403. Por eso config.view se le puede dar a finanzas sin miedo: ve el area de tipos de cambio y nada mas.</t>
+          <t>requires_tax_location no impide guardar una sociedad a medias; hace que el panel de 9.17b lo enseñe en rojo con el nombre que ese pais le da. Y sale a la luz algo que no decia nadie: el sembrador escribe address_line1 = «Por completar» porque la columna es NOT NULL, la sociedad parecia completa, y ese texto habria salido impreso en un comprobante.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="68.25" customHeight="1" s="36">
       <c r="A32" s="67" t="inlineStr">
         <is>
-          <t>DEC-207</t>
+          <t>DEC-205</t>
         </is>
       </c>
       <c r="B32" s="68" t="inlineStr">
@@ -15847,7 +15934,7 @@
       <c r="C32" s="68" t="n"/>
       <c r="D32" s="69" t="inlineStr">
         <is>
-          <t>Una comprobacion que revienta no tumba el panel</t>
+          <t>Un registro de preparacion, y cada modulo declara lo suyo</t>
         </is>
       </c>
       <c r="E32" s="69" t="inlineStr">
@@ -15857,14 +15944,14 @@
       </c>
       <c r="F32" s="69" t="inlineStr">
         <is>
-          <t>Un revisor que lanza una excepcion se convierte en un aviso ambar que lo dice, y las demas areas se siguen viendo. Un panel de «que me falta» que responde 500 porque a un area le pasa algo deja de contestar justo el dia en que hay algo que contestar.</t>
+          <t>9.16 y 9.17 dejaron cada una su lista de avisos y cada una solo se ve entrando en su pantalla. Preparacion las junta, y cada modulo declara las comprobaciones de su area en su ServiceProvider: un revisor central pondria a Shared a saber de cinco modulos sin que deptrac lo vea, porque son consultas a tablas y no clases importadas. Hay una prueba que se rompe cuando alguien construye una pantalla de configuracion nueva y no la enchufa.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45.75" customHeight="1" s="36">
       <c r="A33" s="67" t="inlineStr">
         <is>
-          <t>DEC-208</t>
+          <t>DEC-206</t>
         </is>
       </c>
       <c r="B33" s="68" t="inlineStr">
@@ -15875,7 +15962,7 @@
       <c r="C33" s="68" t="n"/>
       <c r="D33" s="69" t="inlineStr">
         <is>
-          <t>El correo en log es ROJO, y va el primero del panel</t>
+          <t>Si no puedes arreglarlo, no lo ves</t>
         </is>
       </c>
       <c r="E33" s="69" t="inlineStr">
@@ -15885,14 +15972,14 @@
       </c>
       <c r="F33" s="69" t="inlineStr">
         <is>
-          <t>mail.default vale log mientras nadie ponga una cuenta SMTP (Q-20), y con ese valor el correo no sale de la maquina: se escribe en storage/logs. La aplicacion no falla, la bitacora dice enviado y el creador no recibe su enlace de alta. Es el modo de fallo mas caro del sistema porque no se nota desde dentro, y hasta hoy no lo decia ninguna pantalla.</t>
+          <t>Cada area declara el permiso con el que SE ARREGLA, no el que hace falta para abrir el panel, y la revision filtra por el. BR-SEC-001 sigue en pie aunque la pantalla reuna en un sitio lo que estaba repartido en cinco, y ningun aviso lleva a un 403. Por eso config.view se le puede dar a finanzas sin miedo: ve el area de tipos de cambio y nada mas.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45.75" customHeight="1" s="36">
       <c r="A34" s="67" t="inlineStr">
         <is>
-          <t>DEC-199</t>
+          <t>DEC-207</t>
         </is>
       </c>
       <c r="B34" s="68" t="inlineStr">
@@ -15903,24 +15990,24 @@
       <c r="C34" s="68" t="n"/>
       <c r="D34" s="69" t="inlineStr">
         <is>
-          <t>La marca es una fila, y hay UNA sola por defecto</t>
+          <t>Una comprobacion que revienta no tumba el panel</t>
         </is>
       </c>
       <c r="E34" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F34" s="69" t="inlineStr">
         <is>
-          <t>«LATAM Social» estaba escrito en tres plantillas --title, barra lateral y pantalla de acceso--, el favicon era un archivo del repositorio y el pie legal con la razon social y el RUC estaba a mano al pie del formulario de entrada. platform_brands guardaba todo eso desde 2.10 y nadie la leyo nunca. default_gate es la 28.a columna puerta y uq_pb_default la hace unica: dos marcas por defecto es media aplicacion ensenando un nombre y la otra mitad otro sin que nada falle.</t>
+          <t>Un revisor que lanza una excepcion se convierte en un aviso ambar que lo dice, y las demas areas se siguen viendo. Un panel de «que me falta» que responde 500 porque a un area le pasa algo deja de contestar justo el dia en que hay algo que contestar.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="68.25" customHeight="1" s="36">
       <c r="A35" s="67" t="inlineStr">
         <is>
-          <t>DEC-200</t>
+          <t>DEC-208</t>
         </is>
       </c>
       <c r="B35" s="68" t="inlineStr">
@@ -15931,24 +16018,24 @@
       <c r="C35" s="68" t="n"/>
       <c r="D35" s="69" t="inlineStr">
         <is>
-          <t>Una configuracion que falta NO bloquea: valor de partida y aviso con prioridad</t>
+          <t>El correo en log es ROJO, y va el primero del panel</t>
         </is>
       </c>
       <c r="E35" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F35" s="69" t="inlineStr">
         <is>
-          <t>DEC-190 llevado al codigo. Sin tabla, sin fila o con un campo vacio se cae al valor de partida y aparece un badge: rojo lo que un tercero va a ver mal (sin logotipo, sin correo de soporte), ambar lo que conviene (sin favicon, sin pie legal, sin web), verde cuando no falta nada. El sistema arranca con dos rojos y funciona perfectamente con los dos puestos.</t>
+          <t>mail.default vale log mientras nadie ponga una cuenta SMTP (Q-20), y con ese valor el correo no sale de la maquina: se escribe en storage/logs. La aplicacion no falla, la bitacora dice enviado y el creador no recibe su enlace de alta. Es el modo de fallo mas caro del sistema porque no se nota desde dentro, y hasta hoy no lo decia ninguna pantalla.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="57" customHeight="1" s="36">
       <c r="A36" s="67" t="inlineStr">
         <is>
-          <t>DEC-201</t>
+          <t>DEC-199</t>
         </is>
       </c>
       <c r="B36" s="68" t="inlineStr">
@@ -15959,7 +16046,7 @@
       <c r="C36" s="68" t="n"/>
       <c r="D36" s="69" t="inlineStr">
         <is>
-          <t>El logotipo se sirve por una puerta publica propia, sin identificador</t>
+          <t>La marca es una fila, y hay UNA sola por defecto</t>
         </is>
       </c>
       <c r="E36" s="69" t="inlineStr">
@@ -15969,14 +16056,14 @@
       </c>
       <c r="F36" s="69" t="inlineStr">
         <is>
-          <t>La pantalla de acceso la ve quien no ha entrado, asi que el permiso file.view de 9.15 dejaria la marca fuera de la unica pantalla que ve todo el mundo. Lo que hace seguras a /marca/logo y /marca/favicon no es un permiso: es que NO aceptan identificador. Estan en RUTAS-ABIERTAS con su motivo y MuroTest las conoce.</t>
+          <t>«LATAM Social» estaba escrito en tres plantillas --title, barra lateral y pantalla de acceso--, el favicon era un archivo del repositorio y el pie legal con la razon social y el RUC estaba a mano al pie del formulario de entrada. platform_brands guardaba todo eso desde 2.10 y nadie la leyo nunca. default_gate es la 28.a columna puerta y uq_pb_default la hace unica: dos marcas por defecto es media aplicacion ensenando un nombre y la otra mitad otro sin que nada falle.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="68.25" customHeight="1" s="36">
       <c r="A37" s="67" t="inlineStr">
         <is>
-          <t>DEC-202</t>
+          <t>DEC-200</t>
         </is>
       </c>
       <c r="B37" s="68" t="inlineStr">
@@ -15987,7 +16074,7 @@
       <c r="C37" s="68" t="n"/>
       <c r="D37" s="69" t="inlineStr">
         <is>
-          <t>El codigo de la marca no se cambia; el nombre visible si</t>
+          <t>Una configuracion que falta NO bloquea: valor de partida y aviso con prioridad</t>
         </is>
       </c>
       <c r="E37" s="69" t="inlineStr">
@@ -15997,14 +16084,14 @@
       </c>
       <c r="F37" s="69" t="inlineStr">
         <is>
-          <t>tg_pb_code lo impide en el motor. El code es la llave con la que el sembrador encuentra la marca: si cambia, el siguiente db:seed crea otra, el sistema amanece con dos y las pantallas siguen ensenando la vieja mientras alguien edita la nueva.</t>
+          <t>DEC-190 llevado al codigo. Sin tabla, sin fila o con un campo vacio se cae al valor de partida y aparece un badge: rojo lo que un tercero va a ver mal (sin logotipo, sin correo de soporte), ambar lo que conviene (sin favicon, sin pie legal, sin web), verde cuando no falta nada. El sistema arranca con dos rojos y funciona perfectamente con los dos puestos.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="45.75" customHeight="1" s="36">
       <c r="A38" s="67" t="inlineStr">
         <is>
-          <t>DEC-203</t>
+          <t>DEC-201</t>
         </is>
       </c>
       <c r="B38" s="68" t="inlineStr">
@@ -16015,7 +16102,7 @@
       <c r="C38" s="68" t="n"/>
       <c r="D38" s="69" t="inlineStr">
         <is>
-          <t>Los colores y la tipografia se desinfectan ademas del CHECK</t>
+          <t>El logotipo se sirve por una puerta publica propia, sin identificador</t>
         </is>
       </c>
       <c r="E38" s="69" t="inlineStr">
@@ -16025,14 +16112,14 @@
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>El color acaba dentro de una regla CSS y la tipografia dentro de una URL y de una regla CSS, en todas las pantallas a la vez. Un nombre con comillas y llaves cierra la regla y escribe estilo ajeno en toda la aplicacion. Si el valor entra por una via que no pasa por el CHECK --carga masiva, restauracion de copia--, la segunda cerradura es lo unico que queda.</t>
+          <t>La pantalla de acceso la ve quien no ha entrado, asi que el permiso file.view de 9.15 dejaria la marca fuera de la unica pantalla que ve todo el mundo. Lo que hace seguras a /marca/logo y /marca/favicon no es un permiso: es que NO aceptan identificador. Estan en RUTAS-ABIERTAS con su motivo y MuroTest las conoce.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="90.75" customHeight="1" s="36">
       <c r="A39" s="67" t="inlineStr">
         <is>
-          <t>DEC-204</t>
+          <t>DEC-202</t>
         </is>
       </c>
       <c r="B39" s="68" t="inlineStr">
@@ -16043,7 +16130,7 @@
       <c r="C39" s="68" t="n"/>
       <c r="D39" s="69" t="inlineStr">
         <is>
-          <t>brand.manage es un permiso propio, y no legal_entity.manage</t>
+          <t>El codigo de la marca no se cambia; el nombre visible si</t>
         </is>
       </c>
       <c r="E39" s="69" t="inlineStr">
@@ -16053,14 +16140,14 @@
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>Quien da de alta sociedades del grupo no tiene por que poder cambiar lo que ve todo el mundo en todas las pantallas, incluida la de acceso. Hoy los dos los tiene solo admin; el dia que legal_entity.manage se le de a alguien de operaciones, esa persona no podra cambiar la marca. Hay una prueba que lo fija.</t>
+          <t>tg_pb_code lo impide en el motor. El code es la llave con la que el sembrador encuentra la marca: si cambia, el siguiente db:seed crea otra, el sistema amanece con dos y las pantallas siguen ensenando la vieja mientras alguien edita la nueva.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="45.75" customHeight="1" s="36">
       <c r="A40" s="67" t="inlineStr">
         <is>
-          <t>DEC-198</t>
+          <t>DEC-203</t>
         </is>
       </c>
       <c r="B40" s="68" t="inlineStr">
@@ -16071,24 +16158,24 @@
       <c r="C40" s="68" t="n"/>
       <c r="D40" s="69" t="inlineStr">
         <is>
-          <t>El permiso se mira en CADA peticion: no hay URL firmada de archivo.</t>
+          <t>Los colores y la tipografia se desinfectan ademas del CHECK</t>
         </is>
       </c>
       <c r="E40" s="69" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>Una URL firmada sigue funcionando cuando se reenvia y cuando a esa persona ya se le quito el acceso, y lo que sale por aqui son documentos de identidad y comprobantes bancarios. Con ruta propia, quitar un permiso surte efecto en la siguiente peticion y no queda ningun enlace circulando. El archivo se busca por uuid y no por id --un id correlativo invita a probar el siguiente-- y la respuesta lleva no-store (una identidad en la cache de un equipo compartido sobrevive al cierre de sesion), nosniff y una CSP que impide que un HTML o un SVG subido como «evidencia» se ejecute. El creador ve lo suyo, incluida su identidad: es informacion suya y le permite comprobar que archivamos el correcto. Rastro en bitacora solo para los sensibles --identidad, terminos y comprobante bancario--: anotar cada captura convertiria la bitacora en ruido, y una bitacora que nadie lee no protege nada</t>
+          <t>El color acaba dentro de una regla CSS y la tipografia dentro de una URL y de una regla CSS, en todas las pantallas a la vez. Un nombre con comillas y llaves cierra la regla y escribe estilo ajeno en toda la aplicacion. Si el valor entra por una via que no pasa por el CHECK --carga masiva, restauracion de copia--, la segunda cerradura es lo unico que queda.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="57" customHeight="1" s="36">
       <c r="A41" s="67" t="inlineStr">
         <is>
-          <t>DEC-197</t>
+          <t>DEC-204</t>
         </is>
       </c>
       <c r="B41" s="68" t="inlineStr">
@@ -16099,24 +16186,24 @@
       <c r="C41" s="68" t="n"/>
       <c r="D41" s="69" t="inlineStr">
         <is>
-          <t>Cada modulo declara quien puede ver SUS archivos; no hay un switch central.</t>
+          <t>brand.manage es un permiso propio, y no legal_entity.manage</t>
         </is>
       </c>
       <c r="E41" s="69" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>La regla de cada archivo depende de la tabla que lo apunta --identidad de creators, captura de publication_evidence, comprobante de payouts-- y un decisor central que las consultara todas pondria a Shared o a Core a saber de payouts. deptrac no lo veria: son consultas a tablas y no clases importadas, o sea una frontera rota en silencio, que es la peor clase. Cada modulo registra su regla en su ServiceProvider, igual que registra sus escuchas. Y se niega por omision: un proposito sin regla no se abre ni para el administrador, asi que un archivo nuevo cuyo autor olvido declarar quien puede verlo se queda cerrado y no abierto a todos</t>
+          <t>Quien da de alta sociedades del grupo no tiene por que poder cambiar lo que ve todo el mundo en todas las pantallas, incluida la de acceso. Hoy los dos los tiene solo admin; el dia que legal_entity.manage se le de a alguien de operaciones, esa persona no podra cambiar la marca. Hay una prueba que lo fija.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="45.75" customHeight="1" s="36">
       <c r="A42" s="67" t="inlineStr">
         <is>
-          <t>DEC-196</t>
+          <t>DEC-198</t>
         </is>
       </c>
       <c r="B42" s="68" t="inlineStr">
@@ -16127,24 +16214,24 @@
       <c r="C42" s="68" t="n"/>
       <c r="D42" s="69" t="inlineStr">
         <is>
-          <t>La Academia del creador se construye, y cada modulo se configura desde el admin.</t>
+          <t>El permiso se mira en CADA peticion: no hay URL firmada de archivo.</t>
         </is>
       </c>
       <c r="E42" s="69" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>Es G-08 del addendum de gamificacion y la de mas retorno de las once: modulos cortos --leer un brief sin gastar rondas, iluminacion y audio con un movil, como se rotula el contenido comercial, que derechos esta cediendo, como subir su evidencia-- con evaluacion al final e insignia de creador certificado. Ataca tres dolores ya medidos: cada ronda evitada es tiempo del equipo de revision, cada evidencia subida sola es el proceso mas manual que se deja de perseguir, y «creadores certificados» es un argumento de venta ante la marca. El software es la parte barata: modulos, orden, formato, evaluacion, intentos, XP e insignia salen del admin (DEC-190), y al completar uno se levanta TrainingModuleCompleted, previsto en el modelo desde la Fase 2. Lo caro es el CONTENIDO --guiones, video, mantenerlo cuando cambie una norma o una red-- y eso no lo hace el sistema. Se puede arrancar con modulos de solo texto, que cuestan casi nada y ya bajan rondas. Cierra Q-27</t>
+          <t>Una URL firmada sigue funcionando cuando se reenvia y cuando a esa persona ya se le quito el acceso, y lo que sale por aqui son documentos de identidad y comprobantes bancarios. Con ruta propia, quitar un permiso surte efecto en la siguiente peticion y no queda ningun enlace circulando. El archivo se busca por uuid y no por id --un id correlativo invita a probar el siguiente-- y la respuesta lleva no-store (una identidad en la cache de un equipo compartido sobrevive al cierre de sesion), nosniff y una CSP que impide que un HTML o un SVG subido como «evidencia» se ejecute. El creador ve lo suyo, incluida su identidad: es informacion suya y le permite comprobar que archivamos el correcto. Rastro en bitacora solo para los sensibles --identidad, terminos y comprobante bancario--: anotar cada captura convertiria la bitacora en ruido, y una bitacora que nadie lee no protege nada</t>
         </is>
       </c>
     </row>
     <row r="43" ht="68.25" customHeight="1" s="36">
       <c r="A43" s="67" t="inlineStr">
         <is>
-          <t>DEC-195</t>
+          <t>DEC-197</t>
         </is>
       </c>
       <c r="B43" s="68" t="inlineStr">
@@ -16155,24 +16242,24 @@
       <c r="C43" s="68" t="n"/>
       <c r="D43" s="69" t="inlineStr">
         <is>
-          <t>El lado del tipo de cambio se configura POR TIPO DE TRANSACCION.</t>
+          <t>Cada modulo declara quien puede ver SUS archivos; no hay un switch central.</t>
         </is>
       </c>
       <c r="E43" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>No se fija uno en el codigo: lo que se le paga a un creador, lo que se le cobra a un cliente y un gasto operativo no tienen por que convertirse con el mismo lado, y esa eleccion es contable. El admin declara, para cada tipo de transaccion, que lado se aplica (compra, venta o media) y con que fuente. Cierra Q-63, que era la que impedia dar un porcentaje de margen cuando hay dos monedas (DEC-185)</t>
+          <t>La regla de cada archivo depende de la tabla que lo apunta --identidad de creators, captura de publication_evidence, comprobante de payouts-- y un decisor central que las consultara todas pondria a Shared o a Core a saber de payouts. deptrac no lo veria: son consultas a tablas y no clases importadas, o sea una frontera rota en silencio, que es la peor clase. Cada modulo registra su regla en su ServiceProvider, igual que registra sus escuchas. Y se niega por omision: un proposito sin regla no se abre ni para el administrador, asi que un archivo nuevo cuyo autor olvido declarar quien puede verlo se queda cerrado y no abierto a todos</t>
         </is>
       </c>
     </row>
     <row r="44" ht="79.5" customHeight="1" s="36">
       <c r="A44" s="67" t="inlineStr">
         <is>
-          <t>DEC-194</t>
+          <t>DEC-196</t>
         </is>
       </c>
       <c r="B44" s="68" t="inlineStr">
@@ -16183,24 +16270,24 @@
       <c r="C44" s="68" t="n"/>
       <c r="D44" s="69" t="inlineStr">
         <is>
-          <t>La gamificacion premia con reconocimiento y con un catalogo de premios canjeables por XP.</t>
+          <t>La Academia del creador se construye, y cada modulo se configura desde el admin.</t>
         </is>
       </c>
       <c r="E44" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>Nada de dinero. Los premios --viajes, objetos-- viven en una tabla configurable desde el admin con su coste en XP y su disponibilidad, y el creador los canjea. El hito que consolida un referido es la primera campana completada (Q-25). Cierra Q-23, Q-24 y Q-26</t>
+          <t>Es G-08 del addendum de gamificacion y la de mas retorno de las once: modulos cortos --leer un brief sin gastar rondas, iluminacion y audio con un movil, como se rotula el contenido comercial, que derechos esta cediendo, como subir su evidencia-- con evaluacion al final e insignia de creador certificado. Ataca tres dolores ya medidos: cada ronda evitada es tiempo del equipo de revision, cada evidencia subida sola es el proceso mas manual que se deja de perseguir, y «creadores certificados» es un argumento de venta ante la marca. El software es la parte barata: modulos, orden, formato, evaluacion, intentos, XP e insignia salen del admin (DEC-190), y al completar uno se levanta TrainingModuleCompleted, previsto en el modelo desde la Fase 2. Lo caro es el CONTENIDO --guiones, video, mantenerlo cuando cambie una norma o una red-- y eso no lo hace el sistema. Se puede arrancar con modulos de solo texto, que cuestan casi nada y ya bajan rondas. Cierra Q-27</t>
         </is>
       </c>
     </row>
     <row r="45" ht="124.5" customHeight="1" s="36">
       <c r="A45" s="67" t="inlineStr">
         <is>
-          <t>DEC-193</t>
+          <t>DEC-195</t>
         </is>
       </c>
       <c r="B45" s="68" t="inlineStr">
@@ -16211,7 +16298,7 @@
       <c r="C45" s="68" t="n"/>
       <c r="D45" s="69" t="inlineStr">
         <is>
-          <t>Publicar terminos nuevos no expulsa a nadie de golpe: hay plazo, aviso y aterrizaje suave.</t>
+          <t>El lado del tipo de cambio se configura POR TIPO DE TRANSACCION.</t>
         </is>
       </c>
       <c r="E45" s="69" t="inlineStr">
@@ -16221,14 +16308,14 @@
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>Correo con enlace de aceptacion, 15 dias de plazo, aviso en la bandeja interna de la plataforma y recordatorio al entrar. Cumplido el plazo sin aceptar, la sesion cae en una pantalla que exige aceptar para continuar; si no acepta, solo lectura durante 30 dias. Los dos plazos son configurables (DEC-190). Es la respuesta a Q-46, y encaja con el «cambio menor» de 9.16: una errata no dispara nada de esto</t>
+          <t>No se fija uno en el codigo: lo que se le paga a un creador, lo que se le cobra a un cliente y un gasto operativo no tienen por que convertirse con el mismo lado, y esa eleccion es contable. El admin declara, para cada tipo de transaccion, que lado se aplica (compra, venta o media) y con que fuente. Cierra Q-63, que era la que impedia dar un porcentaje de margen cuando hay dos monedas (DEC-185)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="90.75" customHeight="1" s="36">
       <c r="A46" s="67" t="inlineStr">
         <is>
-          <t>DEC-192</t>
+          <t>DEC-194</t>
         </is>
       </c>
       <c r="B46" s="68" t="inlineStr">
@@ -16239,7 +16326,7 @@
       <c r="C46" s="68" t="n"/>
       <c r="D46" s="69" t="inlineStr">
         <is>
-          <t>Facturacion electronica DIRECTA con SUNAT, no por proveedor.</t>
+          <t>La gamificacion premia con reconocimiento y con un catalogo de premios canjeables por XP.</t>
         </is>
       </c>
       <c r="E46" s="69" t="inlineStr">
@@ -16249,14 +16336,14 @@
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>Configurable entero desde el admin: URL, certificado, usuario y clave secundarios, y correlativos independientes de factura, boleta y notas de credito de cada una. Con monitor de documentos timbrados: estado de cada uno, reintento manual, reintento automatico por job con frecuencia y numero de reintentos configurables, descarga de CDR, XML y PDF --el PDF con plantilla configurable-- y envio al cliente por correo con cuerpo configurable y variables arrastrables. Cierra Q-03 y de paso Q-21, que preguntaba por el contrato con un proveedor que ya no hay</t>
+          <t>Nada de dinero. Los premios --viajes, objetos-- viven en una tabla configurable desde el admin con su coste en XP y su disponibilidad, y el creador los canjea. El hito que consolida un referido es la primera campana completada (Q-25). Cierra Q-23, Q-24 y Q-26</t>
         </is>
       </c>
     </row>
     <row r="47" ht="68.25" customHeight="1" s="36">
       <c r="A47" s="67" t="inlineStr">
         <is>
-          <t>DEC-191</t>
+          <t>DEC-193</t>
         </is>
       </c>
       <c r="B47" s="68" t="inlineStr">
@@ -16267,7 +16354,7 @@
       <c r="C47" s="68" t="n"/>
       <c r="D47" s="69" t="inlineStr">
         <is>
-          <t>La retencion se calcula HACIA ATRAS desde el neto pactado, y se compara con un umbral de rentabilidad.</t>
+          <t>Publicar terminos nuevos no expulsa a nadie de golpe: hay plazo, aviso y aterrizaje suave.</t>
         </is>
       </c>
       <c r="E47" s="69" t="inlineStr">
@@ -16277,14 +16364,14 @@
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>Con el creador se pacta lo que VA A RECIBIR --«te pago 100»--; el sistema calcula el bruto que hay que provisionar con la tasa configurada (29,5% por defecto, Q-13/Q-40): bruto = neto / (1 - tasa), o sea 141,84 para 100 netos, de los que 41,84 son retencion. Tres campos y no uno: neto pactado, tasa aplicada (por defecto la del admin, editable en el trato) e importe bruto. Encima va un umbral de rentabilidad minima configurable: con el bruto como costo, la pantalla dice cual es el ingreso mas bajo que hace aceptable esa participacion, y avisa antes de cerrar el trato --no despues--. La tasa, el umbral y la base sobre la que se mide el umbral (sobre costo o sobre ingreso: no dan el mismo numero) salen del admin</t>
+          <t>Correo con enlace de aceptacion, 15 dias de plazo, aviso en la bandeja interna de la plataforma y recordatorio al entrar. Cumplido el plazo sin aceptar, la sesion cae en una pantalla que exige aceptar para continuar; si no acepta, solo lectura durante 30 dias. Los dos plazos son configurables (DEC-190). Es la respuesta a Q-46, y encaja con el «cambio menor» de 9.16: una errata no dispara nada de esto</t>
         </is>
       </c>
     </row>
     <row r="48" ht="45.75" customHeight="1" s="36">
       <c r="A48" s="67" t="inlineStr">
         <is>
-          <t>DEC-190</t>
+          <t>DEC-192</t>
         </is>
       </c>
       <c r="B48" s="68" t="inlineStr">
@@ -16292,14 +16379,10 @@
           <t>Decidida</t>
         </is>
       </c>
-      <c r="C48" s="68" t="inlineStr">
-        <is>
-          <t>Critica</t>
-        </is>
-      </c>
+      <c r="C48" s="68" t="n"/>
       <c r="D48" s="69" t="inlineStr">
         <is>
-          <t>PRINCIPIO RECTOR: la plataforma es WHITE LABEL y todo se configura desde el admin.</t>
+          <t>Facturacion electronica DIRECTA con SUNAT, no por proveedor.</t>
         </is>
       </c>
       <c r="E48" s="69" t="inlineStr">
@@ -16309,14 +16392,14 @@
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>Nada de reglas de negocio quemadas en el codigo: ni la razon social, ni el RUC, ni el representante legal, ni la direccion, ni el ubigeo, ni las tasas, ni los plazos, ni los correlativos, ni las credenciales de ninguna API. Lo que el codigo aporta es la REGLA; el VALOR sale de la configuracion. Y una configuracion sin valor no bloquea: se siembra con un valor de partida y se avisa con su prioridad --rojo si es delicado y sigue de fabrica, ambar si conviene revisarlo--. Esto corrige el criterio con el que se habian tomado varias decisiones anteriores --3.5 dejaba el sistema sin arrancar hasta que alguien corriera un comando, y varias preguntas de negocio se plantearon como «elige una y la quemo» cuando la respuesta correcta era «las dos, y que se elija en el admin»--. Toda decision anterior que fije un valor en el codigo queda sujeta a revision bajo este principio (T-69)</t>
+          <t>Configurable entero desde el admin: URL, certificado, usuario y clave secundarios, y correlativos independientes de factura, boleta y notas de credito de cada una. Con monitor de documentos timbrados: estado de cada uno, reintento manual, reintento automatico por job con frecuencia y numero de reintentos configurables, descarga de CDR, XML y PDF --el PDF con plantilla configurable-- y envio al cliente por correo con cuerpo configurable y variables arrastrables. Cierra Q-03 y de paso Q-21, que preguntaba por el contrato con un proveedor que ya no hay</t>
         </is>
       </c>
     </row>
     <row r="49" ht="57" customHeight="1" s="36">
       <c r="A49" s="67" t="inlineStr">
         <is>
-          <t>DEC-189</t>
+          <t>DEC-191</t>
         </is>
       </c>
       <c r="B49" s="68" t="inlineStr">
@@ -16327,24 +16410,24 @@
       <c r="C49" s="68" t="n"/>
       <c r="D49" s="69" t="inlineStr">
         <is>
-          <t>Las 23 rutas sin permiso se escriben, con su motivo, en RUTAS-ABIERTAS.</t>
+          <t>La retencion se calcula HACIA ATRAS desde el neto pactado, y se compara con un umbral de rentabilidad.</t>
         </is>
       </c>
       <c r="E49" s="69" t="inlineStr">
         <is>
-          <t>9.14b</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>Hasta hoy nada distinguia «es publica a proposito» --entrar, recuperar la contrasena, los enlaces firmados de 7.6 y 8.5-- de «se le olvido el middleware a alguien». verificar-muro.py comprueba que tres sitios digan lo mismo: la lista, routes/web.php y la constante de MuroTest; no se pueden fundir porque una la lee Python sin Laravel y otra PHPUnit, y tres copias es como se pierde una (SUITES, 3.12). Al CI: una ruta nueva sin permiso que no este escrita lo pone en rojo. De paso se cerraron dos puertas que no eran nuestras: storage.local y storage.local.upload, que registra el framework con serve =&gt; true sobre el disco privado. No eran una fuga --exigen URL firmada-- pero la aplicacion no genera ninguna, asi que no servian para nada; y ninguna lectura del codigo las habria encontrado, porque no estan en ningun archivo de rutas</t>
+          <t>Con el creador se pacta lo que VA A RECIBIR --«te pago 100»--; el sistema calcula el bruto que hay que provisionar con la tasa configurada (29,5% por defecto, Q-13/Q-40): bruto = neto / (1 - tasa), o sea 141,84 para 100 netos, de los que 41,84 son retencion. Tres campos y no uno: neto pactado, tasa aplicada (por defecto la del admin, editable en el trato) e importe bruto. Encima va un umbral de rentabilidad minima configurable: con el bruto como costo, la pantalla dice cual es el ingreso mas bajo que hace aceptable esa participacion, y avisa antes de cerrar el trato --no despues--. La tasa, el umbral y la base sobre la que se mide el umbral (sobre costo o sobre ingreso: no dan el mismo numero) salen del admin</t>
         </is>
       </c>
     </row>
     <row r="50" ht="79.5" customHeight="1" s="36">
       <c r="A50" s="67" t="inlineStr">
         <is>
-          <t>DEC-188</t>
+          <t>DEC-190</t>
         </is>
       </c>
       <c r="B50" s="68" t="inlineStr">
@@ -16352,27 +16435,31 @@
           <t>Decidida</t>
         </is>
       </c>
-      <c r="C50" s="68" t="n"/>
+      <c r="C50" s="68" t="inlineStr">
+        <is>
+          <t>Critica</t>
+        </is>
+      </c>
       <c r="D50" s="69" t="inlineStr">
         <is>
-          <t>El muro se prueba recorriendo TODAS las rutas, no las que uno recuerda.</t>
+          <t>PRINCIPIO RECTOR: la plataforma es WHITE LABEL y todo se configura desde el admin.</t>
         </is>
       </c>
       <c r="E50" s="69" t="inlineStr">
         <is>
-          <t>9.14b</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>MuroTest pide las 145 rutas con nombre como creador, como usuario de cliente y como autenticado sin rol, y exige que ninguna se abra --371 aserciones, y el muro aguanta--. Una pantalla nueva entra sola en la prueba. Las afirmaciones dirigidas que ya habia (DEC-172, DEC-179, DEC-181) comprueban lo que alguien se acordo de mirar; el fallo que de verdad paso --5.9, la portada enseñando los totales internos a cualquier autenticado-- no lo habria cazado ninguna. Lo permitido se escribe en positivo: una lista de lo permitido crece solo cuando alguien la toca a proposito. Se admite un 404 porque SubstituteBindings corre antes del middleware --con un id inventado la ruta contesta antes de llegar al permiso-- y para que no sea el escondite de la prueba se exige que mas de 80 rutas contesten 403 de verdad</t>
+          <t>Nada de reglas de negocio quemadas en el codigo: ni la razon social, ni el RUC, ni el representante legal, ni la direccion, ni el ubigeo, ni las tasas, ni los plazos, ni los correlativos, ni las credenciales de ninguna API. Lo que el codigo aporta es la REGLA; el VALOR sale de la configuracion. Y una configuracion sin valor no bloquea: se siembra con un valor de partida y se avisa con su prioridad --rojo si es delicado y sigue de fabrica, ambar si conviene revisarlo--. Esto corrige el criterio con el que se habian tomado varias decisiones anteriores --3.5 dejaba el sistema sin arrancar hasta que alguien corriera un comando, y varias preguntas de negocio se plantearon como «elige una y la quemo» cuando la respuesta correcta era «las dos, y que se elija en el admin»--. Toda decision anterior que fije un valor en el codigo queda sujeta a revision bajo este principio (T-69)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="113.25" customHeight="1" s="36">
       <c r="A51" s="67" t="inlineStr">
         <is>
-          <t>DEC-187</t>
+          <t>DEC-189</t>
         </is>
       </c>
       <c r="B51" s="68" t="inlineStr">
@@ -16383,24 +16470,24 @@
       <c r="C51" s="68" t="n"/>
       <c r="D51" s="69" t="inlineStr">
         <is>
-          <t>Una suite de QA se construye SU caso y no reusa el de nadie.</t>
+          <t>Las 23 rutas sin permiso se escriben, con su motivo, en RUTAS-ABIERTAS.</t>
         </is>
       </c>
       <c r="E51" s="69" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.14b</t>
         </is>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>La primera version de 9.14 reusaba lo que dejaban las suites anteriores, como hace 9.6, y se puso amarilla dos veces por motivos opuestos: corriendo sola porque no habia asientos, y corriendo la bateria entera porque para cuando llega el unico devengo pagable ya esta liquidado por 9.6 y las dos participaciones de la semilla estan ocupadas. Ahora crea su campana, su participacion y su devengo. Una suite de QA que depende del orden mide el orden, no la regla</t>
+          <t>Hasta hoy nada distinguia «es publica a proposito» --entrar, recuperar la contrasena, los enlaces firmados de 7.6 y 8.5-- de «se le olvido el middleware a alguien». verificar-muro.py comprueba que tres sitios digan lo mismo: la lista, routes/web.php y la constante de MuroTest; no se pueden fundir porque una la lee Python sin Laravel y otra PHPUnit, y tres copias es como se pierde una (SUITES, 3.12). Al CI: una ruta nueva sin permiso que no este escrita lo pone en rojo. De paso se cerraron dos puertas que no eran nuestras: storage.local y storage.local.upload, que registra el framework con serve =&gt; true sobre el disco privado. No eran una fuga --exigen URL firmada-- pero la aplicacion no genera ninguna, asi que no servian para nada; y ninguna lectura del codigo las habria encontrado, porque no estan en ningun archivo de rutas</t>
         </is>
       </c>
     </row>
     <row r="52" ht="102" customHeight="1" s="36">
       <c r="A52" s="67" t="inlineStr">
         <is>
-          <t>DEC-186</t>
+          <t>DEC-188</t>
         </is>
       </c>
       <c r="B52" s="68" t="inlineStr">
@@ -16411,24 +16498,24 @@
       <c r="C52" s="68" t="n"/>
       <c r="D52" s="69" t="inlineStr">
         <is>
-          <t>Nace verificar-cobertura-sql.py: que regla de la base no ha contestado NUNCA a nadie.</t>
+          <t>El muro se prueba recorriendo TODAS las rutas, no las que uno recuerda.</t>
         </is>
       </c>
       <c r="E52" s="69" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.14b</t>
         </is>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>Los verificadores que ya habia comprueban que la regla EXISTA y que sea la misma en los dos motores; ninguno comprobaba lo unico que importa el dia que falle: que alguien se lo haya preguntado. Medido: de las 317 reglas del esquema, 167 no aparecian en ninguna suite ni en ninguna prueba --el 53%--. No significa que esten mal: significa que nadie lo sabe. Una regla que nunca se ha probado no es una regla, es una intencion escrita en DDL. Va a correr-todo.sh y al CI con trinquete (MUDAS-BASE), asi que una regla nueva sin asercion pone el CI en rojo. La pregunta salio de 9.10a, donde campaign_costs llevaba dos semanas con cinco restricciones verdes en todos los verificadores y CERO filas</t>
+          <t>MuroTest pide las 145 rutas con nombre como creador, como usuario de cliente y como autenticado sin rol, y exige que ninguna se abra --371 aserciones, y el muro aguanta--. Una pantalla nueva entra sola en la prueba. Las afirmaciones dirigidas que ya habia (DEC-172, DEC-179, DEC-181) comprueban lo que alguien se acordo de mirar; el fallo que de verdad paso --5.9, la portada enseñando los totales internos a cualquier autenticado-- no lo habria cazado ninguna. Lo permitido se escribe en positivo: una lista de lo permitido crece solo cuando alguien la toca a proposito. Se admite un 404 porque SubstituteBindings corre antes del middleware --con un id inventado la ruta contesta antes de llegar al permiso-- y para que no sea el escondite de la prueba se exige que mas de 80 rutas contesten 403 de verdad</t>
         </is>
       </c>
     </row>
     <row r="53" ht="79.5" customHeight="1" s="36">
       <c r="A53" s="67" t="inlineStr">
         <is>
-          <t>DEC-185</t>
+          <t>DEC-187</t>
         </is>
       </c>
       <c r="B53" s="68" t="inlineStr">
@@ -16439,24 +16526,24 @@
       <c r="C53" s="68" t="n"/>
       <c r="D53" s="69" t="inlineStr">
         <is>
-          <t>El porcentaje de margen solo se da cuando todo esta en una moneda, y si no, se dice por que.</t>
+          <t>Una suite de QA se construye SU caso y no reusa el de nadie.</t>
         </is>
       </c>
       <c r="E53" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>Convertir exige elegir compra, venta o media (Q-63) y cada eleccion da un margen distinto para los mismos hechos; el dia que se elija cambian ademas todos los margenes historicos a la vez. Cuando falta, la pantalla escribe el motivo con palabras --«esta campana tiene importes en PEN y USD…»-- y no deja un hueco: quien mira una pantalla donde falta un numero necesita saber si falta porque no lo hay o porque no se puede calcular, y son dos conversaciones distintas. Tampoco hay total por sociedad: el ingreso de hoy es el DECLARADO y no el facturado (9.9), y sumar precios declarados por sociedad se parece a un estado de resultados sin serlo</t>
+          <t>La primera version de 9.14 reusaba lo que dejaban las suites anteriores, como hace 9.6, y se puso amarilla dos veces por motivos opuestos: corriendo sola porque no habia asientos, y corriendo la bateria entera porque para cuando llega el unico devengo pagable ya esta liquidado por 9.6 y las dos participaciones de la semilla estan ocupadas. Ahora crea su campana, su participacion y su devengo. Una suite de QA que depende del orden mide el orden, no la regla</t>
         </is>
       </c>
     </row>
     <row r="54" ht="45.75" customHeight="1" s="36">
       <c r="A54" s="67" t="inlineStr">
         <is>
-          <t>DEC-184</t>
+          <t>DEC-186</t>
         </is>
       </c>
       <c r="B54" s="68" t="inlineStr">
@@ -16467,24 +16554,24 @@
       <c r="C54" s="68" t="n"/>
       <c r="D54" s="69" t="inlineStr">
         <is>
-          <t>Los canjes salen en la lista, marcados, y fuera de todo total.</t>
+          <t>Nace verificar-cobertura-sql.py: que regla de la base no ha contestado NUNCA a nadie.</t>
         </is>
       </c>
       <c r="E54" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="F54" s="69" t="inlineStr">
         <is>
-          <t>Su ingreso es cero POR DECISION (7.2), asi que su margen es siempre negativo: el producto y el envio se gastaron igual. Promediarlos hace que la cartera entera parezca peor por un motivo que fue deliberado. Pero se enseñan con su costo, porque un canje tambien cuesta dinero y ese era justo el numero que nadie tenia. Queda fuera del total una segunda clase de campana: la que tiene gastos en OTRA moneda, cuyo margen en la moneda del grupo esta incompleto --y sumar un numero incompleto lo vuelve invisible--. Y la cabecera dice cuantas quedaron fuera y por que: un total que excluye filas sin contarlas engaña por omision</t>
+          <t>Los verificadores que ya habia comprueban que la regla EXISTA y que sea la misma en los dos motores; ninguno comprobaba lo unico que importa el dia que falle: que alguien se lo haya preguntado. Medido: de las 317 reglas del esquema, 167 no aparecian en ninguna suite ni en ninguna prueba --el 53%--. No significa que esten mal: significa que nadie lo sabe. Una regla que nunca se ha probado no es una regla, es una intencion escrita en DDL. Va a correr-todo.sh y al CI con trinquete (MUDAS-BASE), asi que una regla nueva sin asercion pone el CI en rojo. La pregunta salio de 9.10a, donde campaign_costs llevaba dos semanas con cinco restricciones verdes en todos los verificadores y CERO filas</t>
         </is>
       </c>
     </row>
     <row r="55" ht="79.5" customHeight="1" s="36">
       <c r="A55" s="67" t="inlineStr">
         <is>
-          <t>DEC-183</t>
+          <t>DEC-185</t>
         </is>
       </c>
       <c r="B55" s="68" t="inlineStr">
@@ -16495,7 +16582,7 @@
       <c r="C55" s="68" t="n"/>
       <c r="D55" s="69" t="inlineStr">
         <is>
-          <t>Compromiso::margen() se BORRA, no se arregla.</t>
+          <t>El porcentaje de margen solo se da cuando todo esta en una moneda, y si no, se dice por que.</t>
         </is>
       </c>
       <c r="E55" s="69" t="inlineStr">
@@ -16505,14 +16592,14 @@
       </c>
       <c r="F55" s="69" t="inlineStr">
         <is>
-          <t>Vivia en Campaign desde 7.7 y devolvia revenue_amount menos lo comprometido con creadores: no restaba producto, envios ni produccion, y desde 9.10a esos gastos ya se anotan, asi que el numero habria ido empeorando con cada gasto cargado sin que la pantalla se enterara. No se arregla donde estaba porque campaign_costs es de Finance y deptrac no deja que Campaign la conozca --misma frontera que el devengo de 9.4--. Y se borra en vez de dejarse por si acaso: un metodo que calcula un numero incompleto y se llama margen() es una trampa para quien lo encuentre dentro de seis meses. De paso, SeguimientoController deja de pasar un importe y pasa un booleano mas un enlace: ningun numero interno cruza ya hasta la plantilla, que es BR-SEC-001 un paso mas alla</t>
+          <t>Convertir exige elegir compra, venta o media (Q-63) y cada eleccion da un margen distinto para los mismos hechos; el dia que se elija cambian ademas todos los margenes historicos a la vez. Cuando falta, la pantalla escribe el motivo con palabras --«esta campana tiene importes en PEN y USD…»-- y no deja un hueco: quien mira una pantalla donde falta un numero necesita saber si falta porque no lo hay o porque no se puede calcular, y son dos conversaciones distintas. Tampoco hay total por sociedad: el ingreso de hoy es el DECLARADO y no el facturado (9.9), y sumar precios declarados por sociedad se parece a un estado de resultados sin serlo</t>
         </is>
       </c>
     </row>
     <row r="56" ht="79.5" customHeight="1" s="36">
       <c r="A56" s="67" t="inlineStr">
         <is>
-          <t>DEC-182</t>
+          <t>DEC-184</t>
         </is>
       </c>
       <c r="B56" s="68" t="inlineStr">
@@ -16523,24 +16610,24 @@
       <c r="C56" s="68" t="n"/>
       <c r="D56" s="69" t="inlineStr">
         <is>
-          <t>El costo del creador entra al DEVENGARSE, no al pagarse.</t>
+          <t>Los canjes salen en la lista, marcados, y fuera de todo total.</t>
         </is>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F56" s="69" t="inlineStr">
         <is>
-          <t>La deuda existe desde que acepta (9.4) y su importe esta congelado desde 7.5; esperar al pago haria que una campana terminada en marzo pareciera rentabilisima hasta el lote de abril. Sale del libro mayor y no de campaign_creators, porque el libro es quien sabe que devengos siguen vivos: uno anulado ya no se debe. Y no es Compromiso::comprometido(), que cuenta tambien a los shortlisted: alli es correcto --su trabajo es proteger el presupuesto ANTES de invitar-- y aqui contaria dinero de gente que todavia puede decir que no</t>
+          <t>Su ingreso es cero POR DECISION (7.2), asi que su margen es siempre negativo: el producto y el envio se gastaron igual. Promediarlos hace que la cartera entera parezca peor por un motivo que fue deliberado. Pero se enseñan con su costo, porque un canje tambien cuesta dinero y ese era justo el numero que nadie tenia. Queda fuera del total una segunda clase de campana: la que tiene gastos en OTRA moneda, cuyo margen en la moneda del grupo esta incompleto --y sumar un numero incompleto lo vuelve invisible--. Y la cabecera dice cuantas quedaron fuera y por que: un total que excluye filas sin contarlas engaña por omision</t>
         </is>
       </c>
     </row>
     <row r="57" ht="68.25" customHeight="1" s="36">
       <c r="A57" s="67" t="inlineStr">
         <is>
-          <t>DEC-181</t>
+          <t>DEC-183</t>
         </is>
       </c>
       <c r="B57" s="68" t="inlineStr">
@@ -16551,24 +16638,24 @@
       <c r="C57" s="68" t="n"/>
       <c r="D57" s="69" t="inlineStr">
         <is>
-          <t>Cargar gastos no es ver el margen: campaign_manager pierde campaign.view_margin.</t>
+          <t>Compromiso::margen() se BORRA, no se arregla.</t>
         </is>
       </c>
       <c r="E57" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F57" s="69" t="inlineStr">
         <is>
-          <t>Quien lleva una campana anota lo que se gasta y ve cuanto lleva gastado; el margen --lo que se gana-- es una cifra de direccion, y el camino por el que un numero interno acaba en un correo a un cliente empieza siempre por alguien que podia verlo sin necesitarlo (BR-SEC-001, 🔴). No nace un permiso nuevo para el margen: campaign.view_margin ya existe y hace eso, y un segundo permiso para el mismo secreto es la forma clasica de que un dia se conceda el que nadie mira. Lo que nace es finance.cost.manage, que es la capacidad que de verdad no existia. Y la revocacion va en la MIGRACION y no en el seeder (T-64)</t>
+          <t>Vivia en Campaign desde 7.7 y devolvia revenue_amount menos lo comprometido con creadores: no restaba producto, envios ni produccion, y desde 9.10a esos gastos ya se anotan, asi que el numero habria ido empeorando con cada gasto cargado sin que la pantalla se enterara. No se arregla donde estaba porque campaign_costs es de Finance y deptrac no deja que Campaign la conozca --misma frontera que el devengo de 9.4--. Y se borra en vez de dejarse por si acaso: un metodo que calcula un numero incompleto y se llama margen() es una trampa para quien lo encuentre dentro de seis meses. De paso, SeguimientoController deja de pasar un importe y pasa un booleano mas un enlace: ningun numero interno cruza ya hasta la plantilla, que es BR-SEC-001 un paso mas alla</t>
         </is>
       </c>
     </row>
     <row r="58" ht="34.5" customHeight="1" s="36">
       <c r="A58" s="67" t="inlineStr">
         <is>
-          <t>DEC-180</t>
+          <t>DEC-182</t>
         </is>
       </c>
       <c r="B58" s="68" t="inlineStr">
@@ -16579,7 +16666,7 @@
       <c r="C58" s="68" t="n"/>
       <c r="D58" s="69" t="inlineStr">
         <is>
-          <t>El gasto de una campana se agrupa por moneda: no se suma.</t>
+          <t>El costo del creador entra al DEVENGARSE, no al pagarse.</t>
         </is>
       </c>
       <c r="E58" s="69" t="inlineStr">
@@ -16589,14 +16676,14 @@
       </c>
       <c r="F58" s="69" t="inlineStr">
         <is>
-          <t>Un envio se paga en dolares y la campana se cobra en soles; sumarlos exige un tipo de cambio, y cual --compra, venta o media-- es una decision contable que sigue abierta (Q-63) y que da tres margenes distintos para los mismos hechos. Es la misma decision que el saldo del creador en 9.8, por el mismo motivo. Un numero que parece exacto y depende de una eleccion que nadie ha hecho es peor que dos numeros separados</t>
+          <t>La deuda existe desde que acepta (9.4) y su importe esta congelado desde 7.5; esperar al pago haria que una campana terminada en marzo pareciera rentabilisima hasta el lote de abril. Sale del libro mayor y no de campaign_creators, porque el libro es quien sabe que devengos siguen vivos: uno anulado ya no se debe. Y no es Compromiso::comprometido(), que cuenta tambien a los shortlisted: alli es correcto --su trabajo es proteger el presupuesto ANTES de invitar-- y aqui contaria dinero de gente que todavia puede decir que no</t>
         </is>
       </c>
     </row>
     <row r="59" ht="79.5" customHeight="1" s="36">
       <c r="A59" s="67" t="inlineStr">
         <is>
-          <t>DEC-179</t>
+          <t>DEC-181</t>
         </is>
       </c>
       <c r="B59" s="68" t="inlineStr">
@@ -16607,24 +16694,24 @@
       <c r="C59" s="68" t="n"/>
       <c r="D59" s="69" t="inlineStr">
         <is>
-          <t>Al creador se le avisa al CONFIRMAR y al DEVOLVER, no al enviar.</t>
+          <t>Cargar gastos no es ver el margen: campaign_manager pierde campaign.view_margin.</t>
         </is>
       </c>
       <c r="E59" s="69" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F59" s="69" t="inlineStr">
         <is>
-          <t>Avisar al enviar es avisar de una intencion: si el banco lo rechaza, el creador ya cree que cobro, y el segundo correo desmiente al primero --dos correos que se contradicen cuestan mas confianza que un correo que llega un dia mas tarde--. Ninguno de los dos lleva numero de cuenta ni referencia bancaria: un correo se lee en pantallas ajenas y se reenvia, y para saber que le pagaron no hace falta ver su cuenta; es la misma decision que los avisos de 4.13. Y lo que faltaba en payouts no eran los estados --estan desde la Fase 2-- sino el GRAFO: sin tg_payout_estado, un pago saltaba de pending a confirmed sin haber salido nunca, y uno devuelto volvia a sent con un UPDATE, borrando que el banco lo habia rechazado. Mismo agujero que ledger_entries tenia antes de 9.3</t>
+          <t>Quien lleva una campana anota lo que se gasta y ve cuanto lleva gastado; el margen --lo que se gana-- es una cifra de direccion, y el camino por el que un numero interno acaba en un correo a un cliente empieza siempre por alguien que podia verlo sin necesitarlo (BR-SEC-001, 🔴). No nace un permiso nuevo para el margen: campaign.view_margin ya existe y hace eso, y un segundo permiso para el mismo secreto es la forma clasica de que un dia se conceda el que nadie mira. Lo que nace es finance.cost.manage, que es la capacidad que de verdad no existia. Y la revocacion va en la MIGRACION y no en el seeder (T-64)</t>
         </is>
       </c>
     </row>
     <row r="60" ht="102" customHeight="1" s="36">
       <c r="A60" s="67" t="inlineStr">
         <is>
-          <t>DEC-178</t>
+          <t>DEC-180</t>
         </is>
       </c>
       <c r="B60" s="68" t="inlineStr">
@@ -16635,24 +16722,24 @@
       <c r="C60" s="68" t="n"/>
       <c r="D60" s="69" t="inlineStr">
         <is>
-          <t>Un pago devuelto por el banco NO deshace el devengo.</t>
+          <t>El gasto de una campana se agrupa por moneda: no se suma.</t>
         </is>
       </c>
       <c r="E60" s="69" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F60" s="69" t="inlineStr">
         <is>
-          <t>El devengo se queda en paid porque se pago: lo que fallo fue la transferencia, no el trabajo --y paid es terminal desde DEC-169--. La correccion es un asiento de payment_reversal que apunta al asiento de pago original (BR-FIN-002), positivo, asi que devuelve el saldo; los dos hechos quedan escritos --se pago, y volvio-- en vez de que el segundo borre al primero. Nace accrued porque ck_ledger_estado_inicial no admite nacer pagable --a pagable se LLEGA-- y se mueve a payable en la misma operacion: el creador ya cumplio, y su dinero no tiene que esperar a que alguien se acuerde de revisarlo. Si el pago no tuviera asiento en el libro mayor, devolver() falla en voz alta en vez de dejar el saldo diciendo que cobro algo que no tiene</t>
+          <t>Un envio se paga en dolares y la campana se cobra en soles; sumarlos exige un tipo de cambio, y cual --compra, venta o media-- es una decision contable que sigue abierta (Q-63) y que da tres margenes distintos para los mismos hechos. Es la misma decision que el saldo del creador en 9.8, por el mismo motivo. Un numero que parece exacto y depende de una eleccion que nadie ha hecho es peor que dos numeros separados</t>
         </is>
       </c>
     </row>
     <row r="61" ht="90.75" customHeight="1" s="36">
       <c r="A61" s="67" t="inlineStr">
         <is>
-          <t>DEC-177</t>
+          <t>DEC-179</t>
         </is>
       </c>
       <c r="B61" s="68" t="inlineStr">
@@ -16663,24 +16750,24 @@
       <c r="C61" s="68" t="n"/>
       <c r="D61" s="69" t="inlineStr">
         <is>
-          <t>El CSV del lote NO es el archivo del banco.</t>
+          <t>Al creador se le avisa al CONFIRMAR y al DEVOLVER, no al enviar.</t>
         </is>
       </c>
       <c r="E61" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="F61" s="69" t="inlineStr">
         <is>
-          <t>El formato de una transferencia masiva es especifico de cada entidad y sale de su manual; inventarselo produce un archivo que el banco rechaza sin decir por que, y el sintoma aparece el dia del pago. Lo que hay es un CSV legible por una persona, para teclear o comprobar, y la pantalla lo dice con esas palabras para que nadie lo suba creyendo que es lo otro. El archivo real se construye cuando haya banco y especificacion</t>
+          <t>Avisar al enviar es avisar de una intencion: si el banco lo rechaza, el creador ya cree que cobro, y el segundo correo desmiente al primero --dos correos que se contradicen cuestan mas confianza que un correo que llega un dia mas tarde--. Ninguno de los dos lleva numero de cuenta ni referencia bancaria: un correo se lee en pantallas ajenas y se reenvia, y para saber que le pagaron no hace falta ver su cuenta; es la misma decision que los avisos de 4.13. Y lo que faltaba en payouts no eran los estados --estan desde la Fase 2-- sino el GRAFO: sin tg_payout_estado, un pago saltaba de pending a confirmed sin haber salido nunca, y uno devuelto volvia a sent con un UPDATE, borrando que el banco lo habia rechazado. Mismo agujero que ledger_entries tenia antes de 9.3</t>
         </is>
       </c>
     </row>
     <row r="62" ht="57" customHeight="1" s="36">
       <c r="A62" s="67" t="inlineStr">
         <is>
-          <t>DEC-176</t>
+          <t>DEC-178</t>
         </is>
       </c>
       <c r="B62" s="68" t="inlineStr">
@@ -16691,24 +16778,24 @@
       <c r="C62" s="68" t="n"/>
       <c r="D62" s="69" t="inlineStr">
         <is>
-          <t>Sacar un pago de un lote firmado NO obliga a firmarlo otra vez.</t>
+          <t>Un pago devuelto por el banco NO deshace el devengo.</t>
         </is>
       </c>
       <c r="E62" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="F62" s="69" t="inlineStr">
         <is>
-          <t>Cuando un devengo se retiene entre la firma y la ejecucion --un post que se cae-- ese pago sale y el resto se paga igual. El importe total baja, nunca sube, y eso no puede sorprender a quien ya firmo; devolver el lote entero a borrador castigaria a diez creadores por el problema de uno. La liquidacion se anula, no se borra: es evidencia de que estuvo dentro y de que alguien lo saco, y anularla exige quien y por que (tg_pe_inmutable). Al anularse, el devengo vuelve a la cola. Un lote ya ejecutado no se toca: el dinero salio, y eso se corrige con una devolucion</t>
+          <t>El devengo se queda en paid porque se pago: lo que fallo fue la transferencia, no el trabajo --y paid es terminal desde DEC-169--. La correccion es un asiento de payment_reversal que apunta al asiento de pago original (BR-FIN-002), positivo, asi que devuelve el saldo; los dos hechos quedan escritos --se pago, y volvio-- en vez de que el segundo borre al primero. Nace accrued porque ck_ledger_estado_inicial no admite nacer pagable --a pagable se LLEGA-- y se mueve a payable en la misma operacion: el creador ya cumplio, y su dinero no tiene que esperar a que alguien se acuerde de revisarlo. Si el pago no tuviera asiento en el libro mayor, devolver() falla en voz alta en vez de dejar el saldo diciendo que cobro algo que no tiene</t>
         </is>
       </c>
     </row>
     <row r="63" ht="90.75" customHeight="1" s="36">
       <c r="A63" s="67" t="inlineStr">
         <is>
-          <t>DEC-175</t>
+          <t>DEC-177</t>
         </is>
       </c>
       <c r="B63" s="68" t="inlineStr">
@@ -16719,7 +16806,7 @@
       <c r="C63" s="68" t="n"/>
       <c r="D63" s="69" t="inlineStr">
         <is>
-          <t>Dos firmas SIEMPRE, sin umbral.</t>
+          <t>El CSV del lote NO es el archivo del banco.</t>
         </is>
       </c>
       <c r="E63" s="69" t="inlineStr">
@@ -16729,14 +16816,14 @@
       </c>
       <c r="F63" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-005 habla de un umbral configurable y se decide no tenerlo: el equipo es pequeno y los lotes son pocos y agrupados, asi que la segunda firma cuesta un clic al mes. Un umbral hay que elegirlo, mantenerlo y explicarlo --y el dia que alguien quiera saltarse la firma, parte el lote en dos--. Que el aprobador sea otro no lo comprueba la pantalla: lo impide ck_pbatch_segregation en la base desde la Fase 2; la pantalla solo lo dice ANTES de que nadie pulse. Y el importe del pago no se teclea: sale de sumar lo que liquida, asi que no puede discrepar de lo que el lote dice que paga --Lotes::descuadre() lo comprueba antes de firmar, porque una SUMA sobre otra tabla no cabe en un CHECK--</t>
+          <t>El formato de una transferencia masiva es especifico de cada entidad y sale de su manual; inventarselo produce un archivo que el banco rechaza sin decir por que, y el sintoma aparece el dia del pago. Lo que hay es un CSV legible por una persona, para teclear o comprobar, y la pantalla lo dice con esas palabras para que nadie lo suba creyendo que es lo otro. El archivo real se construye cuando haya banco y especificacion</t>
         </is>
       </c>
     </row>
     <row r="64" ht="102" customHeight="1" s="36">
       <c r="A64" s="67" t="inlineStr">
         <is>
-          <t>DEC-174</t>
+          <t>DEC-176</t>
         </is>
       </c>
       <c r="B64" s="68" t="inlineStr">
@@ -16747,7 +16834,7 @@
       <c r="C64" s="68" t="n"/>
       <c r="D64" s="69" t="inlineStr">
         <is>
-          <t>Nace payout_earnings: que devengos paga cada pago.</t>
+          <t>Sacar un pago de un lote firmado NO obliga a firmarlo otra vez.</t>
         </is>
       </c>
       <c r="E64" s="69" t="inlineStr">
@@ -16757,14 +16844,14 @@
       </c>
       <c r="F64" s="69" t="inlineStr">
         <is>
-          <t>ledger_entries.payout_id ataba UN asiento de pago a su payout (BR-FIN-013), pero el detalle --que devengos liquida-- no existia. Sin el, «.de que campanas es este dinero?» no tiene respuesta, y sin respuesta no hay nada que comparar con la sociedad del lote, que es lo que DEC-157 mando cerrar aqui. Con el detalle, BR-LE-009 se vuelve una consulta de tres saltos que cabe en tg_pe_sociedad. Se comprueba al enganchar el devengo al pago y no al aprobar el lote: aprobar es una firma sobre algo que ya tiene que estar bien, y una regla que solo mira al final deja existir el estado malo mientras tanto --que es como alguien lo ve, lo exporta, o lo cree--. Vigesimoseptima columna puerta: uq_pe_viva, un devengo en una sola liquidacion VIVA</t>
+          <t>Cuando un devengo se retiene entre la firma y la ejecucion --un post que se cae-- ese pago sale y el resto se paga igual. El importe total baja, nunca sube, y eso no puede sorprender a quien ya firmo; devolver el lote entero a borrador castigaria a diez creadores por el problema de uno. La liquidacion se anula, no se borra: es evidencia de que estuvo dentro y de que alguien lo saco, y anularla exige quien y por que (tg_pe_inmutable). Al anularse, el devengo vuelve a la cola. Un lote ya ejecutado no se toca: el dinero salio, y eso se corrige con una devolucion</t>
         </is>
       </c>
     </row>
     <row r="65" ht="90.75" customHeight="1" s="36">
       <c r="A65" s="67" t="inlineStr">
         <is>
-          <t>DEC-173</t>
+          <t>DEC-175</t>
         </is>
       </c>
       <c r="B65" s="68" t="inlineStr">
@@ -16775,24 +16862,24 @@
       <c r="C65" s="68" t="n"/>
       <c r="D65" s="69" t="inlineStr">
         <is>
-          <t>La fecha de cobro se ensena SOLO cuando el asiento ya es pagable.</t>
+          <t>Dos firmas SIEMPRE, sin umbral.</t>
         </is>
       </c>
       <c r="E65" s="69" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F65" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-012 dice que el plazo son 30 dias desde la verificacion y que es visible desde que acepta: lo visible desde que acepta es el plazo, y una FECHA es otra cosa que se lee muy distinto. Mientras el asiento esta devengado se ensena que falta --las cinco condiciones de BR-FIN-003, con sus palabras--, que es accionable: un creador puede hacer algo con «no tienes ningun medio de pago verificado» y no puede hacer nada con una fecha que depende de trabajo que aun no ha hecho. Y si esa fecha se corriera, la culpa pareceria nuestra. La cuenta arranca en la ultima verificacion de sus publicaciones, y si no hay ninguna --un formato que no exige post-- en la fecha en que se completo la participacion</t>
+          <t>BR-FIN-005 habla de un umbral configurable y se decide no tenerlo: el equipo es pequeno y los lotes son pocos y agrupados, asi que la segunda firma cuesta un clic al mes. Un umbral hay que elegirlo, mantenerlo y explicarlo --y el dia que alguien quiera saltarse la firma, parte el lote en dos--. Que el aprobador sea otro no lo comprueba la pantalla: lo impide ck_pbatch_segregation en la base desde la Fase 2; la pantalla solo lo dice ANTES de que nadie pulse. Y el importe del pago no se teclea: sale de sumar lo que liquida, asi que no puede discrepar de lo que el lote dice que paga --Lotes::descuadre() lo comprueba antes de firmar, porque una SUMA sobre otra tabla no cabe en un CHECK--</t>
         </is>
       </c>
     </row>
     <row r="66" ht="68.25" customHeight="1" s="36">
       <c r="A66" s="67" t="inlineStr">
         <is>
-          <t>DEC-172</t>
+          <t>DEC-174</t>
         </is>
       </c>
       <c r="B66" s="68" t="inlineStr">
@@ -16803,24 +16890,24 @@
       <c r="C66" s="68" t="n"/>
       <c r="D66" s="69" t="inlineStr">
         <is>
-          <t>El motivo interno de una retencion NO se le ensena al creador.</t>
+          <t>Nace payout_earnings: que devengos paga cada pago.</t>
         </is>
       </c>
       <c r="E66" s="69" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F66" s="69" t="inlineStr">
         <is>
-          <t>Lo escribe el equipo para el expediente y puede nombrar personas o sospechas todavia sin confirmar; un texto redactado deprisa --«parece que lo borro a proposito»-- leido sin contexto es una acusacion de la que no se vuelve. El creador ve «En revision -- te escribimos» y, desde 8.8, recibe un correo donde se le explica de verdad. Las palabras del portal tampoco son las del back-office: on_hold es «en revision» y no «retenido», porque la palabra interna describe lo que hace el sistema y la del portal tiene que describir lo que le pasa a el. La frontera vive en Ledger::misIngresos(), que enumera columnas --el mismo sitio que Aprobaciones::pieza() en 8.5--: devolver la fila entera y confiar en que la plantilla no imprima de mas es confiar en la plantilla de manana. Tampoco cruzan los asientos anulados: no le afectan y no sabe leerlos</t>
+          <t>ledger_entries.payout_id ataba UN asiento de pago a su payout (BR-FIN-013), pero el detalle --que devengos liquida-- no existia. Sin el, «.de que campanas es este dinero?» no tiene respuesta, y sin respuesta no hay nada que comparar con la sociedad del lote, que es lo que DEC-157 mando cerrar aqui. Con el detalle, BR-LE-009 se vuelve una consulta de tres saltos que cabe en tg_pe_sociedad. Se comprueba al enganchar el devengo al pago y no al aprobar el lote: aprobar es una firma sobre algo que ya tiene que estar bien, y una regla que solo mira al final deja existir el estado malo mientras tanto --que es como alguien lo ve, lo exporta, o lo cree--. Vigesimoseptima columna puerta: uq_pe_viva, un devengo en una sola liquidacion VIVA</t>
         </is>
       </c>
     </row>
     <row r="67" ht="68.25" customHeight="1" s="36">
       <c r="A67" s="67" t="inlineStr">
         <is>
-          <t>DEC-171</t>
+          <t>DEC-173</t>
         </is>
       </c>
       <c r="B67" s="68" t="inlineStr">
@@ -16831,24 +16918,24 @@
       <c r="C67" s="68" t="n"/>
       <c r="D67" s="69" t="inlineStr">
         <is>
-          <t>El barrido rescata las aceptaciones sin devengo, y avisa de que hubo que rescatarlas.</t>
+          <t>La fecha de cobro se ensena SOLO cuando el asiento ya es pagable.</t>
         </is>
       </c>
       <c r="E67" s="69" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="F67" s="69" t="inlineStr">
         <is>
-          <t>Un listener puede fallar, y si falla el creador queda aceptado y su dinero invisible; ademas las participaciones aceptadas antes de 9.4 nunca pasaron por el. ledger:revisar las anota antes de revisar --para que un devengo recuperado hoy pueda pasar a pagable hoy y no manana-- y lo dice en amarillo: que la lista no salga en cero es la noticia, no el arreglo. Es la misma red que 8.1 dejo para los entregables. Las gratuitas quedan fuera de esa lista a proposito: si no, el barrido intentaria lo imposible todos los dias y avisaria todos los dias de algo que esta bien</t>
+          <t>BR-FIN-012 dice que el plazo son 30 dias desde la verificacion y que es visible desde que acepta: lo visible desde que acepta es el plazo, y una FECHA es otra cosa que se lee muy distinto. Mientras el asiento esta devengado se ensena que falta --las cinco condiciones de BR-FIN-003, con sus palabras--, que es accionable: un creador puede hacer algo con «no tienes ningun medio de pago verificado» y no puede hacer nada con una fecha que depende de trabajo que aun no ha hecho. Y si esa fecha se corriera, la culpa pareceria nuestra. La cuenta arranca en la ultima verificacion de sus publicaciones, y si no hay ninguna --un formato que no exige post-- en la fecha en que se completo la participacion</t>
         </is>
       </c>
     </row>
     <row r="68" ht="79.5" customHeight="1" s="36">
       <c r="A68" s="67" t="inlineStr">
         <is>
-          <t>DEC-170</t>
+          <t>DEC-172</t>
         </is>
       </c>
       <c r="B68" s="68" t="inlineStr">
@@ -16859,24 +16946,24 @@
       <c r="C68" s="68" t="n"/>
       <c r="D68" s="69" t="inlineStr">
         <is>
-          <t>Se devenga al ACEPTAR, no al terminar, y por evento.</t>
+          <t>El motivo interno de una retencion NO se le ensena al creador.</t>
         </is>
       </c>
       <c r="E68" s="69" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="F68" s="69" t="inlineStr">
         <is>
-          <t>Al aceptar es cuando existe la deuda: 7.5 congela el agreed_amount en ese instante y BR-CREATOR-008 impide cambiarlo despues sin una enmienda firmada por las dos partes. Que todavia no se le pueda pagar es otra cosa y vive en el estado --accrued significa exactamente «se le debe y aun no se le puede pagar»--. Devengar al terminar habria dejado el trabajo hecho y el compromiso invisible hasta el final, que es como una campana se cierra sin que nadie sepa cuanto costo mientras corria. Va por evento y no por llamada directa por lo mismo que 8.1: deptrac no deja que Campaign conozca a Finance, y esta bien que no lo haga --si anotar el asiento falla, la aceptacion sigue siendo cierta, y el creador ya pulso «acepto»--. Y dos finales NO son fallos: que ya hubiera devengo --uq_ledger_devengo funcionando-- y que la colaboracion sea un canje. Si los tres se escribieran igual, el log diria que algo fallo cada vez que alguien acepta un canje, y a la tercera nadie lo lee</t>
+          <t>Lo escribe el equipo para el expediente y puede nombrar personas o sospechas todavia sin confirmar; un texto redactado deprisa --«parece que lo borro a proposito»-- leido sin contexto es una acusacion de la que no se vuelve. El creador ve «En revision -- te escribimos» y, desde 8.8, recibe un correo donde se le explica de verdad. Las palabras del portal tampoco son las del back-office: on_hold es «en revision» y no «retenido», porque la palabra interna describe lo que hace el sistema y la del portal tiene que describir lo que le pasa a el. La frontera vive en Ledger::misIngresos(), que enumera columnas --el mismo sitio que Aprobaciones::pieza() en 8.5--: devolver la fila entera y confiar en que la plantilla no imprima de mas es confiar en la plantilla de manana. Tampoco cruzan los asientos anulados: no le afectan y no sabe leerlos</t>
         </is>
       </c>
     </row>
     <row r="69" ht="57" customHeight="1" s="36">
       <c r="A69" s="67" t="inlineStr">
         <is>
-          <t>DEC-169</t>
+          <t>DEC-171</t>
         </is>
       </c>
       <c r="B69" s="68" t="inlineStr">
@@ -16887,24 +16974,24 @@
       <c r="C69" s="68" t="n"/>
       <c r="D69" s="69" t="inlineStr">
         <is>
-          <t>El estado de un asiento tiene un grafo, y moverlo exige decir por que.</t>
+          <t>El barrido rescata las aceptaciones sin devengo, y avisa de que hubo que rescatarlas.</t>
         </is>
       </c>
       <c r="E69" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F69" s="69" t="inlineStr">
         <is>
-          <t>tg_ledger_no_update es columna por columna y deja pasar status a proposito --sin eso la tabla no serviria-- pero de ahi no salia QUE transicion es valida: un paid podia volver a accrued, o sea dinero ya pagado reapareciendo como deuda. Es tg_del_rondas de 8.4 otra vez. paid y void son terminales: un pago que se deshace se corrige con un asiento de payment_reversal, no cambiando este estado. Y toda transicion exige status_reason: sin ella, «.por que este creador no cobro?» se contesta mirando la fecha y adivinando. A la bitacora solo va lo que decide una persona --las automaticas son miles y taparian justo lo que se busca ahi--; el rastro completo vive en status_transitions. Ademas nace uq_ledger_devengo, vigesimosexta columna puerta: un devengo por participacion, que BR-FIN-015 daba por hecho sin decirlo</t>
+          <t>Un listener puede fallar, y si falla el creador queda aceptado y su dinero invisible; ademas las participaciones aceptadas antes de 9.4 nunca pasaron por el. ledger:revisar las anota antes de revisar --para que un devengo recuperado hoy pueda pasar a pagable hoy y no manana-- y lo dice en amarillo: que la lista no salga en cero es la noticia, no el arreglo. Es la misma red que 8.1 dejo para los entregables. Las gratuitas quedan fuera de esa lista a proposito: si no, el barrido intentaria lo imposible todos los dias y avisaria todos los dias de algo que esta bien</t>
         </is>
       </c>
     </row>
     <row r="70" ht="57" customHeight="1" s="36">
       <c r="A70" s="67" t="inlineStr">
         <is>
-          <t>DEC-168</t>
+          <t>DEC-170</t>
         </is>
       </c>
       <c r="B70" s="68" t="inlineStr">
@@ -16915,24 +17002,24 @@
       <c r="C70" s="68" t="n"/>
       <c r="D70" s="69" t="inlineStr">
         <is>
-          <t>El asiento va en la moneda PACTADA; se convierte al pagar.</t>
+          <t>Se devenga al ACEPTAR, no al terminar, y por evento.</t>
         </is>
       </c>
       <c r="E70" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F70" s="69" t="inlineStr">
         <is>
-          <t>Se escribe con el agreed_amount y la moneda congelados al aceptar en 7.5: se le debe lo que se le prometio, en la moneda en que se le prometio. La conversion ocurre al armar el pago, con la tasa de ESE dia, y se congela en el asiento de pago (BR-FIN-009). Convertir al devengar habria dejado el saldo del creador en una sola moneda --mas facil de leer-- fijando el tipo de cambio meses antes de pagar: si el dolar sube, el creador cobra menos de lo pactado o nosotros pagamos mas, sin que nadie lo haya decidido</t>
+          <t>Al aceptar es cuando existe la deuda: 7.5 congela el agreed_amount en ese instante y BR-CREATOR-008 impide cambiarlo despues sin una enmienda firmada por las dos partes. Que todavia no se le pueda pagar es otra cosa y vive en el estado --accrued significa exactamente «se le debe y aun no se le puede pagar»--. Devengar al terminar habria dejado el trabajo hecho y el compromiso invisible hasta el final, que es como una campana se cierra sin que nadie sepa cuanto costo mientras corria. Va por evento y no por llamada directa por lo mismo que 8.1: deptrac no deja que Campaign conozca a Finance, y esta bien que no lo haga --si anotar el asiento falla, la aceptacion sigue siendo cierta, y el creador ya pulso «acepto»--. Y dos finales NO son fallos: que ya hubiera devengo --uq_ledger_devengo funcionando-- y que la colaboracion sea un canje. Si los tres se escribieran igual, el log diria que algo fallo cada vez que alguien acepta un canje, y a la tercera nadie lo lee</t>
         </is>
       </c>
     </row>
     <row r="71" ht="45.75" customHeight="1" s="36">
       <c r="A71" s="67" t="inlineStr">
         <is>
-          <t>DEC-167</t>
+          <t>DEC-169</t>
         </is>
       </c>
       <c r="B71" s="68" t="inlineStr">
@@ -16943,7 +17030,7 @@
       <c r="C71" s="68" t="n"/>
       <c r="D71" s="69" t="inlineStr">
         <is>
-          <t>Un post caido RETIENE el asiento; no lo anula.</t>
+          <t>El estado de un asiento tiene un grafo, y moverlo exige decir por que.</t>
         </is>
       </c>
       <c r="E71" s="69" t="inlineStr">
@@ -16953,14 +17040,14 @@
       </c>
       <c r="F71" s="69" t="inlineStr">
         <is>
-          <t>8.8 ya lo decidio para el contenido --«el sistema no descuenta nada; la decision de que se le paga la toma una persona con el expediente montado»-- y aqui es lo mismo aplicado al dinero: on_hold saca el asiento de la cola de pago y espera. Reversible: si el creador repone el post, vuelve a payable. Anularlo con una reversion habria sido contablemente mas limpio y habria decidido por su cuenta que no se le paga, que es justo lo que DEC-145 prohibe. Y un asiento retenido no cuenta como saldo: meterlo seria prometerle al creador algo que todavia no esta decidido</t>
+          <t>tg_ledger_no_update es columna por columna y deja pasar status a proposito --sin eso la tabla no serviria-- pero de ahi no salia QUE transicion es valida: un paid podia volver a accrued, o sea dinero ya pagado reapareciendo como deuda. Es tg_del_rondas de 8.4 otra vez. paid y void son terminales: un pago que se deshace se corrige con un asiento de payment_reversal, no cambiando este estado. Y toda transicion exige status_reason: sin ella, «.por que este creador no cobro?» se contesta mirando la fecha y adivinando. A la bitacora solo va lo que decide una persona --las automaticas son miles y taparian justo lo que se busca ahi--; el rastro completo vive en status_transitions. Ademas nace uq_ledger_devengo, vigesimosexta columna puerta: un devengo por participacion, que BR-FIN-015 daba por hecho sin decirlo</t>
         </is>
       </c>
     </row>
     <row r="72" ht="79.5" customHeight="1" s="36">
       <c r="A72" s="67" t="inlineStr">
         <is>
-          <t>DEC-166</t>
+          <t>DEC-168</t>
         </is>
       </c>
       <c r="B72" s="68" t="inlineStr">
@@ -16971,7 +17058,7 @@
       <c r="C72" s="68" t="n"/>
       <c r="D72" s="69" t="inlineStr">
         <is>
-          <t>Pasar un devengo a pagable lo hace el SISTEMA, no una persona.</t>
+          <t>El asiento va en la moneda PACTADA; se convierte al pagar.</t>
         </is>
       </c>
       <c r="E72" s="69" t="inlineStr">
@@ -16981,14 +17068,14 @@
       </c>
       <c r="F72" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-003 pide cinco cosas --participacion completada, contenido aprobado, publicacion verificada si aplica, documento tributario valido y medio de pago verificado-- y las cinco ya las firmo alguien una por una: quien verifico la publicacion, quien aprobo el perfil fiscal, quien verifico la cuenta. Una sexta firma que solo dice «si, se cumplen las cinco» es un boton que alguien acaba pulsando sin mirar, y una cola que retrasa pagos por acumulacion y no por duda. Ledger::requisitos() devuelve las cinco con su veredicto y no la primera que falla, porque quien mira por que un creador no cobra necesita la lista entera. El «si aplica» de la publicacion se implementa contando: si ningun entregable tiene publicacion el requisito se da por cumplido --un formato que no exige post no puede bloquear un pago para siempre--</t>
+          <t>Se escribe con el agreed_amount y la moneda congelados al aceptar en 7.5: se le debe lo que se le prometio, en la moneda en que se le prometio. La conversion ocurre al armar el pago, con la tasa de ESE dia, y se congela en el asiento de pago (BR-FIN-009). Convertir al devengar habria dejado el saldo del creador en una sola moneda --mas facil de leer-- fijando el tipo de cambio meses antes de pagar: si el dolar sube, el creador cobra menos de lo pactado o nosotros pagamos mas, sin que nadie lo haya decidido</t>
         </is>
       </c>
     </row>
     <row r="73" ht="68.25" customHeight="1" s="36">
       <c r="A73" s="67" t="inlineStr">
         <is>
-          <t>DEC-165</t>
+          <t>DEC-167</t>
         </is>
       </c>
       <c r="B73" s="68" t="inlineStr">
@@ -16999,24 +17086,24 @@
       <c r="C73" s="68" t="n"/>
       <c r="D73" s="69" t="inlineStr">
         <is>
-          <t>Decolecta trae USD → PEN y nada mas, y el sistema lo dice en vez de disimularlo.</t>
+          <t>Un post caido RETIENE el asiento; no lo anula.</t>
         </is>
       </c>
       <c r="E73" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F73" s="69" t="inlineStr">
         <is>
-          <t>Publica el tipo de cambio de SUNAT, y SUNAT solo publica el dolar. Por eso Decolecta no acepta un par como parametro --sabe traer lo unico que su fuente publica, y decirlo es mas honesto que aceptar COP y fallar raro--; el catalogo declara USD → PEN = sunat y ningun otro par, porque declarar una fuente que no publica es peor que no tener ninguna; la pantalla tiene carga manual con fuente manual y no disfrazada de sunat, que es lo que permite distinguir despues que se trajo y que se tecleo; y lo dice en la propia pantalla, para que «no llega la tasa del peso mexicano» no se diagnostique como un cron roto. Que fuente se usa para los demas pares queda como Q-64</t>
+          <t>8.8 ya lo decidio para el contenido --«el sistema no descuenta nada; la decision de que se le paga la toma una persona con el expediente montado»-- y aqui es lo mismo aplicado al dinero: on_hold saca el asiento de la cola de pago y espera. Reversible: si el creador repone el post, vuelve a payable. Anularlo con una reversion habria sido contablemente mas limpio y habria decidido por su cuenta que no se le paga, que es justo lo que DEC-145 prohibe. Y un asiento retenido no cuenta como saldo: meterlo seria prometerle al creador algo que todavia no esta decidido</t>
         </is>
       </c>
     </row>
     <row r="74" ht="68.25" customHeight="1" s="36">
       <c r="A74" s="67" t="inlineStr">
         <is>
-          <t>DEC-164</t>
+          <t>DEC-166</t>
         </is>
       </c>
       <c r="B74" s="68" t="inlineStr">
@@ -17027,24 +17114,24 @@
       <c r="C74" s="68" t="n"/>
       <c r="D74" s="69" t="inlineStr">
         <is>
-          <t>El cron deja rastro de cada intento, y pide TRES dias.</t>
+          <t>Pasar un devengo a pagable lo hace el SISTEMA, no una persona.</t>
         </is>
       </c>
       <c r="E74" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F74" s="69" t="inlineStr">
         <is>
-          <t>fx_fetch_runs. Cambio::DIAS_ATRAS detecta que las tasas dejaron de llegar cuando alguien va a convertir, o sea el dia de la liquidacion; esto lo ensena antes, y la pantalla lo resume arriba solo si hay algo que mirar --una pantalla que siempre tiene un aviso es una pantalla cuyos avisos nadie lee--. ck_ffr_nuevas obliga a que una corrida fallida diga cero, porque el registro que contesta «.sigue vivo el cron?» no puede afirmar que una corrida con error trajo tres tasas. Tres dias y no uno: si no corrio viernes ni sabado, pedir solo el domingo deja dos huecos que nadie rellena a mano, y repetir un dia no cuesta una fila --uq_fx_rate-- sino una peticion. Y termina en 0 aunque un dia falle: un cron que da error a diario hace ruido donde nadie mira; solo falla si NINGUN dia se pudo traer</t>
+          <t>BR-FIN-003 pide cinco cosas --participacion completada, contenido aprobado, publicacion verificada si aplica, documento tributario valido y medio de pago verificado-- y las cinco ya las firmo alguien una por una: quien verifico la publicacion, quien aprobo el perfil fiscal, quien verifico la cuenta. Una sexta firma que solo dice «si, se cumplen las cinco» es un boton que alguien acaba pulsando sin mirar, y una cola que retrasa pagos por acumulacion y no por duda. Ledger::requisitos() devuelve las cinco con su veredicto y no la primera que falla, porque quien mira por que un creador no cobra necesita la lista entera. El «si aplica» de la publicacion se implementa contando: si ningun entregable tiene publicacion el requisito se da por cumplido --un formato que no exige post no puede bloquear un pago para siempre--</t>
         </is>
       </c>
     </row>
     <row r="75" ht="57" customHeight="1" s="36">
       <c r="A75" s="67" t="inlineStr">
         <is>
-          <t>DEC-163</t>
+          <t>DEC-165</t>
         </is>
       </c>
       <c r="B75" s="68" t="inlineStr">
@@ -17055,7 +17142,7 @@
       <c r="C75" s="68" t="n"/>
       <c r="D75" s="69" t="inlineStr">
         <is>
-          <t>Cada final de la traida tiene su nombre, y traer() no lanza.</t>
+          <t>Decolecta trae USD → PEN y nada mas, y el sistema lo dice en vez de disimularlo.</t>
         </is>
       </c>
       <c r="E75" s="69" t="inlineStr">
@@ -17065,14 +17152,14 @@
       </c>
       <c r="F75" s="69" t="inlineStr">
         <is>
-          <t>ok, sin_credencial, error_http, error_red, respuesta_rara. En un catch generico los cinco se ven iguales y exigen cinco arreglos distintos: «no hay clave» se arregla configurandola, «401» rotandola, «200 con un cuerpo raro» mirando la API. Un 404 --dia sin publicar-- ni siquiera se pinta como averia: quien lee la salida del cron todos los dias deja de leerla si le grita por lo normal. Y una respuesta que no se entiende no anota nada: una tasa inventada entraria en una tabla que tg_fx_inmutable no deja corregir</t>
+          <t>Publica el tipo de cambio de SUNAT, y SUNAT solo publica el dolar. Por eso Decolecta no acepta un par como parametro --sabe traer lo unico que su fuente publica, y decirlo es mas honesto que aceptar COP y fallar raro--; el catalogo declara USD → PEN = sunat y ningun otro par, porque declarar una fuente que no publica es peor que no tener ninguna; la pantalla tiene carga manual con fuente manual y no disfrazada de sunat, que es lo que permite distinguir despues que se trajo y que se tecleo; y lo dice en la propia pantalla, para que «no llega la tasa del peso mexicano» no se diagnostique como un cron roto. Que fuente se usa para los demas pares queda como Q-64</t>
         </is>
       </c>
     </row>
     <row r="76" ht="45.75" customHeight="1" s="36">
       <c r="A76" s="67" t="inlineStr">
         <is>
-          <t>DEC-162</t>
+          <t>DEC-164</t>
         </is>
       </c>
       <c r="B76" s="68" t="inlineStr">
@@ -17083,7 +17170,7 @@
       <c r="C76" s="68" t="n"/>
       <c r="D76" s="69" t="inlineStr">
         <is>
-          <t>La credencial se configura desde la pantalla, pero el ENTORNO manda y en la base va CIFRADA.</t>
+          <t>El cron deja rastro de cada intento, y pide TRES dias.</t>
         </is>
       </c>
       <c r="E76" s="69" t="inlineStr">
@@ -17093,14 +17180,14 @@
       </c>
       <c r="F76" s="69" t="inlineStr">
         <is>
-          <t>La peticion era «la configurare en la pantalla del admin». Se hace, con dos condiciones que salen de la regla de seguridad del propio proyecto --«no almacenar secretos en texto plano en BD cuando exista alternativa segura»--: si hay DECOLECTA_API_KEY en el entorno se usa esa y la de la base ni se mira --no viaja por el navegador, no esta en ninguna tabla, no sale en un volcado--; y si no la hay, se guarda con Crypt, la misma maquina que cifra las cuentas bancarias desde 3.8. La clave no se reensena jamas, ni al que la escribio un minuto antes: la pantalla dice «termina en 8f2a» y de donde sale. La bitacora anota que cambio y los cuatro ultimos, nunca el valor. Y tg_fxs_credencial_firmada exige quien la puso, cuando y la pista, las tres o ninguna: media firma es peor que ninguna porque parece que «quien la puso» tiene respuesta. El permiso va aparte: la pantalla es fx.manage --la tiene finanzas-- y la credencial es integration.manage --solo admin--, porque una clave de un tercero es un permiso de gasto y no la necesita quien anota una tasa un lunes</t>
+          <t>fx_fetch_runs. Cambio::DIAS_ATRAS detecta que las tasas dejaron de llegar cuando alguien va a convertir, o sea el dia de la liquidacion; esto lo ensena antes, y la pantalla lo resume arriba solo si hay algo que mirar --una pantalla que siempre tiene un aviso es una pantalla cuyos avisos nadie lee--. ck_ffr_nuevas obliga a que una corrida fallida diga cero, porque el registro que contesta «.sigue vivo el cron?» no puede afirmar que una corrida con error trajo tres tasas. Tres dias y no uno: si no corrio viernes ni sabado, pedir solo el domingo deja dos huecos que nadie rellena a mano, y repetir un dia no cuesta una fila --uq_fx_rate-- sino una peticion. Y termina en 0 aunque un dia falle: un cron que da error a diario hace ruido donde nadie mira; solo falla si NINGUN dia se pudo traer</t>
         </is>
       </c>
     </row>
     <row r="77" ht="68.25" customHeight="1" s="36">
       <c r="A77" s="67" t="inlineStr">
         <is>
-          <t>DEC-161</t>
+          <t>DEC-163</t>
         </is>
       </c>
       <c r="B77" s="68" t="inlineStr">
@@ -17111,24 +17198,24 @@
       <c r="C77" s="68" t="n"/>
       <c r="D77" s="69" t="inlineStr">
         <is>
-          <t>porque() admite alternancia, y eso es lo que faltaba para bajar el trinquete de las 297.</t>
+          <t>Cada final de la traida tiene su nombre, y traer() no lanza.</t>
         </is>
       </c>
       <c r="E77" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F77" s="69" t="inlineStr">
         <is>
-          <t>Los dos motores contestan cosas distintas a la MISMA regla cuando la creo Restriccion: MariaDB dice «CONSTRAINT ck_fos_dates failed» y Percona dice el mensaje. El nombre sale en uno y el mensaje en el otro, y no coinciden en ningun texto, asi que toda regla de Restriccion tenia que quedarse en un probar ... RECHAZO a secas. Con grep -qE, porque ... 'ck_fos_dates|antes de empezar' afirma el motivo en los dos motores. DEC-154 puso el trinquete y conto 297; esto es la herramienta para bajarlo</t>
+          <t>ok, sin_credencial, error_http, error_red, respuesta_rara. En un catch generico los cinco se ven iguales y exigen cinco arreglos distintos: «no hay clave» se arregla configurandola, «401» rotandola, «200 con un cuerpo raro» mirando la API. Un 404 --dia sin publicar-- ni siquiera se pinta como averia: quien lee la salida del cron todos los dias deja de leerla si le grita por lo normal. Y una respuesta que no se entiende no anota nada: una tasa inventada entraria en una tabla que tg_fx_inmutable no deja corregir</t>
         </is>
       </c>
     </row>
     <row r="78" ht="57" customHeight="1" s="36">
       <c r="A78" s="67" t="inlineStr">
         <is>
-          <t>DEC-160</t>
+          <t>DEC-162</t>
         </is>
       </c>
       <c r="B78" s="68" t="inlineStr">
@@ -17139,24 +17226,24 @@
       <c r="C78" s="68" t="n"/>
       <c r="D78" s="69" t="inlineStr">
         <is>
-          <t>Un dia sin tasa usa la ultima anterior, y lo que se guarda es la fecha de ESA tasa.</t>
+          <t>La credencial se configura desde la pantalla, pero el ENTORNO manda y en la base va CIFRADA.</t>
         </is>
       </c>
       <c r="E78" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F78" s="69" t="inlineStr">
         <is>
-          <t>Sabados, domingos y feriados no tienen tipo publicado. Se convierte con la del viernes y el asiento dice «tasa del viernes», no «tasa del domingo»: guardar la fecha de la operacion habria sido mas comodo de leer y habria hecho que el historico afirmara que ese domingo hubo una tasa que nunca existio (BR-FIN-009). Es un supuesto fiscal y esta marcado como tal (§56): que la practica peruana sea el ultimo tipo publicado lo confirma el contador. Y hay un corte de 10 dias, porque «la ultima anterior» tapa una averia: si lo ultimo es de hace tres semanas no fue un feriado, es que el cron dejo de traerlas, y sin ese corte una tabla congelada se ve igual que una sana hasta el dia de la liquidacion</t>
+          <t>La peticion era «la configurare en la pantalla del admin». Se hace, con dos condiciones que salen de la regla de seguridad del propio proyecto --«no almacenar secretos en texto plano en BD cuando exista alternativa segura»--: si hay DECOLECTA_API_KEY en el entorno se usa esa y la de la base ni se mira --no viaja por el navegador, no esta en ninguna tabla, no sale en un volcado--; y si no la hay, se guarda con Crypt, la misma maquina que cifra las cuentas bancarias desde 3.8. La clave no se reensena jamas, ni al que la escribio un minuto antes: la pantalla dice «termina en 8f2a» y de donde sale. La bitacora anota que cambio y los cuatro ultimos, nunca el valor. Y tg_fxs_credencial_firmada exige quien la puso, cuando y la pista, las tres o ninguna: media firma es peor que ninguna porque parece que «quien la puso» tiene respuesta. El permiso va aparte: la pantalla es fx.manage --la tiene finanzas-- y la credencial es integration.manage --solo admin--, porque una clave de un tercero es un permiso de gasto y no la necesita quien anota una tasa un lunes</t>
         </is>
       </c>
     </row>
     <row r="79" ht="57" customHeight="1" s="36">
       <c r="A79" s="67" t="inlineStr">
         <is>
-          <t>DEC-159</t>
+          <t>DEC-161</t>
         </is>
       </c>
       <c r="B79" s="68" t="inlineStr">
@@ -17167,7 +17254,7 @@
       <c r="C79" s="68" t="n"/>
       <c r="D79" s="69" t="inlineStr">
         <is>
-          <t>Compra y venta son dos filas, y cual aplica NO tiene valor por defecto.</t>
+          <t>porque() admite alternancia, y eso es lo que faltaba para bajar el trinquete de las 297.</t>
         </is>
       </c>
       <c r="E79" s="69" t="inlineStr">
@@ -17177,14 +17264,14 @@
       </c>
       <c r="F79" s="69" t="inlineStr">
         <is>
-          <t>SUNAT publica las dos el mismo dia y no son intercambiables. Con una sola columna rate solo cabe una, y elegir cual guardar habria sido tomar por mi cuenta una decision contable en el sitio donde menos se ve. side entra en la clave, asi que las dos caben sin pisarse. Y Cambio::tasa() exige el lado como parametro sin defecto: un defecto aqui es exactamente la forma en que una decision fiscal se toma sola. Queda Q-63 para el contador, y por eso el buscador de creadores sigue sin convertir aunque la maquina ya exista</t>
+          <t>Los dos motores contestan cosas distintas a la MISMA regla cuando la creo Restriccion: MariaDB dice «CONSTRAINT ck_fos_dates failed» y Percona dice el mensaje. El nombre sale en uno y el mensaje en el otro, y no coinciden en ningun texto, asi que toda regla de Restriccion tenia que quedarse en un probar ... RECHAZO a secas. Con grep -qE, porque ... 'ck_fos_dates|antes de empezar' afirma el motivo en los dos motores. DEC-154 puso el trinquete y conto 297; esto es la herramienta para bajarlo</t>
         </is>
       </c>
     </row>
     <row r="80" ht="68.25" customHeight="1" s="36">
       <c r="A80" s="67" t="inlineStr">
         <is>
-          <t>DEC-158</t>
+          <t>DEC-160</t>
         </is>
       </c>
       <c r="B80" s="68" t="inlineStr">
@@ -17195,7 +17282,7 @@
       <c r="C80" s="68" t="n"/>
       <c r="D80" s="69" t="inlineStr">
         <is>
-          <t>Que fuente publica el tipo de cambio se DECLARA, con periodos, y no se elige al convertir.</t>
+          <t>Un dia sin tasa usa la ultima anterior, y lo que se guarda es la fecha de ESA tasa.</t>
         </is>
       </c>
       <c r="E80" s="69" t="inlineStr">
@@ -17205,14 +17292,14 @@
       </c>
       <c r="F80" s="69" t="inlineStr">
         <is>
-          <t>uq_exchange_rates incluia source a proposito --dos fuentes pueden discrepar el mismo dia y BR-FIN-009 exige poder decir de cual salio la que se aplico-- pero de ahi no salia CUAL SE APLICA. Es el estado EMPATE de CoberturaFacturacion, el que una vez produjo una factura emitida por la sociedad equivocada, y la respuesta es la misma que entonces: uq_fos_current garantiza una sola fuente VIGENTE por par, y fos_sin_solape una sola POR FECHA --que es la mitad que se olvida, porque convertir un importe de marzo resuelve por par Y por fecha--. Con periodos y no con una columna porque el historico tiene que seguir explicandose con quien mandaba entonces: si fuera una columna, cambiar de proveedor reescribiria como se convirtio todo lo anterior</t>
+          <t>Sabados, domingos y feriados no tienen tipo publicado. Se convierte con la del viernes y el asiento dice «tasa del viernes», no «tasa del domingo»: guardar la fecha de la operacion habria sido mas comodo de leer y habria hecho que el historico afirmara que ese domingo hubo una tasa que nunca existio (BR-FIN-009). Es un supuesto fiscal y esta marcado como tal (§56): que la practica peruana sea el ultimo tipo publicado lo confirma el contador. Y hay un corte de 10 dias, porque «la ultima anterior» tapa una averia: si lo ultimo es de hace tres semanas no fue un feriado, es que el cron dejo de traerlas, y sin ese corte una tabla congelada se ve igual que una sana hasta el dia de la liquidacion</t>
         </is>
       </c>
     </row>
     <row r="81" ht="68.25" customHeight="1" s="36">
       <c r="A81" s="67" t="inlineStr">
         <is>
-          <t>DEC-157</t>
+          <t>DEC-159</t>
         </is>
       </c>
       <c r="B81" s="68" t="inlineStr">
@@ -17223,24 +17310,24 @@
       <c r="C81" s="68" t="n"/>
       <c r="D81" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-009 se comprueba cuando se escribe el primer pago, no en la iteracion 9.11.</t>
+          <t>Compra y venta son dos filas, y cual aplica NO tiene valor por defecto.</t>
         </is>
       </c>
       <c r="E81" s="69" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F81" s="69" t="inlineStr">
         <is>
-          <t>El roadmap tenia la validacion de «la sociedad que factura y la que liquida son la misma» como iteracion 11 de 14 de la fase de finanzas. Una regla 🔴 que llega la penultima llega despues de que diez iteraciones se hayan construido dandola por buena, y es exactamente la forma de fallo de 8.4: el techo de rondas existia entero en PHP desde 8.3 y nada lo respaldaba en la base. Aqui es peor, porque lo que se cuela no es una ronda: es dinero saliendo de la sociedad equivocada, que es una operacion intercompania no documentada. Pasa a ser requisito de la iteracion que estrene payout_batches, y en la base: un lote nombra su sociedad y sus asientos nombran sus campanas, asi que la comprobacion es cross-table y le toca a un disparador, no a un CHECK. Y con esto DEC-020 deja de ser PROPUESTA: preguntaba si permitir que la entidad que factura y la que liquida divergieran, y recomendaba modelar la separacion y bloquearla en el MVP. DEC-156 lo contesta y ademas le quita el «en el MVP»</t>
+          <t>SUNAT publica las dos el mismo dia y no son intercambiables. Con una sola columna rate solo cabe una, y elegir cual guardar habria sido tomar por mi cuenta una decision contable en el sitio donde menos se ve. side entra en la clave, asi que las dos caben sin pisarse. Y Cambio::tasa() exige el lado como parametro sin defecto: un defecto aqui es exactamente la forma en que una decision fiscal se toma sola. Queda Q-63 para el contador, y por eso el buscador de creadores sigue sin convertir aunque la maquina ya exista</t>
         </is>
       </c>
     </row>
     <row r="82" ht="45.75" customHeight="1" s="36">
       <c r="A82" s="67" t="inlineStr">
         <is>
-          <t>DEC-156</t>
+          <t>DEC-158</t>
         </is>
       </c>
       <c r="B82" s="68" t="inlineStr">
@@ -17251,24 +17338,24 @@
       <c r="C82" s="68" t="n"/>
       <c r="D82" s="69" t="inlineStr">
         <is>
-          <t>La campana decide quien paga a cada creador, y el pais del creador no entra en esa decision.</t>
+          <t>Que fuente publica el tipo de cambio se DECLARA, con periodos, y no se elige al convertir.</t>
         </is>
       </c>
       <c r="E82" s="69" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F82" s="69" t="inlineStr">
         <is>
-          <t>Un creador colombiano en una campana de CTS Peru cobra de CTS Peru. La sociedad sale del pais del CLIENTE, se guarda en la campana y el pago la hereda de ahi, congelada al confirmar igual que agreed_amount; lo implementa F9. [Corregido el 2026-08-27, T-59: la version original de esta entrada decia que «payouts no tiene ninguna columna de sociedad» y eso es falso. payout_batches.legal_entity_id existe desde la migracion de finanzas y el pago la hereda de su lote. Lo que NO existe es la garantia de que sea la correcta: nada ata el lote a las campanas cuyos asientos liquida, asi que hoy un lote de CTS Colombia podria pagar el trabajo de una campana de CTS Peru y ninguna restriccion lo notaria.] Esto no inventa la regla: BR-LE-009 ya la decia, con «en el MVP» delante y en naranja. Se le quita el «en el MVP» y sube a 🔴, porque no es una simplificacion temporal sino como funciona el grupo. La alternativa --que pagara la sociedad del pais del creador-- parte una campana en dos contabilidades, obliga a que el margen de una campana se calcule entre sociedades y exige cobertura en el pais de cada creador antes de poder invitarlo: hoy Espana no tiene sociedad y con esa alternativa un creador espanol seria ininvitable. Y cambia el eje de Q-40: la retencion depende de quien paga Y de donde esta el creador, no solo de lo segundo, asi que la tabla del contador pasa a ser «CTS Peru pagando a un creador de cada pais» y CTS Colombia tiene la suya, para un contador colombiano</t>
+          <t>uq_exchange_rates incluia source a proposito --dos fuentes pueden discrepar el mismo dia y BR-FIN-009 exige poder decir de cual salio la que se aplico-- pero de ahi no salia CUAL SE APLICA. Es el estado EMPATE de CoberturaFacturacion, el que una vez produjo una factura emitida por la sociedad equivocada, y la respuesta es la misma que entonces: uq_fos_current garantiza una sola fuente VIGENTE por par, y fos_sin_solape una sola POR FECHA --que es la mitad que se olvida, porque convertir un importe de marzo resuelve por par Y por fecha--. Con periodos y no con una columna porque el historico tiene que seguir explicandose con quien mandaba entonces: si fuera una columna, cambiar de proveedor reescribiria como se convirtio todo lo anterior</t>
         </is>
       </c>
     </row>
     <row r="83" ht="68.25" customHeight="1" s="36">
       <c r="A83" s="67" t="inlineStr">
         <is>
-          <t>DEC-155</t>
+          <t>DEC-157</t>
         </is>
       </c>
       <c r="B83" s="68" t="inlineStr">
@@ -17279,24 +17366,24 @@
       <c r="C83" s="68" t="n"/>
       <c r="D83" s="69" t="inlineStr">
         <is>
-          <t>La sociedad que factura NO se elige: se resuelve, y la pantalla enseña por que.</t>
+          <t>BR-LE-009 se comprueba cuando se escribe el primer pago, no en la iteracion 9.11.</t>
         </is>
       </c>
       <c r="E83" s="69" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="F83" s="69" t="inlineStr">
         <is>
-          <t>El planteamiento era poner un desplegable «CTS Peru / CTS Colombia» en la campana. No se hace, y el motivo esta en el esquema: uq_lec_country mas tg_lec_sin_solape_ins/upd garantizan que en cualquier fecha hay como mucho una sociedad cubriendo un pais, asi que el desplegable tendria siempre una opcion --y una opcion que se puede cambiar es una que alguien puede cambiar mal--. Ya existia campaigns.billing_legal_entity_id, resuelto a starts_on por Campanas::quienFactura() y congelado al confirmar por tg_camp_entidad_congelada. Lo que faltaba no era el campo: era decirlo. La ficha ahora dice quien factura Y su motivo --«CTS Peru factura a Peru desde el 2025-01-01 (sociedad local)»--, porque una sociedad a secas no se puede comprobar y con su motivo y su fecha quien la lee sabe si es la que esperaba y puede discutirla antes de que salga una factura. El formulario de alta no adelanta una respuesta: el pais del cliente y la fecha todavia no existen, y resolver «con la cobertura de hoy» para ensenarlo es justo el «deducirlo de la configuracion vigente» que prohibe BR-LE-001</t>
+          <t>El roadmap tenia la validacion de «la sociedad que factura y la que liquida son la misma» como iteracion 11 de 14 de la fase de finanzas. Una regla 🔴 que llega la penultima llega despues de que diez iteraciones se hayan construido dandola por buena, y es exactamente la forma de fallo de 8.4: el techo de rondas existia entero en PHP desde 8.3 y nada lo respaldaba en la base. Aqui es peor, porque lo que se cuela no es una ronda: es dinero saliendo de la sociedad equivocada, que es una operacion intercompania no documentada. Pasa a ser requisito de la iteracion que estrene payout_batches, y en la base: un lote nombra su sociedad y sus asientos nombran sus campanas, asi que la comprobacion es cross-table y le toca a un disparador, no a un CHECK. Y con esto DEC-020 deja de ser PROPUESTA: preguntaba si permitir que la entidad que factura y la que liquida divergieran, y recomendaba modelar la separacion y bloquearla en el MVP. DEC-156 lo contesta y ademas le quita el «en el MVP»</t>
         </is>
       </c>
     </row>
     <row r="84" ht="57" customHeight="1" s="36">
       <c r="A84" s="67" t="inlineStr">
         <is>
-          <t>DEC-154</t>
+          <t>DEC-156</t>
         </is>
       </c>
       <c r="B84" s="68" t="inlineStr">
@@ -17307,24 +17394,24 @@
       <c r="C84" s="68" t="n"/>
       <c r="D84" s="69" t="inlineStr">
         <is>
-          <t>Los ayudantes de las suites viven en UN archivo, y nace la SEPTIMA puerta.</t>
+          <t>La campana decide quien paga a cada creador, y el pais del creador no entra en esa decision.</t>
         </is>
       </c>
       <c r="E84" s="69" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="F84" s="69" t="inlineStr">
         <is>
-          <t>tools/pruebas/comun.sh y tools/verificar-suites.py. La puerta comprueba que toda suite listada existe, que ninguna define sus propios probar/valor/porque, que todas cargan comun.sh, y lleva un trinquete: cuantas aserciones negativas afirman POR QUE se rechaza y cuantas solo que algo fallo. Hoy son 89 con motivo y 297 sin el, y ese segundo numero solo puede bajar (tools/pruebas/MOTIVOS-BASE). No se convierten las 297 en esta iteracion --son veintidos suites de cuatro fases-- pero desde hoy no pueden ser 298, y ademas cada probar ... RECHAZO enseña en gris que restriccion respondio, para que el desajuste se vea al leer la salida. Es la leccion de T-48, T-50, T-51 y T-54: las cuatro fueron aserciones verdes por el motivo equivocado y las cuatro eran un probar ... RECHAZO a secas</t>
+          <t>Un creador colombiano en una campana de CTS Peru cobra de CTS Peru. La sociedad sale del pais del CLIENTE, se guarda en la campana y el pago la hereda de ahi, congelada al confirmar igual que agreed_amount; lo implementa F9. [Corregido el 2026-08-27, T-59: la version original de esta entrada decia que «payouts no tiene ninguna columna de sociedad» y eso es falso. payout_batches.legal_entity_id existe desde la migracion de finanzas y el pago la hereda de su lote. Lo que NO existe es la garantia de que sea la correcta: nada ata el lote a las campanas cuyos asientos liquida, asi que hoy un lote de CTS Colombia podria pagar el trabajo de una campana de CTS Peru y ninguna restriccion lo notaria.] Esto no inventa la regla: BR-LE-009 ya la decia, con «en el MVP» delante y en naranja. Se le quita el «en el MVP» y sube a 🔴, porque no es una simplificacion temporal sino como funciona el grupo. La alternativa --que pagara la sociedad del pais del creador-- parte una campana en dos contabilidades, obliga a que el margen de una campana se calcule entre sociedades y exige cobertura en el pais de cada creador antes de poder invitarlo: hoy Espana no tiene sociedad y con esa alternativa un creador espanol seria ininvitable. Y cambia el eje de Q-40: la retencion depende de quien paga Y de donde esta el creador, no solo de lo segundo, asi que la tabla del contador pasa a ser «CTS Peru pagando a un creador de cada pais» y CTS Colombia tiene la suya, para un contador colombiano</t>
         </is>
       </c>
     </row>
     <row r="85" ht="57" customHeight="1" s="36">
       <c r="A85" s="67" t="inlineStr">
         <is>
-          <t>DEC-153</t>
+          <t>DEC-155</t>
         </is>
       </c>
       <c r="B85" s="68" t="inlineStr">
@@ -17335,24 +17422,24 @@
       <c r="C85" s="68" t="n"/>
       <c r="D85" s="69" t="inlineStr">
         <is>
-          <t>Una peticion de cambios sin rondas queda PENDIENTE de autorizar.</t>
+          <t>La sociedad que factura NO se elige: se resuelve, y la pantalla enseña por que.</t>
         </is>
       </c>
       <c r="E85" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="F85" s="69" t="inlineStr">
         <is>
-          <t>Se registra y no se convierte en ronda hasta que alguien del equipo decida si se le cobra o la absorbemos; al cliente se le confirma que su peticion llego --que es verdad-- sin prometerle que sera gratis. Cae solo del modelo de DEC-151: como la respuesta no crea la revision, no hay ronda que consumir hasta que una persona emite el veredicto. Aprobaciones::pendientes() es la lista de lo que espera esa decision. La pantalla de gracias NO dice «lo corregimos»: decirlo seria prometer por su cuenta algo que todavia no esta decidido</t>
+          <t>El planteamiento era poner un desplegable «CTS Peru / CTS Colombia» en la campana. No se hace, y el motivo esta en el esquema: uq_lec_country mas tg_lec_sin_solape_ins/upd garantizan que en cualquier fecha hay como mucho una sociedad cubriendo un pais, asi que el desplegable tendria siempre una opcion --y una opcion que se puede cambiar es una que alguien puede cambiar mal--. Ya existia campaigns.billing_legal_entity_id, resuelto a starts_on por Campanas::quienFactura() y congelado al confirmar por tg_camp_entidad_congelada. Lo que faltaba no era el campo: era decirlo. La ficha ahora dice quien factura Y su motivo --«CTS Peru factura a Peru desde el 2025-01-01 (sociedad local)»--, porque una sociedad a secas no se puede comprobar y con su motivo y su fecha quien la lee sabe si es la que esperaba y puede discutirla antes de que salga una factura. El formulario de alta no adelanta una respuesta: el pais del cliente y la fecha todavia no existen, y resolver «con la cobertura de hoy» para ensenarlo es justo el «deducirlo de la configuracion vigente» que prohibe BR-LE-001</t>
         </is>
       </c>
     </row>
     <row r="86" ht="57" customHeight="1" s="36">
       <c r="A86" s="67" t="inlineStr">
         <is>
-          <t>DEC-152</t>
+          <t>DEC-154</t>
         </is>
       </c>
       <c r="B86" s="68" t="inlineStr">
@@ -17363,24 +17450,24 @@
       <c r="C86" s="68" t="n"/>
       <c r="D86" s="69" t="inlineStr">
         <is>
-          <t>El silencio del cliente no hace nada, y por eso 8.5 no estrena comando.</t>
+          <t>Los ayudantes de las suites viven en UN archivo, y nace la SEPTIMA puerta.</t>
         </is>
       </c>
       <c r="E86" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="F86" s="69" t="inlineStr">
         <is>
-          <t>El enlace caduca, la pieza se queda donde estaba y sale en la bandeja. Nadie aprueba ni rechaza en nombre de nadie. «Silencio = aprobado» habria desbloqueado la campana sin perseguir a nadie y necesita estar escrito en el contrato: dar por buena una pieza que nadie miro es una firma que el sistema pone por el cliente, y de ahi cuelgan la publicacion y el pago. Y de ahi sale que no haga falta un comando de caducidad, al reves que en 7.6: alli una invitacion sin contestar dejaba dinero comprometido y una plaza de cupo ocupada --habia un estado del mundo que corregir-- y aqui expires_at &lt; NOW() basta. Un comando que no arregla nada es una linea de cron mas que mantener y una cosa mas que puede fallar en silencio</t>
+          <t>tools/pruebas/comun.sh y tools/verificar-suites.py. La puerta comprueba que toda suite listada existe, que ninguna define sus propios probar/valor/porque, que todas cargan comun.sh, y lleva un trinquete: cuantas aserciones negativas afirman POR QUE se rechaza y cuantas solo que algo fallo. Hoy son 89 con motivo y 297 sin el, y ese segundo numero solo puede bajar (tools/pruebas/MOTIVOS-BASE). No se convierten las 297 en esta iteracion --son veintidos suites de cuatro fases-- pero desde hoy no pueden ser 298, y ademas cada probar ... RECHAZO enseña en gris que restriccion respondio, para que el desajuste se vea al leer la salida. Es la leccion de T-48, T-50, T-51 y T-54: las cuatro fueron aserciones verdes por el motivo equivocado y las cuatro eran un probar ... RECHAZO a secas</t>
         </is>
       </c>
     </row>
     <row r="87" ht="68.25" customHeight="1" s="36">
       <c r="A87" s="67" t="inlineStr">
         <is>
-          <t>DEC-151</t>
+          <t>DEC-153</t>
         </is>
       </c>
       <c r="B87" s="68" t="inlineStr">
@@ -17391,7 +17478,7 @@
       <c r="C87" s="68" t="n"/>
       <c r="D87" s="69" t="inlineStr">
         <is>
-          <t>La respuesta del cliente se REGISTRA; el equipo cierra.</t>
+          <t>Una peticion de cambios sin rondas queda PENDIENTE de autorizar.</t>
         </is>
       </c>
       <c r="E87" s="69" t="inlineStr">
@@ -17401,14 +17488,14 @@
       </c>
       <c r="F87" s="69" t="inlineStr">
         <is>
-          <t>El cliente dice «me vale» o «cambiad esto» desde un enlace firmado, y eso queda escrito con su hora y su IP --pero no mueve el entregable--. La alternativa era que su OK aprobara la pieza directamente, y se descarto por dos razones. (a) Habria obligado a partir approved en dos estados: hoy significa «listo para publicar» y 8.6 publica desde ahi, asi que sin un «aprobado interno, esperando al cliente» el mismo estado significaria dos cosas --el fallo de T-50--. (b) Y la que decide: la correccion del cliente gasta ronda, y desde 8.4 una ronda de mas exige firma y decision de facturacion. El cliente no puede firmar un cargo contra si mismo. Si su respuesta moviera la pieza sola, o se le cobraria sin que nadie lo autorizara, o habria que dejarle una puerta por la que las rondas no se cuentan. La pantalla se lo dice con esas palabras: quien pulsa «me vale» y no ve nada moverse tiene derecho a saber que pasa despues</t>
+          <t>Se registra y no se convierte en ronda hasta que alguien del equipo decida si se le cobra o la absorbemos; al cliente se le confirma que su peticion llego --que es verdad-- sin prometerle que sera gratis. Cae solo del modelo de DEC-151: como la respuesta no crea la revision, no hay ronda que consumir hasta que una persona emite el veredicto. Aprobaciones::pendientes() es la lista de lo que espera esa decision. La pantalla de gracias NO dice «lo corregimos»: decirlo seria prometer por su cuenta algo que todavia no esta decidido</t>
         </is>
       </c>
     </row>
     <row r="88" ht="34.5" customHeight="1" s="36">
       <c r="A88" s="67" t="inlineStr">
         <is>
-          <t>DEC-150</t>
+          <t>DEC-152</t>
         </is>
       </c>
       <c r="B88" s="68" t="inlineStr">
@@ -17419,24 +17506,24 @@
       <c r="C88" s="68" t="n"/>
       <c r="D88" s="69" t="inlineStr">
         <is>
-          <t>El techo de rondas pasa a la base, y los disparadores siguen siendo GUARDAS.</t>
+          <t>El silencio del cliente no hace nada, y por eso 8.5 no estrena comando.</t>
         </is>
       </c>
       <c r="E88" s="69" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F88" s="69" t="inlineStr">
         <is>
-          <t>8.3 construyo el limite entero --rondas(), vetoParaRevisar(), content.extra_round, over_included, la cola con «quedan/incluidas»-- y lo dejo TODO en PHP. Tres reglas se estaban aplicando sin que nada las respaldara en el esquema: (a) ck_cvw_round no decia DE QUIEN era la correccion, asi que una revision nuestra podia gastarle una ronda al cliente --DEC-133 vivia solo en consumeRonda()--; (b) nada obligaba a over_included a decir la verdad, y esa columna es la que cargosPendientes() cuenta para facturar, o sea que una fila que miente ahi es una correccion que se trabaja y no se cobra; (c) el contador podia bajar, y bajarlo devuelve rondas ya gastadas sin la firma de nadie. tg_cvw_techo mira las DOS direcciones --agotadas sin declarar, y declarada sin estarlo-- y es cross-table, asi que un CHECK no puede verlo; lee el contador ANTES de que emitir() lo suba, que es el mismo valor con el que el servicio calculo su $exceso. Y no se hizo lo tentador: que el contador lo subiera un AFTER INSERT habria hecho imposible la desincronizacion, pero ninguno de los 504 disparadores de este esquema modifica una fila y un disparador que HACE cosas convierte el esquema en algo que actua a espaldas de quien lee el codigo. Habia fecha para esto: 8.5 escribe revisiones del cliente desde un enlace firmado, sin pasar por emitir()</t>
+          <t>El enlace caduca, la pieza se queda donde estaba y sale en la bandeja. Nadie aprueba ni rechaza en nombre de nadie. «Silencio = aprobado» habria desbloqueado la campana sin perseguir a nadie y necesita estar escrito en el contrato: dar por buena una pieza que nadie miro es una firma que el sistema pone por el cliente, y de ahi cuelgan la publicacion y el pago. Y de ahi sale que no haga falta un comando de caducidad, al reves que en 7.6: alli una invitacion sin contestar dejaba dinero comprometido y una plaza de cupo ocupada --habia un estado del mundo que corregir-- y aqui expires_at &lt; NOW() basta. Un comando que no arregla nada es una linea de cron mas que mantener y una cosa mas que puede fallar en silencio</t>
         </is>
       </c>
     </row>
     <row r="89" ht="57" customHeight="1" s="36">
       <c r="A89" s="67" t="inlineStr">
         <is>
-          <t>DEC-149</t>
+          <t>DEC-151</t>
         </is>
       </c>
       <c r="B89" s="68" t="inlineStr">
@@ -17447,24 +17534,24 @@
       <c r="C89" s="68" t="n"/>
       <c r="D89" s="69" t="inlineStr">
         <is>
-          <t>Se trabaja en main hasta que haya produccion.</t>
+          <t>La respuesta del cliente se REGISTRA; el equipo cierra.</t>
         </is>
       </c>
       <c r="E89" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F89" s="69" t="inlineStr">
         <is>
-          <t>La pregunta fue suya y era la correcta: *«no entiendo el sentido de tener varias ramas si al final haremos merge»*. Medido en el repositorio: main (4.9) -- 5.9 -- 7.6 -- 7.6b -- 7.7 -- 8.1 -- 8.1-8.7 -- 8.8 es una linea recta; nunca hubo dos cosas a la vez. Las tres ramas no eran tres caminos sino tres nombres sobre el mismo camino, y dos apuntaban a puntos ya superados --feat/5.9-4.1-enlace-contrasena es el PADRE de la rama de 7.6, comprobado, no supuesto--. De las cinco cosas para las que sirve una rama, hoy no aplica ninguna: un solo desarrollador, ninguna revision externa, nada desplegado, y el CI que podria opinar antes ya lo hace php tools/diagnostico.php en la maquina. Y el coste si se pagaba: la rama que existia para proteger main lo dejo nueve iteraciones obsoleto, o sea mintiendo a quien clonara. Eso es la ceremonia sin ninguno de los beneficios. Lo que sustituye a la rama no es la confianza, son las seis puertas: no se commitea en rojo. Se revierte el dia que haya produccion, y entonces una rama por iteracion fusionada el mismo dia; lo que no se repite nunca es la rama larga que acumula iteraciones, que no es una rama sino un main con otro nombre. De paso, develop sale del on: push del CI: esa rama no ha existido jamas, y CONTRIBUTING.md la nombraba desde el principio</t>
+          <t>El cliente dice «me vale» o «cambiad esto» desde un enlace firmado, y eso queda escrito con su hora y su IP --pero no mueve el entregable--. La alternativa era que su OK aprobara la pieza directamente, y se descarto por dos razones. (a) Habria obligado a partir approved en dos estados: hoy significa «listo para publicar» y 8.6 publica desde ahi, asi que sin un «aprobado interno, esperando al cliente» el mismo estado significaria dos cosas --el fallo de T-50--. (b) Y la que decide: la correccion del cliente gasta ronda, y desde 8.4 una ronda de mas exige firma y decision de facturacion. El cliente no puede firmar un cargo contra si mismo. Si su respuesta moviera la pieza sola, o se le cobraria sin que nadie lo autorizara, o habria que dejarle una puerta por la que las rondas no se cuentan. La pantalla se lo dice con esas palabras: quien pulsa «me vale» y no ve nada moverse tiene derecho a saber que pasa despues</t>
         </is>
       </c>
     </row>
     <row r="90" ht="45.75" customHeight="1" s="36">
       <c r="A90" s="67" t="inlineStr">
         <is>
-          <t>DEC-148</t>
+          <t>DEC-150</t>
         </is>
       </c>
       <c r="B90" s="68" t="inlineStr">
@@ -17475,24 +17562,24 @@
       <c r="C90" s="68" t="n"/>
       <c r="D90" s="69" t="inlineStr">
         <is>
-          <t>El entregable caido tiene estado propio, y expired pasa a llamarse fulfilled.</t>
+          <t>El techo de rondas pasa a la base, y los disparadores siguen siendo GUARDAS.</t>
         </is>
       </c>
       <c r="E90" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="F90" s="69" t="inlineStr">
         <is>
-          <t>Devolver el entregable a published bastaba para que no cobre, y estaba mal: published significa «esperando a que alguien lo mire» y el dia que F9 construya esa cola meteria incumplimientos dentro --un estado que significa dos cosas es el fallo de T-50--. ck_del_status gana removed, y los dos disparadores que definen «entregable cerrado» lo tratan como cerrado; sin eso se le podria subir una version nueva encima o emitir un veredicto sobre el, y el incumplimiento se disolveria solo. Aparte: ck_pub_status tenia expired desde 2.12 con CERO filas y con un nombre que se lee al reves de lo que significa --la ventana cumplida es lo BUENO, es lo que habilita el pago-- asi que se renombra ahora, que no cuesta nada; con mil filas habria costado una migracion de datos y una discusion. De paso, permanence_checks entra en la lista de 3.12: el criterio de T-16 la incluia desde el primer dia --la fila es evidencia y de ella depende dinero-- y nadie la habia mirado</t>
+          <t>8.3 construyo el limite entero --rondas(), vetoParaRevisar(), content.extra_round, over_included, la cola con «quedan/incluidas»-- y lo dejo TODO en PHP. Tres reglas se estaban aplicando sin que nada las respaldara en el esquema: (a) ck_cvw_round no decia DE QUIEN era la correccion, asi que una revision nuestra podia gastarle una ronda al cliente --DEC-133 vivia solo en consumeRonda()--; (b) nada obligaba a over_included a decir la verdad, y esa columna es la que cargosPendientes() cuenta para facturar, o sea que una fila que miente ahi es una correccion que se trabaja y no se cobra; (c) el contador podia bajar, y bajarlo devuelve rondas ya gastadas sin la firma de nadie. tg_cvw_techo mira las DOS direcciones --agotadas sin declarar, y declarada sin estarlo-- y es cross-table, asi que un CHECK no puede verlo; lee el contador ANTES de que emitir() lo suba, que es el mismo valor con el que el servicio calculo su $exceso. Y no se hizo lo tentador: que el contador lo subiera un AFTER INSERT habria hecho imposible la desincronizacion, pero ninguno de los 504 disparadores de este esquema modifica una fila y un disparador que HACE cosas convierte el esquema en algo que actua a espaldas de quien lee el codigo. Habia fecha para esto: 8.5 escribe revisiones del cliente desde un enlace firmado, sin pasar por emitir()</t>
         </is>
       </c>
     </row>
     <row r="91" ht="45.75" customHeight="1" s="36">
       <c r="A91" s="67" t="inlineStr">
         <is>
-          <t>DEC-147</t>
+          <t>DEC-149</t>
         </is>
       </c>
       <c r="B91" s="68" t="inlineStr">
@@ -17503,7 +17590,7 @@
       <c r="C91" s="68" t="n"/>
       <c r="D91" s="69" t="inlineStr">
         <is>
-          <t>Se avisa al creador y al equipo; al cliente no.</t>
+          <t>Se trabaja en main hasta que haya produccion.</t>
         </is>
       </c>
       <c r="E91" s="69" t="inlineStr">
@@ -17513,14 +17600,14 @@
       </c>
       <c r="F91" s="69" t="inlineStr">
         <is>
-          <t>El creador tiene algo que hacer --reponer el post, decir que la cuenta se puso privada, o decir que lo bajo-- y el equipo lo ve en su bandeja sin que nadie le mande nada. El cliente no se entera hasta que hay algo confirmado: avisarle de un falso positivo cuesta mas que el propio incidente. El correo no dice «incumpliste», dice «no lo encontramos», y dice expresamente que el pago esta en pausa: enterarse de eso cuando no llega el dinero es peor que enterarse ahora</t>
+          <t>La pregunta fue suya y era la correcta: *«no entiendo el sentido de tener varias ramas si al final haremos merge»*. Medido en el repositorio: main (4.9) -- 5.9 -- 7.6 -- 7.6b -- 7.7 -- 8.1 -- 8.1-8.7 -- 8.8 es una linea recta; nunca hubo dos cosas a la vez. Las tres ramas no eran tres caminos sino tres nombres sobre el mismo camino, y dos apuntaban a puntos ya superados --feat/5.9-4.1-enlace-contrasena es el PADRE de la rama de 7.6, comprobado, no supuesto--. De las cinco cosas para las que sirve una rama, hoy no aplica ninguna: un solo desarrollador, ninguna revision externa, nada desplegado, y el CI que podria opinar antes ya lo hace php tools/diagnostico.php en la maquina. Y el coste si se pagaba: la rama que existia para proteger main lo dejo nueve iteraciones obsoleto, o sea mintiendo a quien clonara. Eso es la ceremonia sin ninguno de los beneficios. Lo que sustituye a la rama no es la confianza, son las seis puertas: no se commitea en rojo. Se revierte el dia que haya produccion, y entonces una rama por iteracion fusionada el mismo dia; lo que no se repite nunca es la rama larga que acumula iteraciones, que no es una rama sino un main con otro nombre. De paso, develop sale del on: push del CI: esa rama no ha existido jamas, y CONTRIBUTING.md la nombraba desde el principio</t>
         </is>
       </c>
     </row>
     <row r="92" ht="34.5" customHeight="1" s="36">
       <c r="A92" s="67" t="inlineStr">
         <is>
-          <t>DEC-146</t>
+          <t>DEC-148</t>
         </is>
       </c>
       <c r="B92" s="68" t="inlineStr">
@@ -17531,7 +17618,7 @@
       <c r="C92" s="68" t="n"/>
       <c r="D92" s="69" t="inlineStr">
         <is>
-          <t>La sonda marca; una persona confirma.</t>
+          <t>El entregable caido tiene estado propio, y expired pasa a llamarse fulfilled.</t>
         </is>
       </c>
       <c r="E92" s="69" t="inlineStr">
@@ -17541,14 +17628,14 @@
       </c>
       <c r="F92" s="69" t="inlineStr">
         <is>
-          <t>Es DEC-142 otra vez y por lo mismo --Instagram y TikTok responden igual ante un post borrado, un perfil en privado y un bloqueo geografico-- pero aqui duele mas: en 8.7 un falso negativo retrasa una verificacion, aqui acusa a un creador de incumplir un contrato. Asi que Permanencia::anotar() archiva la comprobacion y no toca publications, y lo que mueve una publicacion a removed es una persona con tg_pub_permanencia exigiendole DOS cosas: una comprobacion con is_live = 0 y una captura tomada DESPUES de haber verificado el post. La segunda condicion es la que costo pensar: la captura vieja probo que el post existia, y reutilizarla como prueba de que ya no esta seria archivar lo contrario de lo que ensena. El comando permanencia:vigilar no sale a Internet: cierra ventanas cumplidas --comparar una fecha con el calendario si lo puede hacer solo, y es lo que habilita el pago-- y cuenta las desatendidas. La comprobacion automatica buena son las APIs oficiales, que son F12</t>
+          <t>Devolver el entregable a published bastaba para que no cobre, y estaba mal: published significa «esperando a que alguien lo mire» y el dia que F9 construya esa cola meteria incumplimientos dentro --un estado que significa dos cosas es el fallo de T-50--. ck_del_status gana removed, y los dos disparadores que definen «entregable cerrado» lo tratan como cerrado; sin eso se le podria subir una version nueva encima o emitir un veredicto sobre el, y el incumplimiento se disolveria solo. Aparte: ck_pub_status tenia expired desde 2.12 con CERO filas y con un nombre que se lee al reves de lo que significa --la ventana cumplida es lo BUENO, es lo que habilita el pago-- asi que se renombra ahora, que no cuesta nada; con mil filas habria costado una migracion de datos y una discusion. De paso, permanence_checks entra en la lista de 3.12: el criterio de T-16 la incluia desde el primer dia --la fila es evidencia y de ella depende dinero-- y nadie la habia mirado</t>
         </is>
       </c>
     </row>
     <row r="93" ht="45.75" customHeight="1" s="36">
       <c r="A93" s="67" t="inlineStr">
         <is>
-          <t>DEC-145</t>
+          <t>DEC-147</t>
         </is>
       </c>
       <c r="B93" s="68" t="inlineStr">
@@ -17559,7 +17646,7 @@
       <c r="C93" s="68" t="n"/>
       <c r="D93" s="69" t="inlineStr">
         <is>
-          <t>Retirar el post antes de tiempo BLOQUEA el pago, y el sistema no descuenta nada.</t>
+          <t>Se avisa al creador y al equipo; al cliente no.</t>
         </is>
       </c>
       <c r="E93" s="69" t="inlineStr">
@@ -17569,14 +17656,14 @@
       </c>
       <c r="F93" s="69" t="inlineStr">
         <is>
-          <t>BR-CONTENT-006 decia que el sistema alerta y no decia nada del dinero, que es donde deja de ser tecnico. Las otras dos opciones se descartaron: el descuento proporcional automatico exige que el contrato lo diga por escrito Y que la deteccion sea fiable --y lo segundo hoy no se cumple, ver DEC-146--; solo alertar deja al cliente sin palanca, porque el post se retira, se cobra igual y la unica consecuencia es un correo. Lo que hace: la publicacion pasa a removed con motivo, firma y fecha; el entregable pasa a removed --sale de verified, que es de donde F9 va a pagar--; y ahi se para. La decision de que se le paga la toma una persona con el expediente montado delante. test_firmar_la_caida_para_el_pago_y_no_descuenta_nada afirma las DOS mitades: que el entregable sale de verificado y que el importe acordado sigue intacto. La segunda es la que impide que alguien «mejore» esto manana metiendo una regla de tres</t>
+          <t>El creador tiene algo que hacer --reponer el post, decir que la cuenta se puso privada, o decir que lo bajo-- y el equipo lo ve en su bandeja sin que nadie le mande nada. El cliente no se entera hasta que hay algo confirmado: avisarle de un falso positivo cuesta mas que el propio incidente. El correo no dice «incumpliste», dice «no lo encontramos», y dice expresamente que el pago esta en pausa: enterarse de eso cuando no llega el dinero es peor que enterarse ahora</t>
         </is>
       </c>
     </row>
     <row r="94" ht="45.75" customHeight="1" s="36">
       <c r="A94" s="67" t="inlineStr">
         <is>
-          <t>DEC-144</t>
+          <t>DEC-146</t>
         </is>
       </c>
       <c r="B94" s="68" t="inlineStr">
@@ -17587,24 +17674,24 @@
       <c r="C94" s="68" t="n"/>
       <c r="D94" s="69" t="inlineStr">
         <is>
-          <t>Si el post no esta, el entregable vuelve al CREADOR, no a revision.</t>
+          <t>La sonda marca; una persona confirma.</t>
         </is>
       </c>
       <c r="E94" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F94" s="69" t="inlineStr">
         <is>
-          <t>La publicacion queda rejected con su motivo y el entregable vuelve a approved. El contenido no tenia nada malo --ya se aprobo--: lo que falla es que no esta publicado, asi que lo que hay que rehacer es el ENLACE y no la pieza. Reabrir el entregable entero seria mas duro de lo necesario y dejarlo rechazado sin mas deja una campana con una pieza que nadie va a mover. Motivo de lista cerrada, como en 7.6 y 8.2, para poder contestar «.por que se caen las publicaciones?» con un numero. Y se le avisa por correo con el motivo dentro; el correo dice «no lo encontramos» y no «no publicaste», que es la diferencia que importa cuando la cuenta era privada o el enlace se copio mal. Verificar NO manda correo: no le pide nada, su parte termino</t>
+          <t>Es DEC-142 otra vez y por lo mismo --Instagram y TikTok responden igual ante un post borrado, un perfil en privado y un bloqueo geografico-- pero aqui duele mas: en 8.7 un falso negativo retrasa una verificacion, aqui acusa a un creador de incumplir un contrato. Asi que Permanencia::anotar() archiva la comprobacion y no toca publications, y lo que mueve una publicacion a removed es una persona con tg_pub_permanencia exigiendole DOS cosas: una comprobacion con is_live = 0 y una captura tomada DESPUES de haber verificado el post. La segunda condicion es la que costo pensar: la captura vieja probo que el post existia, y reutilizarla como prueba de que ya no esta seria archivar lo contrario de lo que ensena. El comando permanencia:vigilar no sale a Internet: cierra ventanas cumplidas --comparar una fecha con el calendario si lo puede hacer solo, y es lo que habilita el pago-- y cuenta las desatendidas. La comprobacion automatica buena son las APIs oficiales, que son F12</t>
         </is>
       </c>
     </row>
     <row r="95" ht="57" customHeight="1" s="36">
       <c r="A95" s="67" t="inlineStr">
         <is>
-          <t>DEC-143</t>
+          <t>DEC-145</t>
         </is>
       </c>
       <c r="B95" s="68" t="inlineStr">
@@ -17615,24 +17702,24 @@
       <c r="C95" s="68" t="n"/>
       <c r="D95" s="69" t="inlineStr">
         <is>
-          <t>Verificar tiene su propio permiso, content.verify.</t>
+          <t>Retirar el post antes de tiempo BLOQUEA el pago, y el sistema no descuenta nada.</t>
         </is>
       </c>
       <c r="E95" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F95" s="69" t="inlineStr">
         <is>
-          <t>Mismo criterio que separo revisar de aprobar en 8.3: de verified cuelga el pago, asi que es una firma con dinero detras. Lo tienen campaign_manager y content_reviewer; finanzas NO, porque paga contra lo verificado y darle el permiso convertiria una comprobacion en una autoaprobacion. Se comprueba en el POST y no solo escondiendo el boton: los dos veredictos llegan por el mismo formulario</t>
+          <t>BR-CONTENT-006 decia que el sistema alerta y no decia nada del dinero, que es donde deja de ser tecnico. Las otras dos opciones se descartaron: el descuento proporcional automatico exige que el contrato lo diga por escrito Y que la deteccion sea fiable --y lo segundo hoy no se cumple, ver DEC-146--; solo alertar deja al cliente sin palanca, porque el post se retira, se cobra igual y la unica consecuencia es un correo. Lo que hace: la publicacion pasa a removed con motivo, firma y fecha; el entregable pasa a removed --sale de verified, que es de donde F9 va a pagar--; y ahi se para. La decision de que se le paga la toma una persona con el expediente montado delante. test_firmar_la_caida_para_el_pago_y_no_descuenta_nada afirma las DOS mitades: que el entregable sale de verificado y que el importe acordado sigue intacto. La segunda es la que impide que alguien «mejore» esto manana metiendo una regla de tres</t>
         </is>
       </c>
     </row>
     <row r="96" ht="57" customHeight="1" s="36">
       <c r="A96" s="67" t="inlineStr">
         <is>
-          <t>DEC-142</t>
+          <t>DEC-144</t>
         </is>
       </c>
       <c r="B96" s="68" t="inlineStr">
@@ -17643,7 +17730,7 @@
       <c r="C96" s="68" t="n"/>
       <c r="D96" s="69" t="inlineStr">
         <is>
-          <t>La evidencia de que un post existe es una CAPTURA, no una comprobacion HTTP.</t>
+          <t>Si el post no esta, el entregable vuelve al CREADOR, no a revision.</t>
         </is>
       </c>
       <c r="E96" s="69" t="inlineStr">
@@ -17653,14 +17740,14 @@
       </c>
       <c r="F96" s="69" t="inlineStr">
         <is>
-          <t>Tomada con la limitacion delante: Instagram y TikTok devuelven 200 con un muro de login, 403 a todo lo que no sea un navegador, y 200 otra vez cuando el post no existe. Un http_status no distingue «el post existe» de «nos bloquearon», y BR-CONTENT-004 es 🔴 --de verified cuelga el pago--. Asi que lo que se archiva es un screenshot con file_id y tg_pub_verificada_con_evidencia lo impone en la base; la sonda HTTP se guarda como dato complementario y NO decide. Lo que si automatizaria esto son las APIs oficiales --Instagram Graph, TikTok--, que exigen app revisada por Meta y tokens del creador: semanas, y son F12; elegirlas ahora dejaria 8.7, 8.8 y el pago bloqueados hasta entonces. El dia que existan cambia la forma de capturar, no el modelo: publication_evidence ya admite api_snapshot. §56 del prompt maestro pide exactamente esto: no disenar sobre algo extremadamente fragil</t>
+          <t>La publicacion queda rejected con su motivo y el entregable vuelve a approved. El contenido no tenia nada malo --ya se aprobo--: lo que falla es que no esta publicado, asi que lo que hay que rehacer es el ENLACE y no la pieza. Reabrir el entregable entero seria mas duro de lo necesario y dejarlo rechazado sin mas deja una campana con una pieza que nadie va a mover. Motivo de lista cerrada, como en 7.6 y 8.2, para poder contestar «.por que se caen las publicaciones?» con un numero. Y se le avisa por correo con el motivo dentro; el correo dice «no lo encontramos» y no «no publicaste», que es la diferencia que importa cuando la cuenta era privada o el enlace se copio mal. Verificar NO manda correo: no le pide nada, su parte termino</t>
         </is>
       </c>
     </row>
     <row r="97" ht="57" customHeight="1" s="36">
       <c r="A97" s="67" t="inlineStr">
         <is>
-          <t>DEC-141</t>
+          <t>DEC-143</t>
         </is>
       </c>
       <c r="B97" s="68" t="inlineStr">
@@ -17671,24 +17758,24 @@
       <c r="C97" s="68" t="n"/>
       <c r="D97" s="69" t="inlineStr">
         <is>
-          <t>La red se DEDUCE del enlace, y tiene que ser la del brief.</t>
+          <t>Verificar tiene su propio permiso, content.verify.</t>
         </is>
       </c>
       <c r="E97" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F97" s="69" t="inlineStr">
         <is>
-          <t>El brief compro un reel de Instagram; un TikTok no es eso, por bueno que sea. La red no se pregunta --un desplegable en el formulario solo sirve para que alguien elija mal, y el enlace ya lo dice--: sale de platforms.url_pattern, que es una expresion regular y vive en el catalogo desde 2.6 sin que la usara nadie. Si el enlace no es de ninguna red conocida, tampoco entra. Y la huella: uq_pub_fingerprint existe desde la Fase 2 para que dos creadores no reclamen el mismo post, y con la URL cruda no impediria nada --?utm_source=ig basta para esquivarla--. Se normaliza antes de firmar: esquema y host a minusculas, www. fuera, barra final fuera, fragmento fuera, parametros de MEDICION fuera y el resto ordenados. Lo que identifica el post no se toca: la ruta conserva mayusculas --/p/AbC y /p/abc son dos posts-- y la lista de parametros a quitar es explicita, porque youtube.com/watch?v= lleva el identificador en la query y borrar la query entera fundiria todos los videos del canal en una huella. Esa es la mitad que hace dano: rechazar un post legitimo diciendo que ya esta reclamado. La URL se guarda TAL CUAL: la huella es para comparar, no para sustituir</t>
+          <t>Mismo criterio que separo revisar de aprobar en 8.3: de verified cuelga el pago, asi que es una firma con dinero detras. Lo tienen campaign_manager y content_reviewer; finanzas NO, porque paga contra lo verificado y darle el permiso convertiria una comprobacion en una autoaprobacion. Se comprueba en el POST y no solo escondiendo el boton: los dos veredictos llegan por el mismo formulario</t>
         </is>
       </c>
     </row>
     <row r="98" ht="34.5" customHeight="1" s="36">
       <c r="A98" s="67" t="inlineStr">
         <is>
-          <t>DEC-140</t>
+          <t>DEC-142</t>
         </is>
       </c>
       <c r="B98" s="68" t="inlineStr">
@@ -17699,24 +17786,24 @@
       <c r="C98" s="68" t="n"/>
       <c r="D98" s="69" t="inlineStr">
         <is>
-          <t>Solo se publica lo aprobado, y ESA version.</t>
+          <t>La evidencia de que un post existe es una CAPTURA, no una comprobacion HTTP.</t>
         </is>
       </c>
       <c r="E98" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F98" s="69" t="inlineStr">
         <is>
-          <t>BR-CONTENT-002 dice que nada llega al cliente sin aprobacion interna, y registrar la publicacion de algo no aprobado es darlo por bueno a posteriori con la firma de nadie. No basta con «el entregable esta aprobado»: se guarda QUE version se publico y tiene que ser la aprobada (tg_pub_version_aprobada), porque de esta fila cuelga el pago --8.7 la verifica y 8.8 cuenta su permanencia--. publications.deliverable_version_id es un SNAPSHOT, igual que amount_snapshot en 7.6: registra lo que se publico ENTONCES y sobrevive a que el entregable se reabra y se apruebe otra version despues, asi que se guarda aunque el puntero de 8.2 diga cual es la aprobada de hoy. Su clave ajena es COMPUESTA, como la de 8.2. Detalle que la suite dice en voz alta: al INSERTAR gana el disparador --la version de otro entregable nunca puede ser la aprobada de este-- y donde la clave se ve sola es en un UPDATE, porque el disparador es BEFORE INSERT y no los mira; ahi esta su asercion, y no en un caso inventado que nunca pasa</t>
+          <t>Tomada con la limitacion delante: Instagram y TikTok devuelven 200 con un muro de login, 403 a todo lo que no sea un navegador, y 200 otra vez cuando el post no existe. Un http_status no distingue «el post existe» de «nos bloquearon», y BR-CONTENT-004 es 🔴 --de verified cuelga el pago--. Asi que lo que se archiva es un screenshot con file_id y tg_pub_verificada_con_evidencia lo impone en la base; la sonda HTTP se guarda como dato complementario y NO decide. Lo que si automatizaria esto son las APIs oficiales --Instagram Graph, TikTok--, que exigen app revisada por Meta y tokens del creador: semanas, y son F12; elegirlas ahora dejaria 8.7, 8.8 y el pago bloqueados hasta entonces. El dia que existan cambia la forma de capturar, no el modelo: publication_evidence ya admite api_snapshot. §56 del prompt maestro pide exactamente esto: no disenar sobre algo extremadamente fragil</t>
         </is>
       </c>
     </row>
     <row r="99" ht="57" customHeight="1" s="36">
       <c r="A99" s="67" t="inlineStr">
         <is>
-          <t>DEC-139</t>
+          <t>DEC-141</t>
         </is>
       </c>
       <c r="B99" s="68" t="inlineStr">
@@ -17727,7 +17814,7 @@
       <c r="C99" s="68" t="n"/>
       <c r="D99" s="69" t="inlineStr">
         <is>
-          <t>El post lo reporta el CREADOR, y el equipo tambien puede.</t>
+          <t>La red se DEDUCE del enlace, y tiene que ser la del brief.</t>
         </is>
       </c>
       <c r="E99" s="69" t="inlineStr">
@@ -17737,14 +17824,14 @@
       </c>
       <c r="F99" s="69" t="inlineStr">
         <is>
-          <t>El creador es quien lo sabe primero y quien tiene el enlace en la mano: lo pega en su portal en cuanto publica. Y el equipo puede hacerlo por el, porque el caso real existe --el enlace llega por WhatsApp y el creador no entra--. Las alternativas eran peores por el mismo motivo en direcciones opuestas: solo el equipo convierte cada publicacion en una tarea nuestra --con 150 creadores, 150 tareas que perseguir-- y solo el creador deja sin camino el caso de «me lo mando por WhatsApp». Las dos puertas pasan por el MISMO servicio y el MISMO veto; solo cambia quien firma reported_by_user_id. Una segunda puerta con sus propias reglas es una segunda puerta con sus propios agujeros</t>
+          <t>El brief compro un reel de Instagram; un TikTok no es eso, por bueno que sea. La red no se pregunta --un desplegable en el formulario solo sirve para que alguien elija mal, y el enlace ya lo dice--: sale de platforms.url_pattern, que es una expresion regular y vive en el catalogo desde 2.6 sin que la usara nadie. Si el enlace no es de ninguna red conocida, tampoco entra. Y la huella: uq_pub_fingerprint existe desde la Fase 2 para que dos creadores no reclamen el mismo post, y con la URL cruda no impediria nada --?utm_source=ig basta para esquivarla--. Se normaliza antes de firmar: esquema y host a minusculas, www. fuera, barra final fuera, fragmento fuera, parametros de MEDICION fuera y el resto ordenados. Lo que identifica el post no se toca: la ruta conserva mayusculas --/p/AbC y /p/abc son dos posts-- y la lista de parametros a quitar es explicita, porque youtube.com/watch?v= lleva el identificador en la query y borrar la query entera fundiria todos los videos del canal en una huella. Esa es la mitad que hace dano: rechazar un post legitimo diciendo que ya esta reclamado. La URL se guarda TAL CUAL: la huella es para comparar, no para sustituir</t>
         </is>
       </c>
     </row>
     <row r="100" ht="34.5" customHeight="1" s="36">
       <c r="A100" s="67" t="inlineStr">
         <is>
-          <t>DEC-138</t>
+          <t>DEC-140</t>
         </is>
       </c>
       <c r="B100" s="68" t="inlineStr">
@@ -17755,24 +17842,24 @@
       <c r="C100" s="68" t="n"/>
       <c r="D100" s="69" t="inlineStr">
         <is>
-          <t>Un entregable aprobado se puede REABRIR, con motivo de lista cerrada y firma.</t>
+          <t>Solo se publica lo aprobado, y ESA version.</t>
         </is>
       </c>
       <c r="E100" s="69" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F100" s="69" t="inlineStr">
         <is>
-          <t>Con 8.3 era un callejon sin salida --ni mas veredictos ni mas versiones-- y el cliente cambia de opinion y a veces se aprueba por error: el unico camino cuando eso pasara, y va a pasar, era que alguien tocara la base a mano. Reabrir no deshace nada: es otra fila en content_reviews con outcome='reopened', su motivo y su firma, y la aprobacion anterior se queda en el historial. Misma forma que la anulacion de un perfil fiscal en 3.11, y por la misma razon: el registro tiene que contestar «.que paso?» y no solo «.como esta ahora?». El motivo es de lista cerrada para poder contestar «.por que se reabren las piezas?» con un numero --si el 70% es «se aprobo por error», el problema es la pantalla de revision y no el cliente-- y «otro» exige explicacion, porque «otro» sin explicar es la casilla que se marca para poder seguir. El permiso lo tienen los DOS roles que revisan: «se aprobo por error» lo descubre normalmente quien aprobo, y obligarle a pedirselo a otro convierte un clic en un correo --y en la practica, en que nadie lo arregle--. Reabrir no gasta ronda: la gasta pedir un cambio, y aqui todavia no se ha pedido ninguno</t>
+          <t>BR-CONTENT-002 dice que nada llega al cliente sin aprobacion interna, y registrar la publicacion de algo no aprobado es darlo por bueno a posteriori con la firma de nadie. No basta con «el entregable esta aprobado»: se guarda QUE version se publico y tiene que ser la aprobada (tg_pub_version_aprobada), porque de esta fila cuelga el pago --8.7 la verifica y 8.8 cuenta su permanencia--. publications.deliverable_version_id es un SNAPSHOT, igual que amount_snapshot en 7.6: registra lo que se publico ENTONCES y sobrevive a que el entregable se reabra y se apruebe otra version despues, asi que se guarda aunque el puntero de 8.2 diga cual es la aprobada de hoy. Su clave ajena es COMPUESTA, como la de 8.2. Detalle que la suite dice en voz alta: al INSERTAR gana el disparador --la version de otro entregable nunca puede ser la aprobada de este-- y donde la clave se ve sola es en un UPDATE, porque el disparador es BEFORE INSERT y no los mira; ahi esta su asercion, y no en un caso inventado que nunca pasa</t>
         </is>
       </c>
     </row>
     <row r="101" ht="34.5" customHeight="1" s="36">
       <c r="A101" s="67" t="inlineStr">
         <is>
-          <t>DEC-137</t>
+          <t>DEC-139</t>
         </is>
       </c>
       <c r="B101" s="68" t="inlineStr">
@@ -17783,24 +17870,24 @@
       <c r="C101" s="68" t="n"/>
       <c r="D101" s="69" t="inlineStr">
         <is>
-          <t>El puntero apunta a la version APROBADA, y su clave ajena es COMPUESTA.</t>
+          <t>El post lo reporta el CREADOR, y el equipo tambien puede.</t>
         </is>
       </c>
       <c r="E101" s="69" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F101" s="69" t="inlineStr">
         <is>
-          <t>«La ultima» sale de un MAX(version_number) y guardarla seria una copia que se puede desviar --el proyecto acaba de quitar una columna por eso mismo, el contador de rondas de 8.3--. La aprobada no es derivable sin recorrer content_reviews, y es el dato del que cuelgan 8.6 --se publica lo aprobado-- y 8.7 --se archiva evidencia de eso--; sin ella las dos tendrian que adivinar cual. Y ahi esta casi todo el valor: FOREIGN KEY (approved_version_id, id) REFERENCES deliverable_versions(id, deliverable_id). Una clave simple garantizaria que la version EXISTE; esta garantiza que es DE ESTE ENTREGABLE --sin la segunda columna, un UPDATE mal escrito deja el entregable de Ana apuntando a la version aprobada del de Luis y la fila sigue siendo valida--. Mismo patron que fk_ccr_market_campaign (7.3). Ademas impide borrar la version apuntada mientras siga aprobada, y ck_del_approved_version exige que aprobado y puntero vayan juntos o no vayan: un dato que a veces esta es igual de util que no tenerlo. La columna espero dos iteraciones a proposito: antes de 8.3 no habia nadie que la escribiera, y habria sido el sexto caso de una columna que existe y no tiene una sola fila</t>
+          <t>El creador es quien lo sabe primero y quien tiene el enlace en la mano: lo pega en su portal en cuanto publica. Y el equipo puede hacerlo por el, porque el caso real existe --el enlace llega por WhatsApp y el creador no entra--. Las alternativas eran peores por el mismo motivo en direcciones opuestas: solo el equipo convierte cada publicacion en una tarea nuestra --con 150 creadores, 150 tareas que perseguir-- y solo el creador deja sin camino el caso de «me lo mando por WhatsApp». Las dos puertas pasan por el MISMO servicio y el MISMO veto; solo cambia quien firma reported_by_user_id. Una segunda puerta con sus propias reglas es una segunda puerta con sus propios agujeros</t>
         </is>
       </c>
     </row>
     <row r="102" ht="57" customHeight="1" s="36">
       <c r="A102" s="67" t="inlineStr">
         <is>
-          <t>DEC-136</t>
+          <t>DEC-138</t>
         </is>
       </c>
       <c r="B102" s="68" t="inlineStr">
@@ -17811,24 +17898,24 @@
       <c r="C102" s="68" t="n"/>
       <c r="D102" s="69" t="inlineStr">
         <is>
-          <t>Tres permisos y no uno: revisar, aprobar y autorizar una ronda de mas.</t>
+          <t>Un entregable aprobado se puede REABRIR, con motivo de lista cerrada y firma.</t>
         </is>
       </c>
       <c r="E102" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="F102" s="69" t="inlineStr">
         <is>
-          <t>content.review abre la cola y pide cambios; content.approve da el visto bueno --lo que deja el contenido listo para el cliente y, con F9, lo que dispara el pago--; content.extra_round autoriza el cargo. Mismo criterio que separo capturar de aprobar en el perfil fiscal (DEC-062). content_reviewer tiene los dos primeros y no el tercero: esa decision es de dinero --o se le cobra al cliente o se come el margen-- y quien revisa contenido no tiene por que cargar con ella; la tiene campaign_manager, que responde del margen y es quien va a tener que explicarsela al cliente. Los tres se comprueban en el POST y no solo en la ruta: los tres botones llegan por el mismo formulario, y esconder un boton no es una regla de autorizacion. Y la cola es una BANDEJA GLOBAL, no una por campana: revisar es trabajo por lotes, y una cola por campana obliga a recorrer campanas para descubrir si hay algo esperando --lo que se descubre recorriendo se descubre tarde--. Ordenada por lo que lleva mas esperando y no por lo que vence antes, que es como una cola deja a alguien esperando para siempre</t>
+          <t>Con 8.3 era un callejon sin salida --ni mas veredictos ni mas versiones-- y el cliente cambia de opinion y a veces se aprueba por error: el unico camino cuando eso pasara, y va a pasar, era que alguien tocara la base a mano. Reabrir no deshace nada: es otra fila en content_reviews con outcome='reopened', su motivo y su firma, y la aprobacion anterior se queda en el historial. Misma forma que la anulacion de un perfil fiscal en 3.11, y por la misma razon: el registro tiene que contestar «.que paso?» y no solo «.como esta ahora?». El motivo es de lista cerrada para poder contestar «.por que se reabren las piezas?» con un numero --si el 70% es «se aprobo por error», el problema es la pantalla de revision y no el cliente-- y «otro» exige explicacion, porque «otro» sin explicar es la casilla que se marca para poder seguir. El permiso lo tienen los DOS roles que revisan: «se aprobo por error» lo descubre normalmente quien aprobo, y obligarle a pedirselo a otro convierte un clic en un correo --y en la practica, en que nadie lo arregle--. Reabrir no gasta ronda: la gasta pedir un cambio, y aqui todavia no se ha pedido ninguno</t>
         </is>
       </c>
     </row>
     <row r="103" ht="68.25" customHeight="1" s="36">
       <c r="A103" s="67" t="inlineStr">
         <is>
-          <t>DEC-135</t>
+          <t>DEC-137</t>
         </is>
       </c>
       <c r="B103" s="68" t="inlineStr">
@@ -17839,24 +17926,24 @@
       <c r="C103" s="68" t="n"/>
       <c r="D103" s="69" t="inlineStr">
         <is>
-          <t>Pasarse de las rondas incluidas se BLOQUEA y exige decidir y firmar; y el cargo NO va a campaign_costs.</t>
+          <t>El puntero apunta a la version APROBADA, y su clave ajena es COMPUESTA.</t>
         </is>
       </c>
       <c r="E103" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="F103" s="69" t="inlineStr">
         <is>
-          <t>No un aviso: un aviso que se puede saltar acaba en un cargo que se descubre al facturar, que es tarde para discutirlo con el cliente. Cuando la ronda que se va a pedir es la tercera de dos incluidas hay que decir si se cobra o se absorbe, y quien lo dice queda en authorized_by_user_id (ck_cvw_over, en la base y no solo en la pantalla). campaign_costs seria el sitio equivocado y era tentador: es lo que gastamos NOSOTROS y resta del margen (BR-FIN-011), mientras que una ronda de mas facturada al cliente es INGRESO --meterla ahi bajaria el margen de una campana que acaba de ganar dinero--. Aqui queda la decision y la pantalla de entregables la ensena como pendiente de facturar; donde acaba la linea cuando exista F9 es Q-57, y se decide con invoice_lines delante</t>
+          <t>«La ultima» sale de un MAX(version_number) y guardarla seria una copia que se puede desviar --el proyecto acaba de quitar una columna por eso mismo, el contador de rondas de 8.3--. La aprobada no es derivable sin recorrer content_reviews, y es el dato del que cuelgan 8.6 --se publica lo aprobado-- y 8.7 --se archiva evidencia de eso--; sin ella las dos tendrian que adivinar cual. Y ahi esta casi todo el valor: FOREIGN KEY (approved_version_id, id) REFERENCES deliverable_versions(id, deliverable_id). Una clave simple garantizaria que la version EXISTE; esta garantiza que es DE ESTE ENTREGABLE --sin la segunda columna, un UPDATE mal escrito deja el entregable de Ana apuntando a la version aprobada del de Luis y la fila sigue siendo valida--. Mismo patron que fk_ccr_market_campaign (7.3). Ademas impide borrar la version apuntada mientras siga aprobada, y ck_del_approved_version exige que aprobado y puntero vayan juntos o no vayan: un dato que a veces esta es igual de util que no tenerlo. La columna espero dos iteraciones a proposito: antes de 8.3 no habia nadie que la escribiera, y habria sido el sexto caso de una columna que existe y no tiene una sola fila</t>
         </is>
       </c>
     </row>
     <row r="104" ht="34.5" customHeight="1" s="36">
       <c r="A104" s="67" t="inlineStr">
         <is>
-          <t>DEC-134</t>
+          <t>DEC-136</t>
         </is>
       </c>
       <c r="B104" s="68" t="inlineStr">
@@ -17867,7 +17954,7 @@
       <c r="C104" s="68" t="n"/>
       <c r="D104" s="69" t="inlineStr">
         <is>
-          <t>Hasta 8.5, quien lleva la cuenta marca de parte de quien viene la correccion.</t>
+          <t>Tres permisos y no uno: revisar, aprobar y autorizar una ronda de mas.</t>
         </is>
       </c>
       <c r="E104" s="69" t="inlineStr">
@@ -17877,14 +17964,14 @@
       </c>
       <c r="F104" s="69" t="inlineStr">
         <is>
-          <t>El portal del cliente es 8.5. Sin esto, en 8.3 nada consumiria ronda y el veto de «rondas agotadas» naceria muerto: el QUINTO caso de una regla escrita sobre una tabla vacia en un proyecto que ya lleva cuatro (campaign_creators en 7.4, domain_events en 4.13, invitations en 7.6, deliverables en 8.1). La salida no es inventarse el portal: es reconocer como trabaja una agencia HOY --el ejecutivo traslada el comentario del cliente y marca que es suyo--. En 8.5 el enlace firmado escribe la misma fila sin intermediario y Revisiones no se entera. Quien traslada queda anotado igual en reviewer_user_id: quien la escribio responde de ella. Y ck_cvw_firma exige usuario solo en las NUESTRAS, porque la del cliente en 8.5 no tendra cuenta detras</t>
+          <t>content.review abre la cola y pide cambios; content.approve da el visto bueno --lo que deja el contenido listo para el cliente y, con F9, lo que dispara el pago--; content.extra_round autoriza el cargo. Mismo criterio que separo capturar de aprobar en el perfil fiscal (DEC-062). content_reviewer tiene los dos primeros y no el tercero: esa decision es de dinero --o se le cobra al cliente o se come el margen-- y quien revisa contenido no tiene por que cargar con ella; la tiene campaign_manager, que responde del margen y es quien va a tener que explicarsela al cliente. Los tres se comprueban en el POST y no solo en la ruta: los tres botones llegan por el mismo formulario, y esconder un boton no es una regla de autorizacion. Y la cola es una BANDEJA GLOBAL, no una por campana: revisar es trabajo por lotes, y una cola por campana obliga a recorrer campanas para descubrir si hay algo esperando --lo que se descubre recorriendo se descubre tarde--. Ordenada por lo que lleva mas esperando y no por lo que vence antes, que es como una cola deja a alguien esperando para siempre</t>
         </is>
       </c>
     </row>
     <row r="105" ht="57" customHeight="1" s="36">
       <c r="A105" s="67" t="inlineStr">
         <is>
-          <t>DEC-133</t>
+          <t>DEC-135</t>
         </is>
       </c>
       <c r="B105" s="68" t="inlineStr">
@@ -17895,7 +17982,7 @@
       <c r="C105" s="68" t="n"/>
       <c r="D105" s="69" t="inlineStr">
         <is>
-          <t>Solo las rondas del CLIENTE cuentan contra el precio, y son POR ENTREGABLE.</t>
+          <t>Pasarse de las rondas incluidas se BLOQUEA y exige decidir y firmar; y el cargo NO va a campaign_costs.</t>
         </is>
       </c>
       <c r="E105" s="69" t="inlineStr">
@@ -17905,14 +17992,14 @@
       </c>
       <c r="F105" s="69" t="inlineStr">
         <is>
-          <t>Dos cosas en una porque las dos las decidio la misma conversacion. (1) Que nuestro equipo le pida al creador rehacer el encuadre antes de ensenarselo a nadie es control de calidad NUESTRO; cobrarselo al cliente seria cobrarle nuestro propio error. reviewer_side distinguia platform de client desde la Fase 2 y lo que faltaba era que alguien lo usara. (2) revision_rounds_used vivia en campaign_creators --dos rondas POR CREADOR--, asi que con un creador que entrega dos reels y tres stories, dos correcciones sobre el primer reel dejaban las otras cuatro piezas sin ninguna ronda, y el cliente habia pagado dos por cada una. Baja a deliverables, que es donde se aplica la regla. Y la columna vieja se va, no se queda como suma: una suma almacenada que nadie recalcula se desvia en silencio, y la suma por creador --la que alimenta el Creator Score-- sale de content_reviews con un SUM() que nunca miente. Tenia cero filas: quitarla hoy es gratis y dentro de tres meses no</t>
+          <t>No un aviso: un aviso que se puede saltar acaba en un cargo que se descubre al facturar, que es tarde para discutirlo con el cliente. Cuando la ronda que se va a pedir es la tercera de dos incluidas hay que decir si se cobra o se absorbe, y quien lo dice queda en authorized_by_user_id (ck_cvw_over, en la base y no solo en la pantalla). campaign_costs seria el sitio equivocado y era tentador: es lo que gastamos NOSOTROS y resta del margen (BR-FIN-011), mientras que una ronda de mas facturada al cliente es INGRESO --meterla ahi bajaria el margen de una campana que acaba de ganar dinero--. Aqui queda la decision y la pantalla de entregables la ensena como pendiente de facturar; donde acaba la linea cuando exista F9 es Q-57, y se decide con invoice_lines delante</t>
         </is>
       </c>
     </row>
     <row r="106" ht="34.5" customHeight="1" s="36">
       <c r="A106" s="67" t="inlineStr">
         <is>
-          <t>DEC-132</t>
+          <t>DEC-134</t>
         </is>
       </c>
       <c r="B106" s="68" t="inlineStr">
@@ -17923,24 +18010,24 @@
       <c r="C106" s="68" t="n"/>
       <c r="D106" s="69" t="inlineStr">
         <is>
-          <t>Si al caption le faltan las etiquetas del brief, NO SE ENVIA, y se le dice cuales.</t>
+          <t>Hasta 8.5, quien lleva la cuenta marca de parte de quien viene la correccion.</t>
         </is>
       </c>
       <c r="E106" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F106" s="69" t="inlineStr">
         <is>
-          <t>Comprobacion objetiva y barata que ahorra una ronda de correccion entera: el creador lo arregla en diez segundos en vez de enterarse tres dias despues. Avisar y dejar pasar acaba siempre en un aviso que nadie lee; dejarlo para la revision traslada a una persona la clase de tarea que una maquina hace mejor. Sin distinguir mayusculas --#ACMEVerano y #acmeverano son el mismo hashtag para las plataformas, y rechazar por la caja seria rechazar por algo que da igual-- y devolviendo todos los motivos a la vez, porque quien entrega desde el movil prefiere una lista de tres cosas que arreglar a tres intentos</t>
+          <t>El portal del cliente es 8.5. Sin esto, en 8.3 nada consumiria ronda y el veto de «rondas agotadas» naceria muerto: el QUINTO caso de una regla escrita sobre una tabla vacia en un proyecto que ya lleva cuatro (campaign_creators en 7.4, domain_events en 4.13, invitations en 7.6, deliverables en 8.1). La salida no es inventarse el portal: es reconocer como trabaja una agencia HOY --el ejecutivo traslada el comentario del cliente y marca que es suyo--. En 8.5 el enlace firmado escribe la misma fila sin intermediario y Revisiones no se entera. Quien traslada queda anotado igual en reviewer_user_id: quien la escribio responde de ella. Y ck_cvw_firma exige usuario solo en las NUESTRAS, porque la del cliente en 8.5 no tendra cuenta detras</t>
         </is>
       </c>
     </row>
     <row r="107" ht="45.75" customHeight="1" s="36">
       <c r="A107" s="67" t="inlineStr">
         <is>
-          <t>DEC-131</t>
+          <t>DEC-133</t>
         </is>
       </c>
       <c r="B107" s="68" t="inlineStr">
@@ -17951,24 +18038,24 @@
       <c r="C107" s="68" t="n"/>
       <c r="D107" s="69" t="inlineStr">
         <is>
-          <t>Se entrega un ENLACE externo, y opcionalmente una imagen.</t>
+          <t>Solo las rondas del CLIENTE cuentan contra el precio, y son POR ENTREGABLE.</t>
         </is>
       </c>
       <c r="E107" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F107" s="69" t="inlineStr">
         <is>
-          <t>El contenido de verdad --un reel de 80 MB-- no sube aqui y no deberia: el creador ya lo tiene en Drive o en la propia plataforma, y almacenarlo otra vez es coste y responsabilidad sin contrapartida. Se guarda el enlace, obligatoriamente https://, mas una imagen de referencia opcional por Almacen (10 MB). El https:// se comprueba en tres sitios a proposito: EntregarRequest da el mensaje junto al campo, vetoParaEntregar() lo da junto a los demas motivos, y ck_dv_url_https impide la fila venga de donde venga. Sin el tercero, un comando o un import mete javascript:alert(1) en una columna que una vista pinta dentro de un href; sin el segundo, el creador ve un 3819</t>
+          <t>Dos cosas en una porque las dos las decidio la misma conversacion. (1) Que nuestro equipo le pida al creador rehacer el encuadre antes de ensenarselo a nadie es control de calidad NUESTRO; cobrarselo al cliente seria cobrarle nuestro propio error. reviewer_side distinguia platform de client desde la Fase 2 y lo que faltaba era que alguien lo usara. (2) revision_rounds_used vivia en campaign_creators --dos rondas POR CREADOR--, asi que con un creador que entrega dos reels y tres stories, dos correcciones sobre el primer reel dejaban las otras cuatro piezas sin ninguna ronda, y el cliente habia pagado dos por cada una. Baja a deliverables, que es donde se aplica la regla. Y la columna vieja se va, no se queda como suma: una suma almacenada que nadie recalcula se desvia en silencio, y la suma por creador --la que alimenta el Creator Score-- sale de content_reviews con un SUM() que nunca miente. Tenia cero filas: quitarla hoy es gratis y dentro de tres meses no</t>
         </is>
       </c>
     </row>
     <row r="108" ht="57" customHeight="1" s="36">
       <c r="A108" s="67" t="inlineStr">
         <is>
-          <t>DEC-130</t>
+          <t>DEC-132</t>
         </is>
       </c>
       <c r="B108" s="68" t="inlineStr">
@@ -17979,7 +18066,7 @@
       <c r="C108" s="68" t="n"/>
       <c r="D108" s="69" t="inlineStr">
         <is>
-          <t>El brief que se usa es el EFECTIVO, no el general.</t>
+          <t>Si al caption le faltan las etiquetas del brief, NO SE ENVIA, y se le dice cuales.</t>
         </is>
       </c>
       <c r="E108" s="69" t="inlineStr">
@@ -17989,14 +18076,14 @@
       </c>
       <c r="F108" s="69" t="inlineStr">
         <is>
-          <t>Mercados::briefEfectivo(), que ya resolvia N-03: si el mercado del creador tiene brief propio, ese REEMPLAZA al general. Un creador peruano en una campana con brief especifico para Peru recibe el de Peru, y las etiquetas tambien --que es justo por lo que 7.2 dejo los hashtags fuera hasta que existieran los mercados--. Un entregable generado del brief general cuando hay uno de mercado le pide al creador lo que la campana NO quiere de el, y el error solo se ve al revisar</t>
+          <t>Comprobacion objetiva y barata que ahorra una ronda de correccion entera: el creador lo arregla en diez segundos en vez de enterarse tres dias despues. Avisar y dejar pasar acaba siempre en un aviso que nadie lee; dejarlo para la revision traslada a una persona la clase de tarea que una maquina hace mejor. Sin distinguir mayusculas --#ACMEVerano y #acmeverano son el mismo hashtag para las plataformas, y rechazar por la caja seria rechazar por algo que da igual-- y devolviendo todos los motivos a la vez, porque quien entrega desde el movil prefiere una lista de tres cosas que arreglar a tres intentos</t>
         </is>
       </c>
     </row>
     <row r="109" ht="45.75" customHeight="1" s="36">
       <c r="A109" s="67" t="inlineStr">
         <is>
-          <t>DEC-129</t>
+          <t>DEC-131</t>
         </is>
       </c>
       <c r="B109" s="68" t="inlineStr">
@@ -18007,7 +18094,7 @@
       <c r="C109" s="68" t="n"/>
       <c r="D109" s="69" t="inlineStr">
         <is>
-          <t>Los entregables se generan SOLOS al aceptar, y la generacion es idempotente.</t>
+          <t>Se entrega un ENLACE externo, y opcionalmente una imagen.</t>
         </is>
       </c>
       <c r="E109" s="69" t="inlineStr">
@@ -18017,14 +18104,14 @@
       </c>
       <c r="F109" s="69" t="inlineStr">
         <is>
-          <t>El brief ya lo dice todo --cuantos, de que formato, con cuantos dias de plazo--, asi que pedirle a alguien que lo teclee otra vez por cada creador es pedirle que copie un dato que el sistema ya tiene. Lo que decide no es el ahorro sino el MODO DE FALLO: si se teclea a mano, el dia que se olvide ese creador no tiene nada que entregar y nadie se entera hasta que la campana termina sin su contenido; si se generan solos, el fallo es que sobra un entregable y se ve en la lista. Va por evento (campaign_creator.accepted --&gt; GenerarEntregables) y no dentro de aceptar(), porque Campaign no puede conocer Content: la misma frontera que se cobro el panel de 7.7. Idempotente porque aceptar dos veces no puede pasar --el enlace es de un solo uso-- pero una reanudacion de la cola o un reintento manual si, y duplicar el trabajo de un creador es la clase de error que se descubre tarde y mal</t>
+          <t>El contenido de verdad --un reel de 80 MB-- no sube aqui y no deberia: el creador ya lo tiene en Drive o en la propia plataforma, y almacenarlo otra vez es coste y responsabilidad sin contrapartida. Se guarda el enlace, obligatoriamente https://, mas una imagen de referencia opcional por Almacen (10 MB). El https:// se comprueba en tres sitios a proposito: EntregarRequest da el mensaje junto al campo, vetoParaEntregar() lo da junto a los demas motivos, y ck_dv_url_https impide la fila venga de donde venga. Sin el tercero, un comando o un import mete javascript:alert(1) en una columna que una vista pinta dentro de un href; sin el segundo, el creador ve un 3819</t>
         </is>
       </c>
     </row>
     <row r="110" ht="34.5" customHeight="1" s="36">
       <c r="A110" s="67" t="inlineStr">
         <is>
-          <t>DEC-128</t>
+          <t>DEC-130</t>
         </is>
       </c>
       <c r="B110" s="68" t="inlineStr">
@@ -18035,24 +18122,24 @@
       <c r="C110" s="68" t="n"/>
       <c r="D110" s="69" t="inlineStr">
         <is>
-          <t>En el seguimiento, el dinero SI y el margen solo con su permiso.</t>
+          <t>El brief que se usa es el EFECTIVO, no el general.</t>
         </is>
       </c>
       <c r="E110" s="69" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F110" s="69" t="inlineStr">
         <is>
-          <t>Presupuesto, comprometido y disponible los ve quien puede ver la campana: sin esos tres numeros no se decide a quien invitar, y ponerlos detras de un permiso que entonces necesitaria todo el mundo seria un permiso que no protege nada. El margen sigue detras de campaign.view_margin (BR-FIN-007) y no se calcula y luego se esconde: no se calcula --un dato que llega a la vista es un dato que un @if mal puesto puede ensenar, y BR-SEC-001 es 🔴--. La diferencia no es sutil: lo comprometido es lo que se le paga a los creadores; el margen es lo que gana la empresa. Y el disponible se ensena NEGATIVO cuando lo es: redondearlo a cero esconderia justo el caso que hay que ver, una campana que se paso porque finanzas lo autorizo</t>
+          <t>Mercados::briefEfectivo(), que ya resolvia N-03: si el mercado del creador tiene brief propio, ese REEMPLAZA al general. Un creador peruano en una campana con brief especifico para Peru recibe el de Peru, y las etiquetas tambien --que es justo por lo que 7.2 dejo los hashtags fuera hasta que existieran los mercados--. Un entregable generado del brief general cuando hay uno de mercado le pide al creador lo que la campana NO quiere de el, y el error solo se ve al revisar</t>
         </is>
       </c>
     </row>
     <row r="111" ht="57" customHeight="1" s="36">
       <c r="A111" s="67" t="inlineStr">
         <is>
-          <t>DEC-127</t>
+          <t>DEC-129</t>
         </is>
       </c>
       <c r="B111" s="68" t="inlineStr">
@@ -18063,24 +18150,24 @@
       <c r="C111" s="68" t="n"/>
       <c r="D111" s="69" t="inlineStr">
         <is>
-          <t>Cuatro alertas en el panel de seguimiento, y su orden NO es por gravedad.</t>
+          <t>Los entregables se generan SOLOS al aceptar, y la generacion es idempotente.</t>
         </is>
       </c>
       <c r="E111" s="69" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F111" s="69" t="inlineStr">
         <is>
-          <t>Campana sin confirmar con el arranque a menos de 14 dias, preguntas de creadores sin atender, invitaciones que caducan en menos de 12 h, y cupo de mercado sin cubrir. La de «sin confirmar» va PRIMERA porque bloquea a las demas: sin confirmar no se puede invitar a nadie, asi que un cupo corto ahi no se arregla reclutando. Y las preguntas van antes que las invitaciones urgentes porque un creador que pregunto y no recibe respuesta MIENTRAS su plazo corre es la combinacion exacta que convierte un si en un silencio. Cada alerta dice que pasa y que hacer: una que solo dice que hay un problema obliga a buscarlo, y entonces deja de leerse. Y «cubierto» es ACEPTADO, no invitado: una invitacion sin contestar es una plaza esperando, y contarla como cubierta es como se llega al dia de arranque con la mitad del equipo y los numeros en verde</t>
+          <t>El brief ya lo dice todo --cuantos, de que formato, con cuantos dias de plazo--, asi que pedirle a alguien que lo teclee otra vez por cada creador es pedirle que copie un dato que el sistema ya tiene. Lo que decide no es el ahorro sino el MODO DE FALLO: si se teclea a mano, el dia que se olvide ese creador no tiene nada que entregar y nadie se entera hasta que la campana termina sin su contenido; si se generan solos, el fallo es que sobra un entregable y se ve en la lista. Va por evento (campaign_creator.accepted --&gt; GenerarEntregables) y no dentro de aceptar(), porque Campaign no puede conocer Content: la misma frontera que se cobro el panel de 7.7. Idempotente porque aceptar dos veces no puede pasar --el enlace es de un solo uso-- pero una reanudacion de la cola o un reintento manual si, y duplicar el trabajo de un creador es la clase de error que se descubre tarde y mal</t>
         </is>
       </c>
     </row>
     <row r="112" ht="45.75" customHeight="1" s="36">
       <c r="A112" s="67" t="inlineStr">
         <is>
-          <t>DEC-126</t>
+          <t>DEC-128</t>
         </is>
       </c>
       <c r="B112" s="68" t="inlineStr">
@@ -18091,24 +18178,24 @@
       <c r="C112" s="68" t="n"/>
       <c r="D112" s="69" t="inlineStr">
         <is>
-          <t>usuarios:crear deja de teclear la contrasena; el alta interna usa el mismo enlace de 72 h que la del creador.</t>
+          <t>En el seguimiento, el dinero SI y el margen solo con su permiso.</t>
         </is>
       </c>
       <c r="E112" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="F112" s="69" t="inlineStr">
         <is>
-          <t>Cierra BR-SEC-004 (🔴) del todo. must_change_password era el parche: obligaba a cambiarla DESPUES y dejaba una ventana --de minutos o de meses-- en la que dos personas conocian la credencial, y justo en las cuentas donde la base exige dos personas distintas para el dinero. Ahora no hay ventana: la contrasena no existe hasta que la escribe su dueno. usuarios:contrasena --enlace hace lo mismo para reponer y no toca la contrasena actual --si el correo no llega, la persona no se queda peor de como estaba--. Teclearla a mano sigue existiendo a proposito, como cristal de emergencia para cuando el correo no sale (Q-20), y el comando avisa cada vez de que ese es el camino excepcional</t>
+          <t>Presupuesto, comprometido y disponible los ve quien puede ver la campana: sin esos tres numeros no se decide a quien invitar, y ponerlos detras de un permiso que entonces necesitaria todo el mundo seria un permiso que no protege nada. El margen sigue detras de campaign.view_margin (BR-FIN-007) y no se calcula y luego se esconde: no se calcula --un dato que llega a la vista es un dato que un @if mal puesto puede ensenar, y BR-SEC-001 es 🔴--. La diferencia no es sutil: lo comprometido es lo que se le paga a los creadores; el margen es lo que gana la empresa. Y el disponible se ensena NEGATIVO cuando lo es: redondearlo a cero esconderia justo el caso que hay que ver, una campana que se paso porque finanzas lo autorizo</t>
         </is>
       </c>
     </row>
     <row r="113" ht="68.25" customHeight="1" s="36">
       <c r="A113" s="67" t="inlineStr">
         <is>
-          <t>DEC-125</t>
+          <t>DEC-127</t>
         </is>
       </c>
       <c r="B113" s="68" t="inlineStr">
@@ -18119,24 +18206,24 @@
       <c r="C113" s="68" t="n"/>
       <c r="D113" s="69" t="inlineStr">
         <is>
-          <t>Cuando un creador contesta, se avisa a QUIEN LE INVITO y a nadie mas.</t>
+          <t>Cuatro alertas en el panel de seguimiento, y su orden NO es por gravedad.</t>
         </is>
       </c>
       <c r="E113" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="F113" s="69" t="inlineStr">
         <is>
-          <t>Es quien espera la respuesta y quien va a hacer algo con ella. Avisar a todo el equipo son cuarenta correos por campana a cada uno, y un buzon asi se filtra a una carpeta y deja de leerse --la forma cara de no avisar a nadie--. El precio, dicho: una invitacion mandada por alguien que luego se va de la empresa queda MUDA. A una cuenta desactivada no se le escribe: no avisa a nadie y puede acabar en un buzon reasignado. El hecho no se pierde, queda en domain_events y se ve en la lista</t>
+          <t>Campana sin confirmar con el arranque a menos de 14 dias, preguntas de creadores sin atender, invitaciones que caducan en menos de 12 h, y cupo de mercado sin cubrir. La de «sin confirmar» va PRIMERA porque bloquea a las demas: sin confirmar no se puede invitar a nadie, asi que un cupo corto ahi no se arregla reclutando. Y las preguntas van antes que las invitaciones urgentes porque un creador que pregunto y no recibe respuesta MIENTRAS su plazo corre es la combinacion exacta que convierte un si en un silencio. Cada alerta dice que pasa y que hacer: una que solo dice que hay un problema obliga a buscarlo, y entonces deja de leerse. Y «cubierto» es ACEPTADO, no invitado: una invitacion sin contestar es una plaza esperando, y contarla como cubierta es como se llega al dia de arranque con la mitad del equipo y los numeros en verde</t>
         </is>
       </c>
     </row>
     <row r="114" ht="57" customHeight="1" s="36">
       <c r="A114" s="67" t="inlineStr">
         <is>
-          <t>DEC-124</t>
+          <t>DEC-126</t>
         </is>
       </c>
       <c r="B114" s="68" t="inlineStr">
@@ -18147,7 +18234,7 @@
       <c r="C114" s="68" t="n"/>
       <c r="D114" s="69" t="inlineStr">
         <is>
-          <t>Preguntar NO mueve el plazo de la invitacion.</t>
+          <t>usuarios:crear deja de teclear la contrasena; el alta interna usa el mismo enlace de 72 h que la del creador.</t>
         </is>
       </c>
       <c r="E114" s="69" t="inlineStr">
@@ -18157,14 +18244,14 @@
       </c>
       <c r="F114" s="69" t="inlineStr">
         <is>
-          <t>La alternativa --congelarla hasta que alguien conteste-- deja el importe comprometido para siempre si nadie contesta, que es justo el agujero que invitaciones:caducar existe para tapar. La pantalla se lo dice al creador con todas las letras: callarlo dejaria a alguien esperando tranquilo mientras su invitacion caduca, que es peor que no dejarle preguntar. Quien invito ve la pregunta en la lista de candidatos y decide; si hace falta mas tiempo, anula y manda otra. Y no hay respuesta dentro de la aplicacion: el equipo contesta por correo, que es donde el creador ya esta. Un hilo de ida y vuelta es un modulo de mensajeria --notificaciones, no leidos, permisos-- y habria multiplicado por tres la iteracion para resolver lo que un boton de «Responder» ya resuelve. Lo que si hay es un DUENO: «me hago cargo» marca quien atiende y el segundo clic no pisa al primero</t>
+          <t>Cierra BR-SEC-004 (🔴) del todo. must_change_password era el parche: obligaba a cambiarla DESPUES y dejaba una ventana --de minutos o de meses-- en la que dos personas conocian la credencial, y justo en las cuentas donde la base exige dos personas distintas para el dinero. Ahora no hay ventana: la contrasena no existe hasta que la escribe su dueno. usuarios:contrasena --enlace hace lo mismo para reponer y no toca la contrasena actual --si el correo no llega, la persona no se queda peor de como estaba--. Teclearla a mano sigue existiendo a proposito, como cristal de emergencia para cuando el correo no sale (Q-20), y el comando avisa cada vez de que ese es el camino excepcional</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="36">
       <c r="A115" s="67" t="inlineStr">
         <is>
-          <t>DEC-123</t>
+          <t>DEC-125</t>
         </is>
       </c>
       <c r="B115" s="68" t="inlineStr">
@@ -18175,24 +18262,24 @@
       <c r="C115" s="68" t="n"/>
       <c r="D115" s="69" t="inlineStr">
         <is>
-          <t>Pedir un correo se hace desde Shared, no desde el modulo que lo necesita.</t>
+          <t>Cuando un creador contesta, se avisa a QUIEN LE INVITO y a nadie mas.</t>
         </is>
       </c>
       <c r="E115" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F115" s="69" t="inlineStr">
         <is>
-          <t>deptrac.yaml dice Communication: [Framework, Shared, Core, Identity]. En 5.9 el evento del enlace vivio una iteracion dentro de Identity y funciono de milagro: Identity esta en esa lista. Campaign no, y 7.6 necesita mandar un correo igual. Sube a App\Shared\Eventos\CorreoPedido con un solo oyente en Communication: cualquier modulo puede pedir un correo, ninguno conoce a Communication y Communication no conoce a ninguno. No es EventoOcurrido y no puede serlo --ese persiste su payload en domain_events y aqui el payload lleva el token en claro--; el HECHO si se registra, por separado y sin el token</t>
+          <t>Es quien espera la respuesta y quien va a hacer algo con ella. Avisar a todo el equipo son cuarenta correos por campana a cada uno, y un buzon asi se filtra a una carpeta y deja de leerse --la forma cara de no avisar a nadie--. El precio, dicho: una invitacion mandada por alguien que luego se va de la empresa queda MUDA. A una cuenta desactivada no se le escribe: no avisa a nadie y puede acabar en un buzon reasignado. El hecho no se pierde, queda en domain_events y se ve en la lista</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="36">
       <c r="A116" s="67" t="inlineStr">
         <is>
-          <t>DEC-122</t>
+          <t>DEC-124</t>
         </is>
       </c>
       <c r="B116" s="68" t="inlineStr">
@@ -18203,24 +18290,24 @@
       <c r="C116" s="68" t="n"/>
       <c r="D116" s="69" t="inlineStr">
         <is>
-          <t>La invitacion COPIA el importe con el que salio, y el importe no se mueve mientras este viva.</t>
+          <t>Preguntar NO mueve el plazo de la invitacion.</t>
         </is>
       </c>
       <c r="E116" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F116" s="69" t="inlineStr">
         <is>
-          <t>BR-CREATOR-008 congela el precio al ACEPTAR (tg_ccr_compromiso, 7.5) y entre el envio y la respuesta agreed_amount se podia mover: al creador le llegaba «te pagamos 1.500», alguien lo bajaba a 900, y aceptaba 900 sin haberlo visto nunca. No hace falta mala fe; basta con dos personas sobre la misma campana. Se cierra por los dos lados: amount_snapshot --misma decision que payment_term_days_snapshot y billing_legal_entity_id-- y tg_ccr_monto_con_invitacion, que obliga a anular la invitacion antes de renegociar. Y como en 5.9, responder y anular son dos columnas: responded_at tiene que contestar «.llego a contestar?» sin ambiguedad. Decimocuarta columna puerta del esquema</t>
+          <t>La alternativa --congelarla hasta que alguien conteste-- deja el importe comprometido para siempre si nadie contesta, que es justo el agujero que invitaciones:caducar existe para tapar. La pantalla se lo dice al creador con todas las letras: callarlo dejaria a alguien esperando tranquilo mientras su invitacion caduca, que es peor que no dejarle preguntar. Quien invito ve la pregunta en la lista de candidatos y decide; si hace falta mas tiempo, anula y manda otra. Y no hay respuesta dentro de la aplicacion: el equipo contesta por correo, que es donde el creador ya esta. Un hilo de ida y vuelta es un modulo de mensajeria --notificaciones, no leidos, permisos-- y habria multiplicado por tres la iteracion para resolver lo que un boton de «Responder» ya resuelve. Lo que si hay es un DUENO: «me hago cargo» marca quien atiende y el segundo clic no pisa al primero</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="36">
       <c r="A117" s="67" t="inlineStr">
         <is>
-          <t>DEC-121</t>
+          <t>DEC-123</t>
         </is>
       </c>
       <c r="B117" s="68" t="inlineStr">
@@ -18231,7 +18318,7 @@
       <c r="C117" s="68" t="n"/>
       <c r="D117" s="69" t="inlineStr">
         <is>
-          <t>Rechazar no cierra la campana para ese creador, y quedan las DOS rondas.</t>
+          <t>Pedir un correo se hace desde Shared, no desde el modulo que lo necesita.</t>
         </is>
       </c>
       <c r="E117" s="69" t="inlineStr">
@@ -18241,14 +18328,14 @@
       </c>
       <c r="F117" s="69" t="inlineStr">
         <is>
-          <t>Pasa de verdad: rechaza por el importe, finanzas sube el presupuesto, se vuelve a preguntar. Prohibirlo obligaria a renegociar fuera del sistema. La constancia vive en invitations --una fila por ronda, con su motivo y con lo que se ofrecio entonces--, que es justo para lo que la Fase 2 diseno la tabla («cuantas veces hubo que insistir alimenta el Creator Score»). Lo que si se limpia al reinvitar es campaign_creators.declined_at: esa columna dice cuando se rechazo la ronda ACTUAL, y dejarla puesta haria que un accepted conviviera con una fecha de rechazo. El motivo es de lista cerrada para poder contestar «.por que nos dicen que no?» --si el 70% es el importe, el problema es el presupuesto y no el reclutamiento-- y no decide quien se puede reinvitar</t>
+          <t>deptrac.yaml dice Communication: [Framework, Shared, Core, Identity]. En 5.9 el evento del enlace vivio una iteracion dentro de Identity y funciono de milagro: Identity esta en esa lista. Campaign no, y 7.6 necesita mandar un correo igual. Sube a App\Shared\Eventos\CorreoPedido con un solo oyente en Communication: cualquier modulo puede pedir un correo, ninguno conoce a Communication y Communication no conoce a ninguno. No es EventoOcurrido y no puede serlo --ese persiste su payload en domain_events y aqui el payload lleva el token en claro--; el HECHO si se registra, por separado y sin el token</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="36">
       <c r="A118" s="67" t="inlineStr">
         <is>
-          <t>DEC-120</t>
+          <t>DEC-122</t>
         </is>
       </c>
       <c r="B118" s="68" t="inlineStr">
@@ -18259,7 +18346,7 @@
       <c r="C118" s="68" t="n"/>
       <c r="D118" s="69" t="inlineStr">
         <is>
-          <t>El plazo para contestar vive en la CAMPANA, no en cada invitacion.</t>
+          <t>La invitacion COPIA el importe con el que salio, y el importe no se mueve mientras este viva.</t>
         </is>
       </c>
       <c r="E118" s="69" t="inlineStr">
@@ -18269,14 +18356,14 @@
       </c>
       <c r="F118" s="69" t="inlineStr">
         <is>
-          <t>campaigns.invitation_hours, 72 por omision, entre 1 hora y 30 dias (ck_camp_invitation_hours). Un solo numero que explicar y un solo sitio donde cambiarlo; por invitacion seria un dato que hay que decidir cuarenta veces y que nadie mira dos. Y caducar necesita un comando aunque la caducidad se deduzca: expires_at contra el reloj ya impide contestar, pero la participacion seguiria en invited para siempre, su importe seguiria contando contra el presupuesto (BR-CAMPAIGN-005 bloqueando a otros por dinero que nadie se va a gastar) y el cupo del mercado no se liberaria. invitaciones:caducar cada diez minutos: el plazo minimo es una hora, asi que diez minutos deja el retraso maximo en un 17% del plazo mas corto posible</t>
+          <t>BR-CREATOR-008 congela el precio al ACEPTAR (tg_ccr_compromiso, 7.5) y entre el envio y la respuesta agreed_amount se podia mover: al creador le llegaba «te pagamos 1.500», alguien lo bajaba a 900, y aceptaba 900 sin haberlo visto nunca. No hace falta mala fe; basta con dos personas sobre la misma campana. Se cierra por los dos lados: amount_snapshot --misma decision que payment_term_days_snapshot y billing_legal_entity_id-- y tg_ccr_monto_con_invitacion, que obliga a anular la invitacion antes de renegociar. Y como en 5.9, responder y anular son dos columnas: responded_at tiene que contestar «.llego a contestar?» sin ambiguedad. Decimocuarta columna puerta del esquema</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="36">
       <c r="A119" s="67" t="inlineStr">
         <is>
-          <t>DEC-119</t>
+          <t>DEC-121</t>
         </is>
       </c>
       <c r="B119" s="68" t="inlineStr">
@@ -18287,7 +18374,7 @@
       <c r="C119" s="68" t="n"/>
       <c r="D119" s="69" t="inlineStr">
         <is>
-          <t>El creador contesta la invitacion EL MISMO, por enlace.</t>
+          <t>Rechazar no cierra la campana para ese creador, y quedan las DOS rondas.</t>
         </is>
       </c>
       <c r="E119" s="69" t="inlineStr">
@@ -18297,14 +18384,14 @@
       </c>
       <c r="F119" s="69" t="inlineStr">
         <is>
-          <t>Su portal (F6) sigue bloqueado por T-09, asi que no hay pantalla donde entre a decidir. La alternativa era que un operador tecleara «dijo que si por WhatsApp», y eso convierte una ACEPTACION --de la que sale lo que se le paga a una persona-- en la palabra de un tercero. Con enlace hay una IP, una hora y un token que solo el tenia. Y no habia que construir nada: es la pieza de 5.9, ya probada. invitations.channel admite otros canales desde la Fase 2; el dia que exista el de WhatsApp, la fila ya sabe distinguirlo</t>
+          <t>Pasa de verdad: rechaza por el importe, finanzas sube el presupuesto, se vuelve a preguntar. Prohibirlo obligaria a renegociar fuera del sistema. La constancia vive en invitations --una fila por ronda, con su motivo y con lo que se ofrecio entonces--, que es justo para lo que la Fase 2 diseno la tabla («cuantas veces hubo que insistir alimenta el Creator Score»). Lo que si se limpia al reinvitar es campaign_creators.declined_at: esa columna dice cuando se rechazo la ronda ACTUAL, y dejarla puesta haria que un accepted conviviera con una fecha de rechazo. El motivo es de lista cerrada para poder contestar «.por que nos dicen que no?» --si el 70% es el importe, el problema es el presupuesto y no el reclutamiento-- y no decide quien se puede reinvitar</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="36">
       <c r="A120" s="67" t="inlineStr">
         <is>
-          <t>DEC-118</t>
+          <t>DEC-120</t>
         </is>
       </c>
       <c r="B120" s="68" t="inlineStr">
@@ -18315,24 +18402,24 @@
       <c r="C120" s="68" t="n"/>
       <c r="D120" s="69" t="inlineStr">
         <is>
-          <t>La portada se bifurca por TIPO DE USUARIO, y SESSION_DRIVER=database pasa a ser requisito de seguridad.</t>
+          <t>El plazo para contestar vive en la CAMPANA, no en cada invitacion.</t>
         </is>
       </c>
       <c r="E120" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F120" s="69" t="inlineStr">
         <is>
-          <t>Dos consecuencias de la misma causa: 5.9 crea la primera cuenta que no es del equipo. (a) /panel ensenaba a cualquier autenticado los totales de creadores, clientes y campanas mas el inventario del esquema; nadie lo habia pensado porque hasta hoy todos los usuarios eran internos. Se bifurca por user_type y no por permiso --un creador no tiene ninguno, y comprobar permisos que dicen «no» a todo deja una pantalla vacia en vez de una que explica donde esta--. (b) Poner una contrasena nueva borra las filas de sessions de ese usuario y rota remember_token; con SESSION_DRIVER=file lo primero es imposible --no hay forma de saber que archivo es de quien-- y una contrasena nueva convivira con la sesion abierta de quien entro con la vieja, que es no haber hecho nada</t>
+          <t>campaigns.invitation_hours, 72 por omision, entre 1 hora y 30 dias (ck_camp_invitation_hours). Un solo numero que explicar y un solo sitio donde cambiarlo; por invitacion seria un dato que hay que decidir cuarenta veces y que nadie mira dos. Y caducar necesita un comando aunque la caducidad se deduzca: expires_at contra el reloj ya impide contestar, pero la participacion seguiria en invited para siempre, su importe seguiria contando contra el presupuesto (BR-CAMPAIGN-005 bloqueando a otros por dinero que nadie se va a gastar) y el cupo del mercado no se liberaria. invitaciones:caducar cada diez minutos: el plazo minimo es una hora, asi que diez minutos deja el retraso maximo en un 17% del plazo mas corto posible</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="36">
       <c r="A121" s="67" t="inlineStr">
         <is>
-          <t>DEC-117</t>
+          <t>DEC-119</t>
         </is>
       </c>
       <c r="B121" s="68" t="inlineStr">
@@ -18343,24 +18430,24 @@
       <c r="C121" s="68" t="n"/>
       <c r="D121" s="69" t="inlineStr">
         <is>
-          <t>El token no se queda en la barra de direcciones.</t>
+          <t>El creador contesta la invitacion EL MISMO, por enlace.</t>
         </is>
       </c>
       <c r="E121" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F121" s="69" t="inlineStr">
         <is>
-          <t>El enlace del correo lo lleva --no hay otra forma--, pero esa ruta solo lo guarda en la sesion y redirige a una URL sin el. Una URL con un token dentro viaja en la cabecera Referer a cualquier recurso externo de la pagina --y estas pantallas cargan tipografias de un dominio de terceros--, se queda en el registro de accesos del servidor y en el historial, y se copia entera cuando alguien la pega en un chat preguntando que es. Al guardarlo la sesion se vacia y renueva (invalidate(), no regenerate(): el segundo cambia el identificador y conserva el contenido, y aqui el contenido es lo que sobra)</t>
+          <t>Su portal (F6) sigue bloqueado por T-09, asi que no hay pantalla donde entre a decidir. La alternativa era que un operador tecleara «dijo que si por WhatsApp», y eso convierte una ACEPTACION --de la que sale lo que se le paga a una persona-- en la palabra de un tercero. Con enlace hay una IP, una hora y un token que solo el tenia. Y no habia que construir nada: es la pieza de 5.9, ya probada. invitations.channel admite otros canales desde la Fase 2; el dia que exista el de WhatsApp, la fila ya sabe distinguirlo</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="36">
       <c r="A122" s="67" t="inlineStr">
         <is>
-          <t>DEC-116</t>
+          <t>DEC-118</t>
         </is>
       </c>
       <c r="B122" s="68" t="inlineStr">
@@ -18371,7 +18458,7 @@
       <c r="C122" s="68" t="n"/>
       <c r="D122" s="69" t="inlineStr">
         <is>
-          <t>Un enlace nuevo invalida el anterior, y usar uno mata todos los demas.</t>
+          <t>La portada se bifurca por TIPO DE USUARIO, y SESSION_DRIVER=database pasa a ser requisito de seguridad.</t>
         </is>
       </c>
       <c r="E122" s="69" t="inlineStr">
@@ -18381,14 +18468,14 @@
       </c>
       <c r="F122" s="69" t="inlineStr">
         <is>
-          <t>Quien pide otro suele hacerlo porque sospecha del primero; dejarlo vivo seria dejar abierta justo la puerta que queria cerrar. Lo garantiza la BASE con la decimotercera columna puerta (uq_pl_vigente), no el servicio. Y revocar no es marcar usado: son dos columnas a proposito, porque el dia que alguien pregunte «.llego a usar el enlace?» la respuesta tiene que salir de una columna que solo se escribe cuando lo uso. La primera version de la tabla las mezclaba --una columna menos-- y ademas chocaba con ck_pl_used, que exige la IP de quien lo usa: a un enlace que sustituyes no le puedes poner una IP. Caducar no se escribe: se deduce de expires_at</t>
+          <t>Dos consecuencias de la misma causa: 5.9 crea la primera cuenta que no es del equipo. (a) /panel ensenaba a cualquier autenticado los totales de creadores, clientes y campanas mas el inventario del esquema; nadie lo habia pensado porque hasta hoy todos los usuarios eran internos. Se bifurca por user_type y no por permiso --un creador no tiene ninguno, y comprobar permisos que dicen «no» a todo deja una pantalla vacia en vez de una que explica donde esta--. (b) Poner una contrasena nueva borra las filas de sessions de ese usuario y rota remember_token; con SESSION_DRIVER=file lo primero es imposible --no hay forma de saber que archivo es de quien-- y una contrasena nueva convivira con la sesion abierta de quien entro con la vieja, que es no haber hecho nada</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="36">
       <c r="A123" s="67" t="inlineStr">
         <is>
-          <t>DEC-115</t>
+          <t>DEC-117</t>
         </is>
       </c>
       <c r="B123" s="68" t="inlineStr">
@@ -18399,24 +18486,24 @@
       <c r="C123" s="68" t="n"/>
       <c r="D123" s="69" t="inlineStr">
         <is>
-          <t>Pedir recuperacion contesta lo mismo exista o no el correo.</t>
+          <t>El token no se queda en la barra de direcciones.</t>
         </is>
       </c>
       <c r="E123" s="69" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F123" s="69" t="inlineStr">
         <is>
-          <t>«Si esa direccion tiene una cuenta activa, le acaba de salir un enlace», a los dos, y sin enviar nada en el segundo caso. Distinguirlos convierte la pantalla en un buscador de cuentas dadas de alta: con una lista de direcciones se sabe en un rato cuales son clientes nuestros, y eso vale dinero para quien hace phishing dirigido. El precio es real: quien se equivoca de correo no se entera, y se compensa diciendolo en la propia pantalla en vez de callarlo. La prueba lo afirma byte a byte quitando el testigo anti-CSRF: comparar solo la clave de sesion dejaria pasar una version que escribiera «no tenemos ese correo» dentro de la vista</t>
+          <t>El enlace del correo lo lleva --no hay otra forma--, pero esa ruta solo lo guarda en la sesion y redirige a una URL sin el. Una URL con un token dentro viaja en la cabecera Referer a cualquier recurso externo de la pagina --y estas pantallas cargan tipografias de un dominio de terceros--, se queda en el registro de accesos del servidor y en el historial, y se copia entera cuando alguien la pega en un chat preguntando que es. Al guardarlo la sesion se vacia y renueva (invalidate(), no regenerate(): el segundo cambia el identificador y conserva el contenido, y aqui el contenido es lo que sobra)</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="36">
       <c r="A124" s="67" t="inlineStr">
         <is>
-          <t>DEC-114</t>
+          <t>DEC-116</t>
         </is>
       </c>
       <c r="B124" s="68" t="inlineStr">
@@ -18427,7 +18514,7 @@
       <c r="C124" s="68" t="n"/>
       <c r="D124" s="69" t="inlineStr">
         <is>
-          <t>De un token de contrasena se guarda la HUELLA, nunca el token.</t>
+          <t>Un enlace nuevo invalida el anterior, y usar uno mata todos los demas.</t>
         </is>
       </c>
       <c r="E124" s="69" t="inlineStr">
@@ -18437,14 +18524,14 @@
       </c>
       <c r="F124" s="69" t="inlineStr">
         <is>
-          <t>bin2hex(random_bytes(32)) --no Str::random(), no uniqid(), no el uuid de la fila-- y en password_links solo entra su sha256. Misma decision que email_log (la huella del cuerpo, no el cuerpo) y que los medios de pago (la mascara, no el numero), y aqui es la mas importante de las tres: quien lea esta tabla no puede entrar en ninguna cuenta. Corolario que obligo a romper el patron de DEC-112: el aviso a Communication no puede ir por Eventos::ocurrio(), porque ese bus PERSISTE el payload y el payload lleva el enlace dentro. Va por un evento propio de Identity, que Communication ya tiene permitido conocer. El HECHO --«se emitio un enlace de tipo X para el usuario Y»-- si se guarda en domain_events, y sin el token</t>
+          <t>Quien pide otro suele hacerlo porque sospecha del primero; dejarlo vivo seria dejar abierta justo la puerta que queria cerrar. Lo garantiza la BASE con la decimotercera columna puerta (uq_pl_vigente), no el servicio. Y revocar no es marcar usado: son dos columnas a proposito, porque el dia que alguien pregunte «.llego a usar el enlace?» la respuesta tiene que salir de una columna que solo se escribe cuando lo uso. La primera version de la tabla las mezclaba --una columna menos-- y ademas chocaba con ck_pl_used, que exige la IP de quien lo usa: a un enlace que sustituyes no le puedes poner una IP. Caducar no se escribe: se deduce de expires_at</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="36">
       <c r="A125" s="67" t="inlineStr">
         <is>
-          <t>DEC-113</t>
+          <t>DEC-115</t>
         </is>
       </c>
       <c r="B125" s="68" t="inlineStr">
@@ -18455,24 +18542,24 @@
       <c r="C125" s="68" t="n"/>
       <c r="D125" s="69" t="inlineStr">
         <is>
-          <t>El enlace de alta dura 72 h; el de recuperacion, 1 h.</t>
+          <t>Pedir recuperacion contesta lo mismo exista o no el correo.</t>
         </is>
       </c>
       <c r="E125" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="F125" s="69" t="inlineStr">
         <is>
-          <t>Son la misma pieza con dos relojes: el de alta llega SIN AVISAR y puede caer un viernes por la noche; el de recuperacion lo pide alguien que esta delante de la pantalla ahora. Un solo plazo obligaria a elegir entre dejar la ventana larga del alta valiendo para recuperar, o darle una hora a quien no sabia que iba a recibir nada. La caducidad se guarda en la fila, no es una constante global: un enlace sabe cuando muere</t>
+          <t>«Si esa direccion tiene una cuenta activa, le acaba de salir un enlace», a los dos, y sin enviar nada en el segundo caso. Distinguirlos convierte la pantalla en un buscador de cuentas dadas de alta: con una lista de direcciones se sabe en un rato cuales son clientes nuestros, y eso vale dinero para quien hace phishing dirigido. El precio es real: quien se equivoca de correo no se entera, y se compensa diciendolo en la propia pantalla en vez de callarlo. La prueba lo afirma byte a byte quitando el testigo anti-CSRF: comparar solo la clave de sesion dejaria pasar una version que escribiera «no tenemos ese correo» dentro de la vista</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="36">
       <c r="A126" s="67" t="inlineStr">
         <is>
-          <t>DEC-112</t>
+          <t>DEC-114</t>
         </is>
       </c>
       <c r="B126" s="68" t="inlineStr">
@@ -18483,24 +18570,24 @@
       <c r="C126" s="68" t="n"/>
       <c r="D126" s="69" t="inlineStr">
         <is>
-          <t>Los modulos se comunican por EVENTOS, no llamandose.</t>
+          <t>De un token de contrasena se guarda la HUELLA, nunca el token.</t>
         </is>
       </c>
       <c r="E126" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F126" s="69" t="inlineStr">
         <is>
-          <t>deptrac.yaml no deja que Creator conozca Communication ni al reves, y no es burocracia: si Creator importara Communication, un SMTP caido podria tumbar la captura de un dato fiscal. App\Shared\Eventos estrena domain_events --disenada en 2.4 y sin una sola fila hasta hoy-- y reparte asi: Creator levanta un nombre y un array, Communication recibe un nombre y un array, y ninguno importa al otro. El hecho se GUARDA antes de despachar, para que conste aunque el oyente reviente. Y no es la bitacora: Bitacora responde «quien toco que y que cambio» y es evidencia; esto responde «que paso, para que otros reaccionen» y dispara trabajo</t>
+          <t>bin2hex(random_bytes(32)) --no Str::random(), no uniqid(), no el uuid de la fila-- y en password_links solo entra su sha256. Misma decision que email_log (la huella del cuerpo, no el cuerpo) y que los medios de pago (la mascara, no el numero), y aqui es la mas importante de las tres: quien lea esta tabla no puede entrar en ninguna cuenta. Corolario que obligo a romper el patron de DEC-112: el aviso a Communication no puede ir por Eventos::ocurrio(), porque ese bus PERSISTE el payload y el payload lleva el enlace dentro. Va por un evento propio de Identity, que Communication ya tiene permitido conocer. El HECHO --«se emitio un enlace de tipo X para el usuario Y»-- si se guarda en domain_events, y sin el token</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="36">
       <c r="A127" s="67" t="inlineStr">
         <is>
-          <t>DEC-111</t>
+          <t>DEC-113</t>
         </is>
       </c>
       <c r="B127" s="68" t="inlineStr">
@@ -18511,24 +18598,24 @@
       <c r="C127" s="68" t="n"/>
       <c r="D127" s="69" t="inlineStr">
         <is>
-          <t>Si el aviso no se puede enviar, el cambio sigue adelante.</t>
+          <t>El enlace de alta dura 72 h; el de recuperacion, 1 h.</t>
         </is>
       </c>
       <c r="E127" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F127" s="69" t="inlineStr">
         <is>
-          <t>Bloquear la captura de un dato fiscal porque un SMTP se cayo convierte un problema de infraestructura en un creador al que no se le puede corregir un dato. Pero el fallo NO se traga: si el correo se encolo aparece en /correos como failed con su motivo, y si ni siquiera se pudo encolar --no hay plantilla, que es un fallo de configuracion-- se registra con report() y queda la fila de domain_events diciendo que el hecho ocurrio sin que saliera aviso</t>
+          <t>Son la misma pieza con dos relojes: el de alta llega SIN AVISAR y puede caer un viernes por la noche; el de recuperacion lo pide alguien que esta delante de la pantalla ahora. Un solo plazo obligaria a elegir entre dejar la ventana larga del alta valiendo para recuperar, o darle una hora a quien no sabia que iba a recibir nada. La caducidad se guarda en la fila, no es una constante global: un enlace sabe cuando muere</t>
         </is>
       </c>
     </row>
     <row r="128" ht="23.25" customHeight="1" s="36">
       <c r="A128" s="67" t="inlineStr">
         <is>
-          <t>DEC-110</t>
+          <t>DEC-112</t>
         </is>
       </c>
       <c r="B128" s="68" t="inlineStr">
@@ -18539,7 +18626,7 @@
       <c r="C128" s="68" t="n"/>
       <c r="D128" s="69" t="inlineStr">
         <is>
-          <t>El correo de aviso NO lleva el dato dentro.</t>
+          <t>Los modulos se comunican por EVENTOS, no llamandose.</t>
         </is>
       </c>
       <c r="E128" s="69" t="inlineStr">
@@ -18549,14 +18636,14 @@
       </c>
       <c r="F128" s="69" t="inlineStr">
         <is>
-          <t>«Alguien registro un cambio en sus datos de pago; si no ha sido usted, respondanos.» Sin numero, sin banco, sin regimen, sin RUC. Un correo se lee en pantallas ajenas, se reenvia y se queda en buzones que no controlamos --y el escenario del que nos defendemos es precisamente que alguien tenga acceso a ese buzon--. Para decir «yo no fui» no hace falta ver el numero. Misma regla que ya gobierna la bitacora (la mascara, nunca el numero) y email_log (la huella, nunca el cuerpo)</t>
+          <t>deptrac.yaml no deja que Creator conozca Communication ni al reves, y no es burocracia: si Creator importara Communication, un SMTP caido podria tumbar la captura de un dato fiscal. App\Shared\Eventos estrena domain_events --disenada en 2.4 y sin una sola fila hasta hoy-- y reparte asi: Creator levanta un nombre y un array, Communication recibe un nombre y un array, y ninguno importa al otro. El hecho se GUARDA antes de despachar, para que conste aunque el oyente reviente. Y no es la bitacora: Bitacora responde «quien toco que y que cambio» y es evidencia; esto responde «que paso, para que otros reaccionen» y dispara trabajo</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="36">
       <c r="A129" s="67" t="inlineStr">
         <is>
-          <t>DEC-109</t>
+          <t>DEC-111</t>
         </is>
       </c>
       <c r="B129" s="68" t="inlineStr">
@@ -18567,7 +18654,7 @@
       <c r="C129" s="68" t="n"/>
       <c r="D129" s="69" t="inlineStr">
         <is>
-          <t>El aviso de cambio sensible sale al CAPTURAR, no al aprobar.</t>
+          <t>Si el aviso no se puede enviar, el cambio sigue adelante.</t>
         </is>
       </c>
       <c r="E129" s="69" t="inlineStr">
@@ -18577,14 +18664,14 @@
       </c>
       <c r="F129" s="69" t="inlineStr">
         <is>
-          <t>Es lo unico que le da al creador margen para decir «yo no fui» mientras el cambio todavia se puede parar. Avisar despues de aprobarlo es contarle un hecho consumado: si alguien suplanto su cuenta bancaria, el dinero ya va camino de otro sitio. Hay prueba dedicada: el aviso sale con el perfil todavia en pending</t>
+          <t>Bloquear la captura de un dato fiscal porque un SMTP se cayo convierte un problema de infraestructura en un creador al que no se le puede corregir un dato. Pero el fallo NO se traga: si el correo se encolo aparece en /correos como failed con su motivo, y si ni siquiera se pudo encolar --no hay plantilla, que es un fallo de configuracion-- se registra con report() y queda la fila de domain_events diciendo que el hecho ocurrio sin que saliera aviso</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="36">
       <c r="A130" s="67" t="inlineStr">
         <is>
-          <t>DEC-108</t>
+          <t>DEC-110</t>
         </is>
       </c>
       <c r="B130" s="68" t="inlineStr">
@@ -18595,24 +18682,24 @@
       <c r="C130" s="68" t="n"/>
       <c r="D130" s="69" t="inlineStr">
         <is>
-          <t>Tres intentos espaciados (1, 5 y 15 minutos) y luego failed VISIBLE.</t>
+          <t>El correo de aviso NO lleva el dato dentro.</t>
         </is>
       </c>
       <c r="E130" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F130" s="69" t="inlineStr">
         <is>
-          <t>Cubre la caida pasajera del proveedor sin insistir eternamente sobre una direccion que no existe, que es la causa mas comun. ck_el_failed exige en la BASE que un fallido lleve cuando fallo Y por que: un failed sin motivo obliga a mirar el log del servidor, que es exactamente lo que esta tabla existe para evitar. Y la pantalla abre FILTRADA POR FALLIDOS, porque el modo de fallo que importa --«al creador no le llego su enlace»-- lo descubre operaciones, no un desarrollador leyendo storage/logs</t>
+          <t>«Alguien registro un cambio en sus datos de pago; si no ha sido usted, respondanos.» Sin numero, sin banco, sin regimen, sin RUC. Un correo se lee en pantallas ajenas, se reenvia y se queda en buzones que no controlamos --y el escenario del que nos defendemos es precisamente que alguien tenga acceso a ese buzon--. Para decir «yo no fui» no hace falta ver el numero. Misma regla que ya gobierna la bitacora (la mascara, nunca el numero) y email_log (la huella, nunca el cuerpo)</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="36">
       <c r="A131" s="67" t="inlineStr">
         <is>
-          <t>DEC-107</t>
+          <t>DEC-109</t>
         </is>
       </c>
       <c r="B131" s="68" t="inlineStr">
@@ -18623,24 +18710,24 @@
       <c r="C131" s="68" t="n"/>
       <c r="D131" s="69" t="inlineStr">
         <is>
-          <t>Sin plantilla en el idioma del destinatario se cae al de por defecto, y se ANOTA.</t>
+          <t>El aviso de cambio sensible sale al CAPTURAR, no al aprobar.</t>
         </is>
       </c>
       <c r="E131" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F131" s="69" t="inlineStr">
         <is>
-          <t>Un aviso que no llega es peor que uno en el idioma equivocado. Lo que hace que no sea una chapuza es la segunda mitad: email_log guarda locale_requested junto a template_locale, asi que «que plantillas faltan por traducir» es una consulta sobre envios reales, y sale en la pantalla como lo unico que pide una accion. Sin eso la caida seria silenciosa y nadie se enteraria nunca de que el portugues no existe. pt-BR cae antes a pt que a es: es una caida mucho mas pequena y son dos lineas</t>
+          <t>Es lo unico que le da al creador margen para decir «yo no fui» mientras el cambio todavia se puede parar. Avisar despues de aprobarlo es contarle un hecho consumado: si alguien suplanto su cuenta bancaria, el dinero ya va camino de otro sitio. Hay prueba dedicada: el aviso sale con el perfil todavia en pending</t>
         </is>
       </c>
     </row>
     <row r="132" ht="23.25" customHeight="1" s="36">
       <c r="A132" s="67" t="inlineStr">
         <is>
-          <t>DEC-106</t>
+          <t>DEC-108</t>
         </is>
       </c>
       <c r="B132" s="68" t="inlineStr">
@@ -18651,7 +18738,7 @@
       <c r="C132" s="68" t="n"/>
       <c r="D132" s="69" t="inlineStr">
         <is>
-          <t>Del correo enviado se guarda la HUELLA del cuerpo, no el cuerpo.</t>
+          <t>Tres intentos espaciados (1, 5 y 15 minutos) y luego failed VISIBLE.</t>
         </is>
       </c>
       <c r="E132" s="69" t="inlineStr">
@@ -18661,14 +18748,14 @@
       </c>
       <c r="F132" s="69" t="inlineStr">
         <is>
-          <t>email_log guarda plantilla, version, idioma, asunto y body_sha256. El cuerpo lleva el nombre de la persona, a veces importes y a veces datos fiscales: guardarlo convierte esa tabla en una SEGUNDA COPIA de la ficha del creador, que hay que proteger, anonimizar y borrar igual que la primera. Y no se pierde nada, porque la version de la plantilla es inmutable --publicar la siguiente cierra la anterior, no la edita-- y la huella demuestra que el cuerpo enviado era exactamente el que sale de renderizarla. «Me llegaron condiciones distintas» se contesta con la version y la huella. Es la regla del proyecto sobre logs, aplicada con cabeza</t>
+          <t>Cubre la caida pasajera del proveedor sin insistir eternamente sobre una direccion que no existe, que es la causa mas comun. ck_el_failed exige en la BASE que un fallido lleve cuando fallo Y por que: un failed sin motivo obliga a mirar el log del servidor, que es exactamente lo que esta tabla existe para evitar. Y la pantalla abre FILTRADA POR FALLIDOS, porque el modo de fallo que importa --«al creador no le llego su enlace»-- lo descubre operaciones, no un desarrollador leyendo storage/logs</t>
         </is>
       </c>
     </row>
     <row r="133" ht="23.25" customHeight="1" s="36">
       <c r="A133" s="67" t="inlineStr">
         <is>
-          <t>DEC-105</t>
+          <t>DEC-107</t>
         </is>
       </c>
       <c r="B133" s="68" t="inlineStr">
@@ -18679,24 +18766,24 @@
       <c r="C133" s="68" t="n"/>
       <c r="D133" s="69" t="inlineStr">
         <is>
-          <t>Pasarse del presupuesto de creadores se BLOQUEA, y finanzas lo autoriza dejando el motivo.</t>
+          <t>Sin plantilla en el idioma del destinatario se cae al de por defecto, y se ANOTA.</t>
         </is>
       </c>
       <c r="E133" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F133" s="69" t="inlineStr">
         <is>
-          <t>La regla dice «sin aprobacion explicita de un rol autorizado, que queda auditada», asi que la autorizacion es un dato de la fila: quien, cuando y por que. ck_camp_budget_override exige las tres o ninguna --una firma sin explicacion no responde «por que esta campana se paso» dentro de un ano, misma forma que ck_inv_responded--. Lo firma finanzas y no quien monto la campana (DEC-091, DEC-044), y el motivo exige al menos diez caracteres porque «porque» no es una explicacion. Lo que cuenta como comprometido son las participaciones VIVAS: un creador que rechazo no consume presupuesto, y contarlo dejaria campanas bloqueadas por dinero que nadie se va a gastar</t>
+          <t>Un aviso que no llega es peor que uno en el idioma equivocado. Lo que hace que no sea una chapuza es la segunda mitad: email_log guarda locale_requested junto a template_locale, asi que «que plantillas faltan por traducir» es una consulta sobre envios reales, y sale en la pantalla como lo unico que pide una accion. Sin eso la caida seria silenciosa y nadie se enteraria nunca de que el portugues no existe. pt-BR cae antes a pt que a es: es una caida mucho mas pequena y son dos lineas</t>
         </is>
       </c>
     </row>
     <row r="134" ht="23.25" customHeight="1" s="36">
       <c r="A134" s="67" t="inlineStr">
         <is>
-          <t>DEC-104</t>
+          <t>DEC-106</t>
         </is>
       </c>
       <c r="B134" s="68" t="inlineStr">
@@ -18707,24 +18794,24 @@
       <c r="C134" s="68" t="n"/>
       <c r="D134" s="69" t="inlineStr">
         <is>
-          <t>El monto acordado se fija al INVITAR y se congela al ACEPTAR.</t>
+          <t>Del correo enviado se guarda la HUELLA del cuerpo, no el cuerpo.</t>
         </is>
       </c>
       <c r="E134" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F134" s="69" t="inlineStr">
         <is>
-          <t>BR-CREATOR-008: la tarifa declarada es referencia, el precio vinculante es el monto congelado en la participacion. Se fija al invitar porque el creador no puede aceptar un numero que no ha visto --tg_ccr_compromiso impide pasar a invited con cero-- y se congela al aceptar porque a partir de ahi es un acuerdo entre dos partes. Congelarlo ya en la invitacion obligaria a cancelar y rehacerla por un dedazo, llenando el historico de invitaciones canceladas que no se cancelaron por negocio: mismo argumento que DEC-090. Excepcion coherente con 7.2: en una campana declarada gratuita si se invita con cero</t>
+          <t>email_log guarda plantilla, version, idioma, asunto y body_sha256. El cuerpo lleva el nombre de la persona, a veces importes y a veces datos fiscales: guardarlo convierte esa tabla en una SEGUNDA COPIA de la ficha del creador, que hay que proteger, anonimizar y borrar igual que la primera. Y no se pierde nada, porque la version de la plantilla es inmutable --publicar la siguiente cierra la anterior, no la edita-- y la huella demuestra que el cuerpo enviado era exactamente el que sale de renderizarla. «Me llegaron condiciones distintas» se contesta con la version y la huella. Es la regla del proyecto sobre logs, aplicada con cabeza</t>
         </is>
       </c>
     </row>
     <row r="135" ht="23.25" customHeight="1" s="36">
       <c r="A135" s="67" t="inlineStr">
         <is>
-          <t>DEC-103</t>
+          <t>DEC-105</t>
         </is>
       </c>
       <c r="B135" s="68" t="inlineStr">
@@ -18735,7 +18822,7 @@
       <c r="C135" s="68" t="n"/>
       <c r="D135" s="69" t="inlineStr">
         <is>
-          <t>«2 reels» en el brief es lo que entrega CADA creador, no el total de la campana.</t>
+          <t>Pasarse del presupuesto de creadores se BLOQUEA, y finanzas lo autoriza dejando el motivo.</t>
         </is>
       </c>
       <c r="E135" s="69" t="inlineStr">
@@ -18745,14 +18832,14 @@
       </c>
       <c r="F135" s="69" t="inlineStr">
         <is>
-          <t>El brief es lo que se le dice a UNA persona; cuantos creadores hay lo dice target_creators de cada mercado (7.3). La alternativa --repartir un total entre los seleccionados-- obliga a decidir quien entrega que y a recalcular cada vez que alguien entra o sale, y un creador no sabria que acepta hasta que la lista este cerrada. Ademas confirma lo ya construido: el coste estimado de 7.4 ya multiplicaba tarifa por cantidad</t>
+          <t>La regla dice «sin aprobacion explicita de un rol autorizado, que queda auditada», asi que la autorizacion es un dato de la fila: quien, cuando y por que. ck_camp_budget_override exige las tres o ninguna --una firma sin explicacion no responde «por que esta campana se paso» dentro de un ano, misma forma que ck_inv_responded--. Lo firma finanzas y no quien monto la campana (DEC-091, DEC-044), y el motivo exige al menos diez caracteres porque «porque» no es una explicacion. Lo que cuenta como comprometido son las participaciones VIVAS: un creador que rechazo no consume presupuesto, y contarlo dejaria campanas bloqueadas por dinero que nadie se va a gastar</t>
         </is>
       </c>
     </row>
     <row r="136" ht="23.25" customHeight="1" s="36">
       <c r="A136" s="67" t="inlineStr">
         <is>
-          <t>DEC-102</t>
+          <t>DEC-104</t>
         </is>
       </c>
       <c r="B136" s="68" t="inlineStr">
@@ -18763,24 +18850,24 @@
       <c r="C136" s="68" t="n"/>
       <c r="D136" s="69" t="inlineStr">
         <is>
-          <t>Nadie entra en una campana cerrada, y una participacion que ya estaba solo se puede cancelar.</t>
+          <t>El monto acordado se fija al INVITAR y se congela al ACEPTAR.</t>
         </is>
       </c>
       <c r="E136" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F136" s="69" t="inlineStr">
         <is>
-          <t>campaign_creators existia desde la Fase 2 y hasta 7.4 nadie habia escrito una fila; en cuanto se escribe la primera aparece el hueco. Una participacion en una campana terminada devenga en el ledger (9.3) contra un periodo ya liquidado, sale en el reporte «reproducible» del cliente (10.4) y cuenta en el Creator Score (14.3) por un trabajo que nunca existio. Disparadores y no CHECK porque la condicion esta en otra tabla. El de UPDATE hace falta aparte porque cerrar la campana y mover al creador son operaciones distintas; se deja pasar cancelled porque cerrar una campana con candidatos dentro tiene que poder dejarlos resueltos, y la alternativa seria borrar la fila --lo que 3.12 prohibe--</t>
+          <t>BR-CREATOR-008: la tarifa declarada es referencia, el precio vinculante es el monto congelado en la participacion. Se fija al invitar porque el creador no puede aceptar un numero que no ha visto --tg_ccr_compromiso impide pasar a invited con cero-- y se congela al aceptar porque a partir de ahi es un acuerdo entre dos partes. Congelarlo ya en la invitacion obligaria a cancelar y rehacerla por un dedazo, llenando el historico de invitaciones canceladas que no se cancelaron por negocio: mismo argumento que DEC-090. Excepcion coherente con 7.2: en una campana declarada gratuita si se invita con cero</t>
         </is>
       </c>
     </row>
     <row r="137" ht="23.25" customHeight="1" s="36">
       <c r="A137" s="67" t="inlineStr">
         <is>
-          <t>DEC-101</t>
+          <t>DEC-103</t>
         </is>
       </c>
       <c r="B137" s="68" t="inlineStr">
@@ -18791,24 +18878,24 @@
       <c r="C137" s="68" t="n"/>
       <c r="D137" s="69" t="inlineStr">
         <is>
-          <t>En la lista corta se entra a un mercado CONCRETO, derivado del pais del creador.</t>
+          <t>«2 reels» en el brief es lo que entrega CADA creador, no el total de la campana.</t>
         </is>
       </c>
       <c r="E137" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F137" s="69" t="inlineStr">
         <is>
-          <t>No se pide: es el unico que puede ser, y pedirlo seria pedirle al operador que repita un dato que el sistema ya sabe. De ahi sale el cupo por mercado (target_creators, 7.3) y el reparto de entregables por pais en 7.5. agreed_amount nace en CERO a proposito: el compromiso economico se congela al aceptar (BR-CREATOR-008), no al meter a alguien en una lista, y un candidato con importe es un acuerdo que nadie ha firmado</t>
+          <t>El brief es lo que se le dice a UNA persona; cuantos creadores hay lo dice target_creators de cada mercado (7.3). La alternativa --repartir un total entre los seleccionados-- obliga a decidir quien entrega que y a recalcular cada vez que alguien entra o sale, y un creador no sabria que acepta hasta que la lista este cerrada. Ademas confirma lo ya construido: el coste estimado de 7.4 ya multiplicaba tarifa por cantidad</t>
         </is>
       </c>
     </row>
     <row r="138" ht="34.5" customHeight="1" s="36">
       <c r="A138" s="67" t="inlineStr">
         <is>
-          <t>DEC-100</t>
+          <t>DEC-102</t>
         </is>
       </c>
       <c r="B138" s="68" t="inlineStr">
@@ -18819,7 +18906,7 @@
       <c r="C138" s="68" t="n"/>
       <c r="D138" s="69" t="inlineStr">
         <is>
-          <t>Una categoria que el creador declaro que NO trabaja lo excluye del buscador.</t>
+          <t>Nadie entra en una campana cerrada, y una participacion que ya estaba solo se puede cancelar.</t>
         </is>
       </c>
       <c r="E138" s="69" t="inlineStr">
@@ -18829,14 +18916,14 @@
       </c>
       <c r="F138" s="69" t="inlineStr">
         <is>
-          <t>Es media BR-CAMPAIGN-007 --roja, y hasta 7.4 sin nada detras-- y es la mitad que ya se puede comprobar con lo que hay en el modelo: creator_restrictions contra client_brand_categories. El creador ya dijo que no; invitarlo es hacerle perder el tiempo a los dos. Se sigue viendo con el interruptor de descartados, para poder auditar por que falta alguien. Competidores y exclusividades vigentes llegan en 7.11</t>
+          <t>campaign_creators existia desde la Fase 2 y hasta 7.4 nadie habia escrito una fila; en cuanto se escribe la primera aparece el hueco. Una participacion en una campana terminada devenga en el ledger (9.3) contra un periodo ya liquidado, sale en el reporte «reproducible» del cliente (10.4) y cuenta en el Creator Score (14.3) por un trabajo que nunca existio. Disparadores y no CHECK porque la condicion esta en otra tabla. El de UPDATE hace falta aparte porque cerrar la campana y mover al creador son operaciones distintas; se deja pasar cancelled porque cerrar una campana con candidatos dentro tiene que poder dejarlos resueltos, y la alternativa seria borrar la fila --lo que 3.12 prohibe--</t>
         </is>
       </c>
     </row>
     <row r="139" ht="23.25" customHeight="1" s="36">
       <c r="A139" s="67" t="inlineStr">
         <is>
-          <t>DEC-099</t>
+          <t>DEC-101</t>
         </is>
       </c>
       <c r="B139" s="68" t="inlineStr">
@@ -18847,7 +18934,7 @@
       <c r="C139" s="68" t="n"/>
       <c r="D139" s="69" t="inlineStr">
         <is>
-          <t>El buscador ensena a todos los activos; el veto real salta al anadir.</t>
+          <t>En la lista corta se entra a un mercado CONCRETO, derivado del pais del creador.</t>
         </is>
       </c>
       <c r="E139" s="69" t="inlineStr">
@@ -18857,14 +18944,14 @@
       </c>
       <c r="F139" s="69" t="inlineStr">
         <is>
-          <t>Un creador activado en junio al que en agosto se le retiro el medio de pago sigue con status = 'active': sale en la busqueda, con lo que le falta a la vista, y NO entra en la lista corta. Dos motivos: revalidar los seis requisitos de BR-CREATOR-006 por candidato y por busqueda es caro --en el veto se hace una vez, sobre uno-- y un creador que desaparece sin explicacion parece un fallo del sistema, mientras que uno que sale con «le falta el medio de pago» es una tarea. El veto usa CompletitudOperativa, la MISMA clase que decide la activacion y no una copia: si manana se anade un septimo requisito, lo hereda sin que nadie se acuerde de venir aqui</t>
+          <t>No se pide: es el unico que puede ser, y pedirlo seria pedirle al operador que repita un dato que el sistema ya sabe. De ahi sale el cupo por mercado (target_creators, 7.3) y el reparto de entregables por pais en 7.5. agreed_amount nace en CERO a proposito: el compromiso economico se congela al aceptar (BR-CREATOR-008), no al meter a alguien en una lista, y un candidato con importe es un acuerdo que nadie ha firmado</t>
         </is>
       </c>
     </row>
     <row r="140" ht="23.25" customHeight="1" s="36">
       <c r="A140" s="67" t="inlineStr">
         <is>
-          <t>DEC-098</t>
+          <t>DEC-100</t>
         </is>
       </c>
       <c r="B140" s="68" t="inlineStr">
@@ -18875,24 +18962,24 @@
       <c r="C140" s="68" t="n"/>
       <c r="D140" s="69" t="inlineStr">
         <is>
-          <t>Que el mercado sea DE la campana lo garantiza el esquema, con foraneas COMPUESTAS.</t>
+          <t>Una categoria que el creador declaro que NO trabaja lo excluye del buscador.</t>
         </is>
       </c>
       <c r="E140" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F140" s="69" t="inlineStr">
         <is>
-          <t>campaign_requirements.campaign_market_id y campaign_creators.campaign_market_id apuntaban a campaign_markets(id), y una foranea asi solo comprueba que el mercado exista: nada impedia un requisito de la campana A colgado del mercado de la campana B, ni un creador aceptado atribuido al pais de otra campana. Se anade uq_cm_id_campaign (id, campaign_id) --redundante como clave, necesaria como destino-- y las dos foraneas pasan a (campaign_market_id, campaign_id). Se prefiere a un disparador porque la comprueba el motor en las dos direcciones --tambien impide mover un mercado de campana-- y porque Percona 5.7 si tiene foraneas compuestas. Y el NULL con significado de N-03 sobrevive sin un caso especial: en MySQL una foranea compuesta con un componente NULL no se comprueba</t>
+          <t>Es media BR-CAMPAIGN-007 --roja, y hasta 7.4 sin nada detras-- y es la mitad que ya se puede comprobar con lo que hay en el modelo: creator_restrictions contra client_brand_categories. El creador ya dijo que no; invitarlo es hacerle perder el tiempo a los dos. Se sigue viendo con el interruptor de descartados, para poder auditar por que falta alguien. Competidores y exclusividades vigentes llegan en 7.11</t>
         </is>
       </c>
     </row>
     <row r="141" ht="34.5" customHeight="1" s="36">
       <c r="A141" s="67" t="inlineStr">
         <is>
-          <t>DEC-097</t>
+          <t>DEC-099</t>
         </is>
       </c>
       <c r="B141" s="68" t="inlineStr">
@@ -18903,24 +18990,24 @@
       <c r="C141" s="68" t="n"/>
       <c r="D141" s="69" t="inlineStr">
         <is>
-          <t>El pais de un mercado no necesita cobertura de facturacion.</t>
+          <t>El buscador ensena a todos los activos; el veto real salta al anadir.</t>
         </is>
       </c>
       <c r="E141" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F141" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-003 resuelve quien factura por el pais del CLIENTE: un cliente peruano puede pagar una campana que corre en Colombia sin que el grupo tenga sociedad alli, y exigir cobertura en el mercado bloquearia hoy toda campana fuera de Peru. Lo que si puede hacer falta es como se le paga a un creador colombiano, y eso es Q-40, que sigue abierta y desde 7.3 tiene caso de uso</t>
+          <t>Un creador activado en junio al que en agosto se le retiro el medio de pago sigue con status = 'active': sale en la busqueda, con lo que le falta a la vista, y NO entra en la lista corta. Dos motivos: revalidar los seis requisitos de BR-CREATOR-006 por candidato y por busqueda es caro --en el veto se hace una vez, sobre uno-- y un creador que desaparece sin explicacion parece un fallo del sistema, mientras que uno que sale con «le falta el medio de pago» es una tarea. El veto usa CompletitudOperativa, la MISMA clase que decide la activacion y no una copia: si manana se anade un septimo requisito, lo hereda sin que nadie se acuerde de venir aqui</t>
         </is>
       </c>
     </row>
     <row r="142" ht="23.25" customHeight="1" s="36">
       <c r="A142" s="67" t="inlineStr">
         <is>
-          <t>DEC-096</t>
+          <t>DEC-098</t>
         </is>
       </c>
       <c r="B142" s="68" t="inlineStr">
@@ -18931,7 +19018,7 @@
       <c r="C142" s="68" t="n"/>
       <c r="D142" s="69" t="inlineStr">
         <is>
-          <t>De una campana confirmada se ANADE un mercado, no se quita.</t>
+          <t>Que el mercado sea DE la campana lo garantiza el esquema, con foraneas COMPUESTAS.</t>
         </is>
       </c>
       <c r="E142" s="69" t="inlineStr">
@@ -18941,14 +19028,14 @@
       </c>
       <c r="F142" s="69" t="inlineStr">
         <is>
-          <t>Ampliar a un pais nuevo es una decision comercial normal y no rompe nada de lo prometido; quitar puede dejar fuera a creadores ya invitados o aceptados, y eso exige una enmienda aceptada por las dos partes (BR-CAMPAIGN-003). Lo impide tg_cm_no_quitar_confirmada, un BEFORE DELETE que mira el estado de la CAMPANA y no una columna propia: el congelado de un mercado no es un hecho del mercado. Y hace falta el disparador precisamente porque la regla es asimetrica: una simetrica --«confirmada, no se toca»-- se explica de memoria; una asimetrica se olvida en la mitad de los sitios</t>
+          <t>campaign_requirements.campaign_market_id y campaign_creators.campaign_market_id apuntaban a campaign_markets(id), y una foranea asi solo comprueba que el mercado exista: nada impedia un requisito de la campana A colgado del mercado de la campana B, ni un creador aceptado atribuido al pais de otra campana. Se anade uq_cm_id_campaign (id, campaign_id) --redundante como clave, necesaria como destino-- y las dos foraneas pasan a (campaign_market_id, campaign_id). Se prefiere a un disparador porque la comprueba el motor en las dos direcciones --tambien impide mover un mercado de campana-- y porque Percona 5.7 si tiene foraneas compuestas. Y el NULL con significado de N-03 sobrevive sin un caso especial: en MySQL una foranea compuesta con un componente NULL no se comprueba</t>
         </is>
       </c>
     </row>
     <row r="143" ht="23.25" customHeight="1" s="36">
       <c r="A143" s="67" t="inlineStr">
         <is>
-          <t>DEC-095</t>
+          <t>DEC-097</t>
         </is>
       </c>
       <c r="B143" s="68" t="inlineStr">
@@ -18959,7 +19046,7 @@
       <c r="C143" s="68" t="n"/>
       <c r="D143" s="69" t="inlineStr">
         <is>
-          <t>Una campana necesita al menos un mercado para salir de borrador.</t>
+          <t>El pais de un mercado no necesita cobertura de facturacion.</t>
         </is>
       </c>
       <c r="E143" s="69" t="inlineStr">
@@ -18969,14 +19056,14 @@
       </c>
       <c r="F143" s="69" t="inlineStr">
         <is>
-          <t>Tercer motivo de BR-CAMPAIGN-004, junto al brief y al ingreso declarado. Una campana que no dice donde se ejecuta es una campana que nadie puede empezar: de ahi sale a quien se puede invitar (7.4). Cliente y marca los garantiza el esquema; el mercado no puede --un CHECK no cuenta filas de otra tabla-- asi que vive en Campanas::loQueFaltaParaSalirDeBorrador(), con los otros dos y diciendolos todos de una vez</t>
+          <t>BR-LE-003 resuelve quien factura por el pais del CLIENTE: un cliente peruano puede pagar una campana que corre en Colombia sin que el grupo tenga sociedad alli, y exigir cobertura en el mercado bloquearia hoy toda campana fuera de Peru. Lo que si puede hacer falta es como se le paga a un creador colombiano, y eso es Q-40, que sigue abierta y desde 7.3 tiene caso de uso</t>
         </is>
       </c>
     </row>
     <row r="144" ht="23.25" customHeight="1" s="36">
       <c r="A144" s="67" t="inlineStr">
         <is>
-          <t>DEC-094</t>
+          <t>DEC-096</t>
         </is>
       </c>
       <c r="B144" s="68" t="inlineStr">
@@ -18987,24 +19074,24 @@
       <c r="C144" s="68" t="n"/>
       <c r="D144" s="69" t="inlineStr">
         <is>
-          <t>La regla se recorta a los estados NO iniciales, como sus dos hermanas.</t>
+          <t>De una campana confirmada se ANADE un mercado, no se quita.</t>
         </is>
       </c>
       <c r="E144" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F144" s="69" t="inlineStr">
         <is>
-          <t>La primera version de ck_camp_revenue_declarado no lo hacia y habria rechazado toda campana recien creada: revenue_amount e is_gratis nacen los dos a cero, asi que el formulario vacio violaba la regla antes de que nadie pudiera teclear el precio. Es la misma forma que ck_camp_confirmed y ck_camp_billing_entity: *o estas todavia escribiendo la campana, o el dato existe*. Un borrador tiene derecho a estar a medias; lo que no puede es salir de ahi asi</t>
+          <t>Ampliar a un pais nuevo es una decision comercial normal y no rompe nada de lo prometido; quitar puede dejar fuera a creadores ya invitados o aceptados, y eso exige una enmienda aceptada por las dos partes (BR-CAMPAIGN-003). Lo impide tg_cm_no_quitar_confirmada, un BEFORE DELETE que mira el estado de la CAMPANA y no una columna propia: el congelado de un mercado no es un hecho del mercado. Y hace falta el disparador precisamente porque la regla es asimetrica: una simetrica --«confirmada, no se toca»-- se explica de memoria; una asimetrica se olvida en la mitad de los sitios</t>
         </is>
       </c>
     </row>
     <row r="145" ht="23.25" customHeight="1" s="36">
       <c r="A145" s="67" t="inlineStr">
         <is>
-          <t>DEC-093</t>
+          <t>DEC-095</t>
         </is>
       </c>
       <c r="B145" s="68" t="inlineStr">
@@ -19015,24 +19102,24 @@
       <c r="C145" s="68" t="n"/>
       <c r="D145" s="69" t="inlineStr">
         <is>
-          <t>Ingreso cero es valido, pero hay que declararlo.</t>
+          <t>Una campana necesita al menos un mercado para salir de borrador.</t>
         </is>
       </c>
       <c r="E145" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F145" s="69" t="inlineStr">
         <is>
-          <t>revenue_amount = 0 respondia a dos preguntas distintas con el mismo numero --«esta campana se regala» (canje, cortesia, prueba) y «nadie le ha puesto precio»--, y ante un margen descuadrado la diferencia entre las dos es la diferencia entre «salio como se planeo» y «se nos escapo». Columna is_gratis y ck_camp_revenue_declarado. Va en la BASE y no en la pantalla porque la pregunta que hay que poder responder dentro de un ano es «¿esta campana de cero se regalo o se nos olvido cobrarla?», y esa respuesta tiene que sobrevivir a una importacion y a la proxima pantalla que alguien escriba. Mismo valor por omision que parecia una respuesta que DEC-048 y DEC-068</t>
+          <t>Tercer motivo de BR-CAMPAIGN-004, junto al brief y al ingreso declarado. Una campana que no dice donde se ejecuta es una campana que nadie puede empezar: de ahi sale a quien se puede invitar (7.4). Cliente y marca los garantiza el esquema; el mercado no puede --un CHECK no cuenta filas de otra tabla-- asi que vive en Campanas::loQueFaltaParaSalirDeBorrador(), con los otros dos y diciendolos todos de una vez</t>
         </is>
       </c>
     </row>
     <row r="146" ht="23.25" customHeight="1" s="36">
       <c r="A146" s="67" t="inlineStr">
         <is>
-          <t>DEC-092</t>
+          <t>DEC-094</t>
         </is>
       </c>
       <c r="B146" s="68" t="inlineStr">
@@ -19043,7 +19130,7 @@
       <c r="C146" s="68" t="n"/>
       <c r="D146" s="69" t="inlineStr">
         <is>
-          <t>«Brief definido» son los REQUISITOS, no el texto del briefing.</t>
+          <t>La regla se recorta a los estados NO iniciales, como sus dos hermanas.</t>
         </is>
       </c>
       <c r="E146" s="69" t="inlineStr">
@@ -19053,14 +19140,14 @@
       </c>
       <c r="F146" s="69" t="inlineStr">
         <is>
-          <t>BR-CAMPAIGN-004 exige «brief definido» para aprobar y no dice que es. Se decide: al menos una fila en campaign_requirements --un formato, una cantidad, un plazo--. El campo briefing sigue siendo texto libre opcional porque no se puede comprobar de verdad: un espacio en blanco cumpliria cualquier NOT NULL, asi que exigirlo anadiria friccion sin anadir garantia. Los formatos si se comprueban, y son lo que convierte «hay una campana» en «hay algo que entregar»: es lo minimo que un creador necesita para decidir si acepta</t>
+          <t>La primera version de ck_camp_revenue_declarado no lo hacia y habria rechazado toda campana recien creada: revenue_amount e is_gratis nacen los dos a cero, asi que el formulario vacio violaba la regla antes de que nadie pudiera teclear el precio. Es la misma forma que ck_camp_confirmed y ck_camp_billing_entity: *o estas todavia escribiendo la campana, o el dato existe*. Un borrador tiene derecho a estar a medias; lo que no puede es salir de ahi asi</t>
         </is>
       </c>
     </row>
     <row r="147" ht="23.25" customHeight="1" s="36">
       <c r="A147" s="67" t="inlineStr">
         <is>
-          <t>DEC-091</t>
+          <t>DEC-093</t>
         </is>
       </c>
       <c r="B147" s="68" t="inlineStr">
@@ -19071,24 +19158,24 @@
       <c r="C147" s="68" t="n"/>
       <c r="D147" s="69" t="inlineStr">
         <is>
-          <t>Aprobar una campana es de finanzas, no de quien la monta.</t>
+          <t>Ingreso cero es valido, pero hay que declararlo.</t>
         </is>
       </c>
       <c r="E147" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F147" s="69" t="inlineStr">
         <is>
-          <t>Aprobar fija el ingreso comprometido y congela la sociedad emisora: es una decision de dinero, y la misma separacion que DEC-044 impone en la base para perfiles fiscales y medios de pago. Permiso nuevo campaign.approve, y vive en el GRAFO de transiciones, no en la ruta: una ruta con permiso fijo obligaria a partir la accion en dos y a acordarse de las dos al anadir un estado</t>
+          <t>revenue_amount = 0 respondia a dos preguntas distintas con el mismo numero --«esta campana se regala» (canje, cortesia, prueba) y «nadie le ha puesto precio»--, y ante un margen descuadrado la diferencia entre las dos es la diferencia entre «salio como se planeo» y «se nos escapo». Columna is_gratis y ck_camp_revenue_declarado. Va en la BASE y no en la pantalla porque la pregunta que hay que poder responder dentro de un ano es «¿esta campana de cero se regalo o se nos olvido cobrarla?», y esa respuesta tiene que sobrevivir a una importacion y a la proxima pantalla que alguien escriba. Mismo valor por omision que parecia una respuesta que DEC-048 y DEC-068</t>
         </is>
       </c>
     </row>
     <row r="148" ht="23.25" customHeight="1" s="36">
       <c r="A148" s="67" t="inlineStr">
         <is>
-          <t>DEC-090</t>
+          <t>DEC-092</t>
         </is>
       </c>
       <c r="B148" s="68" t="inlineStr">
@@ -19099,24 +19186,24 @@
       <c r="C148" s="68" t="n"/>
       <c r="D148" s="69" t="inlineStr">
         <is>
-          <t>Se congela al confirmar, no al salir de borrador.</t>
+          <t>«Brief definido» son los REQUISITOS, no el texto del briefing.</t>
         </is>
       </c>
       <c r="E148" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F148" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-002 dice «inmutable una vez emitido» y para una campana «emitido» es ambiguo. Mientras es draft o pending_approval se corrige un dedazo; con confirmed_at puesto, no se toca. Lo impone tg_camp_entidad_congelada y no el controlador: de este dato depende que una factura de dentro de dos anos siga sabiendo quien la emitio, asi que tiene que sobrevivir a un UPDATE de mantenimiento. La alternativa --congelar al salir de borrador-- llenaria el historico de campanas cancelled que no se cancelaron por negocio, y un estado que miente sobre por que existe es peor que un campo editable un rato mas</t>
+          <t>BR-CAMPAIGN-004 exige «brief definido» para aprobar y no dice que es. Se decide: al menos una fila en campaign_requirements --un formato, una cantidad, un plazo--. El campo briefing sigue siendo texto libre opcional porque no se puede comprobar de verdad: un espacio en blanco cumpliria cualquier NOT NULL, asi que exigirlo anadiria friccion sin anadir garantia. Los formatos si se comprueban, y son lo que convierte «hay una campana» en «hay algo que entregar»: es lo minimo que un creador necesita para decidir si acepta</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="36">
       <c r="A149" s="67" t="inlineStr">
         <is>
-          <t>DEC-089</t>
+          <t>DEC-091</t>
         </is>
       </c>
       <c r="B149" s="68" t="inlineStr">
@@ -19127,7 +19214,7 @@
       <c r="C149" s="68" t="n"/>
       <c r="D149" s="69" t="inlineStr">
         <is>
-          <t>La sociedad que factura una campana se resuelve a starts_on.</t>
+          <t>Aprobar una campana es de finanzas, no de quien la monta.</t>
         </is>
       </c>
       <c r="E149" s="69" t="inlineStr">
@@ -19137,14 +19224,14 @@
       </c>
       <c r="F149" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-003 dice «en la fecha de la operacion»; para una campana esa fecha es cuando empieza a prestarse el servicio, que es lo que un contador defiende ante SUNAT. Consecuencia: una campana creada en diciembre para arrancar en febrero usa la cobertura de FEBRERO, asi que si la cobertura cambia el 1 de enero la campana nace ya con la sociedad correcta en vez de con una que habria que corregir --y corregirla es justo lo que DEC-090 impide--</t>
+          <t>Aprobar fija el ingreso comprometido y congela la sociedad emisora: es una decision de dinero, y la misma separacion que DEC-044 impone en la base para perfiles fiscales y medios de pago. Permiso nuevo campaign.approve, y vive en el GRAFO de transiciones, no en la ruta: una ruta con permiso fijo obligaria a partir la accion en dos y a acordarse de las dos al anadir un estado</t>
         </is>
       </c>
     </row>
     <row r="150" ht="68.25" customHeight="1" s="36">
       <c r="A150" s="67" t="inlineStr">
         <is>
-          <t>DEC-088</t>
+          <t>DEC-090</t>
         </is>
       </c>
       <c r="B150" s="68" t="inlineStr">
@@ -19155,24 +19242,24 @@
       <c r="C150" s="68" t="n"/>
       <c r="D150" s="69" t="inlineStr">
         <is>
-          <t>La aritmetica de vigencias vive en Vigencia, y una puerta lo comprueba.</t>
+          <t>Se congela al confirmar, no al salir de borrador.</t>
         </is>
       </c>
       <c r="E150" s="69" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="F150" s="69" t="inlineStr">
         <is>
-          <t>El error de un dia --cerrar un periodo el mismo dia en que empieza el siguiente, siendo valid_to inclusivo-- ha aparecido NUEVE veces. Vigencia (4.5) le dio un sitio; tools/verificar-vigencias.php impide que vuelva a salir de el. Dos reglas: ninguna aritmetica de dias fuera de Vigencia, y ninguna comparacion de una columna de vigencia contra algo sin normalizar. Escrita en PHP con token_get_all() y no en Python con expresiones regulares, porque los comentarios de este proyecto nombran el defecto y las migraciones llevan SQL con &gt;= dentro: una regex se acusaria a si misma. Al estrenarla quedaban tres sitios sueltos, los tres escritos DESPUES de Vigencia, y uno era un fallo real ----desde=2026-2-1 contra effective_from como cadenas, dejando dos textos legales vigentes el mismo dia--. Ver docs/fase-4/4.7-PUERTA-VIGENCIAS.md</t>
+          <t>BR-LE-002 dice «inmutable una vez emitido» y para una campana «emitido» es ambiguo. Mientras es draft o pending_approval se corrige un dedazo; con confirmed_at puesto, no se toca. Lo impone tg_camp_entidad_congelada y no el controlador: de este dato depende que una factura de dentro de dos anos siga sabiendo quien la emitio, asi que tiene que sobrevivir a un UPDATE de mantenimiento. La alternativa --congelar al salir de borrador-- llenaria el historico de campanas cancelled que no se cancelaron por negocio, y un estado que miente sobre por que existe es peor que un campo editable un rato mas</t>
         </is>
       </c>
     </row>
     <row r="151" ht="23.25" customHeight="1" s="36">
       <c r="A151" s="67" t="inlineStr">
         <is>
-          <t>DEC-087</t>
+          <t>DEC-089</t>
         </is>
       </c>
       <c r="B151" s="68" t="inlineStr">
@@ -19183,24 +19270,24 @@
       <c r="C151" s="68" t="n"/>
       <c r="D151" s="69" t="inlineStr">
         <is>
-          <t>Un 1062 se absorbe o se cuenta segun quien eligio el valor, y hay que NOMBRAR el indice para absorberlo.</t>
+          <t>La sociedad que factura una campana se resuelve a starts_on.</t>
         </is>
       </c>
       <c r="E151" s="69" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="F151" s="69" t="inlineStr">
         <is>
-          <t>Si el valor lo calculo el sistema —el slug de una marca— el choque se recalcula y se reintenta en silencio. Si lo escribio la persona —un RUC, el nombre de una marca— tiene que llegar arriba con palabras. App\Shared\Database\Choque obliga a elegir: reintentar() exige el nombre del indice y vuelve a lanzar cualquier otro a la primera, porque un catch (QueryException) a secas absorberia el RUC repetido igual que el slug. Tres intentos como tope: un bucle sin tope convierte un indice mal entendido en una peticion eterna. El nombre se lee cortando por el ultimo punto —MySQL 8 antepone la tabla y Percona 5.7 no—, comprobado contra los dos motores</t>
+          <t>BR-LE-003 dice «en la fecha de la operacion»; para una campana esa fecha es cuando empieza a prestarse el servicio, que es lo que un contador defiende ante SUNAT. Consecuencia: una campana creada en diciembre para arrancar en febrero usa la cobertura de FEBRERO, asi que si la cobertura cambia el 1 de enero la campana nace ya con la sociedad correcta en vez de con una que habria que corregir --y corregirla es justo lo que DEC-090 impide--</t>
         </is>
       </c>
     </row>
     <row r="152" ht="34.5" customHeight="1" s="36">
       <c r="A152" s="67" t="inlineStr">
         <is>
-          <t>DEC-086</t>
+          <t>DEC-088</t>
         </is>
       </c>
       <c r="B152" s="68" t="inlineStr">
@@ -19211,16 +19298,24 @@
       <c r="C152" s="68" t="n"/>
       <c r="D152" s="69" t="inlineStr">
         <is>
-          <t>La contraseña temporal deja de ser válida en el primer acceso</t>
-        </is>
-      </c>
-      <c r="E152" s="69" t="n"/>
-      <c r="F152" s="69" t="n"/>
+          <t>La aritmetica de vigencias vive en Vigencia, y una puerta lo comprueba.</t>
+        </is>
+      </c>
+      <c r="E152" s="69" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="F152" s="69" t="inlineStr">
+        <is>
+          <t>El error de un dia --cerrar un periodo el mismo dia en que empieza el siguiente, siendo valid_to inclusivo-- ha aparecido NUEVE veces. Vigencia (4.5) le dio un sitio; tools/verificar-vigencias.php impide que vuelva a salir de el. Dos reglas: ninguna aritmetica de dias fuera de Vigencia, y ninguna comparacion de una columna de vigencia contra algo sin normalizar. Escrita en PHP con token_get_all() y no en Python con expresiones regulares, porque los comentarios de este proyecto nombran el defecto y las migraciones llevan SQL con &gt;= dentro: una regex se acusaria a si misma. Al estrenarla quedaban tres sitios sueltos, los tres escritos DESPUES de Vigencia, y uno era un fallo real ----desde=2026-2-1 contra effective_from como cadenas, dejando dos textos legales vigentes el mismo dia--. Ver docs/fase-4/4.7-PUERTA-VIGENCIAS.md</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="23.25" customHeight="1" s="36">
       <c r="A153" s="67" t="inlineStr">
         <is>
-          <t>DEC-085</t>
+          <t>DEC-087</t>
         </is>
       </c>
       <c r="B153" s="68" t="inlineStr">
@@ -19231,16 +19326,24 @@
       <c r="C153" s="68" t="n"/>
       <c r="D153" s="69" t="inlineStr">
         <is>
-          <t>La bitácora la protegen dos usuarios de base de datos, no el esquema</t>
-        </is>
-      </c>
-      <c r="E153" s="69" t="n"/>
-      <c r="F153" s="69" t="n"/>
+          <t>Un 1062 se absorbe o se cuenta segun quien eligio el valor, y hay que NOMBRAR el indice para absorberlo.</t>
+        </is>
+      </c>
+      <c r="E153" s="69" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="F153" s="69" t="inlineStr">
+        <is>
+          <t>Si el valor lo calculo el sistema —el slug de una marca— el choque se recalcula y se reintenta en silencio. Si lo escribio la persona —un RUC, el nombre de una marca— tiene que llegar arriba con palabras. App\Shared\Database\Choque obliga a elegir: reintentar() exige el nombre del indice y vuelve a lanzar cualquier otro a la primera, porque un catch (QueryException) a secas absorberia el RUC repetido igual que el slug. Tres intentos como tope: un bucle sin tope convierte un indice mal entendido en una peticion eterna. El nombre se lee cortando por el ultimo punto —MySQL 8 antepone la tabla y Percona 5.7 no—, comprobado contra los dos motores</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="23.25" customHeight="1" s="36">
       <c r="A154" s="67" t="inlineStr">
         <is>
-          <t>DEC-084</t>
+          <t>DEC-086</t>
         </is>
       </c>
       <c r="B154" s="68" t="inlineStr">
@@ -19251,7 +19354,7 @@
       <c r="C154" s="68" t="n"/>
       <c r="D154" s="69" t="inlineStr">
         <is>
-          <t>«Perfil fiscal vigente» exige que ya haya empezado</t>
+          <t>La contraseña temporal deja de ser válida en el primer acceso</t>
         </is>
       </c>
       <c r="E154" s="69" t="n"/>
@@ -19260,7 +19363,7 @@
     <row r="155" ht="23.25" customHeight="1" s="36">
       <c r="A155" s="67" t="inlineStr">
         <is>
-          <t>DEC-083</t>
+          <t>DEC-085</t>
         </is>
       </c>
       <c r="B155" s="68" t="inlineStr">
@@ -19271,7 +19374,7 @@
       <c r="C155" s="68" t="n"/>
       <c r="D155" s="69" t="inlineStr">
         <is>
-          <t>«Cuenta compartida» se calcula al leer, no se guarda</t>
+          <t>La bitácora la protegen dos usuarios de base de datos, no el esquema</t>
         </is>
       </c>
       <c r="E155" s="69" t="n"/>
@@ -19280,7 +19383,7 @@
     <row r="156" ht="23.25" customHeight="1" s="36">
       <c r="A156" s="67" t="inlineStr">
         <is>
-          <t>DEC-082</t>
+          <t>DEC-084</t>
         </is>
       </c>
       <c r="B156" s="68" t="inlineStr">
@@ -19291,7 +19394,7 @@
       <c r="C156" s="68" t="n"/>
       <c r="D156" s="69" t="inlineStr">
         <is>
-          <t>Las sociedades del grupo las gestiona sólo admin</t>
+          <t>«Perfil fiscal vigente» exige que ya haya empezado</t>
         </is>
       </c>
       <c r="E156" s="69" t="n"/>
@@ -19300,7 +19403,7 @@
     <row r="157" ht="23.25" customHeight="1" s="36">
       <c r="A157" s="67" t="inlineStr">
         <is>
-          <t>DEC-081</t>
+          <t>DEC-083</t>
         </is>
       </c>
       <c r="B157" s="68" t="inlineStr">
@@ -19311,7 +19414,7 @@
       <c r="C157" s="68" t="n"/>
       <c r="D157" s="69" t="inlineStr">
         <is>
-          <t>Dar de baja una sociedad cierra sus coberturas abiertas</t>
+          <t>«Cuenta compartida» se calcula al leer, no se guarda</t>
         </is>
       </c>
       <c r="E157" s="69" t="n"/>
@@ -19320,7 +19423,7 @@
     <row r="158" ht="57" customHeight="1" s="36">
       <c r="A158" s="67" t="inlineStr">
         <is>
-          <t>DEC-080</t>
+          <t>DEC-082</t>
         </is>
       </c>
       <c r="B158" s="68" t="inlineStr">
@@ -19331,7 +19434,7 @@
       <c r="C158" s="68" t="n"/>
       <c r="D158" s="69" t="inlineStr">
         <is>
-          <t>Un gate que comprueba que los nombres entre capas existen</t>
+          <t>Las sociedades del grupo las gestiona sólo admin</t>
         </is>
       </c>
       <c r="E158" s="69" t="n"/>
@@ -19340,7 +19443,7 @@
     <row r="159" ht="23.25" customHeight="1" s="36">
       <c r="A159" s="67" t="inlineStr">
         <is>
-          <t>DEC-079</t>
+          <t>DEC-081</t>
         </is>
       </c>
       <c r="B159" s="68" t="inlineStr">
@@ -19351,7 +19454,7 @@
       <c r="C159" s="68" t="n"/>
       <c r="D159" s="69" t="inlineStr">
         <is>
-          <t>La identidad fiscal del cliente tiene permiso propio, en dos roles</t>
+          <t>Dar de baja una sociedad cierra sus coberturas abiertas</t>
         </is>
       </c>
       <c r="E159" s="69" t="n"/>
@@ -19360,7 +19463,7 @@
     <row r="160" ht="34.5" customHeight="1" s="36">
       <c r="A160" s="67" t="inlineStr">
         <is>
-          <t>DEC-078</t>
+          <t>DEC-080</t>
         </is>
       </c>
       <c r="B160" s="68" t="inlineStr">
@@ -19371,7 +19474,7 @@
       <c r="C160" s="68" t="n"/>
       <c r="D160" s="69" t="inlineStr">
         <is>
-          <t>El histórico fiscal del cliente está congelado</t>
+          <t>Un gate que comprueba que los nombres entre capas existen</t>
         </is>
       </c>
       <c r="E160" s="69" t="n"/>
@@ -19380,7 +19483,7 @@
     <row r="161" ht="34.5" customHeight="1" s="36">
       <c r="A161" s="67" t="inlineStr">
         <is>
-          <t>DEC-077</t>
+          <t>DEC-079</t>
         </is>
       </c>
       <c r="B161" s="68" t="inlineStr">
@@ -19391,7 +19494,7 @@
       <c r="C161" s="68" t="n"/>
       <c r="D161" s="69" t="inlineStr">
         <is>
-          <t>Un contacto no cambia de cliente</t>
+          <t>La identidad fiscal del cliente tiene permiso propio, en dos roles</t>
         </is>
       </c>
       <c r="E161" s="69" t="n"/>
@@ -19400,7 +19503,7 @@
     <row r="162" ht="45.75" customHeight="1" s="36">
       <c r="A162" s="67" t="inlineStr">
         <is>
-          <t>DEC-076</t>
+          <t>DEC-078</t>
         </is>
       </c>
       <c r="B162" s="68" t="inlineStr">
@@ -19411,7 +19514,7 @@
       <c r="C162" s="68" t="n"/>
       <c r="D162" s="69" t="inlineStr">
         <is>
-          <t>La lista de suites de restricción vive en un solo archivo</t>
+          <t>El histórico fiscal del cliente está congelado</t>
         </is>
       </c>
       <c r="E162" s="69" t="n"/>
@@ -19420,7 +19523,7 @@
     <row r="163" ht="34.5" customHeight="1" s="36">
       <c r="A163" s="67" t="inlineStr">
         <is>
-          <t>DEC-075</t>
+          <t>DEC-077</t>
         </is>
       </c>
       <c r="B163" s="68" t="inlineStr">
@@ -19431,7 +19534,7 @@
       <c r="C163" s="68" t="n"/>
       <c r="D163" s="69" t="inlineStr">
         <is>
-          <t>El relevo del contacto principal se hace, no se rechaza</t>
+          <t>Un contacto no cambia de cliente</t>
         </is>
       </c>
       <c r="E163" s="69" t="n"/>
@@ -19440,7 +19543,7 @@
     <row r="164" ht="23.25" customHeight="1" s="36">
       <c r="A164" s="67" t="inlineStr">
         <is>
-          <t>DEC-074</t>
+          <t>DEC-076</t>
         </is>
       </c>
       <c r="B164" s="68" t="inlineStr">
@@ -19451,7 +19554,7 @@
       <c r="C164" s="68" t="n"/>
       <c r="D164" s="69" t="inlineStr">
         <is>
-          <t>Al dar de alta un cliente se crea su primera marca</t>
+          <t>La lista de suites de restricción vive en un solo archivo</t>
         </is>
       </c>
       <c r="E164" s="69" t="n"/>
@@ -19460,7 +19563,7 @@
     <row r="165" ht="23.25" customHeight="1" s="36">
       <c r="A165" s="67" t="inlineStr">
         <is>
-          <t>DEC-073</t>
+          <t>DEC-075</t>
         </is>
       </c>
       <c r="B165" s="68" t="inlineStr">
@@ -19471,20 +19574,16 @@
       <c r="C165" s="68" t="n"/>
       <c r="D165" s="69" t="inlineStr">
         <is>
-          <t>Un prospecto se apunta en cualquier país; activarlo exige cobertura</t>
-        </is>
-      </c>
-      <c r="E165" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>El relevo del contacto principal se hace, no se rechaza</t>
+        </is>
+      </c>
+      <c r="E165" s="69" t="n"/>
       <c r="F165" s="69" t="n"/>
     </row>
     <row r="166" ht="23.25" customHeight="1" s="36">
       <c r="A166" s="67" t="inlineStr">
         <is>
-          <t>DEC-072</t>
+          <t>DEC-074</t>
         </is>
       </c>
       <c r="B166" s="68" t="inlineStr">
@@ -19495,7 +19594,7 @@
       <c r="C166" s="68" t="n"/>
       <c r="D166" s="69" t="inlineStr">
         <is>
-          <t>creator_addresses queda fuera de la regla de periodos</t>
+          <t>Al dar de alta un cliente se crea su primera marca</t>
         </is>
       </c>
       <c r="E166" s="69" t="n"/>
@@ -19504,7 +19603,7 @@
     <row r="167" ht="34.5" customHeight="1" s="36">
       <c r="A167" s="67" t="inlineStr">
         <is>
-          <t>DEC-071</t>
+          <t>DEC-073</t>
         </is>
       </c>
       <c r="B167" s="68" t="inlineStr">
@@ -19515,16 +19614,20 @@
       <c r="C167" s="68" t="n"/>
       <c r="D167" s="69" t="inlineStr">
         <is>
-          <t>Un perfil fiscal nuevo no puede empezar antes que el vigente</t>
-        </is>
-      </c>
-      <c r="E167" s="69" t="n"/>
+          <t>Un prospecto se apunta en cualquier país; activarlo exige cobertura</t>
+        </is>
+      </c>
+      <c r="E167" s="69" t="inlineStr">
+        <is>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
+        </is>
+      </c>
       <c r="F167" s="69" t="n"/>
     </row>
     <row r="168" ht="23.25" customHeight="1" s="36">
       <c r="A168" s="67" t="inlineStr">
         <is>
-          <t>DEC-070</t>
+          <t>DEC-072</t>
         </is>
       </c>
       <c r="B168" s="68" t="inlineStr">
@@ -19535,7 +19638,7 @@
       <c r="C168" s="68" t="n"/>
       <c r="D168" s="69" t="inlineStr">
         <is>
-          <t>Un bloqueo de agenda se registra aunque pise una campaña aceptada</t>
+          <t>creator_addresses queda fuera de la regla de periodos</t>
         </is>
       </c>
       <c r="E168" s="69" t="n"/>
@@ -19544,7 +19647,7 @@
     <row r="169" ht="45.75" customHeight="1" s="36">
       <c r="A169" s="67" t="inlineStr">
         <is>
-          <t>DEC-069</t>
+          <t>DEC-071</t>
         </is>
       </c>
       <c r="B169" s="68" t="inlineStr">
@@ -19555,20 +19658,16 @@
       <c r="C169" s="68" t="n"/>
       <c r="D169" s="69" t="inlineStr">
         <is>
-          <t>Las tarifas tienen permiso propio: creator.rate.manage</t>
-        </is>
-      </c>
-      <c r="E169" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>Un perfil fiscal nuevo no puede empezar antes que el vigente</t>
+        </is>
+      </c>
+      <c r="E169" s="69" t="n"/>
       <c r="F169" s="69" t="n"/>
     </row>
     <row r="170" ht="45.75" customHeight="1" s="36">
       <c r="A170" s="67" t="inlineStr">
         <is>
-          <t>DEC-068</t>
+          <t>DEC-070</t>
         </is>
       </c>
       <c r="B170" s="68" t="inlineStr">
@@ -19579,20 +19678,16 @@
       <c r="C170" s="68" t="n"/>
       <c r="D170" s="69" t="inlineStr">
         <is>
-          <t>Cero es un precio válido, pero hay que declararlo</t>
-        </is>
-      </c>
-      <c r="E170" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>Un bloqueo de agenda se registra aunque pise una campaña aceptada</t>
+        </is>
+      </c>
+      <c r="E170" s="69" t="n"/>
       <c r="F170" s="69" t="n"/>
     </row>
     <row r="171" ht="23.25" customHeight="1" s="36">
       <c r="A171" s="67" t="inlineStr">
         <is>
-          <t>DEC-067</t>
+          <t>DEC-069</t>
         </is>
       </c>
       <c r="B171" s="68" t="inlineStr">
@@ -19603,12 +19698,12 @@
       <c r="C171" s="68" t="n"/>
       <c r="D171" s="69" t="inlineStr">
         <is>
-          <t>Los dos permisos de medios de pago van al rol finance</t>
+          <t>Las tarifas tienen permiso propio: creator.rate.manage</t>
         </is>
       </c>
       <c r="E171" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
         </is>
       </c>
       <c r="F171" s="69" t="n"/>
@@ -19616,7 +19711,7 @@
     <row r="172" ht="34.5" customHeight="1" s="36">
       <c r="A172" s="67" t="inlineStr">
         <is>
-          <t>DEC-066</t>
+          <t>DEC-068</t>
         </is>
       </c>
       <c r="B172" s="68" t="inlineStr">
@@ -19627,12 +19722,12 @@
       <c r="C172" s="68" t="n"/>
       <c r="D172" s="69" t="inlineStr">
         <is>
-          <t>La cuenta de un medio de pago es inmutable: se sustituye, no se edita</t>
+          <t>Cero es un precio válido, pero hay que declararlo</t>
         </is>
       </c>
       <c r="E172" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
         </is>
       </c>
       <c r="F172" s="69" t="n"/>
@@ -19640,7 +19735,7 @@
     <row r="173" ht="34.5" customHeight="1" s="36">
       <c r="A173" s="67" t="inlineStr">
         <is>
-          <t>DEC-065</t>
+          <t>DEC-067</t>
         </is>
       </c>
       <c r="B173" s="68" t="inlineStr">
@@ -19651,7 +19746,7 @@
       <c r="C173" s="68" t="n"/>
       <c r="D173" s="69" t="inlineStr">
         <is>
-          <t>La misma cuenta en dos creadores se marca, no se rechaza</t>
+          <t>Los dos permisos de medios de pago van al rol finance</t>
         </is>
       </c>
       <c r="E173" s="69" t="inlineStr">
@@ -19664,7 +19759,7 @@
     <row r="174" ht="45.75" customHeight="1" s="36">
       <c r="A174" s="67" t="inlineStr">
         <is>
-          <t>DEC-064</t>
+          <t>DEC-066</t>
         </is>
       </c>
       <c r="B174" s="68" t="inlineStr">
@@ -19675,7 +19770,7 @@
       <c r="C174" s="68" t="n"/>
       <c r="D174" s="69" t="inlineStr">
         <is>
-          <t>El enfriamiento de un medio de pago son 24 horas, y es configuración</t>
+          <t>La cuenta de un medio de pago es inmutable: se sustituye, no se edita</t>
         </is>
       </c>
       <c r="E174" s="69" t="inlineStr">
@@ -19688,7 +19783,7 @@
     <row r="175" ht="34.5" customHeight="1" s="36">
       <c r="A175" s="67" t="inlineStr">
         <is>
-          <t>DEC-063</t>
+          <t>DEC-065</t>
         </is>
       </c>
       <c r="B175" s="68" t="inlineStr">
@@ -19699,12 +19794,12 @@
       <c r="C175" s="68" t="n"/>
       <c r="D175" s="69" t="inlineStr">
         <is>
-          <t>Los umbrales de coherencia son juicio, no verdad; y no rechazan nada</t>
+          <t>La misma cuenta en dos creadores se marca, no se rechaza</t>
         </is>
       </c>
       <c r="E175" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.7) — umbrales revisables</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F175" s="69" t="n"/>
@@ -19712,7 +19807,7 @@
     <row r="176" ht="45.75" customHeight="1" s="36">
       <c r="A176" s="67" t="inlineStr">
         <is>
-          <t>DEC-062</t>
+          <t>DEC-064</t>
         </is>
       </c>
       <c r="B176" s="68" t="inlineStr">
@@ -19723,12 +19818,12 @@
       <c r="C176" s="68" t="n"/>
       <c r="D176" s="69" t="inlineStr">
         <is>
-          <t>Los dos permisos fiscales van al mismo rol; la separación la impone la base</t>
+          <t>El enfriamiento de un medio de pago son 24 horas, y es configuración</t>
         </is>
       </c>
       <c r="E176" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.6)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F176" s="69" t="n"/>
@@ -19736,7 +19831,7 @@
     <row r="177" ht="34.5" customHeight="1" s="36">
       <c r="A177" s="67" t="inlineStr">
         <is>
-          <t>DEC-061</t>
+          <t>DEC-063</t>
         </is>
       </c>
       <c r="B177" s="68" t="inlineStr">
@@ -19747,12 +19842,12 @@
       <c r="C177" s="68" t="n"/>
       <c r="D177" s="69" t="inlineStr">
         <is>
-          <t>Las pruebas usan una base local y desechable, nunca la de desarrollo</t>
+          <t>Los umbrales de coherencia son juicio, no verdad; y no rechazan nada</t>
         </is>
       </c>
       <c r="E177" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.7) — umbrales revisables</t>
         </is>
       </c>
       <c r="F177" s="69" t="n"/>
@@ -19760,7 +19855,7 @@
     <row r="178" ht="34.5" customHeight="1" s="36">
       <c r="A178" s="67" t="inlineStr">
         <is>
-          <t>DEC-060</t>
+          <t>DEC-062</t>
         </is>
       </c>
       <c r="B178" s="68" t="inlineStr">
@@ -19771,12 +19866,12 @@
       <c r="C178" s="68" t="n"/>
       <c r="D178" s="69" t="inlineStr">
         <is>
-          <t>Verificar y activar son permisos distintos, pero hoy el mismo rol</t>
+          <t>Los dos permisos fiscales van al mismo rol; la separación la impone la base</t>
         </is>
       </c>
       <c r="E178" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-23, iteración 3.5) — decisión de negocio revisable</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.6)</t>
         </is>
       </c>
       <c r="F178" s="69" t="n"/>
@@ -19784,7 +19879,7 @@
     <row r="179" ht="23.25" customHeight="1" s="36">
       <c r="A179" s="67" t="inlineStr">
         <is>
-          <t>DEC-059</t>
+          <t>DEC-061</t>
         </is>
       </c>
       <c r="B179" s="68" t="inlineStr">
@@ -19795,7 +19890,7 @@
       <c r="C179" s="68" t="n"/>
       <c r="D179" s="69" t="inlineStr">
         <is>
-          <t>Se acepta una versión de los términos, no una página</t>
+          <t>Las pruebas usan una base local y desechable, nunca la de desarrollo</t>
         </is>
       </c>
       <c r="E179" s="69" t="inlineStr">
@@ -19808,7 +19903,7 @@
     <row r="180" ht="34.5" customHeight="1" s="36">
       <c r="A180" s="67" t="inlineStr">
         <is>
-          <t>DEC-058</t>
+          <t>DEC-060</t>
         </is>
       </c>
       <c r="B180" s="68" t="inlineStr">
@@ -19819,12 +19914,12 @@
       <c r="C180" s="68" t="n"/>
       <c r="D180" s="69" t="inlineStr">
         <is>
-          <t>La identidad verificada es evidencia, no una casilla</t>
+          <t>Verificar y activar son permisos distintos, pero hoy el mismo rol</t>
         </is>
       </c>
       <c r="E180" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+          <t>ADOPTADA (2026-08-23, iteración 3.5) — decisión de negocio revisable</t>
         </is>
       </c>
       <c r="F180" s="69" t="n"/>
@@ -19832,7 +19927,7 @@
     <row r="181" ht="90.75" customHeight="1" s="36">
       <c r="A181" s="67" t="inlineStr">
         <is>
-          <t>DEC-057</t>
+          <t>DEC-059</t>
         </is>
       </c>
       <c r="B181" s="68" t="inlineStr">
@@ -19843,12 +19938,12 @@
       <c r="C181" s="68" t="n"/>
       <c r="D181" s="69" t="inlineStr">
         <is>
-          <t>Aprobar una solicitud no activa al creador</t>
+          <t>Se acepta una versión de los términos, no una página</t>
         </is>
       </c>
       <c r="E181" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.4)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
         </is>
       </c>
       <c r="F181" s="69" t="n"/>
@@ -19856,7 +19951,7 @@
     <row r="182" ht="34.5" customHeight="1" s="36">
       <c r="A182" s="67" t="inlineStr">
         <is>
-          <t>DEC-056</t>
+          <t>DEC-058</t>
         </is>
       </c>
       <c r="B182" s="68" t="inlineStr">
@@ -19867,12 +19962,12 @@
       <c r="C182" s="68" t="n"/>
       <c r="D182" s="69" t="inlineStr">
         <is>
-          <t>La bitácora se ordena por id, no por fecha, y redacta lo sensible</t>
+          <t>La identidad verificada es evidencia, no una casilla</t>
         </is>
       </c>
       <c r="E182" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.3)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
         </is>
       </c>
       <c r="F182" s="69" t="n"/>
@@ -19880,7 +19975,7 @@
     <row r="183" ht="23.25" customHeight="1" s="36">
       <c r="A183" s="67" t="inlineStr">
         <is>
-          <t>DEC-055</t>
+          <t>DEC-057</t>
         </is>
       </c>
       <c r="B183" s="68" t="inlineStr">
@@ -19891,24 +19986,20 @@
       <c r="C183" s="68" t="n"/>
       <c r="D183" s="69" t="inlineStr">
         <is>
-          <t>La primera pantalla de escritura no toca la identidad</t>
+          <t>Aprobar una solicitud no activa al creador</t>
         </is>
       </c>
       <c r="E183" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
-        </is>
-      </c>
-      <c r="F183" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Primera pantalla del proyecto que escribe: edición de creador.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.4)</t>
+        </is>
+      </c>
+      <c r="F183" s="69" t="n"/>
     </row>
     <row r="184" ht="34.5" customHeight="1" s="36">
       <c r="A184" s="67" t="inlineStr">
         <is>
-          <t>DEC-054</t>
+          <t>DEC-056</t>
         </is>
       </c>
       <c r="B184" s="68" t="inlineStr">
@@ -19919,24 +20010,20 @@
       <c r="C184" s="68" t="n"/>
       <c r="D184" s="69" t="inlineStr">
         <is>
-          <t>La bitácora es inmutable en la base, no por convención</t>
+          <t>La bitácora se ordena por id, no por fecha, y redacta lo sensible</t>
         </is>
       </c>
       <c r="E184" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
-        </is>
-      </c>
-      <c r="F184" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — audit_logs existía desde 2.4 y nadie escribía en ella. Al ir a llenarla apareció el segundo problema: la tabla admitía UPDATE y DELETE como cualquier otra.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.3)</t>
+        </is>
+      </c>
+      <c r="F184" s="69" t="n"/>
     </row>
     <row r="185" ht="34.5" customHeight="1" s="36">
       <c r="A185" s="67" t="inlineStr">
         <is>
-          <t>DEC-053</t>
+          <t>DEC-055</t>
         </is>
       </c>
       <c r="B185" s="68" t="inlineStr">
@@ -19947,20 +20034,24 @@
       <c r="C185" s="68" t="n"/>
       <c r="D185" s="69" t="inlineStr">
         <is>
-          <t>Autorización por permiso, sin atajo para el administrador</t>
+          <t>La primera pantalla de escritura no toca la identidad</t>
         </is>
       </c>
       <c r="E185" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.1)</t>
-        </is>
-      </c>
-      <c r="F185" s="69" t="n"/>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
+        </is>
+      </c>
+      <c r="F185" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — Primera pantalla del proyecto que escribe: edición de creador.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="34.5" customHeight="1" s="36">
       <c r="A186" s="67" t="inlineStr">
         <is>
-          <t>DEC-052</t>
+          <t>DEC-054</t>
         </is>
       </c>
       <c r="B186" s="68" t="inlineStr">
@@ -19971,20 +20062,24 @@
       <c r="C186" s="68" t="n"/>
       <c r="D186" s="69" t="inlineStr">
         <is>
-          <t>MySQL no admite subconsultas sobre la tabla que se está modificando</t>
+          <t>La bitácora es inmutable en la base, no por convención</t>
         </is>
       </c>
       <c r="E186" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22)</t>
-        </is>
-      </c>
-      <c r="F186" s="69" t="n"/>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
+        </is>
+      </c>
+      <c r="F186" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — audit_logs existía desde 2.4 y nadie escribía en ella. Al ir a llenarla apareció el segundo problema: la tabla admitía UPDATE y DELETE como cualquier otra.</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="34.5" customHeight="1" s="36">
       <c r="A187" s="67" t="inlineStr">
         <is>
-          <t>DEC-051</t>
+          <t>DEC-053</t>
         </is>
       </c>
       <c r="B187" s="68" t="inlineStr">
@@ -19995,24 +20090,20 @@
       <c r="C187" s="68" t="n"/>
       <c r="D187" s="69" t="inlineStr">
         <is>
-          <t>El CI corre la suite contra los dos motores, no contra uno</t>
+          <t>Autorización por permiso, sin atajo para el administrador</t>
         </is>
       </c>
       <c r="E187" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22). Recordatorio: tools/github-workflow-ci.yml sigue pendiente de mover a .github/workflows/ci.yml a mano — es ruta protegida</t>
-        </is>
-      </c>
-      <c r="F187" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — El CI validaba formato, análisis estático, fronteras entre módulos, migraciones y pruebas. Nada de eso comprueba que las restricciones se apliquen en el motor de producción, que no aplica CHECK.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.1)</t>
+        </is>
+      </c>
+      <c r="F187" s="69" t="n"/>
     </row>
     <row r="188" ht="34.5" customHeight="1" s="36">
       <c r="A188" s="67" t="inlineStr">
         <is>
-          <t>DEC-050</t>
+          <t>DEC-052</t>
         </is>
       </c>
       <c r="B188" s="68" t="inlineStr">
@@ -20023,12 +20114,12 @@
       <c r="C188" s="68" t="n"/>
       <c r="D188" s="69" t="inlineStr">
         <is>
-          <t>Las migraciones se contrastan contra el esquema de referencia, no se confía en que coincidan</t>
+          <t>MySQL no admite subconsultas sobre la tabla que se está modificando</t>
         </is>
       </c>
       <c r="E188" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22)</t>
+          <t>ADOPTADA (2026-08-22)</t>
         </is>
       </c>
       <c r="F188" s="69" t="n"/>
@@ -20036,7 +20127,7 @@
     <row r="189" ht="34.5" customHeight="1" s="36">
       <c r="A189" s="67" t="inlineStr">
         <is>
-          <t>DEC-049</t>
+          <t>DEC-051</t>
         </is>
       </c>
       <c r="B189" s="68" t="inlineStr">
@@ -20047,24 +20138,24 @@
       <c r="C189" s="68" t="n"/>
       <c r="D189" s="69" t="inlineStr">
         <is>
-          <t>Sin datos fiscales no hay alta, pero acompañamos a formalizarse</t>
+          <t>El CI corre la suite contra los dos motores, no contra uno</t>
         </is>
       </c>
       <c r="E189" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22)</t>
+          <t>ADOPTADA (2026-08-22). Recordatorio: tools/github-workflow-ci.yml sigue pendiente de mover a .github/workflows/ci.yml a mano — es ruta protegida</t>
         </is>
       </c>
       <c r="F189" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Respuesta a Q-45. La propuesta inicial era pagar a un familiar del creador con declaración jurada de parentesco. El análisis de docs/fase-2/2.14-PAGO-A-TERCEROS.md identificó tres problemas: el comprobante deja de coincidir con el pago (riesgo de gasto reparable para la empresa que paga), señales de alerta de prevención de lavado, y contradicción con BR-FIN-003, que ya está implementada.</t>
+          <t xml:space="preserve"> — El CI validaba formato, análisis estático, fronteras entre módulos, migraciones y pruebas. Nada de eso comprueba que las restricciones se apliquen en el motor de producción, que no aplica CHECK.</t>
         </is>
       </c>
     </row>
     <row r="190" ht="23.25" customHeight="1" s="36">
       <c r="A190" s="67" t="inlineStr">
         <is>
-          <t>DEC-048</t>
+          <t>DEC-050</t>
         </is>
       </c>
       <c r="B190" s="68" t="inlineStr">
@@ -20075,24 +20166,20 @@
       <c r="C190" s="68" t="n"/>
       <c r="D190" s="69" t="inlineStr">
         <is>
-          <t>La retención tiene tres estados, no dos</t>
+          <t>Las migraciones se contrastan contra el esquema de referencia, no se confía en que coincidan</t>
         </is>
       </c>
       <c r="E190" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.15)</t>
-        </is>
-      </c>
-      <c r="F190" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Sobre Q-40 se decidió «que el modelo lo deje configurable». Al implementarlo apareció que el riesgo que yo había señalado —*«alguien pone un número a ojo y nadie se entera»*— ya estaba dentro del modelo, y era peor.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="F190" s="69" t="n"/>
     </row>
     <row r="191" ht="23.25" customHeight="1" s="36">
       <c r="A191" s="67" t="inlineStr">
         <is>
-          <t>DEC-047</t>
+          <t>DEC-049</t>
         </is>
       </c>
       <c r="B191" s="68" t="inlineStr">
@@ -20103,24 +20190,24 @@
       <c r="C191" s="68" t="n"/>
       <c r="D191" s="69" t="inlineStr">
         <is>
-          <t>Se factura a todos los países desde Perú</t>
+          <t>Sin datos fiscales no hay alta, pero acompañamos a formalizarse</t>
         </is>
       </c>
       <c r="E191" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22)</t>
+          <t>ADOPTADA (2026-08-22)</t>
         </is>
       </c>
       <c r="F191" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Respuesta a Q-42. En lugar de constituir sociedad en cada país, se emiten todos los comprobantes desde la sociedad peruana. Los países se resuelven uno a uno más adelante.</t>
+          <t xml:space="preserve"> — Respuesta a Q-45. La propuesta inicial era pagar a un familiar del creador con declaración jurada de parentesco. El análisis de docs/fase-2/2.14-PAGO-A-TERCEROS.md identificó tres problemas: el comprobante deja de coincidir con el pago (riesgo de gasto reparable para la empresa que paga), señales de alerta de prevención de lavado, y contradicción con BR-FIN-003, que ya está implementada.</t>
         </is>
       </c>
     </row>
     <row r="192" ht="45.75" customHeight="1" s="36">
       <c r="A192" s="67" t="inlineStr">
         <is>
-          <t>DEC-046</t>
+          <t>DEC-048</t>
         </is>
       </c>
       <c r="B192" s="68" t="inlineStr">
@@ -20131,24 +20218,24 @@
       <c r="C192" s="68" t="n"/>
       <c r="D192" s="69" t="inlineStr">
         <is>
-          <t>La base impone lo que ve en una fila; el resto lo impone el repositorio</t>
+          <t>La retención tiene tres estados, no dos</t>
         </is>
       </c>
       <c r="E192" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.15)</t>
         </is>
       </c>
       <c r="F192" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Cinco invariantes de finanzas son de varias filas o varias tablas (suma de líneas = subtotal, cobros ≤ total facturado, moneda de asiento = moneda de su payout, signo de una reversión, saldo no negativo). Ningún CHECK puede expresarlas.</t>
+          <t xml:space="preserve"> — Sobre Q-40 se decidió «que el modelo lo deje configurable». Al implementarlo apareció que el riesgo que yo había señalado —*«alguien pone un número a ojo y nadie se entera»*— ya estaba dentro del modelo, y era peor.</t>
         </is>
       </c>
     </row>
     <row r="193" ht="34.5" customHeight="1" s="36">
       <c r="A193" s="67" t="inlineStr">
         <is>
-          <t>DEC-045</t>
+          <t>DEC-047</t>
         </is>
       </c>
       <c r="B193" s="68" t="inlineStr">
@@ -20159,24 +20246,24 @@
       <c r="C193" s="68" t="n"/>
       <c r="D193" s="69" t="inlineStr">
         <is>
-          <t>La inmutabilidad financiera se impone con disparadores, no con convención</t>
+          <t>Se factura a todos los países desde Perú</t>
         </is>
       </c>
       <c r="E193" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA e implementada (2026-08-22)</t>
         </is>
       </c>
       <c r="F193" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — BR-FIN-008 («ningún registro financiero se elimina físicamente») y BR-FIN-002 («una corrección es un asiento de reversión») eran hasta ahora reglas de la capa de aplicación.</t>
+          <t xml:space="preserve"> — Respuesta a Q-42. En lugar de constituir sociedad en cada país, se emiten todos los comprobantes desde la sociedad peruana. Los países se resuelven uno a uno más adelante.</t>
         </is>
       </c>
     </row>
     <row r="194" ht="34.5" customHeight="1" s="36">
       <c r="A194" s="67" t="inlineStr">
         <is>
-          <t>DEC-044</t>
+          <t>DEC-046</t>
         </is>
       </c>
       <c r="B194" s="68" t="inlineStr">
@@ -20187,24 +20274,24 @@
       <c r="C194" s="68" t="n"/>
       <c r="D194" s="69" t="inlineStr">
         <is>
-          <t>Todo pago pertenece a un lote (no existen pagos sueltos)</t>
+          <t>La base impone lo que ve en una fila; el resto lo impone el repositorio</t>
         </is>
       </c>
       <c r="E194" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F194" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — La primera versión de payouts permitía payout_batch_id NULL, pensando en el pago puntual fuera de la corrida quincenal.</t>
+          <t xml:space="preserve"> — Cinco invariantes de finanzas son de varias filas o varias tablas (suma de líneas = subtotal, cobros ≤ total facturado, moneda de asiento = moneda de su payout, signo de una reversión, saldo no negativo). Ningún CHECK puede expresarlas.</t>
         </is>
       </c>
     </row>
     <row r="195" ht="23.25" customHeight="1" s="36">
       <c r="A195" s="67" t="inlineStr">
         <is>
-          <t>DEC-043</t>
+          <t>DEC-045</t>
         </is>
       </c>
       <c r="B195" s="68" t="inlineStr">
@@ -20215,24 +20302,24 @@
       <c r="C195" s="68" t="n"/>
       <c r="D195" s="69" t="inlineStr">
         <is>
-          <t>Dónde vive la base de datos de desarrollo</t>
+          <t>La inmutabilidad financiera se impone con disparadores, no con convención</t>
         </is>
       </c>
       <c r="E195" s="69" t="inlineStr">
         <is>
-          <t>ACORDADA en su intención; el motor concreto depende de DEC-042</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F195" s="69" t="inlineStr">
         <is>
-          <t>C. Es lo que hace un equipo profesional y no cuesta más que A: el motor local se instala una vez. El bucle interno —migrar, probar, deshacer, repetir— tiene que ser rápido o se deja de ejecutar, y unas pruebas que tardan minutos son unas pruebas que nadie corre. La base remota es el ensayo general, no el banco de trabajo. — Se propone usar el mismo servidor que producción, con dos bases separadas: una de desarrollo y otra de producción. No es trabajar contra los datos reales; es usar el mismo motor. Ya hay otras aplicaciones Laravel funcionando en ese servidor sin incidencias.</t>
+          <t xml:space="preserve"> — BR-FIN-008 («ningún registro financiero se elimina físicamente») y BR-FIN-002 («una corrección es un asiento de reversión») eran hasta ahora reglas de la capa de aplicación.</t>
         </is>
       </c>
     </row>
     <row r="196" ht="57" customHeight="1" s="36">
       <c r="A196" s="67" t="inlineStr">
         <is>
-          <t>DEC-042</t>
+          <t>DEC-044</t>
         </is>
       </c>
       <c r="B196" s="68" t="inlineStr">
@@ -20243,80 +20330,80 @@
       <c r="C196" s="68" t="n"/>
       <c r="D196" s="69" t="inlineStr">
         <is>
-          <t>🔴 El servidor es MySQL 5.7 y no aplica los CHECK *(confirmado empíricamente)*</t>
+          <t>Todo pago pertenece a un lote (no existen pagos sueltos)</t>
         </is>
       </c>
       <c r="E196" s="69" t="inlineStr">
         <is>
-          <t>🔴 CONFIRMADA — pendiente de elegir entre B y C</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F196" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — El servidor de la aplicación es Percona Server 5.7.44-48 sobre cPanel. La base de desarrollo (..._dev) y la de producción viven en él. docs/03 asumía MySQL 8.</t>
+          <t xml:space="preserve"> — La primera versión de payouts permitía payout_batch_id NULL, pensando en el pago puntual fuera de la corrida quincenal.</t>
         </is>
       </c>
     </row>
     <row r="197" ht="23.25" customHeight="1" s="36">
       <c r="A197" s="67" t="inlineStr">
         <is>
-          <t>DEC-041</t>
+          <t>DEC-043</t>
         </is>
       </c>
       <c r="B197" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C197" s="68" t="n"/>
       <c r="D197" s="69" t="inlineStr">
         <is>
-          <t>Gamificación y Creator Score no se fusionan</t>
+          <t>Dónde vive la base de datos de desarrollo</t>
         </is>
       </c>
       <c r="E197" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>ACORDADA en su intención; el motor concreto depende de DEC-042</t>
         </is>
       </c>
       <c r="F197" s="69" t="inlineStr">
         <is>
-          <t>B. El Score es interno, puede bajar y sirve para decidir a quién invitar; el XP es externo, nunca baja y sirve para motivar. Un creador que incumplió una vez debe bajar en el score y conservar el XP que ganó antes. — Ambos calculan un número sobre un creador a partir de los mismos eventos. La tentación de unirlos es enorme.</t>
+          <t>C. Es lo que hace un equipo profesional y no cuesta más que A: el motor local se instala una vez. El bucle interno —migrar, probar, deshacer, repetir— tiene que ser rápido o se deja de ejecutar, y unas pruebas que tardan minutos son unas pruebas que nadie corre. La base remota es el ensayo general, no el banco de trabajo. — Se propone usar el mismo servidor que producción, con dos bases separadas: una de desarrollo y otra de producción. No es trabajar contra los datos reales; es usar el mismo motor. Ya hay otras aplicaciones Laravel funcionando en ese servidor sin incidencias.</t>
         </is>
       </c>
     </row>
     <row r="198" ht="23.25" customHeight="1" s="36">
       <c r="A198" s="67" t="inlineStr">
         <is>
-          <t>DEC-040</t>
+          <t>DEC-042</t>
         </is>
       </c>
       <c r="B198" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C198" s="68" t="n"/>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>Referidos con consolidación diferida</t>
+          <t>🔴 El servidor es MySQL 5.7 y no aplica los CHECK *(confirmado empíricamente)*</t>
         </is>
       </c>
       <c r="E198" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>🔴 CONFIRMADA — pendiente de elegir entre B y C</t>
         </is>
       </c>
       <c r="F198" s="69" t="inlineStr">
         <is>
-          <t>B, más topes por periodo y verificación de que referente y referido no comparten documento, teléfono ni medio de pago. El vínculo se conserva siempre aunque el XP no se consolide: es dato de negocio. — Un programa de referidos con recompensa es, sin excepción, un imán de fraude: autorreferidos, cuentas falsas, granjas.</t>
+          <t xml:space="preserve"> — El servidor de la aplicación es Percona Server 5.7.44-48 sobre cPanel. La base de desarrollo (..._dev) y la de producción viven en él. docs/03 asumía MySQL 8.</t>
         </is>
       </c>
     </row>
     <row r="199" ht="23.25" customHeight="1" s="36">
       <c r="A199" s="67" t="inlineStr">
         <is>
-          <t>DEC-039</t>
+          <t>DEC-041</t>
         </is>
       </c>
       <c r="B199" s="68" t="inlineStr">
@@ -20327,7 +20414,7 @@
       <c r="C199" s="68" t="n"/>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>Los retos internos llevan siempre recompensa tangible 🔴</t>
+          <t>Gamificación y Creator Score no se fusionan</t>
         </is>
       </c>
       <c r="E199" s="69" t="inlineStr">
@@ -20337,14 +20424,14 @@
       </c>
       <c r="F199" s="69" t="inlineStr">
         <is>
-          <t>B, sin excepción. El XP es el envoltorio y el reconocimiento; nunca el pago. Es la salvaguarda que la propia especificación anticipó en §16. — "Minicampañas de XP por hacer vídeos para la plataforma". Leído desde el otro lado, puede sonar a *"produce contenido de marketing para mi empresa y te pago con puntos"* — a creadores que ya producen por dinero para tus clientes. En una red pequeña, ese daño reputacional se propaga en un grupo de WhatsApp.</t>
+          <t>B. El Score es interno, puede bajar y sirve para decidir a quién invitar; el XP es externo, nunca baja y sirve para motivar. Un creador que incumplió una vez debe bajar en el score y conservar el XP que ganó antes. — Ambos calculan un número sobre un creador a partir de los mismos eventos. La tentación de unirlos es enorme.</t>
         </is>
       </c>
     </row>
     <row r="200" ht="45.75" customHeight="1" s="36">
       <c r="A200" s="67" t="inlineStr">
         <is>
-          <t>DEC-038</t>
+          <t>DEC-040</t>
         </is>
       </c>
       <c r="B200" s="68" t="inlineStr">
@@ -20355,7 +20442,7 @@
       <c r="C200" s="68" t="n"/>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>Ranking por cohortes, sin tabla global</t>
+          <t>Referidos con consolidación diferida</t>
         </is>
       </c>
       <c r="E200" s="69" t="inlineStr">
@@ -20365,14 +20452,14 @@
       </c>
       <c r="F200" s="69" t="inlineStr">
         <is>
-          <t>C. Los puntos de liga se reinician por temporada; el XP nunca. Sin ranking público por ingresos, jamás. Un ranking global solo tiene sentido en una vista interna, y ahí es un reporte, no gamificación. — Una clasificación global con 1.000 creadores significa que 990 abren la app y ven que están perdiendo. Y con el tiempo se estanca: quien lleva más tiempo acumula más.</t>
+          <t>B, más topes por periodo y verificación de que referente y referido no comparten documento, teléfono ni medio de pago. El vínculo se conserva siempre aunque el XP no se consolide: es dato de negocio. — Un programa de referidos con recompensa es, sin excepción, un imán de fraude: autorreferidos, cuentas falsas, granjas.</t>
         </is>
       </c>
     </row>
     <row r="201" ht="34.5" customHeight="1" s="36">
       <c r="A201" s="67" t="inlineStr">
         <is>
-          <t>DEC-037</t>
+          <t>DEC-039</t>
         </is>
       </c>
       <c r="B201" s="68" t="inlineStr">
@@ -20383,7 +20470,7 @@
       <c r="C201" s="68" t="n"/>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>Los niveles se calculan, no se almacenan</t>
+          <t>Los retos internos llevan siempre recompensa tangible 🔴</t>
         </is>
       </c>
       <c r="E201" s="69" t="inlineStr">
@@ -20393,14 +20480,14 @@
       </c>
       <c r="F201" s="69" t="inlineStr">
         <is>
-          <t>B. Permite ajustar umbrales sin quitarle puntos a nadie, que es justamente lo que DEC-035 prohíbe. — Las curvas de nivel se recalibran; el XP ya otorgado no debe verse afectado.</t>
+          <t>B, sin excepción. El XP es el envoltorio y el reconocimiento; nunca el pago. Es la salvaguarda que la propia especificación anticipó en §16. — "Minicampañas de XP por hacer vídeos para la plataforma". Leído desde el otro lado, puede sonar a *"produce contenido de marketing para mi empresa y te pago con puntos"* — a creadores que ya producen por dinero para tus clientes. En una red pequeña, ese daño reputacional se propaga en un grupo de WhatsApp.</t>
         </is>
       </c>
     </row>
     <row r="202" ht="57" customHeight="1" s="36">
       <c r="A202" s="67" t="inlineStr">
         <is>
-          <t>DEC-036</t>
+          <t>DEC-038</t>
         </is>
       </c>
       <c r="B202" s="68" t="inlineStr">
@@ -20411,7 +20498,7 @@
       <c r="C202" s="68" t="n"/>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>Se premia comportamiento verificado, no resultados</t>
+          <t>Ranking por cohortes, sin tabla global</t>
         </is>
       </c>
       <c r="E202" s="69" t="inlineStr">
@@ -20421,14 +20508,14 @@
       </c>
       <c r="F202" s="69" t="inlineStr">
         <is>
-          <t>C. A premia al algoritmo de Instagram, no al creador. B produce sobrecompromiso —creadores que aceptan lo que no pueden cumplir— y, en el caso de seguidores, desmotiva al micro-creador y premia el vector de fraude de R-04. Detalle en docs/13 §3. — ¿Sobre qué se otorga XP?</t>
+          <t>C. Los puntos de liga se reinician por temporada; el XP nunca. Sin ranking público por ingresos, jamás. Un ranking global solo tiene sentido en una vista interna, y ahí es un reporte, no gamificación. — Una clasificación global con 1.000 creadores significa que 990 abren la app y ven que están perdiendo. Y con el tiempo se estanca: quien lleva más tiempo acumula más.</t>
         </is>
       </c>
     </row>
     <row r="203" ht="23.25" customHeight="1" s="36">
       <c r="A203" s="67" t="inlineStr">
         <is>
-          <t>DEC-035</t>
+          <t>DEC-037</t>
         </is>
       </c>
       <c r="B203" s="68" t="inlineStr">
@@ -20439,7 +20526,7 @@
       <c r="C203" s="68" t="n"/>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>El XP es append-only y nunca decrece</t>
+          <t>Los niveles se calculan, no se almacenan</t>
         </is>
       </c>
       <c r="E203" s="69" t="inlineStr">
@@ -20449,14 +20536,14 @@
       </c>
       <c r="F203" s="69" t="inlineStr">
         <is>
-          <t>B. Quitar puntos se percibe como robo y destruye la confianza de golpe. Además sería castigar dos veces con el mecanismo equivocado. Mismo patrón que el ledger financiero: se corrige con asientos nuevos, no editando. — ¿Se puede restar XP por un incumplimiento?</t>
+          <t>B. Permite ajustar umbrales sin quitarle puntos a nadie, que es justamente lo que DEC-035 prohíbe. — Las curvas de nivel se recalibran; el XP ya otorgado no debe verse afectado.</t>
         </is>
       </c>
     </row>
     <row r="204" ht="23.25" customHeight="1" s="36">
       <c r="A204" s="67" t="inlineStr">
         <is>
-          <t>DEC-034</t>
+          <t>DEC-036</t>
         </is>
       </c>
       <c r="B204" s="68" t="inlineStr">
@@ -20467,7 +20554,7 @@
       <c r="C204" s="68" t="n"/>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>Gamificación como dominio propio (D13)</t>
+          <t>Se premia comportamiento verificado, no resultados</t>
         </is>
       </c>
       <c r="E204" s="69" t="inlineStr">
@@ -20477,14 +20564,14 @@
       </c>
       <c r="F204" s="69" t="inlineStr">
         <is>
-          <t>C. Igual que D12: si el motor se cae, la operación sigue igual. Y como se alimenta de eventos, el XP es recalculable: cambiar la tabla de puntos permite reprocesar el histórico. Si el XP se escribiera a mano en el momento, eso sería imposible. — XP, niveles, insignias, ligas, retos y referidos para el creador.</t>
+          <t>C. A premia al algoritmo de Instagram, no al creador. B produce sobrecompromiso —creadores que aceptan lo que no pueden cumplir— y, en el caso de seguidores, desmotiva al micro-creador y premia el vector de fraude de R-04. Detalle en docs/13 §3. — ¿Sobre qué se otorga XP?</t>
         </is>
       </c>
     </row>
     <row r="205" ht="23.25" customHeight="1" s="36">
       <c r="A205" s="67" t="inlineStr">
         <is>
-          <t>DEC-033</t>
+          <t>DEC-035</t>
         </is>
       </c>
       <c r="B205" s="68" t="inlineStr">
@@ -20495,7 +20582,7 @@
       <c r="C205" s="68" t="n"/>
       <c r="D205" s="69" t="inlineStr">
         <is>
-          <t>Registrar la conexión emisora en cada documento</t>
+          <t>El XP es append-only y nunca decrece</t>
         </is>
       </c>
       <c r="E205" s="69" t="inlineStr">
@@ -20505,14 +20592,14 @@
       </c>
       <c r="F205" s="69" t="inlineStr">
         <is>
-          <t>B, aplicado a comprobantes electrónicos, cobros por pasarela, pagos a creadores ejecutados por proveedor y correos enviados. — Paralelo exacto de DEC-019. Si dentro de un año hay que consultar ante el proveedor el estado del comprobante F001-00347, hay que saber por cuál se emitió.</t>
+          <t>B. Quitar puntos se percibe como robo y destruye la confianza de golpe. Además sería castigar dos veces con el mecanismo equivocado. Mismo patrón que el ledger financiero: se corrige con asientos nuevos, no editando. — ¿Se puede restar XP por un incumplimiento?</t>
         </is>
       </c>
     </row>
     <row r="206" ht="45.75" customHeight="1" s="36">
       <c r="A206" s="67" t="inlineStr">
         <is>
-          <t>DEC-032</t>
+          <t>DEC-034</t>
         </is>
       </c>
       <c r="B206" s="68" t="inlineStr">
@@ -20523,7 +20610,7 @@
       <c r="C206" s="68" t="n"/>
       <c r="D206" s="69" t="inlineStr">
         <is>
-          <t>Compartibilidad declarada por propósito</t>
+          <t>Gamificación como dominio propio (D13)</t>
         </is>
       </c>
       <c r="E206" s="69" t="inlineStr">
@@ -20533,14 +20620,14 @@
       </c>
       <c r="F206" s="69" t="inlineStr">
         <is>
-          <t>B. Las credenciales de facturación pertenecen al contribuyente: una sociedad no puede emitir con el certificado de otra. Una validación se cumple; una recomendación en un manual, no. Reformula BR-LE-008 sin contradecirla: lo prohibido era la herencia implícita; compartir por asignación explícita es otra cosa, y aun así sigue vedado para lo fiscal. — El addendum permite que una conexión sirva a varias entidades legales. Correcto para almacenamiento o correo; peligroso para facturación.</t>
+          <t>C. Igual que D12: si el motor se cae, la operación sigue igual. Y como se alimenta de eventos, el XP es recalculable: cambiar la tabla de puntos permite reprocesar el histórico. Si el XP se escribiera a mano en el momento, eso sería imposible. — XP, niveles, insignias, ligas, retos y referidos para el creador.</t>
         </is>
       </c>
     </row>
     <row r="207" ht="34.5" customHeight="1" s="36">
       <c r="A207" s="67" t="inlineStr">
         <is>
-          <t>DEC-031</t>
+          <t>DEC-033</t>
         </is>
       </c>
       <c r="B207" s="68" t="inlineStr">
@@ -20551,7 +20638,7 @@
       <c r="C207" s="68" t="n"/>
       <c r="D207" s="69" t="inlineStr">
         <is>
-          <t>Una URL de webhook por conexión</t>
+          <t>Registrar la conexión emisora en cada documento</t>
         </is>
       </c>
       <c r="E207" s="69" t="inlineStr">
@@ -20561,14 +20648,14 @@
       </c>
       <c r="F207" s="69" t="inlineStr">
         <is>
-          <t>B. El enrutado por URL hace la verificación de firma determinista y de un solo intento. Se acusa de inmediato (2xx) y se procesa en cola: un proveedor que no recibe respuesta en segundos reintenta y multiplica los eventos. — Con varias conexiones del mismo proveedor conviviendo, el payload entrante a menudo no identifica la sociedad, y probar firmas contra todos los secretos es lento e inseguro. El addendum enumera qué registrar de un webhook pero no resuelve de quién es.</t>
+          <t>B, aplicado a comprobantes electrónicos, cobros por pasarela, pagos a creadores ejecutados por proveedor y correos enviados. — Paralelo exacto de DEC-019. Si dentro de un año hay que consultar ante el proveedor el estado del comprobante F001-00347, hay que saber por cuál se emitió.</t>
         </is>
       </c>
     </row>
     <row r="208" ht="23.25" customHeight="1" s="36">
       <c r="A208" s="67" t="inlineStr">
         <is>
-          <t>DEC-030</t>
+          <t>DEC-032</t>
         </is>
       </c>
       <c r="B208" s="68" t="inlineStr">
@@ -20579,7 +20666,7 @@
       <c r="C208" s="68" t="n"/>
       <c r="D208" s="69" t="inlineStr">
         <is>
-          <t>Cifrado sobre para las credenciales</t>
+          <t>Compartibilidad declarada por propósito</t>
         </is>
       </c>
       <c r="E208" s="69" t="inlineStr">
@@ -20589,14 +20676,14 @@
       </c>
       <c r="F208" s="69" t="inlineStr">
         <is>
-          <t>B, con versionado en la rotación (no sobrescribir), escritura sin lectura desde la interfaz, y un filtro de redacción a nivel del logger — no "acordarse de no loguear". — El addendum señala que las credenciales pueden requerir almacenamiento distinto, sin concretar.</t>
+          <t>B. Las credenciales de facturación pertenecen al contribuyente: una sociedad no puede emitir con el certificado de otra. Una validación se cumple; una recomendación en un manual, no. Reformula BR-LE-008 sin contradecirla: lo prohibido era la herencia implícita; compartir por asignación explícita es otra cosa, y aun así sigue vedado para lo fiscal. — El addendum permite que una conexión sirva a varias entidades legales. Correcto para almacenamiento o correo; peligroso para facturación.</t>
         </is>
       </c>
     </row>
     <row r="209" ht="23.25" customHeight="1" s="36">
       <c r="A209" s="67" t="inlineStr">
         <is>
-          <t>DEC-029</t>
+          <t>DEC-031</t>
         </is>
       </c>
       <c r="B209" s="68" t="inlineStr">
@@ -20607,7 +20694,7 @@
       <c r="C209" s="68" t="n"/>
       <c r="D209" s="69" t="inlineStr">
         <is>
-          <t>Aislamiento de ambiente como barrera, no como filtro</t>
+          <t>Una URL de webhook por conexión</t>
         </is>
       </c>
       <c r="E209" s="69" t="inlineStr">
@@ -20617,14 +20704,14 @@
       </c>
       <c r="F209" s="69" t="inlineStr">
         <is>
-          <t>B. La defensa no puede depender de que alguien haya configurado bien. — El fallo más caro posible de este diseño: una conexión de producción resolviéndose fuera de producción. Consecuencias reales: emitir comprobantes fiscales de verdad desde QA, cobrar tarjetas en una demo, o enviar correos reales a 150 creadores desde staging.</t>
+          <t>B. El enrutado por URL hace la verificación de firma determinista y de un solo intento. Se acusa de inmediato (2xx) y se procesa en cola: un proveedor que no recibe respuesta en segundos reintenta y multiplica los eventos. — Con varias conexiones del mismo proveedor conviviendo, el payload entrante a menudo no identifica la sociedad, y probar firmas contra todos los secretos es lento e inseguro. El addendum enumera qué registrar de un webhook pero no resuelve de quién es.</t>
         </is>
       </c>
     </row>
     <row r="210" ht="45.75" customHeight="1" s="36">
       <c r="A210" s="67" t="inlineStr">
         <is>
-          <t>DEC-028</t>
+          <t>DEC-030</t>
         </is>
       </c>
       <c r="B210" s="68" t="inlineStr">
@@ -20635,7 +20722,7 @@
       <c r="C210" s="68" t="n"/>
       <c r="D210" s="69" t="inlineStr">
         <is>
-          <t>Matriz de propósitos obligatorios por país</t>
+          <t>Cifrado sobre para las credenciales</t>
         </is>
       </c>
       <c r="E210" s="69" t="inlineStr">
@@ -20645,14 +20732,14 @@
       </c>
       <c r="F210" s="69" t="inlineStr">
         <is>
-          <t>B, más un panel de cobertura en verde/rojo y una comprobación programada que avisa antes de que una credencial expirada rompa una operación. — Descubrir que no hay conexión de facturación para Ecuador al pulsar "emitir", con el cliente esperando, es un problema de diseño, no de configuración.</t>
+          <t>B, con versionado en la rotación (no sobrescribir), escritura sin lectura desde la interfaz, y un filtro de redacción a nivel del logger — no "acordarse de no loguear". — El addendum señala que las credenciales pueden requerir almacenamiento distinto, sin concretar.</t>
         </is>
       </c>
     </row>
     <row r="211" ht="34.5" customHeight="1" s="36">
       <c r="A211" s="67" t="inlineStr">
         <is>
-          <t>DEC-027</t>
+          <t>DEC-029</t>
         </is>
       </c>
       <c r="B211" s="68" t="inlineStr">
@@ -20663,7 +20750,7 @@
       <c r="C211" s="68" t="n"/>
       <c r="D211" s="69" t="inlineStr">
         <is>
-          <t>Resolución por especificidad, con empates rechazados al guardar</t>
+          <t>Aislamiento de ambiente como barrera, no como filtro</t>
         </is>
       </c>
       <c r="E211" s="69" t="inlineStr">
@@ -20673,14 +20760,14 @@
       </c>
       <c r="F211" s="69" t="inlineStr">
         <is>
-          <t>B, y sobre todo: los empates no se resuelven en ejecución, se prohíben al guardar. Si dos asignaciones activas puntúan igual para la misma combinación, la interfaz rechaza el guardado y explica el conflicto. Así el resolver es siempre determinista y nadie descubre un empate emitiendo una factura. — El addendum propone una escalera de cuatro peldaños. Funciona, pero no contempla el eje de marca ni dice qué hacer ante un empate.</t>
+          <t>B. La defensa no puede depender de que alguien haya configurado bien. — El fallo más caro posible de este diseño: una conexión de producción resolviéndose fuera de producción. Consecuencias reales: emitir comprobantes fiscales de verdad desde QA, cobrar tarjetas en una demo, o enviar correos reales a 150 creadores desde staging.</t>
         </is>
       </c>
     </row>
     <row r="212" ht="23.25" customHeight="1" s="36">
       <c r="A212" s="67" t="inlineStr">
         <is>
-          <t>DEC-026</t>
+          <t>DEC-028</t>
         </is>
       </c>
       <c r="B212" s="68" t="inlineStr">
@@ -20691,7 +20778,7 @@
       <c r="C212" s="68" t="n"/>
       <c r="D212" s="69" t="inlineStr">
         <is>
-          <t>purpose es un enum cerrado en código, no un catálogo editable</t>
+          <t>Matriz de propósitos obligatorios por país</t>
         </is>
       </c>
       <c r="E212" s="69" t="inlineStr">
@@ -20701,14 +20788,14 @@
       </c>
       <c r="F212" s="69" t="inlineStr">
         <is>
-          <t>B. El código se ramifica por propósito: invoicing implica una interfaz con emit()/getStatus(); email_transactional implica otra distinta. Un propósito creado desde el panel produciría una conexión perfectamente configurada que ningún código sabe ejecutar. Los catálogos editables son para datos de negocio; los propósitos son contratos de código. — El addendum lista los propósitos como si fueran datos administrables.</t>
+          <t>B, más un panel de cobertura en verde/rojo y una comprobación programada que avisa antes de que una credencial expirada rompa una operación. — Descubrir que no hay conexión de facturación para Ecuador al pulsar "emitir", con el cliente esperando, es un problema de diseño, no de configuración.</t>
         </is>
       </c>
     </row>
     <row r="213" ht="45.75" customHeight="1" s="36">
       <c r="A213" s="67" t="inlineStr">
         <is>
-          <t>DEC-025</t>
+          <t>DEC-027</t>
         </is>
       </c>
       <c r="B213" s="68" t="inlineStr">
@@ -20719,7 +20806,7 @@
       <c r="C213" s="68" t="n"/>
       <c r="D213" s="69" t="inlineStr">
         <is>
-          <t>Proveedor / Conexión / Asignación como tres entidades</t>
+          <t>Resolución por especificidad, con empates rechazados al guardar</t>
         </is>
       </c>
       <c r="E213" s="69" t="inlineStr">
@@ -20729,14 +20816,14 @@
       </c>
       <c r="F213" s="69" t="inlineStr">
         <is>
-          <t>B, tal como propone el addendum. integration_providers es catálogo respaldado por código (un proveedor solo existe si hay adaptador); integration_connections es la configuración viva; integration_assignments es el alcance, con NULL significando "cualquiera" y con vigencia (valid_from/valid_to) igual que la cobertura de facturación. — Un proveedor puede tener varias conexiones (producción, sandbox, por sociedad) y cada conexión puede aplicar a varios ámbitos.</t>
+          <t>B, y sobre todo: los empates no se resuelven en ejecución, se prohíben al guardar. Si dos asignaciones activas puntúan igual para la misma combinación, la interfaz rechaza el guardado y explica el conflicto. Así el resolver es siempre determinista y nadie descubre un empate emitiendo una factura. — El addendum propone una escalera de cuatro peldaños. Funciona, pero no contempla el eje de marca ni dice qué hacer ante un empate.</t>
         </is>
       </c>
     </row>
     <row r="214" ht="34.5" customHeight="1" s="36">
       <c r="A214" s="67" t="inlineStr">
         <is>
-          <t>DEC-024</t>
+          <t>DEC-026</t>
         </is>
       </c>
       <c r="B214" s="68" t="inlineStr">
@@ -20747,7 +20834,7 @@
       <c r="C214" s="68" t="n"/>
       <c r="D214" s="69" t="inlineStr">
         <is>
-          <t>Las integraciones son un subsistema propio, no Settings</t>
+          <t>purpose es un enum cerrado en código, no un catálogo editable</t>
         </is>
       </c>
       <c r="E214" s="69" t="inlineStr">
@@ -20757,14 +20844,14 @@
       </c>
       <c r="F214" s="69" t="inlineStr">
         <is>
-          <t>B. Un ajuste resuelve un valor; una integración resuelve una conexión viva que tiene estado, ciclo de vida y que falla. Además necesita dos ejes más (purpose, environment). Lo que sí se unifica son los nombres de los niveles, para que nadie confunda "global" con "plataforma". — DEC-018 ya definió una configuración jerárquica. La tentación es meter las integraciones dentro.</t>
+          <t>B. El código se ramifica por propósito: invoicing implica una interfaz con emit()/getStatus(); email_transactional implica otra distinta. Un propósito creado desde el panel produciría una conexión perfectamente configurada que ningún código sabe ejecutar. Los catálogos editables son para datos de negocio; los propósitos son contratos de código. — El addendum lista los propósitos como si fueran datos administrables.</t>
         </is>
       </c>
     </row>
     <row r="215" ht="23.25" customHeight="1" s="36">
       <c r="A215" s="67" t="inlineStr">
         <is>
-          <t>DEC-023</t>
+          <t>DEC-025</t>
         </is>
       </c>
       <c r="B215" s="68" t="inlineStr">
@@ -20775,7 +20862,7 @@
       <c r="C215" s="68" t="n"/>
       <c r="D215" s="69" t="inlineStr">
         <is>
-          <t>Identidad dual en comunicaciones</t>
+          <t>Proveedor / Conexión / Asignación como tres entidades</t>
         </is>
       </c>
       <c r="E215" s="69" t="inlineStr">
@@ -20785,14 +20872,14 @@
       </c>
       <c r="F215" s="69" t="inlineStr">
         <is>
-          <t>C. El creador y la marca cliente se relacionan con LATAM Social; las facturas, contratos y comunicaciones de cobranza deben identificar a la sociedad que responde legalmente. Implica remitente configurable por entidad para los correos de facturación. — ¿Los correos salen de "LATAM Social" o de "Soluciones Tecnológicas a Medida S.A.C."?</t>
+          <t>B, tal como propone el addendum. integration_providers es catálogo respaldado por código (un proveedor solo existe si hay adaptador); integration_connections es la configuración viva; integration_assignments es el alcance, con NULL significando "cualquiera" y con vigencia (valid_from/valid_to) igual que la cobertura de facturación. — Un proveedor puede tener varias conexiones (producción, sandbox, por sociedad) y cada conexión puede aplicar a varios ámbitos.</t>
         </is>
       </c>
     </row>
     <row r="216" ht="23.25" customHeight="1" s="36">
       <c r="A216" s="67" t="inlineStr">
         <is>
-          <t>DEC-022</t>
+          <t>DEC-024</t>
         </is>
       </c>
       <c r="B216" s="68" t="inlineStr">
@@ -20803,7 +20890,7 @@
       <c r="C216" s="68" t="n"/>
       <c r="D216" s="69" t="inlineStr">
         <is>
-          <t>Monedas: no derivar del país de la entidad</t>
+          <t>Las integraciones son un subsistema propio, no Settings</t>
         </is>
       </c>
       <c r="E216" s="69" t="inlineStr">
@@ -20813,14 +20900,14 @@
       </c>
       <c r="F216" s="69" t="inlineStr">
         <is>
-          <t>B. Coherente con BR-FIN-004 y BR-FIN-009, que ya exigían no asumir una sola moneda. — §11 del addendum. CTS Perú puede facturar en PEN a un cliente peruano y en USD a uno ecuatoriano.</t>
+          <t>B. Un ajuste resuelve un valor; una integración resuelve una conexión viva que tiene estado, ciclo de vida y que falla. Además necesita dos ejes más (purpose, environment). Lo que sí se unifica son los nombres de los niveles, para que nadie confunda "global" con "plataforma". — DEC-018 ya definió una configuración jerárquica. La tentación es meter las integraciones dentro.</t>
         </is>
       </c>
     </row>
     <row r="217" ht="45.75" customHeight="1" s="36">
       <c r="A217" s="67" t="inlineStr">
         <is>
-          <t>DEC-021</t>
+          <t>DEC-023</t>
         </is>
       </c>
       <c r="B217" s="68" t="inlineStr">
@@ -20831,7 +20918,7 @@
       <c r="C217" s="68" t="n"/>
       <c r="D217" s="69" t="inlineStr">
         <is>
-          <t>Series y numeración correlativa por entidad legal</t>
+          <t>Identidad dual en comunicaciones</t>
         </is>
       </c>
       <c r="E217" s="69" t="inlineStr">
@@ -20841,42 +20928,42 @@
       </c>
       <c r="F217" s="69" t="inlineStr">
         <is>
-          <t>C. A no permite series por entidad y deja huecos ante transacciones revertidas. B bloquea una fila que se lee constantemente. C aísla el punto de contención. — En Perú la numeración por serie debe ser correlativa y sin huecos. Con varias sociedades hay varios contadores independientes, y bajo concurrencia dos facturas simultáneas pueden tomar el mismo número o saltarse uno.</t>
+          <t>C. El creador y la marca cliente se relacionan con LATAM Social; las facturas, contratos y comunicaciones de cobranza deben identificar a la sociedad que responde legalmente. Implica remitente configurable por entidad para los correos de facturación. — ¿Los correos salen de "LATAM Social" o de "Soluciones Tecnológicas a Medida S.A.C."?</t>
         </is>
       </c>
     </row>
     <row r="218" ht="34.5" customHeight="1" s="36">
       <c r="A218" s="67" t="inlineStr">
         <is>
-          <t>DEC-020</t>
+          <t>DEC-022</t>
         </is>
       </c>
       <c r="B218" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C218" s="68" t="n"/>
       <c r="D218" s="69" t="inlineStr">
         <is>
-          <t>Entidad que factura vs. entidad que liquida al creador</t>
+          <t>Monedas: no derivar del país de la entidad</t>
         </is>
       </c>
       <c r="E218" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ DECIDIDA (2026-08-27) por DEC-156: opción C, y sin el «en el MVP». La sociedad de la campaña paga a todos sus creadores, sea cual sea el país de cada uno (BR-LE-009, ahora 🔴). Dónde se comprueba lo </t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F218" s="69" t="inlineStr">
         <is>
-          <t>C. A cierra la puerta; B la deja abierta para que alguien la cruce sin darse cuenta un martes por la tarde y genere una contingencia fiscal. C conserva la flexibilidad del modelo y exige una decisión consciente, respaldada por asesoría fiscal, para habilitarla. — §12 del addendum pide separar ambos conceptos. Pero si divergen, aparece una operación intercompañía entre dos sociedades del grupo, con precios de transferencia, documentación ante la autoridad tributaria, consolidación contable y posible retención en la fuente.</t>
+          <t>B. Coherente con BR-FIN-004 y BR-FIN-009, que ya exigían no asumir una sola moneda. — §11 del addendum. CTS Perú puede facturar en PEN a un cliente peruano y en USD a uno ecuatoriano.</t>
         </is>
       </c>
     </row>
     <row r="219" ht="23.25" customHeight="1" s="36">
       <c r="A219" s="67" t="inlineStr">
         <is>
-          <t>DEC-019</t>
+          <t>DEC-021</t>
         </is>
       </c>
       <c r="B219" s="68" t="inlineStr">
@@ -20887,7 +20974,7 @@
       <c r="C219" s="68" t="n"/>
       <c r="D219" s="69" t="inlineStr">
         <is>
-          <t>Entidad legal explícita e inmutable en cada documento</t>
+          <t>Series y numeración correlativa por entidad legal</t>
         </is>
       </c>
       <c r="E219" s="69" t="inlineStr">
@@ -20897,42 +20984,42 @@
       </c>
       <c r="F219" s="69" t="inlineStr">
         <is>
-          <t>C. A es un error silencioso: no da error, no rompe nada, y falsifica retroactivamente todos los documentos históricos. La clave foránea sola tampoco basta: si la sociedad cambia de domicilio, la factura antigua debe seguir mostrando el domicilio antiguo. — §14 del addendum. Si mañana Ecuador pasa a facturarse desde otra sociedad, las facturas de ayer deben seguir diciendo lo que decían ayer.</t>
+          <t>C. A no permite series por entidad y deja huecos ante transacciones revertidas. B bloquea una fila que se lee constantemente. C aísla el punto de contención. — En Perú la numeración por serie debe ser correlativa y sin huecos. Con varias sociedades hay varios contadores independientes, y bajo concurrencia dos facturas simultáneas pueden tomar el mismo número o saltarse uno.</t>
         </is>
       </c>
     </row>
     <row r="220" ht="23.25" customHeight="1" s="36">
       <c r="A220" s="67" t="inlineStr">
         <is>
-          <t>DEC-018</t>
+          <t>DEC-020</t>
         </is>
       </c>
       <c r="B220" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C220" s="68" t="n"/>
       <c r="D220" s="69" t="inlineStr">
         <is>
-          <t>Configuración jerárquica en cascada</t>
+          <t>Entidad que factura vs. entidad que liquida al creador</t>
         </is>
       </c>
       <c r="E220" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t xml:space="preserve">✅ DECIDIDA (2026-08-27) por DEC-156: opción C, y sin el «en el MVP». La sociedad de la campaña paga a todos sus creadores, sea cual sea el país de cada uno (BR-LE-009, ahora 🔴). Dónde se comprueba lo </t>
         </is>
       </c>
       <c r="F220" s="69" t="inlineStr">
         <is>
-          <t>B, con dos condiciones no negociables: la interfaz debe mostrar siempre de dónde viene el valor efectivo, y los secretos se cifran por entidad y nunca se heredan. — La configuración deja de ser global: hay ajustes de plataforma, de marca, de entidad legal y de (entidad × país).</t>
+          <t>C. A cierra la puerta; B la deja abierta para que alguien la cruce sin darse cuenta un martes por la tarde y genere una contingencia fiscal. C conserva la flexibilidad del modelo y exige una decisión consciente, respaldada por asesoría fiscal, para habilitarla. — §12 del addendum pide separar ambos conceptos. Pero si divergen, aparece una operación intercompañía entre dos sociedades del grupo, con precios de transferencia, documentación ante la autoridad tributaria, consolidación contable y posible retención en la fuente.</t>
         </is>
       </c>
     </row>
     <row r="221" ht="45.75" customHeight="1" s="36">
       <c r="A221" s="67" t="inlineStr">
         <is>
-          <t>DEC-017</t>
+          <t>DEC-019</t>
         </is>
       </c>
       <c r="B221" s="68" t="inlineStr">
@@ -20943,7 +21030,7 @@
       <c r="C221" s="68" t="n"/>
       <c r="D221" s="69" t="inlineStr">
         <is>
-          <t>Cobertura de facturación como relación N:M con vigencia</t>
+          <t>Entidad legal explícita e inmutable en cada documento</t>
         </is>
       </c>
       <c r="E221" s="69" t="inlineStr">
@@ -20953,14 +21040,14 @@
       </c>
       <c r="F221" s="69" t="inlineStr">
         <is>
-          <t>C. A es directamente incorrecta. B pierde la información de *cuándo* dejó de aplicar una cobertura, y eso hace imposible auditar por qué una factura de 2027 salió de una sociedad y una de 2029 de otra. La vigencia es lo que permite la evolución del §15 del addendum sin destruir historia. — Una sociedad puede facturar clientes de varios países, y un país puede ser atendido por más de una sociedad.</t>
+          <t>C. A es un error silencioso: no da error, no rompe nada, y falsifica retroactivamente todos los documentos históricos. La clave foránea sola tampoco basta: si la sociedad cambia de domicilio, la factura antigua debe seguir mostrando el domicilio antiguo. — §14 del addendum. Si mañana Ecuador pasa a facturarse desde otra sociedad, las facturas de ayer deben seguir diciendo lo que decían ayer.</t>
         </is>
       </c>
     </row>
     <row r="222" ht="34.5" customHeight="1" s="36">
       <c r="A222" s="67" t="inlineStr">
         <is>
-          <t>DEC-016</t>
+          <t>DEC-018</t>
         </is>
       </c>
       <c r="B222" s="68" t="inlineStr">
@@ -20971,7 +21058,7 @@
       <c r="C222" s="68" t="n"/>
       <c r="D222" s="69" t="inlineStr">
         <is>
-          <t>Desambiguación de los conceptos organizacionales</t>
+          <t>Configuración jerárquica en cascada</t>
         </is>
       </c>
       <c r="E222" s="69" t="inlineStr">
@@ -20981,14 +21068,14 @@
       </c>
       <c r="F222" s="69" t="inlineStr">
         <is>
-          <t>B. A garantiza que en seis meses nadie sepa si brand_id apunta a LATAM Social o a Shampoo ABC. Es la fuente número uno de errores de datos en sistemas multi-entidad. — El addendum introduce "marca de plataforma" (LATAM Social) y "entidad legal" (la sociedad). El modelo anterior ya usaba Brand para la marca del cliente. Cuatro conceptos organizacionales con nombres que se pisan.</t>
+          <t>B, con dos condiciones no negociables: la interfaz debe mostrar siempre de dónde viene el valor efectivo, y los secretos se cifran por entidad y nunca se heredan. — La configuración deja de ser global: hay ajustes de plataforma, de marca, de entidad legal y de (entidad × país).</t>
         </is>
       </c>
     </row>
     <row r="223" ht="23.85" customHeight="1" s="36">
       <c r="A223" s="67" t="inlineStr">
         <is>
-          <t>DEC-015</t>
+          <t>DEC-017</t>
         </is>
       </c>
       <c r="B223" s="68" t="inlineStr">
@@ -20999,24 +21086,24 @@
       <c r="C223" s="68" t="n"/>
       <c r="D223" s="69" t="inlineStr">
         <is>
-          <t>Retención y minimización de datos personales</t>
+          <t>Cobertura de facturación como relación N:M con vigencia</t>
         </is>
       </c>
       <c r="E223" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA — requiere validación legal</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F223" s="69" t="inlineStr">
         <is>
-          <t>B. Además: la dirección de envío se purga N meses después de la campaña; las copias de documentos de identidad, si se recogen, se cifran y tienen la retención más corta legalmente posible. Menos datos = menos riesgo. — Se recopilan documento de identidad, fecha de nacimiento, dirección, datos bancarios y dirección de envío de cientos de personas.</t>
+          <t>C. A es directamente incorrecta. B pierde la información de *cuándo* dejó de aplicar una cobertura, y eso hace imposible auditar por qué una factura de 2027 salió de una sociedad y una de 2029 de otra. La vigencia es lo que permite la evolución del §15 del addendum sin destruir historia. — Una sociedad puede facturar clientes de varios países, y un país puede ser atendido por más de una sociedad.</t>
         </is>
       </c>
     </row>
     <row r="224" ht="46.25" customHeight="1" s="36">
       <c r="A224" s="67" t="inlineStr">
         <is>
-          <t>DEC-014</t>
+          <t>DEC-016</t>
         </is>
       </c>
       <c r="B224" s="68" t="inlineStr">
@@ -21027,7 +21114,7 @@
       <c r="C224" s="68" t="n"/>
       <c r="D224" s="69" t="inlineStr">
         <is>
-          <t>Modelo de derechos de uso del contenido</t>
+          <t>Desambiguación de los conceptos organizacionales</t>
         </is>
       </c>
       <c r="E224" s="69" t="inlineStr">
@@ -21037,14 +21124,14 @@
       </c>
       <c r="F224" s="69" t="inlineStr">
         <is>
-          <t>B. Además, alertas de vencimiento: usar contenido después de que expiró la licencia es una infracción con consecuencias legales para el cliente y reputacionales para el operador. — Lo que la marca realmente compra es una licencia. Modelarlo como un booleano "cede derechos: sí/no" es insuficiente y genera disputas.</t>
+          <t>B. A garantiza que en seis meses nadie sepa si brand_id apunta a LATAM Social o a Shampoo ABC. Es la fuente número uno de errores de datos en sistemas multi-entidad. — El addendum introduce "marca de plataforma" (LATAM Social) y "entidad legal" (la sociedad). El modelo anterior ya usaba Brand para la marca del cliente. Cuatro conceptos organizacionales con nombres que se pisan.</t>
         </is>
       </c>
     </row>
     <row r="225" ht="35.05" customHeight="1" s="36">
       <c r="A225" s="67" t="inlineStr">
         <is>
-          <t>DEC-013</t>
+          <t>DEC-015</t>
         </is>
       </c>
       <c r="B225" s="68" t="inlineStr">
@@ -21055,24 +21142,24 @@
       <c r="C225" s="68" t="n"/>
       <c r="D225" s="69" t="inlineStr">
         <is>
-          <t>Alcance del portal de la marca en el MVP</t>
+          <t>Retención y minimización de datos personales</t>
         </is>
       </c>
       <c r="E225" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>PROPUESTA — requiere validación legal</t>
         </is>
       </c>
       <c r="F225" s="69" t="inlineStr">
         <is>
-          <t>B. Entrega el 90% del valor percibido con el 15% del esfuerzo, y es el camino natural hacia A en F13. Requiere cuidado en seguridad: enlaces de un solo destinatario, con expiración, revocables y auditados. — Con 3 marcas, construir un portal con cuentas, roles, facturación y documentos es esfuerzo desproporcionado.</t>
+          <t>B. Además: la dirección de envío se purga N meses después de la campaña; las copias de documentos de identidad, si se recogen, se cifran y tienen la retención más corta legalmente posible. Menos datos = menos riesgo. — Se recopilan documento de identidad, fecha de nacimiento, dirección, datos bancarios y dirección de envío de cientos de personas.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67" t="inlineStr">
         <is>
-          <t>DEC-012</t>
+          <t>DEC-014</t>
         </is>
       </c>
       <c r="B226" s="68" t="inlineStr">
@@ -21083,7 +21170,7 @@
       <c r="C226" s="68" t="n"/>
       <c r="D226" s="69" t="inlineStr">
         <is>
-          <t>Longitud del formulario de lead B2B</t>
+          <t>Modelo de derechos de uso del contenido</t>
         </is>
       </c>
       <c r="E226" s="69" t="inlineStr">
@@ -21093,14 +21180,14 @@
       </c>
       <c r="F226" s="69" t="inlineStr">
         <is>
-          <t>B: empresa, nombre, email corporativo, teléfono/WhatsApp, país, objetivo, mensaje. El resto (presupuesto, cantidad de creadores, países objetivo, industria) se captura en la conversación comercial y se guarda en el CRM. UTM, landing y origen se capturan ocultos, siempre. — La spec lista 16 campos. Cada campo adicional reduce la conversión.</t>
+          <t>B. Además, alertas de vencimiento: usar contenido después de que expiró la licencia es una infracción con consecuencias legales para el cliente y reputacionales para el operador. — Lo que la marca realmente compra es una licencia. Modelarlo como un booleano "cede derechos: sí/no" es insuficiente y genera disputas.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67" t="inlineStr">
         <is>
-          <t>DEC-011</t>
+          <t>DEC-013</t>
         </is>
       </c>
       <c r="B227" s="68" t="inlineStr">
@@ -21111,7 +21198,7 @@
       <c r="C227" s="68" t="n"/>
       <c r="D227" s="69" t="inlineStr">
         <is>
-          <t>¿La plataforma publica en las redes del creador?</t>
+          <t>Alcance del portal de la marca en el MVP</t>
         </is>
       </c>
       <c r="E227" s="69" t="inlineStr">
@@ -21121,14 +21208,14 @@
       </c>
       <c r="F227" s="69" t="inlineStr">
         <is>
-          <t>B. A añade riesgo de cuenta, complejidad enorme y las APIs cambian sin aviso. La verificación posterior aporta casi todo el valor con una fracción del costo. — Publicar automáticamente requiere permisos amplios, es frágil y las plataformas lo restringen.</t>
+          <t>B. Entrega el 90% del valor percibido con el 15% del esfuerzo, y es el camino natural hacia A en F13. Requiere cuidado en seguridad: enlaces de un solo destinatario, con expiración, revocables y auditados. — Con 3 marcas, construir un portal con cuentas, roles, facturación y documentos es esfuerzo desproporcionado.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67" t="inlineStr">
         <is>
-          <t>DEC-010</t>
+          <t>DEC-012</t>
         </is>
       </c>
       <c r="B228" s="68" t="inlineStr">
@@ -21139,7 +21226,7 @@
       <c r="C228" s="68" t="n"/>
       <c r="D228" s="69" t="inlineStr">
         <is>
-          <t>Estado de campaña vs. estado de participación</t>
+          <t>Longitud del formulario de lead B2B</t>
         </is>
       </c>
       <c r="E228" s="69" t="inlineStr">
@@ -21149,14 +21236,14 @@
       </c>
       <c r="F228" s="69" t="inlineStr">
         <is>
-          <t>B, obligatoriamente. A es el error de diseño más frecuente y más caro en plataformas de este tipo: obliga a hacks inmediatos y hace imposible el reporte de avance. — Una campaña live puede tener creadores aún en revisión.</t>
+          <t>B: empresa, nombre, email corporativo, teléfono/WhatsApp, país, objetivo, mensaje. El resto (presupuesto, cantidad de creadores, países objetivo, industria) se captura en la conversación comercial y se guarda en el CRM. UTM, landing y origen se capturan ocultos, siempre. — La spec lista 16 campos. Cada campo adicional reduce la conversión.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67" t="inlineStr">
         <is>
-          <t>DEC-009</t>
+          <t>DEC-011</t>
         </is>
       </c>
       <c r="B229" s="68" t="inlineStr">
@@ -21167,7 +21254,7 @@
       <c r="C229" s="68" t="n"/>
       <c r="D229" s="69" t="inlineStr">
         <is>
-          <t>Origen de los datos de audiencia</t>
+          <t>¿La plataforma publica en las redes del creador?</t>
         </is>
       </c>
       <c r="E229" s="69" t="inlineStr">
@@ -21177,14 +21264,14 @@
       </c>
       <c r="F229" s="69" t="inlineStr">
         <is>
-          <t>A en el MVP (manual + evidencia + chequeos de coherencia), B en F12–F14, C evaluado por costo cuando el volumen lo justifique: comprar datos verificados suele ser más barato que construir y mantener integraciones con 6 plataformas. — Los datos autodeclarados son el principal vector de fraude. Las APIs oficiales exigen que el creador conecte su cuenta (Instagram/Facebook requieren cuenta Business/Creator y autorización explícita; TikTok y YouTube tienen sus propios programas).</t>
+          <t>B. A añade riesgo de cuenta, complejidad enorme y las APIs cambian sin aviso. La verificación posterior aporta casi todo el valor con una fracción del costo. — Publicar automáticamente requiere permisos amplios, es frágil y las plataformas lo restringen.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67" t="inlineStr">
         <is>
-          <t>DEC-008</t>
+          <t>DEC-010</t>
         </is>
       </c>
       <c r="B230" s="68" t="inlineStr">
@@ -21195,7 +21282,7 @@
       <c r="C230" s="68" t="n"/>
       <c r="D230" s="69" t="inlineStr">
         <is>
-          <t>Almacenamiento de archivos</t>
+          <t>Estado de campaña vs. estado de participación</t>
         </is>
       </c>
       <c r="E230" s="69" t="inlineStr">
@@ -21205,14 +21292,14 @@
       </c>
       <c r="F230" s="69" t="inlineStr">
         <is>
-          <t>B, sin excepción. A rompe el despliegue en más de un servidor, complica los backups, no escala y migrar después implica reescribir rutas de miles de archivos. Cloudflare R2 o Backblaze B2 tienen costo de egreso muy bajo, relevante porque los clientes descargarán contenido. — Campañas UGC generan video pesado (0,5–3 GB por campaña).</t>
+          <t>B, obligatoriamente. A es el error de diseño más frecuente y más caro en plataformas de este tipo: obliga a hacks inmediatos y hace imposible el reporte de avance. — Una campaña live puede tener creadores aún en revisión.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67" t="inlineStr">
         <is>
-          <t>DEC-007</t>
+          <t>DEC-009</t>
         </is>
       </c>
       <c r="B231" s="68" t="inlineStr">
@@ -21223,7 +21310,7 @@
       <c r="C231" s="68" t="n"/>
       <c r="D231" s="69" t="inlineStr">
         <is>
-          <t>Pasarela de pago (Culqi) en el MVP</t>
+          <t>Origen de los datos de audiencia</t>
         </is>
       </c>
       <c r="E231" s="69" t="inlineStr">
@@ -21233,14 +21320,14 @@
       </c>
       <c r="F231" s="69" t="inlineStr">
         <is>
-          <t>B. Se construye la abstracción (PaymentGatewayInterface) pero no la integración. Si aparece un segmento de ticket bajo (p. ej. paquetes autoservicio para pymes), se activa. — La spec pide integrar Culqi. Pero en B2B LATAM, campañas de miles de soles se pagan por transferencia contra factura, no con tarjeta. Una campaña de S/ 30.000 no se cobra con tarjeta (comisión ~3,5% = S/ 1.050 regalados).</t>
+          <t>A en el MVP (manual + evidencia + chequeos de coherencia), B en F12–F14, C evaluado por costo cuando el volumen lo justifique: comprar datos verificados suele ser más barato que construir y mantener integraciones con 6 plataformas. — Los datos autodeclarados son el principal vector de fraude. Las APIs oficiales exigen que el creador conecte su cuenta (Instagram/Facebook requieren cuenta Business/Creator y autorización explícita; TikTok y YouTube tienen sus propios programas).</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67" t="inlineStr">
         <is>
-          <t>DEC-006</t>
+          <t>DEC-008</t>
         </is>
       </c>
       <c r="B232" s="68" t="inlineStr">
@@ -21251,7 +21338,7 @@
       <c r="C232" s="68" t="n"/>
       <c r="D232" s="69" t="inlineStr">
         <is>
-          <t>Separación Aplicación vs. Creador</t>
+          <t>Almacenamiento de archivos</t>
         </is>
       </c>
       <c r="E232" s="69" t="inlineStr">
@@ -21261,42 +21348,42 @@
       </c>
       <c r="F232" s="69" t="inlineStr">
         <is>
-          <t>B. Permite reaplicaciones, conserva el histórico de rechazos y evita que un rechazo contamine la entidad permanente. — La spec mezcla el ciclo de vida de la solicitud con el del creador.</t>
+          <t>B, sin excepción. A rompe el despliegue en más de un servidor, complica los backups, no escala y migrar después implica reescribir rutas de miles de archivos. Cloudflare R2 o Backblaze B2 tienen costo de egreso muy bajo, relevante porque los clientes descargarán contenido. — Campañas UGC generan video pesado (0,5–3 GB por campaña).</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67" t="inlineStr">
         <is>
-          <t>DEC-005</t>
+          <t>DEC-007</t>
         </is>
       </c>
       <c r="B233" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C233" s="68" t="n"/>
       <c r="D233" s="69" t="inlineStr">
         <is>
-          <t>Régimen legal y tributario del pago al creador ✅ RESUELTA (parcial)</t>
+          <t>Pasarela de pago (Culqi) en el MVP</t>
         </is>
       </c>
       <c r="E233" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA para creadores peruanos · 🔴 Q-33 abierta para extranjeros (bloquea F9 solo en ese caso)</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F233" s="69" t="inlineStr">
         <is>
-          <t>C, con la vía simplificada definida por un contador. Y en cualquier caso: el sistema debe modelar tax_regime por creador y por país, con requisitos documentales configurables por régimen, y bloquear el pago si falta el documento requerido. — En Perú, pagar a una persona natural por un servicio exige normalmente comprobante (recibo por honorarios electrónico) y puede implicar retención de renta de 4.ª categoría, con umbrales y suspensión de retención. Muchos micro-creadores no tienen RUC ni emiten comprobantes. Sin resolver esto, no se puede pagar legalmente a escala.</t>
+          <t>B. Se construye la abstracción (PaymentGatewayInterface) pero no la integración. Si aparece un segmento de ticket bajo (p. ej. paquetes autoservicio para pymes), se activa. — La spec pide integrar Culqi. Pero en B2B LATAM, campañas de miles de soles se pagan por transferencia contra factura, no con tarjeta. Una campaña de S/ 30.000 no se cobra con tarjeta (comisión ~3,5% = S/ 1.050 regalados).</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67" t="inlineStr">
         <is>
-          <t>DEC-004</t>
+          <t>DEC-006</t>
         </is>
       </c>
       <c r="B234" s="68" t="inlineStr">
@@ -21307,108 +21394,108 @@
       <c r="C234" s="68" t="n"/>
       <c r="D234" s="69" t="inlineStr">
         <is>
-          <t>Modelo económico: principal vs. comisión</t>
+          <t>Separación Aplicación vs. Creador</t>
         </is>
       </c>
       <c r="E234" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA — confirmar con el contador</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F234" s="69" t="inlineStr">
         <is>
-          <t>A, coherente con §53 de la especificación (Revenue − Creator Cost = Margen). Determina el modelo fiscal, contable y financiero completo. — ¿El operador vende la campaña y compra el contenido (reventa), o cobra una comisión sobre una transacción entre marca y creador?</t>
+          <t>B. Permite reaplicaciones, conserva el histórico de rechazos y evita que un rechazo contamine la entidad permanente. — La spec mezcla el ciclo de vida de la solicitud con el del creador.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67" t="inlineStr">
         <is>
-          <t>DEC-003</t>
+          <t>DEC-005</t>
         </is>
       </c>
       <c r="B235" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C235" s="68" t="n"/>
       <c r="D235" s="69" t="inlineStr">
         <is>
-          <t>Estrategia de frontend</t>
+          <t>Régimen legal y tributario del pago al creador ✅ RESUELTA (parcial)</t>
         </is>
       </c>
       <c r="E235" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>✅ APROBADA para creadores peruanos · 🔴 Q-33 abierta para extranjeros (bloquea F9 solo en ese caso)</t>
         </is>
       </c>
       <c r="F235" s="69" t="inlineStr">
         <is>
-          <t>A. B duplica el trabajo y, sobre todo, duplica la autorización —el punto donde este sistema más se puede romper—. El portal del creador se entrega como PWA instalable con A. — Cuatro portales con necesidades distintas. Equipo pequeño.</t>
+          <t>C, con la vía simplificada definida por un contador. Y en cualquier caso: el sistema debe modelar tax_regime por creador y por país, con requisitos documentales configurables por régimen, y bloquear el pago si falta el documento requerido. — En Perú, pagar a una persona natural por un servicio exige normalmente comprobante (recibo por honorarios electrónico) y puede implicar retención de renta de 4.ª categoría, con umbrales y suspensión de retención. Muchos micro-creadores no tienen RUC ni emiten comprobantes. Sin resolver esto, no se puede pagar legalmente a escala.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67" t="inlineStr">
         <is>
-          <t>DEC-002</t>
+          <t>DEC-004</t>
         </is>
       </c>
       <c r="B236" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C236" s="68" t="n"/>
       <c r="D236" s="69" t="inlineStr">
         <is>
-          <t>Multitenancy ✅ RESUELTA</t>
+          <t>Modelo económico: principal vs. comisión</t>
         </is>
       </c>
       <c r="E236" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA (decisión del negocio, 2026-08-21)</t>
+          <t>PROPUESTA — confirmar con el contador</t>
         </is>
       </c>
       <c r="F236" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hoy hay un solo operador. La spec contempla agencias y white-label a futuro (§78).</t>
+          <t>A, coherente con §53 de la especificación (Revenue − Creator Cost = Margen). Determina el modelo fiscal, contable y financiero completo. — ¿El operador vende la campaña y compra el contenido (reventa), o cobra una comisión sobre una transacción entre marca y creador?</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67" t="inlineStr">
         <is>
-          <t>DEC-001</t>
+          <t>DEC-003</t>
         </is>
       </c>
       <c r="B237" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C237" s="68" t="n"/>
       <c r="D237" s="69" t="inlineStr">
         <is>
-          <t>Framework PHP</t>
+          <t>Estrategia de frontend</t>
         </is>
       </c>
       <c r="E237" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA (2026-08-22). Proyecto creado: ver tools/bootstrap-laravel.ps1 y CONTRIBUTING.md</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F237" s="69" t="inlineStr">
         <is>
-          <t>A — Laravel 12. C queda descartada: construir a mano autenticación, colas, migraciones y abstracción de storage añadiría 3–5 meses de trabajo indiferenciado y una superficie de seguridad propia que nadie audita. B es defendible si el equipo ya domina Symfony. — La spec exige PHP 8.3 y "MVC o equivalente bien estructurado", y a la vez pide migraciones, seeders, colas, scheduler, cache, logs, SMTP, webhooks, RBAC, i18n y tests. Todo eso ya existe, probado en producción, en los frameworks maduros.</t>
+          <t>A. B duplica el trabajo y, sobre todo, duplica la autorización —el punto donde este sistema más se puede romper—. El portal del creador se entrega como PWA instalable con A. — Cuatro portales con necesidades distintas. Equipo pequeño.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67" t="inlineStr">
         <is>
-          <t>DEC-000</t>
+          <t>DEC-002</t>
         </is>
       </c>
       <c r="B238" s="68" t="inlineStr">
@@ -21419,15 +21506,71 @@
       <c r="C238" s="68" t="n"/>
       <c r="D238" s="69" t="inlineStr">
         <is>
+          <t>Multitenancy ✅ RESUELTA</t>
+        </is>
+      </c>
+      <c r="E238" s="69" t="inlineStr">
+        <is>
+          <t>✅ APROBADA (decisión del negocio, 2026-08-21)</t>
+        </is>
+      </c>
+      <c r="F238" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — Hoy hay un solo operador. La spec contempla agencias y white-label a futuro (§78).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="67" t="inlineStr">
+        <is>
+          <t>DEC-001</t>
+        </is>
+      </c>
+      <c r="B239" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C239" s="68" t="n"/>
+      <c r="D239" s="69" t="inlineStr">
+        <is>
+          <t>Framework PHP</t>
+        </is>
+      </c>
+      <c r="E239" s="69" t="inlineStr">
+        <is>
+          <t>✅ APROBADA (2026-08-22). Proyecto creado: ver tools/bootstrap-laravel.ps1 y CONTRIBUTING.md</t>
+        </is>
+      </c>
+      <c r="F239" s="69" t="inlineStr">
+        <is>
+          <t>A — Laravel 12. C queda descartada: construir a mano autenticación, colas, migraciones y abstracción de storage añadiría 3–5 meses de trabajo indiferenciado y una superficie de seguridad propia que nadie audita. B es defendible si el equipo ya domina Symfony. — La spec exige PHP 8.3 y "MVC o equivalente bien estructurado", y a la vez pide migraciones, seeders, colas, scheduler, cache, logs, SMTP, webhooks, RBAC, i18n y tests. Todo eso ya existe, probado en producción, en los frameworks maduros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="67" t="inlineStr">
+        <is>
+          <t>DEC-000</t>
+        </is>
+      </c>
+      <c r="B240" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C240" s="68" t="n"/>
+      <c r="D240" s="69" t="inlineStr">
+        <is>
           <t>Nombre del producto y dominio ✅ RESUELTA</t>
         </is>
       </c>
-      <c r="E238" s="69" t="inlineStr">
+      <c r="E240" s="69" t="inlineStr">
         <is>
           <t>✅ APROBADA (addendum 2026-08-21)</t>
         </is>
       </c>
-      <c r="F238" s="69" t="inlineStr">
+      <c r="F240" s="69" t="inlineStr">
         <is>
           <t>El addendum del 2026-08-21 lo define: la marca de plataforma es LATAM Social. El identificador técnico del proyecto pasa a latam-social. El nombre de trabajo provisional "CTS Creators" queda descartado. — El repositorio se llama ManageCampaingInfluencer (con error ortográfico). El nombre afecta marca, dominio, correos y branding.</t>
         </is>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -2241,7 +2241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J180"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="35" min="1" max="1"/>
@@ -10609,6 +10609,56 @@
       <c r="J179" s="35" t="inlineStr">
         <is>
           <t>2026-08-31. FUERA DEL ALCANCE ORIGINAL. Lo vio el negocio antes de escribir una linea de la landing: /creadores era la lista del admin y tiene que ser la puerta publica de los creadores. 149 rutas se mudan con UNA linea --docs/08 prohibe URLs a mano en las vistas, y esa regla es lo que lo hace gratis (DEC-236)--; 21 se quedan fuera con su motivo, incluidas /contrasena/nueva y /marca/logo, que comparten primer segmento con algo que si se movio (DEC-237). Una prueba recorre todas las rutas con nombre. Las 390 URLs a mano de las pruebas quedan como T-78. 984 pruebas. docs/fase-9/9.21a-LA-TRASTIENDA-SE-MUDA.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="57" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B180" s="35" t="inlineStr">
+        <is>
+          <t>Ola 2 - Escalar comercialmente</t>
+        </is>
+      </c>
+      <c r="C180" s="35" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="D180" s="35" t="inlineStr">
+        <is>
+          <t>Finanzas y facturacion</t>
+        </is>
+      </c>
+      <c r="E180" s="35" t="inlineStr">
+        <is>
+          <t>9.21b</t>
+        </is>
+      </c>
+      <c r="F180" s="35" t="inlineStr">
+        <is>
+          <t>La puerta de la calle: dos portadas publicas con el texto editable y la postulacion</t>
+        </is>
+      </c>
+      <c r="G180" s="35" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="H180" s="35">
+        <f>IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G180,Config!$A$3:$A$8,0)),0)</f>
+        <v/>
+      </c>
+      <c r="I180" s="35">
+        <f>IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G180,Config!$A$3:$A$8,0)),0)</f>
+        <v/>
+      </c>
+      <c r="J180" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-31. FUERA DEL ALCANCE ORIGINAL. / habla a las marcas y /creadores a los creadores, enlazadas entre si (DEC-238). El texto es un DATO --titular, bloques, boton y lo que sale en buscadores-- editable desde /backoffice/landing y colgado de la marca (DEC-239). La postulacion publica escribe en creator_applications, que existia desde la Fase 2 con source=landing y sin nadie que escribiera, con throttle y campo trampa en vez de CAPTCHA (DEC-240). Sin portada se va al acceso, no a un 404 (DEC-241). 1001 pruebas; 2182 aserciones SQL en MariaDB y 2172 en MySQL 8. docs/fase-9/9.21b-LA-PUERTA-DE-LA-CALLE.md</t>
         </is>
       </c>
     </row>
@@ -15058,7 +15108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F240"/>
+  <dimension ref="A1:F244"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="35" min="1" max="1"/>
@@ -15111,7 +15161,7 @@
     <row r="3" ht="79.5" customHeight="1" s="36">
       <c r="A3" s="67" t="inlineStr">
         <is>
-          <t>DEC-236</t>
+          <t>DEC-238</t>
         </is>
       </c>
       <c r="B3" s="68" t="inlineStr">
@@ -15122,24 +15172,24 @@
       <c r="C3" s="68" t="n"/>
       <c r="D3" s="69" t="inlineStr">
         <is>
-          <t>Todo lo que exige sesion vive bajo /backoffice</t>
+          <t>/ habla a las MARCAS y /creadores a los creadores</t>
         </is>
       </c>
       <c r="E3" s="69" t="inlineStr">
         <is>
-          <t>9.21a</t>
+          <t>9.21b</t>
         </is>
       </c>
       <c r="F3" s="69" t="inlineStr">
         <is>
-          <t>Lo vio el negocio antes de escribir una linea de la landing: /creadores tiene que ser la puerta PUBLICA de los creadores, y descubrirlo despues de publicar habria roto enlaces ya compartidos. Dentro entra todo lo que pide sesion sea de quien sea; lo que cada uno ve lo siguen decidiendo sus permisos. Costo una linea porque docs/08 prohibe escribir URLs a mano en las vistas: comprobado, cero resultados en app/, resources/ y config/.</t>
+          <t>Es un mercado de dos lados y el lado que PAGA se pone en la puerta: una portada que abre reclutando creadores se lee como «agencia buscando talento». Los creadores llegan por un enlace, no por la home. Las dos se enlazan entre si. El argumento en contra queda escrito: si el cuello de botella es tener creadores, el trafico que hace falta primero es el suyo; aun asi la home no cambia, porque moverla despues cuesta posicionamiento.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="57" customHeight="1" s="36">
       <c r="A4" s="67" t="inlineStr">
         <is>
-          <t>DEC-237</t>
+          <t>DEC-239</t>
         </is>
       </c>
       <c r="B4" s="68" t="inlineStr">
@@ -15150,24 +15200,24 @@
       <c r="C4" s="68" t="n"/>
       <c r="D4" s="69" t="inlineStr">
         <is>
-          <t>Veintiuna rutas se quedan fuera, y cada una con su motivo escrito</t>
+          <t>El texto de la portada es un dato, y cuelga de la marca</t>
         </is>
       </c>
       <c r="E4" s="69" t="inlineStr">
         <is>
-          <t>9.21a</t>
+          <t>9.21b</t>
         </is>
       </c>
       <c r="F4" s="69" t="inlineStr">
         <is>
-          <t>El acceso y la recuperacion son la puerta; la invitacion y la aprobacion llegan por enlace con token a alguien que no tiene cuenta; el logotipo y el favicon los pinta la pantalla de acceso. Dos comparten primer segmento con algo que si se mudo: /contrasena frente a /contrasena/nueva, y /marca frente a /marca/logo. La lista vive en una prueba que recorre todas las rutas con nombre.</t>
+          <t>DEC-190 en el sitio donde mas se nota: la marca del panel la ve quien ya entro; esto lo ve quien todavia esta decidiendo si te escribe. landing_pages lleva platform_brand_id: es UNA columna sobre el eje en el que el producto esta construido --distinto de las asignaciones de tres ejes de 9.17d, que resolvian un problema inexistente--. Dos paginas y no un gestor de contenidos: cada una tiene su formulario y su publico, asi que son codigo.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="79.5" customHeight="1" s="36">
       <c r="A5" s="67" t="inlineStr">
         <is>
-          <t>DEC-233</t>
+          <t>DEC-240</t>
         </is>
       </c>
       <c r="B5" s="68" t="inlineStr">
@@ -15178,24 +15228,24 @@
       <c r="C5" s="68" t="n"/>
       <c r="D5" s="69" t="inlineStr">
         <is>
-          <t>La configuracion tiene UNA sola puerta, y el menu lateral solo lleva trabajo</t>
+          <t>La postulacion publica escribe en creator_applications, que ya existia</t>
         </is>
       </c>
       <c r="E5" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21b</t>
         </is>
       </c>
       <c r="F5" s="69" t="inlineStr">
         <is>
-          <t>Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario en una pantalla que se veia igual que Campanas y con el menu marcando otra entrada. El menu queda en tres grupos --Operacion, Finanzas, Registros-- mas Ajustes: Configuracion, y un grupo del que no se puede ver nada desaparece entero.</t>
+          <t>Existe desde la Fase 2 con source por defecto «landing», su bandeja y su unica de una solicitud abierta por correo; faltaba la landing que escribiera. Un formulario publico que escribe lleva throttle:5,1 y un campo trampa que una persona no ve; si viene lleno se contesta «gracias» y no se escribe nada. Nada de CAPTCHA: barrera para quien lee con dificultad y tramite de segundos para quien automatiza. Vive en Creator y no en Core: T-74 aplicada antes de romperla.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34.5" customHeight="1" s="36">
       <c r="A6" s="67" t="inlineStr">
         <is>
-          <t>DEC-234</t>
+          <t>DEC-241</t>
         </is>
       </c>
       <c r="B6" s="68" t="inlineStr">
@@ -15206,24 +15256,24 @@
       <c r="C6" s="68" t="n"/>
       <c r="D6" s="69" t="inlineStr">
         <is>
-          <t>El orden de los grupos es una decision y vive en el registro, no en la plantilla</t>
+          <t>Sin portada se va al acceso, no a un 404</t>
         </is>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21b</t>
         </is>
       </c>
       <c r="F6" s="69" t="inlineStr">
         <is>
-          <t>revision() ordena por URGENCIA, que es lo correcto para una lista de avisos y lo peor para una navegacion: «Fiscal y facturacion» saldria arriba o abajo segun que falte hoy, y un sitio que cambia de forma segun el dia no se aprende. Por lo mismo, que rutas son configuracion sale de Preparacion::rutas() y no de la plantilla.</t>
+          <t>Una instalacion recien migrada no tiene contenido que ensenar, y eso no puede ser un error en la cara de un visitante: es exactamente lo que habia antes. Lo mismo al apagar una portada desde el admin, que es una decision de contenido y no una averia.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="36">
       <c r="A7" s="67" t="inlineStr">
         <is>
-          <t>DEC-235</t>
+          <t>DEC-236</t>
         </is>
       </c>
       <c r="B7" s="68" t="inlineStr">
@@ -15234,24 +15284,24 @@
       <c r="C7" s="68" t="n"/>
       <c r="D7" s="69" t="inlineStr">
         <is>
-          <t>Los catalogos son configuracion, con portada propia</t>
+          <t>Todo lo que exige sesion vive bajo /backoffice</t>
         </is>
       </c>
       <c r="E7" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21a</t>
         </is>
       </c>
       <c r="F7" s="69" t="inlineStr">
         <is>
-          <t>Los seis colgaban del menu bajo un titulo que no era un sitio: era una etiqueta. Ahora son un area con portada --cuantas filas y cuantas activas-- y su aviso: una lista sin ninguna fila activa sale en rojo, porque un catalogo vacio no da error, deja un desplegable vacio. La pantalla de cada catalogo no se mueve.</t>
+          <t>Lo vio el negocio antes de escribir una linea de la landing: /creadores tiene que ser la puerta PUBLICA de los creadores, y descubrirlo despues de publicar habria roto enlaces ya compartidos. Dentro entra todo lo que pide sesion sea de quien sea; lo que cada uno ve lo siguen decidiendo sus permisos. Costo una linea porque docs/08 prohibe escribir URLs a mano en las vistas: comprobado, cero resultados en app/, resources/ y config/.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34.5" customHeight="1" s="36">
       <c r="A8" s="67" t="inlineStr">
         <is>
-          <t>DEC-228</t>
+          <t>DEC-237</t>
         </is>
       </c>
       <c r="B8" s="68" t="inlineStr">
@@ -15262,24 +15312,24 @@
       <c r="C8" s="68" t="n"/>
       <c r="D8" s="69" t="inlineStr">
         <is>
-          <t>Los tipos de comprobante son un catalogo por pais, no un enum en el codigo</t>
+          <t>Veintiuna rutas se quedan fuera, y cada una con su motivo escrito</t>
         </is>
       </c>
       <c r="E8" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.21a</t>
         </is>
       </c>
       <c r="F8" s="69" t="inlineStr">
         <is>
-          <t>ck_ds_type decia IN ('invoice','boleta','credit_note','debit_note','other') desde la Fase 2: la boleta es peruana, el CFDI mexicano no estaba y anadir uno exigia desplegar. Cada tipo declara su codigo oficial de SUNAT, la forma de su serie, como se le pide a una persona y cuantos digitos tiene el correlativo. No contradice a DEC-026: el codigo SE RAMIFICA por proposito de integracion, mientras que el tipo de comprobante NO se ramifica, VIAJA al emisor electronico.</t>
+          <t>El acceso y la recuperacion son la puerta; la invitacion y la aprobacion llegan por enlace con token a alguien que no tiene cuenta; el logotipo y el favicon los pinta la pantalla de acceso. Dos comparten primer segmento con algo que si se mudo: /contrasena frente a /contrasena/nueva, y /marca frente a /marca/logo. La lista vive en una prueba que recorre todas las rutas con nombre.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1" s="36">
       <c r="A9" s="67" t="inlineStr">
         <is>
-          <t>DEC-229</t>
+          <t>DEC-233</t>
         </is>
       </c>
       <c r="B9" s="68" t="inlineStr">
@@ -15290,24 +15340,24 @@
       <c r="C9" s="68" t="n"/>
       <c r="D9" s="69" t="inlineStr">
         <is>
-          <t>El numero se reserva bajo bloqueo de la fila de la serie, no con MAX()+1</t>
+          <t>La configuracion tiene UNA sola puerta, y el menu lateral solo lleva trabajo</t>
         </is>
       </c>
       <c r="E9" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F9" s="69" t="inlineStr">
         <is>
-          <t>MAX()+1 es correcto exactamente hasta la primera vez que dos personas emiten a la vez, y eso no es raro: es un cierre de mes. El bloqueo pone en fila a la segunda peticion antes de que lea el contador. Y aun asi existe uq_dn_number: el bloqueo es la primera linea y la unica es la ultima. Medido con dos clientes de verdad (patron de 4.11), con su contraejemplo: sin FOR UPDATE, B no espera.</t>
+          <t>Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario en una pantalla que se veia igual que Campanas y con el menu marcando otra entrada. El menu queda en tres grupos --Operacion, Finanzas, Registros-- mas Ajustes: Configuracion, y un grupo del que no se puede ver nada desaparece entero.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="57" customHeight="1" s="36">
       <c r="A10" s="67" t="inlineStr">
         <is>
-          <t>DEC-230</t>
+          <t>DEC-234</t>
         </is>
       </c>
       <c r="B10" s="68" t="inlineStr">
@@ -15318,24 +15368,24 @@
       <c r="C10" s="68" t="n"/>
       <c r="D10" s="69" t="inlineStr">
         <is>
-          <t>Cada numero que sale queda escrito, y el hueco se explica en vez de taparse</t>
+          <t>El orden de los grupos es una decision y vive en el registro, no en la plantilla</t>
         </is>
       </c>
       <c r="E10" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F10" s="69" t="inlineStr">
         <is>
-          <t>Reservar y no emitir deja un numero sin documento, y eso NO se arregla reutilizandolo: reutilizarlo ES el duplicado. document_numbers guarda cada numero con su estado; reserved es el unico del que se sale, used dice a que documento fue y voided dice por que, con un motivo de al menos diez caracteres. Un hueco explicado es defendible ante un requerimiento; uno mudo, no.</t>
+          <t>revision() ordena por URGENCIA, que es lo correcto para una lista de avisos y lo peor para una navegacion: «Fiscal y facturacion» saldria arriba o abajo segun que falte hoy, y un sitio que cambia de forma segun el dia no se aprende. Por lo mismo, que rutas son configuracion sale de Preparacion::rutas() y no de la plantilla.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="68.25" customHeight="1" s="36">
       <c r="A11" s="67" t="inlineStr">
         <is>
-          <t>DEC-231</t>
+          <t>DEC-235</t>
         </is>
       </c>
       <c r="B11" s="68" t="inlineStr">
@@ -15346,24 +15396,24 @@
       <c r="C11" s="68" t="n"/>
       <c r="D11" s="69" t="inlineStr">
         <is>
-          <t>Una sola serie por defecto por (sociedad, tipo, entorno), y la forma la impone el pais</t>
+          <t>Los catalogos son configuracion, con portada propia</t>
         </is>
       </c>
       <c r="E11" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F11" s="69" t="inlineStr">
         <is>
-          <t>uq_ds_default es la columna puerta 32: con dos series por defecto, «emitir una factura» no tendria respuesta hasta que alguien eligiera. El empate se rechaza al CONFIGURAR y no al emitir. Y tg_ds_forma_ins/upd exige que la serie tenga la forma que declara su tipo y que el tipo sea del pais de la sociedad: una sociedad peruana no emite comprobantes colombianos.</t>
+          <t>Los seis colgaban del menu bajo un titulo que no era un sitio: era una etiqueta. Ahora son un area con portada --cuantas filas y cuantas activas-- y su aviso: una lista sin ninguna fila activa sale en rojo, porque un catalogo vacio no da error, deja un desplegable vacio. La pantalla de cada catalogo no se mueve.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="68.25" customHeight="1" s="36">
       <c r="A12" s="67" t="inlineStr">
         <is>
-          <t>DEC-232</t>
+          <t>DEC-228</t>
         </is>
       </c>
       <c r="B12" s="68" t="inlineStr">
@@ -15374,7 +15424,7 @@
       <c r="C12" s="68" t="n"/>
       <c r="D12" s="69" t="inlineStr">
         <is>
-          <t>Las series NO se siembran: unica configuracion sin valor de partida</t>
+          <t>Los tipos de comprobante son un catalogo por pais, no un enum en el codigo</t>
         </is>
       </c>
       <c r="E12" s="69" t="inlineStr">
@@ -15384,14 +15434,14 @@
       </c>
       <c r="F12" s="69" t="inlineStr">
         <is>
-          <t>Excepcion razonada a DEC-190: una serie se registra ante la administracion tributaria y una inventada produciria comprobantes invalidos ante SUNAT --un valor de fabrica aqui no es comodidad, es un error fiscal--. No bloquea nada, que es lo que DEC-190 exige de verdad: sale en rojo en el panel con las palabras que explican por que no hay ninguna. Lo que si se siembra son los TIPOS, que son la regla del pais.</t>
+          <t>ck_ds_type decia IN ('invoice','boleta','credit_note','debit_note','other') desde la Fase 2: la boleta es peruana, el CFDI mexicano no estaba y anadir uno exigia desplegar. Cada tipo declara su codigo oficial de SUNAT, la forma de su serie, como se le pide a una persona y cuantos digitos tiene el correlativo. No contradice a DEC-026: el codigo SE RAMIFICA por proposito de integracion, mientras que el tipo de comprobante NO se ramifica, VIAJA al emisor electronico.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="68.25" customHeight="1" s="36">
       <c r="A13" s="67" t="inlineStr">
         <is>
-          <t>DEC-223</t>
+          <t>DEC-229</t>
         </is>
       </c>
       <c r="B13" s="68" t="inlineStr">
@@ -15402,24 +15452,24 @@
       <c r="C13" s="68" t="n"/>
       <c r="D13" s="69" t="inlineStr">
         <is>
-          <t>Las credenciales de las APIs viven en tres tablas propias, no en .env ni en legal_entities</t>
+          <t>El numero se reserva bajo bloqueo de la fila de la serie, no con MAX()+1</t>
         </is>
       </c>
       <c r="E13" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F13" s="69" t="inlineStr">
         <is>
-          <t>DEC-033 y docs/12 ya lo habian decidido y aqui se construye. Una sociedad es QUIEN factura; una conexion es CON QUE se conecta uno a un proveedor, y cambia mucho mas a menudo que una razon social. En .env seria peor: cambiar de entorno de pruebas a produccion exigiria entrar por SSH, que es DEC-190 roto por la puerta de atras.</t>
+          <t>MAX()+1 es correcto exactamente hasta la primera vez que dos personas emiten a la vez, y eso no es raro: es un cierre de mes. El bloqueo pone en fila a la segunda peticion antes de que lea el contador. Y aun asi existe uq_dn_number: el bloqueo es la primera linea y la unica es la ultima. Medido con dos clientes de verdad (patron de 4.11), con su contraejemplo: sin FOR UPDATE, B no espera.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45.75" customHeight="1" s="36">
       <c r="A14" s="67" t="inlineStr">
         <is>
-          <t>DEC-224</t>
+          <t>DEC-230</t>
         </is>
       </c>
       <c r="B14" s="68" t="inlineStr">
@@ -15430,24 +15480,24 @@
       <c r="C14" s="68" t="n"/>
       <c r="D14" s="69" t="inlineStr">
         <is>
-          <t>Tres tablas de las cinco de docs/12: las asignaciones no se construyen todavia</t>
+          <t>Cada numero que sale queda escrito, y el hueco se explica en vez de taparse</t>
         </is>
       </c>
       <c r="E14" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F14" s="69" t="inlineStr">
         <is>
-          <t>El eje (marca, sociedad, pais) con vigencia resuelve un problema que hoy no existe: una conexion sirve a una sociedad o a la plataforma entera, y eso cabe en un legal_entity_id nullable donde NULL significa «de la plataforma». Construir la tabla de tres ejes antes de tener el segundo caso es construir contra un supuesto. Queda escrito en la cabecera de la migracion para que no se tome por un olvido.</t>
+          <t>Reservar y no emitir deja un numero sin documento, y eso NO se arregla reutilizandolo: reutilizarlo ES el duplicado. document_numbers guarda cada numero con su estado; reserved es el unico del que se sale, used dice a que documento fue y voided dice por que, con un motivo de al menos diez caracteres. Un hueco explicado es defendible ante un requerimiento; uno mudo, no.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1" s="36">
       <c r="A15" s="67" t="inlineStr">
         <is>
-          <t>DEC-225</t>
+          <t>DEC-231</t>
         </is>
       </c>
       <c r="B15" s="68" t="inlineStr">
@@ -15458,24 +15508,24 @@
       <c r="C15" s="68" t="n"/>
       <c r="D15" s="69" t="inlineStr">
         <is>
-          <t>Rotar una credencial crea la version siguiente y cierra la anterior; no la pisa</t>
+          <t>Una sola serie por defecto por (sociedad, tipo, entorno), y la forma la impone el pais</t>
         </is>
       </c>
       <c r="E15" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F15" s="69" t="inlineStr">
         <is>
-          <t>Se guardan el cifrado y los cuatro ultimos caracteres, nada mas. Pisar el valor deja sin respuesta «cual era la de antes» y «cuando cambio». Las dos escrituras van en la misma transaccion y en ese orden, porque uq_icred_vigente solo admite una viva por (conexion, clase). tg_icred_inmutable impide reescribir una credencial: lo unico que cambia en una fila existente es revocarla.</t>
+          <t>uq_ds_default es la columna puerta 32: con dos series por defecto, «emitir una factura» no tendria respuesta hasta que alguien eligiera. El empate se rechaza al CONFIGURAR y no al emitir. Y tg_ds_forma_ins/upd exige que la serie tenga la forma que declara su tipo y que el tipo sea del pais de la sociedad: una sociedad peruana no emite comprobantes colombianos.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="57" customHeight="1" s="36">
       <c r="A16" s="67" t="inlineStr">
         <is>
-          <t>DEC-226</t>
+          <t>DEC-232</t>
         </is>
       </c>
       <c r="B16" s="68" t="inlineStr">
@@ -15486,24 +15536,24 @@
       <c r="C16" s="68" t="n"/>
       <c r="D16" s="69" t="inlineStr">
         <is>
-          <t>La bitacora anota QUE cambio, no que valor</t>
+          <t>Las series NO se siembran: unica configuracion sin valor de partida</t>
         </is>
       </c>
       <c r="E16" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F16" s="69" t="inlineStr">
         <is>
-          <t>Ni el secreto ni los cuatro ultimos entran en audit_log (BR-SEC-001). Un registro de auditoria que guarda el secreto es un segundo sitio donde esta el secreto, y ademas uno que por diseno no se puede borrar. Por eso el servicio parte la lectura en dos: estado() es lo que ve una persona y secreto() lo llama el cliente de la API.</t>
+          <t>Excepcion razonada a DEC-190: una serie se registra ante la administracion tributaria y una inventada produciria comprobantes invalidos ante SUNAT --un valor de fabrica aqui no es comodidad, es un error fiscal--. No bloquea nada, que es lo que DEC-190 exige de verdad: sale en rojo en el panel con las palabras que explican por que no hay ninguna. Lo que si se siembra son los TIPOS, que son la regla del pais.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="57" customHeight="1" s="36">
       <c r="A17" s="67" t="inlineStr">
         <is>
-          <t>DEC-227</t>
+          <t>DEC-223</t>
         </is>
       </c>
       <c r="B17" s="68" t="inlineStr">
@@ -15514,7 +15564,7 @@
       <c r="C17" s="68" t="n"/>
       <c r="D17" s="69" t="inlineStr">
         <is>
-          <t>Una conexion ACTIVA exige https; un borrador no</t>
+          <t>Las credenciales de las APIs viven en tres tablas propias, no en .env ni en legal_entities</t>
         </is>
       </c>
       <c r="E17" s="69" t="inlineStr">
@@ -15524,14 +15574,14 @@
       </c>
       <c r="F17" s="69" t="inlineStr">
         <is>
-          <t>ck_iconn_url es la unica regla de la iteracion que no es de forma sino de fondo: una URL http a un servicio de facturacion manda las claves secundarias por la red en claro. Se puede escribir mientras la conexion es un borrador y no se puede activar. La regla vive en la base y no en el formulario, porque el formulario no es el unico que escribe.</t>
+          <t>DEC-033 y docs/12 ya lo habian decidido y aqui se construye. Una sociedad es QUIEN factura; una conexion es CON QUE se conecta uno a un proveedor, y cambia mucho mas a menudo que una razon social. En .env seria peor: cambiar de entorno de pruebas a produccion exigiria entrar por SSH, que es DEC-190 roto por la puerta de atras.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="68.25" customHeight="1" s="36">
       <c r="A18" s="67" t="inlineStr">
         <is>
-          <t>DEC-220</t>
+          <t>DEC-224</t>
         </is>
       </c>
       <c r="B18" s="68" t="inlineStr">
@@ -15542,24 +15592,24 @@
       <c r="C18" s="68" t="n"/>
       <c r="D18" s="69" t="inlineStr">
         <is>
-          <t>Core levanta un evento; Creator escucha</t>
+          <t>Tres tablas de las cinco de docs/12: las asignaciones no se construyen todavia</t>
         </is>
       </c>
       <c r="E18" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F18" s="69" t="inlineStr">
         <is>
-          <t>Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
+          <t>El eje (marca, sociedad, pais) con vigencia resuelve un problema que hoy no existe: una conexion sirve a una sociedad o a la plataforma entera, y eso cabe en un legal_entity_id nullable donde NULL significa «de la plataforma». Construir la tabla de tres ejes antes de tener el segundo caso es construir contra un supuesto. Queda escrito en la cabecera de la migracion para que no se tome por un olvido.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45.75" customHeight="1" s="36">
       <c r="A19" s="67" t="inlineStr">
         <is>
-          <t>DEC-221</t>
+          <t>DEC-225</t>
         </is>
       </c>
       <c r="B19" s="68" t="inlineStr">
@@ -15570,24 +15620,24 @@
       <c r="C19" s="68" t="n"/>
       <c r="D19" s="69" t="inlineStr">
         <is>
-          <t>El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
+          <t>Rotar una credencial crea la version siguiente y cierra la anterior; no la pisa</t>
         </is>
       </c>
       <c r="E19" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F19" s="69" t="inlineStr">
         <is>
-          <t>Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
+          <t>Se guardan el cifrado y los cuatro ultimos caracteres, nada mas. Pisar el valor deja sin respuesta «cual era la de antes» y «cuando cambio». Las dos escrituras van en la misma transaccion y en ese orden, porque uq_icred_vigente solo admite una viva por (conexion, clase). tg_icred_inmutable impide reescribir una credencial: lo unico que cambia en una fila existente es revocarla.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="57" customHeight="1" s="36">
       <c r="A20" s="67" t="inlineStr">
         <is>
-          <t>DEC-222</t>
+          <t>DEC-226</t>
         </is>
       </c>
       <c r="B20" s="68" t="inlineStr">
@@ -15598,24 +15648,24 @@
       <c r="C20" s="68" t="n"/>
       <c r="D20" s="69" t="inlineStr">
         <is>
-          <t>Un correo que falla no deja sin avisar a los demas</t>
+          <t>La bitacora anota QUE cambio, no que valor</t>
         </is>
       </c>
       <c r="E20" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F20" s="69" t="inlineStr">
         <is>
-          <t>Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
+          <t>Ni el secreto ni los cuatro ultimos entran en audit_log (BR-SEC-001). Un registro de auditoria que guarda el secreto es un segundo sitio donde esta el secreto, y ademas uno que por diseno no se puede borrar. Por eso el servicio parte la lectura en dos: estado() es lo que ve una persona y secreto() lo llama el cliente de la API.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34.5" customHeight="1" s="36">
       <c r="A21" s="67" t="inlineStr">
         <is>
-          <t>DEC-216</t>
+          <t>DEC-227</t>
         </is>
       </c>
       <c r="B21" s="68" t="inlineStr">
@@ -15626,24 +15676,24 @@
       <c r="C21" s="68" t="n"/>
       <c r="D21" s="69" t="inlineStr">
         <is>
-          <t>Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
+          <t>Una conexion ACTIVA exige https; un borrador no</t>
         </is>
       </c>
       <c r="E21" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F21" s="69" t="inlineStr">
         <is>
-          <t>El plazo es parte de lo que se le comunico a la gente: «tienes 15 dias» dicho en enero no puede convertirse en «tenias 10» porque en marzo alguien cambio un ajuste global. Cada version lleva los suyos, se eligen al publicarla y despues son inmutables. Lo configurable es el valor por defecto, que es lo que el formulario trae puesto. readonly_days = 0 significa «sin periodo de solo lectura»; un numero muy grande, lo contrario.</t>
+          <t>ck_iconn_url es la unica regla de la iteracion que no es de forma sino de fondo: una URL http a un servicio de facturacion manda las claves secundarias por la red en claro. Se puede escribir mientras la conexion es un borrador y no se puede activar. La regla vive en la base y no en el formulario, porque el formulario no es el unico que escribe.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="68.25" customHeight="1" s="36">
       <c r="A22" s="67" t="inlineStr">
         <is>
-          <t>DEC-217</t>
+          <t>DEC-220</t>
         </is>
       </c>
       <c r="B22" s="68" t="inlineStr">
@@ -15654,24 +15704,24 @@
       <c r="C22" s="68" t="n"/>
       <c r="D22" s="69" t="inlineStr">
         <is>
-          <t>El reloj no empieza al publicar: empieza cuando le toca a el</t>
+          <t>Core levanta un evento; Creator escucha</t>
         </is>
       </c>
       <c r="E22" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F22" s="69" t="inlineStr">
         <is>
-          <t>Un creador activado ayer no puede aparecer bloqueado por una version de hace tres meses. Su plazo cuenta desde el dia en que se activo, o desde la fecha de la version si es posterior. Sin esto, el primer creador que se diera de alta despues de un cambio de fondo entraria directamente al muro sin haber tenido un solo dia.</t>
+          <t>Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="57" customHeight="1" s="36">
       <c r="A23" s="67" t="inlineStr">
         <is>
-          <t>DEC-218</t>
+          <t>DEC-221</t>
         </is>
       </c>
       <c r="B23" s="68" t="inlineStr">
@@ -15682,24 +15732,24 @@
       <c r="C23" s="68" t="n"/>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>La pantalla del muro no lleva permiso, y eso es la decision</t>
+          <t>El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
         </is>
       </c>
       <c r="E23" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F23" s="69" t="inlineStr">
         <is>
-          <t>/mis-terminos es la unica salida de un creador bloqueado: un permiso dejaria sin salida justo a quien la necesita. La autorizacion es tener ficha de creador atada a la sesion. El trinquete de rutas exentas subio de 4 a 6 a mano y con motivo escrito, que es todo el sentido de ese trinquete. Lleva throttle:10,1.</t>
+          <t>Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34.5" customHeight="1" s="36">
       <c r="A24" s="67" t="inlineStr">
         <is>
-          <t>DEC-219</t>
+          <t>DEC-222</t>
         </is>
       </c>
       <c r="B24" s="68" t="inlineStr">
@@ -15710,24 +15760,24 @@
       <c r="C24" s="68" t="n"/>
       <c r="D24" s="69" t="inlineStr">
         <is>
-          <t>Una franja fija, no un popup</t>
+          <t>Un correo que falla no deja sin avisar a los demas</t>
         </is>
       </c>
       <c r="E24" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F24" s="69" t="inlineStr">
         <is>
-          <t>El negocio pidio «popup como recordatorio al loguearse». Un popup se cierra sin leerlo y no vuelve hasta la siguiente sesion; la franja sigue ahi mientras siga sin aceptarse. El equipo interno no la ve nunca.</t>
+          <t>Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45.75" customHeight="1" s="36">
       <c r="A25" s="67" t="inlineStr">
         <is>
-          <t>DEC-212</t>
+          <t>DEC-216</t>
         </is>
       </c>
       <c r="B25" s="68" t="inlineStr">
@@ -15738,24 +15788,24 @@
       <c r="C25" s="68" t="n"/>
       <c r="D25" s="69" t="inlineStr">
         <is>
-          <t>Una politica de precios con vigencia, no dos constantes</t>
+          <t>Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
         </is>
       </c>
       <c r="E25" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F25" s="69" t="inlineStr">
         <is>
-          <t>pricing_policies guarda la retencion (Q-13), el umbral de rentabilidad y sobre que se calcula. Los tres cambian: el 29,5 % por decreto y el 20 % con datos reales. Tiene historia --una sola vigente-- y una cerrada no se reescribe ni se borra: es la que explica como se pacto un compromiso de hace tres meses.</t>
+          <t>El plazo es parte de lo que se le comunico a la gente: «tienes 15 dias» dicho en enero no puede convertirse en «tenias 10» porque en marzo alguien cambio un ajuste global. Cada version lleva los suyos, se eligen al publicarla y despues son inmutables. Lo configurable es el valor por defecto, que es lo que el formulario trae puesto. readonly_days = 0 significa «sin periodo de solo lectura»; un numero muy grande, lo contrario.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="57" customHeight="1" s="36">
       <c r="A26" s="67" t="inlineStr">
         <is>
-          <t>DEC-213</t>
+          <t>DEC-217</t>
         </is>
       </c>
       <c r="B26" s="68" t="inlineStr">
@@ -15766,24 +15816,24 @@
       <c r="C26" s="68" t="n"/>
       <c r="D26" s="69" t="inlineStr">
         <is>
-          <t>margin_basis es configuracion, no una pregunta</t>
+          <t>El reloj no empieza al publicar: empieza cuando le toca a el</t>
         </is>
       </c>
       <c r="E26" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F26" s="69" t="inlineStr">
         <is>
-          <t>Con 100 de neto y 29,5 % el costo es 141,84; el ejemplo del negocio dio 170,21, que es 141,84 x 1,20 (recargo sobre el COSTO). Un 20 % de margen sobre el INGRESO habria dado 177,31. Lo iba a preguntar dos veces; DEC-190 dice que estas cosas se configuran, y preguntarlo habria sido quemar la respuesta en el codigo con la firma del negocio encima. Es una columna con dos valores, sembrada en cost, con la pantalla ensenando las dos cifras y una prueba de cada una.</t>
+          <t>Un creador activado ayer no puede aparecer bloqueado por una version de hace tres meses. Su plazo cuenta desde el dia en que se activo, o desde la fecha de la version si es posterior. Sin esto, el primer creador que se diera de alta despues de un cambio de fondo entraria directamente al muro sin haber tenido un solo dia.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="68.25" customHeight="1" s="36">
       <c r="A27" s="67" t="inlineStr">
         <is>
-          <t>DEC-214</t>
+          <t>DEC-218</t>
         </is>
       </c>
       <c r="B27" s="68" t="inlineStr">
@@ -15794,24 +15844,24 @@
       <c r="C27" s="68" t="n"/>
       <c r="D27" s="69" t="inlineStr">
         <is>
-          <t>Se pacta el costo o el neto, y el ingreso minimo se dice, no se impone</t>
+          <t>La pantalla del muro no lleva permiso, y eso es la decision</t>
         </is>
       </c>
       <c r="E27" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F27" s="69" t="inlineStr">
         <is>
-          <t>agreed_amount sigue siendo el costo: de esa columna cuelgan devengos, pagos y la rentabilidad de 9.10. Se anaden la base, el neto y la tasa. Con net se teclean 100 y se escriben 141,8440, y el motor rehace la resta: un neto que no cuadra con su bruto se descubriria en la conversacion con el creador que cobro de menos. El mensaje dice el ingreso minimo y no bloquea: se puede aceptar menos margen, pero sabiendolo y antes de invitar. Los tres numeros se congelan en la participacion.</t>
+          <t>/mis-terminos es la unica salida de un creador bloqueado: un permiso dejaria sin salida justo a quien la necesita. La autorizacion es tener ficha de creador atada a la sesion. El trinquete de rutas exentas subio de 4 a 6 a mano y con motivo escrito, que es todo el sentido de ese trinquete. Lleva throttle:10,1.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="57" customHeight="1" s="36">
       <c r="A28" s="67" t="inlineStr">
         <is>
-          <t>DEC-215</t>
+          <t>DEC-219</t>
         </is>
       </c>
       <c r="B28" s="68" t="inlineStr">
@@ -15822,24 +15872,24 @@
       <c r="C28" s="68" t="n"/>
       <c r="D28" s="69" t="inlineStr">
         <is>
-          <t>La cuenta la hace el motor, no PHP</t>
+          <t>Una franja fija, no un popup</t>
         </is>
       </c>
       <c r="E28" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F28" s="69" t="inlineStr">
         <is>
-          <t>neto / (1 - tasa/100) con float da 141.84397163120568 y de ahi a un DECIMAL(18,4) hay un redondeo que puede caer del lado que el CHECK no admite. El contenedor no tiene bcmath, asi que la aritmetica exacta se hace en el motor con CAST a DECIMAL(28,12). Misma tecnica que 9.1 y 9.3.</t>
+          <t>El negocio pidio «popup como recordatorio al loguearse». Un popup se cierra sin leerlo y no vuelve hasta la siguiente sesion; la franja sigue ahi mientras siga sin aceptarse. El equipo interno no la ve nunca.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="68.25" customHeight="1" s="36">
       <c r="A29" s="67" t="inlineStr">
         <is>
-          <t>DEC-209</t>
+          <t>DEC-212</t>
         </is>
       </c>
       <c r="B29" s="68" t="inlineStr">
@@ -15850,24 +15900,24 @@
       <c r="C29" s="68" t="n"/>
       <c r="D29" s="69" t="inlineStr">
         <is>
-          <t>La forma del codigo de localidad la declara el pais, no el codigo</t>
+          <t>Una politica de precios con vigencia, no dos constantes</t>
         </is>
       </c>
       <c r="E29" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F29" s="69" t="inlineStr">
         <is>
-          <t>El comprobante peruano lleva el ubigeo del INEI (seis digitos) y el colombiano el codigo DANE (cinco). Una columna ubigeo CHAR(6) habria sido la regla de un pais escrita en el codigo de los seis y rechazaria un codigo colombiano correcto. countries declara como se llama, que forma tiene y si ese pais lo exige; el formulario pide «Ubigeo» a una peruana y «Codigo DANE» a una colombiana sin una linea de codigo por pais. La imponen dos disparadores cruzados que leen el patron de countries.</t>
+          <t>pricing_policies guarda la retencion (Q-13), el umbral de rentabilidad y sobre que se calcula. Los tres cambian: el 29,5 % por decreto y el 20 % con datos reales. Tiene historia --una sola vigente-- y una cerrada no se reescribe ni se borra: es la que explica como se pacto un compromiso de hace tres meses.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45.75" customHeight="1" s="36">
       <c r="A30" s="67" t="inlineStr">
         <is>
-          <t>DEC-210</t>
+          <t>DEC-213</t>
         </is>
       </c>
       <c r="B30" s="68" t="inlineStr">
@@ -15878,24 +15928,24 @@
       <c r="C30" s="68" t="n"/>
       <c r="D30" s="69" t="inlineStr">
         <is>
-          <t>El codigo de establecimiento nace en «0000» y no admite nulo</t>
+          <t>margin_basis es configuracion, no una pregunta</t>
         </is>
       </c>
       <c r="E30" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F30" s="69" t="inlineStr">
         <is>
-          <t>Un comprobante SIEMPRE lleva uno; dejarlo nulo obligaria a decidirlo al emitir, que es tarde. «0000» es el domicilio fiscal en SUNAT. El formulario lo puede dejar en blanco --al crear y al editar-- y entonces vale 0000: sin esa normalizacion, vaciar el campo metia una cadena vacia que ck_le_establecimiento rechaza con un 45000 sin explicar nada.</t>
+          <t>Con 100 de neto y 29,5 % el costo es 141,84; el ejemplo del negocio dio 170,21, que es 141,84 x 1,20 (recargo sobre el COSTO). Un 20 % de margen sobre el INGRESO habria dado 177,31. Lo iba a preguntar dos veces; DEC-190 dice que estas cosas se configuran, y preguntarlo habria sido quemar la respuesta en el codigo con la firma del negocio encima. Es una columna con dos valores, sembrada en cost, con la pantalla ensenando las dos cifras y una prueba de cada una.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="79.5" customHeight="1" s="36">
       <c r="A31" s="67" t="inlineStr">
         <is>
-          <t>DEC-211</t>
+          <t>DEC-214</t>
         </is>
       </c>
       <c r="B31" s="68" t="inlineStr">
@@ -15906,24 +15956,24 @@
       <c r="C31" s="68" t="n"/>
       <c r="D31" s="69" t="inlineStr">
         <is>
-          <t>Que falte el ubigeo no bloquea: es un aviso rojo</t>
+          <t>Se pacta el costo o el neto, y el ingreso minimo se dice, no se impone</t>
         </is>
       </c>
       <c r="E31" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F31" s="69" t="inlineStr">
         <is>
-          <t>requires_tax_location no impide guardar una sociedad a medias; hace que el panel de 9.17b lo enseñe en rojo con el nombre que ese pais le da. Y sale a la luz algo que no decia nadie: el sembrador escribe address_line1 = «Por completar» porque la columna es NOT NULL, la sociedad parecia completa, y ese texto habria salido impreso en un comprobante.</t>
+          <t>agreed_amount sigue siendo el costo: de esa columna cuelgan devengos, pagos y la rentabilidad de 9.10. Se anaden la base, el neto y la tasa. Con net se teclean 100 y se escriben 141,8440, y el motor rehace la resta: un neto que no cuadra con su bruto se descubriria en la conversacion con el creador que cobro de menos. El mensaje dice el ingreso minimo y no bloquea: se puede aceptar menos margen, pero sabiendolo y antes de invitar. Los tres numeros se congelan en la participacion.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="68.25" customHeight="1" s="36">
       <c r="A32" s="67" t="inlineStr">
         <is>
-          <t>DEC-205</t>
+          <t>DEC-215</t>
         </is>
       </c>
       <c r="B32" s="68" t="inlineStr">
@@ -15934,24 +15984,24 @@
       <c r="C32" s="68" t="n"/>
       <c r="D32" s="69" t="inlineStr">
         <is>
-          <t>Un registro de preparacion, y cada modulo declara lo suyo</t>
+          <t>La cuenta la hace el motor, no PHP</t>
         </is>
       </c>
       <c r="E32" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F32" s="69" t="inlineStr">
         <is>
-          <t>9.16 y 9.17 dejaron cada una su lista de avisos y cada una solo se ve entrando en su pantalla. Preparacion las junta, y cada modulo declara las comprobaciones de su area en su ServiceProvider: un revisor central pondria a Shared a saber de cinco modulos sin que deptrac lo vea, porque son consultas a tablas y no clases importadas. Hay una prueba que se rompe cuando alguien construye una pantalla de configuracion nueva y no la enchufa.</t>
+          <t>neto / (1 - tasa/100) con float da 141.84397163120568 y de ahi a un DECIMAL(18,4) hay un redondeo que puede caer del lado que el CHECK no admite. El contenedor no tiene bcmath, asi que la aritmetica exacta se hace en el motor con CAST a DECIMAL(28,12). Misma tecnica que 9.1 y 9.3.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45.75" customHeight="1" s="36">
       <c r="A33" s="67" t="inlineStr">
         <is>
-          <t>DEC-206</t>
+          <t>DEC-209</t>
         </is>
       </c>
       <c r="B33" s="68" t="inlineStr">
@@ -15962,24 +16012,24 @@
       <c r="C33" s="68" t="n"/>
       <c r="D33" s="69" t="inlineStr">
         <is>
-          <t>Si no puedes arreglarlo, no lo ves</t>
+          <t>La forma del codigo de localidad la declara el pais, no el codigo</t>
         </is>
       </c>
       <c r="E33" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F33" s="69" t="inlineStr">
         <is>
-          <t>Cada area declara el permiso con el que SE ARREGLA, no el que hace falta para abrir el panel, y la revision filtra por el. BR-SEC-001 sigue en pie aunque la pantalla reuna en un sitio lo que estaba repartido en cinco, y ningun aviso lleva a un 403. Por eso config.view se le puede dar a finanzas sin miedo: ve el area de tipos de cambio y nada mas.</t>
+          <t>El comprobante peruano lleva el ubigeo del INEI (seis digitos) y el colombiano el codigo DANE (cinco). Una columna ubigeo CHAR(6) habria sido la regla de un pais escrita en el codigo de los seis y rechazaria un codigo colombiano correcto. countries declara como se llama, que forma tiene y si ese pais lo exige; el formulario pide «Ubigeo» a una peruana y «Codigo DANE» a una colombiana sin una linea de codigo por pais. La imponen dos disparadores cruzados que leen el patron de countries.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45.75" customHeight="1" s="36">
       <c r="A34" s="67" t="inlineStr">
         <is>
-          <t>DEC-207</t>
+          <t>DEC-210</t>
         </is>
       </c>
       <c r="B34" s="68" t="inlineStr">
@@ -15990,24 +16040,24 @@
       <c r="C34" s="68" t="n"/>
       <c r="D34" s="69" t="inlineStr">
         <is>
-          <t>Una comprobacion que revienta no tumba el panel</t>
+          <t>El codigo de establecimiento nace en «0000» y no admite nulo</t>
         </is>
       </c>
       <c r="E34" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F34" s="69" t="inlineStr">
         <is>
-          <t>Un revisor que lanza una excepcion se convierte en un aviso ambar que lo dice, y las demas areas se siguen viendo. Un panel de «que me falta» que responde 500 porque a un area le pasa algo deja de contestar justo el dia en que hay algo que contestar.</t>
+          <t>Un comprobante SIEMPRE lleva uno; dejarlo nulo obligaria a decidirlo al emitir, que es tarde. «0000» es el domicilio fiscal en SUNAT. El formulario lo puede dejar en blanco --al crear y al editar-- y entonces vale 0000: sin esa normalizacion, vaciar el campo metia una cadena vacia que ck_le_establecimiento rechaza con un 45000 sin explicar nada.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="68.25" customHeight="1" s="36">
       <c r="A35" s="67" t="inlineStr">
         <is>
-          <t>DEC-208</t>
+          <t>DEC-211</t>
         </is>
       </c>
       <c r="B35" s="68" t="inlineStr">
@@ -16018,24 +16068,24 @@
       <c r="C35" s="68" t="n"/>
       <c r="D35" s="69" t="inlineStr">
         <is>
-          <t>El correo en log es ROJO, y va el primero del panel</t>
+          <t>Que falte el ubigeo no bloquea: es un aviso rojo</t>
         </is>
       </c>
       <c r="E35" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F35" s="69" t="inlineStr">
         <is>
-          <t>mail.default vale log mientras nadie ponga una cuenta SMTP (Q-20), y con ese valor el correo no sale de la maquina: se escribe en storage/logs. La aplicacion no falla, la bitacora dice enviado y el creador no recibe su enlace de alta. Es el modo de fallo mas caro del sistema porque no se nota desde dentro, y hasta hoy no lo decia ninguna pantalla.</t>
+          <t>requires_tax_location no impide guardar una sociedad a medias; hace que el panel de 9.17b lo enseñe en rojo con el nombre que ese pais le da. Y sale a la luz algo que no decia nadie: el sembrador escribe address_line1 = «Por completar» porque la columna es NOT NULL, la sociedad parecia completa, y ese texto habria salido impreso en un comprobante.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="57" customHeight="1" s="36">
       <c r="A36" s="67" t="inlineStr">
         <is>
-          <t>DEC-199</t>
+          <t>DEC-205</t>
         </is>
       </c>
       <c r="B36" s="68" t="inlineStr">
@@ -16046,24 +16096,24 @@
       <c r="C36" s="68" t="n"/>
       <c r="D36" s="69" t="inlineStr">
         <is>
-          <t>La marca es una fila, y hay UNA sola por defecto</t>
+          <t>Un registro de preparacion, y cada modulo declara lo suyo</t>
         </is>
       </c>
       <c r="E36" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F36" s="69" t="inlineStr">
         <is>
-          <t>«LATAM Social» estaba escrito en tres plantillas --title, barra lateral y pantalla de acceso--, el favicon era un archivo del repositorio y el pie legal con la razon social y el RUC estaba a mano al pie del formulario de entrada. platform_brands guardaba todo eso desde 2.10 y nadie la leyo nunca. default_gate es la 28.a columna puerta y uq_pb_default la hace unica: dos marcas por defecto es media aplicacion ensenando un nombre y la otra mitad otro sin que nada falle.</t>
+          <t>9.16 y 9.17 dejaron cada una su lista de avisos y cada una solo se ve entrando en su pantalla. Preparacion las junta, y cada modulo declara las comprobaciones de su area en su ServiceProvider: un revisor central pondria a Shared a saber de cinco modulos sin que deptrac lo vea, porque son consultas a tablas y no clases importadas. Hay una prueba que se rompe cuando alguien construye una pantalla de configuracion nueva y no la enchufa.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="68.25" customHeight="1" s="36">
       <c r="A37" s="67" t="inlineStr">
         <is>
-          <t>DEC-200</t>
+          <t>DEC-206</t>
         </is>
       </c>
       <c r="B37" s="68" t="inlineStr">
@@ -16074,24 +16124,24 @@
       <c r="C37" s="68" t="n"/>
       <c r="D37" s="69" t="inlineStr">
         <is>
-          <t>Una configuracion que falta NO bloquea: valor de partida y aviso con prioridad</t>
+          <t>Si no puedes arreglarlo, no lo ves</t>
         </is>
       </c>
       <c r="E37" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F37" s="69" t="inlineStr">
         <is>
-          <t>DEC-190 llevado al codigo. Sin tabla, sin fila o con un campo vacio se cae al valor de partida y aparece un badge: rojo lo que un tercero va a ver mal (sin logotipo, sin correo de soporte), ambar lo que conviene (sin favicon, sin pie legal, sin web), verde cuando no falta nada. El sistema arranca con dos rojos y funciona perfectamente con los dos puestos.</t>
+          <t>Cada area declara el permiso con el que SE ARREGLA, no el que hace falta para abrir el panel, y la revision filtra por el. BR-SEC-001 sigue en pie aunque la pantalla reuna en un sitio lo que estaba repartido en cinco, y ningun aviso lleva a un 403. Por eso config.view se le puede dar a finanzas sin miedo: ve el area de tipos de cambio y nada mas.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="45.75" customHeight="1" s="36">
       <c r="A38" s="67" t="inlineStr">
         <is>
-          <t>DEC-201</t>
+          <t>DEC-207</t>
         </is>
       </c>
       <c r="B38" s="68" t="inlineStr">
@@ -16102,24 +16152,24 @@
       <c r="C38" s="68" t="n"/>
       <c r="D38" s="69" t="inlineStr">
         <is>
-          <t>El logotipo se sirve por una puerta publica propia, sin identificador</t>
+          <t>Una comprobacion que revienta no tumba el panel</t>
         </is>
       </c>
       <c r="E38" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>La pantalla de acceso la ve quien no ha entrado, asi que el permiso file.view de 9.15 dejaria la marca fuera de la unica pantalla que ve todo el mundo. Lo que hace seguras a /marca/logo y /marca/favicon no es un permiso: es que NO aceptan identificador. Estan en RUTAS-ABIERTAS con su motivo y MuroTest las conoce.</t>
+          <t>Un revisor que lanza una excepcion se convierte en un aviso ambar que lo dice, y las demas areas se siguen viendo. Un panel de «que me falta» que responde 500 porque a un area le pasa algo deja de contestar justo el dia en que hay algo que contestar.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="90.75" customHeight="1" s="36">
       <c r="A39" s="67" t="inlineStr">
         <is>
-          <t>DEC-202</t>
+          <t>DEC-208</t>
         </is>
       </c>
       <c r="B39" s="68" t="inlineStr">
@@ -16130,24 +16180,24 @@
       <c r="C39" s="68" t="n"/>
       <c r="D39" s="69" t="inlineStr">
         <is>
-          <t>El codigo de la marca no se cambia; el nombre visible si</t>
+          <t>El correo en log es ROJO, y va el primero del panel</t>
         </is>
       </c>
       <c r="E39" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>tg_pb_code lo impide en el motor. El code es la llave con la que el sembrador encuentra la marca: si cambia, el siguiente db:seed crea otra, el sistema amanece con dos y las pantallas siguen ensenando la vieja mientras alguien edita la nueva.</t>
+          <t>mail.default vale log mientras nadie ponga una cuenta SMTP (Q-20), y con ese valor el correo no sale de la maquina: se escribe en storage/logs. La aplicacion no falla, la bitacora dice enviado y el creador no recibe su enlace de alta. Es el modo de fallo mas caro del sistema porque no se nota desde dentro, y hasta hoy no lo decia ninguna pantalla.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="45.75" customHeight="1" s="36">
       <c r="A40" s="67" t="inlineStr">
         <is>
-          <t>DEC-203</t>
+          <t>DEC-199</t>
         </is>
       </c>
       <c r="B40" s="68" t="inlineStr">
@@ -16158,7 +16208,7 @@
       <c r="C40" s="68" t="n"/>
       <c r="D40" s="69" t="inlineStr">
         <is>
-          <t>Los colores y la tipografia se desinfectan ademas del CHECK</t>
+          <t>La marca es una fila, y hay UNA sola por defecto</t>
         </is>
       </c>
       <c r="E40" s="69" t="inlineStr">
@@ -16168,14 +16218,14 @@
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>El color acaba dentro de una regla CSS y la tipografia dentro de una URL y de una regla CSS, en todas las pantallas a la vez. Un nombre con comillas y llaves cierra la regla y escribe estilo ajeno en toda la aplicacion. Si el valor entra por una via que no pasa por el CHECK --carga masiva, restauracion de copia--, la segunda cerradura es lo unico que queda.</t>
+          <t>«LATAM Social» estaba escrito en tres plantillas --title, barra lateral y pantalla de acceso--, el favicon era un archivo del repositorio y el pie legal con la razon social y el RUC estaba a mano al pie del formulario de entrada. platform_brands guardaba todo eso desde 2.10 y nadie la leyo nunca. default_gate es la 28.a columna puerta y uq_pb_default la hace unica: dos marcas por defecto es media aplicacion ensenando un nombre y la otra mitad otro sin que nada falle.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="57" customHeight="1" s="36">
       <c r="A41" s="67" t="inlineStr">
         <is>
-          <t>DEC-204</t>
+          <t>DEC-200</t>
         </is>
       </c>
       <c r="B41" s="68" t="inlineStr">
@@ -16186,7 +16236,7 @@
       <c r="C41" s="68" t="n"/>
       <c r="D41" s="69" t="inlineStr">
         <is>
-          <t>brand.manage es un permiso propio, y no legal_entity.manage</t>
+          <t>Una configuracion que falta NO bloquea: valor de partida y aviso con prioridad</t>
         </is>
       </c>
       <c r="E41" s="69" t="inlineStr">
@@ -16196,14 +16246,14 @@
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>Quien da de alta sociedades del grupo no tiene por que poder cambiar lo que ve todo el mundo en todas las pantallas, incluida la de acceso. Hoy los dos los tiene solo admin; el dia que legal_entity.manage se le de a alguien de operaciones, esa persona no podra cambiar la marca. Hay una prueba que lo fija.</t>
+          <t>DEC-190 llevado al codigo. Sin tabla, sin fila o con un campo vacio se cae al valor de partida y aparece un badge: rojo lo que un tercero va a ver mal (sin logotipo, sin correo de soporte), ambar lo que conviene (sin favicon, sin pie legal, sin web), verde cuando no falta nada. El sistema arranca con dos rojos y funciona perfectamente con los dos puestos.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="45.75" customHeight="1" s="36">
       <c r="A42" s="67" t="inlineStr">
         <is>
-          <t>DEC-198</t>
+          <t>DEC-201</t>
         </is>
       </c>
       <c r="B42" s="68" t="inlineStr">
@@ -16214,24 +16264,24 @@
       <c r="C42" s="68" t="n"/>
       <c r="D42" s="69" t="inlineStr">
         <is>
-          <t>El permiso se mira en CADA peticion: no hay URL firmada de archivo.</t>
+          <t>El logotipo se sirve por una puerta publica propia, sin identificador</t>
         </is>
       </c>
       <c r="E42" s="69" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>Una URL firmada sigue funcionando cuando se reenvia y cuando a esa persona ya se le quito el acceso, y lo que sale por aqui son documentos de identidad y comprobantes bancarios. Con ruta propia, quitar un permiso surte efecto en la siguiente peticion y no queda ningun enlace circulando. El archivo se busca por uuid y no por id --un id correlativo invita a probar el siguiente-- y la respuesta lleva no-store (una identidad en la cache de un equipo compartido sobrevive al cierre de sesion), nosniff y una CSP que impide que un HTML o un SVG subido como «evidencia» se ejecute. El creador ve lo suyo, incluida su identidad: es informacion suya y le permite comprobar que archivamos el correcto. Rastro en bitacora solo para los sensibles --identidad, terminos y comprobante bancario--: anotar cada captura convertiria la bitacora en ruido, y una bitacora que nadie lee no protege nada</t>
+          <t>La pantalla de acceso la ve quien no ha entrado, asi que el permiso file.view de 9.15 dejaria la marca fuera de la unica pantalla que ve todo el mundo. Lo que hace seguras a /marca/logo y /marca/favicon no es un permiso: es que NO aceptan identificador. Estan en RUTAS-ABIERTAS con su motivo y MuroTest las conoce.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="68.25" customHeight="1" s="36">
       <c r="A43" s="67" t="inlineStr">
         <is>
-          <t>DEC-197</t>
+          <t>DEC-202</t>
         </is>
       </c>
       <c r="B43" s="68" t="inlineStr">
@@ -16242,24 +16292,24 @@
       <c r="C43" s="68" t="n"/>
       <c r="D43" s="69" t="inlineStr">
         <is>
-          <t>Cada modulo declara quien puede ver SUS archivos; no hay un switch central.</t>
+          <t>El codigo de la marca no se cambia; el nombre visible si</t>
         </is>
       </c>
       <c r="E43" s="69" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>La regla de cada archivo depende de la tabla que lo apunta --identidad de creators, captura de publication_evidence, comprobante de payouts-- y un decisor central que las consultara todas pondria a Shared o a Core a saber de payouts. deptrac no lo veria: son consultas a tablas y no clases importadas, o sea una frontera rota en silencio, que es la peor clase. Cada modulo registra su regla en su ServiceProvider, igual que registra sus escuchas. Y se niega por omision: un proposito sin regla no se abre ni para el administrador, asi que un archivo nuevo cuyo autor olvido declarar quien puede verlo se queda cerrado y no abierto a todos</t>
+          <t>tg_pb_code lo impide en el motor. El code es la llave con la que el sembrador encuentra la marca: si cambia, el siguiente db:seed crea otra, el sistema amanece con dos y las pantallas siguen ensenando la vieja mientras alguien edita la nueva.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="79.5" customHeight="1" s="36">
       <c r="A44" s="67" t="inlineStr">
         <is>
-          <t>DEC-196</t>
+          <t>DEC-203</t>
         </is>
       </c>
       <c r="B44" s="68" t="inlineStr">
@@ -16270,24 +16320,24 @@
       <c r="C44" s="68" t="n"/>
       <c r="D44" s="69" t="inlineStr">
         <is>
-          <t>La Academia del creador se construye, y cada modulo se configura desde el admin.</t>
+          <t>Los colores y la tipografia se desinfectan ademas del CHECK</t>
         </is>
       </c>
       <c r="E44" s="69" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>Es G-08 del addendum de gamificacion y la de mas retorno de las once: modulos cortos --leer un brief sin gastar rondas, iluminacion y audio con un movil, como se rotula el contenido comercial, que derechos esta cediendo, como subir su evidencia-- con evaluacion al final e insignia de creador certificado. Ataca tres dolores ya medidos: cada ronda evitada es tiempo del equipo de revision, cada evidencia subida sola es el proceso mas manual que se deja de perseguir, y «creadores certificados» es un argumento de venta ante la marca. El software es la parte barata: modulos, orden, formato, evaluacion, intentos, XP e insignia salen del admin (DEC-190), y al completar uno se levanta TrainingModuleCompleted, previsto en el modelo desde la Fase 2. Lo caro es el CONTENIDO --guiones, video, mantenerlo cuando cambie una norma o una red-- y eso no lo hace el sistema. Se puede arrancar con modulos de solo texto, que cuestan casi nada y ya bajan rondas. Cierra Q-27</t>
+          <t>El color acaba dentro de una regla CSS y la tipografia dentro de una URL y de una regla CSS, en todas las pantallas a la vez. Un nombre con comillas y llaves cierra la regla y escribe estilo ajeno en toda la aplicacion. Si el valor entra por una via que no pasa por el CHECK --carga masiva, restauracion de copia--, la segunda cerradura es lo unico que queda.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="124.5" customHeight="1" s="36">
       <c r="A45" s="67" t="inlineStr">
         <is>
-          <t>DEC-195</t>
+          <t>DEC-204</t>
         </is>
       </c>
       <c r="B45" s="68" t="inlineStr">
@@ -16298,24 +16348,24 @@
       <c r="C45" s="68" t="n"/>
       <c r="D45" s="69" t="inlineStr">
         <is>
-          <t>El lado del tipo de cambio se configura POR TIPO DE TRANSACCION.</t>
+          <t>brand.manage es un permiso propio, y no legal_entity.manage</t>
         </is>
       </c>
       <c r="E45" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>No se fija uno en el codigo: lo que se le paga a un creador, lo que se le cobra a un cliente y un gasto operativo no tienen por que convertirse con el mismo lado, y esa eleccion es contable. El admin declara, para cada tipo de transaccion, que lado se aplica (compra, venta o media) y con que fuente. Cierra Q-63, que era la que impedia dar un porcentaje de margen cuando hay dos monedas (DEC-185)</t>
+          <t>Quien da de alta sociedades del grupo no tiene por que poder cambiar lo que ve todo el mundo en todas las pantallas, incluida la de acceso. Hoy los dos los tiene solo admin; el dia que legal_entity.manage se le de a alguien de operaciones, esa persona no podra cambiar la marca. Hay una prueba que lo fija.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="90.75" customHeight="1" s="36">
       <c r="A46" s="67" t="inlineStr">
         <is>
-          <t>DEC-194</t>
+          <t>DEC-198</t>
         </is>
       </c>
       <c r="B46" s="68" t="inlineStr">
@@ -16326,24 +16376,24 @@
       <c r="C46" s="68" t="n"/>
       <c r="D46" s="69" t="inlineStr">
         <is>
-          <t>La gamificacion premia con reconocimiento y con un catalogo de premios canjeables por XP.</t>
+          <t>El permiso se mira en CADA peticion: no hay URL firmada de archivo.</t>
         </is>
       </c>
       <c r="E46" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>Nada de dinero. Los premios --viajes, objetos-- viven en una tabla configurable desde el admin con su coste en XP y su disponibilidad, y el creador los canjea. El hito que consolida un referido es la primera campana completada (Q-25). Cierra Q-23, Q-24 y Q-26</t>
+          <t>Una URL firmada sigue funcionando cuando se reenvia y cuando a esa persona ya se le quito el acceso, y lo que sale por aqui son documentos de identidad y comprobantes bancarios. Con ruta propia, quitar un permiso surte efecto en la siguiente peticion y no queda ningun enlace circulando. El archivo se busca por uuid y no por id --un id correlativo invita a probar el siguiente-- y la respuesta lleva no-store (una identidad en la cache de un equipo compartido sobrevive al cierre de sesion), nosniff y una CSP que impide que un HTML o un SVG subido como «evidencia» se ejecute. El creador ve lo suyo, incluida su identidad: es informacion suya y le permite comprobar que archivamos el correcto. Rastro en bitacora solo para los sensibles --identidad, terminos y comprobante bancario--: anotar cada captura convertiria la bitacora en ruido, y una bitacora que nadie lee no protege nada</t>
         </is>
       </c>
     </row>
     <row r="47" ht="68.25" customHeight="1" s="36">
       <c r="A47" s="67" t="inlineStr">
         <is>
-          <t>DEC-193</t>
+          <t>DEC-197</t>
         </is>
       </c>
       <c r="B47" s="68" t="inlineStr">
@@ -16354,24 +16404,24 @@
       <c r="C47" s="68" t="n"/>
       <c r="D47" s="69" t="inlineStr">
         <is>
-          <t>Publicar terminos nuevos no expulsa a nadie de golpe: hay plazo, aviso y aterrizaje suave.</t>
+          <t>Cada modulo declara quien puede ver SUS archivos; no hay un switch central.</t>
         </is>
       </c>
       <c r="E47" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>Correo con enlace de aceptacion, 15 dias de plazo, aviso en la bandeja interna de la plataforma y recordatorio al entrar. Cumplido el plazo sin aceptar, la sesion cae en una pantalla que exige aceptar para continuar; si no acepta, solo lectura durante 30 dias. Los dos plazos son configurables (DEC-190). Es la respuesta a Q-46, y encaja con el «cambio menor» de 9.16: una errata no dispara nada de esto</t>
+          <t>La regla de cada archivo depende de la tabla que lo apunta --identidad de creators, captura de publication_evidence, comprobante de payouts-- y un decisor central que las consultara todas pondria a Shared o a Core a saber de payouts. deptrac no lo veria: son consultas a tablas y no clases importadas, o sea una frontera rota en silencio, que es la peor clase. Cada modulo registra su regla en su ServiceProvider, igual que registra sus escuchas. Y se niega por omision: un proposito sin regla no se abre ni para el administrador, asi que un archivo nuevo cuyo autor olvido declarar quien puede verlo se queda cerrado y no abierto a todos</t>
         </is>
       </c>
     </row>
     <row r="48" ht="45.75" customHeight="1" s="36">
       <c r="A48" s="67" t="inlineStr">
         <is>
-          <t>DEC-192</t>
+          <t>DEC-196</t>
         </is>
       </c>
       <c r="B48" s="68" t="inlineStr">
@@ -16382,24 +16432,24 @@
       <c r="C48" s="68" t="n"/>
       <c r="D48" s="69" t="inlineStr">
         <is>
-          <t>Facturacion electronica DIRECTA con SUNAT, no por proveedor.</t>
+          <t>La Academia del creador se construye, y cada modulo se configura desde el admin.</t>
         </is>
       </c>
       <c r="E48" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>Configurable entero desde el admin: URL, certificado, usuario y clave secundarios, y correlativos independientes de factura, boleta y notas de credito de cada una. Con monitor de documentos timbrados: estado de cada uno, reintento manual, reintento automatico por job con frecuencia y numero de reintentos configurables, descarga de CDR, XML y PDF --el PDF con plantilla configurable-- y envio al cliente por correo con cuerpo configurable y variables arrastrables. Cierra Q-03 y de paso Q-21, que preguntaba por el contrato con un proveedor que ya no hay</t>
+          <t>Es G-08 del addendum de gamificacion y la de mas retorno de las once: modulos cortos --leer un brief sin gastar rondas, iluminacion y audio con un movil, como se rotula el contenido comercial, que derechos esta cediendo, como subir su evidencia-- con evaluacion al final e insignia de creador certificado. Ataca tres dolores ya medidos: cada ronda evitada es tiempo del equipo de revision, cada evidencia subida sola es el proceso mas manual que se deja de perseguir, y «creadores certificados» es un argumento de venta ante la marca. El software es la parte barata: modulos, orden, formato, evaluacion, intentos, XP e insignia salen del admin (DEC-190), y al completar uno se levanta TrainingModuleCompleted, previsto en el modelo desde la Fase 2. Lo caro es el CONTENIDO --guiones, video, mantenerlo cuando cambie una norma o una red-- y eso no lo hace el sistema. Se puede arrancar con modulos de solo texto, que cuestan casi nada y ya bajan rondas. Cierra Q-27</t>
         </is>
       </c>
     </row>
     <row r="49" ht="57" customHeight="1" s="36">
       <c r="A49" s="67" t="inlineStr">
         <is>
-          <t>DEC-191</t>
+          <t>DEC-195</t>
         </is>
       </c>
       <c r="B49" s="68" t="inlineStr">
@@ -16410,7 +16460,7 @@
       <c r="C49" s="68" t="n"/>
       <c r="D49" s="69" t="inlineStr">
         <is>
-          <t>La retencion se calcula HACIA ATRAS desde el neto pactado, y se compara con un umbral de rentabilidad.</t>
+          <t>El lado del tipo de cambio se configura POR TIPO DE TRANSACCION.</t>
         </is>
       </c>
       <c r="E49" s="69" t="inlineStr">
@@ -16420,14 +16470,14 @@
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>Con el creador se pacta lo que VA A RECIBIR --«te pago 100»--; el sistema calcula el bruto que hay que provisionar con la tasa configurada (29,5% por defecto, Q-13/Q-40): bruto = neto / (1 - tasa), o sea 141,84 para 100 netos, de los que 41,84 son retencion. Tres campos y no uno: neto pactado, tasa aplicada (por defecto la del admin, editable en el trato) e importe bruto. Encima va un umbral de rentabilidad minima configurable: con el bruto como costo, la pantalla dice cual es el ingreso mas bajo que hace aceptable esa participacion, y avisa antes de cerrar el trato --no despues--. La tasa, el umbral y la base sobre la que se mide el umbral (sobre costo o sobre ingreso: no dan el mismo numero) salen del admin</t>
+          <t>No se fija uno en el codigo: lo que se le paga a un creador, lo que se le cobra a un cliente y un gasto operativo no tienen por que convertirse con el mismo lado, y esa eleccion es contable. El admin declara, para cada tipo de transaccion, que lado se aplica (compra, venta o media) y con que fuente. Cierra Q-63, que era la que impedia dar un porcentaje de margen cuando hay dos monedas (DEC-185)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="79.5" customHeight="1" s="36">
       <c r="A50" s="67" t="inlineStr">
         <is>
-          <t>DEC-190</t>
+          <t>DEC-194</t>
         </is>
       </c>
       <c r="B50" s="68" t="inlineStr">
@@ -16435,14 +16485,10 @@
           <t>Decidida</t>
         </is>
       </c>
-      <c r="C50" s="68" t="inlineStr">
-        <is>
-          <t>Critica</t>
-        </is>
-      </c>
+      <c r="C50" s="68" t="n"/>
       <c r="D50" s="69" t="inlineStr">
         <is>
-          <t>PRINCIPIO RECTOR: la plataforma es WHITE LABEL y todo se configura desde el admin.</t>
+          <t>La gamificacion premia con reconocimiento y con un catalogo de premios canjeables por XP.</t>
         </is>
       </c>
       <c r="E50" s="69" t="inlineStr">
@@ -16452,14 +16498,14 @@
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>Nada de reglas de negocio quemadas en el codigo: ni la razon social, ni el RUC, ni el representante legal, ni la direccion, ni el ubigeo, ni las tasas, ni los plazos, ni los correlativos, ni las credenciales de ninguna API. Lo que el codigo aporta es la REGLA; el VALOR sale de la configuracion. Y una configuracion sin valor no bloquea: se siembra con un valor de partida y se avisa con su prioridad --rojo si es delicado y sigue de fabrica, ambar si conviene revisarlo--. Esto corrige el criterio con el que se habian tomado varias decisiones anteriores --3.5 dejaba el sistema sin arrancar hasta que alguien corriera un comando, y varias preguntas de negocio se plantearon como «elige una y la quemo» cuando la respuesta correcta era «las dos, y que se elija en el admin»--. Toda decision anterior que fije un valor en el codigo queda sujeta a revision bajo este principio (T-69)</t>
+          <t>Nada de dinero. Los premios --viajes, objetos-- viven en una tabla configurable desde el admin con su coste en XP y su disponibilidad, y el creador los canjea. El hito que consolida un referido es la primera campana completada (Q-25). Cierra Q-23, Q-24 y Q-26</t>
         </is>
       </c>
     </row>
     <row r="51" ht="113.25" customHeight="1" s="36">
       <c r="A51" s="67" t="inlineStr">
         <is>
-          <t>DEC-189</t>
+          <t>DEC-193</t>
         </is>
       </c>
       <c r="B51" s="68" t="inlineStr">
@@ -16470,24 +16516,24 @@
       <c r="C51" s="68" t="n"/>
       <c r="D51" s="69" t="inlineStr">
         <is>
-          <t>Las 23 rutas sin permiso se escriben, con su motivo, en RUTAS-ABIERTAS.</t>
+          <t>Publicar terminos nuevos no expulsa a nadie de golpe: hay plazo, aviso y aterrizaje suave.</t>
         </is>
       </c>
       <c r="E51" s="69" t="inlineStr">
         <is>
-          <t>9.14b</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>Hasta hoy nada distinguia «es publica a proposito» --entrar, recuperar la contrasena, los enlaces firmados de 7.6 y 8.5-- de «se le olvido el middleware a alguien». verificar-muro.py comprueba que tres sitios digan lo mismo: la lista, routes/web.php y la constante de MuroTest; no se pueden fundir porque una la lee Python sin Laravel y otra PHPUnit, y tres copias es como se pierde una (SUITES, 3.12). Al CI: una ruta nueva sin permiso que no este escrita lo pone en rojo. De paso se cerraron dos puertas que no eran nuestras: storage.local y storage.local.upload, que registra el framework con serve =&gt; true sobre el disco privado. No eran una fuga --exigen URL firmada-- pero la aplicacion no genera ninguna, asi que no servian para nada; y ninguna lectura del codigo las habria encontrado, porque no estan en ningun archivo de rutas</t>
+          <t>Correo con enlace de aceptacion, 15 dias de plazo, aviso en la bandeja interna de la plataforma y recordatorio al entrar. Cumplido el plazo sin aceptar, la sesion cae en una pantalla que exige aceptar para continuar; si no acepta, solo lectura durante 30 dias. Los dos plazos son configurables (DEC-190). Es la respuesta a Q-46, y encaja con el «cambio menor» de 9.16: una errata no dispara nada de esto</t>
         </is>
       </c>
     </row>
     <row r="52" ht="102" customHeight="1" s="36">
       <c r="A52" s="67" t="inlineStr">
         <is>
-          <t>DEC-188</t>
+          <t>DEC-192</t>
         </is>
       </c>
       <c r="B52" s="68" t="inlineStr">
@@ -16498,24 +16544,24 @@
       <c r="C52" s="68" t="n"/>
       <c r="D52" s="69" t="inlineStr">
         <is>
-          <t>El muro se prueba recorriendo TODAS las rutas, no las que uno recuerda.</t>
+          <t>Facturacion electronica DIRECTA con SUNAT, no por proveedor.</t>
         </is>
       </c>
       <c r="E52" s="69" t="inlineStr">
         <is>
-          <t>9.14b</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>MuroTest pide las 145 rutas con nombre como creador, como usuario de cliente y como autenticado sin rol, y exige que ninguna se abra --371 aserciones, y el muro aguanta--. Una pantalla nueva entra sola en la prueba. Las afirmaciones dirigidas que ya habia (DEC-172, DEC-179, DEC-181) comprueban lo que alguien se acordo de mirar; el fallo que de verdad paso --5.9, la portada enseñando los totales internos a cualquier autenticado-- no lo habria cazado ninguna. Lo permitido se escribe en positivo: una lista de lo permitido crece solo cuando alguien la toca a proposito. Se admite un 404 porque SubstituteBindings corre antes del middleware --con un id inventado la ruta contesta antes de llegar al permiso-- y para que no sea el escondite de la prueba se exige que mas de 80 rutas contesten 403 de verdad</t>
+          <t>Configurable entero desde el admin: URL, certificado, usuario y clave secundarios, y correlativos independientes de factura, boleta y notas de credito de cada una. Con monitor de documentos timbrados: estado de cada uno, reintento manual, reintento automatico por job con frecuencia y numero de reintentos configurables, descarga de CDR, XML y PDF --el PDF con plantilla configurable-- y envio al cliente por correo con cuerpo configurable y variables arrastrables. Cierra Q-03 y de paso Q-21, que preguntaba por el contrato con un proveedor que ya no hay</t>
         </is>
       </c>
     </row>
     <row r="53" ht="79.5" customHeight="1" s="36">
       <c r="A53" s="67" t="inlineStr">
         <is>
-          <t>DEC-187</t>
+          <t>DEC-191</t>
         </is>
       </c>
       <c r="B53" s="68" t="inlineStr">
@@ -16526,24 +16572,24 @@
       <c r="C53" s="68" t="n"/>
       <c r="D53" s="69" t="inlineStr">
         <is>
-          <t>Una suite de QA se construye SU caso y no reusa el de nadie.</t>
+          <t>La retencion se calcula HACIA ATRAS desde el neto pactado, y se compara con un umbral de rentabilidad.</t>
         </is>
       </c>
       <c r="E53" s="69" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>La primera version de 9.14 reusaba lo que dejaban las suites anteriores, como hace 9.6, y se puso amarilla dos veces por motivos opuestos: corriendo sola porque no habia asientos, y corriendo la bateria entera porque para cuando llega el unico devengo pagable ya esta liquidado por 9.6 y las dos participaciones de la semilla estan ocupadas. Ahora crea su campana, su participacion y su devengo. Una suite de QA que depende del orden mide el orden, no la regla</t>
+          <t>Con el creador se pacta lo que VA A RECIBIR --«te pago 100»--; el sistema calcula el bruto que hay que provisionar con la tasa configurada (29,5% por defecto, Q-13/Q-40): bruto = neto / (1 - tasa), o sea 141,84 para 100 netos, de los que 41,84 son retencion. Tres campos y no uno: neto pactado, tasa aplicada (por defecto la del admin, editable en el trato) e importe bruto. Encima va un umbral de rentabilidad minima configurable: con el bruto como costo, la pantalla dice cual es el ingreso mas bajo que hace aceptable esa participacion, y avisa antes de cerrar el trato --no despues--. La tasa, el umbral y la base sobre la que se mide el umbral (sobre costo o sobre ingreso: no dan el mismo numero) salen del admin</t>
         </is>
       </c>
     </row>
     <row r="54" ht="45.75" customHeight="1" s="36">
       <c r="A54" s="67" t="inlineStr">
         <is>
-          <t>DEC-186</t>
+          <t>DEC-190</t>
         </is>
       </c>
       <c r="B54" s="68" t="inlineStr">
@@ -16551,27 +16597,31 @@
           <t>Decidida</t>
         </is>
       </c>
-      <c r="C54" s="68" t="n"/>
+      <c r="C54" s="68" t="inlineStr">
+        <is>
+          <t>Critica</t>
+        </is>
+      </c>
       <c r="D54" s="69" t="inlineStr">
         <is>
-          <t>Nace verificar-cobertura-sql.py: que regla de la base no ha contestado NUNCA a nadie.</t>
+          <t>PRINCIPIO RECTOR: la plataforma es WHITE LABEL y todo se configura desde el admin.</t>
         </is>
       </c>
       <c r="E54" s="69" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F54" s="69" t="inlineStr">
         <is>
-          <t>Los verificadores que ya habia comprueban que la regla EXISTA y que sea la misma en los dos motores; ninguno comprobaba lo unico que importa el dia que falle: que alguien se lo haya preguntado. Medido: de las 317 reglas del esquema, 167 no aparecian en ninguna suite ni en ninguna prueba --el 53%--. No significa que esten mal: significa que nadie lo sabe. Una regla que nunca se ha probado no es una regla, es una intencion escrita en DDL. Va a correr-todo.sh y al CI con trinquete (MUDAS-BASE), asi que una regla nueva sin asercion pone el CI en rojo. La pregunta salio de 9.10a, donde campaign_costs llevaba dos semanas con cinco restricciones verdes en todos los verificadores y CERO filas</t>
+          <t>Nada de reglas de negocio quemadas en el codigo: ni la razon social, ni el RUC, ni el representante legal, ni la direccion, ni el ubigeo, ni las tasas, ni los plazos, ni los correlativos, ni las credenciales de ninguna API. Lo que el codigo aporta es la REGLA; el VALOR sale de la configuracion. Y una configuracion sin valor no bloquea: se siembra con un valor de partida y se avisa con su prioridad --rojo si es delicado y sigue de fabrica, ambar si conviene revisarlo--. Esto corrige el criterio con el que se habian tomado varias decisiones anteriores --3.5 dejaba el sistema sin arrancar hasta que alguien corriera un comando, y varias preguntas de negocio se plantearon como «elige una y la quemo» cuando la respuesta correcta era «las dos, y que se elija en el admin»--. Toda decision anterior que fije un valor en el codigo queda sujeta a revision bajo este principio (T-69)</t>
         </is>
       </c>
     </row>
     <row r="55" ht="79.5" customHeight="1" s="36">
       <c r="A55" s="67" t="inlineStr">
         <is>
-          <t>DEC-185</t>
+          <t>DEC-189</t>
         </is>
       </c>
       <c r="B55" s="68" t="inlineStr">
@@ -16582,24 +16632,24 @@
       <c r="C55" s="68" t="n"/>
       <c r="D55" s="69" t="inlineStr">
         <is>
-          <t>El porcentaje de margen solo se da cuando todo esta en una moneda, y si no, se dice por que.</t>
+          <t>Las 23 rutas sin permiso se escriben, con su motivo, en RUTAS-ABIERTAS.</t>
         </is>
       </c>
       <c r="E55" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14b</t>
         </is>
       </c>
       <c r="F55" s="69" t="inlineStr">
         <is>
-          <t>Convertir exige elegir compra, venta o media (Q-63) y cada eleccion da un margen distinto para los mismos hechos; el dia que se elija cambian ademas todos los margenes historicos a la vez. Cuando falta, la pantalla escribe el motivo con palabras --«esta campana tiene importes en PEN y USD…»-- y no deja un hueco: quien mira una pantalla donde falta un numero necesita saber si falta porque no lo hay o porque no se puede calcular, y son dos conversaciones distintas. Tampoco hay total por sociedad: el ingreso de hoy es el DECLARADO y no el facturado (9.9), y sumar precios declarados por sociedad se parece a un estado de resultados sin serlo</t>
+          <t>Hasta hoy nada distinguia «es publica a proposito» --entrar, recuperar la contrasena, los enlaces firmados de 7.6 y 8.5-- de «se le olvido el middleware a alguien». verificar-muro.py comprueba que tres sitios digan lo mismo: la lista, routes/web.php y la constante de MuroTest; no se pueden fundir porque una la lee Python sin Laravel y otra PHPUnit, y tres copias es como se pierde una (SUITES, 3.12). Al CI: una ruta nueva sin permiso que no este escrita lo pone en rojo. De paso se cerraron dos puertas que no eran nuestras: storage.local y storage.local.upload, que registra el framework con serve =&gt; true sobre el disco privado. No eran una fuga --exigen URL firmada-- pero la aplicacion no genera ninguna, asi que no servian para nada; y ninguna lectura del codigo las habria encontrado, porque no estan en ningun archivo de rutas</t>
         </is>
       </c>
     </row>
     <row r="56" ht="79.5" customHeight="1" s="36">
       <c r="A56" s="67" t="inlineStr">
         <is>
-          <t>DEC-184</t>
+          <t>DEC-188</t>
         </is>
       </c>
       <c r="B56" s="68" t="inlineStr">
@@ -16610,24 +16660,24 @@
       <c r="C56" s="68" t="n"/>
       <c r="D56" s="69" t="inlineStr">
         <is>
-          <t>Los canjes salen en la lista, marcados, y fuera de todo total.</t>
+          <t>El muro se prueba recorriendo TODAS las rutas, no las que uno recuerda.</t>
         </is>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14b</t>
         </is>
       </c>
       <c r="F56" s="69" t="inlineStr">
         <is>
-          <t>Su ingreso es cero POR DECISION (7.2), asi que su margen es siempre negativo: el producto y el envio se gastaron igual. Promediarlos hace que la cartera entera parezca peor por un motivo que fue deliberado. Pero se enseñan con su costo, porque un canje tambien cuesta dinero y ese era justo el numero que nadie tenia. Queda fuera del total una segunda clase de campana: la que tiene gastos en OTRA moneda, cuyo margen en la moneda del grupo esta incompleto --y sumar un numero incompleto lo vuelve invisible--. Y la cabecera dice cuantas quedaron fuera y por que: un total que excluye filas sin contarlas engaña por omision</t>
+          <t>MuroTest pide las 145 rutas con nombre como creador, como usuario de cliente y como autenticado sin rol, y exige que ninguna se abra --371 aserciones, y el muro aguanta--. Una pantalla nueva entra sola en la prueba. Las afirmaciones dirigidas que ya habia (DEC-172, DEC-179, DEC-181) comprueban lo que alguien se acordo de mirar; el fallo que de verdad paso --5.9, la portada enseñando los totales internos a cualquier autenticado-- no lo habria cazado ninguna. Lo permitido se escribe en positivo: una lista de lo permitido crece solo cuando alguien la toca a proposito. Se admite un 404 porque SubstituteBindings corre antes del middleware --con un id inventado la ruta contesta antes de llegar al permiso-- y para que no sea el escondite de la prueba se exige que mas de 80 rutas contesten 403 de verdad</t>
         </is>
       </c>
     </row>
     <row r="57" ht="68.25" customHeight="1" s="36">
       <c r="A57" s="67" t="inlineStr">
         <is>
-          <t>DEC-183</t>
+          <t>DEC-187</t>
         </is>
       </c>
       <c r="B57" s="68" t="inlineStr">
@@ -16638,24 +16688,24 @@
       <c r="C57" s="68" t="n"/>
       <c r="D57" s="69" t="inlineStr">
         <is>
-          <t>Compromiso::margen() se BORRA, no se arregla.</t>
+          <t>Una suite de QA se construye SU caso y no reusa el de nadie.</t>
         </is>
       </c>
       <c r="E57" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="F57" s="69" t="inlineStr">
         <is>
-          <t>Vivia en Campaign desde 7.7 y devolvia revenue_amount menos lo comprometido con creadores: no restaba producto, envios ni produccion, y desde 9.10a esos gastos ya se anotan, asi que el numero habria ido empeorando con cada gasto cargado sin que la pantalla se enterara. No se arregla donde estaba porque campaign_costs es de Finance y deptrac no deja que Campaign la conozca --misma frontera que el devengo de 9.4--. Y se borra en vez de dejarse por si acaso: un metodo que calcula un numero incompleto y se llama margen() es una trampa para quien lo encuentre dentro de seis meses. De paso, SeguimientoController deja de pasar un importe y pasa un booleano mas un enlace: ningun numero interno cruza ya hasta la plantilla, que es BR-SEC-001 un paso mas alla</t>
+          <t>La primera version de 9.14 reusaba lo que dejaban las suites anteriores, como hace 9.6, y se puso amarilla dos veces por motivos opuestos: corriendo sola porque no habia asientos, y corriendo la bateria entera porque para cuando llega el unico devengo pagable ya esta liquidado por 9.6 y las dos participaciones de la semilla estan ocupadas. Ahora crea su campana, su participacion y su devengo. Una suite de QA que depende del orden mide el orden, no la regla</t>
         </is>
       </c>
     </row>
     <row r="58" ht="34.5" customHeight="1" s="36">
       <c r="A58" s="67" t="inlineStr">
         <is>
-          <t>DEC-182</t>
+          <t>DEC-186</t>
         </is>
       </c>
       <c r="B58" s="68" t="inlineStr">
@@ -16666,24 +16716,24 @@
       <c r="C58" s="68" t="n"/>
       <c r="D58" s="69" t="inlineStr">
         <is>
-          <t>El costo del creador entra al DEVENGARSE, no al pagarse.</t>
+          <t>Nace verificar-cobertura-sql.py: que regla de la base no ha contestado NUNCA a nadie.</t>
         </is>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="F58" s="69" t="inlineStr">
         <is>
-          <t>La deuda existe desde que acepta (9.4) y su importe esta congelado desde 7.5; esperar al pago haria que una campana terminada en marzo pareciera rentabilisima hasta el lote de abril. Sale del libro mayor y no de campaign_creators, porque el libro es quien sabe que devengos siguen vivos: uno anulado ya no se debe. Y no es Compromiso::comprometido(), que cuenta tambien a los shortlisted: alli es correcto --su trabajo es proteger el presupuesto ANTES de invitar-- y aqui contaria dinero de gente que todavia puede decir que no</t>
+          <t>Los verificadores que ya habia comprueban que la regla EXISTA y que sea la misma en los dos motores; ninguno comprobaba lo unico que importa el dia que falle: que alguien se lo haya preguntado. Medido: de las 317 reglas del esquema, 167 no aparecian en ninguna suite ni en ninguna prueba --el 53%--. No significa que esten mal: significa que nadie lo sabe. Una regla que nunca se ha probado no es una regla, es una intencion escrita en DDL. Va a correr-todo.sh y al CI con trinquete (MUDAS-BASE), asi que una regla nueva sin asercion pone el CI en rojo. La pregunta salio de 9.10a, donde campaign_costs llevaba dos semanas con cinco restricciones verdes en todos los verificadores y CERO filas</t>
         </is>
       </c>
     </row>
     <row r="59" ht="79.5" customHeight="1" s="36">
       <c r="A59" s="67" t="inlineStr">
         <is>
-          <t>DEC-181</t>
+          <t>DEC-185</t>
         </is>
       </c>
       <c r="B59" s="68" t="inlineStr">
@@ -16694,24 +16744,24 @@
       <c r="C59" s="68" t="n"/>
       <c r="D59" s="69" t="inlineStr">
         <is>
-          <t>Cargar gastos no es ver el margen: campaign_manager pierde campaign.view_margin.</t>
+          <t>El porcentaje de margen solo se da cuando todo esta en una moneda, y si no, se dice por que.</t>
         </is>
       </c>
       <c r="E59" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F59" s="69" t="inlineStr">
         <is>
-          <t>Quien lleva una campana anota lo que se gasta y ve cuanto lleva gastado; el margen --lo que se gana-- es una cifra de direccion, y el camino por el que un numero interno acaba en un correo a un cliente empieza siempre por alguien que podia verlo sin necesitarlo (BR-SEC-001, 🔴). No nace un permiso nuevo para el margen: campaign.view_margin ya existe y hace eso, y un segundo permiso para el mismo secreto es la forma clasica de que un dia se conceda el que nadie mira. Lo que nace es finance.cost.manage, que es la capacidad que de verdad no existia. Y la revocacion va en la MIGRACION y no en el seeder (T-64)</t>
+          <t>Convertir exige elegir compra, venta o media (Q-63) y cada eleccion da un margen distinto para los mismos hechos; el dia que se elija cambian ademas todos los margenes historicos a la vez. Cuando falta, la pantalla escribe el motivo con palabras --«esta campana tiene importes en PEN y USD…»-- y no deja un hueco: quien mira una pantalla donde falta un numero necesita saber si falta porque no lo hay o porque no se puede calcular, y son dos conversaciones distintas. Tampoco hay total por sociedad: el ingreso de hoy es el DECLARADO y no el facturado (9.9), y sumar precios declarados por sociedad se parece a un estado de resultados sin serlo</t>
         </is>
       </c>
     </row>
     <row r="60" ht="102" customHeight="1" s="36">
       <c r="A60" s="67" t="inlineStr">
         <is>
-          <t>DEC-180</t>
+          <t>DEC-184</t>
         </is>
       </c>
       <c r="B60" s="68" t="inlineStr">
@@ -16722,24 +16772,24 @@
       <c r="C60" s="68" t="n"/>
       <c r="D60" s="69" t="inlineStr">
         <is>
-          <t>El gasto de una campana se agrupa por moneda: no se suma.</t>
+          <t>Los canjes salen en la lista, marcados, y fuera de todo total.</t>
         </is>
       </c>
       <c r="E60" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F60" s="69" t="inlineStr">
         <is>
-          <t>Un envio se paga en dolares y la campana se cobra en soles; sumarlos exige un tipo de cambio, y cual --compra, venta o media-- es una decision contable que sigue abierta (Q-63) y que da tres margenes distintos para los mismos hechos. Es la misma decision que el saldo del creador en 9.8, por el mismo motivo. Un numero que parece exacto y depende de una eleccion que nadie ha hecho es peor que dos numeros separados</t>
+          <t>Su ingreso es cero POR DECISION (7.2), asi que su margen es siempre negativo: el producto y el envio se gastaron igual. Promediarlos hace que la cartera entera parezca peor por un motivo que fue deliberado. Pero se enseñan con su costo, porque un canje tambien cuesta dinero y ese era justo el numero que nadie tenia. Queda fuera del total una segunda clase de campana: la que tiene gastos en OTRA moneda, cuyo margen en la moneda del grupo esta incompleto --y sumar un numero incompleto lo vuelve invisible--. Y la cabecera dice cuantas quedaron fuera y por que: un total que excluye filas sin contarlas engaña por omision</t>
         </is>
       </c>
     </row>
     <row r="61" ht="90.75" customHeight="1" s="36">
       <c r="A61" s="67" t="inlineStr">
         <is>
-          <t>DEC-179</t>
+          <t>DEC-183</t>
         </is>
       </c>
       <c r="B61" s="68" t="inlineStr">
@@ -16750,24 +16800,24 @@
       <c r="C61" s="68" t="n"/>
       <c r="D61" s="69" t="inlineStr">
         <is>
-          <t>Al creador se le avisa al CONFIRMAR y al DEVOLVER, no al enviar.</t>
+          <t>Compromiso::margen() se BORRA, no se arregla.</t>
         </is>
       </c>
       <c r="E61" s="69" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F61" s="69" t="inlineStr">
         <is>
-          <t>Avisar al enviar es avisar de una intencion: si el banco lo rechaza, el creador ya cree que cobro, y el segundo correo desmiente al primero --dos correos que se contradicen cuestan mas confianza que un correo que llega un dia mas tarde--. Ninguno de los dos lleva numero de cuenta ni referencia bancaria: un correo se lee en pantallas ajenas y se reenvia, y para saber que le pagaron no hace falta ver su cuenta; es la misma decision que los avisos de 4.13. Y lo que faltaba en payouts no eran los estados --estan desde la Fase 2-- sino el GRAFO: sin tg_payout_estado, un pago saltaba de pending a confirmed sin haber salido nunca, y uno devuelto volvia a sent con un UPDATE, borrando que el banco lo habia rechazado. Mismo agujero que ledger_entries tenia antes de 9.3</t>
+          <t>Vivia en Campaign desde 7.7 y devolvia revenue_amount menos lo comprometido con creadores: no restaba producto, envios ni produccion, y desde 9.10a esos gastos ya se anotan, asi que el numero habria ido empeorando con cada gasto cargado sin que la pantalla se enterara. No se arregla donde estaba porque campaign_costs es de Finance y deptrac no deja que Campaign la conozca --misma frontera que el devengo de 9.4--. Y se borra en vez de dejarse por si acaso: un metodo que calcula un numero incompleto y se llama margen() es una trampa para quien lo encuentre dentro de seis meses. De paso, SeguimientoController deja de pasar un importe y pasa un booleano mas un enlace: ningun numero interno cruza ya hasta la plantilla, que es BR-SEC-001 un paso mas alla</t>
         </is>
       </c>
     </row>
     <row r="62" ht="57" customHeight="1" s="36">
       <c r="A62" s="67" t="inlineStr">
         <is>
-          <t>DEC-178</t>
+          <t>DEC-182</t>
         </is>
       </c>
       <c r="B62" s="68" t="inlineStr">
@@ -16778,24 +16828,24 @@
       <c r="C62" s="68" t="n"/>
       <c r="D62" s="69" t="inlineStr">
         <is>
-          <t>Un pago devuelto por el banco NO deshace el devengo.</t>
+          <t>El costo del creador entra al DEVENGARSE, no al pagarse.</t>
         </is>
       </c>
       <c r="E62" s="69" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F62" s="69" t="inlineStr">
         <is>
-          <t>El devengo se queda en paid porque se pago: lo que fallo fue la transferencia, no el trabajo --y paid es terminal desde DEC-169--. La correccion es un asiento de payment_reversal que apunta al asiento de pago original (BR-FIN-002), positivo, asi que devuelve el saldo; los dos hechos quedan escritos --se pago, y volvio-- en vez de que el segundo borre al primero. Nace accrued porque ck_ledger_estado_inicial no admite nacer pagable --a pagable se LLEGA-- y se mueve a payable en la misma operacion: el creador ya cumplio, y su dinero no tiene que esperar a que alguien se acuerde de revisarlo. Si el pago no tuviera asiento en el libro mayor, devolver() falla en voz alta en vez de dejar el saldo diciendo que cobro algo que no tiene</t>
+          <t>La deuda existe desde que acepta (9.4) y su importe esta congelado desde 7.5; esperar al pago haria que una campana terminada en marzo pareciera rentabilisima hasta el lote de abril. Sale del libro mayor y no de campaign_creators, porque el libro es quien sabe que devengos siguen vivos: uno anulado ya no se debe. Y no es Compromiso::comprometido(), que cuenta tambien a los shortlisted: alli es correcto --su trabajo es proteger el presupuesto ANTES de invitar-- y aqui contaria dinero de gente que todavia puede decir que no</t>
         </is>
       </c>
     </row>
     <row r="63" ht="90.75" customHeight="1" s="36">
       <c r="A63" s="67" t="inlineStr">
         <is>
-          <t>DEC-177</t>
+          <t>DEC-181</t>
         </is>
       </c>
       <c r="B63" s="68" t="inlineStr">
@@ -16806,24 +16856,24 @@
       <c r="C63" s="68" t="n"/>
       <c r="D63" s="69" t="inlineStr">
         <is>
-          <t>El CSV del lote NO es el archivo del banco.</t>
+          <t>Cargar gastos no es ver el margen: campaign_manager pierde campaign.view_margin.</t>
         </is>
       </c>
       <c r="E63" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F63" s="69" t="inlineStr">
         <is>
-          <t>El formato de una transferencia masiva es especifico de cada entidad y sale de su manual; inventarselo produce un archivo que el banco rechaza sin decir por que, y el sintoma aparece el dia del pago. Lo que hay es un CSV legible por una persona, para teclear o comprobar, y la pantalla lo dice con esas palabras para que nadie lo suba creyendo que es lo otro. El archivo real se construye cuando haya banco y especificacion</t>
+          <t>Quien lleva una campana anota lo que se gasta y ve cuanto lleva gastado; el margen --lo que se gana-- es una cifra de direccion, y el camino por el que un numero interno acaba en un correo a un cliente empieza siempre por alguien que podia verlo sin necesitarlo (BR-SEC-001, 🔴). No nace un permiso nuevo para el margen: campaign.view_margin ya existe y hace eso, y un segundo permiso para el mismo secreto es la forma clasica de que un dia se conceda el que nadie mira. Lo que nace es finance.cost.manage, que es la capacidad que de verdad no existia. Y la revocacion va en la MIGRACION y no en el seeder (T-64)</t>
         </is>
       </c>
     </row>
     <row r="64" ht="102" customHeight="1" s="36">
       <c r="A64" s="67" t="inlineStr">
         <is>
-          <t>DEC-176</t>
+          <t>DEC-180</t>
         </is>
       </c>
       <c r="B64" s="68" t="inlineStr">
@@ -16834,24 +16884,24 @@
       <c r="C64" s="68" t="n"/>
       <c r="D64" s="69" t="inlineStr">
         <is>
-          <t>Sacar un pago de un lote firmado NO obliga a firmarlo otra vez.</t>
+          <t>El gasto de una campana se agrupa por moneda: no se suma.</t>
         </is>
       </c>
       <c r="E64" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F64" s="69" t="inlineStr">
         <is>
-          <t>Cuando un devengo se retiene entre la firma y la ejecucion --un post que se cae-- ese pago sale y el resto se paga igual. El importe total baja, nunca sube, y eso no puede sorprender a quien ya firmo; devolver el lote entero a borrador castigaria a diez creadores por el problema de uno. La liquidacion se anula, no se borra: es evidencia de que estuvo dentro y de que alguien lo saco, y anularla exige quien y por que (tg_pe_inmutable). Al anularse, el devengo vuelve a la cola. Un lote ya ejecutado no se toca: el dinero salio, y eso se corrige con una devolucion</t>
+          <t>Un envio se paga en dolares y la campana se cobra en soles; sumarlos exige un tipo de cambio, y cual --compra, venta o media-- es una decision contable que sigue abierta (Q-63) y que da tres margenes distintos para los mismos hechos. Es la misma decision que el saldo del creador en 9.8, por el mismo motivo. Un numero que parece exacto y depende de una eleccion que nadie ha hecho es peor que dos numeros separados</t>
         </is>
       </c>
     </row>
     <row r="65" ht="90.75" customHeight="1" s="36">
       <c r="A65" s="67" t="inlineStr">
         <is>
-          <t>DEC-175</t>
+          <t>DEC-179</t>
         </is>
       </c>
       <c r="B65" s="68" t="inlineStr">
@@ -16862,24 +16912,24 @@
       <c r="C65" s="68" t="n"/>
       <c r="D65" s="69" t="inlineStr">
         <is>
-          <t>Dos firmas SIEMPRE, sin umbral.</t>
+          <t>Al creador se le avisa al CONFIRMAR y al DEVOLVER, no al enviar.</t>
         </is>
       </c>
       <c r="E65" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="F65" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-005 habla de un umbral configurable y se decide no tenerlo: el equipo es pequeno y los lotes son pocos y agrupados, asi que la segunda firma cuesta un clic al mes. Un umbral hay que elegirlo, mantenerlo y explicarlo --y el dia que alguien quiera saltarse la firma, parte el lote en dos--. Que el aprobador sea otro no lo comprueba la pantalla: lo impide ck_pbatch_segregation en la base desde la Fase 2; la pantalla solo lo dice ANTES de que nadie pulse. Y el importe del pago no se teclea: sale de sumar lo que liquida, asi que no puede discrepar de lo que el lote dice que paga --Lotes::descuadre() lo comprueba antes de firmar, porque una SUMA sobre otra tabla no cabe en un CHECK--</t>
+          <t>Avisar al enviar es avisar de una intencion: si el banco lo rechaza, el creador ya cree que cobro, y el segundo correo desmiente al primero --dos correos que se contradicen cuestan mas confianza que un correo que llega un dia mas tarde--. Ninguno de los dos lleva numero de cuenta ni referencia bancaria: un correo se lee en pantallas ajenas y se reenvia, y para saber que le pagaron no hace falta ver su cuenta; es la misma decision que los avisos de 4.13. Y lo que faltaba en payouts no eran los estados --estan desde la Fase 2-- sino el GRAFO: sin tg_payout_estado, un pago saltaba de pending a confirmed sin haber salido nunca, y uno devuelto volvia a sent con un UPDATE, borrando que el banco lo habia rechazado. Mismo agujero que ledger_entries tenia antes de 9.3</t>
         </is>
       </c>
     </row>
     <row r="66" ht="68.25" customHeight="1" s="36">
       <c r="A66" s="67" t="inlineStr">
         <is>
-          <t>DEC-174</t>
+          <t>DEC-178</t>
         </is>
       </c>
       <c r="B66" s="68" t="inlineStr">
@@ -16890,24 +16940,24 @@
       <c r="C66" s="68" t="n"/>
       <c r="D66" s="69" t="inlineStr">
         <is>
-          <t>Nace payout_earnings: que devengos paga cada pago.</t>
+          <t>Un pago devuelto por el banco NO deshace el devengo.</t>
         </is>
       </c>
       <c r="E66" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="F66" s="69" t="inlineStr">
         <is>
-          <t>ledger_entries.payout_id ataba UN asiento de pago a su payout (BR-FIN-013), pero el detalle --que devengos liquida-- no existia. Sin el, «.de que campanas es este dinero?» no tiene respuesta, y sin respuesta no hay nada que comparar con la sociedad del lote, que es lo que DEC-157 mando cerrar aqui. Con el detalle, BR-LE-009 se vuelve una consulta de tres saltos que cabe en tg_pe_sociedad. Se comprueba al enganchar el devengo al pago y no al aprobar el lote: aprobar es una firma sobre algo que ya tiene que estar bien, y una regla que solo mira al final deja existir el estado malo mientras tanto --que es como alguien lo ve, lo exporta, o lo cree--. Vigesimoseptima columna puerta: uq_pe_viva, un devengo en una sola liquidacion VIVA</t>
+          <t>El devengo se queda en paid porque se pago: lo que fallo fue la transferencia, no el trabajo --y paid es terminal desde DEC-169--. La correccion es un asiento de payment_reversal que apunta al asiento de pago original (BR-FIN-002), positivo, asi que devuelve el saldo; los dos hechos quedan escritos --se pago, y volvio-- en vez de que el segundo borre al primero. Nace accrued porque ck_ledger_estado_inicial no admite nacer pagable --a pagable se LLEGA-- y se mueve a payable en la misma operacion: el creador ya cumplio, y su dinero no tiene que esperar a que alguien se acuerde de revisarlo. Si el pago no tuviera asiento en el libro mayor, devolver() falla en voz alta en vez de dejar el saldo diciendo que cobro algo que no tiene</t>
         </is>
       </c>
     </row>
     <row r="67" ht="68.25" customHeight="1" s="36">
       <c r="A67" s="67" t="inlineStr">
         <is>
-          <t>DEC-173</t>
+          <t>DEC-177</t>
         </is>
       </c>
       <c r="B67" s="68" t="inlineStr">
@@ -16918,24 +16968,24 @@
       <c r="C67" s="68" t="n"/>
       <c r="D67" s="69" t="inlineStr">
         <is>
-          <t>La fecha de cobro se ensena SOLO cuando el asiento ya es pagable.</t>
+          <t>El CSV del lote NO es el archivo del banco.</t>
         </is>
       </c>
       <c r="E67" s="69" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F67" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-012 dice que el plazo son 30 dias desde la verificacion y que es visible desde que acepta: lo visible desde que acepta es el plazo, y una FECHA es otra cosa que se lee muy distinto. Mientras el asiento esta devengado se ensena que falta --las cinco condiciones de BR-FIN-003, con sus palabras--, que es accionable: un creador puede hacer algo con «no tienes ningun medio de pago verificado» y no puede hacer nada con una fecha que depende de trabajo que aun no ha hecho. Y si esa fecha se corriera, la culpa pareceria nuestra. La cuenta arranca en la ultima verificacion de sus publicaciones, y si no hay ninguna --un formato que no exige post-- en la fecha en que se completo la participacion</t>
+          <t>El formato de una transferencia masiva es especifico de cada entidad y sale de su manual; inventarselo produce un archivo que el banco rechaza sin decir por que, y el sintoma aparece el dia del pago. Lo que hay es un CSV legible por una persona, para teclear o comprobar, y la pantalla lo dice con esas palabras para que nadie lo suba creyendo que es lo otro. El archivo real se construye cuando haya banco y especificacion</t>
         </is>
       </c>
     </row>
     <row r="68" ht="79.5" customHeight="1" s="36">
       <c r="A68" s="67" t="inlineStr">
         <is>
-          <t>DEC-172</t>
+          <t>DEC-176</t>
         </is>
       </c>
       <c r="B68" s="68" t="inlineStr">
@@ -16946,24 +16996,24 @@
       <c r="C68" s="68" t="n"/>
       <c r="D68" s="69" t="inlineStr">
         <is>
-          <t>El motivo interno de una retencion NO se le ensena al creador.</t>
+          <t>Sacar un pago de un lote firmado NO obliga a firmarlo otra vez.</t>
         </is>
       </c>
       <c r="E68" s="69" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F68" s="69" t="inlineStr">
         <is>
-          <t>Lo escribe el equipo para el expediente y puede nombrar personas o sospechas todavia sin confirmar; un texto redactado deprisa --«parece que lo borro a proposito»-- leido sin contexto es una acusacion de la que no se vuelve. El creador ve «En revision -- te escribimos» y, desde 8.8, recibe un correo donde se le explica de verdad. Las palabras del portal tampoco son las del back-office: on_hold es «en revision» y no «retenido», porque la palabra interna describe lo que hace el sistema y la del portal tiene que describir lo que le pasa a el. La frontera vive en Ledger::misIngresos(), que enumera columnas --el mismo sitio que Aprobaciones::pieza() en 8.5--: devolver la fila entera y confiar en que la plantilla no imprima de mas es confiar en la plantilla de manana. Tampoco cruzan los asientos anulados: no le afectan y no sabe leerlos</t>
+          <t>Cuando un devengo se retiene entre la firma y la ejecucion --un post que se cae-- ese pago sale y el resto se paga igual. El importe total baja, nunca sube, y eso no puede sorprender a quien ya firmo; devolver el lote entero a borrador castigaria a diez creadores por el problema de uno. La liquidacion se anula, no se borra: es evidencia de que estuvo dentro y de que alguien lo saco, y anularla exige quien y por que (tg_pe_inmutable). Al anularse, el devengo vuelve a la cola. Un lote ya ejecutado no se toca: el dinero salio, y eso se corrige con una devolucion</t>
         </is>
       </c>
     </row>
     <row r="69" ht="57" customHeight="1" s="36">
       <c r="A69" s="67" t="inlineStr">
         <is>
-          <t>DEC-171</t>
+          <t>DEC-175</t>
         </is>
       </c>
       <c r="B69" s="68" t="inlineStr">
@@ -16974,24 +17024,24 @@
       <c r="C69" s="68" t="n"/>
       <c r="D69" s="69" t="inlineStr">
         <is>
-          <t>El barrido rescata las aceptaciones sin devengo, y avisa de que hubo que rescatarlas.</t>
+          <t>Dos firmas SIEMPRE, sin umbral.</t>
         </is>
       </c>
       <c r="E69" s="69" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F69" s="69" t="inlineStr">
         <is>
-          <t>Un listener puede fallar, y si falla el creador queda aceptado y su dinero invisible; ademas las participaciones aceptadas antes de 9.4 nunca pasaron por el. ledger:revisar las anota antes de revisar --para que un devengo recuperado hoy pueda pasar a pagable hoy y no manana-- y lo dice en amarillo: que la lista no salga en cero es la noticia, no el arreglo. Es la misma red que 8.1 dejo para los entregables. Las gratuitas quedan fuera de esa lista a proposito: si no, el barrido intentaria lo imposible todos los dias y avisaria todos los dias de algo que esta bien</t>
+          <t>BR-FIN-005 habla de un umbral configurable y se decide no tenerlo: el equipo es pequeno y los lotes son pocos y agrupados, asi que la segunda firma cuesta un clic al mes. Un umbral hay que elegirlo, mantenerlo y explicarlo --y el dia que alguien quiera saltarse la firma, parte el lote en dos--. Que el aprobador sea otro no lo comprueba la pantalla: lo impide ck_pbatch_segregation en la base desde la Fase 2; la pantalla solo lo dice ANTES de que nadie pulse. Y el importe del pago no se teclea: sale de sumar lo que liquida, asi que no puede discrepar de lo que el lote dice que paga --Lotes::descuadre() lo comprueba antes de firmar, porque una SUMA sobre otra tabla no cabe en un CHECK--</t>
         </is>
       </c>
     </row>
     <row r="70" ht="57" customHeight="1" s="36">
       <c r="A70" s="67" t="inlineStr">
         <is>
-          <t>DEC-170</t>
+          <t>DEC-174</t>
         </is>
       </c>
       <c r="B70" s="68" t="inlineStr">
@@ -17002,24 +17052,24 @@
       <c r="C70" s="68" t="n"/>
       <c r="D70" s="69" t="inlineStr">
         <is>
-          <t>Se devenga al ACEPTAR, no al terminar, y por evento.</t>
+          <t>Nace payout_earnings: que devengos paga cada pago.</t>
         </is>
       </c>
       <c r="E70" s="69" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F70" s="69" t="inlineStr">
         <is>
-          <t>Al aceptar es cuando existe la deuda: 7.5 congela el agreed_amount en ese instante y BR-CREATOR-008 impide cambiarlo despues sin una enmienda firmada por las dos partes. Que todavia no se le pueda pagar es otra cosa y vive en el estado --accrued significa exactamente «se le debe y aun no se le puede pagar»--. Devengar al terminar habria dejado el trabajo hecho y el compromiso invisible hasta el final, que es como una campana se cierra sin que nadie sepa cuanto costo mientras corria. Va por evento y no por llamada directa por lo mismo que 8.1: deptrac no deja que Campaign conozca a Finance, y esta bien que no lo haga --si anotar el asiento falla, la aceptacion sigue siendo cierta, y el creador ya pulso «acepto»--. Y dos finales NO son fallos: que ya hubiera devengo --uq_ledger_devengo funcionando-- y que la colaboracion sea un canje. Si los tres se escribieran igual, el log diria que algo fallo cada vez que alguien acepta un canje, y a la tercera nadie lo lee</t>
+          <t>ledger_entries.payout_id ataba UN asiento de pago a su payout (BR-FIN-013), pero el detalle --que devengos liquida-- no existia. Sin el, «.de que campanas es este dinero?» no tiene respuesta, y sin respuesta no hay nada que comparar con la sociedad del lote, que es lo que DEC-157 mando cerrar aqui. Con el detalle, BR-LE-009 se vuelve una consulta de tres saltos que cabe en tg_pe_sociedad. Se comprueba al enganchar el devengo al pago y no al aprobar el lote: aprobar es una firma sobre algo que ya tiene que estar bien, y una regla que solo mira al final deja existir el estado malo mientras tanto --que es como alguien lo ve, lo exporta, o lo cree--. Vigesimoseptima columna puerta: uq_pe_viva, un devengo en una sola liquidacion VIVA</t>
         </is>
       </c>
     </row>
     <row r="71" ht="45.75" customHeight="1" s="36">
       <c r="A71" s="67" t="inlineStr">
         <is>
-          <t>DEC-169</t>
+          <t>DEC-173</t>
         </is>
       </c>
       <c r="B71" s="68" t="inlineStr">
@@ -17030,24 +17080,24 @@
       <c r="C71" s="68" t="n"/>
       <c r="D71" s="69" t="inlineStr">
         <is>
-          <t>El estado de un asiento tiene un grafo, y moverlo exige decir por que.</t>
+          <t>La fecha de cobro se ensena SOLO cuando el asiento ya es pagable.</t>
         </is>
       </c>
       <c r="E71" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="F71" s="69" t="inlineStr">
         <is>
-          <t>tg_ledger_no_update es columna por columna y deja pasar status a proposito --sin eso la tabla no serviria-- pero de ahi no salia QUE transicion es valida: un paid podia volver a accrued, o sea dinero ya pagado reapareciendo como deuda. Es tg_del_rondas de 8.4 otra vez. paid y void son terminales: un pago que se deshace se corrige con un asiento de payment_reversal, no cambiando este estado. Y toda transicion exige status_reason: sin ella, «.por que este creador no cobro?» se contesta mirando la fecha y adivinando. A la bitacora solo va lo que decide una persona --las automaticas son miles y taparian justo lo que se busca ahi--; el rastro completo vive en status_transitions. Ademas nace uq_ledger_devengo, vigesimosexta columna puerta: un devengo por participacion, que BR-FIN-015 daba por hecho sin decirlo</t>
+          <t>BR-FIN-012 dice que el plazo son 30 dias desde la verificacion y que es visible desde que acepta: lo visible desde que acepta es el plazo, y una FECHA es otra cosa que se lee muy distinto. Mientras el asiento esta devengado se ensena que falta --las cinco condiciones de BR-FIN-003, con sus palabras--, que es accionable: un creador puede hacer algo con «no tienes ningun medio de pago verificado» y no puede hacer nada con una fecha que depende de trabajo que aun no ha hecho. Y si esa fecha se corriera, la culpa pareceria nuestra. La cuenta arranca en la ultima verificacion de sus publicaciones, y si no hay ninguna --un formato que no exige post-- en la fecha en que se completo la participacion</t>
         </is>
       </c>
     </row>
     <row r="72" ht="79.5" customHeight="1" s="36">
       <c r="A72" s="67" t="inlineStr">
         <is>
-          <t>DEC-168</t>
+          <t>DEC-172</t>
         </is>
       </c>
       <c r="B72" s="68" t="inlineStr">
@@ -17058,24 +17108,24 @@
       <c r="C72" s="68" t="n"/>
       <c r="D72" s="69" t="inlineStr">
         <is>
-          <t>El asiento va en la moneda PACTADA; se convierte al pagar.</t>
+          <t>El motivo interno de una retencion NO se le ensena al creador.</t>
         </is>
       </c>
       <c r="E72" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="F72" s="69" t="inlineStr">
         <is>
-          <t>Se escribe con el agreed_amount y la moneda congelados al aceptar en 7.5: se le debe lo que se le prometio, en la moneda en que se le prometio. La conversion ocurre al armar el pago, con la tasa de ESE dia, y se congela en el asiento de pago (BR-FIN-009). Convertir al devengar habria dejado el saldo del creador en una sola moneda --mas facil de leer-- fijando el tipo de cambio meses antes de pagar: si el dolar sube, el creador cobra menos de lo pactado o nosotros pagamos mas, sin que nadie lo haya decidido</t>
+          <t>Lo escribe el equipo para el expediente y puede nombrar personas o sospechas todavia sin confirmar; un texto redactado deprisa --«parece que lo borro a proposito»-- leido sin contexto es una acusacion de la que no se vuelve. El creador ve «En revision -- te escribimos» y, desde 8.8, recibe un correo donde se le explica de verdad. Las palabras del portal tampoco son las del back-office: on_hold es «en revision» y no «retenido», porque la palabra interna describe lo que hace el sistema y la del portal tiene que describir lo que le pasa a el. La frontera vive en Ledger::misIngresos(), que enumera columnas --el mismo sitio que Aprobaciones::pieza() en 8.5--: devolver la fila entera y confiar en que la plantilla no imprima de mas es confiar en la plantilla de manana. Tampoco cruzan los asientos anulados: no le afectan y no sabe leerlos</t>
         </is>
       </c>
     </row>
     <row r="73" ht="68.25" customHeight="1" s="36">
       <c r="A73" s="67" t="inlineStr">
         <is>
-          <t>DEC-167</t>
+          <t>DEC-171</t>
         </is>
       </c>
       <c r="B73" s="68" t="inlineStr">
@@ -17086,24 +17136,24 @@
       <c r="C73" s="68" t="n"/>
       <c r="D73" s="69" t="inlineStr">
         <is>
-          <t>Un post caido RETIENE el asiento; no lo anula.</t>
+          <t>El barrido rescata las aceptaciones sin devengo, y avisa de que hubo que rescatarlas.</t>
         </is>
       </c>
       <c r="E73" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F73" s="69" t="inlineStr">
         <is>
-          <t>8.8 ya lo decidio para el contenido --«el sistema no descuenta nada; la decision de que se le paga la toma una persona con el expediente montado»-- y aqui es lo mismo aplicado al dinero: on_hold saca el asiento de la cola de pago y espera. Reversible: si el creador repone el post, vuelve a payable. Anularlo con una reversion habria sido contablemente mas limpio y habria decidido por su cuenta que no se le paga, que es justo lo que DEC-145 prohibe. Y un asiento retenido no cuenta como saldo: meterlo seria prometerle al creador algo que todavia no esta decidido</t>
+          <t>Un listener puede fallar, y si falla el creador queda aceptado y su dinero invisible; ademas las participaciones aceptadas antes de 9.4 nunca pasaron por el. ledger:revisar las anota antes de revisar --para que un devengo recuperado hoy pueda pasar a pagable hoy y no manana-- y lo dice en amarillo: que la lista no salga en cero es la noticia, no el arreglo. Es la misma red que 8.1 dejo para los entregables. Las gratuitas quedan fuera de esa lista a proposito: si no, el barrido intentaria lo imposible todos los dias y avisaria todos los dias de algo que esta bien</t>
         </is>
       </c>
     </row>
     <row r="74" ht="68.25" customHeight="1" s="36">
       <c r="A74" s="67" t="inlineStr">
         <is>
-          <t>DEC-166</t>
+          <t>DEC-170</t>
         </is>
       </c>
       <c r="B74" s="68" t="inlineStr">
@@ -17114,24 +17164,24 @@
       <c r="C74" s="68" t="n"/>
       <c r="D74" s="69" t="inlineStr">
         <is>
-          <t>Pasar un devengo a pagable lo hace el SISTEMA, no una persona.</t>
+          <t>Se devenga al ACEPTAR, no al terminar, y por evento.</t>
         </is>
       </c>
       <c r="E74" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F74" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-003 pide cinco cosas --participacion completada, contenido aprobado, publicacion verificada si aplica, documento tributario valido y medio de pago verificado-- y las cinco ya las firmo alguien una por una: quien verifico la publicacion, quien aprobo el perfil fiscal, quien verifico la cuenta. Una sexta firma que solo dice «si, se cumplen las cinco» es un boton que alguien acaba pulsando sin mirar, y una cola que retrasa pagos por acumulacion y no por duda. Ledger::requisitos() devuelve las cinco con su veredicto y no la primera que falla, porque quien mira por que un creador no cobra necesita la lista entera. El «si aplica» de la publicacion se implementa contando: si ningun entregable tiene publicacion el requisito se da por cumplido --un formato que no exige post no puede bloquear un pago para siempre--</t>
+          <t>Al aceptar es cuando existe la deuda: 7.5 congela el agreed_amount en ese instante y BR-CREATOR-008 impide cambiarlo despues sin una enmienda firmada por las dos partes. Que todavia no se le pueda pagar es otra cosa y vive en el estado --accrued significa exactamente «se le debe y aun no se le puede pagar»--. Devengar al terminar habria dejado el trabajo hecho y el compromiso invisible hasta el final, que es como una campana se cierra sin que nadie sepa cuanto costo mientras corria. Va por evento y no por llamada directa por lo mismo que 8.1: deptrac no deja que Campaign conozca a Finance, y esta bien que no lo haga --si anotar el asiento falla, la aceptacion sigue siendo cierta, y el creador ya pulso «acepto»--. Y dos finales NO son fallos: que ya hubiera devengo --uq_ledger_devengo funcionando-- y que la colaboracion sea un canje. Si los tres se escribieran igual, el log diria que algo fallo cada vez que alguien acepta un canje, y a la tercera nadie lo lee</t>
         </is>
       </c>
     </row>
     <row r="75" ht="57" customHeight="1" s="36">
       <c r="A75" s="67" t="inlineStr">
         <is>
-          <t>DEC-165</t>
+          <t>DEC-169</t>
         </is>
       </c>
       <c r="B75" s="68" t="inlineStr">
@@ -17142,24 +17192,24 @@
       <c r="C75" s="68" t="n"/>
       <c r="D75" s="69" t="inlineStr">
         <is>
-          <t>Decolecta trae USD → PEN y nada mas, y el sistema lo dice en vez de disimularlo.</t>
+          <t>El estado de un asiento tiene un grafo, y moverlo exige decir por que.</t>
         </is>
       </c>
       <c r="E75" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F75" s="69" t="inlineStr">
         <is>
-          <t>Publica el tipo de cambio de SUNAT, y SUNAT solo publica el dolar. Por eso Decolecta no acepta un par como parametro --sabe traer lo unico que su fuente publica, y decirlo es mas honesto que aceptar COP y fallar raro--; el catalogo declara USD → PEN = sunat y ningun otro par, porque declarar una fuente que no publica es peor que no tener ninguna; la pantalla tiene carga manual con fuente manual y no disfrazada de sunat, que es lo que permite distinguir despues que se trajo y que se tecleo; y lo dice en la propia pantalla, para que «no llega la tasa del peso mexicano» no se diagnostique como un cron roto. Que fuente se usa para los demas pares queda como Q-64</t>
+          <t>tg_ledger_no_update es columna por columna y deja pasar status a proposito --sin eso la tabla no serviria-- pero de ahi no salia QUE transicion es valida: un paid podia volver a accrued, o sea dinero ya pagado reapareciendo como deuda. Es tg_del_rondas de 8.4 otra vez. paid y void son terminales: un pago que se deshace se corrige con un asiento de payment_reversal, no cambiando este estado. Y toda transicion exige status_reason: sin ella, «.por que este creador no cobro?» se contesta mirando la fecha y adivinando. A la bitacora solo va lo que decide una persona --las automaticas son miles y taparian justo lo que se busca ahi--; el rastro completo vive en status_transitions. Ademas nace uq_ledger_devengo, vigesimosexta columna puerta: un devengo por participacion, que BR-FIN-015 daba por hecho sin decirlo</t>
         </is>
       </c>
     </row>
     <row r="76" ht="45.75" customHeight="1" s="36">
       <c r="A76" s="67" t="inlineStr">
         <is>
-          <t>DEC-164</t>
+          <t>DEC-168</t>
         </is>
       </c>
       <c r="B76" s="68" t="inlineStr">
@@ -17170,24 +17220,24 @@
       <c r="C76" s="68" t="n"/>
       <c r="D76" s="69" t="inlineStr">
         <is>
-          <t>El cron deja rastro de cada intento, y pide TRES dias.</t>
+          <t>El asiento va en la moneda PACTADA; se convierte al pagar.</t>
         </is>
       </c>
       <c r="E76" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F76" s="69" t="inlineStr">
         <is>
-          <t>fx_fetch_runs. Cambio::DIAS_ATRAS detecta que las tasas dejaron de llegar cuando alguien va a convertir, o sea el dia de la liquidacion; esto lo ensena antes, y la pantalla lo resume arriba solo si hay algo que mirar --una pantalla que siempre tiene un aviso es una pantalla cuyos avisos nadie lee--. ck_ffr_nuevas obliga a que una corrida fallida diga cero, porque el registro que contesta «.sigue vivo el cron?» no puede afirmar que una corrida con error trajo tres tasas. Tres dias y no uno: si no corrio viernes ni sabado, pedir solo el domingo deja dos huecos que nadie rellena a mano, y repetir un dia no cuesta una fila --uq_fx_rate-- sino una peticion. Y termina en 0 aunque un dia falle: un cron que da error a diario hace ruido donde nadie mira; solo falla si NINGUN dia se pudo traer</t>
+          <t>Se escribe con el agreed_amount y la moneda congelados al aceptar en 7.5: se le debe lo que se le prometio, en la moneda en que se le prometio. La conversion ocurre al armar el pago, con la tasa de ESE dia, y se congela en el asiento de pago (BR-FIN-009). Convertir al devengar habria dejado el saldo del creador en una sola moneda --mas facil de leer-- fijando el tipo de cambio meses antes de pagar: si el dolar sube, el creador cobra menos de lo pactado o nosotros pagamos mas, sin que nadie lo haya decidido</t>
         </is>
       </c>
     </row>
     <row r="77" ht="68.25" customHeight="1" s="36">
       <c r="A77" s="67" t="inlineStr">
         <is>
-          <t>DEC-163</t>
+          <t>DEC-167</t>
         </is>
       </c>
       <c r="B77" s="68" t="inlineStr">
@@ -17198,24 +17248,24 @@
       <c r="C77" s="68" t="n"/>
       <c r="D77" s="69" t="inlineStr">
         <is>
-          <t>Cada final de la traida tiene su nombre, y traer() no lanza.</t>
+          <t>Un post caido RETIENE el asiento; no lo anula.</t>
         </is>
       </c>
       <c r="E77" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F77" s="69" t="inlineStr">
         <is>
-          <t>ok, sin_credencial, error_http, error_red, respuesta_rara. En un catch generico los cinco se ven iguales y exigen cinco arreglos distintos: «no hay clave» se arregla configurandola, «401» rotandola, «200 con un cuerpo raro» mirando la API. Un 404 --dia sin publicar-- ni siquiera se pinta como averia: quien lee la salida del cron todos los dias deja de leerla si le grita por lo normal. Y una respuesta que no se entiende no anota nada: una tasa inventada entraria en una tabla que tg_fx_inmutable no deja corregir</t>
+          <t>8.8 ya lo decidio para el contenido --«el sistema no descuenta nada; la decision de que se le paga la toma una persona con el expediente montado»-- y aqui es lo mismo aplicado al dinero: on_hold saca el asiento de la cola de pago y espera. Reversible: si el creador repone el post, vuelve a payable. Anularlo con una reversion habria sido contablemente mas limpio y habria decidido por su cuenta que no se le paga, que es justo lo que DEC-145 prohibe. Y un asiento retenido no cuenta como saldo: meterlo seria prometerle al creador algo que todavia no esta decidido</t>
         </is>
       </c>
     </row>
     <row r="78" ht="57" customHeight="1" s="36">
       <c r="A78" s="67" t="inlineStr">
         <is>
-          <t>DEC-162</t>
+          <t>DEC-166</t>
         </is>
       </c>
       <c r="B78" s="68" t="inlineStr">
@@ -17226,24 +17276,24 @@
       <c r="C78" s="68" t="n"/>
       <c r="D78" s="69" t="inlineStr">
         <is>
-          <t>La credencial se configura desde la pantalla, pero el ENTORNO manda y en la base va CIFRADA.</t>
+          <t>Pasar un devengo a pagable lo hace el SISTEMA, no una persona.</t>
         </is>
       </c>
       <c r="E78" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F78" s="69" t="inlineStr">
         <is>
-          <t>La peticion era «la configurare en la pantalla del admin». Se hace, con dos condiciones que salen de la regla de seguridad del propio proyecto --«no almacenar secretos en texto plano en BD cuando exista alternativa segura»--: si hay DECOLECTA_API_KEY en el entorno se usa esa y la de la base ni se mira --no viaja por el navegador, no esta en ninguna tabla, no sale en un volcado--; y si no la hay, se guarda con Crypt, la misma maquina que cifra las cuentas bancarias desde 3.8. La clave no se reensena jamas, ni al que la escribio un minuto antes: la pantalla dice «termina en 8f2a» y de donde sale. La bitacora anota que cambio y los cuatro ultimos, nunca el valor. Y tg_fxs_credencial_firmada exige quien la puso, cuando y la pista, las tres o ninguna: media firma es peor que ninguna porque parece que «quien la puso» tiene respuesta. El permiso va aparte: la pantalla es fx.manage --la tiene finanzas-- y la credencial es integration.manage --solo admin--, porque una clave de un tercero es un permiso de gasto y no la necesita quien anota una tasa un lunes</t>
+          <t>BR-FIN-003 pide cinco cosas --participacion completada, contenido aprobado, publicacion verificada si aplica, documento tributario valido y medio de pago verificado-- y las cinco ya las firmo alguien una por una: quien verifico la publicacion, quien aprobo el perfil fiscal, quien verifico la cuenta. Una sexta firma que solo dice «si, se cumplen las cinco» es un boton que alguien acaba pulsando sin mirar, y una cola que retrasa pagos por acumulacion y no por duda. Ledger::requisitos() devuelve las cinco con su veredicto y no la primera que falla, porque quien mira por que un creador no cobra necesita la lista entera. El «si aplica» de la publicacion se implementa contando: si ningun entregable tiene publicacion el requisito se da por cumplido --un formato que no exige post no puede bloquear un pago para siempre--</t>
         </is>
       </c>
     </row>
     <row r="79" ht="57" customHeight="1" s="36">
       <c r="A79" s="67" t="inlineStr">
         <is>
-          <t>DEC-161</t>
+          <t>DEC-165</t>
         </is>
       </c>
       <c r="B79" s="68" t="inlineStr">
@@ -17254,24 +17304,24 @@
       <c r="C79" s="68" t="n"/>
       <c r="D79" s="69" t="inlineStr">
         <is>
-          <t>porque() admite alternancia, y eso es lo que faltaba para bajar el trinquete de las 297.</t>
+          <t>Decolecta trae USD → PEN y nada mas, y el sistema lo dice en vez de disimularlo.</t>
         </is>
       </c>
       <c r="E79" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F79" s="69" t="inlineStr">
         <is>
-          <t>Los dos motores contestan cosas distintas a la MISMA regla cuando la creo Restriccion: MariaDB dice «CONSTRAINT ck_fos_dates failed» y Percona dice el mensaje. El nombre sale en uno y el mensaje en el otro, y no coinciden en ningun texto, asi que toda regla de Restriccion tenia que quedarse en un probar ... RECHAZO a secas. Con grep -qE, porque ... 'ck_fos_dates|antes de empezar' afirma el motivo en los dos motores. DEC-154 puso el trinquete y conto 297; esto es la herramienta para bajarlo</t>
+          <t>Publica el tipo de cambio de SUNAT, y SUNAT solo publica el dolar. Por eso Decolecta no acepta un par como parametro --sabe traer lo unico que su fuente publica, y decirlo es mas honesto que aceptar COP y fallar raro--; el catalogo declara USD → PEN = sunat y ningun otro par, porque declarar una fuente que no publica es peor que no tener ninguna; la pantalla tiene carga manual con fuente manual y no disfrazada de sunat, que es lo que permite distinguir despues que se trajo y que se tecleo; y lo dice en la propia pantalla, para que «no llega la tasa del peso mexicano» no se diagnostique como un cron roto. Que fuente se usa para los demas pares queda como Q-64</t>
         </is>
       </c>
     </row>
     <row r="80" ht="68.25" customHeight="1" s="36">
       <c r="A80" s="67" t="inlineStr">
         <is>
-          <t>DEC-160</t>
+          <t>DEC-164</t>
         </is>
       </c>
       <c r="B80" s="68" t="inlineStr">
@@ -17282,24 +17332,24 @@
       <c r="C80" s="68" t="n"/>
       <c r="D80" s="69" t="inlineStr">
         <is>
-          <t>Un dia sin tasa usa la ultima anterior, y lo que se guarda es la fecha de ESA tasa.</t>
+          <t>El cron deja rastro de cada intento, y pide TRES dias.</t>
         </is>
       </c>
       <c r="E80" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F80" s="69" t="inlineStr">
         <is>
-          <t>Sabados, domingos y feriados no tienen tipo publicado. Se convierte con la del viernes y el asiento dice «tasa del viernes», no «tasa del domingo»: guardar la fecha de la operacion habria sido mas comodo de leer y habria hecho que el historico afirmara que ese domingo hubo una tasa que nunca existio (BR-FIN-009). Es un supuesto fiscal y esta marcado como tal (§56): que la practica peruana sea el ultimo tipo publicado lo confirma el contador. Y hay un corte de 10 dias, porque «la ultima anterior» tapa una averia: si lo ultimo es de hace tres semanas no fue un feriado, es que el cron dejo de traerlas, y sin ese corte una tabla congelada se ve igual que una sana hasta el dia de la liquidacion</t>
+          <t>fx_fetch_runs. Cambio::DIAS_ATRAS detecta que las tasas dejaron de llegar cuando alguien va a convertir, o sea el dia de la liquidacion; esto lo ensena antes, y la pantalla lo resume arriba solo si hay algo que mirar --una pantalla que siempre tiene un aviso es una pantalla cuyos avisos nadie lee--. ck_ffr_nuevas obliga a que una corrida fallida diga cero, porque el registro que contesta «.sigue vivo el cron?» no puede afirmar que una corrida con error trajo tres tasas. Tres dias y no uno: si no corrio viernes ni sabado, pedir solo el domingo deja dos huecos que nadie rellena a mano, y repetir un dia no cuesta una fila --uq_fx_rate-- sino una peticion. Y termina en 0 aunque un dia falle: un cron que da error a diario hace ruido donde nadie mira; solo falla si NINGUN dia se pudo traer</t>
         </is>
       </c>
     </row>
     <row r="81" ht="68.25" customHeight="1" s="36">
       <c r="A81" s="67" t="inlineStr">
         <is>
-          <t>DEC-159</t>
+          <t>DEC-163</t>
         </is>
       </c>
       <c r="B81" s="68" t="inlineStr">
@@ -17310,24 +17360,24 @@
       <c r="C81" s="68" t="n"/>
       <c r="D81" s="69" t="inlineStr">
         <is>
-          <t>Compra y venta son dos filas, y cual aplica NO tiene valor por defecto.</t>
+          <t>Cada final de la traida tiene su nombre, y traer() no lanza.</t>
         </is>
       </c>
       <c r="E81" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F81" s="69" t="inlineStr">
         <is>
-          <t>SUNAT publica las dos el mismo dia y no son intercambiables. Con una sola columna rate solo cabe una, y elegir cual guardar habria sido tomar por mi cuenta una decision contable en el sitio donde menos se ve. side entra en la clave, asi que las dos caben sin pisarse. Y Cambio::tasa() exige el lado como parametro sin defecto: un defecto aqui es exactamente la forma en que una decision fiscal se toma sola. Queda Q-63 para el contador, y por eso el buscador de creadores sigue sin convertir aunque la maquina ya exista</t>
+          <t>ok, sin_credencial, error_http, error_red, respuesta_rara. En un catch generico los cinco se ven iguales y exigen cinco arreglos distintos: «no hay clave» se arregla configurandola, «401» rotandola, «200 con un cuerpo raro» mirando la API. Un 404 --dia sin publicar-- ni siquiera se pinta como averia: quien lee la salida del cron todos los dias deja de leerla si le grita por lo normal. Y una respuesta que no se entiende no anota nada: una tasa inventada entraria en una tabla que tg_fx_inmutable no deja corregir</t>
         </is>
       </c>
     </row>
     <row r="82" ht="45.75" customHeight="1" s="36">
       <c r="A82" s="67" t="inlineStr">
         <is>
-          <t>DEC-158</t>
+          <t>DEC-162</t>
         </is>
       </c>
       <c r="B82" s="68" t="inlineStr">
@@ -17338,24 +17388,24 @@
       <c r="C82" s="68" t="n"/>
       <c r="D82" s="69" t="inlineStr">
         <is>
-          <t>Que fuente publica el tipo de cambio se DECLARA, con periodos, y no se elige al convertir.</t>
+          <t>La credencial se configura desde la pantalla, pero el ENTORNO manda y en la base va CIFRADA.</t>
         </is>
       </c>
       <c r="E82" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F82" s="69" t="inlineStr">
         <is>
-          <t>uq_exchange_rates incluia source a proposito --dos fuentes pueden discrepar el mismo dia y BR-FIN-009 exige poder decir de cual salio la que se aplico-- pero de ahi no salia CUAL SE APLICA. Es el estado EMPATE de CoberturaFacturacion, el que una vez produjo una factura emitida por la sociedad equivocada, y la respuesta es la misma que entonces: uq_fos_current garantiza una sola fuente VIGENTE por par, y fos_sin_solape una sola POR FECHA --que es la mitad que se olvida, porque convertir un importe de marzo resuelve por par Y por fecha--. Con periodos y no con una columna porque el historico tiene que seguir explicandose con quien mandaba entonces: si fuera una columna, cambiar de proveedor reescribiria como se convirtio todo lo anterior</t>
+          <t>La peticion era «la configurare en la pantalla del admin». Se hace, con dos condiciones que salen de la regla de seguridad del propio proyecto --«no almacenar secretos en texto plano en BD cuando exista alternativa segura»--: si hay DECOLECTA_API_KEY en el entorno se usa esa y la de la base ni se mira --no viaja por el navegador, no esta en ninguna tabla, no sale en un volcado--; y si no la hay, se guarda con Crypt, la misma maquina que cifra las cuentas bancarias desde 3.8. La clave no se reensena jamas, ni al que la escribio un minuto antes: la pantalla dice «termina en 8f2a» y de donde sale. La bitacora anota que cambio y los cuatro ultimos, nunca el valor. Y tg_fxs_credencial_firmada exige quien la puso, cuando y la pista, las tres o ninguna: media firma es peor que ninguna porque parece que «quien la puso» tiene respuesta. El permiso va aparte: la pantalla es fx.manage --la tiene finanzas-- y la credencial es integration.manage --solo admin--, porque una clave de un tercero es un permiso de gasto y no la necesita quien anota una tasa un lunes</t>
         </is>
       </c>
     </row>
     <row r="83" ht="68.25" customHeight="1" s="36">
       <c r="A83" s="67" t="inlineStr">
         <is>
-          <t>DEC-157</t>
+          <t>DEC-161</t>
         </is>
       </c>
       <c r="B83" s="68" t="inlineStr">
@@ -17366,24 +17416,24 @@
       <c r="C83" s="68" t="n"/>
       <c r="D83" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-009 se comprueba cuando se escribe el primer pago, no en la iteracion 9.11.</t>
+          <t>porque() admite alternancia, y eso es lo que faltaba para bajar el trinquete de las 297.</t>
         </is>
       </c>
       <c r="E83" s="69" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F83" s="69" t="inlineStr">
         <is>
-          <t>El roadmap tenia la validacion de «la sociedad que factura y la que liquida son la misma» como iteracion 11 de 14 de la fase de finanzas. Una regla 🔴 que llega la penultima llega despues de que diez iteraciones se hayan construido dandola por buena, y es exactamente la forma de fallo de 8.4: el techo de rondas existia entero en PHP desde 8.3 y nada lo respaldaba en la base. Aqui es peor, porque lo que se cuela no es una ronda: es dinero saliendo de la sociedad equivocada, que es una operacion intercompania no documentada. Pasa a ser requisito de la iteracion que estrene payout_batches, y en la base: un lote nombra su sociedad y sus asientos nombran sus campanas, asi que la comprobacion es cross-table y le toca a un disparador, no a un CHECK. Y con esto DEC-020 deja de ser PROPUESTA: preguntaba si permitir que la entidad que factura y la que liquida divergieran, y recomendaba modelar la separacion y bloquearla en el MVP. DEC-156 lo contesta y ademas le quita el «en el MVP»</t>
+          <t>Los dos motores contestan cosas distintas a la MISMA regla cuando la creo Restriccion: MariaDB dice «CONSTRAINT ck_fos_dates failed» y Percona dice el mensaje. El nombre sale en uno y el mensaje en el otro, y no coinciden en ningun texto, asi que toda regla de Restriccion tenia que quedarse en un probar ... RECHAZO a secas. Con grep -qE, porque ... 'ck_fos_dates|antes de empezar' afirma el motivo en los dos motores. DEC-154 puso el trinquete y conto 297; esto es la herramienta para bajarlo</t>
         </is>
       </c>
     </row>
     <row r="84" ht="57" customHeight="1" s="36">
       <c r="A84" s="67" t="inlineStr">
         <is>
-          <t>DEC-156</t>
+          <t>DEC-160</t>
         </is>
       </c>
       <c r="B84" s="68" t="inlineStr">
@@ -17394,24 +17444,24 @@
       <c r="C84" s="68" t="n"/>
       <c r="D84" s="69" t="inlineStr">
         <is>
-          <t>La campana decide quien paga a cada creador, y el pais del creador no entra en esa decision.</t>
+          <t>Un dia sin tasa usa la ultima anterior, y lo que se guarda es la fecha de ESA tasa.</t>
         </is>
       </c>
       <c r="E84" s="69" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F84" s="69" t="inlineStr">
         <is>
-          <t>Un creador colombiano en una campana de CTS Peru cobra de CTS Peru. La sociedad sale del pais del CLIENTE, se guarda en la campana y el pago la hereda de ahi, congelada al confirmar igual que agreed_amount; lo implementa F9. [Corregido el 2026-08-27, T-59: la version original de esta entrada decia que «payouts no tiene ninguna columna de sociedad» y eso es falso. payout_batches.legal_entity_id existe desde la migracion de finanzas y el pago la hereda de su lote. Lo que NO existe es la garantia de que sea la correcta: nada ata el lote a las campanas cuyos asientos liquida, asi que hoy un lote de CTS Colombia podria pagar el trabajo de una campana de CTS Peru y ninguna restriccion lo notaria.] Esto no inventa la regla: BR-LE-009 ya la decia, con «en el MVP» delante y en naranja. Se le quita el «en el MVP» y sube a 🔴, porque no es una simplificacion temporal sino como funciona el grupo. La alternativa --que pagara la sociedad del pais del creador-- parte una campana en dos contabilidades, obliga a que el margen de una campana se calcule entre sociedades y exige cobertura en el pais de cada creador antes de poder invitarlo: hoy Espana no tiene sociedad y con esa alternativa un creador espanol seria ininvitable. Y cambia el eje de Q-40: la retencion depende de quien paga Y de donde esta el creador, no solo de lo segundo, asi que la tabla del contador pasa a ser «CTS Peru pagando a un creador de cada pais» y CTS Colombia tiene la suya, para un contador colombiano</t>
+          <t>Sabados, domingos y feriados no tienen tipo publicado. Se convierte con la del viernes y el asiento dice «tasa del viernes», no «tasa del domingo»: guardar la fecha de la operacion habria sido mas comodo de leer y habria hecho que el historico afirmara que ese domingo hubo una tasa que nunca existio (BR-FIN-009). Es un supuesto fiscal y esta marcado como tal (§56): que la practica peruana sea el ultimo tipo publicado lo confirma el contador. Y hay un corte de 10 dias, porque «la ultima anterior» tapa una averia: si lo ultimo es de hace tres semanas no fue un feriado, es que el cron dejo de traerlas, y sin ese corte una tabla congelada se ve igual que una sana hasta el dia de la liquidacion</t>
         </is>
       </c>
     </row>
     <row r="85" ht="57" customHeight="1" s="36">
       <c r="A85" s="67" t="inlineStr">
         <is>
-          <t>DEC-155</t>
+          <t>DEC-159</t>
         </is>
       </c>
       <c r="B85" s="68" t="inlineStr">
@@ -17422,24 +17472,24 @@
       <c r="C85" s="68" t="n"/>
       <c r="D85" s="69" t="inlineStr">
         <is>
-          <t>La sociedad que factura NO se elige: se resuelve, y la pantalla enseña por que.</t>
+          <t>Compra y venta son dos filas, y cual aplica NO tiene valor por defecto.</t>
         </is>
       </c>
       <c r="E85" s="69" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F85" s="69" t="inlineStr">
         <is>
-          <t>El planteamiento era poner un desplegable «CTS Peru / CTS Colombia» en la campana. No se hace, y el motivo esta en el esquema: uq_lec_country mas tg_lec_sin_solape_ins/upd garantizan que en cualquier fecha hay como mucho una sociedad cubriendo un pais, asi que el desplegable tendria siempre una opcion --y una opcion que se puede cambiar es una que alguien puede cambiar mal--. Ya existia campaigns.billing_legal_entity_id, resuelto a starts_on por Campanas::quienFactura() y congelado al confirmar por tg_camp_entidad_congelada. Lo que faltaba no era el campo: era decirlo. La ficha ahora dice quien factura Y su motivo --«CTS Peru factura a Peru desde el 2025-01-01 (sociedad local)»--, porque una sociedad a secas no se puede comprobar y con su motivo y su fecha quien la lee sabe si es la que esperaba y puede discutirla antes de que salga una factura. El formulario de alta no adelanta una respuesta: el pais del cliente y la fecha todavia no existen, y resolver «con la cobertura de hoy» para ensenarlo es justo el «deducirlo de la configuracion vigente» que prohibe BR-LE-001</t>
+          <t>SUNAT publica las dos el mismo dia y no son intercambiables. Con una sola columna rate solo cabe una, y elegir cual guardar habria sido tomar por mi cuenta una decision contable en el sitio donde menos se ve. side entra en la clave, asi que las dos caben sin pisarse. Y Cambio::tasa() exige el lado como parametro sin defecto: un defecto aqui es exactamente la forma en que una decision fiscal se toma sola. Queda Q-63 para el contador, y por eso el buscador de creadores sigue sin convertir aunque la maquina ya exista</t>
         </is>
       </c>
     </row>
     <row r="86" ht="57" customHeight="1" s="36">
       <c r="A86" s="67" t="inlineStr">
         <is>
-          <t>DEC-154</t>
+          <t>DEC-158</t>
         </is>
       </c>
       <c r="B86" s="68" t="inlineStr">
@@ -17450,24 +17500,24 @@
       <c r="C86" s="68" t="n"/>
       <c r="D86" s="69" t="inlineStr">
         <is>
-          <t>Los ayudantes de las suites viven en UN archivo, y nace la SEPTIMA puerta.</t>
+          <t>Que fuente publica el tipo de cambio se DECLARA, con periodos, y no se elige al convertir.</t>
         </is>
       </c>
       <c r="E86" s="69" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F86" s="69" t="inlineStr">
         <is>
-          <t>tools/pruebas/comun.sh y tools/verificar-suites.py. La puerta comprueba que toda suite listada existe, que ninguna define sus propios probar/valor/porque, que todas cargan comun.sh, y lleva un trinquete: cuantas aserciones negativas afirman POR QUE se rechaza y cuantas solo que algo fallo. Hoy son 89 con motivo y 297 sin el, y ese segundo numero solo puede bajar (tools/pruebas/MOTIVOS-BASE). No se convierten las 297 en esta iteracion --son veintidos suites de cuatro fases-- pero desde hoy no pueden ser 298, y ademas cada probar ... RECHAZO enseña en gris que restriccion respondio, para que el desajuste se vea al leer la salida. Es la leccion de T-48, T-50, T-51 y T-54: las cuatro fueron aserciones verdes por el motivo equivocado y las cuatro eran un probar ... RECHAZO a secas</t>
+          <t>uq_exchange_rates incluia source a proposito --dos fuentes pueden discrepar el mismo dia y BR-FIN-009 exige poder decir de cual salio la que se aplico-- pero de ahi no salia CUAL SE APLICA. Es el estado EMPATE de CoberturaFacturacion, el que una vez produjo una factura emitida por la sociedad equivocada, y la respuesta es la misma que entonces: uq_fos_current garantiza una sola fuente VIGENTE por par, y fos_sin_solape una sola POR FECHA --que es la mitad que se olvida, porque convertir un importe de marzo resuelve por par Y por fecha--. Con periodos y no con una columna porque el historico tiene que seguir explicandose con quien mandaba entonces: si fuera una columna, cambiar de proveedor reescribiria como se convirtio todo lo anterior</t>
         </is>
       </c>
     </row>
     <row r="87" ht="68.25" customHeight="1" s="36">
       <c r="A87" s="67" t="inlineStr">
         <is>
-          <t>DEC-153</t>
+          <t>DEC-157</t>
         </is>
       </c>
       <c r="B87" s="68" t="inlineStr">
@@ -17478,24 +17528,24 @@
       <c r="C87" s="68" t="n"/>
       <c r="D87" s="69" t="inlineStr">
         <is>
-          <t>Una peticion de cambios sin rondas queda PENDIENTE de autorizar.</t>
+          <t>BR-LE-009 se comprueba cuando se escribe el primer pago, no en la iteracion 9.11.</t>
         </is>
       </c>
       <c r="E87" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="F87" s="69" t="inlineStr">
         <is>
-          <t>Se registra y no se convierte en ronda hasta que alguien del equipo decida si se le cobra o la absorbemos; al cliente se le confirma que su peticion llego --que es verdad-- sin prometerle que sera gratis. Cae solo del modelo de DEC-151: como la respuesta no crea la revision, no hay ronda que consumir hasta que una persona emite el veredicto. Aprobaciones::pendientes() es la lista de lo que espera esa decision. La pantalla de gracias NO dice «lo corregimos»: decirlo seria prometer por su cuenta algo que todavia no esta decidido</t>
+          <t>El roadmap tenia la validacion de «la sociedad que factura y la que liquida son la misma» como iteracion 11 de 14 de la fase de finanzas. Una regla 🔴 que llega la penultima llega despues de que diez iteraciones se hayan construido dandola por buena, y es exactamente la forma de fallo de 8.4: el techo de rondas existia entero en PHP desde 8.3 y nada lo respaldaba en la base. Aqui es peor, porque lo que se cuela no es una ronda: es dinero saliendo de la sociedad equivocada, que es una operacion intercompania no documentada. Pasa a ser requisito de la iteracion que estrene payout_batches, y en la base: un lote nombra su sociedad y sus asientos nombran sus campanas, asi que la comprobacion es cross-table y le toca a un disparador, no a un CHECK. Y con esto DEC-020 deja de ser PROPUESTA: preguntaba si permitir que la entidad que factura y la que liquida divergieran, y recomendaba modelar la separacion y bloquearla en el MVP. DEC-156 lo contesta y ademas le quita el «en el MVP»</t>
         </is>
       </c>
     </row>
     <row r="88" ht="34.5" customHeight="1" s="36">
       <c r="A88" s="67" t="inlineStr">
         <is>
-          <t>DEC-152</t>
+          <t>DEC-156</t>
         </is>
       </c>
       <c r="B88" s="68" t="inlineStr">
@@ -17506,24 +17556,24 @@
       <c r="C88" s="68" t="n"/>
       <c r="D88" s="69" t="inlineStr">
         <is>
-          <t>El silencio del cliente no hace nada, y por eso 8.5 no estrena comando.</t>
+          <t>La campana decide quien paga a cada creador, y el pais del creador no entra en esa decision.</t>
         </is>
       </c>
       <c r="E88" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="F88" s="69" t="inlineStr">
         <is>
-          <t>El enlace caduca, la pieza se queda donde estaba y sale en la bandeja. Nadie aprueba ni rechaza en nombre de nadie. «Silencio = aprobado» habria desbloqueado la campana sin perseguir a nadie y necesita estar escrito en el contrato: dar por buena una pieza que nadie miro es una firma que el sistema pone por el cliente, y de ahi cuelgan la publicacion y el pago. Y de ahi sale que no haga falta un comando de caducidad, al reves que en 7.6: alli una invitacion sin contestar dejaba dinero comprometido y una plaza de cupo ocupada --habia un estado del mundo que corregir-- y aqui expires_at &lt; NOW() basta. Un comando que no arregla nada es una linea de cron mas que mantener y una cosa mas que puede fallar en silencio</t>
+          <t>Un creador colombiano en una campana de CTS Peru cobra de CTS Peru. La sociedad sale del pais del CLIENTE, se guarda en la campana y el pago la hereda de ahi, congelada al confirmar igual que agreed_amount; lo implementa F9. [Corregido el 2026-08-27, T-59: la version original de esta entrada decia que «payouts no tiene ninguna columna de sociedad» y eso es falso. payout_batches.legal_entity_id existe desde la migracion de finanzas y el pago la hereda de su lote. Lo que NO existe es la garantia de que sea la correcta: nada ata el lote a las campanas cuyos asientos liquida, asi que hoy un lote de CTS Colombia podria pagar el trabajo de una campana de CTS Peru y ninguna restriccion lo notaria.] Esto no inventa la regla: BR-LE-009 ya la decia, con «en el MVP» delante y en naranja. Se le quita el «en el MVP» y sube a 🔴, porque no es una simplificacion temporal sino como funciona el grupo. La alternativa --que pagara la sociedad del pais del creador-- parte una campana en dos contabilidades, obliga a que el margen de una campana se calcule entre sociedades y exige cobertura en el pais de cada creador antes de poder invitarlo: hoy Espana no tiene sociedad y con esa alternativa un creador espanol seria ininvitable. Y cambia el eje de Q-40: la retencion depende de quien paga Y de donde esta el creador, no solo de lo segundo, asi que la tabla del contador pasa a ser «CTS Peru pagando a un creador de cada pais» y CTS Colombia tiene la suya, para un contador colombiano</t>
         </is>
       </c>
     </row>
     <row r="89" ht="57" customHeight="1" s="36">
       <c r="A89" s="67" t="inlineStr">
         <is>
-          <t>DEC-151</t>
+          <t>DEC-155</t>
         </is>
       </c>
       <c r="B89" s="68" t="inlineStr">
@@ -17534,24 +17584,24 @@
       <c r="C89" s="68" t="n"/>
       <c r="D89" s="69" t="inlineStr">
         <is>
-          <t>La respuesta del cliente se REGISTRA; el equipo cierra.</t>
+          <t>La sociedad que factura NO se elige: se resuelve, y la pantalla enseña por que.</t>
         </is>
       </c>
       <c r="E89" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="F89" s="69" t="inlineStr">
         <is>
-          <t>El cliente dice «me vale» o «cambiad esto» desde un enlace firmado, y eso queda escrito con su hora y su IP --pero no mueve el entregable--. La alternativa era que su OK aprobara la pieza directamente, y se descarto por dos razones. (a) Habria obligado a partir approved en dos estados: hoy significa «listo para publicar» y 8.6 publica desde ahi, asi que sin un «aprobado interno, esperando al cliente» el mismo estado significaria dos cosas --el fallo de T-50--. (b) Y la que decide: la correccion del cliente gasta ronda, y desde 8.4 una ronda de mas exige firma y decision de facturacion. El cliente no puede firmar un cargo contra si mismo. Si su respuesta moviera la pieza sola, o se le cobraria sin que nadie lo autorizara, o habria que dejarle una puerta por la que las rondas no se cuentan. La pantalla se lo dice con esas palabras: quien pulsa «me vale» y no ve nada moverse tiene derecho a saber que pasa despues</t>
+          <t>El planteamiento era poner un desplegable «CTS Peru / CTS Colombia» en la campana. No se hace, y el motivo esta en el esquema: uq_lec_country mas tg_lec_sin_solape_ins/upd garantizan que en cualquier fecha hay como mucho una sociedad cubriendo un pais, asi que el desplegable tendria siempre una opcion --y una opcion que se puede cambiar es una que alguien puede cambiar mal--. Ya existia campaigns.billing_legal_entity_id, resuelto a starts_on por Campanas::quienFactura() y congelado al confirmar por tg_camp_entidad_congelada. Lo que faltaba no era el campo: era decirlo. La ficha ahora dice quien factura Y su motivo --«CTS Peru factura a Peru desde el 2025-01-01 (sociedad local)»--, porque una sociedad a secas no se puede comprobar y con su motivo y su fecha quien la lee sabe si es la que esperaba y puede discutirla antes de que salga una factura. El formulario de alta no adelanta una respuesta: el pais del cliente y la fecha todavia no existen, y resolver «con la cobertura de hoy» para ensenarlo es justo el «deducirlo de la configuracion vigente» que prohibe BR-LE-001</t>
         </is>
       </c>
     </row>
     <row r="90" ht="45.75" customHeight="1" s="36">
       <c r="A90" s="67" t="inlineStr">
         <is>
-          <t>DEC-150</t>
+          <t>DEC-154</t>
         </is>
       </c>
       <c r="B90" s="68" t="inlineStr">
@@ -17562,24 +17612,24 @@
       <c r="C90" s="68" t="n"/>
       <c r="D90" s="69" t="inlineStr">
         <is>
-          <t>El techo de rondas pasa a la base, y los disparadores siguen siendo GUARDAS.</t>
+          <t>Los ayudantes de las suites viven en UN archivo, y nace la SEPTIMA puerta.</t>
         </is>
       </c>
       <c r="E90" s="69" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="F90" s="69" t="inlineStr">
         <is>
-          <t>8.3 construyo el limite entero --rondas(), vetoParaRevisar(), content.extra_round, over_included, la cola con «quedan/incluidas»-- y lo dejo TODO en PHP. Tres reglas se estaban aplicando sin que nada las respaldara en el esquema: (a) ck_cvw_round no decia DE QUIEN era la correccion, asi que una revision nuestra podia gastarle una ronda al cliente --DEC-133 vivia solo en consumeRonda()--; (b) nada obligaba a over_included a decir la verdad, y esa columna es la que cargosPendientes() cuenta para facturar, o sea que una fila que miente ahi es una correccion que se trabaja y no se cobra; (c) el contador podia bajar, y bajarlo devuelve rondas ya gastadas sin la firma de nadie. tg_cvw_techo mira las DOS direcciones --agotadas sin declarar, y declarada sin estarlo-- y es cross-table, asi que un CHECK no puede verlo; lee el contador ANTES de que emitir() lo suba, que es el mismo valor con el que el servicio calculo su $exceso. Y no se hizo lo tentador: que el contador lo subiera un AFTER INSERT habria hecho imposible la desincronizacion, pero ninguno de los 504 disparadores de este esquema modifica una fila y un disparador que HACE cosas convierte el esquema en algo que actua a espaldas de quien lee el codigo. Habia fecha para esto: 8.5 escribe revisiones del cliente desde un enlace firmado, sin pasar por emitir()</t>
+          <t>tools/pruebas/comun.sh y tools/verificar-suites.py. La puerta comprueba que toda suite listada existe, que ninguna define sus propios probar/valor/porque, que todas cargan comun.sh, y lleva un trinquete: cuantas aserciones negativas afirman POR QUE se rechaza y cuantas solo que algo fallo. Hoy son 89 con motivo y 297 sin el, y ese segundo numero solo puede bajar (tools/pruebas/MOTIVOS-BASE). No se convierten las 297 en esta iteracion --son veintidos suites de cuatro fases-- pero desde hoy no pueden ser 298, y ademas cada probar ... RECHAZO enseña en gris que restriccion respondio, para que el desajuste se vea al leer la salida. Es la leccion de T-48, T-50, T-51 y T-54: las cuatro fueron aserciones verdes por el motivo equivocado y las cuatro eran un probar ... RECHAZO a secas</t>
         </is>
       </c>
     </row>
     <row r="91" ht="45.75" customHeight="1" s="36">
       <c r="A91" s="67" t="inlineStr">
         <is>
-          <t>DEC-149</t>
+          <t>DEC-153</t>
         </is>
       </c>
       <c r="B91" s="68" t="inlineStr">
@@ -17590,24 +17640,24 @@
       <c r="C91" s="68" t="n"/>
       <c r="D91" s="69" t="inlineStr">
         <is>
-          <t>Se trabaja en main hasta que haya produccion.</t>
+          <t>Una peticion de cambios sin rondas queda PENDIENTE de autorizar.</t>
         </is>
       </c>
       <c r="E91" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F91" s="69" t="inlineStr">
         <is>
-          <t>La pregunta fue suya y era la correcta: *«no entiendo el sentido de tener varias ramas si al final haremos merge»*. Medido en el repositorio: main (4.9) -- 5.9 -- 7.6 -- 7.6b -- 7.7 -- 8.1 -- 8.1-8.7 -- 8.8 es una linea recta; nunca hubo dos cosas a la vez. Las tres ramas no eran tres caminos sino tres nombres sobre el mismo camino, y dos apuntaban a puntos ya superados --feat/5.9-4.1-enlace-contrasena es el PADRE de la rama de 7.6, comprobado, no supuesto--. De las cinco cosas para las que sirve una rama, hoy no aplica ninguna: un solo desarrollador, ninguna revision externa, nada desplegado, y el CI que podria opinar antes ya lo hace php tools/diagnostico.php en la maquina. Y el coste si se pagaba: la rama que existia para proteger main lo dejo nueve iteraciones obsoleto, o sea mintiendo a quien clonara. Eso es la ceremonia sin ninguno de los beneficios. Lo que sustituye a la rama no es la confianza, son las seis puertas: no se commitea en rojo. Se revierte el dia que haya produccion, y entonces una rama por iteracion fusionada el mismo dia; lo que no se repite nunca es la rama larga que acumula iteraciones, que no es una rama sino un main con otro nombre. De paso, develop sale del on: push del CI: esa rama no ha existido jamas, y CONTRIBUTING.md la nombraba desde el principio</t>
+          <t>Se registra y no se convierte en ronda hasta que alguien del equipo decida si se le cobra o la absorbemos; al cliente se le confirma que su peticion llego --que es verdad-- sin prometerle que sera gratis. Cae solo del modelo de DEC-151: como la respuesta no crea la revision, no hay ronda que consumir hasta que una persona emite el veredicto. Aprobaciones::pendientes() es la lista de lo que espera esa decision. La pantalla de gracias NO dice «lo corregimos»: decirlo seria prometer por su cuenta algo que todavia no esta decidido</t>
         </is>
       </c>
     </row>
     <row r="92" ht="34.5" customHeight="1" s="36">
       <c r="A92" s="67" t="inlineStr">
         <is>
-          <t>DEC-148</t>
+          <t>DEC-152</t>
         </is>
       </c>
       <c r="B92" s="68" t="inlineStr">
@@ -17618,24 +17668,24 @@
       <c r="C92" s="68" t="n"/>
       <c r="D92" s="69" t="inlineStr">
         <is>
-          <t>El entregable caido tiene estado propio, y expired pasa a llamarse fulfilled.</t>
+          <t>El silencio del cliente no hace nada, y por eso 8.5 no estrena comando.</t>
         </is>
       </c>
       <c r="E92" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F92" s="69" t="inlineStr">
         <is>
-          <t>Devolver el entregable a published bastaba para que no cobre, y estaba mal: published significa «esperando a que alguien lo mire» y el dia que F9 construya esa cola meteria incumplimientos dentro --un estado que significa dos cosas es el fallo de T-50--. ck_del_status gana removed, y los dos disparadores que definen «entregable cerrado» lo tratan como cerrado; sin eso se le podria subir una version nueva encima o emitir un veredicto sobre el, y el incumplimiento se disolveria solo. Aparte: ck_pub_status tenia expired desde 2.12 con CERO filas y con un nombre que se lee al reves de lo que significa --la ventana cumplida es lo BUENO, es lo que habilita el pago-- asi que se renombra ahora, que no cuesta nada; con mil filas habria costado una migracion de datos y una discusion. De paso, permanence_checks entra en la lista de 3.12: el criterio de T-16 la incluia desde el primer dia --la fila es evidencia y de ella depende dinero-- y nadie la habia mirado</t>
+          <t>El enlace caduca, la pieza se queda donde estaba y sale en la bandeja. Nadie aprueba ni rechaza en nombre de nadie. «Silencio = aprobado» habria desbloqueado la campana sin perseguir a nadie y necesita estar escrito en el contrato: dar por buena una pieza que nadie miro es una firma que el sistema pone por el cliente, y de ahi cuelgan la publicacion y el pago. Y de ahi sale que no haga falta un comando de caducidad, al reves que en 7.6: alli una invitacion sin contestar dejaba dinero comprometido y una plaza de cupo ocupada --habia un estado del mundo que corregir-- y aqui expires_at &lt; NOW() basta. Un comando que no arregla nada es una linea de cron mas que mantener y una cosa mas que puede fallar en silencio</t>
         </is>
       </c>
     </row>
     <row r="93" ht="45.75" customHeight="1" s="36">
       <c r="A93" s="67" t="inlineStr">
         <is>
-          <t>DEC-147</t>
+          <t>DEC-151</t>
         </is>
       </c>
       <c r="B93" s="68" t="inlineStr">
@@ -17646,24 +17696,24 @@
       <c r="C93" s="68" t="n"/>
       <c r="D93" s="69" t="inlineStr">
         <is>
-          <t>Se avisa al creador y al equipo; al cliente no.</t>
+          <t>La respuesta del cliente se REGISTRA; el equipo cierra.</t>
         </is>
       </c>
       <c r="E93" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F93" s="69" t="inlineStr">
         <is>
-          <t>El creador tiene algo que hacer --reponer el post, decir que la cuenta se puso privada, o decir que lo bajo-- y el equipo lo ve en su bandeja sin que nadie le mande nada. El cliente no se entera hasta que hay algo confirmado: avisarle de un falso positivo cuesta mas que el propio incidente. El correo no dice «incumpliste», dice «no lo encontramos», y dice expresamente que el pago esta en pausa: enterarse de eso cuando no llega el dinero es peor que enterarse ahora</t>
+          <t>El cliente dice «me vale» o «cambiad esto» desde un enlace firmado, y eso queda escrito con su hora y su IP --pero no mueve el entregable--. La alternativa era que su OK aprobara la pieza directamente, y se descarto por dos razones. (a) Habria obligado a partir approved en dos estados: hoy significa «listo para publicar» y 8.6 publica desde ahi, asi que sin un «aprobado interno, esperando al cliente» el mismo estado significaria dos cosas --el fallo de T-50--. (b) Y la que decide: la correccion del cliente gasta ronda, y desde 8.4 una ronda de mas exige firma y decision de facturacion. El cliente no puede firmar un cargo contra si mismo. Si su respuesta moviera la pieza sola, o se le cobraria sin que nadie lo autorizara, o habria que dejarle una puerta por la que las rondas no se cuentan. La pantalla se lo dice con esas palabras: quien pulsa «me vale» y no ve nada moverse tiene derecho a saber que pasa despues</t>
         </is>
       </c>
     </row>
     <row r="94" ht="45.75" customHeight="1" s="36">
       <c r="A94" s="67" t="inlineStr">
         <is>
-          <t>DEC-146</t>
+          <t>DEC-150</t>
         </is>
       </c>
       <c r="B94" s="68" t="inlineStr">
@@ -17674,24 +17724,24 @@
       <c r="C94" s="68" t="n"/>
       <c r="D94" s="69" t="inlineStr">
         <is>
-          <t>La sonda marca; una persona confirma.</t>
+          <t>El techo de rondas pasa a la base, y los disparadores siguen siendo GUARDAS.</t>
         </is>
       </c>
       <c r="E94" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="F94" s="69" t="inlineStr">
         <is>
-          <t>Es DEC-142 otra vez y por lo mismo --Instagram y TikTok responden igual ante un post borrado, un perfil en privado y un bloqueo geografico-- pero aqui duele mas: en 8.7 un falso negativo retrasa una verificacion, aqui acusa a un creador de incumplir un contrato. Asi que Permanencia::anotar() archiva la comprobacion y no toca publications, y lo que mueve una publicacion a removed es una persona con tg_pub_permanencia exigiendole DOS cosas: una comprobacion con is_live = 0 y una captura tomada DESPUES de haber verificado el post. La segunda condicion es la que costo pensar: la captura vieja probo que el post existia, y reutilizarla como prueba de que ya no esta seria archivar lo contrario de lo que ensena. El comando permanencia:vigilar no sale a Internet: cierra ventanas cumplidas --comparar una fecha con el calendario si lo puede hacer solo, y es lo que habilita el pago-- y cuenta las desatendidas. La comprobacion automatica buena son las APIs oficiales, que son F12</t>
+          <t>8.3 construyo el limite entero --rondas(), vetoParaRevisar(), content.extra_round, over_included, la cola con «quedan/incluidas»-- y lo dejo TODO en PHP. Tres reglas se estaban aplicando sin que nada las respaldara en el esquema: (a) ck_cvw_round no decia DE QUIEN era la correccion, asi que una revision nuestra podia gastarle una ronda al cliente --DEC-133 vivia solo en consumeRonda()--; (b) nada obligaba a over_included a decir la verdad, y esa columna es la que cargosPendientes() cuenta para facturar, o sea que una fila que miente ahi es una correccion que se trabaja y no se cobra; (c) el contador podia bajar, y bajarlo devuelve rondas ya gastadas sin la firma de nadie. tg_cvw_techo mira las DOS direcciones --agotadas sin declarar, y declarada sin estarlo-- y es cross-table, asi que un CHECK no puede verlo; lee el contador ANTES de que emitir() lo suba, que es el mismo valor con el que el servicio calculo su $exceso. Y no se hizo lo tentador: que el contador lo subiera un AFTER INSERT habria hecho imposible la desincronizacion, pero ninguno de los 504 disparadores de este esquema modifica una fila y un disparador que HACE cosas convierte el esquema en algo que actua a espaldas de quien lee el codigo. Habia fecha para esto: 8.5 escribe revisiones del cliente desde un enlace firmado, sin pasar por emitir()</t>
         </is>
       </c>
     </row>
     <row r="95" ht="57" customHeight="1" s="36">
       <c r="A95" s="67" t="inlineStr">
         <is>
-          <t>DEC-145</t>
+          <t>DEC-149</t>
         </is>
       </c>
       <c r="B95" s="68" t="inlineStr">
@@ -17702,7 +17752,7 @@
       <c r="C95" s="68" t="n"/>
       <c r="D95" s="69" t="inlineStr">
         <is>
-          <t>Retirar el post antes de tiempo BLOQUEA el pago, y el sistema no descuenta nada.</t>
+          <t>Se trabaja en main hasta que haya produccion.</t>
         </is>
       </c>
       <c r="E95" s="69" t="inlineStr">
@@ -17712,14 +17762,14 @@
       </c>
       <c r="F95" s="69" t="inlineStr">
         <is>
-          <t>BR-CONTENT-006 decia que el sistema alerta y no decia nada del dinero, que es donde deja de ser tecnico. Las otras dos opciones se descartaron: el descuento proporcional automatico exige que el contrato lo diga por escrito Y que la deteccion sea fiable --y lo segundo hoy no se cumple, ver DEC-146--; solo alertar deja al cliente sin palanca, porque el post se retira, se cobra igual y la unica consecuencia es un correo. Lo que hace: la publicacion pasa a removed con motivo, firma y fecha; el entregable pasa a removed --sale de verified, que es de donde F9 va a pagar--; y ahi se para. La decision de que se le paga la toma una persona con el expediente montado delante. test_firmar_la_caida_para_el_pago_y_no_descuenta_nada afirma las DOS mitades: que el entregable sale de verificado y que el importe acordado sigue intacto. La segunda es la que impide que alguien «mejore» esto manana metiendo una regla de tres</t>
+          <t>La pregunta fue suya y era la correcta: *«no entiendo el sentido de tener varias ramas si al final haremos merge»*. Medido en el repositorio: main (4.9) -- 5.9 -- 7.6 -- 7.6b -- 7.7 -- 8.1 -- 8.1-8.7 -- 8.8 es una linea recta; nunca hubo dos cosas a la vez. Las tres ramas no eran tres caminos sino tres nombres sobre el mismo camino, y dos apuntaban a puntos ya superados --feat/5.9-4.1-enlace-contrasena es el PADRE de la rama de 7.6, comprobado, no supuesto--. De las cinco cosas para las que sirve una rama, hoy no aplica ninguna: un solo desarrollador, ninguna revision externa, nada desplegado, y el CI que podria opinar antes ya lo hace php tools/diagnostico.php en la maquina. Y el coste si se pagaba: la rama que existia para proteger main lo dejo nueve iteraciones obsoleto, o sea mintiendo a quien clonara. Eso es la ceremonia sin ninguno de los beneficios. Lo que sustituye a la rama no es la confianza, son las seis puertas: no se commitea en rojo. Se revierte el dia que haya produccion, y entonces una rama por iteracion fusionada el mismo dia; lo que no se repite nunca es la rama larga que acumula iteraciones, que no es una rama sino un main con otro nombre. De paso, develop sale del on: push del CI: esa rama no ha existido jamas, y CONTRIBUTING.md la nombraba desde el principio</t>
         </is>
       </c>
     </row>
     <row r="96" ht="57" customHeight="1" s="36">
       <c r="A96" s="67" t="inlineStr">
         <is>
-          <t>DEC-144</t>
+          <t>DEC-148</t>
         </is>
       </c>
       <c r="B96" s="68" t="inlineStr">
@@ -17730,24 +17780,24 @@
       <c r="C96" s="68" t="n"/>
       <c r="D96" s="69" t="inlineStr">
         <is>
-          <t>Si el post no esta, el entregable vuelve al CREADOR, no a revision.</t>
+          <t>El entregable caido tiene estado propio, y expired pasa a llamarse fulfilled.</t>
         </is>
       </c>
       <c r="E96" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F96" s="69" t="inlineStr">
         <is>
-          <t>La publicacion queda rejected con su motivo y el entregable vuelve a approved. El contenido no tenia nada malo --ya se aprobo--: lo que falla es que no esta publicado, asi que lo que hay que rehacer es el ENLACE y no la pieza. Reabrir el entregable entero seria mas duro de lo necesario y dejarlo rechazado sin mas deja una campana con una pieza que nadie va a mover. Motivo de lista cerrada, como en 7.6 y 8.2, para poder contestar «.por que se caen las publicaciones?» con un numero. Y se le avisa por correo con el motivo dentro; el correo dice «no lo encontramos» y no «no publicaste», que es la diferencia que importa cuando la cuenta era privada o el enlace se copio mal. Verificar NO manda correo: no le pide nada, su parte termino</t>
+          <t>Devolver el entregable a published bastaba para que no cobre, y estaba mal: published significa «esperando a que alguien lo mire» y el dia que F9 construya esa cola meteria incumplimientos dentro --un estado que significa dos cosas es el fallo de T-50--. ck_del_status gana removed, y los dos disparadores que definen «entregable cerrado» lo tratan como cerrado; sin eso se le podria subir una version nueva encima o emitir un veredicto sobre el, y el incumplimiento se disolveria solo. Aparte: ck_pub_status tenia expired desde 2.12 con CERO filas y con un nombre que se lee al reves de lo que significa --la ventana cumplida es lo BUENO, es lo que habilita el pago-- asi que se renombra ahora, que no cuesta nada; con mil filas habria costado una migracion de datos y una discusion. De paso, permanence_checks entra en la lista de 3.12: el criterio de T-16 la incluia desde el primer dia --la fila es evidencia y de ella depende dinero-- y nadie la habia mirado</t>
         </is>
       </c>
     </row>
     <row r="97" ht="57" customHeight="1" s="36">
       <c r="A97" s="67" t="inlineStr">
         <is>
-          <t>DEC-143</t>
+          <t>DEC-147</t>
         </is>
       </c>
       <c r="B97" s="68" t="inlineStr">
@@ -17758,24 +17808,24 @@
       <c r="C97" s="68" t="n"/>
       <c r="D97" s="69" t="inlineStr">
         <is>
-          <t>Verificar tiene su propio permiso, content.verify.</t>
+          <t>Se avisa al creador y al equipo; al cliente no.</t>
         </is>
       </c>
       <c r="E97" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F97" s="69" t="inlineStr">
         <is>
-          <t>Mismo criterio que separo revisar de aprobar en 8.3: de verified cuelga el pago, asi que es una firma con dinero detras. Lo tienen campaign_manager y content_reviewer; finanzas NO, porque paga contra lo verificado y darle el permiso convertiria una comprobacion en una autoaprobacion. Se comprueba en el POST y no solo escondiendo el boton: los dos veredictos llegan por el mismo formulario</t>
+          <t>El creador tiene algo que hacer --reponer el post, decir que la cuenta se puso privada, o decir que lo bajo-- y el equipo lo ve en su bandeja sin que nadie le mande nada. El cliente no se entera hasta que hay algo confirmado: avisarle de un falso positivo cuesta mas que el propio incidente. El correo no dice «incumpliste», dice «no lo encontramos», y dice expresamente que el pago esta en pausa: enterarse de eso cuando no llega el dinero es peor que enterarse ahora</t>
         </is>
       </c>
     </row>
     <row r="98" ht="34.5" customHeight="1" s="36">
       <c r="A98" s="67" t="inlineStr">
         <is>
-          <t>DEC-142</t>
+          <t>DEC-146</t>
         </is>
       </c>
       <c r="B98" s="68" t="inlineStr">
@@ -17786,24 +17836,24 @@
       <c r="C98" s="68" t="n"/>
       <c r="D98" s="69" t="inlineStr">
         <is>
-          <t>La evidencia de que un post existe es una CAPTURA, no una comprobacion HTTP.</t>
+          <t>La sonda marca; una persona confirma.</t>
         </is>
       </c>
       <c r="E98" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F98" s="69" t="inlineStr">
         <is>
-          <t>Tomada con la limitacion delante: Instagram y TikTok devuelven 200 con un muro de login, 403 a todo lo que no sea un navegador, y 200 otra vez cuando el post no existe. Un http_status no distingue «el post existe» de «nos bloquearon», y BR-CONTENT-004 es 🔴 --de verified cuelga el pago--. Asi que lo que se archiva es un screenshot con file_id y tg_pub_verificada_con_evidencia lo impone en la base; la sonda HTTP se guarda como dato complementario y NO decide. Lo que si automatizaria esto son las APIs oficiales --Instagram Graph, TikTok--, que exigen app revisada por Meta y tokens del creador: semanas, y son F12; elegirlas ahora dejaria 8.7, 8.8 y el pago bloqueados hasta entonces. El dia que existan cambia la forma de capturar, no el modelo: publication_evidence ya admite api_snapshot. §56 del prompt maestro pide exactamente esto: no disenar sobre algo extremadamente fragil</t>
+          <t>Es DEC-142 otra vez y por lo mismo --Instagram y TikTok responden igual ante un post borrado, un perfil en privado y un bloqueo geografico-- pero aqui duele mas: en 8.7 un falso negativo retrasa una verificacion, aqui acusa a un creador de incumplir un contrato. Asi que Permanencia::anotar() archiva la comprobacion y no toca publications, y lo que mueve una publicacion a removed es una persona con tg_pub_permanencia exigiendole DOS cosas: una comprobacion con is_live = 0 y una captura tomada DESPUES de haber verificado el post. La segunda condicion es la que costo pensar: la captura vieja probo que el post existia, y reutilizarla como prueba de que ya no esta seria archivar lo contrario de lo que ensena. El comando permanencia:vigilar no sale a Internet: cierra ventanas cumplidas --comparar una fecha con el calendario si lo puede hacer solo, y es lo que habilita el pago-- y cuenta las desatendidas. La comprobacion automatica buena son las APIs oficiales, que son F12</t>
         </is>
       </c>
     </row>
     <row r="99" ht="57" customHeight="1" s="36">
       <c r="A99" s="67" t="inlineStr">
         <is>
-          <t>DEC-141</t>
+          <t>DEC-145</t>
         </is>
       </c>
       <c r="B99" s="68" t="inlineStr">
@@ -17814,24 +17864,24 @@
       <c r="C99" s="68" t="n"/>
       <c r="D99" s="69" t="inlineStr">
         <is>
-          <t>La red se DEDUCE del enlace, y tiene que ser la del brief.</t>
+          <t>Retirar el post antes de tiempo BLOQUEA el pago, y el sistema no descuenta nada.</t>
         </is>
       </c>
       <c r="E99" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F99" s="69" t="inlineStr">
         <is>
-          <t>El brief compro un reel de Instagram; un TikTok no es eso, por bueno que sea. La red no se pregunta --un desplegable en el formulario solo sirve para que alguien elija mal, y el enlace ya lo dice--: sale de platforms.url_pattern, que es una expresion regular y vive en el catalogo desde 2.6 sin que la usara nadie. Si el enlace no es de ninguna red conocida, tampoco entra. Y la huella: uq_pub_fingerprint existe desde la Fase 2 para que dos creadores no reclamen el mismo post, y con la URL cruda no impediria nada --?utm_source=ig basta para esquivarla--. Se normaliza antes de firmar: esquema y host a minusculas, www. fuera, barra final fuera, fragmento fuera, parametros de MEDICION fuera y el resto ordenados. Lo que identifica el post no se toca: la ruta conserva mayusculas --/p/AbC y /p/abc son dos posts-- y la lista de parametros a quitar es explicita, porque youtube.com/watch?v= lleva el identificador en la query y borrar la query entera fundiria todos los videos del canal en una huella. Esa es la mitad que hace dano: rechazar un post legitimo diciendo que ya esta reclamado. La URL se guarda TAL CUAL: la huella es para comparar, no para sustituir</t>
+          <t>BR-CONTENT-006 decia que el sistema alerta y no decia nada del dinero, que es donde deja de ser tecnico. Las otras dos opciones se descartaron: el descuento proporcional automatico exige que el contrato lo diga por escrito Y que la deteccion sea fiable --y lo segundo hoy no se cumple, ver DEC-146--; solo alertar deja al cliente sin palanca, porque el post se retira, se cobra igual y la unica consecuencia es un correo. Lo que hace: la publicacion pasa a removed con motivo, firma y fecha; el entregable pasa a removed --sale de verified, que es de donde F9 va a pagar--; y ahi se para. La decision de que se le paga la toma una persona con el expediente montado delante. test_firmar_la_caida_para_el_pago_y_no_descuenta_nada afirma las DOS mitades: que el entregable sale de verificado y que el importe acordado sigue intacto. La segunda es la que impide que alguien «mejore» esto manana metiendo una regla de tres</t>
         </is>
       </c>
     </row>
     <row r="100" ht="34.5" customHeight="1" s="36">
       <c r="A100" s="67" t="inlineStr">
         <is>
-          <t>DEC-140</t>
+          <t>DEC-144</t>
         </is>
       </c>
       <c r="B100" s="68" t="inlineStr">
@@ -17842,24 +17892,24 @@
       <c r="C100" s="68" t="n"/>
       <c r="D100" s="69" t="inlineStr">
         <is>
-          <t>Solo se publica lo aprobado, y ESA version.</t>
+          <t>Si el post no esta, el entregable vuelve al CREADOR, no a revision.</t>
         </is>
       </c>
       <c r="E100" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F100" s="69" t="inlineStr">
         <is>
-          <t>BR-CONTENT-002 dice que nada llega al cliente sin aprobacion interna, y registrar la publicacion de algo no aprobado es darlo por bueno a posteriori con la firma de nadie. No basta con «el entregable esta aprobado»: se guarda QUE version se publico y tiene que ser la aprobada (tg_pub_version_aprobada), porque de esta fila cuelga el pago --8.7 la verifica y 8.8 cuenta su permanencia--. publications.deliverable_version_id es un SNAPSHOT, igual que amount_snapshot en 7.6: registra lo que se publico ENTONCES y sobrevive a que el entregable se reabra y se apruebe otra version despues, asi que se guarda aunque el puntero de 8.2 diga cual es la aprobada de hoy. Su clave ajena es COMPUESTA, como la de 8.2. Detalle que la suite dice en voz alta: al INSERTAR gana el disparador --la version de otro entregable nunca puede ser la aprobada de este-- y donde la clave se ve sola es en un UPDATE, porque el disparador es BEFORE INSERT y no los mira; ahi esta su asercion, y no en un caso inventado que nunca pasa</t>
+          <t>La publicacion queda rejected con su motivo y el entregable vuelve a approved. El contenido no tenia nada malo --ya se aprobo--: lo que falla es que no esta publicado, asi que lo que hay que rehacer es el ENLACE y no la pieza. Reabrir el entregable entero seria mas duro de lo necesario y dejarlo rechazado sin mas deja una campana con una pieza que nadie va a mover. Motivo de lista cerrada, como en 7.6 y 8.2, para poder contestar «.por que se caen las publicaciones?» con un numero. Y se le avisa por correo con el motivo dentro; el correo dice «no lo encontramos» y no «no publicaste», que es la diferencia que importa cuando la cuenta era privada o el enlace se copio mal. Verificar NO manda correo: no le pide nada, su parte termino</t>
         </is>
       </c>
     </row>
     <row r="101" ht="34.5" customHeight="1" s="36">
       <c r="A101" s="67" t="inlineStr">
         <is>
-          <t>DEC-139</t>
+          <t>DEC-143</t>
         </is>
       </c>
       <c r="B101" s="68" t="inlineStr">
@@ -17870,24 +17920,24 @@
       <c r="C101" s="68" t="n"/>
       <c r="D101" s="69" t="inlineStr">
         <is>
-          <t>El post lo reporta el CREADOR, y el equipo tambien puede.</t>
+          <t>Verificar tiene su propio permiso, content.verify.</t>
         </is>
       </c>
       <c r="E101" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F101" s="69" t="inlineStr">
         <is>
-          <t>El creador es quien lo sabe primero y quien tiene el enlace en la mano: lo pega en su portal en cuanto publica. Y el equipo puede hacerlo por el, porque el caso real existe --el enlace llega por WhatsApp y el creador no entra--. Las alternativas eran peores por el mismo motivo en direcciones opuestas: solo el equipo convierte cada publicacion en una tarea nuestra --con 150 creadores, 150 tareas que perseguir-- y solo el creador deja sin camino el caso de «me lo mando por WhatsApp». Las dos puertas pasan por el MISMO servicio y el MISMO veto; solo cambia quien firma reported_by_user_id. Una segunda puerta con sus propias reglas es una segunda puerta con sus propios agujeros</t>
+          <t>Mismo criterio que separo revisar de aprobar en 8.3: de verified cuelga el pago, asi que es una firma con dinero detras. Lo tienen campaign_manager y content_reviewer; finanzas NO, porque paga contra lo verificado y darle el permiso convertiria una comprobacion en una autoaprobacion. Se comprueba en el POST y no solo escondiendo el boton: los dos veredictos llegan por el mismo formulario</t>
         </is>
       </c>
     </row>
     <row r="102" ht="57" customHeight="1" s="36">
       <c r="A102" s="67" t="inlineStr">
         <is>
-          <t>DEC-138</t>
+          <t>DEC-142</t>
         </is>
       </c>
       <c r="B102" s="68" t="inlineStr">
@@ -17898,24 +17948,24 @@
       <c r="C102" s="68" t="n"/>
       <c r="D102" s="69" t="inlineStr">
         <is>
-          <t>Un entregable aprobado se puede REABRIR, con motivo de lista cerrada y firma.</t>
+          <t>La evidencia de que un post existe es una CAPTURA, no una comprobacion HTTP.</t>
         </is>
       </c>
       <c r="E102" s="69" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F102" s="69" t="inlineStr">
         <is>
-          <t>Con 8.3 era un callejon sin salida --ni mas veredictos ni mas versiones-- y el cliente cambia de opinion y a veces se aprueba por error: el unico camino cuando eso pasara, y va a pasar, era que alguien tocara la base a mano. Reabrir no deshace nada: es otra fila en content_reviews con outcome='reopened', su motivo y su firma, y la aprobacion anterior se queda en el historial. Misma forma que la anulacion de un perfil fiscal en 3.11, y por la misma razon: el registro tiene que contestar «.que paso?» y no solo «.como esta ahora?». El motivo es de lista cerrada para poder contestar «.por que se reabren las piezas?» con un numero --si el 70% es «se aprobo por error», el problema es la pantalla de revision y no el cliente-- y «otro» exige explicacion, porque «otro» sin explicar es la casilla que se marca para poder seguir. El permiso lo tienen los DOS roles que revisan: «se aprobo por error» lo descubre normalmente quien aprobo, y obligarle a pedirselo a otro convierte un clic en un correo --y en la practica, en que nadie lo arregle--. Reabrir no gasta ronda: la gasta pedir un cambio, y aqui todavia no se ha pedido ninguno</t>
+          <t>Tomada con la limitacion delante: Instagram y TikTok devuelven 200 con un muro de login, 403 a todo lo que no sea un navegador, y 200 otra vez cuando el post no existe. Un http_status no distingue «el post existe» de «nos bloquearon», y BR-CONTENT-004 es 🔴 --de verified cuelga el pago--. Asi que lo que se archiva es un screenshot con file_id y tg_pub_verificada_con_evidencia lo impone en la base; la sonda HTTP se guarda como dato complementario y NO decide. Lo que si automatizaria esto son las APIs oficiales --Instagram Graph, TikTok--, que exigen app revisada por Meta y tokens del creador: semanas, y son F12; elegirlas ahora dejaria 8.7, 8.8 y el pago bloqueados hasta entonces. El dia que existan cambia la forma de capturar, no el modelo: publication_evidence ya admite api_snapshot. §56 del prompt maestro pide exactamente esto: no disenar sobre algo extremadamente fragil</t>
         </is>
       </c>
     </row>
     <row r="103" ht="68.25" customHeight="1" s="36">
       <c r="A103" s="67" t="inlineStr">
         <is>
-          <t>DEC-137</t>
+          <t>DEC-141</t>
         </is>
       </c>
       <c r="B103" s="68" t="inlineStr">
@@ -17926,24 +17976,24 @@
       <c r="C103" s="68" t="n"/>
       <c r="D103" s="69" t="inlineStr">
         <is>
-          <t>El puntero apunta a la version APROBADA, y su clave ajena es COMPUESTA.</t>
+          <t>La red se DEDUCE del enlace, y tiene que ser la del brief.</t>
         </is>
       </c>
       <c r="E103" s="69" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F103" s="69" t="inlineStr">
         <is>
-          <t>«La ultima» sale de un MAX(version_number) y guardarla seria una copia que se puede desviar --el proyecto acaba de quitar una columna por eso mismo, el contador de rondas de 8.3--. La aprobada no es derivable sin recorrer content_reviews, y es el dato del que cuelgan 8.6 --se publica lo aprobado-- y 8.7 --se archiva evidencia de eso--; sin ella las dos tendrian que adivinar cual. Y ahi esta casi todo el valor: FOREIGN KEY (approved_version_id, id) REFERENCES deliverable_versions(id, deliverable_id). Una clave simple garantizaria que la version EXISTE; esta garantiza que es DE ESTE ENTREGABLE --sin la segunda columna, un UPDATE mal escrito deja el entregable de Ana apuntando a la version aprobada del de Luis y la fila sigue siendo valida--. Mismo patron que fk_ccr_market_campaign (7.3). Ademas impide borrar la version apuntada mientras siga aprobada, y ck_del_approved_version exige que aprobado y puntero vayan juntos o no vayan: un dato que a veces esta es igual de util que no tenerlo. La columna espero dos iteraciones a proposito: antes de 8.3 no habia nadie que la escribiera, y habria sido el sexto caso de una columna que existe y no tiene una sola fila</t>
+          <t>El brief compro un reel de Instagram; un TikTok no es eso, por bueno que sea. La red no se pregunta --un desplegable en el formulario solo sirve para que alguien elija mal, y el enlace ya lo dice--: sale de platforms.url_pattern, que es una expresion regular y vive en el catalogo desde 2.6 sin que la usara nadie. Si el enlace no es de ninguna red conocida, tampoco entra. Y la huella: uq_pub_fingerprint existe desde la Fase 2 para que dos creadores no reclamen el mismo post, y con la URL cruda no impediria nada --?utm_source=ig basta para esquivarla--. Se normaliza antes de firmar: esquema y host a minusculas, www. fuera, barra final fuera, fragmento fuera, parametros de MEDICION fuera y el resto ordenados. Lo que identifica el post no se toca: la ruta conserva mayusculas --/p/AbC y /p/abc son dos posts-- y la lista de parametros a quitar es explicita, porque youtube.com/watch?v= lleva el identificador en la query y borrar la query entera fundiria todos los videos del canal en una huella. Esa es la mitad que hace dano: rechazar un post legitimo diciendo que ya esta reclamado. La URL se guarda TAL CUAL: la huella es para comparar, no para sustituir</t>
         </is>
       </c>
     </row>
     <row r="104" ht="34.5" customHeight="1" s="36">
       <c r="A104" s="67" t="inlineStr">
         <is>
-          <t>DEC-136</t>
+          <t>DEC-140</t>
         </is>
       </c>
       <c r="B104" s="68" t="inlineStr">
@@ -17954,24 +18004,24 @@
       <c r="C104" s="68" t="n"/>
       <c r="D104" s="69" t="inlineStr">
         <is>
-          <t>Tres permisos y no uno: revisar, aprobar y autorizar una ronda de mas.</t>
+          <t>Solo se publica lo aprobado, y ESA version.</t>
         </is>
       </c>
       <c r="E104" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F104" s="69" t="inlineStr">
         <is>
-          <t>content.review abre la cola y pide cambios; content.approve da el visto bueno --lo que deja el contenido listo para el cliente y, con F9, lo que dispara el pago--; content.extra_round autoriza el cargo. Mismo criterio que separo capturar de aprobar en el perfil fiscal (DEC-062). content_reviewer tiene los dos primeros y no el tercero: esa decision es de dinero --o se le cobra al cliente o se come el margen-- y quien revisa contenido no tiene por que cargar con ella; la tiene campaign_manager, que responde del margen y es quien va a tener que explicarsela al cliente. Los tres se comprueban en el POST y no solo en la ruta: los tres botones llegan por el mismo formulario, y esconder un boton no es una regla de autorizacion. Y la cola es una BANDEJA GLOBAL, no una por campana: revisar es trabajo por lotes, y una cola por campana obliga a recorrer campanas para descubrir si hay algo esperando --lo que se descubre recorriendo se descubre tarde--. Ordenada por lo que lleva mas esperando y no por lo que vence antes, que es como una cola deja a alguien esperando para siempre</t>
+          <t>BR-CONTENT-002 dice que nada llega al cliente sin aprobacion interna, y registrar la publicacion de algo no aprobado es darlo por bueno a posteriori con la firma de nadie. No basta con «el entregable esta aprobado»: se guarda QUE version se publico y tiene que ser la aprobada (tg_pub_version_aprobada), porque de esta fila cuelga el pago --8.7 la verifica y 8.8 cuenta su permanencia--. publications.deliverable_version_id es un SNAPSHOT, igual que amount_snapshot en 7.6: registra lo que se publico ENTONCES y sobrevive a que el entregable se reabra y se apruebe otra version despues, asi que se guarda aunque el puntero de 8.2 diga cual es la aprobada de hoy. Su clave ajena es COMPUESTA, como la de 8.2. Detalle que la suite dice en voz alta: al INSERTAR gana el disparador --la version de otro entregable nunca puede ser la aprobada de este-- y donde la clave se ve sola es en un UPDATE, porque el disparador es BEFORE INSERT y no los mira; ahi esta su asercion, y no en un caso inventado que nunca pasa</t>
         </is>
       </c>
     </row>
     <row r="105" ht="57" customHeight="1" s="36">
       <c r="A105" s="67" t="inlineStr">
         <is>
-          <t>DEC-135</t>
+          <t>DEC-139</t>
         </is>
       </c>
       <c r="B105" s="68" t="inlineStr">
@@ -17982,24 +18032,24 @@
       <c r="C105" s="68" t="n"/>
       <c r="D105" s="69" t="inlineStr">
         <is>
-          <t>Pasarse de las rondas incluidas se BLOQUEA y exige decidir y firmar; y el cargo NO va a campaign_costs.</t>
+          <t>El post lo reporta el CREADOR, y el equipo tambien puede.</t>
         </is>
       </c>
       <c r="E105" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F105" s="69" t="inlineStr">
         <is>
-          <t>No un aviso: un aviso que se puede saltar acaba en un cargo que se descubre al facturar, que es tarde para discutirlo con el cliente. Cuando la ronda que se va a pedir es la tercera de dos incluidas hay que decir si se cobra o se absorbe, y quien lo dice queda en authorized_by_user_id (ck_cvw_over, en la base y no solo en la pantalla). campaign_costs seria el sitio equivocado y era tentador: es lo que gastamos NOSOTROS y resta del margen (BR-FIN-011), mientras que una ronda de mas facturada al cliente es INGRESO --meterla ahi bajaria el margen de una campana que acaba de ganar dinero--. Aqui queda la decision y la pantalla de entregables la ensena como pendiente de facturar; donde acaba la linea cuando exista F9 es Q-57, y se decide con invoice_lines delante</t>
+          <t>El creador es quien lo sabe primero y quien tiene el enlace en la mano: lo pega en su portal en cuanto publica. Y el equipo puede hacerlo por el, porque el caso real existe --el enlace llega por WhatsApp y el creador no entra--. Las alternativas eran peores por el mismo motivo en direcciones opuestas: solo el equipo convierte cada publicacion en una tarea nuestra --con 150 creadores, 150 tareas que perseguir-- y solo el creador deja sin camino el caso de «me lo mando por WhatsApp». Las dos puertas pasan por el MISMO servicio y el MISMO veto; solo cambia quien firma reported_by_user_id. Una segunda puerta con sus propias reglas es una segunda puerta con sus propios agujeros</t>
         </is>
       </c>
     </row>
     <row r="106" ht="34.5" customHeight="1" s="36">
       <c r="A106" s="67" t="inlineStr">
         <is>
-          <t>DEC-134</t>
+          <t>DEC-138</t>
         </is>
       </c>
       <c r="B106" s="68" t="inlineStr">
@@ -18010,24 +18060,24 @@
       <c r="C106" s="68" t="n"/>
       <c r="D106" s="69" t="inlineStr">
         <is>
-          <t>Hasta 8.5, quien lleva la cuenta marca de parte de quien viene la correccion.</t>
+          <t>Un entregable aprobado se puede REABRIR, con motivo de lista cerrada y firma.</t>
         </is>
       </c>
       <c r="E106" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="F106" s="69" t="inlineStr">
         <is>
-          <t>El portal del cliente es 8.5. Sin esto, en 8.3 nada consumiria ronda y el veto de «rondas agotadas» naceria muerto: el QUINTO caso de una regla escrita sobre una tabla vacia en un proyecto que ya lleva cuatro (campaign_creators en 7.4, domain_events en 4.13, invitations en 7.6, deliverables en 8.1). La salida no es inventarse el portal: es reconocer como trabaja una agencia HOY --el ejecutivo traslada el comentario del cliente y marca que es suyo--. En 8.5 el enlace firmado escribe la misma fila sin intermediario y Revisiones no se entera. Quien traslada queda anotado igual en reviewer_user_id: quien la escribio responde de ella. Y ck_cvw_firma exige usuario solo en las NUESTRAS, porque la del cliente en 8.5 no tendra cuenta detras</t>
+          <t>Con 8.3 era un callejon sin salida --ni mas veredictos ni mas versiones-- y el cliente cambia de opinion y a veces se aprueba por error: el unico camino cuando eso pasara, y va a pasar, era que alguien tocara la base a mano. Reabrir no deshace nada: es otra fila en content_reviews con outcome='reopened', su motivo y su firma, y la aprobacion anterior se queda en el historial. Misma forma que la anulacion de un perfil fiscal en 3.11, y por la misma razon: el registro tiene que contestar «.que paso?» y no solo «.como esta ahora?». El motivo es de lista cerrada para poder contestar «.por que se reabren las piezas?» con un numero --si el 70% es «se aprobo por error», el problema es la pantalla de revision y no el cliente-- y «otro» exige explicacion, porque «otro» sin explicar es la casilla que se marca para poder seguir. El permiso lo tienen los DOS roles que revisan: «se aprobo por error» lo descubre normalmente quien aprobo, y obligarle a pedirselo a otro convierte un clic en un correo --y en la practica, en que nadie lo arregle--. Reabrir no gasta ronda: la gasta pedir un cambio, y aqui todavia no se ha pedido ninguno</t>
         </is>
       </c>
     </row>
     <row r="107" ht="45.75" customHeight="1" s="36">
       <c r="A107" s="67" t="inlineStr">
         <is>
-          <t>DEC-133</t>
+          <t>DEC-137</t>
         </is>
       </c>
       <c r="B107" s="68" t="inlineStr">
@@ -18038,24 +18088,24 @@
       <c r="C107" s="68" t="n"/>
       <c r="D107" s="69" t="inlineStr">
         <is>
-          <t>Solo las rondas del CLIENTE cuentan contra el precio, y son POR ENTREGABLE.</t>
+          <t>El puntero apunta a la version APROBADA, y su clave ajena es COMPUESTA.</t>
         </is>
       </c>
       <c r="E107" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="F107" s="69" t="inlineStr">
         <is>
-          <t>Dos cosas en una porque las dos las decidio la misma conversacion. (1) Que nuestro equipo le pida al creador rehacer el encuadre antes de ensenarselo a nadie es control de calidad NUESTRO; cobrarselo al cliente seria cobrarle nuestro propio error. reviewer_side distinguia platform de client desde la Fase 2 y lo que faltaba era que alguien lo usara. (2) revision_rounds_used vivia en campaign_creators --dos rondas POR CREADOR--, asi que con un creador que entrega dos reels y tres stories, dos correcciones sobre el primer reel dejaban las otras cuatro piezas sin ninguna ronda, y el cliente habia pagado dos por cada una. Baja a deliverables, que es donde se aplica la regla. Y la columna vieja se va, no se queda como suma: una suma almacenada que nadie recalcula se desvia en silencio, y la suma por creador --la que alimenta el Creator Score-- sale de content_reviews con un SUM() que nunca miente. Tenia cero filas: quitarla hoy es gratis y dentro de tres meses no</t>
+          <t>«La ultima» sale de un MAX(version_number) y guardarla seria una copia que se puede desviar --el proyecto acaba de quitar una columna por eso mismo, el contador de rondas de 8.3--. La aprobada no es derivable sin recorrer content_reviews, y es el dato del que cuelgan 8.6 --se publica lo aprobado-- y 8.7 --se archiva evidencia de eso--; sin ella las dos tendrian que adivinar cual. Y ahi esta casi todo el valor: FOREIGN KEY (approved_version_id, id) REFERENCES deliverable_versions(id, deliverable_id). Una clave simple garantizaria que la version EXISTE; esta garantiza que es DE ESTE ENTREGABLE --sin la segunda columna, un UPDATE mal escrito deja el entregable de Ana apuntando a la version aprobada del de Luis y la fila sigue siendo valida--. Mismo patron que fk_ccr_market_campaign (7.3). Ademas impide borrar la version apuntada mientras siga aprobada, y ck_del_approved_version exige que aprobado y puntero vayan juntos o no vayan: un dato que a veces esta es igual de util que no tenerlo. La columna espero dos iteraciones a proposito: antes de 8.3 no habia nadie que la escribiera, y habria sido el sexto caso de una columna que existe y no tiene una sola fila</t>
         </is>
       </c>
     </row>
     <row r="108" ht="57" customHeight="1" s="36">
       <c r="A108" s="67" t="inlineStr">
         <is>
-          <t>DEC-132</t>
+          <t>DEC-136</t>
         </is>
       </c>
       <c r="B108" s="68" t="inlineStr">
@@ -18066,24 +18116,24 @@
       <c r="C108" s="68" t="n"/>
       <c r="D108" s="69" t="inlineStr">
         <is>
-          <t>Si al caption le faltan las etiquetas del brief, NO SE ENVIA, y se le dice cuales.</t>
+          <t>Tres permisos y no uno: revisar, aprobar y autorizar una ronda de mas.</t>
         </is>
       </c>
       <c r="E108" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F108" s="69" t="inlineStr">
         <is>
-          <t>Comprobacion objetiva y barata que ahorra una ronda de correccion entera: el creador lo arregla en diez segundos en vez de enterarse tres dias despues. Avisar y dejar pasar acaba siempre en un aviso que nadie lee; dejarlo para la revision traslada a una persona la clase de tarea que una maquina hace mejor. Sin distinguir mayusculas --#ACMEVerano y #acmeverano son el mismo hashtag para las plataformas, y rechazar por la caja seria rechazar por algo que da igual-- y devolviendo todos los motivos a la vez, porque quien entrega desde el movil prefiere una lista de tres cosas que arreglar a tres intentos</t>
+          <t>content.review abre la cola y pide cambios; content.approve da el visto bueno --lo que deja el contenido listo para el cliente y, con F9, lo que dispara el pago--; content.extra_round autoriza el cargo. Mismo criterio que separo capturar de aprobar en el perfil fiscal (DEC-062). content_reviewer tiene los dos primeros y no el tercero: esa decision es de dinero --o se le cobra al cliente o se come el margen-- y quien revisa contenido no tiene por que cargar con ella; la tiene campaign_manager, que responde del margen y es quien va a tener que explicarsela al cliente. Los tres se comprueban en el POST y no solo en la ruta: los tres botones llegan por el mismo formulario, y esconder un boton no es una regla de autorizacion. Y la cola es una BANDEJA GLOBAL, no una por campana: revisar es trabajo por lotes, y una cola por campana obliga a recorrer campanas para descubrir si hay algo esperando --lo que se descubre recorriendo se descubre tarde--. Ordenada por lo que lleva mas esperando y no por lo que vence antes, que es como una cola deja a alguien esperando para siempre</t>
         </is>
       </c>
     </row>
     <row r="109" ht="45.75" customHeight="1" s="36">
       <c r="A109" s="67" t="inlineStr">
         <is>
-          <t>DEC-131</t>
+          <t>DEC-135</t>
         </is>
       </c>
       <c r="B109" s="68" t="inlineStr">
@@ -18094,24 +18144,24 @@
       <c r="C109" s="68" t="n"/>
       <c r="D109" s="69" t="inlineStr">
         <is>
-          <t>Se entrega un ENLACE externo, y opcionalmente una imagen.</t>
+          <t>Pasarse de las rondas incluidas se BLOQUEA y exige decidir y firmar; y el cargo NO va a campaign_costs.</t>
         </is>
       </c>
       <c r="E109" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F109" s="69" t="inlineStr">
         <is>
-          <t>El contenido de verdad --un reel de 80 MB-- no sube aqui y no deberia: el creador ya lo tiene en Drive o en la propia plataforma, y almacenarlo otra vez es coste y responsabilidad sin contrapartida. Se guarda el enlace, obligatoriamente https://, mas una imagen de referencia opcional por Almacen (10 MB). El https:// se comprueba en tres sitios a proposito: EntregarRequest da el mensaje junto al campo, vetoParaEntregar() lo da junto a los demas motivos, y ck_dv_url_https impide la fila venga de donde venga. Sin el tercero, un comando o un import mete javascript:alert(1) en una columna que una vista pinta dentro de un href; sin el segundo, el creador ve un 3819</t>
+          <t>No un aviso: un aviso que se puede saltar acaba en un cargo que se descubre al facturar, que es tarde para discutirlo con el cliente. Cuando la ronda que se va a pedir es la tercera de dos incluidas hay que decir si se cobra o se absorbe, y quien lo dice queda en authorized_by_user_id (ck_cvw_over, en la base y no solo en la pantalla). campaign_costs seria el sitio equivocado y era tentador: es lo que gastamos NOSOTROS y resta del margen (BR-FIN-011), mientras que una ronda de mas facturada al cliente es INGRESO --meterla ahi bajaria el margen de una campana que acaba de ganar dinero--. Aqui queda la decision y la pantalla de entregables la ensena como pendiente de facturar; donde acaba la linea cuando exista F9 es Q-57, y se decide con invoice_lines delante</t>
         </is>
       </c>
     </row>
     <row r="110" ht="34.5" customHeight="1" s="36">
       <c r="A110" s="67" t="inlineStr">
         <is>
-          <t>DEC-130</t>
+          <t>DEC-134</t>
         </is>
       </c>
       <c r="B110" s="68" t="inlineStr">
@@ -18122,24 +18172,24 @@
       <c r="C110" s="68" t="n"/>
       <c r="D110" s="69" t="inlineStr">
         <is>
-          <t>El brief que se usa es el EFECTIVO, no el general.</t>
+          <t>Hasta 8.5, quien lleva la cuenta marca de parte de quien viene la correccion.</t>
         </is>
       </c>
       <c r="E110" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F110" s="69" t="inlineStr">
         <is>
-          <t>Mercados::briefEfectivo(), que ya resolvia N-03: si el mercado del creador tiene brief propio, ese REEMPLAZA al general. Un creador peruano en una campana con brief especifico para Peru recibe el de Peru, y las etiquetas tambien --que es justo por lo que 7.2 dejo los hashtags fuera hasta que existieran los mercados--. Un entregable generado del brief general cuando hay uno de mercado le pide al creador lo que la campana NO quiere de el, y el error solo se ve al revisar</t>
+          <t>El portal del cliente es 8.5. Sin esto, en 8.3 nada consumiria ronda y el veto de «rondas agotadas» naceria muerto: el QUINTO caso de una regla escrita sobre una tabla vacia en un proyecto que ya lleva cuatro (campaign_creators en 7.4, domain_events en 4.13, invitations en 7.6, deliverables en 8.1). La salida no es inventarse el portal: es reconocer como trabaja una agencia HOY --el ejecutivo traslada el comentario del cliente y marca que es suyo--. En 8.5 el enlace firmado escribe la misma fila sin intermediario y Revisiones no se entera. Quien traslada queda anotado igual en reviewer_user_id: quien la escribio responde de ella. Y ck_cvw_firma exige usuario solo en las NUESTRAS, porque la del cliente en 8.5 no tendra cuenta detras</t>
         </is>
       </c>
     </row>
     <row r="111" ht="57" customHeight="1" s="36">
       <c r="A111" s="67" t="inlineStr">
         <is>
-          <t>DEC-129</t>
+          <t>DEC-133</t>
         </is>
       </c>
       <c r="B111" s="68" t="inlineStr">
@@ -18150,24 +18200,24 @@
       <c r="C111" s="68" t="n"/>
       <c r="D111" s="69" t="inlineStr">
         <is>
-          <t>Los entregables se generan SOLOS al aceptar, y la generacion es idempotente.</t>
+          <t>Solo las rondas del CLIENTE cuentan contra el precio, y son POR ENTREGABLE.</t>
         </is>
       </c>
       <c r="E111" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F111" s="69" t="inlineStr">
         <is>
-          <t>El brief ya lo dice todo --cuantos, de que formato, con cuantos dias de plazo--, asi que pedirle a alguien que lo teclee otra vez por cada creador es pedirle que copie un dato que el sistema ya tiene. Lo que decide no es el ahorro sino el MODO DE FALLO: si se teclea a mano, el dia que se olvide ese creador no tiene nada que entregar y nadie se entera hasta que la campana termina sin su contenido; si se generan solos, el fallo es que sobra un entregable y se ve en la lista. Va por evento (campaign_creator.accepted --&gt; GenerarEntregables) y no dentro de aceptar(), porque Campaign no puede conocer Content: la misma frontera que se cobro el panel de 7.7. Idempotente porque aceptar dos veces no puede pasar --el enlace es de un solo uso-- pero una reanudacion de la cola o un reintento manual si, y duplicar el trabajo de un creador es la clase de error que se descubre tarde y mal</t>
+          <t>Dos cosas en una porque las dos las decidio la misma conversacion. (1) Que nuestro equipo le pida al creador rehacer el encuadre antes de ensenarselo a nadie es control de calidad NUESTRO; cobrarselo al cliente seria cobrarle nuestro propio error. reviewer_side distinguia platform de client desde la Fase 2 y lo que faltaba era que alguien lo usara. (2) revision_rounds_used vivia en campaign_creators --dos rondas POR CREADOR--, asi que con un creador que entrega dos reels y tres stories, dos correcciones sobre el primer reel dejaban las otras cuatro piezas sin ninguna ronda, y el cliente habia pagado dos por cada una. Baja a deliverables, que es donde se aplica la regla. Y la columna vieja se va, no se queda como suma: una suma almacenada que nadie recalcula se desvia en silencio, y la suma por creador --la que alimenta el Creator Score-- sale de content_reviews con un SUM() que nunca miente. Tenia cero filas: quitarla hoy es gratis y dentro de tres meses no</t>
         </is>
       </c>
     </row>
     <row r="112" ht="45.75" customHeight="1" s="36">
       <c r="A112" s="67" t="inlineStr">
         <is>
-          <t>DEC-128</t>
+          <t>DEC-132</t>
         </is>
       </c>
       <c r="B112" s="68" t="inlineStr">
@@ -18178,24 +18228,24 @@
       <c r="C112" s="68" t="n"/>
       <c r="D112" s="69" t="inlineStr">
         <is>
-          <t>En el seguimiento, el dinero SI y el margen solo con su permiso.</t>
+          <t>Si al caption le faltan las etiquetas del brief, NO SE ENVIA, y se le dice cuales.</t>
         </is>
       </c>
       <c r="E112" s="69" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F112" s="69" t="inlineStr">
         <is>
-          <t>Presupuesto, comprometido y disponible los ve quien puede ver la campana: sin esos tres numeros no se decide a quien invitar, y ponerlos detras de un permiso que entonces necesitaria todo el mundo seria un permiso que no protege nada. El margen sigue detras de campaign.view_margin (BR-FIN-007) y no se calcula y luego se esconde: no se calcula --un dato que llega a la vista es un dato que un @if mal puesto puede ensenar, y BR-SEC-001 es 🔴--. La diferencia no es sutil: lo comprometido es lo que se le paga a los creadores; el margen es lo que gana la empresa. Y el disponible se ensena NEGATIVO cuando lo es: redondearlo a cero esconderia justo el caso que hay que ver, una campana que se paso porque finanzas lo autorizo</t>
+          <t>Comprobacion objetiva y barata que ahorra una ronda de correccion entera: el creador lo arregla en diez segundos en vez de enterarse tres dias despues. Avisar y dejar pasar acaba siempre en un aviso que nadie lee; dejarlo para la revision traslada a una persona la clase de tarea que una maquina hace mejor. Sin distinguir mayusculas --#ACMEVerano y #acmeverano son el mismo hashtag para las plataformas, y rechazar por la caja seria rechazar por algo que da igual-- y devolviendo todos los motivos a la vez, porque quien entrega desde el movil prefiere una lista de tres cosas que arreglar a tres intentos</t>
         </is>
       </c>
     </row>
     <row r="113" ht="68.25" customHeight="1" s="36">
       <c r="A113" s="67" t="inlineStr">
         <is>
-          <t>DEC-127</t>
+          <t>DEC-131</t>
         </is>
       </c>
       <c r="B113" s="68" t="inlineStr">
@@ -18206,24 +18256,24 @@
       <c r="C113" s="68" t="n"/>
       <c r="D113" s="69" t="inlineStr">
         <is>
-          <t>Cuatro alertas en el panel de seguimiento, y su orden NO es por gravedad.</t>
+          <t>Se entrega un ENLACE externo, y opcionalmente una imagen.</t>
         </is>
       </c>
       <c r="E113" s="69" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F113" s="69" t="inlineStr">
         <is>
-          <t>Campana sin confirmar con el arranque a menos de 14 dias, preguntas de creadores sin atender, invitaciones que caducan en menos de 12 h, y cupo de mercado sin cubrir. La de «sin confirmar» va PRIMERA porque bloquea a las demas: sin confirmar no se puede invitar a nadie, asi que un cupo corto ahi no se arregla reclutando. Y las preguntas van antes que las invitaciones urgentes porque un creador que pregunto y no recibe respuesta MIENTRAS su plazo corre es la combinacion exacta que convierte un si en un silencio. Cada alerta dice que pasa y que hacer: una que solo dice que hay un problema obliga a buscarlo, y entonces deja de leerse. Y «cubierto» es ACEPTADO, no invitado: una invitacion sin contestar es una plaza esperando, y contarla como cubierta es como se llega al dia de arranque con la mitad del equipo y los numeros en verde</t>
+          <t>El contenido de verdad --un reel de 80 MB-- no sube aqui y no deberia: el creador ya lo tiene en Drive o en la propia plataforma, y almacenarlo otra vez es coste y responsabilidad sin contrapartida. Se guarda el enlace, obligatoriamente https://, mas una imagen de referencia opcional por Almacen (10 MB). El https:// se comprueba en tres sitios a proposito: EntregarRequest da el mensaje junto al campo, vetoParaEntregar() lo da junto a los demas motivos, y ck_dv_url_https impide la fila venga de donde venga. Sin el tercero, un comando o un import mete javascript:alert(1) en una columna que una vista pinta dentro de un href; sin el segundo, el creador ve un 3819</t>
         </is>
       </c>
     </row>
     <row r="114" ht="57" customHeight="1" s="36">
       <c r="A114" s="67" t="inlineStr">
         <is>
-          <t>DEC-126</t>
+          <t>DEC-130</t>
         </is>
       </c>
       <c r="B114" s="68" t="inlineStr">
@@ -18234,24 +18284,24 @@
       <c r="C114" s="68" t="n"/>
       <c r="D114" s="69" t="inlineStr">
         <is>
-          <t>usuarios:crear deja de teclear la contrasena; el alta interna usa el mismo enlace de 72 h que la del creador.</t>
+          <t>El brief que se usa es el EFECTIVO, no el general.</t>
         </is>
       </c>
       <c r="E114" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F114" s="69" t="inlineStr">
         <is>
-          <t>Cierra BR-SEC-004 (🔴) del todo. must_change_password era el parche: obligaba a cambiarla DESPUES y dejaba una ventana --de minutos o de meses-- en la que dos personas conocian la credencial, y justo en las cuentas donde la base exige dos personas distintas para el dinero. Ahora no hay ventana: la contrasena no existe hasta que la escribe su dueno. usuarios:contrasena --enlace hace lo mismo para reponer y no toca la contrasena actual --si el correo no llega, la persona no se queda peor de como estaba--. Teclearla a mano sigue existiendo a proposito, como cristal de emergencia para cuando el correo no sale (Q-20), y el comando avisa cada vez de que ese es el camino excepcional</t>
+          <t>Mercados::briefEfectivo(), que ya resolvia N-03: si el mercado del creador tiene brief propio, ese REEMPLAZA al general. Un creador peruano en una campana con brief especifico para Peru recibe el de Peru, y las etiquetas tambien --que es justo por lo que 7.2 dejo los hashtags fuera hasta que existieran los mercados--. Un entregable generado del brief general cuando hay uno de mercado le pide al creador lo que la campana NO quiere de el, y el error solo se ve al revisar</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="36">
       <c r="A115" s="67" t="inlineStr">
         <is>
-          <t>DEC-125</t>
+          <t>DEC-129</t>
         </is>
       </c>
       <c r="B115" s="68" t="inlineStr">
@@ -18262,24 +18312,24 @@
       <c r="C115" s="68" t="n"/>
       <c r="D115" s="69" t="inlineStr">
         <is>
-          <t>Cuando un creador contesta, se avisa a QUIEN LE INVITO y a nadie mas.</t>
+          <t>Los entregables se generan SOLOS al aceptar, y la generacion es idempotente.</t>
         </is>
       </c>
       <c r="E115" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F115" s="69" t="inlineStr">
         <is>
-          <t>Es quien espera la respuesta y quien va a hacer algo con ella. Avisar a todo el equipo son cuarenta correos por campana a cada uno, y un buzon asi se filtra a una carpeta y deja de leerse --la forma cara de no avisar a nadie--. El precio, dicho: una invitacion mandada por alguien que luego se va de la empresa queda MUDA. A una cuenta desactivada no se le escribe: no avisa a nadie y puede acabar en un buzon reasignado. El hecho no se pierde, queda en domain_events y se ve en la lista</t>
+          <t>El brief ya lo dice todo --cuantos, de que formato, con cuantos dias de plazo--, asi que pedirle a alguien que lo teclee otra vez por cada creador es pedirle que copie un dato que el sistema ya tiene. Lo que decide no es el ahorro sino el MODO DE FALLO: si se teclea a mano, el dia que se olvide ese creador no tiene nada que entregar y nadie se entera hasta que la campana termina sin su contenido; si se generan solos, el fallo es que sobra un entregable y se ve en la lista. Va por evento (campaign_creator.accepted --&gt; GenerarEntregables) y no dentro de aceptar(), porque Campaign no puede conocer Content: la misma frontera que se cobro el panel de 7.7. Idempotente porque aceptar dos veces no puede pasar --el enlace es de un solo uso-- pero una reanudacion de la cola o un reintento manual si, y duplicar el trabajo de un creador es la clase de error que se descubre tarde y mal</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="36">
       <c r="A116" s="67" t="inlineStr">
         <is>
-          <t>DEC-124</t>
+          <t>DEC-128</t>
         </is>
       </c>
       <c r="B116" s="68" t="inlineStr">
@@ -18290,24 +18340,24 @@
       <c r="C116" s="68" t="n"/>
       <c r="D116" s="69" t="inlineStr">
         <is>
-          <t>Preguntar NO mueve el plazo de la invitacion.</t>
+          <t>En el seguimiento, el dinero SI y el margen solo con su permiso.</t>
         </is>
       </c>
       <c r="E116" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="F116" s="69" t="inlineStr">
         <is>
-          <t>La alternativa --congelarla hasta que alguien conteste-- deja el importe comprometido para siempre si nadie contesta, que es justo el agujero que invitaciones:caducar existe para tapar. La pantalla se lo dice al creador con todas las letras: callarlo dejaria a alguien esperando tranquilo mientras su invitacion caduca, que es peor que no dejarle preguntar. Quien invito ve la pregunta en la lista de candidatos y decide; si hace falta mas tiempo, anula y manda otra. Y no hay respuesta dentro de la aplicacion: el equipo contesta por correo, que es donde el creador ya esta. Un hilo de ida y vuelta es un modulo de mensajeria --notificaciones, no leidos, permisos-- y habria multiplicado por tres la iteracion para resolver lo que un boton de «Responder» ya resuelve. Lo que si hay es un DUENO: «me hago cargo» marca quien atiende y el segundo clic no pisa al primero</t>
+          <t>Presupuesto, comprometido y disponible los ve quien puede ver la campana: sin esos tres numeros no se decide a quien invitar, y ponerlos detras de un permiso que entonces necesitaria todo el mundo seria un permiso que no protege nada. El margen sigue detras de campaign.view_margin (BR-FIN-007) y no se calcula y luego se esconde: no se calcula --un dato que llega a la vista es un dato que un @if mal puesto puede ensenar, y BR-SEC-001 es 🔴--. La diferencia no es sutil: lo comprometido es lo que se le paga a los creadores; el margen es lo que gana la empresa. Y el disponible se ensena NEGATIVO cuando lo es: redondearlo a cero esconderia justo el caso que hay que ver, una campana que se paso porque finanzas lo autorizo</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="36">
       <c r="A117" s="67" t="inlineStr">
         <is>
-          <t>DEC-123</t>
+          <t>DEC-127</t>
         </is>
       </c>
       <c r="B117" s="68" t="inlineStr">
@@ -18318,24 +18368,24 @@
       <c r="C117" s="68" t="n"/>
       <c r="D117" s="69" t="inlineStr">
         <is>
-          <t>Pedir un correo se hace desde Shared, no desde el modulo que lo necesita.</t>
+          <t>Cuatro alertas en el panel de seguimiento, y su orden NO es por gravedad.</t>
         </is>
       </c>
       <c r="E117" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="F117" s="69" t="inlineStr">
         <is>
-          <t>deptrac.yaml dice Communication: [Framework, Shared, Core, Identity]. En 5.9 el evento del enlace vivio una iteracion dentro de Identity y funciono de milagro: Identity esta en esa lista. Campaign no, y 7.6 necesita mandar un correo igual. Sube a App\Shared\Eventos\CorreoPedido con un solo oyente en Communication: cualquier modulo puede pedir un correo, ninguno conoce a Communication y Communication no conoce a ninguno. No es EventoOcurrido y no puede serlo --ese persiste su payload en domain_events y aqui el payload lleva el token en claro--; el HECHO si se registra, por separado y sin el token</t>
+          <t>Campana sin confirmar con el arranque a menos de 14 dias, preguntas de creadores sin atender, invitaciones que caducan en menos de 12 h, y cupo de mercado sin cubrir. La de «sin confirmar» va PRIMERA porque bloquea a las demas: sin confirmar no se puede invitar a nadie, asi que un cupo corto ahi no se arregla reclutando. Y las preguntas van antes que las invitaciones urgentes porque un creador que pregunto y no recibe respuesta MIENTRAS su plazo corre es la combinacion exacta que convierte un si en un silencio. Cada alerta dice que pasa y que hacer: una que solo dice que hay un problema obliga a buscarlo, y entonces deja de leerse. Y «cubierto» es ACEPTADO, no invitado: una invitacion sin contestar es una plaza esperando, y contarla como cubierta es como se llega al dia de arranque con la mitad del equipo y los numeros en verde</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="36">
       <c r="A118" s="67" t="inlineStr">
         <is>
-          <t>DEC-122</t>
+          <t>DEC-126</t>
         </is>
       </c>
       <c r="B118" s="68" t="inlineStr">
@@ -18346,24 +18396,24 @@
       <c r="C118" s="68" t="n"/>
       <c r="D118" s="69" t="inlineStr">
         <is>
-          <t>La invitacion COPIA el importe con el que salio, y el importe no se mueve mientras este viva.</t>
+          <t>usuarios:crear deja de teclear la contrasena; el alta interna usa el mismo enlace de 72 h que la del creador.</t>
         </is>
       </c>
       <c r="E118" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F118" s="69" t="inlineStr">
         <is>
-          <t>BR-CREATOR-008 congela el precio al ACEPTAR (tg_ccr_compromiso, 7.5) y entre el envio y la respuesta agreed_amount se podia mover: al creador le llegaba «te pagamos 1.500», alguien lo bajaba a 900, y aceptaba 900 sin haberlo visto nunca. No hace falta mala fe; basta con dos personas sobre la misma campana. Se cierra por los dos lados: amount_snapshot --misma decision que payment_term_days_snapshot y billing_legal_entity_id-- y tg_ccr_monto_con_invitacion, que obliga a anular la invitacion antes de renegociar. Y como en 5.9, responder y anular son dos columnas: responded_at tiene que contestar «.llego a contestar?» sin ambiguedad. Decimocuarta columna puerta del esquema</t>
+          <t>Cierra BR-SEC-004 (🔴) del todo. must_change_password era el parche: obligaba a cambiarla DESPUES y dejaba una ventana --de minutos o de meses-- en la que dos personas conocian la credencial, y justo en las cuentas donde la base exige dos personas distintas para el dinero. Ahora no hay ventana: la contrasena no existe hasta que la escribe su dueno. usuarios:contrasena --enlace hace lo mismo para reponer y no toca la contrasena actual --si el correo no llega, la persona no se queda peor de como estaba--. Teclearla a mano sigue existiendo a proposito, como cristal de emergencia para cuando el correo no sale (Q-20), y el comando avisa cada vez de que ese es el camino excepcional</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="36">
       <c r="A119" s="67" t="inlineStr">
         <is>
-          <t>DEC-121</t>
+          <t>DEC-125</t>
         </is>
       </c>
       <c r="B119" s="68" t="inlineStr">
@@ -18374,24 +18424,24 @@
       <c r="C119" s="68" t="n"/>
       <c r="D119" s="69" t="inlineStr">
         <is>
-          <t>Rechazar no cierra la campana para ese creador, y quedan las DOS rondas.</t>
+          <t>Cuando un creador contesta, se avisa a QUIEN LE INVITO y a nadie mas.</t>
         </is>
       </c>
       <c r="E119" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F119" s="69" t="inlineStr">
         <is>
-          <t>Pasa de verdad: rechaza por el importe, finanzas sube el presupuesto, se vuelve a preguntar. Prohibirlo obligaria a renegociar fuera del sistema. La constancia vive en invitations --una fila por ronda, con su motivo y con lo que se ofrecio entonces--, que es justo para lo que la Fase 2 diseno la tabla («cuantas veces hubo que insistir alimenta el Creator Score»). Lo que si se limpia al reinvitar es campaign_creators.declined_at: esa columna dice cuando se rechazo la ronda ACTUAL, y dejarla puesta haria que un accepted conviviera con una fecha de rechazo. El motivo es de lista cerrada para poder contestar «.por que nos dicen que no?» --si el 70% es el importe, el problema es el presupuesto y no el reclutamiento-- y no decide quien se puede reinvitar</t>
+          <t>Es quien espera la respuesta y quien va a hacer algo con ella. Avisar a todo el equipo son cuarenta correos por campana a cada uno, y un buzon asi se filtra a una carpeta y deja de leerse --la forma cara de no avisar a nadie--. El precio, dicho: una invitacion mandada por alguien que luego se va de la empresa queda MUDA. A una cuenta desactivada no se le escribe: no avisa a nadie y puede acabar en un buzon reasignado. El hecho no se pierde, queda en domain_events y se ve en la lista</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="36">
       <c r="A120" s="67" t="inlineStr">
         <is>
-          <t>DEC-120</t>
+          <t>DEC-124</t>
         </is>
       </c>
       <c r="B120" s="68" t="inlineStr">
@@ -18402,24 +18452,24 @@
       <c r="C120" s="68" t="n"/>
       <c r="D120" s="69" t="inlineStr">
         <is>
-          <t>El plazo para contestar vive en la CAMPANA, no en cada invitacion.</t>
+          <t>Preguntar NO mueve el plazo de la invitacion.</t>
         </is>
       </c>
       <c r="E120" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F120" s="69" t="inlineStr">
         <is>
-          <t>campaigns.invitation_hours, 72 por omision, entre 1 hora y 30 dias (ck_camp_invitation_hours). Un solo numero que explicar y un solo sitio donde cambiarlo; por invitacion seria un dato que hay que decidir cuarenta veces y que nadie mira dos. Y caducar necesita un comando aunque la caducidad se deduzca: expires_at contra el reloj ya impide contestar, pero la participacion seguiria en invited para siempre, su importe seguiria contando contra el presupuesto (BR-CAMPAIGN-005 bloqueando a otros por dinero que nadie se va a gastar) y el cupo del mercado no se liberaria. invitaciones:caducar cada diez minutos: el plazo minimo es una hora, asi que diez minutos deja el retraso maximo en un 17% del plazo mas corto posible</t>
+          <t>La alternativa --congelarla hasta que alguien conteste-- deja el importe comprometido para siempre si nadie contesta, que es justo el agujero que invitaciones:caducar existe para tapar. La pantalla se lo dice al creador con todas las letras: callarlo dejaria a alguien esperando tranquilo mientras su invitacion caduca, que es peor que no dejarle preguntar. Quien invito ve la pregunta en la lista de candidatos y decide; si hace falta mas tiempo, anula y manda otra. Y no hay respuesta dentro de la aplicacion: el equipo contesta por correo, que es donde el creador ya esta. Un hilo de ida y vuelta es un modulo de mensajeria --notificaciones, no leidos, permisos-- y habria multiplicado por tres la iteracion para resolver lo que un boton de «Responder» ya resuelve. Lo que si hay es un DUENO: «me hago cargo» marca quien atiende y el segundo clic no pisa al primero</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="36">
       <c r="A121" s="67" t="inlineStr">
         <is>
-          <t>DEC-119</t>
+          <t>DEC-123</t>
         </is>
       </c>
       <c r="B121" s="68" t="inlineStr">
@@ -18430,7 +18480,7 @@
       <c r="C121" s="68" t="n"/>
       <c r="D121" s="69" t="inlineStr">
         <is>
-          <t>El creador contesta la invitacion EL MISMO, por enlace.</t>
+          <t>Pedir un correo se hace desde Shared, no desde el modulo que lo necesita.</t>
         </is>
       </c>
       <c r="E121" s="69" t="inlineStr">
@@ -18440,14 +18490,14 @@
       </c>
       <c r="F121" s="69" t="inlineStr">
         <is>
-          <t>Su portal (F6) sigue bloqueado por T-09, asi que no hay pantalla donde entre a decidir. La alternativa era que un operador tecleara «dijo que si por WhatsApp», y eso convierte una ACEPTACION --de la que sale lo que se le paga a una persona-- en la palabra de un tercero. Con enlace hay una IP, una hora y un token que solo el tenia. Y no habia que construir nada: es la pieza de 5.9, ya probada. invitations.channel admite otros canales desde la Fase 2; el dia que exista el de WhatsApp, la fila ya sabe distinguirlo</t>
+          <t>deptrac.yaml dice Communication: [Framework, Shared, Core, Identity]. En 5.9 el evento del enlace vivio una iteracion dentro de Identity y funciono de milagro: Identity esta en esa lista. Campaign no, y 7.6 necesita mandar un correo igual. Sube a App\Shared\Eventos\CorreoPedido con un solo oyente en Communication: cualquier modulo puede pedir un correo, ninguno conoce a Communication y Communication no conoce a ninguno. No es EventoOcurrido y no puede serlo --ese persiste su payload en domain_events y aqui el payload lleva el token en claro--; el HECHO si se registra, por separado y sin el token</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="36">
       <c r="A122" s="67" t="inlineStr">
         <is>
-          <t>DEC-118</t>
+          <t>DEC-122</t>
         </is>
       </c>
       <c r="B122" s="68" t="inlineStr">
@@ -18458,24 +18508,24 @@
       <c r="C122" s="68" t="n"/>
       <c r="D122" s="69" t="inlineStr">
         <is>
-          <t>La portada se bifurca por TIPO DE USUARIO, y SESSION_DRIVER=database pasa a ser requisito de seguridad.</t>
+          <t>La invitacion COPIA el importe con el que salio, y el importe no se mueve mientras este viva.</t>
         </is>
       </c>
       <c r="E122" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F122" s="69" t="inlineStr">
         <is>
-          <t>Dos consecuencias de la misma causa: 5.9 crea la primera cuenta que no es del equipo. (a) /panel ensenaba a cualquier autenticado los totales de creadores, clientes y campanas mas el inventario del esquema; nadie lo habia pensado porque hasta hoy todos los usuarios eran internos. Se bifurca por user_type y no por permiso --un creador no tiene ninguno, y comprobar permisos que dicen «no» a todo deja una pantalla vacia en vez de una que explica donde esta--. (b) Poner una contrasena nueva borra las filas de sessions de ese usuario y rota remember_token; con SESSION_DRIVER=file lo primero es imposible --no hay forma de saber que archivo es de quien-- y una contrasena nueva convivira con la sesion abierta de quien entro con la vieja, que es no haber hecho nada</t>
+          <t>BR-CREATOR-008 congela el precio al ACEPTAR (tg_ccr_compromiso, 7.5) y entre el envio y la respuesta agreed_amount se podia mover: al creador le llegaba «te pagamos 1.500», alguien lo bajaba a 900, y aceptaba 900 sin haberlo visto nunca. No hace falta mala fe; basta con dos personas sobre la misma campana. Se cierra por los dos lados: amount_snapshot --misma decision que payment_term_days_snapshot y billing_legal_entity_id-- y tg_ccr_monto_con_invitacion, que obliga a anular la invitacion antes de renegociar. Y como en 5.9, responder y anular son dos columnas: responded_at tiene que contestar «.llego a contestar?» sin ambiguedad. Decimocuarta columna puerta del esquema</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="36">
       <c r="A123" s="67" t="inlineStr">
         <is>
-          <t>DEC-117</t>
+          <t>DEC-121</t>
         </is>
       </c>
       <c r="B123" s="68" t="inlineStr">
@@ -18486,24 +18536,24 @@
       <c r="C123" s="68" t="n"/>
       <c r="D123" s="69" t="inlineStr">
         <is>
-          <t>El token no se queda en la barra de direcciones.</t>
+          <t>Rechazar no cierra la campana para ese creador, y quedan las DOS rondas.</t>
         </is>
       </c>
       <c r="E123" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F123" s="69" t="inlineStr">
         <is>
-          <t>El enlace del correo lo lleva --no hay otra forma--, pero esa ruta solo lo guarda en la sesion y redirige a una URL sin el. Una URL con un token dentro viaja en la cabecera Referer a cualquier recurso externo de la pagina --y estas pantallas cargan tipografias de un dominio de terceros--, se queda en el registro de accesos del servidor y en el historial, y se copia entera cuando alguien la pega en un chat preguntando que es. Al guardarlo la sesion se vacia y renueva (invalidate(), no regenerate(): el segundo cambia el identificador y conserva el contenido, y aqui el contenido es lo que sobra)</t>
+          <t>Pasa de verdad: rechaza por el importe, finanzas sube el presupuesto, se vuelve a preguntar. Prohibirlo obligaria a renegociar fuera del sistema. La constancia vive en invitations --una fila por ronda, con su motivo y con lo que se ofrecio entonces--, que es justo para lo que la Fase 2 diseno la tabla («cuantas veces hubo que insistir alimenta el Creator Score»). Lo que si se limpia al reinvitar es campaign_creators.declined_at: esa columna dice cuando se rechazo la ronda ACTUAL, y dejarla puesta haria que un accepted conviviera con una fecha de rechazo. El motivo es de lista cerrada para poder contestar «.por que nos dicen que no?» --si el 70% es el importe, el problema es el presupuesto y no el reclutamiento-- y no decide quien se puede reinvitar</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="36">
       <c r="A124" s="67" t="inlineStr">
         <is>
-          <t>DEC-116</t>
+          <t>DEC-120</t>
         </is>
       </c>
       <c r="B124" s="68" t="inlineStr">
@@ -18514,24 +18564,24 @@
       <c r="C124" s="68" t="n"/>
       <c r="D124" s="69" t="inlineStr">
         <is>
-          <t>Un enlace nuevo invalida el anterior, y usar uno mata todos los demas.</t>
+          <t>El plazo para contestar vive en la CAMPANA, no en cada invitacion.</t>
         </is>
       </c>
       <c r="E124" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F124" s="69" t="inlineStr">
         <is>
-          <t>Quien pide otro suele hacerlo porque sospecha del primero; dejarlo vivo seria dejar abierta justo la puerta que queria cerrar. Lo garantiza la BASE con la decimotercera columna puerta (uq_pl_vigente), no el servicio. Y revocar no es marcar usado: son dos columnas a proposito, porque el dia que alguien pregunte «.llego a usar el enlace?» la respuesta tiene que salir de una columna que solo se escribe cuando lo uso. La primera version de la tabla las mezclaba --una columna menos-- y ademas chocaba con ck_pl_used, que exige la IP de quien lo usa: a un enlace que sustituyes no le puedes poner una IP. Caducar no se escribe: se deduce de expires_at</t>
+          <t>campaigns.invitation_hours, 72 por omision, entre 1 hora y 30 dias (ck_camp_invitation_hours). Un solo numero que explicar y un solo sitio donde cambiarlo; por invitacion seria un dato que hay que decidir cuarenta veces y que nadie mira dos. Y caducar necesita un comando aunque la caducidad se deduzca: expires_at contra el reloj ya impide contestar, pero la participacion seguiria en invited para siempre, su importe seguiria contando contra el presupuesto (BR-CAMPAIGN-005 bloqueando a otros por dinero que nadie se va a gastar) y el cupo del mercado no se liberaria. invitaciones:caducar cada diez minutos: el plazo minimo es una hora, asi que diez minutos deja el retraso maximo en un 17% del plazo mas corto posible</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="36">
       <c r="A125" s="67" t="inlineStr">
         <is>
-          <t>DEC-115</t>
+          <t>DEC-119</t>
         </is>
       </c>
       <c r="B125" s="68" t="inlineStr">
@@ -18542,24 +18592,24 @@
       <c r="C125" s="68" t="n"/>
       <c r="D125" s="69" t="inlineStr">
         <is>
-          <t>Pedir recuperacion contesta lo mismo exista o no el correo.</t>
+          <t>El creador contesta la invitacion EL MISMO, por enlace.</t>
         </is>
       </c>
       <c r="E125" s="69" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F125" s="69" t="inlineStr">
         <is>
-          <t>«Si esa direccion tiene una cuenta activa, le acaba de salir un enlace», a los dos, y sin enviar nada en el segundo caso. Distinguirlos convierte la pantalla en un buscador de cuentas dadas de alta: con una lista de direcciones se sabe en un rato cuales son clientes nuestros, y eso vale dinero para quien hace phishing dirigido. El precio es real: quien se equivoca de correo no se entera, y se compensa diciendolo en la propia pantalla en vez de callarlo. La prueba lo afirma byte a byte quitando el testigo anti-CSRF: comparar solo la clave de sesion dejaria pasar una version que escribiera «no tenemos ese correo» dentro de la vista</t>
+          <t>Su portal (F6) sigue bloqueado por T-09, asi que no hay pantalla donde entre a decidir. La alternativa era que un operador tecleara «dijo que si por WhatsApp», y eso convierte una ACEPTACION --de la que sale lo que se le paga a una persona-- en la palabra de un tercero. Con enlace hay una IP, una hora y un token que solo el tenia. Y no habia que construir nada: es la pieza de 5.9, ya probada. invitations.channel admite otros canales desde la Fase 2; el dia que exista el de WhatsApp, la fila ya sabe distinguirlo</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="36">
       <c r="A126" s="67" t="inlineStr">
         <is>
-          <t>DEC-114</t>
+          <t>DEC-118</t>
         </is>
       </c>
       <c r="B126" s="68" t="inlineStr">
@@ -18570,7 +18620,7 @@
       <c r="C126" s="68" t="n"/>
       <c r="D126" s="69" t="inlineStr">
         <is>
-          <t>De un token de contrasena se guarda la HUELLA, nunca el token.</t>
+          <t>La portada se bifurca por TIPO DE USUARIO, y SESSION_DRIVER=database pasa a ser requisito de seguridad.</t>
         </is>
       </c>
       <c r="E126" s="69" t="inlineStr">
@@ -18580,14 +18630,14 @@
       </c>
       <c r="F126" s="69" t="inlineStr">
         <is>
-          <t>bin2hex(random_bytes(32)) --no Str::random(), no uniqid(), no el uuid de la fila-- y en password_links solo entra su sha256. Misma decision que email_log (la huella del cuerpo, no el cuerpo) y que los medios de pago (la mascara, no el numero), y aqui es la mas importante de las tres: quien lea esta tabla no puede entrar en ninguna cuenta. Corolario que obligo a romper el patron de DEC-112: el aviso a Communication no puede ir por Eventos::ocurrio(), porque ese bus PERSISTE el payload y el payload lleva el enlace dentro. Va por un evento propio de Identity, que Communication ya tiene permitido conocer. El HECHO --«se emitio un enlace de tipo X para el usuario Y»-- si se guarda en domain_events, y sin el token</t>
+          <t>Dos consecuencias de la misma causa: 5.9 crea la primera cuenta que no es del equipo. (a) /panel ensenaba a cualquier autenticado los totales de creadores, clientes y campanas mas el inventario del esquema; nadie lo habia pensado porque hasta hoy todos los usuarios eran internos. Se bifurca por user_type y no por permiso --un creador no tiene ninguno, y comprobar permisos que dicen «no» a todo deja una pantalla vacia en vez de una que explica donde esta--. (b) Poner una contrasena nueva borra las filas de sessions de ese usuario y rota remember_token; con SESSION_DRIVER=file lo primero es imposible --no hay forma de saber que archivo es de quien-- y una contrasena nueva convivira con la sesion abierta de quien entro con la vieja, que es no haber hecho nada</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="36">
       <c r="A127" s="67" t="inlineStr">
         <is>
-          <t>DEC-113</t>
+          <t>DEC-117</t>
         </is>
       </c>
       <c r="B127" s="68" t="inlineStr">
@@ -18598,7 +18648,7 @@
       <c r="C127" s="68" t="n"/>
       <c r="D127" s="69" t="inlineStr">
         <is>
-          <t>El enlace de alta dura 72 h; el de recuperacion, 1 h.</t>
+          <t>El token no se queda en la barra de direcciones.</t>
         </is>
       </c>
       <c r="E127" s="69" t="inlineStr">
@@ -18608,14 +18658,14 @@
       </c>
       <c r="F127" s="69" t="inlineStr">
         <is>
-          <t>Son la misma pieza con dos relojes: el de alta llega SIN AVISAR y puede caer un viernes por la noche; el de recuperacion lo pide alguien que esta delante de la pantalla ahora. Un solo plazo obligaria a elegir entre dejar la ventana larga del alta valiendo para recuperar, o darle una hora a quien no sabia que iba a recibir nada. La caducidad se guarda en la fila, no es una constante global: un enlace sabe cuando muere</t>
+          <t>El enlace del correo lo lleva --no hay otra forma--, pero esa ruta solo lo guarda en la sesion y redirige a una URL sin el. Una URL con un token dentro viaja en la cabecera Referer a cualquier recurso externo de la pagina --y estas pantallas cargan tipografias de un dominio de terceros--, se queda en el registro de accesos del servidor y en el historial, y se copia entera cuando alguien la pega en un chat preguntando que es. Al guardarlo la sesion se vacia y renueva (invalidate(), no regenerate(): el segundo cambia el identificador y conserva el contenido, y aqui el contenido es lo que sobra)</t>
         </is>
       </c>
     </row>
     <row r="128" ht="23.25" customHeight="1" s="36">
       <c r="A128" s="67" t="inlineStr">
         <is>
-          <t>DEC-112</t>
+          <t>DEC-116</t>
         </is>
       </c>
       <c r="B128" s="68" t="inlineStr">
@@ -18626,24 +18676,24 @@
       <c r="C128" s="68" t="n"/>
       <c r="D128" s="69" t="inlineStr">
         <is>
-          <t>Los modulos se comunican por EVENTOS, no llamandose.</t>
+          <t>Un enlace nuevo invalida el anterior, y usar uno mata todos los demas.</t>
         </is>
       </c>
       <c r="E128" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F128" s="69" t="inlineStr">
         <is>
-          <t>deptrac.yaml no deja que Creator conozca Communication ni al reves, y no es burocracia: si Creator importara Communication, un SMTP caido podria tumbar la captura de un dato fiscal. App\Shared\Eventos estrena domain_events --disenada en 2.4 y sin una sola fila hasta hoy-- y reparte asi: Creator levanta un nombre y un array, Communication recibe un nombre y un array, y ninguno importa al otro. El hecho se GUARDA antes de despachar, para que conste aunque el oyente reviente. Y no es la bitacora: Bitacora responde «quien toco que y que cambio» y es evidencia; esto responde «que paso, para que otros reaccionen» y dispara trabajo</t>
+          <t>Quien pide otro suele hacerlo porque sospecha del primero; dejarlo vivo seria dejar abierta justo la puerta que queria cerrar. Lo garantiza la BASE con la decimotercera columna puerta (uq_pl_vigente), no el servicio. Y revocar no es marcar usado: son dos columnas a proposito, porque el dia que alguien pregunte «.llego a usar el enlace?» la respuesta tiene que salir de una columna que solo se escribe cuando lo uso. La primera version de la tabla las mezclaba --una columna menos-- y ademas chocaba con ck_pl_used, que exige la IP de quien lo usa: a un enlace que sustituyes no le puedes poner una IP. Caducar no se escribe: se deduce de expires_at</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="36">
       <c r="A129" s="67" t="inlineStr">
         <is>
-          <t>DEC-111</t>
+          <t>DEC-115</t>
         </is>
       </c>
       <c r="B129" s="68" t="inlineStr">
@@ -18654,24 +18704,24 @@
       <c r="C129" s="68" t="n"/>
       <c r="D129" s="69" t="inlineStr">
         <is>
-          <t>Si el aviso no se puede enviar, el cambio sigue adelante.</t>
+          <t>Pedir recuperacion contesta lo mismo exista o no el correo.</t>
         </is>
       </c>
       <c r="E129" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="F129" s="69" t="inlineStr">
         <is>
-          <t>Bloquear la captura de un dato fiscal porque un SMTP se cayo convierte un problema de infraestructura en un creador al que no se le puede corregir un dato. Pero el fallo NO se traga: si el correo se encolo aparece en /correos como failed con su motivo, y si ni siquiera se pudo encolar --no hay plantilla, que es un fallo de configuracion-- se registra con report() y queda la fila de domain_events diciendo que el hecho ocurrio sin que saliera aviso</t>
+          <t>«Si esa direccion tiene una cuenta activa, le acaba de salir un enlace», a los dos, y sin enviar nada en el segundo caso. Distinguirlos convierte la pantalla en un buscador de cuentas dadas de alta: con una lista de direcciones se sabe en un rato cuales son clientes nuestros, y eso vale dinero para quien hace phishing dirigido. El precio es real: quien se equivoca de correo no se entera, y se compensa diciendolo en la propia pantalla en vez de callarlo. La prueba lo afirma byte a byte quitando el testigo anti-CSRF: comparar solo la clave de sesion dejaria pasar una version que escribiera «no tenemos ese correo» dentro de la vista</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="36">
       <c r="A130" s="67" t="inlineStr">
         <is>
-          <t>DEC-110</t>
+          <t>DEC-114</t>
         </is>
       </c>
       <c r="B130" s="68" t="inlineStr">
@@ -18682,24 +18732,24 @@
       <c r="C130" s="68" t="n"/>
       <c r="D130" s="69" t="inlineStr">
         <is>
-          <t>El correo de aviso NO lleva el dato dentro.</t>
+          <t>De un token de contrasena se guarda la HUELLA, nunca el token.</t>
         </is>
       </c>
       <c r="E130" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F130" s="69" t="inlineStr">
         <is>
-          <t>«Alguien registro un cambio en sus datos de pago; si no ha sido usted, respondanos.» Sin numero, sin banco, sin regimen, sin RUC. Un correo se lee en pantallas ajenas, se reenvia y se queda en buzones que no controlamos --y el escenario del que nos defendemos es precisamente que alguien tenga acceso a ese buzon--. Para decir «yo no fui» no hace falta ver el numero. Misma regla que ya gobierna la bitacora (la mascara, nunca el numero) y email_log (la huella, nunca el cuerpo)</t>
+          <t>bin2hex(random_bytes(32)) --no Str::random(), no uniqid(), no el uuid de la fila-- y en password_links solo entra su sha256. Misma decision que email_log (la huella del cuerpo, no el cuerpo) y que los medios de pago (la mascara, no el numero), y aqui es la mas importante de las tres: quien lea esta tabla no puede entrar en ninguna cuenta. Corolario que obligo a romper el patron de DEC-112: el aviso a Communication no puede ir por Eventos::ocurrio(), porque ese bus PERSISTE el payload y el payload lleva el enlace dentro. Va por un evento propio de Identity, que Communication ya tiene permitido conocer. El HECHO --«se emitio un enlace de tipo X para el usuario Y»-- si se guarda en domain_events, y sin el token</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="36">
       <c r="A131" s="67" t="inlineStr">
         <is>
-          <t>DEC-109</t>
+          <t>DEC-113</t>
         </is>
       </c>
       <c r="B131" s="68" t="inlineStr">
@@ -18710,24 +18760,24 @@
       <c r="C131" s="68" t="n"/>
       <c r="D131" s="69" t="inlineStr">
         <is>
-          <t>El aviso de cambio sensible sale al CAPTURAR, no al aprobar.</t>
+          <t>El enlace de alta dura 72 h; el de recuperacion, 1 h.</t>
         </is>
       </c>
       <c r="E131" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F131" s="69" t="inlineStr">
         <is>
-          <t>Es lo unico que le da al creador margen para decir «yo no fui» mientras el cambio todavia se puede parar. Avisar despues de aprobarlo es contarle un hecho consumado: si alguien suplanto su cuenta bancaria, el dinero ya va camino de otro sitio. Hay prueba dedicada: el aviso sale con el perfil todavia en pending</t>
+          <t>Son la misma pieza con dos relojes: el de alta llega SIN AVISAR y puede caer un viernes por la noche; el de recuperacion lo pide alguien que esta delante de la pantalla ahora. Un solo plazo obligaria a elegir entre dejar la ventana larga del alta valiendo para recuperar, o darle una hora a quien no sabia que iba a recibir nada. La caducidad se guarda en la fila, no es una constante global: un enlace sabe cuando muere</t>
         </is>
       </c>
     </row>
     <row r="132" ht="23.25" customHeight="1" s="36">
       <c r="A132" s="67" t="inlineStr">
         <is>
-          <t>DEC-108</t>
+          <t>DEC-112</t>
         </is>
       </c>
       <c r="B132" s="68" t="inlineStr">
@@ -18738,24 +18788,24 @@
       <c r="C132" s="68" t="n"/>
       <c r="D132" s="69" t="inlineStr">
         <is>
-          <t>Tres intentos espaciados (1, 5 y 15 minutos) y luego failed VISIBLE.</t>
+          <t>Los modulos se comunican por EVENTOS, no llamandose.</t>
         </is>
       </c>
       <c r="E132" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F132" s="69" t="inlineStr">
         <is>
-          <t>Cubre la caida pasajera del proveedor sin insistir eternamente sobre una direccion que no existe, que es la causa mas comun. ck_el_failed exige en la BASE que un fallido lleve cuando fallo Y por que: un failed sin motivo obliga a mirar el log del servidor, que es exactamente lo que esta tabla existe para evitar. Y la pantalla abre FILTRADA POR FALLIDOS, porque el modo de fallo que importa --«al creador no le llego su enlace»-- lo descubre operaciones, no un desarrollador leyendo storage/logs</t>
+          <t>deptrac.yaml no deja que Creator conozca Communication ni al reves, y no es burocracia: si Creator importara Communication, un SMTP caido podria tumbar la captura de un dato fiscal. App\Shared\Eventos estrena domain_events --disenada en 2.4 y sin una sola fila hasta hoy-- y reparte asi: Creator levanta un nombre y un array, Communication recibe un nombre y un array, y ninguno importa al otro. El hecho se GUARDA antes de despachar, para que conste aunque el oyente reviente. Y no es la bitacora: Bitacora responde «quien toco que y que cambio» y es evidencia; esto responde «que paso, para que otros reaccionen» y dispara trabajo</t>
         </is>
       </c>
     </row>
     <row r="133" ht="23.25" customHeight="1" s="36">
       <c r="A133" s="67" t="inlineStr">
         <is>
-          <t>DEC-107</t>
+          <t>DEC-111</t>
         </is>
       </c>
       <c r="B133" s="68" t="inlineStr">
@@ -18766,24 +18816,24 @@
       <c r="C133" s="68" t="n"/>
       <c r="D133" s="69" t="inlineStr">
         <is>
-          <t>Sin plantilla en el idioma del destinatario se cae al de por defecto, y se ANOTA.</t>
+          <t>Si el aviso no se puede enviar, el cambio sigue adelante.</t>
         </is>
       </c>
       <c r="E133" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F133" s="69" t="inlineStr">
         <is>
-          <t>Un aviso que no llega es peor que uno en el idioma equivocado. Lo que hace que no sea una chapuza es la segunda mitad: email_log guarda locale_requested junto a template_locale, asi que «que plantillas faltan por traducir» es una consulta sobre envios reales, y sale en la pantalla como lo unico que pide una accion. Sin eso la caida seria silenciosa y nadie se enteraria nunca de que el portugues no existe. pt-BR cae antes a pt que a es: es una caida mucho mas pequena y son dos lineas</t>
+          <t>Bloquear la captura de un dato fiscal porque un SMTP se cayo convierte un problema de infraestructura en un creador al que no se le puede corregir un dato. Pero el fallo NO se traga: si el correo se encolo aparece en /correos como failed con su motivo, y si ni siquiera se pudo encolar --no hay plantilla, que es un fallo de configuracion-- se registra con report() y queda la fila de domain_events diciendo que el hecho ocurrio sin que saliera aviso</t>
         </is>
       </c>
     </row>
     <row r="134" ht="23.25" customHeight="1" s="36">
       <c r="A134" s="67" t="inlineStr">
         <is>
-          <t>DEC-106</t>
+          <t>DEC-110</t>
         </is>
       </c>
       <c r="B134" s="68" t="inlineStr">
@@ -18794,24 +18844,24 @@
       <c r="C134" s="68" t="n"/>
       <c r="D134" s="69" t="inlineStr">
         <is>
-          <t>Del correo enviado se guarda la HUELLA del cuerpo, no el cuerpo.</t>
+          <t>El correo de aviso NO lleva el dato dentro.</t>
         </is>
       </c>
       <c r="E134" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F134" s="69" t="inlineStr">
         <is>
-          <t>email_log guarda plantilla, version, idioma, asunto y body_sha256. El cuerpo lleva el nombre de la persona, a veces importes y a veces datos fiscales: guardarlo convierte esa tabla en una SEGUNDA COPIA de la ficha del creador, que hay que proteger, anonimizar y borrar igual que la primera. Y no se pierde nada, porque la version de la plantilla es inmutable --publicar la siguiente cierra la anterior, no la edita-- y la huella demuestra que el cuerpo enviado era exactamente el que sale de renderizarla. «Me llegaron condiciones distintas» se contesta con la version y la huella. Es la regla del proyecto sobre logs, aplicada con cabeza</t>
+          <t>«Alguien registro un cambio en sus datos de pago; si no ha sido usted, respondanos.» Sin numero, sin banco, sin regimen, sin RUC. Un correo se lee en pantallas ajenas, se reenvia y se queda en buzones que no controlamos --y el escenario del que nos defendemos es precisamente que alguien tenga acceso a ese buzon--. Para decir «yo no fui» no hace falta ver el numero. Misma regla que ya gobierna la bitacora (la mascara, nunca el numero) y email_log (la huella, nunca el cuerpo)</t>
         </is>
       </c>
     </row>
     <row r="135" ht="23.25" customHeight="1" s="36">
       <c r="A135" s="67" t="inlineStr">
         <is>
-          <t>DEC-105</t>
+          <t>DEC-109</t>
         </is>
       </c>
       <c r="B135" s="68" t="inlineStr">
@@ -18822,24 +18872,24 @@
       <c r="C135" s="68" t="n"/>
       <c r="D135" s="69" t="inlineStr">
         <is>
-          <t>Pasarse del presupuesto de creadores se BLOQUEA, y finanzas lo autoriza dejando el motivo.</t>
+          <t>El aviso de cambio sensible sale al CAPTURAR, no al aprobar.</t>
         </is>
       </c>
       <c r="E135" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F135" s="69" t="inlineStr">
         <is>
-          <t>La regla dice «sin aprobacion explicita de un rol autorizado, que queda auditada», asi que la autorizacion es un dato de la fila: quien, cuando y por que. ck_camp_budget_override exige las tres o ninguna --una firma sin explicacion no responde «por que esta campana se paso» dentro de un ano, misma forma que ck_inv_responded--. Lo firma finanzas y no quien monto la campana (DEC-091, DEC-044), y el motivo exige al menos diez caracteres porque «porque» no es una explicacion. Lo que cuenta como comprometido son las participaciones VIVAS: un creador que rechazo no consume presupuesto, y contarlo dejaria campanas bloqueadas por dinero que nadie se va a gastar</t>
+          <t>Es lo unico que le da al creador margen para decir «yo no fui» mientras el cambio todavia se puede parar. Avisar despues de aprobarlo es contarle un hecho consumado: si alguien suplanto su cuenta bancaria, el dinero ya va camino de otro sitio. Hay prueba dedicada: el aviso sale con el perfil todavia en pending</t>
         </is>
       </c>
     </row>
     <row r="136" ht="23.25" customHeight="1" s="36">
       <c r="A136" s="67" t="inlineStr">
         <is>
-          <t>DEC-104</t>
+          <t>DEC-108</t>
         </is>
       </c>
       <c r="B136" s="68" t="inlineStr">
@@ -18850,24 +18900,24 @@
       <c r="C136" s="68" t="n"/>
       <c r="D136" s="69" t="inlineStr">
         <is>
-          <t>El monto acordado se fija al INVITAR y se congela al ACEPTAR.</t>
+          <t>Tres intentos espaciados (1, 5 y 15 minutos) y luego failed VISIBLE.</t>
         </is>
       </c>
       <c r="E136" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F136" s="69" t="inlineStr">
         <is>
-          <t>BR-CREATOR-008: la tarifa declarada es referencia, el precio vinculante es el monto congelado en la participacion. Se fija al invitar porque el creador no puede aceptar un numero que no ha visto --tg_ccr_compromiso impide pasar a invited con cero-- y se congela al aceptar porque a partir de ahi es un acuerdo entre dos partes. Congelarlo ya en la invitacion obligaria a cancelar y rehacerla por un dedazo, llenando el historico de invitaciones canceladas que no se cancelaron por negocio: mismo argumento que DEC-090. Excepcion coherente con 7.2: en una campana declarada gratuita si se invita con cero</t>
+          <t>Cubre la caida pasajera del proveedor sin insistir eternamente sobre una direccion que no existe, que es la causa mas comun. ck_el_failed exige en la BASE que un fallido lleve cuando fallo Y por que: un failed sin motivo obliga a mirar el log del servidor, que es exactamente lo que esta tabla existe para evitar. Y la pantalla abre FILTRADA POR FALLIDOS, porque el modo de fallo que importa --«al creador no le llego su enlace»-- lo descubre operaciones, no un desarrollador leyendo storage/logs</t>
         </is>
       </c>
     </row>
     <row r="137" ht="23.25" customHeight="1" s="36">
       <c r="A137" s="67" t="inlineStr">
         <is>
-          <t>DEC-103</t>
+          <t>DEC-107</t>
         </is>
       </c>
       <c r="B137" s="68" t="inlineStr">
@@ -18878,24 +18928,24 @@
       <c r="C137" s="68" t="n"/>
       <c r="D137" s="69" t="inlineStr">
         <is>
-          <t>«2 reels» en el brief es lo que entrega CADA creador, no el total de la campana.</t>
+          <t>Sin plantilla en el idioma del destinatario se cae al de por defecto, y se ANOTA.</t>
         </is>
       </c>
       <c r="E137" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F137" s="69" t="inlineStr">
         <is>
-          <t>El brief es lo que se le dice a UNA persona; cuantos creadores hay lo dice target_creators de cada mercado (7.3). La alternativa --repartir un total entre los seleccionados-- obliga a decidir quien entrega que y a recalcular cada vez que alguien entra o sale, y un creador no sabria que acepta hasta que la lista este cerrada. Ademas confirma lo ya construido: el coste estimado de 7.4 ya multiplicaba tarifa por cantidad</t>
+          <t>Un aviso que no llega es peor que uno en el idioma equivocado. Lo que hace que no sea una chapuza es la segunda mitad: email_log guarda locale_requested junto a template_locale, asi que «que plantillas faltan por traducir» es una consulta sobre envios reales, y sale en la pantalla como lo unico que pide una accion. Sin eso la caida seria silenciosa y nadie se enteraria nunca de que el portugues no existe. pt-BR cae antes a pt que a es: es una caida mucho mas pequena y son dos lineas</t>
         </is>
       </c>
     </row>
     <row r="138" ht="34.5" customHeight="1" s="36">
       <c r="A138" s="67" t="inlineStr">
         <is>
-          <t>DEC-102</t>
+          <t>DEC-106</t>
         </is>
       </c>
       <c r="B138" s="68" t="inlineStr">
@@ -18906,24 +18956,24 @@
       <c r="C138" s="68" t="n"/>
       <c r="D138" s="69" t="inlineStr">
         <is>
-          <t>Nadie entra en una campana cerrada, y una participacion que ya estaba solo se puede cancelar.</t>
+          <t>Del correo enviado se guarda la HUELLA del cuerpo, no el cuerpo.</t>
         </is>
       </c>
       <c r="E138" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F138" s="69" t="inlineStr">
         <is>
-          <t>campaign_creators existia desde la Fase 2 y hasta 7.4 nadie habia escrito una fila; en cuanto se escribe la primera aparece el hueco. Una participacion en una campana terminada devenga en el ledger (9.3) contra un periodo ya liquidado, sale en el reporte «reproducible» del cliente (10.4) y cuenta en el Creator Score (14.3) por un trabajo que nunca existio. Disparadores y no CHECK porque la condicion esta en otra tabla. El de UPDATE hace falta aparte porque cerrar la campana y mover al creador son operaciones distintas; se deja pasar cancelled porque cerrar una campana con candidatos dentro tiene que poder dejarlos resueltos, y la alternativa seria borrar la fila --lo que 3.12 prohibe--</t>
+          <t>email_log guarda plantilla, version, idioma, asunto y body_sha256. El cuerpo lleva el nombre de la persona, a veces importes y a veces datos fiscales: guardarlo convierte esa tabla en una SEGUNDA COPIA de la ficha del creador, que hay que proteger, anonimizar y borrar igual que la primera. Y no se pierde nada, porque la version de la plantilla es inmutable --publicar la siguiente cierra la anterior, no la edita-- y la huella demuestra que el cuerpo enviado era exactamente el que sale de renderizarla. «Me llegaron condiciones distintas» se contesta con la version y la huella. Es la regla del proyecto sobre logs, aplicada con cabeza</t>
         </is>
       </c>
     </row>
     <row r="139" ht="23.25" customHeight="1" s="36">
       <c r="A139" s="67" t="inlineStr">
         <is>
-          <t>DEC-101</t>
+          <t>DEC-105</t>
         </is>
       </c>
       <c r="B139" s="68" t="inlineStr">
@@ -18934,24 +18984,24 @@
       <c r="C139" s="68" t="n"/>
       <c r="D139" s="69" t="inlineStr">
         <is>
-          <t>En la lista corta se entra a un mercado CONCRETO, derivado del pais del creador.</t>
+          <t>Pasarse del presupuesto de creadores se BLOQUEA, y finanzas lo autoriza dejando el motivo.</t>
         </is>
       </c>
       <c r="E139" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F139" s="69" t="inlineStr">
         <is>
-          <t>No se pide: es el unico que puede ser, y pedirlo seria pedirle al operador que repita un dato que el sistema ya sabe. De ahi sale el cupo por mercado (target_creators, 7.3) y el reparto de entregables por pais en 7.5. agreed_amount nace en CERO a proposito: el compromiso economico se congela al aceptar (BR-CREATOR-008), no al meter a alguien en una lista, y un candidato con importe es un acuerdo que nadie ha firmado</t>
+          <t>La regla dice «sin aprobacion explicita de un rol autorizado, que queda auditada», asi que la autorizacion es un dato de la fila: quien, cuando y por que. ck_camp_budget_override exige las tres o ninguna --una firma sin explicacion no responde «por que esta campana se paso» dentro de un ano, misma forma que ck_inv_responded--. Lo firma finanzas y no quien monto la campana (DEC-091, DEC-044), y el motivo exige al menos diez caracteres porque «porque» no es una explicacion. Lo que cuenta como comprometido son las participaciones VIVAS: un creador que rechazo no consume presupuesto, y contarlo dejaria campanas bloqueadas por dinero que nadie se va a gastar</t>
         </is>
       </c>
     </row>
     <row r="140" ht="23.25" customHeight="1" s="36">
       <c r="A140" s="67" t="inlineStr">
         <is>
-          <t>DEC-100</t>
+          <t>DEC-104</t>
         </is>
       </c>
       <c r="B140" s="68" t="inlineStr">
@@ -18962,24 +19012,24 @@
       <c r="C140" s="68" t="n"/>
       <c r="D140" s="69" t="inlineStr">
         <is>
-          <t>Una categoria que el creador declaro que NO trabaja lo excluye del buscador.</t>
+          <t>El monto acordado se fija al INVITAR y se congela al ACEPTAR.</t>
         </is>
       </c>
       <c r="E140" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F140" s="69" t="inlineStr">
         <is>
-          <t>Es media BR-CAMPAIGN-007 --roja, y hasta 7.4 sin nada detras-- y es la mitad que ya se puede comprobar con lo que hay en el modelo: creator_restrictions contra client_brand_categories. El creador ya dijo que no; invitarlo es hacerle perder el tiempo a los dos. Se sigue viendo con el interruptor de descartados, para poder auditar por que falta alguien. Competidores y exclusividades vigentes llegan en 7.11</t>
+          <t>BR-CREATOR-008: la tarifa declarada es referencia, el precio vinculante es el monto congelado en la participacion. Se fija al invitar porque el creador no puede aceptar un numero que no ha visto --tg_ccr_compromiso impide pasar a invited con cero-- y se congela al aceptar porque a partir de ahi es un acuerdo entre dos partes. Congelarlo ya en la invitacion obligaria a cancelar y rehacerla por un dedazo, llenando el historico de invitaciones canceladas que no se cancelaron por negocio: mismo argumento que DEC-090. Excepcion coherente con 7.2: en una campana declarada gratuita si se invita con cero</t>
         </is>
       </c>
     </row>
     <row r="141" ht="34.5" customHeight="1" s="36">
       <c r="A141" s="67" t="inlineStr">
         <is>
-          <t>DEC-099</t>
+          <t>DEC-103</t>
         </is>
       </c>
       <c r="B141" s="68" t="inlineStr">
@@ -18990,24 +19040,24 @@
       <c r="C141" s="68" t="n"/>
       <c r="D141" s="69" t="inlineStr">
         <is>
-          <t>El buscador ensena a todos los activos; el veto real salta al anadir.</t>
+          <t>«2 reels» en el brief es lo que entrega CADA creador, no el total de la campana.</t>
         </is>
       </c>
       <c r="E141" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F141" s="69" t="inlineStr">
         <is>
-          <t>Un creador activado en junio al que en agosto se le retiro el medio de pago sigue con status = 'active': sale en la busqueda, con lo que le falta a la vista, y NO entra en la lista corta. Dos motivos: revalidar los seis requisitos de BR-CREATOR-006 por candidato y por busqueda es caro --en el veto se hace una vez, sobre uno-- y un creador que desaparece sin explicacion parece un fallo del sistema, mientras que uno que sale con «le falta el medio de pago» es una tarea. El veto usa CompletitudOperativa, la MISMA clase que decide la activacion y no una copia: si manana se anade un septimo requisito, lo hereda sin que nadie se acuerde de venir aqui</t>
+          <t>El brief es lo que se le dice a UNA persona; cuantos creadores hay lo dice target_creators de cada mercado (7.3). La alternativa --repartir un total entre los seleccionados-- obliga a decidir quien entrega que y a recalcular cada vez que alguien entra o sale, y un creador no sabria que acepta hasta que la lista este cerrada. Ademas confirma lo ya construido: el coste estimado de 7.4 ya multiplicaba tarifa por cantidad</t>
         </is>
       </c>
     </row>
     <row r="142" ht="23.25" customHeight="1" s="36">
       <c r="A142" s="67" t="inlineStr">
         <is>
-          <t>DEC-098</t>
+          <t>DEC-102</t>
         </is>
       </c>
       <c r="B142" s="68" t="inlineStr">
@@ -19018,24 +19068,24 @@
       <c r="C142" s="68" t="n"/>
       <c r="D142" s="69" t="inlineStr">
         <is>
-          <t>Que el mercado sea DE la campana lo garantiza el esquema, con foraneas COMPUESTAS.</t>
+          <t>Nadie entra en una campana cerrada, y una participacion que ya estaba solo se puede cancelar.</t>
         </is>
       </c>
       <c r="E142" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F142" s="69" t="inlineStr">
         <is>
-          <t>campaign_requirements.campaign_market_id y campaign_creators.campaign_market_id apuntaban a campaign_markets(id), y una foranea asi solo comprueba que el mercado exista: nada impedia un requisito de la campana A colgado del mercado de la campana B, ni un creador aceptado atribuido al pais de otra campana. Se anade uq_cm_id_campaign (id, campaign_id) --redundante como clave, necesaria como destino-- y las dos foraneas pasan a (campaign_market_id, campaign_id). Se prefiere a un disparador porque la comprueba el motor en las dos direcciones --tambien impide mover un mercado de campana-- y porque Percona 5.7 si tiene foraneas compuestas. Y el NULL con significado de N-03 sobrevive sin un caso especial: en MySQL una foranea compuesta con un componente NULL no se comprueba</t>
+          <t>campaign_creators existia desde la Fase 2 y hasta 7.4 nadie habia escrito una fila; en cuanto se escribe la primera aparece el hueco. Una participacion en una campana terminada devenga en el ledger (9.3) contra un periodo ya liquidado, sale en el reporte «reproducible» del cliente (10.4) y cuenta en el Creator Score (14.3) por un trabajo que nunca existio. Disparadores y no CHECK porque la condicion esta en otra tabla. El de UPDATE hace falta aparte porque cerrar la campana y mover al creador son operaciones distintas; se deja pasar cancelled porque cerrar una campana con candidatos dentro tiene que poder dejarlos resueltos, y la alternativa seria borrar la fila --lo que 3.12 prohibe--</t>
         </is>
       </c>
     </row>
     <row r="143" ht="23.25" customHeight="1" s="36">
       <c r="A143" s="67" t="inlineStr">
         <is>
-          <t>DEC-097</t>
+          <t>DEC-101</t>
         </is>
       </c>
       <c r="B143" s="68" t="inlineStr">
@@ -19046,24 +19096,24 @@
       <c r="C143" s="68" t="n"/>
       <c r="D143" s="69" t="inlineStr">
         <is>
-          <t>El pais de un mercado no necesita cobertura de facturacion.</t>
+          <t>En la lista corta se entra a un mercado CONCRETO, derivado del pais del creador.</t>
         </is>
       </c>
       <c r="E143" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F143" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-003 resuelve quien factura por el pais del CLIENTE: un cliente peruano puede pagar una campana que corre en Colombia sin que el grupo tenga sociedad alli, y exigir cobertura en el mercado bloquearia hoy toda campana fuera de Peru. Lo que si puede hacer falta es como se le paga a un creador colombiano, y eso es Q-40, que sigue abierta y desde 7.3 tiene caso de uso</t>
+          <t>No se pide: es el unico que puede ser, y pedirlo seria pedirle al operador que repita un dato que el sistema ya sabe. De ahi sale el cupo por mercado (target_creators, 7.3) y el reparto de entregables por pais en 7.5. agreed_amount nace en CERO a proposito: el compromiso economico se congela al aceptar (BR-CREATOR-008), no al meter a alguien en una lista, y un candidato con importe es un acuerdo que nadie ha firmado</t>
         </is>
       </c>
     </row>
     <row r="144" ht="23.25" customHeight="1" s="36">
       <c r="A144" s="67" t="inlineStr">
         <is>
-          <t>DEC-096</t>
+          <t>DEC-100</t>
         </is>
       </c>
       <c r="B144" s="68" t="inlineStr">
@@ -19074,24 +19124,24 @@
       <c r="C144" s="68" t="n"/>
       <c r="D144" s="69" t="inlineStr">
         <is>
-          <t>De una campana confirmada se ANADE un mercado, no se quita.</t>
+          <t>Una categoria que el creador declaro que NO trabaja lo excluye del buscador.</t>
         </is>
       </c>
       <c r="E144" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F144" s="69" t="inlineStr">
         <is>
-          <t>Ampliar a un pais nuevo es una decision comercial normal y no rompe nada de lo prometido; quitar puede dejar fuera a creadores ya invitados o aceptados, y eso exige una enmienda aceptada por las dos partes (BR-CAMPAIGN-003). Lo impide tg_cm_no_quitar_confirmada, un BEFORE DELETE que mira el estado de la CAMPANA y no una columna propia: el congelado de un mercado no es un hecho del mercado. Y hace falta el disparador precisamente porque la regla es asimetrica: una simetrica --«confirmada, no se toca»-- se explica de memoria; una asimetrica se olvida en la mitad de los sitios</t>
+          <t>Es media BR-CAMPAIGN-007 --roja, y hasta 7.4 sin nada detras-- y es la mitad que ya se puede comprobar con lo que hay en el modelo: creator_restrictions contra client_brand_categories. El creador ya dijo que no; invitarlo es hacerle perder el tiempo a los dos. Se sigue viendo con el interruptor de descartados, para poder auditar por que falta alguien. Competidores y exclusividades vigentes llegan en 7.11</t>
         </is>
       </c>
     </row>
     <row r="145" ht="23.25" customHeight="1" s="36">
       <c r="A145" s="67" t="inlineStr">
         <is>
-          <t>DEC-095</t>
+          <t>DEC-099</t>
         </is>
       </c>
       <c r="B145" s="68" t="inlineStr">
@@ -19102,24 +19152,24 @@
       <c r="C145" s="68" t="n"/>
       <c r="D145" s="69" t="inlineStr">
         <is>
-          <t>Una campana necesita al menos un mercado para salir de borrador.</t>
+          <t>El buscador ensena a todos los activos; el veto real salta al anadir.</t>
         </is>
       </c>
       <c r="E145" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F145" s="69" t="inlineStr">
         <is>
-          <t>Tercer motivo de BR-CAMPAIGN-004, junto al brief y al ingreso declarado. Una campana que no dice donde se ejecuta es una campana que nadie puede empezar: de ahi sale a quien se puede invitar (7.4). Cliente y marca los garantiza el esquema; el mercado no puede --un CHECK no cuenta filas de otra tabla-- asi que vive en Campanas::loQueFaltaParaSalirDeBorrador(), con los otros dos y diciendolos todos de una vez</t>
+          <t>Un creador activado en junio al que en agosto se le retiro el medio de pago sigue con status = 'active': sale en la busqueda, con lo que le falta a la vista, y NO entra en la lista corta. Dos motivos: revalidar los seis requisitos de BR-CREATOR-006 por candidato y por busqueda es caro --en el veto se hace una vez, sobre uno-- y un creador que desaparece sin explicacion parece un fallo del sistema, mientras que uno que sale con «le falta el medio de pago» es una tarea. El veto usa CompletitudOperativa, la MISMA clase que decide la activacion y no una copia: si manana se anade un septimo requisito, lo hereda sin que nadie se acuerde de venir aqui</t>
         </is>
       </c>
     </row>
     <row r="146" ht="23.25" customHeight="1" s="36">
       <c r="A146" s="67" t="inlineStr">
         <is>
-          <t>DEC-094</t>
+          <t>DEC-098</t>
         </is>
       </c>
       <c r="B146" s="68" t="inlineStr">
@@ -19130,24 +19180,24 @@
       <c r="C146" s="68" t="n"/>
       <c r="D146" s="69" t="inlineStr">
         <is>
-          <t>La regla se recorta a los estados NO iniciales, como sus dos hermanas.</t>
+          <t>Que el mercado sea DE la campana lo garantiza el esquema, con foraneas COMPUESTAS.</t>
         </is>
       </c>
       <c r="E146" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F146" s="69" t="inlineStr">
         <is>
-          <t>La primera version de ck_camp_revenue_declarado no lo hacia y habria rechazado toda campana recien creada: revenue_amount e is_gratis nacen los dos a cero, asi que el formulario vacio violaba la regla antes de que nadie pudiera teclear el precio. Es la misma forma que ck_camp_confirmed y ck_camp_billing_entity: *o estas todavia escribiendo la campana, o el dato existe*. Un borrador tiene derecho a estar a medias; lo que no puede es salir de ahi asi</t>
+          <t>campaign_requirements.campaign_market_id y campaign_creators.campaign_market_id apuntaban a campaign_markets(id), y una foranea asi solo comprueba que el mercado exista: nada impedia un requisito de la campana A colgado del mercado de la campana B, ni un creador aceptado atribuido al pais de otra campana. Se anade uq_cm_id_campaign (id, campaign_id) --redundante como clave, necesaria como destino-- y las dos foraneas pasan a (campaign_market_id, campaign_id). Se prefiere a un disparador porque la comprueba el motor en las dos direcciones --tambien impide mover un mercado de campana-- y porque Percona 5.7 si tiene foraneas compuestas. Y el NULL con significado de N-03 sobrevive sin un caso especial: en MySQL una foranea compuesta con un componente NULL no se comprueba</t>
         </is>
       </c>
     </row>
     <row r="147" ht="23.25" customHeight="1" s="36">
       <c r="A147" s="67" t="inlineStr">
         <is>
-          <t>DEC-093</t>
+          <t>DEC-097</t>
         </is>
       </c>
       <c r="B147" s="68" t="inlineStr">
@@ -19158,24 +19208,24 @@
       <c r="C147" s="68" t="n"/>
       <c r="D147" s="69" t="inlineStr">
         <is>
-          <t>Ingreso cero es valido, pero hay que declararlo.</t>
+          <t>El pais de un mercado no necesita cobertura de facturacion.</t>
         </is>
       </c>
       <c r="E147" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F147" s="69" t="inlineStr">
         <is>
-          <t>revenue_amount = 0 respondia a dos preguntas distintas con el mismo numero --«esta campana se regala» (canje, cortesia, prueba) y «nadie le ha puesto precio»--, y ante un margen descuadrado la diferencia entre las dos es la diferencia entre «salio como se planeo» y «se nos escapo». Columna is_gratis y ck_camp_revenue_declarado. Va en la BASE y no en la pantalla porque la pregunta que hay que poder responder dentro de un ano es «¿esta campana de cero se regalo o se nos olvido cobrarla?», y esa respuesta tiene que sobrevivir a una importacion y a la proxima pantalla que alguien escriba. Mismo valor por omision que parecia una respuesta que DEC-048 y DEC-068</t>
+          <t>BR-LE-003 resuelve quien factura por el pais del CLIENTE: un cliente peruano puede pagar una campana que corre en Colombia sin que el grupo tenga sociedad alli, y exigir cobertura en el mercado bloquearia hoy toda campana fuera de Peru. Lo que si puede hacer falta es como se le paga a un creador colombiano, y eso es Q-40, que sigue abierta y desde 7.3 tiene caso de uso</t>
         </is>
       </c>
     </row>
     <row r="148" ht="23.25" customHeight="1" s="36">
       <c r="A148" s="67" t="inlineStr">
         <is>
-          <t>DEC-092</t>
+          <t>DEC-096</t>
         </is>
       </c>
       <c r="B148" s="68" t="inlineStr">
@@ -19186,24 +19236,24 @@
       <c r="C148" s="68" t="n"/>
       <c r="D148" s="69" t="inlineStr">
         <is>
-          <t>«Brief definido» son los REQUISITOS, no el texto del briefing.</t>
+          <t>De una campana confirmada se ANADE un mercado, no se quita.</t>
         </is>
       </c>
       <c r="E148" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F148" s="69" t="inlineStr">
         <is>
-          <t>BR-CAMPAIGN-004 exige «brief definido» para aprobar y no dice que es. Se decide: al menos una fila en campaign_requirements --un formato, una cantidad, un plazo--. El campo briefing sigue siendo texto libre opcional porque no se puede comprobar de verdad: un espacio en blanco cumpliria cualquier NOT NULL, asi que exigirlo anadiria friccion sin anadir garantia. Los formatos si se comprueban, y son lo que convierte «hay una campana» en «hay algo que entregar»: es lo minimo que un creador necesita para decidir si acepta</t>
+          <t>Ampliar a un pais nuevo es una decision comercial normal y no rompe nada de lo prometido; quitar puede dejar fuera a creadores ya invitados o aceptados, y eso exige una enmienda aceptada por las dos partes (BR-CAMPAIGN-003). Lo impide tg_cm_no_quitar_confirmada, un BEFORE DELETE que mira el estado de la CAMPANA y no una columna propia: el congelado de un mercado no es un hecho del mercado. Y hace falta el disparador precisamente porque la regla es asimetrica: una simetrica --«confirmada, no se toca»-- se explica de memoria; una asimetrica se olvida en la mitad de los sitios</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="36">
       <c r="A149" s="67" t="inlineStr">
         <is>
-          <t>DEC-091</t>
+          <t>DEC-095</t>
         </is>
       </c>
       <c r="B149" s="68" t="inlineStr">
@@ -19214,24 +19264,24 @@
       <c r="C149" s="68" t="n"/>
       <c r="D149" s="69" t="inlineStr">
         <is>
-          <t>Aprobar una campana es de finanzas, no de quien la monta.</t>
+          <t>Una campana necesita al menos un mercado para salir de borrador.</t>
         </is>
       </c>
       <c r="E149" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F149" s="69" t="inlineStr">
         <is>
-          <t>Aprobar fija el ingreso comprometido y congela la sociedad emisora: es una decision de dinero, y la misma separacion que DEC-044 impone en la base para perfiles fiscales y medios de pago. Permiso nuevo campaign.approve, y vive en el GRAFO de transiciones, no en la ruta: una ruta con permiso fijo obligaria a partir la accion en dos y a acordarse de las dos al anadir un estado</t>
+          <t>Tercer motivo de BR-CAMPAIGN-004, junto al brief y al ingreso declarado. Una campana que no dice donde se ejecuta es una campana que nadie puede empezar: de ahi sale a quien se puede invitar (7.4). Cliente y marca los garantiza el esquema; el mercado no puede --un CHECK no cuenta filas de otra tabla-- asi que vive en Campanas::loQueFaltaParaSalirDeBorrador(), con los otros dos y diciendolos todos de una vez</t>
         </is>
       </c>
     </row>
     <row r="150" ht="68.25" customHeight="1" s="36">
       <c r="A150" s="67" t="inlineStr">
         <is>
-          <t>DEC-090</t>
+          <t>DEC-094</t>
         </is>
       </c>
       <c r="B150" s="68" t="inlineStr">
@@ -19242,24 +19292,24 @@
       <c r="C150" s="68" t="n"/>
       <c r="D150" s="69" t="inlineStr">
         <is>
-          <t>Se congela al confirmar, no al salir de borrador.</t>
+          <t>La regla se recorta a los estados NO iniciales, como sus dos hermanas.</t>
         </is>
       </c>
       <c r="E150" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F150" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-002 dice «inmutable una vez emitido» y para una campana «emitido» es ambiguo. Mientras es draft o pending_approval se corrige un dedazo; con confirmed_at puesto, no se toca. Lo impone tg_camp_entidad_congelada y no el controlador: de este dato depende que una factura de dentro de dos anos siga sabiendo quien la emitio, asi que tiene que sobrevivir a un UPDATE de mantenimiento. La alternativa --congelar al salir de borrador-- llenaria el historico de campanas cancelled que no se cancelaron por negocio, y un estado que miente sobre por que existe es peor que un campo editable un rato mas</t>
+          <t>La primera version de ck_camp_revenue_declarado no lo hacia y habria rechazado toda campana recien creada: revenue_amount e is_gratis nacen los dos a cero, asi que el formulario vacio violaba la regla antes de que nadie pudiera teclear el precio. Es la misma forma que ck_camp_confirmed y ck_camp_billing_entity: *o estas todavia escribiendo la campana, o el dato existe*. Un borrador tiene derecho a estar a medias; lo que no puede es salir de ahi asi</t>
         </is>
       </c>
     </row>
     <row r="151" ht="23.25" customHeight="1" s="36">
       <c r="A151" s="67" t="inlineStr">
         <is>
-          <t>DEC-089</t>
+          <t>DEC-093</t>
         </is>
       </c>
       <c r="B151" s="68" t="inlineStr">
@@ -19270,24 +19320,24 @@
       <c r="C151" s="68" t="n"/>
       <c r="D151" s="69" t="inlineStr">
         <is>
-          <t>La sociedad que factura una campana se resuelve a starts_on.</t>
+          <t>Ingreso cero es valido, pero hay que declararlo.</t>
         </is>
       </c>
       <c r="E151" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F151" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-003 dice «en la fecha de la operacion»; para una campana esa fecha es cuando empieza a prestarse el servicio, que es lo que un contador defiende ante SUNAT. Consecuencia: una campana creada en diciembre para arrancar en febrero usa la cobertura de FEBRERO, asi que si la cobertura cambia el 1 de enero la campana nace ya con la sociedad correcta en vez de con una que habria que corregir --y corregirla es justo lo que DEC-090 impide--</t>
+          <t>revenue_amount = 0 respondia a dos preguntas distintas con el mismo numero --«esta campana se regala» (canje, cortesia, prueba) y «nadie le ha puesto precio»--, y ante un margen descuadrado la diferencia entre las dos es la diferencia entre «salio como se planeo» y «se nos escapo». Columna is_gratis y ck_camp_revenue_declarado. Va en la BASE y no en la pantalla porque la pregunta que hay que poder responder dentro de un ano es «¿esta campana de cero se regalo o se nos olvido cobrarla?», y esa respuesta tiene que sobrevivir a una importacion y a la proxima pantalla que alguien escriba. Mismo valor por omision que parecia una respuesta que DEC-048 y DEC-068</t>
         </is>
       </c>
     </row>
     <row r="152" ht="34.5" customHeight="1" s="36">
       <c r="A152" s="67" t="inlineStr">
         <is>
-          <t>DEC-088</t>
+          <t>DEC-092</t>
         </is>
       </c>
       <c r="B152" s="68" t="inlineStr">
@@ -19298,24 +19348,24 @@
       <c r="C152" s="68" t="n"/>
       <c r="D152" s="69" t="inlineStr">
         <is>
-          <t>La aritmetica de vigencias vive en Vigencia, y una puerta lo comprueba.</t>
+          <t>«Brief definido» son los REQUISITOS, no el texto del briefing.</t>
         </is>
       </c>
       <c r="E152" s="69" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F152" s="69" t="inlineStr">
         <is>
-          <t>El error de un dia --cerrar un periodo el mismo dia en que empieza el siguiente, siendo valid_to inclusivo-- ha aparecido NUEVE veces. Vigencia (4.5) le dio un sitio; tools/verificar-vigencias.php impide que vuelva a salir de el. Dos reglas: ninguna aritmetica de dias fuera de Vigencia, y ninguna comparacion de una columna de vigencia contra algo sin normalizar. Escrita en PHP con token_get_all() y no en Python con expresiones regulares, porque los comentarios de este proyecto nombran el defecto y las migraciones llevan SQL con &gt;= dentro: una regex se acusaria a si misma. Al estrenarla quedaban tres sitios sueltos, los tres escritos DESPUES de Vigencia, y uno era un fallo real ----desde=2026-2-1 contra effective_from como cadenas, dejando dos textos legales vigentes el mismo dia--. Ver docs/fase-4/4.7-PUERTA-VIGENCIAS.md</t>
+          <t>BR-CAMPAIGN-004 exige «brief definido» para aprobar y no dice que es. Se decide: al menos una fila en campaign_requirements --un formato, una cantidad, un plazo--. El campo briefing sigue siendo texto libre opcional porque no se puede comprobar de verdad: un espacio en blanco cumpliria cualquier NOT NULL, asi que exigirlo anadiria friccion sin anadir garantia. Los formatos si se comprueban, y son lo que convierte «hay una campana» en «hay algo que entregar»: es lo minimo que un creador necesita para decidir si acepta</t>
         </is>
       </c>
     </row>
     <row r="153" ht="23.25" customHeight="1" s="36">
       <c r="A153" s="67" t="inlineStr">
         <is>
-          <t>DEC-087</t>
+          <t>DEC-091</t>
         </is>
       </c>
       <c r="B153" s="68" t="inlineStr">
@@ -19326,24 +19376,24 @@
       <c r="C153" s="68" t="n"/>
       <c r="D153" s="69" t="inlineStr">
         <is>
-          <t>Un 1062 se absorbe o se cuenta segun quien eligio el valor, y hay que NOMBRAR el indice para absorberlo.</t>
+          <t>Aprobar una campana es de finanzas, no de quien la monta.</t>
         </is>
       </c>
       <c r="E153" s="69" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="F153" s="69" t="inlineStr">
         <is>
-          <t>Si el valor lo calculo el sistema —el slug de una marca— el choque se recalcula y se reintenta en silencio. Si lo escribio la persona —un RUC, el nombre de una marca— tiene que llegar arriba con palabras. App\Shared\Database\Choque obliga a elegir: reintentar() exige el nombre del indice y vuelve a lanzar cualquier otro a la primera, porque un catch (QueryException) a secas absorberia el RUC repetido igual que el slug. Tres intentos como tope: un bucle sin tope convierte un indice mal entendido en una peticion eterna. El nombre se lee cortando por el ultimo punto —MySQL 8 antepone la tabla y Percona 5.7 no—, comprobado contra los dos motores</t>
+          <t>Aprobar fija el ingreso comprometido y congela la sociedad emisora: es una decision de dinero, y la misma separacion que DEC-044 impone en la base para perfiles fiscales y medios de pago. Permiso nuevo campaign.approve, y vive en el GRAFO de transiciones, no en la ruta: una ruta con permiso fijo obligaria a partir la accion en dos y a acordarse de las dos al anadir un estado</t>
         </is>
       </c>
     </row>
     <row r="154" ht="23.25" customHeight="1" s="36">
       <c r="A154" s="67" t="inlineStr">
         <is>
-          <t>DEC-086</t>
+          <t>DEC-090</t>
         </is>
       </c>
       <c r="B154" s="68" t="inlineStr">
@@ -19354,16 +19404,24 @@
       <c r="C154" s="68" t="n"/>
       <c r="D154" s="69" t="inlineStr">
         <is>
-          <t>La contraseña temporal deja de ser válida en el primer acceso</t>
-        </is>
-      </c>
-      <c r="E154" s="69" t="n"/>
-      <c r="F154" s="69" t="n"/>
+          <t>Se congela al confirmar, no al salir de borrador.</t>
+        </is>
+      </c>
+      <c r="E154" s="69" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="F154" s="69" t="inlineStr">
+        <is>
+          <t>BR-LE-002 dice «inmutable una vez emitido» y para una campana «emitido» es ambiguo. Mientras es draft o pending_approval se corrige un dedazo; con confirmed_at puesto, no se toca. Lo impone tg_camp_entidad_congelada y no el controlador: de este dato depende que una factura de dentro de dos anos siga sabiendo quien la emitio, asi que tiene que sobrevivir a un UPDATE de mantenimiento. La alternativa --congelar al salir de borrador-- llenaria el historico de campanas cancelled que no se cancelaron por negocio, y un estado que miente sobre por que existe es peor que un campo editable un rato mas</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="23.25" customHeight="1" s="36">
       <c r="A155" s="67" t="inlineStr">
         <is>
-          <t>DEC-085</t>
+          <t>DEC-089</t>
         </is>
       </c>
       <c r="B155" s="68" t="inlineStr">
@@ -19374,16 +19432,24 @@
       <c r="C155" s="68" t="n"/>
       <c r="D155" s="69" t="inlineStr">
         <is>
-          <t>La bitácora la protegen dos usuarios de base de datos, no el esquema</t>
-        </is>
-      </c>
-      <c r="E155" s="69" t="n"/>
-      <c r="F155" s="69" t="n"/>
+          <t>La sociedad que factura una campana se resuelve a starts_on.</t>
+        </is>
+      </c>
+      <c r="E155" s="69" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="F155" s="69" t="inlineStr">
+        <is>
+          <t>BR-LE-003 dice «en la fecha de la operacion»; para una campana esa fecha es cuando empieza a prestarse el servicio, que es lo que un contador defiende ante SUNAT. Consecuencia: una campana creada en diciembre para arrancar en febrero usa la cobertura de FEBRERO, asi que si la cobertura cambia el 1 de enero la campana nace ya con la sociedad correcta en vez de con una que habria que corregir --y corregirla es justo lo que DEC-090 impide--</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="23.25" customHeight="1" s="36">
       <c r="A156" s="67" t="inlineStr">
         <is>
-          <t>DEC-084</t>
+          <t>DEC-088</t>
         </is>
       </c>
       <c r="B156" s="68" t="inlineStr">
@@ -19394,16 +19460,24 @@
       <c r="C156" s="68" t="n"/>
       <c r="D156" s="69" t="inlineStr">
         <is>
-          <t>«Perfil fiscal vigente» exige que ya haya empezado</t>
-        </is>
-      </c>
-      <c r="E156" s="69" t="n"/>
-      <c r="F156" s="69" t="n"/>
+          <t>La aritmetica de vigencias vive en Vigencia, y una puerta lo comprueba.</t>
+        </is>
+      </c>
+      <c r="E156" s="69" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="F156" s="69" t="inlineStr">
+        <is>
+          <t>El error de un dia --cerrar un periodo el mismo dia en que empieza el siguiente, siendo valid_to inclusivo-- ha aparecido NUEVE veces. Vigencia (4.5) le dio un sitio; tools/verificar-vigencias.php impide que vuelva a salir de el. Dos reglas: ninguna aritmetica de dias fuera de Vigencia, y ninguna comparacion de una columna de vigencia contra algo sin normalizar. Escrita en PHP con token_get_all() y no en Python con expresiones regulares, porque los comentarios de este proyecto nombran el defecto y las migraciones llevan SQL con &gt;= dentro: una regex se acusaria a si misma. Al estrenarla quedaban tres sitios sueltos, los tres escritos DESPUES de Vigencia, y uno era un fallo real ----desde=2026-2-1 contra effective_from como cadenas, dejando dos textos legales vigentes el mismo dia--. Ver docs/fase-4/4.7-PUERTA-VIGENCIAS.md</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="23.25" customHeight="1" s="36">
       <c r="A157" s="67" t="inlineStr">
         <is>
-          <t>DEC-083</t>
+          <t>DEC-087</t>
         </is>
       </c>
       <c r="B157" s="68" t="inlineStr">
@@ -19414,16 +19488,24 @@
       <c r="C157" s="68" t="n"/>
       <c r="D157" s="69" t="inlineStr">
         <is>
-          <t>«Cuenta compartida» se calcula al leer, no se guarda</t>
-        </is>
-      </c>
-      <c r="E157" s="69" t="n"/>
-      <c r="F157" s="69" t="n"/>
+          <t>Un 1062 se absorbe o se cuenta segun quien eligio el valor, y hay que NOMBRAR el indice para absorberlo.</t>
+        </is>
+      </c>
+      <c r="E157" s="69" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="F157" s="69" t="inlineStr">
+        <is>
+          <t>Si el valor lo calculo el sistema —el slug de una marca— el choque se recalcula y se reintenta en silencio. Si lo escribio la persona —un RUC, el nombre de una marca— tiene que llegar arriba con palabras. App\Shared\Database\Choque obliga a elegir: reintentar() exige el nombre del indice y vuelve a lanzar cualquier otro a la primera, porque un catch (QueryException) a secas absorberia el RUC repetido igual que el slug. Tres intentos como tope: un bucle sin tope convierte un indice mal entendido en una peticion eterna. El nombre se lee cortando por el ultimo punto —MySQL 8 antepone la tabla y Percona 5.7 no—, comprobado contra los dos motores</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="57" customHeight="1" s="36">
       <c r="A158" s="67" t="inlineStr">
         <is>
-          <t>DEC-082</t>
+          <t>DEC-086</t>
         </is>
       </c>
       <c r="B158" s="68" t="inlineStr">
@@ -19434,7 +19516,7 @@
       <c r="C158" s="68" t="n"/>
       <c r="D158" s="69" t="inlineStr">
         <is>
-          <t>Las sociedades del grupo las gestiona sólo admin</t>
+          <t>La contraseña temporal deja de ser válida en el primer acceso</t>
         </is>
       </c>
       <c r="E158" s="69" t="n"/>
@@ -19443,7 +19525,7 @@
     <row r="159" ht="23.25" customHeight="1" s="36">
       <c r="A159" s="67" t="inlineStr">
         <is>
-          <t>DEC-081</t>
+          <t>DEC-085</t>
         </is>
       </c>
       <c r="B159" s="68" t="inlineStr">
@@ -19454,7 +19536,7 @@
       <c r="C159" s="68" t="n"/>
       <c r="D159" s="69" t="inlineStr">
         <is>
-          <t>Dar de baja una sociedad cierra sus coberturas abiertas</t>
+          <t>La bitácora la protegen dos usuarios de base de datos, no el esquema</t>
         </is>
       </c>
       <c r="E159" s="69" t="n"/>
@@ -19463,7 +19545,7 @@
     <row r="160" ht="34.5" customHeight="1" s="36">
       <c r="A160" s="67" t="inlineStr">
         <is>
-          <t>DEC-080</t>
+          <t>DEC-084</t>
         </is>
       </c>
       <c r="B160" s="68" t="inlineStr">
@@ -19474,7 +19556,7 @@
       <c r="C160" s="68" t="n"/>
       <c r="D160" s="69" t="inlineStr">
         <is>
-          <t>Un gate que comprueba que los nombres entre capas existen</t>
+          <t>«Perfil fiscal vigente» exige que ya haya empezado</t>
         </is>
       </c>
       <c r="E160" s="69" t="n"/>
@@ -19483,7 +19565,7 @@
     <row r="161" ht="34.5" customHeight="1" s="36">
       <c r="A161" s="67" t="inlineStr">
         <is>
-          <t>DEC-079</t>
+          <t>DEC-083</t>
         </is>
       </c>
       <c r="B161" s="68" t="inlineStr">
@@ -19494,7 +19576,7 @@
       <c r="C161" s="68" t="n"/>
       <c r="D161" s="69" t="inlineStr">
         <is>
-          <t>La identidad fiscal del cliente tiene permiso propio, en dos roles</t>
+          <t>«Cuenta compartida» se calcula al leer, no se guarda</t>
         </is>
       </c>
       <c r="E161" s="69" t="n"/>
@@ -19503,7 +19585,7 @@
     <row r="162" ht="45.75" customHeight="1" s="36">
       <c r="A162" s="67" t="inlineStr">
         <is>
-          <t>DEC-078</t>
+          <t>DEC-082</t>
         </is>
       </c>
       <c r="B162" s="68" t="inlineStr">
@@ -19514,7 +19596,7 @@
       <c r="C162" s="68" t="n"/>
       <c r="D162" s="69" t="inlineStr">
         <is>
-          <t>El histórico fiscal del cliente está congelado</t>
+          <t>Las sociedades del grupo las gestiona sólo admin</t>
         </is>
       </c>
       <c r="E162" s="69" t="n"/>
@@ -19523,7 +19605,7 @@
     <row r="163" ht="34.5" customHeight="1" s="36">
       <c r="A163" s="67" t="inlineStr">
         <is>
-          <t>DEC-077</t>
+          <t>DEC-081</t>
         </is>
       </c>
       <c r="B163" s="68" t="inlineStr">
@@ -19534,7 +19616,7 @@
       <c r="C163" s="68" t="n"/>
       <c r="D163" s="69" t="inlineStr">
         <is>
-          <t>Un contacto no cambia de cliente</t>
+          <t>Dar de baja una sociedad cierra sus coberturas abiertas</t>
         </is>
       </c>
       <c r="E163" s="69" t="n"/>
@@ -19543,7 +19625,7 @@
     <row r="164" ht="23.25" customHeight="1" s="36">
       <c r="A164" s="67" t="inlineStr">
         <is>
-          <t>DEC-076</t>
+          <t>DEC-080</t>
         </is>
       </c>
       <c r="B164" s="68" t="inlineStr">
@@ -19554,7 +19636,7 @@
       <c r="C164" s="68" t="n"/>
       <c r="D164" s="69" t="inlineStr">
         <is>
-          <t>La lista de suites de restricción vive en un solo archivo</t>
+          <t>Un gate que comprueba que los nombres entre capas existen</t>
         </is>
       </c>
       <c r="E164" s="69" t="n"/>
@@ -19563,7 +19645,7 @@
     <row r="165" ht="23.25" customHeight="1" s="36">
       <c r="A165" s="67" t="inlineStr">
         <is>
-          <t>DEC-075</t>
+          <t>DEC-079</t>
         </is>
       </c>
       <c r="B165" s="68" t="inlineStr">
@@ -19574,7 +19656,7 @@
       <c r="C165" s="68" t="n"/>
       <c r="D165" s="69" t="inlineStr">
         <is>
-          <t>El relevo del contacto principal se hace, no se rechaza</t>
+          <t>La identidad fiscal del cliente tiene permiso propio, en dos roles</t>
         </is>
       </c>
       <c r="E165" s="69" t="n"/>
@@ -19583,7 +19665,7 @@
     <row r="166" ht="23.25" customHeight="1" s="36">
       <c r="A166" s="67" t="inlineStr">
         <is>
-          <t>DEC-074</t>
+          <t>DEC-078</t>
         </is>
       </c>
       <c r="B166" s="68" t="inlineStr">
@@ -19594,7 +19676,7 @@
       <c r="C166" s="68" t="n"/>
       <c r="D166" s="69" t="inlineStr">
         <is>
-          <t>Al dar de alta un cliente se crea su primera marca</t>
+          <t>El histórico fiscal del cliente está congelado</t>
         </is>
       </c>
       <c r="E166" s="69" t="n"/>
@@ -19603,7 +19685,7 @@
     <row r="167" ht="34.5" customHeight="1" s="36">
       <c r="A167" s="67" t="inlineStr">
         <is>
-          <t>DEC-073</t>
+          <t>DEC-077</t>
         </is>
       </c>
       <c r="B167" s="68" t="inlineStr">
@@ -19614,20 +19696,16 @@
       <c r="C167" s="68" t="n"/>
       <c r="D167" s="69" t="inlineStr">
         <is>
-          <t>Un prospecto se apunta en cualquier país; activarlo exige cobertura</t>
-        </is>
-      </c>
-      <c r="E167" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>Un contacto no cambia de cliente</t>
+        </is>
+      </c>
+      <c r="E167" s="69" t="n"/>
       <c r="F167" s="69" t="n"/>
     </row>
     <row r="168" ht="23.25" customHeight="1" s="36">
       <c r="A168" s="67" t="inlineStr">
         <is>
-          <t>DEC-072</t>
+          <t>DEC-076</t>
         </is>
       </c>
       <c r="B168" s="68" t="inlineStr">
@@ -19638,7 +19716,7 @@
       <c r="C168" s="68" t="n"/>
       <c r="D168" s="69" t="inlineStr">
         <is>
-          <t>creator_addresses queda fuera de la regla de periodos</t>
+          <t>La lista de suites de restricción vive en un solo archivo</t>
         </is>
       </c>
       <c r="E168" s="69" t="n"/>
@@ -19647,7 +19725,7 @@
     <row r="169" ht="45.75" customHeight="1" s="36">
       <c r="A169" s="67" t="inlineStr">
         <is>
-          <t>DEC-071</t>
+          <t>DEC-075</t>
         </is>
       </c>
       <c r="B169" s="68" t="inlineStr">
@@ -19658,7 +19736,7 @@
       <c r="C169" s="68" t="n"/>
       <c r="D169" s="69" t="inlineStr">
         <is>
-          <t>Un perfil fiscal nuevo no puede empezar antes que el vigente</t>
+          <t>El relevo del contacto principal se hace, no se rechaza</t>
         </is>
       </c>
       <c r="E169" s="69" t="n"/>
@@ -19667,7 +19745,7 @@
     <row r="170" ht="45.75" customHeight="1" s="36">
       <c r="A170" s="67" t="inlineStr">
         <is>
-          <t>DEC-070</t>
+          <t>DEC-074</t>
         </is>
       </c>
       <c r="B170" s="68" t="inlineStr">
@@ -19678,7 +19756,7 @@
       <c r="C170" s="68" t="n"/>
       <c r="D170" s="69" t="inlineStr">
         <is>
-          <t>Un bloqueo de agenda se registra aunque pise una campaña aceptada</t>
+          <t>Al dar de alta un cliente se crea su primera marca</t>
         </is>
       </c>
       <c r="E170" s="69" t="n"/>
@@ -19687,7 +19765,7 @@
     <row r="171" ht="23.25" customHeight="1" s="36">
       <c r="A171" s="67" t="inlineStr">
         <is>
-          <t>DEC-069</t>
+          <t>DEC-073</t>
         </is>
       </c>
       <c r="B171" s="68" t="inlineStr">
@@ -19698,7 +19776,7 @@
       <c r="C171" s="68" t="n"/>
       <c r="D171" s="69" t="inlineStr">
         <is>
-          <t>Las tarifas tienen permiso propio: creator.rate.manage</t>
+          <t>Un prospecto se apunta en cualquier país; activarlo exige cobertura</t>
         </is>
       </c>
       <c r="E171" s="69" t="inlineStr">
@@ -19711,7 +19789,7 @@
     <row r="172" ht="34.5" customHeight="1" s="36">
       <c r="A172" s="67" t="inlineStr">
         <is>
-          <t>DEC-068</t>
+          <t>DEC-072</t>
         </is>
       </c>
       <c r="B172" s="68" t="inlineStr">
@@ -19722,20 +19800,16 @@
       <c r="C172" s="68" t="n"/>
       <c r="D172" s="69" t="inlineStr">
         <is>
-          <t>Cero es un precio válido, pero hay que declararlo</t>
-        </is>
-      </c>
-      <c r="E172" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>creator_addresses queda fuera de la regla de periodos</t>
+        </is>
+      </c>
+      <c r="E172" s="69" t="n"/>
       <c r="F172" s="69" t="n"/>
     </row>
     <row r="173" ht="34.5" customHeight="1" s="36">
       <c r="A173" s="67" t="inlineStr">
         <is>
-          <t>DEC-067</t>
+          <t>DEC-071</t>
         </is>
       </c>
       <c r="B173" s="68" t="inlineStr">
@@ -19746,20 +19820,16 @@
       <c r="C173" s="68" t="n"/>
       <c r="D173" s="69" t="inlineStr">
         <is>
-          <t>Los dos permisos de medios de pago van al rol finance</t>
-        </is>
-      </c>
-      <c r="E173" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
-        </is>
-      </c>
+          <t>Un perfil fiscal nuevo no puede empezar antes que el vigente</t>
+        </is>
+      </c>
+      <c r="E173" s="69" t="n"/>
       <c r="F173" s="69" t="n"/>
     </row>
     <row r="174" ht="45.75" customHeight="1" s="36">
       <c r="A174" s="67" t="inlineStr">
         <is>
-          <t>DEC-066</t>
+          <t>DEC-070</t>
         </is>
       </c>
       <c r="B174" s="68" t="inlineStr">
@@ -19770,20 +19840,16 @@
       <c r="C174" s="68" t="n"/>
       <c r="D174" s="69" t="inlineStr">
         <is>
-          <t>La cuenta de un medio de pago es inmutable: se sustituye, no se edita</t>
-        </is>
-      </c>
-      <c r="E174" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
-        </is>
-      </c>
+          <t>Un bloqueo de agenda se registra aunque pise una campaña aceptada</t>
+        </is>
+      </c>
+      <c r="E174" s="69" t="n"/>
       <c r="F174" s="69" t="n"/>
     </row>
     <row r="175" ht="34.5" customHeight="1" s="36">
       <c r="A175" s="67" t="inlineStr">
         <is>
-          <t>DEC-065</t>
+          <t>DEC-069</t>
         </is>
       </c>
       <c r="B175" s="68" t="inlineStr">
@@ -19794,12 +19860,12 @@
       <c r="C175" s="68" t="n"/>
       <c r="D175" s="69" t="inlineStr">
         <is>
-          <t>La misma cuenta en dos creadores se marca, no se rechaza</t>
+          <t>Las tarifas tienen permiso propio: creator.rate.manage</t>
         </is>
       </c>
       <c r="E175" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
         </is>
       </c>
       <c r="F175" s="69" t="n"/>
@@ -19807,7 +19873,7 @@
     <row r="176" ht="45.75" customHeight="1" s="36">
       <c r="A176" s="67" t="inlineStr">
         <is>
-          <t>DEC-064</t>
+          <t>DEC-068</t>
         </is>
       </c>
       <c r="B176" s="68" t="inlineStr">
@@ -19818,12 +19884,12 @@
       <c r="C176" s="68" t="n"/>
       <c r="D176" s="69" t="inlineStr">
         <is>
-          <t>El enfriamiento de un medio de pago son 24 horas, y es configuración</t>
+          <t>Cero es un precio válido, pero hay que declararlo</t>
         </is>
       </c>
       <c r="E176" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
         </is>
       </c>
       <c r="F176" s="69" t="n"/>
@@ -19831,7 +19897,7 @@
     <row r="177" ht="34.5" customHeight="1" s="36">
       <c r="A177" s="67" t="inlineStr">
         <is>
-          <t>DEC-063</t>
+          <t>DEC-067</t>
         </is>
       </c>
       <c r="B177" s="68" t="inlineStr">
@@ -19842,12 +19908,12 @@
       <c r="C177" s="68" t="n"/>
       <c r="D177" s="69" t="inlineStr">
         <is>
-          <t>Los umbrales de coherencia son juicio, no verdad; y no rechazan nada</t>
+          <t>Los dos permisos de medios de pago van al rol finance</t>
         </is>
       </c>
       <c r="E177" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.7) — umbrales revisables</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F177" s="69" t="n"/>
@@ -19855,7 +19921,7 @@
     <row r="178" ht="34.5" customHeight="1" s="36">
       <c r="A178" s="67" t="inlineStr">
         <is>
-          <t>DEC-062</t>
+          <t>DEC-066</t>
         </is>
       </c>
       <c r="B178" s="68" t="inlineStr">
@@ -19866,12 +19932,12 @@
       <c r="C178" s="68" t="n"/>
       <c r="D178" s="69" t="inlineStr">
         <is>
-          <t>Los dos permisos fiscales van al mismo rol; la separación la impone la base</t>
+          <t>La cuenta de un medio de pago es inmutable: se sustituye, no se edita</t>
         </is>
       </c>
       <c r="E178" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.6)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F178" s="69" t="n"/>
@@ -19879,7 +19945,7 @@
     <row r="179" ht="23.25" customHeight="1" s="36">
       <c r="A179" s="67" t="inlineStr">
         <is>
-          <t>DEC-061</t>
+          <t>DEC-065</t>
         </is>
       </c>
       <c r="B179" s="68" t="inlineStr">
@@ -19890,12 +19956,12 @@
       <c r="C179" s="68" t="n"/>
       <c r="D179" s="69" t="inlineStr">
         <is>
-          <t>Las pruebas usan una base local y desechable, nunca la de desarrollo</t>
+          <t>La misma cuenta en dos creadores se marca, no se rechaza</t>
         </is>
       </c>
       <c r="E179" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F179" s="69" t="n"/>
@@ -19903,7 +19969,7 @@
     <row r="180" ht="34.5" customHeight="1" s="36">
       <c r="A180" s="67" t="inlineStr">
         <is>
-          <t>DEC-060</t>
+          <t>DEC-064</t>
         </is>
       </c>
       <c r="B180" s="68" t="inlineStr">
@@ -19914,12 +19980,12 @@
       <c r="C180" s="68" t="n"/>
       <c r="D180" s="69" t="inlineStr">
         <is>
-          <t>Verificar y activar son permisos distintos, pero hoy el mismo rol</t>
+          <t>El enfriamiento de un medio de pago son 24 horas, y es configuración</t>
         </is>
       </c>
       <c r="E180" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-23, iteración 3.5) — decisión de negocio revisable</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F180" s="69" t="n"/>
@@ -19927,7 +19993,7 @@
     <row r="181" ht="90.75" customHeight="1" s="36">
       <c r="A181" s="67" t="inlineStr">
         <is>
-          <t>DEC-059</t>
+          <t>DEC-063</t>
         </is>
       </c>
       <c r="B181" s="68" t="inlineStr">
@@ -19938,12 +20004,12 @@
       <c r="C181" s="68" t="n"/>
       <c r="D181" s="69" t="inlineStr">
         <is>
-          <t>Se acepta una versión de los términos, no una página</t>
+          <t>Los umbrales de coherencia son juicio, no verdad; y no rechazan nada</t>
         </is>
       </c>
       <c r="E181" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.7) — umbrales revisables</t>
         </is>
       </c>
       <c r="F181" s="69" t="n"/>
@@ -19951,7 +20017,7 @@
     <row r="182" ht="34.5" customHeight="1" s="36">
       <c r="A182" s="67" t="inlineStr">
         <is>
-          <t>DEC-058</t>
+          <t>DEC-062</t>
         </is>
       </c>
       <c r="B182" s="68" t="inlineStr">
@@ -19962,12 +20028,12 @@
       <c r="C182" s="68" t="n"/>
       <c r="D182" s="69" t="inlineStr">
         <is>
-          <t>La identidad verificada es evidencia, no una casilla</t>
+          <t>Los dos permisos fiscales van al mismo rol; la separación la impone la base</t>
         </is>
       </c>
       <c r="E182" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.6)</t>
         </is>
       </c>
       <c r="F182" s="69" t="n"/>
@@ -19975,7 +20041,7 @@
     <row r="183" ht="23.25" customHeight="1" s="36">
       <c r="A183" s="67" t="inlineStr">
         <is>
-          <t>DEC-057</t>
+          <t>DEC-061</t>
         </is>
       </c>
       <c r="B183" s="68" t="inlineStr">
@@ -19986,12 +20052,12 @@
       <c r="C183" s="68" t="n"/>
       <c r="D183" s="69" t="inlineStr">
         <is>
-          <t>Aprobar una solicitud no activa al creador</t>
+          <t>Las pruebas usan una base local y desechable, nunca la de desarrollo</t>
         </is>
       </c>
       <c r="E183" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.4)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
         </is>
       </c>
       <c r="F183" s="69" t="n"/>
@@ -19999,7 +20065,7 @@
     <row r="184" ht="34.5" customHeight="1" s="36">
       <c r="A184" s="67" t="inlineStr">
         <is>
-          <t>DEC-056</t>
+          <t>DEC-060</t>
         </is>
       </c>
       <c r="B184" s="68" t="inlineStr">
@@ -20010,12 +20076,12 @@
       <c r="C184" s="68" t="n"/>
       <c r="D184" s="69" t="inlineStr">
         <is>
-          <t>La bitácora se ordena por id, no por fecha, y redacta lo sensible</t>
+          <t>Verificar y activar son permisos distintos, pero hoy el mismo rol</t>
         </is>
       </c>
       <c r="E184" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.3)</t>
+          <t>ADOPTADA (2026-08-23, iteración 3.5) — decisión de negocio revisable</t>
         </is>
       </c>
       <c r="F184" s="69" t="n"/>
@@ -20023,7 +20089,7 @@
     <row r="185" ht="34.5" customHeight="1" s="36">
       <c r="A185" s="67" t="inlineStr">
         <is>
-          <t>DEC-055</t>
+          <t>DEC-059</t>
         </is>
       </c>
       <c r="B185" s="68" t="inlineStr">
@@ -20034,24 +20100,20 @@
       <c r="C185" s="68" t="n"/>
       <c r="D185" s="69" t="inlineStr">
         <is>
-          <t>La primera pantalla de escritura no toca la identidad</t>
+          <t>Se acepta una versión de los términos, no una página</t>
         </is>
       </c>
       <c r="E185" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
-        </is>
-      </c>
-      <c r="F185" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Primera pantalla del proyecto que escribe: edición de creador.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+        </is>
+      </c>
+      <c r="F185" s="69" t="n"/>
     </row>
     <row r="186" ht="34.5" customHeight="1" s="36">
       <c r="A186" s="67" t="inlineStr">
         <is>
-          <t>DEC-054</t>
+          <t>DEC-058</t>
         </is>
       </c>
       <c r="B186" s="68" t="inlineStr">
@@ -20062,24 +20124,20 @@
       <c r="C186" s="68" t="n"/>
       <c r="D186" s="69" t="inlineStr">
         <is>
-          <t>La bitácora es inmutable en la base, no por convención</t>
+          <t>La identidad verificada es evidencia, no una casilla</t>
         </is>
       </c>
       <c r="E186" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
-        </is>
-      </c>
-      <c r="F186" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — audit_logs existía desde 2.4 y nadie escribía en ella. Al ir a llenarla apareció el segundo problema: la tabla admitía UPDATE y DELETE como cualquier otra.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+        </is>
+      </c>
+      <c r="F186" s="69" t="n"/>
     </row>
     <row r="187" ht="34.5" customHeight="1" s="36">
       <c r="A187" s="67" t="inlineStr">
         <is>
-          <t>DEC-053</t>
+          <t>DEC-057</t>
         </is>
       </c>
       <c r="B187" s="68" t="inlineStr">
@@ -20090,12 +20148,12 @@
       <c r="C187" s="68" t="n"/>
       <c r="D187" s="69" t="inlineStr">
         <is>
-          <t>Autorización por permiso, sin atajo para el administrador</t>
+          <t>Aprobar una solicitud no activa al creador</t>
         </is>
       </c>
       <c r="E187" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.1)</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.4)</t>
         </is>
       </c>
       <c r="F187" s="69" t="n"/>
@@ -20103,7 +20161,7 @@
     <row r="188" ht="34.5" customHeight="1" s="36">
       <c r="A188" s="67" t="inlineStr">
         <is>
-          <t>DEC-052</t>
+          <t>DEC-056</t>
         </is>
       </c>
       <c r="B188" s="68" t="inlineStr">
@@ -20114,12 +20172,12 @@
       <c r="C188" s="68" t="n"/>
       <c r="D188" s="69" t="inlineStr">
         <is>
-          <t>MySQL no admite subconsultas sobre la tabla que se está modificando</t>
+          <t>La bitácora se ordena por id, no por fecha, y redacta lo sensible</t>
         </is>
       </c>
       <c r="E188" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22)</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.3)</t>
         </is>
       </c>
       <c r="F188" s="69" t="n"/>
@@ -20127,7 +20185,7 @@
     <row r="189" ht="34.5" customHeight="1" s="36">
       <c r="A189" s="67" t="inlineStr">
         <is>
-          <t>DEC-051</t>
+          <t>DEC-055</t>
         </is>
       </c>
       <c r="B189" s="68" t="inlineStr">
@@ -20138,24 +20196,24 @@
       <c r="C189" s="68" t="n"/>
       <c r="D189" s="69" t="inlineStr">
         <is>
-          <t>El CI corre la suite contra los dos motores, no contra uno</t>
+          <t>La primera pantalla de escritura no toca la identidad</t>
         </is>
       </c>
       <c r="E189" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22). Recordatorio: tools/github-workflow-ci.yml sigue pendiente de mover a .github/workflows/ci.yml a mano — es ruta protegida</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
         </is>
       </c>
       <c r="F189" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — El CI validaba formato, análisis estático, fronteras entre módulos, migraciones y pruebas. Nada de eso comprueba que las restricciones se apliquen en el motor de producción, que no aplica CHECK.</t>
+          <t xml:space="preserve"> — Primera pantalla del proyecto que escribe: edición de creador.</t>
         </is>
       </c>
     </row>
     <row r="190" ht="23.25" customHeight="1" s="36">
       <c r="A190" s="67" t="inlineStr">
         <is>
-          <t>DEC-050</t>
+          <t>DEC-054</t>
         </is>
       </c>
       <c r="B190" s="68" t="inlineStr">
@@ -20166,20 +20224,24 @@
       <c r="C190" s="68" t="n"/>
       <c r="D190" s="69" t="inlineStr">
         <is>
-          <t>Las migraciones se contrastan contra el esquema de referencia, no se confía en que coincidan</t>
+          <t>La bitácora es inmutable en la base, no por convención</t>
         </is>
       </c>
       <c r="E190" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22)</t>
-        </is>
-      </c>
-      <c r="F190" s="69" t="n"/>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
+        </is>
+      </c>
+      <c r="F190" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — audit_logs existía desde 2.4 y nadie escribía en ella. Al ir a llenarla apareció el segundo problema: la tabla admitía UPDATE y DELETE como cualquier otra.</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="23.25" customHeight="1" s="36">
       <c r="A191" s="67" t="inlineStr">
         <is>
-          <t>DEC-049</t>
+          <t>DEC-053</t>
         </is>
       </c>
       <c r="B191" s="68" t="inlineStr">
@@ -20190,24 +20252,20 @@
       <c r="C191" s="68" t="n"/>
       <c r="D191" s="69" t="inlineStr">
         <is>
-          <t>Sin datos fiscales no hay alta, pero acompañamos a formalizarse</t>
+          <t>Autorización por permiso, sin atajo para el administrador</t>
         </is>
       </c>
       <c r="E191" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22)</t>
-        </is>
-      </c>
-      <c r="F191" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Respuesta a Q-45. La propuesta inicial era pagar a un familiar del creador con declaración jurada de parentesco. El análisis de docs/fase-2/2.14-PAGO-A-TERCEROS.md identificó tres problemas: el comprobante deja de coincidir con el pago (riesgo de gasto reparable para la empresa que paga), señales de alerta de prevención de lavado, y contradicción con BR-FIN-003, que ya está implementada.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.1)</t>
+        </is>
+      </c>
+      <c r="F191" s="69" t="n"/>
     </row>
     <row r="192" ht="45.75" customHeight="1" s="36">
       <c r="A192" s="67" t="inlineStr">
         <is>
-          <t>DEC-048</t>
+          <t>DEC-052</t>
         </is>
       </c>
       <c r="B192" s="68" t="inlineStr">
@@ -20218,24 +20276,20 @@
       <c r="C192" s="68" t="n"/>
       <c r="D192" s="69" t="inlineStr">
         <is>
-          <t>La retención tiene tres estados, no dos</t>
+          <t>MySQL no admite subconsultas sobre la tabla que se está modificando</t>
         </is>
       </c>
       <c r="E192" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.15)</t>
-        </is>
-      </c>
-      <c r="F192" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Sobre Q-40 se decidió «que el modelo lo deje configurable». Al implementarlo apareció que el riesgo que yo había señalado —*«alguien pone un número a ojo y nadie se entera»*— ya estaba dentro del modelo, y era peor.</t>
-        </is>
-      </c>
+          <t>ADOPTADA (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="F192" s="69" t="n"/>
     </row>
     <row r="193" ht="34.5" customHeight="1" s="36">
       <c r="A193" s="67" t="inlineStr">
         <is>
-          <t>DEC-047</t>
+          <t>DEC-051</t>
         </is>
       </c>
       <c r="B193" s="68" t="inlineStr">
@@ -20246,24 +20300,24 @@
       <c r="C193" s="68" t="n"/>
       <c r="D193" s="69" t="inlineStr">
         <is>
-          <t>Se factura a todos los países desde Perú</t>
+          <t>El CI corre la suite contra los dos motores, no contra uno</t>
         </is>
       </c>
       <c r="E193" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22)</t>
+          <t>ADOPTADA (2026-08-22). Recordatorio: tools/github-workflow-ci.yml sigue pendiente de mover a .github/workflows/ci.yml a mano — es ruta protegida</t>
         </is>
       </c>
       <c r="F193" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Respuesta a Q-42. En lugar de constituir sociedad en cada país, se emiten todos los comprobantes desde la sociedad peruana. Los países se resuelven uno a uno más adelante.</t>
+          <t xml:space="preserve"> — El CI validaba formato, análisis estático, fronteras entre módulos, migraciones y pruebas. Nada de eso comprueba que las restricciones se apliquen en el motor de producción, que no aplica CHECK.</t>
         </is>
       </c>
     </row>
     <row r="194" ht="34.5" customHeight="1" s="36">
       <c r="A194" s="67" t="inlineStr">
         <is>
-          <t>DEC-046</t>
+          <t>DEC-050</t>
         </is>
       </c>
       <c r="B194" s="68" t="inlineStr">
@@ -20274,24 +20328,20 @@
       <c r="C194" s="68" t="n"/>
       <c r="D194" s="69" t="inlineStr">
         <is>
-          <t>La base impone lo que ve en una fila; el resto lo impone el repositorio</t>
+          <t>Las migraciones se contrastan contra el esquema de referencia, no se confía en que coincidan</t>
         </is>
       </c>
       <c r="E194" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22, iteración 2.13)</t>
-        </is>
-      </c>
-      <c r="F194" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Cinco invariantes de finanzas son de varias filas o varias tablas (suma de líneas = subtotal, cobros ≤ total facturado, moneda de asiento = moneda de su payout, signo de una reversión, saldo no negativo). Ningún CHECK puede expresarlas.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="F194" s="69" t="n"/>
     </row>
     <row r="195" ht="23.25" customHeight="1" s="36">
       <c r="A195" s="67" t="inlineStr">
         <is>
-          <t>DEC-045</t>
+          <t>DEC-049</t>
         </is>
       </c>
       <c r="B195" s="68" t="inlineStr">
@@ -20302,24 +20352,24 @@
       <c r="C195" s="68" t="n"/>
       <c r="D195" s="69" t="inlineStr">
         <is>
-          <t>La inmutabilidad financiera se impone con disparadores, no con convención</t>
+          <t>Sin datos fiscales no hay alta, pero acompañamos a formalizarse</t>
         </is>
       </c>
       <c r="E195" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA (2026-08-22)</t>
         </is>
       </c>
       <c r="F195" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — BR-FIN-008 («ningún registro financiero se elimina físicamente») y BR-FIN-002 («una corrección es un asiento de reversión») eran hasta ahora reglas de la capa de aplicación.</t>
+          <t xml:space="preserve"> — Respuesta a Q-45. La propuesta inicial era pagar a un familiar del creador con declaración jurada de parentesco. El análisis de docs/fase-2/2.14-PAGO-A-TERCEROS.md identificó tres problemas: el comprobante deja de coincidir con el pago (riesgo de gasto reparable para la empresa que paga), señales de alerta de prevención de lavado, y contradicción con BR-FIN-003, que ya está implementada.</t>
         </is>
       </c>
     </row>
     <row r="196" ht="57" customHeight="1" s="36">
       <c r="A196" s="67" t="inlineStr">
         <is>
-          <t>DEC-044</t>
+          <t>DEC-048</t>
         </is>
       </c>
       <c r="B196" s="68" t="inlineStr">
@@ -20330,24 +20380,24 @@
       <c r="C196" s="68" t="n"/>
       <c r="D196" s="69" t="inlineStr">
         <is>
-          <t>Todo pago pertenece a un lote (no existen pagos sueltos)</t>
+          <t>La retención tiene tres estados, no dos</t>
         </is>
       </c>
       <c r="E196" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.15)</t>
         </is>
       </c>
       <c r="F196" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — La primera versión de payouts permitía payout_batch_id NULL, pensando en el pago puntual fuera de la corrida quincenal.</t>
+          <t xml:space="preserve"> — Sobre Q-40 se decidió «que el modelo lo deje configurable». Al implementarlo apareció que el riesgo que yo había señalado —*«alguien pone un número a ojo y nadie se entera»*— ya estaba dentro del modelo, y era peor.</t>
         </is>
       </c>
     </row>
     <row r="197" ht="23.25" customHeight="1" s="36">
       <c r="A197" s="67" t="inlineStr">
         <is>
-          <t>DEC-043</t>
+          <t>DEC-047</t>
         </is>
       </c>
       <c r="B197" s="68" t="inlineStr">
@@ -20358,24 +20408,24 @@
       <c r="C197" s="68" t="n"/>
       <c r="D197" s="69" t="inlineStr">
         <is>
-          <t>Dónde vive la base de datos de desarrollo</t>
+          <t>Se factura a todos los países desde Perú</t>
         </is>
       </c>
       <c r="E197" s="69" t="inlineStr">
         <is>
-          <t>ACORDADA en su intención; el motor concreto depende de DEC-042</t>
+          <t>ADOPTADA e implementada (2026-08-22)</t>
         </is>
       </c>
       <c r="F197" s="69" t="inlineStr">
         <is>
-          <t>C. Es lo que hace un equipo profesional y no cuesta más que A: el motor local se instala una vez. El bucle interno —migrar, probar, deshacer, repetir— tiene que ser rápido o se deja de ejecutar, y unas pruebas que tardan minutos son unas pruebas que nadie corre. La base remota es el ensayo general, no el banco de trabajo. — Se propone usar el mismo servidor que producción, con dos bases separadas: una de desarrollo y otra de producción. No es trabajar contra los datos reales; es usar el mismo motor. Ya hay otras aplicaciones Laravel funcionando en ese servidor sin incidencias.</t>
+          <t xml:space="preserve"> — Respuesta a Q-42. En lugar de constituir sociedad en cada país, se emiten todos los comprobantes desde la sociedad peruana. Los países se resuelven uno a uno más adelante.</t>
         </is>
       </c>
     </row>
     <row r="198" ht="23.25" customHeight="1" s="36">
       <c r="A198" s="67" t="inlineStr">
         <is>
-          <t>DEC-042</t>
+          <t>DEC-046</t>
         </is>
       </c>
       <c r="B198" s="68" t="inlineStr">
@@ -20386,136 +20436,136 @@
       <c r="C198" s="68" t="n"/>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>🔴 El servidor es MySQL 5.7 y no aplica los CHECK *(confirmado empíricamente)*</t>
+          <t>La base impone lo que ve en una fila; el resto lo impone el repositorio</t>
         </is>
       </c>
       <c r="E198" s="69" t="inlineStr">
         <is>
-          <t>🔴 CONFIRMADA — pendiente de elegir entre B y C</t>
+          <t>ADOPTADA (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F198" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — El servidor de la aplicación es Percona Server 5.7.44-48 sobre cPanel. La base de desarrollo (..._dev) y la de producción viven en él. docs/03 asumía MySQL 8.</t>
+          <t xml:space="preserve"> — Cinco invariantes de finanzas son de varias filas o varias tablas (suma de líneas = subtotal, cobros ≤ total facturado, moneda de asiento = moneda de su payout, signo de una reversión, saldo no negativo). Ningún CHECK puede expresarlas.</t>
         </is>
       </c>
     </row>
     <row r="199" ht="23.25" customHeight="1" s="36">
       <c r="A199" s="67" t="inlineStr">
         <is>
-          <t>DEC-041</t>
+          <t>DEC-045</t>
         </is>
       </c>
       <c r="B199" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C199" s="68" t="n"/>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>Gamificación y Creator Score no se fusionan</t>
+          <t>La inmutabilidad financiera se impone con disparadores, no con convención</t>
         </is>
       </c>
       <c r="E199" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F199" s="69" t="inlineStr">
         <is>
-          <t>B. El Score es interno, puede bajar y sirve para decidir a quién invitar; el XP es externo, nunca baja y sirve para motivar. Un creador que incumplió una vez debe bajar en el score y conservar el XP que ganó antes. — Ambos calculan un número sobre un creador a partir de los mismos eventos. La tentación de unirlos es enorme.</t>
+          <t xml:space="preserve"> — BR-FIN-008 («ningún registro financiero se elimina físicamente») y BR-FIN-002 («una corrección es un asiento de reversión») eran hasta ahora reglas de la capa de aplicación.</t>
         </is>
       </c>
     </row>
     <row r="200" ht="45.75" customHeight="1" s="36">
       <c r="A200" s="67" t="inlineStr">
         <is>
-          <t>DEC-040</t>
+          <t>DEC-044</t>
         </is>
       </c>
       <c r="B200" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C200" s="68" t="n"/>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>Referidos con consolidación diferida</t>
+          <t>Todo pago pertenece a un lote (no existen pagos sueltos)</t>
         </is>
       </c>
       <c r="E200" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F200" s="69" t="inlineStr">
         <is>
-          <t>B, más topes por periodo y verificación de que referente y referido no comparten documento, teléfono ni medio de pago. El vínculo se conserva siempre aunque el XP no se consolide: es dato de negocio. — Un programa de referidos con recompensa es, sin excepción, un imán de fraude: autorreferidos, cuentas falsas, granjas.</t>
+          <t xml:space="preserve"> — La primera versión de payouts permitía payout_batch_id NULL, pensando en el pago puntual fuera de la corrida quincenal.</t>
         </is>
       </c>
     </row>
     <row r="201" ht="34.5" customHeight="1" s="36">
       <c r="A201" s="67" t="inlineStr">
         <is>
-          <t>DEC-039</t>
+          <t>DEC-043</t>
         </is>
       </c>
       <c r="B201" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C201" s="68" t="n"/>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>Los retos internos llevan siempre recompensa tangible 🔴</t>
+          <t>Dónde vive la base de datos de desarrollo</t>
         </is>
       </c>
       <c r="E201" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>ACORDADA en su intención; el motor concreto depende de DEC-042</t>
         </is>
       </c>
       <c r="F201" s="69" t="inlineStr">
         <is>
-          <t>B, sin excepción. El XP es el envoltorio y el reconocimiento; nunca el pago. Es la salvaguarda que la propia especificación anticipó en §16. — "Minicampañas de XP por hacer vídeos para la plataforma". Leído desde el otro lado, puede sonar a *"produce contenido de marketing para mi empresa y te pago con puntos"* — a creadores que ya producen por dinero para tus clientes. En una red pequeña, ese daño reputacional se propaga en un grupo de WhatsApp.</t>
+          <t>C. Es lo que hace un equipo profesional y no cuesta más que A: el motor local se instala una vez. El bucle interno —migrar, probar, deshacer, repetir— tiene que ser rápido o se deja de ejecutar, y unas pruebas que tardan minutos son unas pruebas que nadie corre. La base remota es el ensayo general, no el banco de trabajo. — Se propone usar el mismo servidor que producción, con dos bases separadas: una de desarrollo y otra de producción. No es trabajar contra los datos reales; es usar el mismo motor. Ya hay otras aplicaciones Laravel funcionando en ese servidor sin incidencias.</t>
         </is>
       </c>
     </row>
     <row r="202" ht="57" customHeight="1" s="36">
       <c r="A202" s="67" t="inlineStr">
         <is>
-          <t>DEC-038</t>
+          <t>DEC-042</t>
         </is>
       </c>
       <c r="B202" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C202" s="68" t="n"/>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>Ranking por cohortes, sin tabla global</t>
+          <t>🔴 El servidor es MySQL 5.7 y no aplica los CHECK *(confirmado empíricamente)*</t>
         </is>
       </c>
       <c r="E202" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>🔴 CONFIRMADA — pendiente de elegir entre B y C</t>
         </is>
       </c>
       <c r="F202" s="69" t="inlineStr">
         <is>
-          <t>C. Los puntos de liga se reinician por temporada; el XP nunca. Sin ranking público por ingresos, jamás. Un ranking global solo tiene sentido en una vista interna, y ahí es un reporte, no gamificación. — Una clasificación global con 1.000 creadores significa que 990 abren la app y ven que están perdiendo. Y con el tiempo se estanca: quien lleva más tiempo acumula más.</t>
+          <t xml:space="preserve"> — El servidor de la aplicación es Percona Server 5.7.44-48 sobre cPanel. La base de desarrollo (..._dev) y la de producción viven en él. docs/03 asumía MySQL 8.</t>
         </is>
       </c>
     </row>
     <row r="203" ht="23.25" customHeight="1" s="36">
       <c r="A203" s="67" t="inlineStr">
         <is>
-          <t>DEC-037</t>
+          <t>DEC-041</t>
         </is>
       </c>
       <c r="B203" s="68" t="inlineStr">
@@ -20526,7 +20576,7 @@
       <c r="C203" s="68" t="n"/>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>Los niveles se calculan, no se almacenan</t>
+          <t>Gamificación y Creator Score no se fusionan</t>
         </is>
       </c>
       <c r="E203" s="69" t="inlineStr">
@@ -20536,14 +20586,14 @@
       </c>
       <c r="F203" s="69" t="inlineStr">
         <is>
-          <t>B. Permite ajustar umbrales sin quitarle puntos a nadie, que es justamente lo que DEC-035 prohíbe. — Las curvas de nivel se recalibran; el XP ya otorgado no debe verse afectado.</t>
+          <t>B. El Score es interno, puede bajar y sirve para decidir a quién invitar; el XP es externo, nunca baja y sirve para motivar. Un creador que incumplió una vez debe bajar en el score y conservar el XP que ganó antes. — Ambos calculan un número sobre un creador a partir de los mismos eventos. La tentación de unirlos es enorme.</t>
         </is>
       </c>
     </row>
     <row r="204" ht="23.25" customHeight="1" s="36">
       <c r="A204" s="67" t="inlineStr">
         <is>
-          <t>DEC-036</t>
+          <t>DEC-040</t>
         </is>
       </c>
       <c r="B204" s="68" t="inlineStr">
@@ -20554,7 +20604,7 @@
       <c r="C204" s="68" t="n"/>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>Se premia comportamiento verificado, no resultados</t>
+          <t>Referidos con consolidación diferida</t>
         </is>
       </c>
       <c r="E204" s="69" t="inlineStr">
@@ -20564,14 +20614,14 @@
       </c>
       <c r="F204" s="69" t="inlineStr">
         <is>
-          <t>C. A premia al algoritmo de Instagram, no al creador. B produce sobrecompromiso —creadores que aceptan lo que no pueden cumplir— y, en el caso de seguidores, desmotiva al micro-creador y premia el vector de fraude de R-04. Detalle en docs/13 §3. — ¿Sobre qué se otorga XP?</t>
+          <t>B, más topes por periodo y verificación de que referente y referido no comparten documento, teléfono ni medio de pago. El vínculo se conserva siempre aunque el XP no se consolide: es dato de negocio. — Un programa de referidos con recompensa es, sin excepción, un imán de fraude: autorreferidos, cuentas falsas, granjas.</t>
         </is>
       </c>
     </row>
     <row r="205" ht="23.25" customHeight="1" s="36">
       <c r="A205" s="67" t="inlineStr">
         <is>
-          <t>DEC-035</t>
+          <t>DEC-039</t>
         </is>
       </c>
       <c r="B205" s="68" t="inlineStr">
@@ -20582,7 +20632,7 @@
       <c r="C205" s="68" t="n"/>
       <c r="D205" s="69" t="inlineStr">
         <is>
-          <t>El XP es append-only y nunca decrece</t>
+          <t>Los retos internos llevan siempre recompensa tangible 🔴</t>
         </is>
       </c>
       <c r="E205" s="69" t="inlineStr">
@@ -20592,14 +20642,14 @@
       </c>
       <c r="F205" s="69" t="inlineStr">
         <is>
-          <t>B. Quitar puntos se percibe como robo y destruye la confianza de golpe. Además sería castigar dos veces con el mecanismo equivocado. Mismo patrón que el ledger financiero: se corrige con asientos nuevos, no editando. — ¿Se puede restar XP por un incumplimiento?</t>
+          <t>B, sin excepción. El XP es el envoltorio y el reconocimiento; nunca el pago. Es la salvaguarda que la propia especificación anticipó en §16. — "Minicampañas de XP por hacer vídeos para la plataforma". Leído desde el otro lado, puede sonar a *"produce contenido de marketing para mi empresa y te pago con puntos"* — a creadores que ya producen por dinero para tus clientes. En una red pequeña, ese daño reputacional se propaga en un grupo de WhatsApp.</t>
         </is>
       </c>
     </row>
     <row r="206" ht="45.75" customHeight="1" s="36">
       <c r="A206" s="67" t="inlineStr">
         <is>
-          <t>DEC-034</t>
+          <t>DEC-038</t>
         </is>
       </c>
       <c r="B206" s="68" t="inlineStr">
@@ -20610,7 +20660,7 @@
       <c r="C206" s="68" t="n"/>
       <c r="D206" s="69" t="inlineStr">
         <is>
-          <t>Gamificación como dominio propio (D13)</t>
+          <t>Ranking por cohortes, sin tabla global</t>
         </is>
       </c>
       <c r="E206" s="69" t="inlineStr">
@@ -20620,14 +20670,14 @@
       </c>
       <c r="F206" s="69" t="inlineStr">
         <is>
-          <t>C. Igual que D12: si el motor se cae, la operación sigue igual. Y como se alimenta de eventos, el XP es recalculable: cambiar la tabla de puntos permite reprocesar el histórico. Si el XP se escribiera a mano en el momento, eso sería imposible. — XP, niveles, insignias, ligas, retos y referidos para el creador.</t>
+          <t>C. Los puntos de liga se reinician por temporada; el XP nunca. Sin ranking público por ingresos, jamás. Un ranking global solo tiene sentido en una vista interna, y ahí es un reporte, no gamificación. — Una clasificación global con 1.000 creadores significa que 990 abren la app y ven que están perdiendo. Y con el tiempo se estanca: quien lleva más tiempo acumula más.</t>
         </is>
       </c>
     </row>
     <row r="207" ht="34.5" customHeight="1" s="36">
       <c r="A207" s="67" t="inlineStr">
         <is>
-          <t>DEC-033</t>
+          <t>DEC-037</t>
         </is>
       </c>
       <c r="B207" s="68" t="inlineStr">
@@ -20638,7 +20688,7 @@
       <c r="C207" s="68" t="n"/>
       <c r="D207" s="69" t="inlineStr">
         <is>
-          <t>Registrar la conexión emisora en cada documento</t>
+          <t>Los niveles se calculan, no se almacenan</t>
         </is>
       </c>
       <c r="E207" s="69" t="inlineStr">
@@ -20648,14 +20698,14 @@
       </c>
       <c r="F207" s="69" t="inlineStr">
         <is>
-          <t>B, aplicado a comprobantes electrónicos, cobros por pasarela, pagos a creadores ejecutados por proveedor y correos enviados. — Paralelo exacto de DEC-019. Si dentro de un año hay que consultar ante el proveedor el estado del comprobante F001-00347, hay que saber por cuál se emitió.</t>
+          <t>B. Permite ajustar umbrales sin quitarle puntos a nadie, que es justamente lo que DEC-035 prohíbe. — Las curvas de nivel se recalibran; el XP ya otorgado no debe verse afectado.</t>
         </is>
       </c>
     </row>
     <row r="208" ht="23.25" customHeight="1" s="36">
       <c r="A208" s="67" t="inlineStr">
         <is>
-          <t>DEC-032</t>
+          <t>DEC-036</t>
         </is>
       </c>
       <c r="B208" s="68" t="inlineStr">
@@ -20666,7 +20716,7 @@
       <c r="C208" s="68" t="n"/>
       <c r="D208" s="69" t="inlineStr">
         <is>
-          <t>Compartibilidad declarada por propósito</t>
+          <t>Se premia comportamiento verificado, no resultados</t>
         </is>
       </c>
       <c r="E208" s="69" t="inlineStr">
@@ -20676,14 +20726,14 @@
       </c>
       <c r="F208" s="69" t="inlineStr">
         <is>
-          <t>B. Las credenciales de facturación pertenecen al contribuyente: una sociedad no puede emitir con el certificado de otra. Una validación se cumple; una recomendación en un manual, no. Reformula BR-LE-008 sin contradecirla: lo prohibido era la herencia implícita; compartir por asignación explícita es otra cosa, y aun así sigue vedado para lo fiscal. — El addendum permite que una conexión sirva a varias entidades legales. Correcto para almacenamiento o correo; peligroso para facturación.</t>
+          <t>C. A premia al algoritmo de Instagram, no al creador. B produce sobrecompromiso —creadores que aceptan lo que no pueden cumplir— y, en el caso de seguidores, desmotiva al micro-creador y premia el vector de fraude de R-04. Detalle en docs/13 §3. — ¿Sobre qué se otorga XP?</t>
         </is>
       </c>
     </row>
     <row r="209" ht="23.25" customHeight="1" s="36">
       <c r="A209" s="67" t="inlineStr">
         <is>
-          <t>DEC-031</t>
+          <t>DEC-035</t>
         </is>
       </c>
       <c r="B209" s="68" t="inlineStr">
@@ -20694,7 +20744,7 @@
       <c r="C209" s="68" t="n"/>
       <c r="D209" s="69" t="inlineStr">
         <is>
-          <t>Una URL de webhook por conexión</t>
+          <t>El XP es append-only y nunca decrece</t>
         </is>
       </c>
       <c r="E209" s="69" t="inlineStr">
@@ -20704,14 +20754,14 @@
       </c>
       <c r="F209" s="69" t="inlineStr">
         <is>
-          <t>B. El enrutado por URL hace la verificación de firma determinista y de un solo intento. Se acusa de inmediato (2xx) y se procesa en cola: un proveedor que no recibe respuesta en segundos reintenta y multiplica los eventos. — Con varias conexiones del mismo proveedor conviviendo, el payload entrante a menudo no identifica la sociedad, y probar firmas contra todos los secretos es lento e inseguro. El addendum enumera qué registrar de un webhook pero no resuelve de quién es.</t>
+          <t>B. Quitar puntos se percibe como robo y destruye la confianza de golpe. Además sería castigar dos veces con el mecanismo equivocado. Mismo patrón que el ledger financiero: se corrige con asientos nuevos, no editando. — ¿Se puede restar XP por un incumplimiento?</t>
         </is>
       </c>
     </row>
     <row r="210" ht="45.75" customHeight="1" s="36">
       <c r="A210" s="67" t="inlineStr">
         <is>
-          <t>DEC-030</t>
+          <t>DEC-034</t>
         </is>
       </c>
       <c r="B210" s="68" t="inlineStr">
@@ -20722,7 +20772,7 @@
       <c r="C210" s="68" t="n"/>
       <c r="D210" s="69" t="inlineStr">
         <is>
-          <t>Cifrado sobre para las credenciales</t>
+          <t>Gamificación como dominio propio (D13)</t>
         </is>
       </c>
       <c r="E210" s="69" t="inlineStr">
@@ -20732,14 +20782,14 @@
       </c>
       <c r="F210" s="69" t="inlineStr">
         <is>
-          <t>B, con versionado en la rotación (no sobrescribir), escritura sin lectura desde la interfaz, y un filtro de redacción a nivel del logger — no "acordarse de no loguear". — El addendum señala que las credenciales pueden requerir almacenamiento distinto, sin concretar.</t>
+          <t>C. Igual que D12: si el motor se cae, la operación sigue igual. Y como se alimenta de eventos, el XP es recalculable: cambiar la tabla de puntos permite reprocesar el histórico. Si el XP se escribiera a mano en el momento, eso sería imposible. — XP, niveles, insignias, ligas, retos y referidos para el creador.</t>
         </is>
       </c>
     </row>
     <row r="211" ht="34.5" customHeight="1" s="36">
       <c r="A211" s="67" t="inlineStr">
         <is>
-          <t>DEC-029</t>
+          <t>DEC-033</t>
         </is>
       </c>
       <c r="B211" s="68" t="inlineStr">
@@ -20750,7 +20800,7 @@
       <c r="C211" s="68" t="n"/>
       <c r="D211" s="69" t="inlineStr">
         <is>
-          <t>Aislamiento de ambiente como barrera, no como filtro</t>
+          <t>Registrar la conexión emisora en cada documento</t>
         </is>
       </c>
       <c r="E211" s="69" t="inlineStr">
@@ -20760,14 +20810,14 @@
       </c>
       <c r="F211" s="69" t="inlineStr">
         <is>
-          <t>B. La defensa no puede depender de que alguien haya configurado bien. — El fallo más caro posible de este diseño: una conexión de producción resolviéndose fuera de producción. Consecuencias reales: emitir comprobantes fiscales de verdad desde QA, cobrar tarjetas en una demo, o enviar correos reales a 150 creadores desde staging.</t>
+          <t>B, aplicado a comprobantes electrónicos, cobros por pasarela, pagos a creadores ejecutados por proveedor y correos enviados. — Paralelo exacto de DEC-019. Si dentro de un año hay que consultar ante el proveedor el estado del comprobante F001-00347, hay que saber por cuál se emitió.</t>
         </is>
       </c>
     </row>
     <row r="212" ht="23.25" customHeight="1" s="36">
       <c r="A212" s="67" t="inlineStr">
         <is>
-          <t>DEC-028</t>
+          <t>DEC-032</t>
         </is>
       </c>
       <c r="B212" s="68" t="inlineStr">
@@ -20778,7 +20828,7 @@
       <c r="C212" s="68" t="n"/>
       <c r="D212" s="69" t="inlineStr">
         <is>
-          <t>Matriz de propósitos obligatorios por país</t>
+          <t>Compartibilidad declarada por propósito</t>
         </is>
       </c>
       <c r="E212" s="69" t="inlineStr">
@@ -20788,14 +20838,14 @@
       </c>
       <c r="F212" s="69" t="inlineStr">
         <is>
-          <t>B, más un panel de cobertura en verde/rojo y una comprobación programada que avisa antes de que una credencial expirada rompa una operación. — Descubrir que no hay conexión de facturación para Ecuador al pulsar "emitir", con el cliente esperando, es un problema de diseño, no de configuración.</t>
+          <t>B. Las credenciales de facturación pertenecen al contribuyente: una sociedad no puede emitir con el certificado de otra. Una validación se cumple; una recomendación en un manual, no. Reformula BR-LE-008 sin contradecirla: lo prohibido era la herencia implícita; compartir por asignación explícita es otra cosa, y aun así sigue vedado para lo fiscal. — El addendum permite que una conexión sirva a varias entidades legales. Correcto para almacenamiento o correo; peligroso para facturación.</t>
         </is>
       </c>
     </row>
     <row r="213" ht="45.75" customHeight="1" s="36">
       <c r="A213" s="67" t="inlineStr">
         <is>
-          <t>DEC-027</t>
+          <t>DEC-031</t>
         </is>
       </c>
       <c r="B213" s="68" t="inlineStr">
@@ -20806,7 +20856,7 @@
       <c r="C213" s="68" t="n"/>
       <c r="D213" s="69" t="inlineStr">
         <is>
-          <t>Resolución por especificidad, con empates rechazados al guardar</t>
+          <t>Una URL de webhook por conexión</t>
         </is>
       </c>
       <c r="E213" s="69" t="inlineStr">
@@ -20816,14 +20866,14 @@
       </c>
       <c r="F213" s="69" t="inlineStr">
         <is>
-          <t>B, y sobre todo: los empates no se resuelven en ejecución, se prohíben al guardar. Si dos asignaciones activas puntúan igual para la misma combinación, la interfaz rechaza el guardado y explica el conflicto. Así el resolver es siempre determinista y nadie descubre un empate emitiendo una factura. — El addendum propone una escalera de cuatro peldaños. Funciona, pero no contempla el eje de marca ni dice qué hacer ante un empate.</t>
+          <t>B. El enrutado por URL hace la verificación de firma determinista y de un solo intento. Se acusa de inmediato (2xx) y se procesa en cola: un proveedor que no recibe respuesta en segundos reintenta y multiplica los eventos. — Con varias conexiones del mismo proveedor conviviendo, el payload entrante a menudo no identifica la sociedad, y probar firmas contra todos los secretos es lento e inseguro. El addendum enumera qué registrar de un webhook pero no resuelve de quién es.</t>
         </is>
       </c>
     </row>
     <row r="214" ht="34.5" customHeight="1" s="36">
       <c r="A214" s="67" t="inlineStr">
         <is>
-          <t>DEC-026</t>
+          <t>DEC-030</t>
         </is>
       </c>
       <c r="B214" s="68" t="inlineStr">
@@ -20834,7 +20884,7 @@
       <c r="C214" s="68" t="n"/>
       <c r="D214" s="69" t="inlineStr">
         <is>
-          <t>purpose es un enum cerrado en código, no un catálogo editable</t>
+          <t>Cifrado sobre para las credenciales</t>
         </is>
       </c>
       <c r="E214" s="69" t="inlineStr">
@@ -20844,14 +20894,14 @@
       </c>
       <c r="F214" s="69" t="inlineStr">
         <is>
-          <t>B. El código se ramifica por propósito: invoicing implica una interfaz con emit()/getStatus(); email_transactional implica otra distinta. Un propósito creado desde el panel produciría una conexión perfectamente configurada que ningún código sabe ejecutar. Los catálogos editables son para datos de negocio; los propósitos son contratos de código. — El addendum lista los propósitos como si fueran datos administrables.</t>
+          <t>B, con versionado en la rotación (no sobrescribir), escritura sin lectura desde la interfaz, y un filtro de redacción a nivel del logger — no "acordarse de no loguear". — El addendum señala que las credenciales pueden requerir almacenamiento distinto, sin concretar.</t>
         </is>
       </c>
     </row>
     <row r="215" ht="23.25" customHeight="1" s="36">
       <c r="A215" s="67" t="inlineStr">
         <is>
-          <t>DEC-025</t>
+          <t>DEC-029</t>
         </is>
       </c>
       <c r="B215" s="68" t="inlineStr">
@@ -20862,7 +20912,7 @@
       <c r="C215" s="68" t="n"/>
       <c r="D215" s="69" t="inlineStr">
         <is>
-          <t>Proveedor / Conexión / Asignación como tres entidades</t>
+          <t>Aislamiento de ambiente como barrera, no como filtro</t>
         </is>
       </c>
       <c r="E215" s="69" t="inlineStr">
@@ -20872,14 +20922,14 @@
       </c>
       <c r="F215" s="69" t="inlineStr">
         <is>
-          <t>B, tal como propone el addendum. integration_providers es catálogo respaldado por código (un proveedor solo existe si hay adaptador); integration_connections es la configuración viva; integration_assignments es el alcance, con NULL significando "cualquiera" y con vigencia (valid_from/valid_to) igual que la cobertura de facturación. — Un proveedor puede tener varias conexiones (producción, sandbox, por sociedad) y cada conexión puede aplicar a varios ámbitos.</t>
+          <t>B. La defensa no puede depender de que alguien haya configurado bien. — El fallo más caro posible de este diseño: una conexión de producción resolviéndose fuera de producción. Consecuencias reales: emitir comprobantes fiscales de verdad desde QA, cobrar tarjetas en una demo, o enviar correos reales a 150 creadores desde staging.</t>
         </is>
       </c>
     </row>
     <row r="216" ht="23.25" customHeight="1" s="36">
       <c r="A216" s="67" t="inlineStr">
         <is>
-          <t>DEC-024</t>
+          <t>DEC-028</t>
         </is>
       </c>
       <c r="B216" s="68" t="inlineStr">
@@ -20890,7 +20940,7 @@
       <c r="C216" s="68" t="n"/>
       <c r="D216" s="69" t="inlineStr">
         <is>
-          <t>Las integraciones son un subsistema propio, no Settings</t>
+          <t>Matriz de propósitos obligatorios por país</t>
         </is>
       </c>
       <c r="E216" s="69" t="inlineStr">
@@ -20900,14 +20950,14 @@
       </c>
       <c r="F216" s="69" t="inlineStr">
         <is>
-          <t>B. Un ajuste resuelve un valor; una integración resuelve una conexión viva que tiene estado, ciclo de vida y que falla. Además necesita dos ejes más (purpose, environment). Lo que sí se unifica son los nombres de los niveles, para que nadie confunda "global" con "plataforma". — DEC-018 ya definió una configuración jerárquica. La tentación es meter las integraciones dentro.</t>
+          <t>B, más un panel de cobertura en verde/rojo y una comprobación programada que avisa antes de que una credencial expirada rompa una operación. — Descubrir que no hay conexión de facturación para Ecuador al pulsar "emitir", con el cliente esperando, es un problema de diseño, no de configuración.</t>
         </is>
       </c>
     </row>
     <row r="217" ht="45.75" customHeight="1" s="36">
       <c r="A217" s="67" t="inlineStr">
         <is>
-          <t>DEC-023</t>
+          <t>DEC-027</t>
         </is>
       </c>
       <c r="B217" s="68" t="inlineStr">
@@ -20918,7 +20968,7 @@
       <c r="C217" s="68" t="n"/>
       <c r="D217" s="69" t="inlineStr">
         <is>
-          <t>Identidad dual en comunicaciones</t>
+          <t>Resolución por especificidad, con empates rechazados al guardar</t>
         </is>
       </c>
       <c r="E217" s="69" t="inlineStr">
@@ -20928,14 +20978,14 @@
       </c>
       <c r="F217" s="69" t="inlineStr">
         <is>
-          <t>C. El creador y la marca cliente se relacionan con LATAM Social; las facturas, contratos y comunicaciones de cobranza deben identificar a la sociedad que responde legalmente. Implica remitente configurable por entidad para los correos de facturación. — ¿Los correos salen de "LATAM Social" o de "Soluciones Tecnológicas a Medida S.A.C."?</t>
+          <t>B, y sobre todo: los empates no se resuelven en ejecución, se prohíben al guardar. Si dos asignaciones activas puntúan igual para la misma combinación, la interfaz rechaza el guardado y explica el conflicto. Así el resolver es siempre determinista y nadie descubre un empate emitiendo una factura. — El addendum propone una escalera de cuatro peldaños. Funciona, pero no contempla el eje de marca ni dice qué hacer ante un empate.</t>
         </is>
       </c>
     </row>
     <row r="218" ht="34.5" customHeight="1" s="36">
       <c r="A218" s="67" t="inlineStr">
         <is>
-          <t>DEC-022</t>
+          <t>DEC-026</t>
         </is>
       </c>
       <c r="B218" s="68" t="inlineStr">
@@ -20946,7 +20996,7 @@
       <c r="C218" s="68" t="n"/>
       <c r="D218" s="69" t="inlineStr">
         <is>
-          <t>Monedas: no derivar del país de la entidad</t>
+          <t>purpose es un enum cerrado en código, no un catálogo editable</t>
         </is>
       </c>
       <c r="E218" s="69" t="inlineStr">
@@ -20956,14 +21006,14 @@
       </c>
       <c r="F218" s="69" t="inlineStr">
         <is>
-          <t>B. Coherente con BR-FIN-004 y BR-FIN-009, que ya exigían no asumir una sola moneda. — §11 del addendum. CTS Perú puede facturar en PEN a un cliente peruano y en USD a uno ecuatoriano.</t>
+          <t>B. El código se ramifica por propósito: invoicing implica una interfaz con emit()/getStatus(); email_transactional implica otra distinta. Un propósito creado desde el panel produciría una conexión perfectamente configurada que ningún código sabe ejecutar. Los catálogos editables son para datos de negocio; los propósitos son contratos de código. — El addendum lista los propósitos como si fueran datos administrables.</t>
         </is>
       </c>
     </row>
     <row r="219" ht="23.25" customHeight="1" s="36">
       <c r="A219" s="67" t="inlineStr">
         <is>
-          <t>DEC-021</t>
+          <t>DEC-025</t>
         </is>
       </c>
       <c r="B219" s="68" t="inlineStr">
@@ -20974,7 +21024,7 @@
       <c r="C219" s="68" t="n"/>
       <c r="D219" s="69" t="inlineStr">
         <is>
-          <t>Series y numeración correlativa por entidad legal</t>
+          <t>Proveedor / Conexión / Asignación como tres entidades</t>
         </is>
       </c>
       <c r="E219" s="69" t="inlineStr">
@@ -20984,42 +21034,42 @@
       </c>
       <c r="F219" s="69" t="inlineStr">
         <is>
-          <t>C. A no permite series por entidad y deja huecos ante transacciones revertidas. B bloquea una fila que se lee constantemente. C aísla el punto de contención. — En Perú la numeración por serie debe ser correlativa y sin huecos. Con varias sociedades hay varios contadores independientes, y bajo concurrencia dos facturas simultáneas pueden tomar el mismo número o saltarse uno.</t>
+          <t>B, tal como propone el addendum. integration_providers es catálogo respaldado por código (un proveedor solo existe si hay adaptador); integration_connections es la configuración viva; integration_assignments es el alcance, con NULL significando "cualquiera" y con vigencia (valid_from/valid_to) igual que la cobertura de facturación. — Un proveedor puede tener varias conexiones (producción, sandbox, por sociedad) y cada conexión puede aplicar a varios ámbitos.</t>
         </is>
       </c>
     </row>
     <row r="220" ht="23.25" customHeight="1" s="36">
       <c r="A220" s="67" t="inlineStr">
         <is>
-          <t>DEC-020</t>
+          <t>DEC-024</t>
         </is>
       </c>
       <c r="B220" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C220" s="68" t="n"/>
       <c r="D220" s="69" t="inlineStr">
         <is>
-          <t>Entidad que factura vs. entidad que liquida al creador</t>
+          <t>Las integraciones son un subsistema propio, no Settings</t>
         </is>
       </c>
       <c r="E220" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ DECIDIDA (2026-08-27) por DEC-156: opción C, y sin el «en el MVP». La sociedad de la campaña paga a todos sus creadores, sea cual sea el país de cada uno (BR-LE-009, ahora 🔴). Dónde se comprueba lo </t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F220" s="69" t="inlineStr">
         <is>
-          <t>C. A cierra la puerta; B la deja abierta para que alguien la cruce sin darse cuenta un martes por la tarde y genere una contingencia fiscal. C conserva la flexibilidad del modelo y exige una decisión consciente, respaldada por asesoría fiscal, para habilitarla. — §12 del addendum pide separar ambos conceptos. Pero si divergen, aparece una operación intercompañía entre dos sociedades del grupo, con precios de transferencia, documentación ante la autoridad tributaria, consolidación contable y posible retención en la fuente.</t>
+          <t>B. Un ajuste resuelve un valor; una integración resuelve una conexión viva que tiene estado, ciclo de vida y que falla. Además necesita dos ejes más (purpose, environment). Lo que sí se unifica son los nombres de los niveles, para que nadie confunda "global" con "plataforma". — DEC-018 ya definió una configuración jerárquica. La tentación es meter las integraciones dentro.</t>
         </is>
       </c>
     </row>
     <row r="221" ht="45.75" customHeight="1" s="36">
       <c r="A221" s="67" t="inlineStr">
         <is>
-          <t>DEC-019</t>
+          <t>DEC-023</t>
         </is>
       </c>
       <c r="B221" s="68" t="inlineStr">
@@ -21030,7 +21080,7 @@
       <c r="C221" s="68" t="n"/>
       <c r="D221" s="69" t="inlineStr">
         <is>
-          <t>Entidad legal explícita e inmutable en cada documento</t>
+          <t>Identidad dual en comunicaciones</t>
         </is>
       </c>
       <c r="E221" s="69" t="inlineStr">
@@ -21040,14 +21090,14 @@
       </c>
       <c r="F221" s="69" t="inlineStr">
         <is>
-          <t>C. A es un error silencioso: no da error, no rompe nada, y falsifica retroactivamente todos los documentos históricos. La clave foránea sola tampoco basta: si la sociedad cambia de domicilio, la factura antigua debe seguir mostrando el domicilio antiguo. — §14 del addendum. Si mañana Ecuador pasa a facturarse desde otra sociedad, las facturas de ayer deben seguir diciendo lo que decían ayer.</t>
+          <t>C. El creador y la marca cliente se relacionan con LATAM Social; las facturas, contratos y comunicaciones de cobranza deben identificar a la sociedad que responde legalmente. Implica remitente configurable por entidad para los correos de facturación. — ¿Los correos salen de "LATAM Social" o de "Soluciones Tecnológicas a Medida S.A.C."?</t>
         </is>
       </c>
     </row>
     <row r="222" ht="34.5" customHeight="1" s="36">
       <c r="A222" s="67" t="inlineStr">
         <is>
-          <t>DEC-018</t>
+          <t>DEC-022</t>
         </is>
       </c>
       <c r="B222" s="68" t="inlineStr">
@@ -21058,7 +21108,7 @@
       <c r="C222" s="68" t="n"/>
       <c r="D222" s="69" t="inlineStr">
         <is>
-          <t>Configuración jerárquica en cascada</t>
+          <t>Monedas: no derivar del país de la entidad</t>
         </is>
       </c>
       <c r="E222" s="69" t="inlineStr">
@@ -21068,14 +21118,14 @@
       </c>
       <c r="F222" s="69" t="inlineStr">
         <is>
-          <t>B, con dos condiciones no negociables: la interfaz debe mostrar siempre de dónde viene el valor efectivo, y los secretos se cifran por entidad y nunca se heredan. — La configuración deja de ser global: hay ajustes de plataforma, de marca, de entidad legal y de (entidad × país).</t>
+          <t>B. Coherente con BR-FIN-004 y BR-FIN-009, que ya exigían no asumir una sola moneda. — §11 del addendum. CTS Perú puede facturar en PEN a un cliente peruano y en USD a uno ecuatoriano.</t>
         </is>
       </c>
     </row>
     <row r="223" ht="23.85" customHeight="1" s="36">
       <c r="A223" s="67" t="inlineStr">
         <is>
-          <t>DEC-017</t>
+          <t>DEC-021</t>
         </is>
       </c>
       <c r="B223" s="68" t="inlineStr">
@@ -21086,7 +21136,7 @@
       <c r="C223" s="68" t="n"/>
       <c r="D223" s="69" t="inlineStr">
         <is>
-          <t>Cobertura de facturación como relación N:M con vigencia</t>
+          <t>Series y numeración correlativa por entidad legal</t>
         </is>
       </c>
       <c r="E223" s="69" t="inlineStr">
@@ -21096,42 +21146,42 @@
       </c>
       <c r="F223" s="69" t="inlineStr">
         <is>
-          <t>C. A es directamente incorrecta. B pierde la información de *cuándo* dejó de aplicar una cobertura, y eso hace imposible auditar por qué una factura de 2027 salió de una sociedad y una de 2029 de otra. La vigencia es lo que permite la evolución del §15 del addendum sin destruir historia. — Una sociedad puede facturar clientes de varios países, y un país puede ser atendido por más de una sociedad.</t>
+          <t>C. A no permite series por entidad y deja huecos ante transacciones revertidas. B bloquea una fila que se lee constantemente. C aísla el punto de contención. — En Perú la numeración por serie debe ser correlativa y sin huecos. Con varias sociedades hay varios contadores independientes, y bajo concurrencia dos facturas simultáneas pueden tomar el mismo número o saltarse uno.</t>
         </is>
       </c>
     </row>
     <row r="224" ht="46.25" customHeight="1" s="36">
       <c r="A224" s="67" t="inlineStr">
         <is>
-          <t>DEC-016</t>
+          <t>DEC-020</t>
         </is>
       </c>
       <c r="B224" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C224" s="68" t="n"/>
       <c r="D224" s="69" t="inlineStr">
         <is>
-          <t>Desambiguación de los conceptos organizacionales</t>
+          <t>Entidad que factura vs. entidad que liquida al creador</t>
         </is>
       </c>
       <c r="E224" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t xml:space="preserve">✅ DECIDIDA (2026-08-27) por DEC-156: opción C, y sin el «en el MVP». La sociedad de la campaña paga a todos sus creadores, sea cual sea el país de cada uno (BR-LE-009, ahora 🔴). Dónde se comprueba lo </t>
         </is>
       </c>
       <c r="F224" s="69" t="inlineStr">
         <is>
-          <t>B. A garantiza que en seis meses nadie sepa si brand_id apunta a LATAM Social o a Shampoo ABC. Es la fuente número uno de errores de datos en sistemas multi-entidad. — El addendum introduce "marca de plataforma" (LATAM Social) y "entidad legal" (la sociedad). El modelo anterior ya usaba Brand para la marca del cliente. Cuatro conceptos organizacionales con nombres que se pisan.</t>
+          <t>C. A cierra la puerta; B la deja abierta para que alguien la cruce sin darse cuenta un martes por la tarde y genere una contingencia fiscal. C conserva la flexibilidad del modelo y exige una decisión consciente, respaldada por asesoría fiscal, para habilitarla. — §12 del addendum pide separar ambos conceptos. Pero si divergen, aparece una operación intercompañía entre dos sociedades del grupo, con precios de transferencia, documentación ante la autoridad tributaria, consolidación contable y posible retención en la fuente.</t>
         </is>
       </c>
     </row>
     <row r="225" ht="35.05" customHeight="1" s="36">
       <c r="A225" s="67" t="inlineStr">
         <is>
-          <t>DEC-015</t>
+          <t>DEC-019</t>
         </is>
       </c>
       <c r="B225" s="68" t="inlineStr">
@@ -21142,24 +21192,24 @@
       <c r="C225" s="68" t="n"/>
       <c r="D225" s="69" t="inlineStr">
         <is>
-          <t>Retención y minimización de datos personales</t>
+          <t>Entidad legal explícita e inmutable en cada documento</t>
         </is>
       </c>
       <c r="E225" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA — requiere validación legal</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F225" s="69" t="inlineStr">
         <is>
-          <t>B. Además: la dirección de envío se purga N meses después de la campaña; las copias de documentos de identidad, si se recogen, se cifran y tienen la retención más corta legalmente posible. Menos datos = menos riesgo. — Se recopilan documento de identidad, fecha de nacimiento, dirección, datos bancarios y dirección de envío de cientos de personas.</t>
+          <t>C. A es un error silencioso: no da error, no rompe nada, y falsifica retroactivamente todos los documentos históricos. La clave foránea sola tampoco basta: si la sociedad cambia de domicilio, la factura antigua debe seguir mostrando el domicilio antiguo. — §14 del addendum. Si mañana Ecuador pasa a facturarse desde otra sociedad, las facturas de ayer deben seguir diciendo lo que decían ayer.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67" t="inlineStr">
         <is>
-          <t>DEC-014</t>
+          <t>DEC-018</t>
         </is>
       </c>
       <c r="B226" s="68" t="inlineStr">
@@ -21170,7 +21220,7 @@
       <c r="C226" s="68" t="n"/>
       <c r="D226" s="69" t="inlineStr">
         <is>
-          <t>Modelo de derechos de uso del contenido</t>
+          <t>Configuración jerárquica en cascada</t>
         </is>
       </c>
       <c r="E226" s="69" t="inlineStr">
@@ -21180,14 +21230,14 @@
       </c>
       <c r="F226" s="69" t="inlineStr">
         <is>
-          <t>B. Además, alertas de vencimiento: usar contenido después de que expiró la licencia es una infracción con consecuencias legales para el cliente y reputacionales para el operador. — Lo que la marca realmente compra es una licencia. Modelarlo como un booleano "cede derechos: sí/no" es insuficiente y genera disputas.</t>
+          <t>B, con dos condiciones no negociables: la interfaz debe mostrar siempre de dónde viene el valor efectivo, y los secretos se cifran por entidad y nunca se heredan. — La configuración deja de ser global: hay ajustes de plataforma, de marca, de entidad legal y de (entidad × país).</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67" t="inlineStr">
         <is>
-          <t>DEC-013</t>
+          <t>DEC-017</t>
         </is>
       </c>
       <c r="B227" s="68" t="inlineStr">
@@ -21198,7 +21248,7 @@
       <c r="C227" s="68" t="n"/>
       <c r="D227" s="69" t="inlineStr">
         <is>
-          <t>Alcance del portal de la marca en el MVP</t>
+          <t>Cobertura de facturación como relación N:M con vigencia</t>
         </is>
       </c>
       <c r="E227" s="69" t="inlineStr">
@@ -21208,14 +21258,14 @@
       </c>
       <c r="F227" s="69" t="inlineStr">
         <is>
-          <t>B. Entrega el 90% del valor percibido con el 15% del esfuerzo, y es el camino natural hacia A en F13. Requiere cuidado en seguridad: enlaces de un solo destinatario, con expiración, revocables y auditados. — Con 3 marcas, construir un portal con cuentas, roles, facturación y documentos es esfuerzo desproporcionado.</t>
+          <t>C. A es directamente incorrecta. B pierde la información de *cuándo* dejó de aplicar una cobertura, y eso hace imposible auditar por qué una factura de 2027 salió de una sociedad y una de 2029 de otra. La vigencia es lo que permite la evolución del §15 del addendum sin destruir historia. — Una sociedad puede facturar clientes de varios países, y un país puede ser atendido por más de una sociedad.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67" t="inlineStr">
         <is>
-          <t>DEC-012</t>
+          <t>DEC-016</t>
         </is>
       </c>
       <c r="B228" s="68" t="inlineStr">
@@ -21226,7 +21276,7 @@
       <c r="C228" s="68" t="n"/>
       <c r="D228" s="69" t="inlineStr">
         <is>
-          <t>Longitud del formulario de lead B2B</t>
+          <t>Desambiguación de los conceptos organizacionales</t>
         </is>
       </c>
       <c r="E228" s="69" t="inlineStr">
@@ -21236,14 +21286,14 @@
       </c>
       <c r="F228" s="69" t="inlineStr">
         <is>
-          <t>B: empresa, nombre, email corporativo, teléfono/WhatsApp, país, objetivo, mensaje. El resto (presupuesto, cantidad de creadores, países objetivo, industria) se captura en la conversación comercial y se guarda en el CRM. UTM, landing y origen se capturan ocultos, siempre. — La spec lista 16 campos. Cada campo adicional reduce la conversión.</t>
+          <t>B. A garantiza que en seis meses nadie sepa si brand_id apunta a LATAM Social o a Shampoo ABC. Es la fuente número uno de errores de datos en sistemas multi-entidad. — El addendum introduce "marca de plataforma" (LATAM Social) y "entidad legal" (la sociedad). El modelo anterior ya usaba Brand para la marca del cliente. Cuatro conceptos organizacionales con nombres que se pisan.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67" t="inlineStr">
         <is>
-          <t>DEC-011</t>
+          <t>DEC-015</t>
         </is>
       </c>
       <c r="B229" s="68" t="inlineStr">
@@ -21254,24 +21304,24 @@
       <c r="C229" s="68" t="n"/>
       <c r="D229" s="69" t="inlineStr">
         <is>
-          <t>¿La plataforma publica en las redes del creador?</t>
+          <t>Retención y minimización de datos personales</t>
         </is>
       </c>
       <c r="E229" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>PROPUESTA — requiere validación legal</t>
         </is>
       </c>
       <c r="F229" s="69" t="inlineStr">
         <is>
-          <t>B. A añade riesgo de cuenta, complejidad enorme y las APIs cambian sin aviso. La verificación posterior aporta casi todo el valor con una fracción del costo. — Publicar automáticamente requiere permisos amplios, es frágil y las plataformas lo restringen.</t>
+          <t>B. Además: la dirección de envío se purga N meses después de la campaña; las copias de documentos de identidad, si se recogen, se cifran y tienen la retención más corta legalmente posible. Menos datos = menos riesgo. — Se recopilan documento de identidad, fecha de nacimiento, dirección, datos bancarios y dirección de envío de cientos de personas.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67" t="inlineStr">
         <is>
-          <t>DEC-010</t>
+          <t>DEC-014</t>
         </is>
       </c>
       <c r="B230" s="68" t="inlineStr">
@@ -21282,7 +21332,7 @@
       <c r="C230" s="68" t="n"/>
       <c r="D230" s="69" t="inlineStr">
         <is>
-          <t>Estado de campaña vs. estado de participación</t>
+          <t>Modelo de derechos de uso del contenido</t>
         </is>
       </c>
       <c r="E230" s="69" t="inlineStr">
@@ -21292,14 +21342,14 @@
       </c>
       <c r="F230" s="69" t="inlineStr">
         <is>
-          <t>B, obligatoriamente. A es el error de diseño más frecuente y más caro en plataformas de este tipo: obliga a hacks inmediatos y hace imposible el reporte de avance. — Una campaña live puede tener creadores aún en revisión.</t>
+          <t>B. Además, alertas de vencimiento: usar contenido después de que expiró la licencia es una infracción con consecuencias legales para el cliente y reputacionales para el operador. — Lo que la marca realmente compra es una licencia. Modelarlo como un booleano "cede derechos: sí/no" es insuficiente y genera disputas.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67" t="inlineStr">
         <is>
-          <t>DEC-009</t>
+          <t>DEC-013</t>
         </is>
       </c>
       <c r="B231" s="68" t="inlineStr">
@@ -21310,7 +21360,7 @@
       <c r="C231" s="68" t="n"/>
       <c r="D231" s="69" t="inlineStr">
         <is>
-          <t>Origen de los datos de audiencia</t>
+          <t>Alcance del portal de la marca en el MVP</t>
         </is>
       </c>
       <c r="E231" s="69" t="inlineStr">
@@ -21320,14 +21370,14 @@
       </c>
       <c r="F231" s="69" t="inlineStr">
         <is>
-          <t>A en el MVP (manual + evidencia + chequeos de coherencia), B en F12–F14, C evaluado por costo cuando el volumen lo justifique: comprar datos verificados suele ser más barato que construir y mantener integraciones con 6 plataformas. — Los datos autodeclarados son el principal vector de fraude. Las APIs oficiales exigen que el creador conecte su cuenta (Instagram/Facebook requieren cuenta Business/Creator y autorización explícita; TikTok y YouTube tienen sus propios programas).</t>
+          <t>B. Entrega el 90% del valor percibido con el 15% del esfuerzo, y es el camino natural hacia A en F13. Requiere cuidado en seguridad: enlaces de un solo destinatario, con expiración, revocables y auditados. — Con 3 marcas, construir un portal con cuentas, roles, facturación y documentos es esfuerzo desproporcionado.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67" t="inlineStr">
         <is>
-          <t>DEC-008</t>
+          <t>DEC-012</t>
         </is>
       </c>
       <c r="B232" s="68" t="inlineStr">
@@ -21338,7 +21388,7 @@
       <c r="C232" s="68" t="n"/>
       <c r="D232" s="69" t="inlineStr">
         <is>
-          <t>Almacenamiento de archivos</t>
+          <t>Longitud del formulario de lead B2B</t>
         </is>
       </c>
       <c r="E232" s="69" t="inlineStr">
@@ -21348,14 +21398,14 @@
       </c>
       <c r="F232" s="69" t="inlineStr">
         <is>
-          <t>B, sin excepción. A rompe el despliegue en más de un servidor, complica los backups, no escala y migrar después implica reescribir rutas de miles de archivos. Cloudflare R2 o Backblaze B2 tienen costo de egreso muy bajo, relevante porque los clientes descargarán contenido. — Campañas UGC generan video pesado (0,5–3 GB por campaña).</t>
+          <t>B: empresa, nombre, email corporativo, teléfono/WhatsApp, país, objetivo, mensaje. El resto (presupuesto, cantidad de creadores, países objetivo, industria) se captura en la conversación comercial y se guarda en el CRM. UTM, landing y origen se capturan ocultos, siempre. — La spec lista 16 campos. Cada campo adicional reduce la conversión.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67" t="inlineStr">
         <is>
-          <t>DEC-007</t>
+          <t>DEC-011</t>
         </is>
       </c>
       <c r="B233" s="68" t="inlineStr">
@@ -21366,7 +21416,7 @@
       <c r="C233" s="68" t="n"/>
       <c r="D233" s="69" t="inlineStr">
         <is>
-          <t>Pasarela de pago (Culqi) en el MVP</t>
+          <t>¿La plataforma publica en las redes del creador?</t>
         </is>
       </c>
       <c r="E233" s="69" t="inlineStr">
@@ -21376,14 +21426,14 @@
       </c>
       <c r="F233" s="69" t="inlineStr">
         <is>
-          <t>B. Se construye la abstracción (PaymentGatewayInterface) pero no la integración. Si aparece un segmento de ticket bajo (p. ej. paquetes autoservicio para pymes), se activa. — La spec pide integrar Culqi. Pero en B2B LATAM, campañas de miles de soles se pagan por transferencia contra factura, no con tarjeta. Una campaña de S/ 30.000 no se cobra con tarjeta (comisión ~3,5% = S/ 1.050 regalados).</t>
+          <t>B. A añade riesgo de cuenta, complejidad enorme y las APIs cambian sin aviso. La verificación posterior aporta casi todo el valor con una fracción del costo. — Publicar automáticamente requiere permisos amplios, es frágil y las plataformas lo restringen.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67" t="inlineStr">
         <is>
-          <t>DEC-006</t>
+          <t>DEC-010</t>
         </is>
       </c>
       <c r="B234" s="68" t="inlineStr">
@@ -21394,7 +21444,7 @@
       <c r="C234" s="68" t="n"/>
       <c r="D234" s="69" t="inlineStr">
         <is>
-          <t>Separación Aplicación vs. Creador</t>
+          <t>Estado de campaña vs. estado de participación</t>
         </is>
       </c>
       <c r="E234" s="69" t="inlineStr">
@@ -21404,42 +21454,42 @@
       </c>
       <c r="F234" s="69" t="inlineStr">
         <is>
-          <t>B. Permite reaplicaciones, conserva el histórico de rechazos y evita que un rechazo contamine la entidad permanente. — La spec mezcla el ciclo de vida de la solicitud con el del creador.</t>
+          <t>B, obligatoriamente. A es el error de diseño más frecuente y más caro en plataformas de este tipo: obliga a hacks inmediatos y hace imposible el reporte de avance. — Una campaña live puede tener creadores aún en revisión.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67" t="inlineStr">
         <is>
-          <t>DEC-005</t>
+          <t>DEC-009</t>
         </is>
       </c>
       <c r="B235" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C235" s="68" t="n"/>
       <c r="D235" s="69" t="inlineStr">
         <is>
-          <t>Régimen legal y tributario del pago al creador ✅ RESUELTA (parcial)</t>
+          <t>Origen de los datos de audiencia</t>
         </is>
       </c>
       <c r="E235" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA para creadores peruanos · 🔴 Q-33 abierta para extranjeros (bloquea F9 solo en ese caso)</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F235" s="69" t="inlineStr">
         <is>
-          <t>C, con la vía simplificada definida por un contador. Y en cualquier caso: el sistema debe modelar tax_regime por creador y por país, con requisitos documentales configurables por régimen, y bloquear el pago si falta el documento requerido. — En Perú, pagar a una persona natural por un servicio exige normalmente comprobante (recibo por honorarios electrónico) y puede implicar retención de renta de 4.ª categoría, con umbrales y suspensión de retención. Muchos micro-creadores no tienen RUC ni emiten comprobantes. Sin resolver esto, no se puede pagar legalmente a escala.</t>
+          <t>A en el MVP (manual + evidencia + chequeos de coherencia), B en F12–F14, C evaluado por costo cuando el volumen lo justifique: comprar datos verificados suele ser más barato que construir y mantener integraciones con 6 plataformas. — Los datos autodeclarados son el principal vector de fraude. Las APIs oficiales exigen que el creador conecte su cuenta (Instagram/Facebook requieren cuenta Business/Creator y autorización explícita; TikTok y YouTube tienen sus propios programas).</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67" t="inlineStr">
         <is>
-          <t>DEC-004</t>
+          <t>DEC-008</t>
         </is>
       </c>
       <c r="B236" s="68" t="inlineStr">
@@ -21450,24 +21500,24 @@
       <c r="C236" s="68" t="n"/>
       <c r="D236" s="69" t="inlineStr">
         <is>
-          <t>Modelo económico: principal vs. comisión</t>
+          <t>Almacenamiento de archivos</t>
         </is>
       </c>
       <c r="E236" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA — confirmar con el contador</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F236" s="69" t="inlineStr">
         <is>
-          <t>A, coherente con §53 de la especificación (Revenue − Creator Cost = Margen). Determina el modelo fiscal, contable y financiero completo. — ¿El operador vende la campaña y compra el contenido (reventa), o cobra una comisión sobre una transacción entre marca y creador?</t>
+          <t>B, sin excepción. A rompe el despliegue en más de un servidor, complica los backups, no escala y migrar después implica reescribir rutas de miles de archivos. Cloudflare R2 o Backblaze B2 tienen costo de egreso muy bajo, relevante porque los clientes descargarán contenido. — Campañas UGC generan video pesado (0,5–3 GB por campaña).</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67" t="inlineStr">
         <is>
-          <t>DEC-003</t>
+          <t>DEC-007</t>
         </is>
       </c>
       <c r="B237" s="68" t="inlineStr">
@@ -21478,7 +21528,7 @@
       <c r="C237" s="68" t="n"/>
       <c r="D237" s="69" t="inlineStr">
         <is>
-          <t>Estrategia de frontend</t>
+          <t>Pasarela de pago (Culqi) en el MVP</t>
         </is>
       </c>
       <c r="E237" s="69" t="inlineStr">
@@ -21488,42 +21538,42 @@
       </c>
       <c r="F237" s="69" t="inlineStr">
         <is>
-          <t>A. B duplica el trabajo y, sobre todo, duplica la autorización —el punto donde este sistema más se puede romper—. El portal del creador se entrega como PWA instalable con A. — Cuatro portales con necesidades distintas. Equipo pequeño.</t>
+          <t>B. Se construye la abstracción (PaymentGatewayInterface) pero no la integración. Si aparece un segmento de ticket bajo (p. ej. paquetes autoservicio para pymes), se activa. — La spec pide integrar Culqi. Pero en B2B LATAM, campañas de miles de soles se pagan por transferencia contra factura, no con tarjeta. Una campaña de S/ 30.000 no se cobra con tarjeta (comisión ~3,5% = S/ 1.050 regalados).</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67" t="inlineStr">
         <is>
-          <t>DEC-002</t>
+          <t>DEC-006</t>
         </is>
       </c>
       <c r="B238" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C238" s="68" t="n"/>
       <c r="D238" s="69" t="inlineStr">
         <is>
-          <t>Multitenancy ✅ RESUELTA</t>
+          <t>Separación Aplicación vs. Creador</t>
         </is>
       </c>
       <c r="E238" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA (decisión del negocio, 2026-08-21)</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F238" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hoy hay un solo operador. La spec contempla agencias y white-label a futuro (§78).</t>
+          <t>B. Permite reaplicaciones, conserva el histórico de rechazos y evita que un rechazo contamine la entidad permanente. — La spec mezcla el ciclo de vida de la solicitud con el del creador.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67" t="inlineStr">
         <is>
-          <t>DEC-001</t>
+          <t>DEC-005</t>
         </is>
       </c>
       <c r="B239" s="68" t="inlineStr">
@@ -21534,43 +21584,155 @@
       <c r="C239" s="68" t="n"/>
       <c r="D239" s="69" t="inlineStr">
         <is>
-          <t>Framework PHP</t>
+          <t>Régimen legal y tributario del pago al creador ✅ RESUELTA (parcial)</t>
         </is>
       </c>
       <c r="E239" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA (2026-08-22). Proyecto creado: ver tools/bootstrap-laravel.ps1 y CONTRIBUTING.md</t>
+          <t>✅ APROBADA para creadores peruanos · 🔴 Q-33 abierta para extranjeros (bloquea F9 solo en ese caso)</t>
         </is>
       </c>
       <c r="F239" s="69" t="inlineStr">
         <is>
-          <t>A — Laravel 12. C queda descartada: construir a mano autenticación, colas, migraciones y abstracción de storage añadiría 3–5 meses de trabajo indiferenciado y una superficie de seguridad propia que nadie audita. B es defendible si el equipo ya domina Symfony. — La spec exige PHP 8.3 y "MVC o equivalente bien estructurado", y a la vez pide migraciones, seeders, colas, scheduler, cache, logs, SMTP, webhooks, RBAC, i18n y tests. Todo eso ya existe, probado en producción, en los frameworks maduros.</t>
+          <t>C, con la vía simplificada definida por un contador. Y en cualquier caso: el sistema debe modelar tax_regime por creador y por país, con requisitos documentales configurables por régimen, y bloquear el pago si falta el documento requerido. — En Perú, pagar a una persona natural por un servicio exige normalmente comprobante (recibo por honorarios electrónico) y puede implicar retención de renta de 4.ª categoría, con umbrales y suspensión de retención. Muchos micro-creadores no tienen RUC ni emiten comprobantes. Sin resolver esto, no se puede pagar legalmente a escala.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67" t="inlineStr">
         <is>
-          <t>DEC-000</t>
+          <t>DEC-004</t>
         </is>
       </c>
       <c r="B240" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C240" s="68" t="n"/>
       <c r="D240" s="69" t="inlineStr">
         <is>
+          <t>Modelo económico: principal vs. comisión</t>
+        </is>
+      </c>
+      <c r="E240" s="69" t="inlineStr">
+        <is>
+          <t>PROPUESTA — confirmar con el contador</t>
+        </is>
+      </c>
+      <c r="F240" s="69" t="inlineStr">
+        <is>
+          <t>A, coherente con §53 de la especificación (Revenue − Creator Cost = Margen). Determina el modelo fiscal, contable y financiero completo. — ¿El operador vende la campaña y compra el contenido (reventa), o cobra una comisión sobre una transacción entre marca y creador?</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="67" t="inlineStr">
+        <is>
+          <t>DEC-003</t>
+        </is>
+      </c>
+      <c r="B241" s="68" t="inlineStr">
+        <is>
+          <t>Propuesta</t>
+        </is>
+      </c>
+      <c r="C241" s="68" t="n"/>
+      <c r="D241" s="69" t="inlineStr">
+        <is>
+          <t>Estrategia de frontend</t>
+        </is>
+      </c>
+      <c r="E241" s="69" t="inlineStr">
+        <is>
+          <t>PROPUESTA</t>
+        </is>
+      </c>
+      <c r="F241" s="69" t="inlineStr">
+        <is>
+          <t>A. B duplica el trabajo y, sobre todo, duplica la autorización —el punto donde este sistema más se puede romper—. El portal del creador se entrega como PWA instalable con A. — Cuatro portales con necesidades distintas. Equipo pequeño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="67" t="inlineStr">
+        <is>
+          <t>DEC-002</t>
+        </is>
+      </c>
+      <c r="B242" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C242" s="68" t="n"/>
+      <c r="D242" s="69" t="inlineStr">
+        <is>
+          <t>Multitenancy ✅ RESUELTA</t>
+        </is>
+      </c>
+      <c r="E242" s="69" t="inlineStr">
+        <is>
+          <t>✅ APROBADA (decisión del negocio, 2026-08-21)</t>
+        </is>
+      </c>
+      <c r="F242" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — Hoy hay un solo operador. La spec contempla agencias y white-label a futuro (§78).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="67" t="inlineStr">
+        <is>
+          <t>DEC-001</t>
+        </is>
+      </c>
+      <c r="B243" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C243" s="68" t="n"/>
+      <c r="D243" s="69" t="inlineStr">
+        <is>
+          <t>Framework PHP</t>
+        </is>
+      </c>
+      <c r="E243" s="69" t="inlineStr">
+        <is>
+          <t>✅ APROBADA (2026-08-22). Proyecto creado: ver tools/bootstrap-laravel.ps1 y CONTRIBUTING.md</t>
+        </is>
+      </c>
+      <c r="F243" s="69" t="inlineStr">
+        <is>
+          <t>A — Laravel 12. C queda descartada: construir a mano autenticación, colas, migraciones y abstracción de storage añadiría 3–5 meses de trabajo indiferenciado y una superficie de seguridad propia que nadie audita. B es defendible si el equipo ya domina Symfony. — La spec exige PHP 8.3 y "MVC o equivalente bien estructurado", y a la vez pide migraciones, seeders, colas, scheduler, cache, logs, SMTP, webhooks, RBAC, i18n y tests. Todo eso ya existe, probado en producción, en los frameworks maduros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="67" t="inlineStr">
+        <is>
+          <t>DEC-000</t>
+        </is>
+      </c>
+      <c r="B244" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C244" s="68" t="n"/>
+      <c r="D244" s="69" t="inlineStr">
+        <is>
           <t>Nombre del producto y dominio ✅ RESUELTA</t>
         </is>
       </c>
-      <c r="E240" s="69" t="inlineStr">
+      <c r="E244" s="69" t="inlineStr">
         <is>
           <t>✅ APROBADA (addendum 2026-08-21)</t>
         </is>
       </c>
-      <c r="F240" s="69" t="inlineStr">
+      <c r="F244" s="69" t="inlineStr">
         <is>
           <t>El addendum del 2026-08-21 lo define: la marca de plataforma es LATAM Social. El identificador técnico del proyecto pasa a latam-social. El nombre de trabajo provisional "CTS Creators" queda descartado. — El repositorio se llama ManageCampaingInfluencer (con error ortográfico). El nombre afecta marca, dominio, correos y branding.</t>
         </is>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -2241,7 +2241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J180"/>
+  <dimension ref="A1:J181"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="35" min="1" max="1"/>
@@ -10659,6 +10659,56 @@
       <c r="J180" s="35" t="inlineStr">
         <is>
           <t>2026-08-31. FUERA DEL ALCANCE ORIGINAL. / habla a las marcas y /creadores a los creadores, enlazadas entre si (DEC-238). El texto es un DATO --titular, bloques, boton y lo que sale en buscadores-- editable desde /backoffice/landing y colgado de la marca (DEC-239). La postulacion publica escribe en creator_applications, que existia desde la Fase 2 con source=landing y sin nadie que escribiera, con throttle y campo trampa en vez de CAPTCHA (DEC-240). Sin portada se va al acceso, no a un 404 (DEC-241). 1001 pruebas; 2182 aserciones SQL en MariaDB y 2172 en MySQL 8. docs/fase-9/9.21b-LA-PUERTA-DE-LA-CALLE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="57" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B181" s="35" t="inlineStr">
+        <is>
+          <t>Ola 2 - Escalar comercialmente</t>
+        </is>
+      </c>
+      <c r="C181" s="35" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="D181" s="35" t="inlineStr">
+        <is>
+          <t>Finanzas y facturacion</t>
+        </is>
+      </c>
+      <c r="E181" s="35" t="inlineStr">
+        <is>
+          <t>9.21c</t>
+        </is>
+      </c>
+      <c r="F181" s="35" t="inlineStr">
+        <is>
+          <t>El contacto que no se pierde: prospecto de marcas con su bandeja</t>
+        </is>
+      </c>
+      <c r="G181" s="35" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="H181" s="35">
+        <f>IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G181,Config!$A$3:$A$8,0)),0)</f>
+        <v/>
+      </c>
+      <c r="I181" s="35">
+        <f>IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G181,Config!$A$3:$A$8,0)),0)</f>
+        <v/>
+      </c>
+      <c r="J181" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-31. FUERA DEL ALCANCE ORIGINAL. El formulario de la portada de marcas crea una FILA y no un correo: hoy el correo esta en «log» y una instalacion con el SMTP a medio configurar perderia cada contacto sin que nadie se entere (DEC-242). Misma forma que creator_applications, con columna puerta para que solo lo abierto ocupe sitio (DEC-243). Descartar exige motivo y no borra; convertir exige decir en que cliente (DEC-244). Una asercion pasaba por casualidad y los dos motores la delataron. 1014 pruebas; 2208 aserciones SQL en MariaDB y 2197 en MySQL 8. docs/fase-9/9.21c-EL-PROSPECTO.md</t>
         </is>
       </c>
     </row>
@@ -15108,7 +15158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F244"/>
+  <dimension ref="A1:F247"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="35" min="1" max="1"/>
@@ -15161,7 +15211,7 @@
     <row r="3" ht="79.5" customHeight="1" s="36">
       <c r="A3" s="67" t="inlineStr">
         <is>
-          <t>DEC-238</t>
+          <t>DEC-242</t>
         </is>
       </c>
       <c r="B3" s="68" t="inlineStr">
@@ -15172,24 +15222,24 @@
       <c r="C3" s="68" t="n"/>
       <c r="D3" s="69" t="inlineStr">
         <is>
-          <t>/ habla a las MARCAS y /creadores a los creadores</t>
+          <t>El contacto de una marca es una FILA, no un correo</t>
         </is>
       </c>
       <c r="E3" s="69" t="inlineStr">
         <is>
-          <t>9.21b</t>
+          <t>9.21c</t>
         </is>
       </c>
       <c r="F3" s="69" t="inlineStr">
         <is>
-          <t>Es un mercado de dos lados y el lado que PAGA se pone en la puerta: una portada que abre reclutando creadores se lee como «agencia buscando talento». Los creadores llegan por un enlace, no por la home. Las dos se enlazan entre si. El argumento en contra queda escrito: si el cuello de botella es tener creadores, el trafico que hace falta primero es el suyo; aun asi la home no cambia, porque moverla despues cuesta posicionamiento.</t>
+          <t>Hoy el correo esta en «log» --no sale del servidor-- asi que una instalacion con el SMTP a medio configurar perderia cada contacto sin que nadie se entere. Un correo que no llega no deja rastro; una fila si, y ademas se puede contar. El aviso por correo va encima de la fila, no en lugar de ella.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="57" customHeight="1" s="36">
       <c r="A4" s="67" t="inlineStr">
         <is>
-          <t>DEC-239</t>
+          <t>DEC-243</t>
         </is>
       </c>
       <c r="B4" s="68" t="inlineStr">
@@ -15200,24 +15250,24 @@
       <c r="C4" s="68" t="n"/>
       <c r="D4" s="69" t="inlineStr">
         <is>
-          <t>El texto de la portada es un dato, y cuelga de la marca</t>
+          <t>Misma forma que creator_applications, y solo lo abierto ocupa la puerta</t>
         </is>
       </c>
       <c r="E4" s="69" t="inlineStr">
         <is>
-          <t>9.21b</t>
+          <t>9.21c</t>
         </is>
       </c>
       <c r="F4" s="69" t="inlineStr">
         <is>
-          <t>DEC-190 en el sitio donde mas se nota: la marca del panel la ve quien ya entro; esto lo ve quien todavia esta decidiendo si te escribe. landing_pages lleva platform_brand_id: es UNA columna sobre el eje en el que el producto esta construido --distinto de las asignaciones de tres ejes de 9.17d, que resolvian un problema inexistente--. Dos paginas y no un gestor de contenidos: cada una tiene su formulario y su publico, asi que son codigo.</t>
+          <t>Son el mismo problema: alguien de fuera deja sus datos y alguien de dentro los atiende. Copiar la forma que ya funciona sale mas barato que inventar la segunda, y quien conozca una bandeja conoce las dos. Lo cerrado deja el hueco libre: quien vuelve a escribir el ano que viene es un contacto nuevo de verdad, no un duplicado.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="79.5" customHeight="1" s="36">
       <c r="A5" s="67" t="inlineStr">
         <is>
-          <t>DEC-240</t>
+          <t>DEC-244</t>
         </is>
       </c>
       <c r="B5" s="68" t="inlineStr">
@@ -15228,24 +15278,24 @@
       <c r="C5" s="68" t="n"/>
       <c r="D5" s="69" t="inlineStr">
         <is>
-          <t>La postulacion publica escribe en creator_applications, que ya existia</t>
+          <t>Descartar no es borrar, y convertir se hace en dos pasos</t>
         </is>
       </c>
       <c r="E5" s="69" t="inlineStr">
         <is>
-          <t>9.21b</t>
+          <t>9.21c</t>
         </is>
       </c>
       <c r="F5" s="69" t="inlineStr">
         <is>
-          <t>Existe desde la Fase 2 con source por defecto «landing», su bandeja y su unica de una solicitud abierta por correo; faltaba la landing que escribiera. Un formulario publico que escribe lleva throttle:5,1 y un campo trampa que una persona no ve; si viene lleno se contesta «gracias» y no se escribe nada. Nada de CAPTCHA: barrera para quien lee con dificultad y tramite de segundos para quien automatiza. Vive en Creator y no en Core: T-74 aplicada antes de romperla.</t>
+          <t>De esta tabla salen «.de donde salio este cliente?» y «.cuantos descartamos y por que?»; borrar se lleva las dos por delante. Descartar exige un motivo de al menos diez caracteres. Y convertir exige decir en que cliente: crear ese cliente se sigue haciendo en su pantalla de siempre, porque duplicar el formulario seria tener dos sitios donde se crea un cliente.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34.5" customHeight="1" s="36">
       <c r="A6" s="67" t="inlineStr">
         <is>
-          <t>DEC-241</t>
+          <t>DEC-238</t>
         </is>
       </c>
       <c r="B6" s="68" t="inlineStr">
@@ -15256,7 +15306,7 @@
       <c r="C6" s="68" t="n"/>
       <c r="D6" s="69" t="inlineStr">
         <is>
-          <t>Sin portada se va al acceso, no a un 404</t>
+          <t>/ habla a las MARCAS y /creadores a los creadores</t>
         </is>
       </c>
       <c r="E6" s="69" t="inlineStr">
@@ -15266,14 +15316,14 @@
       </c>
       <c r="F6" s="69" t="inlineStr">
         <is>
-          <t>Una instalacion recien migrada no tiene contenido que ensenar, y eso no puede ser un error en la cara de un visitante: es exactamente lo que habia antes. Lo mismo al apagar una portada desde el admin, que es una decision de contenido y no una averia.</t>
+          <t>Es un mercado de dos lados y el lado que PAGA se pone en la puerta: una portada que abre reclutando creadores se lee como «agencia buscando talento». Los creadores llegan por un enlace, no por la home. Las dos se enlazan entre si. El argumento en contra queda escrito: si el cuello de botella es tener creadores, el trafico que hace falta primero es el suyo; aun asi la home no cambia, porque moverla despues cuesta posicionamiento.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="36">
       <c r="A7" s="67" t="inlineStr">
         <is>
-          <t>DEC-236</t>
+          <t>DEC-239</t>
         </is>
       </c>
       <c r="B7" s="68" t="inlineStr">
@@ -15284,24 +15334,24 @@
       <c r="C7" s="68" t="n"/>
       <c r="D7" s="69" t="inlineStr">
         <is>
-          <t>Todo lo que exige sesion vive bajo /backoffice</t>
+          <t>El texto de la portada es un dato, y cuelga de la marca</t>
         </is>
       </c>
       <c r="E7" s="69" t="inlineStr">
         <is>
-          <t>9.21a</t>
+          <t>9.21b</t>
         </is>
       </c>
       <c r="F7" s="69" t="inlineStr">
         <is>
-          <t>Lo vio el negocio antes de escribir una linea de la landing: /creadores tiene que ser la puerta PUBLICA de los creadores, y descubrirlo despues de publicar habria roto enlaces ya compartidos. Dentro entra todo lo que pide sesion sea de quien sea; lo que cada uno ve lo siguen decidiendo sus permisos. Costo una linea porque docs/08 prohibe escribir URLs a mano en las vistas: comprobado, cero resultados en app/, resources/ y config/.</t>
+          <t>DEC-190 en el sitio donde mas se nota: la marca del panel la ve quien ya entro; esto lo ve quien todavia esta decidiendo si te escribe. landing_pages lleva platform_brand_id: es UNA columna sobre el eje en el que el producto esta construido --distinto de las asignaciones de tres ejes de 9.17d, que resolvian un problema inexistente--. Dos paginas y no un gestor de contenidos: cada una tiene su formulario y su publico, asi que son codigo.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34.5" customHeight="1" s="36">
       <c r="A8" s="67" t="inlineStr">
         <is>
-          <t>DEC-237</t>
+          <t>DEC-240</t>
         </is>
       </c>
       <c r="B8" s="68" t="inlineStr">
@@ -15312,24 +15362,24 @@
       <c r="C8" s="68" t="n"/>
       <c r="D8" s="69" t="inlineStr">
         <is>
-          <t>Veintiuna rutas se quedan fuera, y cada una con su motivo escrito</t>
+          <t>La postulacion publica escribe en creator_applications, que ya existia</t>
         </is>
       </c>
       <c r="E8" s="69" t="inlineStr">
         <is>
-          <t>9.21a</t>
+          <t>9.21b</t>
         </is>
       </c>
       <c r="F8" s="69" t="inlineStr">
         <is>
-          <t>El acceso y la recuperacion son la puerta; la invitacion y la aprobacion llegan por enlace con token a alguien que no tiene cuenta; el logotipo y el favicon los pinta la pantalla de acceso. Dos comparten primer segmento con algo que si se mudo: /contrasena frente a /contrasena/nueva, y /marca frente a /marca/logo. La lista vive en una prueba que recorre todas las rutas con nombre.</t>
+          <t>Existe desde la Fase 2 con source por defecto «landing», su bandeja y su unica de una solicitud abierta por correo; faltaba la landing que escribiera. Un formulario publico que escribe lleva throttle:5,1 y un campo trampa que una persona no ve; si viene lleno se contesta «gracias» y no se escribe nada. Nada de CAPTCHA: barrera para quien lee con dificultad y tramite de segundos para quien automatiza. Vive en Creator y no en Core: T-74 aplicada antes de romperla.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1" s="36">
       <c r="A9" s="67" t="inlineStr">
         <is>
-          <t>DEC-233</t>
+          <t>DEC-241</t>
         </is>
       </c>
       <c r="B9" s="68" t="inlineStr">
@@ -15340,24 +15390,24 @@
       <c r="C9" s="68" t="n"/>
       <c r="D9" s="69" t="inlineStr">
         <is>
-          <t>La configuracion tiene UNA sola puerta, y el menu lateral solo lleva trabajo</t>
+          <t>Sin portada se va al acceso, no a un 404</t>
         </is>
       </c>
       <c r="E9" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21b</t>
         </is>
       </c>
       <c r="F9" s="69" t="inlineStr">
         <is>
-          <t>Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario en una pantalla que se veia igual que Campanas y con el menu marcando otra entrada. El menu queda en tres grupos --Operacion, Finanzas, Registros-- mas Ajustes: Configuracion, y un grupo del que no se puede ver nada desaparece entero.</t>
+          <t>Una instalacion recien migrada no tiene contenido que ensenar, y eso no puede ser un error en la cara de un visitante: es exactamente lo que habia antes. Lo mismo al apagar una portada desde el admin, que es una decision de contenido y no una averia.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="57" customHeight="1" s="36">
       <c r="A10" s="67" t="inlineStr">
         <is>
-          <t>DEC-234</t>
+          <t>DEC-236</t>
         </is>
       </c>
       <c r="B10" s="68" t="inlineStr">
@@ -15368,24 +15418,24 @@
       <c r="C10" s="68" t="n"/>
       <c r="D10" s="69" t="inlineStr">
         <is>
-          <t>El orden de los grupos es una decision y vive en el registro, no en la plantilla</t>
+          <t>Todo lo que exige sesion vive bajo /backoffice</t>
         </is>
       </c>
       <c r="E10" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21a</t>
         </is>
       </c>
       <c r="F10" s="69" t="inlineStr">
         <is>
-          <t>revision() ordena por URGENCIA, que es lo correcto para una lista de avisos y lo peor para una navegacion: «Fiscal y facturacion» saldria arriba o abajo segun que falte hoy, y un sitio que cambia de forma segun el dia no se aprende. Por lo mismo, que rutas son configuracion sale de Preparacion::rutas() y no de la plantilla.</t>
+          <t>Lo vio el negocio antes de escribir una linea de la landing: /creadores tiene que ser la puerta PUBLICA de los creadores, y descubrirlo despues de publicar habria roto enlaces ya compartidos. Dentro entra todo lo que pide sesion sea de quien sea; lo que cada uno ve lo siguen decidiendo sus permisos. Costo una linea porque docs/08 prohibe escribir URLs a mano en las vistas: comprobado, cero resultados en app/, resources/ y config/.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="68.25" customHeight="1" s="36">
       <c r="A11" s="67" t="inlineStr">
         <is>
-          <t>DEC-235</t>
+          <t>DEC-237</t>
         </is>
       </c>
       <c r="B11" s="68" t="inlineStr">
@@ -15396,24 +15446,24 @@
       <c r="C11" s="68" t="n"/>
       <c r="D11" s="69" t="inlineStr">
         <is>
-          <t>Los catalogos son configuracion, con portada propia</t>
+          <t>Veintiuna rutas se quedan fuera, y cada una con su motivo escrito</t>
         </is>
       </c>
       <c r="E11" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21a</t>
         </is>
       </c>
       <c r="F11" s="69" t="inlineStr">
         <is>
-          <t>Los seis colgaban del menu bajo un titulo que no era un sitio: era una etiqueta. Ahora son un area con portada --cuantas filas y cuantas activas-- y su aviso: una lista sin ninguna fila activa sale en rojo, porque un catalogo vacio no da error, deja un desplegable vacio. La pantalla de cada catalogo no se mueve.</t>
+          <t>El acceso y la recuperacion son la puerta; la invitacion y la aprobacion llegan por enlace con token a alguien que no tiene cuenta; el logotipo y el favicon los pinta la pantalla de acceso. Dos comparten primer segmento con algo que si se mudo: /contrasena frente a /contrasena/nueva, y /marca frente a /marca/logo. La lista vive en una prueba que recorre todas las rutas con nombre.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="68.25" customHeight="1" s="36">
       <c r="A12" s="67" t="inlineStr">
         <is>
-          <t>DEC-228</t>
+          <t>DEC-233</t>
         </is>
       </c>
       <c r="B12" s="68" t="inlineStr">
@@ -15424,24 +15474,24 @@
       <c r="C12" s="68" t="n"/>
       <c r="D12" s="69" t="inlineStr">
         <is>
-          <t>Los tipos de comprobante son un catalogo por pais, no un enum en el codigo</t>
+          <t>La configuracion tiene UNA sola puerta, y el menu lateral solo lleva trabajo</t>
         </is>
       </c>
       <c r="E12" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F12" s="69" t="inlineStr">
         <is>
-          <t>ck_ds_type decia IN ('invoice','boleta','credit_note','debit_note','other') desde la Fase 2: la boleta es peruana, el CFDI mexicano no estaba y anadir uno exigia desplegar. Cada tipo declara su codigo oficial de SUNAT, la forma de su serie, como se le pide a una persona y cuantos digitos tiene el correlativo. No contradice a DEC-026: el codigo SE RAMIFICA por proposito de integracion, mientras que el tipo de comprobante NO se ramifica, VIAJA al emisor electronico.</t>
+          <t>Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario en una pantalla que se veia igual que Campanas y con el menu marcando otra entrada. El menu queda en tres grupos --Operacion, Finanzas, Registros-- mas Ajustes: Configuracion, y un grupo del que no se puede ver nada desaparece entero.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="68.25" customHeight="1" s="36">
       <c r="A13" s="67" t="inlineStr">
         <is>
-          <t>DEC-229</t>
+          <t>DEC-234</t>
         </is>
       </c>
       <c r="B13" s="68" t="inlineStr">
@@ -15452,24 +15502,24 @@
       <c r="C13" s="68" t="n"/>
       <c r="D13" s="69" t="inlineStr">
         <is>
-          <t>El numero se reserva bajo bloqueo de la fila de la serie, no con MAX()+1</t>
+          <t>El orden de los grupos es una decision y vive en el registro, no en la plantilla</t>
         </is>
       </c>
       <c r="E13" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F13" s="69" t="inlineStr">
         <is>
-          <t>MAX()+1 es correcto exactamente hasta la primera vez que dos personas emiten a la vez, y eso no es raro: es un cierre de mes. El bloqueo pone en fila a la segunda peticion antes de que lea el contador. Y aun asi existe uq_dn_number: el bloqueo es la primera linea y la unica es la ultima. Medido con dos clientes de verdad (patron de 4.11), con su contraejemplo: sin FOR UPDATE, B no espera.</t>
+          <t>revision() ordena por URGENCIA, que es lo correcto para una lista de avisos y lo peor para una navegacion: «Fiscal y facturacion» saldria arriba o abajo segun que falte hoy, y un sitio que cambia de forma segun el dia no se aprende. Por lo mismo, que rutas son configuracion sale de Preparacion::rutas() y no de la plantilla.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45.75" customHeight="1" s="36">
       <c r="A14" s="67" t="inlineStr">
         <is>
-          <t>DEC-230</t>
+          <t>DEC-235</t>
         </is>
       </c>
       <c r="B14" s="68" t="inlineStr">
@@ -15480,24 +15530,24 @@
       <c r="C14" s="68" t="n"/>
       <c r="D14" s="69" t="inlineStr">
         <is>
-          <t>Cada numero que sale queda escrito, y el hueco se explica en vez de taparse</t>
+          <t>Los catalogos son configuracion, con portada propia</t>
         </is>
       </c>
       <c r="E14" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F14" s="69" t="inlineStr">
         <is>
-          <t>Reservar y no emitir deja un numero sin documento, y eso NO se arregla reutilizandolo: reutilizarlo ES el duplicado. document_numbers guarda cada numero con su estado; reserved es el unico del que se sale, used dice a que documento fue y voided dice por que, con un motivo de al menos diez caracteres. Un hueco explicado es defendible ante un requerimiento; uno mudo, no.</t>
+          <t>Los seis colgaban del menu bajo un titulo que no era un sitio: era una etiqueta. Ahora son un area con portada --cuantas filas y cuantas activas-- y su aviso: una lista sin ninguna fila activa sale en rojo, porque un catalogo vacio no da error, deja un desplegable vacio. La pantalla de cada catalogo no se mueve.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1" s="36">
       <c r="A15" s="67" t="inlineStr">
         <is>
-          <t>DEC-231</t>
+          <t>DEC-228</t>
         </is>
       </c>
       <c r="B15" s="68" t="inlineStr">
@@ -15508,7 +15558,7 @@
       <c r="C15" s="68" t="n"/>
       <c r="D15" s="69" t="inlineStr">
         <is>
-          <t>Una sola serie por defecto por (sociedad, tipo, entorno), y la forma la impone el pais</t>
+          <t>Los tipos de comprobante son un catalogo por pais, no un enum en el codigo</t>
         </is>
       </c>
       <c r="E15" s="69" t="inlineStr">
@@ -15518,14 +15568,14 @@
       </c>
       <c r="F15" s="69" t="inlineStr">
         <is>
-          <t>uq_ds_default es la columna puerta 32: con dos series por defecto, «emitir una factura» no tendria respuesta hasta que alguien eligiera. El empate se rechaza al CONFIGURAR y no al emitir. Y tg_ds_forma_ins/upd exige que la serie tenga la forma que declara su tipo y que el tipo sea del pais de la sociedad: una sociedad peruana no emite comprobantes colombianos.</t>
+          <t>ck_ds_type decia IN ('invoice','boleta','credit_note','debit_note','other') desde la Fase 2: la boleta es peruana, el CFDI mexicano no estaba y anadir uno exigia desplegar. Cada tipo declara su codigo oficial de SUNAT, la forma de su serie, como se le pide a una persona y cuantos digitos tiene el correlativo. No contradice a DEC-026: el codigo SE RAMIFICA por proposito de integracion, mientras que el tipo de comprobante NO se ramifica, VIAJA al emisor electronico.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="57" customHeight="1" s="36">
       <c r="A16" s="67" t="inlineStr">
         <is>
-          <t>DEC-232</t>
+          <t>DEC-229</t>
         </is>
       </c>
       <c r="B16" s="68" t="inlineStr">
@@ -15536,7 +15586,7 @@
       <c r="C16" s="68" t="n"/>
       <c r="D16" s="69" t="inlineStr">
         <is>
-          <t>Las series NO se siembran: unica configuracion sin valor de partida</t>
+          <t>El numero se reserva bajo bloqueo de la fila de la serie, no con MAX()+1</t>
         </is>
       </c>
       <c r="E16" s="69" t="inlineStr">
@@ -15546,14 +15596,14 @@
       </c>
       <c r="F16" s="69" t="inlineStr">
         <is>
-          <t>Excepcion razonada a DEC-190: una serie se registra ante la administracion tributaria y una inventada produciria comprobantes invalidos ante SUNAT --un valor de fabrica aqui no es comodidad, es un error fiscal--. No bloquea nada, que es lo que DEC-190 exige de verdad: sale en rojo en el panel con las palabras que explican por que no hay ninguna. Lo que si se siembra son los TIPOS, que son la regla del pais.</t>
+          <t>MAX()+1 es correcto exactamente hasta la primera vez que dos personas emiten a la vez, y eso no es raro: es un cierre de mes. El bloqueo pone en fila a la segunda peticion antes de que lea el contador. Y aun asi existe uq_dn_number: el bloqueo es la primera linea y la unica es la ultima. Medido con dos clientes de verdad (patron de 4.11), con su contraejemplo: sin FOR UPDATE, B no espera.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="57" customHeight="1" s="36">
       <c r="A17" s="67" t="inlineStr">
         <is>
-          <t>DEC-223</t>
+          <t>DEC-230</t>
         </is>
       </c>
       <c r="B17" s="68" t="inlineStr">
@@ -15564,24 +15614,24 @@
       <c r="C17" s="68" t="n"/>
       <c r="D17" s="69" t="inlineStr">
         <is>
-          <t>Las credenciales de las APIs viven en tres tablas propias, no en .env ni en legal_entities</t>
+          <t>Cada numero que sale queda escrito, y el hueco se explica en vez de taparse</t>
         </is>
       </c>
       <c r="E17" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F17" s="69" t="inlineStr">
         <is>
-          <t>DEC-033 y docs/12 ya lo habian decidido y aqui se construye. Una sociedad es QUIEN factura; una conexion es CON QUE se conecta uno a un proveedor, y cambia mucho mas a menudo que una razon social. En .env seria peor: cambiar de entorno de pruebas a produccion exigiria entrar por SSH, que es DEC-190 roto por la puerta de atras.</t>
+          <t>Reservar y no emitir deja un numero sin documento, y eso NO se arregla reutilizandolo: reutilizarlo ES el duplicado. document_numbers guarda cada numero con su estado; reserved es el unico del que se sale, used dice a que documento fue y voided dice por que, con un motivo de al menos diez caracteres. Un hueco explicado es defendible ante un requerimiento; uno mudo, no.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="68.25" customHeight="1" s="36">
       <c r="A18" s="67" t="inlineStr">
         <is>
-          <t>DEC-224</t>
+          <t>DEC-231</t>
         </is>
       </c>
       <c r="B18" s="68" t="inlineStr">
@@ -15592,24 +15642,24 @@
       <c r="C18" s="68" t="n"/>
       <c r="D18" s="69" t="inlineStr">
         <is>
-          <t>Tres tablas de las cinco de docs/12: las asignaciones no se construyen todavia</t>
+          <t>Una sola serie por defecto por (sociedad, tipo, entorno), y la forma la impone el pais</t>
         </is>
       </c>
       <c r="E18" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F18" s="69" t="inlineStr">
         <is>
-          <t>El eje (marca, sociedad, pais) con vigencia resuelve un problema que hoy no existe: una conexion sirve a una sociedad o a la plataforma entera, y eso cabe en un legal_entity_id nullable donde NULL significa «de la plataforma». Construir la tabla de tres ejes antes de tener el segundo caso es construir contra un supuesto. Queda escrito en la cabecera de la migracion para que no se tome por un olvido.</t>
+          <t>uq_ds_default es la columna puerta 32: con dos series por defecto, «emitir una factura» no tendria respuesta hasta que alguien eligiera. El empate se rechaza al CONFIGURAR y no al emitir. Y tg_ds_forma_ins/upd exige que la serie tenga la forma que declara su tipo y que el tipo sea del pais de la sociedad: una sociedad peruana no emite comprobantes colombianos.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45.75" customHeight="1" s="36">
       <c r="A19" s="67" t="inlineStr">
         <is>
-          <t>DEC-225</t>
+          <t>DEC-232</t>
         </is>
       </c>
       <c r="B19" s="68" t="inlineStr">
@@ -15620,24 +15670,24 @@
       <c r="C19" s="68" t="n"/>
       <c r="D19" s="69" t="inlineStr">
         <is>
-          <t>Rotar una credencial crea la version siguiente y cierra la anterior; no la pisa</t>
+          <t>Las series NO se siembran: unica configuracion sin valor de partida</t>
         </is>
       </c>
       <c r="E19" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F19" s="69" t="inlineStr">
         <is>
-          <t>Se guardan el cifrado y los cuatro ultimos caracteres, nada mas. Pisar el valor deja sin respuesta «cual era la de antes» y «cuando cambio». Las dos escrituras van en la misma transaccion y en ese orden, porque uq_icred_vigente solo admite una viva por (conexion, clase). tg_icred_inmutable impide reescribir una credencial: lo unico que cambia en una fila existente es revocarla.</t>
+          <t>Excepcion razonada a DEC-190: una serie se registra ante la administracion tributaria y una inventada produciria comprobantes invalidos ante SUNAT --un valor de fabrica aqui no es comodidad, es un error fiscal--. No bloquea nada, que es lo que DEC-190 exige de verdad: sale en rojo en el panel con las palabras que explican por que no hay ninguna. Lo que si se siembra son los TIPOS, que son la regla del pais.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="57" customHeight="1" s="36">
       <c r="A20" s="67" t="inlineStr">
         <is>
-          <t>DEC-226</t>
+          <t>DEC-223</t>
         </is>
       </c>
       <c r="B20" s="68" t="inlineStr">
@@ -15648,7 +15698,7 @@
       <c r="C20" s="68" t="n"/>
       <c r="D20" s="69" t="inlineStr">
         <is>
-          <t>La bitacora anota QUE cambio, no que valor</t>
+          <t>Las credenciales de las APIs viven en tres tablas propias, no en .env ni en legal_entities</t>
         </is>
       </c>
       <c r="E20" s="69" t="inlineStr">
@@ -15658,14 +15708,14 @@
       </c>
       <c r="F20" s="69" t="inlineStr">
         <is>
-          <t>Ni el secreto ni los cuatro ultimos entran en audit_log (BR-SEC-001). Un registro de auditoria que guarda el secreto es un segundo sitio donde esta el secreto, y ademas uno que por diseno no se puede borrar. Por eso el servicio parte la lectura en dos: estado() es lo que ve una persona y secreto() lo llama el cliente de la API.</t>
+          <t>DEC-033 y docs/12 ya lo habian decidido y aqui se construye. Una sociedad es QUIEN factura; una conexion es CON QUE se conecta uno a un proveedor, y cambia mucho mas a menudo que una razon social. En .env seria peor: cambiar de entorno de pruebas a produccion exigiria entrar por SSH, que es DEC-190 roto por la puerta de atras.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34.5" customHeight="1" s="36">
       <c r="A21" s="67" t="inlineStr">
         <is>
-          <t>DEC-227</t>
+          <t>DEC-224</t>
         </is>
       </c>
       <c r="B21" s="68" t="inlineStr">
@@ -15676,7 +15726,7 @@
       <c r="C21" s="68" t="n"/>
       <c r="D21" s="69" t="inlineStr">
         <is>
-          <t>Una conexion ACTIVA exige https; un borrador no</t>
+          <t>Tres tablas de las cinco de docs/12: las asignaciones no se construyen todavia</t>
         </is>
       </c>
       <c r="E21" s="69" t="inlineStr">
@@ -15686,14 +15736,14 @@
       </c>
       <c r="F21" s="69" t="inlineStr">
         <is>
-          <t>ck_iconn_url es la unica regla de la iteracion que no es de forma sino de fondo: una URL http a un servicio de facturacion manda las claves secundarias por la red en claro. Se puede escribir mientras la conexion es un borrador y no se puede activar. La regla vive en la base y no en el formulario, porque el formulario no es el unico que escribe.</t>
+          <t>El eje (marca, sociedad, pais) con vigencia resuelve un problema que hoy no existe: una conexion sirve a una sociedad o a la plataforma entera, y eso cabe en un legal_entity_id nullable donde NULL significa «de la plataforma». Construir la tabla de tres ejes antes de tener el segundo caso es construir contra un supuesto. Queda escrito en la cabecera de la migracion para que no se tome por un olvido.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="68.25" customHeight="1" s="36">
       <c r="A22" s="67" t="inlineStr">
         <is>
-          <t>DEC-220</t>
+          <t>DEC-225</t>
         </is>
       </c>
       <c r="B22" s="68" t="inlineStr">
@@ -15704,24 +15754,24 @@
       <c r="C22" s="68" t="n"/>
       <c r="D22" s="69" t="inlineStr">
         <is>
-          <t>Core levanta un evento; Creator escucha</t>
+          <t>Rotar una credencial crea la version siguiente y cierra la anterior; no la pisa</t>
         </is>
       </c>
       <c r="E22" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F22" s="69" t="inlineStr">
         <is>
-          <t>Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
+          <t>Se guardan el cifrado y los cuatro ultimos caracteres, nada mas. Pisar el valor deja sin respuesta «cual era la de antes» y «cuando cambio». Las dos escrituras van en la misma transaccion y en ese orden, porque uq_icred_vigente solo admite una viva por (conexion, clase). tg_icred_inmutable impide reescribir una credencial: lo unico que cambia en una fila existente es revocarla.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="57" customHeight="1" s="36">
       <c r="A23" s="67" t="inlineStr">
         <is>
-          <t>DEC-221</t>
+          <t>DEC-226</t>
         </is>
       </c>
       <c r="B23" s="68" t="inlineStr">
@@ -15732,24 +15782,24 @@
       <c r="C23" s="68" t="n"/>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
+          <t>La bitacora anota QUE cambio, no que valor</t>
         </is>
       </c>
       <c r="E23" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F23" s="69" t="inlineStr">
         <is>
-          <t>Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
+          <t>Ni el secreto ni los cuatro ultimos entran en audit_log (BR-SEC-001). Un registro de auditoria que guarda el secreto es un segundo sitio donde esta el secreto, y ademas uno que por diseno no se puede borrar. Por eso el servicio parte la lectura en dos: estado() es lo que ve una persona y secreto() lo llama el cliente de la API.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34.5" customHeight="1" s="36">
       <c r="A24" s="67" t="inlineStr">
         <is>
-          <t>DEC-222</t>
+          <t>DEC-227</t>
         </is>
       </c>
       <c r="B24" s="68" t="inlineStr">
@@ -15760,24 +15810,24 @@
       <c r="C24" s="68" t="n"/>
       <c r="D24" s="69" t="inlineStr">
         <is>
-          <t>Un correo que falla no deja sin avisar a los demas</t>
+          <t>Una conexion ACTIVA exige https; un borrador no</t>
         </is>
       </c>
       <c r="E24" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F24" s="69" t="inlineStr">
         <is>
-          <t>Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
+          <t>ck_iconn_url es la unica regla de la iteracion que no es de forma sino de fondo: una URL http a un servicio de facturacion manda las claves secundarias por la red en claro. Se puede escribir mientras la conexion es un borrador y no se puede activar. La regla vive en la base y no en el formulario, porque el formulario no es el unico que escribe.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45.75" customHeight="1" s="36">
       <c r="A25" s="67" t="inlineStr">
         <is>
-          <t>DEC-216</t>
+          <t>DEC-220</t>
         </is>
       </c>
       <c r="B25" s="68" t="inlineStr">
@@ -15788,24 +15838,24 @@
       <c r="C25" s="68" t="n"/>
       <c r="D25" s="69" t="inlineStr">
         <is>
-          <t>Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
+          <t>Core levanta un evento; Creator escucha</t>
         </is>
       </c>
       <c r="E25" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F25" s="69" t="inlineStr">
         <is>
-          <t>El plazo es parte de lo que se le comunico a la gente: «tienes 15 dias» dicho en enero no puede convertirse en «tenias 10» porque en marzo alguien cambio un ajuste global. Cada version lleva los suyos, se eligen al publicarla y despues son inmutables. Lo configurable es el valor por defecto, que es lo que el formulario trae puesto. readonly_days = 0 significa «sin periodo de solo lectura»; un numero muy grande, lo contrario.</t>
+          <t>Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="57" customHeight="1" s="36">
       <c r="A26" s="67" t="inlineStr">
         <is>
-          <t>DEC-217</t>
+          <t>DEC-221</t>
         </is>
       </c>
       <c r="B26" s="68" t="inlineStr">
@@ -15816,24 +15866,24 @@
       <c r="C26" s="68" t="n"/>
       <c r="D26" s="69" t="inlineStr">
         <is>
-          <t>El reloj no empieza al publicar: empieza cuando le toca a el</t>
+          <t>El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
         </is>
       </c>
       <c r="E26" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F26" s="69" t="inlineStr">
         <is>
-          <t>Un creador activado ayer no puede aparecer bloqueado por una version de hace tres meses. Su plazo cuenta desde el dia en que se activo, o desde la fecha de la version si es posterior. Sin esto, el primer creador que se diera de alta despues de un cambio de fondo entraria directamente al muro sin haber tenido un solo dia.</t>
+          <t>Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="68.25" customHeight="1" s="36">
       <c r="A27" s="67" t="inlineStr">
         <is>
-          <t>DEC-218</t>
+          <t>DEC-222</t>
         </is>
       </c>
       <c r="B27" s="68" t="inlineStr">
@@ -15844,24 +15894,24 @@
       <c r="C27" s="68" t="n"/>
       <c r="D27" s="69" t="inlineStr">
         <is>
-          <t>La pantalla del muro no lleva permiso, y eso es la decision</t>
+          <t>Un correo que falla no deja sin avisar a los demas</t>
         </is>
       </c>
       <c r="E27" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F27" s="69" t="inlineStr">
         <is>
-          <t>/mis-terminos es la unica salida de un creador bloqueado: un permiso dejaria sin salida justo a quien la necesita. La autorizacion es tener ficha de creador atada a la sesion. El trinquete de rutas exentas subio de 4 a 6 a mano y con motivo escrito, que es todo el sentido de ese trinquete. Lleva throttle:10,1.</t>
+          <t>Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="57" customHeight="1" s="36">
       <c r="A28" s="67" t="inlineStr">
         <is>
-          <t>DEC-219</t>
+          <t>DEC-216</t>
         </is>
       </c>
       <c r="B28" s="68" t="inlineStr">
@@ -15872,7 +15922,7 @@
       <c r="C28" s="68" t="n"/>
       <c r="D28" s="69" t="inlineStr">
         <is>
-          <t>Una franja fija, no un popup</t>
+          <t>Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
         </is>
       </c>
       <c r="E28" s="69" t="inlineStr">
@@ -15882,14 +15932,14 @@
       </c>
       <c r="F28" s="69" t="inlineStr">
         <is>
-          <t>El negocio pidio «popup como recordatorio al loguearse». Un popup se cierra sin leerlo y no vuelve hasta la siguiente sesion; la franja sigue ahi mientras siga sin aceptarse. El equipo interno no la ve nunca.</t>
+          <t>El plazo es parte de lo que se le comunico a la gente: «tienes 15 dias» dicho en enero no puede convertirse en «tenias 10» porque en marzo alguien cambio un ajuste global. Cada version lleva los suyos, se eligen al publicarla y despues son inmutables. Lo configurable es el valor por defecto, que es lo que el formulario trae puesto. readonly_days = 0 significa «sin periodo de solo lectura»; un numero muy grande, lo contrario.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="68.25" customHeight="1" s="36">
       <c r="A29" s="67" t="inlineStr">
         <is>
-          <t>DEC-212</t>
+          <t>DEC-217</t>
         </is>
       </c>
       <c r="B29" s="68" t="inlineStr">
@@ -15900,24 +15950,24 @@
       <c r="C29" s="68" t="n"/>
       <c r="D29" s="69" t="inlineStr">
         <is>
-          <t>Una politica de precios con vigencia, no dos constantes</t>
+          <t>El reloj no empieza al publicar: empieza cuando le toca a el</t>
         </is>
       </c>
       <c r="E29" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F29" s="69" t="inlineStr">
         <is>
-          <t>pricing_policies guarda la retencion (Q-13), el umbral de rentabilidad y sobre que se calcula. Los tres cambian: el 29,5 % por decreto y el 20 % con datos reales. Tiene historia --una sola vigente-- y una cerrada no se reescribe ni se borra: es la que explica como se pacto un compromiso de hace tres meses.</t>
+          <t>Un creador activado ayer no puede aparecer bloqueado por una version de hace tres meses. Su plazo cuenta desde el dia en que se activo, o desde la fecha de la version si es posterior. Sin esto, el primer creador que se diera de alta despues de un cambio de fondo entraria directamente al muro sin haber tenido un solo dia.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45.75" customHeight="1" s="36">
       <c r="A30" s="67" t="inlineStr">
         <is>
-          <t>DEC-213</t>
+          <t>DEC-218</t>
         </is>
       </c>
       <c r="B30" s="68" t="inlineStr">
@@ -15928,24 +15978,24 @@
       <c r="C30" s="68" t="n"/>
       <c r="D30" s="69" t="inlineStr">
         <is>
-          <t>margin_basis es configuracion, no una pregunta</t>
+          <t>La pantalla del muro no lleva permiso, y eso es la decision</t>
         </is>
       </c>
       <c r="E30" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F30" s="69" t="inlineStr">
         <is>
-          <t>Con 100 de neto y 29,5 % el costo es 141,84; el ejemplo del negocio dio 170,21, que es 141,84 x 1,20 (recargo sobre el COSTO). Un 20 % de margen sobre el INGRESO habria dado 177,31. Lo iba a preguntar dos veces; DEC-190 dice que estas cosas se configuran, y preguntarlo habria sido quemar la respuesta en el codigo con la firma del negocio encima. Es una columna con dos valores, sembrada en cost, con la pantalla ensenando las dos cifras y una prueba de cada una.</t>
+          <t>/mis-terminos es la unica salida de un creador bloqueado: un permiso dejaria sin salida justo a quien la necesita. La autorizacion es tener ficha de creador atada a la sesion. El trinquete de rutas exentas subio de 4 a 6 a mano y con motivo escrito, que es todo el sentido de ese trinquete. Lleva throttle:10,1.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="79.5" customHeight="1" s="36">
       <c r="A31" s="67" t="inlineStr">
         <is>
-          <t>DEC-214</t>
+          <t>DEC-219</t>
         </is>
       </c>
       <c r="B31" s="68" t="inlineStr">
@@ -15956,24 +16006,24 @@
       <c r="C31" s="68" t="n"/>
       <c r="D31" s="69" t="inlineStr">
         <is>
-          <t>Se pacta el costo o el neto, y el ingreso minimo se dice, no se impone</t>
+          <t>Una franja fija, no un popup</t>
         </is>
       </c>
       <c r="E31" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F31" s="69" t="inlineStr">
         <is>
-          <t>agreed_amount sigue siendo el costo: de esa columna cuelgan devengos, pagos y la rentabilidad de 9.10. Se anaden la base, el neto y la tasa. Con net se teclean 100 y se escriben 141,8440, y el motor rehace la resta: un neto que no cuadra con su bruto se descubriria en la conversacion con el creador que cobro de menos. El mensaje dice el ingreso minimo y no bloquea: se puede aceptar menos margen, pero sabiendolo y antes de invitar. Los tres numeros se congelan en la participacion.</t>
+          <t>El negocio pidio «popup como recordatorio al loguearse». Un popup se cierra sin leerlo y no vuelve hasta la siguiente sesion; la franja sigue ahi mientras siga sin aceptarse. El equipo interno no la ve nunca.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="68.25" customHeight="1" s="36">
       <c r="A32" s="67" t="inlineStr">
         <is>
-          <t>DEC-215</t>
+          <t>DEC-212</t>
         </is>
       </c>
       <c r="B32" s="68" t="inlineStr">
@@ -15984,7 +16034,7 @@
       <c r="C32" s="68" t="n"/>
       <c r="D32" s="69" t="inlineStr">
         <is>
-          <t>La cuenta la hace el motor, no PHP</t>
+          <t>Una politica de precios con vigencia, no dos constantes</t>
         </is>
       </c>
       <c r="E32" s="69" t="inlineStr">
@@ -15994,14 +16044,14 @@
       </c>
       <c r="F32" s="69" t="inlineStr">
         <is>
-          <t>neto / (1 - tasa/100) con float da 141.84397163120568 y de ahi a un DECIMAL(18,4) hay un redondeo que puede caer del lado que el CHECK no admite. El contenedor no tiene bcmath, asi que la aritmetica exacta se hace en el motor con CAST a DECIMAL(28,12). Misma tecnica que 9.1 y 9.3.</t>
+          <t>pricing_policies guarda la retencion (Q-13), el umbral de rentabilidad y sobre que se calcula. Los tres cambian: el 29,5 % por decreto y el 20 % con datos reales. Tiene historia --una sola vigente-- y una cerrada no se reescribe ni se borra: es la que explica como se pacto un compromiso de hace tres meses.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45.75" customHeight="1" s="36">
       <c r="A33" s="67" t="inlineStr">
         <is>
-          <t>DEC-209</t>
+          <t>DEC-213</t>
         </is>
       </c>
       <c r="B33" s="68" t="inlineStr">
@@ -16012,24 +16062,24 @@
       <c r="C33" s="68" t="n"/>
       <c r="D33" s="69" t="inlineStr">
         <is>
-          <t>La forma del codigo de localidad la declara el pais, no el codigo</t>
+          <t>margin_basis es configuracion, no una pregunta</t>
         </is>
       </c>
       <c r="E33" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F33" s="69" t="inlineStr">
         <is>
-          <t>El comprobante peruano lleva el ubigeo del INEI (seis digitos) y el colombiano el codigo DANE (cinco). Una columna ubigeo CHAR(6) habria sido la regla de un pais escrita en el codigo de los seis y rechazaria un codigo colombiano correcto. countries declara como se llama, que forma tiene y si ese pais lo exige; el formulario pide «Ubigeo» a una peruana y «Codigo DANE» a una colombiana sin una linea de codigo por pais. La imponen dos disparadores cruzados que leen el patron de countries.</t>
+          <t>Con 100 de neto y 29,5 % el costo es 141,84; el ejemplo del negocio dio 170,21, que es 141,84 x 1,20 (recargo sobre el COSTO). Un 20 % de margen sobre el INGRESO habria dado 177,31. Lo iba a preguntar dos veces; DEC-190 dice que estas cosas se configuran, y preguntarlo habria sido quemar la respuesta en el codigo con la firma del negocio encima. Es una columna con dos valores, sembrada en cost, con la pantalla ensenando las dos cifras y una prueba de cada una.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45.75" customHeight="1" s="36">
       <c r="A34" s="67" t="inlineStr">
         <is>
-          <t>DEC-210</t>
+          <t>DEC-214</t>
         </is>
       </c>
       <c r="B34" s="68" t="inlineStr">
@@ -16040,24 +16090,24 @@
       <c r="C34" s="68" t="n"/>
       <c r="D34" s="69" t="inlineStr">
         <is>
-          <t>El codigo de establecimiento nace en «0000» y no admite nulo</t>
+          <t>Se pacta el costo o el neto, y el ingreso minimo se dice, no se impone</t>
         </is>
       </c>
       <c r="E34" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F34" s="69" t="inlineStr">
         <is>
-          <t>Un comprobante SIEMPRE lleva uno; dejarlo nulo obligaria a decidirlo al emitir, que es tarde. «0000» es el domicilio fiscal en SUNAT. El formulario lo puede dejar en blanco --al crear y al editar-- y entonces vale 0000: sin esa normalizacion, vaciar el campo metia una cadena vacia que ck_le_establecimiento rechaza con un 45000 sin explicar nada.</t>
+          <t>agreed_amount sigue siendo el costo: de esa columna cuelgan devengos, pagos y la rentabilidad de 9.10. Se anaden la base, el neto y la tasa. Con net se teclean 100 y se escriben 141,8440, y el motor rehace la resta: un neto que no cuadra con su bruto se descubriria en la conversacion con el creador que cobro de menos. El mensaje dice el ingreso minimo y no bloquea: se puede aceptar menos margen, pero sabiendolo y antes de invitar. Los tres numeros se congelan en la participacion.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="68.25" customHeight="1" s="36">
       <c r="A35" s="67" t="inlineStr">
         <is>
-          <t>DEC-211</t>
+          <t>DEC-215</t>
         </is>
       </c>
       <c r="B35" s="68" t="inlineStr">
@@ -16068,24 +16118,24 @@
       <c r="C35" s="68" t="n"/>
       <c r="D35" s="69" t="inlineStr">
         <is>
-          <t>Que falte el ubigeo no bloquea: es un aviso rojo</t>
+          <t>La cuenta la hace el motor, no PHP</t>
         </is>
       </c>
       <c r="E35" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F35" s="69" t="inlineStr">
         <is>
-          <t>requires_tax_location no impide guardar una sociedad a medias; hace que el panel de 9.17b lo enseñe en rojo con el nombre que ese pais le da. Y sale a la luz algo que no decia nadie: el sembrador escribe address_line1 = «Por completar» porque la columna es NOT NULL, la sociedad parecia completa, y ese texto habria salido impreso en un comprobante.</t>
+          <t>neto / (1 - tasa/100) con float da 141.84397163120568 y de ahi a un DECIMAL(18,4) hay un redondeo que puede caer del lado que el CHECK no admite. El contenedor no tiene bcmath, asi que la aritmetica exacta se hace en el motor con CAST a DECIMAL(28,12). Misma tecnica que 9.1 y 9.3.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="57" customHeight="1" s="36">
       <c r="A36" s="67" t="inlineStr">
         <is>
-          <t>DEC-205</t>
+          <t>DEC-209</t>
         </is>
       </c>
       <c r="B36" s="68" t="inlineStr">
@@ -16096,24 +16146,24 @@
       <c r="C36" s="68" t="n"/>
       <c r="D36" s="69" t="inlineStr">
         <is>
-          <t>Un registro de preparacion, y cada modulo declara lo suyo</t>
+          <t>La forma del codigo de localidad la declara el pais, no el codigo</t>
         </is>
       </c>
       <c r="E36" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F36" s="69" t="inlineStr">
         <is>
-          <t>9.16 y 9.17 dejaron cada una su lista de avisos y cada una solo se ve entrando en su pantalla. Preparacion las junta, y cada modulo declara las comprobaciones de su area en su ServiceProvider: un revisor central pondria a Shared a saber de cinco modulos sin que deptrac lo vea, porque son consultas a tablas y no clases importadas. Hay una prueba que se rompe cuando alguien construye una pantalla de configuracion nueva y no la enchufa.</t>
+          <t>El comprobante peruano lleva el ubigeo del INEI (seis digitos) y el colombiano el codigo DANE (cinco). Una columna ubigeo CHAR(6) habria sido la regla de un pais escrita en el codigo de los seis y rechazaria un codigo colombiano correcto. countries declara como se llama, que forma tiene y si ese pais lo exige; el formulario pide «Ubigeo» a una peruana y «Codigo DANE» a una colombiana sin una linea de codigo por pais. La imponen dos disparadores cruzados que leen el patron de countries.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="68.25" customHeight="1" s="36">
       <c r="A37" s="67" t="inlineStr">
         <is>
-          <t>DEC-206</t>
+          <t>DEC-210</t>
         </is>
       </c>
       <c r="B37" s="68" t="inlineStr">
@@ -16124,24 +16174,24 @@
       <c r="C37" s="68" t="n"/>
       <c r="D37" s="69" t="inlineStr">
         <is>
-          <t>Si no puedes arreglarlo, no lo ves</t>
+          <t>El codigo de establecimiento nace en «0000» y no admite nulo</t>
         </is>
       </c>
       <c r="E37" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F37" s="69" t="inlineStr">
         <is>
-          <t>Cada area declara el permiso con el que SE ARREGLA, no el que hace falta para abrir el panel, y la revision filtra por el. BR-SEC-001 sigue en pie aunque la pantalla reuna en un sitio lo que estaba repartido en cinco, y ningun aviso lleva a un 403. Por eso config.view se le puede dar a finanzas sin miedo: ve el area de tipos de cambio y nada mas.</t>
+          <t>Un comprobante SIEMPRE lleva uno; dejarlo nulo obligaria a decidirlo al emitir, que es tarde. «0000» es el domicilio fiscal en SUNAT. El formulario lo puede dejar en blanco --al crear y al editar-- y entonces vale 0000: sin esa normalizacion, vaciar el campo metia una cadena vacia que ck_le_establecimiento rechaza con un 45000 sin explicar nada.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="45.75" customHeight="1" s="36">
       <c r="A38" s="67" t="inlineStr">
         <is>
-          <t>DEC-207</t>
+          <t>DEC-211</t>
         </is>
       </c>
       <c r="B38" s="68" t="inlineStr">
@@ -16152,24 +16202,24 @@
       <c r="C38" s="68" t="n"/>
       <c r="D38" s="69" t="inlineStr">
         <is>
-          <t>Una comprobacion que revienta no tumba el panel</t>
+          <t>Que falte el ubigeo no bloquea: es un aviso rojo</t>
         </is>
       </c>
       <c r="E38" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>Un revisor que lanza una excepcion se convierte en un aviso ambar que lo dice, y las demas areas se siguen viendo. Un panel de «que me falta» que responde 500 porque a un area le pasa algo deja de contestar justo el dia en que hay algo que contestar.</t>
+          <t>requires_tax_location no impide guardar una sociedad a medias; hace que el panel de 9.17b lo enseñe en rojo con el nombre que ese pais le da. Y sale a la luz algo que no decia nadie: el sembrador escribe address_line1 = «Por completar» porque la columna es NOT NULL, la sociedad parecia completa, y ese texto habria salido impreso en un comprobante.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="90.75" customHeight="1" s="36">
       <c r="A39" s="67" t="inlineStr">
         <is>
-          <t>DEC-208</t>
+          <t>DEC-205</t>
         </is>
       </c>
       <c r="B39" s="68" t="inlineStr">
@@ -16180,7 +16230,7 @@
       <c r="C39" s="68" t="n"/>
       <c r="D39" s="69" t="inlineStr">
         <is>
-          <t>El correo en log es ROJO, y va el primero del panel</t>
+          <t>Un registro de preparacion, y cada modulo declara lo suyo</t>
         </is>
       </c>
       <c r="E39" s="69" t="inlineStr">
@@ -16190,14 +16240,14 @@
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>mail.default vale log mientras nadie ponga una cuenta SMTP (Q-20), y con ese valor el correo no sale de la maquina: se escribe en storage/logs. La aplicacion no falla, la bitacora dice enviado y el creador no recibe su enlace de alta. Es el modo de fallo mas caro del sistema porque no se nota desde dentro, y hasta hoy no lo decia ninguna pantalla.</t>
+          <t>9.16 y 9.17 dejaron cada una su lista de avisos y cada una solo se ve entrando en su pantalla. Preparacion las junta, y cada modulo declara las comprobaciones de su area en su ServiceProvider: un revisor central pondria a Shared a saber de cinco modulos sin que deptrac lo vea, porque son consultas a tablas y no clases importadas. Hay una prueba que se rompe cuando alguien construye una pantalla de configuracion nueva y no la enchufa.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="45.75" customHeight="1" s="36">
       <c r="A40" s="67" t="inlineStr">
         <is>
-          <t>DEC-199</t>
+          <t>DEC-206</t>
         </is>
       </c>
       <c r="B40" s="68" t="inlineStr">
@@ -16208,24 +16258,24 @@
       <c r="C40" s="68" t="n"/>
       <c r="D40" s="69" t="inlineStr">
         <is>
-          <t>La marca es una fila, y hay UNA sola por defecto</t>
+          <t>Si no puedes arreglarlo, no lo ves</t>
         </is>
       </c>
       <c r="E40" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>«LATAM Social» estaba escrito en tres plantillas --title, barra lateral y pantalla de acceso--, el favicon era un archivo del repositorio y el pie legal con la razon social y el RUC estaba a mano al pie del formulario de entrada. platform_brands guardaba todo eso desde 2.10 y nadie la leyo nunca. default_gate es la 28.a columna puerta y uq_pb_default la hace unica: dos marcas por defecto es media aplicacion ensenando un nombre y la otra mitad otro sin que nada falle.</t>
+          <t>Cada area declara el permiso con el que SE ARREGLA, no el que hace falta para abrir el panel, y la revision filtra por el. BR-SEC-001 sigue en pie aunque la pantalla reuna en un sitio lo que estaba repartido en cinco, y ningun aviso lleva a un 403. Por eso config.view se le puede dar a finanzas sin miedo: ve el area de tipos de cambio y nada mas.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="57" customHeight="1" s="36">
       <c r="A41" s="67" t="inlineStr">
         <is>
-          <t>DEC-200</t>
+          <t>DEC-207</t>
         </is>
       </c>
       <c r="B41" s="68" t="inlineStr">
@@ -16236,24 +16286,24 @@
       <c r="C41" s="68" t="n"/>
       <c r="D41" s="69" t="inlineStr">
         <is>
-          <t>Una configuracion que falta NO bloquea: valor de partida y aviso con prioridad</t>
+          <t>Una comprobacion que revienta no tumba el panel</t>
         </is>
       </c>
       <c r="E41" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>DEC-190 llevado al codigo. Sin tabla, sin fila o con un campo vacio se cae al valor de partida y aparece un badge: rojo lo que un tercero va a ver mal (sin logotipo, sin correo de soporte), ambar lo que conviene (sin favicon, sin pie legal, sin web), verde cuando no falta nada. El sistema arranca con dos rojos y funciona perfectamente con los dos puestos.</t>
+          <t>Un revisor que lanza una excepcion se convierte en un aviso ambar que lo dice, y las demas areas se siguen viendo. Un panel de «que me falta» que responde 500 porque a un area le pasa algo deja de contestar justo el dia en que hay algo que contestar.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="45.75" customHeight="1" s="36">
       <c r="A42" s="67" t="inlineStr">
         <is>
-          <t>DEC-201</t>
+          <t>DEC-208</t>
         </is>
       </c>
       <c r="B42" s="68" t="inlineStr">
@@ -16264,24 +16314,24 @@
       <c r="C42" s="68" t="n"/>
       <c r="D42" s="69" t="inlineStr">
         <is>
-          <t>El logotipo se sirve por una puerta publica propia, sin identificador</t>
+          <t>El correo en log es ROJO, y va el primero del panel</t>
         </is>
       </c>
       <c r="E42" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>La pantalla de acceso la ve quien no ha entrado, asi que el permiso file.view de 9.15 dejaria la marca fuera de la unica pantalla que ve todo el mundo. Lo que hace seguras a /marca/logo y /marca/favicon no es un permiso: es que NO aceptan identificador. Estan en RUTAS-ABIERTAS con su motivo y MuroTest las conoce.</t>
+          <t>mail.default vale log mientras nadie ponga una cuenta SMTP (Q-20), y con ese valor el correo no sale de la maquina: se escribe en storage/logs. La aplicacion no falla, la bitacora dice enviado y el creador no recibe su enlace de alta. Es el modo de fallo mas caro del sistema porque no se nota desde dentro, y hasta hoy no lo decia ninguna pantalla.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="68.25" customHeight="1" s="36">
       <c r="A43" s="67" t="inlineStr">
         <is>
-          <t>DEC-202</t>
+          <t>DEC-199</t>
         </is>
       </c>
       <c r="B43" s="68" t="inlineStr">
@@ -16292,7 +16342,7 @@
       <c r="C43" s="68" t="n"/>
       <c r="D43" s="69" t="inlineStr">
         <is>
-          <t>El codigo de la marca no se cambia; el nombre visible si</t>
+          <t>La marca es una fila, y hay UNA sola por defecto</t>
         </is>
       </c>
       <c r="E43" s="69" t="inlineStr">
@@ -16302,14 +16352,14 @@
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>tg_pb_code lo impide en el motor. El code es la llave con la que el sembrador encuentra la marca: si cambia, el siguiente db:seed crea otra, el sistema amanece con dos y las pantallas siguen ensenando la vieja mientras alguien edita la nueva.</t>
+          <t>«LATAM Social» estaba escrito en tres plantillas --title, barra lateral y pantalla de acceso--, el favicon era un archivo del repositorio y el pie legal con la razon social y el RUC estaba a mano al pie del formulario de entrada. platform_brands guardaba todo eso desde 2.10 y nadie la leyo nunca. default_gate es la 28.a columna puerta y uq_pb_default la hace unica: dos marcas por defecto es media aplicacion ensenando un nombre y la otra mitad otro sin que nada falle.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="79.5" customHeight="1" s="36">
       <c r="A44" s="67" t="inlineStr">
         <is>
-          <t>DEC-203</t>
+          <t>DEC-200</t>
         </is>
       </c>
       <c r="B44" s="68" t="inlineStr">
@@ -16320,7 +16370,7 @@
       <c r="C44" s="68" t="n"/>
       <c r="D44" s="69" t="inlineStr">
         <is>
-          <t>Los colores y la tipografia se desinfectan ademas del CHECK</t>
+          <t>Una configuracion que falta NO bloquea: valor de partida y aviso con prioridad</t>
         </is>
       </c>
       <c r="E44" s="69" t="inlineStr">
@@ -16330,14 +16380,14 @@
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>El color acaba dentro de una regla CSS y la tipografia dentro de una URL y de una regla CSS, en todas las pantallas a la vez. Un nombre con comillas y llaves cierra la regla y escribe estilo ajeno en toda la aplicacion. Si el valor entra por una via que no pasa por el CHECK --carga masiva, restauracion de copia--, la segunda cerradura es lo unico que queda.</t>
+          <t>DEC-190 llevado al codigo. Sin tabla, sin fila o con un campo vacio se cae al valor de partida y aparece un badge: rojo lo que un tercero va a ver mal (sin logotipo, sin correo de soporte), ambar lo que conviene (sin favicon, sin pie legal, sin web), verde cuando no falta nada. El sistema arranca con dos rojos y funciona perfectamente con los dos puestos.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="124.5" customHeight="1" s="36">
       <c r="A45" s="67" t="inlineStr">
         <is>
-          <t>DEC-204</t>
+          <t>DEC-201</t>
         </is>
       </c>
       <c r="B45" s="68" t="inlineStr">
@@ -16348,7 +16398,7 @@
       <c r="C45" s="68" t="n"/>
       <c r="D45" s="69" t="inlineStr">
         <is>
-          <t>brand.manage es un permiso propio, y no legal_entity.manage</t>
+          <t>El logotipo se sirve por una puerta publica propia, sin identificador</t>
         </is>
       </c>
       <c r="E45" s="69" t="inlineStr">
@@ -16358,14 +16408,14 @@
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>Quien da de alta sociedades del grupo no tiene por que poder cambiar lo que ve todo el mundo en todas las pantallas, incluida la de acceso. Hoy los dos los tiene solo admin; el dia que legal_entity.manage se le de a alguien de operaciones, esa persona no podra cambiar la marca. Hay una prueba que lo fija.</t>
+          <t>La pantalla de acceso la ve quien no ha entrado, asi que el permiso file.view de 9.15 dejaria la marca fuera de la unica pantalla que ve todo el mundo. Lo que hace seguras a /marca/logo y /marca/favicon no es un permiso: es que NO aceptan identificador. Estan en RUTAS-ABIERTAS con su motivo y MuroTest las conoce.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="90.75" customHeight="1" s="36">
       <c r="A46" s="67" t="inlineStr">
         <is>
-          <t>DEC-198</t>
+          <t>DEC-202</t>
         </is>
       </c>
       <c r="B46" s="68" t="inlineStr">
@@ -16376,24 +16426,24 @@
       <c r="C46" s="68" t="n"/>
       <c r="D46" s="69" t="inlineStr">
         <is>
-          <t>El permiso se mira en CADA peticion: no hay URL firmada de archivo.</t>
+          <t>El codigo de la marca no se cambia; el nombre visible si</t>
         </is>
       </c>
       <c r="E46" s="69" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>Una URL firmada sigue funcionando cuando se reenvia y cuando a esa persona ya se le quito el acceso, y lo que sale por aqui son documentos de identidad y comprobantes bancarios. Con ruta propia, quitar un permiso surte efecto en la siguiente peticion y no queda ningun enlace circulando. El archivo se busca por uuid y no por id --un id correlativo invita a probar el siguiente-- y la respuesta lleva no-store (una identidad en la cache de un equipo compartido sobrevive al cierre de sesion), nosniff y una CSP que impide que un HTML o un SVG subido como «evidencia» se ejecute. El creador ve lo suyo, incluida su identidad: es informacion suya y le permite comprobar que archivamos el correcto. Rastro en bitacora solo para los sensibles --identidad, terminos y comprobante bancario--: anotar cada captura convertiria la bitacora en ruido, y una bitacora que nadie lee no protege nada</t>
+          <t>tg_pb_code lo impide en el motor. El code es la llave con la que el sembrador encuentra la marca: si cambia, el siguiente db:seed crea otra, el sistema amanece con dos y las pantallas siguen ensenando la vieja mientras alguien edita la nueva.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="68.25" customHeight="1" s="36">
       <c r="A47" s="67" t="inlineStr">
         <is>
-          <t>DEC-197</t>
+          <t>DEC-203</t>
         </is>
       </c>
       <c r="B47" s="68" t="inlineStr">
@@ -16404,24 +16454,24 @@
       <c r="C47" s="68" t="n"/>
       <c r="D47" s="69" t="inlineStr">
         <is>
-          <t>Cada modulo declara quien puede ver SUS archivos; no hay un switch central.</t>
+          <t>Los colores y la tipografia se desinfectan ademas del CHECK</t>
         </is>
       </c>
       <c r="E47" s="69" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>La regla de cada archivo depende de la tabla que lo apunta --identidad de creators, captura de publication_evidence, comprobante de payouts-- y un decisor central que las consultara todas pondria a Shared o a Core a saber de payouts. deptrac no lo veria: son consultas a tablas y no clases importadas, o sea una frontera rota en silencio, que es la peor clase. Cada modulo registra su regla en su ServiceProvider, igual que registra sus escuchas. Y se niega por omision: un proposito sin regla no se abre ni para el administrador, asi que un archivo nuevo cuyo autor olvido declarar quien puede verlo se queda cerrado y no abierto a todos</t>
+          <t>El color acaba dentro de una regla CSS y la tipografia dentro de una URL y de una regla CSS, en todas las pantallas a la vez. Un nombre con comillas y llaves cierra la regla y escribe estilo ajeno en toda la aplicacion. Si el valor entra por una via que no pasa por el CHECK --carga masiva, restauracion de copia--, la segunda cerradura es lo unico que queda.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="45.75" customHeight="1" s="36">
       <c r="A48" s="67" t="inlineStr">
         <is>
-          <t>DEC-196</t>
+          <t>DEC-204</t>
         </is>
       </c>
       <c r="B48" s="68" t="inlineStr">
@@ -16432,24 +16482,24 @@
       <c r="C48" s="68" t="n"/>
       <c r="D48" s="69" t="inlineStr">
         <is>
-          <t>La Academia del creador se construye, y cada modulo se configura desde el admin.</t>
+          <t>brand.manage es un permiso propio, y no legal_entity.manage</t>
         </is>
       </c>
       <c r="E48" s="69" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>Es G-08 del addendum de gamificacion y la de mas retorno de las once: modulos cortos --leer un brief sin gastar rondas, iluminacion y audio con un movil, como se rotula el contenido comercial, que derechos esta cediendo, como subir su evidencia-- con evaluacion al final e insignia de creador certificado. Ataca tres dolores ya medidos: cada ronda evitada es tiempo del equipo de revision, cada evidencia subida sola es el proceso mas manual que se deja de perseguir, y «creadores certificados» es un argumento de venta ante la marca. El software es la parte barata: modulos, orden, formato, evaluacion, intentos, XP e insignia salen del admin (DEC-190), y al completar uno se levanta TrainingModuleCompleted, previsto en el modelo desde la Fase 2. Lo caro es el CONTENIDO --guiones, video, mantenerlo cuando cambie una norma o una red-- y eso no lo hace el sistema. Se puede arrancar con modulos de solo texto, que cuestan casi nada y ya bajan rondas. Cierra Q-27</t>
+          <t>Quien da de alta sociedades del grupo no tiene por que poder cambiar lo que ve todo el mundo en todas las pantallas, incluida la de acceso. Hoy los dos los tiene solo admin; el dia que legal_entity.manage se le de a alguien de operaciones, esa persona no podra cambiar la marca. Hay una prueba que lo fija.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="57" customHeight="1" s="36">
       <c r="A49" s="67" t="inlineStr">
         <is>
-          <t>DEC-195</t>
+          <t>DEC-198</t>
         </is>
       </c>
       <c r="B49" s="68" t="inlineStr">
@@ -16460,24 +16510,24 @@
       <c r="C49" s="68" t="n"/>
       <c r="D49" s="69" t="inlineStr">
         <is>
-          <t>El lado del tipo de cambio se configura POR TIPO DE TRANSACCION.</t>
+          <t>El permiso se mira en CADA peticion: no hay URL firmada de archivo.</t>
         </is>
       </c>
       <c r="E49" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>No se fija uno en el codigo: lo que se le paga a un creador, lo que se le cobra a un cliente y un gasto operativo no tienen por que convertirse con el mismo lado, y esa eleccion es contable. El admin declara, para cada tipo de transaccion, que lado se aplica (compra, venta o media) y con que fuente. Cierra Q-63, que era la que impedia dar un porcentaje de margen cuando hay dos monedas (DEC-185)</t>
+          <t>Una URL firmada sigue funcionando cuando se reenvia y cuando a esa persona ya se le quito el acceso, y lo que sale por aqui son documentos de identidad y comprobantes bancarios. Con ruta propia, quitar un permiso surte efecto en la siguiente peticion y no queda ningun enlace circulando. El archivo se busca por uuid y no por id --un id correlativo invita a probar el siguiente-- y la respuesta lleva no-store (una identidad en la cache de un equipo compartido sobrevive al cierre de sesion), nosniff y una CSP que impide que un HTML o un SVG subido como «evidencia» se ejecute. El creador ve lo suyo, incluida su identidad: es informacion suya y le permite comprobar que archivamos el correcto. Rastro en bitacora solo para los sensibles --identidad, terminos y comprobante bancario--: anotar cada captura convertiria la bitacora en ruido, y una bitacora que nadie lee no protege nada</t>
         </is>
       </c>
     </row>
     <row r="50" ht="79.5" customHeight="1" s="36">
       <c r="A50" s="67" t="inlineStr">
         <is>
-          <t>DEC-194</t>
+          <t>DEC-197</t>
         </is>
       </c>
       <c r="B50" s="68" t="inlineStr">
@@ -16488,24 +16538,24 @@
       <c r="C50" s="68" t="n"/>
       <c r="D50" s="69" t="inlineStr">
         <is>
-          <t>La gamificacion premia con reconocimiento y con un catalogo de premios canjeables por XP.</t>
+          <t>Cada modulo declara quien puede ver SUS archivos; no hay un switch central.</t>
         </is>
       </c>
       <c r="E50" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>Nada de dinero. Los premios --viajes, objetos-- viven en una tabla configurable desde el admin con su coste en XP y su disponibilidad, y el creador los canjea. El hito que consolida un referido es la primera campana completada (Q-25). Cierra Q-23, Q-24 y Q-26</t>
+          <t>La regla de cada archivo depende de la tabla que lo apunta --identidad de creators, captura de publication_evidence, comprobante de payouts-- y un decisor central que las consultara todas pondria a Shared o a Core a saber de payouts. deptrac no lo veria: son consultas a tablas y no clases importadas, o sea una frontera rota en silencio, que es la peor clase. Cada modulo registra su regla en su ServiceProvider, igual que registra sus escuchas. Y se niega por omision: un proposito sin regla no se abre ni para el administrador, asi que un archivo nuevo cuyo autor olvido declarar quien puede verlo se queda cerrado y no abierto a todos</t>
         </is>
       </c>
     </row>
     <row r="51" ht="113.25" customHeight="1" s="36">
       <c r="A51" s="67" t="inlineStr">
         <is>
-          <t>DEC-193</t>
+          <t>DEC-196</t>
         </is>
       </c>
       <c r="B51" s="68" t="inlineStr">
@@ -16516,24 +16566,24 @@
       <c r="C51" s="68" t="n"/>
       <c r="D51" s="69" t="inlineStr">
         <is>
-          <t>Publicar terminos nuevos no expulsa a nadie de golpe: hay plazo, aviso y aterrizaje suave.</t>
+          <t>La Academia del creador se construye, y cada modulo se configura desde el admin.</t>
         </is>
       </c>
       <c r="E51" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>Correo con enlace de aceptacion, 15 dias de plazo, aviso en la bandeja interna de la plataforma y recordatorio al entrar. Cumplido el plazo sin aceptar, la sesion cae en una pantalla que exige aceptar para continuar; si no acepta, solo lectura durante 30 dias. Los dos plazos son configurables (DEC-190). Es la respuesta a Q-46, y encaja con el «cambio menor» de 9.16: una errata no dispara nada de esto</t>
+          <t>Es G-08 del addendum de gamificacion y la de mas retorno de las once: modulos cortos --leer un brief sin gastar rondas, iluminacion y audio con un movil, como se rotula el contenido comercial, que derechos esta cediendo, como subir su evidencia-- con evaluacion al final e insignia de creador certificado. Ataca tres dolores ya medidos: cada ronda evitada es tiempo del equipo de revision, cada evidencia subida sola es el proceso mas manual que se deja de perseguir, y «creadores certificados» es un argumento de venta ante la marca. El software es la parte barata: modulos, orden, formato, evaluacion, intentos, XP e insignia salen del admin (DEC-190), y al completar uno se levanta TrainingModuleCompleted, previsto en el modelo desde la Fase 2. Lo caro es el CONTENIDO --guiones, video, mantenerlo cuando cambie una norma o una red-- y eso no lo hace el sistema. Se puede arrancar con modulos de solo texto, que cuestan casi nada y ya bajan rondas. Cierra Q-27</t>
         </is>
       </c>
     </row>
     <row r="52" ht="102" customHeight="1" s="36">
       <c r="A52" s="67" t="inlineStr">
         <is>
-          <t>DEC-192</t>
+          <t>DEC-195</t>
         </is>
       </c>
       <c r="B52" s="68" t="inlineStr">
@@ -16544,7 +16594,7 @@
       <c r="C52" s="68" t="n"/>
       <c r="D52" s="69" t="inlineStr">
         <is>
-          <t>Facturacion electronica DIRECTA con SUNAT, no por proveedor.</t>
+          <t>El lado del tipo de cambio se configura POR TIPO DE TRANSACCION.</t>
         </is>
       </c>
       <c r="E52" s="69" t="inlineStr">
@@ -16554,14 +16604,14 @@
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>Configurable entero desde el admin: URL, certificado, usuario y clave secundarios, y correlativos independientes de factura, boleta y notas de credito de cada una. Con monitor de documentos timbrados: estado de cada uno, reintento manual, reintento automatico por job con frecuencia y numero de reintentos configurables, descarga de CDR, XML y PDF --el PDF con plantilla configurable-- y envio al cliente por correo con cuerpo configurable y variables arrastrables. Cierra Q-03 y de paso Q-21, que preguntaba por el contrato con un proveedor que ya no hay</t>
+          <t>No se fija uno en el codigo: lo que se le paga a un creador, lo que se le cobra a un cliente y un gasto operativo no tienen por que convertirse con el mismo lado, y esa eleccion es contable. El admin declara, para cada tipo de transaccion, que lado se aplica (compra, venta o media) y con que fuente. Cierra Q-63, que era la que impedia dar un porcentaje de margen cuando hay dos monedas (DEC-185)</t>
         </is>
       </c>
     </row>
     <row r="53" ht="79.5" customHeight="1" s="36">
       <c r="A53" s="67" t="inlineStr">
         <is>
-          <t>DEC-191</t>
+          <t>DEC-194</t>
         </is>
       </c>
       <c r="B53" s="68" t="inlineStr">
@@ -16572,7 +16622,7 @@
       <c r="C53" s="68" t="n"/>
       <c r="D53" s="69" t="inlineStr">
         <is>
-          <t>La retencion se calcula HACIA ATRAS desde el neto pactado, y se compara con un umbral de rentabilidad.</t>
+          <t>La gamificacion premia con reconocimiento y con un catalogo de premios canjeables por XP.</t>
         </is>
       </c>
       <c r="E53" s="69" t="inlineStr">
@@ -16582,14 +16632,14 @@
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>Con el creador se pacta lo que VA A RECIBIR --«te pago 100»--; el sistema calcula el bruto que hay que provisionar con la tasa configurada (29,5% por defecto, Q-13/Q-40): bruto = neto / (1 - tasa), o sea 141,84 para 100 netos, de los que 41,84 son retencion. Tres campos y no uno: neto pactado, tasa aplicada (por defecto la del admin, editable en el trato) e importe bruto. Encima va un umbral de rentabilidad minima configurable: con el bruto como costo, la pantalla dice cual es el ingreso mas bajo que hace aceptable esa participacion, y avisa antes de cerrar el trato --no despues--. La tasa, el umbral y la base sobre la que se mide el umbral (sobre costo o sobre ingreso: no dan el mismo numero) salen del admin</t>
+          <t>Nada de dinero. Los premios --viajes, objetos-- viven en una tabla configurable desde el admin con su coste en XP y su disponibilidad, y el creador los canjea. El hito que consolida un referido es la primera campana completada (Q-25). Cierra Q-23, Q-24 y Q-26</t>
         </is>
       </c>
     </row>
     <row r="54" ht="45.75" customHeight="1" s="36">
       <c r="A54" s="67" t="inlineStr">
         <is>
-          <t>DEC-190</t>
+          <t>DEC-193</t>
         </is>
       </c>
       <c r="B54" s="68" t="inlineStr">
@@ -16597,14 +16647,10 @@
           <t>Decidida</t>
         </is>
       </c>
-      <c r="C54" s="68" t="inlineStr">
-        <is>
-          <t>Critica</t>
-        </is>
-      </c>
+      <c r="C54" s="68" t="n"/>
       <c r="D54" s="69" t="inlineStr">
         <is>
-          <t>PRINCIPIO RECTOR: la plataforma es WHITE LABEL y todo se configura desde el admin.</t>
+          <t>Publicar terminos nuevos no expulsa a nadie de golpe: hay plazo, aviso y aterrizaje suave.</t>
         </is>
       </c>
       <c r="E54" s="69" t="inlineStr">
@@ -16614,14 +16660,14 @@
       </c>
       <c r="F54" s="69" t="inlineStr">
         <is>
-          <t>Nada de reglas de negocio quemadas en el codigo: ni la razon social, ni el RUC, ni el representante legal, ni la direccion, ni el ubigeo, ni las tasas, ni los plazos, ni los correlativos, ni las credenciales de ninguna API. Lo que el codigo aporta es la REGLA; el VALOR sale de la configuracion. Y una configuracion sin valor no bloquea: se siembra con un valor de partida y se avisa con su prioridad --rojo si es delicado y sigue de fabrica, ambar si conviene revisarlo--. Esto corrige el criterio con el que se habian tomado varias decisiones anteriores --3.5 dejaba el sistema sin arrancar hasta que alguien corriera un comando, y varias preguntas de negocio se plantearon como «elige una y la quemo» cuando la respuesta correcta era «las dos, y que se elija en el admin»--. Toda decision anterior que fije un valor en el codigo queda sujeta a revision bajo este principio (T-69)</t>
+          <t>Correo con enlace de aceptacion, 15 dias de plazo, aviso en la bandeja interna de la plataforma y recordatorio al entrar. Cumplido el plazo sin aceptar, la sesion cae en una pantalla que exige aceptar para continuar; si no acepta, solo lectura durante 30 dias. Los dos plazos son configurables (DEC-190). Es la respuesta a Q-46, y encaja con el «cambio menor» de 9.16: una errata no dispara nada de esto</t>
         </is>
       </c>
     </row>
     <row r="55" ht="79.5" customHeight="1" s="36">
       <c r="A55" s="67" t="inlineStr">
         <is>
-          <t>DEC-189</t>
+          <t>DEC-192</t>
         </is>
       </c>
       <c r="B55" s="68" t="inlineStr">
@@ -16632,24 +16678,24 @@
       <c r="C55" s="68" t="n"/>
       <c r="D55" s="69" t="inlineStr">
         <is>
-          <t>Las 23 rutas sin permiso se escriben, con su motivo, en RUTAS-ABIERTAS.</t>
+          <t>Facturacion electronica DIRECTA con SUNAT, no por proveedor.</t>
         </is>
       </c>
       <c r="E55" s="69" t="inlineStr">
         <is>
-          <t>9.14b</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F55" s="69" t="inlineStr">
         <is>
-          <t>Hasta hoy nada distinguia «es publica a proposito» --entrar, recuperar la contrasena, los enlaces firmados de 7.6 y 8.5-- de «se le olvido el middleware a alguien». verificar-muro.py comprueba que tres sitios digan lo mismo: la lista, routes/web.php y la constante de MuroTest; no se pueden fundir porque una la lee Python sin Laravel y otra PHPUnit, y tres copias es como se pierde una (SUITES, 3.12). Al CI: una ruta nueva sin permiso que no este escrita lo pone en rojo. De paso se cerraron dos puertas que no eran nuestras: storage.local y storage.local.upload, que registra el framework con serve =&gt; true sobre el disco privado. No eran una fuga --exigen URL firmada-- pero la aplicacion no genera ninguna, asi que no servian para nada; y ninguna lectura del codigo las habria encontrado, porque no estan en ningun archivo de rutas</t>
+          <t>Configurable entero desde el admin: URL, certificado, usuario y clave secundarios, y correlativos independientes de factura, boleta y notas de credito de cada una. Con monitor de documentos timbrados: estado de cada uno, reintento manual, reintento automatico por job con frecuencia y numero de reintentos configurables, descarga de CDR, XML y PDF --el PDF con plantilla configurable-- y envio al cliente por correo con cuerpo configurable y variables arrastrables. Cierra Q-03 y de paso Q-21, que preguntaba por el contrato con un proveedor que ya no hay</t>
         </is>
       </c>
     </row>
     <row r="56" ht="79.5" customHeight="1" s="36">
       <c r="A56" s="67" t="inlineStr">
         <is>
-          <t>DEC-188</t>
+          <t>DEC-191</t>
         </is>
       </c>
       <c r="B56" s="68" t="inlineStr">
@@ -16660,24 +16706,24 @@
       <c r="C56" s="68" t="n"/>
       <c r="D56" s="69" t="inlineStr">
         <is>
-          <t>El muro se prueba recorriendo TODAS las rutas, no las que uno recuerda.</t>
+          <t>La retencion se calcula HACIA ATRAS desde el neto pactado, y se compara con un umbral de rentabilidad.</t>
         </is>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>9.14b</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F56" s="69" t="inlineStr">
         <is>
-          <t>MuroTest pide las 145 rutas con nombre como creador, como usuario de cliente y como autenticado sin rol, y exige que ninguna se abra --371 aserciones, y el muro aguanta--. Una pantalla nueva entra sola en la prueba. Las afirmaciones dirigidas que ya habia (DEC-172, DEC-179, DEC-181) comprueban lo que alguien se acordo de mirar; el fallo que de verdad paso --5.9, la portada enseñando los totales internos a cualquier autenticado-- no lo habria cazado ninguna. Lo permitido se escribe en positivo: una lista de lo permitido crece solo cuando alguien la toca a proposito. Se admite un 404 porque SubstituteBindings corre antes del middleware --con un id inventado la ruta contesta antes de llegar al permiso-- y para que no sea el escondite de la prueba se exige que mas de 80 rutas contesten 403 de verdad</t>
+          <t>Con el creador se pacta lo que VA A RECIBIR --«te pago 100»--; el sistema calcula el bruto que hay que provisionar con la tasa configurada (29,5% por defecto, Q-13/Q-40): bruto = neto / (1 - tasa), o sea 141,84 para 100 netos, de los que 41,84 son retencion. Tres campos y no uno: neto pactado, tasa aplicada (por defecto la del admin, editable en el trato) e importe bruto. Encima va un umbral de rentabilidad minima configurable: con el bruto como costo, la pantalla dice cual es el ingreso mas bajo que hace aceptable esa participacion, y avisa antes de cerrar el trato --no despues--. La tasa, el umbral y la base sobre la que se mide el umbral (sobre costo o sobre ingreso: no dan el mismo numero) salen del admin</t>
         </is>
       </c>
     </row>
     <row r="57" ht="68.25" customHeight="1" s="36">
       <c r="A57" s="67" t="inlineStr">
         <is>
-          <t>DEC-187</t>
+          <t>DEC-190</t>
         </is>
       </c>
       <c r="B57" s="68" t="inlineStr">
@@ -16685,27 +16731,31 @@
           <t>Decidida</t>
         </is>
       </c>
-      <c r="C57" s="68" t="n"/>
+      <c r="C57" s="68" t="inlineStr">
+        <is>
+          <t>Critica</t>
+        </is>
+      </c>
       <c r="D57" s="69" t="inlineStr">
         <is>
-          <t>Una suite de QA se construye SU caso y no reusa el de nadie.</t>
+          <t>PRINCIPIO RECTOR: la plataforma es WHITE LABEL y todo se configura desde el admin.</t>
         </is>
       </c>
       <c r="E57" s="69" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F57" s="69" t="inlineStr">
         <is>
-          <t>La primera version de 9.14 reusaba lo que dejaban las suites anteriores, como hace 9.6, y se puso amarilla dos veces por motivos opuestos: corriendo sola porque no habia asientos, y corriendo la bateria entera porque para cuando llega el unico devengo pagable ya esta liquidado por 9.6 y las dos participaciones de la semilla estan ocupadas. Ahora crea su campana, su participacion y su devengo. Una suite de QA que depende del orden mide el orden, no la regla</t>
+          <t>Nada de reglas de negocio quemadas en el codigo: ni la razon social, ni el RUC, ni el representante legal, ni la direccion, ni el ubigeo, ni las tasas, ni los plazos, ni los correlativos, ni las credenciales de ninguna API. Lo que el codigo aporta es la REGLA; el VALOR sale de la configuracion. Y una configuracion sin valor no bloquea: se siembra con un valor de partida y se avisa con su prioridad --rojo si es delicado y sigue de fabrica, ambar si conviene revisarlo--. Esto corrige el criterio con el que se habian tomado varias decisiones anteriores --3.5 dejaba el sistema sin arrancar hasta que alguien corriera un comando, y varias preguntas de negocio se plantearon como «elige una y la quemo» cuando la respuesta correcta era «las dos, y que se elija en el admin»--. Toda decision anterior que fije un valor en el codigo queda sujeta a revision bajo este principio (T-69)</t>
         </is>
       </c>
     </row>
     <row r="58" ht="34.5" customHeight="1" s="36">
       <c r="A58" s="67" t="inlineStr">
         <is>
-          <t>DEC-186</t>
+          <t>DEC-189</t>
         </is>
       </c>
       <c r="B58" s="68" t="inlineStr">
@@ -16716,24 +16766,24 @@
       <c r="C58" s="68" t="n"/>
       <c r="D58" s="69" t="inlineStr">
         <is>
-          <t>Nace verificar-cobertura-sql.py: que regla de la base no ha contestado NUNCA a nadie.</t>
+          <t>Las 23 rutas sin permiso se escriben, con su motivo, en RUTAS-ABIERTAS.</t>
         </is>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.14b</t>
         </is>
       </c>
       <c r="F58" s="69" t="inlineStr">
         <is>
-          <t>Los verificadores que ya habia comprueban que la regla EXISTA y que sea la misma en los dos motores; ninguno comprobaba lo unico que importa el dia que falle: que alguien se lo haya preguntado. Medido: de las 317 reglas del esquema, 167 no aparecian en ninguna suite ni en ninguna prueba --el 53%--. No significa que esten mal: significa que nadie lo sabe. Una regla que nunca se ha probado no es una regla, es una intencion escrita en DDL. Va a correr-todo.sh y al CI con trinquete (MUDAS-BASE), asi que una regla nueva sin asercion pone el CI en rojo. La pregunta salio de 9.10a, donde campaign_costs llevaba dos semanas con cinco restricciones verdes en todos los verificadores y CERO filas</t>
+          <t>Hasta hoy nada distinguia «es publica a proposito» --entrar, recuperar la contrasena, los enlaces firmados de 7.6 y 8.5-- de «se le olvido el middleware a alguien». verificar-muro.py comprueba que tres sitios digan lo mismo: la lista, routes/web.php y la constante de MuroTest; no se pueden fundir porque una la lee Python sin Laravel y otra PHPUnit, y tres copias es como se pierde una (SUITES, 3.12). Al CI: una ruta nueva sin permiso que no este escrita lo pone en rojo. De paso se cerraron dos puertas que no eran nuestras: storage.local y storage.local.upload, que registra el framework con serve =&gt; true sobre el disco privado. No eran una fuga --exigen URL firmada-- pero la aplicacion no genera ninguna, asi que no servian para nada; y ninguna lectura del codigo las habria encontrado, porque no estan en ningun archivo de rutas</t>
         </is>
       </c>
     </row>
     <row r="59" ht="79.5" customHeight="1" s="36">
       <c r="A59" s="67" t="inlineStr">
         <is>
-          <t>DEC-185</t>
+          <t>DEC-188</t>
         </is>
       </c>
       <c r="B59" s="68" t="inlineStr">
@@ -16744,24 +16794,24 @@
       <c r="C59" s="68" t="n"/>
       <c r="D59" s="69" t="inlineStr">
         <is>
-          <t>El porcentaje de margen solo se da cuando todo esta en una moneda, y si no, se dice por que.</t>
+          <t>El muro se prueba recorriendo TODAS las rutas, no las que uno recuerda.</t>
         </is>
       </c>
       <c r="E59" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14b</t>
         </is>
       </c>
       <c r="F59" s="69" t="inlineStr">
         <is>
-          <t>Convertir exige elegir compra, venta o media (Q-63) y cada eleccion da un margen distinto para los mismos hechos; el dia que se elija cambian ademas todos los margenes historicos a la vez. Cuando falta, la pantalla escribe el motivo con palabras --«esta campana tiene importes en PEN y USD…»-- y no deja un hueco: quien mira una pantalla donde falta un numero necesita saber si falta porque no lo hay o porque no se puede calcular, y son dos conversaciones distintas. Tampoco hay total por sociedad: el ingreso de hoy es el DECLARADO y no el facturado (9.9), y sumar precios declarados por sociedad se parece a un estado de resultados sin serlo</t>
+          <t>MuroTest pide las 145 rutas con nombre como creador, como usuario de cliente y como autenticado sin rol, y exige que ninguna se abra --371 aserciones, y el muro aguanta--. Una pantalla nueva entra sola en la prueba. Las afirmaciones dirigidas que ya habia (DEC-172, DEC-179, DEC-181) comprueban lo que alguien se acordo de mirar; el fallo que de verdad paso --5.9, la portada enseñando los totales internos a cualquier autenticado-- no lo habria cazado ninguna. Lo permitido se escribe en positivo: una lista de lo permitido crece solo cuando alguien la toca a proposito. Se admite un 404 porque SubstituteBindings corre antes del middleware --con un id inventado la ruta contesta antes de llegar al permiso-- y para que no sea el escondite de la prueba se exige que mas de 80 rutas contesten 403 de verdad</t>
         </is>
       </c>
     </row>
     <row r="60" ht="102" customHeight="1" s="36">
       <c r="A60" s="67" t="inlineStr">
         <is>
-          <t>DEC-184</t>
+          <t>DEC-187</t>
         </is>
       </c>
       <c r="B60" s="68" t="inlineStr">
@@ -16772,24 +16822,24 @@
       <c r="C60" s="68" t="n"/>
       <c r="D60" s="69" t="inlineStr">
         <is>
-          <t>Los canjes salen en la lista, marcados, y fuera de todo total.</t>
+          <t>Una suite de QA se construye SU caso y no reusa el de nadie.</t>
         </is>
       </c>
       <c r="E60" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="F60" s="69" t="inlineStr">
         <is>
-          <t>Su ingreso es cero POR DECISION (7.2), asi que su margen es siempre negativo: el producto y el envio se gastaron igual. Promediarlos hace que la cartera entera parezca peor por un motivo que fue deliberado. Pero se enseñan con su costo, porque un canje tambien cuesta dinero y ese era justo el numero que nadie tenia. Queda fuera del total una segunda clase de campana: la que tiene gastos en OTRA moneda, cuyo margen en la moneda del grupo esta incompleto --y sumar un numero incompleto lo vuelve invisible--. Y la cabecera dice cuantas quedaron fuera y por que: un total que excluye filas sin contarlas engaña por omision</t>
+          <t>La primera version de 9.14 reusaba lo que dejaban las suites anteriores, como hace 9.6, y se puso amarilla dos veces por motivos opuestos: corriendo sola porque no habia asientos, y corriendo la bateria entera porque para cuando llega el unico devengo pagable ya esta liquidado por 9.6 y las dos participaciones de la semilla estan ocupadas. Ahora crea su campana, su participacion y su devengo. Una suite de QA que depende del orden mide el orden, no la regla</t>
         </is>
       </c>
     </row>
     <row r="61" ht="90.75" customHeight="1" s="36">
       <c r="A61" s="67" t="inlineStr">
         <is>
-          <t>DEC-183</t>
+          <t>DEC-186</t>
         </is>
       </c>
       <c r="B61" s="68" t="inlineStr">
@@ -16800,24 +16850,24 @@
       <c r="C61" s="68" t="n"/>
       <c r="D61" s="69" t="inlineStr">
         <is>
-          <t>Compromiso::margen() se BORRA, no se arregla.</t>
+          <t>Nace verificar-cobertura-sql.py: que regla de la base no ha contestado NUNCA a nadie.</t>
         </is>
       </c>
       <c r="E61" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="F61" s="69" t="inlineStr">
         <is>
-          <t>Vivia en Campaign desde 7.7 y devolvia revenue_amount menos lo comprometido con creadores: no restaba producto, envios ni produccion, y desde 9.10a esos gastos ya se anotan, asi que el numero habria ido empeorando con cada gasto cargado sin que la pantalla se enterara. No se arregla donde estaba porque campaign_costs es de Finance y deptrac no deja que Campaign la conozca --misma frontera que el devengo de 9.4--. Y se borra en vez de dejarse por si acaso: un metodo que calcula un numero incompleto y se llama margen() es una trampa para quien lo encuentre dentro de seis meses. De paso, SeguimientoController deja de pasar un importe y pasa un booleano mas un enlace: ningun numero interno cruza ya hasta la plantilla, que es BR-SEC-001 un paso mas alla</t>
+          <t>Los verificadores que ya habia comprueban que la regla EXISTA y que sea la misma en los dos motores; ninguno comprobaba lo unico que importa el dia que falle: que alguien se lo haya preguntado. Medido: de las 317 reglas del esquema, 167 no aparecian en ninguna suite ni en ninguna prueba --el 53%--. No significa que esten mal: significa que nadie lo sabe. Una regla que nunca se ha probado no es una regla, es una intencion escrita en DDL. Va a correr-todo.sh y al CI con trinquete (MUDAS-BASE), asi que una regla nueva sin asercion pone el CI en rojo. La pregunta salio de 9.10a, donde campaign_costs llevaba dos semanas con cinco restricciones verdes en todos los verificadores y CERO filas</t>
         </is>
       </c>
     </row>
     <row r="62" ht="57" customHeight="1" s="36">
       <c r="A62" s="67" t="inlineStr">
         <is>
-          <t>DEC-182</t>
+          <t>DEC-185</t>
         </is>
       </c>
       <c r="B62" s="68" t="inlineStr">
@@ -16828,24 +16878,24 @@
       <c r="C62" s="68" t="n"/>
       <c r="D62" s="69" t="inlineStr">
         <is>
-          <t>El costo del creador entra al DEVENGARSE, no al pagarse.</t>
+          <t>El porcentaje de margen solo se da cuando todo esta en una moneda, y si no, se dice por que.</t>
         </is>
       </c>
       <c r="E62" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F62" s="69" t="inlineStr">
         <is>
-          <t>La deuda existe desde que acepta (9.4) y su importe esta congelado desde 7.5; esperar al pago haria que una campana terminada en marzo pareciera rentabilisima hasta el lote de abril. Sale del libro mayor y no de campaign_creators, porque el libro es quien sabe que devengos siguen vivos: uno anulado ya no se debe. Y no es Compromiso::comprometido(), que cuenta tambien a los shortlisted: alli es correcto --su trabajo es proteger el presupuesto ANTES de invitar-- y aqui contaria dinero de gente que todavia puede decir que no</t>
+          <t>Convertir exige elegir compra, venta o media (Q-63) y cada eleccion da un margen distinto para los mismos hechos; el dia que se elija cambian ademas todos los margenes historicos a la vez. Cuando falta, la pantalla escribe el motivo con palabras --«esta campana tiene importes en PEN y USD…»-- y no deja un hueco: quien mira una pantalla donde falta un numero necesita saber si falta porque no lo hay o porque no se puede calcular, y son dos conversaciones distintas. Tampoco hay total por sociedad: el ingreso de hoy es el DECLARADO y no el facturado (9.9), y sumar precios declarados por sociedad se parece a un estado de resultados sin serlo</t>
         </is>
       </c>
     </row>
     <row r="63" ht="90.75" customHeight="1" s="36">
       <c r="A63" s="67" t="inlineStr">
         <is>
-          <t>DEC-181</t>
+          <t>DEC-184</t>
         </is>
       </c>
       <c r="B63" s="68" t="inlineStr">
@@ -16856,24 +16906,24 @@
       <c r="C63" s="68" t="n"/>
       <c r="D63" s="69" t="inlineStr">
         <is>
-          <t>Cargar gastos no es ver el margen: campaign_manager pierde campaign.view_margin.</t>
+          <t>Los canjes salen en la lista, marcados, y fuera de todo total.</t>
         </is>
       </c>
       <c r="E63" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F63" s="69" t="inlineStr">
         <is>
-          <t>Quien lleva una campana anota lo que se gasta y ve cuanto lleva gastado; el margen --lo que se gana-- es una cifra de direccion, y el camino por el que un numero interno acaba en un correo a un cliente empieza siempre por alguien que podia verlo sin necesitarlo (BR-SEC-001, 🔴). No nace un permiso nuevo para el margen: campaign.view_margin ya existe y hace eso, y un segundo permiso para el mismo secreto es la forma clasica de que un dia se conceda el que nadie mira. Lo que nace es finance.cost.manage, que es la capacidad que de verdad no existia. Y la revocacion va en la MIGRACION y no en el seeder (T-64)</t>
+          <t>Su ingreso es cero POR DECISION (7.2), asi que su margen es siempre negativo: el producto y el envio se gastaron igual. Promediarlos hace que la cartera entera parezca peor por un motivo que fue deliberado. Pero se enseñan con su costo, porque un canje tambien cuesta dinero y ese era justo el numero que nadie tenia. Queda fuera del total una segunda clase de campana: la que tiene gastos en OTRA moneda, cuyo margen en la moneda del grupo esta incompleto --y sumar un numero incompleto lo vuelve invisible--. Y la cabecera dice cuantas quedaron fuera y por que: un total que excluye filas sin contarlas engaña por omision</t>
         </is>
       </c>
     </row>
     <row r="64" ht="102" customHeight="1" s="36">
       <c r="A64" s="67" t="inlineStr">
         <is>
-          <t>DEC-180</t>
+          <t>DEC-183</t>
         </is>
       </c>
       <c r="B64" s="68" t="inlineStr">
@@ -16884,24 +16934,24 @@
       <c r="C64" s="68" t="n"/>
       <c r="D64" s="69" t="inlineStr">
         <is>
-          <t>El gasto de una campana se agrupa por moneda: no se suma.</t>
+          <t>Compromiso::margen() se BORRA, no se arregla.</t>
         </is>
       </c>
       <c r="E64" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F64" s="69" t="inlineStr">
         <is>
-          <t>Un envio se paga en dolares y la campana se cobra en soles; sumarlos exige un tipo de cambio, y cual --compra, venta o media-- es una decision contable que sigue abierta (Q-63) y que da tres margenes distintos para los mismos hechos. Es la misma decision que el saldo del creador en 9.8, por el mismo motivo. Un numero que parece exacto y depende de una eleccion que nadie ha hecho es peor que dos numeros separados</t>
+          <t>Vivia en Campaign desde 7.7 y devolvia revenue_amount menos lo comprometido con creadores: no restaba producto, envios ni produccion, y desde 9.10a esos gastos ya se anotan, asi que el numero habria ido empeorando con cada gasto cargado sin que la pantalla se enterara. No se arregla donde estaba porque campaign_costs es de Finance y deptrac no deja que Campaign la conozca --misma frontera que el devengo de 9.4--. Y se borra en vez de dejarse por si acaso: un metodo que calcula un numero incompleto y se llama margen() es una trampa para quien lo encuentre dentro de seis meses. De paso, SeguimientoController deja de pasar un importe y pasa un booleano mas un enlace: ningun numero interno cruza ya hasta la plantilla, que es BR-SEC-001 un paso mas alla</t>
         </is>
       </c>
     </row>
     <row r="65" ht="90.75" customHeight="1" s="36">
       <c r="A65" s="67" t="inlineStr">
         <is>
-          <t>DEC-179</t>
+          <t>DEC-182</t>
         </is>
       </c>
       <c r="B65" s="68" t="inlineStr">
@@ -16912,24 +16962,24 @@
       <c r="C65" s="68" t="n"/>
       <c r="D65" s="69" t="inlineStr">
         <is>
-          <t>Al creador se le avisa al CONFIRMAR y al DEVOLVER, no al enviar.</t>
+          <t>El costo del creador entra al DEVENGARSE, no al pagarse.</t>
         </is>
       </c>
       <c r="E65" s="69" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F65" s="69" t="inlineStr">
         <is>
-          <t>Avisar al enviar es avisar de una intencion: si el banco lo rechaza, el creador ya cree que cobro, y el segundo correo desmiente al primero --dos correos que se contradicen cuestan mas confianza que un correo que llega un dia mas tarde--. Ninguno de los dos lleva numero de cuenta ni referencia bancaria: un correo se lee en pantallas ajenas y se reenvia, y para saber que le pagaron no hace falta ver su cuenta; es la misma decision que los avisos de 4.13. Y lo que faltaba en payouts no eran los estados --estan desde la Fase 2-- sino el GRAFO: sin tg_payout_estado, un pago saltaba de pending a confirmed sin haber salido nunca, y uno devuelto volvia a sent con un UPDATE, borrando que el banco lo habia rechazado. Mismo agujero que ledger_entries tenia antes de 9.3</t>
+          <t>La deuda existe desde que acepta (9.4) y su importe esta congelado desde 7.5; esperar al pago haria que una campana terminada en marzo pareciera rentabilisima hasta el lote de abril. Sale del libro mayor y no de campaign_creators, porque el libro es quien sabe que devengos siguen vivos: uno anulado ya no se debe. Y no es Compromiso::comprometido(), que cuenta tambien a los shortlisted: alli es correcto --su trabajo es proteger el presupuesto ANTES de invitar-- y aqui contaria dinero de gente que todavia puede decir que no</t>
         </is>
       </c>
     </row>
     <row r="66" ht="68.25" customHeight="1" s="36">
       <c r="A66" s="67" t="inlineStr">
         <is>
-          <t>DEC-178</t>
+          <t>DEC-181</t>
         </is>
       </c>
       <c r="B66" s="68" t="inlineStr">
@@ -16940,24 +16990,24 @@
       <c r="C66" s="68" t="n"/>
       <c r="D66" s="69" t="inlineStr">
         <is>
-          <t>Un pago devuelto por el banco NO deshace el devengo.</t>
+          <t>Cargar gastos no es ver el margen: campaign_manager pierde campaign.view_margin.</t>
         </is>
       </c>
       <c r="E66" s="69" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F66" s="69" t="inlineStr">
         <is>
-          <t>El devengo se queda en paid porque se pago: lo que fallo fue la transferencia, no el trabajo --y paid es terminal desde DEC-169--. La correccion es un asiento de payment_reversal que apunta al asiento de pago original (BR-FIN-002), positivo, asi que devuelve el saldo; los dos hechos quedan escritos --se pago, y volvio-- en vez de que el segundo borre al primero. Nace accrued porque ck_ledger_estado_inicial no admite nacer pagable --a pagable se LLEGA-- y se mueve a payable en la misma operacion: el creador ya cumplio, y su dinero no tiene que esperar a que alguien se acuerde de revisarlo. Si el pago no tuviera asiento en el libro mayor, devolver() falla en voz alta en vez de dejar el saldo diciendo que cobro algo que no tiene</t>
+          <t>Quien lleva una campana anota lo que se gasta y ve cuanto lleva gastado; el margen --lo que se gana-- es una cifra de direccion, y el camino por el que un numero interno acaba en un correo a un cliente empieza siempre por alguien que podia verlo sin necesitarlo (BR-SEC-001, 🔴). No nace un permiso nuevo para el margen: campaign.view_margin ya existe y hace eso, y un segundo permiso para el mismo secreto es la forma clasica de que un dia se conceda el que nadie mira. Lo que nace es finance.cost.manage, que es la capacidad que de verdad no existia. Y la revocacion va en la MIGRACION y no en el seeder (T-64)</t>
         </is>
       </c>
     </row>
     <row r="67" ht="68.25" customHeight="1" s="36">
       <c r="A67" s="67" t="inlineStr">
         <is>
-          <t>DEC-177</t>
+          <t>DEC-180</t>
         </is>
       </c>
       <c r="B67" s="68" t="inlineStr">
@@ -16968,24 +17018,24 @@
       <c r="C67" s="68" t="n"/>
       <c r="D67" s="69" t="inlineStr">
         <is>
-          <t>El CSV del lote NO es el archivo del banco.</t>
+          <t>El gasto de una campana se agrupa por moneda: no se suma.</t>
         </is>
       </c>
       <c r="E67" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F67" s="69" t="inlineStr">
         <is>
-          <t>El formato de una transferencia masiva es especifico de cada entidad y sale de su manual; inventarselo produce un archivo que el banco rechaza sin decir por que, y el sintoma aparece el dia del pago. Lo que hay es un CSV legible por una persona, para teclear o comprobar, y la pantalla lo dice con esas palabras para que nadie lo suba creyendo que es lo otro. El archivo real se construye cuando haya banco y especificacion</t>
+          <t>Un envio se paga en dolares y la campana se cobra en soles; sumarlos exige un tipo de cambio, y cual --compra, venta o media-- es una decision contable que sigue abierta (Q-63) y que da tres margenes distintos para los mismos hechos. Es la misma decision que el saldo del creador en 9.8, por el mismo motivo. Un numero que parece exacto y depende de una eleccion que nadie ha hecho es peor que dos numeros separados</t>
         </is>
       </c>
     </row>
     <row r="68" ht="79.5" customHeight="1" s="36">
       <c r="A68" s="67" t="inlineStr">
         <is>
-          <t>DEC-176</t>
+          <t>DEC-179</t>
         </is>
       </c>
       <c r="B68" s="68" t="inlineStr">
@@ -16996,24 +17046,24 @@
       <c r="C68" s="68" t="n"/>
       <c r="D68" s="69" t="inlineStr">
         <is>
-          <t>Sacar un pago de un lote firmado NO obliga a firmarlo otra vez.</t>
+          <t>Al creador se le avisa al CONFIRMAR y al DEVOLVER, no al enviar.</t>
         </is>
       </c>
       <c r="E68" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="F68" s="69" t="inlineStr">
         <is>
-          <t>Cuando un devengo se retiene entre la firma y la ejecucion --un post que se cae-- ese pago sale y el resto se paga igual. El importe total baja, nunca sube, y eso no puede sorprender a quien ya firmo; devolver el lote entero a borrador castigaria a diez creadores por el problema de uno. La liquidacion se anula, no se borra: es evidencia de que estuvo dentro y de que alguien lo saco, y anularla exige quien y por que (tg_pe_inmutable). Al anularse, el devengo vuelve a la cola. Un lote ya ejecutado no se toca: el dinero salio, y eso se corrige con una devolucion</t>
+          <t>Avisar al enviar es avisar de una intencion: si el banco lo rechaza, el creador ya cree que cobro, y el segundo correo desmiente al primero --dos correos que se contradicen cuestan mas confianza que un correo que llega un dia mas tarde--. Ninguno de los dos lleva numero de cuenta ni referencia bancaria: un correo se lee en pantallas ajenas y se reenvia, y para saber que le pagaron no hace falta ver su cuenta; es la misma decision que los avisos de 4.13. Y lo que faltaba en payouts no eran los estados --estan desde la Fase 2-- sino el GRAFO: sin tg_payout_estado, un pago saltaba de pending a confirmed sin haber salido nunca, y uno devuelto volvia a sent con un UPDATE, borrando que el banco lo habia rechazado. Mismo agujero que ledger_entries tenia antes de 9.3</t>
         </is>
       </c>
     </row>
     <row r="69" ht="57" customHeight="1" s="36">
       <c r="A69" s="67" t="inlineStr">
         <is>
-          <t>DEC-175</t>
+          <t>DEC-178</t>
         </is>
       </c>
       <c r="B69" s="68" t="inlineStr">
@@ -17024,24 +17074,24 @@
       <c r="C69" s="68" t="n"/>
       <c r="D69" s="69" t="inlineStr">
         <is>
-          <t>Dos firmas SIEMPRE, sin umbral.</t>
+          <t>Un pago devuelto por el banco NO deshace el devengo.</t>
         </is>
       </c>
       <c r="E69" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="F69" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-005 habla de un umbral configurable y se decide no tenerlo: el equipo es pequeno y los lotes son pocos y agrupados, asi que la segunda firma cuesta un clic al mes. Un umbral hay que elegirlo, mantenerlo y explicarlo --y el dia que alguien quiera saltarse la firma, parte el lote en dos--. Que el aprobador sea otro no lo comprueba la pantalla: lo impide ck_pbatch_segregation en la base desde la Fase 2; la pantalla solo lo dice ANTES de que nadie pulse. Y el importe del pago no se teclea: sale de sumar lo que liquida, asi que no puede discrepar de lo que el lote dice que paga --Lotes::descuadre() lo comprueba antes de firmar, porque una SUMA sobre otra tabla no cabe en un CHECK--</t>
+          <t>El devengo se queda en paid porque se pago: lo que fallo fue la transferencia, no el trabajo --y paid es terminal desde DEC-169--. La correccion es un asiento de payment_reversal que apunta al asiento de pago original (BR-FIN-002), positivo, asi que devuelve el saldo; los dos hechos quedan escritos --se pago, y volvio-- en vez de que el segundo borre al primero. Nace accrued porque ck_ledger_estado_inicial no admite nacer pagable --a pagable se LLEGA-- y se mueve a payable en la misma operacion: el creador ya cumplio, y su dinero no tiene que esperar a que alguien se acuerde de revisarlo. Si el pago no tuviera asiento en el libro mayor, devolver() falla en voz alta en vez de dejar el saldo diciendo que cobro algo que no tiene</t>
         </is>
       </c>
     </row>
     <row r="70" ht="57" customHeight="1" s="36">
       <c r="A70" s="67" t="inlineStr">
         <is>
-          <t>DEC-174</t>
+          <t>DEC-177</t>
         </is>
       </c>
       <c r="B70" s="68" t="inlineStr">
@@ -17052,7 +17102,7 @@
       <c r="C70" s="68" t="n"/>
       <c r="D70" s="69" t="inlineStr">
         <is>
-          <t>Nace payout_earnings: que devengos paga cada pago.</t>
+          <t>El CSV del lote NO es el archivo del banco.</t>
         </is>
       </c>
       <c r="E70" s="69" t="inlineStr">
@@ -17062,14 +17112,14 @@
       </c>
       <c r="F70" s="69" t="inlineStr">
         <is>
-          <t>ledger_entries.payout_id ataba UN asiento de pago a su payout (BR-FIN-013), pero el detalle --que devengos liquida-- no existia. Sin el, «.de que campanas es este dinero?» no tiene respuesta, y sin respuesta no hay nada que comparar con la sociedad del lote, que es lo que DEC-157 mando cerrar aqui. Con el detalle, BR-LE-009 se vuelve una consulta de tres saltos que cabe en tg_pe_sociedad. Se comprueba al enganchar el devengo al pago y no al aprobar el lote: aprobar es una firma sobre algo que ya tiene que estar bien, y una regla que solo mira al final deja existir el estado malo mientras tanto --que es como alguien lo ve, lo exporta, o lo cree--. Vigesimoseptima columna puerta: uq_pe_viva, un devengo en una sola liquidacion VIVA</t>
+          <t>El formato de una transferencia masiva es especifico de cada entidad y sale de su manual; inventarselo produce un archivo que el banco rechaza sin decir por que, y el sintoma aparece el dia del pago. Lo que hay es un CSV legible por una persona, para teclear o comprobar, y la pantalla lo dice con esas palabras para que nadie lo suba creyendo que es lo otro. El archivo real se construye cuando haya banco y especificacion</t>
         </is>
       </c>
     </row>
     <row r="71" ht="45.75" customHeight="1" s="36">
       <c r="A71" s="67" t="inlineStr">
         <is>
-          <t>DEC-173</t>
+          <t>DEC-176</t>
         </is>
       </c>
       <c r="B71" s="68" t="inlineStr">
@@ -17080,24 +17130,24 @@
       <c r="C71" s="68" t="n"/>
       <c r="D71" s="69" t="inlineStr">
         <is>
-          <t>La fecha de cobro se ensena SOLO cuando el asiento ya es pagable.</t>
+          <t>Sacar un pago de un lote firmado NO obliga a firmarlo otra vez.</t>
         </is>
       </c>
       <c r="E71" s="69" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F71" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-012 dice que el plazo son 30 dias desde la verificacion y que es visible desde que acepta: lo visible desde que acepta es el plazo, y una FECHA es otra cosa que se lee muy distinto. Mientras el asiento esta devengado se ensena que falta --las cinco condiciones de BR-FIN-003, con sus palabras--, que es accionable: un creador puede hacer algo con «no tienes ningun medio de pago verificado» y no puede hacer nada con una fecha que depende de trabajo que aun no ha hecho. Y si esa fecha se corriera, la culpa pareceria nuestra. La cuenta arranca en la ultima verificacion de sus publicaciones, y si no hay ninguna --un formato que no exige post-- en la fecha en que se completo la participacion</t>
+          <t>Cuando un devengo se retiene entre la firma y la ejecucion --un post que se cae-- ese pago sale y el resto se paga igual. El importe total baja, nunca sube, y eso no puede sorprender a quien ya firmo; devolver el lote entero a borrador castigaria a diez creadores por el problema de uno. La liquidacion se anula, no se borra: es evidencia de que estuvo dentro y de que alguien lo saco, y anularla exige quien y por que (tg_pe_inmutable). Al anularse, el devengo vuelve a la cola. Un lote ya ejecutado no se toca: el dinero salio, y eso se corrige con una devolucion</t>
         </is>
       </c>
     </row>
     <row r="72" ht="79.5" customHeight="1" s="36">
       <c r="A72" s="67" t="inlineStr">
         <is>
-          <t>DEC-172</t>
+          <t>DEC-175</t>
         </is>
       </c>
       <c r="B72" s="68" t="inlineStr">
@@ -17108,24 +17158,24 @@
       <c r="C72" s="68" t="n"/>
       <c r="D72" s="69" t="inlineStr">
         <is>
-          <t>El motivo interno de una retencion NO se le ensena al creador.</t>
+          <t>Dos firmas SIEMPRE, sin umbral.</t>
         </is>
       </c>
       <c r="E72" s="69" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F72" s="69" t="inlineStr">
         <is>
-          <t>Lo escribe el equipo para el expediente y puede nombrar personas o sospechas todavia sin confirmar; un texto redactado deprisa --«parece que lo borro a proposito»-- leido sin contexto es una acusacion de la que no se vuelve. El creador ve «En revision -- te escribimos» y, desde 8.8, recibe un correo donde se le explica de verdad. Las palabras del portal tampoco son las del back-office: on_hold es «en revision» y no «retenido», porque la palabra interna describe lo que hace el sistema y la del portal tiene que describir lo que le pasa a el. La frontera vive en Ledger::misIngresos(), que enumera columnas --el mismo sitio que Aprobaciones::pieza() en 8.5--: devolver la fila entera y confiar en que la plantilla no imprima de mas es confiar en la plantilla de manana. Tampoco cruzan los asientos anulados: no le afectan y no sabe leerlos</t>
+          <t>BR-FIN-005 habla de un umbral configurable y se decide no tenerlo: el equipo es pequeno y los lotes son pocos y agrupados, asi que la segunda firma cuesta un clic al mes. Un umbral hay que elegirlo, mantenerlo y explicarlo --y el dia que alguien quiera saltarse la firma, parte el lote en dos--. Que el aprobador sea otro no lo comprueba la pantalla: lo impide ck_pbatch_segregation en la base desde la Fase 2; la pantalla solo lo dice ANTES de que nadie pulse. Y el importe del pago no se teclea: sale de sumar lo que liquida, asi que no puede discrepar de lo que el lote dice que paga --Lotes::descuadre() lo comprueba antes de firmar, porque una SUMA sobre otra tabla no cabe en un CHECK--</t>
         </is>
       </c>
     </row>
     <row r="73" ht="68.25" customHeight="1" s="36">
       <c r="A73" s="67" t="inlineStr">
         <is>
-          <t>DEC-171</t>
+          <t>DEC-174</t>
         </is>
       </c>
       <c r="B73" s="68" t="inlineStr">
@@ -17136,24 +17186,24 @@
       <c r="C73" s="68" t="n"/>
       <c r="D73" s="69" t="inlineStr">
         <is>
-          <t>El barrido rescata las aceptaciones sin devengo, y avisa de que hubo que rescatarlas.</t>
+          <t>Nace payout_earnings: que devengos paga cada pago.</t>
         </is>
       </c>
       <c r="E73" s="69" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F73" s="69" t="inlineStr">
         <is>
-          <t>Un listener puede fallar, y si falla el creador queda aceptado y su dinero invisible; ademas las participaciones aceptadas antes de 9.4 nunca pasaron por el. ledger:revisar las anota antes de revisar --para que un devengo recuperado hoy pueda pasar a pagable hoy y no manana-- y lo dice en amarillo: que la lista no salga en cero es la noticia, no el arreglo. Es la misma red que 8.1 dejo para los entregables. Las gratuitas quedan fuera de esa lista a proposito: si no, el barrido intentaria lo imposible todos los dias y avisaria todos los dias de algo que esta bien</t>
+          <t>ledger_entries.payout_id ataba UN asiento de pago a su payout (BR-FIN-013), pero el detalle --que devengos liquida-- no existia. Sin el, «.de que campanas es este dinero?» no tiene respuesta, y sin respuesta no hay nada que comparar con la sociedad del lote, que es lo que DEC-157 mando cerrar aqui. Con el detalle, BR-LE-009 se vuelve una consulta de tres saltos que cabe en tg_pe_sociedad. Se comprueba al enganchar el devengo al pago y no al aprobar el lote: aprobar es una firma sobre algo que ya tiene que estar bien, y una regla que solo mira al final deja existir el estado malo mientras tanto --que es como alguien lo ve, lo exporta, o lo cree--. Vigesimoseptima columna puerta: uq_pe_viva, un devengo en una sola liquidacion VIVA</t>
         </is>
       </c>
     </row>
     <row r="74" ht="68.25" customHeight="1" s="36">
       <c r="A74" s="67" t="inlineStr">
         <is>
-          <t>DEC-170</t>
+          <t>DEC-173</t>
         </is>
       </c>
       <c r="B74" s="68" t="inlineStr">
@@ -17164,24 +17214,24 @@
       <c r="C74" s="68" t="n"/>
       <c r="D74" s="69" t="inlineStr">
         <is>
-          <t>Se devenga al ACEPTAR, no al terminar, y por evento.</t>
+          <t>La fecha de cobro se ensena SOLO cuando el asiento ya es pagable.</t>
         </is>
       </c>
       <c r="E74" s="69" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="F74" s="69" t="inlineStr">
         <is>
-          <t>Al aceptar es cuando existe la deuda: 7.5 congela el agreed_amount en ese instante y BR-CREATOR-008 impide cambiarlo despues sin una enmienda firmada por las dos partes. Que todavia no se le pueda pagar es otra cosa y vive en el estado --accrued significa exactamente «se le debe y aun no se le puede pagar»--. Devengar al terminar habria dejado el trabajo hecho y el compromiso invisible hasta el final, que es como una campana se cierra sin que nadie sepa cuanto costo mientras corria. Va por evento y no por llamada directa por lo mismo que 8.1: deptrac no deja que Campaign conozca a Finance, y esta bien que no lo haga --si anotar el asiento falla, la aceptacion sigue siendo cierta, y el creador ya pulso «acepto»--. Y dos finales NO son fallos: que ya hubiera devengo --uq_ledger_devengo funcionando-- y que la colaboracion sea un canje. Si los tres se escribieran igual, el log diria que algo fallo cada vez que alguien acepta un canje, y a la tercera nadie lo lee</t>
+          <t>BR-FIN-012 dice que el plazo son 30 dias desde la verificacion y que es visible desde que acepta: lo visible desde que acepta es el plazo, y una FECHA es otra cosa que se lee muy distinto. Mientras el asiento esta devengado se ensena que falta --las cinco condiciones de BR-FIN-003, con sus palabras--, que es accionable: un creador puede hacer algo con «no tienes ningun medio de pago verificado» y no puede hacer nada con una fecha que depende de trabajo que aun no ha hecho. Y si esa fecha se corriera, la culpa pareceria nuestra. La cuenta arranca en la ultima verificacion de sus publicaciones, y si no hay ninguna --un formato que no exige post-- en la fecha en que se completo la participacion</t>
         </is>
       </c>
     </row>
     <row r="75" ht="57" customHeight="1" s="36">
       <c r="A75" s="67" t="inlineStr">
         <is>
-          <t>DEC-169</t>
+          <t>DEC-172</t>
         </is>
       </c>
       <c r="B75" s="68" t="inlineStr">
@@ -17192,24 +17242,24 @@
       <c r="C75" s="68" t="n"/>
       <c r="D75" s="69" t="inlineStr">
         <is>
-          <t>El estado de un asiento tiene un grafo, y moverlo exige decir por que.</t>
+          <t>El motivo interno de una retencion NO se le ensena al creador.</t>
         </is>
       </c>
       <c r="E75" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="F75" s="69" t="inlineStr">
         <is>
-          <t>tg_ledger_no_update es columna por columna y deja pasar status a proposito --sin eso la tabla no serviria-- pero de ahi no salia QUE transicion es valida: un paid podia volver a accrued, o sea dinero ya pagado reapareciendo como deuda. Es tg_del_rondas de 8.4 otra vez. paid y void son terminales: un pago que se deshace se corrige con un asiento de payment_reversal, no cambiando este estado. Y toda transicion exige status_reason: sin ella, «.por que este creador no cobro?» se contesta mirando la fecha y adivinando. A la bitacora solo va lo que decide una persona --las automaticas son miles y taparian justo lo que se busca ahi--; el rastro completo vive en status_transitions. Ademas nace uq_ledger_devengo, vigesimosexta columna puerta: un devengo por participacion, que BR-FIN-015 daba por hecho sin decirlo</t>
+          <t>Lo escribe el equipo para el expediente y puede nombrar personas o sospechas todavia sin confirmar; un texto redactado deprisa --«parece que lo borro a proposito»-- leido sin contexto es una acusacion de la que no se vuelve. El creador ve «En revision -- te escribimos» y, desde 8.8, recibe un correo donde se le explica de verdad. Las palabras del portal tampoco son las del back-office: on_hold es «en revision» y no «retenido», porque la palabra interna describe lo que hace el sistema y la del portal tiene que describir lo que le pasa a el. La frontera vive en Ledger::misIngresos(), que enumera columnas --el mismo sitio que Aprobaciones::pieza() en 8.5--: devolver la fila entera y confiar en que la plantilla no imprima de mas es confiar en la plantilla de manana. Tampoco cruzan los asientos anulados: no le afectan y no sabe leerlos</t>
         </is>
       </c>
     </row>
     <row r="76" ht="45.75" customHeight="1" s="36">
       <c r="A76" s="67" t="inlineStr">
         <is>
-          <t>DEC-168</t>
+          <t>DEC-171</t>
         </is>
       </c>
       <c r="B76" s="68" t="inlineStr">
@@ -17220,24 +17270,24 @@
       <c r="C76" s="68" t="n"/>
       <c r="D76" s="69" t="inlineStr">
         <is>
-          <t>El asiento va en la moneda PACTADA; se convierte al pagar.</t>
+          <t>El barrido rescata las aceptaciones sin devengo, y avisa de que hubo que rescatarlas.</t>
         </is>
       </c>
       <c r="E76" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F76" s="69" t="inlineStr">
         <is>
-          <t>Se escribe con el agreed_amount y la moneda congelados al aceptar en 7.5: se le debe lo que se le prometio, en la moneda en que se le prometio. La conversion ocurre al armar el pago, con la tasa de ESE dia, y se congela en el asiento de pago (BR-FIN-009). Convertir al devengar habria dejado el saldo del creador en una sola moneda --mas facil de leer-- fijando el tipo de cambio meses antes de pagar: si el dolar sube, el creador cobra menos de lo pactado o nosotros pagamos mas, sin que nadie lo haya decidido</t>
+          <t>Un listener puede fallar, y si falla el creador queda aceptado y su dinero invisible; ademas las participaciones aceptadas antes de 9.4 nunca pasaron por el. ledger:revisar las anota antes de revisar --para que un devengo recuperado hoy pueda pasar a pagable hoy y no manana-- y lo dice en amarillo: que la lista no salga en cero es la noticia, no el arreglo. Es la misma red que 8.1 dejo para los entregables. Las gratuitas quedan fuera de esa lista a proposito: si no, el barrido intentaria lo imposible todos los dias y avisaria todos los dias de algo que esta bien</t>
         </is>
       </c>
     </row>
     <row r="77" ht="68.25" customHeight="1" s="36">
       <c r="A77" s="67" t="inlineStr">
         <is>
-          <t>DEC-167</t>
+          <t>DEC-170</t>
         </is>
       </c>
       <c r="B77" s="68" t="inlineStr">
@@ -17248,24 +17298,24 @@
       <c r="C77" s="68" t="n"/>
       <c r="D77" s="69" t="inlineStr">
         <is>
-          <t>Un post caido RETIENE el asiento; no lo anula.</t>
+          <t>Se devenga al ACEPTAR, no al terminar, y por evento.</t>
         </is>
       </c>
       <c r="E77" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F77" s="69" t="inlineStr">
         <is>
-          <t>8.8 ya lo decidio para el contenido --«el sistema no descuenta nada; la decision de que se le paga la toma una persona con el expediente montado»-- y aqui es lo mismo aplicado al dinero: on_hold saca el asiento de la cola de pago y espera. Reversible: si el creador repone el post, vuelve a payable. Anularlo con una reversion habria sido contablemente mas limpio y habria decidido por su cuenta que no se le paga, que es justo lo que DEC-145 prohibe. Y un asiento retenido no cuenta como saldo: meterlo seria prometerle al creador algo que todavia no esta decidido</t>
+          <t>Al aceptar es cuando existe la deuda: 7.5 congela el agreed_amount en ese instante y BR-CREATOR-008 impide cambiarlo despues sin una enmienda firmada por las dos partes. Que todavia no se le pueda pagar es otra cosa y vive en el estado --accrued significa exactamente «se le debe y aun no se le puede pagar»--. Devengar al terminar habria dejado el trabajo hecho y el compromiso invisible hasta el final, que es como una campana se cierra sin que nadie sepa cuanto costo mientras corria. Va por evento y no por llamada directa por lo mismo que 8.1: deptrac no deja que Campaign conozca a Finance, y esta bien que no lo haga --si anotar el asiento falla, la aceptacion sigue siendo cierta, y el creador ya pulso «acepto»--. Y dos finales NO son fallos: que ya hubiera devengo --uq_ledger_devengo funcionando-- y que la colaboracion sea un canje. Si los tres se escribieran igual, el log diria que algo fallo cada vez que alguien acepta un canje, y a la tercera nadie lo lee</t>
         </is>
       </c>
     </row>
     <row r="78" ht="57" customHeight="1" s="36">
       <c r="A78" s="67" t="inlineStr">
         <is>
-          <t>DEC-166</t>
+          <t>DEC-169</t>
         </is>
       </c>
       <c r="B78" s="68" t="inlineStr">
@@ -17276,7 +17326,7 @@
       <c r="C78" s="68" t="n"/>
       <c r="D78" s="69" t="inlineStr">
         <is>
-          <t>Pasar un devengo a pagable lo hace el SISTEMA, no una persona.</t>
+          <t>El estado de un asiento tiene un grafo, y moverlo exige decir por que.</t>
         </is>
       </c>
       <c r="E78" s="69" t="inlineStr">
@@ -17286,14 +17336,14 @@
       </c>
       <c r="F78" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-003 pide cinco cosas --participacion completada, contenido aprobado, publicacion verificada si aplica, documento tributario valido y medio de pago verificado-- y las cinco ya las firmo alguien una por una: quien verifico la publicacion, quien aprobo el perfil fiscal, quien verifico la cuenta. Una sexta firma que solo dice «si, se cumplen las cinco» es un boton que alguien acaba pulsando sin mirar, y una cola que retrasa pagos por acumulacion y no por duda. Ledger::requisitos() devuelve las cinco con su veredicto y no la primera que falla, porque quien mira por que un creador no cobra necesita la lista entera. El «si aplica» de la publicacion se implementa contando: si ningun entregable tiene publicacion el requisito se da por cumplido --un formato que no exige post no puede bloquear un pago para siempre--</t>
+          <t>tg_ledger_no_update es columna por columna y deja pasar status a proposito --sin eso la tabla no serviria-- pero de ahi no salia QUE transicion es valida: un paid podia volver a accrued, o sea dinero ya pagado reapareciendo como deuda. Es tg_del_rondas de 8.4 otra vez. paid y void son terminales: un pago que se deshace se corrige con un asiento de payment_reversal, no cambiando este estado. Y toda transicion exige status_reason: sin ella, «.por que este creador no cobro?» se contesta mirando la fecha y adivinando. A la bitacora solo va lo que decide una persona --las automaticas son miles y taparian justo lo que se busca ahi--; el rastro completo vive en status_transitions. Ademas nace uq_ledger_devengo, vigesimosexta columna puerta: un devengo por participacion, que BR-FIN-015 daba por hecho sin decirlo</t>
         </is>
       </c>
     </row>
     <row r="79" ht="57" customHeight="1" s="36">
       <c r="A79" s="67" t="inlineStr">
         <is>
-          <t>DEC-165</t>
+          <t>DEC-168</t>
         </is>
       </c>
       <c r="B79" s="68" t="inlineStr">
@@ -17304,24 +17354,24 @@
       <c r="C79" s="68" t="n"/>
       <c r="D79" s="69" t="inlineStr">
         <is>
-          <t>Decolecta trae USD → PEN y nada mas, y el sistema lo dice en vez de disimularlo.</t>
+          <t>El asiento va en la moneda PACTADA; se convierte al pagar.</t>
         </is>
       </c>
       <c r="E79" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F79" s="69" t="inlineStr">
         <is>
-          <t>Publica el tipo de cambio de SUNAT, y SUNAT solo publica el dolar. Por eso Decolecta no acepta un par como parametro --sabe traer lo unico que su fuente publica, y decirlo es mas honesto que aceptar COP y fallar raro--; el catalogo declara USD → PEN = sunat y ningun otro par, porque declarar una fuente que no publica es peor que no tener ninguna; la pantalla tiene carga manual con fuente manual y no disfrazada de sunat, que es lo que permite distinguir despues que se trajo y que se tecleo; y lo dice en la propia pantalla, para que «no llega la tasa del peso mexicano» no se diagnostique como un cron roto. Que fuente se usa para los demas pares queda como Q-64</t>
+          <t>Se escribe con el agreed_amount y la moneda congelados al aceptar en 7.5: se le debe lo que se le prometio, en la moneda en que se le prometio. La conversion ocurre al armar el pago, con la tasa de ESE dia, y se congela en el asiento de pago (BR-FIN-009). Convertir al devengar habria dejado el saldo del creador en una sola moneda --mas facil de leer-- fijando el tipo de cambio meses antes de pagar: si el dolar sube, el creador cobra menos de lo pactado o nosotros pagamos mas, sin que nadie lo haya decidido</t>
         </is>
       </c>
     </row>
     <row r="80" ht="68.25" customHeight="1" s="36">
       <c r="A80" s="67" t="inlineStr">
         <is>
-          <t>DEC-164</t>
+          <t>DEC-167</t>
         </is>
       </c>
       <c r="B80" s="68" t="inlineStr">
@@ -17332,24 +17382,24 @@
       <c r="C80" s="68" t="n"/>
       <c r="D80" s="69" t="inlineStr">
         <is>
-          <t>El cron deja rastro de cada intento, y pide TRES dias.</t>
+          <t>Un post caido RETIENE el asiento; no lo anula.</t>
         </is>
       </c>
       <c r="E80" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F80" s="69" t="inlineStr">
         <is>
-          <t>fx_fetch_runs. Cambio::DIAS_ATRAS detecta que las tasas dejaron de llegar cuando alguien va a convertir, o sea el dia de la liquidacion; esto lo ensena antes, y la pantalla lo resume arriba solo si hay algo que mirar --una pantalla que siempre tiene un aviso es una pantalla cuyos avisos nadie lee--. ck_ffr_nuevas obliga a que una corrida fallida diga cero, porque el registro que contesta «.sigue vivo el cron?» no puede afirmar que una corrida con error trajo tres tasas. Tres dias y no uno: si no corrio viernes ni sabado, pedir solo el domingo deja dos huecos que nadie rellena a mano, y repetir un dia no cuesta una fila --uq_fx_rate-- sino una peticion. Y termina en 0 aunque un dia falle: un cron que da error a diario hace ruido donde nadie mira; solo falla si NINGUN dia se pudo traer</t>
+          <t>8.8 ya lo decidio para el contenido --«el sistema no descuenta nada; la decision de que se le paga la toma una persona con el expediente montado»-- y aqui es lo mismo aplicado al dinero: on_hold saca el asiento de la cola de pago y espera. Reversible: si el creador repone el post, vuelve a payable. Anularlo con una reversion habria sido contablemente mas limpio y habria decidido por su cuenta que no se le paga, que es justo lo que DEC-145 prohibe. Y un asiento retenido no cuenta como saldo: meterlo seria prometerle al creador algo que todavia no esta decidido</t>
         </is>
       </c>
     </row>
     <row r="81" ht="68.25" customHeight="1" s="36">
       <c r="A81" s="67" t="inlineStr">
         <is>
-          <t>DEC-163</t>
+          <t>DEC-166</t>
         </is>
       </c>
       <c r="B81" s="68" t="inlineStr">
@@ -17360,24 +17410,24 @@
       <c r="C81" s="68" t="n"/>
       <c r="D81" s="69" t="inlineStr">
         <is>
-          <t>Cada final de la traida tiene su nombre, y traer() no lanza.</t>
+          <t>Pasar un devengo a pagable lo hace el SISTEMA, no una persona.</t>
         </is>
       </c>
       <c r="E81" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F81" s="69" t="inlineStr">
         <is>
-          <t>ok, sin_credencial, error_http, error_red, respuesta_rara. En un catch generico los cinco se ven iguales y exigen cinco arreglos distintos: «no hay clave» se arregla configurandola, «401» rotandola, «200 con un cuerpo raro» mirando la API. Un 404 --dia sin publicar-- ni siquiera se pinta como averia: quien lee la salida del cron todos los dias deja de leerla si le grita por lo normal. Y una respuesta que no se entiende no anota nada: una tasa inventada entraria en una tabla que tg_fx_inmutable no deja corregir</t>
+          <t>BR-FIN-003 pide cinco cosas --participacion completada, contenido aprobado, publicacion verificada si aplica, documento tributario valido y medio de pago verificado-- y las cinco ya las firmo alguien una por una: quien verifico la publicacion, quien aprobo el perfil fiscal, quien verifico la cuenta. Una sexta firma que solo dice «si, se cumplen las cinco» es un boton que alguien acaba pulsando sin mirar, y una cola que retrasa pagos por acumulacion y no por duda. Ledger::requisitos() devuelve las cinco con su veredicto y no la primera que falla, porque quien mira por que un creador no cobra necesita la lista entera. El «si aplica» de la publicacion se implementa contando: si ningun entregable tiene publicacion el requisito se da por cumplido --un formato que no exige post no puede bloquear un pago para siempre--</t>
         </is>
       </c>
     </row>
     <row r="82" ht="45.75" customHeight="1" s="36">
       <c r="A82" s="67" t="inlineStr">
         <is>
-          <t>DEC-162</t>
+          <t>DEC-165</t>
         </is>
       </c>
       <c r="B82" s="68" t="inlineStr">
@@ -17388,7 +17438,7 @@
       <c r="C82" s="68" t="n"/>
       <c r="D82" s="69" t="inlineStr">
         <is>
-          <t>La credencial se configura desde la pantalla, pero el ENTORNO manda y en la base va CIFRADA.</t>
+          <t>Decolecta trae USD → PEN y nada mas, y el sistema lo dice en vez de disimularlo.</t>
         </is>
       </c>
       <c r="E82" s="69" t="inlineStr">
@@ -17398,14 +17448,14 @@
       </c>
       <c r="F82" s="69" t="inlineStr">
         <is>
-          <t>La peticion era «la configurare en la pantalla del admin». Se hace, con dos condiciones que salen de la regla de seguridad del propio proyecto --«no almacenar secretos en texto plano en BD cuando exista alternativa segura»--: si hay DECOLECTA_API_KEY en el entorno se usa esa y la de la base ni se mira --no viaja por el navegador, no esta en ninguna tabla, no sale en un volcado--; y si no la hay, se guarda con Crypt, la misma maquina que cifra las cuentas bancarias desde 3.8. La clave no se reensena jamas, ni al que la escribio un minuto antes: la pantalla dice «termina en 8f2a» y de donde sale. La bitacora anota que cambio y los cuatro ultimos, nunca el valor. Y tg_fxs_credencial_firmada exige quien la puso, cuando y la pista, las tres o ninguna: media firma es peor que ninguna porque parece que «quien la puso» tiene respuesta. El permiso va aparte: la pantalla es fx.manage --la tiene finanzas-- y la credencial es integration.manage --solo admin--, porque una clave de un tercero es un permiso de gasto y no la necesita quien anota una tasa un lunes</t>
+          <t>Publica el tipo de cambio de SUNAT, y SUNAT solo publica el dolar. Por eso Decolecta no acepta un par como parametro --sabe traer lo unico que su fuente publica, y decirlo es mas honesto que aceptar COP y fallar raro--; el catalogo declara USD → PEN = sunat y ningun otro par, porque declarar una fuente que no publica es peor que no tener ninguna; la pantalla tiene carga manual con fuente manual y no disfrazada de sunat, que es lo que permite distinguir despues que se trajo y que se tecleo; y lo dice en la propia pantalla, para que «no llega la tasa del peso mexicano» no se diagnostique como un cron roto. Que fuente se usa para los demas pares queda como Q-64</t>
         </is>
       </c>
     </row>
     <row r="83" ht="68.25" customHeight="1" s="36">
       <c r="A83" s="67" t="inlineStr">
         <is>
-          <t>DEC-161</t>
+          <t>DEC-164</t>
         </is>
       </c>
       <c r="B83" s="68" t="inlineStr">
@@ -17416,24 +17466,24 @@
       <c r="C83" s="68" t="n"/>
       <c r="D83" s="69" t="inlineStr">
         <is>
-          <t>porque() admite alternancia, y eso es lo que faltaba para bajar el trinquete de las 297.</t>
+          <t>El cron deja rastro de cada intento, y pide TRES dias.</t>
         </is>
       </c>
       <c r="E83" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F83" s="69" t="inlineStr">
         <is>
-          <t>Los dos motores contestan cosas distintas a la MISMA regla cuando la creo Restriccion: MariaDB dice «CONSTRAINT ck_fos_dates failed» y Percona dice el mensaje. El nombre sale en uno y el mensaje en el otro, y no coinciden en ningun texto, asi que toda regla de Restriccion tenia que quedarse en un probar ... RECHAZO a secas. Con grep -qE, porque ... 'ck_fos_dates|antes de empezar' afirma el motivo en los dos motores. DEC-154 puso el trinquete y conto 297; esto es la herramienta para bajarlo</t>
+          <t>fx_fetch_runs. Cambio::DIAS_ATRAS detecta que las tasas dejaron de llegar cuando alguien va a convertir, o sea el dia de la liquidacion; esto lo ensena antes, y la pantalla lo resume arriba solo si hay algo que mirar --una pantalla que siempre tiene un aviso es una pantalla cuyos avisos nadie lee--. ck_ffr_nuevas obliga a que una corrida fallida diga cero, porque el registro que contesta «.sigue vivo el cron?» no puede afirmar que una corrida con error trajo tres tasas. Tres dias y no uno: si no corrio viernes ni sabado, pedir solo el domingo deja dos huecos que nadie rellena a mano, y repetir un dia no cuesta una fila --uq_fx_rate-- sino una peticion. Y termina en 0 aunque un dia falle: un cron que da error a diario hace ruido donde nadie mira; solo falla si NINGUN dia se pudo traer</t>
         </is>
       </c>
     </row>
     <row r="84" ht="57" customHeight="1" s="36">
       <c r="A84" s="67" t="inlineStr">
         <is>
-          <t>DEC-160</t>
+          <t>DEC-163</t>
         </is>
       </c>
       <c r="B84" s="68" t="inlineStr">
@@ -17444,24 +17494,24 @@
       <c r="C84" s="68" t="n"/>
       <c r="D84" s="69" t="inlineStr">
         <is>
-          <t>Un dia sin tasa usa la ultima anterior, y lo que se guarda es la fecha de ESA tasa.</t>
+          <t>Cada final de la traida tiene su nombre, y traer() no lanza.</t>
         </is>
       </c>
       <c r="E84" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F84" s="69" t="inlineStr">
         <is>
-          <t>Sabados, domingos y feriados no tienen tipo publicado. Se convierte con la del viernes y el asiento dice «tasa del viernes», no «tasa del domingo»: guardar la fecha de la operacion habria sido mas comodo de leer y habria hecho que el historico afirmara que ese domingo hubo una tasa que nunca existio (BR-FIN-009). Es un supuesto fiscal y esta marcado como tal (§56): que la practica peruana sea el ultimo tipo publicado lo confirma el contador. Y hay un corte de 10 dias, porque «la ultima anterior» tapa una averia: si lo ultimo es de hace tres semanas no fue un feriado, es que el cron dejo de traerlas, y sin ese corte una tabla congelada se ve igual que una sana hasta el dia de la liquidacion</t>
+          <t>ok, sin_credencial, error_http, error_red, respuesta_rara. En un catch generico los cinco se ven iguales y exigen cinco arreglos distintos: «no hay clave» se arregla configurandola, «401» rotandola, «200 con un cuerpo raro» mirando la API. Un 404 --dia sin publicar-- ni siquiera se pinta como averia: quien lee la salida del cron todos los dias deja de leerla si le grita por lo normal. Y una respuesta que no se entiende no anota nada: una tasa inventada entraria en una tabla que tg_fx_inmutable no deja corregir</t>
         </is>
       </c>
     </row>
     <row r="85" ht="57" customHeight="1" s="36">
       <c r="A85" s="67" t="inlineStr">
         <is>
-          <t>DEC-159</t>
+          <t>DEC-162</t>
         </is>
       </c>
       <c r="B85" s="68" t="inlineStr">
@@ -17472,24 +17522,24 @@
       <c r="C85" s="68" t="n"/>
       <c r="D85" s="69" t="inlineStr">
         <is>
-          <t>Compra y venta son dos filas, y cual aplica NO tiene valor por defecto.</t>
+          <t>La credencial se configura desde la pantalla, pero el ENTORNO manda y en la base va CIFRADA.</t>
         </is>
       </c>
       <c r="E85" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F85" s="69" t="inlineStr">
         <is>
-          <t>SUNAT publica las dos el mismo dia y no son intercambiables. Con una sola columna rate solo cabe una, y elegir cual guardar habria sido tomar por mi cuenta una decision contable en el sitio donde menos se ve. side entra en la clave, asi que las dos caben sin pisarse. Y Cambio::tasa() exige el lado como parametro sin defecto: un defecto aqui es exactamente la forma en que una decision fiscal se toma sola. Queda Q-63 para el contador, y por eso el buscador de creadores sigue sin convertir aunque la maquina ya exista</t>
+          <t>La peticion era «la configurare en la pantalla del admin». Se hace, con dos condiciones que salen de la regla de seguridad del propio proyecto --«no almacenar secretos en texto plano en BD cuando exista alternativa segura»--: si hay DECOLECTA_API_KEY en el entorno se usa esa y la de la base ni se mira --no viaja por el navegador, no esta en ninguna tabla, no sale en un volcado--; y si no la hay, se guarda con Crypt, la misma maquina que cifra las cuentas bancarias desde 3.8. La clave no se reensena jamas, ni al que la escribio un minuto antes: la pantalla dice «termina en 8f2a» y de donde sale. La bitacora anota que cambio y los cuatro ultimos, nunca el valor. Y tg_fxs_credencial_firmada exige quien la puso, cuando y la pista, las tres o ninguna: media firma es peor que ninguna porque parece que «quien la puso» tiene respuesta. El permiso va aparte: la pantalla es fx.manage --la tiene finanzas-- y la credencial es integration.manage --solo admin--, porque una clave de un tercero es un permiso de gasto y no la necesita quien anota una tasa un lunes</t>
         </is>
       </c>
     </row>
     <row r="86" ht="57" customHeight="1" s="36">
       <c r="A86" s="67" t="inlineStr">
         <is>
-          <t>DEC-158</t>
+          <t>DEC-161</t>
         </is>
       </c>
       <c r="B86" s="68" t="inlineStr">
@@ -17500,7 +17550,7 @@
       <c r="C86" s="68" t="n"/>
       <c r="D86" s="69" t="inlineStr">
         <is>
-          <t>Que fuente publica el tipo de cambio se DECLARA, con periodos, y no se elige al convertir.</t>
+          <t>porque() admite alternancia, y eso es lo que faltaba para bajar el trinquete de las 297.</t>
         </is>
       </c>
       <c r="E86" s="69" t="inlineStr">
@@ -17510,14 +17560,14 @@
       </c>
       <c r="F86" s="69" t="inlineStr">
         <is>
-          <t>uq_exchange_rates incluia source a proposito --dos fuentes pueden discrepar el mismo dia y BR-FIN-009 exige poder decir de cual salio la que se aplico-- pero de ahi no salia CUAL SE APLICA. Es el estado EMPATE de CoberturaFacturacion, el que una vez produjo una factura emitida por la sociedad equivocada, y la respuesta es la misma que entonces: uq_fos_current garantiza una sola fuente VIGENTE por par, y fos_sin_solape una sola POR FECHA --que es la mitad que se olvida, porque convertir un importe de marzo resuelve por par Y por fecha--. Con periodos y no con una columna porque el historico tiene que seguir explicandose con quien mandaba entonces: si fuera una columna, cambiar de proveedor reescribiria como se convirtio todo lo anterior</t>
+          <t>Los dos motores contestan cosas distintas a la MISMA regla cuando la creo Restriccion: MariaDB dice «CONSTRAINT ck_fos_dates failed» y Percona dice el mensaje. El nombre sale en uno y el mensaje en el otro, y no coinciden en ningun texto, asi que toda regla de Restriccion tenia que quedarse en un probar ... RECHAZO a secas. Con grep -qE, porque ... 'ck_fos_dates|antes de empezar' afirma el motivo en los dos motores. DEC-154 puso el trinquete y conto 297; esto es la herramienta para bajarlo</t>
         </is>
       </c>
     </row>
     <row r="87" ht="68.25" customHeight="1" s="36">
       <c r="A87" s="67" t="inlineStr">
         <is>
-          <t>DEC-157</t>
+          <t>DEC-160</t>
         </is>
       </c>
       <c r="B87" s="68" t="inlineStr">
@@ -17528,24 +17578,24 @@
       <c r="C87" s="68" t="n"/>
       <c r="D87" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-009 se comprueba cuando se escribe el primer pago, no en la iteracion 9.11.</t>
+          <t>Un dia sin tasa usa la ultima anterior, y lo que se guarda es la fecha de ESA tasa.</t>
         </is>
       </c>
       <c r="E87" s="69" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F87" s="69" t="inlineStr">
         <is>
-          <t>El roadmap tenia la validacion de «la sociedad que factura y la que liquida son la misma» como iteracion 11 de 14 de la fase de finanzas. Una regla 🔴 que llega la penultima llega despues de que diez iteraciones se hayan construido dandola por buena, y es exactamente la forma de fallo de 8.4: el techo de rondas existia entero en PHP desde 8.3 y nada lo respaldaba en la base. Aqui es peor, porque lo que se cuela no es una ronda: es dinero saliendo de la sociedad equivocada, que es una operacion intercompania no documentada. Pasa a ser requisito de la iteracion que estrene payout_batches, y en la base: un lote nombra su sociedad y sus asientos nombran sus campanas, asi que la comprobacion es cross-table y le toca a un disparador, no a un CHECK. Y con esto DEC-020 deja de ser PROPUESTA: preguntaba si permitir que la entidad que factura y la que liquida divergieran, y recomendaba modelar la separacion y bloquearla en el MVP. DEC-156 lo contesta y ademas le quita el «en el MVP»</t>
+          <t>Sabados, domingos y feriados no tienen tipo publicado. Se convierte con la del viernes y el asiento dice «tasa del viernes», no «tasa del domingo»: guardar la fecha de la operacion habria sido mas comodo de leer y habria hecho que el historico afirmara que ese domingo hubo una tasa que nunca existio (BR-FIN-009). Es un supuesto fiscal y esta marcado como tal (§56): que la practica peruana sea el ultimo tipo publicado lo confirma el contador. Y hay un corte de 10 dias, porque «la ultima anterior» tapa una averia: si lo ultimo es de hace tres semanas no fue un feriado, es que el cron dejo de traerlas, y sin ese corte una tabla congelada se ve igual que una sana hasta el dia de la liquidacion</t>
         </is>
       </c>
     </row>
     <row r="88" ht="34.5" customHeight="1" s="36">
       <c r="A88" s="67" t="inlineStr">
         <is>
-          <t>DEC-156</t>
+          <t>DEC-159</t>
         </is>
       </c>
       <c r="B88" s="68" t="inlineStr">
@@ -17556,24 +17606,24 @@
       <c r="C88" s="68" t="n"/>
       <c r="D88" s="69" t="inlineStr">
         <is>
-          <t>La campana decide quien paga a cada creador, y el pais del creador no entra en esa decision.</t>
+          <t>Compra y venta son dos filas, y cual aplica NO tiene valor por defecto.</t>
         </is>
       </c>
       <c r="E88" s="69" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F88" s="69" t="inlineStr">
         <is>
-          <t>Un creador colombiano en una campana de CTS Peru cobra de CTS Peru. La sociedad sale del pais del CLIENTE, se guarda en la campana y el pago la hereda de ahi, congelada al confirmar igual que agreed_amount; lo implementa F9. [Corregido el 2026-08-27, T-59: la version original de esta entrada decia que «payouts no tiene ninguna columna de sociedad» y eso es falso. payout_batches.legal_entity_id existe desde la migracion de finanzas y el pago la hereda de su lote. Lo que NO existe es la garantia de que sea la correcta: nada ata el lote a las campanas cuyos asientos liquida, asi que hoy un lote de CTS Colombia podria pagar el trabajo de una campana de CTS Peru y ninguna restriccion lo notaria.] Esto no inventa la regla: BR-LE-009 ya la decia, con «en el MVP» delante y en naranja. Se le quita el «en el MVP» y sube a 🔴, porque no es una simplificacion temporal sino como funciona el grupo. La alternativa --que pagara la sociedad del pais del creador-- parte una campana en dos contabilidades, obliga a que el margen de una campana se calcule entre sociedades y exige cobertura en el pais de cada creador antes de poder invitarlo: hoy Espana no tiene sociedad y con esa alternativa un creador espanol seria ininvitable. Y cambia el eje de Q-40: la retencion depende de quien paga Y de donde esta el creador, no solo de lo segundo, asi que la tabla del contador pasa a ser «CTS Peru pagando a un creador de cada pais» y CTS Colombia tiene la suya, para un contador colombiano</t>
+          <t>SUNAT publica las dos el mismo dia y no son intercambiables. Con una sola columna rate solo cabe una, y elegir cual guardar habria sido tomar por mi cuenta una decision contable en el sitio donde menos se ve. side entra en la clave, asi que las dos caben sin pisarse. Y Cambio::tasa() exige el lado como parametro sin defecto: un defecto aqui es exactamente la forma en que una decision fiscal se toma sola. Queda Q-63 para el contador, y por eso el buscador de creadores sigue sin convertir aunque la maquina ya exista</t>
         </is>
       </c>
     </row>
     <row r="89" ht="57" customHeight="1" s="36">
       <c r="A89" s="67" t="inlineStr">
         <is>
-          <t>DEC-155</t>
+          <t>DEC-158</t>
         </is>
       </c>
       <c r="B89" s="68" t="inlineStr">
@@ -17584,24 +17634,24 @@
       <c r="C89" s="68" t="n"/>
       <c r="D89" s="69" t="inlineStr">
         <is>
-          <t>La sociedad que factura NO se elige: se resuelve, y la pantalla enseña por que.</t>
+          <t>Que fuente publica el tipo de cambio se DECLARA, con periodos, y no se elige al convertir.</t>
         </is>
       </c>
       <c r="E89" s="69" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F89" s="69" t="inlineStr">
         <is>
-          <t>El planteamiento era poner un desplegable «CTS Peru / CTS Colombia» en la campana. No se hace, y el motivo esta en el esquema: uq_lec_country mas tg_lec_sin_solape_ins/upd garantizan que en cualquier fecha hay como mucho una sociedad cubriendo un pais, asi que el desplegable tendria siempre una opcion --y una opcion que se puede cambiar es una que alguien puede cambiar mal--. Ya existia campaigns.billing_legal_entity_id, resuelto a starts_on por Campanas::quienFactura() y congelado al confirmar por tg_camp_entidad_congelada. Lo que faltaba no era el campo: era decirlo. La ficha ahora dice quien factura Y su motivo --«CTS Peru factura a Peru desde el 2025-01-01 (sociedad local)»--, porque una sociedad a secas no se puede comprobar y con su motivo y su fecha quien la lee sabe si es la que esperaba y puede discutirla antes de que salga una factura. El formulario de alta no adelanta una respuesta: el pais del cliente y la fecha todavia no existen, y resolver «con la cobertura de hoy» para ensenarlo es justo el «deducirlo de la configuracion vigente» que prohibe BR-LE-001</t>
+          <t>uq_exchange_rates incluia source a proposito --dos fuentes pueden discrepar el mismo dia y BR-FIN-009 exige poder decir de cual salio la que se aplico-- pero de ahi no salia CUAL SE APLICA. Es el estado EMPATE de CoberturaFacturacion, el que una vez produjo una factura emitida por la sociedad equivocada, y la respuesta es la misma que entonces: uq_fos_current garantiza una sola fuente VIGENTE por par, y fos_sin_solape una sola POR FECHA --que es la mitad que se olvida, porque convertir un importe de marzo resuelve por par Y por fecha--. Con periodos y no con una columna porque el historico tiene que seguir explicandose con quien mandaba entonces: si fuera una columna, cambiar de proveedor reescribiria como se convirtio todo lo anterior</t>
         </is>
       </c>
     </row>
     <row r="90" ht="45.75" customHeight="1" s="36">
       <c r="A90" s="67" t="inlineStr">
         <is>
-          <t>DEC-154</t>
+          <t>DEC-157</t>
         </is>
       </c>
       <c r="B90" s="68" t="inlineStr">
@@ -17612,24 +17662,24 @@
       <c r="C90" s="68" t="n"/>
       <c r="D90" s="69" t="inlineStr">
         <is>
-          <t>Los ayudantes de las suites viven en UN archivo, y nace la SEPTIMA puerta.</t>
+          <t>BR-LE-009 se comprueba cuando se escribe el primer pago, no en la iteracion 9.11.</t>
         </is>
       </c>
       <c r="E90" s="69" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="F90" s="69" t="inlineStr">
         <is>
-          <t>tools/pruebas/comun.sh y tools/verificar-suites.py. La puerta comprueba que toda suite listada existe, que ninguna define sus propios probar/valor/porque, que todas cargan comun.sh, y lleva un trinquete: cuantas aserciones negativas afirman POR QUE se rechaza y cuantas solo que algo fallo. Hoy son 89 con motivo y 297 sin el, y ese segundo numero solo puede bajar (tools/pruebas/MOTIVOS-BASE). No se convierten las 297 en esta iteracion --son veintidos suites de cuatro fases-- pero desde hoy no pueden ser 298, y ademas cada probar ... RECHAZO enseña en gris que restriccion respondio, para que el desajuste se vea al leer la salida. Es la leccion de T-48, T-50, T-51 y T-54: las cuatro fueron aserciones verdes por el motivo equivocado y las cuatro eran un probar ... RECHAZO a secas</t>
+          <t>El roadmap tenia la validacion de «la sociedad que factura y la que liquida son la misma» como iteracion 11 de 14 de la fase de finanzas. Una regla 🔴 que llega la penultima llega despues de que diez iteraciones se hayan construido dandola por buena, y es exactamente la forma de fallo de 8.4: el techo de rondas existia entero en PHP desde 8.3 y nada lo respaldaba en la base. Aqui es peor, porque lo que se cuela no es una ronda: es dinero saliendo de la sociedad equivocada, que es una operacion intercompania no documentada. Pasa a ser requisito de la iteracion que estrene payout_batches, y en la base: un lote nombra su sociedad y sus asientos nombran sus campanas, asi que la comprobacion es cross-table y le toca a un disparador, no a un CHECK. Y con esto DEC-020 deja de ser PROPUESTA: preguntaba si permitir que la entidad que factura y la que liquida divergieran, y recomendaba modelar la separacion y bloquearla en el MVP. DEC-156 lo contesta y ademas le quita el «en el MVP»</t>
         </is>
       </c>
     </row>
     <row r="91" ht="45.75" customHeight="1" s="36">
       <c r="A91" s="67" t="inlineStr">
         <is>
-          <t>DEC-153</t>
+          <t>DEC-156</t>
         </is>
       </c>
       <c r="B91" s="68" t="inlineStr">
@@ -17640,24 +17690,24 @@
       <c r="C91" s="68" t="n"/>
       <c r="D91" s="69" t="inlineStr">
         <is>
-          <t>Una peticion de cambios sin rondas queda PENDIENTE de autorizar.</t>
+          <t>La campana decide quien paga a cada creador, y el pais del creador no entra en esa decision.</t>
         </is>
       </c>
       <c r="E91" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="F91" s="69" t="inlineStr">
         <is>
-          <t>Se registra y no se convierte en ronda hasta que alguien del equipo decida si se le cobra o la absorbemos; al cliente se le confirma que su peticion llego --que es verdad-- sin prometerle que sera gratis. Cae solo del modelo de DEC-151: como la respuesta no crea la revision, no hay ronda que consumir hasta que una persona emite el veredicto. Aprobaciones::pendientes() es la lista de lo que espera esa decision. La pantalla de gracias NO dice «lo corregimos»: decirlo seria prometer por su cuenta algo que todavia no esta decidido</t>
+          <t>Un creador colombiano en una campana de CTS Peru cobra de CTS Peru. La sociedad sale del pais del CLIENTE, se guarda en la campana y el pago la hereda de ahi, congelada al confirmar igual que agreed_amount; lo implementa F9. [Corregido el 2026-08-27, T-59: la version original de esta entrada decia que «payouts no tiene ninguna columna de sociedad» y eso es falso. payout_batches.legal_entity_id existe desde la migracion de finanzas y el pago la hereda de su lote. Lo que NO existe es la garantia de que sea la correcta: nada ata el lote a las campanas cuyos asientos liquida, asi que hoy un lote de CTS Colombia podria pagar el trabajo de una campana de CTS Peru y ninguna restriccion lo notaria.] Esto no inventa la regla: BR-LE-009 ya la decia, con «en el MVP» delante y en naranja. Se le quita el «en el MVP» y sube a 🔴, porque no es una simplificacion temporal sino como funciona el grupo. La alternativa --que pagara la sociedad del pais del creador-- parte una campana en dos contabilidades, obliga a que el margen de una campana se calcule entre sociedades y exige cobertura en el pais de cada creador antes de poder invitarlo: hoy Espana no tiene sociedad y con esa alternativa un creador espanol seria ininvitable. Y cambia el eje de Q-40: la retencion depende de quien paga Y de donde esta el creador, no solo de lo segundo, asi que la tabla del contador pasa a ser «CTS Peru pagando a un creador de cada pais» y CTS Colombia tiene la suya, para un contador colombiano</t>
         </is>
       </c>
     </row>
     <row r="92" ht="34.5" customHeight="1" s="36">
       <c r="A92" s="67" t="inlineStr">
         <is>
-          <t>DEC-152</t>
+          <t>DEC-155</t>
         </is>
       </c>
       <c r="B92" s="68" t="inlineStr">
@@ -17668,24 +17718,24 @@
       <c r="C92" s="68" t="n"/>
       <c r="D92" s="69" t="inlineStr">
         <is>
-          <t>El silencio del cliente no hace nada, y por eso 8.5 no estrena comando.</t>
+          <t>La sociedad que factura NO se elige: se resuelve, y la pantalla enseña por que.</t>
         </is>
       </c>
       <c r="E92" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="F92" s="69" t="inlineStr">
         <is>
-          <t>El enlace caduca, la pieza se queda donde estaba y sale en la bandeja. Nadie aprueba ni rechaza en nombre de nadie. «Silencio = aprobado» habria desbloqueado la campana sin perseguir a nadie y necesita estar escrito en el contrato: dar por buena una pieza que nadie miro es una firma que el sistema pone por el cliente, y de ahi cuelgan la publicacion y el pago. Y de ahi sale que no haga falta un comando de caducidad, al reves que en 7.6: alli una invitacion sin contestar dejaba dinero comprometido y una plaza de cupo ocupada --habia un estado del mundo que corregir-- y aqui expires_at &lt; NOW() basta. Un comando que no arregla nada es una linea de cron mas que mantener y una cosa mas que puede fallar en silencio</t>
+          <t>El planteamiento era poner un desplegable «CTS Peru / CTS Colombia» en la campana. No se hace, y el motivo esta en el esquema: uq_lec_country mas tg_lec_sin_solape_ins/upd garantizan que en cualquier fecha hay como mucho una sociedad cubriendo un pais, asi que el desplegable tendria siempre una opcion --y una opcion que se puede cambiar es una que alguien puede cambiar mal--. Ya existia campaigns.billing_legal_entity_id, resuelto a starts_on por Campanas::quienFactura() y congelado al confirmar por tg_camp_entidad_congelada. Lo que faltaba no era el campo: era decirlo. La ficha ahora dice quien factura Y su motivo --«CTS Peru factura a Peru desde el 2025-01-01 (sociedad local)»--, porque una sociedad a secas no se puede comprobar y con su motivo y su fecha quien la lee sabe si es la que esperaba y puede discutirla antes de que salga una factura. El formulario de alta no adelanta una respuesta: el pais del cliente y la fecha todavia no existen, y resolver «con la cobertura de hoy» para ensenarlo es justo el «deducirlo de la configuracion vigente» que prohibe BR-LE-001</t>
         </is>
       </c>
     </row>
     <row r="93" ht="45.75" customHeight="1" s="36">
       <c r="A93" s="67" t="inlineStr">
         <is>
-          <t>DEC-151</t>
+          <t>DEC-154</t>
         </is>
       </c>
       <c r="B93" s="68" t="inlineStr">
@@ -17696,24 +17746,24 @@
       <c r="C93" s="68" t="n"/>
       <c r="D93" s="69" t="inlineStr">
         <is>
-          <t>La respuesta del cliente se REGISTRA; el equipo cierra.</t>
+          <t>Los ayudantes de las suites viven en UN archivo, y nace la SEPTIMA puerta.</t>
         </is>
       </c>
       <c r="E93" s="69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="F93" s="69" t="inlineStr">
         <is>
-          <t>El cliente dice «me vale» o «cambiad esto» desde un enlace firmado, y eso queda escrito con su hora y su IP --pero no mueve el entregable--. La alternativa era que su OK aprobara la pieza directamente, y se descarto por dos razones. (a) Habria obligado a partir approved en dos estados: hoy significa «listo para publicar» y 8.6 publica desde ahi, asi que sin un «aprobado interno, esperando al cliente» el mismo estado significaria dos cosas --el fallo de T-50--. (b) Y la que decide: la correccion del cliente gasta ronda, y desde 8.4 una ronda de mas exige firma y decision de facturacion. El cliente no puede firmar un cargo contra si mismo. Si su respuesta moviera la pieza sola, o se le cobraria sin que nadie lo autorizara, o habria que dejarle una puerta por la que las rondas no se cuentan. La pantalla se lo dice con esas palabras: quien pulsa «me vale» y no ve nada moverse tiene derecho a saber que pasa despues</t>
+          <t>tools/pruebas/comun.sh y tools/verificar-suites.py. La puerta comprueba que toda suite listada existe, que ninguna define sus propios probar/valor/porque, que todas cargan comun.sh, y lleva un trinquete: cuantas aserciones negativas afirman POR QUE se rechaza y cuantas solo que algo fallo. Hoy son 89 con motivo y 297 sin el, y ese segundo numero solo puede bajar (tools/pruebas/MOTIVOS-BASE). No se convierten las 297 en esta iteracion --son veintidos suites de cuatro fases-- pero desde hoy no pueden ser 298, y ademas cada probar ... RECHAZO enseña en gris que restriccion respondio, para que el desajuste se vea al leer la salida. Es la leccion de T-48, T-50, T-51 y T-54: las cuatro fueron aserciones verdes por el motivo equivocado y las cuatro eran un probar ... RECHAZO a secas</t>
         </is>
       </c>
     </row>
     <row r="94" ht="45.75" customHeight="1" s="36">
       <c r="A94" s="67" t="inlineStr">
         <is>
-          <t>DEC-150</t>
+          <t>DEC-153</t>
         </is>
       </c>
       <c r="B94" s="68" t="inlineStr">
@@ -17724,24 +17774,24 @@
       <c r="C94" s="68" t="n"/>
       <c r="D94" s="69" t="inlineStr">
         <is>
-          <t>El techo de rondas pasa a la base, y los disparadores siguen siendo GUARDAS.</t>
+          <t>Una peticion de cambios sin rondas queda PENDIENTE de autorizar.</t>
         </is>
       </c>
       <c r="E94" s="69" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F94" s="69" t="inlineStr">
         <is>
-          <t>8.3 construyo el limite entero --rondas(), vetoParaRevisar(), content.extra_round, over_included, la cola con «quedan/incluidas»-- y lo dejo TODO en PHP. Tres reglas se estaban aplicando sin que nada las respaldara en el esquema: (a) ck_cvw_round no decia DE QUIEN era la correccion, asi que una revision nuestra podia gastarle una ronda al cliente --DEC-133 vivia solo en consumeRonda()--; (b) nada obligaba a over_included a decir la verdad, y esa columna es la que cargosPendientes() cuenta para facturar, o sea que una fila que miente ahi es una correccion que se trabaja y no se cobra; (c) el contador podia bajar, y bajarlo devuelve rondas ya gastadas sin la firma de nadie. tg_cvw_techo mira las DOS direcciones --agotadas sin declarar, y declarada sin estarlo-- y es cross-table, asi que un CHECK no puede verlo; lee el contador ANTES de que emitir() lo suba, que es el mismo valor con el que el servicio calculo su $exceso. Y no se hizo lo tentador: que el contador lo subiera un AFTER INSERT habria hecho imposible la desincronizacion, pero ninguno de los 504 disparadores de este esquema modifica una fila y un disparador que HACE cosas convierte el esquema en algo que actua a espaldas de quien lee el codigo. Habia fecha para esto: 8.5 escribe revisiones del cliente desde un enlace firmado, sin pasar por emitir()</t>
+          <t>Se registra y no se convierte en ronda hasta que alguien del equipo decida si se le cobra o la absorbemos; al cliente se le confirma que su peticion llego --que es verdad-- sin prometerle que sera gratis. Cae solo del modelo de DEC-151: como la respuesta no crea la revision, no hay ronda que consumir hasta que una persona emite el veredicto. Aprobaciones::pendientes() es la lista de lo que espera esa decision. La pantalla de gracias NO dice «lo corregimos»: decirlo seria prometer por su cuenta algo que todavia no esta decidido</t>
         </is>
       </c>
     </row>
     <row r="95" ht="57" customHeight="1" s="36">
       <c r="A95" s="67" t="inlineStr">
         <is>
-          <t>DEC-149</t>
+          <t>DEC-152</t>
         </is>
       </c>
       <c r="B95" s="68" t="inlineStr">
@@ -17752,24 +17802,24 @@
       <c r="C95" s="68" t="n"/>
       <c r="D95" s="69" t="inlineStr">
         <is>
-          <t>Se trabaja en main hasta que haya produccion.</t>
+          <t>El silencio del cliente no hace nada, y por eso 8.5 no estrena comando.</t>
         </is>
       </c>
       <c r="E95" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F95" s="69" t="inlineStr">
         <is>
-          <t>La pregunta fue suya y era la correcta: *«no entiendo el sentido de tener varias ramas si al final haremos merge»*. Medido en el repositorio: main (4.9) -- 5.9 -- 7.6 -- 7.6b -- 7.7 -- 8.1 -- 8.1-8.7 -- 8.8 es una linea recta; nunca hubo dos cosas a la vez. Las tres ramas no eran tres caminos sino tres nombres sobre el mismo camino, y dos apuntaban a puntos ya superados --feat/5.9-4.1-enlace-contrasena es el PADRE de la rama de 7.6, comprobado, no supuesto--. De las cinco cosas para las que sirve una rama, hoy no aplica ninguna: un solo desarrollador, ninguna revision externa, nada desplegado, y el CI que podria opinar antes ya lo hace php tools/diagnostico.php en la maquina. Y el coste si se pagaba: la rama que existia para proteger main lo dejo nueve iteraciones obsoleto, o sea mintiendo a quien clonara. Eso es la ceremonia sin ninguno de los beneficios. Lo que sustituye a la rama no es la confianza, son las seis puertas: no se commitea en rojo. Se revierte el dia que haya produccion, y entonces una rama por iteracion fusionada el mismo dia; lo que no se repite nunca es la rama larga que acumula iteraciones, que no es una rama sino un main con otro nombre. De paso, develop sale del on: push del CI: esa rama no ha existido jamas, y CONTRIBUTING.md la nombraba desde el principio</t>
+          <t>El enlace caduca, la pieza se queda donde estaba y sale en la bandeja. Nadie aprueba ni rechaza en nombre de nadie. «Silencio = aprobado» habria desbloqueado la campana sin perseguir a nadie y necesita estar escrito en el contrato: dar por buena una pieza que nadie miro es una firma que el sistema pone por el cliente, y de ahi cuelgan la publicacion y el pago. Y de ahi sale que no haga falta un comando de caducidad, al reves que en 7.6: alli una invitacion sin contestar dejaba dinero comprometido y una plaza de cupo ocupada --habia un estado del mundo que corregir-- y aqui expires_at &lt; NOW() basta. Un comando que no arregla nada es una linea de cron mas que mantener y una cosa mas que puede fallar en silencio</t>
         </is>
       </c>
     </row>
     <row r="96" ht="57" customHeight="1" s="36">
       <c r="A96" s="67" t="inlineStr">
         <is>
-          <t>DEC-148</t>
+          <t>DEC-151</t>
         </is>
       </c>
       <c r="B96" s="68" t="inlineStr">
@@ -17780,24 +17830,24 @@
       <c r="C96" s="68" t="n"/>
       <c r="D96" s="69" t="inlineStr">
         <is>
-          <t>El entregable caido tiene estado propio, y expired pasa a llamarse fulfilled.</t>
+          <t>La respuesta del cliente se REGISTRA; el equipo cierra.</t>
         </is>
       </c>
       <c r="E96" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="F96" s="69" t="inlineStr">
         <is>
-          <t>Devolver el entregable a published bastaba para que no cobre, y estaba mal: published significa «esperando a que alguien lo mire» y el dia que F9 construya esa cola meteria incumplimientos dentro --un estado que significa dos cosas es el fallo de T-50--. ck_del_status gana removed, y los dos disparadores que definen «entregable cerrado» lo tratan como cerrado; sin eso se le podria subir una version nueva encima o emitir un veredicto sobre el, y el incumplimiento se disolveria solo. Aparte: ck_pub_status tenia expired desde 2.12 con CERO filas y con un nombre que se lee al reves de lo que significa --la ventana cumplida es lo BUENO, es lo que habilita el pago-- asi que se renombra ahora, que no cuesta nada; con mil filas habria costado una migracion de datos y una discusion. De paso, permanence_checks entra en la lista de 3.12: el criterio de T-16 la incluia desde el primer dia --la fila es evidencia y de ella depende dinero-- y nadie la habia mirado</t>
+          <t>El cliente dice «me vale» o «cambiad esto» desde un enlace firmado, y eso queda escrito con su hora y su IP --pero no mueve el entregable--. La alternativa era que su OK aprobara la pieza directamente, y se descarto por dos razones. (a) Habria obligado a partir approved en dos estados: hoy significa «listo para publicar» y 8.6 publica desde ahi, asi que sin un «aprobado interno, esperando al cliente» el mismo estado significaria dos cosas --el fallo de T-50--. (b) Y la que decide: la correccion del cliente gasta ronda, y desde 8.4 una ronda de mas exige firma y decision de facturacion. El cliente no puede firmar un cargo contra si mismo. Si su respuesta moviera la pieza sola, o se le cobraria sin que nadie lo autorizara, o habria que dejarle una puerta por la que las rondas no se cuentan. La pantalla se lo dice con esas palabras: quien pulsa «me vale» y no ve nada moverse tiene derecho a saber que pasa despues</t>
         </is>
       </c>
     </row>
     <row r="97" ht="57" customHeight="1" s="36">
       <c r="A97" s="67" t="inlineStr">
         <is>
-          <t>DEC-147</t>
+          <t>DEC-150</t>
         </is>
       </c>
       <c r="B97" s="68" t="inlineStr">
@@ -17808,24 +17858,24 @@
       <c r="C97" s="68" t="n"/>
       <c r="D97" s="69" t="inlineStr">
         <is>
-          <t>Se avisa al creador y al equipo; al cliente no.</t>
+          <t>El techo de rondas pasa a la base, y los disparadores siguen siendo GUARDAS.</t>
         </is>
       </c>
       <c r="E97" s="69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="F97" s="69" t="inlineStr">
         <is>
-          <t>El creador tiene algo que hacer --reponer el post, decir que la cuenta se puso privada, o decir que lo bajo-- y el equipo lo ve en su bandeja sin que nadie le mande nada. El cliente no se entera hasta que hay algo confirmado: avisarle de un falso positivo cuesta mas que el propio incidente. El correo no dice «incumpliste», dice «no lo encontramos», y dice expresamente que el pago esta en pausa: enterarse de eso cuando no llega el dinero es peor que enterarse ahora</t>
+          <t>8.3 construyo el limite entero --rondas(), vetoParaRevisar(), content.extra_round, over_included, la cola con «quedan/incluidas»-- y lo dejo TODO en PHP. Tres reglas se estaban aplicando sin que nada las respaldara en el esquema: (a) ck_cvw_round no decia DE QUIEN era la correccion, asi que una revision nuestra podia gastarle una ronda al cliente --DEC-133 vivia solo en consumeRonda()--; (b) nada obligaba a over_included a decir la verdad, y esa columna es la que cargosPendientes() cuenta para facturar, o sea que una fila que miente ahi es una correccion que se trabaja y no se cobra; (c) el contador podia bajar, y bajarlo devuelve rondas ya gastadas sin la firma de nadie. tg_cvw_techo mira las DOS direcciones --agotadas sin declarar, y declarada sin estarlo-- y es cross-table, asi que un CHECK no puede verlo; lee el contador ANTES de que emitir() lo suba, que es el mismo valor con el que el servicio calculo su $exceso. Y no se hizo lo tentador: que el contador lo subiera un AFTER INSERT habria hecho imposible la desincronizacion, pero ninguno de los 504 disparadores de este esquema modifica una fila y un disparador que HACE cosas convierte el esquema en algo que actua a espaldas de quien lee el codigo. Habia fecha para esto: 8.5 escribe revisiones del cliente desde un enlace firmado, sin pasar por emitir()</t>
         </is>
       </c>
     </row>
     <row r="98" ht="34.5" customHeight="1" s="36">
       <c r="A98" s="67" t="inlineStr">
         <is>
-          <t>DEC-146</t>
+          <t>DEC-149</t>
         </is>
       </c>
       <c r="B98" s="68" t="inlineStr">
@@ -17836,7 +17886,7 @@
       <c r="C98" s="68" t="n"/>
       <c r="D98" s="69" t="inlineStr">
         <is>
-          <t>La sonda marca; una persona confirma.</t>
+          <t>Se trabaja en main hasta que haya produccion.</t>
         </is>
       </c>
       <c r="E98" s="69" t="inlineStr">
@@ -17846,14 +17896,14 @@
       </c>
       <c r="F98" s="69" t="inlineStr">
         <is>
-          <t>Es DEC-142 otra vez y por lo mismo --Instagram y TikTok responden igual ante un post borrado, un perfil en privado y un bloqueo geografico-- pero aqui duele mas: en 8.7 un falso negativo retrasa una verificacion, aqui acusa a un creador de incumplir un contrato. Asi que Permanencia::anotar() archiva la comprobacion y no toca publications, y lo que mueve una publicacion a removed es una persona con tg_pub_permanencia exigiendole DOS cosas: una comprobacion con is_live = 0 y una captura tomada DESPUES de haber verificado el post. La segunda condicion es la que costo pensar: la captura vieja probo que el post existia, y reutilizarla como prueba de que ya no esta seria archivar lo contrario de lo que ensena. El comando permanencia:vigilar no sale a Internet: cierra ventanas cumplidas --comparar una fecha con el calendario si lo puede hacer solo, y es lo que habilita el pago-- y cuenta las desatendidas. La comprobacion automatica buena son las APIs oficiales, que son F12</t>
+          <t>La pregunta fue suya y era la correcta: *«no entiendo el sentido de tener varias ramas si al final haremos merge»*. Medido en el repositorio: main (4.9) -- 5.9 -- 7.6 -- 7.6b -- 7.7 -- 8.1 -- 8.1-8.7 -- 8.8 es una linea recta; nunca hubo dos cosas a la vez. Las tres ramas no eran tres caminos sino tres nombres sobre el mismo camino, y dos apuntaban a puntos ya superados --feat/5.9-4.1-enlace-contrasena es el PADRE de la rama de 7.6, comprobado, no supuesto--. De las cinco cosas para las que sirve una rama, hoy no aplica ninguna: un solo desarrollador, ninguna revision externa, nada desplegado, y el CI que podria opinar antes ya lo hace php tools/diagnostico.php en la maquina. Y el coste si se pagaba: la rama que existia para proteger main lo dejo nueve iteraciones obsoleto, o sea mintiendo a quien clonara. Eso es la ceremonia sin ninguno de los beneficios. Lo que sustituye a la rama no es la confianza, son las seis puertas: no se commitea en rojo. Se revierte el dia que haya produccion, y entonces una rama por iteracion fusionada el mismo dia; lo que no se repite nunca es la rama larga que acumula iteraciones, que no es una rama sino un main con otro nombre. De paso, develop sale del on: push del CI: esa rama no ha existido jamas, y CONTRIBUTING.md la nombraba desde el principio</t>
         </is>
       </c>
     </row>
     <row r="99" ht="57" customHeight="1" s="36">
       <c r="A99" s="67" t="inlineStr">
         <is>
-          <t>DEC-145</t>
+          <t>DEC-148</t>
         </is>
       </c>
       <c r="B99" s="68" t="inlineStr">
@@ -17864,7 +17914,7 @@
       <c r="C99" s="68" t="n"/>
       <c r="D99" s="69" t="inlineStr">
         <is>
-          <t>Retirar el post antes de tiempo BLOQUEA el pago, y el sistema no descuenta nada.</t>
+          <t>El entregable caido tiene estado propio, y expired pasa a llamarse fulfilled.</t>
         </is>
       </c>
       <c r="E99" s="69" t="inlineStr">
@@ -17874,14 +17924,14 @@
       </c>
       <c r="F99" s="69" t="inlineStr">
         <is>
-          <t>BR-CONTENT-006 decia que el sistema alerta y no decia nada del dinero, que es donde deja de ser tecnico. Las otras dos opciones se descartaron: el descuento proporcional automatico exige que el contrato lo diga por escrito Y que la deteccion sea fiable --y lo segundo hoy no se cumple, ver DEC-146--; solo alertar deja al cliente sin palanca, porque el post se retira, se cobra igual y la unica consecuencia es un correo. Lo que hace: la publicacion pasa a removed con motivo, firma y fecha; el entregable pasa a removed --sale de verified, que es de donde F9 va a pagar--; y ahi se para. La decision de que se le paga la toma una persona con el expediente montado delante. test_firmar_la_caida_para_el_pago_y_no_descuenta_nada afirma las DOS mitades: que el entregable sale de verificado y que el importe acordado sigue intacto. La segunda es la que impide que alguien «mejore» esto manana metiendo una regla de tres</t>
+          <t>Devolver el entregable a published bastaba para que no cobre, y estaba mal: published significa «esperando a que alguien lo mire» y el dia que F9 construya esa cola meteria incumplimientos dentro --un estado que significa dos cosas es el fallo de T-50--. ck_del_status gana removed, y los dos disparadores que definen «entregable cerrado» lo tratan como cerrado; sin eso se le podria subir una version nueva encima o emitir un veredicto sobre el, y el incumplimiento se disolveria solo. Aparte: ck_pub_status tenia expired desde 2.12 con CERO filas y con un nombre que se lee al reves de lo que significa --la ventana cumplida es lo BUENO, es lo que habilita el pago-- asi que se renombra ahora, que no cuesta nada; con mil filas habria costado una migracion de datos y una discusion. De paso, permanence_checks entra en la lista de 3.12: el criterio de T-16 la incluia desde el primer dia --la fila es evidencia y de ella depende dinero-- y nadie la habia mirado</t>
         </is>
       </c>
     </row>
     <row r="100" ht="34.5" customHeight="1" s="36">
       <c r="A100" s="67" t="inlineStr">
         <is>
-          <t>DEC-144</t>
+          <t>DEC-147</t>
         </is>
       </c>
       <c r="B100" s="68" t="inlineStr">
@@ -17892,24 +17942,24 @@
       <c r="C100" s="68" t="n"/>
       <c r="D100" s="69" t="inlineStr">
         <is>
-          <t>Si el post no esta, el entregable vuelve al CREADOR, no a revision.</t>
+          <t>Se avisa al creador y al equipo; al cliente no.</t>
         </is>
       </c>
       <c r="E100" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F100" s="69" t="inlineStr">
         <is>
-          <t>La publicacion queda rejected con su motivo y el entregable vuelve a approved. El contenido no tenia nada malo --ya se aprobo--: lo que falla es que no esta publicado, asi que lo que hay que rehacer es el ENLACE y no la pieza. Reabrir el entregable entero seria mas duro de lo necesario y dejarlo rechazado sin mas deja una campana con una pieza que nadie va a mover. Motivo de lista cerrada, como en 7.6 y 8.2, para poder contestar «.por que se caen las publicaciones?» con un numero. Y se le avisa por correo con el motivo dentro; el correo dice «no lo encontramos» y no «no publicaste», que es la diferencia que importa cuando la cuenta era privada o el enlace se copio mal. Verificar NO manda correo: no le pide nada, su parte termino</t>
+          <t>El creador tiene algo que hacer --reponer el post, decir que la cuenta se puso privada, o decir que lo bajo-- y el equipo lo ve en su bandeja sin que nadie le mande nada. El cliente no se entera hasta que hay algo confirmado: avisarle de un falso positivo cuesta mas que el propio incidente. El correo no dice «incumpliste», dice «no lo encontramos», y dice expresamente que el pago esta en pausa: enterarse de eso cuando no llega el dinero es peor que enterarse ahora</t>
         </is>
       </c>
     </row>
     <row r="101" ht="34.5" customHeight="1" s="36">
       <c r="A101" s="67" t="inlineStr">
         <is>
-          <t>DEC-143</t>
+          <t>DEC-146</t>
         </is>
       </c>
       <c r="B101" s="68" t="inlineStr">
@@ -17920,24 +17970,24 @@
       <c r="C101" s="68" t="n"/>
       <c r="D101" s="69" t="inlineStr">
         <is>
-          <t>Verificar tiene su propio permiso, content.verify.</t>
+          <t>La sonda marca; una persona confirma.</t>
         </is>
       </c>
       <c r="E101" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F101" s="69" t="inlineStr">
         <is>
-          <t>Mismo criterio que separo revisar de aprobar en 8.3: de verified cuelga el pago, asi que es una firma con dinero detras. Lo tienen campaign_manager y content_reviewer; finanzas NO, porque paga contra lo verificado y darle el permiso convertiria una comprobacion en una autoaprobacion. Se comprueba en el POST y no solo escondiendo el boton: los dos veredictos llegan por el mismo formulario</t>
+          <t>Es DEC-142 otra vez y por lo mismo --Instagram y TikTok responden igual ante un post borrado, un perfil en privado y un bloqueo geografico-- pero aqui duele mas: en 8.7 un falso negativo retrasa una verificacion, aqui acusa a un creador de incumplir un contrato. Asi que Permanencia::anotar() archiva la comprobacion y no toca publications, y lo que mueve una publicacion a removed es una persona con tg_pub_permanencia exigiendole DOS cosas: una comprobacion con is_live = 0 y una captura tomada DESPUES de haber verificado el post. La segunda condicion es la que costo pensar: la captura vieja probo que el post existia, y reutilizarla como prueba de que ya no esta seria archivar lo contrario de lo que ensena. El comando permanencia:vigilar no sale a Internet: cierra ventanas cumplidas --comparar una fecha con el calendario si lo puede hacer solo, y es lo que habilita el pago-- y cuenta las desatendidas. La comprobacion automatica buena son las APIs oficiales, que son F12</t>
         </is>
       </c>
     </row>
     <row r="102" ht="57" customHeight="1" s="36">
       <c r="A102" s="67" t="inlineStr">
         <is>
-          <t>DEC-142</t>
+          <t>DEC-145</t>
         </is>
       </c>
       <c r="B102" s="68" t="inlineStr">
@@ -17948,24 +17998,24 @@
       <c r="C102" s="68" t="n"/>
       <c r="D102" s="69" t="inlineStr">
         <is>
-          <t>La evidencia de que un post existe es una CAPTURA, no una comprobacion HTTP.</t>
+          <t>Retirar el post antes de tiempo BLOQUEA el pago, y el sistema no descuenta nada.</t>
         </is>
       </c>
       <c r="E102" s="69" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="F102" s="69" t="inlineStr">
         <is>
-          <t>Tomada con la limitacion delante: Instagram y TikTok devuelven 200 con un muro de login, 403 a todo lo que no sea un navegador, y 200 otra vez cuando el post no existe. Un http_status no distingue «el post existe» de «nos bloquearon», y BR-CONTENT-004 es 🔴 --de verified cuelga el pago--. Asi que lo que se archiva es un screenshot con file_id y tg_pub_verificada_con_evidencia lo impone en la base; la sonda HTTP se guarda como dato complementario y NO decide. Lo que si automatizaria esto son las APIs oficiales --Instagram Graph, TikTok--, que exigen app revisada por Meta y tokens del creador: semanas, y son F12; elegirlas ahora dejaria 8.7, 8.8 y el pago bloqueados hasta entonces. El dia que existan cambia la forma de capturar, no el modelo: publication_evidence ya admite api_snapshot. §56 del prompt maestro pide exactamente esto: no disenar sobre algo extremadamente fragil</t>
+          <t>BR-CONTENT-006 decia que el sistema alerta y no decia nada del dinero, que es donde deja de ser tecnico. Las otras dos opciones se descartaron: el descuento proporcional automatico exige que el contrato lo diga por escrito Y que la deteccion sea fiable --y lo segundo hoy no se cumple, ver DEC-146--; solo alertar deja al cliente sin palanca, porque el post se retira, se cobra igual y la unica consecuencia es un correo. Lo que hace: la publicacion pasa a removed con motivo, firma y fecha; el entregable pasa a removed --sale de verified, que es de donde F9 va a pagar--; y ahi se para. La decision de que se le paga la toma una persona con el expediente montado delante. test_firmar_la_caida_para_el_pago_y_no_descuenta_nada afirma las DOS mitades: que el entregable sale de verificado y que el importe acordado sigue intacto. La segunda es la que impide que alguien «mejore» esto manana metiendo una regla de tres</t>
         </is>
       </c>
     </row>
     <row r="103" ht="68.25" customHeight="1" s="36">
       <c r="A103" s="67" t="inlineStr">
         <is>
-          <t>DEC-141</t>
+          <t>DEC-144</t>
         </is>
       </c>
       <c r="B103" s="68" t="inlineStr">
@@ -17976,24 +18026,24 @@
       <c r="C103" s="68" t="n"/>
       <c r="D103" s="69" t="inlineStr">
         <is>
-          <t>La red se DEDUCE del enlace, y tiene que ser la del brief.</t>
+          <t>Si el post no esta, el entregable vuelve al CREADOR, no a revision.</t>
         </is>
       </c>
       <c r="E103" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F103" s="69" t="inlineStr">
         <is>
-          <t>El brief compro un reel de Instagram; un TikTok no es eso, por bueno que sea. La red no se pregunta --un desplegable en el formulario solo sirve para que alguien elija mal, y el enlace ya lo dice--: sale de platforms.url_pattern, que es una expresion regular y vive en el catalogo desde 2.6 sin que la usara nadie. Si el enlace no es de ninguna red conocida, tampoco entra. Y la huella: uq_pub_fingerprint existe desde la Fase 2 para que dos creadores no reclamen el mismo post, y con la URL cruda no impediria nada --?utm_source=ig basta para esquivarla--. Se normaliza antes de firmar: esquema y host a minusculas, www. fuera, barra final fuera, fragmento fuera, parametros de MEDICION fuera y el resto ordenados. Lo que identifica el post no se toca: la ruta conserva mayusculas --/p/AbC y /p/abc son dos posts-- y la lista de parametros a quitar es explicita, porque youtube.com/watch?v= lleva el identificador en la query y borrar la query entera fundiria todos los videos del canal en una huella. Esa es la mitad que hace dano: rechazar un post legitimo diciendo que ya esta reclamado. La URL se guarda TAL CUAL: la huella es para comparar, no para sustituir</t>
+          <t>La publicacion queda rejected con su motivo y el entregable vuelve a approved. El contenido no tenia nada malo --ya se aprobo--: lo que falla es que no esta publicado, asi que lo que hay que rehacer es el ENLACE y no la pieza. Reabrir el entregable entero seria mas duro de lo necesario y dejarlo rechazado sin mas deja una campana con una pieza que nadie va a mover. Motivo de lista cerrada, como en 7.6 y 8.2, para poder contestar «.por que se caen las publicaciones?» con un numero. Y se le avisa por correo con el motivo dentro; el correo dice «no lo encontramos» y no «no publicaste», que es la diferencia que importa cuando la cuenta era privada o el enlace se copio mal. Verificar NO manda correo: no le pide nada, su parte termino</t>
         </is>
       </c>
     </row>
     <row r="104" ht="34.5" customHeight="1" s="36">
       <c r="A104" s="67" t="inlineStr">
         <is>
-          <t>DEC-140</t>
+          <t>DEC-143</t>
         </is>
       </c>
       <c r="B104" s="68" t="inlineStr">
@@ -18004,24 +18054,24 @@
       <c r="C104" s="68" t="n"/>
       <c r="D104" s="69" t="inlineStr">
         <is>
-          <t>Solo se publica lo aprobado, y ESA version.</t>
+          <t>Verificar tiene su propio permiso, content.verify.</t>
         </is>
       </c>
       <c r="E104" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F104" s="69" t="inlineStr">
         <is>
-          <t>BR-CONTENT-002 dice que nada llega al cliente sin aprobacion interna, y registrar la publicacion de algo no aprobado es darlo por bueno a posteriori con la firma de nadie. No basta con «el entregable esta aprobado»: se guarda QUE version se publico y tiene que ser la aprobada (tg_pub_version_aprobada), porque de esta fila cuelga el pago --8.7 la verifica y 8.8 cuenta su permanencia--. publications.deliverable_version_id es un SNAPSHOT, igual que amount_snapshot en 7.6: registra lo que se publico ENTONCES y sobrevive a que el entregable se reabra y se apruebe otra version despues, asi que se guarda aunque el puntero de 8.2 diga cual es la aprobada de hoy. Su clave ajena es COMPUESTA, como la de 8.2. Detalle que la suite dice en voz alta: al INSERTAR gana el disparador --la version de otro entregable nunca puede ser la aprobada de este-- y donde la clave se ve sola es en un UPDATE, porque el disparador es BEFORE INSERT y no los mira; ahi esta su asercion, y no en un caso inventado que nunca pasa</t>
+          <t>Mismo criterio que separo revisar de aprobar en 8.3: de verified cuelga el pago, asi que es una firma con dinero detras. Lo tienen campaign_manager y content_reviewer; finanzas NO, porque paga contra lo verificado y darle el permiso convertiria una comprobacion en una autoaprobacion. Se comprueba en el POST y no solo escondiendo el boton: los dos veredictos llegan por el mismo formulario</t>
         </is>
       </c>
     </row>
     <row r="105" ht="57" customHeight="1" s="36">
       <c r="A105" s="67" t="inlineStr">
         <is>
-          <t>DEC-139</t>
+          <t>DEC-142</t>
         </is>
       </c>
       <c r="B105" s="68" t="inlineStr">
@@ -18032,24 +18082,24 @@
       <c r="C105" s="68" t="n"/>
       <c r="D105" s="69" t="inlineStr">
         <is>
-          <t>El post lo reporta el CREADOR, y el equipo tambien puede.</t>
+          <t>La evidencia de que un post existe es una CAPTURA, no una comprobacion HTTP.</t>
         </is>
       </c>
       <c r="E105" s="69" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="F105" s="69" t="inlineStr">
         <is>
-          <t>El creador es quien lo sabe primero y quien tiene el enlace en la mano: lo pega en su portal en cuanto publica. Y el equipo puede hacerlo por el, porque el caso real existe --el enlace llega por WhatsApp y el creador no entra--. Las alternativas eran peores por el mismo motivo en direcciones opuestas: solo el equipo convierte cada publicacion en una tarea nuestra --con 150 creadores, 150 tareas que perseguir-- y solo el creador deja sin camino el caso de «me lo mando por WhatsApp». Las dos puertas pasan por el MISMO servicio y el MISMO veto; solo cambia quien firma reported_by_user_id. Una segunda puerta con sus propias reglas es una segunda puerta con sus propios agujeros</t>
+          <t>Tomada con la limitacion delante: Instagram y TikTok devuelven 200 con un muro de login, 403 a todo lo que no sea un navegador, y 200 otra vez cuando el post no existe. Un http_status no distingue «el post existe» de «nos bloquearon», y BR-CONTENT-004 es 🔴 --de verified cuelga el pago--. Asi que lo que se archiva es un screenshot con file_id y tg_pub_verificada_con_evidencia lo impone en la base; la sonda HTTP se guarda como dato complementario y NO decide. Lo que si automatizaria esto son las APIs oficiales --Instagram Graph, TikTok--, que exigen app revisada por Meta y tokens del creador: semanas, y son F12; elegirlas ahora dejaria 8.7, 8.8 y el pago bloqueados hasta entonces. El dia que existan cambia la forma de capturar, no el modelo: publication_evidence ya admite api_snapshot. §56 del prompt maestro pide exactamente esto: no disenar sobre algo extremadamente fragil</t>
         </is>
       </c>
     </row>
     <row r="106" ht="34.5" customHeight="1" s="36">
       <c r="A106" s="67" t="inlineStr">
         <is>
-          <t>DEC-138</t>
+          <t>DEC-141</t>
         </is>
       </c>
       <c r="B106" s="68" t="inlineStr">
@@ -18060,24 +18110,24 @@
       <c r="C106" s="68" t="n"/>
       <c r="D106" s="69" t="inlineStr">
         <is>
-          <t>Un entregable aprobado se puede REABRIR, con motivo de lista cerrada y firma.</t>
+          <t>La red se DEDUCE del enlace, y tiene que ser la del brief.</t>
         </is>
       </c>
       <c r="E106" s="69" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F106" s="69" t="inlineStr">
         <is>
-          <t>Con 8.3 era un callejon sin salida --ni mas veredictos ni mas versiones-- y el cliente cambia de opinion y a veces se aprueba por error: el unico camino cuando eso pasara, y va a pasar, era que alguien tocara la base a mano. Reabrir no deshace nada: es otra fila en content_reviews con outcome='reopened', su motivo y su firma, y la aprobacion anterior se queda en el historial. Misma forma que la anulacion de un perfil fiscal en 3.11, y por la misma razon: el registro tiene que contestar «.que paso?» y no solo «.como esta ahora?». El motivo es de lista cerrada para poder contestar «.por que se reabren las piezas?» con un numero --si el 70% es «se aprobo por error», el problema es la pantalla de revision y no el cliente-- y «otro» exige explicacion, porque «otro» sin explicar es la casilla que se marca para poder seguir. El permiso lo tienen los DOS roles que revisan: «se aprobo por error» lo descubre normalmente quien aprobo, y obligarle a pedirselo a otro convierte un clic en un correo --y en la practica, en que nadie lo arregle--. Reabrir no gasta ronda: la gasta pedir un cambio, y aqui todavia no se ha pedido ninguno</t>
+          <t>El brief compro un reel de Instagram; un TikTok no es eso, por bueno que sea. La red no se pregunta --un desplegable en el formulario solo sirve para que alguien elija mal, y el enlace ya lo dice--: sale de platforms.url_pattern, que es una expresion regular y vive en el catalogo desde 2.6 sin que la usara nadie. Si el enlace no es de ninguna red conocida, tampoco entra. Y la huella: uq_pub_fingerprint existe desde la Fase 2 para que dos creadores no reclamen el mismo post, y con la URL cruda no impediria nada --?utm_source=ig basta para esquivarla--. Se normaliza antes de firmar: esquema y host a minusculas, www. fuera, barra final fuera, fragmento fuera, parametros de MEDICION fuera y el resto ordenados. Lo que identifica el post no se toca: la ruta conserva mayusculas --/p/AbC y /p/abc son dos posts-- y la lista de parametros a quitar es explicita, porque youtube.com/watch?v= lleva el identificador en la query y borrar la query entera fundiria todos los videos del canal en una huella. Esa es la mitad que hace dano: rechazar un post legitimo diciendo que ya esta reclamado. La URL se guarda TAL CUAL: la huella es para comparar, no para sustituir</t>
         </is>
       </c>
     </row>
     <row r="107" ht="45.75" customHeight="1" s="36">
       <c r="A107" s="67" t="inlineStr">
         <is>
-          <t>DEC-137</t>
+          <t>DEC-140</t>
         </is>
       </c>
       <c r="B107" s="68" t="inlineStr">
@@ -18088,24 +18138,24 @@
       <c r="C107" s="68" t="n"/>
       <c r="D107" s="69" t="inlineStr">
         <is>
-          <t>El puntero apunta a la version APROBADA, y su clave ajena es COMPUESTA.</t>
+          <t>Solo se publica lo aprobado, y ESA version.</t>
         </is>
       </c>
       <c r="E107" s="69" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F107" s="69" t="inlineStr">
         <is>
-          <t>«La ultima» sale de un MAX(version_number) y guardarla seria una copia que se puede desviar --el proyecto acaba de quitar una columna por eso mismo, el contador de rondas de 8.3--. La aprobada no es derivable sin recorrer content_reviews, y es el dato del que cuelgan 8.6 --se publica lo aprobado-- y 8.7 --se archiva evidencia de eso--; sin ella las dos tendrian que adivinar cual. Y ahi esta casi todo el valor: FOREIGN KEY (approved_version_id, id) REFERENCES deliverable_versions(id, deliverable_id). Una clave simple garantizaria que la version EXISTE; esta garantiza que es DE ESTE ENTREGABLE --sin la segunda columna, un UPDATE mal escrito deja el entregable de Ana apuntando a la version aprobada del de Luis y la fila sigue siendo valida--. Mismo patron que fk_ccr_market_campaign (7.3). Ademas impide borrar la version apuntada mientras siga aprobada, y ck_del_approved_version exige que aprobado y puntero vayan juntos o no vayan: un dato que a veces esta es igual de util que no tenerlo. La columna espero dos iteraciones a proposito: antes de 8.3 no habia nadie que la escribiera, y habria sido el sexto caso de una columna que existe y no tiene una sola fila</t>
+          <t>BR-CONTENT-002 dice que nada llega al cliente sin aprobacion interna, y registrar la publicacion de algo no aprobado es darlo por bueno a posteriori con la firma de nadie. No basta con «el entregable esta aprobado»: se guarda QUE version se publico y tiene que ser la aprobada (tg_pub_version_aprobada), porque de esta fila cuelga el pago --8.7 la verifica y 8.8 cuenta su permanencia--. publications.deliverable_version_id es un SNAPSHOT, igual que amount_snapshot en 7.6: registra lo que se publico ENTONCES y sobrevive a que el entregable se reabra y se apruebe otra version despues, asi que se guarda aunque el puntero de 8.2 diga cual es la aprobada de hoy. Su clave ajena es COMPUESTA, como la de 8.2. Detalle que la suite dice en voz alta: al INSERTAR gana el disparador --la version de otro entregable nunca puede ser la aprobada de este-- y donde la clave se ve sola es en un UPDATE, porque el disparador es BEFORE INSERT y no los mira; ahi esta su asercion, y no en un caso inventado que nunca pasa</t>
         </is>
       </c>
     </row>
     <row r="108" ht="57" customHeight="1" s="36">
       <c r="A108" s="67" t="inlineStr">
         <is>
-          <t>DEC-136</t>
+          <t>DEC-139</t>
         </is>
       </c>
       <c r="B108" s="68" t="inlineStr">
@@ -18116,24 +18166,24 @@
       <c r="C108" s="68" t="n"/>
       <c r="D108" s="69" t="inlineStr">
         <is>
-          <t>Tres permisos y no uno: revisar, aprobar y autorizar una ronda de mas.</t>
+          <t>El post lo reporta el CREADOR, y el equipo tambien puede.</t>
         </is>
       </c>
       <c r="E108" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="F108" s="69" t="inlineStr">
         <is>
-          <t>content.review abre la cola y pide cambios; content.approve da el visto bueno --lo que deja el contenido listo para el cliente y, con F9, lo que dispara el pago--; content.extra_round autoriza el cargo. Mismo criterio que separo capturar de aprobar en el perfil fiscal (DEC-062). content_reviewer tiene los dos primeros y no el tercero: esa decision es de dinero --o se le cobra al cliente o se come el margen-- y quien revisa contenido no tiene por que cargar con ella; la tiene campaign_manager, que responde del margen y es quien va a tener que explicarsela al cliente. Los tres se comprueban en el POST y no solo en la ruta: los tres botones llegan por el mismo formulario, y esconder un boton no es una regla de autorizacion. Y la cola es una BANDEJA GLOBAL, no una por campana: revisar es trabajo por lotes, y una cola por campana obliga a recorrer campanas para descubrir si hay algo esperando --lo que se descubre recorriendo se descubre tarde--. Ordenada por lo que lleva mas esperando y no por lo que vence antes, que es como una cola deja a alguien esperando para siempre</t>
+          <t>El creador es quien lo sabe primero y quien tiene el enlace en la mano: lo pega en su portal en cuanto publica. Y el equipo puede hacerlo por el, porque el caso real existe --el enlace llega por WhatsApp y el creador no entra--. Las alternativas eran peores por el mismo motivo en direcciones opuestas: solo el equipo convierte cada publicacion en una tarea nuestra --con 150 creadores, 150 tareas que perseguir-- y solo el creador deja sin camino el caso de «me lo mando por WhatsApp». Las dos puertas pasan por el MISMO servicio y el MISMO veto; solo cambia quien firma reported_by_user_id. Una segunda puerta con sus propias reglas es una segunda puerta con sus propios agujeros</t>
         </is>
       </c>
     </row>
     <row r="109" ht="45.75" customHeight="1" s="36">
       <c r="A109" s="67" t="inlineStr">
         <is>
-          <t>DEC-135</t>
+          <t>DEC-138</t>
         </is>
       </c>
       <c r="B109" s="68" t="inlineStr">
@@ -18144,24 +18194,24 @@
       <c r="C109" s="68" t="n"/>
       <c r="D109" s="69" t="inlineStr">
         <is>
-          <t>Pasarse de las rondas incluidas se BLOQUEA y exige decidir y firmar; y el cargo NO va a campaign_costs.</t>
+          <t>Un entregable aprobado se puede REABRIR, con motivo de lista cerrada y firma.</t>
         </is>
       </c>
       <c r="E109" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="F109" s="69" t="inlineStr">
         <is>
-          <t>No un aviso: un aviso que se puede saltar acaba en un cargo que se descubre al facturar, que es tarde para discutirlo con el cliente. Cuando la ronda que se va a pedir es la tercera de dos incluidas hay que decir si se cobra o se absorbe, y quien lo dice queda en authorized_by_user_id (ck_cvw_over, en la base y no solo en la pantalla). campaign_costs seria el sitio equivocado y era tentador: es lo que gastamos NOSOTROS y resta del margen (BR-FIN-011), mientras que una ronda de mas facturada al cliente es INGRESO --meterla ahi bajaria el margen de una campana que acaba de ganar dinero--. Aqui queda la decision y la pantalla de entregables la ensena como pendiente de facturar; donde acaba la linea cuando exista F9 es Q-57, y se decide con invoice_lines delante</t>
+          <t>Con 8.3 era un callejon sin salida --ni mas veredictos ni mas versiones-- y el cliente cambia de opinion y a veces se aprueba por error: el unico camino cuando eso pasara, y va a pasar, era que alguien tocara la base a mano. Reabrir no deshace nada: es otra fila en content_reviews con outcome='reopened', su motivo y su firma, y la aprobacion anterior se queda en el historial. Misma forma que la anulacion de un perfil fiscal en 3.11, y por la misma razon: el registro tiene que contestar «.que paso?» y no solo «.como esta ahora?». El motivo es de lista cerrada para poder contestar «.por que se reabren las piezas?» con un numero --si el 70% es «se aprobo por error», el problema es la pantalla de revision y no el cliente-- y «otro» exige explicacion, porque «otro» sin explicar es la casilla que se marca para poder seguir. El permiso lo tienen los DOS roles que revisan: «se aprobo por error» lo descubre normalmente quien aprobo, y obligarle a pedirselo a otro convierte un clic en un correo --y en la practica, en que nadie lo arregle--. Reabrir no gasta ronda: la gasta pedir un cambio, y aqui todavia no se ha pedido ninguno</t>
         </is>
       </c>
     </row>
     <row r="110" ht="34.5" customHeight="1" s="36">
       <c r="A110" s="67" t="inlineStr">
         <is>
-          <t>DEC-134</t>
+          <t>DEC-137</t>
         </is>
       </c>
       <c r="B110" s="68" t="inlineStr">
@@ -18172,24 +18222,24 @@
       <c r="C110" s="68" t="n"/>
       <c r="D110" s="69" t="inlineStr">
         <is>
-          <t>Hasta 8.5, quien lleva la cuenta marca de parte de quien viene la correccion.</t>
+          <t>El puntero apunta a la version APROBADA, y su clave ajena es COMPUESTA.</t>
         </is>
       </c>
       <c r="E110" s="69" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="F110" s="69" t="inlineStr">
         <is>
-          <t>El portal del cliente es 8.5. Sin esto, en 8.3 nada consumiria ronda y el veto de «rondas agotadas» naceria muerto: el QUINTO caso de una regla escrita sobre una tabla vacia en un proyecto que ya lleva cuatro (campaign_creators en 7.4, domain_events en 4.13, invitations en 7.6, deliverables en 8.1). La salida no es inventarse el portal: es reconocer como trabaja una agencia HOY --el ejecutivo traslada el comentario del cliente y marca que es suyo--. En 8.5 el enlace firmado escribe la misma fila sin intermediario y Revisiones no se entera. Quien traslada queda anotado igual en reviewer_user_id: quien la escribio responde de ella. Y ck_cvw_firma exige usuario solo en las NUESTRAS, porque la del cliente en 8.5 no tendra cuenta detras</t>
+          <t>«La ultima» sale de un MAX(version_number) y guardarla seria una copia que se puede desviar --el proyecto acaba de quitar una columna por eso mismo, el contador de rondas de 8.3--. La aprobada no es derivable sin recorrer content_reviews, y es el dato del que cuelgan 8.6 --se publica lo aprobado-- y 8.7 --se archiva evidencia de eso--; sin ella las dos tendrian que adivinar cual. Y ahi esta casi todo el valor: FOREIGN KEY (approved_version_id, id) REFERENCES deliverable_versions(id, deliverable_id). Una clave simple garantizaria que la version EXISTE; esta garantiza que es DE ESTE ENTREGABLE --sin la segunda columna, un UPDATE mal escrito deja el entregable de Ana apuntando a la version aprobada del de Luis y la fila sigue siendo valida--. Mismo patron que fk_ccr_market_campaign (7.3). Ademas impide borrar la version apuntada mientras siga aprobada, y ck_del_approved_version exige que aprobado y puntero vayan juntos o no vayan: un dato que a veces esta es igual de util que no tenerlo. La columna espero dos iteraciones a proposito: antes de 8.3 no habia nadie que la escribiera, y habria sido el sexto caso de una columna que existe y no tiene una sola fila</t>
         </is>
       </c>
     </row>
     <row r="111" ht="57" customHeight="1" s="36">
       <c r="A111" s="67" t="inlineStr">
         <is>
-          <t>DEC-133</t>
+          <t>DEC-136</t>
         </is>
       </c>
       <c r="B111" s="68" t="inlineStr">
@@ -18200,7 +18250,7 @@
       <c r="C111" s="68" t="n"/>
       <c r="D111" s="69" t="inlineStr">
         <is>
-          <t>Solo las rondas del CLIENTE cuentan contra el precio, y son POR ENTREGABLE.</t>
+          <t>Tres permisos y no uno: revisar, aprobar y autorizar una ronda de mas.</t>
         </is>
       </c>
       <c r="E111" s="69" t="inlineStr">
@@ -18210,14 +18260,14 @@
       </c>
       <c r="F111" s="69" t="inlineStr">
         <is>
-          <t>Dos cosas en una porque las dos las decidio la misma conversacion. (1) Que nuestro equipo le pida al creador rehacer el encuadre antes de ensenarselo a nadie es control de calidad NUESTRO; cobrarselo al cliente seria cobrarle nuestro propio error. reviewer_side distinguia platform de client desde la Fase 2 y lo que faltaba era que alguien lo usara. (2) revision_rounds_used vivia en campaign_creators --dos rondas POR CREADOR--, asi que con un creador que entrega dos reels y tres stories, dos correcciones sobre el primer reel dejaban las otras cuatro piezas sin ninguna ronda, y el cliente habia pagado dos por cada una. Baja a deliverables, que es donde se aplica la regla. Y la columna vieja se va, no se queda como suma: una suma almacenada que nadie recalcula se desvia en silencio, y la suma por creador --la que alimenta el Creator Score-- sale de content_reviews con un SUM() que nunca miente. Tenia cero filas: quitarla hoy es gratis y dentro de tres meses no</t>
+          <t>content.review abre la cola y pide cambios; content.approve da el visto bueno --lo que deja el contenido listo para el cliente y, con F9, lo que dispara el pago--; content.extra_round autoriza el cargo. Mismo criterio que separo capturar de aprobar en el perfil fiscal (DEC-062). content_reviewer tiene los dos primeros y no el tercero: esa decision es de dinero --o se le cobra al cliente o se come el margen-- y quien revisa contenido no tiene por que cargar con ella; la tiene campaign_manager, que responde del margen y es quien va a tener que explicarsela al cliente. Los tres se comprueban en el POST y no solo en la ruta: los tres botones llegan por el mismo formulario, y esconder un boton no es una regla de autorizacion. Y la cola es una BANDEJA GLOBAL, no una por campana: revisar es trabajo por lotes, y una cola por campana obliga a recorrer campanas para descubrir si hay algo esperando --lo que se descubre recorriendo se descubre tarde--. Ordenada por lo que lleva mas esperando y no por lo que vence antes, que es como una cola deja a alguien esperando para siempre</t>
         </is>
       </c>
     </row>
     <row r="112" ht="45.75" customHeight="1" s="36">
       <c r="A112" s="67" t="inlineStr">
         <is>
-          <t>DEC-132</t>
+          <t>DEC-135</t>
         </is>
       </c>
       <c r="B112" s="68" t="inlineStr">
@@ -18228,24 +18278,24 @@
       <c r="C112" s="68" t="n"/>
       <c r="D112" s="69" t="inlineStr">
         <is>
-          <t>Si al caption le faltan las etiquetas del brief, NO SE ENVIA, y se le dice cuales.</t>
+          <t>Pasarse de las rondas incluidas se BLOQUEA y exige decidir y firmar; y el cargo NO va a campaign_costs.</t>
         </is>
       </c>
       <c r="E112" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F112" s="69" t="inlineStr">
         <is>
-          <t>Comprobacion objetiva y barata que ahorra una ronda de correccion entera: el creador lo arregla en diez segundos en vez de enterarse tres dias despues. Avisar y dejar pasar acaba siempre en un aviso que nadie lee; dejarlo para la revision traslada a una persona la clase de tarea que una maquina hace mejor. Sin distinguir mayusculas --#ACMEVerano y #acmeverano son el mismo hashtag para las plataformas, y rechazar por la caja seria rechazar por algo que da igual-- y devolviendo todos los motivos a la vez, porque quien entrega desde el movil prefiere una lista de tres cosas que arreglar a tres intentos</t>
+          <t>No un aviso: un aviso que se puede saltar acaba en un cargo que se descubre al facturar, que es tarde para discutirlo con el cliente. Cuando la ronda que se va a pedir es la tercera de dos incluidas hay que decir si se cobra o se absorbe, y quien lo dice queda en authorized_by_user_id (ck_cvw_over, en la base y no solo en la pantalla). campaign_costs seria el sitio equivocado y era tentador: es lo que gastamos NOSOTROS y resta del margen (BR-FIN-011), mientras que una ronda de mas facturada al cliente es INGRESO --meterla ahi bajaria el margen de una campana que acaba de ganar dinero--. Aqui queda la decision y la pantalla de entregables la ensena como pendiente de facturar; donde acaba la linea cuando exista F9 es Q-57, y se decide con invoice_lines delante</t>
         </is>
       </c>
     </row>
     <row r="113" ht="68.25" customHeight="1" s="36">
       <c r="A113" s="67" t="inlineStr">
         <is>
-          <t>DEC-131</t>
+          <t>DEC-134</t>
         </is>
       </c>
       <c r="B113" s="68" t="inlineStr">
@@ -18256,24 +18306,24 @@
       <c r="C113" s="68" t="n"/>
       <c r="D113" s="69" t="inlineStr">
         <is>
-          <t>Se entrega un ENLACE externo, y opcionalmente una imagen.</t>
+          <t>Hasta 8.5, quien lleva la cuenta marca de parte de quien viene la correccion.</t>
         </is>
       </c>
       <c r="E113" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F113" s="69" t="inlineStr">
         <is>
-          <t>El contenido de verdad --un reel de 80 MB-- no sube aqui y no deberia: el creador ya lo tiene en Drive o en la propia plataforma, y almacenarlo otra vez es coste y responsabilidad sin contrapartida. Se guarda el enlace, obligatoriamente https://, mas una imagen de referencia opcional por Almacen (10 MB). El https:// se comprueba en tres sitios a proposito: EntregarRequest da el mensaje junto al campo, vetoParaEntregar() lo da junto a los demas motivos, y ck_dv_url_https impide la fila venga de donde venga. Sin el tercero, un comando o un import mete javascript:alert(1) en una columna que una vista pinta dentro de un href; sin el segundo, el creador ve un 3819</t>
+          <t>El portal del cliente es 8.5. Sin esto, en 8.3 nada consumiria ronda y el veto de «rondas agotadas» naceria muerto: el QUINTO caso de una regla escrita sobre una tabla vacia en un proyecto que ya lleva cuatro (campaign_creators en 7.4, domain_events en 4.13, invitations en 7.6, deliverables en 8.1). La salida no es inventarse el portal: es reconocer como trabaja una agencia HOY --el ejecutivo traslada el comentario del cliente y marca que es suyo--. En 8.5 el enlace firmado escribe la misma fila sin intermediario y Revisiones no se entera. Quien traslada queda anotado igual en reviewer_user_id: quien la escribio responde de ella. Y ck_cvw_firma exige usuario solo en las NUESTRAS, porque la del cliente en 8.5 no tendra cuenta detras</t>
         </is>
       </c>
     </row>
     <row r="114" ht="57" customHeight="1" s="36">
       <c r="A114" s="67" t="inlineStr">
         <is>
-          <t>DEC-130</t>
+          <t>DEC-133</t>
         </is>
       </c>
       <c r="B114" s="68" t="inlineStr">
@@ -18284,24 +18334,24 @@
       <c r="C114" s="68" t="n"/>
       <c r="D114" s="69" t="inlineStr">
         <is>
-          <t>El brief que se usa es el EFECTIVO, no el general.</t>
+          <t>Solo las rondas del CLIENTE cuentan contra el precio, y son POR ENTREGABLE.</t>
         </is>
       </c>
       <c r="E114" s="69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="F114" s="69" t="inlineStr">
         <is>
-          <t>Mercados::briefEfectivo(), que ya resolvia N-03: si el mercado del creador tiene brief propio, ese REEMPLAZA al general. Un creador peruano en una campana con brief especifico para Peru recibe el de Peru, y las etiquetas tambien --que es justo por lo que 7.2 dejo los hashtags fuera hasta que existieran los mercados--. Un entregable generado del brief general cuando hay uno de mercado le pide al creador lo que la campana NO quiere de el, y el error solo se ve al revisar</t>
+          <t>Dos cosas en una porque las dos las decidio la misma conversacion. (1) Que nuestro equipo le pida al creador rehacer el encuadre antes de ensenarselo a nadie es control de calidad NUESTRO; cobrarselo al cliente seria cobrarle nuestro propio error. reviewer_side distinguia platform de client desde la Fase 2 y lo que faltaba era que alguien lo usara. (2) revision_rounds_used vivia en campaign_creators --dos rondas POR CREADOR--, asi que con un creador que entrega dos reels y tres stories, dos correcciones sobre el primer reel dejaban las otras cuatro piezas sin ninguna ronda, y el cliente habia pagado dos por cada una. Baja a deliverables, que es donde se aplica la regla. Y la columna vieja se va, no se queda como suma: una suma almacenada que nadie recalcula se desvia en silencio, y la suma por creador --la que alimenta el Creator Score-- sale de content_reviews con un SUM() que nunca miente. Tenia cero filas: quitarla hoy es gratis y dentro de tres meses no</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="36">
       <c r="A115" s="67" t="inlineStr">
         <is>
-          <t>DEC-129</t>
+          <t>DEC-132</t>
         </is>
       </c>
       <c r="B115" s="68" t="inlineStr">
@@ -18312,7 +18362,7 @@
       <c r="C115" s="68" t="n"/>
       <c r="D115" s="69" t="inlineStr">
         <is>
-          <t>Los entregables se generan SOLOS al aceptar, y la generacion es idempotente.</t>
+          <t>Si al caption le faltan las etiquetas del brief, NO SE ENVIA, y se le dice cuales.</t>
         </is>
       </c>
       <c r="E115" s="69" t="inlineStr">
@@ -18322,14 +18372,14 @@
       </c>
       <c r="F115" s="69" t="inlineStr">
         <is>
-          <t>El brief ya lo dice todo --cuantos, de que formato, con cuantos dias de plazo--, asi que pedirle a alguien que lo teclee otra vez por cada creador es pedirle que copie un dato que el sistema ya tiene. Lo que decide no es el ahorro sino el MODO DE FALLO: si se teclea a mano, el dia que se olvide ese creador no tiene nada que entregar y nadie se entera hasta que la campana termina sin su contenido; si se generan solos, el fallo es que sobra un entregable y se ve en la lista. Va por evento (campaign_creator.accepted --&gt; GenerarEntregables) y no dentro de aceptar(), porque Campaign no puede conocer Content: la misma frontera que se cobro el panel de 7.7. Idempotente porque aceptar dos veces no puede pasar --el enlace es de un solo uso-- pero una reanudacion de la cola o un reintento manual si, y duplicar el trabajo de un creador es la clase de error que se descubre tarde y mal</t>
+          <t>Comprobacion objetiva y barata que ahorra una ronda de correccion entera: el creador lo arregla en diez segundos en vez de enterarse tres dias despues. Avisar y dejar pasar acaba siempre en un aviso que nadie lee; dejarlo para la revision traslada a una persona la clase de tarea que una maquina hace mejor. Sin distinguir mayusculas --#ACMEVerano y #acmeverano son el mismo hashtag para las plataformas, y rechazar por la caja seria rechazar por algo que da igual-- y devolviendo todos los motivos a la vez, porque quien entrega desde el movil prefiere una lista de tres cosas que arreglar a tres intentos</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="36">
       <c r="A116" s="67" t="inlineStr">
         <is>
-          <t>DEC-128</t>
+          <t>DEC-131</t>
         </is>
       </c>
       <c r="B116" s="68" t="inlineStr">
@@ -18340,24 +18390,24 @@
       <c r="C116" s="68" t="n"/>
       <c r="D116" s="69" t="inlineStr">
         <is>
-          <t>En el seguimiento, el dinero SI y el margen solo con su permiso.</t>
+          <t>Se entrega un ENLACE externo, y opcionalmente una imagen.</t>
         </is>
       </c>
       <c r="E116" s="69" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F116" s="69" t="inlineStr">
         <is>
-          <t>Presupuesto, comprometido y disponible los ve quien puede ver la campana: sin esos tres numeros no se decide a quien invitar, y ponerlos detras de un permiso que entonces necesitaria todo el mundo seria un permiso que no protege nada. El margen sigue detras de campaign.view_margin (BR-FIN-007) y no se calcula y luego se esconde: no se calcula --un dato que llega a la vista es un dato que un @if mal puesto puede ensenar, y BR-SEC-001 es 🔴--. La diferencia no es sutil: lo comprometido es lo que se le paga a los creadores; el margen es lo que gana la empresa. Y el disponible se ensena NEGATIVO cuando lo es: redondearlo a cero esconderia justo el caso que hay que ver, una campana que se paso porque finanzas lo autorizo</t>
+          <t>El contenido de verdad --un reel de 80 MB-- no sube aqui y no deberia: el creador ya lo tiene en Drive o en la propia plataforma, y almacenarlo otra vez es coste y responsabilidad sin contrapartida. Se guarda el enlace, obligatoriamente https://, mas una imagen de referencia opcional por Almacen (10 MB). El https:// se comprueba en tres sitios a proposito: EntregarRequest da el mensaje junto al campo, vetoParaEntregar() lo da junto a los demas motivos, y ck_dv_url_https impide la fila venga de donde venga. Sin el tercero, un comando o un import mete javascript:alert(1) en una columna que una vista pinta dentro de un href; sin el segundo, el creador ve un 3819</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="36">
       <c r="A117" s="67" t="inlineStr">
         <is>
-          <t>DEC-127</t>
+          <t>DEC-130</t>
         </is>
       </c>
       <c r="B117" s="68" t="inlineStr">
@@ -18368,24 +18418,24 @@
       <c r="C117" s="68" t="n"/>
       <c r="D117" s="69" t="inlineStr">
         <is>
-          <t>Cuatro alertas en el panel de seguimiento, y su orden NO es por gravedad.</t>
+          <t>El brief que se usa es el EFECTIVO, no el general.</t>
         </is>
       </c>
       <c r="E117" s="69" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F117" s="69" t="inlineStr">
         <is>
-          <t>Campana sin confirmar con el arranque a menos de 14 dias, preguntas de creadores sin atender, invitaciones que caducan en menos de 12 h, y cupo de mercado sin cubrir. La de «sin confirmar» va PRIMERA porque bloquea a las demas: sin confirmar no se puede invitar a nadie, asi que un cupo corto ahi no se arregla reclutando. Y las preguntas van antes que las invitaciones urgentes porque un creador que pregunto y no recibe respuesta MIENTRAS su plazo corre es la combinacion exacta que convierte un si en un silencio. Cada alerta dice que pasa y que hacer: una que solo dice que hay un problema obliga a buscarlo, y entonces deja de leerse. Y «cubierto» es ACEPTADO, no invitado: una invitacion sin contestar es una plaza esperando, y contarla como cubierta es como se llega al dia de arranque con la mitad del equipo y los numeros en verde</t>
+          <t>Mercados::briefEfectivo(), que ya resolvia N-03: si el mercado del creador tiene brief propio, ese REEMPLAZA al general. Un creador peruano en una campana con brief especifico para Peru recibe el de Peru, y las etiquetas tambien --que es justo por lo que 7.2 dejo los hashtags fuera hasta que existieran los mercados--. Un entregable generado del brief general cuando hay uno de mercado le pide al creador lo que la campana NO quiere de el, y el error solo se ve al revisar</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="36">
       <c r="A118" s="67" t="inlineStr">
         <is>
-          <t>DEC-126</t>
+          <t>DEC-129</t>
         </is>
       </c>
       <c r="B118" s="68" t="inlineStr">
@@ -18396,24 +18446,24 @@
       <c r="C118" s="68" t="n"/>
       <c r="D118" s="69" t="inlineStr">
         <is>
-          <t>usuarios:crear deja de teclear la contrasena; el alta interna usa el mismo enlace de 72 h que la del creador.</t>
+          <t>Los entregables se generan SOLOS al aceptar, y la generacion es idempotente.</t>
         </is>
       </c>
       <c r="E118" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F118" s="69" t="inlineStr">
         <is>
-          <t>Cierra BR-SEC-004 (🔴) del todo. must_change_password era el parche: obligaba a cambiarla DESPUES y dejaba una ventana --de minutos o de meses-- en la que dos personas conocian la credencial, y justo en las cuentas donde la base exige dos personas distintas para el dinero. Ahora no hay ventana: la contrasena no existe hasta que la escribe su dueno. usuarios:contrasena --enlace hace lo mismo para reponer y no toca la contrasena actual --si el correo no llega, la persona no se queda peor de como estaba--. Teclearla a mano sigue existiendo a proposito, como cristal de emergencia para cuando el correo no sale (Q-20), y el comando avisa cada vez de que ese es el camino excepcional</t>
+          <t>El brief ya lo dice todo --cuantos, de que formato, con cuantos dias de plazo--, asi que pedirle a alguien que lo teclee otra vez por cada creador es pedirle que copie un dato que el sistema ya tiene. Lo que decide no es el ahorro sino el MODO DE FALLO: si se teclea a mano, el dia que se olvide ese creador no tiene nada que entregar y nadie se entera hasta que la campana termina sin su contenido; si se generan solos, el fallo es que sobra un entregable y se ve en la lista. Va por evento (campaign_creator.accepted --&gt; GenerarEntregables) y no dentro de aceptar(), porque Campaign no puede conocer Content: la misma frontera que se cobro el panel de 7.7. Idempotente porque aceptar dos veces no puede pasar --el enlace es de un solo uso-- pero una reanudacion de la cola o un reintento manual si, y duplicar el trabajo de un creador es la clase de error que se descubre tarde y mal</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="36">
       <c r="A119" s="67" t="inlineStr">
         <is>
-          <t>DEC-125</t>
+          <t>DEC-128</t>
         </is>
       </c>
       <c r="B119" s="68" t="inlineStr">
@@ -18424,24 +18474,24 @@
       <c r="C119" s="68" t="n"/>
       <c r="D119" s="69" t="inlineStr">
         <is>
-          <t>Cuando un creador contesta, se avisa a QUIEN LE INVITO y a nadie mas.</t>
+          <t>En el seguimiento, el dinero SI y el margen solo con su permiso.</t>
         </is>
       </c>
       <c r="E119" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="F119" s="69" t="inlineStr">
         <is>
-          <t>Es quien espera la respuesta y quien va a hacer algo con ella. Avisar a todo el equipo son cuarenta correos por campana a cada uno, y un buzon asi se filtra a una carpeta y deja de leerse --la forma cara de no avisar a nadie--. El precio, dicho: una invitacion mandada por alguien que luego se va de la empresa queda MUDA. A una cuenta desactivada no se le escribe: no avisa a nadie y puede acabar en un buzon reasignado. El hecho no se pierde, queda en domain_events y se ve en la lista</t>
+          <t>Presupuesto, comprometido y disponible los ve quien puede ver la campana: sin esos tres numeros no se decide a quien invitar, y ponerlos detras de un permiso que entonces necesitaria todo el mundo seria un permiso que no protege nada. El margen sigue detras de campaign.view_margin (BR-FIN-007) y no se calcula y luego se esconde: no se calcula --un dato que llega a la vista es un dato que un @if mal puesto puede ensenar, y BR-SEC-001 es 🔴--. La diferencia no es sutil: lo comprometido es lo que se le paga a los creadores; el margen es lo que gana la empresa. Y el disponible se ensena NEGATIVO cuando lo es: redondearlo a cero esconderia justo el caso que hay que ver, una campana que se paso porque finanzas lo autorizo</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="36">
       <c r="A120" s="67" t="inlineStr">
         <is>
-          <t>DEC-124</t>
+          <t>DEC-127</t>
         </is>
       </c>
       <c r="B120" s="68" t="inlineStr">
@@ -18452,24 +18502,24 @@
       <c r="C120" s="68" t="n"/>
       <c r="D120" s="69" t="inlineStr">
         <is>
-          <t>Preguntar NO mueve el plazo de la invitacion.</t>
+          <t>Cuatro alertas en el panel de seguimiento, y su orden NO es por gravedad.</t>
         </is>
       </c>
       <c r="E120" s="69" t="inlineStr">
         <is>
-          <t>7.6b</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="F120" s="69" t="inlineStr">
         <is>
-          <t>La alternativa --congelarla hasta que alguien conteste-- deja el importe comprometido para siempre si nadie contesta, que es justo el agujero que invitaciones:caducar existe para tapar. La pantalla se lo dice al creador con todas las letras: callarlo dejaria a alguien esperando tranquilo mientras su invitacion caduca, que es peor que no dejarle preguntar. Quien invito ve la pregunta en la lista de candidatos y decide; si hace falta mas tiempo, anula y manda otra. Y no hay respuesta dentro de la aplicacion: el equipo contesta por correo, que es donde el creador ya esta. Un hilo de ida y vuelta es un modulo de mensajeria --notificaciones, no leidos, permisos-- y habria multiplicado por tres la iteracion para resolver lo que un boton de «Responder» ya resuelve. Lo que si hay es un DUENO: «me hago cargo» marca quien atiende y el segundo clic no pisa al primero</t>
+          <t>Campana sin confirmar con el arranque a menos de 14 dias, preguntas de creadores sin atender, invitaciones que caducan en menos de 12 h, y cupo de mercado sin cubrir. La de «sin confirmar» va PRIMERA porque bloquea a las demas: sin confirmar no se puede invitar a nadie, asi que un cupo corto ahi no se arregla reclutando. Y las preguntas van antes que las invitaciones urgentes porque un creador que pregunto y no recibe respuesta MIENTRAS su plazo corre es la combinacion exacta que convierte un si en un silencio. Cada alerta dice que pasa y que hacer: una que solo dice que hay un problema obliga a buscarlo, y entonces deja de leerse. Y «cubierto» es ACEPTADO, no invitado: una invitacion sin contestar es una plaza esperando, y contarla como cubierta es como se llega al dia de arranque con la mitad del equipo y los numeros en verde</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="36">
       <c r="A121" s="67" t="inlineStr">
         <is>
-          <t>DEC-123</t>
+          <t>DEC-126</t>
         </is>
       </c>
       <c r="B121" s="68" t="inlineStr">
@@ -18480,24 +18530,24 @@
       <c r="C121" s="68" t="n"/>
       <c r="D121" s="69" t="inlineStr">
         <is>
-          <t>Pedir un correo se hace desde Shared, no desde el modulo que lo necesita.</t>
+          <t>usuarios:crear deja de teclear la contrasena; el alta interna usa el mismo enlace de 72 h que la del creador.</t>
         </is>
       </c>
       <c r="E121" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F121" s="69" t="inlineStr">
         <is>
-          <t>deptrac.yaml dice Communication: [Framework, Shared, Core, Identity]. En 5.9 el evento del enlace vivio una iteracion dentro de Identity y funciono de milagro: Identity esta en esa lista. Campaign no, y 7.6 necesita mandar un correo igual. Sube a App\Shared\Eventos\CorreoPedido con un solo oyente en Communication: cualquier modulo puede pedir un correo, ninguno conoce a Communication y Communication no conoce a ninguno. No es EventoOcurrido y no puede serlo --ese persiste su payload en domain_events y aqui el payload lleva el token en claro--; el HECHO si se registra, por separado y sin el token</t>
+          <t>Cierra BR-SEC-004 (🔴) del todo. must_change_password era el parche: obligaba a cambiarla DESPUES y dejaba una ventana --de minutos o de meses-- en la que dos personas conocian la credencial, y justo en las cuentas donde la base exige dos personas distintas para el dinero. Ahora no hay ventana: la contrasena no existe hasta que la escribe su dueno. usuarios:contrasena --enlace hace lo mismo para reponer y no toca la contrasena actual --si el correo no llega, la persona no se queda peor de como estaba--. Teclearla a mano sigue existiendo a proposito, como cristal de emergencia para cuando el correo no sale (Q-20), y el comando avisa cada vez de que ese es el camino excepcional</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="36">
       <c r="A122" s="67" t="inlineStr">
         <is>
-          <t>DEC-122</t>
+          <t>DEC-125</t>
         </is>
       </c>
       <c r="B122" s="68" t="inlineStr">
@@ -18508,24 +18558,24 @@
       <c r="C122" s="68" t="n"/>
       <c r="D122" s="69" t="inlineStr">
         <is>
-          <t>La invitacion COPIA el importe con el que salio, y el importe no se mueve mientras este viva.</t>
+          <t>Cuando un creador contesta, se avisa a QUIEN LE INVITO y a nadie mas.</t>
         </is>
       </c>
       <c r="E122" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F122" s="69" t="inlineStr">
         <is>
-          <t>BR-CREATOR-008 congela el precio al ACEPTAR (tg_ccr_compromiso, 7.5) y entre el envio y la respuesta agreed_amount se podia mover: al creador le llegaba «te pagamos 1.500», alguien lo bajaba a 900, y aceptaba 900 sin haberlo visto nunca. No hace falta mala fe; basta con dos personas sobre la misma campana. Se cierra por los dos lados: amount_snapshot --misma decision que payment_term_days_snapshot y billing_legal_entity_id-- y tg_ccr_monto_con_invitacion, que obliga a anular la invitacion antes de renegociar. Y como en 5.9, responder y anular son dos columnas: responded_at tiene que contestar «.llego a contestar?» sin ambiguedad. Decimocuarta columna puerta del esquema</t>
+          <t>Es quien espera la respuesta y quien va a hacer algo con ella. Avisar a todo el equipo son cuarenta correos por campana a cada uno, y un buzon asi se filtra a una carpeta y deja de leerse --la forma cara de no avisar a nadie--. El precio, dicho: una invitacion mandada por alguien que luego se va de la empresa queda MUDA. A una cuenta desactivada no se le escribe: no avisa a nadie y puede acabar en un buzon reasignado. El hecho no se pierde, queda en domain_events y se ve en la lista</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="36">
       <c r="A123" s="67" t="inlineStr">
         <is>
-          <t>DEC-121</t>
+          <t>DEC-124</t>
         </is>
       </c>
       <c r="B123" s="68" t="inlineStr">
@@ -18536,24 +18586,24 @@
       <c r="C123" s="68" t="n"/>
       <c r="D123" s="69" t="inlineStr">
         <is>
-          <t>Rechazar no cierra la campana para ese creador, y quedan las DOS rondas.</t>
+          <t>Preguntar NO mueve el plazo de la invitacion.</t>
         </is>
       </c>
       <c r="E123" s="69" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6b</t>
         </is>
       </c>
       <c r="F123" s="69" t="inlineStr">
         <is>
-          <t>Pasa de verdad: rechaza por el importe, finanzas sube el presupuesto, se vuelve a preguntar. Prohibirlo obligaria a renegociar fuera del sistema. La constancia vive en invitations --una fila por ronda, con su motivo y con lo que se ofrecio entonces--, que es justo para lo que la Fase 2 diseno la tabla («cuantas veces hubo que insistir alimenta el Creator Score»). Lo que si se limpia al reinvitar es campaign_creators.declined_at: esa columna dice cuando se rechazo la ronda ACTUAL, y dejarla puesta haria que un accepted conviviera con una fecha de rechazo. El motivo es de lista cerrada para poder contestar «.por que nos dicen que no?» --si el 70% es el importe, el problema es el presupuesto y no el reclutamiento-- y no decide quien se puede reinvitar</t>
+          <t>La alternativa --congelarla hasta que alguien conteste-- deja el importe comprometido para siempre si nadie contesta, que es justo el agujero que invitaciones:caducar existe para tapar. La pantalla se lo dice al creador con todas las letras: callarlo dejaria a alguien esperando tranquilo mientras su invitacion caduca, que es peor que no dejarle preguntar. Quien invito ve la pregunta en la lista de candidatos y decide; si hace falta mas tiempo, anula y manda otra. Y no hay respuesta dentro de la aplicacion: el equipo contesta por correo, que es donde el creador ya esta. Un hilo de ida y vuelta es un modulo de mensajeria --notificaciones, no leidos, permisos-- y habria multiplicado por tres la iteracion para resolver lo que un boton de «Responder» ya resuelve. Lo que si hay es un DUENO: «me hago cargo» marca quien atiende y el segundo clic no pisa al primero</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="36">
       <c r="A124" s="67" t="inlineStr">
         <is>
-          <t>DEC-120</t>
+          <t>DEC-123</t>
         </is>
       </c>
       <c r="B124" s="68" t="inlineStr">
@@ -18564,7 +18614,7 @@
       <c r="C124" s="68" t="n"/>
       <c r="D124" s="69" t="inlineStr">
         <is>
-          <t>El plazo para contestar vive en la CAMPANA, no en cada invitacion.</t>
+          <t>Pedir un correo se hace desde Shared, no desde el modulo que lo necesita.</t>
         </is>
       </c>
       <c r="E124" s="69" t="inlineStr">
@@ -18574,14 +18624,14 @@
       </c>
       <c r="F124" s="69" t="inlineStr">
         <is>
-          <t>campaigns.invitation_hours, 72 por omision, entre 1 hora y 30 dias (ck_camp_invitation_hours). Un solo numero que explicar y un solo sitio donde cambiarlo; por invitacion seria un dato que hay que decidir cuarenta veces y que nadie mira dos. Y caducar necesita un comando aunque la caducidad se deduzca: expires_at contra el reloj ya impide contestar, pero la participacion seguiria en invited para siempre, su importe seguiria contando contra el presupuesto (BR-CAMPAIGN-005 bloqueando a otros por dinero que nadie se va a gastar) y el cupo del mercado no se liberaria. invitaciones:caducar cada diez minutos: el plazo minimo es una hora, asi que diez minutos deja el retraso maximo en un 17% del plazo mas corto posible</t>
+          <t>deptrac.yaml dice Communication: [Framework, Shared, Core, Identity]. En 5.9 el evento del enlace vivio una iteracion dentro de Identity y funciono de milagro: Identity esta en esa lista. Campaign no, y 7.6 necesita mandar un correo igual. Sube a App\Shared\Eventos\CorreoPedido con un solo oyente en Communication: cualquier modulo puede pedir un correo, ninguno conoce a Communication y Communication no conoce a ninguno. No es EventoOcurrido y no puede serlo --ese persiste su payload en domain_events y aqui el payload lleva el token en claro--; el HECHO si se registra, por separado y sin el token</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="36">
       <c r="A125" s="67" t="inlineStr">
         <is>
-          <t>DEC-119</t>
+          <t>DEC-122</t>
         </is>
       </c>
       <c r="B125" s="68" t="inlineStr">
@@ -18592,7 +18642,7 @@
       <c r="C125" s="68" t="n"/>
       <c r="D125" s="69" t="inlineStr">
         <is>
-          <t>El creador contesta la invitacion EL MISMO, por enlace.</t>
+          <t>La invitacion COPIA el importe con el que salio, y el importe no se mueve mientras este viva.</t>
         </is>
       </c>
       <c r="E125" s="69" t="inlineStr">
@@ -18602,14 +18652,14 @@
       </c>
       <c r="F125" s="69" t="inlineStr">
         <is>
-          <t>Su portal (F6) sigue bloqueado por T-09, asi que no hay pantalla donde entre a decidir. La alternativa era que un operador tecleara «dijo que si por WhatsApp», y eso convierte una ACEPTACION --de la que sale lo que se le paga a una persona-- en la palabra de un tercero. Con enlace hay una IP, una hora y un token que solo el tenia. Y no habia que construir nada: es la pieza de 5.9, ya probada. invitations.channel admite otros canales desde la Fase 2; el dia que exista el de WhatsApp, la fila ya sabe distinguirlo</t>
+          <t>BR-CREATOR-008 congela el precio al ACEPTAR (tg_ccr_compromiso, 7.5) y entre el envio y la respuesta agreed_amount se podia mover: al creador le llegaba «te pagamos 1.500», alguien lo bajaba a 900, y aceptaba 900 sin haberlo visto nunca. No hace falta mala fe; basta con dos personas sobre la misma campana. Se cierra por los dos lados: amount_snapshot --misma decision que payment_term_days_snapshot y billing_legal_entity_id-- y tg_ccr_monto_con_invitacion, que obliga a anular la invitacion antes de renegociar. Y como en 5.9, responder y anular son dos columnas: responded_at tiene que contestar «.llego a contestar?» sin ambiguedad. Decimocuarta columna puerta del esquema</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="36">
       <c r="A126" s="67" t="inlineStr">
         <is>
-          <t>DEC-118</t>
+          <t>DEC-121</t>
         </is>
       </c>
       <c r="B126" s="68" t="inlineStr">
@@ -18620,24 +18670,24 @@
       <c r="C126" s="68" t="n"/>
       <c r="D126" s="69" t="inlineStr">
         <is>
-          <t>La portada se bifurca por TIPO DE USUARIO, y SESSION_DRIVER=database pasa a ser requisito de seguridad.</t>
+          <t>Rechazar no cierra la campana para ese creador, y quedan las DOS rondas.</t>
         </is>
       </c>
       <c r="E126" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F126" s="69" t="inlineStr">
         <is>
-          <t>Dos consecuencias de la misma causa: 5.9 crea la primera cuenta que no es del equipo. (a) /panel ensenaba a cualquier autenticado los totales de creadores, clientes y campanas mas el inventario del esquema; nadie lo habia pensado porque hasta hoy todos los usuarios eran internos. Se bifurca por user_type y no por permiso --un creador no tiene ninguno, y comprobar permisos que dicen «no» a todo deja una pantalla vacia en vez de una que explica donde esta--. (b) Poner una contrasena nueva borra las filas de sessions de ese usuario y rota remember_token; con SESSION_DRIVER=file lo primero es imposible --no hay forma de saber que archivo es de quien-- y una contrasena nueva convivira con la sesion abierta de quien entro con la vieja, que es no haber hecho nada</t>
+          <t>Pasa de verdad: rechaza por el importe, finanzas sube el presupuesto, se vuelve a preguntar. Prohibirlo obligaria a renegociar fuera del sistema. La constancia vive en invitations --una fila por ronda, con su motivo y con lo que se ofrecio entonces--, que es justo para lo que la Fase 2 diseno la tabla («cuantas veces hubo que insistir alimenta el Creator Score»). Lo que si se limpia al reinvitar es campaign_creators.declined_at: esa columna dice cuando se rechazo la ronda ACTUAL, y dejarla puesta haria que un accepted conviviera con una fecha de rechazo. El motivo es de lista cerrada para poder contestar «.por que nos dicen que no?» --si el 70% es el importe, el problema es el presupuesto y no el reclutamiento-- y no decide quien se puede reinvitar</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="36">
       <c r="A127" s="67" t="inlineStr">
         <is>
-          <t>DEC-117</t>
+          <t>DEC-120</t>
         </is>
       </c>
       <c r="B127" s="68" t="inlineStr">
@@ -18648,24 +18698,24 @@
       <c r="C127" s="68" t="n"/>
       <c r="D127" s="69" t="inlineStr">
         <is>
-          <t>El token no se queda en la barra de direcciones.</t>
+          <t>El plazo para contestar vive en la CAMPANA, no en cada invitacion.</t>
         </is>
       </c>
       <c r="E127" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F127" s="69" t="inlineStr">
         <is>
-          <t>El enlace del correo lo lleva --no hay otra forma--, pero esa ruta solo lo guarda en la sesion y redirige a una URL sin el. Una URL con un token dentro viaja en la cabecera Referer a cualquier recurso externo de la pagina --y estas pantallas cargan tipografias de un dominio de terceros--, se queda en el registro de accesos del servidor y en el historial, y se copia entera cuando alguien la pega en un chat preguntando que es. Al guardarlo la sesion se vacia y renueva (invalidate(), no regenerate(): el segundo cambia el identificador y conserva el contenido, y aqui el contenido es lo que sobra)</t>
+          <t>campaigns.invitation_hours, 72 por omision, entre 1 hora y 30 dias (ck_camp_invitation_hours). Un solo numero que explicar y un solo sitio donde cambiarlo; por invitacion seria un dato que hay que decidir cuarenta veces y que nadie mira dos. Y caducar necesita un comando aunque la caducidad se deduzca: expires_at contra el reloj ya impide contestar, pero la participacion seguiria en invited para siempre, su importe seguiria contando contra el presupuesto (BR-CAMPAIGN-005 bloqueando a otros por dinero que nadie se va a gastar) y el cupo del mercado no se liberaria. invitaciones:caducar cada diez minutos: el plazo minimo es una hora, asi que diez minutos deja el retraso maximo en un 17% del plazo mas corto posible</t>
         </is>
       </c>
     </row>
     <row r="128" ht="23.25" customHeight="1" s="36">
       <c r="A128" s="67" t="inlineStr">
         <is>
-          <t>DEC-116</t>
+          <t>DEC-119</t>
         </is>
       </c>
       <c r="B128" s="68" t="inlineStr">
@@ -18676,24 +18726,24 @@
       <c r="C128" s="68" t="n"/>
       <c r="D128" s="69" t="inlineStr">
         <is>
-          <t>Un enlace nuevo invalida el anterior, y usar uno mata todos los demas.</t>
+          <t>El creador contesta la invitacion EL MISMO, por enlace.</t>
         </is>
       </c>
       <c r="E128" s="69" t="inlineStr">
         <is>
-          <t>5.9 + 4.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="F128" s="69" t="inlineStr">
         <is>
-          <t>Quien pide otro suele hacerlo porque sospecha del primero; dejarlo vivo seria dejar abierta justo la puerta que queria cerrar. Lo garantiza la BASE con la decimotercera columna puerta (uq_pl_vigente), no el servicio. Y revocar no es marcar usado: son dos columnas a proposito, porque el dia que alguien pregunte «.llego a usar el enlace?» la respuesta tiene que salir de una columna que solo se escribe cuando lo uso. La primera version de la tabla las mezclaba --una columna menos-- y ademas chocaba con ck_pl_used, que exige la IP de quien lo usa: a un enlace que sustituyes no le puedes poner una IP. Caducar no se escribe: se deduce de expires_at</t>
+          <t>Su portal (F6) sigue bloqueado por T-09, asi que no hay pantalla donde entre a decidir. La alternativa era que un operador tecleara «dijo que si por WhatsApp», y eso convierte una ACEPTACION --de la que sale lo que se le paga a una persona-- en la palabra de un tercero. Con enlace hay una IP, una hora y un token que solo el tenia. Y no habia que construir nada: es la pieza de 5.9, ya probada. invitations.channel admite otros canales desde la Fase 2; el dia que exista el de WhatsApp, la fila ya sabe distinguirlo</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="36">
       <c r="A129" s="67" t="inlineStr">
         <is>
-          <t>DEC-115</t>
+          <t>DEC-118</t>
         </is>
       </c>
       <c r="B129" s="68" t="inlineStr">
@@ -18704,24 +18754,24 @@
       <c r="C129" s="68" t="n"/>
       <c r="D129" s="69" t="inlineStr">
         <is>
-          <t>Pedir recuperacion contesta lo mismo exista o no el correo.</t>
+          <t>La portada se bifurca por TIPO DE USUARIO, y SESSION_DRIVER=database pasa a ser requisito de seguridad.</t>
         </is>
       </c>
       <c r="E129" s="69" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F129" s="69" t="inlineStr">
         <is>
-          <t>«Si esa direccion tiene una cuenta activa, le acaba de salir un enlace», a los dos, y sin enviar nada en el segundo caso. Distinguirlos convierte la pantalla en un buscador de cuentas dadas de alta: con una lista de direcciones se sabe en un rato cuales son clientes nuestros, y eso vale dinero para quien hace phishing dirigido. El precio es real: quien se equivoca de correo no se entera, y se compensa diciendolo en la propia pantalla en vez de callarlo. La prueba lo afirma byte a byte quitando el testigo anti-CSRF: comparar solo la clave de sesion dejaria pasar una version que escribiera «no tenemos ese correo» dentro de la vista</t>
+          <t>Dos consecuencias de la misma causa: 5.9 crea la primera cuenta que no es del equipo. (a) /panel ensenaba a cualquier autenticado los totales de creadores, clientes y campanas mas el inventario del esquema; nadie lo habia pensado porque hasta hoy todos los usuarios eran internos. Se bifurca por user_type y no por permiso --un creador no tiene ninguno, y comprobar permisos que dicen «no» a todo deja una pantalla vacia en vez de una que explica donde esta--. (b) Poner una contrasena nueva borra las filas de sessions de ese usuario y rota remember_token; con SESSION_DRIVER=file lo primero es imposible --no hay forma de saber que archivo es de quien-- y una contrasena nueva convivira con la sesion abierta de quien entro con la vieja, que es no haber hecho nada</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="36">
       <c r="A130" s="67" t="inlineStr">
         <is>
-          <t>DEC-114</t>
+          <t>DEC-117</t>
         </is>
       </c>
       <c r="B130" s="68" t="inlineStr">
@@ -18732,7 +18782,7 @@
       <c r="C130" s="68" t="n"/>
       <c r="D130" s="69" t="inlineStr">
         <is>
-          <t>De un token de contrasena se guarda la HUELLA, nunca el token.</t>
+          <t>El token no se queda en la barra de direcciones.</t>
         </is>
       </c>
       <c r="E130" s="69" t="inlineStr">
@@ -18742,14 +18792,14 @@
       </c>
       <c r="F130" s="69" t="inlineStr">
         <is>
-          <t>bin2hex(random_bytes(32)) --no Str::random(), no uniqid(), no el uuid de la fila-- y en password_links solo entra su sha256. Misma decision que email_log (la huella del cuerpo, no el cuerpo) y que los medios de pago (la mascara, no el numero), y aqui es la mas importante de las tres: quien lea esta tabla no puede entrar en ninguna cuenta. Corolario que obligo a romper el patron de DEC-112: el aviso a Communication no puede ir por Eventos::ocurrio(), porque ese bus PERSISTE el payload y el payload lleva el enlace dentro. Va por un evento propio de Identity, que Communication ya tiene permitido conocer. El HECHO --«se emitio un enlace de tipo X para el usuario Y»-- si se guarda en domain_events, y sin el token</t>
+          <t>El enlace del correo lo lleva --no hay otra forma--, pero esa ruta solo lo guarda en la sesion y redirige a una URL sin el. Una URL con un token dentro viaja en la cabecera Referer a cualquier recurso externo de la pagina --y estas pantallas cargan tipografias de un dominio de terceros--, se queda en el registro de accesos del servidor y en el historial, y se copia entera cuando alguien la pega en un chat preguntando que es. Al guardarlo la sesion se vacia y renueva (invalidate(), no regenerate(): el segundo cambia el identificador y conserva el contenido, y aqui el contenido es lo que sobra)</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="36">
       <c r="A131" s="67" t="inlineStr">
         <is>
-          <t>DEC-113</t>
+          <t>DEC-116</t>
         </is>
       </c>
       <c r="B131" s="68" t="inlineStr">
@@ -18760,7 +18810,7 @@
       <c r="C131" s="68" t="n"/>
       <c r="D131" s="69" t="inlineStr">
         <is>
-          <t>El enlace de alta dura 72 h; el de recuperacion, 1 h.</t>
+          <t>Un enlace nuevo invalida el anterior, y usar uno mata todos los demas.</t>
         </is>
       </c>
       <c r="E131" s="69" t="inlineStr">
@@ -18770,14 +18820,14 @@
       </c>
       <c r="F131" s="69" t="inlineStr">
         <is>
-          <t>Son la misma pieza con dos relojes: el de alta llega SIN AVISAR y puede caer un viernes por la noche; el de recuperacion lo pide alguien que esta delante de la pantalla ahora. Un solo plazo obligaria a elegir entre dejar la ventana larga del alta valiendo para recuperar, o darle una hora a quien no sabia que iba a recibir nada. La caducidad se guarda en la fila, no es una constante global: un enlace sabe cuando muere</t>
+          <t>Quien pide otro suele hacerlo porque sospecha del primero; dejarlo vivo seria dejar abierta justo la puerta que queria cerrar. Lo garantiza la BASE con la decimotercera columna puerta (uq_pl_vigente), no el servicio. Y revocar no es marcar usado: son dos columnas a proposito, porque el dia que alguien pregunte «.llego a usar el enlace?» la respuesta tiene que salir de una columna que solo se escribe cuando lo uso. La primera version de la tabla las mezclaba --una columna menos-- y ademas chocaba con ck_pl_used, que exige la IP de quien lo usa: a un enlace que sustituyes no le puedes poner una IP. Caducar no se escribe: se deduce de expires_at</t>
         </is>
       </c>
     </row>
     <row r="132" ht="23.25" customHeight="1" s="36">
       <c r="A132" s="67" t="inlineStr">
         <is>
-          <t>DEC-112</t>
+          <t>DEC-115</t>
         </is>
       </c>
       <c r="B132" s="68" t="inlineStr">
@@ -18788,24 +18838,24 @@
       <c r="C132" s="68" t="n"/>
       <c r="D132" s="69" t="inlineStr">
         <is>
-          <t>Los modulos se comunican por EVENTOS, no llamandose.</t>
+          <t>Pedir recuperacion contesta lo mismo exista o no el correo.</t>
         </is>
       </c>
       <c r="E132" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="F132" s="69" t="inlineStr">
         <is>
-          <t>deptrac.yaml no deja que Creator conozca Communication ni al reves, y no es burocracia: si Creator importara Communication, un SMTP caido podria tumbar la captura de un dato fiscal. App\Shared\Eventos estrena domain_events --disenada en 2.4 y sin una sola fila hasta hoy-- y reparte asi: Creator levanta un nombre y un array, Communication recibe un nombre y un array, y ninguno importa al otro. El hecho se GUARDA antes de despachar, para que conste aunque el oyente reviente. Y no es la bitacora: Bitacora responde «quien toco que y que cambio» y es evidencia; esto responde «que paso, para que otros reaccionen» y dispara trabajo</t>
+          <t>«Si esa direccion tiene una cuenta activa, le acaba de salir un enlace», a los dos, y sin enviar nada en el segundo caso. Distinguirlos convierte la pantalla en un buscador de cuentas dadas de alta: con una lista de direcciones se sabe en un rato cuales son clientes nuestros, y eso vale dinero para quien hace phishing dirigido. El precio es real: quien se equivoca de correo no se entera, y se compensa diciendolo en la propia pantalla en vez de callarlo. La prueba lo afirma byte a byte quitando el testigo anti-CSRF: comparar solo la clave de sesion dejaria pasar una version que escribiera «no tenemos ese correo» dentro de la vista</t>
         </is>
       </c>
     </row>
     <row r="133" ht="23.25" customHeight="1" s="36">
       <c r="A133" s="67" t="inlineStr">
         <is>
-          <t>DEC-111</t>
+          <t>DEC-114</t>
         </is>
       </c>
       <c r="B133" s="68" t="inlineStr">
@@ -18816,24 +18866,24 @@
       <c r="C133" s="68" t="n"/>
       <c r="D133" s="69" t="inlineStr">
         <is>
-          <t>Si el aviso no se puede enviar, el cambio sigue adelante.</t>
+          <t>De un token de contrasena se guarda la HUELLA, nunca el token.</t>
         </is>
       </c>
       <c r="E133" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F133" s="69" t="inlineStr">
         <is>
-          <t>Bloquear la captura de un dato fiscal porque un SMTP se cayo convierte un problema de infraestructura en un creador al que no se le puede corregir un dato. Pero el fallo NO se traga: si el correo se encolo aparece en /correos como failed con su motivo, y si ni siquiera se pudo encolar --no hay plantilla, que es un fallo de configuracion-- se registra con report() y queda la fila de domain_events diciendo que el hecho ocurrio sin que saliera aviso</t>
+          <t>bin2hex(random_bytes(32)) --no Str::random(), no uniqid(), no el uuid de la fila-- y en password_links solo entra su sha256. Misma decision que email_log (la huella del cuerpo, no el cuerpo) y que los medios de pago (la mascara, no el numero), y aqui es la mas importante de las tres: quien lea esta tabla no puede entrar en ninguna cuenta. Corolario que obligo a romper el patron de DEC-112: el aviso a Communication no puede ir por Eventos::ocurrio(), porque ese bus PERSISTE el payload y el payload lleva el enlace dentro. Va por un evento propio de Identity, que Communication ya tiene permitido conocer. El HECHO --«se emitio un enlace de tipo X para el usuario Y»-- si se guarda en domain_events, y sin el token</t>
         </is>
       </c>
     </row>
     <row r="134" ht="23.25" customHeight="1" s="36">
       <c r="A134" s="67" t="inlineStr">
         <is>
-          <t>DEC-110</t>
+          <t>DEC-113</t>
         </is>
       </c>
       <c r="B134" s="68" t="inlineStr">
@@ -18844,24 +18894,24 @@
       <c r="C134" s="68" t="n"/>
       <c r="D134" s="69" t="inlineStr">
         <is>
-          <t>El correo de aviso NO lleva el dato dentro.</t>
+          <t>El enlace de alta dura 72 h; el de recuperacion, 1 h.</t>
         </is>
       </c>
       <c r="E134" s="69" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.9 + 4.1</t>
         </is>
       </c>
       <c r="F134" s="69" t="inlineStr">
         <is>
-          <t>«Alguien registro un cambio en sus datos de pago; si no ha sido usted, respondanos.» Sin numero, sin banco, sin regimen, sin RUC. Un correo se lee en pantallas ajenas, se reenvia y se queda en buzones que no controlamos --y el escenario del que nos defendemos es precisamente que alguien tenga acceso a ese buzon--. Para decir «yo no fui» no hace falta ver el numero. Misma regla que ya gobierna la bitacora (la mascara, nunca el numero) y email_log (la huella, nunca el cuerpo)</t>
+          <t>Son la misma pieza con dos relojes: el de alta llega SIN AVISAR y puede caer un viernes por la noche; el de recuperacion lo pide alguien que esta delante de la pantalla ahora. Un solo plazo obligaria a elegir entre dejar la ventana larga del alta valiendo para recuperar, o darle una hora a quien no sabia que iba a recibir nada. La caducidad se guarda en la fila, no es una constante global: un enlace sabe cuando muere</t>
         </is>
       </c>
     </row>
     <row r="135" ht="23.25" customHeight="1" s="36">
       <c r="A135" s="67" t="inlineStr">
         <is>
-          <t>DEC-109</t>
+          <t>DEC-112</t>
         </is>
       </c>
       <c r="B135" s="68" t="inlineStr">
@@ -18872,7 +18922,7 @@
       <c r="C135" s="68" t="n"/>
       <c r="D135" s="69" t="inlineStr">
         <is>
-          <t>El aviso de cambio sensible sale al CAPTURAR, no al aprobar.</t>
+          <t>Los modulos se comunican por EVENTOS, no llamandose.</t>
         </is>
       </c>
       <c r="E135" s="69" t="inlineStr">
@@ -18882,14 +18932,14 @@
       </c>
       <c r="F135" s="69" t="inlineStr">
         <is>
-          <t>Es lo unico que le da al creador margen para decir «yo no fui» mientras el cambio todavia se puede parar. Avisar despues de aprobarlo es contarle un hecho consumado: si alguien suplanto su cuenta bancaria, el dinero ya va camino de otro sitio. Hay prueba dedicada: el aviso sale con el perfil todavia en pending</t>
+          <t>deptrac.yaml no deja que Creator conozca Communication ni al reves, y no es burocracia: si Creator importara Communication, un SMTP caido podria tumbar la captura de un dato fiscal. App\Shared\Eventos estrena domain_events --disenada en 2.4 y sin una sola fila hasta hoy-- y reparte asi: Creator levanta un nombre y un array, Communication recibe un nombre y un array, y ninguno importa al otro. El hecho se GUARDA antes de despachar, para que conste aunque el oyente reviente. Y no es la bitacora: Bitacora responde «quien toco que y que cambio» y es evidencia; esto responde «que paso, para que otros reaccionen» y dispara trabajo</t>
         </is>
       </c>
     </row>
     <row r="136" ht="23.25" customHeight="1" s="36">
       <c r="A136" s="67" t="inlineStr">
         <is>
-          <t>DEC-108</t>
+          <t>DEC-111</t>
         </is>
       </c>
       <c r="B136" s="68" t="inlineStr">
@@ -18900,24 +18950,24 @@
       <c r="C136" s="68" t="n"/>
       <c r="D136" s="69" t="inlineStr">
         <is>
-          <t>Tres intentos espaciados (1, 5 y 15 minutos) y luego failed VISIBLE.</t>
+          <t>Si el aviso no se puede enviar, el cambio sigue adelante.</t>
         </is>
       </c>
       <c r="E136" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F136" s="69" t="inlineStr">
         <is>
-          <t>Cubre la caida pasajera del proveedor sin insistir eternamente sobre una direccion que no existe, que es la causa mas comun. ck_el_failed exige en la BASE que un fallido lleve cuando fallo Y por que: un failed sin motivo obliga a mirar el log del servidor, que es exactamente lo que esta tabla existe para evitar. Y la pantalla abre FILTRADA POR FALLIDOS, porque el modo de fallo que importa --«al creador no le llego su enlace»-- lo descubre operaciones, no un desarrollador leyendo storage/logs</t>
+          <t>Bloquear la captura de un dato fiscal porque un SMTP se cayo convierte un problema de infraestructura en un creador al que no se le puede corregir un dato. Pero el fallo NO se traga: si el correo se encolo aparece en /correos como failed con su motivo, y si ni siquiera se pudo encolar --no hay plantilla, que es un fallo de configuracion-- se registra con report() y queda la fila de domain_events diciendo que el hecho ocurrio sin que saliera aviso</t>
         </is>
       </c>
     </row>
     <row r="137" ht="23.25" customHeight="1" s="36">
       <c r="A137" s="67" t="inlineStr">
         <is>
-          <t>DEC-107</t>
+          <t>DEC-110</t>
         </is>
       </c>
       <c r="B137" s="68" t="inlineStr">
@@ -18928,24 +18978,24 @@
       <c r="C137" s="68" t="n"/>
       <c r="D137" s="69" t="inlineStr">
         <is>
-          <t>Sin plantilla en el idioma del destinatario se cae al de por defecto, y se ANOTA.</t>
+          <t>El correo de aviso NO lleva el dato dentro.</t>
         </is>
       </c>
       <c r="E137" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F137" s="69" t="inlineStr">
         <is>
-          <t>Un aviso que no llega es peor que uno en el idioma equivocado. Lo que hace que no sea una chapuza es la segunda mitad: email_log guarda locale_requested junto a template_locale, asi que «que plantillas faltan por traducir» es una consulta sobre envios reales, y sale en la pantalla como lo unico que pide una accion. Sin eso la caida seria silenciosa y nadie se enteraria nunca de que el portugues no existe. pt-BR cae antes a pt que a es: es una caida mucho mas pequena y son dos lineas</t>
+          <t>«Alguien registro un cambio en sus datos de pago; si no ha sido usted, respondanos.» Sin numero, sin banco, sin regimen, sin RUC. Un correo se lee en pantallas ajenas, se reenvia y se queda en buzones que no controlamos --y el escenario del que nos defendemos es precisamente que alguien tenga acceso a ese buzon--. Para decir «yo no fui» no hace falta ver el numero. Misma regla que ya gobierna la bitacora (la mascara, nunca el numero) y email_log (la huella, nunca el cuerpo)</t>
         </is>
       </c>
     </row>
     <row r="138" ht="34.5" customHeight="1" s="36">
       <c r="A138" s="67" t="inlineStr">
         <is>
-          <t>DEC-106</t>
+          <t>DEC-109</t>
         </is>
       </c>
       <c r="B138" s="68" t="inlineStr">
@@ -18956,24 +19006,24 @@
       <c r="C138" s="68" t="n"/>
       <c r="D138" s="69" t="inlineStr">
         <is>
-          <t>Del correo enviado se guarda la HUELLA del cuerpo, no el cuerpo.</t>
+          <t>El aviso de cambio sensible sale al CAPTURAR, no al aprobar.</t>
         </is>
       </c>
       <c r="E138" s="69" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="F138" s="69" t="inlineStr">
         <is>
-          <t>email_log guarda plantilla, version, idioma, asunto y body_sha256. El cuerpo lleva el nombre de la persona, a veces importes y a veces datos fiscales: guardarlo convierte esa tabla en una SEGUNDA COPIA de la ficha del creador, que hay que proteger, anonimizar y borrar igual que la primera. Y no se pierde nada, porque la version de la plantilla es inmutable --publicar la siguiente cierra la anterior, no la edita-- y la huella demuestra que el cuerpo enviado era exactamente el que sale de renderizarla. «Me llegaron condiciones distintas» se contesta con la version y la huella. Es la regla del proyecto sobre logs, aplicada con cabeza</t>
+          <t>Es lo unico que le da al creador margen para decir «yo no fui» mientras el cambio todavia se puede parar. Avisar despues de aprobarlo es contarle un hecho consumado: si alguien suplanto su cuenta bancaria, el dinero ya va camino de otro sitio. Hay prueba dedicada: el aviso sale con el perfil todavia en pending</t>
         </is>
       </c>
     </row>
     <row r="139" ht="23.25" customHeight="1" s="36">
       <c r="A139" s="67" t="inlineStr">
         <is>
-          <t>DEC-105</t>
+          <t>DEC-108</t>
         </is>
       </c>
       <c r="B139" s="68" t="inlineStr">
@@ -18984,24 +19034,24 @@
       <c r="C139" s="68" t="n"/>
       <c r="D139" s="69" t="inlineStr">
         <is>
-          <t>Pasarse del presupuesto de creadores se BLOQUEA, y finanzas lo autoriza dejando el motivo.</t>
+          <t>Tres intentos espaciados (1, 5 y 15 minutos) y luego failed VISIBLE.</t>
         </is>
       </c>
       <c r="E139" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F139" s="69" t="inlineStr">
         <is>
-          <t>La regla dice «sin aprobacion explicita de un rol autorizado, que queda auditada», asi que la autorizacion es un dato de la fila: quien, cuando y por que. ck_camp_budget_override exige las tres o ninguna --una firma sin explicacion no responde «por que esta campana se paso» dentro de un ano, misma forma que ck_inv_responded--. Lo firma finanzas y no quien monto la campana (DEC-091, DEC-044), y el motivo exige al menos diez caracteres porque «porque» no es una explicacion. Lo que cuenta como comprometido son las participaciones VIVAS: un creador que rechazo no consume presupuesto, y contarlo dejaria campanas bloqueadas por dinero que nadie se va a gastar</t>
+          <t>Cubre la caida pasajera del proveedor sin insistir eternamente sobre una direccion que no existe, que es la causa mas comun. ck_el_failed exige en la BASE que un fallido lleve cuando fallo Y por que: un failed sin motivo obliga a mirar el log del servidor, que es exactamente lo que esta tabla existe para evitar. Y la pantalla abre FILTRADA POR FALLIDOS, porque el modo de fallo que importa --«al creador no le llego su enlace»-- lo descubre operaciones, no un desarrollador leyendo storage/logs</t>
         </is>
       </c>
     </row>
     <row r="140" ht="23.25" customHeight="1" s="36">
       <c r="A140" s="67" t="inlineStr">
         <is>
-          <t>DEC-104</t>
+          <t>DEC-107</t>
         </is>
       </c>
       <c r="B140" s="68" t="inlineStr">
@@ -19012,24 +19062,24 @@
       <c r="C140" s="68" t="n"/>
       <c r="D140" s="69" t="inlineStr">
         <is>
-          <t>El monto acordado se fija al INVITAR y se congela al ACEPTAR.</t>
+          <t>Sin plantilla en el idioma del destinatario se cae al de por defecto, y se ANOTA.</t>
         </is>
       </c>
       <c r="E140" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F140" s="69" t="inlineStr">
         <is>
-          <t>BR-CREATOR-008: la tarifa declarada es referencia, el precio vinculante es el monto congelado en la participacion. Se fija al invitar porque el creador no puede aceptar un numero que no ha visto --tg_ccr_compromiso impide pasar a invited con cero-- y se congela al aceptar porque a partir de ahi es un acuerdo entre dos partes. Congelarlo ya en la invitacion obligaria a cancelar y rehacerla por un dedazo, llenando el historico de invitaciones canceladas que no se cancelaron por negocio: mismo argumento que DEC-090. Excepcion coherente con 7.2: en una campana declarada gratuita si se invita con cero</t>
+          <t>Un aviso que no llega es peor que uno en el idioma equivocado. Lo que hace que no sea una chapuza es la segunda mitad: email_log guarda locale_requested junto a template_locale, asi que «que plantillas faltan por traducir» es una consulta sobre envios reales, y sale en la pantalla como lo unico que pide una accion. Sin eso la caida seria silenciosa y nadie se enteraria nunca de que el portugues no existe. pt-BR cae antes a pt que a es: es una caida mucho mas pequena y son dos lineas</t>
         </is>
       </c>
     </row>
     <row r="141" ht="34.5" customHeight="1" s="36">
       <c r="A141" s="67" t="inlineStr">
         <is>
-          <t>DEC-103</t>
+          <t>DEC-106</t>
         </is>
       </c>
       <c r="B141" s="68" t="inlineStr">
@@ -19040,24 +19090,24 @@
       <c r="C141" s="68" t="n"/>
       <c r="D141" s="69" t="inlineStr">
         <is>
-          <t>«2 reels» en el brief es lo que entrega CADA creador, no el total de la campana.</t>
+          <t>Del correo enviado se guarda la HUELLA del cuerpo, no el cuerpo.</t>
         </is>
       </c>
       <c r="E141" s="69" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="F141" s="69" t="inlineStr">
         <is>
-          <t>El brief es lo que se le dice a UNA persona; cuantos creadores hay lo dice target_creators de cada mercado (7.3). La alternativa --repartir un total entre los seleccionados-- obliga a decidir quien entrega que y a recalcular cada vez que alguien entra o sale, y un creador no sabria que acepta hasta que la lista este cerrada. Ademas confirma lo ya construido: el coste estimado de 7.4 ya multiplicaba tarifa por cantidad</t>
+          <t>email_log guarda plantilla, version, idioma, asunto y body_sha256. El cuerpo lleva el nombre de la persona, a veces importes y a veces datos fiscales: guardarlo convierte esa tabla en una SEGUNDA COPIA de la ficha del creador, que hay que proteger, anonimizar y borrar igual que la primera. Y no se pierde nada, porque la version de la plantilla es inmutable --publicar la siguiente cierra la anterior, no la edita-- y la huella demuestra que el cuerpo enviado era exactamente el que sale de renderizarla. «Me llegaron condiciones distintas» se contesta con la version y la huella. Es la regla del proyecto sobre logs, aplicada con cabeza</t>
         </is>
       </c>
     </row>
     <row r="142" ht="23.25" customHeight="1" s="36">
       <c r="A142" s="67" t="inlineStr">
         <is>
-          <t>DEC-102</t>
+          <t>DEC-105</t>
         </is>
       </c>
       <c r="B142" s="68" t="inlineStr">
@@ -19068,24 +19118,24 @@
       <c r="C142" s="68" t="n"/>
       <c r="D142" s="69" t="inlineStr">
         <is>
-          <t>Nadie entra en una campana cerrada, y una participacion que ya estaba solo se puede cancelar.</t>
+          <t>Pasarse del presupuesto de creadores se BLOQUEA, y finanzas lo autoriza dejando el motivo.</t>
         </is>
       </c>
       <c r="E142" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F142" s="69" t="inlineStr">
         <is>
-          <t>campaign_creators existia desde la Fase 2 y hasta 7.4 nadie habia escrito una fila; en cuanto se escribe la primera aparece el hueco. Una participacion en una campana terminada devenga en el ledger (9.3) contra un periodo ya liquidado, sale en el reporte «reproducible» del cliente (10.4) y cuenta en el Creator Score (14.3) por un trabajo que nunca existio. Disparadores y no CHECK porque la condicion esta en otra tabla. El de UPDATE hace falta aparte porque cerrar la campana y mover al creador son operaciones distintas; se deja pasar cancelled porque cerrar una campana con candidatos dentro tiene que poder dejarlos resueltos, y la alternativa seria borrar la fila --lo que 3.12 prohibe--</t>
+          <t>La regla dice «sin aprobacion explicita de un rol autorizado, que queda auditada», asi que la autorizacion es un dato de la fila: quien, cuando y por que. ck_camp_budget_override exige las tres o ninguna --una firma sin explicacion no responde «por que esta campana se paso» dentro de un ano, misma forma que ck_inv_responded--. Lo firma finanzas y no quien monto la campana (DEC-091, DEC-044), y el motivo exige al menos diez caracteres porque «porque» no es una explicacion. Lo que cuenta como comprometido son las participaciones VIVAS: un creador que rechazo no consume presupuesto, y contarlo dejaria campanas bloqueadas por dinero que nadie se va a gastar</t>
         </is>
       </c>
     </row>
     <row r="143" ht="23.25" customHeight="1" s="36">
       <c r="A143" s="67" t="inlineStr">
         <is>
-          <t>DEC-101</t>
+          <t>DEC-104</t>
         </is>
       </c>
       <c r="B143" s="68" t="inlineStr">
@@ -19096,24 +19146,24 @@
       <c r="C143" s="68" t="n"/>
       <c r="D143" s="69" t="inlineStr">
         <is>
-          <t>En la lista corta se entra a un mercado CONCRETO, derivado del pais del creador.</t>
+          <t>El monto acordado se fija al INVITAR y se congela al ACEPTAR.</t>
         </is>
       </c>
       <c r="E143" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F143" s="69" t="inlineStr">
         <is>
-          <t>No se pide: es el unico que puede ser, y pedirlo seria pedirle al operador que repita un dato que el sistema ya sabe. De ahi sale el cupo por mercado (target_creators, 7.3) y el reparto de entregables por pais en 7.5. agreed_amount nace en CERO a proposito: el compromiso economico se congela al aceptar (BR-CREATOR-008), no al meter a alguien en una lista, y un candidato con importe es un acuerdo que nadie ha firmado</t>
+          <t>BR-CREATOR-008: la tarifa declarada es referencia, el precio vinculante es el monto congelado en la participacion. Se fija al invitar porque el creador no puede aceptar un numero que no ha visto --tg_ccr_compromiso impide pasar a invited con cero-- y se congela al aceptar porque a partir de ahi es un acuerdo entre dos partes. Congelarlo ya en la invitacion obligaria a cancelar y rehacerla por un dedazo, llenando el historico de invitaciones canceladas que no se cancelaron por negocio: mismo argumento que DEC-090. Excepcion coherente con 7.2: en una campana declarada gratuita si se invita con cero</t>
         </is>
       </c>
     </row>
     <row r="144" ht="23.25" customHeight="1" s="36">
       <c r="A144" s="67" t="inlineStr">
         <is>
-          <t>DEC-100</t>
+          <t>DEC-103</t>
         </is>
       </c>
       <c r="B144" s="68" t="inlineStr">
@@ -19124,24 +19174,24 @@
       <c r="C144" s="68" t="n"/>
       <c r="D144" s="69" t="inlineStr">
         <is>
-          <t>Una categoria que el creador declaro que NO trabaja lo excluye del buscador.</t>
+          <t>«2 reels» en el brief es lo que entrega CADA creador, no el total de la campana.</t>
         </is>
       </c>
       <c r="E144" s="69" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F144" s="69" t="inlineStr">
         <is>
-          <t>Es media BR-CAMPAIGN-007 --roja, y hasta 7.4 sin nada detras-- y es la mitad que ya se puede comprobar con lo que hay en el modelo: creator_restrictions contra client_brand_categories. El creador ya dijo que no; invitarlo es hacerle perder el tiempo a los dos. Se sigue viendo con el interruptor de descartados, para poder auditar por que falta alguien. Competidores y exclusividades vigentes llegan en 7.11</t>
+          <t>El brief es lo que se le dice a UNA persona; cuantos creadores hay lo dice target_creators de cada mercado (7.3). La alternativa --repartir un total entre los seleccionados-- obliga a decidir quien entrega que y a recalcular cada vez que alguien entra o sale, y un creador no sabria que acepta hasta que la lista este cerrada. Ademas confirma lo ya construido: el coste estimado de 7.4 ya multiplicaba tarifa por cantidad</t>
         </is>
       </c>
     </row>
     <row r="145" ht="23.25" customHeight="1" s="36">
       <c r="A145" s="67" t="inlineStr">
         <is>
-          <t>DEC-099</t>
+          <t>DEC-102</t>
         </is>
       </c>
       <c r="B145" s="68" t="inlineStr">
@@ -19152,7 +19202,7 @@
       <c r="C145" s="68" t="n"/>
       <c r="D145" s="69" t="inlineStr">
         <is>
-          <t>El buscador ensena a todos los activos; el veto real salta al anadir.</t>
+          <t>Nadie entra en una campana cerrada, y una participacion que ya estaba solo se puede cancelar.</t>
         </is>
       </c>
       <c r="E145" s="69" t="inlineStr">
@@ -19162,14 +19212,14 @@
       </c>
       <c r="F145" s="69" t="inlineStr">
         <is>
-          <t>Un creador activado en junio al que en agosto se le retiro el medio de pago sigue con status = 'active': sale en la busqueda, con lo que le falta a la vista, y NO entra en la lista corta. Dos motivos: revalidar los seis requisitos de BR-CREATOR-006 por candidato y por busqueda es caro --en el veto se hace una vez, sobre uno-- y un creador que desaparece sin explicacion parece un fallo del sistema, mientras que uno que sale con «le falta el medio de pago» es una tarea. El veto usa CompletitudOperativa, la MISMA clase que decide la activacion y no una copia: si manana se anade un septimo requisito, lo hereda sin que nadie se acuerde de venir aqui</t>
+          <t>campaign_creators existia desde la Fase 2 y hasta 7.4 nadie habia escrito una fila; en cuanto se escribe la primera aparece el hueco. Una participacion en una campana terminada devenga en el ledger (9.3) contra un periodo ya liquidado, sale en el reporte «reproducible» del cliente (10.4) y cuenta en el Creator Score (14.3) por un trabajo que nunca existio. Disparadores y no CHECK porque la condicion esta en otra tabla. El de UPDATE hace falta aparte porque cerrar la campana y mover al creador son operaciones distintas; se deja pasar cancelled porque cerrar una campana con candidatos dentro tiene que poder dejarlos resueltos, y la alternativa seria borrar la fila --lo que 3.12 prohibe--</t>
         </is>
       </c>
     </row>
     <row r="146" ht="23.25" customHeight="1" s="36">
       <c r="A146" s="67" t="inlineStr">
         <is>
-          <t>DEC-098</t>
+          <t>DEC-101</t>
         </is>
       </c>
       <c r="B146" s="68" t="inlineStr">
@@ -19180,24 +19230,24 @@
       <c r="C146" s="68" t="n"/>
       <c r="D146" s="69" t="inlineStr">
         <is>
-          <t>Que el mercado sea DE la campana lo garantiza el esquema, con foraneas COMPUESTAS.</t>
+          <t>En la lista corta se entra a un mercado CONCRETO, derivado del pais del creador.</t>
         </is>
       </c>
       <c r="E146" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F146" s="69" t="inlineStr">
         <is>
-          <t>campaign_requirements.campaign_market_id y campaign_creators.campaign_market_id apuntaban a campaign_markets(id), y una foranea asi solo comprueba que el mercado exista: nada impedia un requisito de la campana A colgado del mercado de la campana B, ni un creador aceptado atribuido al pais de otra campana. Se anade uq_cm_id_campaign (id, campaign_id) --redundante como clave, necesaria como destino-- y las dos foraneas pasan a (campaign_market_id, campaign_id). Se prefiere a un disparador porque la comprueba el motor en las dos direcciones --tambien impide mover un mercado de campana-- y porque Percona 5.7 si tiene foraneas compuestas. Y el NULL con significado de N-03 sobrevive sin un caso especial: en MySQL una foranea compuesta con un componente NULL no se comprueba</t>
+          <t>No se pide: es el unico que puede ser, y pedirlo seria pedirle al operador que repita un dato que el sistema ya sabe. De ahi sale el cupo por mercado (target_creators, 7.3) y el reparto de entregables por pais en 7.5. agreed_amount nace en CERO a proposito: el compromiso economico se congela al aceptar (BR-CREATOR-008), no al meter a alguien en una lista, y un candidato con importe es un acuerdo que nadie ha firmado</t>
         </is>
       </c>
     </row>
     <row r="147" ht="23.25" customHeight="1" s="36">
       <c r="A147" s="67" t="inlineStr">
         <is>
-          <t>DEC-097</t>
+          <t>DEC-100</t>
         </is>
       </c>
       <c r="B147" s="68" t="inlineStr">
@@ -19208,24 +19258,24 @@
       <c r="C147" s="68" t="n"/>
       <c r="D147" s="69" t="inlineStr">
         <is>
-          <t>El pais de un mercado no necesita cobertura de facturacion.</t>
+          <t>Una categoria que el creador declaro que NO trabaja lo excluye del buscador.</t>
         </is>
       </c>
       <c r="E147" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F147" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-003 resuelve quien factura por el pais del CLIENTE: un cliente peruano puede pagar una campana que corre en Colombia sin que el grupo tenga sociedad alli, y exigir cobertura en el mercado bloquearia hoy toda campana fuera de Peru. Lo que si puede hacer falta es como se le paga a un creador colombiano, y eso es Q-40, que sigue abierta y desde 7.3 tiene caso de uso</t>
+          <t>Es media BR-CAMPAIGN-007 --roja, y hasta 7.4 sin nada detras-- y es la mitad que ya se puede comprobar con lo que hay en el modelo: creator_restrictions contra client_brand_categories. El creador ya dijo que no; invitarlo es hacerle perder el tiempo a los dos. Se sigue viendo con el interruptor de descartados, para poder auditar por que falta alguien. Competidores y exclusividades vigentes llegan en 7.11</t>
         </is>
       </c>
     </row>
     <row r="148" ht="23.25" customHeight="1" s="36">
       <c r="A148" s="67" t="inlineStr">
         <is>
-          <t>DEC-096</t>
+          <t>DEC-099</t>
         </is>
       </c>
       <c r="B148" s="68" t="inlineStr">
@@ -19236,24 +19286,24 @@
       <c r="C148" s="68" t="n"/>
       <c r="D148" s="69" t="inlineStr">
         <is>
-          <t>De una campana confirmada se ANADE un mercado, no se quita.</t>
+          <t>El buscador ensena a todos los activos; el veto real salta al anadir.</t>
         </is>
       </c>
       <c r="E148" s="69" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F148" s="69" t="inlineStr">
         <is>
-          <t>Ampliar a un pais nuevo es una decision comercial normal y no rompe nada de lo prometido; quitar puede dejar fuera a creadores ya invitados o aceptados, y eso exige una enmienda aceptada por las dos partes (BR-CAMPAIGN-003). Lo impide tg_cm_no_quitar_confirmada, un BEFORE DELETE que mira el estado de la CAMPANA y no una columna propia: el congelado de un mercado no es un hecho del mercado. Y hace falta el disparador precisamente porque la regla es asimetrica: una simetrica --«confirmada, no se toca»-- se explica de memoria; una asimetrica se olvida en la mitad de los sitios</t>
+          <t>Un creador activado en junio al que en agosto se le retiro el medio de pago sigue con status = 'active': sale en la busqueda, con lo que le falta a la vista, y NO entra en la lista corta. Dos motivos: revalidar los seis requisitos de BR-CREATOR-006 por candidato y por busqueda es caro --en el veto se hace una vez, sobre uno-- y un creador que desaparece sin explicacion parece un fallo del sistema, mientras que uno que sale con «le falta el medio de pago» es una tarea. El veto usa CompletitudOperativa, la MISMA clase que decide la activacion y no una copia: si manana se anade un septimo requisito, lo hereda sin que nadie se acuerde de venir aqui</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="36">
       <c r="A149" s="67" t="inlineStr">
         <is>
-          <t>DEC-095</t>
+          <t>DEC-098</t>
         </is>
       </c>
       <c r="B149" s="68" t="inlineStr">
@@ -19264,7 +19314,7 @@
       <c r="C149" s="68" t="n"/>
       <c r="D149" s="69" t="inlineStr">
         <is>
-          <t>Una campana necesita al menos un mercado para salir de borrador.</t>
+          <t>Que el mercado sea DE la campana lo garantiza el esquema, con foraneas COMPUESTAS.</t>
         </is>
       </c>
       <c r="E149" s="69" t="inlineStr">
@@ -19274,14 +19324,14 @@
       </c>
       <c r="F149" s="69" t="inlineStr">
         <is>
-          <t>Tercer motivo de BR-CAMPAIGN-004, junto al brief y al ingreso declarado. Una campana que no dice donde se ejecuta es una campana que nadie puede empezar: de ahi sale a quien se puede invitar (7.4). Cliente y marca los garantiza el esquema; el mercado no puede --un CHECK no cuenta filas de otra tabla-- asi que vive en Campanas::loQueFaltaParaSalirDeBorrador(), con los otros dos y diciendolos todos de una vez</t>
+          <t>campaign_requirements.campaign_market_id y campaign_creators.campaign_market_id apuntaban a campaign_markets(id), y una foranea asi solo comprueba que el mercado exista: nada impedia un requisito de la campana A colgado del mercado de la campana B, ni un creador aceptado atribuido al pais de otra campana. Se anade uq_cm_id_campaign (id, campaign_id) --redundante como clave, necesaria como destino-- y las dos foraneas pasan a (campaign_market_id, campaign_id). Se prefiere a un disparador porque la comprueba el motor en las dos direcciones --tambien impide mover un mercado de campana-- y porque Percona 5.7 si tiene foraneas compuestas. Y el NULL con significado de N-03 sobrevive sin un caso especial: en MySQL una foranea compuesta con un componente NULL no se comprueba</t>
         </is>
       </c>
     </row>
     <row r="150" ht="68.25" customHeight="1" s="36">
       <c r="A150" s="67" t="inlineStr">
         <is>
-          <t>DEC-094</t>
+          <t>DEC-097</t>
         </is>
       </c>
       <c r="B150" s="68" t="inlineStr">
@@ -19292,24 +19342,24 @@
       <c r="C150" s="68" t="n"/>
       <c r="D150" s="69" t="inlineStr">
         <is>
-          <t>La regla se recorta a los estados NO iniciales, como sus dos hermanas.</t>
+          <t>El pais de un mercado no necesita cobertura de facturacion.</t>
         </is>
       </c>
       <c r="E150" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F150" s="69" t="inlineStr">
         <is>
-          <t>La primera version de ck_camp_revenue_declarado no lo hacia y habria rechazado toda campana recien creada: revenue_amount e is_gratis nacen los dos a cero, asi que el formulario vacio violaba la regla antes de que nadie pudiera teclear el precio. Es la misma forma que ck_camp_confirmed y ck_camp_billing_entity: *o estas todavia escribiendo la campana, o el dato existe*. Un borrador tiene derecho a estar a medias; lo que no puede es salir de ahi asi</t>
+          <t>BR-LE-003 resuelve quien factura por el pais del CLIENTE: un cliente peruano puede pagar una campana que corre en Colombia sin que el grupo tenga sociedad alli, y exigir cobertura en el mercado bloquearia hoy toda campana fuera de Peru. Lo que si puede hacer falta es como se le paga a un creador colombiano, y eso es Q-40, que sigue abierta y desde 7.3 tiene caso de uso</t>
         </is>
       </c>
     </row>
     <row r="151" ht="23.25" customHeight="1" s="36">
       <c r="A151" s="67" t="inlineStr">
         <is>
-          <t>DEC-093</t>
+          <t>DEC-096</t>
         </is>
       </c>
       <c r="B151" s="68" t="inlineStr">
@@ -19320,24 +19370,24 @@
       <c r="C151" s="68" t="n"/>
       <c r="D151" s="69" t="inlineStr">
         <is>
-          <t>Ingreso cero es valido, pero hay que declararlo.</t>
+          <t>De una campana confirmada se ANADE un mercado, no se quita.</t>
         </is>
       </c>
       <c r="E151" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F151" s="69" t="inlineStr">
         <is>
-          <t>revenue_amount = 0 respondia a dos preguntas distintas con el mismo numero --«esta campana se regala» (canje, cortesia, prueba) y «nadie le ha puesto precio»--, y ante un margen descuadrado la diferencia entre las dos es la diferencia entre «salio como se planeo» y «se nos escapo». Columna is_gratis y ck_camp_revenue_declarado. Va en la BASE y no en la pantalla porque la pregunta que hay que poder responder dentro de un ano es «¿esta campana de cero se regalo o se nos olvido cobrarla?», y esa respuesta tiene que sobrevivir a una importacion y a la proxima pantalla que alguien escriba. Mismo valor por omision que parecia una respuesta que DEC-048 y DEC-068</t>
+          <t>Ampliar a un pais nuevo es una decision comercial normal y no rompe nada de lo prometido; quitar puede dejar fuera a creadores ya invitados o aceptados, y eso exige una enmienda aceptada por las dos partes (BR-CAMPAIGN-003). Lo impide tg_cm_no_quitar_confirmada, un BEFORE DELETE que mira el estado de la CAMPANA y no una columna propia: el congelado de un mercado no es un hecho del mercado. Y hace falta el disparador precisamente porque la regla es asimetrica: una simetrica --«confirmada, no se toca»-- se explica de memoria; una asimetrica se olvida en la mitad de los sitios</t>
         </is>
       </c>
     </row>
     <row r="152" ht="34.5" customHeight="1" s="36">
       <c r="A152" s="67" t="inlineStr">
         <is>
-          <t>DEC-092</t>
+          <t>DEC-095</t>
         </is>
       </c>
       <c r="B152" s="68" t="inlineStr">
@@ -19348,24 +19398,24 @@
       <c r="C152" s="68" t="n"/>
       <c r="D152" s="69" t="inlineStr">
         <is>
-          <t>«Brief definido» son los REQUISITOS, no el texto del briefing.</t>
+          <t>Una campana necesita al menos un mercado para salir de borrador.</t>
         </is>
       </c>
       <c r="E152" s="69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F152" s="69" t="inlineStr">
         <is>
-          <t>BR-CAMPAIGN-004 exige «brief definido» para aprobar y no dice que es. Se decide: al menos una fila en campaign_requirements --un formato, una cantidad, un plazo--. El campo briefing sigue siendo texto libre opcional porque no se puede comprobar de verdad: un espacio en blanco cumpliria cualquier NOT NULL, asi que exigirlo anadiria friccion sin anadir garantia. Los formatos si se comprueban, y son lo que convierte «hay una campana» en «hay algo que entregar»: es lo minimo que un creador necesita para decidir si acepta</t>
+          <t>Tercer motivo de BR-CAMPAIGN-004, junto al brief y al ingreso declarado. Una campana que no dice donde se ejecuta es una campana que nadie puede empezar: de ahi sale a quien se puede invitar (7.4). Cliente y marca los garantiza el esquema; el mercado no puede --un CHECK no cuenta filas de otra tabla-- asi que vive en Campanas::loQueFaltaParaSalirDeBorrador(), con los otros dos y diciendolos todos de una vez</t>
         </is>
       </c>
     </row>
     <row r="153" ht="23.25" customHeight="1" s="36">
       <c r="A153" s="67" t="inlineStr">
         <is>
-          <t>DEC-091</t>
+          <t>DEC-094</t>
         </is>
       </c>
       <c r="B153" s="68" t="inlineStr">
@@ -19376,24 +19426,24 @@
       <c r="C153" s="68" t="n"/>
       <c r="D153" s="69" t="inlineStr">
         <is>
-          <t>Aprobar una campana es de finanzas, no de quien la monta.</t>
+          <t>La regla se recorta a los estados NO iniciales, como sus dos hermanas.</t>
         </is>
       </c>
       <c r="E153" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F153" s="69" t="inlineStr">
         <is>
-          <t>Aprobar fija el ingreso comprometido y congela la sociedad emisora: es una decision de dinero, y la misma separacion que DEC-044 impone en la base para perfiles fiscales y medios de pago. Permiso nuevo campaign.approve, y vive en el GRAFO de transiciones, no en la ruta: una ruta con permiso fijo obligaria a partir la accion en dos y a acordarse de las dos al anadir un estado</t>
+          <t>La primera version de ck_camp_revenue_declarado no lo hacia y habria rechazado toda campana recien creada: revenue_amount e is_gratis nacen los dos a cero, asi que el formulario vacio violaba la regla antes de que nadie pudiera teclear el precio. Es la misma forma que ck_camp_confirmed y ck_camp_billing_entity: *o estas todavia escribiendo la campana, o el dato existe*. Un borrador tiene derecho a estar a medias; lo que no puede es salir de ahi asi</t>
         </is>
       </c>
     </row>
     <row r="154" ht="23.25" customHeight="1" s="36">
       <c r="A154" s="67" t="inlineStr">
         <is>
-          <t>DEC-090</t>
+          <t>DEC-093</t>
         </is>
       </c>
       <c r="B154" s="68" t="inlineStr">
@@ -19404,24 +19454,24 @@
       <c r="C154" s="68" t="n"/>
       <c r="D154" s="69" t="inlineStr">
         <is>
-          <t>Se congela al confirmar, no al salir de borrador.</t>
+          <t>Ingreso cero es valido, pero hay que declararlo.</t>
         </is>
       </c>
       <c r="E154" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F154" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-002 dice «inmutable una vez emitido» y para una campana «emitido» es ambiguo. Mientras es draft o pending_approval se corrige un dedazo; con confirmed_at puesto, no se toca. Lo impone tg_camp_entidad_congelada y no el controlador: de este dato depende que una factura de dentro de dos anos siga sabiendo quien la emitio, asi que tiene que sobrevivir a un UPDATE de mantenimiento. La alternativa --congelar al salir de borrador-- llenaria el historico de campanas cancelled que no se cancelaron por negocio, y un estado que miente sobre por que existe es peor que un campo editable un rato mas</t>
+          <t>revenue_amount = 0 respondia a dos preguntas distintas con el mismo numero --«esta campana se regala» (canje, cortesia, prueba) y «nadie le ha puesto precio»--, y ante un margen descuadrado la diferencia entre las dos es la diferencia entre «salio como se planeo» y «se nos escapo». Columna is_gratis y ck_camp_revenue_declarado. Va en la BASE y no en la pantalla porque la pregunta que hay que poder responder dentro de un ano es «¿esta campana de cero se regalo o se nos olvido cobrarla?», y esa respuesta tiene que sobrevivir a una importacion y a la proxima pantalla que alguien escriba. Mismo valor por omision que parecia una respuesta que DEC-048 y DEC-068</t>
         </is>
       </c>
     </row>
     <row r="155" ht="23.25" customHeight="1" s="36">
       <c r="A155" s="67" t="inlineStr">
         <is>
-          <t>DEC-089</t>
+          <t>DEC-092</t>
         </is>
       </c>
       <c r="B155" s="68" t="inlineStr">
@@ -19432,24 +19482,24 @@
       <c r="C155" s="68" t="n"/>
       <c r="D155" s="69" t="inlineStr">
         <is>
-          <t>La sociedad que factura una campana se resuelve a starts_on.</t>
+          <t>«Brief definido» son los REQUISITOS, no el texto del briefing.</t>
         </is>
       </c>
       <c r="E155" s="69" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="F155" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-003 dice «en la fecha de la operacion»; para una campana esa fecha es cuando empieza a prestarse el servicio, que es lo que un contador defiende ante SUNAT. Consecuencia: una campana creada en diciembre para arrancar en febrero usa la cobertura de FEBRERO, asi que si la cobertura cambia el 1 de enero la campana nace ya con la sociedad correcta en vez de con una que habria que corregir --y corregirla es justo lo que DEC-090 impide--</t>
+          <t>BR-CAMPAIGN-004 exige «brief definido» para aprobar y no dice que es. Se decide: al menos una fila en campaign_requirements --un formato, una cantidad, un plazo--. El campo briefing sigue siendo texto libre opcional porque no se puede comprobar de verdad: un espacio en blanco cumpliria cualquier NOT NULL, asi que exigirlo anadiria friccion sin anadir garantia. Los formatos si se comprueban, y son lo que convierte «hay una campana» en «hay algo que entregar»: es lo minimo que un creador necesita para decidir si acepta</t>
         </is>
       </c>
     </row>
     <row r="156" ht="23.25" customHeight="1" s="36">
       <c r="A156" s="67" t="inlineStr">
         <is>
-          <t>DEC-088</t>
+          <t>DEC-091</t>
         </is>
       </c>
       <c r="B156" s="68" t="inlineStr">
@@ -19460,24 +19510,24 @@
       <c r="C156" s="68" t="n"/>
       <c r="D156" s="69" t="inlineStr">
         <is>
-          <t>La aritmetica de vigencias vive en Vigencia, y una puerta lo comprueba.</t>
+          <t>Aprobar una campana es de finanzas, no de quien la monta.</t>
         </is>
       </c>
       <c r="E156" s="69" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="F156" s="69" t="inlineStr">
         <is>
-          <t>El error de un dia --cerrar un periodo el mismo dia en que empieza el siguiente, siendo valid_to inclusivo-- ha aparecido NUEVE veces. Vigencia (4.5) le dio un sitio; tools/verificar-vigencias.php impide que vuelva a salir de el. Dos reglas: ninguna aritmetica de dias fuera de Vigencia, y ninguna comparacion de una columna de vigencia contra algo sin normalizar. Escrita en PHP con token_get_all() y no en Python con expresiones regulares, porque los comentarios de este proyecto nombran el defecto y las migraciones llevan SQL con &gt;= dentro: una regex se acusaria a si misma. Al estrenarla quedaban tres sitios sueltos, los tres escritos DESPUES de Vigencia, y uno era un fallo real ----desde=2026-2-1 contra effective_from como cadenas, dejando dos textos legales vigentes el mismo dia--. Ver docs/fase-4/4.7-PUERTA-VIGENCIAS.md</t>
+          <t>Aprobar fija el ingreso comprometido y congela la sociedad emisora: es una decision de dinero, y la misma separacion que DEC-044 impone en la base para perfiles fiscales y medios de pago. Permiso nuevo campaign.approve, y vive en el GRAFO de transiciones, no en la ruta: una ruta con permiso fijo obligaria a partir la accion en dos y a acordarse de las dos al anadir un estado</t>
         </is>
       </c>
     </row>
     <row r="157" ht="23.25" customHeight="1" s="36">
       <c r="A157" s="67" t="inlineStr">
         <is>
-          <t>DEC-087</t>
+          <t>DEC-090</t>
         </is>
       </c>
       <c r="B157" s="68" t="inlineStr">
@@ -19488,24 +19538,24 @@
       <c r="C157" s="68" t="n"/>
       <c r="D157" s="69" t="inlineStr">
         <is>
-          <t>Un 1062 se absorbe o se cuenta segun quien eligio el valor, y hay que NOMBRAR el indice para absorberlo.</t>
+          <t>Se congela al confirmar, no al salir de borrador.</t>
         </is>
       </c>
       <c r="E157" s="69" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="F157" s="69" t="inlineStr">
         <is>
-          <t>Si el valor lo calculo el sistema —el slug de una marca— el choque se recalcula y se reintenta en silencio. Si lo escribio la persona —un RUC, el nombre de una marca— tiene que llegar arriba con palabras. App\Shared\Database\Choque obliga a elegir: reintentar() exige el nombre del indice y vuelve a lanzar cualquier otro a la primera, porque un catch (QueryException) a secas absorberia el RUC repetido igual que el slug. Tres intentos como tope: un bucle sin tope convierte un indice mal entendido en una peticion eterna. El nombre se lee cortando por el ultimo punto —MySQL 8 antepone la tabla y Percona 5.7 no—, comprobado contra los dos motores</t>
+          <t>BR-LE-002 dice «inmutable una vez emitido» y para una campana «emitido» es ambiguo. Mientras es draft o pending_approval se corrige un dedazo; con confirmed_at puesto, no se toca. Lo impone tg_camp_entidad_congelada y no el controlador: de este dato depende que una factura de dentro de dos anos siga sabiendo quien la emitio, asi que tiene que sobrevivir a un UPDATE de mantenimiento. La alternativa --congelar al salir de borrador-- llenaria el historico de campanas cancelled que no se cancelaron por negocio, y un estado que miente sobre por que existe es peor que un campo editable un rato mas</t>
         </is>
       </c>
     </row>
     <row r="158" ht="57" customHeight="1" s="36">
       <c r="A158" s="67" t="inlineStr">
         <is>
-          <t>DEC-086</t>
+          <t>DEC-089</t>
         </is>
       </c>
       <c r="B158" s="68" t="inlineStr">
@@ -19516,16 +19566,24 @@
       <c r="C158" s="68" t="n"/>
       <c r="D158" s="69" t="inlineStr">
         <is>
-          <t>La contraseña temporal deja de ser válida en el primer acceso</t>
-        </is>
-      </c>
-      <c r="E158" s="69" t="n"/>
-      <c r="F158" s="69" t="n"/>
+          <t>La sociedad que factura una campana se resuelve a starts_on.</t>
+        </is>
+      </c>
+      <c r="E158" s="69" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="F158" s="69" t="inlineStr">
+        <is>
+          <t>BR-LE-003 dice «en la fecha de la operacion»; para una campana esa fecha es cuando empieza a prestarse el servicio, que es lo que un contador defiende ante SUNAT. Consecuencia: una campana creada en diciembre para arrancar en febrero usa la cobertura de FEBRERO, asi que si la cobertura cambia el 1 de enero la campana nace ya con la sociedad correcta en vez de con una que habria que corregir --y corregirla es justo lo que DEC-090 impide--</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="23.25" customHeight="1" s="36">
       <c r="A159" s="67" t="inlineStr">
         <is>
-          <t>DEC-085</t>
+          <t>DEC-088</t>
         </is>
       </c>
       <c r="B159" s="68" t="inlineStr">
@@ -19536,16 +19594,24 @@
       <c r="C159" s="68" t="n"/>
       <c r="D159" s="69" t="inlineStr">
         <is>
-          <t>La bitácora la protegen dos usuarios de base de datos, no el esquema</t>
-        </is>
-      </c>
-      <c r="E159" s="69" t="n"/>
-      <c r="F159" s="69" t="n"/>
+          <t>La aritmetica de vigencias vive en Vigencia, y una puerta lo comprueba.</t>
+        </is>
+      </c>
+      <c r="E159" s="69" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="F159" s="69" t="inlineStr">
+        <is>
+          <t>El error de un dia --cerrar un periodo el mismo dia en que empieza el siguiente, siendo valid_to inclusivo-- ha aparecido NUEVE veces. Vigencia (4.5) le dio un sitio; tools/verificar-vigencias.php impide que vuelva a salir de el. Dos reglas: ninguna aritmetica de dias fuera de Vigencia, y ninguna comparacion de una columna de vigencia contra algo sin normalizar. Escrita en PHP con token_get_all() y no en Python con expresiones regulares, porque los comentarios de este proyecto nombran el defecto y las migraciones llevan SQL con &gt;= dentro: una regex se acusaria a si misma. Al estrenarla quedaban tres sitios sueltos, los tres escritos DESPUES de Vigencia, y uno era un fallo real ----desde=2026-2-1 contra effective_from como cadenas, dejando dos textos legales vigentes el mismo dia--. Ver docs/fase-4/4.7-PUERTA-VIGENCIAS.md</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="34.5" customHeight="1" s="36">
       <c r="A160" s="67" t="inlineStr">
         <is>
-          <t>DEC-084</t>
+          <t>DEC-087</t>
         </is>
       </c>
       <c r="B160" s="68" t="inlineStr">
@@ -19556,16 +19622,24 @@
       <c r="C160" s="68" t="n"/>
       <c r="D160" s="69" t="inlineStr">
         <is>
-          <t>«Perfil fiscal vigente» exige que ya haya empezado</t>
-        </is>
-      </c>
-      <c r="E160" s="69" t="n"/>
-      <c r="F160" s="69" t="n"/>
+          <t>Un 1062 se absorbe o se cuenta segun quien eligio el valor, y hay que NOMBRAR el indice para absorberlo.</t>
+        </is>
+      </c>
+      <c r="E160" s="69" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="F160" s="69" t="inlineStr">
+        <is>
+          <t>Si el valor lo calculo el sistema —el slug de una marca— el choque se recalcula y se reintenta en silencio. Si lo escribio la persona —un RUC, el nombre de una marca— tiene que llegar arriba con palabras. App\Shared\Database\Choque obliga a elegir: reintentar() exige el nombre del indice y vuelve a lanzar cualquier otro a la primera, porque un catch (QueryException) a secas absorberia el RUC repetido igual que el slug. Tres intentos como tope: un bucle sin tope convierte un indice mal entendido en una peticion eterna. El nombre se lee cortando por el ultimo punto —MySQL 8 antepone la tabla y Percona 5.7 no—, comprobado contra los dos motores</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="34.5" customHeight="1" s="36">
       <c r="A161" s="67" t="inlineStr">
         <is>
-          <t>DEC-083</t>
+          <t>DEC-086</t>
         </is>
       </c>
       <c r="B161" s="68" t="inlineStr">
@@ -19576,7 +19650,7 @@
       <c r="C161" s="68" t="n"/>
       <c r="D161" s="69" t="inlineStr">
         <is>
-          <t>«Cuenta compartida» se calcula al leer, no se guarda</t>
+          <t>La contraseña temporal deja de ser válida en el primer acceso</t>
         </is>
       </c>
       <c r="E161" s="69" t="n"/>
@@ -19585,7 +19659,7 @@
     <row r="162" ht="45.75" customHeight="1" s="36">
       <c r="A162" s="67" t="inlineStr">
         <is>
-          <t>DEC-082</t>
+          <t>DEC-085</t>
         </is>
       </c>
       <c r="B162" s="68" t="inlineStr">
@@ -19596,7 +19670,7 @@
       <c r="C162" s="68" t="n"/>
       <c r="D162" s="69" t="inlineStr">
         <is>
-          <t>Las sociedades del grupo las gestiona sólo admin</t>
+          <t>La bitácora la protegen dos usuarios de base de datos, no el esquema</t>
         </is>
       </c>
       <c r="E162" s="69" t="n"/>
@@ -19605,7 +19679,7 @@
     <row r="163" ht="34.5" customHeight="1" s="36">
       <c r="A163" s="67" t="inlineStr">
         <is>
-          <t>DEC-081</t>
+          <t>DEC-084</t>
         </is>
       </c>
       <c r="B163" s="68" t="inlineStr">
@@ -19616,7 +19690,7 @@
       <c r="C163" s="68" t="n"/>
       <c r="D163" s="69" t="inlineStr">
         <is>
-          <t>Dar de baja una sociedad cierra sus coberturas abiertas</t>
+          <t>«Perfil fiscal vigente» exige que ya haya empezado</t>
         </is>
       </c>
       <c r="E163" s="69" t="n"/>
@@ -19625,7 +19699,7 @@
     <row r="164" ht="23.25" customHeight="1" s="36">
       <c r="A164" s="67" t="inlineStr">
         <is>
-          <t>DEC-080</t>
+          <t>DEC-083</t>
         </is>
       </c>
       <c r="B164" s="68" t="inlineStr">
@@ -19636,7 +19710,7 @@
       <c r="C164" s="68" t="n"/>
       <c r="D164" s="69" t="inlineStr">
         <is>
-          <t>Un gate que comprueba que los nombres entre capas existen</t>
+          <t>«Cuenta compartida» se calcula al leer, no se guarda</t>
         </is>
       </c>
       <c r="E164" s="69" t="n"/>
@@ -19645,7 +19719,7 @@
     <row r="165" ht="23.25" customHeight="1" s="36">
       <c r="A165" s="67" t="inlineStr">
         <is>
-          <t>DEC-079</t>
+          <t>DEC-082</t>
         </is>
       </c>
       <c r="B165" s="68" t="inlineStr">
@@ -19656,7 +19730,7 @@
       <c r="C165" s="68" t="n"/>
       <c r="D165" s="69" t="inlineStr">
         <is>
-          <t>La identidad fiscal del cliente tiene permiso propio, en dos roles</t>
+          <t>Las sociedades del grupo las gestiona sólo admin</t>
         </is>
       </c>
       <c r="E165" s="69" t="n"/>
@@ -19665,7 +19739,7 @@
     <row r="166" ht="23.25" customHeight="1" s="36">
       <c r="A166" s="67" t="inlineStr">
         <is>
-          <t>DEC-078</t>
+          <t>DEC-081</t>
         </is>
       </c>
       <c r="B166" s="68" t="inlineStr">
@@ -19676,7 +19750,7 @@
       <c r="C166" s="68" t="n"/>
       <c r="D166" s="69" t="inlineStr">
         <is>
-          <t>El histórico fiscal del cliente está congelado</t>
+          <t>Dar de baja una sociedad cierra sus coberturas abiertas</t>
         </is>
       </c>
       <c r="E166" s="69" t="n"/>
@@ -19685,7 +19759,7 @@
     <row r="167" ht="34.5" customHeight="1" s="36">
       <c r="A167" s="67" t="inlineStr">
         <is>
-          <t>DEC-077</t>
+          <t>DEC-080</t>
         </is>
       </c>
       <c r="B167" s="68" t="inlineStr">
@@ -19696,7 +19770,7 @@
       <c r="C167" s="68" t="n"/>
       <c r="D167" s="69" t="inlineStr">
         <is>
-          <t>Un contacto no cambia de cliente</t>
+          <t>Un gate que comprueba que los nombres entre capas existen</t>
         </is>
       </c>
       <c r="E167" s="69" t="n"/>
@@ -19705,7 +19779,7 @@
     <row r="168" ht="23.25" customHeight="1" s="36">
       <c r="A168" s="67" t="inlineStr">
         <is>
-          <t>DEC-076</t>
+          <t>DEC-079</t>
         </is>
       </c>
       <c r="B168" s="68" t="inlineStr">
@@ -19716,7 +19790,7 @@
       <c r="C168" s="68" t="n"/>
       <c r="D168" s="69" t="inlineStr">
         <is>
-          <t>La lista de suites de restricción vive en un solo archivo</t>
+          <t>La identidad fiscal del cliente tiene permiso propio, en dos roles</t>
         </is>
       </c>
       <c r="E168" s="69" t="n"/>
@@ -19725,7 +19799,7 @@
     <row r="169" ht="45.75" customHeight="1" s="36">
       <c r="A169" s="67" t="inlineStr">
         <is>
-          <t>DEC-075</t>
+          <t>DEC-078</t>
         </is>
       </c>
       <c r="B169" s="68" t="inlineStr">
@@ -19736,7 +19810,7 @@
       <c r="C169" s="68" t="n"/>
       <c r="D169" s="69" t="inlineStr">
         <is>
-          <t>El relevo del contacto principal se hace, no se rechaza</t>
+          <t>El histórico fiscal del cliente está congelado</t>
         </is>
       </c>
       <c r="E169" s="69" t="n"/>
@@ -19745,7 +19819,7 @@
     <row r="170" ht="45.75" customHeight="1" s="36">
       <c r="A170" s="67" t="inlineStr">
         <is>
-          <t>DEC-074</t>
+          <t>DEC-077</t>
         </is>
       </c>
       <c r="B170" s="68" t="inlineStr">
@@ -19756,7 +19830,7 @@
       <c r="C170" s="68" t="n"/>
       <c r="D170" s="69" t="inlineStr">
         <is>
-          <t>Al dar de alta un cliente se crea su primera marca</t>
+          <t>Un contacto no cambia de cliente</t>
         </is>
       </c>
       <c r="E170" s="69" t="n"/>
@@ -19765,7 +19839,7 @@
     <row r="171" ht="23.25" customHeight="1" s="36">
       <c r="A171" s="67" t="inlineStr">
         <is>
-          <t>DEC-073</t>
+          <t>DEC-076</t>
         </is>
       </c>
       <c r="B171" s="68" t="inlineStr">
@@ -19776,20 +19850,16 @@
       <c r="C171" s="68" t="n"/>
       <c r="D171" s="69" t="inlineStr">
         <is>
-          <t>Un prospecto se apunta en cualquier país; activarlo exige cobertura</t>
-        </is>
-      </c>
-      <c r="E171" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>La lista de suites de restricción vive en un solo archivo</t>
+        </is>
+      </c>
+      <c r="E171" s="69" t="n"/>
       <c r="F171" s="69" t="n"/>
     </row>
     <row r="172" ht="34.5" customHeight="1" s="36">
       <c r="A172" s="67" t="inlineStr">
         <is>
-          <t>DEC-072</t>
+          <t>DEC-075</t>
         </is>
       </c>
       <c r="B172" s="68" t="inlineStr">
@@ -19800,7 +19870,7 @@
       <c r="C172" s="68" t="n"/>
       <c r="D172" s="69" t="inlineStr">
         <is>
-          <t>creator_addresses queda fuera de la regla de periodos</t>
+          <t>El relevo del contacto principal se hace, no se rechaza</t>
         </is>
       </c>
       <c r="E172" s="69" t="n"/>
@@ -19809,7 +19879,7 @@
     <row r="173" ht="34.5" customHeight="1" s="36">
       <c r="A173" s="67" t="inlineStr">
         <is>
-          <t>DEC-071</t>
+          <t>DEC-074</t>
         </is>
       </c>
       <c r="B173" s="68" t="inlineStr">
@@ -19820,7 +19890,7 @@
       <c r="C173" s="68" t="n"/>
       <c r="D173" s="69" t="inlineStr">
         <is>
-          <t>Un perfil fiscal nuevo no puede empezar antes que el vigente</t>
+          <t>Al dar de alta un cliente se crea su primera marca</t>
         </is>
       </c>
       <c r="E173" s="69" t="n"/>
@@ -19829,7 +19899,7 @@
     <row r="174" ht="45.75" customHeight="1" s="36">
       <c r="A174" s="67" t="inlineStr">
         <is>
-          <t>DEC-070</t>
+          <t>DEC-073</t>
         </is>
       </c>
       <c r="B174" s="68" t="inlineStr">
@@ -19840,16 +19910,20 @@
       <c r="C174" s="68" t="n"/>
       <c r="D174" s="69" t="inlineStr">
         <is>
-          <t>Un bloqueo de agenda se registra aunque pise una campaña aceptada</t>
-        </is>
-      </c>
-      <c r="E174" s="69" t="n"/>
+          <t>Un prospecto se apunta en cualquier país; activarlo exige cobertura</t>
+        </is>
+      </c>
+      <c r="E174" s="69" t="inlineStr">
+        <is>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
+        </is>
+      </c>
       <c r="F174" s="69" t="n"/>
     </row>
     <row r="175" ht="34.5" customHeight="1" s="36">
       <c r="A175" s="67" t="inlineStr">
         <is>
-          <t>DEC-069</t>
+          <t>DEC-072</t>
         </is>
       </c>
       <c r="B175" s="68" t="inlineStr">
@@ -19860,20 +19934,16 @@
       <c r="C175" s="68" t="n"/>
       <c r="D175" s="69" t="inlineStr">
         <is>
-          <t>Las tarifas tienen permiso propio: creator.rate.manage</t>
-        </is>
-      </c>
-      <c r="E175" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>creator_addresses queda fuera de la regla de periodos</t>
+        </is>
+      </c>
+      <c r="E175" s="69" t="n"/>
       <c r="F175" s="69" t="n"/>
     </row>
     <row r="176" ht="45.75" customHeight="1" s="36">
       <c r="A176" s="67" t="inlineStr">
         <is>
-          <t>DEC-068</t>
+          <t>DEC-071</t>
         </is>
       </c>
       <c r="B176" s="68" t="inlineStr">
@@ -19884,20 +19954,16 @@
       <c r="C176" s="68" t="n"/>
       <c r="D176" s="69" t="inlineStr">
         <is>
-          <t>Cero es un precio válido, pero hay que declararlo</t>
-        </is>
-      </c>
-      <c r="E176" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
-        </is>
-      </c>
+          <t>Un perfil fiscal nuevo no puede empezar antes que el vigente</t>
+        </is>
+      </c>
+      <c r="E176" s="69" t="n"/>
       <c r="F176" s="69" t="n"/>
     </row>
     <row r="177" ht="34.5" customHeight="1" s="36">
       <c r="A177" s="67" t="inlineStr">
         <is>
-          <t>DEC-067</t>
+          <t>DEC-070</t>
         </is>
       </c>
       <c r="B177" s="68" t="inlineStr">
@@ -19908,20 +19974,16 @@
       <c r="C177" s="68" t="n"/>
       <c r="D177" s="69" t="inlineStr">
         <is>
-          <t>Los dos permisos de medios de pago van al rol finance</t>
-        </is>
-      </c>
-      <c r="E177" s="69" t="inlineStr">
-        <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
-        </is>
-      </c>
+          <t>Un bloqueo de agenda se registra aunque pise una campaña aceptada</t>
+        </is>
+      </c>
+      <c r="E177" s="69" t="n"/>
       <c r="F177" s="69" t="n"/>
     </row>
     <row r="178" ht="34.5" customHeight="1" s="36">
       <c r="A178" s="67" t="inlineStr">
         <is>
-          <t>DEC-066</t>
+          <t>DEC-069</t>
         </is>
       </c>
       <c r="B178" s="68" t="inlineStr">
@@ -19932,12 +19994,12 @@
       <c r="C178" s="68" t="n"/>
       <c r="D178" s="69" t="inlineStr">
         <is>
-          <t>La cuenta de un medio de pago es inmutable: se sustituye, no se edita</t>
+          <t>Las tarifas tienen permiso propio: creator.rate.manage</t>
         </is>
       </c>
       <c r="E178" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
         </is>
       </c>
       <c r="F178" s="69" t="n"/>
@@ -19945,7 +20007,7 @@
     <row r="179" ht="23.25" customHeight="1" s="36">
       <c r="A179" s="67" t="inlineStr">
         <is>
-          <t>DEC-065</t>
+          <t>DEC-068</t>
         </is>
       </c>
       <c r="B179" s="68" t="inlineStr">
@@ -19956,12 +20018,12 @@
       <c r="C179" s="68" t="n"/>
       <c r="D179" s="69" t="inlineStr">
         <is>
-          <t>La misma cuenta en dos creadores se marca, no se rechaza</t>
+          <t>Cero es un precio válido, pero hay que declararlo</t>
         </is>
       </c>
       <c r="E179" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
+          <t>ADOPTADA e implementada (2026-08-24, iteración 3.9)</t>
         </is>
       </c>
       <c r="F179" s="69" t="n"/>
@@ -19969,7 +20031,7 @@
     <row r="180" ht="34.5" customHeight="1" s="36">
       <c r="A180" s="67" t="inlineStr">
         <is>
-          <t>DEC-064</t>
+          <t>DEC-067</t>
         </is>
       </c>
       <c r="B180" s="68" t="inlineStr">
@@ -19980,7 +20042,7 @@
       <c r="C180" s="68" t="n"/>
       <c r="D180" s="69" t="inlineStr">
         <is>
-          <t>El enfriamiento de un medio de pago son 24 horas, y es configuración</t>
+          <t>Los dos permisos de medios de pago van al rol finance</t>
         </is>
       </c>
       <c r="E180" s="69" t="inlineStr">
@@ -19993,7 +20055,7 @@
     <row r="181" ht="90.75" customHeight="1" s="36">
       <c r="A181" s="67" t="inlineStr">
         <is>
-          <t>DEC-063</t>
+          <t>DEC-066</t>
         </is>
       </c>
       <c r="B181" s="68" t="inlineStr">
@@ -20004,12 +20066,12 @@
       <c r="C181" s="68" t="n"/>
       <c r="D181" s="69" t="inlineStr">
         <is>
-          <t>Los umbrales de coherencia son juicio, no verdad; y no rechazan nada</t>
+          <t>La cuenta de un medio de pago es inmutable: se sustituye, no se edita</t>
         </is>
       </c>
       <c r="E181" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.7) — umbrales revisables</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F181" s="69" t="n"/>
@@ -20017,7 +20079,7 @@
     <row r="182" ht="34.5" customHeight="1" s="36">
       <c r="A182" s="67" t="inlineStr">
         <is>
-          <t>DEC-062</t>
+          <t>DEC-065</t>
         </is>
       </c>
       <c r="B182" s="68" t="inlineStr">
@@ -20028,12 +20090,12 @@
       <c r="C182" s="68" t="n"/>
       <c r="D182" s="69" t="inlineStr">
         <is>
-          <t>Los dos permisos fiscales van al mismo rol; la separación la impone la base</t>
+          <t>La misma cuenta en dos creadores se marca, no se rechaza</t>
         </is>
       </c>
       <c r="E182" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.6)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F182" s="69" t="n"/>
@@ -20041,7 +20103,7 @@
     <row r="183" ht="23.25" customHeight="1" s="36">
       <c r="A183" s="67" t="inlineStr">
         <is>
-          <t>DEC-061</t>
+          <t>DEC-064</t>
         </is>
       </c>
       <c r="B183" s="68" t="inlineStr">
@@ -20052,12 +20114,12 @@
       <c r="C183" s="68" t="n"/>
       <c r="D183" s="69" t="inlineStr">
         <is>
-          <t>Las pruebas usan una base local y desechable, nunca la de desarrollo</t>
+          <t>El enfriamiento de un medio de pago son 24 horas, y es configuración</t>
         </is>
       </c>
       <c r="E183" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.8)</t>
         </is>
       </c>
       <c r="F183" s="69" t="n"/>
@@ -20065,7 +20127,7 @@
     <row r="184" ht="34.5" customHeight="1" s="36">
       <c r="A184" s="67" t="inlineStr">
         <is>
-          <t>DEC-060</t>
+          <t>DEC-063</t>
         </is>
       </c>
       <c r="B184" s="68" t="inlineStr">
@@ -20076,12 +20138,12 @@
       <c r="C184" s="68" t="n"/>
       <c r="D184" s="69" t="inlineStr">
         <is>
-          <t>Verificar y activar son permisos distintos, pero hoy el mismo rol</t>
+          <t>Los umbrales de coherencia son juicio, no verdad; y no rechazan nada</t>
         </is>
       </c>
       <c r="E184" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-23, iteración 3.5) — decisión de negocio revisable</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.7) — umbrales revisables</t>
         </is>
       </c>
       <c r="F184" s="69" t="n"/>
@@ -20089,7 +20151,7 @@
     <row r="185" ht="34.5" customHeight="1" s="36">
       <c r="A185" s="67" t="inlineStr">
         <is>
-          <t>DEC-059</t>
+          <t>DEC-062</t>
         </is>
       </c>
       <c r="B185" s="68" t="inlineStr">
@@ -20100,12 +20162,12 @@
       <c r="C185" s="68" t="n"/>
       <c r="D185" s="69" t="inlineStr">
         <is>
-          <t>Se acepta una versión de los términos, no una página</t>
+          <t>Los dos permisos fiscales van al mismo rol; la separación la impone la base</t>
         </is>
       </c>
       <c r="E185" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.6)</t>
         </is>
       </c>
       <c r="F185" s="69" t="n"/>
@@ -20113,7 +20175,7 @@
     <row r="186" ht="34.5" customHeight="1" s="36">
       <c r="A186" s="67" t="inlineStr">
         <is>
-          <t>DEC-058</t>
+          <t>DEC-061</t>
         </is>
       </c>
       <c r="B186" s="68" t="inlineStr">
@@ -20124,7 +20186,7 @@
       <c r="C186" s="68" t="n"/>
       <c r="D186" s="69" t="inlineStr">
         <is>
-          <t>La identidad verificada es evidencia, no una casilla</t>
+          <t>Las pruebas usan una base local y desechable, nunca la de desarrollo</t>
         </is>
       </c>
       <c r="E186" s="69" t="inlineStr">
@@ -20137,7 +20199,7 @@
     <row r="187" ht="34.5" customHeight="1" s="36">
       <c r="A187" s="67" t="inlineStr">
         <is>
-          <t>DEC-057</t>
+          <t>DEC-060</t>
         </is>
       </c>
       <c r="B187" s="68" t="inlineStr">
@@ -20148,12 +20210,12 @@
       <c r="C187" s="68" t="n"/>
       <c r="D187" s="69" t="inlineStr">
         <is>
-          <t>Aprobar una solicitud no activa al creador</t>
+          <t>Verificar y activar son permisos distintos, pero hoy el mismo rol</t>
         </is>
       </c>
       <c r="E187" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.4)</t>
+          <t>ADOPTADA (2026-08-23, iteración 3.5) — decisión de negocio revisable</t>
         </is>
       </c>
       <c r="F187" s="69" t="n"/>
@@ -20161,7 +20223,7 @@
     <row r="188" ht="34.5" customHeight="1" s="36">
       <c r="A188" s="67" t="inlineStr">
         <is>
-          <t>DEC-056</t>
+          <t>DEC-059</t>
         </is>
       </c>
       <c r="B188" s="68" t="inlineStr">
@@ -20172,12 +20234,12 @@
       <c r="C188" s="68" t="n"/>
       <c r="D188" s="69" t="inlineStr">
         <is>
-          <t>La bitácora se ordena por id, no por fecha, y redacta lo sensible</t>
+          <t>Se acepta una versión de los términos, no una página</t>
         </is>
       </c>
       <c r="E188" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.3)</t>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
         </is>
       </c>
       <c r="F188" s="69" t="n"/>
@@ -20185,7 +20247,7 @@
     <row r="189" ht="34.5" customHeight="1" s="36">
       <c r="A189" s="67" t="inlineStr">
         <is>
-          <t>DEC-055</t>
+          <t>DEC-058</t>
         </is>
       </c>
       <c r="B189" s="68" t="inlineStr">
@@ -20196,24 +20258,20 @@
       <c r="C189" s="68" t="n"/>
       <c r="D189" s="69" t="inlineStr">
         <is>
-          <t>La primera pantalla de escritura no toca la identidad</t>
+          <t>La identidad verificada es evidencia, no una casilla</t>
         </is>
       </c>
       <c r="E189" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
-        </is>
-      </c>
-      <c r="F189" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Primera pantalla del proyecto que escribe: edición de creador.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-23, iteración 3.5)</t>
+        </is>
+      </c>
+      <c r="F189" s="69" t="n"/>
     </row>
     <row r="190" ht="23.25" customHeight="1" s="36">
       <c r="A190" s="67" t="inlineStr">
         <is>
-          <t>DEC-054</t>
+          <t>DEC-057</t>
         </is>
       </c>
       <c r="B190" s="68" t="inlineStr">
@@ -20224,24 +20282,20 @@
       <c r="C190" s="68" t="n"/>
       <c r="D190" s="69" t="inlineStr">
         <is>
-          <t>La bitácora es inmutable en la base, no por convención</t>
+          <t>Aprobar una solicitud no activa al creador</t>
         </is>
       </c>
       <c r="E190" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
-        </is>
-      </c>
-      <c r="F190" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — audit_logs existía desde 2.4 y nadie escribía en ella. Al ir a llenarla apareció el segundo problema: la tabla admitía UPDATE y DELETE como cualquier otra.</t>
-        </is>
-      </c>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.4)</t>
+        </is>
+      </c>
+      <c r="F190" s="69" t="n"/>
     </row>
     <row r="191" ht="23.25" customHeight="1" s="36">
       <c r="A191" s="67" t="inlineStr">
         <is>
-          <t>DEC-053</t>
+          <t>DEC-056</t>
         </is>
       </c>
       <c r="B191" s="68" t="inlineStr">
@@ -20252,12 +20306,12 @@
       <c r="C191" s="68" t="n"/>
       <c r="D191" s="69" t="inlineStr">
         <is>
-          <t>Autorización por permiso, sin atajo para el administrador</t>
+          <t>La bitácora se ordena por id, no por fecha, y redacta lo sensible</t>
         </is>
       </c>
       <c r="E191" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 3.1)</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.3)</t>
         </is>
       </c>
       <c r="F191" s="69" t="n"/>
@@ -20265,7 +20319,7 @@
     <row r="192" ht="45.75" customHeight="1" s="36">
       <c r="A192" s="67" t="inlineStr">
         <is>
-          <t>DEC-052</t>
+          <t>DEC-055</t>
         </is>
       </c>
       <c r="B192" s="68" t="inlineStr">
@@ -20276,20 +20330,24 @@
       <c r="C192" s="68" t="n"/>
       <c r="D192" s="69" t="inlineStr">
         <is>
-          <t>MySQL no admite subconsultas sobre la tabla que se está modificando</t>
+          <t>La primera pantalla de escritura no toca la identidad</t>
         </is>
       </c>
       <c r="E192" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22)</t>
-        </is>
-      </c>
-      <c r="F192" s="69" t="n"/>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
+        </is>
+      </c>
+      <c r="F192" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — Primera pantalla del proyecto que escribe: edición de creador.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="34.5" customHeight="1" s="36">
       <c r="A193" s="67" t="inlineStr">
         <is>
-          <t>DEC-051</t>
+          <t>DEC-054</t>
         </is>
       </c>
       <c r="B193" s="68" t="inlineStr">
@@ -20300,24 +20358,24 @@
       <c r="C193" s="68" t="n"/>
       <c r="D193" s="69" t="inlineStr">
         <is>
-          <t>El CI corre la suite contra los dos motores, no contra uno</t>
+          <t>La bitácora es inmutable en la base, no por convención</t>
         </is>
       </c>
       <c r="E193" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22). Recordatorio: tools/github-workflow-ci.yml sigue pendiente de mover a .github/workflows/ci.yml a mano — es ruta protegida</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.2)</t>
         </is>
       </c>
       <c r="F193" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — El CI validaba formato, análisis estático, fronteras entre módulos, migraciones y pruebas. Nada de eso comprueba que las restricciones se apliquen en el motor de producción, que no aplica CHECK.</t>
+          <t xml:space="preserve"> — audit_logs existía desde 2.4 y nadie escribía en ella. Al ir a llenarla apareció el segundo problema: la tabla admitía UPDATE y DELETE como cualquier otra.</t>
         </is>
       </c>
     </row>
     <row r="194" ht="34.5" customHeight="1" s="36">
       <c r="A194" s="67" t="inlineStr">
         <is>
-          <t>DEC-050</t>
+          <t>DEC-053</t>
         </is>
       </c>
       <c r="B194" s="68" t="inlineStr">
@@ -20328,12 +20386,12 @@
       <c r="C194" s="68" t="n"/>
       <c r="D194" s="69" t="inlineStr">
         <is>
-          <t>Las migraciones se contrastan contra el esquema de referencia, no se confía en que coincidan</t>
+          <t>Autorización por permiso, sin atajo para el administrador</t>
         </is>
       </c>
       <c r="E194" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22)</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 3.1)</t>
         </is>
       </c>
       <c r="F194" s="69" t="n"/>
@@ -20341,7 +20399,7 @@
     <row r="195" ht="23.25" customHeight="1" s="36">
       <c r="A195" s="67" t="inlineStr">
         <is>
-          <t>DEC-049</t>
+          <t>DEC-052</t>
         </is>
       </c>
       <c r="B195" s="68" t="inlineStr">
@@ -20352,7 +20410,7 @@
       <c r="C195" s="68" t="n"/>
       <c r="D195" s="69" t="inlineStr">
         <is>
-          <t>Sin datos fiscales no hay alta, pero acompañamos a formalizarse</t>
+          <t>MySQL no admite subconsultas sobre la tabla que se está modificando</t>
         </is>
       </c>
       <c r="E195" s="69" t="inlineStr">
@@ -20360,16 +20418,12 @@
           <t>ADOPTADA (2026-08-22)</t>
         </is>
       </c>
-      <c r="F195" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Respuesta a Q-45. La propuesta inicial era pagar a un familiar del creador con declaración jurada de parentesco. El análisis de docs/fase-2/2.14-PAGO-A-TERCEROS.md identificó tres problemas: el comprobante deja de coincidir con el pago (riesgo de gasto reparable para la empresa que paga), señales de alerta de prevención de lavado, y contradicción con BR-FIN-003, que ya está implementada.</t>
-        </is>
-      </c>
+      <c r="F195" s="69" t="n"/>
     </row>
     <row r="196" ht="57" customHeight="1" s="36">
       <c r="A196" s="67" t="inlineStr">
         <is>
-          <t>DEC-048</t>
+          <t>DEC-051</t>
         </is>
       </c>
       <c r="B196" s="68" t="inlineStr">
@@ -20380,24 +20434,24 @@
       <c r="C196" s="68" t="n"/>
       <c r="D196" s="69" t="inlineStr">
         <is>
-          <t>La retención tiene tres estados, no dos</t>
+          <t>El CI corre la suite contra los dos motores, no contra uno</t>
         </is>
       </c>
       <c r="E196" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.15)</t>
+          <t>ADOPTADA (2026-08-22). Recordatorio: tools/github-workflow-ci.yml sigue pendiente de mover a .github/workflows/ci.yml a mano — es ruta protegida</t>
         </is>
       </c>
       <c r="F196" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Sobre Q-40 se decidió «que el modelo lo deje configurable». Al implementarlo apareció que el riesgo que yo había señalado —*«alguien pone un número a ojo y nadie se entera»*— ya estaba dentro del modelo, y era peor.</t>
+          <t xml:space="preserve"> — El CI validaba formato, análisis estático, fronteras entre módulos, migraciones y pruebas. Nada de eso comprueba que las restricciones se apliquen en el motor de producción, que no aplica CHECK.</t>
         </is>
       </c>
     </row>
     <row r="197" ht="23.25" customHeight="1" s="36">
       <c r="A197" s="67" t="inlineStr">
         <is>
-          <t>DEC-047</t>
+          <t>DEC-050</t>
         </is>
       </c>
       <c r="B197" s="68" t="inlineStr">
@@ -20408,7 +20462,7 @@
       <c r="C197" s="68" t="n"/>
       <c r="D197" s="69" t="inlineStr">
         <is>
-          <t>Se factura a todos los países desde Perú</t>
+          <t>Las migraciones se contrastan contra el esquema de referencia, no se confía en que coincidan</t>
         </is>
       </c>
       <c r="E197" s="69" t="inlineStr">
@@ -20416,16 +20470,12 @@
           <t>ADOPTADA e implementada (2026-08-22)</t>
         </is>
       </c>
-      <c r="F197" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — Respuesta a Q-42. En lugar de constituir sociedad en cada país, se emiten todos los comprobantes desde la sociedad peruana. Los países se resuelven uno a uno más adelante.</t>
-        </is>
-      </c>
+      <c r="F197" s="69" t="n"/>
     </row>
     <row r="198" ht="23.25" customHeight="1" s="36">
       <c r="A198" s="67" t="inlineStr">
         <is>
-          <t>DEC-046</t>
+          <t>DEC-049</t>
         </is>
       </c>
       <c r="B198" s="68" t="inlineStr">
@@ -20436,24 +20486,24 @@
       <c r="C198" s="68" t="n"/>
       <c r="D198" s="69" t="inlineStr">
         <is>
-          <t>La base impone lo que ve en una fila; el resto lo impone el repositorio</t>
+          <t>Sin datos fiscales no hay alta, pero acompañamos a formalizarse</t>
         </is>
       </c>
       <c r="E198" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA (2026-08-22)</t>
         </is>
       </c>
       <c r="F198" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Cinco invariantes de finanzas son de varias filas o varias tablas (suma de líneas = subtotal, cobros ≤ total facturado, moneda de asiento = moneda de su payout, signo de una reversión, saldo no negativo). Ningún CHECK puede expresarlas.</t>
+          <t xml:space="preserve"> — Respuesta a Q-45. La propuesta inicial era pagar a un familiar del creador con declaración jurada de parentesco. El análisis de docs/fase-2/2.14-PAGO-A-TERCEROS.md identificó tres problemas: el comprobante deja de coincidir con el pago (riesgo de gasto reparable para la empresa que paga), señales de alerta de prevención de lavado, y contradicción con BR-FIN-003, que ya está implementada.</t>
         </is>
       </c>
     </row>
     <row r="199" ht="23.25" customHeight="1" s="36">
       <c r="A199" s="67" t="inlineStr">
         <is>
-          <t>DEC-045</t>
+          <t>DEC-048</t>
         </is>
       </c>
       <c r="B199" s="68" t="inlineStr">
@@ -20464,24 +20514,24 @@
       <c r="C199" s="68" t="n"/>
       <c r="D199" s="69" t="inlineStr">
         <is>
-          <t>La inmutabilidad financiera se impone con disparadores, no con convención</t>
+          <t>La retención tiene tres estados, no dos</t>
         </is>
       </c>
       <c r="E199" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.15)</t>
         </is>
       </c>
       <c r="F199" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — BR-FIN-008 («ningún registro financiero se elimina físicamente») y BR-FIN-002 («una corrección es un asiento de reversión») eran hasta ahora reglas de la capa de aplicación.</t>
+          <t xml:space="preserve"> — Sobre Q-40 se decidió «que el modelo lo deje configurable». Al implementarlo apareció que el riesgo que yo había señalado —*«alguien pone un número a ojo y nadie se entera»*— ya estaba dentro del modelo, y era peor.</t>
         </is>
       </c>
     </row>
     <row r="200" ht="45.75" customHeight="1" s="36">
       <c r="A200" s="67" t="inlineStr">
         <is>
-          <t>DEC-044</t>
+          <t>DEC-047</t>
         </is>
       </c>
       <c r="B200" s="68" t="inlineStr">
@@ -20492,24 +20542,24 @@
       <c r="C200" s="68" t="n"/>
       <c r="D200" s="69" t="inlineStr">
         <is>
-          <t>Todo pago pertenece a un lote (no existen pagos sueltos)</t>
+          <t>Se factura a todos los países desde Perú</t>
         </is>
       </c>
       <c r="E200" s="69" t="inlineStr">
         <is>
-          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
+          <t>ADOPTADA e implementada (2026-08-22)</t>
         </is>
       </c>
       <c r="F200" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — La primera versión de payouts permitía payout_batch_id NULL, pensando en el pago puntual fuera de la corrida quincenal.</t>
+          <t xml:space="preserve"> — Respuesta a Q-42. En lugar de constituir sociedad en cada país, se emiten todos los comprobantes desde la sociedad peruana. Los países se resuelven uno a uno más adelante.</t>
         </is>
       </c>
     </row>
     <row r="201" ht="34.5" customHeight="1" s="36">
       <c r="A201" s="67" t="inlineStr">
         <is>
-          <t>DEC-043</t>
+          <t>DEC-046</t>
         </is>
       </c>
       <c r="B201" s="68" t="inlineStr">
@@ -20520,24 +20570,24 @@
       <c r="C201" s="68" t="n"/>
       <c r="D201" s="69" t="inlineStr">
         <is>
-          <t>Dónde vive la base de datos de desarrollo</t>
+          <t>La base impone lo que ve en una fila; el resto lo impone el repositorio</t>
         </is>
       </c>
       <c r="E201" s="69" t="inlineStr">
         <is>
-          <t>ACORDADA en su intención; el motor concreto depende de DEC-042</t>
+          <t>ADOPTADA (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F201" s="69" t="inlineStr">
         <is>
-          <t>C. Es lo que hace un equipo profesional y no cuesta más que A: el motor local se instala una vez. El bucle interno —migrar, probar, deshacer, repetir— tiene que ser rápido o se deja de ejecutar, y unas pruebas que tardan minutos son unas pruebas que nadie corre. La base remota es el ensayo general, no el banco de trabajo. — Se propone usar el mismo servidor que producción, con dos bases separadas: una de desarrollo y otra de producción. No es trabajar contra los datos reales; es usar el mismo motor. Ya hay otras aplicaciones Laravel funcionando en ese servidor sin incidencias.</t>
+          <t xml:space="preserve"> — Cinco invariantes de finanzas son de varias filas o varias tablas (suma de líneas = subtotal, cobros ≤ total facturado, moneda de asiento = moneda de su payout, signo de una reversión, saldo no negativo). Ningún CHECK puede expresarlas.</t>
         </is>
       </c>
     </row>
     <row r="202" ht="57" customHeight="1" s="36">
       <c r="A202" s="67" t="inlineStr">
         <is>
-          <t>DEC-042</t>
+          <t>DEC-045</t>
         </is>
       </c>
       <c r="B202" s="68" t="inlineStr">
@@ -20548,108 +20598,108 @@
       <c r="C202" s="68" t="n"/>
       <c r="D202" s="69" t="inlineStr">
         <is>
-          <t>🔴 El servidor es MySQL 5.7 y no aplica los CHECK *(confirmado empíricamente)*</t>
+          <t>La inmutabilidad financiera se impone con disparadores, no con convención</t>
         </is>
       </c>
       <c r="E202" s="69" t="inlineStr">
         <is>
-          <t>🔴 CONFIRMADA — pendiente de elegir entre B y C</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F202" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — El servidor de la aplicación es Percona Server 5.7.44-48 sobre cPanel. La base de desarrollo (..._dev) y la de producción viven en él. docs/03 asumía MySQL 8.</t>
+          <t xml:space="preserve"> — BR-FIN-008 («ningún registro financiero se elimina físicamente») y BR-FIN-002 («una corrección es un asiento de reversión») eran hasta ahora reglas de la capa de aplicación.</t>
         </is>
       </c>
     </row>
     <row r="203" ht="23.25" customHeight="1" s="36">
       <c r="A203" s="67" t="inlineStr">
         <is>
-          <t>DEC-041</t>
+          <t>DEC-044</t>
         </is>
       </c>
       <c r="B203" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C203" s="68" t="n"/>
       <c r="D203" s="69" t="inlineStr">
         <is>
-          <t>Gamificación y Creator Score no se fusionan</t>
+          <t>Todo pago pertenece a un lote (no existen pagos sueltos)</t>
         </is>
       </c>
       <c r="E203" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>ADOPTADA e implementada (2026-08-22, iteración 2.13)</t>
         </is>
       </c>
       <c r="F203" s="69" t="inlineStr">
         <is>
-          <t>B. El Score es interno, puede bajar y sirve para decidir a quién invitar; el XP es externo, nunca baja y sirve para motivar. Un creador que incumplió una vez debe bajar en el score y conservar el XP que ganó antes. — Ambos calculan un número sobre un creador a partir de los mismos eventos. La tentación de unirlos es enorme.</t>
+          <t xml:space="preserve"> — La primera versión de payouts permitía payout_batch_id NULL, pensando en el pago puntual fuera de la corrida quincenal.</t>
         </is>
       </c>
     </row>
     <row r="204" ht="23.25" customHeight="1" s="36">
       <c r="A204" s="67" t="inlineStr">
         <is>
-          <t>DEC-040</t>
+          <t>DEC-043</t>
         </is>
       </c>
       <c r="B204" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C204" s="68" t="n"/>
       <c r="D204" s="69" t="inlineStr">
         <is>
-          <t>Referidos con consolidación diferida</t>
+          <t>Dónde vive la base de datos de desarrollo</t>
         </is>
       </c>
       <c r="E204" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>ACORDADA en su intención; el motor concreto depende de DEC-042</t>
         </is>
       </c>
       <c r="F204" s="69" t="inlineStr">
         <is>
-          <t>B, más topes por periodo y verificación de que referente y referido no comparten documento, teléfono ni medio de pago. El vínculo se conserva siempre aunque el XP no se consolide: es dato de negocio. — Un programa de referidos con recompensa es, sin excepción, un imán de fraude: autorreferidos, cuentas falsas, granjas.</t>
+          <t>C. Es lo que hace un equipo profesional y no cuesta más que A: el motor local se instala una vez. El bucle interno —migrar, probar, deshacer, repetir— tiene que ser rápido o se deja de ejecutar, y unas pruebas que tardan minutos son unas pruebas que nadie corre. La base remota es el ensayo general, no el banco de trabajo. — Se propone usar el mismo servidor que producción, con dos bases separadas: una de desarrollo y otra de producción. No es trabajar contra los datos reales; es usar el mismo motor. Ya hay otras aplicaciones Laravel funcionando en ese servidor sin incidencias.</t>
         </is>
       </c>
     </row>
     <row r="205" ht="23.25" customHeight="1" s="36">
       <c r="A205" s="67" t="inlineStr">
         <is>
-          <t>DEC-039</t>
+          <t>DEC-042</t>
         </is>
       </c>
       <c r="B205" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C205" s="68" t="n"/>
       <c r="D205" s="69" t="inlineStr">
         <is>
-          <t>Los retos internos llevan siempre recompensa tangible 🔴</t>
+          <t>🔴 El servidor es MySQL 5.7 y no aplica los CHECK *(confirmado empíricamente)*</t>
         </is>
       </c>
       <c r="E205" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>🔴 CONFIRMADA — pendiente de elegir entre B y C</t>
         </is>
       </c>
       <c r="F205" s="69" t="inlineStr">
         <is>
-          <t>B, sin excepción. El XP es el envoltorio y el reconocimiento; nunca el pago. Es la salvaguarda que la propia especificación anticipó en §16. — "Minicampañas de XP por hacer vídeos para la plataforma". Leído desde el otro lado, puede sonar a *"produce contenido de marketing para mi empresa y te pago con puntos"* — a creadores que ya producen por dinero para tus clientes. En una red pequeña, ese daño reputacional se propaga en un grupo de WhatsApp.</t>
+          <t xml:space="preserve"> — El servidor de la aplicación es Percona Server 5.7.44-48 sobre cPanel. La base de desarrollo (..._dev) y la de producción viven en él. docs/03 asumía MySQL 8.</t>
         </is>
       </c>
     </row>
     <row r="206" ht="45.75" customHeight="1" s="36">
       <c r="A206" s="67" t="inlineStr">
         <is>
-          <t>DEC-038</t>
+          <t>DEC-041</t>
         </is>
       </c>
       <c r="B206" s="68" t="inlineStr">
@@ -20660,7 +20710,7 @@
       <c r="C206" s="68" t="n"/>
       <c r="D206" s="69" t="inlineStr">
         <is>
-          <t>Ranking por cohortes, sin tabla global</t>
+          <t>Gamificación y Creator Score no se fusionan</t>
         </is>
       </c>
       <c r="E206" s="69" t="inlineStr">
@@ -20670,14 +20720,14 @@
       </c>
       <c r="F206" s="69" t="inlineStr">
         <is>
-          <t>C. Los puntos de liga se reinician por temporada; el XP nunca. Sin ranking público por ingresos, jamás. Un ranking global solo tiene sentido en una vista interna, y ahí es un reporte, no gamificación. — Una clasificación global con 1.000 creadores significa que 990 abren la app y ven que están perdiendo. Y con el tiempo se estanca: quien lleva más tiempo acumula más.</t>
+          <t>B. El Score es interno, puede bajar y sirve para decidir a quién invitar; el XP es externo, nunca baja y sirve para motivar. Un creador que incumplió una vez debe bajar en el score y conservar el XP que ganó antes. — Ambos calculan un número sobre un creador a partir de los mismos eventos. La tentación de unirlos es enorme.</t>
         </is>
       </c>
     </row>
     <row r="207" ht="34.5" customHeight="1" s="36">
       <c r="A207" s="67" t="inlineStr">
         <is>
-          <t>DEC-037</t>
+          <t>DEC-040</t>
         </is>
       </c>
       <c r="B207" s="68" t="inlineStr">
@@ -20688,7 +20738,7 @@
       <c r="C207" s="68" t="n"/>
       <c r="D207" s="69" t="inlineStr">
         <is>
-          <t>Los niveles se calculan, no se almacenan</t>
+          <t>Referidos con consolidación diferida</t>
         </is>
       </c>
       <c r="E207" s="69" t="inlineStr">
@@ -20698,14 +20748,14 @@
       </c>
       <c r="F207" s="69" t="inlineStr">
         <is>
-          <t>B. Permite ajustar umbrales sin quitarle puntos a nadie, que es justamente lo que DEC-035 prohíbe. — Las curvas de nivel se recalibran; el XP ya otorgado no debe verse afectado.</t>
+          <t>B, más topes por periodo y verificación de que referente y referido no comparten documento, teléfono ni medio de pago. El vínculo se conserva siempre aunque el XP no se consolide: es dato de negocio. — Un programa de referidos con recompensa es, sin excepción, un imán de fraude: autorreferidos, cuentas falsas, granjas.</t>
         </is>
       </c>
     </row>
     <row r="208" ht="23.25" customHeight="1" s="36">
       <c r="A208" s="67" t="inlineStr">
         <is>
-          <t>DEC-036</t>
+          <t>DEC-039</t>
         </is>
       </c>
       <c r="B208" s="68" t="inlineStr">
@@ -20716,7 +20766,7 @@
       <c r="C208" s="68" t="n"/>
       <c r="D208" s="69" t="inlineStr">
         <is>
-          <t>Se premia comportamiento verificado, no resultados</t>
+          <t>Los retos internos llevan siempre recompensa tangible 🔴</t>
         </is>
       </c>
       <c r="E208" s="69" t="inlineStr">
@@ -20726,14 +20776,14 @@
       </c>
       <c r="F208" s="69" t="inlineStr">
         <is>
-          <t>C. A premia al algoritmo de Instagram, no al creador. B produce sobrecompromiso —creadores que aceptan lo que no pueden cumplir— y, en el caso de seguidores, desmotiva al micro-creador y premia el vector de fraude de R-04. Detalle en docs/13 §3. — ¿Sobre qué se otorga XP?</t>
+          <t>B, sin excepción. El XP es el envoltorio y el reconocimiento; nunca el pago. Es la salvaguarda que la propia especificación anticipó en §16. — "Minicampañas de XP por hacer vídeos para la plataforma". Leído desde el otro lado, puede sonar a *"produce contenido de marketing para mi empresa y te pago con puntos"* — a creadores que ya producen por dinero para tus clientes. En una red pequeña, ese daño reputacional se propaga en un grupo de WhatsApp.</t>
         </is>
       </c>
     </row>
     <row r="209" ht="23.25" customHeight="1" s="36">
       <c r="A209" s="67" t="inlineStr">
         <is>
-          <t>DEC-035</t>
+          <t>DEC-038</t>
         </is>
       </c>
       <c r="B209" s="68" t="inlineStr">
@@ -20744,7 +20794,7 @@
       <c r="C209" s="68" t="n"/>
       <c r="D209" s="69" t="inlineStr">
         <is>
-          <t>El XP es append-only y nunca decrece</t>
+          <t>Ranking por cohortes, sin tabla global</t>
         </is>
       </c>
       <c r="E209" s="69" t="inlineStr">
@@ -20754,14 +20804,14 @@
       </c>
       <c r="F209" s="69" t="inlineStr">
         <is>
-          <t>B. Quitar puntos se percibe como robo y destruye la confianza de golpe. Además sería castigar dos veces con el mecanismo equivocado. Mismo patrón que el ledger financiero: se corrige con asientos nuevos, no editando. — ¿Se puede restar XP por un incumplimiento?</t>
+          <t>C. Los puntos de liga se reinician por temporada; el XP nunca. Sin ranking público por ingresos, jamás. Un ranking global solo tiene sentido en una vista interna, y ahí es un reporte, no gamificación. — Una clasificación global con 1.000 creadores significa que 990 abren la app y ven que están perdiendo. Y con el tiempo se estanca: quien lleva más tiempo acumula más.</t>
         </is>
       </c>
     </row>
     <row r="210" ht="45.75" customHeight="1" s="36">
       <c r="A210" s="67" t="inlineStr">
         <is>
-          <t>DEC-034</t>
+          <t>DEC-037</t>
         </is>
       </c>
       <c r="B210" s="68" t="inlineStr">
@@ -20772,7 +20822,7 @@
       <c r="C210" s="68" t="n"/>
       <c r="D210" s="69" t="inlineStr">
         <is>
-          <t>Gamificación como dominio propio (D13)</t>
+          <t>Los niveles se calculan, no se almacenan</t>
         </is>
       </c>
       <c r="E210" s="69" t="inlineStr">
@@ -20782,14 +20832,14 @@
       </c>
       <c r="F210" s="69" t="inlineStr">
         <is>
-          <t>C. Igual que D12: si el motor se cae, la operación sigue igual. Y como se alimenta de eventos, el XP es recalculable: cambiar la tabla de puntos permite reprocesar el histórico. Si el XP se escribiera a mano en el momento, eso sería imposible. — XP, niveles, insignias, ligas, retos y referidos para el creador.</t>
+          <t>B. Permite ajustar umbrales sin quitarle puntos a nadie, que es justamente lo que DEC-035 prohíbe. — Las curvas de nivel se recalibran; el XP ya otorgado no debe verse afectado.</t>
         </is>
       </c>
     </row>
     <row r="211" ht="34.5" customHeight="1" s="36">
       <c r="A211" s="67" t="inlineStr">
         <is>
-          <t>DEC-033</t>
+          <t>DEC-036</t>
         </is>
       </c>
       <c r="B211" s="68" t="inlineStr">
@@ -20800,7 +20850,7 @@
       <c r="C211" s="68" t="n"/>
       <c r="D211" s="69" t="inlineStr">
         <is>
-          <t>Registrar la conexión emisora en cada documento</t>
+          <t>Se premia comportamiento verificado, no resultados</t>
         </is>
       </c>
       <c r="E211" s="69" t="inlineStr">
@@ -20810,14 +20860,14 @@
       </c>
       <c r="F211" s="69" t="inlineStr">
         <is>
-          <t>B, aplicado a comprobantes electrónicos, cobros por pasarela, pagos a creadores ejecutados por proveedor y correos enviados. — Paralelo exacto de DEC-019. Si dentro de un año hay que consultar ante el proveedor el estado del comprobante F001-00347, hay que saber por cuál se emitió.</t>
+          <t>C. A premia al algoritmo de Instagram, no al creador. B produce sobrecompromiso —creadores que aceptan lo que no pueden cumplir— y, en el caso de seguidores, desmotiva al micro-creador y premia el vector de fraude de R-04. Detalle en docs/13 §3. — ¿Sobre qué se otorga XP?</t>
         </is>
       </c>
     </row>
     <row r="212" ht="23.25" customHeight="1" s="36">
       <c r="A212" s="67" t="inlineStr">
         <is>
-          <t>DEC-032</t>
+          <t>DEC-035</t>
         </is>
       </c>
       <c r="B212" s="68" t="inlineStr">
@@ -20828,7 +20878,7 @@
       <c r="C212" s="68" t="n"/>
       <c r="D212" s="69" t="inlineStr">
         <is>
-          <t>Compartibilidad declarada por propósito</t>
+          <t>El XP es append-only y nunca decrece</t>
         </is>
       </c>
       <c r="E212" s="69" t="inlineStr">
@@ -20838,14 +20888,14 @@
       </c>
       <c r="F212" s="69" t="inlineStr">
         <is>
-          <t>B. Las credenciales de facturación pertenecen al contribuyente: una sociedad no puede emitir con el certificado de otra. Una validación se cumple; una recomendación en un manual, no. Reformula BR-LE-008 sin contradecirla: lo prohibido era la herencia implícita; compartir por asignación explícita es otra cosa, y aun así sigue vedado para lo fiscal. — El addendum permite que una conexión sirva a varias entidades legales. Correcto para almacenamiento o correo; peligroso para facturación.</t>
+          <t>B. Quitar puntos se percibe como robo y destruye la confianza de golpe. Además sería castigar dos veces con el mecanismo equivocado. Mismo patrón que el ledger financiero: se corrige con asientos nuevos, no editando. — ¿Se puede restar XP por un incumplimiento?</t>
         </is>
       </c>
     </row>
     <row r="213" ht="45.75" customHeight="1" s="36">
       <c r="A213" s="67" t="inlineStr">
         <is>
-          <t>DEC-031</t>
+          <t>DEC-034</t>
         </is>
       </c>
       <c r="B213" s="68" t="inlineStr">
@@ -20856,7 +20906,7 @@
       <c r="C213" s="68" t="n"/>
       <c r="D213" s="69" t="inlineStr">
         <is>
-          <t>Una URL de webhook por conexión</t>
+          <t>Gamificación como dominio propio (D13)</t>
         </is>
       </c>
       <c r="E213" s="69" t="inlineStr">
@@ -20866,14 +20916,14 @@
       </c>
       <c r="F213" s="69" t="inlineStr">
         <is>
-          <t>B. El enrutado por URL hace la verificación de firma determinista y de un solo intento. Se acusa de inmediato (2xx) y se procesa en cola: un proveedor que no recibe respuesta en segundos reintenta y multiplica los eventos. — Con varias conexiones del mismo proveedor conviviendo, el payload entrante a menudo no identifica la sociedad, y probar firmas contra todos los secretos es lento e inseguro. El addendum enumera qué registrar de un webhook pero no resuelve de quién es.</t>
+          <t>C. Igual que D12: si el motor se cae, la operación sigue igual. Y como se alimenta de eventos, el XP es recalculable: cambiar la tabla de puntos permite reprocesar el histórico. Si el XP se escribiera a mano en el momento, eso sería imposible. — XP, niveles, insignias, ligas, retos y referidos para el creador.</t>
         </is>
       </c>
     </row>
     <row r="214" ht="34.5" customHeight="1" s="36">
       <c r="A214" s="67" t="inlineStr">
         <is>
-          <t>DEC-030</t>
+          <t>DEC-033</t>
         </is>
       </c>
       <c r="B214" s="68" t="inlineStr">
@@ -20884,7 +20934,7 @@
       <c r="C214" s="68" t="n"/>
       <c r="D214" s="69" t="inlineStr">
         <is>
-          <t>Cifrado sobre para las credenciales</t>
+          <t>Registrar la conexión emisora en cada documento</t>
         </is>
       </c>
       <c r="E214" s="69" t="inlineStr">
@@ -20894,14 +20944,14 @@
       </c>
       <c r="F214" s="69" t="inlineStr">
         <is>
-          <t>B, con versionado en la rotación (no sobrescribir), escritura sin lectura desde la interfaz, y un filtro de redacción a nivel del logger — no "acordarse de no loguear". — El addendum señala que las credenciales pueden requerir almacenamiento distinto, sin concretar.</t>
+          <t>B, aplicado a comprobantes electrónicos, cobros por pasarela, pagos a creadores ejecutados por proveedor y correos enviados. — Paralelo exacto de DEC-019. Si dentro de un año hay que consultar ante el proveedor el estado del comprobante F001-00347, hay que saber por cuál se emitió.</t>
         </is>
       </c>
     </row>
     <row r="215" ht="23.25" customHeight="1" s="36">
       <c r="A215" s="67" t="inlineStr">
         <is>
-          <t>DEC-029</t>
+          <t>DEC-032</t>
         </is>
       </c>
       <c r="B215" s="68" t="inlineStr">
@@ -20912,7 +20962,7 @@
       <c r="C215" s="68" t="n"/>
       <c r="D215" s="69" t="inlineStr">
         <is>
-          <t>Aislamiento de ambiente como barrera, no como filtro</t>
+          <t>Compartibilidad declarada por propósito</t>
         </is>
       </c>
       <c r="E215" s="69" t="inlineStr">
@@ -20922,14 +20972,14 @@
       </c>
       <c r="F215" s="69" t="inlineStr">
         <is>
-          <t>B. La defensa no puede depender de que alguien haya configurado bien. — El fallo más caro posible de este diseño: una conexión de producción resolviéndose fuera de producción. Consecuencias reales: emitir comprobantes fiscales de verdad desde QA, cobrar tarjetas en una demo, o enviar correos reales a 150 creadores desde staging.</t>
+          <t>B. Las credenciales de facturación pertenecen al contribuyente: una sociedad no puede emitir con el certificado de otra. Una validación se cumple; una recomendación en un manual, no. Reformula BR-LE-008 sin contradecirla: lo prohibido era la herencia implícita; compartir por asignación explícita es otra cosa, y aun así sigue vedado para lo fiscal. — El addendum permite que una conexión sirva a varias entidades legales. Correcto para almacenamiento o correo; peligroso para facturación.</t>
         </is>
       </c>
     </row>
     <row r="216" ht="23.25" customHeight="1" s="36">
       <c r="A216" s="67" t="inlineStr">
         <is>
-          <t>DEC-028</t>
+          <t>DEC-031</t>
         </is>
       </c>
       <c r="B216" s="68" t="inlineStr">
@@ -20940,7 +20990,7 @@
       <c r="C216" s="68" t="n"/>
       <c r="D216" s="69" t="inlineStr">
         <is>
-          <t>Matriz de propósitos obligatorios por país</t>
+          <t>Una URL de webhook por conexión</t>
         </is>
       </c>
       <c r="E216" s="69" t="inlineStr">
@@ -20950,14 +21000,14 @@
       </c>
       <c r="F216" s="69" t="inlineStr">
         <is>
-          <t>B, más un panel de cobertura en verde/rojo y una comprobación programada que avisa antes de que una credencial expirada rompa una operación. — Descubrir que no hay conexión de facturación para Ecuador al pulsar "emitir", con el cliente esperando, es un problema de diseño, no de configuración.</t>
+          <t>B. El enrutado por URL hace la verificación de firma determinista y de un solo intento. Se acusa de inmediato (2xx) y se procesa en cola: un proveedor que no recibe respuesta en segundos reintenta y multiplica los eventos. — Con varias conexiones del mismo proveedor conviviendo, el payload entrante a menudo no identifica la sociedad, y probar firmas contra todos los secretos es lento e inseguro. El addendum enumera qué registrar de un webhook pero no resuelve de quién es.</t>
         </is>
       </c>
     </row>
     <row r="217" ht="45.75" customHeight="1" s="36">
       <c r="A217" s="67" t="inlineStr">
         <is>
-          <t>DEC-027</t>
+          <t>DEC-030</t>
         </is>
       </c>
       <c r="B217" s="68" t="inlineStr">
@@ -20968,7 +21018,7 @@
       <c r="C217" s="68" t="n"/>
       <c r="D217" s="69" t="inlineStr">
         <is>
-          <t>Resolución por especificidad, con empates rechazados al guardar</t>
+          <t>Cifrado sobre para las credenciales</t>
         </is>
       </c>
       <c r="E217" s="69" t="inlineStr">
@@ -20978,14 +21028,14 @@
       </c>
       <c r="F217" s="69" t="inlineStr">
         <is>
-          <t>B, y sobre todo: los empates no se resuelven en ejecución, se prohíben al guardar. Si dos asignaciones activas puntúan igual para la misma combinación, la interfaz rechaza el guardado y explica el conflicto. Así el resolver es siempre determinista y nadie descubre un empate emitiendo una factura. — El addendum propone una escalera de cuatro peldaños. Funciona, pero no contempla el eje de marca ni dice qué hacer ante un empate.</t>
+          <t>B, con versionado en la rotación (no sobrescribir), escritura sin lectura desde la interfaz, y un filtro de redacción a nivel del logger — no "acordarse de no loguear". — El addendum señala que las credenciales pueden requerir almacenamiento distinto, sin concretar.</t>
         </is>
       </c>
     </row>
     <row r="218" ht="34.5" customHeight="1" s="36">
       <c r="A218" s="67" t="inlineStr">
         <is>
-          <t>DEC-026</t>
+          <t>DEC-029</t>
         </is>
       </c>
       <c r="B218" s="68" t="inlineStr">
@@ -20996,7 +21046,7 @@
       <c r="C218" s="68" t="n"/>
       <c r="D218" s="69" t="inlineStr">
         <is>
-          <t>purpose es un enum cerrado en código, no un catálogo editable</t>
+          <t>Aislamiento de ambiente como barrera, no como filtro</t>
         </is>
       </c>
       <c r="E218" s="69" t="inlineStr">
@@ -21006,14 +21056,14 @@
       </c>
       <c r="F218" s="69" t="inlineStr">
         <is>
-          <t>B. El código se ramifica por propósito: invoicing implica una interfaz con emit()/getStatus(); email_transactional implica otra distinta. Un propósito creado desde el panel produciría una conexión perfectamente configurada que ningún código sabe ejecutar. Los catálogos editables son para datos de negocio; los propósitos son contratos de código. — El addendum lista los propósitos como si fueran datos administrables.</t>
+          <t>B. La defensa no puede depender de que alguien haya configurado bien. — El fallo más caro posible de este diseño: una conexión de producción resolviéndose fuera de producción. Consecuencias reales: emitir comprobantes fiscales de verdad desde QA, cobrar tarjetas en una demo, o enviar correos reales a 150 creadores desde staging.</t>
         </is>
       </c>
     </row>
     <row r="219" ht="23.25" customHeight="1" s="36">
       <c r="A219" s="67" t="inlineStr">
         <is>
-          <t>DEC-025</t>
+          <t>DEC-028</t>
         </is>
       </c>
       <c r="B219" s="68" t="inlineStr">
@@ -21024,7 +21074,7 @@
       <c r="C219" s="68" t="n"/>
       <c r="D219" s="69" t="inlineStr">
         <is>
-          <t>Proveedor / Conexión / Asignación como tres entidades</t>
+          <t>Matriz de propósitos obligatorios por país</t>
         </is>
       </c>
       <c r="E219" s="69" t="inlineStr">
@@ -21034,14 +21084,14 @@
       </c>
       <c r="F219" s="69" t="inlineStr">
         <is>
-          <t>B, tal como propone el addendum. integration_providers es catálogo respaldado por código (un proveedor solo existe si hay adaptador); integration_connections es la configuración viva; integration_assignments es el alcance, con NULL significando "cualquiera" y con vigencia (valid_from/valid_to) igual que la cobertura de facturación. — Un proveedor puede tener varias conexiones (producción, sandbox, por sociedad) y cada conexión puede aplicar a varios ámbitos.</t>
+          <t>B, más un panel de cobertura en verde/rojo y una comprobación programada que avisa antes de que una credencial expirada rompa una operación. — Descubrir que no hay conexión de facturación para Ecuador al pulsar "emitir", con el cliente esperando, es un problema de diseño, no de configuración.</t>
         </is>
       </c>
     </row>
     <row r="220" ht="23.25" customHeight="1" s="36">
       <c r="A220" s="67" t="inlineStr">
         <is>
-          <t>DEC-024</t>
+          <t>DEC-027</t>
         </is>
       </c>
       <c r="B220" s="68" t="inlineStr">
@@ -21052,7 +21102,7 @@
       <c r="C220" s="68" t="n"/>
       <c r="D220" s="69" t="inlineStr">
         <is>
-          <t>Las integraciones son un subsistema propio, no Settings</t>
+          <t>Resolución por especificidad, con empates rechazados al guardar</t>
         </is>
       </c>
       <c r="E220" s="69" t="inlineStr">
@@ -21062,14 +21112,14 @@
       </c>
       <c r="F220" s="69" t="inlineStr">
         <is>
-          <t>B. Un ajuste resuelve un valor; una integración resuelve una conexión viva que tiene estado, ciclo de vida y que falla. Además necesita dos ejes más (purpose, environment). Lo que sí se unifica son los nombres de los niveles, para que nadie confunda "global" con "plataforma". — DEC-018 ya definió una configuración jerárquica. La tentación es meter las integraciones dentro.</t>
+          <t>B, y sobre todo: los empates no se resuelven en ejecución, se prohíben al guardar. Si dos asignaciones activas puntúan igual para la misma combinación, la interfaz rechaza el guardado y explica el conflicto. Así el resolver es siempre determinista y nadie descubre un empate emitiendo una factura. — El addendum propone una escalera de cuatro peldaños. Funciona, pero no contempla el eje de marca ni dice qué hacer ante un empate.</t>
         </is>
       </c>
     </row>
     <row r="221" ht="45.75" customHeight="1" s="36">
       <c r="A221" s="67" t="inlineStr">
         <is>
-          <t>DEC-023</t>
+          <t>DEC-026</t>
         </is>
       </c>
       <c r="B221" s="68" t="inlineStr">
@@ -21080,7 +21130,7 @@
       <c r="C221" s="68" t="n"/>
       <c r="D221" s="69" t="inlineStr">
         <is>
-          <t>Identidad dual en comunicaciones</t>
+          <t>purpose es un enum cerrado en código, no un catálogo editable</t>
         </is>
       </c>
       <c r="E221" s="69" t="inlineStr">
@@ -21090,14 +21140,14 @@
       </c>
       <c r="F221" s="69" t="inlineStr">
         <is>
-          <t>C. El creador y la marca cliente se relacionan con LATAM Social; las facturas, contratos y comunicaciones de cobranza deben identificar a la sociedad que responde legalmente. Implica remitente configurable por entidad para los correos de facturación. — ¿Los correos salen de "LATAM Social" o de "Soluciones Tecnológicas a Medida S.A.C."?</t>
+          <t>B. El código se ramifica por propósito: invoicing implica una interfaz con emit()/getStatus(); email_transactional implica otra distinta. Un propósito creado desde el panel produciría una conexión perfectamente configurada que ningún código sabe ejecutar. Los catálogos editables son para datos de negocio; los propósitos son contratos de código. — El addendum lista los propósitos como si fueran datos administrables.</t>
         </is>
       </c>
     </row>
     <row r="222" ht="34.5" customHeight="1" s="36">
       <c r="A222" s="67" t="inlineStr">
         <is>
-          <t>DEC-022</t>
+          <t>DEC-025</t>
         </is>
       </c>
       <c r="B222" s="68" t="inlineStr">
@@ -21108,7 +21158,7 @@
       <c r="C222" s="68" t="n"/>
       <c r="D222" s="69" t="inlineStr">
         <is>
-          <t>Monedas: no derivar del país de la entidad</t>
+          <t>Proveedor / Conexión / Asignación como tres entidades</t>
         </is>
       </c>
       <c r="E222" s="69" t="inlineStr">
@@ -21118,14 +21168,14 @@
       </c>
       <c r="F222" s="69" t="inlineStr">
         <is>
-          <t>B. Coherente con BR-FIN-004 y BR-FIN-009, que ya exigían no asumir una sola moneda. — §11 del addendum. CTS Perú puede facturar en PEN a un cliente peruano y en USD a uno ecuatoriano.</t>
+          <t>B, tal como propone el addendum. integration_providers es catálogo respaldado por código (un proveedor solo existe si hay adaptador); integration_connections es la configuración viva; integration_assignments es el alcance, con NULL significando "cualquiera" y con vigencia (valid_from/valid_to) igual que la cobertura de facturación. — Un proveedor puede tener varias conexiones (producción, sandbox, por sociedad) y cada conexión puede aplicar a varios ámbitos.</t>
         </is>
       </c>
     </row>
     <row r="223" ht="23.85" customHeight="1" s="36">
       <c r="A223" s="67" t="inlineStr">
         <is>
-          <t>DEC-021</t>
+          <t>DEC-024</t>
         </is>
       </c>
       <c r="B223" s="68" t="inlineStr">
@@ -21136,7 +21186,7 @@
       <c r="C223" s="68" t="n"/>
       <c r="D223" s="69" t="inlineStr">
         <is>
-          <t>Series y numeración correlativa por entidad legal</t>
+          <t>Las integraciones son un subsistema propio, no Settings</t>
         </is>
       </c>
       <c r="E223" s="69" t="inlineStr">
@@ -21146,42 +21196,42 @@
       </c>
       <c r="F223" s="69" t="inlineStr">
         <is>
-          <t>C. A no permite series por entidad y deja huecos ante transacciones revertidas. B bloquea una fila que se lee constantemente. C aísla el punto de contención. — En Perú la numeración por serie debe ser correlativa y sin huecos. Con varias sociedades hay varios contadores independientes, y bajo concurrencia dos facturas simultáneas pueden tomar el mismo número o saltarse uno.</t>
+          <t>B. Un ajuste resuelve un valor; una integración resuelve una conexión viva que tiene estado, ciclo de vida y que falla. Además necesita dos ejes más (purpose, environment). Lo que sí se unifica son los nombres de los niveles, para que nadie confunda "global" con "plataforma". — DEC-018 ya definió una configuración jerárquica. La tentación es meter las integraciones dentro.</t>
         </is>
       </c>
     </row>
     <row r="224" ht="46.25" customHeight="1" s="36">
       <c r="A224" s="67" t="inlineStr">
         <is>
-          <t>DEC-020</t>
+          <t>DEC-023</t>
         </is>
       </c>
       <c r="B224" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C224" s="68" t="n"/>
       <c r="D224" s="69" t="inlineStr">
         <is>
-          <t>Entidad que factura vs. entidad que liquida al creador</t>
+          <t>Identidad dual en comunicaciones</t>
         </is>
       </c>
       <c r="E224" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ DECIDIDA (2026-08-27) por DEC-156: opción C, y sin el «en el MVP». La sociedad de la campaña paga a todos sus creadores, sea cual sea el país de cada uno (BR-LE-009, ahora 🔴). Dónde se comprueba lo </t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F224" s="69" t="inlineStr">
         <is>
-          <t>C. A cierra la puerta; B la deja abierta para que alguien la cruce sin darse cuenta un martes por la tarde y genere una contingencia fiscal. C conserva la flexibilidad del modelo y exige una decisión consciente, respaldada por asesoría fiscal, para habilitarla. — §12 del addendum pide separar ambos conceptos. Pero si divergen, aparece una operación intercompañía entre dos sociedades del grupo, con precios de transferencia, documentación ante la autoridad tributaria, consolidación contable y posible retención en la fuente.</t>
+          <t>C. El creador y la marca cliente se relacionan con LATAM Social; las facturas, contratos y comunicaciones de cobranza deben identificar a la sociedad que responde legalmente. Implica remitente configurable por entidad para los correos de facturación. — ¿Los correos salen de "LATAM Social" o de "Soluciones Tecnológicas a Medida S.A.C."?</t>
         </is>
       </c>
     </row>
     <row r="225" ht="35.05" customHeight="1" s="36">
       <c r="A225" s="67" t="inlineStr">
         <is>
-          <t>DEC-019</t>
+          <t>DEC-022</t>
         </is>
       </c>
       <c r="B225" s="68" t="inlineStr">
@@ -21192,7 +21242,7 @@
       <c r="C225" s="68" t="n"/>
       <c r="D225" s="69" t="inlineStr">
         <is>
-          <t>Entidad legal explícita e inmutable en cada documento</t>
+          <t>Monedas: no derivar del país de la entidad</t>
         </is>
       </c>
       <c r="E225" s="69" t="inlineStr">
@@ -21202,14 +21252,14 @@
       </c>
       <c r="F225" s="69" t="inlineStr">
         <is>
-          <t>C. A es un error silencioso: no da error, no rompe nada, y falsifica retroactivamente todos los documentos históricos. La clave foránea sola tampoco basta: si la sociedad cambia de domicilio, la factura antigua debe seguir mostrando el domicilio antiguo. — §14 del addendum. Si mañana Ecuador pasa a facturarse desde otra sociedad, las facturas de ayer deben seguir diciendo lo que decían ayer.</t>
+          <t>B. Coherente con BR-FIN-004 y BR-FIN-009, que ya exigían no asumir una sola moneda. — §11 del addendum. CTS Perú puede facturar en PEN a un cliente peruano y en USD a uno ecuatoriano.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67" t="inlineStr">
         <is>
-          <t>DEC-018</t>
+          <t>DEC-021</t>
         </is>
       </c>
       <c r="B226" s="68" t="inlineStr">
@@ -21220,7 +21270,7 @@
       <c r="C226" s="68" t="n"/>
       <c r="D226" s="69" t="inlineStr">
         <is>
-          <t>Configuración jerárquica en cascada</t>
+          <t>Series y numeración correlativa por entidad legal</t>
         </is>
       </c>
       <c r="E226" s="69" t="inlineStr">
@@ -21230,42 +21280,42 @@
       </c>
       <c r="F226" s="69" t="inlineStr">
         <is>
-          <t>B, con dos condiciones no negociables: la interfaz debe mostrar siempre de dónde viene el valor efectivo, y los secretos se cifran por entidad y nunca se heredan. — La configuración deja de ser global: hay ajustes de plataforma, de marca, de entidad legal y de (entidad × país).</t>
+          <t>C. A no permite series por entidad y deja huecos ante transacciones revertidas. B bloquea una fila que se lee constantemente. C aísla el punto de contención. — En Perú la numeración por serie debe ser correlativa y sin huecos. Con varias sociedades hay varios contadores independientes, y bajo concurrencia dos facturas simultáneas pueden tomar el mismo número o saltarse uno.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67" t="inlineStr">
         <is>
-          <t>DEC-017</t>
+          <t>DEC-020</t>
         </is>
       </c>
       <c r="B227" s="68" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Decidida</t>
         </is>
       </c>
       <c r="C227" s="68" t="n"/>
       <c r="D227" s="69" t="inlineStr">
         <is>
-          <t>Cobertura de facturación como relación N:M con vigencia</t>
+          <t>Entidad que factura vs. entidad que liquida al creador</t>
         </is>
       </c>
       <c r="E227" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t xml:space="preserve">✅ DECIDIDA (2026-08-27) por DEC-156: opción C, y sin el «en el MVP». La sociedad de la campaña paga a todos sus creadores, sea cual sea el país de cada uno (BR-LE-009, ahora 🔴). Dónde se comprueba lo </t>
         </is>
       </c>
       <c r="F227" s="69" t="inlineStr">
         <is>
-          <t>C. A es directamente incorrecta. B pierde la información de *cuándo* dejó de aplicar una cobertura, y eso hace imposible auditar por qué una factura de 2027 salió de una sociedad y una de 2029 de otra. La vigencia es lo que permite la evolución del §15 del addendum sin destruir historia. — Una sociedad puede facturar clientes de varios países, y un país puede ser atendido por más de una sociedad.</t>
+          <t>C. A cierra la puerta; B la deja abierta para que alguien la cruce sin darse cuenta un martes por la tarde y genere una contingencia fiscal. C conserva la flexibilidad del modelo y exige una decisión consciente, respaldada por asesoría fiscal, para habilitarla. — §12 del addendum pide separar ambos conceptos. Pero si divergen, aparece una operación intercompañía entre dos sociedades del grupo, con precios de transferencia, documentación ante la autoridad tributaria, consolidación contable y posible retención en la fuente.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67" t="inlineStr">
         <is>
-          <t>DEC-016</t>
+          <t>DEC-019</t>
         </is>
       </c>
       <c r="B228" s="68" t="inlineStr">
@@ -21276,7 +21326,7 @@
       <c r="C228" s="68" t="n"/>
       <c r="D228" s="69" t="inlineStr">
         <is>
-          <t>Desambiguación de los conceptos organizacionales</t>
+          <t>Entidad legal explícita e inmutable en cada documento</t>
         </is>
       </c>
       <c r="E228" s="69" t="inlineStr">
@@ -21286,14 +21336,14 @@
       </c>
       <c r="F228" s="69" t="inlineStr">
         <is>
-          <t>B. A garantiza que en seis meses nadie sepa si brand_id apunta a LATAM Social o a Shampoo ABC. Es la fuente número uno de errores de datos en sistemas multi-entidad. — El addendum introduce "marca de plataforma" (LATAM Social) y "entidad legal" (la sociedad). El modelo anterior ya usaba Brand para la marca del cliente. Cuatro conceptos organizacionales con nombres que se pisan.</t>
+          <t>C. A es un error silencioso: no da error, no rompe nada, y falsifica retroactivamente todos los documentos históricos. La clave foránea sola tampoco basta: si la sociedad cambia de domicilio, la factura antigua debe seguir mostrando el domicilio antiguo. — §14 del addendum. Si mañana Ecuador pasa a facturarse desde otra sociedad, las facturas de ayer deben seguir diciendo lo que decían ayer.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67" t="inlineStr">
         <is>
-          <t>DEC-015</t>
+          <t>DEC-018</t>
         </is>
       </c>
       <c r="B229" s="68" t="inlineStr">
@@ -21304,24 +21354,24 @@
       <c r="C229" s="68" t="n"/>
       <c r="D229" s="69" t="inlineStr">
         <is>
-          <t>Retención y minimización de datos personales</t>
+          <t>Configuración jerárquica en cascada</t>
         </is>
       </c>
       <c r="E229" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA — requiere validación legal</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F229" s="69" t="inlineStr">
         <is>
-          <t>B. Además: la dirección de envío se purga N meses después de la campaña; las copias de documentos de identidad, si se recogen, se cifran y tienen la retención más corta legalmente posible. Menos datos = menos riesgo. — Se recopilan documento de identidad, fecha de nacimiento, dirección, datos bancarios y dirección de envío de cientos de personas.</t>
+          <t>B, con dos condiciones no negociables: la interfaz debe mostrar siempre de dónde viene el valor efectivo, y los secretos se cifran por entidad y nunca se heredan. — La configuración deja de ser global: hay ajustes de plataforma, de marca, de entidad legal y de (entidad × país).</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67" t="inlineStr">
         <is>
-          <t>DEC-014</t>
+          <t>DEC-017</t>
         </is>
       </c>
       <c r="B230" s="68" t="inlineStr">
@@ -21332,7 +21382,7 @@
       <c r="C230" s="68" t="n"/>
       <c r="D230" s="69" t="inlineStr">
         <is>
-          <t>Modelo de derechos de uso del contenido</t>
+          <t>Cobertura de facturación como relación N:M con vigencia</t>
         </is>
       </c>
       <c r="E230" s="69" t="inlineStr">
@@ -21342,14 +21392,14 @@
       </c>
       <c r="F230" s="69" t="inlineStr">
         <is>
-          <t>B. Además, alertas de vencimiento: usar contenido después de que expiró la licencia es una infracción con consecuencias legales para el cliente y reputacionales para el operador. — Lo que la marca realmente compra es una licencia. Modelarlo como un booleano "cede derechos: sí/no" es insuficiente y genera disputas.</t>
+          <t>C. A es directamente incorrecta. B pierde la información de *cuándo* dejó de aplicar una cobertura, y eso hace imposible auditar por qué una factura de 2027 salió de una sociedad y una de 2029 de otra. La vigencia es lo que permite la evolución del §15 del addendum sin destruir historia. — Una sociedad puede facturar clientes de varios países, y un país puede ser atendido por más de una sociedad.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67" t="inlineStr">
         <is>
-          <t>DEC-013</t>
+          <t>DEC-016</t>
         </is>
       </c>
       <c r="B231" s="68" t="inlineStr">
@@ -21360,7 +21410,7 @@
       <c r="C231" s="68" t="n"/>
       <c r="D231" s="69" t="inlineStr">
         <is>
-          <t>Alcance del portal de la marca en el MVP</t>
+          <t>Desambiguación de los conceptos organizacionales</t>
         </is>
       </c>
       <c r="E231" s="69" t="inlineStr">
@@ -21370,14 +21420,14 @@
       </c>
       <c r="F231" s="69" t="inlineStr">
         <is>
-          <t>B. Entrega el 90% del valor percibido con el 15% del esfuerzo, y es el camino natural hacia A en F13. Requiere cuidado en seguridad: enlaces de un solo destinatario, con expiración, revocables y auditados. — Con 3 marcas, construir un portal con cuentas, roles, facturación y documentos es esfuerzo desproporcionado.</t>
+          <t>B. A garantiza que en seis meses nadie sepa si brand_id apunta a LATAM Social o a Shampoo ABC. Es la fuente número uno de errores de datos en sistemas multi-entidad. — El addendum introduce "marca de plataforma" (LATAM Social) y "entidad legal" (la sociedad). El modelo anterior ya usaba Brand para la marca del cliente. Cuatro conceptos organizacionales con nombres que se pisan.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67" t="inlineStr">
         <is>
-          <t>DEC-012</t>
+          <t>DEC-015</t>
         </is>
       </c>
       <c r="B232" s="68" t="inlineStr">
@@ -21388,24 +21438,24 @@
       <c r="C232" s="68" t="n"/>
       <c r="D232" s="69" t="inlineStr">
         <is>
-          <t>Longitud del formulario de lead B2B</t>
+          <t>Retención y minimización de datos personales</t>
         </is>
       </c>
       <c r="E232" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>PROPUESTA — requiere validación legal</t>
         </is>
       </c>
       <c r="F232" s="69" t="inlineStr">
         <is>
-          <t>B: empresa, nombre, email corporativo, teléfono/WhatsApp, país, objetivo, mensaje. El resto (presupuesto, cantidad de creadores, países objetivo, industria) se captura en la conversación comercial y se guarda en el CRM. UTM, landing y origen se capturan ocultos, siempre. — La spec lista 16 campos. Cada campo adicional reduce la conversión.</t>
+          <t>B. Además: la dirección de envío se purga N meses después de la campaña; las copias de documentos de identidad, si se recogen, se cifran y tienen la retención más corta legalmente posible. Menos datos = menos riesgo. — Se recopilan documento de identidad, fecha de nacimiento, dirección, datos bancarios y dirección de envío de cientos de personas.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67" t="inlineStr">
         <is>
-          <t>DEC-011</t>
+          <t>DEC-014</t>
         </is>
       </c>
       <c r="B233" s="68" t="inlineStr">
@@ -21416,7 +21466,7 @@
       <c r="C233" s="68" t="n"/>
       <c r="D233" s="69" t="inlineStr">
         <is>
-          <t>¿La plataforma publica en las redes del creador?</t>
+          <t>Modelo de derechos de uso del contenido</t>
         </is>
       </c>
       <c r="E233" s="69" t="inlineStr">
@@ -21426,14 +21476,14 @@
       </c>
       <c r="F233" s="69" t="inlineStr">
         <is>
-          <t>B. A añade riesgo de cuenta, complejidad enorme y las APIs cambian sin aviso. La verificación posterior aporta casi todo el valor con una fracción del costo. — Publicar automáticamente requiere permisos amplios, es frágil y las plataformas lo restringen.</t>
+          <t>B. Además, alertas de vencimiento: usar contenido después de que expiró la licencia es una infracción con consecuencias legales para el cliente y reputacionales para el operador. — Lo que la marca realmente compra es una licencia. Modelarlo como un booleano "cede derechos: sí/no" es insuficiente y genera disputas.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67" t="inlineStr">
         <is>
-          <t>DEC-010</t>
+          <t>DEC-013</t>
         </is>
       </c>
       <c r="B234" s="68" t="inlineStr">
@@ -21444,7 +21494,7 @@
       <c r="C234" s="68" t="n"/>
       <c r="D234" s="69" t="inlineStr">
         <is>
-          <t>Estado de campaña vs. estado de participación</t>
+          <t>Alcance del portal de la marca en el MVP</t>
         </is>
       </c>
       <c r="E234" s="69" t="inlineStr">
@@ -21454,14 +21504,14 @@
       </c>
       <c r="F234" s="69" t="inlineStr">
         <is>
-          <t>B, obligatoriamente. A es el error de diseño más frecuente y más caro en plataformas de este tipo: obliga a hacks inmediatos y hace imposible el reporte de avance. — Una campaña live puede tener creadores aún en revisión.</t>
+          <t>B. Entrega el 90% del valor percibido con el 15% del esfuerzo, y es el camino natural hacia A en F13. Requiere cuidado en seguridad: enlaces de un solo destinatario, con expiración, revocables y auditados. — Con 3 marcas, construir un portal con cuentas, roles, facturación y documentos es esfuerzo desproporcionado.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67" t="inlineStr">
         <is>
-          <t>DEC-009</t>
+          <t>DEC-012</t>
         </is>
       </c>
       <c r="B235" s="68" t="inlineStr">
@@ -21472,7 +21522,7 @@
       <c r="C235" s="68" t="n"/>
       <c r="D235" s="69" t="inlineStr">
         <is>
-          <t>Origen de los datos de audiencia</t>
+          <t>Longitud del formulario de lead B2B</t>
         </is>
       </c>
       <c r="E235" s="69" t="inlineStr">
@@ -21482,14 +21532,14 @@
       </c>
       <c r="F235" s="69" t="inlineStr">
         <is>
-          <t>A en el MVP (manual + evidencia + chequeos de coherencia), B en F12–F14, C evaluado por costo cuando el volumen lo justifique: comprar datos verificados suele ser más barato que construir y mantener integraciones con 6 plataformas. — Los datos autodeclarados son el principal vector de fraude. Las APIs oficiales exigen que el creador conecte su cuenta (Instagram/Facebook requieren cuenta Business/Creator y autorización explícita; TikTok y YouTube tienen sus propios programas).</t>
+          <t>B: empresa, nombre, email corporativo, teléfono/WhatsApp, país, objetivo, mensaje. El resto (presupuesto, cantidad de creadores, países objetivo, industria) se captura en la conversación comercial y se guarda en el CRM. UTM, landing y origen se capturan ocultos, siempre. — La spec lista 16 campos. Cada campo adicional reduce la conversión.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67" t="inlineStr">
         <is>
-          <t>DEC-008</t>
+          <t>DEC-011</t>
         </is>
       </c>
       <c r="B236" s="68" t="inlineStr">
@@ -21500,7 +21550,7 @@
       <c r="C236" s="68" t="n"/>
       <c r="D236" s="69" t="inlineStr">
         <is>
-          <t>Almacenamiento de archivos</t>
+          <t>¿La plataforma publica en las redes del creador?</t>
         </is>
       </c>
       <c r="E236" s="69" t="inlineStr">
@@ -21510,14 +21560,14 @@
       </c>
       <c r="F236" s="69" t="inlineStr">
         <is>
-          <t>B, sin excepción. A rompe el despliegue en más de un servidor, complica los backups, no escala y migrar después implica reescribir rutas de miles de archivos. Cloudflare R2 o Backblaze B2 tienen costo de egreso muy bajo, relevante porque los clientes descargarán contenido. — Campañas UGC generan video pesado (0,5–3 GB por campaña).</t>
+          <t>B. A añade riesgo de cuenta, complejidad enorme y las APIs cambian sin aviso. La verificación posterior aporta casi todo el valor con una fracción del costo. — Publicar automáticamente requiere permisos amplios, es frágil y las plataformas lo restringen.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67" t="inlineStr">
         <is>
-          <t>DEC-007</t>
+          <t>DEC-010</t>
         </is>
       </c>
       <c r="B237" s="68" t="inlineStr">
@@ -21528,7 +21578,7 @@
       <c r="C237" s="68" t="n"/>
       <c r="D237" s="69" t="inlineStr">
         <is>
-          <t>Pasarela de pago (Culqi) en el MVP</t>
+          <t>Estado de campaña vs. estado de participación</t>
         </is>
       </c>
       <c r="E237" s="69" t="inlineStr">
@@ -21538,14 +21588,14 @@
       </c>
       <c r="F237" s="69" t="inlineStr">
         <is>
-          <t>B. Se construye la abstracción (PaymentGatewayInterface) pero no la integración. Si aparece un segmento de ticket bajo (p. ej. paquetes autoservicio para pymes), se activa. — La spec pide integrar Culqi. Pero en B2B LATAM, campañas de miles de soles se pagan por transferencia contra factura, no con tarjeta. Una campaña de S/ 30.000 no se cobra con tarjeta (comisión ~3,5% = S/ 1.050 regalados).</t>
+          <t>B, obligatoriamente. A es el error de diseño más frecuente y más caro en plataformas de este tipo: obliga a hacks inmediatos y hace imposible el reporte de avance. — Una campaña live puede tener creadores aún en revisión.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67" t="inlineStr">
         <is>
-          <t>DEC-006</t>
+          <t>DEC-009</t>
         </is>
       </c>
       <c r="B238" s="68" t="inlineStr">
@@ -21556,7 +21606,7 @@
       <c r="C238" s="68" t="n"/>
       <c r="D238" s="69" t="inlineStr">
         <is>
-          <t>Separación Aplicación vs. Creador</t>
+          <t>Origen de los datos de audiencia</t>
         </is>
       </c>
       <c r="E238" s="69" t="inlineStr">
@@ -21566,42 +21616,42 @@
       </c>
       <c r="F238" s="69" t="inlineStr">
         <is>
-          <t>B. Permite reaplicaciones, conserva el histórico de rechazos y evita que un rechazo contamine la entidad permanente. — La spec mezcla el ciclo de vida de la solicitud con el del creador.</t>
+          <t>A en el MVP (manual + evidencia + chequeos de coherencia), B en F12–F14, C evaluado por costo cuando el volumen lo justifique: comprar datos verificados suele ser más barato que construir y mantener integraciones con 6 plataformas. — Los datos autodeclarados son el principal vector de fraude. Las APIs oficiales exigen que el creador conecte su cuenta (Instagram/Facebook requieren cuenta Business/Creator y autorización explícita; TikTok y YouTube tienen sus propios programas).</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67" t="inlineStr">
         <is>
-          <t>DEC-005</t>
+          <t>DEC-008</t>
         </is>
       </c>
       <c r="B239" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C239" s="68" t="n"/>
       <c r="D239" s="69" t="inlineStr">
         <is>
-          <t>Régimen legal y tributario del pago al creador ✅ RESUELTA (parcial)</t>
+          <t>Almacenamiento de archivos</t>
         </is>
       </c>
       <c r="E239" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA para creadores peruanos · 🔴 Q-33 abierta para extranjeros (bloquea F9 solo en ese caso)</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F239" s="69" t="inlineStr">
         <is>
-          <t>C, con la vía simplificada definida por un contador. Y en cualquier caso: el sistema debe modelar tax_regime por creador y por país, con requisitos documentales configurables por régimen, y bloquear el pago si falta el documento requerido. — En Perú, pagar a una persona natural por un servicio exige normalmente comprobante (recibo por honorarios electrónico) y puede implicar retención de renta de 4.ª categoría, con umbrales y suspensión de retención. Muchos micro-creadores no tienen RUC ni emiten comprobantes. Sin resolver esto, no se puede pagar legalmente a escala.</t>
+          <t>B, sin excepción. A rompe el despliegue en más de un servidor, complica los backups, no escala y migrar después implica reescribir rutas de miles de archivos. Cloudflare R2 o Backblaze B2 tienen costo de egreso muy bajo, relevante porque los clientes descargarán contenido. — Campañas UGC generan video pesado (0,5–3 GB por campaña).</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67" t="inlineStr">
         <is>
-          <t>DEC-004</t>
+          <t>DEC-007</t>
         </is>
       </c>
       <c r="B240" s="68" t="inlineStr">
@@ -21612,24 +21662,24 @@
       <c r="C240" s="68" t="n"/>
       <c r="D240" s="69" t="inlineStr">
         <is>
-          <t>Modelo económico: principal vs. comisión</t>
+          <t>Pasarela de pago (Culqi) en el MVP</t>
         </is>
       </c>
       <c r="E240" s="69" t="inlineStr">
         <is>
-          <t>PROPUESTA — confirmar con el contador</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="F240" s="69" t="inlineStr">
         <is>
-          <t>A, coherente con §53 de la especificación (Revenue − Creator Cost = Margen). Determina el modelo fiscal, contable y financiero completo. — ¿El operador vende la campaña y compra el contenido (reventa), o cobra una comisión sobre una transacción entre marca y creador?</t>
+          <t>B. Se construye la abstracción (PaymentGatewayInterface) pero no la integración. Si aparece un segmento de ticket bajo (p. ej. paquetes autoservicio para pymes), se activa. — La spec pide integrar Culqi. Pero en B2B LATAM, campañas de miles de soles se pagan por transferencia contra factura, no con tarjeta. Una campaña de S/ 30.000 no se cobra con tarjeta (comisión ~3,5% = S/ 1.050 regalados).</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="67" t="inlineStr">
         <is>
-          <t>DEC-003</t>
+          <t>DEC-006</t>
         </is>
       </c>
       <c r="B241" s="68" t="inlineStr">
@@ -21640,7 +21690,7 @@
       <c r="C241" s="68" t="n"/>
       <c r="D241" s="69" t="inlineStr">
         <is>
-          <t>Estrategia de frontend</t>
+          <t>Separación Aplicación vs. Creador</t>
         </is>
       </c>
       <c r="E241" s="69" t="inlineStr">
@@ -21650,14 +21700,14 @@
       </c>
       <c r="F241" s="69" t="inlineStr">
         <is>
-          <t>A. B duplica el trabajo y, sobre todo, duplica la autorización —el punto donde este sistema más se puede romper—. El portal del creador se entrega como PWA instalable con A. — Cuatro portales con necesidades distintas. Equipo pequeño.</t>
+          <t>B. Permite reaplicaciones, conserva el histórico de rechazos y evita que un rechazo contamine la entidad permanente. — La spec mezcla el ciclo de vida de la solicitud con el del creador.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="67" t="inlineStr">
         <is>
-          <t>DEC-002</t>
+          <t>DEC-005</t>
         </is>
       </c>
       <c r="B242" s="68" t="inlineStr">
@@ -21668,71 +21718,155 @@
       <c r="C242" s="68" t="n"/>
       <c r="D242" s="69" t="inlineStr">
         <is>
-          <t>Multitenancy ✅ RESUELTA</t>
+          <t>Régimen legal y tributario del pago al creador ✅ RESUELTA (parcial)</t>
         </is>
       </c>
       <c r="E242" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA (decisión del negocio, 2026-08-21)</t>
+          <t>✅ APROBADA para creadores peruanos · 🔴 Q-33 abierta para extranjeros (bloquea F9 solo en ese caso)</t>
         </is>
       </c>
       <c r="F242" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hoy hay un solo operador. La spec contempla agencias y white-label a futuro (§78).</t>
+          <t>C, con la vía simplificada definida por un contador. Y en cualquier caso: el sistema debe modelar tax_regime por creador y por país, con requisitos documentales configurables por régimen, y bloquear el pago si falta el documento requerido. — En Perú, pagar a una persona natural por un servicio exige normalmente comprobante (recibo por honorarios electrónico) y puede implicar retención de renta de 4.ª categoría, con umbrales y suspensión de retención. Muchos micro-creadores no tienen RUC ni emiten comprobantes. Sin resolver esto, no se puede pagar legalmente a escala.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="67" t="inlineStr">
         <is>
-          <t>DEC-001</t>
+          <t>DEC-004</t>
         </is>
       </c>
       <c r="B243" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C243" s="68" t="n"/>
       <c r="D243" s="69" t="inlineStr">
         <is>
-          <t>Framework PHP</t>
+          <t>Modelo económico: principal vs. comisión</t>
         </is>
       </c>
       <c r="E243" s="69" t="inlineStr">
         <is>
-          <t>✅ APROBADA (2026-08-22). Proyecto creado: ver tools/bootstrap-laravel.ps1 y CONTRIBUTING.md</t>
+          <t>PROPUESTA — confirmar con el contador</t>
         </is>
       </c>
       <c r="F243" s="69" t="inlineStr">
         <is>
-          <t>A — Laravel 12. C queda descartada: construir a mano autenticación, colas, migraciones y abstracción de storage añadiría 3–5 meses de trabajo indiferenciado y una superficie de seguridad propia que nadie audita. B es defendible si el equipo ya domina Symfony. — La spec exige PHP 8.3 y "MVC o equivalente bien estructurado", y a la vez pide migraciones, seeders, colas, scheduler, cache, logs, SMTP, webhooks, RBAC, i18n y tests. Todo eso ya existe, probado en producción, en los frameworks maduros.</t>
+          <t>A, coherente con §53 de la especificación (Revenue − Creator Cost = Margen). Determina el modelo fiscal, contable y financiero completo. — ¿El operador vende la campaña y compra el contenido (reventa), o cobra una comisión sobre una transacción entre marca y creador?</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="67" t="inlineStr">
         <is>
-          <t>DEC-000</t>
+          <t>DEC-003</t>
         </is>
       </c>
       <c r="B244" s="68" t="inlineStr">
         <is>
-          <t>Decidida</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="C244" s="68" t="n"/>
       <c r="D244" s="69" t="inlineStr">
         <is>
+          <t>Estrategia de frontend</t>
+        </is>
+      </c>
+      <c r="E244" s="69" t="inlineStr">
+        <is>
+          <t>PROPUESTA</t>
+        </is>
+      </c>
+      <c r="F244" s="69" t="inlineStr">
+        <is>
+          <t>A. B duplica el trabajo y, sobre todo, duplica la autorización —el punto donde este sistema más se puede romper—. El portal del creador se entrega como PWA instalable con A. — Cuatro portales con necesidades distintas. Equipo pequeño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="67" t="inlineStr">
+        <is>
+          <t>DEC-002</t>
+        </is>
+      </c>
+      <c r="B245" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C245" s="68" t="n"/>
+      <c r="D245" s="69" t="inlineStr">
+        <is>
+          <t>Multitenancy ✅ RESUELTA</t>
+        </is>
+      </c>
+      <c r="E245" s="69" t="inlineStr">
+        <is>
+          <t>✅ APROBADA (decisión del negocio, 2026-08-21)</t>
+        </is>
+      </c>
+      <c r="F245" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — Hoy hay un solo operador. La spec contempla agencias y white-label a futuro (§78).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="67" t="inlineStr">
+        <is>
+          <t>DEC-001</t>
+        </is>
+      </c>
+      <c r="B246" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C246" s="68" t="n"/>
+      <c r="D246" s="69" t="inlineStr">
+        <is>
+          <t>Framework PHP</t>
+        </is>
+      </c>
+      <c r="E246" s="69" t="inlineStr">
+        <is>
+          <t>✅ APROBADA (2026-08-22). Proyecto creado: ver tools/bootstrap-laravel.ps1 y CONTRIBUTING.md</t>
+        </is>
+      </c>
+      <c r="F246" s="69" t="inlineStr">
+        <is>
+          <t>A — Laravel 12. C queda descartada: construir a mano autenticación, colas, migraciones y abstracción de storage añadiría 3–5 meses de trabajo indiferenciado y una superficie de seguridad propia que nadie audita. B es defendible si el equipo ya domina Symfony. — La spec exige PHP 8.3 y "MVC o equivalente bien estructurado", y a la vez pide migraciones, seeders, colas, scheduler, cache, logs, SMTP, webhooks, RBAC, i18n y tests. Todo eso ya existe, probado en producción, en los frameworks maduros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="67" t="inlineStr">
+        <is>
+          <t>DEC-000</t>
+        </is>
+      </c>
+      <c r="B247" s="68" t="inlineStr">
+        <is>
+          <t>Decidida</t>
+        </is>
+      </c>
+      <c r="C247" s="68" t="n"/>
+      <c r="D247" s="69" t="inlineStr">
+        <is>
           <t>Nombre del producto y dominio ✅ RESUELTA</t>
         </is>
       </c>
-      <c r="E244" s="69" t="inlineStr">
+      <c r="E247" s="69" t="inlineStr">
         <is>
           <t>✅ APROBADA (addendum 2026-08-21)</t>
         </is>
       </c>
-      <c r="F244" s="69" t="inlineStr">
+      <c r="F247" s="69" t="inlineStr">
         <is>
           <t>El addendum del 2026-08-21 lo define: la marca de plataforma es LATAM Social. El identificador técnico del proyecto pasa a latam-social. El nombre de trabajo provisional "CTS Creators" queda descartado. — El repositorio se llama ManageCampaingInfluencer (con error ortográfico). El nombre afecta marca, dominio, correos y branding.</t>
         </is>

--- a/docs/LATAM-Social-avance.xlsx
+++ b/docs/LATAM-Social-avance.xlsx
@@ -2241,7 +2241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J181"/>
+  <dimension ref="A1:J182"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="35" min="1" max="1"/>
@@ -10709,6 +10709,56 @@
       <c r="J181" s="35" t="inlineStr">
         <is>
           <t>2026-08-31. FUERA DEL ALCANCE ORIGINAL. El formulario de la portada de marcas crea una FILA y no un correo: hoy el correo esta en «log» y una instalacion con el SMTP a medio configurar perderia cada contacto sin que nadie se entere (DEC-242). Misma forma que creator_applications, con columna puerta para que solo lo abierto ocupe sitio (DEC-243). Descartar exige motivo y no borra; convertir exige decir en que cliente (DEC-244). Una asercion pasaba por casualidad y los dos motores la delataron. 1014 pruebas; 2208 aserciones SQL en MariaDB y 2197 en MySQL 8. docs/fase-9/9.21c-EL-PROSPECTO.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="57" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B182" s="35" t="inlineStr">
+        <is>
+          <t>Ola 2 - Escalar comercialmente</t>
+        </is>
+      </c>
+      <c r="C182" s="35" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="D182" s="35" t="inlineStr">
+        <is>
+          <t>Finanzas y facturacion</t>
+        </is>
+      </c>
+      <c r="E182" s="35" t="inlineStr">
+        <is>
+          <t>9.9a</t>
+        </is>
+      </c>
+      <c r="F182" s="35" t="inlineStr">
+        <is>
+          <t>El impuesto es un dato: tasas con vigencia por pais</t>
+        </is>
+      </c>
+      <c r="G182" s="35" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="H182" s="35">
+        <f>IFERROR(INDEX(Config!$B$3:$B$8,MATCH($G182,Config!$A$3:$A$8,0)),0)</f>
+        <v/>
+      </c>
+      <c r="I182" s="35">
+        <f>IFERROR(INDEX(Config!$C$3:$C$8,MATCH($G182,Config!$A$3:$A$8,0)),0)</f>
+        <v/>
+      </c>
+      <c r="J182" s="35" t="inlineStr">
+        <is>
+          <t>2026-08-31. invoices existe desde la Fase 2 con tax_amount y con la aritmetica comprobada, pero la TASA no existia en ninguna parte: nadie sabia que el IGV es 18 %. Es un PERIODO con no solape porque las tasas cambian y las facturas de antes no (DEC-245); se pregunta siempre por la fecha del documento y no se corrige --se publica la siguiente cerrando la anterior el dia antes (DEC-246)--. Solo se siembra el IGV peruano y desde el arranque (DEC-247). 1026 pruebas; 2232 aserciones SQL en MariaDB y 2222 en MySQL 8. Novena vez que se usa Periodo y la primera sin haber tenido que descubrir el defecto antes. docs/fase-9/9.9a-EL-IMPUESTO-ES-UN-DATO.md</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F247"/>
+  <dimension ref="A1:F250"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="35" min="1" max="1"/>
@@ -15211,7 +15261,7 @@
     <row r="3" ht="79.5" customHeight="1" s="36">
       <c r="A3" s="67" t="inlineStr">
         <is>
-          <t>DEC-242</t>
+          <t>DEC-245</t>
         </is>
       </c>
       <c r="B3" s="68" t="inlineStr">
@@ -15222,24 +15272,24 @@
       <c r="C3" s="68" t="n"/>
       <c r="D3" s="69" t="inlineStr">
         <is>
-          <t>El contacto de una marca es una FILA, no un correo</t>
+          <t>La tasa de impuesto es un PERIODO, no una constante</t>
         </is>
       </c>
       <c r="E3" s="69" t="inlineStr">
         <is>
-          <t>9.21c</t>
+          <t>9.9a</t>
         </is>
       </c>
       <c r="F3" s="69" t="inlineStr">
         <is>
-          <t>Hoy el correo esta en «log» --no sale del servidor-- asi que una instalacion con el SMTP a medio configurar perderia cada contacto sin que nadie se entere. Un correo que no llega no deja rastro; una fila si, y ademas se puede contar. El aviso por correo va encima de la fila, no en lugar de ella.</t>
+          <t>invoices tenia el importe del impuesto desde la Fase 2, pero la TASA no existia: nadie sabia que el IGV es 18 %. No puede ser un 18 en el codigo por dos motivos: es la regla de un pais escrita en el codigo de todos, y sobre todo las tasas cambian y las facturas de antes no --el IGV peruano ha sido 16, 17 y 19 %--. Sin vigencia, subir la tasa hoy reescribiria el impuesto de una factura de hace dos anos.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="57" customHeight="1" s="36">
       <c r="A4" s="67" t="inlineStr">
         <is>
-          <t>DEC-243</t>
+          <t>DEC-246</t>
         </is>
       </c>
       <c r="B4" s="68" t="inlineStr">
@@ -15250,24 +15300,24 @@
       <c r="C4" s="68" t="n"/>
       <c r="D4" s="69" t="inlineStr">
         <is>
-          <t>Misma forma que creator_applications, y solo lo abierto ocupa la puerta</t>
+          <t>Se pregunta por una FECHA, y una tasa no se corrige: se publica la siguiente</t>
         </is>
       </c>
       <c r="E4" s="69" t="inlineStr">
         <is>
-          <t>9.21c</t>
+          <t>9.9a</t>
         </is>
       </c>
       <c r="F4" s="69" t="inlineStr">
         <is>
-          <t>Son el mismo problema: alguien de fuera deja sus datos y alguien de dentro los atiende. Copiar la forma que ya funciona sale mas barato que inventar la segunda, y quien conozca una bandeja conoce las dos. Lo cerrado deja el hueco libre: quien vuelve a escribir el ano que viene es un contacto nuevo de verdad, no un duplicado.</t>
+          <t>vigente() recibe la fecha del documento y no usa now(): es la disciplina de T-73. Corregir el 18 % de una fila que ya explico cien facturas es reescribir el pasado, asi que publicar() cierra la que rige EL DIA ANTES --con Vigencia, no con una resta a mano-- y abre la nueva. Publicar hacia atras se rechaza con palabras, y tg_tax_no_delete impide borrar.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="79.5" customHeight="1" s="36">
       <c r="A5" s="67" t="inlineStr">
         <is>
-          <t>DEC-244</t>
+          <t>DEC-247</t>
         </is>
       </c>
       <c r="B5" s="68" t="inlineStr">
@@ -15278,24 +15328,24 @@
       <c r="C5" s="68" t="n"/>
       <c r="D5" s="69" t="inlineStr">
         <is>
-          <t>Descartar no es borrar, y convertir se hace en dos pasos</t>
+          <t>Solo se siembra el IGV de Peru, y desde el arranque de la instalacion</t>
         </is>
       </c>
       <c r="E5" s="69" t="inlineStr">
         <is>
-          <t>9.21c</t>
+          <t>9.9a</t>
         </is>
       </c>
       <c r="F5" s="69" t="inlineStr">
         <is>
-          <t>De esta tabla salen «.de donde salio este cliente?» y «.cuantos descartamos y por que?»; borrar se lleva las dos por delante. Descartar exige un motivo de al menos diez caracteres. Y convertir exige decir en que cliente: crear ese cliente se sigue haciendo en su pantalla de siempre, porque duplicar el formulario seria tener dos sitios donde se crea un cliente.</t>
+          <t>Sembrar el IVA colombiano o el mexicano seria inventar el dato de un pais donde todavia no se emite nada --mismo criterio que Q-64--: una tasa que nadie ha confirmado es peor que ninguna, porque se usa sin mirarla. Y rige desde el arranque y no desde 2011: fechar una vigencia hacia atras es inventarse una historia que nadie puede comprobar.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34.5" customHeight="1" s="36">
       <c r="A6" s="67" t="inlineStr">
         <is>
-          <t>DEC-238</t>
+          <t>DEC-242</t>
         </is>
       </c>
       <c r="B6" s="68" t="inlineStr">
@@ -15306,24 +15356,24 @@
       <c r="C6" s="68" t="n"/>
       <c r="D6" s="69" t="inlineStr">
         <is>
-          <t>/ habla a las MARCAS y /creadores a los creadores</t>
+          <t>El contacto de una marca es una FILA, no un correo</t>
         </is>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>9.21b</t>
+          <t>9.21c</t>
         </is>
       </c>
       <c r="F6" s="69" t="inlineStr">
         <is>
-          <t>Es un mercado de dos lados y el lado que PAGA se pone en la puerta: una portada que abre reclutando creadores se lee como «agencia buscando talento». Los creadores llegan por un enlace, no por la home. Las dos se enlazan entre si. El argumento en contra queda escrito: si el cuello de botella es tener creadores, el trafico que hace falta primero es el suyo; aun asi la home no cambia, porque moverla despues cuesta posicionamiento.</t>
+          <t>Hoy el correo esta en «log» --no sale del servidor-- asi que una instalacion con el SMTP a medio configurar perderia cada contacto sin que nadie se entere. Un correo que no llega no deja rastro; una fila si, y ademas se puede contar. El aviso por correo va encima de la fila, no en lugar de ella.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="36">
       <c r="A7" s="67" t="inlineStr">
         <is>
-          <t>DEC-239</t>
+          <t>DEC-243</t>
         </is>
       </c>
       <c r="B7" s="68" t="inlineStr">
@@ -15334,24 +15384,24 @@
       <c r="C7" s="68" t="n"/>
       <c r="D7" s="69" t="inlineStr">
         <is>
-          <t>El texto de la portada es un dato, y cuelga de la marca</t>
+          <t>Misma forma que creator_applications, y solo lo abierto ocupa la puerta</t>
         </is>
       </c>
       <c r="E7" s="69" t="inlineStr">
         <is>
-          <t>9.21b</t>
+          <t>9.21c</t>
         </is>
       </c>
       <c r="F7" s="69" t="inlineStr">
         <is>
-          <t>DEC-190 en el sitio donde mas se nota: la marca del panel la ve quien ya entro; esto lo ve quien todavia esta decidiendo si te escribe. landing_pages lleva platform_brand_id: es UNA columna sobre el eje en el que el producto esta construido --distinto de las asignaciones de tres ejes de 9.17d, que resolvian un problema inexistente--. Dos paginas y no un gestor de contenidos: cada una tiene su formulario y su publico, asi que son codigo.</t>
+          <t>Son el mismo problema: alguien de fuera deja sus datos y alguien de dentro los atiende. Copiar la forma que ya funciona sale mas barato que inventar la segunda, y quien conozca una bandeja conoce las dos. Lo cerrado deja el hueco libre: quien vuelve a escribir el ano que viene es un contacto nuevo de verdad, no un duplicado.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34.5" customHeight="1" s="36">
       <c r="A8" s="67" t="inlineStr">
         <is>
-          <t>DEC-240</t>
+          <t>DEC-244</t>
         </is>
       </c>
       <c r="B8" s="68" t="inlineStr">
@@ -15362,24 +15412,24 @@
       <c r="C8" s="68" t="n"/>
       <c r="D8" s="69" t="inlineStr">
         <is>
-          <t>La postulacion publica escribe en creator_applications, que ya existia</t>
+          <t>Descartar no es borrar, y convertir se hace en dos pasos</t>
         </is>
       </c>
       <c r="E8" s="69" t="inlineStr">
         <is>
-          <t>9.21b</t>
+          <t>9.21c</t>
         </is>
       </c>
       <c r="F8" s="69" t="inlineStr">
         <is>
-          <t>Existe desde la Fase 2 con source por defecto «landing», su bandeja y su unica de una solicitud abierta por correo; faltaba la landing que escribiera. Un formulario publico que escribe lleva throttle:5,1 y un campo trampa que una persona no ve; si viene lleno se contesta «gracias» y no se escribe nada. Nada de CAPTCHA: barrera para quien lee con dificultad y tramite de segundos para quien automatiza. Vive en Creator y no en Core: T-74 aplicada antes de romperla.</t>
+          <t>De esta tabla salen «.de donde salio este cliente?» y «.cuantos descartamos y por que?»; borrar se lleva las dos por delante. Descartar exige un motivo de al menos diez caracteres. Y convertir exige decir en que cliente: crear ese cliente se sigue haciendo en su pantalla de siempre, porque duplicar el formulario seria tener dos sitios donde se crea un cliente.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1" s="36">
       <c r="A9" s="67" t="inlineStr">
         <is>
-          <t>DEC-241</t>
+          <t>DEC-238</t>
         </is>
       </c>
       <c r="B9" s="68" t="inlineStr">
@@ -15390,7 +15440,7 @@
       <c r="C9" s="68" t="n"/>
       <c r="D9" s="69" t="inlineStr">
         <is>
-          <t>Sin portada se va al acceso, no a un 404</t>
+          <t>/ habla a las MARCAS y /creadores a los creadores</t>
         </is>
       </c>
       <c r="E9" s="69" t="inlineStr">
@@ -15400,14 +15450,14 @@
       </c>
       <c r="F9" s="69" t="inlineStr">
         <is>
-          <t>Una instalacion recien migrada no tiene contenido que ensenar, y eso no puede ser un error en la cara de un visitante: es exactamente lo que habia antes. Lo mismo al apagar una portada desde el admin, que es una decision de contenido y no una averia.</t>
+          <t>Es un mercado de dos lados y el lado que PAGA se pone en la puerta: una portada que abre reclutando creadores se lee como «agencia buscando talento». Los creadores llegan por un enlace, no por la home. Las dos se enlazan entre si. El argumento en contra queda escrito: si el cuello de botella es tener creadores, el trafico que hace falta primero es el suyo; aun asi la home no cambia, porque moverla despues cuesta posicionamiento.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="57" customHeight="1" s="36">
       <c r="A10" s="67" t="inlineStr">
         <is>
-          <t>DEC-236</t>
+          <t>DEC-239</t>
         </is>
       </c>
       <c r="B10" s="68" t="inlineStr">
@@ -15418,24 +15468,24 @@
       <c r="C10" s="68" t="n"/>
       <c r="D10" s="69" t="inlineStr">
         <is>
-          <t>Todo lo que exige sesion vive bajo /backoffice</t>
+          <t>El texto de la portada es un dato, y cuelga de la marca</t>
         </is>
       </c>
       <c r="E10" s="69" t="inlineStr">
         <is>
-          <t>9.21a</t>
+          <t>9.21b</t>
         </is>
       </c>
       <c r="F10" s="69" t="inlineStr">
         <is>
-          <t>Lo vio el negocio antes de escribir una linea de la landing: /creadores tiene que ser la puerta PUBLICA de los creadores, y descubrirlo despues de publicar habria roto enlaces ya compartidos. Dentro entra todo lo que pide sesion sea de quien sea; lo que cada uno ve lo siguen decidiendo sus permisos. Costo una linea porque docs/08 prohibe escribir URLs a mano en las vistas: comprobado, cero resultados en app/, resources/ y config/.</t>
+          <t>DEC-190 en el sitio donde mas se nota: la marca del panel la ve quien ya entro; esto lo ve quien todavia esta decidiendo si te escribe. landing_pages lleva platform_brand_id: es UNA columna sobre el eje en el que el producto esta construido --distinto de las asignaciones de tres ejes de 9.17d, que resolvian un problema inexistente--. Dos paginas y no un gestor de contenidos: cada una tiene su formulario y su publico, asi que son codigo.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="68.25" customHeight="1" s="36">
       <c r="A11" s="67" t="inlineStr">
         <is>
-          <t>DEC-237</t>
+          <t>DEC-240</t>
         </is>
       </c>
       <c r="B11" s="68" t="inlineStr">
@@ -15446,24 +15496,24 @@
       <c r="C11" s="68" t="n"/>
       <c r="D11" s="69" t="inlineStr">
         <is>
-          <t>Veintiuna rutas se quedan fuera, y cada una con su motivo escrito</t>
+          <t>La postulacion publica escribe en creator_applications, que ya existia</t>
         </is>
       </c>
       <c r="E11" s="69" t="inlineStr">
         <is>
-          <t>9.21a</t>
+          <t>9.21b</t>
         </is>
       </c>
       <c r="F11" s="69" t="inlineStr">
         <is>
-          <t>El acceso y la recuperacion son la puerta; la invitacion y la aprobacion llegan por enlace con token a alguien que no tiene cuenta; el logotipo y el favicon los pinta la pantalla de acceso. Dos comparten primer segmento con algo que si se mudo: /contrasena frente a /contrasena/nueva, y /marca frente a /marca/logo. La lista vive en una prueba que recorre todas las rutas con nombre.</t>
+          <t>Existe desde la Fase 2 con source por defecto «landing», su bandeja y su unica de una solicitud abierta por correo; faltaba la landing que escribiera. Un formulario publico que escribe lleva throttle:5,1 y un campo trampa que una persona no ve; si viene lleno se contesta «gracias» y no se escribe nada. Nada de CAPTCHA: barrera para quien lee con dificultad y tramite de segundos para quien automatiza. Vive en Creator y no en Core: T-74 aplicada antes de romperla.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="68.25" customHeight="1" s="36">
       <c r="A12" s="67" t="inlineStr">
         <is>
-          <t>DEC-233</t>
+          <t>DEC-241</t>
         </is>
       </c>
       <c r="B12" s="68" t="inlineStr">
@@ -15474,24 +15524,24 @@
       <c r="C12" s="68" t="n"/>
       <c r="D12" s="69" t="inlineStr">
         <is>
-          <t>La configuracion tiene UNA sola puerta, y el menu lateral solo lleva trabajo</t>
+          <t>Sin portada se va al acceso, no a un 404</t>
         </is>
       </c>
       <c r="E12" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21b</t>
         </is>
       </c>
       <c r="F12" s="69" t="inlineStr">
         <is>
-          <t>Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario en una pantalla que se veia igual que Campanas y con el menu marcando otra entrada. El menu queda en tres grupos --Operacion, Finanzas, Registros-- mas Ajustes: Configuracion, y un grupo del que no se puede ver nada desaparece entero.</t>
+          <t>Una instalacion recien migrada no tiene contenido que ensenar, y eso no puede ser un error en la cara de un visitante: es exactamente lo que habia antes. Lo mismo al apagar una portada desde el admin, que es una decision de contenido y no una averia.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="68.25" customHeight="1" s="36">
       <c r="A13" s="67" t="inlineStr">
         <is>
-          <t>DEC-234</t>
+          <t>DEC-236</t>
         </is>
       </c>
       <c r="B13" s="68" t="inlineStr">
@@ -15502,24 +15552,24 @@
       <c r="C13" s="68" t="n"/>
       <c r="D13" s="69" t="inlineStr">
         <is>
-          <t>El orden de los grupos es una decision y vive en el registro, no en la plantilla</t>
+          <t>Todo lo que exige sesion vive bajo /backoffice</t>
         </is>
       </c>
       <c r="E13" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21a</t>
         </is>
       </c>
       <c r="F13" s="69" t="inlineStr">
         <is>
-          <t>revision() ordena por URGENCIA, que es lo correcto para una lista de avisos y lo peor para una navegacion: «Fiscal y facturacion» saldria arriba o abajo segun que falte hoy, y un sitio que cambia de forma segun el dia no se aprende. Por lo mismo, que rutas son configuracion sale de Preparacion::rutas() y no de la plantilla.</t>
+          <t>Lo vio el negocio antes de escribir una linea de la landing: /creadores tiene que ser la puerta PUBLICA de los creadores, y descubrirlo despues de publicar habria roto enlaces ya compartidos. Dentro entra todo lo que pide sesion sea de quien sea; lo que cada uno ve lo siguen decidiendo sus permisos. Costo una linea porque docs/08 prohibe escribir URLs a mano en las vistas: comprobado, cero resultados en app/, resources/ y config/.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45.75" customHeight="1" s="36">
       <c r="A14" s="67" t="inlineStr">
         <is>
-          <t>DEC-235</t>
+          <t>DEC-237</t>
         </is>
       </c>
       <c r="B14" s="68" t="inlineStr">
@@ -15530,24 +15580,24 @@
       <c r="C14" s="68" t="n"/>
       <c r="D14" s="69" t="inlineStr">
         <is>
-          <t>Los catalogos son configuracion, con portada propia</t>
+          <t>Veintiuna rutas se quedan fuera, y cada una con su motivo escrito</t>
         </is>
       </c>
       <c r="E14" s="69" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.21a</t>
         </is>
       </c>
       <c r="F14" s="69" t="inlineStr">
         <is>
-          <t>Los seis colgaban del menu bajo un titulo que no era un sitio: era una etiqueta. Ahora son un area con portada --cuantas filas y cuantas activas-- y su aviso: una lista sin ninguna fila activa sale en rojo, porque un catalogo vacio no da error, deja un desplegable vacio. La pantalla de cada catalogo no se mueve.</t>
+          <t>El acceso y la recuperacion son la puerta; la invitacion y la aprobacion llegan por enlace con token a alguien que no tiene cuenta; el logotipo y el favicon los pinta la pantalla de acceso. Dos comparten primer segmento con algo que si se mudo: /contrasena frente a /contrasena/nueva, y /marca frente a /marca/logo. La lista vive en una prueba que recorre todas las rutas con nombre.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1" s="36">
       <c r="A15" s="67" t="inlineStr">
         <is>
-          <t>DEC-228</t>
+          <t>DEC-233</t>
         </is>
       </c>
       <c r="B15" s="68" t="inlineStr">
@@ -15558,24 +15608,24 @@
       <c r="C15" s="68" t="n"/>
       <c r="D15" s="69" t="inlineStr">
         <is>
-          <t>Los tipos de comprobante son un catalogo por pais, no un enum en el codigo</t>
+          <t>La configuracion tiene UNA sola puerta, y el menu lateral solo lleva trabajo</t>
         </is>
       </c>
       <c r="E15" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F15" s="69" t="inlineStr">
         <is>
-          <t>ck_ds_type decia IN ('invoice','boleta','credit_note','debit_note','other') desde la Fase 2: la boleta es peruana, el CFDI mexicano no estaba y anadir uno exigia desplegar. Cada tipo declara su codigo oficial de SUNAT, la forma de su serie, como se le pide a una persona y cuantos digitos tiene el correlativo. No contradice a DEC-026: el codigo SE RAMIFICA por proposito de integracion, mientras que el tipo de comprobante NO se ramifica, VIAJA al emisor electronico.</t>
+          <t>Nueve pantallas estaban dos veces --sueltas en el menu y dentro de /configuracion--, asi que entrar desde el panel dejaba al usuario en una pantalla que se veia igual que Campanas y con el menu marcando otra entrada. El menu queda en tres grupos --Operacion, Finanzas, Registros-- mas Ajustes: Configuracion, y un grupo del que no se puede ver nada desaparece entero.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="57" customHeight="1" s="36">
       <c r="A16" s="67" t="inlineStr">
         <is>
-          <t>DEC-229</t>
+          <t>DEC-234</t>
         </is>
       </c>
       <c r="B16" s="68" t="inlineStr">
@@ -15586,24 +15636,24 @@
       <c r="C16" s="68" t="n"/>
       <c r="D16" s="69" t="inlineStr">
         <is>
-          <t>El numero se reserva bajo bloqueo de la fila de la serie, no con MAX()+1</t>
+          <t>El orden de los grupos es una decision y vive en el registro, no en la plantilla</t>
         </is>
       </c>
       <c r="E16" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F16" s="69" t="inlineStr">
         <is>
-          <t>MAX()+1 es correcto exactamente hasta la primera vez que dos personas emiten a la vez, y eso no es raro: es un cierre de mes. El bloqueo pone en fila a la segunda peticion antes de que lea el contador. Y aun asi existe uq_dn_number: el bloqueo es la primera linea y la unica es la ultima. Medido con dos clientes de verdad (patron de 4.11), con su contraejemplo: sin FOR UPDATE, B no espera.</t>
+          <t>revision() ordena por URGENCIA, que es lo correcto para una lista de avisos y lo peor para una navegacion: «Fiscal y facturacion» saldria arriba o abajo segun que falte hoy, y un sitio que cambia de forma segun el dia no se aprende. Por lo mismo, que rutas son configuracion sale de Preparacion::rutas() y no de la plantilla.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="57" customHeight="1" s="36">
       <c r="A17" s="67" t="inlineStr">
         <is>
-          <t>DEC-230</t>
+          <t>DEC-235</t>
         </is>
       </c>
       <c r="B17" s="68" t="inlineStr">
@@ -15614,24 +15664,24 @@
       <c r="C17" s="68" t="n"/>
       <c r="D17" s="69" t="inlineStr">
         <is>
-          <t>Cada numero que sale queda escrito, y el hueco se explica en vez de taparse</t>
+          <t>Los catalogos son configuracion, con portada propia</t>
         </is>
       </c>
       <c r="E17" s="69" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="F17" s="69" t="inlineStr">
         <is>
-          <t>Reservar y no emitir deja un numero sin documento, y eso NO se arregla reutilizandolo: reutilizarlo ES el duplicado. document_numbers guarda cada numero con su estado; reserved es el unico del que se sale, used dice a que documento fue y voided dice por que, con un motivo de al menos diez caracteres. Un hueco explicado es defendible ante un requerimiento; uno mudo, no.</t>
+          <t>Los seis colgaban del menu bajo un titulo que no era un sitio: era una etiqueta. Ahora son un area con portada --cuantas filas y cuantas activas-- y su aviso: una lista sin ninguna fila activa sale en rojo, porque un catalogo vacio no da error, deja un desplegable vacio. La pantalla de cada catalogo no se mueve.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="68.25" customHeight="1" s="36">
       <c r="A18" s="67" t="inlineStr">
         <is>
-          <t>DEC-231</t>
+          <t>DEC-228</t>
         </is>
       </c>
       <c r="B18" s="68" t="inlineStr">
@@ -15642,7 +15692,7 @@
       <c r="C18" s="68" t="n"/>
       <c r="D18" s="69" t="inlineStr">
         <is>
-          <t>Una sola serie por defecto por (sociedad, tipo, entorno), y la forma la impone el pais</t>
+          <t>Los tipos de comprobante son un catalogo por pais, no un enum en el codigo</t>
         </is>
       </c>
       <c r="E18" s="69" t="inlineStr">
@@ -15652,14 +15702,14 @@
       </c>
       <c r="F18" s="69" t="inlineStr">
         <is>
-          <t>uq_ds_default es la columna puerta 32: con dos series por defecto, «emitir una factura» no tendria respuesta hasta que alguien eligiera. El empate se rechaza al CONFIGURAR y no al emitir. Y tg_ds_forma_ins/upd exige que la serie tenga la forma que declara su tipo y que el tipo sea del pais de la sociedad: una sociedad peruana no emite comprobantes colombianos.</t>
+          <t>ck_ds_type decia IN ('invoice','boleta','credit_note','debit_note','other') desde la Fase 2: la boleta es peruana, el CFDI mexicano no estaba y anadir uno exigia desplegar. Cada tipo declara su codigo oficial de SUNAT, la forma de su serie, como se le pide a una persona y cuantos digitos tiene el correlativo. No contradice a DEC-026: el codigo SE RAMIFICA por proposito de integracion, mientras que el tipo de comprobante NO se ramifica, VIAJA al emisor electronico.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45.75" customHeight="1" s="36">
       <c r="A19" s="67" t="inlineStr">
         <is>
-          <t>DEC-232</t>
+          <t>DEC-229</t>
         </is>
       </c>
       <c r="B19" s="68" t="inlineStr">
@@ -15670,7 +15720,7 @@
       <c r="C19" s="68" t="n"/>
       <c r="D19" s="69" t="inlineStr">
         <is>
-          <t>Las series NO se siembran: unica configuracion sin valor de partida</t>
+          <t>El numero se reserva bajo bloqueo de la fila de la serie, no con MAX()+1</t>
         </is>
       </c>
       <c r="E19" s="69" t="inlineStr">
@@ -15680,14 +15730,14 @@
       </c>
       <c r="F19" s="69" t="inlineStr">
         <is>
-          <t>Excepcion razonada a DEC-190: una serie se registra ante la administracion tributaria y una inventada produciria comprobantes invalidos ante SUNAT --un valor de fabrica aqui no es comodidad, es un error fiscal--. No bloquea nada, que es lo que DEC-190 exige de verdad: sale en rojo en el panel con las palabras que explican por que no hay ninguna. Lo que si se siembra son los TIPOS, que son la regla del pais.</t>
+          <t>MAX()+1 es correcto exactamente hasta la primera vez que dos personas emiten a la vez, y eso no es raro: es un cierre de mes. El bloqueo pone en fila a la segunda peticion antes de que lea el contador. Y aun asi existe uq_dn_number: el bloqueo es la primera linea y la unica es la ultima. Medido con dos clientes de verdad (patron de 4.11), con su contraejemplo: sin FOR UPDATE, B no espera.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="57" customHeight="1" s="36">
       <c r="A20" s="67" t="inlineStr">
         <is>
-          <t>DEC-223</t>
+          <t>DEC-230</t>
         </is>
       </c>
       <c r="B20" s="68" t="inlineStr">
@@ -15698,24 +15748,24 @@
       <c r="C20" s="68" t="n"/>
       <c r="D20" s="69" t="inlineStr">
         <is>
-          <t>Las credenciales de las APIs viven en tres tablas propias, no en .env ni en legal_entities</t>
+          <t>Cada numero que sale queda escrito, y el hueco se explica en vez de taparse</t>
         </is>
       </c>
       <c r="E20" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F20" s="69" t="inlineStr">
         <is>
-          <t>DEC-033 y docs/12 ya lo habian decidido y aqui se construye. Una sociedad es QUIEN factura; una conexion es CON QUE se conecta uno a un proveedor, y cambia mucho mas a menudo que una razon social. En .env seria peor: cambiar de entorno de pruebas a produccion exigiria entrar por SSH, que es DEC-190 roto por la puerta de atras.</t>
+          <t>Reservar y no emitir deja un numero sin documento, y eso NO se arregla reutilizandolo: reutilizarlo ES el duplicado. document_numbers guarda cada numero con su estado; reserved es el unico del que se sale, used dice a que documento fue y voided dice por que, con un motivo de al menos diez caracteres. Un hueco explicado es defendible ante un requerimiento; uno mudo, no.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34.5" customHeight="1" s="36">
       <c r="A21" s="67" t="inlineStr">
         <is>
-          <t>DEC-224</t>
+          <t>DEC-231</t>
         </is>
       </c>
       <c r="B21" s="68" t="inlineStr">
@@ -15726,24 +15776,24 @@
       <c r="C21" s="68" t="n"/>
       <c r="D21" s="69" t="inlineStr">
         <is>
-          <t>Tres tablas de las cinco de docs/12: las asignaciones no se construyen todavia</t>
+          <t>Una sola serie por defecto por (sociedad, tipo, entorno), y la forma la impone el pais</t>
         </is>
       </c>
       <c r="E21" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F21" s="69" t="inlineStr">
         <is>
-          <t>El eje (marca, sociedad, pais) con vigencia resuelve un problema que hoy no existe: una conexion sirve a una sociedad o a la plataforma entera, y eso cabe en un legal_entity_id nullable donde NULL significa «de la plataforma». Construir la tabla de tres ejes antes de tener el segundo caso es construir contra un supuesto. Queda escrito en la cabecera de la migracion para que no se tome por un olvido.</t>
+          <t>uq_ds_default es la columna puerta 32: con dos series por defecto, «emitir una factura» no tendria respuesta hasta que alguien eligiera. El empate se rechaza al CONFIGURAR y no al emitir. Y tg_ds_forma_ins/upd exige que la serie tenga la forma que declara su tipo y que el tipo sea del pais de la sociedad: una sociedad peruana no emite comprobantes colombianos.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="68.25" customHeight="1" s="36">
       <c r="A22" s="67" t="inlineStr">
         <is>
-          <t>DEC-225</t>
+          <t>DEC-232</t>
         </is>
       </c>
       <c r="B22" s="68" t="inlineStr">
@@ -15754,24 +15804,24 @@
       <c r="C22" s="68" t="n"/>
       <c r="D22" s="69" t="inlineStr">
         <is>
-          <t>Rotar una credencial crea la version siguiente y cierra la anterior; no la pisa</t>
+          <t>Las series NO se siembran: unica configuracion sin valor de partida</t>
         </is>
       </c>
       <c r="E22" s="69" t="inlineStr">
         <is>
-          <t>9.17d</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F22" s="69" t="inlineStr">
         <is>
-          <t>Se guardan el cifrado y los cuatro ultimos caracteres, nada mas. Pisar el valor deja sin respuesta «cual era la de antes» y «cuando cambio». Las dos escrituras van en la misma transaccion y en ese orden, porque uq_icred_vigente solo admite una viva por (conexion, clase). tg_icred_inmutable impide reescribir una credencial: lo unico que cambia en una fila existente es revocarla.</t>
+          <t>Excepcion razonada a DEC-190: una serie se registra ante la administracion tributaria y una inventada produciria comprobantes invalidos ante SUNAT --un valor de fabrica aqui no es comodidad, es un error fiscal--. No bloquea nada, que es lo que DEC-190 exige de verdad: sale en rojo en el panel con las palabras que explican por que no hay ninguna. Lo que si se siembra son los TIPOS, que son la regla del pais.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="57" customHeight="1" s="36">
       <c r="A23" s="67" t="inlineStr">
         <is>
-          <t>DEC-226</t>
+          <t>DEC-223</t>
         </is>
       </c>
       <c r="B23" s="68" t="inlineStr">
@@ -15782,7 +15832,7 @@
       <c r="C23" s="68" t="n"/>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>La bitacora anota QUE cambio, no que valor</t>
+          <t>Las credenciales de las APIs viven en tres tablas propias, no en .env ni en legal_entities</t>
         </is>
       </c>
       <c r="E23" s="69" t="inlineStr">
@@ -15792,14 +15842,14 @@
       </c>
       <c r="F23" s="69" t="inlineStr">
         <is>
-          <t>Ni el secreto ni los cuatro ultimos entran en audit_log (BR-SEC-001). Un registro de auditoria que guarda el secreto es un segundo sitio donde esta el secreto, y ademas uno que por diseno no se puede borrar. Por eso el servicio parte la lectura en dos: estado() es lo que ve una persona y secreto() lo llama el cliente de la API.</t>
+          <t>DEC-033 y docs/12 ya lo habian decidido y aqui se construye. Una sociedad es QUIEN factura; una conexion es CON QUE se conecta uno a un proveedor, y cambia mucho mas a menudo que una razon social. En .env seria peor: cambiar de entorno de pruebas a produccion exigiria entrar por SSH, que es DEC-190 roto por la puerta de atras.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34.5" customHeight="1" s="36">
       <c r="A24" s="67" t="inlineStr">
         <is>
-          <t>DEC-227</t>
+          <t>DEC-224</t>
         </is>
       </c>
       <c r="B24" s="68" t="inlineStr">
@@ -15810,7 +15860,7 @@
       <c r="C24" s="68" t="n"/>
       <c r="D24" s="69" t="inlineStr">
         <is>
-          <t>Una conexion ACTIVA exige https; un borrador no</t>
+          <t>Tres tablas de las cinco de docs/12: las asignaciones no se construyen todavia</t>
         </is>
       </c>
       <c r="E24" s="69" t="inlineStr">
@@ -15820,14 +15870,14 @@
       </c>
       <c r="F24" s="69" t="inlineStr">
         <is>
-          <t>ck_iconn_url es la unica regla de la iteracion que no es de forma sino de fondo: una URL http a un servicio de facturacion manda las claves secundarias por la red en claro. Se puede escribir mientras la conexion es un borrador y no se puede activar. La regla vive en la base y no en el formulario, porque el formulario no es el unico que escribe.</t>
+          <t>El eje (marca, sociedad, pais) con vigencia resuelve un problema que hoy no existe: una conexion sirve a una sociedad o a la plataforma entera, y eso cabe en un legal_entity_id nullable donde NULL significa «de la plataforma». Construir la tabla de tres ejes antes de tener el segundo caso es construir contra un supuesto. Queda escrito en la cabecera de la migracion para que no se tome por un olvido.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45.75" customHeight="1" s="36">
       <c r="A25" s="67" t="inlineStr">
         <is>
-          <t>DEC-220</t>
+          <t>DEC-225</t>
         </is>
       </c>
       <c r="B25" s="68" t="inlineStr">
@@ -15838,24 +15888,24 @@
       <c r="C25" s="68" t="n"/>
       <c r="D25" s="69" t="inlineStr">
         <is>
-          <t>Core levanta un evento; Creator escucha</t>
+          <t>Rotar una credencial crea la version siguiente y cierra la anterior; no la pisa</t>
         </is>
       </c>
       <c r="E25" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F25" s="69" t="inlineStr">
         <is>
-          <t>Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
+          <t>Se guardan el cifrado y los cuatro ultimos caracteres, nada mas. Pisar el valor deja sin respuesta «cual era la de antes» y «cuando cambio». Las dos escrituras van en la misma transaccion y en ese orden, porque uq_icred_vigente solo admite una viva por (conexion, clase). tg_icred_inmutable impide reescribir una credencial: lo unico que cambia en una fila existente es revocarla.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="57" customHeight="1" s="36">
       <c r="A26" s="67" t="inlineStr">
         <is>
-          <t>DEC-221</t>
+          <t>DEC-226</t>
         </is>
       </c>
       <c r="B26" s="68" t="inlineStr">
@@ -15866,24 +15916,24 @@
       <c r="C26" s="68" t="n"/>
       <c r="D26" s="69" t="inlineStr">
         <is>
-          <t>El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
+          <t>La bitacora anota QUE cambio, no que valor</t>
         </is>
       </c>
       <c r="E26" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F26" s="69" t="inlineStr">
         <is>
-          <t>Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
+          <t>Ni el secreto ni los cuatro ultimos entran en audit_log (BR-SEC-001). Un registro de auditoria que guarda el secreto es un segundo sitio donde esta el secreto, y ademas uno que por diseno no se puede borrar. Por eso el servicio parte la lectura en dos: estado() es lo que ve una persona y secreto() lo llama el cliente de la API.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="68.25" customHeight="1" s="36">
       <c r="A27" s="67" t="inlineStr">
         <is>
-          <t>DEC-222</t>
+          <t>DEC-227</t>
         </is>
       </c>
       <c r="B27" s="68" t="inlineStr">
@@ -15894,24 +15944,24 @@
       <c r="C27" s="68" t="n"/>
       <c r="D27" s="69" t="inlineStr">
         <is>
-          <t>Un correo que falla no deja sin avisar a los demas</t>
+          <t>Una conexion ACTIVA exige https; un borrador no</t>
         </is>
       </c>
       <c r="E27" s="69" t="inlineStr">
         <is>
-          <t>9.19b</t>
+          <t>9.17d</t>
         </is>
       </c>
       <c r="F27" s="69" t="inlineStr">
         <is>
-          <t>Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
+          <t>ck_iconn_url es la unica regla de la iteracion que no es de forma sino de fondo: una URL http a un servicio de facturacion manda las claves secundarias por la red en claro. Se puede escribir mientras la conexion es un borrador y no se puede activar. La regla vive en la base y no en el formulario, porque el formulario no es el unico que escribe.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="57" customHeight="1" s="36">
       <c r="A28" s="67" t="inlineStr">
         <is>
-          <t>DEC-216</t>
+          <t>DEC-220</t>
         </is>
       </c>
       <c r="B28" s="68" t="inlineStr">
@@ -15922,24 +15972,24 @@
       <c r="C28" s="68" t="n"/>
       <c r="D28" s="69" t="inlineStr">
         <is>
-          <t>Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
+          <t>Core levanta un evento; Creator escucha</t>
         </is>
       </c>
       <c r="E28" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F28" s="69" t="inlineStr">
         <is>
-          <t>El plazo es parte de lo que se le comunico a la gente: «tienes 15 dias» dicho en enero no puede convertirse en «tenias 10» porque en marzo alguien cambio un ajuste global. Cada version lleva los suyos, se eligen al publicarla y despues son inmutables. Lo configurable es el valor por defecto, que es lo que el formulario trae puesto. readonly_days = 0 significa «sin periodo de solo lectura»; un numero muy grande, lo contrario.</t>
+          <t>Avisar a los creadores exige leer creators, y Core no puede saber de esa tabla (fue T-74). Terminos::publicar() levanta TerminosPublicados en Shared y no sabe quien escucha; AvisarReaceptacion en Creator escucha y no sabe quien lo levanto. Consecuencia que no es teorica: si el envio falla, la publicacion ya esta hecha. Un SMTP caido no tumba unos terminos.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="68.25" customHeight="1" s="36">
       <c r="A29" s="67" t="inlineStr">
         <is>
-          <t>DEC-217</t>
+          <t>DEC-221</t>
         </is>
       </c>
       <c r="B29" s="68" t="inlineStr">
@@ -15950,24 +16000,24 @@
       <c r="C29" s="68" t="n"/>
       <c r="D29" s="69" t="inlineStr">
         <is>
-          <t>El reloj no empieza al publicar: empieza cuando le toca a el</t>
+          <t>El aviso sale solo si el cambio es de fondo, y solo a su audiencia</t>
         </is>
       </c>
       <c r="E29" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F29" s="69" t="inlineStr">
         <is>
-          <t>Un creador activado ayer no puede aparecer bloqueado por una version de hace tres meses. Su plazo cuenta desde el dia en que se activo, o desde la fecha de la version si es posterior. Sin esto, el primer creador que se diera de alta despues de un cambio de fondo entraria directamente al muro sin haber tenido un solo dia.</t>
+          <t>Un cambio menor no invalida la aceptacion anterior: avisar de el seria molestar a todo el mundo por una errata, y el aviso que llega por todo deja de leerse. El texto dice ademas QUE PASA DESPUES --«podras seguir viendo, pero no cambiar nada»-- porque «hay terminos nuevos» a secas se pospone y «el dia X dejas de poder trabajar» no.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45.75" customHeight="1" s="36">
       <c r="A30" s="67" t="inlineStr">
         <is>
-          <t>DEC-218</t>
+          <t>DEC-222</t>
         </is>
       </c>
       <c r="B30" s="68" t="inlineStr">
@@ -15978,24 +16028,24 @@
       <c r="C30" s="68" t="n"/>
       <c r="D30" s="69" t="inlineStr">
         <is>
-          <t>La pantalla del muro no lleva permiso, y eso es la decision</t>
+          <t>Un correo que falla no deja sin avisar a los demas</t>
         </is>
       </c>
       <c r="E30" s="69" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.19b</t>
         </is>
       </c>
       <c r="F30" s="69" t="inlineStr">
         <is>
-          <t>/mis-terminos es la unica salida de un creador bloqueado: un permiso dejaria sin salida justo a quien la necesita. La autorizacion es tener ficha de creador atada a la sesion. El trinquete de rutas exentas subio de 4 a 6 a mano y con motivo escrito, que es todo el sentido de ese trinquete. Lleva throttle:10,1.</t>
+          <t>Cada envio va en su propio try: con doscientos creadores, que el numero 37 tenga el correo mal escrito no puede dejar sin aviso a los 163 siguientes. Lo que falla queda en el registro para que «a este no le llego» se pueda contestar.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="79.5" customHeight="1" s="36">
       <c r="A31" s="67" t="inlineStr">
         <is>
-          <t>DEC-219</t>
+          <t>DEC-216</t>
         </is>
       </c>
       <c r="B31" s="68" t="inlineStr">
@@ -16006,7 +16056,7 @@
       <c r="C31" s="68" t="n"/>
       <c r="D31" s="69" t="inlineStr">
         <is>
-          <t>Una franja fija, no un popup</t>
+          <t>Los plazos de reaceptacion van en la version, no en una tabla de ajustes</t>
         </is>
       </c>
       <c r="E31" s="69" t="inlineStr">
@@ -16016,14 +16066,14 @@
       </c>
       <c r="F31" s="69" t="inlineStr">
         <is>
-          <t>El negocio pidio «popup como recordatorio al loguearse». Un popup se cierra sin leerlo y no vuelve hasta la siguiente sesion; la franja sigue ahi mientras siga sin aceptarse. El equipo interno no la ve nunca.</t>
+          <t>El plazo es parte de lo que se le comunico a la gente: «tienes 15 dias» dicho en enero no puede convertirse en «tenias 10» porque en marzo alguien cambio un ajuste global. Cada version lleva los suyos, se eligen al publicarla y despues son inmutables. Lo configurable es el valor por defecto, que es lo que el formulario trae puesto. readonly_days = 0 significa «sin periodo de solo lectura»; un numero muy grande, lo contrario.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="68.25" customHeight="1" s="36">
       <c r="A32" s="67" t="inlineStr">
         <is>
-          <t>DEC-212</t>
+          <t>DEC-217</t>
         </is>
       </c>
       <c r="B32" s="68" t="inlineStr">
@@ -16034,24 +16084,24 @@
       <c r="C32" s="68" t="n"/>
       <c r="D32" s="69" t="inlineStr">
         <is>
-          <t>Una politica de precios con vigencia, no dos constantes</t>
+          <t>El reloj no empieza al publicar: empieza cuando le toca a el</t>
         </is>
       </c>
       <c r="E32" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F32" s="69" t="inlineStr">
         <is>
-          <t>pricing_policies guarda la retencion (Q-13), el umbral de rentabilidad y sobre que se calcula. Los tres cambian: el 29,5 % por decreto y el 20 % con datos reales. Tiene historia --una sola vigente-- y una cerrada no se reescribe ni se borra: es la que explica como se pacto un compromiso de hace tres meses.</t>
+          <t>Un creador activado ayer no puede aparecer bloqueado por una version de hace tres meses. Su plazo cuenta desde el dia en que se activo, o desde la fecha de la version si es posterior. Sin esto, el primer creador que se diera de alta despues de un cambio de fondo entraria directamente al muro sin haber tenido un solo dia.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45.75" customHeight="1" s="36">
       <c r="A33" s="67" t="inlineStr">
         <is>
-          <t>DEC-213</t>
+          <t>DEC-218</t>
         </is>
       </c>
       <c r="B33" s="68" t="inlineStr">
@@ -16062,24 +16112,24 @@
       <c r="C33" s="68" t="n"/>
       <c r="D33" s="69" t="inlineStr">
         <is>
-          <t>margin_basis es configuracion, no una pregunta</t>
+          <t>La pantalla del muro no lleva permiso, y eso es la decision</t>
         </is>
       </c>
       <c r="E33" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F33" s="69" t="inlineStr">
         <is>
-          <t>Con 100 de neto y 29,5 % el costo es 141,84; el ejemplo del negocio dio 170,21, que es 141,84 x 1,20 (recargo sobre el COSTO). Un 20 % de margen sobre el INGRESO habria dado 177,31. Lo iba a preguntar dos veces; DEC-190 dice que estas cosas se configuran, y preguntarlo habria sido quemar la respuesta en el codigo con la firma del negocio encima. Es una columna con dos valores, sembrada en cost, con la pantalla ensenando las dos cifras y una prueba de cada una.</t>
+          <t>/mis-terminos es la unica salida de un creador bloqueado: un permiso dejaria sin salida justo a quien la necesita. La autorizacion es tener ficha de creador atada a la sesion. El trinquete de rutas exentas subio de 4 a 6 a mano y con motivo escrito, que es todo el sentido de ese trinquete. Lleva throttle:10,1.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45.75" customHeight="1" s="36">
       <c r="A34" s="67" t="inlineStr">
         <is>
-          <t>DEC-214</t>
+          <t>DEC-219</t>
         </is>
       </c>
       <c r="B34" s="68" t="inlineStr">
@@ -16090,24 +16140,24 @@
       <c r="C34" s="68" t="n"/>
       <c r="D34" s="69" t="inlineStr">
         <is>
-          <t>Se pacta el costo o el neto, y el ingreso minimo se dice, no se impone</t>
+          <t>Una franja fija, no un popup</t>
         </is>
       </c>
       <c r="E34" s="69" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="F34" s="69" t="inlineStr">
         <is>
-          <t>agreed_amount sigue siendo el costo: de esa columna cuelgan devengos, pagos y la rentabilidad de 9.10. Se anaden la base, el neto y la tasa. Con net se teclean 100 y se escriben 141,8440, y el motor rehace la resta: un neto que no cuadra con su bruto se descubriria en la conversacion con el creador que cobro de menos. El mensaje dice el ingreso minimo y no bloquea: se puede aceptar menos margen, pero sabiendolo y antes de invitar. Los tres numeros se congelan en la participacion.</t>
+          <t>El negocio pidio «popup como recordatorio al loguearse». Un popup se cierra sin leerlo y no vuelve hasta la siguiente sesion; la franja sigue ahi mientras siga sin aceptarse. El equipo interno no la ve nunca.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="68.25" customHeight="1" s="36">
       <c r="A35" s="67" t="inlineStr">
         <is>
-          <t>DEC-215</t>
+          <t>DEC-212</t>
         </is>
       </c>
       <c r="B35" s="68" t="inlineStr">
@@ -16118,7 +16168,7 @@
       <c r="C35" s="68" t="n"/>
       <c r="D35" s="69" t="inlineStr">
         <is>
-          <t>La cuenta la hace el motor, no PHP</t>
+          <t>Una politica de precios con vigencia, no dos constantes</t>
         </is>
       </c>
       <c r="E35" s="69" t="inlineStr">
@@ -16128,14 +16178,14 @@
       </c>
       <c r="F35" s="69" t="inlineStr">
         <is>
-          <t>neto / (1 - tasa/100) con float da 141.84397163120568 y de ahi a un DECIMAL(18,4) hay un redondeo que puede caer del lado que el CHECK no admite. El contenedor no tiene bcmath, asi que la aritmetica exacta se hace en el motor con CAST a DECIMAL(28,12). Misma tecnica que 9.1 y 9.3.</t>
+          <t>pricing_policies guarda la retencion (Q-13), el umbral de rentabilidad y sobre que se calcula. Los tres cambian: el 29,5 % por decreto y el 20 % con datos reales. Tiene historia --una sola vigente-- y una cerrada no se reescribe ni se borra: es la que explica como se pacto un compromiso de hace tres meses.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="57" customHeight="1" s="36">
       <c r="A36" s="67" t="inlineStr">
         <is>
-          <t>DEC-209</t>
+          <t>DEC-213</t>
         </is>
       </c>
       <c r="B36" s="68" t="inlineStr">
@@ -16146,24 +16196,24 @@
       <c r="C36" s="68" t="n"/>
       <c r="D36" s="69" t="inlineStr">
         <is>
-          <t>La forma del codigo de localidad la declara el pais, no el codigo</t>
+          <t>margin_basis es configuracion, no una pregunta</t>
         </is>
       </c>
       <c r="E36" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F36" s="69" t="inlineStr">
         <is>
-          <t>El comprobante peruano lleva el ubigeo del INEI (seis digitos) y el colombiano el codigo DANE (cinco). Una columna ubigeo CHAR(6) habria sido la regla de un pais escrita en el codigo de los seis y rechazaria un codigo colombiano correcto. countries declara como se llama, que forma tiene y si ese pais lo exige; el formulario pide «Ubigeo» a una peruana y «Codigo DANE» a una colombiana sin una linea de codigo por pais. La imponen dos disparadores cruzados que leen el patron de countries.</t>
+          <t>Con 100 de neto y 29,5 % el costo es 141,84; el ejemplo del negocio dio 170,21, que es 141,84 x 1,20 (recargo sobre el COSTO). Un 20 % de margen sobre el INGRESO habria dado 177,31. Lo iba a preguntar dos veces; DEC-190 dice que estas cosas se configuran, y preguntarlo habria sido quemar la respuesta en el codigo con la firma del negocio encima. Es una columna con dos valores, sembrada en cost, con la pantalla ensenando las dos cifras y una prueba de cada una.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="68.25" customHeight="1" s="36">
       <c r="A37" s="67" t="inlineStr">
         <is>
-          <t>DEC-210</t>
+          <t>DEC-214</t>
         </is>
       </c>
       <c r="B37" s="68" t="inlineStr">
@@ -16174,24 +16224,24 @@
       <c r="C37" s="68" t="n"/>
       <c r="D37" s="69" t="inlineStr">
         <is>
-          <t>El codigo de establecimiento nace en «0000» y no admite nulo</t>
+          <t>Se pacta el costo o el neto, y el ingreso minimo se dice, no se impone</t>
         </is>
       </c>
       <c r="E37" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F37" s="69" t="inlineStr">
         <is>
-          <t>Un comprobante SIEMPRE lleva uno; dejarlo nulo obligaria a decidirlo al emitir, que es tarde. «0000» es el domicilio fiscal en SUNAT. El formulario lo puede dejar en blanco --al crear y al editar-- y entonces vale 0000: sin esa normalizacion, vaciar el campo metia una cadena vacia que ck_le_establecimiento rechaza con un 45000 sin explicar nada.</t>
+          <t>agreed_amount sigue siendo el costo: de esa columna cuelgan devengos, pagos y la rentabilidad de 9.10. Se anaden la base, el neto y la tasa. Con net se teclean 100 y se escriben 141,8440, y el motor rehace la resta: un neto que no cuadra con su bruto se descubriria en la conversacion con el creador que cobro de menos. El mensaje dice el ingreso minimo y no bloquea: se puede aceptar menos margen, pero sabiendolo y antes de invitar. Los tres numeros se congelan en la participacion.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="45.75" customHeight="1" s="36">
       <c r="A38" s="67" t="inlineStr">
         <is>
-          <t>DEC-211</t>
+          <t>DEC-215</t>
         </is>
       </c>
       <c r="B38" s="68" t="inlineStr">
@@ -16202,24 +16252,24 @@
       <c r="C38" s="68" t="n"/>
       <c r="D38" s="69" t="inlineStr">
         <is>
-          <t>Que falte el ubigeo no bloquea: es un aviso rojo</t>
+          <t>La cuenta la hace el motor, no PHP</t>
         </is>
       </c>
       <c r="E38" s="69" t="inlineStr">
         <is>
-          <t>9.17c</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>requires_tax_location no impide guardar una sociedad a medias; hace que el panel de 9.17b lo enseñe en rojo con el nombre que ese pais le da. Y sale a la luz algo que no decia nadie: el sembrador escribe address_line1 = «Por completar» porque la columna es NOT NULL, la sociedad parecia completa, y ese texto habria salido impreso en un comprobante.</t>
+          <t>neto / (1 - tasa/100) con float da 141.84397163120568 y de ahi a un DECIMAL(18,4) hay un redondeo que puede caer del lado que el CHECK no admite. El contenedor no tiene bcmath, asi que la aritmetica exacta se hace en el motor con CAST a DECIMAL(28,12). Misma tecnica que 9.1 y 9.3.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="90.75" customHeight="1" s="36">
       <c r="A39" s="67" t="inlineStr">
         <is>
-          <t>DEC-205</t>
+          <t>DEC-209</t>
         </is>
       </c>
       <c r="B39" s="68" t="inlineStr">
@@ -16230,24 +16280,24 @@
       <c r="C39" s="68" t="n"/>
       <c r="D39" s="69" t="inlineStr">
         <is>
-          <t>Un registro de preparacion, y cada modulo declara lo suyo</t>
+          <t>La forma del codigo de localidad la declara el pais, no el codigo</t>
         </is>
       </c>
       <c r="E39" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>9.16 y 9.17 dejaron cada una su lista de avisos y cada una solo se ve entrando en su pantalla. Preparacion las junta, y cada modulo declara las comprobaciones de su area en su ServiceProvider: un revisor central pondria a Shared a saber de cinco modulos sin que deptrac lo vea, porque son consultas a tablas y no clases importadas. Hay una prueba que se rompe cuando alguien construye una pantalla de configuracion nueva y no la enchufa.</t>
+          <t>El comprobante peruano lleva el ubigeo del INEI (seis digitos) y el colombiano el codigo DANE (cinco). Una columna ubigeo CHAR(6) habria sido la regla de un pais escrita en el codigo de los seis y rechazaria un codigo colombiano correcto. countries declara como se llama, que forma tiene y si ese pais lo exige; el formulario pide «Ubigeo» a una peruana y «Codigo DANE» a una colombiana sin una linea de codigo por pais. La imponen dos disparadores cruzados que leen el patron de countries.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="45.75" customHeight="1" s="36">
       <c r="A40" s="67" t="inlineStr">
         <is>
-          <t>DEC-206</t>
+          <t>DEC-210</t>
         </is>
       </c>
       <c r="B40" s="68" t="inlineStr">
@@ -16258,24 +16308,24 @@
       <c r="C40" s="68" t="n"/>
       <c r="D40" s="69" t="inlineStr">
         <is>
-          <t>Si no puedes arreglarlo, no lo ves</t>
+          <t>El codigo de establecimiento nace en «0000» y no admite nulo</t>
         </is>
       </c>
       <c r="E40" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>Cada area declara el permiso con el que SE ARREGLA, no el que hace falta para abrir el panel, y la revision filtra por el. BR-SEC-001 sigue en pie aunque la pantalla reuna en un sitio lo que estaba repartido en cinco, y ningun aviso lleva a un 403. Por eso config.view se le puede dar a finanzas sin miedo: ve el area de tipos de cambio y nada mas.</t>
+          <t>Un comprobante SIEMPRE lleva uno; dejarlo nulo obligaria a decidirlo al emitir, que es tarde. «0000» es el domicilio fiscal en SUNAT. El formulario lo puede dejar en blanco --al crear y al editar-- y entonces vale 0000: sin esa normalizacion, vaciar el campo metia una cadena vacia que ck_le_establecimiento rechaza con un 45000 sin explicar nada.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="57" customHeight="1" s="36">
       <c r="A41" s="67" t="inlineStr">
         <is>
-          <t>DEC-207</t>
+          <t>DEC-211</t>
         </is>
       </c>
       <c r="B41" s="68" t="inlineStr">
@@ -16286,24 +16336,24 @@
       <c r="C41" s="68" t="n"/>
       <c r="D41" s="69" t="inlineStr">
         <is>
-          <t>Una comprobacion que revienta no tumba el panel</t>
+          <t>Que falte el ubigeo no bloquea: es un aviso rojo</t>
         </is>
       </c>
       <c r="E41" s="69" t="inlineStr">
         <is>
-          <t>9.17b</t>
+          <t>9.17c</t>
         </is>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>Un revisor que lanza una excepcion se convierte en un aviso ambar que lo dice, y las demas areas se siguen viendo. Un panel de «que me falta» que responde 500 porque a un area le pasa algo deja de contestar justo el dia en que hay algo que contestar.</t>
+          <t>requires_tax_location no impide guardar una sociedad a medias; hace que el panel de 9.17b lo enseñe en rojo con el nombre que ese pais le da. Y sale a la luz algo que no decia nadie: el sembrador escribe address_line1 = «Por completar» porque la columna es NOT NULL, la sociedad parecia completa, y ese texto habria salido impreso en un comprobante.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="45.75" customHeight="1" s="36">
       <c r="A42" s="67" t="inlineStr">
         <is>
-          <t>DEC-208</t>
+          <t>DEC-205</t>
         </is>
       </c>
       <c r="B42" s="68" t="inlineStr">
@@ -16314,7 +16364,7 @@
       <c r="C42" s="68" t="n"/>
       <c r="D42" s="69" t="inlineStr">
         <is>
-          <t>El correo en log es ROJO, y va el primero del panel</t>
+          <t>Un registro de preparacion, y cada modulo declara lo suyo</t>
         </is>
       </c>
       <c r="E42" s="69" t="inlineStr">
@@ -16324,14 +16374,14 @@
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>mail.default vale log mientras nadie ponga una cuenta SMTP (Q-20), y con ese valor el correo no sale de la maquina: se escribe en storage/logs. La aplicacion no falla, la bitacora dice enviado y el creador no recibe su enlace de alta. Es el modo de fallo mas caro del sistema porque no se nota desde dentro, y hasta hoy no lo decia ninguna pantalla.</t>
+          <t>9.16 y 9.17 dejaron cada una su lista de avisos y cada una solo se ve entrando en su pantalla. Preparacion las junta, y cada modulo declara las comprobaciones de su area en su ServiceProvider: un revisor central pondria a Shared a saber de cinco modulos sin que deptrac lo vea, porque son consultas a tablas y no clases importadas. Hay una prueba que se rompe cuando alguien construye una pantalla de configuracion nueva y no la enchufa.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="68.25" customHeight="1" s="36">
       <c r="A43" s="67" t="inlineStr">
         <is>
-          <t>DEC-199</t>
+          <t>DEC-206</t>
         </is>
       </c>
       <c r="B43" s="68" t="inlineStr">
@@ -16342,24 +16392,24 @@
       <c r="C43" s="68" t="n"/>
       <c r="D43" s="69" t="inlineStr">
         <is>
-          <t>La marca es una fila, y hay UNA sola por defecto</t>
+          <t>Si no puedes arreglarlo, no lo ves</t>
         </is>
       </c>
       <c r="E43" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>«LATAM Social» estaba escrito en tres plantillas --title, barra lateral y pantalla de acceso--, el favicon era un archivo del repositorio y el pie legal con la razon social y el RUC estaba a mano al pie del formulario de entrada. platform_brands guardaba todo eso desde 2.10 y nadie la leyo nunca. default_gate es la 28.a columna puerta y uq_pb_default la hace unica: dos marcas por defecto es media aplicacion ensenando un nombre y la otra mitad otro sin que nada falle.</t>
+          <t>Cada area declara el permiso con el que SE ARREGLA, no el que hace falta para abrir el panel, y la revision filtra por el. BR-SEC-001 sigue en pie aunque la pantalla reuna en un sitio lo que estaba repartido en cinco, y ningun aviso lleva a un 403. Por eso config.view se le puede dar a finanzas sin miedo: ve el area de tipos de cambio y nada mas.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="79.5" customHeight="1" s="36">
       <c r="A44" s="67" t="inlineStr">
         <is>
-          <t>DEC-200</t>
+          <t>DEC-207</t>
         </is>
       </c>
       <c r="B44" s="68" t="inlineStr">
@@ -16370,24 +16420,24 @@
       <c r="C44" s="68" t="n"/>
       <c r="D44" s="69" t="inlineStr">
         <is>
-          <t>Una configuracion que falta NO bloquea: valor de partida y aviso con prioridad</t>
+          <t>Una comprobacion que revienta no tumba el panel</t>
         </is>
       </c>
       <c r="E44" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>DEC-190 llevado al codigo. Sin tabla, sin fila o con un campo vacio se cae al valor de partida y aparece un badge: rojo lo que un tercero va a ver mal (sin logotipo, sin correo de soporte), ambar lo que conviene (sin favicon, sin pie legal, sin web), verde cuando no falta nada. El sistema arranca con dos rojos y funciona perfectamente con los dos puestos.</t>
+          <t>Un revisor que lanza una excepcion se convierte en un aviso ambar que lo dice, y las demas areas se siguen viendo. Un panel de «que me falta» que responde 500 porque a un area le pasa algo deja de contestar justo el dia en que hay algo que contestar.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="124.5" customHeight="1" s="36">
       <c r="A45" s="67" t="inlineStr">
         <is>
-          <t>DEC-201</t>
+          <t>DEC-208</t>
         </is>
       </c>
       <c r="B45" s="68" t="inlineStr">
@@ -16398,24 +16448,24 @@
       <c r="C45" s="68" t="n"/>
       <c r="D45" s="69" t="inlineStr">
         <is>
-          <t>El logotipo se sirve por una puerta publica propia, sin identificador</t>
+          <t>El correo en log es ROJO, y va el primero del panel</t>
         </is>
       </c>
       <c r="E45" s="69" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>9.17b</t>
         </is>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>La pantalla de acceso la ve quien no ha entrado, asi que el permiso file.view de 9.15 dejaria la marca fuera de la unica pantalla que ve todo el mundo. Lo que hace seguras a /marca/logo y /marca/favicon no es un permiso: es que NO aceptan identificador. Estan en RUTAS-ABIERTAS con su motivo y MuroTest las conoce.</t>
+          <t>mail.default vale log mientras nadie ponga una cuenta SMTP (Q-20), y con ese valor el correo no sale de la maquina: se escribe en storage/logs. La aplicacion no falla, la bitacora dice enviado y el creador no recibe su enlace de alta. Es el modo de fallo mas caro del sistema porque no se nota desde dentro, y hasta hoy no lo decia ninguna pantalla.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="90.75" customHeight="1" s="36">
       <c r="A46" s="67" t="inlineStr">
         <is>
-          <t>DEC-202</t>
+          <t>DEC-199</t>
         </is>
       </c>
       <c r="B46" s="68" t="inlineStr">
@@ -16426,7 +16476,7 @@
       <c r="C46" s="68" t="n"/>
       <c r="D46" s="69" t="inlineStr">
         <is>
-          <t>El codigo de la marca no se cambia; el nombre visible si</t>
+          <t>La marca es una fila, y hay UNA sola por defecto</t>
         </is>
       </c>
       <c r="E46" s="69" t="inlineStr">
@@ -16436,14 +16486,14 @@
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>tg_pb_code lo impide en el motor. El code es la llave con la que el sembrador encuentra la marca: si cambia, el siguiente db:seed crea otra, el sistema amanece con dos y las pantallas siguen ensenando la vieja mientras alguien edita la nueva.</t>
+          <t>«LATAM Social» estaba escrito en tres plantillas --title, barra lateral y pantalla de acceso--, el favicon era un archivo del repositorio y el pie legal con la razon social y el RUC estaba a mano al pie del formulario de entrada. platform_brands guardaba todo eso desde 2.10 y nadie la leyo nunca. default_gate es la 28.a columna puerta y uq_pb_default la hace unica: dos marcas por defecto es media aplicacion ensenando un nombre y la otra mitad otro sin que nada falle.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="68.25" customHeight="1" s="36">
       <c r="A47" s="67" t="inlineStr">
         <is>
-          <t>DEC-203</t>
+          <t>DEC-200</t>
         </is>
       </c>
       <c r="B47" s="68" t="inlineStr">
@@ -16454,7 +16504,7 @@
       <c r="C47" s="68" t="n"/>
       <c r="D47" s="69" t="inlineStr">
         <is>
-          <t>Los colores y la tipografia se desinfectan ademas del CHECK</t>
+          <t>Una configuracion que falta NO bloquea: valor de partida y aviso con prioridad</t>
         </is>
       </c>
       <c r="E47" s="69" t="inlineStr">
@@ -16464,14 +16514,14 @@
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>El color acaba dentro de una regla CSS y la tipografia dentro de una URL y de una regla CSS, en todas las pantallas a la vez. Un nombre con comillas y llaves cierra la regla y escribe estilo ajeno en toda la aplicacion. Si el valor entra por una via que no pasa por el CHECK --carga masiva, restauracion de copia--, la segunda cerradura es lo unico que queda.</t>
+          <t>DEC-190 llevado al codigo. Sin tabla, sin fila o con un campo vacio se cae al valor de partida y aparece un badge: rojo lo que un tercero va a ver mal (sin logotipo, sin correo de soporte), ambar lo que conviene (sin favicon, sin pie legal, sin web), verde cuando no falta nada. El sistema arranca con dos rojos y funciona perfectamente con los dos puestos.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="45.75" customHeight="1" s="36">
       <c r="A48" s="67" t="inlineStr">
         <is>
-          <t>DEC-204</t>
+          <t>DEC-201</t>
         </is>
       </c>
       <c r="B48" s="68" t="inlineStr">
@@ -16482,7 +16532,7 @@
       <c r="C48" s="68" t="n"/>
       <c r="D48" s="69" t="inlineStr">
         <is>
-          <t>brand.manage es un permiso propio, y no legal_entity.manage</t>
+          <t>El logotipo se sirve por una puerta publica propia, sin identificador</t>
         </is>
       </c>
       <c r="E48" s="69" t="inlineStr">
@@ -16492,14 +16542,14 @@
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>Quien da de alta sociedades del grupo no tiene por que poder cambiar lo que ve todo el mundo en todas las pantallas, incluida la de acceso. Hoy los dos los tiene solo admin; el dia que legal_entity.manage se le de a alguien de operaciones, esa persona no podra cambiar la marca. Hay una prueba que lo fija.</t>
+          <t>La pantalla de acceso la ve quien no ha entrado, asi que el permiso file.view de 9.15 dejaria la marca fuera de la unica pantalla que ve todo el mundo. Lo que hace seguras a /marca/logo y /marca/favicon no es un permiso: es que NO aceptan identificador. Estan en RUTAS-ABIERTAS con su motivo y MuroTest las conoce.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="57" customHeight="1" s="36">
       <c r="A49" s="67" t="inlineStr">
         <is>
-          <t>DEC-198</t>
+          <t>DEC-202</t>
         </is>
       </c>
       <c r="B49" s="68" t="inlineStr">
@@ -16510,24 +16560,24 @@
       <c r="C49" s="68" t="n"/>
       <c r="D49" s="69" t="inlineStr">
         <is>
-          <t>El permiso se mira en CADA peticion: no hay URL firmada de archivo.</t>
+          <t>El codigo de la marca no se cambia; el nombre visible si</t>
         </is>
       </c>
       <c r="E49" s="69" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>Una URL firmada sigue funcionando cuando se reenvia y cuando a esa persona ya se le quito el acceso, y lo que sale por aqui son documentos de identidad y comprobantes bancarios. Con ruta propia, quitar un permiso surte efecto en la siguiente peticion y no queda ningun enlace circulando. El archivo se busca por uuid y no por id --un id correlativo invita a probar el siguiente-- y la respuesta lleva no-store (una identidad en la cache de un equipo compartido sobrevive al cierre de sesion), nosniff y una CSP que impide que un HTML o un SVG subido como «evidencia» se ejecute. El creador ve lo suyo, incluida su identidad: es informacion suya y le permite comprobar que archivamos el correcto. Rastro en bitacora solo para los sensibles --identidad, terminos y comprobante bancario--: anotar cada captura convertiria la bitacora en ruido, y una bitacora que nadie lee no protege nada</t>
+          <t>tg_pb_code lo impide en el motor. El code es la llave con la que el sembrador encuentra la marca: si cambia, el siguiente db:seed crea otra, el sistema amanece con dos y las pantallas siguen ensenando la vieja mientras alguien edita la nueva.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="79.5" customHeight="1" s="36">
       <c r="A50" s="67" t="inlineStr">
         <is>
-          <t>DEC-197</t>
+          <t>DEC-203</t>
         </is>
       </c>
       <c r="B50" s="68" t="inlineStr">
@@ -16538,24 +16588,24 @@
       <c r="C50" s="68" t="n"/>
       <c r="D50" s="69" t="inlineStr">
         <is>
-          <t>Cada modulo declara quien puede ver SUS archivos; no hay un switch central.</t>
+          <t>Los colores y la tipografia se desinfectan ademas del CHECK</t>
         </is>
       </c>
       <c r="E50" s="69" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>La regla de cada archivo depende de la tabla que lo apunta --identidad de creators, captura de publication_evidence, comprobante de payouts-- y un decisor central que las consultara todas pondria a Shared o a Core a saber de payouts. deptrac no lo veria: son consultas a tablas y no clases importadas, o sea una frontera rota en silencio, que es la peor clase. Cada modulo registra su regla en su ServiceProvider, igual que registra sus escuchas. Y se niega por omision: un proposito sin regla no se abre ni para el administrador, asi que un archivo nuevo cuyo autor olvido declarar quien puede verlo se queda cerrado y no abierto a todos</t>
+          <t>El color acaba dentro de una regla CSS y la tipografia dentro de una URL y de una regla CSS, en todas las pantallas a la vez. Un nombre con comillas y llaves cierra la regla y escribe estilo ajeno en toda la aplicacion. Si el valor entra por una via que no pasa por el CHECK --carga masiva, restauracion de copia--, la segunda cerradura es lo unico que queda.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="113.25" customHeight="1" s="36">
       <c r="A51" s="67" t="inlineStr">
         <is>
-          <t>DEC-196</t>
+          <t>DEC-204</t>
         </is>
       </c>
       <c r="B51" s="68" t="inlineStr">
@@ -16566,24 +16616,24 @@
       <c r="C51" s="68" t="n"/>
       <c r="D51" s="69" t="inlineStr">
         <is>
-          <t>La Academia del creador se construye, y cada modulo se configura desde el admin.</t>
+          <t>brand.manage es un permiso propio, y no legal_entity.manage</t>
         </is>
       </c>
       <c r="E51" s="69" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>Es G-08 del addendum de gamificacion y la de mas retorno de las once: modulos cortos --leer un brief sin gastar rondas, iluminacion y audio con un movil, como se rotula el contenido comercial, que derechos esta cediendo, como subir su evidencia-- con evaluacion al final e insignia de creador certificado. Ataca tres dolores ya medidos: cada ronda evitada es tiempo del equipo de revision, cada evidencia subida sola es el proceso mas manual que se deja de perseguir, y «creadores certificados» es un argumento de venta ante la marca. El software es la parte barata: modulos, orden, formato, evaluacion, intentos, XP e insignia salen del admin (DEC-190), y al completar uno se levanta TrainingModuleCompleted, previsto en el modelo desde la Fase 2. Lo caro es el CONTENIDO --guiones, video, mantenerlo cuando cambie una norma o una red-- y eso no lo hace el sistema. Se puede arrancar con modulos de solo texto, que cuestan casi nada y ya bajan rondas. Cierra Q-27</t>
+          <t>Quien da de alta sociedades del grupo no tiene por que poder cambiar lo que ve todo el mundo en todas las pantallas, incluida la de acceso. Hoy los dos los tiene solo admin; el dia que legal_entity.manage se le de a alguien de operaciones, esa persona no podra cambiar la marca. Hay una prueba que lo fija.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="102" customHeight="1" s="36">
       <c r="A52" s="67" t="inlineStr">
         <is>
-          <t>DEC-195</t>
+          <t>DEC-198</t>
         </is>
       </c>
       <c r="B52" s="68" t="inlineStr">
@@ -16594,24 +16644,24 @@
       <c r="C52" s="68" t="n"/>
       <c r="D52" s="69" t="inlineStr">
         <is>
-          <t>El lado del tipo de cambio se configura POR TIPO DE TRANSACCION.</t>
+          <t>El permiso se mira en CADA peticion: no hay URL firmada de archivo.</t>
         </is>
       </c>
       <c r="E52" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>No se fija uno en el codigo: lo que se le paga a un creador, lo que se le cobra a un cliente y un gasto operativo no tienen por que convertirse con el mismo lado, y esa eleccion es contable. El admin declara, para cada tipo de transaccion, que lado se aplica (compra, venta o media) y con que fuente. Cierra Q-63, que era la que impedia dar un porcentaje de margen cuando hay dos monedas (DEC-185)</t>
+          <t>Una URL firmada sigue funcionando cuando se reenvia y cuando a esa persona ya se le quito el acceso, y lo que sale por aqui son documentos de identidad y comprobantes bancarios. Con ruta propia, quitar un permiso surte efecto en la siguiente peticion y no queda ningun enlace circulando. El archivo se busca por uuid y no por id --un id correlativo invita a probar el siguiente-- y la respuesta lleva no-store (una identidad en la cache de un equipo compartido sobrevive al cierre de sesion), nosniff y una CSP que impide que un HTML o un SVG subido como «evidencia» se ejecute. El creador ve lo suyo, incluida su identidad: es informacion suya y le permite comprobar que archivamos el correcto. Rastro en bitacora solo para los sensibles --identidad, terminos y comprobante bancario--: anotar cada captura convertiria la bitacora en ruido, y una bitacora que nadie lee no protege nada</t>
         </is>
       </c>
     </row>
     <row r="53" ht="79.5" customHeight="1" s="36">
       <c r="A53" s="67" t="inlineStr">
         <is>
-          <t>DEC-194</t>
+          <t>DEC-197</t>
         </is>
       </c>
       <c r="B53" s="68" t="inlineStr">
@@ -16622,24 +16672,24 @@
       <c r="C53" s="68" t="n"/>
       <c r="D53" s="69" t="inlineStr">
         <is>
-          <t>La gamificacion premia con reconocimiento y con un catalogo de premios canjeables por XP.</t>
+          <t>Cada modulo declara quien puede ver SUS archivos; no hay un switch central.</t>
         </is>
       </c>
       <c r="E53" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>Nada de dinero. Los premios --viajes, objetos-- viven en una tabla configurable desde el admin con su coste en XP y su disponibilidad, y el creador los canjea. El hito que consolida un referido es la primera campana completada (Q-25). Cierra Q-23, Q-24 y Q-26</t>
+          <t>La regla de cada archivo depende de la tabla que lo apunta --identidad de creators, captura de publication_evidence, comprobante de payouts-- y un decisor central que las consultara todas pondria a Shared o a Core a saber de payouts. deptrac no lo veria: son consultas a tablas y no clases importadas, o sea una frontera rota en silencio, que es la peor clase. Cada modulo registra su regla en su ServiceProvider, igual que registra sus escuchas. Y se niega por omision: un proposito sin regla no se abre ni para el administrador, asi que un archivo nuevo cuyo autor olvido declarar quien puede verlo se queda cerrado y no abierto a todos</t>
         </is>
       </c>
     </row>
     <row r="54" ht="45.75" customHeight="1" s="36">
       <c r="A54" s="67" t="inlineStr">
         <is>
-          <t>DEC-193</t>
+          <t>DEC-196</t>
         </is>
       </c>
       <c r="B54" s="68" t="inlineStr">
@@ -16650,24 +16700,24 @@
       <c r="C54" s="68" t="n"/>
       <c r="D54" s="69" t="inlineStr">
         <is>
-          <t>Publicar terminos nuevos no expulsa a nadie de golpe: hay plazo, aviso y aterrizaje suave.</t>
+          <t>La Academia del creador se construye, y cada modulo se configura desde el admin.</t>
         </is>
       </c>
       <c r="E54" s="69" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="F54" s="69" t="inlineStr">
         <is>
-          <t>Correo con enlace de aceptacion, 15 dias de plazo, aviso en la bandeja interna de la plataforma y recordatorio al entrar. Cumplido el plazo sin aceptar, la sesion cae en una pantalla que exige aceptar para continuar; si no acepta, solo lectura durante 30 dias. Los dos plazos son configurables (DEC-190). Es la respuesta a Q-46, y encaja con el «cambio menor» de 9.16: una errata no dispara nada de esto</t>
+          <t>Es G-08 del addendum de gamificacion y la de mas retorno de las once: modulos cortos --leer un brief sin gastar rondas, iluminacion y audio con un movil, como se rotula el contenido comercial, que derechos esta cediendo, como subir su evidencia-- con evaluacion al final e insignia de creador certificado. Ataca tres dolores ya medidos: cada ronda evitada es tiempo del equipo de revision, cada evidencia subida sola es el proceso mas manual que se deja de perseguir, y «creadores certificados» es un argumento de venta ante la marca. El software es la parte barata: modulos, orden, formato, evaluacion, intentos, XP e insignia salen del admin (DEC-190), y al completar uno se levanta TrainingModuleCompleted, previsto en el modelo desde la Fase 2. Lo caro es el CONTENIDO --guiones, video, mantenerlo cuando cambie una norma o una red-- y eso no lo hace el sistema. Se puede arrancar con modulos de solo texto, que cuestan casi nada y ya bajan rondas. Cierra Q-27</t>
         </is>
       </c>
     </row>
     <row r="55" ht="79.5" customHeight="1" s="36">
       <c r="A55" s="67" t="inlineStr">
         <is>
-          <t>DEC-192</t>
+          <t>DEC-195</t>
         </is>
       </c>
       <c r="B55" s="68" t="inlineStr">
@@ -16678,7 +16728,7 @@
       <c r="C55" s="68" t="n"/>
       <c r="D55" s="69" t="inlineStr">
         <is>
-          <t>Facturacion electronica DIRECTA con SUNAT, no por proveedor.</t>
+          <t>El lado del tipo de cambio se configura POR TIPO DE TRANSACCION.</t>
         </is>
       </c>
       <c r="E55" s="69" t="inlineStr">
@@ -16688,14 +16738,14 @@
       </c>
       <c r="F55" s="69" t="inlineStr">
         <is>
-          <t>Configurable entero desde el admin: URL, certificado, usuario y clave secundarios, y correlativos independientes de factura, boleta y notas de credito de cada una. Con monitor de documentos timbrados: estado de cada uno, reintento manual, reintento automatico por job con frecuencia y numero de reintentos configurables, descarga de CDR, XML y PDF --el PDF con plantilla configurable-- y envio al cliente por correo con cuerpo configurable y variables arrastrables. Cierra Q-03 y de paso Q-21, que preguntaba por el contrato con un proveedor que ya no hay</t>
+          <t>No se fija uno en el codigo: lo que se le paga a un creador, lo que se le cobra a un cliente y un gasto operativo no tienen por que convertirse con el mismo lado, y esa eleccion es contable. El admin declara, para cada tipo de transaccion, que lado se aplica (compra, venta o media) y con que fuente. Cierra Q-63, que era la que impedia dar un porcentaje de margen cuando hay dos monedas (DEC-185)</t>
         </is>
       </c>
     </row>
     <row r="56" ht="79.5" customHeight="1" s="36">
       <c r="A56" s="67" t="inlineStr">
         <is>
-          <t>DEC-191</t>
+          <t>DEC-194</t>
         </is>
       </c>
       <c r="B56" s="68" t="inlineStr">
@@ -16706,7 +16756,7 @@
       <c r="C56" s="68" t="n"/>
       <c r="D56" s="69" t="inlineStr">
         <is>
-          <t>La retencion se calcula HACIA ATRAS desde el neto pactado, y se compara con un umbral de rentabilidad.</t>
+          <t>La gamificacion premia con reconocimiento y con un catalogo de premios canjeables por XP.</t>
         </is>
       </c>
       <c r="E56" s="69" t="inlineStr">
@@ -16716,14 +16766,14 @@
       </c>
       <c r="F56" s="69" t="inlineStr">
         <is>
-          <t>Con el creador se pacta lo que VA A RECIBIR --«te pago 100»--; el sistema calcula el bruto que hay que provisionar con la tasa configurada (29,5% por defecto, Q-13/Q-40): bruto = neto / (1 - tasa), o sea 141,84 para 100 netos, de los que 41,84 son retencion. Tres campos y no uno: neto pactado, tasa aplicada (por defecto la del admin, editable en el trato) e importe bruto. Encima va un umbral de rentabilidad minima configurable: con el bruto como costo, la pantalla dice cual es el ingreso mas bajo que hace aceptable esa participacion, y avisa antes de cerrar el trato --no despues--. La tasa, el umbral y la base sobre la que se mide el umbral (sobre costo o sobre ingreso: no dan el mismo numero) salen del admin</t>
+          <t>Nada de dinero. Los premios --viajes, objetos-- viven en una tabla configurable desde el admin con su coste en XP y su disponibilidad, y el creador los canjea. El hito que consolida un referido es la primera campana completada (Q-25). Cierra Q-23, Q-24 y Q-26</t>
         </is>
       </c>
     </row>
     <row r="57" ht="68.25" customHeight="1" s="36">
       <c r="A57" s="67" t="inlineStr">
         <is>
-          <t>DEC-190</t>
+          <t>DEC-193</t>
         </is>
       </c>
       <c r="B57" s="68" t="inlineStr">
@@ -16731,14 +16781,10 @@
           <t>Decidida</t>
         </is>
       </c>
-      <c r="C57" s="68" t="inlineStr">
-        <is>
-          <t>Critica</t>
-        </is>
-      </c>
+      <c r="C57" s="68" t="n"/>
       <c r="D57" s="69" t="inlineStr">
         <is>
-          <t>PRINCIPIO RECTOR: la plataforma es WHITE LABEL y todo se configura desde el admin.</t>
+          <t>Publicar terminos nuevos no expulsa a nadie de golpe: hay plazo, aviso y aterrizaje suave.</t>
         </is>
       </c>
       <c r="E57" s="69" t="inlineStr">
@@ -16748,14 +16794,14 @@
       </c>
       <c r="F57" s="69" t="inlineStr">
         <is>
-          <t>Nada de reglas de negocio quemadas en el codigo: ni la razon social, ni el RUC, ni el representante legal, ni la direccion, ni el ubigeo, ni las tasas, ni los plazos, ni los correlativos, ni las credenciales de ninguna API. Lo que el codigo aporta es la REGLA; el VALOR sale de la configuracion. Y una configuracion sin valor no bloquea: se siembra con un valor de partida y se avisa con su prioridad --rojo si es delicado y sigue de fabrica, ambar si conviene revisarlo--. Esto corrige el criterio con el que se habian tomado varias decisiones anteriores --3.5 dejaba el sistema sin arrancar hasta que alguien corriera un comando, y varias preguntas de negocio se plantearon como «elige una y la quemo» cuando la respuesta correcta era «las dos, y que se elija en el admin»--. Toda decision anterior que fije un valor en el codigo queda sujeta a revision bajo este principio (T-69)</t>
+          <t>Correo con enlace de aceptacion, 15 dias de plazo, aviso en la bandeja interna de la plataforma y recordatorio al entrar. Cumplido el plazo sin aceptar, la sesion cae en una pantalla que exige aceptar para continuar; si no acepta, solo lectura durante 30 dias. Los dos plazos son configurables (DEC-190). Es la respuesta a Q-46, y encaja con el «cambio menor» de 9.16: una errata no dispara nada de esto</t>
         </is>
       </c>
     </row>
     <row r="58" ht="34.5" customHeight="1" s="36">
       <c r="A58" s="67" t="inlineStr">
         <is>
-          <t>DEC-189</t>
+          <t>DEC-192</t>
         </is>
       </c>
       <c r="B58" s="68" t="inlineStr">
@@ -16766,24 +16812,24 @@
       <c r="C58" s="68" t="n"/>
       <c r="D58" s="69" t="inlineStr">
         <is>
-          <t>Las 23 rutas sin permiso se escriben, con su motivo, en RUTAS-ABIERTAS.</t>
+          <t>Facturacion electronica DIRECTA con SUNAT, no por proveedor.</t>
         </is>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>9.14b</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F58" s="69" t="inlineStr">
         <is>
-          <t>Hasta hoy nada distinguia «es publica a proposito» --entrar, recuperar la contrasena, los enlaces firmados de 7.6 y 8.5-- de «se le olvido el middleware a alguien». verificar-muro.py comprueba que tres sitios digan lo mismo: la lista, routes/web.php y la constante de MuroTest; no se pueden fundir porque una la lee Python sin Laravel y otra PHPUnit, y tres copias es como se pierde una (SUITES, 3.12). Al CI: una ruta nueva sin permiso que no este escrita lo pone en rojo. De paso se cerraron dos puertas que no eran nuestras: storage.local y storage.local.upload, que registra el framework con serve =&gt; true sobre el disco privado. No eran una fuga --exigen URL firmada-- pero la aplicacion no genera ninguna, asi que no servian para nada; y ninguna lectura del codigo las habria encontrado, porque no estan en ningun archivo de rutas</t>
+          <t>Configurable entero desde el admin: URL, certificado, usuario y clave secundarios, y correlativos independientes de factura, boleta y notas de credito de cada una. Con monitor de documentos timbrados: estado de cada uno, reintento manual, reintento automatico por job con frecuencia y numero de reintentos configurables, descarga de CDR, XML y PDF --el PDF con plantilla configurable-- y envio al cliente por correo con cuerpo configurable y variables arrastrables. Cierra Q-03 y de paso Q-21, que preguntaba por el contrato con un proveedor que ya no hay</t>
         </is>
       </c>
     </row>
     <row r="59" ht="79.5" customHeight="1" s="36">
       <c r="A59" s="67" t="inlineStr">
         <is>
-          <t>DEC-188</t>
+          <t>DEC-191</t>
         </is>
       </c>
       <c r="B59" s="68" t="inlineStr">
@@ -16794,24 +16840,24 @@
       <c r="C59" s="68" t="n"/>
       <c r="D59" s="69" t="inlineStr">
         <is>
-          <t>El muro se prueba recorriendo TODAS las rutas, no las que uno recuerda.</t>
+          <t>La retencion se calcula HACIA ATRAS desde el neto pactado, y se compara con un umbral de rentabilidad.</t>
         </is>
       </c>
       <c r="E59" s="69" t="inlineStr">
         <is>
-          <t>9.14b</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F59" s="69" t="inlineStr">
         <is>
-          <t>MuroTest pide las 145 rutas con nombre como creador, como usuario de cliente y como autenticado sin rol, y exige que ninguna se abra --371 aserciones, y el muro aguanta--. Una pantalla nueva entra sola en la prueba. Las afirmaciones dirigidas que ya habia (DEC-172, DEC-179, DEC-181) comprueban lo que alguien se acordo de mirar; el fallo que de verdad paso --5.9, la portada enseñando los totales internos a cualquier autenticado-- no lo habria cazado ninguna. Lo permitido se escribe en positivo: una lista de lo permitido crece solo cuando alguien la toca a proposito. Se admite un 404 porque SubstituteBindings corre antes del middleware --con un id inventado la ruta contesta antes de llegar al permiso-- y para que no sea el escondite de la prueba se exige que mas de 80 rutas contesten 403 de verdad</t>
+          <t>Con el creador se pacta lo que VA A RECIBIR --«te pago 100»--; el sistema calcula el bruto que hay que provisionar con la tasa configurada (29,5% por defecto, Q-13/Q-40): bruto = neto / (1 - tasa), o sea 141,84 para 100 netos, de los que 41,84 son retencion. Tres campos y no uno: neto pactado, tasa aplicada (por defecto la del admin, editable en el trato) e importe bruto. Encima va un umbral de rentabilidad minima configurable: con el bruto como costo, la pantalla dice cual es el ingreso mas bajo que hace aceptable esa participacion, y avisa antes de cerrar el trato --no despues--. La tasa, el umbral y la base sobre la que se mide el umbral (sobre costo o sobre ingreso: no dan el mismo numero) salen del admin</t>
         </is>
       </c>
     </row>
     <row r="60" ht="102" customHeight="1" s="36">
       <c r="A60" s="67" t="inlineStr">
         <is>
-          <t>DEC-187</t>
+          <t>DEC-190</t>
         </is>
       </c>
       <c r="B60" s="68" t="inlineStr">
@@ -16819,27 +16865,31 @@
           <t>Decidida</t>
         </is>
       </c>
-      <c r="C60" s="68" t="n"/>
+      <c r="C60" s="68" t="inlineStr">
+        <is>
+          <t>Critica</t>
+        </is>
+      </c>
       <c r="D60" s="69" t="inlineStr">
         <is>
-          <t>Una suite de QA se construye SU caso y no reusa el de nadie.</t>
+          <t>PRINCIPIO RECTOR: la plataforma es WHITE LABEL y todo se configura desde el admin.</t>
         </is>
       </c>
       <c r="E60" s="69" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="F60" s="69" t="inlineStr">
         <is>
-          <t>La primera version de 9.14 reusaba lo que dejaban las suites anteriores, como hace 9.6, y se puso amarilla dos veces por motivos opuestos: corriendo sola porque no habia asientos, y corriendo la bateria entera porque para cuando llega el unico devengo pagable ya esta liquidado por 9.6 y las dos participaciones de la semilla estan ocupadas. Ahora crea su campana, su participacion y su devengo. Una suite de QA que depende del orden mide el orden, no la regla</t>
+          <t>Nada de reglas de negocio quemadas en el codigo: ni la razon social, ni el RUC, ni el representante legal, ni la direccion, ni el ubigeo, ni las tasas, ni los plazos, ni los correlativos, ni las credenciales de ninguna API. Lo que el codigo aporta es la REGLA; el VALOR sale de la configuracion. Y una configuracion sin valor no bloquea: se siembra con un valor de partida y se avisa con su prioridad --rojo si es delicado y sigue de fabrica, ambar si conviene revisarlo--. Esto corrige el criterio con el que se habian tomado varias decisiones anteriores --3.5 dejaba el sistema sin arrancar hasta que alguien corriera un comando, y varias preguntas de negocio se plantearon como «elige una y la quemo» cuando la respuesta correcta era «las dos, y que se elija en el admin»--. Toda decision anterior que fije un valor en el codigo queda sujeta a revision bajo este principio (T-69)</t>
         </is>
       </c>
     </row>
     <row r="61" ht="90.75" customHeight="1" s="36">
       <c r="A61" s="67" t="inlineStr">
         <is>
-          <t>DEC-186</t>
+          <t>DEC-189</t>
         </is>
       </c>
       <c r="B61" s="68" t="inlineStr">
@@ -16850,24 +16900,24 @@
       <c r="C61" s="68" t="n"/>
       <c r="D61" s="69" t="inlineStr">
         <is>
-          <t>Nace verificar-cobertura-sql.py: que regla de la base no ha contestado NUNCA a nadie.</t>
+          <t>Las 23 rutas sin permiso se escriben, con su motivo, en RUTAS-ABIERTAS.</t>
         </is>
       </c>
       <c r="E61" s="69" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.14b</t>
         </is>
       </c>
       <c r="F61" s="69" t="inlineStr">
         <is>
-          <t>Los verificadores que ya habia comprueban que la regla EXISTA y que sea la misma en los dos motores; ninguno comprobaba lo unico que importa el dia que falle: que alguien se lo haya preguntado. Medido: de las 317 reglas del esquema, 167 no aparecian en ninguna suite ni en ninguna prueba --el 53%--. No significa que esten mal: significa que nadie lo sabe. Una regla que nunca se ha probado no es una regla, es una intencion escrita en DDL. Va a correr-todo.sh y al CI con trinquete (MUDAS-BASE), asi que una regla nueva sin asercion pone el CI en rojo. La pregunta salio de 9.10a, donde campaign_costs llevaba dos semanas con cinco restricciones verdes en todos los verificadores y CERO filas</t>
+          <t>Hasta hoy nada distinguia «es publica a proposito» --entrar, recuperar la contrasena, los enlaces firmados de 7.6 y 8.5-- de «se le olvido el middleware a alguien». verificar-muro.py comprueba que tres sitios digan lo mismo: la lista, routes/web.php y la constante de MuroTest; no se pueden fundir porque una la lee Python sin Laravel y otra PHPUnit, y tres copias es como se pierde una (SUITES, 3.12). Al CI: una ruta nueva sin permiso que no este escrita lo pone en rojo. De paso se cerraron dos puertas que no eran nuestras: storage.local y storage.local.upload, que registra el framework con serve =&gt; true sobre el disco privado. No eran una fuga --exigen URL firmada-- pero la aplicacion no genera ninguna, asi que no servian para nada; y ninguna lectura del codigo las habria encontrado, porque no estan en ningun archivo de rutas</t>
         </is>
       </c>
     </row>
     <row r="62" ht="57" customHeight="1" s="36">
       <c r="A62" s="67" t="inlineStr">
         <is>
-          <t>DEC-185</t>
+          <t>DEC-188</t>
         </is>
       </c>
       <c r="B62" s="68" t="inlineStr">
@@ -16878,24 +16928,24 @@
       <c r="C62" s="68" t="n"/>
       <c r="D62" s="69" t="inlineStr">
         <is>
-          <t>El porcentaje de margen solo se da cuando todo esta en una moneda, y si no, se dice por que.</t>
+          <t>El muro se prueba recorriendo TODAS las rutas, no las que uno recuerda.</t>
         </is>
       </c>
       <c r="E62" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14b</t>
         </is>
       </c>
       <c r="F62" s="69" t="inlineStr">
         <is>
-          <t>Convertir exige elegir compra, venta o media (Q-63) y cada eleccion da un margen distinto para los mismos hechos; el dia que se elija cambian ademas todos los margenes historicos a la vez. Cuando falta, la pantalla escribe el motivo con palabras --«esta campana tiene importes en PEN y USD…»-- y no deja un hueco: quien mira una pantalla donde falta un numero necesita saber si falta porque no lo hay o porque no se puede calcular, y son dos conversaciones distintas. Tampoco hay total por sociedad: el ingreso de hoy es el DECLARADO y no el facturado (9.9), y sumar precios declarados por sociedad se parece a un estado de resultados sin serlo</t>
+          <t>MuroTest pide las 145 rutas con nombre como creador, como usuario de cliente y como autenticado sin rol, y exige que ninguna se abra --371 aserciones, y el muro aguanta--. Una pantalla nueva entra sola en la prueba. Las afirmaciones dirigidas que ya habia (DEC-172, DEC-179, DEC-181) comprueban lo que alguien se acordo de mirar; el fallo que de verdad paso --5.9, la portada enseñando los totales internos a cualquier autenticado-- no lo habria cazado ninguna. Lo permitido se escribe en positivo: una lista de lo permitido crece solo cuando alguien la toca a proposito. Se admite un 404 porque SubstituteBindings corre antes del middleware --con un id inventado la ruta contesta antes de llegar al permiso-- y para que no sea el escondite de la prueba se exige que mas de 80 rutas contesten 403 de verdad</t>
         </is>
       </c>
     </row>
     <row r="63" ht="90.75" customHeight="1" s="36">
       <c r="A63" s="67" t="inlineStr">
         <is>
-          <t>DEC-184</t>
+          <t>DEC-187</t>
         </is>
       </c>
       <c r="B63" s="68" t="inlineStr">
@@ -16906,24 +16956,24 @@
       <c r="C63" s="68" t="n"/>
       <c r="D63" s="69" t="inlineStr">
         <is>
-          <t>Los canjes salen en la lista, marcados, y fuera de todo total.</t>
+          <t>Una suite de QA se construye SU caso y no reusa el de nadie.</t>
         </is>
       </c>
       <c r="E63" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="F63" s="69" t="inlineStr">
         <is>
-          <t>Su ingreso es cero POR DECISION (7.2), asi que su margen es siempre negativo: el producto y el envio se gastaron igual. Promediarlos hace que la cartera entera parezca peor por un motivo que fue deliberado. Pero se enseñan con su costo, porque un canje tambien cuesta dinero y ese era justo el numero que nadie tenia. Queda fuera del total una segunda clase de campana: la que tiene gastos en OTRA moneda, cuyo margen en la moneda del grupo esta incompleto --y sumar un numero incompleto lo vuelve invisible--. Y la cabecera dice cuantas quedaron fuera y por que: un total que excluye filas sin contarlas engaña por omision</t>
+          <t>La primera version de 9.14 reusaba lo que dejaban las suites anteriores, como hace 9.6, y se puso amarilla dos veces por motivos opuestos: corriendo sola porque no habia asientos, y corriendo la bateria entera porque para cuando llega el unico devengo pagable ya esta liquidado por 9.6 y las dos participaciones de la semilla estan ocupadas. Ahora crea su campana, su participacion y su devengo. Una suite de QA que depende del orden mide el orden, no la regla</t>
         </is>
       </c>
     </row>
     <row r="64" ht="102" customHeight="1" s="36">
       <c r="A64" s="67" t="inlineStr">
         <is>
-          <t>DEC-183</t>
+          <t>DEC-186</t>
         </is>
       </c>
       <c r="B64" s="68" t="inlineStr">
@@ -16934,24 +16984,24 @@
       <c r="C64" s="68" t="n"/>
       <c r="D64" s="69" t="inlineStr">
         <is>
-          <t>Compromiso::margen() se BORRA, no se arregla.</t>
+          <t>Nace verificar-cobertura-sql.py: que regla de la base no ha contestado NUNCA a nadie.</t>
         </is>
       </c>
       <c r="E64" s="69" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="F64" s="69" t="inlineStr">
         <is>
-          <t>Vivia en Campaign desde 7.7 y devolvia revenue_amount menos lo comprometido con creadores: no restaba producto, envios ni produccion, y desde 9.10a esos gastos ya se anotan, asi que el numero habria ido empeorando con cada gasto cargado sin que la pantalla se enterara. No se arregla donde estaba porque campaign_costs es de Finance y deptrac no deja que Campaign la conozca --misma frontera que el devengo de 9.4--. Y se borra en vez de dejarse por si acaso: un metodo que calcula un numero incompleto y se llama margen() es una trampa para quien lo encuentre dentro de seis meses. De paso, SeguimientoController deja de pasar un importe y pasa un booleano mas un enlace: ningun numero interno cruza ya hasta la plantilla, que es BR-SEC-001 un paso mas alla</t>
+          <t>Los verificadores que ya habia comprueban que la regla EXISTA y que sea la misma en los dos motores; ninguno comprobaba lo unico que importa el dia que falle: que alguien se lo haya preguntado. Medido: de las 317 reglas del esquema, 167 no aparecian en ninguna suite ni en ninguna prueba --el 53%--. No significa que esten mal: significa que nadie lo sabe. Una regla que nunca se ha probado no es una regla, es una intencion escrita en DDL. Va a correr-todo.sh y al CI con trinquete (MUDAS-BASE), asi que una regla nueva sin asercion pone el CI en rojo. La pregunta salio de 9.10a, donde campaign_costs llevaba dos semanas con cinco restricciones verdes en todos los verificadores y CERO filas</t>
         </is>
       </c>
     </row>
     <row r="65" ht="90.75" customHeight="1" s="36">
       <c r="A65" s="67" t="inlineStr">
         <is>
-          <t>DEC-182</t>
+          <t>DEC-185</t>
         </is>
       </c>
       <c r="B65" s="68" t="inlineStr">
@@ -16962,24 +17012,24 @@
       <c r="C65" s="68" t="n"/>
       <c r="D65" s="69" t="inlineStr">
         <is>
-          <t>El costo del creador entra al DEVENGARSE, no al pagarse.</t>
+          <t>El porcentaje de margen solo se da cuando todo esta en una moneda, y si no, se dice por que.</t>
         </is>
       </c>
       <c r="E65" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F65" s="69" t="inlineStr">
         <is>
-          <t>La deuda existe desde que acepta (9.4) y su importe esta congelado desde 7.5; esperar al pago haria que una campana terminada en marzo pareciera rentabilisima hasta el lote de abril. Sale del libro mayor y no de campaign_creators, porque el libro es quien sabe que devengos siguen vivos: uno anulado ya no se debe. Y no es Compromiso::comprometido(), que cuenta tambien a los shortlisted: alli es correcto --su trabajo es proteger el presupuesto ANTES de invitar-- y aqui contaria dinero de gente que todavia puede decir que no</t>
+          <t>Convertir exige elegir compra, venta o media (Q-63) y cada eleccion da un margen distinto para los mismos hechos; el dia que se elija cambian ademas todos los margenes historicos a la vez. Cuando falta, la pantalla escribe el motivo con palabras --«esta campana tiene importes en PEN y USD…»-- y no deja un hueco: quien mira una pantalla donde falta un numero necesita saber si falta porque no lo hay o porque no se puede calcular, y son dos conversaciones distintas. Tampoco hay total por sociedad: el ingreso de hoy es el DECLARADO y no el facturado (9.9), y sumar precios declarados por sociedad se parece a un estado de resultados sin serlo</t>
         </is>
       </c>
     </row>
     <row r="66" ht="68.25" customHeight="1" s="36">
       <c r="A66" s="67" t="inlineStr">
         <is>
-          <t>DEC-181</t>
+          <t>DEC-184</t>
         </is>
       </c>
       <c r="B66" s="68" t="inlineStr">
@@ -16990,24 +17040,24 @@
       <c r="C66" s="68" t="n"/>
       <c r="D66" s="69" t="inlineStr">
         <is>
-          <t>Cargar gastos no es ver el margen: campaign_manager pierde campaign.view_margin.</t>
+          <t>Los canjes salen en la lista, marcados, y fuera de todo total.</t>
         </is>
       </c>
       <c r="E66" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F66" s="69" t="inlineStr">
         <is>
-          <t>Quien lleva una campana anota lo que se gasta y ve cuanto lleva gastado; el margen --lo que se gana-- es una cifra de direccion, y el camino por el que un numero interno acaba en un correo a un cliente empieza siempre por alguien que podia verlo sin necesitarlo (BR-SEC-001, 🔴). No nace un permiso nuevo para el margen: campaign.view_margin ya existe y hace eso, y un segundo permiso para el mismo secreto es la forma clasica de que un dia se conceda el que nadie mira. Lo que nace es finance.cost.manage, que es la capacidad que de verdad no existia. Y la revocacion va en la MIGRACION y no en el seeder (T-64)</t>
+          <t>Su ingreso es cero POR DECISION (7.2), asi que su margen es siempre negativo: el producto y el envio se gastaron igual. Promediarlos hace que la cartera entera parezca peor por un motivo que fue deliberado. Pero se enseñan con su costo, porque un canje tambien cuesta dinero y ese era justo el numero que nadie tenia. Queda fuera del total una segunda clase de campana: la que tiene gastos en OTRA moneda, cuyo margen en la moneda del grupo esta incompleto --y sumar un numero incompleto lo vuelve invisible--. Y la cabecera dice cuantas quedaron fuera y por que: un total que excluye filas sin contarlas engaña por omision</t>
         </is>
       </c>
     </row>
     <row r="67" ht="68.25" customHeight="1" s="36">
       <c r="A67" s="67" t="inlineStr">
         <is>
-          <t>DEC-180</t>
+          <t>DEC-183</t>
         </is>
       </c>
       <c r="B67" s="68" t="inlineStr">
@@ -17018,24 +17068,24 @@
       <c r="C67" s="68" t="n"/>
       <c r="D67" s="69" t="inlineStr">
         <is>
-          <t>El gasto de una campana se agrupa por moneda: no se suma.</t>
+          <t>Compromiso::margen() se BORRA, no se arregla.</t>
         </is>
       </c>
       <c r="E67" s="69" t="inlineStr">
         <is>
-          <t>9.10a</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="F67" s="69" t="inlineStr">
         <is>
-          <t>Un envio se paga en dolares y la campana se cobra en soles; sumarlos exige un tipo de cambio, y cual --compra, venta o media-- es una decision contable que sigue abierta (Q-63) y que da tres margenes distintos para los mismos hechos. Es la misma decision que el saldo del creador en 9.8, por el mismo motivo. Un numero que parece exacto y depende de una eleccion que nadie ha hecho es peor que dos numeros separados</t>
+          <t>Vivia en Campaign desde 7.7 y devolvia revenue_amount menos lo comprometido con creadores: no restaba producto, envios ni produccion, y desde 9.10a esos gastos ya se anotan, asi que el numero habria ido empeorando con cada gasto cargado sin que la pantalla se enterara. No se arregla donde estaba porque campaign_costs es de Finance y deptrac no deja que Campaign la conozca --misma frontera que el devengo de 9.4--. Y se borra en vez de dejarse por si acaso: un metodo que calcula un numero incompleto y se llama margen() es una trampa para quien lo encuentre dentro de seis meses. De paso, SeguimientoController deja de pasar un importe y pasa un booleano mas un enlace: ningun numero interno cruza ya hasta la plantilla, que es BR-SEC-001 un paso mas alla</t>
         </is>
       </c>
     </row>
     <row r="68" ht="79.5" customHeight="1" s="36">
       <c r="A68" s="67" t="inlineStr">
         <is>
-          <t>DEC-179</t>
+          <t>DEC-182</t>
         </is>
       </c>
       <c r="B68" s="68" t="inlineStr">
@@ -17046,24 +17096,24 @@
       <c r="C68" s="68" t="n"/>
       <c r="D68" s="69" t="inlineStr">
         <is>
-          <t>Al creador se le avisa al CONFIRMAR y al DEVOLVER, no al enviar.</t>
+          <t>El costo del creador entra al DEVENGARSE, no al pagarse.</t>
         </is>
       </c>
       <c r="E68" s="69" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F68" s="69" t="inlineStr">
         <is>
-          <t>Avisar al enviar es avisar de una intencion: si el banco lo rechaza, el creador ya cree que cobro, y el segundo correo desmiente al primero --dos correos que se contradicen cuestan mas confianza que un correo que llega un dia mas tarde--. Ninguno de los dos lleva numero de cuenta ni referencia bancaria: un correo se lee en pantallas ajenas y se reenvia, y para saber que le pagaron no hace falta ver su cuenta; es la misma decision que los avisos de 4.13. Y lo que faltaba en payouts no eran los estados --estan desde la Fase 2-- sino el GRAFO: sin tg_payout_estado, un pago saltaba de pending a confirmed sin haber salido nunca, y uno devuelto volvia a sent con un UPDATE, borrando que el banco lo habia rechazado. Mismo agujero que ledger_entries tenia antes de 9.3</t>
+          <t>La deuda existe desde que acepta (9.4) y su importe esta congelado desde 7.5; esperar al pago haria que una campana terminada en marzo pareciera rentabilisima hasta el lote de abril. Sale del libro mayor y no de campaign_creators, porque el libro es quien sabe que devengos siguen vivos: uno anulado ya no se debe. Y no es Compromiso::comprometido(), que cuenta tambien a los shortlisted: alli es correcto --su trabajo es proteger el presupuesto ANTES de invitar-- y aqui contaria dinero de gente que todavia puede decir que no</t>
         </is>
       </c>
     </row>
     <row r="69" ht="57" customHeight="1" s="36">
       <c r="A69" s="67" t="inlineStr">
         <is>
-          <t>DEC-178</t>
+          <t>DEC-181</t>
         </is>
       </c>
       <c r="B69" s="68" t="inlineStr">
@@ -17074,24 +17124,24 @@
       <c r="C69" s="68" t="n"/>
       <c r="D69" s="69" t="inlineStr">
         <is>
-          <t>Un pago devuelto por el banco NO deshace el devengo.</t>
+          <t>Cargar gastos no es ver el margen: campaign_manager pierde campaign.view_margin.</t>
         </is>
       </c>
       <c r="E69" s="69" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F69" s="69" t="inlineStr">
         <is>
-          <t>El devengo se queda en paid porque se pago: lo que fallo fue la transferencia, no el trabajo --y paid es terminal desde DEC-169--. La correccion es un asiento de payment_reversal que apunta al asiento de pago original (BR-FIN-002), positivo, asi que devuelve el saldo; los dos hechos quedan escritos --se pago, y volvio-- en vez de que el segundo borre al primero. Nace accrued porque ck_ledger_estado_inicial no admite nacer pagable --a pagable se LLEGA-- y se mueve a payable en la misma operacion: el creador ya cumplio, y su dinero no tiene que esperar a que alguien se acuerde de revisarlo. Si el pago no tuviera asiento en el libro mayor, devolver() falla en voz alta en vez de dejar el saldo diciendo que cobro algo que no tiene</t>
+          <t>Quien lleva una campana anota lo que se gasta y ve cuanto lleva gastado; el margen --lo que se gana-- es una cifra de direccion, y el camino por el que un numero interno acaba en un correo a un cliente empieza siempre por alguien que podia verlo sin necesitarlo (BR-SEC-001, 🔴). No nace un permiso nuevo para el margen: campaign.view_margin ya existe y hace eso, y un segundo permiso para el mismo secreto es la forma clasica de que un dia se conceda el que nadie mira. Lo que nace es finance.cost.manage, que es la capacidad que de verdad no existia. Y la revocacion va en la MIGRACION y no en el seeder (T-64)</t>
         </is>
       </c>
     </row>
     <row r="70" ht="57" customHeight="1" s="36">
       <c r="A70" s="67" t="inlineStr">
         <is>
-          <t>DEC-177</t>
+          <t>DEC-180</t>
         </is>
       </c>
       <c r="B70" s="68" t="inlineStr">
@@ -17102,24 +17152,24 @@
       <c r="C70" s="68" t="n"/>
       <c r="D70" s="69" t="inlineStr">
         <is>
-          <t>El CSV del lote NO es el archivo del banco.</t>
+          <t>El gasto de una campana se agrupa por moneda: no se suma.</t>
         </is>
       </c>
       <c r="E70" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.10a</t>
         </is>
       </c>
       <c r="F70" s="69" t="inlineStr">
         <is>
-          <t>El formato de una transferencia masiva es especifico de cada entidad y sale de su manual; inventarselo produce un archivo que el banco rechaza sin decir por que, y el sintoma aparece el dia del pago. Lo que hay es un CSV legible por una persona, para teclear o comprobar, y la pantalla lo dice con esas palabras para que nadie lo suba creyendo que es lo otro. El archivo real se construye cuando haya banco y especificacion</t>
+          <t>Un envio se paga en dolares y la campana se cobra en soles; sumarlos exige un tipo de cambio, y cual --compra, venta o media-- es una decision contable que sigue abierta (Q-63) y que da tres margenes distintos para los mismos hechos. Es la misma decision que el saldo del creador en 9.8, por el mismo motivo. Un numero que parece exacto y depende de una eleccion que nadie ha hecho es peor que dos numeros separados</t>
         </is>
       </c>
     </row>
     <row r="71" ht="45.75" customHeight="1" s="36">
       <c r="A71" s="67" t="inlineStr">
         <is>
-          <t>DEC-176</t>
+          <t>DEC-179</t>
         </is>
       </c>
       <c r="B71" s="68" t="inlineStr">
@@ -17130,24 +17180,24 @@
       <c r="C71" s="68" t="n"/>
       <c r="D71" s="69" t="inlineStr">
         <is>
-          <t>Sacar un pago de un lote firmado NO obliga a firmarlo otra vez.</t>
+          <t>Al creador se le avisa al CONFIRMAR y al DEVOLVER, no al enviar.</t>
         </is>
       </c>
       <c r="E71" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="F71" s="69" t="inlineStr">
         <is>
-          <t>Cuando un devengo se retiene entre la firma y la ejecucion --un post que se cae-- ese pago sale y el resto se paga igual. El importe total baja, nunca sube, y eso no puede sorprender a quien ya firmo; devolver el lote entero a borrador castigaria a diez creadores por el problema de uno. La liquidacion se anula, no se borra: es evidencia de que estuvo dentro y de que alguien lo saco, y anularla exige quien y por que (tg_pe_inmutable). Al anularse, el devengo vuelve a la cola. Un lote ya ejecutado no se toca: el dinero salio, y eso se corrige con una devolucion</t>
+          <t>Avisar al enviar es avisar de una intencion: si el banco lo rechaza, el creador ya cree que cobro, y el segundo correo desmiente al primero --dos correos que se contradicen cuestan mas confianza que un correo que llega un dia mas tarde--. Ninguno de los dos lleva numero de cuenta ni referencia bancaria: un correo se lee en pantallas ajenas y se reenvia, y para saber que le pagaron no hace falta ver su cuenta; es la misma decision que los avisos de 4.13. Y lo que faltaba en payouts no eran los estados --estan desde la Fase 2-- sino el GRAFO: sin tg_payout_estado, un pago saltaba de pending a confirmed sin haber salido nunca, y uno devuelto volvia a sent con un UPDATE, borrando que el banco lo habia rechazado. Mismo agujero que ledger_entries tenia antes de 9.3</t>
         </is>
       </c>
     </row>
     <row r="72" ht="79.5" customHeight="1" s="36">
       <c r="A72" s="67" t="inlineStr">
         <is>
-          <t>DEC-175</t>
+          <t>DEC-178</t>
         </is>
       </c>
       <c r="B72" s="68" t="inlineStr">
@@ -17158,24 +17208,24 @@
       <c r="C72" s="68" t="n"/>
       <c r="D72" s="69" t="inlineStr">
         <is>
-          <t>Dos firmas SIEMPRE, sin umbral.</t>
+          <t>Un pago devuelto por el banco NO deshace el devengo.</t>
         </is>
       </c>
       <c r="E72" s="69" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="F72" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-005 habla de un umbral configurable y se decide no tenerlo: el equipo es pequeno y los lotes son pocos y agrupados, asi que la segunda firma cuesta un clic al mes. Un umbral hay que elegirlo, mantenerlo y explicarlo --y el dia que alguien quiera saltarse la firma, parte el lote en dos--. Que el aprobador sea otro no lo comprueba la pantalla: lo impide ck_pbatch_segregation en la base desde la Fase 2; la pantalla solo lo dice ANTES de que nadie pulse. Y el importe del pago no se teclea: sale de sumar lo que liquida, asi que no puede discrepar de lo que el lote dice que paga --Lotes::descuadre() lo comprueba antes de firmar, porque una SUMA sobre otra tabla no cabe en un CHECK--</t>
+          <t>El devengo se queda en paid porque se pago: lo que fallo fue la transferencia, no el trabajo --y paid es terminal desde DEC-169--. La correccion es un asiento de payment_reversal que apunta al asiento de pago original (BR-FIN-002), positivo, asi que devuelve el saldo; los dos hechos quedan escritos --se pago, y volvio-- en vez de que el segundo borre al primero. Nace accrued porque ck_ledger_estado_inicial no admite nacer pagable --a pagable se LLEGA-- y se mueve a payable en la misma operacion: el creador ya cumplio, y su dinero no tiene que esperar a que alguien se acuerde de revisarlo. Si el pago no tuviera asiento en el libro mayor, devolver() falla en voz alta en vez de dejar el saldo diciendo que cobro algo que no tiene</t>
         </is>
       </c>
     </row>
     <row r="73" ht="68.25" customHeight="1" s="36">
       <c r="A73" s="67" t="inlineStr">
         <is>
-          <t>DEC-174</t>
+          <t>DEC-177</t>
         </is>
       </c>
       <c r="B73" s="68" t="inlineStr">
@@ -17186,7 +17236,7 @@
       <c r="C73" s="68" t="n"/>
       <c r="D73" s="69" t="inlineStr">
         <is>
-          <t>Nace payout_earnings: que devengos paga cada pago.</t>
+          <t>El CSV del lote NO es el archivo del banco.</t>
         </is>
       </c>
       <c r="E73" s="69" t="inlineStr">
@@ -17196,14 +17246,14 @@
       </c>
       <c r="F73" s="69" t="inlineStr">
         <is>
-          <t>ledger_entries.payout_id ataba UN asiento de pago a su payout (BR-FIN-013), pero el detalle --que devengos liquida-- no existia. Sin el, «.de que campanas es este dinero?» no tiene respuesta, y sin respuesta no hay nada que comparar con la sociedad del lote, que es lo que DEC-157 mando cerrar aqui. Con el detalle, BR-LE-009 se vuelve una consulta de tres saltos que cabe en tg_pe_sociedad. Se comprueba al enganchar el devengo al pago y no al aprobar el lote: aprobar es una firma sobre algo que ya tiene que estar bien, y una regla que solo mira al final deja existir el estado malo mientras tanto --que es como alguien lo ve, lo exporta, o lo cree--. Vigesimoseptima columna puerta: uq_pe_viva, un devengo en una sola liquidacion VIVA</t>
+          <t>El formato de una transferencia masiva es especifico de cada entidad y sale de su manual; inventarselo produce un archivo que el banco rechaza sin decir por que, y el sintoma aparece el dia del pago. Lo que hay es un CSV legible por una persona, para teclear o comprobar, y la pantalla lo dice con esas palabras para que nadie lo suba creyendo que es lo otro. El archivo real se construye cuando haya banco y especificacion</t>
         </is>
       </c>
     </row>
     <row r="74" ht="68.25" customHeight="1" s="36">
       <c r="A74" s="67" t="inlineStr">
         <is>
-          <t>DEC-173</t>
+          <t>DEC-176</t>
         </is>
       </c>
       <c r="B74" s="68" t="inlineStr">
@@ -17214,24 +17264,24 @@
       <c r="C74" s="68" t="n"/>
       <c r="D74" s="69" t="inlineStr">
         <is>
-          <t>La fecha de cobro se ensena SOLO cuando el asiento ya es pagable.</t>
+          <t>Sacar un pago de un lote firmado NO obliga a firmarlo otra vez.</t>
         </is>
       </c>
       <c r="E74" s="69" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F74" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-012 dice que el plazo son 30 dias desde la verificacion y que es visible desde que acepta: lo visible desde que acepta es el plazo, y una FECHA es otra cosa que se lee muy distinto. Mientras el asiento esta devengado se ensena que falta --las cinco condiciones de BR-FIN-003, con sus palabras--, que es accionable: un creador puede hacer algo con «no tienes ningun medio de pago verificado» y no puede hacer nada con una fecha que depende de trabajo que aun no ha hecho. Y si esa fecha se corriera, la culpa pareceria nuestra. La cuenta arranca en la ultima verificacion de sus publicaciones, y si no hay ninguna --un formato que no exige post-- en la fecha en que se completo la participacion</t>
+          <t>Cuando un devengo se retiene entre la firma y la ejecucion --un post que se cae-- ese pago sale y el resto se paga igual. El importe total baja, nunca sube, y eso no puede sorprender a quien ya firmo; devolver el lote entero a borrador castigaria a diez creadores por el problema de uno. La liquidacion se anula, no se borra: es evidencia de que estuvo dentro y de que alguien lo saco, y anularla exige quien y por que (tg_pe_inmutable). Al anularse, el devengo vuelve a la cola. Un lote ya ejecutado no se toca: el dinero salio, y eso se corrige con una devolucion</t>
         </is>
       </c>
     </row>
     <row r="75" ht="57" customHeight="1" s="36">
       <c r="A75" s="67" t="inlineStr">
         <is>
-          <t>DEC-172</t>
+          <t>DEC-175</t>
         </is>
       </c>
       <c r="B75" s="68" t="inlineStr">
@@ -17242,24 +17292,24 @@
       <c r="C75" s="68" t="n"/>
       <c r="D75" s="69" t="inlineStr">
         <is>
-          <t>El motivo interno de una retencion NO se le ensena al creador.</t>
+          <t>Dos firmas SIEMPRE, sin umbral.</t>
         </is>
       </c>
       <c r="E75" s="69" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F75" s="69" t="inlineStr">
         <is>
-          <t>Lo escribe el equipo para el expediente y puede nombrar personas o sospechas todavia sin confirmar; un texto redactado deprisa --«parece que lo borro a proposito»-- leido sin contexto es una acusacion de la que no se vuelve. El creador ve «En revision -- te escribimos» y, desde 8.8, recibe un correo donde se le explica de verdad. Las palabras del portal tampoco son las del back-office: on_hold es «en revision» y no «retenido», porque la palabra interna describe lo que hace el sistema y la del portal tiene que describir lo que le pasa a el. La frontera vive en Ledger::misIngresos(), que enumera columnas --el mismo sitio que Aprobaciones::pieza() en 8.5--: devolver la fila entera y confiar en que la plantilla no imprima de mas es confiar en la plantilla de manana. Tampoco cruzan los asientos anulados: no le afectan y no sabe leerlos</t>
+          <t>BR-FIN-005 habla de un umbral configurable y se decide no tenerlo: el equipo es pequeno y los lotes son pocos y agrupados, asi que la segunda firma cuesta un clic al mes. Un umbral hay que elegirlo, mantenerlo y explicarlo --y el dia que alguien quiera saltarse la firma, parte el lote en dos--. Que el aprobador sea otro no lo comprueba la pantalla: lo impide ck_pbatch_segregation en la base desde la Fase 2; la pantalla solo lo dice ANTES de que nadie pulse. Y el importe del pago no se teclea: sale de sumar lo que liquida, asi que no puede discrepar de lo que el lote dice que paga --Lotes::descuadre() lo comprueba antes de firmar, porque una SUMA sobre otra tabla no cabe en un CHECK--</t>
         </is>
       </c>
     </row>
     <row r="76" ht="45.75" customHeight="1" s="36">
       <c r="A76" s="67" t="inlineStr">
         <is>
-          <t>DEC-171</t>
+          <t>DEC-174</t>
         </is>
       </c>
       <c r="B76" s="68" t="inlineStr">
@@ -17270,24 +17320,24 @@
       <c r="C76" s="68" t="n"/>
       <c r="D76" s="69" t="inlineStr">
         <is>
-          <t>El barrido rescata las aceptaciones sin devengo, y avisa de que hubo que rescatarlas.</t>
+          <t>Nace payout_earnings: que devengos paga cada pago.</t>
         </is>
       </c>
       <c r="E76" s="69" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="F76" s="69" t="inlineStr">
         <is>
-          <t>Un listener puede fallar, y si falla el creador queda aceptado y su dinero invisible; ademas las participaciones aceptadas antes de 9.4 nunca pasaron por el. ledger:revisar las anota antes de revisar --para que un devengo recuperado hoy pueda pasar a pagable hoy y no manana-- y lo dice en amarillo: que la lista no salga en cero es la noticia, no el arreglo. Es la misma red que 8.1 dejo para los entregables. Las gratuitas quedan fuera de esa lista a proposito: si no, el barrido intentaria lo imposible todos los dias y avisaria todos los dias de algo que esta bien</t>
+          <t>ledger_entries.payout_id ataba UN asiento de pago a su payout (BR-FIN-013), pero el detalle --que devengos liquida-- no existia. Sin el, «.de que campanas es este dinero?» no tiene respuesta, y sin respuesta no hay nada que comparar con la sociedad del lote, que es lo que DEC-157 mando cerrar aqui. Con el detalle, BR-LE-009 se vuelve una consulta de tres saltos que cabe en tg_pe_sociedad. Se comprueba al enganchar el devengo al pago y no al aprobar el lote: aprobar es una firma sobre algo que ya tiene que estar bien, y una regla que solo mira al final deja existir el estado malo mientras tanto --que es como alguien lo ve, lo exporta, o lo cree--. Vigesimoseptima columna puerta: uq_pe_viva, un devengo en una sola liquidacion VIVA</t>
         </is>
       </c>
     </row>
     <row r="77" ht="68.25" customHeight="1" s="36">
       <c r="A77" s="67" t="inlineStr">
         <is>
-          <t>DEC-170</t>
+          <t>DEC-173</t>
         </is>
       </c>
       <c r="B77" s="68" t="inlineStr">
@@ -17298,24 +17348,24 @@
       <c r="C77" s="68" t="n"/>
       <c r="D77" s="69" t="inlineStr">
         <is>
-          <t>Se devenga al ACEPTAR, no al terminar, y por evento.</t>
+          <t>La fecha de cobro se ensena SOLO cuando el asiento ya es pagable.</t>
         </is>
       </c>
       <c r="E77" s="69" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="F77" s="69" t="inlineStr">
         <is>
-          <t>Al aceptar es cuando existe la deuda: 7.5 congela el agreed_amount en ese instante y BR-CREATOR-008 impide cambiarlo despues sin una enmienda firmada por las dos partes. Que todavia no se le pueda pagar es otra cosa y vive en el estado --accrued significa exactamente «se le debe y aun no se le puede pagar»--. Devengar al terminar habria dejado el trabajo hecho y el compromiso invisible hasta el final, que es como una campana se cierra sin que nadie sepa cuanto costo mientras corria. Va por evento y no por llamada directa por lo mismo que 8.1: deptrac no deja que Campaign conozca a Finance, y esta bien que no lo haga --si anotar el asiento falla, la aceptacion sigue siendo cierta, y el creador ya pulso «acepto»--. Y dos finales NO son fallos: que ya hubiera devengo --uq_ledger_devengo funcionando-- y que la colaboracion sea un canje. Si los tres se escribieran igual, el log diria que algo fallo cada vez que alguien acepta un canje, y a la tercera nadie lo lee</t>
+          <t>BR-FIN-012 dice que el plazo son 30 dias desde la verificacion y que es visible desde que acepta: lo visible desde que acepta es el plazo, y una FECHA es otra cosa que se lee muy distinto. Mientras el asiento esta devengado se ensena que falta --las cinco condiciones de BR-FIN-003, con sus palabras--, que es accionable: un creador puede hacer algo con «no tienes ningun medio de pago verificado» y no puede hacer nada con una fecha que depende de trabajo que aun no ha hecho. Y si esa fecha se corriera, la culpa pareceria nuestra. La cuenta arranca en la ultima verificacion de sus publicaciones, y si no hay ninguna --un formato que no exige post-- en la fecha en que se completo la participacion</t>
         </is>
       </c>
     </row>
     <row r="78" ht="57" customHeight="1" s="36">
       <c r="A78" s="67" t="inlineStr">
         <is>
-          <t>DEC-169</t>
+          <t>DEC-172</t>
         </is>
       </c>
       <c r="B78" s="68" t="inlineStr">
@@ -17326,24 +17376,24 @@
       <c r="C78" s="68" t="n"/>
       <c r="D78" s="69" t="inlineStr">
         <is>
-          <t>El estado de un asiento tiene un grafo, y moverlo exige decir por que.</t>
+          <t>El motivo interno de una retencion NO se le ensena al creador.</t>
         </is>
       </c>
       <c r="E78" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="F78" s="69" t="inlineStr">
         <is>
-          <t>tg_ledger_no_update es columna por columna y deja pasar status a proposito --sin eso la tabla no serviria-- pero de ahi no salia QUE transicion es valida: un paid podia volver a accrued, o sea dinero ya pagado reapareciendo como deuda. Es tg_del_rondas de 8.4 otra vez. paid y void son terminales: un pago que se deshace se corrige con un asiento de payment_reversal, no cambiando este estado. Y toda transicion exige status_reason: sin ella, «.por que este creador no cobro?» se contesta mirando la fecha y adivinando. A la bitacora solo va lo que decide una persona --las automaticas son miles y taparian justo lo que se busca ahi--; el rastro completo vive en status_transitions. Ademas nace uq_ledger_devengo, vigesimosexta columna puerta: un devengo por participacion, que BR-FIN-015 daba por hecho sin decirlo</t>
+          <t>Lo escribe el equipo para el expediente y puede nombrar personas o sospechas todavia sin confirmar; un texto redactado deprisa --«parece que lo borro a proposito»-- leido sin contexto es una acusacion de la que no se vuelve. El creador ve «En revision -- te escribimos» y, desde 8.8, recibe un correo donde se le explica de verdad. Las palabras del portal tampoco son las del back-office: on_hold es «en revision» y no «retenido», porque la palabra interna describe lo que hace el sistema y la del portal tiene que describir lo que le pasa a el. La frontera vive en Ledger::misIngresos(), que enumera columnas --el mismo sitio que Aprobaciones::pieza() en 8.5--: devolver la fila entera y confiar en que la plantilla no imprima de mas es confiar en la plantilla de manana. Tampoco cruzan los asientos anulados: no le afectan y no sabe leerlos</t>
         </is>
       </c>
     </row>
     <row r="79" ht="57" customHeight="1" s="36">
       <c r="A79" s="67" t="inlineStr">
         <is>
-          <t>DEC-168</t>
+          <t>DEC-171</t>
         </is>
       </c>
       <c r="B79" s="68" t="inlineStr">
@@ -17354,24 +17404,24 @@
       <c r="C79" s="68" t="n"/>
       <c r="D79" s="69" t="inlineStr">
         <is>
-          <t>El asiento va en la moneda PACTADA; se convierte al pagar.</t>
+          <t>El barrido rescata las aceptaciones sin devengo, y avisa de que hubo que rescatarlas.</t>
         </is>
       </c>
       <c r="E79" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F79" s="69" t="inlineStr">
         <is>
-          <t>Se escribe con el agreed_amount y la moneda congelados al aceptar en 7.5: se le debe lo que se le prometio, en la moneda en que se le prometio. La conversion ocurre al armar el pago, con la tasa de ESE dia, y se congela en el asiento de pago (BR-FIN-009). Convertir al devengar habria dejado el saldo del creador en una sola moneda --mas facil de leer-- fijando el tipo de cambio meses antes de pagar: si el dolar sube, el creador cobra menos de lo pactado o nosotros pagamos mas, sin que nadie lo haya decidido</t>
+          <t>Un listener puede fallar, y si falla el creador queda aceptado y su dinero invisible; ademas las participaciones aceptadas antes de 9.4 nunca pasaron por el. ledger:revisar las anota antes de revisar --para que un devengo recuperado hoy pueda pasar a pagable hoy y no manana-- y lo dice en amarillo: que la lista no salga en cero es la noticia, no el arreglo. Es la misma red que 8.1 dejo para los entregables. Las gratuitas quedan fuera de esa lista a proposito: si no, el barrido intentaria lo imposible todos los dias y avisaria todos los dias de algo que esta bien</t>
         </is>
       </c>
     </row>
     <row r="80" ht="68.25" customHeight="1" s="36">
       <c r="A80" s="67" t="inlineStr">
         <is>
-          <t>DEC-167</t>
+          <t>DEC-170</t>
         </is>
       </c>
       <c r="B80" s="68" t="inlineStr">
@@ -17382,24 +17432,24 @@
       <c r="C80" s="68" t="n"/>
       <c r="D80" s="69" t="inlineStr">
         <is>
-          <t>Un post caido RETIENE el asiento; no lo anula.</t>
+          <t>Se devenga al ACEPTAR, no al terminar, y por evento.</t>
         </is>
       </c>
       <c r="E80" s="69" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F80" s="69" t="inlineStr">
         <is>
-          <t>8.8 ya lo decidio para el contenido --«el sistema no descuenta nada; la decision de que se le paga la toma una persona con el expediente montado»-- y aqui es lo mismo aplicado al dinero: on_hold saca el asiento de la cola de pago y espera. Reversible: si el creador repone el post, vuelve a payable. Anularlo con una reversion habria sido contablemente mas limpio y habria decidido por su cuenta que no se le paga, que es justo lo que DEC-145 prohibe. Y un asiento retenido no cuenta como saldo: meterlo seria prometerle al creador algo que todavia no esta decidido</t>
+          <t>Al aceptar es cuando existe la deuda: 7.5 congela el agreed_amount en ese instante y BR-CREATOR-008 impide cambiarlo despues sin una enmienda firmada por las dos partes. Que todavia no se le pueda pagar es otra cosa y vive en el estado --accrued significa exactamente «se le debe y aun no se le puede pagar»--. Devengar al terminar habria dejado el trabajo hecho y el compromiso invisible hasta el final, que es como una campana se cierra sin que nadie sepa cuanto costo mientras corria. Va por evento y no por llamada directa por lo mismo que 8.1: deptrac no deja que Campaign conozca a Finance, y esta bien que no lo haga --si anotar el asiento falla, la aceptacion sigue siendo cierta, y el creador ya pulso «acepto»--. Y dos finales NO son fallos: que ya hubiera devengo --uq_ledger_devengo funcionando-- y que la colaboracion sea un canje. Si los tres se escribieran igual, el log diria que algo fallo cada vez que alguien acepta un canje, y a la tercera nadie lo lee</t>
         </is>
       </c>
     </row>
     <row r="81" ht="68.25" customHeight="1" s="36">
       <c r="A81" s="67" t="inlineStr">
         <is>
-          <t>DEC-166</t>
+          <t>DEC-169</t>
         </is>
       </c>
       <c r="B81" s="68" t="inlineStr">
@@ -17410,7 +17460,7 @@
       <c r="C81" s="68" t="n"/>
       <c r="D81" s="69" t="inlineStr">
         <is>
-          <t>Pasar un devengo a pagable lo hace el SISTEMA, no una persona.</t>
+          <t>El estado de un asiento tiene un grafo, y moverlo exige decir por que.</t>
         </is>
       </c>
       <c r="E81" s="69" t="inlineStr">
@@ -17420,14 +17470,14 @@
       </c>
       <c r="F81" s="69" t="inlineStr">
         <is>
-          <t>BR-FIN-003 pide cinco cosas --participacion completada, contenido aprobado, publicacion verificada si aplica, documento tributario valido y medio de pago verificado-- y las cinco ya las firmo alguien una por una: quien verifico la publicacion, quien aprobo el perfil fiscal, quien verifico la cuenta. Una sexta firma que solo dice «si, se cumplen las cinco» es un boton que alguien acaba pulsando sin mirar, y una cola que retrasa pagos por acumulacion y no por duda. Ledger::requisitos() devuelve las cinco con su veredicto y no la primera que falla, porque quien mira por que un creador no cobra necesita la lista entera. El «si aplica» de la publicacion se implementa contando: si ningun entregable tiene publicacion el requisito se da por cumplido --un formato que no exige post no puede bloquear un pago para siempre--</t>
+          <t>tg_ledger_no_update es columna por columna y deja pasar status a proposito --sin eso la tabla no serviria-- pero de ahi no salia QUE transicion es valida: un paid podia volver a accrued, o sea dinero ya pagado reapareciendo como deuda. Es tg_del_rondas de 8.4 otra vez. paid y void son terminales: un pago que se deshace se corrige con un asiento de payment_reversal, no cambiando este estado. Y toda transicion exige status_reason: sin ella, «.por que este creador no cobro?» se contesta mirando la fecha y adivinando. A la bitacora solo va lo que decide una persona --las automaticas son miles y taparian justo lo que se busca ahi--; el rastro completo vive en status_transitions. Ademas nace uq_ledger_devengo, vigesimosexta columna puerta: un devengo por participacion, que BR-FIN-015 daba por hecho sin decirlo</t>
         </is>
       </c>
     </row>
     <row r="82" ht="45.75" customHeight="1" s="36">
       <c r="A82" s="67" t="inlineStr">
         <is>
-          <t>DEC-165</t>
+          <t>DEC-168</t>
         </is>
       </c>
       <c r="B82" s="68" t="inlineStr">
@@ -17438,24 +17488,24 @@
       <c r="C82" s="68" t="n"/>
       <c r="D82" s="69" t="inlineStr">
         <is>
-          <t>Decolecta trae USD → PEN y nada mas, y el sistema lo dice en vez de disimularlo.</t>
+          <t>El asiento va en la moneda PACTADA; se convierte al pagar.</t>
         </is>
       </c>
       <c r="E82" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F82" s="69" t="inlineStr">
         <is>
-          <t>Publica el tipo de cambio de SUNAT, y SUNAT solo publica el dolar. Por eso Decolecta no acepta un par como parametro --sabe traer lo unico que su fuente publica, y decirlo es mas honesto que aceptar COP y fallar raro--; el catalogo declara USD → PEN = sunat y ningun otro par, porque declarar una fuente que no publica es peor que no tener ninguna; la pantalla tiene carga manual con fuente manual y no disfrazada de sunat, que es lo que permite distinguir despues que se trajo y que se tecleo; y lo dice en la propia pantalla, para que «no llega la tasa del peso mexicano» no se diagnostique como un cron roto. Que fuente se usa para los demas pares queda como Q-64</t>
+          <t>Se escribe con el agreed_amount y la moneda congelados al aceptar en 7.5: se le debe lo que se le prometio, en la moneda en que se le prometio. La conversion ocurre al armar el pago, con la tasa de ESE dia, y se congela en el asiento de pago (BR-FIN-009). Convertir al devengar habria dejado el saldo del creador en una sola moneda --mas facil de leer-- fijando el tipo de cambio meses antes de pagar: si el dolar sube, el creador cobra menos de lo pactado o nosotros pagamos mas, sin que nadie lo haya decidido</t>
         </is>
       </c>
     </row>
     <row r="83" ht="68.25" customHeight="1" s="36">
       <c r="A83" s="67" t="inlineStr">
         <is>
-          <t>DEC-164</t>
+          <t>DEC-167</t>
         </is>
       </c>
       <c r="B83" s="68" t="inlineStr">
@@ -17466,24 +17516,24 @@
       <c r="C83" s="68" t="n"/>
       <c r="D83" s="69" t="inlineStr">
         <is>
-          <t>El cron deja rastro de cada intento, y pide TRES dias.</t>
+          <t>Un post caido RETIENE el asiento; no lo anula.</t>
         </is>
       </c>
       <c r="E83" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F83" s="69" t="inlineStr">
         <is>
-          <t>fx_fetch_runs. Cambio::DIAS_ATRAS detecta que las tasas dejaron de llegar cuando alguien va a convertir, o sea el dia de la liquidacion; esto lo ensena antes, y la pantalla lo resume arriba solo si hay algo que mirar --una pantalla que siempre tiene un aviso es una pantalla cuyos avisos nadie lee--. ck_ffr_nuevas obliga a que una corrida fallida diga cero, porque el registro que contesta «.sigue vivo el cron?» no puede afirmar que una corrida con error trajo tres tasas. Tres dias y no uno: si no corrio viernes ni sabado, pedir solo el domingo deja dos huecos que nadie rellena a mano, y repetir un dia no cuesta una fila --uq_fx_rate-- sino una peticion. Y termina en 0 aunque un dia falle: un cron que da error a diario hace ruido donde nadie mira; solo falla si NINGUN dia se pudo traer</t>
+          <t>8.8 ya lo decidio para el contenido --«el sistema no descuenta nada; la decision de que se le paga la toma una persona con el expediente montado»-- y aqui es lo mismo aplicado al dinero: on_hold saca el asiento de la cola de pago y espera. Reversible: si el creador repone el post, vuelve a payable. Anularlo con una reversion habria sido contablemente mas limpio y habria decidido por su cuenta que no se le paga, que es justo lo que DEC-145 prohibe. Y un asiento retenido no cuenta como saldo: meterlo seria prometerle al creador algo que todavia no esta decidido</t>
         </is>
       </c>
     </row>
     <row r="84" ht="57" customHeight="1" s="36">
       <c r="A84" s="67" t="inlineStr">
         <is>
-          <t>DEC-163</t>
+          <t>DEC-166</t>
         </is>
       </c>
       <c r="B84" s="68" t="inlineStr">
@@ -17494,24 +17544,24 @@
       <c r="C84" s="68" t="n"/>
       <c r="D84" s="69" t="inlineStr">
         <is>
-          <t>Cada final de la traida tiene su nombre, y traer() no lanza.</t>
+          <t>Pasar un devengo a pagable lo hace el SISTEMA, no una persona.</t>
         </is>
       </c>
       <c r="E84" s="69" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F84" s="69" t="inlineStr">
         <is>
-          <t>ok, sin_credencial, error_http, error_red, respuesta_rara. En un catch generico los cinco se ven iguales y exigen cinco arreglos distintos: «no hay clave» se arregla configurandola, «401» rotandola, «200 con un cuerpo raro» mirando la API. Un 404 --dia sin publicar-- ni siquiera se pinta como averia: quien lee la salida del cron todos los dias deja de leerla si le grita por lo normal. Y una respuesta que no se entiende no anota nada: una tasa inventada entraria en una tabla que tg_fx_inmutable no deja corregir</t>
+          <t>BR-FIN-003 pide cinco cosas --participacion completada, contenido aprobado, publicacion verificada si aplica, documento tributario valido y medio de pago verificado-- y las cinco ya las firmo alguien una por una: quien verifico la publicacion, quien aprobo el perfil fiscal, quien verifico la cuenta. Una sexta firma que solo dice «si, se cumplen las cinco» es un boton que alguien acaba pulsando sin mirar, y una cola que retrasa pagos por acumulacion y no por duda. Ledger::requisitos() devuelve las cinco con su veredicto y no la primera que falla, porque quien mira por que un creador no cobra necesita la lista entera. El «si aplica» de la publicacion se implementa contando: si ningun entregable tiene publicacion el requisito se da por cumplido --un formato que no exige post no puede bloquear un pago para siempre--</t>
         </is>
       </c>
     </row>
     <row r="85" ht="57" customHeight="1" s="36">
       <c r="A85" s="67" t="inlineStr">
         <is>
-          <t>DEC-162</t>
+          <t>DEC-165</t>
         </is>
       </c>
       <c r="B85" s="68" t="inlineStr">
@@ -17522,7 +17572,7 @@
       <c r="C85" s="68" t="n"/>
       <c r="D85" s="69" t="inlineStr">
         <is>
-          <t>La credencial se configura desde la pantalla, pero el ENTORNO manda y en la base va CIFRADA.</t>
+          <t>Decolecta trae USD → PEN y nada mas, y el sistema lo dice en vez de disimularlo.</t>
         </is>
       </c>
       <c r="E85" s="69" t="inlineStr">
@@ -17532,14 +17582,14 @@
       </c>
       <c r="F85" s="69" t="inlineStr">
         <is>
-          <t>La peticion era «la configurare en la pantalla del admin». Se hace, con dos condiciones que salen de la regla de seguridad del propio proyecto --«no almacenar secretos en texto plano en BD cuando exista alternativa segura»--: si hay DECOLECTA_API_KEY en el entorno se usa esa y la de la base ni se mira --no viaja por el navegador, no esta en ninguna tabla, no sale en un volcado--; y si no la hay, se guarda con Crypt, la misma maquina que cifra las cuentas bancarias desde 3.8. La clave no se reensena jamas, ni al que la escribio un minuto antes: la pantalla dice «termina en 8f2a» y de donde sale. La bitacora anota que cambio y los cuatro ultimos, nunca el valor. Y tg_fxs_credencial_firmada exige quien la puso, cuando y la pista, las tres o ninguna: media firma es peor que ninguna porque parece que «quien la puso» tiene respuesta. El permiso va aparte: la pantalla es fx.manage --la tiene finanzas-- y la credencial es integration.manage --solo admin--, porque una clave de un tercero es un permiso de gasto y no la necesita quien anota una tasa un lunes</t>
+          <t>Publica el tipo de cambio de SUNAT, y SUNAT solo publica el dolar. Por eso Decolecta no acepta un par como parametro --sabe traer lo unico que su fuente publica, y decirlo es mas honesto que aceptar COP y fallar raro--; el catalogo declara USD → PEN = sunat y ningun otro par, porque declarar una fuente que no publica es peor que no tener ninguna; la pantalla tiene carga manual con fuente manual y no disfrazada de sunat, que es lo que permite distinguir despues que se trajo y que se tecleo; y lo dice en la propia pantalla, para que «no llega la tasa del peso mexicano» no se diagnostique como un cron roto. Que fuente se usa para los demas pares queda como Q-64</t>
         </is>
       </c>
     </row>
     <row r="86" ht="57" customHeight="1" s="36">
       <c r="A86" s="67" t="inlineStr">
         <is>
-          <t>DEC-161</t>
+          <t>DEC-164</t>
         </is>
       </c>
       <c r="B86" s="68" t="inlineStr">
@@ -17550,24 +17600,24 @@
       <c r="C86" s="68" t="n"/>
       <c r="D86" s="69" t="inlineStr">
         <is>
-          <t>porque() admite alternancia, y eso es lo que faltaba para bajar el trinquete de las 297.</t>
+          <t>El cron deja rastro de cada intento, y pide TRES dias.</t>
         </is>
       </c>
       <c r="E86" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F86" s="69" t="inlineStr">
         <is>
-          <t>Los dos motores contestan cosas distintas a la MISMA regla cuando la creo Restriccion: MariaDB dice «CONSTRAINT ck_fos_dates failed» y Percona dice el mensaje. El nombre sale en uno y el mensaje en el otro, y no coinciden en ningun texto, asi que toda regla de Restriccion tenia que quedarse en un probar ... RECHAZO a secas. Con grep -qE, porque ... 'ck_fos_dates|antes de empezar' afirma el motivo en los dos motores. DEC-154 puso el trinquete y conto 297; esto es la herramienta para bajarlo</t>
+          <t>fx_fetch_runs. Cambio::DIAS_ATRAS detecta que las tasas dejaron de llegar cuando alguien va a convertir, o sea el dia de la liquidacion; esto lo ensena antes, y la pantalla lo resume arriba solo si hay algo que mirar --una pantalla que siempre tiene un aviso es una pantalla cuyos avisos nadie lee--. ck_ffr_nuevas obliga a que una corrida fallida diga cero, porque el registro que contesta «.sigue vivo el cron?» no puede afirmar que una corrida con error trajo tres tasas. Tres dias y no uno: si no corrio viernes ni sabado, pedir solo el domingo deja dos huecos que nadie rellena a mano, y repetir un dia no cuesta una fila --uq_fx_rate-- sino una peticion. Y termina en 0 aunque un dia falle: un cron que da error a diario hace ruido donde nadie mira; solo falla si NINGUN dia se pudo traer</t>
         </is>
       </c>
     </row>
     <row r="87" ht="68.25" customHeight="1" s="36">
       <c r="A87" s="67" t="inlineStr">
         <is>
-          <t>DEC-160</t>
+          <t>DEC-163</t>
         </is>
       </c>
       <c r="B87" s="68" t="inlineStr">
@@ -17578,24 +17628,24 @@
       <c r="C87" s="68" t="n"/>
       <c r="D87" s="69" t="inlineStr">
         <is>
-          <t>Un dia sin tasa usa la ultima anterior, y lo que se guarda es la fecha de ESA tasa.</t>
+          <t>Cada final de la traida tiene su nombre, y traer() no lanza.</t>
         </is>
       </c>
       <c r="E87" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F87" s="69" t="inlineStr">
         <is>
-          <t>Sabados, domingos y feriados no tienen tipo publicado. Se convierte con la del viernes y el asiento dice «tasa del viernes», no «tasa del domingo»: guardar la fecha de la operacion habria sido mas comodo de leer y habria hecho que el historico afirmara que ese domingo hubo una tasa que nunca existio (BR-FIN-009). Es un supuesto fiscal y esta marcado como tal (§56): que la practica peruana sea el ultimo tipo publicado lo confirma el contador. Y hay un corte de 10 dias, porque «la ultima anterior» tapa una averia: si lo ultimo es de hace tres semanas no fue un feriado, es que el cron dejo de traerlas, y sin ese corte una tabla congelada se ve igual que una sana hasta el dia de la liquidacion</t>
+          <t>ok, sin_credencial, error_http, error_red, respuesta_rara. En un catch generico los cinco se ven iguales y exigen cinco arreglos distintos: «no hay clave» se arregla configurandola, «401» rotandola, «200 con un cuerpo raro» mirando la API. Un 404 --dia sin publicar-- ni siquiera se pinta como averia: quien lee la salida del cron todos los dias deja de leerla si le grita por lo normal. Y una respuesta que no se entiende no anota nada: una tasa inventada entraria en una tabla que tg_fx_inmutable no deja corregir</t>
         </is>
       </c>
     </row>
     <row r="88" ht="34.5" customHeight="1" s="36">
       <c r="A88" s="67" t="inlineStr">
         <is>
-          <t>DEC-159</t>
+          <t>DEC-162</t>
         </is>
       </c>
       <c r="B88" s="68" t="inlineStr">
@@ -17606,24 +17656,24 @@
       <c r="C88" s="68" t="n"/>
       <c r="D88" s="69" t="inlineStr">
         <is>
-          <t>Compra y venta son dos filas, y cual aplica NO tiene valor por defecto.</t>
+          <t>La credencial se configura desde la pantalla, pero el ENTORNO manda y en la base va CIFRADA.</t>
         </is>
       </c>
       <c r="E88" s="69" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F88" s="69" t="inlineStr">
         <is>
-          <t>SUNAT publica las dos el mismo dia y no son intercambiables. Con una sola columna rate solo cabe una, y elegir cual guardar habria sido tomar por mi cuenta una decision contable en el sitio donde menos se ve. side entra en la clave, asi que las dos caben sin pisarse. Y Cambio::tasa() exige el lado como parametro sin defecto: un defecto aqui es exactamente la forma en que una decision fiscal se toma sola. Queda Q-63 para el contador, y por eso el buscador de creadores sigue sin convertir aunque la maquina ya exista</t>
+          <t>La peticion era «la configurare en la pantalla del admin». Se hace, con dos condiciones que salen de la regla de seguridad del propio proyecto --«no almacenar secretos en texto plano en BD cuando exista alternativa segura»--: si hay DECOLECTA_API_KEY en el entorno se usa esa y la de la base ni se mira --no viaja por el navegador, no esta en ninguna tabla, no sale en un volcado--; y si no la hay, se guarda con Crypt, la misma maquina que cifra las cuentas bancarias desde 3.8. La clave no se reensena jamas, ni al que la escribio un minuto antes: la pantalla dice «termina en 8f2a» y de donde sale. La bitacora anota que cambio y los cuatro ultimos, nunca el valor. Y tg_fxs_credencial_firmada exige quien la puso, cuando y la pista, las tres o ninguna: media firma es peor que ninguna porque parece que «quien la puso» tiene respuesta. El permiso va aparte: la pantalla es fx.manage --la tiene finanzas-- y la credencial es integration.manage --solo admin--, porque una clave de un tercero es un permiso de gasto y no la necesita quien anota una tasa un lunes</t>
         </is>
       </c>
     </row>
     <row r="89" ht="57" customHeight="1" s="36">
       <c r="A89" s="67" t="inlineStr">
         <is>
-          <t>DEC-158</t>
+          <t>DEC-161</t>
         </is>
       </c>
       <c r="B89" s="68" t="inlineStr">
@@ -17634,7 +17684,7 @@
       <c r="C89" s="68" t="n"/>
       <c r="D89" s="69" t="inlineStr">
         <is>
-          <t>Que fuente publica el tipo de cambio se DECLARA, con periodos, y no se elige al convertir.</t>
+          <t>porque() admite alternancia, y eso es lo que faltaba para bajar el trinquete de las 297.</t>
         </is>
       </c>
       <c r="E89" s="69" t="inlineStr">
@@ -17644,14 +17694,14 @@
       </c>
       <c r="F89" s="69" t="inlineStr">
         <is>
-          <t>uq_exchange_rates incluia source a proposito --dos fuentes pueden discrepar el mismo dia y BR-FIN-009 exige poder decir de cual salio la que se aplico-- pero de ahi no salia CUAL SE APLICA. Es el estado EMPATE de CoberturaFacturacion, el que una vez produjo una factura emitida por la sociedad equivocada, y la respuesta es la misma que entonces: uq_fos_current garantiza una sola fuente VIGENTE por par, y fos_sin_solape una sola POR FECHA --que es la mitad que se olvida, porque convertir un importe de marzo resuelve por par Y por fecha--. Con periodos y no con una columna porque el historico tiene que seguir explicandose con quien mandaba entonces: si fuera una columna, cambiar de proveedor reescribiria como se convirtio todo lo anterior</t>
+          <t>Los dos motores contestan cosas distintas a la MISMA regla cuando la creo Restriccion: MariaDB dice «CONSTRAINT ck_fos_dates failed» y Percona dice el mensaje. El nombre sale en uno y el mensaje en el otro, y no coinciden en ningun texto, asi que toda regla de Restriccion tenia que quedarse en un probar ... RECHAZO a secas. Con grep -qE, porque ... 'ck_fos_dates|antes de empezar' afirma el motivo en los dos motores. DEC-154 puso el trinquete y conto 297; esto es la herramienta para bajarlo</t>
         </is>
       </c>
     </row>
     <row r="90" ht="45.75" customHeight="1" s="36">
       <c r="A90" s="67" t="inlineStr">
         <is>
-          <t>DEC-157</t>
+          <t>DEC-160</t>
         </is>
       </c>
       <c r="B90" s="68" t="inlineStr">
@@ -17662,24 +17712,24 @@
       <c r="C90" s="68" t="n"/>
       <c r="D90" s="69" t="inlineStr">
         <is>
-          <t>BR-LE-009 se comprueba cuando se escribe el primer pago, no en la iteracion 9.11.</t>
+          <t>Un dia sin tasa usa la ultima anterior, y lo que se guarda es la fecha de ESA tasa.</t>
         </is>
       </c>
       <c r="E90" s="69" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F90" s="69" t="inlineStr">
         <is>
-          <t>El roadmap tenia la validacion de «la sociedad que factura y la que liquida son la misma» como iteracion 11 de 14 de la fase de finanzas. Una regla 🔴 que llega la penultima llega despues de que diez iteraciones se hayan construido dandola por buena, y es exactamente la forma de fallo de 8.4: el techo de rondas existia entero en PHP desde 8.3 y nada lo respaldaba en la base. Aqui es peor, porque lo que se cuela no es una ronda: es dinero saliendo de la sociedad equivocada, que es una operacion intercompania no documentada. Pasa a ser requisito de la iteracion que estrene payout_batches, y en la base: un lote nombra su sociedad y sus asientos nombran sus campanas, asi que la comprobacion es cross-table y le toca a un disparador, no a un CHECK. Y con esto DEC-020 deja de ser PROPUESTA: preguntaba si permitir que la entidad que factura y la que liquida divergieran, y recomendaba modelar la separacion y bloquearla en el MVP. DEC-156 lo contesta y ademas le quita el «en el MVP»</t>
+          <t>Sabados, domingos y feriados no tienen tipo publicado. Se convierte con la del viernes y el asiento dice «tasa del viernes», no «tasa del domingo»: guardar la fecha de la operacion habria sido mas comodo de leer y habria hecho que el historico afirmara que ese domingo hubo una tasa que nunca existio (BR-FIN-009). Es un supuesto fiscal y esta marcado como tal (§56): que la practica peruana sea el ultimo tipo publicado lo confirma el contador. Y hay un corte de 10 dias, porque «la ultima anterior» tapa una averia: si lo ultimo es de hace tres semanas no fue un feriado, es que el cron dejo de traerlas, y sin ese corte una tabla congelada se ve igual que una sana hasta el dia de la liquidacion</t>
         </is>
       </c>
     </row>
     <row r="91" ht="45.75" customHeight="1" s="36">
       <c r="A91" s="67" t="inlineStr">
         <is>
-          <t>DEC-156</t>
+          <t>DEC-159</t>
         </is>
       </c>
       <c r="B91" s="68" t="inlineStr">
@@ -17690,24 +17740,24 @@
       <c r="C91" s="68" t="n"/>
       <c r="D91" s="69" t="inlineStr">
         <is>
-          <t>La campana decide quien paga a cada creador, y el pais del creador no entra en esa decision.</t>
+          <t>Compra y venta son dos filas, y cual aplica NO tiene valor por defecto.</t>
         </is>
       </c>
       <c r="E91" s="69" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F91" s="69" t="inlineStr">
         <is>
-          <t>Un creador colombiano en una campana de CTS Peru cobra de CTS Peru. La sociedad sale del pais del CLIENTE, se guarda en la campana y el pago la hereda de ahi, congelada al confirmar igual que agreed_amount; lo implementa F9. [Corregido el 2026-08-27, T-59: la version original de esta entrada decia que «payouts no tiene ninguna columna de sociedad» y eso es falso. payout_batches.legal_entity_id existe desde la migracion de finanzas y el pago la hereda de su lote. Lo que NO existe es la garantia de que sea la correcta: nada ata el lote a las campanas cuyos asientos liquida, asi que hoy un lote de CTS Colombia podria pagar el trabajo de una campana de CTS Peru y ninguna restriccion lo notaria.] Esto no inventa la regla: BR-LE-009 ya la decia, con «en el MVP» delante y en naranja. Se le quita el «en el MVP» y sube a 🔴, porque no es una simplificacion temporal sino como funciona el grupo. La alternativa --que pagara la sociedad del pais del creador-- parte una campana en dos contabilidades, obliga a que el margen de una campana se calcule entre sociedades y exige cobertura en el pais de cada creador antes de poder invitarlo: hoy Espana no tiene sociedad y con esa alternativa un creador espanol seria ininvitable. Y cambia el eje de Q-40: la retencion depende de quien paga Y de donde esta el creador, no solo de lo segundo, asi que la tabla del contador pasa a ser «CTS Peru pagando a un creador de cada pais» y CTS Colombia tiene la suya, para un contador colombiano</t>
+          <t>SUNAT publica las dos el mismo dia y no son intercambiables. Con una sola columna rate solo cabe una, y elegir cual guardar habria sido tomar por mi cuenta una decision contable en el sitio donde menos se ve. side entra en la clave, asi que las dos caben sin pisarse. Y Cambio::tasa() exige el lado como parametro sin defecto: un defecto aqui es exactamente la forma en que una decision fiscal se toma sola. Queda Q-63 para el contador, y por eso el buscador de creadores sigue sin convertir aunque la maquina ya exista</t>
         </is>
       </c>
     </row>
     <row r="92" ht="34.5" customHeight="1" s="36">
       <c r="A92" s="67" t="inlineStr">
         <is>
-          <t>DEC-155</t>
+          <t>DEC-158</t>
         </is>
       </c>
       <c r="B92" s="68" t="inlineStr">
@@ -17718,24 +17768,24 @@
       <c r="C92" s="68" t="n"/>
       <c r="D92" s="69" t="inlineStr">
         <is>
-          <t>La sociedad que factura NO se elige: se resuelve, y la pantalla enseña por que.</t>
+          <t>Que fuente publica el tipo de cambio se DECLARA, con periodos, y no se elige al convertir.</t>
         </is>
       </c>
       <c r="E92" s="69" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F92" s="69" t="inlineStr">
         <is>
-          <t>El planteamiento era poner un desplegable «CTS Peru / CTS Colombia» en la campana. No se hace, y el motivo esta en el esquema: uq_lec_country mas tg_lec_sin_solape_ins/upd garantizan que en cualquier fecha hay como mucho una sociedad cubriendo un pais, asi que el desplegable tendria siempre una opcion --y una opcion que se puede cambiar es una que alguien puede cambiar mal--. Ya existia campaigns.billing_legal_entity_id, resuelto a starts_on por Campanas::quienFactura() y congelado al confirmar por tg_camp_entidad_congelada. Lo que faltaba no era el campo: era decirlo. La ficha ahora dice quien factura Y su motivo --«CTS Peru factura a Peru desde el 2025-01-01 (sociedad local)»--, porque una sociedad a secas no se puede comprobar y con su motivo y su fecha quien la lee sabe si es la que esperaba y puede discutirla antes de que salga una factura. El formulario de alta no adelanta una respuesta: el pais del cliente y la fecha todavia no existen, y resolver «con la cobertura de hoy» para ensenarlo es justo el «deducirlo de la configuracion vigente» que prohibe BR-LE-001</t>
+          <t>uq_exchange_rates incluia source a proposito --dos fuentes pueden discrepar el mismo dia y BR-FIN-009 exige poder decir de cual salio la que se aplico-- pero de ahi no salia CUAL SE APLICA. Es el estado EMPATE de CoberturaFacturacion, el que una vez produjo una factura emitida por la sociedad equivocada, y la respuesta es la misma que entonces: uq_fos_current garantiza una sola fuente VIGENTE por par, y fos_sin_solape una sola POR FECHA --que es la mitad que se olvida, porque convertir un importe de marzo resuelve por par Y por fecha--. Con periodos y no con una columna porque el historico tiene que seguir explicandose con quien mandaba entonces: si fuera una columna, cambiar de proveedor reescribiria como se convirtio todo lo anterior</t>
         </is>
       </c>
     </row>
     <row r="93" ht="45.75" customHeight="1" s="36">
       <c r="A93" s="67" t="inlineStr">
         <is>
-          <t>DEC-154</t>
+          <t>DEC-157</t>
         </is>
       </c>
       <c r="B93" s="68" t="inlineStr">
@@ -17746,24 +17796,24 @@
       <c r="C93" s="68" t="n"/>
       <c r="D93" s="69" t="inlineStr">
         <is>
-          <t>Los ayudantes de las suites viven en UN archivo, y nace la SEPTIMA puerta.</t>
+          <t>BR-LE-009 se comprueba cuando se escribe el primer pago, no en la iteracion 9.11.</t>
         </is>
       </c>
       <c r="E93" s="69" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="F93" s="69" t="inlineStr">
         <is>
-          <t>tools/pruebas/comun.sh y tools/verificar-suites.py. La puerta comprueba que toda suite listada existe, que ninguna define sus propios probar/valor/porque, que todas cargan comun.sh, y lleva un trinquete: cuantas aserciones negativas afirman POR QUE se rechaza y cuantas solo que algo fallo. Hoy son 89 con motivo y 297 sin el, y ese segundo numero solo puede bajar (tools/pruebas/MOTIVOS-BASE). No se convierten las 297 en esta iteracion --son veintidos suites de cuatro fases-- pero desde hoy no pueden ser 298, y ademas cada probar ... RECHAZO enseña en gris que restriccion respondio